--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="154">
   <si>
     <t>PICK</t>
   </si>
@@ -92,34 +92,37 @@
     <t>Ed</t>
   </si>
   <si>
+    <t>Makayla</t>
+  </si>
+  <si>
     <t>Blaine</t>
+  </si>
+  <si>
+    <t>Brent</t>
   </si>
   <si>
     <t>Jason</t>
   </si>
   <si>
-    <t>Brent</t>
+    <t>Collin</t>
   </si>
   <si>
     <t>Joey</t>
   </si>
   <si>
-    <t>Ty</t>
+    <t>Eric</t>
   </si>
   <si>
     <t>MaKayla</t>
   </si>
   <si>
-    <t>Eric</t>
-  </si>
-  <si>
-    <t>Roy</t>
+    <t>Ty</t>
   </si>
   <si>
     <t>Kich</t>
   </si>
   <si>
-    <t>Collin</t>
+    <t>Roy</t>
   </si>
   <si>
     <t>Joel</t>
@@ -134,6 +137,9 @@
     <t>Auction$</t>
   </si>
   <si>
+    <t>Composite</t>
+  </si>
+  <si>
     <t>Rank</t>
   </si>
   <si>
@@ -141,9 +147,6 @@
   </si>
   <si>
     <t>Pos</t>
-  </si>
-  <si>
-    <t>Composite</t>
   </si>
   <si>
     <t>Jeremiyah Love</t>
@@ -569,14 +572,14 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -3084,17 +3087,17 @@
       </c>
       <c r="U30" s="7"/>
       <c r="V30" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="W30" s="13" t="s">
+        <v>3.0</v>
+      </c>
+      <c r="W30" s="12" t="s">
         <v>26</v>
       </c>
       <c r="X30" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Y30" s="7" t="str">
-        <f t="shared" ref="Y30:Y79" si="17">TEXT(V30,"0")&amp;"|"&amp;TRIM(W30)</f>
-        <v>1|Blaine</v>
+        <f t="shared" ref="Y30:Y81" si="17">TEXT(V30,"0")&amp;"|"&amp;TRIM(W30)</f>
+        <v>3|Makayla</v>
       </c>
       <c r="Z30" s="7"/>
       <c r="AA30" s="7"/>
@@ -3164,18 +3167,18 @@
         <v>Brent</v>
       </c>
       <c r="U31" s="7"/>
-      <c r="V31" s="12">
-        <v>1.0</v>
+      <c r="V31" s="14">
+        <v>2.0</v>
       </c>
       <c r="W31" s="13" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="X31" s="13" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="Y31" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1|Ed</v>
+        <v>2|Jason</v>
       </c>
       <c r="Z31" s="7"/>
       <c r="AA31" s="7"/>
@@ -3233,7 +3236,7 @@
         <v>3.0</v>
       </c>
       <c r="P32" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Q32" s="7"/>
       <c r="R32" s="4">
@@ -3245,18 +3248,18 @@
         <v>Joey</v>
       </c>
       <c r="U32" s="7"/>
-      <c r="V32" s="12">
-        <v>1.0</v>
+      <c r="V32" s="14">
+        <v>2.0</v>
       </c>
       <c r="W32" s="13" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="X32" s="13" t="s">
         <v>30</v>
       </c>
       <c r="Y32" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1|Brent</v>
+        <v>2|Eric</v>
       </c>
       <c r="Z32" s="7"/>
       <c r="AA32" s="7"/>
@@ -3314,7 +3317,7 @@
         <v>4.0</v>
       </c>
       <c r="P33" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q33" s="7"/>
       <c r="R33" s="4">
@@ -3326,18 +3329,18 @@
         <v>MaKayla</v>
       </c>
       <c r="U33" s="7"/>
-      <c r="V33" s="12">
-        <v>1.0</v>
+      <c r="V33" s="14">
+        <v>2.0</v>
       </c>
       <c r="W33" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="X33" s="13" t="s">
         <v>30</v>
-      </c>
-      <c r="X33" s="13" t="s">
-        <v>31</v>
       </c>
       <c r="Y33" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1|Ty</v>
+        <v>2|Ed</v>
       </c>
       <c r="Z33" s="7"/>
       <c r="AA33" s="7"/>
@@ -3395,7 +3398,7 @@
         <v>5.0</v>
       </c>
       <c r="P34" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Q34" s="7"/>
       <c r="R34" s="4">
@@ -3407,18 +3410,18 @@
         <v>Ty</v>
       </c>
       <c r="U34" s="7"/>
-      <c r="V34" s="13">
-        <v>1.0</v>
+      <c r="V34" s="14">
+        <v>4.0</v>
       </c>
       <c r="W34" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="X34" s="13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Y34" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1|Eric</v>
+        <v>4|Joey</v>
       </c>
       <c r="Z34" s="7"/>
       <c r="AA34" s="7"/>
@@ -3476,7 +3479,7 @@
         <v>6.0</v>
       </c>
       <c r="P35" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q35" s="7"/>
       <c r="R35" s="4">
@@ -3489,17 +3492,17 @@
       </c>
       <c r="U35" s="7"/>
       <c r="V35" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="W35" s="14" t="s">
+        <v>5.0</v>
+      </c>
+      <c r="W35" s="13" t="s">
         <v>31</v>
       </c>
       <c r="X35" s="13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Y35" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1|MaKayla</v>
+        <v>5|Joey</v>
       </c>
       <c r="Z35" s="7"/>
       <c r="AA35" s="7"/>
@@ -3570,17 +3573,17 @@
       </c>
       <c r="U36" s="7"/>
       <c r="V36" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="W36" s="14" t="s">
-        <v>33</v>
+        <v>5.0</v>
+      </c>
+      <c r="W36" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="X36" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y36" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1|Roy</v>
+        <v>5|Brent</v>
       </c>
       <c r="Z36" s="7"/>
       <c r="AA36" s="7"/>
@@ -3638,7 +3641,7 @@
         <v>8.0</v>
       </c>
       <c r="P37" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="Q37" s="7"/>
       <c r="R37" s="4">
@@ -3650,18 +3653,18 @@
         <v>Collin</v>
       </c>
       <c r="U37" s="7"/>
-      <c r="V37" s="12">
-        <v>2.0</v>
+      <c r="V37" s="14">
+        <v>6.0</v>
       </c>
       <c r="W37" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="X37" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y37" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>2|Blaine</v>
+        <v>6|Brent</v>
       </c>
       <c r="Z37" s="7"/>
       <c r="AA37" s="7"/>
@@ -3719,7 +3722,7 @@
         <v>9.0</v>
       </c>
       <c r="P38" s="5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q38" s="7"/>
       <c r="R38" s="4">
@@ -3731,18 +3734,18 @@
         <v>Roy</v>
       </c>
       <c r="U38" s="7"/>
-      <c r="V38" s="12">
-        <v>2.0</v>
+      <c r="V38" s="14">
+        <v>1.0</v>
       </c>
       <c r="W38" s="13" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="X38" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y38" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>2|Roy</v>
+        <v>1|Blaine</v>
       </c>
       <c r="Z38" s="7"/>
       <c r="AA38" s="7"/>
@@ -3800,7 +3803,7 @@
         <v>10.0</v>
       </c>
       <c r="P39" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Q39" s="7"/>
       <c r="R39" s="4">
@@ -3812,18 +3815,18 @@
         <v>Jason</v>
       </c>
       <c r="U39" s="7"/>
-      <c r="V39" s="12">
-        <v>2.0</v>
+      <c r="V39" s="14">
+        <v>1.0</v>
       </c>
       <c r="W39" s="13" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="X39" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y39" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>2|Collin</v>
+        <v>1|Ed</v>
       </c>
       <c r="Z39" s="7"/>
       <c r="AA39" s="7"/>
@@ -3881,7 +3884,7 @@
         <v>11.0</v>
       </c>
       <c r="P40" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q40" s="7"/>
       <c r="R40" s="4">
@@ -3893,18 +3896,18 @@
         <v>Blaine</v>
       </c>
       <c r="U40" s="7"/>
-      <c r="V40" s="12">
+      <c r="V40" s="14">
         <v>2.0</v>
       </c>
       <c r="W40" s="13" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="X40" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y40" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>2|Kich</v>
+        <v>2|Blaine</v>
       </c>
       <c r="Z40" s="7"/>
       <c r="AA40" s="7"/>
@@ -3962,7 +3965,7 @@
         <v>12.0</v>
       </c>
       <c r="P41" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q41" s="7"/>
       <c r="R41" s="4">
@@ -3974,18 +3977,18 @@
         <v>Joel</v>
       </c>
       <c r="U41" s="7"/>
-      <c r="V41" s="12">
+      <c r="V41" s="14">
         <v>2.0</v>
       </c>
       <c r="W41" s="13" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="X41" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y41" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>2|Ty</v>
+        <v>2|Roy</v>
       </c>
       <c r="Z41" s="7"/>
       <c r="AA41" s="7"/>
@@ -4046,18 +4049,18 @@
       <c r="S42" s="7"/>
       <c r="T42" s="7"/>
       <c r="U42" s="7"/>
-      <c r="V42" s="12">
+      <c r="V42" s="14">
         <v>2.0</v>
       </c>
       <c r="W42" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="X42" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="X42" s="13" t="s">
-        <v>27</v>
       </c>
       <c r="Y42" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>2|Joey</v>
+        <v>2|Collin</v>
       </c>
       <c r="Z42" s="7"/>
       <c r="AA42" s="7"/>
@@ -4118,18 +4121,18 @@
       <c r="S43" s="7"/>
       <c r="T43" s="7"/>
       <c r="U43" s="7"/>
-      <c r="V43" s="12">
+      <c r="V43" s="14">
         <v>2.0</v>
       </c>
       <c r="W43" s="13" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="X43" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y43" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>2|Brent</v>
+        <v>2|Kich</v>
       </c>
       <c r="Z43" s="7"/>
       <c r="AA43" s="7"/>
@@ -4190,7 +4193,7 @@
         <v>9</v>
       </c>
       <c r="Q44" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R44" s="5" t="s">
         <v>17</v>
@@ -4198,18 +4201,18 @@
       <c r="S44" s="7"/>
       <c r="T44" s="7"/>
       <c r="U44" s="7"/>
-      <c r="V44" s="12">
+      <c r="V44" s="14">
         <v>2.0</v>
       </c>
       <c r="W44" s="13" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="X44" s="13" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="Y44" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>2|Jason</v>
+        <v>2|Ty</v>
       </c>
       <c r="Z44" s="7"/>
       <c r="AA44" s="7"/>
@@ -4285,10 +4288,10 @@
   INDEX($S$30:$S$41, MATCH(P45,$R$30:$R$41,0))&lt;&gt;"",
   INDEX($T$30:$T$41, MATCH(P45,$R$30:$R$41,0)),
   IFERROR(
-    INDEX($X$30:$X$200,
+    INDEX($X$30:$X$202,
           MATCH(
             TEXT(O45,"0")&amp;"|"&amp;TRIM(INDEX($P$30:$P$41, MATCH(13-P45,$O$30:$O$41,0))),
-            $Y$30:$Y$200, 0)),
+            $Y$30:$Y$202, 0)),
     INDEX($P$30:$P$41, MATCH(13-P45,$O$30:$O$41,0))
   )
 )
@@ -4298,18 +4301,18 @@
       <c r="S45" s="7"/>
       <c r="T45" s="7"/>
       <c r="U45" s="7"/>
-      <c r="V45" s="12">
+      <c r="V45" s="14">
         <v>2.0</v>
       </c>
       <c r="W45" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="X45" s="13" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="Y45" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>2|Eric</v>
+        <v>2|Joey</v>
       </c>
       <c r="Z45" s="7"/>
       <c r="AA45" s="7"/>
@@ -4382,18 +4385,18 @@
       <c r="S46" s="7"/>
       <c r="T46" s="7"/>
       <c r="U46" s="7"/>
-      <c r="V46" s="12">
+      <c r="V46" s="14">
         <v>2.0</v>
       </c>
       <c r="W46" s="13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="X46" s="13" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="Y46" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>2|Ed</v>
+        <v>2|Brent</v>
       </c>
       <c r="Z46" s="7"/>
       <c r="AA46" s="7"/>
@@ -4466,14 +4469,14 @@
       <c r="S47" s="7"/>
       <c r="T47" s="7"/>
       <c r="U47" s="7"/>
-      <c r="V47" s="12">
+      <c r="V47" s="14">
         <v>3.0</v>
       </c>
       <c r="W47" s="13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X47" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y47" s="7" t="str">
         <f t="shared" si="17"/>
@@ -4545,19 +4548,19 @@
       </c>
       <c r="R48" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>Blaine</v>
+        <v>MaKayla</v>
       </c>
       <c r="S48" s="7"/>
       <c r="T48" s="7"/>
       <c r="U48" s="7"/>
-      <c r="V48" s="12">
+      <c r="V48" s="14">
         <v>3.0</v>
       </c>
       <c r="W48" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X48" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y48" s="7" t="str">
         <f t="shared" si="17"/>
@@ -4634,14 +4637,14 @@
       <c r="S49" s="7"/>
       <c r="T49" s="7"/>
       <c r="U49" s="7"/>
-      <c r="V49" s="12">
+      <c r="V49" s="14">
         <v>3.0</v>
       </c>
       <c r="W49" s="13" t="s">
         <v>28</v>
       </c>
       <c r="X49" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y49" s="7" t="str">
         <f t="shared" si="17"/>
@@ -4718,14 +4721,14 @@
       <c r="S50" s="7"/>
       <c r="T50" s="7"/>
       <c r="U50" s="7"/>
-      <c r="V50" s="12">
+      <c r="V50" s="14">
         <v>3.0</v>
       </c>
       <c r="W50" s="13" t="s">
         <v>25</v>
       </c>
       <c r="X50" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y50" s="7" t="str">
         <f t="shared" si="17"/>
@@ -4802,18 +4805,18 @@
       <c r="S51" s="7"/>
       <c r="T51" s="7"/>
       <c r="U51" s="7"/>
-      <c r="V51" s="13">
-        <v>3.0</v>
+      <c r="V51" s="14">
+        <v>4.0</v>
       </c>
       <c r="W51" s="13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="X51" s="13" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="Y51" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>3|Eric</v>
+        <v>4|Roy</v>
       </c>
       <c r="Z51" s="7"/>
       <c r="AA51" s="7"/>
@@ -4886,18 +4889,18 @@
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
       <c r="U52" s="7"/>
-      <c r="V52" s="12">
+      <c r="V52" s="14">
         <v>4.0</v>
       </c>
       <c r="W52" s="13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="X52" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y52" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>4|Roy</v>
+        <v>4|Collin</v>
       </c>
       <c r="Z52" s="7"/>
       <c r="AA52" s="7"/>
@@ -4970,18 +4973,18 @@
       <c r="S53" s="7"/>
       <c r="T53" s="7"/>
       <c r="U53" s="7"/>
-      <c r="V53" s="12">
+      <c r="V53" s="14">
         <v>4.0</v>
       </c>
       <c r="W53" s="13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="X53" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y53" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>4|Collin</v>
+        <v>4|Eric</v>
       </c>
       <c r="Z53" s="7"/>
       <c r="AA53" s="7"/>
@@ -5054,18 +5057,18 @@
       <c r="S54" s="7"/>
       <c r="T54" s="7"/>
       <c r="U54" s="7"/>
-      <c r="V54" s="12">
+      <c r="V54" s="14">
         <v>4.0</v>
       </c>
       <c r="W54" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X54" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y54" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>4|Eric</v>
+        <v>4|MaKayla</v>
       </c>
       <c r="Z54" s="7"/>
       <c r="AA54" s="7"/>
@@ -5138,18 +5141,18 @@
       <c r="S55" s="7"/>
       <c r="T55" s="7"/>
       <c r="U55" s="7"/>
-      <c r="V55" s="12">
+      <c r="V55" s="14">
         <v>4.0</v>
       </c>
       <c r="W55" s="13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="X55" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y55" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>4|MaKayla</v>
+        <v>4|Brent</v>
       </c>
       <c r="Z55" s="7"/>
       <c r="AA55" s="7"/>
@@ -5222,18 +5225,18 @@
       <c r="S56" s="7"/>
       <c r="T56" s="7"/>
       <c r="U56" s="7"/>
-      <c r="V56" s="12">
+      <c r="V56" s="14">
         <v>4.0</v>
       </c>
       <c r="W56" s="13" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="X56" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y56" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>4|Brent</v>
+        <v>4|Ed</v>
       </c>
       <c r="Z56" s="7"/>
       <c r="AA56" s="7"/>
@@ -5306,18 +5309,18 @@
       <c r="S57" s="7"/>
       <c r="T57" s="7"/>
       <c r="U57" s="7"/>
-      <c r="V57" s="12">
-        <v>4.0</v>
+      <c r="V57" s="14">
+        <v>5.0</v>
       </c>
       <c r="W57" s="13" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="X57" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y57" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>4|Ed</v>
+        <v>5|Eric</v>
       </c>
       <c r="Z57" s="7"/>
       <c r="AA57" s="7"/>
@@ -5393,15 +5396,15 @@
       <c r="V58" s="12">
         <v>4.0</v>
       </c>
-      <c r="W58" s="13" t="s">
+      <c r="W58" s="12" t="s">
         <v>29</v>
       </c>
       <c r="X58" s="13" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="Y58" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>4|Joey</v>
+        <v>4|Jason</v>
       </c>
       <c r="Z58" s="7"/>
       <c r="AA58" s="7"/>
@@ -5474,18 +5477,18 @@
       <c r="S59" s="7"/>
       <c r="T59" s="7"/>
       <c r="U59" s="7"/>
-      <c r="V59" s="14">
-        <v>4.0</v>
-      </c>
-      <c r="W59" s="14" t="s">
-        <v>27</v>
+      <c r="V59" s="12">
+        <v>6.0</v>
+      </c>
+      <c r="W59" s="12" t="s">
+        <v>32</v>
       </c>
       <c r="X59" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Y59" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>4|Jason</v>
+        <v>6|Eric</v>
       </c>
       <c r="Z59" s="7"/>
       <c r="AA59" s="7"/>
@@ -5559,17 +5562,17 @@
       <c r="T60" s="7"/>
       <c r="U60" s="7"/>
       <c r="V60" s="12">
-        <v>5.0</v>
-      </c>
-      <c r="W60" s="13" t="s">
-        <v>32</v>
+        <v>6.0</v>
+      </c>
+      <c r="W60" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="X60" s="13" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Y60" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>5|Eric</v>
+        <v>6|Collin</v>
       </c>
       <c r="Z60" s="7"/>
       <c r="AA60" s="7"/>
@@ -5642,18 +5645,18 @@
       <c r="S61" s="7"/>
       <c r="T61" s="7"/>
       <c r="U61" s="7"/>
-      <c r="V61" s="12">
-        <v>5.0</v>
+      <c r="V61" s="14">
+        <v>1.0</v>
       </c>
       <c r="W61" s="13" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="X61" s="13" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="Y61" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>5|Brent</v>
+        <v>1|Ty</v>
       </c>
       <c r="Z61" s="7"/>
       <c r="AA61" s="7"/>
@@ -5725,23 +5728,23 @@
       </c>
       <c r="S62" s="7"/>
       <c r="T62" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U62" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="V62" s="12">
-        <v>5.0</v>
+        <v>40</v>
+      </c>
+      <c r="V62" s="13">
+        <v>1.0</v>
       </c>
       <c r="W62" s="13" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="X62" s="13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Y62" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>5|Jason</v>
+        <v>1|Roy</v>
       </c>
       <c r="Z62" s="7"/>
       <c r="AA62" s="7"/>
@@ -5813,24 +5816,24 @@
       </c>
       <c r="S63" s="7"/>
       <c r="T63" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="U63" s="10">
         <f t="shared" ref="U63:U74" si="22">SUMIF($R$45:$R$116, T63, $Q$45:$Q$116)</f>
         <v>418</v>
       </c>
-      <c r="V63" s="12">
-        <v>5.0</v>
+      <c r="V63" s="13">
+        <v>1.0</v>
       </c>
       <c r="W63" s="13" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="X63" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y63" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>5|Joey</v>
+        <v>1|Eric</v>
       </c>
       <c r="Z63" s="7"/>
       <c r="AA63" s="7"/>
@@ -5902,24 +5905,24 @@
       </c>
       <c r="S64" s="7"/>
       <c r="T64" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U64" s="10">
         <f t="shared" si="22"/>
         <v>170.75</v>
       </c>
       <c r="V64" s="12">
-        <v>6.0</v>
-      </c>
-      <c r="W64" s="13" t="s">
-        <v>28</v>
+        <v>1.0</v>
+      </c>
+      <c r="W64" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="X64" s="13" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="Y64" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>6|Brent</v>
+        <v>1|MaKayla</v>
       </c>
       <c r="Z64" s="7"/>
       <c r="AA64" s="7"/>
@@ -5991,24 +5994,24 @@
       </c>
       <c r="S65" s="7"/>
       <c r="T65" s="7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="U65" s="10">
         <f t="shared" si="22"/>
         <v>140</v>
       </c>
-      <c r="V65" s="12">
-        <v>6.0</v>
+      <c r="V65" s="13">
+        <v>3.0</v>
       </c>
       <c r="W65" s="13" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="X65" s="13" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Y65" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>6|Jason</v>
+        <v>3|Eric</v>
       </c>
       <c r="Z65" s="7"/>
       <c r="AA65" s="7"/>
@@ -6080,24 +6083,24 @@
       </c>
       <c r="S66" s="7"/>
       <c r="T66" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U66" s="10">
         <f t="shared" si="22"/>
         <v>128</v>
       </c>
       <c r="V66" s="14">
-        <v>6.0</v>
-      </c>
-      <c r="W66" s="14" t="s">
-        <v>35</v>
+        <v>1.0</v>
+      </c>
+      <c r="W66" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="X66" s="13" t="s">
         <v>34</v>
       </c>
       <c r="Y66" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>6|Collin</v>
+        <v>1|Brent</v>
       </c>
       <c r="Z66" s="7"/>
       <c r="AA66" s="7"/>
@@ -6169,18 +6172,24 @@
       </c>
       <c r="S67" s="7"/>
       <c r="T67" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U67" s="10">
         <f t="shared" si="22"/>
-        <v>102.75</v>
-      </c>
-      <c r="V67" s="14"/>
-      <c r="W67" s="14"/>
-      <c r="X67" s="13"/>
+        <v>18.25</v>
+      </c>
+      <c r="V67" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="W67" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="X67" s="13" t="s">
+        <v>34</v>
+      </c>
       <c r="Y67" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>0|</v>
+        <v>5|Jason</v>
       </c>
       <c r="Z67" s="7"/>
       <c r="AA67" s="7"/>
@@ -6252,18 +6261,24 @@
       </c>
       <c r="S68" s="7"/>
       <c r="T68" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="U68" s="10">
         <f t="shared" si="22"/>
-        <v>72</v>
-      </c>
-      <c r="V68" s="3"/>
-      <c r="W68" s="3"/>
-      <c r="X68" s="7"/>
+        <v>156.5</v>
+      </c>
+      <c r="V68" s="14">
+        <v>6.0</v>
+      </c>
+      <c r="W68" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="X68" s="13" t="s">
+        <v>34</v>
+      </c>
       <c r="Y68" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>0|</v>
+        <v>6|Jason</v>
       </c>
       <c r="Z68" s="7"/>
       <c r="AA68" s="7"/>
@@ -6335,15 +6350,15 @@
       </c>
       <c r="S69" s="7"/>
       <c r="T69" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U69" s="10">
         <f t="shared" si="22"/>
         <v>64.5</v>
       </c>
-      <c r="V69" s="3"/>
-      <c r="W69" s="3"/>
-      <c r="X69" s="7"/>
+      <c r="V69" s="12"/>
+      <c r="W69" s="12"/>
+      <c r="X69" s="13"/>
       <c r="Y69" s="7" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -6418,7 +6433,7 @@
       </c>
       <c r="S70" s="7"/>
       <c r="T70" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U70" s="10">
         <f t="shared" si="22"/>
@@ -6501,11 +6516,11 @@
       </c>
       <c r="S71" s="7"/>
       <c r="T71" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="U71" s="10">
         <f t="shared" si="22"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V71" s="3"/>
       <c r="W71" s="3"/>
@@ -6671,7 +6686,7 @@
       </c>
       <c r="U73" s="10">
         <f t="shared" si="22"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V73" s="3"/>
       <c r="W73" s="3"/>
@@ -6834,8 +6849,8 @@
       <c r="S76" s="7"/>
       <c r="T76" s="7"/>
       <c r="U76" s="3"/>
-      <c r="V76" s="7"/>
-      <c r="W76" s="7"/>
+      <c r="V76" s="3"/>
+      <c r="W76" s="3"/>
       <c r="X76" s="7"/>
       <c r="Y76" s="7" t="str">
         <f t="shared" si="17"/>
@@ -6876,13 +6891,13 @@
       </c>
       <c r="R77" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>MaKayla</v>
+        <v>Blaine</v>
       </c>
       <c r="S77" s="7"/>
       <c r="T77" s="7"/>
       <c r="U77" s="7"/>
-      <c r="V77" s="7"/>
-      <c r="W77" s="7"/>
+      <c r="V77" s="3"/>
+      <c r="W77" s="3"/>
       <c r="X77" s="7"/>
       <c r="Y77" s="7" t="str">
         <f t="shared" si="17"/>
@@ -7025,7 +7040,10 @@
       <c r="V80" s="7"/>
       <c r="W80" s="7"/>
       <c r="X80" s="7"/>
-      <c r="Y80" s="7"/>
+      <c r="Y80" s="7" t="str">
+        <f t="shared" si="17"/>
+        <v>0|</v>
+      </c>
       <c r="Z80" s="7"/>
       <c r="AA80" s="7"/>
       <c r="AB80" s="7"/>
@@ -7069,7 +7087,10 @@
       <c r="V81" s="7"/>
       <c r="W81" s="7"/>
       <c r="X81" s="7"/>
-      <c r="Y81" s="7"/>
+      <c r="Y81" s="7" t="str">
+        <f t="shared" si="17"/>
+        <v>0|</v>
+      </c>
       <c r="Z81" s="7"/>
       <c r="AA81" s="7"/>
       <c r="AB81" s="7"/>
@@ -8337,7 +8358,7 @@
       </c>
       <c r="R110" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>Eric</v>
+        <v>Joey</v>
       </c>
       <c r="S110" s="7"/>
       <c r="T110" s="7"/>
@@ -9291,17 +9312,11 @@
       <c r="T137" s="7"/>
       <c r="U137" s="7"/>
       <c r="V137" s="7"/>
-      <c r="W137" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="X137" s="13" t="s">
+      <c r="W137" s="7"/>
+      <c r="X137" s="7"/>
+      <c r="Y137" s="7"/>
+      <c r="Z137" s="13" t="s">
         <v>41</v>
-      </c>
-      <c r="Y137" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="Z137" s="13" t="s">
-        <v>43</v>
       </c>
       <c r="AA137" s="7"/>
       <c r="AB137" s="7"/>
@@ -9331,15 +9346,9 @@
       <c r="T138" s="7"/>
       <c r="U138" s="7"/>
       <c r="V138" s="7"/>
-      <c r="W138" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="X138" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y138" s="13" t="s">
-        <v>45</v>
-      </c>
+      <c r="W138" s="7"/>
+      <c r="X138" s="7"/>
+      <c r="Y138" s="7"/>
       <c r="Z138" s="13">
         <v>6817.0</v>
       </c>
@@ -9371,14 +9380,14 @@
       <c r="T139" s="7"/>
       <c r="U139" s="7"/>
       <c r="V139" s="7"/>
-      <c r="W139" s="13">
-        <v>3.0</v>
+      <c r="W139" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="X139" s="13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Y139" s="13" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Z139" s="13">
         <v>5203.0</v>
@@ -9412,13 +9421,13 @@
       <c r="U140" s="7"/>
       <c r="V140" s="7"/>
       <c r="W140" s="13">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="X140" s="13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="Y140" s="13" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Z140" s="13">
         <v>5103.0</v>
@@ -9452,13 +9461,13 @@
       <c r="U141" s="7"/>
       <c r="V141" s="7"/>
       <c r="W141" s="13">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="X141" s="13" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Y141" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Z141" s="13">
         <v>5020.0</v>
@@ -9492,13 +9501,13 @@
       <c r="U142" s="7"/>
       <c r="V142" s="7"/>
       <c r="W142" s="13">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="X142" s="13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Y142" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Z142" s="13">
         <v>4517.0</v>
@@ -9532,13 +9541,13 @@
       <c r="U143" s="7"/>
       <c r="V143" s="7"/>
       <c r="W143" s="13">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="X143" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y143" s="13" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="Z143" s="13">
         <v>4164.0</v>
@@ -9572,13 +9581,13 @@
       <c r="U144" s="7"/>
       <c r="V144" s="7"/>
       <c r="W144" s="13">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="X144" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="Y144" s="13" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Z144" s="13">
         <v>4025.0</v>
@@ -9612,13 +9621,13 @@
       <c r="U145" s="7"/>
       <c r="V145" s="7"/>
       <c r="W145" s="13">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="X145" s="13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="Y145" s="13" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="Z145" s="13">
         <v>3650.0</v>
@@ -9652,13 +9661,13 @@
       <c r="U146" s="7"/>
       <c r="V146" s="7"/>
       <c r="W146" s="13">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="X146" s="13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Y146" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Z146" s="13">
         <v>3611.0</v>
@@ -9692,13 +9701,13 @@
       <c r="U147" s="7"/>
       <c r="V147" s="7"/>
       <c r="W147" s="13">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="X147" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Y147" s="13" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="Z147" s="13">
         <v>3608.0</v>
@@ -9732,13 +9741,13 @@
       <c r="U148" s="7"/>
       <c r="V148" s="7"/>
       <c r="W148" s="13">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="X148" s="13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Y148" s="13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="Z148" s="13">
         <v>3596.0</v>
@@ -9772,13 +9781,13 @@
       <c r="U149" s="7"/>
       <c r="V149" s="7"/>
       <c r="W149" s="13">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="X149" s="13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Y149" s="13" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="Z149" s="13">
         <v>3426.0</v>
@@ -9812,13 +9821,13 @@
       <c r="U150" s="7"/>
       <c r="V150" s="7"/>
       <c r="W150" s="13">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="X150" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Y150" s="13" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="Z150" s="13">
         <v>3264.0</v>
@@ -9852,13 +9861,13 @@
       <c r="U151" s="7"/>
       <c r="V151" s="7"/>
       <c r="W151" s="13">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="X151" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Y151" s="13" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="Z151" s="13">
         <v>3179.0</v>
@@ -9892,13 +9901,13 @@
       <c r="U152" s="7"/>
       <c r="V152" s="7"/>
       <c r="W152" s="13">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="X152" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Y152" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z152" s="13">
         <v>3162.0</v>
@@ -9932,13 +9941,13 @@
       <c r="U153" s="7"/>
       <c r="V153" s="7"/>
       <c r="W153" s="13">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="X153" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Y153" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Z153" s="13">
         <v>3125.0</v>
@@ -9972,13 +9981,13 @@
       <c r="U154" s="7"/>
       <c r="V154" s="7"/>
       <c r="W154" s="13">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="X154" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Y154" s="13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="Z154" s="13">
         <v>2971.0</v>
@@ -10012,13 +10021,13 @@
       <c r="U155" s="7"/>
       <c r="V155" s="7"/>
       <c r="W155" s="13">
-        <v>19.0</v>
+        <v>17.0</v>
       </c>
       <c r="X155" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y155" s="13" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="Z155" s="13">
         <v>2963.0</v>
@@ -10052,13 +10061,13 @@
       <c r="U156" s="7"/>
       <c r="V156" s="7"/>
       <c r="W156" s="13">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="X156" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Y156" s="13" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="Z156" s="13">
         <v>2953.0</v>
@@ -10092,13 +10101,13 @@
       <c r="U157" s="7"/>
       <c r="V157" s="7"/>
       <c r="W157" s="13">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="X157" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y157" s="13" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="Z157" s="13">
         <v>2807.0</v>
@@ -10132,13 +10141,13 @@
       <c r="U158" s="7"/>
       <c r="V158" s="7"/>
       <c r="W158" s="13">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="X158" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Y158" s="13" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="Z158" s="13">
         <v>2696.0</v>
@@ -10172,13 +10181,13 @@
       <c r="U159" s="7"/>
       <c r="V159" s="7"/>
       <c r="W159" s="13">
-        <v>23.0</v>
+        <v>21.0</v>
       </c>
       <c r="X159" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y159" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z159" s="13">
         <v>2672.0</v>
@@ -10212,13 +10221,13 @@
       <c r="U160" s="7"/>
       <c r="V160" s="7"/>
       <c r="W160" s="13">
-        <v>24.0</v>
+        <v>22.0</v>
       </c>
       <c r="X160" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Y160" s="13" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="Z160" s="13">
         <v>2480.0</v>
@@ -10252,13 +10261,13 @@
       <c r="U161" s="7"/>
       <c r="V161" s="7"/>
       <c r="W161" s="13">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
       <c r="X161" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y161" s="13" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Z161" s="13">
         <v>2416.0</v>
@@ -10292,13 +10301,13 @@
       <c r="U162" s="7"/>
       <c r="V162" s="7"/>
       <c r="W162" s="13">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
       <c r="X162" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Y162" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Z162" s="13">
         <v>2416.0</v>
@@ -10332,13 +10341,13 @@
       <c r="U163" s="7"/>
       <c r="V163" s="7"/>
       <c r="W163" s="13">
-        <v>27.0</v>
+        <v>25.0</v>
       </c>
       <c r="X163" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Y163" s="13" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Z163" s="13">
         <v>2109.0</v>
@@ -10372,13 +10381,13 @@
       <c r="U164" s="7"/>
       <c r="V164" s="7"/>
       <c r="W164" s="13">
-        <v>28.0</v>
+        <v>26.0</v>
       </c>
       <c r="X164" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y164" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Z164" s="13">
         <v>2106.0</v>
@@ -10412,13 +10421,13 @@
       <c r="U165" s="7"/>
       <c r="V165" s="7"/>
       <c r="W165" s="13">
-        <v>29.0</v>
+        <v>27.0</v>
       </c>
       <c r="X165" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Y165" s="13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="Z165" s="13">
         <v>2098.0</v>
@@ -10452,13 +10461,13 @@
       <c r="U166" s="7"/>
       <c r="V166" s="7"/>
       <c r="W166" s="13">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
       <c r="X166" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Y166" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Z166" s="13">
         <v>2078.0</v>
@@ -10492,13 +10501,13 @@
       <c r="U167" s="7"/>
       <c r="V167" s="7"/>
       <c r="W167" s="13">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
       <c r="X167" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y167" s="13" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="Z167" s="13">
         <v>2074.0</v>
@@ -10532,13 +10541,13 @@
       <c r="U168" s="7"/>
       <c r="V168" s="7"/>
       <c r="W168" s="13">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
       <c r="X168" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Y168" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Z168" s="13">
         <v>2066.0</v>
@@ -10572,13 +10581,13 @@
       <c r="U169" s="7"/>
       <c r="V169" s="7"/>
       <c r="W169" s="13">
-        <v>33.0</v>
+        <v>31.0</v>
       </c>
       <c r="X169" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Y169" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Z169" s="13">
         <v>2045.0</v>
@@ -10612,13 +10621,13 @@
       <c r="U170" s="7"/>
       <c r="V170" s="7"/>
       <c r="W170" s="13">
-        <v>34.0</v>
+        <v>32.0</v>
       </c>
       <c r="X170" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y170" s="13" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="Z170" s="13">
         <v>1977.0</v>
@@ -10652,13 +10661,13 @@
       <c r="U171" s="7"/>
       <c r="V171" s="7"/>
       <c r="W171" s="13">
-        <v>35.0</v>
+        <v>33.0</v>
       </c>
       <c r="X171" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y171" s="13" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="Z171" s="13">
         <v>1967.0</v>
@@ -10692,13 +10701,13 @@
       <c r="U172" s="7"/>
       <c r="V172" s="7"/>
       <c r="W172" s="13">
-        <v>36.0</v>
+        <v>34.0</v>
       </c>
       <c r="X172" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y172" s="13" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="Z172" s="13">
         <v>1962.0</v>
@@ -10732,13 +10741,13 @@
       <c r="U173" s="7"/>
       <c r="V173" s="7"/>
       <c r="W173" s="13">
-        <v>37.0</v>
+        <v>35.0</v>
       </c>
       <c r="X173" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Y173" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z173" s="13">
         <v>1961.0</v>
@@ -10772,13 +10781,13 @@
       <c r="U174" s="7"/>
       <c r="V174" s="7"/>
       <c r="W174" s="13">
-        <v>38.0</v>
+        <v>36.0</v>
       </c>
       <c r="X174" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Y174" s="13" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="Z174" s="13">
         <v>1910.0</v>
@@ -10812,13 +10821,13 @@
       <c r="U175" s="7"/>
       <c r="V175" s="7"/>
       <c r="W175" s="13">
-        <v>39.0</v>
+        <v>37.0</v>
       </c>
       <c r="X175" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y175" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Z175" s="13">
         <v>1873.0</v>
@@ -10852,13 +10861,13 @@
       <c r="U176" s="7"/>
       <c r="V176" s="7"/>
       <c r="W176" s="13">
-        <v>40.0</v>
+        <v>38.0</v>
       </c>
       <c r="X176" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y176" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Z176" s="13">
         <v>1822.0</v>
@@ -10892,13 +10901,13 @@
       <c r="U177" s="7"/>
       <c r="V177" s="7"/>
       <c r="W177" s="13">
-        <v>41.0</v>
+        <v>39.0</v>
       </c>
       <c r="X177" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Y177" s="13" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="Z177" s="13">
         <v>1741.0</v>
@@ -10932,13 +10941,13 @@
       <c r="U178" s="7"/>
       <c r="V178" s="7"/>
       <c r="W178" s="13">
-        <v>42.0</v>
+        <v>40.0</v>
       </c>
       <c r="X178" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Y178" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Z178" s="13">
         <v>1724.0</v>
@@ -10972,13 +10981,13 @@
       <c r="U179" s="7"/>
       <c r="V179" s="7"/>
       <c r="W179" s="13">
-        <v>43.0</v>
+        <v>41.0</v>
       </c>
       <c r="X179" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Y179" s="13" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Z179" s="13">
         <v>1660.0</v>
@@ -11012,13 +11021,13 @@
       <c r="U180" s="7"/>
       <c r="V180" s="7"/>
       <c r="W180" s="13">
-        <v>44.0</v>
+        <v>42.0</v>
       </c>
       <c r="X180" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y180" s="13" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Z180" s="13">
         <v>1640.0</v>
@@ -11052,13 +11061,13 @@
       <c r="U181" s="7"/>
       <c r="V181" s="7"/>
       <c r="W181" s="13">
-        <v>45.0</v>
+        <v>43.0</v>
       </c>
       <c r="X181" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y181" s="13" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="Z181" s="13">
         <v>1577.0</v>
@@ -11092,13 +11101,13 @@
       <c r="U182" s="7"/>
       <c r="V182" s="7"/>
       <c r="W182" s="13">
-        <v>46.0</v>
+        <v>44.0</v>
       </c>
       <c r="X182" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Y182" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Z182" s="13">
         <v>1565.0</v>
@@ -11132,13 +11141,13 @@
       <c r="U183" s="7"/>
       <c r="V183" s="7"/>
       <c r="W183" s="13">
-        <v>47.0</v>
+        <v>45.0</v>
       </c>
       <c r="X183" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y183" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Z183" s="13">
         <v>1552.0</v>
@@ -11172,13 +11181,13 @@
       <c r="U184" s="7"/>
       <c r="V184" s="7"/>
       <c r="W184" s="13">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
       <c r="X184" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Y184" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Z184" s="13">
         <v>1404.0</v>
@@ -11212,13 +11221,13 @@
       <c r="U185" s="7"/>
       <c r="V185" s="7"/>
       <c r="W185" s="13">
-        <v>49.0</v>
+        <v>47.0</v>
       </c>
       <c r="X185" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Y185" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Z185" s="13">
         <v>1351.0</v>
@@ -11252,13 +11261,13 @@
       <c r="U186" s="7"/>
       <c r="V186" s="7"/>
       <c r="W186" s="13">
-        <v>50.0</v>
+        <v>48.0</v>
       </c>
       <c r="X186" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Y186" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z186" s="13">
         <v>1344.0</v>
@@ -11292,13 +11301,13 @@
       <c r="U187" s="7"/>
       <c r="V187" s="7"/>
       <c r="W187" s="13">
-        <v>51.0</v>
+        <v>49.0</v>
       </c>
       <c r="X187" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Y187" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Z187" s="13">
         <v>1299.0</v>
@@ -11332,13 +11341,13 @@
       <c r="U188" s="7"/>
       <c r="V188" s="7"/>
       <c r="W188" s="13">
-        <v>52.0</v>
+        <v>50.0</v>
       </c>
       <c r="X188" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Y188" s="13" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Z188" s="13">
         <v>1261.0</v>
@@ -11372,13 +11381,13 @@
       <c r="U189" s="7"/>
       <c r="V189" s="7"/>
       <c r="W189" s="13">
-        <v>53.0</v>
+        <v>51.0</v>
       </c>
       <c r="X189" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Y189" s="13" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="Z189" s="13">
         <v>1247.0</v>
@@ -11412,13 +11421,13 @@
       <c r="U190" s="7"/>
       <c r="V190" s="7"/>
       <c r="W190" s="13">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
       <c r="X190" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Y190" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Z190" s="13">
         <v>1226.0</v>
@@ -11452,13 +11461,13 @@
       <c r="U191" s="7"/>
       <c r="V191" s="7"/>
       <c r="W191" s="13">
-        <v>55.0</v>
+        <v>53.0</v>
       </c>
       <c r="X191" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Y191" s="13" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="Z191" s="13">
         <v>1211.0</v>
@@ -11492,13 +11501,13 @@
       <c r="U192" s="7"/>
       <c r="V192" s="7"/>
       <c r="W192" s="13">
-        <v>56.0</v>
+        <v>54.0</v>
       </c>
       <c r="X192" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Y192" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Z192" s="13">
         <v>1197.0</v>
@@ -11532,13 +11541,13 @@
       <c r="U193" s="7"/>
       <c r="V193" s="7"/>
       <c r="W193" s="13">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
       <c r="X193" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Y193" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Z193" s="13">
         <v>1184.0</v>
@@ -11572,13 +11581,13 @@
       <c r="U194" s="7"/>
       <c r="V194" s="7"/>
       <c r="W194" s="13">
-        <v>58.0</v>
+        <v>56.0</v>
       </c>
       <c r="X194" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Y194" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Z194" s="13">
         <v>1157.0</v>
@@ -11612,13 +11621,13 @@
       <c r="U195" s="7"/>
       <c r="V195" s="7"/>
       <c r="W195" s="13">
-        <v>59.0</v>
+        <v>57.0</v>
       </c>
       <c r="X195" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Y195" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Z195" s="13">
         <v>1143.0</v>
@@ -11652,13 +11661,13 @@
       <c r="U196" s="7"/>
       <c r="V196" s="7"/>
       <c r="W196" s="13">
-        <v>60.0</v>
+        <v>58.0</v>
       </c>
       <c r="X196" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y196" s="13" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Z196" s="13">
         <v>1078.0</v>
@@ -11692,13 +11701,13 @@
       <c r="U197" s="7"/>
       <c r="V197" s="7"/>
       <c r="W197" s="13">
-        <v>61.0</v>
+        <v>59.0</v>
       </c>
       <c r="X197" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Y197" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Z197" s="13">
         <v>1069.0</v>
@@ -11732,13 +11741,13 @@
       <c r="U198" s="7"/>
       <c r="V198" s="7"/>
       <c r="W198" s="13">
-        <v>62.0</v>
+        <v>60.0</v>
       </c>
       <c r="X198" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Y198" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Z198" s="13">
         <v>1000.0</v>
@@ -11772,13 +11781,13 @@
       <c r="U199" s="7"/>
       <c r="V199" s="7"/>
       <c r="W199" s="13">
-        <v>63.0</v>
+        <v>61.0</v>
       </c>
       <c r="X199" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y199" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Z199" s="13">
         <v>987.0</v>
@@ -11812,13 +11821,13 @@
       <c r="U200" s="7"/>
       <c r="V200" s="7"/>
       <c r="W200" s="13">
-        <v>64.0</v>
+        <v>62.0</v>
       </c>
       <c r="X200" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Y200" s="13" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="Z200" s="13">
         <v>952.0</v>
@@ -11852,13 +11861,13 @@
       <c r="U201" s="7"/>
       <c r="V201" s="7"/>
       <c r="W201" s="13">
-        <v>65.0</v>
+        <v>63.0</v>
       </c>
       <c r="X201" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y201" s="13" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Z201" s="13">
         <v>913.0</v>
@@ -11892,13 +11901,13 @@
       <c r="U202" s="7"/>
       <c r="V202" s="7"/>
       <c r="W202" s="13">
-        <v>66.0</v>
+        <v>64.0</v>
       </c>
       <c r="X202" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Y202" s="13" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z202" s="13">
         <v>905.0</v>
@@ -11932,13 +11941,13 @@
       <c r="U203" s="7"/>
       <c r="V203" s="7"/>
       <c r="W203" s="13">
-        <v>67.0</v>
+        <v>65.0</v>
       </c>
       <c r="X203" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Y203" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Z203" s="13">
         <v>842.0</v>
@@ -11972,13 +11981,13 @@
       <c r="U204" s="7"/>
       <c r="V204" s="7"/>
       <c r="W204" s="13">
-        <v>68.0</v>
+        <v>66.0</v>
       </c>
       <c r="X204" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y204" s="13" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="Z204" s="13">
         <v>823.0</v>
@@ -12012,13 +12021,13 @@
       <c r="U205" s="7"/>
       <c r="V205" s="7"/>
       <c r="W205" s="13">
-        <v>69.0</v>
+        <v>67.0</v>
       </c>
       <c r="X205" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y205" s="13" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Z205" s="13">
         <v>820.0</v>
@@ -12052,13 +12061,13 @@
       <c r="U206" s="7"/>
       <c r="V206" s="7"/>
       <c r="W206" s="13">
-        <v>70.0</v>
+        <v>68.0</v>
       </c>
       <c r="X206" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y206" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Z206" s="13">
         <v>805.0</v>
@@ -12092,13 +12101,13 @@
       <c r="U207" s="7"/>
       <c r="V207" s="7"/>
       <c r="W207" s="13">
-        <v>71.0</v>
+        <v>69.0</v>
       </c>
       <c r="X207" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Y207" s="13" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="Z207" s="13">
         <v>782.0</v>
@@ -12132,13 +12141,13 @@
       <c r="U208" s="7"/>
       <c r="V208" s="7"/>
       <c r="W208" s="13">
-        <v>72.0</v>
+        <v>70.0</v>
       </c>
       <c r="X208" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Y208" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Z208" s="13">
         <v>736.0</v>
@@ -12172,13 +12181,13 @@
       <c r="U209" s="7"/>
       <c r="V209" s="7"/>
       <c r="W209" s="13">
-        <v>73.0</v>
+        <v>71.0</v>
       </c>
       <c r="X209" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Y209" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Z209" s="13">
         <v>733.0</v>
@@ -12212,13 +12221,13 @@
       <c r="U210" s="7"/>
       <c r="V210" s="7"/>
       <c r="W210" s="13">
-        <v>74.0</v>
+        <v>72.0</v>
       </c>
       <c r="X210" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y210" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z210" s="13">
         <v>700.0</v>
@@ -12252,13 +12261,13 @@
       <c r="U211" s="7"/>
       <c r="V211" s="7"/>
       <c r="W211" s="13">
-        <v>75.0</v>
+        <v>73.0</v>
       </c>
       <c r="X211" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y211" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Z211" s="13">
         <v>649.0</v>
@@ -12292,13 +12301,13 @@
       <c r="U212" s="7"/>
       <c r="V212" s="7"/>
       <c r="W212" s="13">
-        <v>76.0</v>
+        <v>74.0</v>
       </c>
       <c r="X212" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Y212" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Z212" s="13">
         <v>636.0</v>
@@ -12332,13 +12341,13 @@
       <c r="U213" s="7"/>
       <c r="V213" s="7"/>
       <c r="W213" s="13">
-        <v>78.0</v>
+        <v>75.0</v>
       </c>
       <c r="X213" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Y213" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Z213" s="13">
         <v>528.0</v>
@@ -12372,13 +12381,13 @@
       <c r="U214" s="7"/>
       <c r="V214" s="7"/>
       <c r="W214" s="13">
-        <v>79.0</v>
+        <v>76.0</v>
       </c>
       <c r="X214" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y214" s="13" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Z214" s="13">
         <v>473.0</v>
@@ -12412,13 +12421,13 @@
       <c r="U215" s="7"/>
       <c r="V215" s="7"/>
       <c r="W215" s="13">
-        <v>80.0</v>
+        <v>78.0</v>
       </c>
       <c r="X215" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y215" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Z215" s="13">
         <v>435.0</v>
@@ -12451,9 +12460,15 @@
       <c r="T216" s="7"/>
       <c r="U216" s="7"/>
       <c r="V216" s="7"/>
-      <c r="W216" s="7"/>
-      <c r="X216" s="7"/>
-      <c r="Y216" s="7"/>
+      <c r="W216" s="13">
+        <v>79.0</v>
+      </c>
+      <c r="X216" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y216" s="13" t="s">
+        <v>46</v>
+      </c>
       <c r="Z216" s="7"/>
       <c r="AA216" s="7"/>
       <c r="AB216" s="7"/>
@@ -12483,9 +12498,15 @@
       <c r="T217" s="7"/>
       <c r="U217" s="7"/>
       <c r="V217" s="7"/>
-      <c r="W217" s="7"/>
-      <c r="X217" s="7"/>
-      <c r="Y217" s="7"/>
+      <c r="W217" s="13">
+        <v>80.0</v>
+      </c>
+      <c r="X217" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y217" s="13" t="s">
+        <v>46</v>
+      </c>
       <c r="Z217" s="7"/>
       <c r="AA217" s="7"/>
       <c r="AB217" s="7"/>
@@ -37554,6 +37575,10 @@
       <c r="D1001" s="17"/>
       <c r="E1001" s="17"/>
       <c r="L1001" s="18"/>
+      <c r="V1001" s="7"/>
+      <c r="W1001" s="7"/>
+      <c r="X1001" s="7"/>
+      <c r="Y1001" s="7"/>
     </row>
     <row r="1002">
       <c r="A1002" s="17"/>
@@ -37561,6 +37586,10 @@
       <c r="D1002" s="17"/>
       <c r="E1002" s="17"/>
       <c r="L1002" s="18"/>
+      <c r="V1002" s="7"/>
+      <c r="W1002" s="7"/>
+      <c r="X1002" s="7"/>
+      <c r="Y1002" s="7"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -37584,34 +37613,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2">
@@ -37619,7 +37648,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="17">
         <v>133.5</v>
@@ -37663,7 +37692,7 @@
         <v/>
       </c>
       <c r="K2" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L2" s="9">
         <v>1200.0</v>
@@ -37674,7 +37703,7 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3" s="17">
         <v>104.5</v>
@@ -37705,7 +37734,7 @@
         <v/>
       </c>
       <c r="K3" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L3" s="9">
         <v>12.0</v>
@@ -37716,7 +37745,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C4" s="17">
         <v>92.5</v>
@@ -37742,7 +37771,7 @@
         <v/>
       </c>
       <c r="K4" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L4" s="19">
         <f>'Draft Data'!U63</f>
@@ -37754,7 +37783,7 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" s="17">
         <v>85.5</v>
@@ -37779,7 +37808,7 @@
         <v/>
       </c>
       <c r="K5" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L5" s="22">
         <f>SUM($D$2:$D$500)
@@ -37792,7 +37821,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6" s="17">
         <v>73.5</v>
@@ -37817,7 +37846,7 @@
         <v/>
       </c>
       <c r="K6" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L6" s="22">
         <f>L2-L5
@@ -37830,7 +37859,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" s="17">
         <v>65.0</v>
@@ -37855,7 +37884,7 @@
         <v/>
       </c>
       <c r="K7" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L7" s="22">
         <f>SUMIF($E$2:$E$500,TRUE,$D$2:$D$500)</f>
@@ -37867,7 +37896,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" s="17">
         <v>59.0</v>
@@ -37892,7 +37921,7 @@
         <v/>
       </c>
       <c r="K8" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L8" s="17">
         <f>L4-L7
@@ -37905,7 +37934,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9" s="17">
         <v>52.0</v>
@@ -37930,7 +37959,7 @@
         <v/>
       </c>
       <c r="K9" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L9" s="17">
         <f>L6-L8
@@ -37943,7 +37972,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10" s="17">
         <v>48.0</v>
@@ -37968,7 +37997,7 @@
         <v/>
       </c>
       <c r="K10" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L10" s="17">
         <f>IF(L3&gt;1,L9/(L3-1),0)</f>
@@ -37980,7 +38009,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C11" s="17">
         <v>43.0</v>
@@ -38005,7 +38034,7 @@
         <v/>
       </c>
       <c r="K11" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L11" s="23">
         <f>IF(L10&gt;0,L8/L10,1)</f>
@@ -38017,7 +38046,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12" s="17">
         <v>40.0</v>
@@ -38047,7 +38076,7 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C13" s="17">
         <v>35.0</v>
@@ -38072,7 +38101,7 @@
         <v/>
       </c>
       <c r="K13" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L13" s="22">
         <f>SUMIF($D$2:$D$73,"",$C$2:$C$73)</f>
@@ -38084,7 +38113,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C14" s="17">
         <v>30.5</v>
@@ -38109,7 +38138,7 @@
         <v/>
       </c>
       <c r="K14" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L14" s="23">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -38121,7 +38150,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C15" s="17">
         <v>27.5</v>
@@ -38151,7 +38180,7 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C16" s="17">
         <v>25.5</v>
@@ -38176,7 +38205,7 @@
         <v/>
       </c>
       <c r="K16" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L16" s="9">
         <f>IF($L$18&lt;0.3,
@@ -38198,7 +38227,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C17" s="17">
         <v>23.5</v>
@@ -38228,7 +38257,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C18" s="17">
         <v>20.5</v>
@@ -38253,7 +38282,7 @@
         <v/>
       </c>
       <c r="K18" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L18" s="24">
         <f>L5/L2</f>
@@ -38265,7 +38294,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C19" s="17">
         <v>19.0</v>
@@ -38295,7 +38324,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C20" s="17">
         <v>17.5</v>
@@ -38325,7 +38354,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" s="17">
         <v>16.0</v>
@@ -38355,7 +38384,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C22" s="17">
         <v>14.0</v>
@@ -38385,7 +38414,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C23" s="17">
         <v>13.0</v>
@@ -38415,7 +38444,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C24" s="17">
         <v>11.5</v>
@@ -38445,7 +38474,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C25" s="17">
         <v>10.5</v>
@@ -38475,7 +38504,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C26" s="17">
         <v>9.5</v>
@@ -38505,7 +38534,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C27" s="17">
         <v>8.5</v>
@@ -38530,7 +38559,7 @@
         <v/>
       </c>
       <c r="K27" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L27" s="9">
         <v>0.8</v>
@@ -38541,7 +38570,7 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C28" s="17">
         <v>7.5</v>
@@ -38571,7 +38600,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C29" s="17">
         <v>7.0</v>
@@ -38601,7 +38630,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C30" s="17">
         <v>6.5</v>
@@ -38631,7 +38660,7 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C31" s="17">
         <v>6.0</v>
@@ -38661,7 +38690,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C32" s="17">
         <v>5.5</v>
@@ -38691,7 +38720,7 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C33" s="17">
         <v>5.0</v>
@@ -38721,7 +38750,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C34" s="17">
         <v>4.5</v>
@@ -38751,7 +38780,7 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" s="17">
         <v>4.5</v>
@@ -38781,7 +38810,7 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C36" s="17">
         <v>4.0</v>
@@ -38811,7 +38840,7 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C37" s="17">
         <v>4.0</v>
@@ -38841,7 +38870,7 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C38" s="17">
         <v>3.5</v>
@@ -38871,7 +38900,7 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C39" s="17">
         <v>3.5</v>
@@ -38901,7 +38930,7 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C40" s="17">
         <v>3.0</v>
@@ -38931,7 +38960,7 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C41" s="17">
         <v>3.0</v>
@@ -38961,7 +38990,7 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C42" s="17">
         <v>2.5</v>
@@ -38991,7 +39020,7 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C43" s="17">
         <v>2.5</v>
@@ -39021,7 +39050,7 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C44" s="17">
         <v>2.5</v>
@@ -39051,7 +39080,7 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C45" s="17">
         <v>2.5</v>
@@ -39081,7 +39110,7 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C46" s="17">
         <v>2.0</v>
@@ -39111,7 +39140,7 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C47" s="17">
         <v>2.0</v>
@@ -39141,7 +39170,7 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C48" s="17">
         <v>2.0</v>
@@ -39171,7 +39200,7 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C49" s="17">
         <v>2.0</v>
@@ -39201,7 +39230,7 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C50" s="17">
         <v>2.0</v>
@@ -39231,7 +39260,7 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C51" s="17">
         <v>2.0</v>
@@ -39261,7 +39290,7 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C52" s="17">
         <v>2.0</v>
@@ -39291,7 +39320,7 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C53" s="17">
         <v>2.0</v>
@@ -39321,7 +39350,7 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C54" s="17">
         <v>2.0</v>
@@ -39351,7 +39380,7 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C55" s="17">
         <v>2.0</v>
@@ -39381,7 +39410,7 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C56" s="17">
         <v>2.0</v>
@@ -39411,7 +39440,7 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C57" s="17">
         <v>2.0</v>
@@ -39441,7 +39470,7 @@
         <v>57.0</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C58" s="17">
         <v>2.0</v>
@@ -39471,7 +39500,7 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C59" s="17">
         <v>2.0</v>
@@ -39501,7 +39530,7 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C60" s="17">
         <v>2.0</v>
@@ -39531,7 +39560,7 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C61" s="17">
         <v>2.0</v>
@@ -39561,7 +39590,7 @@
         <v>61.0</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C62" s="17">
         <v>1.0</v>
@@ -39591,7 +39620,7 @@
         <v>62.0</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C63" s="17">
         <v>1.0</v>
@@ -39621,7 +39650,7 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C64" s="17">
         <v>1.0</v>
@@ -39651,7 +39680,7 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C65" s="17">
         <v>1.0</v>
@@ -39681,7 +39710,7 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C66" s="17">
         <v>1.0</v>
@@ -39711,7 +39740,7 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C67" s="17">
         <v>1.0</v>
@@ -39741,7 +39770,7 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C68" s="17">
         <v>1.0</v>
@@ -39771,7 +39800,7 @@
         <v>68.0</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C69" s="17">
         <v>1.0</v>
@@ -39801,7 +39830,7 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C70" s="17">
         <v>1.0</v>
@@ -39831,7 +39860,7 @@
         <v>70.0</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C71" s="17">
         <v>1.0</v>
@@ -39861,7 +39890,7 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C72" s="17">
         <v>1.0</v>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -5994,11 +5994,11 @@
       </c>
       <c r="S65" s="7"/>
       <c r="T65" s="7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="U65" s="10">
         <f t="shared" si="22"/>
-        <v>140</v>
+        <v>156.5</v>
       </c>
       <c r="V65" s="13">
         <v>3.0</v>
@@ -6083,11 +6083,11 @@
       </c>
       <c r="S66" s="7"/>
       <c r="T66" s="7" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="U66" s="10">
         <f t="shared" si="22"/>
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="V66" s="14">
         <v>1.0</v>
@@ -6172,11 +6172,11 @@
       </c>
       <c r="S67" s="7"/>
       <c r="T67" s="7" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="U67" s="10">
         <f t="shared" si="22"/>
-        <v>18.25</v>
+        <v>128</v>
       </c>
       <c r="V67" s="14">
         <v>5.0</v>
@@ -6261,11 +6261,11 @@
       </c>
       <c r="S68" s="7"/>
       <c r="T68" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="U68" s="10">
         <f t="shared" si="22"/>
-        <v>156.5</v>
+        <v>64.5</v>
       </c>
       <c r="V68" s="14">
         <v>6.0</v>
@@ -6350,11 +6350,11 @@
       </c>
       <c r="S69" s="7"/>
       <c r="T69" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="U69" s="10">
         <f t="shared" si="22"/>
-        <v>64.5</v>
+        <v>50</v>
       </c>
       <c r="V69" s="12"/>
       <c r="W69" s="12"/>
@@ -6516,11 +6516,11 @@
       </c>
       <c r="S71" s="7"/>
       <c r="T71" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="U71" s="10">
         <f t="shared" si="22"/>
-        <v>50</v>
+        <v>18.25</v>
       </c>
       <c r="V71" s="3"/>
       <c r="W71" s="3"/>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="173">
   <si>
     <t>PICK</t>
   </si>
@@ -464,7 +464,13 @@
     <t>Undrafted Predraft$</t>
   </si>
   <si>
+    <t>CJ Allen</t>
+  </si>
+  <si>
     <t>Inflation Factor</t>
+  </si>
+  <si>
+    <t>Omar Cooper</t>
   </si>
   <si>
     <t>Aggression</t>
@@ -473,7 +479,58 @@
     <t>League Spent %</t>
   </si>
   <si>
+    <t>Rueben Bain</t>
+  </si>
+  <si>
+    <t>Mike Washington</t>
+  </si>
+  <si>
+    <t>Chris Brazzell</t>
+  </si>
+  <si>
     <t>Enforce % of Fair</t>
+  </si>
+  <si>
+    <t>Anthony Hill</t>
+  </si>
+  <si>
+    <t>Cashius Howell</t>
+  </si>
+  <si>
+    <t>Vinny Anthony</t>
+  </si>
+  <si>
+    <t>Akheem Mesidor</t>
+  </si>
+  <si>
+    <t>Sam Roush</t>
+  </si>
+  <si>
+    <t>A.J. Haulcy</t>
+  </si>
+  <si>
+    <t>Keldric Faulk</t>
+  </si>
+  <si>
+    <t>Peter Woods</t>
+  </si>
+  <si>
+    <t>Kevin Coleman</t>
+  </si>
+  <si>
+    <t>Tanner Koziol</t>
+  </si>
+  <si>
+    <t>John Michael Gyllenborg</t>
+  </si>
+  <si>
+    <t>De'Zhaun Stribling</t>
+  </si>
+  <si>
+    <t>Jeff Caldwell</t>
+  </si>
+  <si>
+    <t>CJ Daniels</t>
   </si>
 </sst>
 </file>
@@ -932,7 +989,7 @@
         <v>1.01</v>
       </c>
       <c r="B2" s="9">
-        <v>7217.0</v>
+        <v>7660.0</v>
       </c>
       <c r="C2" s="10">
         <f t="shared" ref="C2:C73" si="2">1 + --(INT((ROW()-ROW($B$2))/12)=4)
@@ -952,7 +1009,7 @@
         )
     )
 </f>
-        <v>142.9398565</v>
+        <v>133.9537944</v>
       </c>
       <c r="D2" s="10">
         <f t="shared" ref="D2:D73" si="3">( K2
@@ -964,7 +1021,7 @@
      )
   ) / 2
 </f>
-        <v>144</v>
+        <v>134.5</v>
       </c>
       <c r="E2" s="10">
         <f t="shared" ref="E2:E73" si="4">(MEDIAN(F2:H2)+AVERAGE(F2:H2))/2
@@ -982,19 +1039,19 @@
       </c>
       <c r="I2" s="10">
         <f t="shared" ref="I2:I73" si="5">ROUNDDOWN(C2*2,0)</f>
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="J2" s="10">
         <f t="shared" ref="J2:J73" si="6">C2*2 - I2</f>
-        <v>0.8797130175</v>
+        <v>0.9075888904</v>
       </c>
       <c r="K2" s="10">
         <f>I2 + --(RANK(J2,$J$2:$J$73,0) &lt;= 1200*2 - SUM($I$2:$I$73))</f>
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="L2" s="11">
         <f t="shared" ref="L2:L74" si="7">D2</f>
-        <v>144</v>
+        <v>134.5</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
@@ -1003,55 +1060,55 @@
       </c>
       <c r="P2" s="10">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
-        <v>144</v>
+        <v>134.5</v>
       </c>
       <c r="Q2" s="10">
         <f t="shared" si="1"/>
-        <v>114</v>
+        <v>101.5</v>
       </c>
       <c r="R2" s="10">
         <f t="shared" si="1"/>
-        <v>97.5</v>
+        <v>90</v>
       </c>
       <c r="S2" s="10">
         <f t="shared" si="1"/>
-        <v>88.5</v>
+        <v>83</v>
       </c>
       <c r="T2" s="10">
         <f t="shared" si="1"/>
-        <v>79.5</v>
+        <v>72.5</v>
       </c>
       <c r="U2" s="10">
         <f t="shared" si="1"/>
-        <v>73.5</v>
+        <v>65.5</v>
       </c>
       <c r="V2" s="10">
         <f t="shared" si="1"/>
-        <v>59</v>
+        <v>60.5</v>
       </c>
       <c r="W2" s="10">
         <f t="shared" si="1"/>
-        <v>52.5</v>
+        <v>55</v>
       </c>
       <c r="X2" s="10">
         <f t="shared" si="1"/>
-        <v>46.5</v>
+        <v>50.5</v>
       </c>
       <c r="Y2" s="10">
         <f t="shared" si="1"/>
-        <v>41.5</v>
+        <v>45</v>
       </c>
       <c r="Z2" s="10">
         <f t="shared" si="1"/>
-        <v>37.5</v>
+        <v>40.5</v>
       </c>
       <c r="AA2" s="10">
         <f t="shared" si="1"/>
-        <v>33.5</v>
+        <v>36</v>
       </c>
       <c r="AB2" s="10">
         <f t="shared" ref="AB2:AB7" si="9">SUM(P2:AA2)</f>
-        <v>867.5</v>
+        <v>834.5</v>
       </c>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
@@ -1061,15 +1118,15 @@
         <v>1.02</v>
       </c>
       <c r="B3" s="9">
-        <v>5694.0</v>
+        <v>5543.0</v>
       </c>
       <c r="C3" s="10">
         <f t="shared" si="2"/>
-        <v>112.8867548</v>
+        <v>100.9919999</v>
       </c>
       <c r="D3" s="10">
         <f t="shared" si="3"/>
-        <v>114</v>
+        <v>101.5</v>
       </c>
       <c r="E3" s="10">
         <f t="shared" si="4"/>
@@ -1086,11 +1143,11 @@
       </c>
       <c r="I3" s="10">
         <f t="shared" si="5"/>
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="J3" s="10">
         <f t="shared" si="6"/>
-        <v>0.7735096992</v>
+        <v>0.9839998555</v>
       </c>
       <c r="K3" s="10">
         <f t="shared" ref="K3:K73" si="10">MIN(
@@ -1099,11 +1156,11 @@
   K2
 )
 </f>
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="L3" s="11">
         <f t="shared" si="7"/>
-        <v>114</v>
+        <v>101.5</v>
       </c>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
@@ -1112,43 +1169,43 @@
       </c>
       <c r="P3" s="10">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
-        <v>29.5</v>
+        <v>32</v>
       </c>
       <c r="Q3" s="10">
         <f t="shared" si="8"/>
-        <v>25.5</v>
+        <v>29</v>
       </c>
       <c r="R3" s="10">
         <f t="shared" si="8"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="S3" s="10">
         <f t="shared" si="8"/>
-        <v>20.5</v>
+        <v>23.5</v>
       </c>
       <c r="T3" s="10">
         <f t="shared" si="8"/>
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="U3" s="10">
         <f t="shared" si="8"/>
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="V3" s="10">
         <f t="shared" si="8"/>
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="W3" s="10">
         <f t="shared" si="8"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X3" s="10">
         <f t="shared" si="8"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y3" s="10">
         <f t="shared" si="8"/>
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" s="10">
         <f t="shared" si="8"/>
@@ -1160,7 +1217,7 @@
       </c>
       <c r="AB3" s="10">
         <f t="shared" si="9"/>
-        <v>208.5</v>
+        <v>228.5</v>
       </c>
       <c r="AC3" s="5"/>
       <c r="AD3" s="5"/>
@@ -1170,15 +1227,15 @@
         <v>1.03</v>
       </c>
       <c r="B4" s="9">
-        <v>5242.0</v>
+        <v>5428.0</v>
       </c>
       <c r="C4" s="10">
         <f t="shared" si="2"/>
-        <v>96.56525582</v>
+        <v>89.38178209</v>
       </c>
       <c r="D4" s="10">
         <f t="shared" si="3"/>
-        <v>97.5</v>
+        <v>90</v>
       </c>
       <c r="E4" s="10">
         <f t="shared" si="4"/>
@@ -1195,19 +1252,19 @@
       </c>
       <c r="I4" s="10">
         <f t="shared" si="5"/>
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="J4" s="10">
         <f t="shared" si="6"/>
-        <v>0.1305116368</v>
+        <v>0.7635641715</v>
       </c>
       <c r="K4" s="10">
         <f t="shared" si="10"/>
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="L4" s="11">
         <f t="shared" si="7"/>
-        <v>97.5</v>
+        <v>90</v>
       </c>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
@@ -1232,11 +1289,11 @@
       </c>
       <c r="T4" s="10">
         <f t="shared" si="11"/>
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="U4" s="10">
         <f t="shared" si="11"/>
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="V4" s="10">
         <f t="shared" si="11"/>
@@ -1244,11 +1301,11 @@
       </c>
       <c r="W4" s="10">
         <f t="shared" si="11"/>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="X4" s="10">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Y4" s="10">
         <f t="shared" si="11"/>
@@ -1256,7 +1313,7 @@
       </c>
       <c r="Z4" s="10">
         <f t="shared" si="11"/>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AA4" s="10">
         <f t="shared" si="11"/>
@@ -1264,7 +1321,7 @@
       </c>
       <c r="AB4" s="10">
         <f t="shared" si="9"/>
-        <v>68</v>
+        <v>70.5</v>
       </c>
       <c r="AC4" s="5"/>
       <c r="AD4" s="5"/>
@@ -1274,15 +1331,15 @@
         <v>1.04</v>
       </c>
       <c r="B5" s="9">
-        <v>4978.0</v>
+        <v>5351.0</v>
       </c>
       <c r="C5" s="10">
         <f t="shared" si="2"/>
-        <v>87.30618621</v>
+        <v>82.68227902</v>
       </c>
       <c r="D5" s="10">
         <f t="shared" si="3"/>
-        <v>88.5</v>
+        <v>83</v>
       </c>
       <c r="E5" s="10">
         <f t="shared" si="4"/>
@@ -1299,19 +1356,19 @@
       </c>
       <c r="I5" s="10">
         <f t="shared" si="5"/>
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="J5" s="10">
         <f t="shared" si="6"/>
-        <v>0.6123724131</v>
+        <v>0.3645580416</v>
       </c>
       <c r="K5" s="10">
         <f t="shared" si="10"/>
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="L5" s="11">
         <f t="shared" si="7"/>
-        <v>88.5</v>
+        <v>83</v>
       </c>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
@@ -1320,7 +1377,7 @@
       </c>
       <c r="P5" s="10">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q5" s="10">
         <f t="shared" si="12"/>
@@ -1328,11 +1385,11 @@
       </c>
       <c r="R5" s="10">
         <f t="shared" si="12"/>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="S5" s="10">
         <f t="shared" si="12"/>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T5" s="10">
         <f t="shared" si="12"/>
@@ -1340,15 +1397,15 @@
       </c>
       <c r="U5" s="10">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="V5" s="10">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="W5" s="10">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="X5" s="10">
         <f t="shared" si="12"/>
@@ -1356,19 +1413,19 @@
       </c>
       <c r="Y5" s="10">
         <f t="shared" si="12"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Z5" s="10">
         <f t="shared" si="12"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AA5" s="10">
         <f t="shared" si="12"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AB5" s="10">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>30.5</v>
       </c>
       <c r="AC5" s="5"/>
       <c r="AD5" s="5"/>
@@ -1378,15 +1435,15 @@
         <v>1.05</v>
       </c>
       <c r="B6" s="9">
-        <v>4817.0</v>
+        <v>4887.0</v>
       </c>
       <c r="C6" s="10">
         <f t="shared" si="2"/>
-        <v>78.73560269</v>
+        <v>72.01382412</v>
       </c>
       <c r="D6" s="10">
         <f t="shared" si="3"/>
-        <v>79.5</v>
+        <v>72.5</v>
       </c>
       <c r="E6" s="10">
         <f t="shared" si="4"/>
@@ -1403,19 +1460,19 @@
       </c>
       <c r="I6" s="10">
         <f t="shared" si="5"/>
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="J6" s="10">
         <f t="shared" si="6"/>
-        <v>0.4712053753</v>
+        <v>0.02764823796</v>
       </c>
       <c r="K6" s="10">
         <f t="shared" si="10"/>
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="L6" s="11">
         <f t="shared" si="7"/>
-        <v>79.5</v>
+        <v>72.5</v>
       </c>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
@@ -1424,55 +1481,55 @@
       </c>
       <c r="P6" s="10">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="S6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="U6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="V6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="W6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="X6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Y6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Z6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AA6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AB6" s="10">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AC6" s="5"/>
       <c r="AD6" s="5"/>
@@ -1482,15 +1539,15 @@
         <v>1.06</v>
       </c>
       <c r="B7" s="9">
-        <v>4766.0</v>
+        <v>4647.0</v>
       </c>
       <c r="C7" s="10">
         <f t="shared" si="2"/>
-        <v>72.61528198</v>
+        <v>64.85125191</v>
       </c>
       <c r="D7" s="10">
         <f t="shared" si="3"/>
-        <v>73.5</v>
+        <v>65.5</v>
       </c>
       <c r="E7" s="10">
         <f t="shared" si="4"/>
@@ -1507,19 +1564,19 @@
       </c>
       <c r="I7" s="10">
         <f t="shared" si="5"/>
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="J7" s="10">
         <f t="shared" si="6"/>
-        <v>0.2305639522</v>
+        <v>0.7025038107</v>
       </c>
       <c r="K7" s="10">
         <f t="shared" si="10"/>
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="L7" s="11">
         <f t="shared" si="7"/>
-        <v>73.5</v>
+        <v>65.5</v>
       </c>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
@@ -1586,15 +1643,15 @@
         <v>1.07</v>
       </c>
       <c r="B8" s="9">
-        <v>3703.0</v>
+        <v>4640.0</v>
       </c>
       <c r="C8" s="10">
         <f t="shared" si="2"/>
-        <v>57.79151562</v>
+        <v>59.95933081</v>
       </c>
       <c r="D8" s="10">
         <f t="shared" si="3"/>
-        <v>59</v>
+        <v>60.5</v>
       </c>
       <c r="E8" s="10">
         <f t="shared" si="4"/>
@@ -1611,70 +1668,70 @@
       </c>
       <c r="I8" s="10">
         <f t="shared" si="5"/>
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="J8" s="10">
         <f t="shared" si="6"/>
-        <v>0.5830312392</v>
+        <v>0.9186616216</v>
       </c>
       <c r="K8" s="10">
         <f t="shared" si="10"/>
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="L8" s="11">
         <f t="shared" si="7"/>
-        <v>59</v>
+        <v>60.5</v>
       </c>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
       <c r="P8" s="10">
         <f t="shared" ref="P8:AB8" si="15">SUM(P2:P7)</f>
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="Q8" s="10">
         <f t="shared" si="15"/>
-        <v>153.5</v>
+        <v>145</v>
       </c>
       <c r="R8" s="10">
         <f t="shared" si="15"/>
-        <v>133</v>
+        <v>129.5</v>
       </c>
       <c r="S8" s="10">
         <f t="shared" si="15"/>
-        <v>121</v>
+        <v>119.5</v>
       </c>
       <c r="T8" s="10">
         <f t="shared" si="15"/>
-        <v>109</v>
+        <v>105.5</v>
       </c>
       <c r="U8" s="10">
         <f t="shared" si="15"/>
-        <v>100.5</v>
+        <v>95.5</v>
       </c>
       <c r="V8" s="10">
         <f t="shared" si="15"/>
-        <v>84</v>
+        <v>87.5</v>
       </c>
       <c r="W8" s="10">
         <f t="shared" si="15"/>
-        <v>75.5</v>
+        <v>80.5</v>
       </c>
       <c r="X8" s="10">
         <f t="shared" si="15"/>
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="Y8" s="10">
         <f t="shared" si="15"/>
-        <v>61</v>
+        <v>66.5</v>
       </c>
       <c r="Z8" s="10">
         <f t="shared" si="15"/>
-        <v>55.5</v>
+        <v>60</v>
       </c>
       <c r="AA8" s="10">
         <f t="shared" si="15"/>
-        <v>51</v>
+        <v>54.5</v>
       </c>
       <c r="AB8" s="10">
         <f t="shared" si="15"/>
@@ -1688,15 +1745,15 @@
         <v>1.08</v>
       </c>
       <c r="B9" s="9">
-        <v>3406.0</v>
+        <v>4440.0</v>
       </c>
       <c r="C9" s="10">
         <f t="shared" si="2"/>
-        <v>51.27650378</v>
+        <v>54.36054894</v>
       </c>
       <c r="D9" s="10">
         <f t="shared" si="3"/>
-        <v>52.5</v>
+        <v>55</v>
       </c>
       <c r="E9" s="10">
         <f t="shared" si="4"/>
@@ -1713,19 +1770,19 @@
       </c>
       <c r="I9" s="10">
         <f t="shared" si="5"/>
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="J9" s="10">
         <f t="shared" si="6"/>
-        <v>0.5530075617</v>
+        <v>0.7210978795</v>
       </c>
       <c r="K9" s="10">
         <f t="shared" si="10"/>
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="L9" s="11">
         <f t="shared" si="7"/>
-        <v>52.5</v>
+        <v>55</v>
       </c>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
@@ -1751,15 +1808,15 @@
         <v>1.09</v>
       </c>
       <c r="B10" s="9">
-        <v>3168.0</v>
+        <v>4352.0</v>
       </c>
       <c r="C10" s="10">
         <f t="shared" si="2"/>
-        <v>45.61910024</v>
+        <v>49.76603403</v>
       </c>
       <c r="D10" s="10">
         <f t="shared" si="3"/>
-        <v>46.5</v>
+        <v>50.5</v>
       </c>
       <c r="E10" s="10">
         <f t="shared" si="4"/>
@@ -1776,19 +1833,19 @@
       </c>
       <c r="I10" s="10">
         <f t="shared" si="5"/>
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="J10" s="10">
         <f t="shared" si="6"/>
-        <v>0.2382004809</v>
+        <v>0.5320680636</v>
       </c>
       <c r="K10" s="10">
         <f t="shared" si="10"/>
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="L10" s="11">
         <f t="shared" si="7"/>
-        <v>46.5</v>
+        <v>50.5</v>
       </c>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
@@ -1814,15 +1871,15 @@
         <v>1.1</v>
       </c>
       <c r="B11" s="9">
-        <v>3119.0</v>
+        <v>4277.0</v>
       </c>
       <c r="C11" s="10">
         <f t="shared" si="2"/>
-        <v>40.63096022</v>
+        <v>44.38780232</v>
       </c>
       <c r="D11" s="10">
         <f t="shared" si="3"/>
-        <v>41.5</v>
+        <v>45</v>
       </c>
       <c r="E11" s="10">
         <f t="shared" si="4"/>
@@ -1839,19 +1896,19 @@
       </c>
       <c r="I11" s="10">
         <f t="shared" si="5"/>
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J11" s="10">
         <f t="shared" si="6"/>
-        <v>0.2619204444</v>
+        <v>0.7756046318</v>
       </c>
       <c r="K11" s="10">
         <f t="shared" si="10"/>
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="L11" s="11">
         <f t="shared" si="7"/>
-        <v>41.5</v>
+        <v>45</v>
       </c>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -1877,15 +1934,15 @@
         <v>1.11</v>
       </c>
       <c r="B12" s="9">
-        <v>2960.0</v>
+        <v>4071.0</v>
       </c>
       <c r="C12" s="10">
         <f t="shared" si="2"/>
-        <v>36.61431272</v>
+        <v>40.0016894</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="3"/>
-        <v>37.5</v>
+        <v>40.5</v>
       </c>
       <c r="E12" s="10">
         <f t="shared" si="4"/>
@@ -1902,19 +1959,19 @@
       </c>
       <c r="I12" s="10">
         <f t="shared" si="5"/>
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="J12" s="10">
         <f t="shared" si="6"/>
-        <v>0.2286254402</v>
+        <v>0.003378792016</v>
       </c>
       <c r="K12" s="10">
         <f t="shared" si="10"/>
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L12" s="11">
         <f t="shared" si="7"/>
-        <v>37.5</v>
+        <v>40.5</v>
       </c>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
@@ -1940,15 +1997,15 @@
         <v>1.12</v>
       </c>
       <c r="B13" s="9">
-        <v>2862.0</v>
+        <v>3962.0</v>
       </c>
       <c r="C13" s="10">
         <f t="shared" si="2"/>
-        <v>32.3349513</v>
+        <v>35.51785008</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="3"/>
-        <v>33.5</v>
+        <v>36</v>
       </c>
       <c r="E13" s="10">
         <f t="shared" si="4"/>
@@ -1965,19 +2022,19 @@
       </c>
       <c r="I13" s="10">
         <f t="shared" si="5"/>
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="J13" s="10">
         <f t="shared" si="6"/>
-        <v>0.6699025904</v>
+        <v>0.03570016782</v>
       </c>
       <c r="K13" s="10">
         <f t="shared" si="10"/>
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="L13" s="11">
         <f t="shared" si="7"/>
-        <v>33.5</v>
+        <v>36</v>
       </c>
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
@@ -2003,15 +2060,15 @@
         <v>2.01</v>
       </c>
       <c r="B14" s="9">
-        <v>2843.0</v>
+        <v>3841.0</v>
       </c>
       <c r="C14" s="10">
         <f t="shared" si="2"/>
-        <v>29.30993478</v>
+        <v>31.77784632</v>
       </c>
       <c r="D14" s="10">
         <f t="shared" si="3"/>
-        <v>29.5</v>
+        <v>32</v>
       </c>
       <c r="E14" s="10">
         <f t="shared" si="4"/>
@@ -2028,19 +2085,19 @@
       </c>
       <c r="I14" s="10">
         <f t="shared" si="5"/>
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J14" s="10">
         <f t="shared" si="6"/>
-        <v>0.6198695618</v>
+        <v>0.555692644</v>
       </c>
       <c r="K14" s="10">
         <f t="shared" si="10"/>
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="L14" s="11">
         <f t="shared" si="7"/>
-        <v>29.5</v>
+        <v>32</v>
       </c>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
@@ -2066,15 +2123,15 @@
         <v>2.02</v>
       </c>
       <c r="B15" s="9">
-        <v>2606.0</v>
+        <v>3808.0</v>
       </c>
       <c r="C15" s="10">
         <f t="shared" si="2"/>
-        <v>25.46237165</v>
+        <v>28.88389075</v>
       </c>
       <c r="D15" s="10">
         <f t="shared" si="3"/>
-        <v>25.5</v>
+        <v>29</v>
       </c>
       <c r="E15" s="10">
         <f t="shared" si="4"/>
@@ -2091,19 +2148,19 @@
       </c>
       <c r="I15" s="10">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="J15" s="10">
         <f t="shared" si="6"/>
-        <v>0.9247432916</v>
+        <v>0.7677815012</v>
       </c>
       <c r="K15" s="10">
         <f t="shared" si="10"/>
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="L15" s="11">
         <f t="shared" si="7"/>
-        <v>25.5</v>
+        <v>29</v>
       </c>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
@@ -2129,15 +2186,15 @@
         <v>2.03</v>
       </c>
       <c r="B16" s="9">
-        <v>2511.0</v>
+        <v>3683.0</v>
       </c>
       <c r="C16" s="10">
         <f t="shared" si="2"/>
-        <v>23.11342237</v>
+        <v>26.23082668</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E16" s="10">
         <f t="shared" si="4"/>
@@ -2154,19 +2211,19 @@
       </c>
       <c r="I16" s="10">
         <f t="shared" si="5"/>
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J16" s="10">
         <f t="shared" si="6"/>
-        <v>0.2268447433</v>
+        <v>0.4616533503</v>
       </c>
       <c r="K16" s="10">
         <f t="shared" si="10"/>
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="L16" s="11">
         <f t="shared" si="7"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
@@ -2192,15 +2249,15 @@
         <v>2.04</v>
       </c>
       <c r="B17" s="9">
-        <v>2309.0</v>
+        <v>3508.0</v>
       </c>
       <c r="C17" s="10">
         <f t="shared" si="2"/>
-        <v>20.33706605</v>
+        <v>23.47489006</v>
       </c>
       <c r="D17" s="10">
         <f t="shared" si="3"/>
-        <v>20.5</v>
+        <v>23.5</v>
       </c>
       <c r="E17" s="10">
         <f t="shared" si="4"/>
@@ -2217,19 +2274,19 @@
       </c>
       <c r="I17" s="10">
         <f t="shared" si="5"/>
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J17" s="10">
         <f t="shared" si="6"/>
-        <v>0.6741321066</v>
+        <v>0.9497801196</v>
       </c>
       <c r="K17" s="10">
         <f t="shared" si="10"/>
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L17" s="11">
         <f t="shared" si="7"/>
-        <v>20.5</v>
+        <v>23.5</v>
       </c>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
@@ -2255,15 +2312,15 @@
         <v>2.05</v>
       </c>
       <c r="B18" s="9">
-        <v>2298.0</v>
+        <v>3440.0</v>
       </c>
       <c r="C18" s="10">
         <f t="shared" si="2"/>
-        <v>18.48529164</v>
+        <v>21.1911087</v>
       </c>
       <c r="D18" s="10">
         <f t="shared" si="3"/>
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="E18" s="10">
         <f t="shared" si="4"/>
@@ -2280,19 +2337,19 @@
       </c>
       <c r="I18" s="10">
         <f t="shared" si="5"/>
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J18" s="10">
         <f t="shared" si="6"/>
-        <v>0.9705832755</v>
+        <v>0.3822174041</v>
       </c>
       <c r="K18" s="10">
         <f t="shared" si="10"/>
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L18" s="11">
         <f t="shared" si="7"/>
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="M18" s="7"/>
       <c r="N18" s="7"/>
@@ -2318,15 +2375,15 @@
         <v>2.06</v>
       </c>
       <c r="B19" s="9">
-        <v>2297.0</v>
+        <v>3140.0</v>
       </c>
       <c r="C19" s="10">
         <f t="shared" si="2"/>
-        <v>17.16034899</v>
+        <v>18.65149366</v>
       </c>
       <c r="D19" s="10">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="E19" s="10">
         <f t="shared" si="4"/>
@@ -2343,19 +2400,19 @@
       </c>
       <c r="I19" s="10">
         <f t="shared" si="5"/>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J19" s="10">
         <f t="shared" si="6"/>
-        <v>0.3206979856</v>
+        <v>0.3029873246</v>
       </c>
       <c r="K19" s="10">
         <f t="shared" si="10"/>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L19" s="11">
         <f t="shared" si="7"/>
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="M19" s="7"/>
       <c r="N19" s="7"/>
@@ -2381,15 +2438,15 @@
         <v>2.07</v>
       </c>
       <c r="B20" s="9">
-        <v>2181.0</v>
+        <v>3024.0</v>
       </c>
       <c r="C20" s="10">
         <f t="shared" si="2"/>
-        <v>15.29720081</v>
+        <v>16.74204307</v>
       </c>
       <c r="D20" s="10">
         <f t="shared" si="3"/>
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="E20" s="10">
         <f t="shared" si="4"/>
@@ -2406,19 +2463,19 @@
       </c>
       <c r="I20" s="10">
         <f t="shared" si="5"/>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J20" s="10">
         <f t="shared" si="6"/>
-        <v>0.594401616</v>
+        <v>0.4840861454</v>
       </c>
       <c r="K20" s="10">
         <f t="shared" si="10"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L20" s="11">
         <f t="shared" si="7"/>
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="M20" s="7"/>
       <c r="N20" s="7"/>
@@ -2444,15 +2501,15 @@
         <v>2.08</v>
       </c>
       <c r="B21" s="9">
-        <v>2172.0</v>
+        <v>2901.0</v>
       </c>
       <c r="C21" s="10">
         <f t="shared" si="2"/>
-        <v>14.10861256</v>
+        <v>15.11863921</v>
       </c>
       <c r="D21" s="10">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" s="10">
         <f t="shared" si="4"/>
@@ -2469,19 +2526,19 @@
       </c>
       <c r="I21" s="10">
         <f t="shared" si="5"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J21" s="10">
         <f t="shared" si="6"/>
-        <v>0.2172251176</v>
+        <v>0.2372784142</v>
       </c>
       <c r="K21" s="10">
         <f t="shared" si="10"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L21" s="11">
         <f t="shared" si="7"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M21" s="7"/>
       <c r="N21" s="7"/>
@@ -2507,15 +2564,15 @@
         <v>2.09</v>
       </c>
       <c r="B22" s="9">
-        <v>2147.0</v>
+        <v>2887.0</v>
       </c>
       <c r="C22" s="10">
         <f t="shared" si="2"/>
-        <v>12.8837063</v>
+        <v>13.85976068</v>
       </c>
       <c r="D22" s="10">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E22" s="10">
         <f t="shared" si="4"/>
@@ -2532,19 +2589,19 @@
       </c>
       <c r="I22" s="10">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J22" s="10">
         <f t="shared" si="6"/>
-        <v>0.7674126043</v>
+        <v>0.719521356</v>
       </c>
       <c r="K22" s="10">
         <f t="shared" si="10"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L22" s="11">
         <f t="shared" si="7"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
@@ -2570,15 +2627,15 @@
         <v>2.1</v>
       </c>
       <c r="B23" s="9">
-        <v>2052.0</v>
+        <v>2769.0</v>
       </c>
       <c r="C23" s="10">
         <f t="shared" si="2"/>
-        <v>11.40694705</v>
+        <v>12.29417089</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="3"/>
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="E23" s="10">
         <f t="shared" si="4"/>
@@ -2595,19 +2652,19 @@
       </c>
       <c r="I23" s="10">
         <f t="shared" si="5"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J23" s="10">
         <f t="shared" si="6"/>
-        <v>0.8138941019</v>
+        <v>0.5883417803</v>
       </c>
       <c r="K23" s="10">
         <f t="shared" si="10"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L23" s="11">
         <f t="shared" si="7"/>
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="M23" s="7"/>
       <c r="N23" s="7"/>
@@ -2633,11 +2690,11 @@
         <v>2.11</v>
       </c>
       <c r="B24" s="9">
-        <v>2039.0</v>
+        <v>2446.0</v>
       </c>
       <c r="C24" s="10">
         <f t="shared" si="2"/>
-        <v>10.52619418</v>
+        <v>10.63754613</v>
       </c>
       <c r="D24" s="10">
         <f t="shared" si="3"/>
@@ -2662,7 +2719,7 @@
       </c>
       <c r="J24" s="10">
         <f t="shared" si="6"/>
-        <v>0.05238836607</v>
+        <v>0.2750922692</v>
       </c>
       <c r="K24" s="10">
         <f t="shared" si="10"/>
@@ -2696,11 +2753,11 @@
         <v>2.12</v>
       </c>
       <c r="B25" s="9">
-        <v>2033.0</v>
+        <v>2436.0</v>
       </c>
       <c r="C25" s="10">
         <f t="shared" si="2"/>
-        <v>9.865135699</v>
+        <v>9.961820154</v>
       </c>
       <c r="D25" s="10">
         <f t="shared" si="3"/>
@@ -2725,7 +2782,7 @@
       </c>
       <c r="J25" s="10">
         <f t="shared" si="6"/>
-        <v>0.7302713983</v>
+        <v>0.923640308</v>
       </c>
       <c r="K25" s="10">
         <f t="shared" si="10"/>
@@ -2759,11 +2816,11 @@
         <v>3.01</v>
       </c>
       <c r="B26" s="9">
-        <v>2002.0</v>
+        <v>2412.0</v>
       </c>
       <c r="C26" s="10">
         <f t="shared" si="2"/>
-        <v>9.014995044</v>
+        <v>9.128907957</v>
       </c>
       <c r="D26" s="10">
         <f t="shared" si="3"/>
@@ -2788,7 +2845,7 @@
       </c>
       <c r="J26" s="10">
         <f t="shared" si="6"/>
-        <v>0.02999008892</v>
+        <v>0.2578159146</v>
       </c>
       <c r="K26" s="10">
         <f t="shared" si="10"/>
@@ -2822,11 +2879,11 @@
         <v>3.02</v>
       </c>
       <c r="B27" s="9">
-        <v>1943.0</v>
+        <v>2367.0</v>
       </c>
       <c r="C27" s="10">
         <f t="shared" si="2"/>
-        <v>8.275286279</v>
+        <v>8.424966136</v>
       </c>
       <c r="D27" s="10">
         <f t="shared" si="3"/>
@@ -2851,7 +2908,7 @@
       </c>
       <c r="J27" s="10">
         <f t="shared" si="6"/>
-        <v>0.5505725575</v>
+        <v>0.8499322724</v>
       </c>
       <c r="K27" s="10">
         <f t="shared" si="10"/>
@@ -2885,11 +2942,11 @@
         <v>3.03</v>
       </c>
       <c r="B28" s="9">
-        <v>1864.0</v>
+        <v>2319.0</v>
       </c>
       <c r="C28" s="10">
         <f t="shared" si="2"/>
-        <v>7.442787032</v>
+        <v>7.656667123</v>
       </c>
       <c r="D28" s="10">
         <f t="shared" si="3"/>
@@ -2910,11 +2967,11 @@
       </c>
       <c r="I28" s="10">
         <f t="shared" si="5"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J28" s="10">
         <f t="shared" si="6"/>
-        <v>0.885574063</v>
+        <v>0.3133342455</v>
       </c>
       <c r="K28" s="10">
         <f t="shared" si="10"/>
@@ -2948,11 +3005,11 @@
         <v>3.04</v>
       </c>
       <c r="B29" s="9">
-        <v>1848.0</v>
+        <v>2190.0</v>
       </c>
       <c r="C29" s="10">
         <f t="shared" si="2"/>
-        <v>6.838272684</v>
+        <v>6.864574946</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="3"/>
@@ -2977,7 +3034,7 @@
       </c>
       <c r="J29" s="10">
         <f t="shared" si="6"/>
-        <v>0.6765453679</v>
+        <v>0.729149893</v>
       </c>
       <c r="K29" s="10">
         <f t="shared" si="10"/>
@@ -3029,15 +3086,15 @@
         <v>3.05</v>
       </c>
       <c r="B30" s="9">
-        <v>1727.0</v>
+        <v>2125.0</v>
       </c>
       <c r="C30" s="10">
         <f t="shared" si="2"/>
-        <v>6.180107027</v>
+        <v>6.315443152</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="E30" s="10">
         <f t="shared" si="4"/>
@@ -3058,15 +3115,15 @@
       </c>
       <c r="J30" s="10">
         <f t="shared" si="6"/>
-        <v>0.3602140542</v>
+        <v>0.6308863033</v>
       </c>
       <c r="K30" s="10">
         <f t="shared" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L30" s="11">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="M30" s="7"/>
       <c r="N30" s="7"/>
@@ -3110,15 +3167,15 @@
         <v>3.06</v>
       </c>
       <c r="B31" s="9">
-        <v>1709.0</v>
+        <v>2094.0</v>
       </c>
       <c r="C31" s="10">
         <f t="shared" si="2"/>
-        <v>5.73308862</v>
+        <v>5.845066575</v>
       </c>
       <c r="D31" s="10">
         <f t="shared" si="3"/>
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="E31" s="10">
         <f t="shared" si="4"/>
@@ -3139,15 +3196,15 @@
       </c>
       <c r="J31" s="10">
         <f t="shared" si="6"/>
-        <v>0.4661772408</v>
+        <v>0.6901331501</v>
       </c>
       <c r="K31" s="10">
         <f t="shared" si="10"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L31" s="11">
         <f t="shared" si="7"/>
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="M31" s="7"/>
       <c r="N31" s="7"/>
@@ -3191,11 +3248,11 @@
         <v>3.07</v>
       </c>
       <c r="B32" s="9">
-        <v>1567.0</v>
+        <v>2061.0</v>
       </c>
       <c r="C32" s="10">
         <f t="shared" si="2"/>
-        <v>4.964321669</v>
+        <v>5.23203327</v>
       </c>
       <c r="D32" s="10">
         <f t="shared" si="3"/>
@@ -3216,11 +3273,11 @@
       </c>
       <c r="I32" s="10">
         <f t="shared" si="5"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J32" s="10">
         <f t="shared" si="6"/>
-        <v>0.9286433373</v>
+        <v>0.4640665396</v>
       </c>
       <c r="K32" s="10">
         <f t="shared" si="10"/>
@@ -3272,15 +3329,15 @@
         <v>3.08</v>
       </c>
       <c r="B33" s="9">
-        <v>1496.0</v>
+        <v>1957.0</v>
       </c>
       <c r="C33" s="10">
         <f t="shared" si="2"/>
-        <v>4.533414863</v>
+        <v>4.757468998</v>
       </c>
       <c r="D33" s="10">
         <f t="shared" si="3"/>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="E33" s="10">
         <f t="shared" si="4"/>
@@ -3301,15 +3358,15 @@
       </c>
       <c r="J33" s="10">
         <f t="shared" si="6"/>
-        <v>0.06682972679</v>
+        <v>0.5149379963</v>
       </c>
       <c r="K33" s="10">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L33" s="11">
         <f t="shared" si="7"/>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -3353,15 +3410,15 @@
         <v>3.09</v>
       </c>
       <c r="B34" s="9">
-        <v>1422.0</v>
+        <v>1907.0</v>
       </c>
       <c r="C34" s="10">
         <f t="shared" si="2"/>
-        <v>4.093491503</v>
+        <v>4.339154724</v>
       </c>
       <c r="D34" s="10">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="E34" s="10">
         <f t="shared" si="4"/>
@@ -3382,15 +3439,15 @@
       </c>
       <c r="J34" s="10">
         <f t="shared" si="6"/>
-        <v>0.1869830063</v>
+        <v>0.678309448</v>
       </c>
       <c r="K34" s="10">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L34" s="11">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="M34" s="7"/>
       <c r="N34" s="7"/>
@@ -3434,11 +3491,11 @@
         <v>3.1</v>
       </c>
       <c r="B35" s="9">
-        <v>1324.0</v>
+        <v>1865.0</v>
       </c>
       <c r="C35" s="10">
         <f t="shared" si="2"/>
-        <v>3.815681967</v>
+        <v>4.113323206</v>
       </c>
       <c r="D35" s="10">
         <f t="shared" si="3"/>
@@ -3459,11 +3516,11 @@
       </c>
       <c r="I35" s="10">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J35" s="10">
         <f t="shared" si="6"/>
-        <v>0.6313639344</v>
+        <v>0.2266464123</v>
       </c>
       <c r="K35" s="10">
         <f t="shared" si="10"/>
@@ -3515,15 +3572,15 @@
         <v>3.11</v>
       </c>
       <c r="B36" s="9">
-        <v>1243.0</v>
+        <v>1837.0</v>
       </c>
       <c r="C36" s="10">
         <f t="shared" si="2"/>
-        <v>3.418924443</v>
+        <v>3.753799375</v>
       </c>
       <c r="D36" s="10">
         <f t="shared" si="3"/>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E36" s="10">
         <f t="shared" si="4"/>
@@ -3540,19 +3597,19 @@
       </c>
       <c r="I36" s="10">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J36" s="10">
         <f t="shared" si="6"/>
-        <v>0.8378488865</v>
+        <v>0.5075987505</v>
       </c>
       <c r="K36" s="10">
         <f t="shared" si="10"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L36" s="11">
         <f t="shared" si="7"/>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="M36" s="7"/>
       <c r="N36" s="7"/>
@@ -3596,11 +3653,11 @@
         <v>3.12</v>
       </c>
       <c r="B37" s="9">
-        <v>1239.0</v>
+        <v>1782.0</v>
       </c>
       <c r="C37" s="10">
         <f t="shared" si="2"/>
-        <v>3.315249116</v>
+        <v>3.58305667</v>
       </c>
       <c r="D37" s="10">
         <f t="shared" si="3"/>
@@ -3621,11 +3678,11 @@
       </c>
       <c r="I37" s="10">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J37" s="10">
         <f t="shared" si="6"/>
-        <v>0.6304982319</v>
+        <v>0.1661133392</v>
       </c>
       <c r="K37" s="10">
         <f t="shared" si="10"/>
@@ -3677,15 +3734,15 @@
         <v>4.01</v>
       </c>
       <c r="B38" s="9">
-        <v>1200.0</v>
+        <v>1771.0</v>
       </c>
       <c r="C38" s="10">
         <f t="shared" si="2"/>
-        <v>3.024494573</v>
+        <v>3.298318867</v>
       </c>
       <c r="D38" s="10">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E38" s="10">
         <f t="shared" si="4"/>
@@ -3706,15 +3763,15 @@
       </c>
       <c r="J38" s="10">
         <f t="shared" si="6"/>
-        <v>0.04898914558</v>
+        <v>0.5966377345</v>
       </c>
       <c r="K38" s="10">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L38" s="11">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="M38" s="7"/>
       <c r="N38" s="7"/>
@@ -3758,11 +3815,11 @@
         <v>4.02</v>
       </c>
       <c r="B39" s="9">
-        <v>1181.0</v>
+        <v>1714.0</v>
       </c>
       <c r="C39" s="10">
         <f t="shared" si="2"/>
-        <v>2.893765735</v>
+        <v>3.122265286</v>
       </c>
       <c r="D39" s="10">
         <f t="shared" si="3"/>
@@ -3783,11 +3840,11 @@
       </c>
       <c r="I39" s="10">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J39" s="10">
         <f t="shared" si="6"/>
-        <v>0.787531469</v>
+        <v>0.2445305714</v>
       </c>
       <c r="K39" s="10">
         <f t="shared" si="10"/>
@@ -3839,15 +3896,15 @@
         <v>4.03</v>
       </c>
       <c r="B40" s="9">
-        <v>1179.0</v>
+        <v>1683.0</v>
       </c>
       <c r="C40" s="10">
         <f t="shared" si="2"/>
-        <v>2.653520379</v>
+        <v>2.845924425</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="3"/>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E40" s="10">
         <f t="shared" si="4"/>
@@ -3868,15 +3925,15 @@
       </c>
       <c r="J40" s="10">
         <f t="shared" si="6"/>
-        <v>0.3070407576</v>
+        <v>0.6918488493</v>
       </c>
       <c r="K40" s="10">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L40" s="11">
         <f t="shared" si="7"/>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M40" s="7"/>
       <c r="N40" s="7"/>
@@ -3920,15 +3977,15 @@
         <v>4.04</v>
       </c>
       <c r="B41" s="9">
-        <v>1157.0</v>
+        <v>1672.0</v>
       </c>
       <c r="C41" s="10">
         <f t="shared" si="2"/>
-        <v>2.569076196</v>
+        <v>2.75563629</v>
       </c>
       <c r="D41" s="10">
         <f t="shared" si="3"/>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E41" s="10">
         <f t="shared" si="4"/>
@@ -3949,15 +4006,15 @@
       </c>
       <c r="J41" s="10">
         <f t="shared" si="6"/>
-        <v>0.1381523915</v>
+        <v>0.5112725794</v>
       </c>
       <c r="K41" s="10">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L41" s="11">
         <f t="shared" si="7"/>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
@@ -4000,12 +4057,12 @@
       <c r="A42" s="8">
         <v>4.05</v>
       </c>
-      <c r="B42" s="9">
-        <v>1139.0</v>
+      <c r="B42" s="13">
+        <v>1619.0</v>
       </c>
       <c r="C42" s="10">
         <f t="shared" si="2"/>
-        <v>2.330926417</v>
+        <v>2.485574312</v>
       </c>
       <c r="D42" s="10">
         <f t="shared" si="3"/>
@@ -4030,7 +4087,7 @@
       </c>
       <c r="J42" s="10">
         <f t="shared" si="6"/>
-        <v>0.6618528346</v>
+        <v>0.9711486246</v>
       </c>
       <c r="K42" s="10">
         <f t="shared" si="10"/>
@@ -4073,15 +4130,15 @@
         <v>4.06</v>
       </c>
       <c r="B43" s="9">
-        <v>1033.0</v>
+        <v>1601.0</v>
       </c>
       <c r="C43" s="10">
         <f t="shared" si="2"/>
-        <v>2.177670043</v>
+        <v>2.374909263</v>
       </c>
       <c r="D43" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E43" s="10">
         <f t="shared" si="4"/>
@@ -4102,15 +4159,15 @@
       </c>
       <c r="J43" s="10">
         <f t="shared" si="6"/>
-        <v>0.3553400854</v>
+        <v>0.7498185261</v>
       </c>
       <c r="K43" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L43" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M43" s="7"/>
       <c r="N43" s="7"/>
@@ -4145,15 +4202,15 @@
         <v>4.07</v>
       </c>
       <c r="B44" s="9">
-        <v>1003.0</v>
+        <v>1596.0</v>
       </c>
       <c r="C44" s="10">
         <f t="shared" si="2"/>
-        <v>2.11344734</v>
+        <v>2.309825789</v>
       </c>
       <c r="D44" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E44" s="10">
         <f t="shared" si="4"/>
@@ -4174,15 +4231,15 @@
       </c>
       <c r="J44" s="10">
         <f t="shared" si="6"/>
-        <v>0.2268946793</v>
+        <v>0.6196515786</v>
       </c>
       <c r="K44" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L44" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
@@ -4225,15 +4282,15 @@
         <v>4.08</v>
       </c>
       <c r="B45" s="9">
-        <v>912.0</v>
+        <v>1593.0</v>
       </c>
       <c r="C45" s="10">
         <f t="shared" si="2"/>
-        <v>2.024198752</v>
+        <v>2.250774638</v>
       </c>
       <c r="D45" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E45" s="10">
         <f t="shared" si="4"/>
@@ -4254,15 +4311,15 @@
       </c>
       <c r="J45" s="10">
         <f t="shared" si="6"/>
-        <v>0.0483975038</v>
+        <v>0.5015492767</v>
       </c>
       <c r="K45" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L45" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
@@ -4281,7 +4338,7 @@
    INDEX($P$2:$AA$7,O45,P45) * $AD$1
 )
 </f>
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="R45" s="7" t="str">
         <f t="shared" ref="R45:R116" si="21">IF(
@@ -4325,11 +4382,11 @@
         <v>4.09</v>
       </c>
       <c r="B46" s="9">
-        <v>908.0</v>
+        <v>1506.0</v>
       </c>
       <c r="C46" s="10">
         <f t="shared" si="2"/>
-        <v>1.822528617</v>
+        <v>1.998642088</v>
       </c>
       <c r="D46" s="10">
         <f t="shared" si="3"/>
@@ -4354,7 +4411,7 @@
       </c>
       <c r="J46" s="10">
         <f t="shared" si="6"/>
-        <v>0.6450572349</v>
+        <v>0.9972841761</v>
       </c>
       <c r="K46" s="10">
         <f t="shared" si="10"/>
@@ -4376,7 +4433,7 @@
       </c>
       <c r="Q46" s="10">
         <f t="shared" si="20"/>
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="R46" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4409,15 +4466,15 @@
         <v>4.1</v>
       </c>
       <c r="B47" s="9">
-        <v>873.0</v>
+        <v>1502.0</v>
       </c>
       <c r="C47" s="10">
         <f t="shared" si="2"/>
-        <v>1.741528916</v>
+        <v>1.917905501</v>
       </c>
       <c r="D47" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E47" s="10">
         <f t="shared" si="4"/>
@@ -4438,15 +4495,15 @@
       </c>
       <c r="J47" s="10">
         <f t="shared" si="6"/>
-        <v>0.4830578314</v>
+        <v>0.8358110019</v>
       </c>
       <c r="K47" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L47" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
@@ -4460,7 +4517,7 @@
       </c>
       <c r="Q47" s="10">
         <f t="shared" si="20"/>
-        <v>97.5</v>
+        <v>90</v>
       </c>
       <c r="R47" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4493,15 +4550,15 @@
         <v>4.11</v>
       </c>
       <c r="B48" s="9">
-        <v>838.0</v>
+        <v>1359.0</v>
       </c>
       <c r="C48" s="10">
         <f t="shared" si="2"/>
-        <v>1.698188288</v>
+        <v>1.82614015</v>
       </c>
       <c r="D48" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E48" s="10">
         <f t="shared" si="4"/>
@@ -4522,15 +4579,15 @@
       </c>
       <c r="J48" s="10">
         <f t="shared" si="6"/>
-        <v>0.3963765755</v>
+        <v>0.6522802998</v>
       </c>
       <c r="K48" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L48" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M48" s="7"/>
       <c r="N48" s="7"/>
@@ -4544,7 +4601,7 @@
       </c>
       <c r="Q48" s="10">
         <f t="shared" si="20"/>
-        <v>88.5</v>
+        <v>83</v>
       </c>
       <c r="R48" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4577,15 +4634,15 @@
         <v>4.12</v>
       </c>
       <c r="B49" s="9">
-        <v>804.0</v>
+        <v>1327.0</v>
       </c>
       <c r="C49" s="10">
         <f t="shared" si="2"/>
-        <v>1.659626544</v>
+        <v>1.780275243</v>
       </c>
       <c r="D49" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E49" s="10">
         <f t="shared" si="4"/>
@@ -4606,15 +4663,15 @@
       </c>
       <c r="J49" s="10">
         <f t="shared" si="6"/>
-        <v>0.319253089</v>
+        <v>0.5605504851</v>
       </c>
       <c r="K49" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L49" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M49" s="7"/>
       <c r="N49" s="7"/>
@@ -4628,7 +4685,7 @@
       </c>
       <c r="Q49" s="10">
         <f t="shared" si="20"/>
-        <v>79.5</v>
+        <v>72.5</v>
       </c>
       <c r="R49" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4661,15 +4718,15 @@
         <v>5.01</v>
       </c>
       <c r="B50" s="9">
-        <v>771.0</v>
+        <v>1326.0</v>
       </c>
       <c r="C50" s="10">
         <f t="shared" si="2"/>
-        <v>2.625337768</v>
+        <v>2.747755044</v>
       </c>
       <c r="D50" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E50" s="10">
         <f t="shared" si="4"/>
@@ -4690,15 +4747,15 @@
       </c>
       <c r="J50" s="10">
         <f t="shared" si="6"/>
-        <v>0.2506755353</v>
+        <v>0.4955100887</v>
       </c>
       <c r="K50" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L50" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M50" s="7"/>
       <c r="N50" s="7"/>
@@ -4712,7 +4769,7 @@
       </c>
       <c r="Q50" s="10">
         <f t="shared" si="20"/>
-        <v>73.5</v>
+        <v>65.5</v>
       </c>
       <c r="R50" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4745,15 +4802,15 @@
         <v>5.02</v>
       </c>
       <c r="B51" s="9">
-        <v>739.0</v>
+        <v>1314.0</v>
       </c>
       <c r="C51" s="10">
         <f t="shared" si="2"/>
-        <v>2.594867507</v>
+        <v>2.714787569</v>
       </c>
       <c r="D51" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E51" s="10">
         <f t="shared" si="4"/>
@@ -4774,15 +4831,15 @@
       </c>
       <c r="J51" s="10">
         <f t="shared" si="6"/>
-        <v>0.189735013</v>
+        <v>0.4295751377</v>
       </c>
       <c r="K51" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L51" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M51" s="7"/>
       <c r="N51" s="7"/>
@@ -4796,7 +4853,7 @@
       </c>
       <c r="Q51" s="10">
         <f t="shared" si="20"/>
-        <v>59</v>
+        <v>60.5</v>
       </c>
       <c r="R51" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4829,15 +4886,15 @@
         <v>5.03</v>
       </c>
       <c r="B52" s="9">
-        <v>707.0</v>
+        <v>1300.0</v>
       </c>
       <c r="C52" s="10">
         <f t="shared" si="2"/>
-        <v>2.5675152</v>
+        <v>2.684100824</v>
       </c>
       <c r="D52" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E52" s="10">
         <f t="shared" si="4"/>
@@ -4858,15 +4915,15 @@
       </c>
       <c r="J52" s="10">
         <f t="shared" si="6"/>
-        <v>0.1350303997</v>
+        <v>0.3682016476</v>
       </c>
       <c r="K52" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L52" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
@@ -4880,7 +4937,7 @@
       </c>
       <c r="Q52" s="10">
         <f t="shared" si="20"/>
-        <v>52.5</v>
+        <v>55</v>
       </c>
       <c r="R52" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4913,15 +4970,15 @@
         <v>5.04</v>
       </c>
       <c r="B53" s="9">
-        <v>676.0</v>
+        <v>1292.0</v>
       </c>
       <c r="C53" s="10">
         <f t="shared" si="2"/>
-        <v>2.543252193</v>
+        <v>2.65741505</v>
       </c>
       <c r="D53" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E53" s="10">
         <f t="shared" si="4"/>
@@ -4942,15 +4999,15 @@
       </c>
       <c r="J53" s="10">
         <f t="shared" si="6"/>
-        <v>0.08650438585</v>
+        <v>0.314830101</v>
       </c>
       <c r="K53" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L53" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M53" s="7"/>
       <c r="N53" s="7"/>
@@ -4964,7 +5021,7 @@
       </c>
       <c r="Q53" s="10">
         <f t="shared" si="20"/>
-        <v>46.5</v>
+        <v>50.5</v>
       </c>
       <c r="R53" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4997,15 +5054,15 @@
         <v>5.05</v>
       </c>
       <c r="B54" s="9">
-        <v>646.0</v>
+        <v>1291.0</v>
       </c>
       <c r="C54" s="10">
         <f t="shared" si="2"/>
-        <v>2.521744893</v>
+        <v>2.634403161</v>
       </c>
       <c r="D54" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E54" s="10">
         <f t="shared" si="4"/>
@@ -5026,15 +5083,15 @@
       </c>
       <c r="J54" s="10">
         <f t="shared" si="6"/>
-        <v>0.04348978629</v>
+        <v>0.2688063222</v>
       </c>
       <c r="K54" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L54" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M54" s="7"/>
       <c r="N54" s="7"/>
@@ -5048,7 +5105,7 @@
       </c>
       <c r="Q54" s="10">
         <f t="shared" si="20"/>
-        <v>41.5</v>
+        <v>45</v>
       </c>
       <c r="R54" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5081,15 +5138,15 @@
         <v>5.06</v>
       </c>
       <c r="B55" s="9">
-        <v>616.0</v>
+        <v>1285.0</v>
       </c>
       <c r="C55" s="10">
         <f t="shared" si="2"/>
-        <v>2.502464071</v>
+        <v>2.612195693</v>
       </c>
       <c r="D55" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E55" s="10">
         <f t="shared" si="4"/>
@@ -5110,15 +5167,15 @@
       </c>
       <c r="J55" s="10">
         <f t="shared" si="6"/>
-        <v>0.004928142805</v>
+        <v>0.2243913851</v>
       </c>
       <c r="K55" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L55" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
@@ -5132,7 +5189,7 @@
       </c>
       <c r="Q55" s="10">
         <f t="shared" si="20"/>
-        <v>37.5</v>
+        <v>40.5</v>
       </c>
       <c r="R55" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5165,15 +5222,15 @@
         <v>5.07</v>
       </c>
       <c r="B56" s="9">
-        <v>586.0</v>
+        <v>1279.0</v>
       </c>
       <c r="C56" s="10">
         <f t="shared" si="2"/>
-        <v>2.485194801</v>
+        <v>2.591783799</v>
       </c>
       <c r="D56" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E56" s="10">
         <f t="shared" si="4"/>
@@ -5190,19 +5247,19 @@
       </c>
       <c r="I56" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J56" s="10">
         <f t="shared" si="6"/>
-        <v>0.9703896015</v>
+        <v>0.1835675977</v>
       </c>
       <c r="K56" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L56" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M56" s="7"/>
       <c r="N56" s="7"/>
@@ -5216,7 +5273,7 @@
       </c>
       <c r="Q56" s="10">
         <f t="shared" si="20"/>
-        <v>33.5</v>
+        <v>36</v>
       </c>
       <c r="R56" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5249,15 +5306,15 @@
         <v>5.08</v>
       </c>
       <c r="B57" s="9">
-        <v>557.0</v>
+        <v>1262.0</v>
       </c>
       <c r="C57" s="10">
         <f t="shared" si="2"/>
-        <v>2.469938123</v>
+        <v>2.571188089</v>
       </c>
       <c r="D57" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E57" s="10">
         <f t="shared" si="4"/>
@@ -5274,19 +5331,19 @@
       </c>
       <c r="I57" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J57" s="10">
         <f t="shared" si="6"/>
-        <v>0.9398762455</v>
+        <v>0.1423761789</v>
       </c>
       <c r="K57" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L57" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M57" s="7"/>
       <c r="N57" s="7"/>
@@ -5300,7 +5357,7 @@
       </c>
       <c r="Q57" s="10">
         <f t="shared" si="20"/>
-        <v>27.5</v>
+        <v>30.5</v>
       </c>
       <c r="R57" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5333,15 +5390,15 @@
         <v>5.09</v>
       </c>
       <c r="B58" s="9">
-        <v>529.0</v>
+        <v>1236.0</v>
       </c>
       <c r="C58" s="10">
         <f t="shared" si="2"/>
-        <v>2.456471776</v>
+        <v>2.551006543</v>
       </c>
       <c r="D58" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E58" s="10">
         <f t="shared" si="4"/>
@@ -5358,19 +5415,19 @@
       </c>
       <c r="I58" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J58" s="10">
         <f t="shared" si="6"/>
-        <v>0.9129435516</v>
+        <v>0.1020130854</v>
       </c>
       <c r="K58" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L58" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
@@ -5384,7 +5441,7 @@
       </c>
       <c r="Q58" s="10">
         <f t="shared" si="20"/>
-        <v>27.5</v>
+        <v>30.5</v>
       </c>
       <c r="R58" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5417,15 +5474,15 @@
         <v>5.1</v>
       </c>
       <c r="B59" s="9">
-        <v>501.0</v>
+        <v>1231.0</v>
       </c>
       <c r="C59" s="10">
         <f t="shared" si="2"/>
-        <v>2.444429742</v>
+        <v>2.535668191</v>
       </c>
       <c r="D59" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E59" s="10">
         <f t="shared" si="4"/>
@@ -5442,19 +5499,19 @@
       </c>
       <c r="I59" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J59" s="10">
         <f t="shared" si="6"/>
-        <v>0.888859485</v>
+        <v>0.0713363818</v>
       </c>
       <c r="K59" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L59" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M59" s="7"/>
       <c r="N59" s="7"/>
@@ -5468,7 +5525,7 @@
       </c>
       <c r="Q59" s="10">
         <f t="shared" si="20"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="R59" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5501,15 +5558,15 @@
         <v>5.11</v>
       </c>
       <c r="B60" s="9">
-        <v>474.0</v>
+        <v>1229.0</v>
       </c>
       <c r="C60" s="10">
         <f t="shared" si="2"/>
-        <v>2.433827032</v>
+        <v>2.521956509</v>
       </c>
       <c r="D60" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E60" s="10">
         <f t="shared" si="4"/>
@@ -5526,19 +5583,19 @@
       </c>
       <c r="I60" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J60" s="10">
         <f t="shared" si="6"/>
-        <v>0.867654064</v>
+        <v>0.04391301772</v>
       </c>
       <c r="K60" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L60" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M60" s="7"/>
       <c r="N60" s="7"/>
@@ -5552,7 +5609,7 @@
       </c>
       <c r="Q60" s="10">
         <f t="shared" si="20"/>
-        <v>20.5</v>
+        <v>23.5</v>
       </c>
       <c r="R60" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5585,15 +5642,15 @@
         <v>5.12</v>
       </c>
       <c r="B61" s="9">
-        <v>447.0</v>
+        <v>1226.0</v>
       </c>
       <c r="C61" s="10">
         <f t="shared" si="2"/>
-        <v>2.424359303</v>
+        <v>2.509197356</v>
       </c>
       <c r="D61" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E61" s="10">
         <f t="shared" si="4"/>
@@ -5610,19 +5667,19 @@
       </c>
       <c r="I61" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J61" s="10">
         <f t="shared" si="6"/>
-        <v>0.848718606</v>
+        <v>0.01839471107</v>
       </c>
       <c r="K61" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L61" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M61" s="7"/>
       <c r="N61" s="7"/>
@@ -5636,7 +5693,7 @@
       </c>
       <c r="Q61" s="10">
         <f t="shared" si="20"/>
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="R61" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5669,11 +5726,11 @@
         <v>6.01</v>
       </c>
       <c r="B62" s="9">
-        <v>420.0</v>
+        <v>1220.0</v>
       </c>
       <c r="C62" s="10">
         <f t="shared" si="2"/>
-        <v>1.055227252</v>
+        <v>1.136423525</v>
       </c>
       <c r="D62" s="10">
         <f t="shared" si="3"/>
@@ -5698,7 +5755,7 @@
       </c>
       <c r="J62" s="10">
         <f t="shared" si="6"/>
-        <v>0.110454505</v>
+        <v>0.2728470495</v>
       </c>
       <c r="K62" s="10">
         <f t="shared" si="10"/>
@@ -5720,7 +5777,7 @@
       </c>
       <c r="Q62" s="10">
         <f t="shared" si="20"/>
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="R62" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5757,11 +5814,11 @@
         <v>6.02</v>
       </c>
       <c r="B63" s="9">
-        <v>394.0</v>
+        <v>1171.0</v>
       </c>
       <c r="C63" s="10">
         <f t="shared" si="2"/>
-        <v>1.047826009</v>
+        <v>1.120878791</v>
       </c>
       <c r="D63" s="10">
         <f t="shared" si="3"/>
@@ -5786,7 +5843,7 @@
       </c>
       <c r="J63" s="10">
         <f t="shared" si="6"/>
-        <v>0.09565201878</v>
+        <v>0.2417575811</v>
       </c>
       <c r="K63" s="10">
         <f t="shared" si="10"/>
@@ -5808,7 +5865,7 @@
       </c>
       <c r="Q63" s="10">
         <f t="shared" si="20"/>
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="R63" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5820,7 +5877,7 @@
       </c>
       <c r="U63" s="10">
         <f t="shared" ref="U63:U74" si="22">SUMIF($R$45:$R$116, T63, $Q$45:$Q$116)</f>
-        <v>418</v>
+        <v>416.5</v>
       </c>
       <c r="V63" s="13">
         <v>1.0</v>
@@ -5846,11 +5903,11 @@
         <v>6.03</v>
       </c>
       <c r="B64" s="9">
-        <v>368.0</v>
+        <v>1154.0</v>
       </c>
       <c r="C64" s="10">
         <f t="shared" si="2"/>
-        <v>1.041236205</v>
+        <v>1.109966896</v>
       </c>
       <c r="D64" s="10">
         <f t="shared" si="3"/>
@@ -5875,7 +5932,7 @@
       </c>
       <c r="J64" s="10">
         <f t="shared" si="6"/>
-        <v>0.08247240955</v>
+        <v>0.2199337916</v>
       </c>
       <c r="K64" s="10">
         <f t="shared" si="10"/>
@@ -5897,7 +5954,7 @@
       </c>
       <c r="Q64" s="10">
         <f t="shared" si="20"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R64" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5909,7 +5966,7 @@
       </c>
       <c r="U64" s="10">
         <f t="shared" si="22"/>
-        <v>170.75</v>
+        <v>163.5</v>
       </c>
       <c r="V64" s="12">
         <v>1.0</v>
@@ -5935,11 +5992,11 @@
         <v>6.04</v>
       </c>
       <c r="B65" s="9">
-        <v>343.0</v>
+        <v>1142.0</v>
       </c>
       <c r="C65" s="10">
         <f t="shared" si="2"/>
-        <v>1.035480293</v>
+        <v>1.100457987</v>
       </c>
       <c r="D65" s="10">
         <f t="shared" si="3"/>
@@ -5964,7 +6021,7 @@
       </c>
       <c r="J65" s="10">
         <f t="shared" si="6"/>
-        <v>0.07096058629</v>
+        <v>0.2009159739</v>
       </c>
       <c r="K65" s="10">
         <f t="shared" si="10"/>
@@ -5986,7 +6043,7 @@
       </c>
       <c r="Q65" s="10">
         <f t="shared" si="20"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R65" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5998,7 +6055,7 @@
       </c>
       <c r="U65" s="10">
         <f t="shared" si="22"/>
-        <v>156.5</v>
+        <v>155</v>
       </c>
       <c r="V65" s="13">
         <v>3.0</v>
@@ -6024,11 +6081,11 @@
         <v>6.05</v>
       </c>
       <c r="B66" s="9">
-        <v>318.0</v>
+        <v>1140.0</v>
       </c>
       <c r="C66" s="10">
         <f t="shared" si="2"/>
-        <v>1.030365592</v>
+        <v>1.092573093</v>
       </c>
       <c r="D66" s="10">
         <f t="shared" si="3"/>
@@ -6053,7 +6110,7 @@
       </c>
       <c r="J66" s="10">
         <f t="shared" si="6"/>
-        <v>0.06073118468</v>
+        <v>0.185146187</v>
       </c>
       <c r="K66" s="10">
         <f t="shared" si="10"/>
@@ -6075,7 +6132,7 @@
       </c>
       <c r="Q66" s="10">
         <f t="shared" si="20"/>
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="R66" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6087,7 +6144,7 @@
       </c>
       <c r="U66" s="10">
         <f t="shared" si="22"/>
-        <v>140</v>
+        <v>139.5</v>
       </c>
       <c r="V66" s="14">
         <v>1.0</v>
@@ -6113,11 +6170,11 @@
         <v>6.06</v>
       </c>
       <c r="B67" s="9">
-        <v>294.0</v>
+        <v>1126.0</v>
       </c>
       <c r="C67" s="10">
         <f t="shared" si="2"/>
-        <v>1.0259157</v>
+        <v>1.084407161</v>
       </c>
       <c r="D67" s="10">
         <f t="shared" si="3"/>
@@ -6142,7 +6199,7 @@
       </c>
       <c r="J67" s="10">
         <f t="shared" si="6"/>
-        <v>0.05183140038</v>
+        <v>0.1688143228</v>
       </c>
       <c r="K67" s="10">
         <f t="shared" si="10"/>
@@ -6176,7 +6233,7 @@
       </c>
       <c r="U67" s="10">
         <f t="shared" si="22"/>
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="V67" s="14">
         <v>5.0</v>
@@ -6202,11 +6259,11 @@
         <v>6.07</v>
       </c>
       <c r="B68" s="9">
-        <v>270.0</v>
+        <v>1096.0</v>
       </c>
       <c r="C68" s="10">
         <f t="shared" si="2"/>
-        <v>1.021970495</v>
+        <v>1.075842375</v>
       </c>
       <c r="D68" s="10">
         <f t="shared" si="3"/>
@@ -6231,7 +6288,7 @@
       </c>
       <c r="J68" s="10">
         <f t="shared" si="6"/>
-        <v>0.04394099053</v>
+        <v>0.1516847502</v>
       </c>
       <c r="K68" s="10">
         <f t="shared" si="10"/>
@@ -6265,7 +6322,7 @@
       </c>
       <c r="U68" s="10">
         <f t="shared" si="22"/>
-        <v>64.5</v>
+        <v>67</v>
       </c>
       <c r="V68" s="14">
         <v>6.0</v>
@@ -6290,12 +6347,12 @@
       <c r="A69" s="8">
         <v>6.08</v>
       </c>
-      <c r="B69" s="9">
-        <v>246.0</v>
+      <c r="B69" s="13">
+        <v>1026.0</v>
       </c>
       <c r="C69" s="10">
         <f t="shared" si="2"/>
-        <v>1.018478691</v>
+        <v>1.065540348</v>
       </c>
       <c r="D69" s="10">
         <f t="shared" si="3"/>
@@ -6320,7 +6377,7 @@
       </c>
       <c r="J69" s="10">
         <f t="shared" si="6"/>
-        <v>0.0369573818</v>
+        <v>0.1310806959</v>
       </c>
       <c r="K69" s="10">
         <f t="shared" si="10"/>
@@ -6354,7 +6411,7 @@
       </c>
       <c r="U69" s="10">
         <f t="shared" si="22"/>
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="V69" s="12"/>
       <c r="W69" s="12"/>
@@ -6374,11 +6431,11 @@
         <v>6.09</v>
       </c>
       <c r="B70" s="9">
-        <v>222.0</v>
+        <v>1021.0</v>
       </c>
       <c r="C70" s="10">
         <f t="shared" si="2"/>
-        <v>1.015393901</v>
+        <v>1.060206964</v>
       </c>
       <c r="D70" s="10">
         <f t="shared" si="3"/>
@@ -6403,7 +6460,7 @@
       </c>
       <c r="J70" s="10">
         <f t="shared" si="6"/>
-        <v>0.03078780104</v>
+        <v>0.1204139289</v>
       </c>
       <c r="K70" s="10">
         <f t="shared" si="10"/>
@@ -6437,7 +6494,7 @@
       </c>
       <c r="U70" s="10">
         <f t="shared" si="22"/>
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="V70" s="3"/>
       <c r="W70" s="3"/>
@@ -6457,11 +6514,11 @@
         <v>6.1</v>
       </c>
       <c r="B71" s="9">
-        <v>199.0</v>
+        <v>1011.0</v>
       </c>
       <c r="C71" s="10">
         <f t="shared" si="2"/>
-        <v>1.012738199</v>
+        <v>1.05503404</v>
       </c>
       <c r="D71" s="10">
         <f t="shared" si="3"/>
@@ -6486,7 +6543,7 @@
       </c>
       <c r="J71" s="10">
         <f t="shared" si="6"/>
-        <v>0.02547639786</v>
+        <v>0.1100680797</v>
       </c>
       <c r="K71" s="10">
         <f t="shared" si="10"/>
@@ -6520,7 +6577,7 @@
       </c>
       <c r="U71" s="10">
         <f t="shared" si="22"/>
-        <v>18.25</v>
+        <v>19.5</v>
       </c>
       <c r="V71" s="3"/>
       <c r="W71" s="3"/>
@@ -6539,12 +6596,12 @@
       <c r="A72" s="8">
         <v>6.11</v>
       </c>
-      <c r="B72" s="9">
-        <v>177.0</v>
+      <c r="B72" s="13">
+        <v>1004.0</v>
       </c>
       <c r="C72" s="10">
         <f t="shared" si="2"/>
-        <v>1.010458927</v>
+        <v>1.050451361</v>
       </c>
       <c r="D72" s="10">
         <f t="shared" si="3"/>
@@ -6569,7 +6626,7 @@
       </c>
       <c r="J72" s="10">
         <f t="shared" si="6"/>
-        <v>0.02091785481</v>
+        <v>0.1009027212</v>
       </c>
       <c r="K72" s="10">
         <f t="shared" si="10"/>
@@ -6603,7 +6660,7 @@
       </c>
       <c r="U72" s="10">
         <f t="shared" si="22"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V72" s="3"/>
       <c r="W72" s="3"/>
@@ -6623,11 +6680,11 @@
         <v>6.12</v>
       </c>
       <c r="B73" s="9">
-        <v>154.0</v>
+        <v>946.0</v>
       </c>
       <c r="C73" s="10">
         <f t="shared" si="2"/>
-        <v>1.00840027</v>
+        <v>1.043882257</v>
       </c>
       <c r="D73" s="10">
         <f t="shared" si="3"/>
@@ -6652,7 +6709,7 @@
       </c>
       <c r="J73" s="10">
         <f t="shared" si="6"/>
-        <v>0.01680054031</v>
+        <v>0.08776451406</v>
       </c>
       <c r="K73" s="10">
         <f t="shared" si="10"/>
@@ -6674,7 +6731,7 @@
       </c>
       <c r="Q73" s="10">
         <f t="shared" si="20"/>
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="R73" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6703,7 +6760,9 @@
     </row>
     <row r="74">
       <c r="A74" s="3"/>
-      <c r="B74" s="13"/>
+      <c r="B74" s="9">
+        <v>836.0</v>
+      </c>
       <c r="C74" s="3"/>
       <c r="D74" s="10">
         <f>Sum(D2:D73)</f>
@@ -6738,7 +6797,7 @@
       </c>
       <c r="Q74" s="10">
         <f t="shared" si="20"/>
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="R74" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6767,7 +6826,9 @@
     </row>
     <row r="75">
       <c r="A75" s="3"/>
-      <c r="B75" s="13"/>
+      <c r="B75" s="13">
+        <v>786.0</v>
+      </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -6817,7 +6878,9 @@
     </row>
     <row r="76">
       <c r="A76" s="3"/>
-      <c r="B76" s="13"/>
+      <c r="B76" s="9">
+        <v>577.0</v>
+      </c>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -6840,7 +6903,7 @@
       </c>
       <c r="Q76" s="10">
         <f t="shared" si="20"/>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="R76" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6864,7 +6927,9 @@
     </row>
     <row r="77">
       <c r="A77" s="3"/>
-      <c r="B77" s="13"/>
+      <c r="B77" s="13">
+        <v>542.0</v>
+      </c>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -6887,7 +6952,7 @@
       </c>
       <c r="Q77" s="10">
         <f t="shared" si="20"/>
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R77" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6911,7 +6976,9 @@
     </row>
     <row r="78">
       <c r="A78" s="3"/>
-      <c r="B78" s="13"/>
+      <c r="B78" s="13">
+        <v>449.0</v>
+      </c>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -6958,7 +7025,9 @@
     </row>
     <row r="79">
       <c r="A79" s="3"/>
-      <c r="B79" s="13"/>
+      <c r="B79" s="13">
+        <v>351.0</v>
+      </c>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -6981,7 +7050,7 @@
       </c>
       <c r="Q79" s="10">
         <f t="shared" si="20"/>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R79" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7005,7 +7074,9 @@
     </row>
     <row r="80">
       <c r="A80" s="3"/>
-      <c r="B80" s="7"/>
+      <c r="B80" s="13">
+        <v>310.0</v>
+      </c>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -7052,7 +7123,9 @@
     </row>
     <row r="81">
       <c r="A81" s="3"/>
-      <c r="B81" s="7"/>
+      <c r="B81" s="13">
+        <v>243.0</v>
+      </c>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -7075,7 +7148,7 @@
       </c>
       <c r="Q81" s="10">
         <f t="shared" si="20"/>
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R81" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7099,7 +7172,9 @@
     </row>
     <row r="82">
       <c r="A82" s="3"/>
-      <c r="B82" s="7"/>
+      <c r="B82" s="13">
+        <v>214.0</v>
+      </c>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -7122,7 +7197,7 @@
       </c>
       <c r="Q82" s="10">
         <f t="shared" si="20"/>
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R82" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7143,7 +7218,9 @@
     </row>
     <row r="83">
       <c r="A83" s="7"/>
-      <c r="B83" s="7"/>
+      <c r="B83" s="13">
+        <v>201.0</v>
+      </c>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -7166,7 +7243,7 @@
       </c>
       <c r="Q83" s="10">
         <f t="shared" si="20"/>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R83" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7187,7 +7264,9 @@
     </row>
     <row r="84">
       <c r="A84" s="7"/>
-      <c r="B84" s="7"/>
+      <c r="B84" s="13">
+        <v>157.0</v>
+      </c>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -7210,7 +7289,7 @@
       </c>
       <c r="Q84" s="10">
         <f t="shared" si="20"/>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R84" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7231,7 +7310,9 @@
     </row>
     <row r="85">
       <c r="A85" s="7"/>
-      <c r="B85" s="7"/>
+      <c r="B85" s="9">
+        <v>148.0</v>
+      </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -7275,7 +7356,9 @@
     </row>
     <row r="86">
       <c r="A86" s="7"/>
-      <c r="B86" s="7"/>
+      <c r="B86" s="13">
+        <v>116.0</v>
+      </c>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -7298,7 +7381,7 @@
       </c>
       <c r="Q86" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="R86" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7319,7 +7402,9 @@
     </row>
     <row r="87">
       <c r="A87" s="7"/>
-      <c r="B87" s="7"/>
+      <c r="B87" s="13">
+        <v>102.0</v>
+      </c>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -7342,7 +7427,7 @@
       </c>
       <c r="Q87" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="R87" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7363,7 +7448,9 @@
     </row>
     <row r="88">
       <c r="A88" s="7"/>
-      <c r="B88" s="7"/>
+      <c r="B88" s="13">
+        <v>90.0</v>
+      </c>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -7386,7 +7473,7 @@
       </c>
       <c r="Q88" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="R88" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7407,7 +7494,9 @@
     </row>
     <row r="89">
       <c r="A89" s="7"/>
-      <c r="B89" s="7"/>
+      <c r="B89" s="13">
+        <v>75.0</v>
+      </c>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -7451,7 +7540,9 @@
     </row>
     <row r="90">
       <c r="A90" s="3"/>
-      <c r="B90" s="7"/>
+      <c r="B90" s="13">
+        <v>70.0</v>
+      </c>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -7474,7 +7565,7 @@
       </c>
       <c r="Q90" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R90" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7495,7 +7586,9 @@
     </row>
     <row r="91">
       <c r="A91" s="3"/>
-      <c r="B91" s="7"/>
+      <c r="B91" s="13">
+        <v>58.0</v>
+      </c>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -7518,7 +7611,7 @@
       </c>
       <c r="Q91" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R91" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7539,7 +7632,9 @@
     </row>
     <row r="92">
       <c r="A92" s="3"/>
-      <c r="B92" s="7"/>
+      <c r="B92" s="13">
+        <v>52.0</v>
+      </c>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -7562,7 +7657,7 @@
       </c>
       <c r="Q92" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R92" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7583,7 +7678,9 @@
     </row>
     <row r="93">
       <c r="A93" s="3"/>
-      <c r="B93" s="7"/>
+      <c r="B93" s="13">
+        <v>49.0</v>
+      </c>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -7606,7 +7703,7 @@
       </c>
       <c r="Q93" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R93" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7627,7 +7724,9 @@
     </row>
     <row r="94">
       <c r="A94" s="7"/>
-      <c r="B94" s="7"/>
+      <c r="B94" s="13">
+        <v>46.0</v>
+      </c>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -7650,7 +7749,7 @@
       </c>
       <c r="Q94" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R94" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7671,7 +7770,9 @@
     </row>
     <row r="95">
       <c r="A95" s="7"/>
-      <c r="B95" s="7"/>
+      <c r="B95" s="13">
+        <v>43.0</v>
+      </c>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -7694,7 +7795,7 @@
       </c>
       <c r="Q95" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R95" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7715,7 +7816,9 @@
     </row>
     <row r="96">
       <c r="A96" s="7"/>
-      <c r="B96" s="7"/>
+      <c r="B96" s="13">
+        <v>40.0</v>
+      </c>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -7738,7 +7841,7 @@
       </c>
       <c r="Q96" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R96" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7759,7 +7862,9 @@
     </row>
     <row r="97">
       <c r="A97" s="7"/>
-      <c r="B97" s="7"/>
+      <c r="B97" s="13">
+        <v>36.0</v>
+      </c>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -7782,7 +7887,7 @@
       </c>
       <c r="Q97" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R97" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7803,7 +7908,9 @@
     </row>
     <row r="98">
       <c r="A98" s="7"/>
-      <c r="B98" s="7"/>
+      <c r="B98" s="13">
+        <v>32.0</v>
+      </c>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -7826,7 +7933,7 @@
       </c>
       <c r="Q98" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R98" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7847,7 +7954,9 @@
     </row>
     <row r="99">
       <c r="A99" s="7"/>
-      <c r="B99" s="7"/>
+      <c r="B99" s="13">
+        <v>30.0</v>
+      </c>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -7870,7 +7979,7 @@
       </c>
       <c r="Q99" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R99" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7891,7 +8000,9 @@
     </row>
     <row r="100">
       <c r="A100" s="7"/>
-      <c r="B100" s="7"/>
+      <c r="B100" s="13">
+        <v>16.0</v>
+      </c>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -7914,7 +8025,7 @@
       </c>
       <c r="Q100" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R100" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7935,7 +8046,9 @@
     </row>
     <row r="101">
       <c r="A101" s="3"/>
-      <c r="B101" s="7"/>
+      <c r="B101" s="13">
+        <v>14.0</v>
+      </c>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
@@ -7958,7 +8071,7 @@
       </c>
       <c r="Q101" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R101" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7979,7 +8092,9 @@
     </row>
     <row r="102">
       <c r="A102" s="3"/>
-      <c r="B102" s="7"/>
+      <c r="B102" s="13">
+        <v>8.0</v>
+      </c>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
@@ -8002,7 +8117,7 @@
       </c>
       <c r="Q102" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R102" s="7" t="str">
         <f t="shared" si="21"/>
@@ -8046,7 +8161,7 @@
       </c>
       <c r="Q103" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R103" s="7" t="str">
         <f t="shared" si="21"/>
@@ -8090,7 +8205,7 @@
       </c>
       <c r="Q104" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R104" s="7" t="str">
         <f t="shared" si="21"/>
@@ -8853,7 +8968,7 @@
      )
      &lt;= 1200 - SUMPRODUCT(ROUNDDOWN($C$2:$C$73,0)) )
 </f>
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="N123" s="7"/>
       <c r="O123" s="7"/>
@@ -37651,7 +37766,7 @@
         <v>45</v>
       </c>
       <c r="C2" s="17">
-        <v>133.5</v>
+        <v>134.5</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="b">
@@ -37660,11 +37775,11 @@
       <c r="F2" s="17">
         <f t="shared" ref="F2:F73" si="1">IF($D2&gt;0,"",$C2*$L$14)
 </f>
-        <v>133.5</v>
+        <v>134.5</v>
       </c>
       <c r="G2" s="17">
         <f t="shared" ref="G2:G73" si="2">IF($D2&gt;0,"",MIN($L$8, $C2*$L$14*(1+($L$11-1)*$L$16)))</f>
-        <v>192.1307417</v>
+        <v>193.1787364</v>
       </c>
       <c r="H2" s="20">
         <f t="shared" ref="H2:H73" si="3">IF($D2&lt;&gt;"","",
@@ -37674,7 +37789,7 @@
    )
 )
 </f>
-        <v>106.8</v>
+        <v>107.6</v>
       </c>
       <c r="I2" s="21" t="str">
         <f>IF($D2="","",
@@ -37703,10 +37818,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C3" s="17">
-        <v>104.5</v>
+        <v>101.5</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9" t="b">
@@ -37714,15 +37829,15 @@
       </c>
       <c r="F3" s="17">
         <f t="shared" si="1"/>
-        <v>104.5</v>
+        <v>101.5</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" si="2"/>
-        <v>150.3944757</v>
+        <v>145.781723</v>
       </c>
       <c r="H3" s="20">
         <f t="shared" si="3"/>
-        <v>83.6</v>
+        <v>81.2</v>
       </c>
       <c r="I3" s="21" t="str">
         <f t="shared" ref="I3:I73" si="4">IF($D3="","",
@@ -37745,10 +37860,10 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C4" s="17">
-        <v>92.5</v>
+        <v>90.0</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9" t="b">
@@ -37756,15 +37871,15 @@
       </c>
       <c r="F4" s="17">
         <f t="shared" si="1"/>
-        <v>92.5</v>
+        <v>90</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" si="2"/>
-        <v>133.1242967</v>
+        <v>129.264582</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" si="3"/>
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I4" s="21" t="str">
         <f t="shared" si="4"/>
@@ -37775,7 +37890,7 @@
       </c>
       <c r="L4" s="19">
         <f>'Draft Data'!U63</f>
-        <v>418</v>
+        <v>416.5</v>
       </c>
     </row>
     <row r="5">
@@ -37783,25 +37898,25 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C5" s="17">
-        <v>85.5</v>
+        <v>83.0</v>
       </c>
       <c r="E5" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F5" s="17">
         <f t="shared" si="1"/>
-        <v>85.5</v>
+        <v>83</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" si="2"/>
-        <v>123.0500256</v>
+        <v>119.2106701</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="3"/>
-        <v>68.4</v>
+        <v>66.4</v>
       </c>
       <c r="I5" s="21" t="str">
         <f t="shared" si="4"/>
@@ -37824,22 +37939,22 @@
         <v>52</v>
       </c>
       <c r="C6" s="17">
-        <v>73.5</v>
+        <v>72.5</v>
       </c>
       <c r="E6" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F6" s="17">
         <f t="shared" si="1"/>
-        <v>73.5</v>
+        <v>72.5</v>
       </c>
       <c r="G6" s="17">
         <f t="shared" si="2"/>
-        <v>105.7798465</v>
+        <v>104.1298022</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="3"/>
-        <v>58.8</v>
+        <v>58</v>
       </c>
       <c r="I6" s="21" t="str">
         <f t="shared" si="4"/>
@@ -37862,22 +37977,22 @@
         <v>53</v>
       </c>
       <c r="C7" s="17">
-        <v>65.0</v>
+        <v>65.5</v>
       </c>
       <c r="E7" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F7" s="17">
         <f t="shared" si="1"/>
-        <v>65</v>
+        <v>65.5</v>
       </c>
       <c r="G7" s="17">
         <f t="shared" si="2"/>
-        <v>93.54680307</v>
+        <v>94.07589024</v>
       </c>
       <c r="H7" s="20">
         <f t="shared" si="3"/>
-        <v>52</v>
+        <v>52.4</v>
       </c>
       <c r="I7" s="21" t="str">
         <f t="shared" si="4"/>
@@ -37896,25 +38011,25 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C8" s="17">
-        <v>59.0</v>
+        <v>60.5</v>
       </c>
       <c r="E8" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F8" s="17">
         <f t="shared" si="1"/>
-        <v>59</v>
+        <v>60.5</v>
       </c>
       <c r="G8" s="17">
         <f t="shared" si="2"/>
-        <v>84.91171355</v>
+        <v>86.89452457</v>
       </c>
       <c r="H8" s="20">
         <f t="shared" si="3"/>
-        <v>47.2</v>
+        <v>48.4</v>
       </c>
       <c r="I8" s="21" t="str">
         <f t="shared" si="4"/>
@@ -37926,7 +38041,7 @@
       <c r="L8" s="17">
         <f>L4-L7
 </f>
-        <v>418</v>
+        <v>416.5</v>
       </c>
     </row>
     <row r="9">
@@ -37934,25 +38049,25 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C9" s="17">
-        <v>52.0</v>
+        <v>55.0</v>
       </c>
       <c r="E9" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F9" s="17">
         <f t="shared" si="1"/>
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G9" s="17">
         <f t="shared" si="2"/>
-        <v>74.83744246</v>
+        <v>78.99502234</v>
       </c>
       <c r="H9" s="20">
         <f t="shared" si="3"/>
-        <v>41.6</v>
+        <v>44</v>
       </c>
       <c r="I9" s="21" t="str">
         <f t="shared" si="4"/>
@@ -37964,7 +38079,7 @@
       <c r="L9" s="17">
         <f>L6-L8
 </f>
-        <v>782</v>
+        <v>783.5</v>
       </c>
     </row>
     <row r="10">
@@ -37972,25 +38087,25 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C10" s="17">
-        <v>48.0</v>
+        <v>50.5</v>
       </c>
       <c r="E10" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F10" s="17">
         <f t="shared" si="1"/>
-        <v>48</v>
+        <v>50.5</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" si="2"/>
-        <v>69.08071611</v>
+        <v>72.53179324</v>
       </c>
       <c r="H10" s="20">
         <f t="shared" si="3"/>
-        <v>38.4</v>
+        <v>40.4</v>
       </c>
       <c r="I10" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38001,7 +38116,7 @@
       </c>
       <c r="L10" s="17">
         <f>IF(L3&gt;1,L9/(L3-1),0)</f>
-        <v>71.09090909</v>
+        <v>71.22727273</v>
       </c>
     </row>
     <row r="11">
@@ -38009,25 +38124,25 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C11" s="17">
-        <v>43.0</v>
+        <v>45.0</v>
       </c>
       <c r="E11" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F11" s="17">
         <f t="shared" si="1"/>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G11" s="17">
         <f t="shared" si="2"/>
-        <v>61.88480818</v>
+        <v>64.632291</v>
       </c>
       <c r="H11" s="20">
         <f t="shared" si="3"/>
-        <v>34.4</v>
+        <v>36</v>
       </c>
       <c r="I11" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38038,7 +38153,7 @@
       </c>
       <c r="L11" s="23">
         <f>IF(L10&gt;0,L8/L10,1)</f>
-        <v>5.879795396</v>
+        <v>5.84747926</v>
       </c>
     </row>
     <row r="12">
@@ -38049,22 +38164,22 @@
         <v>61</v>
       </c>
       <c r="C12" s="17">
-        <v>40.0</v>
+        <v>40.5</v>
       </c>
       <c r="E12" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F12" s="17">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="G12" s="17">
         <f t="shared" si="2"/>
-        <v>57.56726343</v>
+        <v>58.1690619</v>
       </c>
       <c r="H12" s="20">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>32.4</v>
       </c>
       <c r="I12" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38076,25 +38191,25 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C13" s="17">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="E13" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F13" s="17">
         <f t="shared" si="1"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G13" s="17">
         <f t="shared" si="2"/>
-        <v>50.3713555</v>
+        <v>51.7058328</v>
       </c>
       <c r="H13" s="20">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>28.8</v>
       </c>
       <c r="I13" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38113,32 +38228,32 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="C14" s="17">
-        <v>30.5</v>
+        <v>32.0</v>
       </c>
       <c r="E14" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F14" s="17">
         <f t="shared" si="1"/>
-        <v>30.5</v>
+        <v>32</v>
       </c>
       <c r="G14" s="17">
         <f t="shared" si="2"/>
-        <v>43.89503836</v>
+        <v>45.96074027</v>
       </c>
       <c r="H14" s="20">
         <f t="shared" si="3"/>
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
       <c r="I14" s="21" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K14" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L14" s="23">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -38153,22 +38268,22 @@
         <v>65</v>
       </c>
       <c r="C15" s="17">
-        <v>27.5</v>
+        <v>29.0</v>
       </c>
       <c r="E15" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" si="1"/>
-        <v>27.5</v>
+        <v>29</v>
       </c>
       <c r="G15" s="17">
         <f t="shared" si="2"/>
-        <v>39.57749361</v>
+        <v>41.65192087</v>
       </c>
       <c r="H15" s="20">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23.2</v>
       </c>
       <c r="I15" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38180,32 +38295,32 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>66</v>
+        <v>152</v>
       </c>
       <c r="C16" s="17">
-        <v>25.5</v>
+        <v>26.0</v>
       </c>
       <c r="E16" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F16" s="17">
         <f t="shared" si="1"/>
-        <v>25.5</v>
+        <v>26</v>
       </c>
       <c r="G16" s="17">
         <f t="shared" si="2"/>
-        <v>36.69913043</v>
+        <v>37.34310147</v>
       </c>
       <c r="H16" s="20">
         <f t="shared" si="3"/>
-        <v>20.4</v>
+        <v>20.8</v>
       </c>
       <c r="I16" s="21" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K16" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L16" s="9">
         <f>IF($L$18&lt;0.3,
@@ -38227,7 +38342,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C17" s="17">
         <v>23.5</v>
@@ -38241,7 +38356,7 @@
       </c>
       <c r="G17" s="17">
         <f t="shared" si="2"/>
-        <v>33.82076726</v>
+        <v>33.75241863</v>
       </c>
       <c r="H17" s="20">
         <f t="shared" si="3"/>
@@ -38257,32 +38372,32 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C18" s="17">
-        <v>20.5</v>
+        <v>21.0</v>
       </c>
       <c r="E18" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F18" s="17">
         <f t="shared" si="1"/>
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="G18" s="17">
         <f t="shared" si="2"/>
-        <v>29.50322251</v>
+        <v>30.1617358</v>
       </c>
       <c r="H18" s="20">
         <f t="shared" si="3"/>
-        <v>16.4</v>
+        <v>16.8</v>
       </c>
       <c r="I18" s="21" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K18" s="9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L18" s="24">
         <f>L5/L2</f>
@@ -38294,25 +38409,25 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C19" s="17">
-        <v>19.0</v>
+        <v>18.5</v>
       </c>
       <c r="E19" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F19" s="17">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="G19" s="17">
         <f t="shared" si="2"/>
-        <v>27.34445013</v>
+        <v>26.57105297</v>
       </c>
       <c r="H19" s="20">
         <f t="shared" si="3"/>
-        <v>15.2</v>
+        <v>14.8</v>
       </c>
       <c r="I19" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38327,22 +38442,22 @@
         <v>70</v>
       </c>
       <c r="C20" s="17">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="E20" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F20" s="17">
         <f t="shared" si="1"/>
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="G20" s="17">
         <f t="shared" si="2"/>
-        <v>25.18567775</v>
+        <v>23.6985067</v>
       </c>
       <c r="H20" s="20">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>13.2</v>
       </c>
       <c r="I20" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38354,25 +38469,25 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>71</v>
+        <v>155</v>
       </c>
       <c r="C21" s="17">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="E21" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F21" s="17">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G21" s="17">
         <f t="shared" si="2"/>
-        <v>23.02690537</v>
+        <v>21.544097</v>
       </c>
       <c r="H21" s="20">
         <f t="shared" si="3"/>
-        <v>12.8</v>
+        <v>12</v>
       </c>
       <c r="I21" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38384,7 +38499,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C22" s="17">
         <v>14.0</v>
@@ -38398,7 +38513,7 @@
       </c>
       <c r="G22" s="17">
         <f t="shared" si="2"/>
-        <v>20.1485422</v>
+        <v>20.10782387</v>
       </c>
       <c r="H22" s="20">
         <f t="shared" si="3"/>
@@ -38414,25 +38529,25 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>73</v>
+        <v>156</v>
       </c>
       <c r="C23" s="17">
-        <v>13.0</v>
+        <v>12.5</v>
       </c>
       <c r="E23" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F23" s="17">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="G23" s="17">
         <f t="shared" si="2"/>
-        <v>18.70936061</v>
+        <v>17.95341417</v>
       </c>
       <c r="H23" s="20">
         <f t="shared" si="3"/>
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="I23" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38444,25 +38559,25 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C24" s="17">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="E24" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F24" s="17">
         <f t="shared" si="1"/>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="G24" s="17">
         <f t="shared" si="2"/>
-        <v>16.55058824</v>
+        <v>15.0808679</v>
       </c>
       <c r="H24" s="20">
         <f t="shared" si="3"/>
-        <v>9.2</v>
+        <v>8.4</v>
       </c>
       <c r="I24" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38477,22 +38592,22 @@
         <v>75</v>
       </c>
       <c r="C25" s="17">
-        <v>10.5</v>
+        <v>10.0</v>
       </c>
       <c r="E25" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F25" s="17">
         <f t="shared" si="1"/>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="G25" s="17">
         <f t="shared" si="2"/>
-        <v>15.11140665</v>
+        <v>14.36273133</v>
       </c>
       <c r="H25" s="20">
         <f t="shared" si="3"/>
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I25" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38504,25 +38619,25 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C26" s="17">
-        <v>9.5</v>
+        <v>9.0</v>
       </c>
       <c r="E26" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F26" s="17">
         <f t="shared" si="1"/>
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G26" s="17">
         <f t="shared" si="2"/>
-        <v>13.67222506</v>
+        <v>12.9264582</v>
       </c>
       <c r="H26" s="20">
         <f t="shared" si="3"/>
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I26" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38534,7 +38649,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="C27" s="17">
         <v>8.5</v>
@@ -38548,7 +38663,7 @@
       </c>
       <c r="G27" s="17">
         <f t="shared" si="2"/>
-        <v>12.23304348</v>
+        <v>12.20832163</v>
       </c>
       <c r="H27" s="20">
         <f t="shared" si="3"/>
@@ -38559,7 +38674,7 @@
         <v/>
       </c>
       <c r="K27" s="9" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="L27" s="9">
         <v>0.8</v>
@@ -38570,7 +38685,7 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C28" s="17">
         <v>7.5</v>
@@ -38584,7 +38699,7 @@
       </c>
       <c r="G28" s="17">
         <f t="shared" si="2"/>
-        <v>10.79386189</v>
+        <v>10.7720485</v>
       </c>
       <c r="H28" s="20">
         <f t="shared" si="3"/>
@@ -38600,7 +38715,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C29" s="17">
         <v>7.0</v>
@@ -38614,7 +38729,7 @@
       </c>
       <c r="G29" s="17">
         <f t="shared" si="2"/>
-        <v>10.0742711</v>
+        <v>10.05391193</v>
       </c>
       <c r="H29" s="20">
         <f t="shared" si="3"/>
@@ -38630,7 +38745,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C30" s="17">
         <v>6.5</v>
@@ -38644,7 +38759,7 @@
       </c>
       <c r="G30" s="17">
         <f t="shared" si="2"/>
-        <v>9.354680307</v>
+        <v>9.335775367</v>
       </c>
       <c r="H30" s="20">
         <f t="shared" si="3"/>
@@ -38660,7 +38775,7 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C31" s="17">
         <v>6.0</v>
@@ -38674,7 +38789,7 @@
       </c>
       <c r="G31" s="17">
         <f t="shared" si="2"/>
-        <v>8.635089514</v>
+        <v>8.6176388</v>
       </c>
       <c r="H31" s="20">
         <f t="shared" si="3"/>
@@ -38690,25 +38805,25 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C32" s="17">
-        <v>5.5</v>
+        <v>5.0</v>
       </c>
       <c r="E32" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F32" s="17">
         <f t="shared" si="1"/>
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="G32" s="17">
         <f t="shared" si="2"/>
-        <v>7.915498721</v>
+        <v>7.181365667</v>
       </c>
       <c r="H32" s="20">
         <f t="shared" si="3"/>
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I32" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38720,7 +38835,7 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C33" s="17">
         <v>5.0</v>
@@ -38734,7 +38849,7 @@
       </c>
       <c r="G33" s="17">
         <f t="shared" si="2"/>
-        <v>7.195907928</v>
+        <v>7.181365667</v>
       </c>
       <c r="H33" s="20">
         <f t="shared" si="3"/>
@@ -38750,7 +38865,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C34" s="17">
         <v>4.5</v>
@@ -38764,7 +38879,7 @@
       </c>
       <c r="G34" s="17">
         <f t="shared" si="2"/>
-        <v>6.476317136</v>
+        <v>6.4632291</v>
       </c>
       <c r="H34" s="20">
         <f t="shared" si="3"/>
@@ -38780,25 +38895,25 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C35" s="17">
-        <v>4.5</v>
+        <v>4.0</v>
       </c>
       <c r="E35" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F35" s="17">
         <f t="shared" si="1"/>
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G35" s="17">
         <f t="shared" si="2"/>
-        <v>6.476317136</v>
+        <v>5.745092534</v>
       </c>
       <c r="H35" s="20">
         <f t="shared" si="3"/>
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="I35" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38810,7 +38925,7 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C36" s="17">
         <v>4.0</v>
@@ -38824,7 +38939,7 @@
       </c>
       <c r="G36" s="17">
         <f t="shared" si="2"/>
-        <v>5.756726343</v>
+        <v>5.745092534</v>
       </c>
       <c r="H36" s="20">
         <f t="shared" si="3"/>
@@ -38840,25 +38955,25 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="C37" s="17">
-        <v>4.0</v>
+        <v>3.5</v>
       </c>
       <c r="E37" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F37" s="17">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="G37" s="17">
         <f t="shared" si="2"/>
-        <v>5.756726343</v>
+        <v>5.026955967</v>
       </c>
       <c r="H37" s="20">
         <f t="shared" si="3"/>
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="I37" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38870,7 +38985,7 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C38" s="17">
         <v>3.5</v>
@@ -38884,7 +38999,7 @@
       </c>
       <c r="G38" s="17">
         <f t="shared" si="2"/>
-        <v>5.03713555</v>
+        <v>5.026955967</v>
       </c>
       <c r="H38" s="20">
         <f t="shared" si="3"/>
@@ -38900,25 +39015,25 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C39" s="17">
-        <v>3.5</v>
+        <v>3.0</v>
       </c>
       <c r="E39" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F39" s="17">
         <f t="shared" si="1"/>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G39" s="17">
         <f t="shared" si="2"/>
-        <v>5.03713555</v>
+        <v>4.3088194</v>
       </c>
       <c r="H39" s="20">
         <f t="shared" si="3"/>
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="I39" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38930,7 +39045,7 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>90</v>
+        <v>159</v>
       </c>
       <c r="C40" s="17">
         <v>3.0</v>
@@ -38944,7 +39059,7 @@
       </c>
       <c r="G40" s="17">
         <f t="shared" si="2"/>
-        <v>4.317544757</v>
+        <v>4.3088194</v>
       </c>
       <c r="H40" s="20">
         <f t="shared" si="3"/>
@@ -38960,7 +39075,7 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C41" s="17">
         <v>3.0</v>
@@ -38974,7 +39089,7 @@
       </c>
       <c r="G41" s="17">
         <f t="shared" si="2"/>
-        <v>4.317544757</v>
+        <v>4.3088194</v>
       </c>
       <c r="H41" s="20">
         <f t="shared" si="3"/>
@@ -38990,7 +39105,7 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="C42" s="17">
         <v>2.5</v>
@@ -39004,7 +39119,7 @@
       </c>
       <c r="G42" s="17">
         <f t="shared" si="2"/>
-        <v>3.597953964</v>
+        <v>3.590682833</v>
       </c>
       <c r="H42" s="20">
         <f t="shared" si="3"/>
@@ -39020,7 +39135,7 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C43" s="17">
         <v>2.5</v>
@@ -39034,7 +39149,7 @@
       </c>
       <c r="G43" s="17">
         <f t="shared" si="2"/>
-        <v>3.597953964</v>
+        <v>3.590682833</v>
       </c>
       <c r="H43" s="20">
         <f t="shared" si="3"/>
@@ -39050,7 +39165,7 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C44" s="17">
         <v>2.5</v>
@@ -39064,7 +39179,7 @@
       </c>
       <c r="G44" s="17">
         <f t="shared" si="2"/>
-        <v>3.597953964</v>
+        <v>3.590682833</v>
       </c>
       <c r="H44" s="20">
         <f t="shared" si="3"/>
@@ -39094,7 +39209,7 @@
       </c>
       <c r="G45" s="17">
         <f t="shared" si="2"/>
-        <v>3.597953964</v>
+        <v>3.590682833</v>
       </c>
       <c r="H45" s="20">
         <f t="shared" si="3"/>
@@ -39110,7 +39225,7 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="C46" s="17">
         <v>2.0</v>
@@ -39124,7 +39239,7 @@
       </c>
       <c r="G46" s="17">
         <f t="shared" si="2"/>
-        <v>2.878363171</v>
+        <v>2.872546267</v>
       </c>
       <c r="H46" s="20">
         <f t="shared" si="3"/>
@@ -39140,7 +39255,7 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>97</v>
+        <v>160</v>
       </c>
       <c r="C47" s="17">
         <v>2.0</v>
@@ -39154,7 +39269,7 @@
       </c>
       <c r="G47" s="17">
         <f t="shared" si="2"/>
-        <v>2.878363171</v>
+        <v>2.872546267</v>
       </c>
       <c r="H47" s="20">
         <f t="shared" si="3"/>
@@ -39170,7 +39285,7 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C48" s="17">
         <v>2.0</v>
@@ -39184,7 +39299,7 @@
       </c>
       <c r="G48" s="17">
         <f t="shared" si="2"/>
-        <v>2.878363171</v>
+        <v>2.872546267</v>
       </c>
       <c r="H48" s="20">
         <f t="shared" si="3"/>
@@ -39200,7 +39315,7 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="C49" s="17">
         <v>2.0</v>
@@ -39214,7 +39329,7 @@
       </c>
       <c r="G49" s="17">
         <f t="shared" si="2"/>
-        <v>2.878363171</v>
+        <v>2.872546267</v>
       </c>
       <c r="H49" s="20">
         <f t="shared" si="3"/>
@@ -39230,7 +39345,7 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="C50" s="17">
         <v>2.0</v>
@@ -39244,7 +39359,7 @@
       </c>
       <c r="G50" s="17">
         <f t="shared" si="2"/>
-        <v>2.878363171</v>
+        <v>2.872546267</v>
       </c>
       <c r="H50" s="20">
         <f t="shared" si="3"/>
@@ -39260,7 +39375,7 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="C51" s="17">
         <v>2.0</v>
@@ -39274,7 +39389,7 @@
       </c>
       <c r="G51" s="17">
         <f t="shared" si="2"/>
-        <v>2.878363171</v>
+        <v>2.872546267</v>
       </c>
       <c r="H51" s="20">
         <f t="shared" si="3"/>
@@ -39290,7 +39405,7 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="C52" s="17">
         <v>2.0</v>
@@ -39304,7 +39419,7 @@
       </c>
       <c r="G52" s="17">
         <f t="shared" si="2"/>
-        <v>2.878363171</v>
+        <v>2.872546267</v>
       </c>
       <c r="H52" s="20">
         <f t="shared" si="3"/>
@@ -39320,7 +39435,7 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="C53" s="17">
         <v>2.0</v>
@@ -39334,7 +39449,7 @@
       </c>
       <c r="G53" s="17">
         <f t="shared" si="2"/>
-        <v>2.878363171</v>
+        <v>2.872546267</v>
       </c>
       <c r="H53" s="20">
         <f t="shared" si="3"/>
@@ -39350,7 +39465,7 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>104</v>
+        <v>165</v>
       </c>
       <c r="C54" s="17">
         <v>2.0</v>
@@ -39364,7 +39479,7 @@
       </c>
       <c r="G54" s="17">
         <f t="shared" si="2"/>
-        <v>2.878363171</v>
+        <v>2.872546267</v>
       </c>
       <c r="H54" s="20">
         <f t="shared" si="3"/>
@@ -39380,7 +39495,7 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="C55" s="17">
         <v>2.0</v>
@@ -39394,7 +39509,7 @@
       </c>
       <c r="G55" s="17">
         <f t="shared" si="2"/>
-        <v>2.878363171</v>
+        <v>2.872546267</v>
       </c>
       <c r="H55" s="20">
         <f t="shared" si="3"/>
@@ -39410,7 +39525,7 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="C56" s="17">
         <v>2.0</v>
@@ -39424,7 +39539,7 @@
       </c>
       <c r="G56" s="17">
         <f t="shared" si="2"/>
-        <v>2.878363171</v>
+        <v>2.872546267</v>
       </c>
       <c r="H56" s="20">
         <f t="shared" si="3"/>
@@ -39440,7 +39555,7 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>107</v>
+        <v>168</v>
       </c>
       <c r="C57" s="17">
         <v>2.0</v>
@@ -39454,7 +39569,7 @@
       </c>
       <c r="G57" s="17">
         <f t="shared" si="2"/>
-        <v>2.878363171</v>
+        <v>2.872546267</v>
       </c>
       <c r="H57" s="20">
         <f t="shared" si="3"/>
@@ -39484,7 +39599,7 @@
       </c>
       <c r="G58" s="17">
         <f t="shared" si="2"/>
-        <v>2.878363171</v>
+        <v>2.872546267</v>
       </c>
       <c r="H58" s="20">
         <f t="shared" si="3"/>
@@ -39500,7 +39615,7 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C59" s="17">
         <v>2.0</v>
@@ -39514,7 +39629,7 @@
       </c>
       <c r="G59" s="17">
         <f t="shared" si="2"/>
-        <v>2.878363171</v>
+        <v>2.872546267</v>
       </c>
       <c r="H59" s="20">
         <f t="shared" si="3"/>
@@ -39530,7 +39645,7 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C60" s="17">
         <v>2.0</v>
@@ -39544,7 +39659,7 @@
       </c>
       <c r="G60" s="17">
         <f t="shared" si="2"/>
-        <v>2.878363171</v>
+        <v>2.872546267</v>
       </c>
       <c r="H60" s="20">
         <f t="shared" si="3"/>
@@ -39560,7 +39675,7 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>111</v>
+        <v>169</v>
       </c>
       <c r="C61" s="17">
         <v>2.0</v>
@@ -39574,7 +39689,7 @@
       </c>
       <c r="G61" s="17">
         <f t="shared" si="2"/>
-        <v>2.878363171</v>
+        <v>2.872546267</v>
       </c>
       <c r="H61" s="20">
         <f t="shared" si="3"/>
@@ -39590,7 +39705,7 @@
         <v>61.0</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="C62" s="17">
         <v>1.0</v>
@@ -39604,7 +39719,7 @@
       </c>
       <c r="G62" s="17">
         <f t="shared" si="2"/>
-        <v>1.439181586</v>
+        <v>1.436273133</v>
       </c>
       <c r="H62" s="20">
         <f t="shared" si="3"/>
@@ -39620,7 +39735,7 @@
         <v>62.0</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C63" s="17">
         <v>1.0</v>
@@ -39634,7 +39749,7 @@
       </c>
       <c r="G63" s="17">
         <f t="shared" si="2"/>
-        <v>1.439181586</v>
+        <v>1.436273133</v>
       </c>
       <c r="H63" s="20">
         <f t="shared" si="3"/>
@@ -39650,7 +39765,7 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C64" s="17">
         <v>1.0</v>
@@ -39664,7 +39779,7 @@
       </c>
       <c r="G64" s="17">
         <f t="shared" si="2"/>
-        <v>1.439181586</v>
+        <v>1.436273133</v>
       </c>
       <c r="H64" s="20">
         <f t="shared" si="3"/>
@@ -39680,7 +39795,7 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="C65" s="17">
         <v>1.0</v>
@@ -39694,7 +39809,7 @@
       </c>
       <c r="G65" s="17">
         <f t="shared" si="2"/>
-        <v>1.439181586</v>
+        <v>1.436273133</v>
       </c>
       <c r="H65" s="20">
         <f t="shared" si="3"/>
@@ -39710,7 +39825,7 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C66" s="17">
         <v>1.0</v>
@@ -39724,7 +39839,7 @@
       </c>
       <c r="G66" s="17">
         <f t="shared" si="2"/>
-        <v>1.439181586</v>
+        <v>1.436273133</v>
       </c>
       <c r="H66" s="20">
         <f t="shared" si="3"/>
@@ -39740,7 +39855,7 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="C67" s="17">
         <v>1.0</v>
@@ -39754,7 +39869,7 @@
       </c>
       <c r="G67" s="17">
         <f t="shared" si="2"/>
-        <v>1.439181586</v>
+        <v>1.436273133</v>
       </c>
       <c r="H67" s="20">
         <f t="shared" si="3"/>
@@ -39770,7 +39885,7 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="C68" s="17">
         <v>1.0</v>
@@ -39784,7 +39899,7 @@
       </c>
       <c r="G68" s="17">
         <f t="shared" si="2"/>
-        <v>1.439181586</v>
+        <v>1.436273133</v>
       </c>
       <c r="H68" s="20">
         <f t="shared" si="3"/>
@@ -39800,7 +39915,7 @@
         <v>68.0</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C69" s="17">
         <v>1.0</v>
@@ -39814,7 +39929,7 @@
       </c>
       <c r="G69" s="17">
         <f t="shared" si="2"/>
-        <v>1.439181586</v>
+        <v>1.436273133</v>
       </c>
       <c r="H69" s="20">
         <f t="shared" si="3"/>
@@ -39830,7 +39945,7 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C70" s="17">
         <v>1.0</v>
@@ -39844,7 +39959,7 @@
       </c>
       <c r="G70" s="17">
         <f t="shared" si="2"/>
-        <v>1.439181586</v>
+        <v>1.436273133</v>
       </c>
       <c r="H70" s="20">
         <f t="shared" si="3"/>
@@ -39860,7 +39975,7 @@
         <v>70.0</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="C71" s="17">
         <v>1.0</v>
@@ -39874,7 +39989,7 @@
       </c>
       <c r="G71" s="17">
         <f t="shared" si="2"/>
-        <v>1.439181586</v>
+        <v>1.436273133</v>
       </c>
       <c r="H71" s="20">
         <f t="shared" si="3"/>
@@ -39890,7 +40005,7 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C72" s="17">
         <v>1.0</v>
@@ -39904,7 +40019,7 @@
       </c>
       <c r="G72" s="17">
         <f t="shared" si="2"/>
-        <v>1.439181586</v>
+        <v>1.436273133</v>
       </c>
       <c r="H72" s="20">
         <f t="shared" si="3"/>
@@ -39919,6 +40034,9 @@
       <c r="A73" s="9">
         <v>72.0</v>
       </c>
+      <c r="B73" s="9" t="s">
+        <v>125</v>
+      </c>
       <c r="C73" s="17">
         <v>1.0</v>
       </c>
@@ -39931,7 +40049,7 @@
       </c>
       <c r="G73" s="17">
         <f t="shared" si="2"/>
-        <v>1.439181586</v>
+        <v>1.436273133</v>
       </c>
       <c r="H73" s="20">
         <f t="shared" si="3"/>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -989,7 +989,7 @@
         <v>1.01</v>
       </c>
       <c r="B2" s="9">
-        <v>7660.0</v>
+        <v>7552.0</v>
       </c>
       <c r="C2" s="10">
         <f t="shared" ref="C2:C73" si="2">1 + --(INT((ROW()-ROW($B$2))/12)=4)
@@ -1009,7 +1009,7 @@
         )
     )
 </f>
-        <v>133.9537944</v>
+        <v>146.0244645</v>
       </c>
       <c r="D2" s="10">
         <f t="shared" ref="D2:D73" si="3">( K2
@@ -1021,7 +1021,7 @@
      )
   ) / 2
 </f>
-        <v>134.5</v>
+        <v>147</v>
       </c>
       <c r="E2" s="10">
         <f t="shared" ref="E2:E73" si="4">(MEDIAN(F2:H2)+AVERAGE(F2:H2))/2
@@ -1039,19 +1039,19 @@
       </c>
       <c r="I2" s="10">
         <f t="shared" ref="I2:I73" si="5">ROUNDDOWN(C2*2,0)</f>
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="J2" s="10">
         <f t="shared" ref="J2:J73" si="6">C2*2 - I2</f>
-        <v>0.9075888904</v>
+        <v>0.04892906141</v>
       </c>
       <c r="K2" s="10">
         <f>I2 + --(RANK(J2,$J$2:$J$73,0) &lt;= 1200*2 - SUM($I$2:$I$73))</f>
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="L2" s="11">
         <f t="shared" ref="L2:L74" si="7">D2</f>
-        <v>134.5</v>
+        <v>147</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
@@ -1060,55 +1060,55 @@
       </c>
       <c r="P2" s="10">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
-        <v>134.5</v>
+        <v>147</v>
       </c>
       <c r="Q2" s="10">
         <f t="shared" si="1"/>
-        <v>101.5</v>
+        <v>112</v>
       </c>
       <c r="R2" s="10">
         <f t="shared" si="1"/>
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="S2" s="10">
         <f t="shared" si="1"/>
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="T2" s="10">
         <f t="shared" si="1"/>
-        <v>72.5</v>
+        <v>80</v>
       </c>
       <c r="U2" s="10">
         <f t="shared" si="1"/>
-        <v>65.5</v>
+        <v>73.5</v>
       </c>
       <c r="V2" s="10">
         <f t="shared" si="1"/>
-        <v>60.5</v>
+        <v>63</v>
       </c>
       <c r="W2" s="10">
         <f t="shared" si="1"/>
-        <v>55</v>
+        <v>54.5</v>
       </c>
       <c r="X2" s="10">
         <f t="shared" si="1"/>
-        <v>50.5</v>
+        <v>48.5</v>
       </c>
       <c r="Y2" s="10">
         <f t="shared" si="1"/>
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Z2" s="10">
         <f t="shared" si="1"/>
-        <v>40.5</v>
+        <v>40</v>
       </c>
       <c r="AA2" s="10">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>34.5</v>
       </c>
       <c r="AB2" s="10">
         <f t="shared" ref="AB2:AB7" si="9">SUM(P2:AA2)</f>
-        <v>834.5</v>
+        <v>883</v>
       </c>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
@@ -1118,15 +1118,15 @@
         <v>1.02</v>
       </c>
       <c r="B3" s="9">
-        <v>5543.0</v>
+        <v>5610.0</v>
       </c>
       <c r="C3" s="10">
         <f t="shared" si="2"/>
-        <v>100.9919999</v>
+        <v>111.0226246</v>
       </c>
       <c r="D3" s="10">
         <f t="shared" si="3"/>
-        <v>101.5</v>
+        <v>112</v>
       </c>
       <c r="E3" s="10">
         <f t="shared" si="4"/>
@@ -1143,11 +1143,11 @@
       </c>
       <c r="I3" s="10">
         <f t="shared" si="5"/>
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="J3" s="10">
         <f t="shared" si="6"/>
-        <v>0.9839998555</v>
+        <v>0.04524926955</v>
       </c>
       <c r="K3" s="10">
         <f t="shared" ref="K3:K73" si="10">MIN(
@@ -1156,11 +1156,11 @@
   K2
 )
 </f>
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="L3" s="11">
         <f t="shared" si="7"/>
-        <v>101.5</v>
+        <v>112</v>
       </c>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
@@ -1169,55 +1169,55 @@
       </c>
       <c r="P3" s="10">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Q3" s="10">
         <f t="shared" si="8"/>
-        <v>29</v>
+        <v>24.5</v>
       </c>
       <c r="R3" s="10">
         <f t="shared" si="8"/>
-        <v>26</v>
+        <v>22.5</v>
       </c>
       <c r="S3" s="10">
         <f t="shared" si="8"/>
-        <v>23.5</v>
+        <v>20.5</v>
       </c>
       <c r="T3" s="10">
         <f t="shared" si="8"/>
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="U3" s="10">
         <f t="shared" si="8"/>
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="V3" s="10">
         <f t="shared" si="8"/>
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="W3" s="10">
         <f t="shared" si="8"/>
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="X3" s="10">
         <f t="shared" si="8"/>
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" s="10">
         <f t="shared" si="8"/>
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z3" s="10">
         <f t="shared" si="8"/>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA3" s="10">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AB3" s="10">
         <f t="shared" si="9"/>
-        <v>228.5</v>
+        <v>203</v>
       </c>
       <c r="AC3" s="5"/>
       <c r="AD3" s="5"/>
@@ -1227,15 +1227,15 @@
         <v>1.03</v>
       </c>
       <c r="B4" s="9">
-        <v>5428.0</v>
+        <v>5328.0</v>
       </c>
       <c r="C4" s="10">
         <f t="shared" si="2"/>
-        <v>89.38178209</v>
+        <v>96.79340493</v>
       </c>
       <c r="D4" s="10">
         <f t="shared" si="3"/>
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E4" s="10">
         <f t="shared" si="4"/>
@@ -1252,19 +1252,19 @@
       </c>
       <c r="I4" s="10">
         <f t="shared" si="5"/>
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="J4" s="10">
         <f t="shared" si="6"/>
-        <v>0.7635641715</v>
+        <v>0.5868098528</v>
       </c>
       <c r="K4" s="10">
         <f t="shared" si="10"/>
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="L4" s="11">
         <f t="shared" si="7"/>
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
@@ -1273,55 +1273,55 @@
       </c>
       <c r="P4" s="10">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q4" s="10">
         <f t="shared" si="11"/>
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="R4" s="10">
         <f t="shared" si="11"/>
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="S4" s="10">
         <f t="shared" si="11"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T4" s="10">
         <f t="shared" si="11"/>
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="U4" s="10">
         <f t="shared" si="11"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V4" s="10">
         <f t="shared" si="11"/>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="W4" s="10">
         <f t="shared" si="11"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X4" s="10">
         <f t="shared" si="11"/>
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="Y4" s="10">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Z4" s="10">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA4" s="10">
         <f t="shared" si="11"/>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AB4" s="10">
         <f t="shared" si="9"/>
-        <v>70.5</v>
+        <v>60.5</v>
       </c>
       <c r="AC4" s="5"/>
       <c r="AD4" s="5"/>
@@ -1331,15 +1331,15 @@
         <v>1.04</v>
       </c>
       <c r="B5" s="9">
-        <v>5351.0</v>
+        <v>5124.0</v>
       </c>
       <c r="C5" s="10">
         <f t="shared" si="2"/>
-        <v>82.68227902</v>
+        <v>88.1976102</v>
       </c>
       <c r="D5" s="10">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E5" s="10">
         <f t="shared" si="4"/>
@@ -1356,19 +1356,19 @@
       </c>
       <c r="I5" s="10">
         <f t="shared" si="5"/>
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="J5" s="10">
         <f t="shared" si="6"/>
-        <v>0.3645580416</v>
+        <v>0.3952204032</v>
       </c>
       <c r="K5" s="10">
         <f t="shared" si="10"/>
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L5" s="11">
         <f t="shared" si="7"/>
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
@@ -1377,55 +1377,55 @@
       </c>
       <c r="P5" s="10">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" s="10">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R5" s="10">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="S5" s="10">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T5" s="10">
         <f t="shared" si="12"/>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="U5" s="10">
         <f t="shared" si="12"/>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="V5" s="10">
         <f t="shared" si="12"/>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="W5" s="10">
         <f t="shared" si="12"/>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="X5" s="10">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Y5" s="10">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" s="10">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AA5" s="10">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AB5" s="10">
         <f t="shared" si="9"/>
-        <v>30.5</v>
+        <v>23.5</v>
       </c>
       <c r="AC5" s="5"/>
       <c r="AD5" s="5"/>
@@ -1435,15 +1435,15 @@
         <v>1.05</v>
       </c>
       <c r="B6" s="9">
-        <v>4887.0</v>
+        <v>4886.0</v>
       </c>
       <c r="C6" s="10">
         <f t="shared" si="2"/>
-        <v>72.01382412</v>
+        <v>78.82067948</v>
       </c>
       <c r="D6" s="10">
         <f t="shared" si="3"/>
-        <v>72.5</v>
+        <v>80</v>
       </c>
       <c r="E6" s="10">
         <f t="shared" si="4"/>
@@ -1460,19 +1460,19 @@
       </c>
       <c r="I6" s="10">
         <f t="shared" si="5"/>
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="J6" s="10">
         <f t="shared" si="6"/>
-        <v>0.02764823796</v>
+        <v>0.6413589668</v>
       </c>
       <c r="K6" s="10">
         <f t="shared" si="10"/>
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="L6" s="11">
         <f t="shared" si="7"/>
-        <v>72.5</v>
+        <v>80</v>
       </c>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
@@ -1481,55 +1481,55 @@
       </c>
       <c r="P6" s="10">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q6" s="10">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R6" s="10">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="S6" s="10">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T6" s="10">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="U6" s="10">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="V6" s="10">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="W6" s="10">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="X6" s="10">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Y6" s="10">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" s="10">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AA6" s="10">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AB6" s="10">
         <f t="shared" si="9"/>
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AC6" s="5"/>
       <c r="AD6" s="5"/>
@@ -1539,15 +1539,15 @@
         <v>1.06</v>
       </c>
       <c r="B7" s="9">
-        <v>4647.0</v>
+        <v>4811.0</v>
       </c>
       <c r="C7" s="10">
         <f t="shared" si="2"/>
-        <v>64.85125191</v>
+        <v>72.47508107</v>
       </c>
       <c r="D7" s="10">
         <f t="shared" si="3"/>
-        <v>65.5</v>
+        <v>73.5</v>
       </c>
       <c r="E7" s="10">
         <f t="shared" si="4"/>
@@ -1564,19 +1564,19 @@
       </c>
       <c r="I7" s="10">
         <f t="shared" si="5"/>
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="J7" s="10">
         <f t="shared" si="6"/>
-        <v>0.7025038107</v>
+        <v>0.9501621308</v>
       </c>
       <c r="K7" s="10">
         <f t="shared" si="10"/>
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="L7" s="11">
         <f t="shared" si="7"/>
-        <v>65.5</v>
+        <v>73.5</v>
       </c>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
@@ -1643,15 +1643,15 @@
         <v>1.07</v>
       </c>
       <c r="B8" s="9">
-        <v>4640.0</v>
+        <v>4211.0</v>
       </c>
       <c r="C8" s="10">
         <f t="shared" si="2"/>
-        <v>59.95933081</v>
+        <v>61.85932775</v>
       </c>
       <c r="D8" s="10">
         <f t="shared" si="3"/>
-        <v>60.5</v>
+        <v>63</v>
       </c>
       <c r="E8" s="10">
         <f t="shared" si="4"/>
@@ -1668,70 +1668,70 @@
       </c>
       <c r="I8" s="10">
         <f t="shared" si="5"/>
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="J8" s="10">
         <f t="shared" si="6"/>
-        <v>0.9186616216</v>
+        <v>0.7186555071</v>
       </c>
       <c r="K8" s="10">
         <f t="shared" si="10"/>
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="L8" s="11">
         <f t="shared" si="7"/>
-        <v>60.5</v>
+        <v>63</v>
       </c>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
       <c r="P8" s="10">
         <f t="shared" ref="P8:AB8" si="15">SUM(P2:P7)</f>
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="Q8" s="10">
         <f t="shared" si="15"/>
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="R8" s="10">
         <f t="shared" si="15"/>
-        <v>129.5</v>
+        <v>132.5</v>
       </c>
       <c r="S8" s="10">
         <f t="shared" si="15"/>
-        <v>119.5</v>
+        <v>120</v>
       </c>
       <c r="T8" s="10">
         <f t="shared" si="15"/>
-        <v>105.5</v>
+        <v>108.5</v>
       </c>
       <c r="U8" s="10">
         <f t="shared" si="15"/>
-        <v>95.5</v>
+        <v>99.5</v>
       </c>
       <c r="V8" s="10">
         <f t="shared" si="15"/>
-        <v>87.5</v>
+        <v>87</v>
       </c>
       <c r="W8" s="10">
         <f t="shared" si="15"/>
-        <v>80.5</v>
+        <v>76.5</v>
       </c>
       <c r="X8" s="10">
         <f t="shared" si="15"/>
-        <v>74</v>
+        <v>68.5</v>
       </c>
       <c r="Y8" s="10">
         <f t="shared" si="15"/>
-        <v>66.5</v>
+        <v>61.5</v>
       </c>
       <c r="Z8" s="10">
         <f t="shared" si="15"/>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="AA8" s="10">
         <f t="shared" si="15"/>
-        <v>54.5</v>
+        <v>51</v>
       </c>
       <c r="AB8" s="10">
         <f t="shared" si="15"/>
@@ -1745,15 +1745,15 @@
         <v>1.08</v>
       </c>
       <c r="B9" s="9">
-        <v>4440.0</v>
+        <v>3731.0</v>
       </c>
       <c r="C9" s="10">
         <f t="shared" si="2"/>
-        <v>54.36054894</v>
+        <v>53.60083706</v>
       </c>
       <c r="D9" s="10">
         <f t="shared" si="3"/>
-        <v>55</v>
+        <v>54.5</v>
       </c>
       <c r="E9" s="10">
         <f t="shared" si="4"/>
@@ -1770,19 +1770,19 @@
       </c>
       <c r="I9" s="10">
         <f t="shared" si="5"/>
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J9" s="10">
         <f t="shared" si="6"/>
-        <v>0.7210978795</v>
+        <v>0.2016741119</v>
       </c>
       <c r="K9" s="10">
         <f t="shared" si="10"/>
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L9" s="11">
         <f t="shared" si="7"/>
-        <v>55</v>
+        <v>54.5</v>
       </c>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
@@ -1808,15 +1808,15 @@
         <v>1.09</v>
       </c>
       <c r="B10" s="9">
-        <v>4352.0</v>
+        <v>3458.0</v>
       </c>
       <c r="C10" s="10">
         <f t="shared" si="2"/>
-        <v>49.76603403</v>
+        <v>47.54168514</v>
       </c>
       <c r="D10" s="10">
         <f t="shared" si="3"/>
-        <v>50.5</v>
+        <v>48.5</v>
       </c>
       <c r="E10" s="10">
         <f t="shared" si="4"/>
@@ -1833,19 +1833,19 @@
       </c>
       <c r="I10" s="10">
         <f t="shared" si="5"/>
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="J10" s="10">
         <f t="shared" si="6"/>
-        <v>0.5320680636</v>
+        <v>0.08337028504</v>
       </c>
       <c r="K10" s="10">
         <f t="shared" si="10"/>
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L10" s="11">
         <f t="shared" si="7"/>
-        <v>50.5</v>
+        <v>48.5</v>
       </c>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
@@ -1871,15 +1871,15 @@
         <v>1.1</v>
       </c>
       <c r="B11" s="9">
-        <v>4277.0</v>
+        <v>3375.0</v>
       </c>
       <c r="C11" s="10">
         <f t="shared" si="2"/>
-        <v>44.38780232</v>
+        <v>42.18333691</v>
       </c>
       <c r="D11" s="10">
         <f t="shared" si="3"/>
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E11" s="10">
         <f t="shared" si="4"/>
@@ -1896,19 +1896,19 @@
       </c>
       <c r="I11" s="10">
         <f t="shared" si="5"/>
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J11" s="10">
         <f t="shared" si="6"/>
-        <v>0.7756046318</v>
+        <v>0.3666738246</v>
       </c>
       <c r="K11" s="10">
         <f t="shared" si="10"/>
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="L11" s="11">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -1934,15 +1934,15 @@
         <v>1.11</v>
       </c>
       <c r="B12" s="9">
-        <v>4071.0</v>
+        <v>3348.0</v>
       </c>
       <c r="C12" s="10">
         <f t="shared" si="2"/>
-        <v>40.0016894</v>
+        <v>38.95212006</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="3"/>
-        <v>40.5</v>
+        <v>40</v>
       </c>
       <c r="E12" s="10">
         <f t="shared" si="4"/>
@@ -1959,19 +1959,19 @@
       </c>
       <c r="I12" s="10">
         <f t="shared" si="5"/>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J12" s="10">
         <f t="shared" si="6"/>
-        <v>0.003378792016</v>
+        <v>0.9042401243</v>
       </c>
       <c r="K12" s="10">
         <f t="shared" si="10"/>
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L12" s="11">
         <f t="shared" si="7"/>
-        <v>40.5</v>
+        <v>40</v>
       </c>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
@@ -1997,15 +1997,15 @@
         <v>1.12</v>
       </c>
       <c r="B13" s="9">
-        <v>3962.0</v>
+        <v>3060.0</v>
       </c>
       <c r="C13" s="10">
         <f t="shared" si="2"/>
-        <v>35.51785008</v>
+        <v>33.33899008</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>34.5</v>
       </c>
       <c r="E13" s="10">
         <f t="shared" si="4"/>
@@ -2022,19 +2022,19 @@
       </c>
       <c r="I13" s="10">
         <f t="shared" si="5"/>
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="J13" s="10">
         <f t="shared" si="6"/>
-        <v>0.03570016782</v>
+        <v>0.6779801635</v>
       </c>
       <c r="K13" s="10">
         <f t="shared" si="10"/>
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="L13" s="11">
         <f t="shared" si="7"/>
-        <v>36</v>
+        <v>34.5</v>
       </c>
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
@@ -2060,15 +2060,15 @@
         <v>2.01</v>
       </c>
       <c r="B14" s="9">
-        <v>3841.0</v>
+        <v>2817.0</v>
       </c>
       <c r="C14" s="10">
         <f t="shared" si="2"/>
-        <v>31.77784632</v>
+        <v>28.95462706</v>
       </c>
       <c r="D14" s="10">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E14" s="10">
         <f t="shared" si="4"/>
@@ -2085,19 +2085,19 @@
       </c>
       <c r="I14" s="10">
         <f t="shared" si="5"/>
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="J14" s="10">
         <f t="shared" si="6"/>
-        <v>0.555692644</v>
+        <v>0.9092541106</v>
       </c>
       <c r="K14" s="10">
         <f t="shared" si="10"/>
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="L14" s="11">
         <f t="shared" si="7"/>
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
@@ -2123,15 +2123,15 @@
         <v>2.02</v>
       </c>
       <c r="B15" s="9">
-        <v>3808.0</v>
+        <v>2486.0</v>
       </c>
       <c r="C15" s="10">
         <f t="shared" si="2"/>
-        <v>28.88389075</v>
+        <v>24.64613739</v>
       </c>
       <c r="D15" s="10">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>24.5</v>
       </c>
       <c r="E15" s="10">
         <f t="shared" si="4"/>
@@ -2148,19 +2148,19 @@
       </c>
       <c r="I15" s="10">
         <f t="shared" si="5"/>
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="J15" s="10">
         <f t="shared" si="6"/>
-        <v>0.7677815012</v>
+        <v>0.2922747722</v>
       </c>
       <c r="K15" s="10">
         <f t="shared" si="10"/>
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L15" s="11">
         <f t="shared" si="7"/>
-        <v>29</v>
+        <v>24.5</v>
       </c>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
@@ -2186,15 +2186,15 @@
         <v>2.03</v>
       </c>
       <c r="B16" s="9">
-        <v>3683.0</v>
+        <v>2454.0</v>
       </c>
       <c r="C16" s="10">
         <f t="shared" si="2"/>
-        <v>26.23082668</v>
+        <v>22.67443769</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>22.5</v>
       </c>
       <c r="E16" s="10">
         <f t="shared" si="4"/>
@@ -2211,19 +2211,19 @@
       </c>
       <c r="I16" s="10">
         <f t="shared" si="5"/>
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="J16" s="10">
         <f t="shared" si="6"/>
-        <v>0.4616533503</v>
+        <v>0.3488753704</v>
       </c>
       <c r="K16" s="10">
         <f t="shared" si="10"/>
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="L16" s="11">
         <f t="shared" si="7"/>
-        <v>26</v>
+        <v>22.5</v>
       </c>
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
@@ -2249,15 +2249,15 @@
         <v>2.04</v>
       </c>
       <c r="B17" s="9">
-        <v>3508.0</v>
+        <v>2382.0</v>
       </c>
       <c r="C17" s="10">
         <f t="shared" si="2"/>
-        <v>23.47489006</v>
+        <v>20.53923953</v>
       </c>
       <c r="D17" s="10">
         <f t="shared" si="3"/>
-        <v>23.5</v>
+        <v>20.5</v>
       </c>
       <c r="E17" s="10">
         <f t="shared" si="4"/>
@@ -2274,19 +2274,19 @@
       </c>
       <c r="I17" s="10">
         <f t="shared" si="5"/>
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J17" s="10">
         <f t="shared" si="6"/>
-        <v>0.9497801196</v>
+        <v>0.07847905937</v>
       </c>
       <c r="K17" s="10">
         <f t="shared" si="10"/>
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="L17" s="11">
         <f t="shared" si="7"/>
-        <v>23.5</v>
+        <v>20.5</v>
       </c>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
@@ -2312,15 +2312,15 @@
         <v>2.05</v>
       </c>
       <c r="B18" s="9">
-        <v>3440.0</v>
+        <v>2314.0</v>
       </c>
       <c r="C18" s="10">
         <f t="shared" si="2"/>
-        <v>21.1911087</v>
+        <v>18.43045161</v>
       </c>
       <c r="D18" s="10">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="E18" s="10">
         <f t="shared" si="4"/>
@@ -2337,19 +2337,19 @@
       </c>
       <c r="I18" s="10">
         <f t="shared" si="5"/>
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J18" s="10">
         <f t="shared" si="6"/>
-        <v>0.3822174041</v>
+        <v>0.8609032195</v>
       </c>
       <c r="K18" s="10">
         <f t="shared" si="10"/>
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="L18" s="11">
         <f t="shared" si="7"/>
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="M18" s="7"/>
       <c r="N18" s="7"/>
@@ -2375,15 +2375,15 @@
         <v>2.06</v>
       </c>
       <c r="B19" s="9">
-        <v>3140.0</v>
+        <v>2140.0</v>
       </c>
       <c r="C19" s="10">
         <f t="shared" si="2"/>
-        <v>18.65149366</v>
+        <v>16.42707243</v>
       </c>
       <c r="D19" s="10">
         <f t="shared" si="3"/>
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="E19" s="10">
         <f t="shared" si="4"/>
@@ -2400,19 +2400,19 @@
       </c>
       <c r="I19" s="10">
         <f t="shared" si="5"/>
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J19" s="10">
         <f t="shared" si="6"/>
-        <v>0.3029873246</v>
+        <v>0.8541448641</v>
       </c>
       <c r="K19" s="10">
         <f t="shared" si="10"/>
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="L19" s="11">
         <f t="shared" si="7"/>
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="M19" s="7"/>
       <c r="N19" s="7"/>
@@ -2438,15 +2438,15 @@
         <v>2.07</v>
       </c>
       <c r="B20" s="9">
-        <v>3024.0</v>
+        <v>2127.0</v>
       </c>
       <c r="C20" s="10">
         <f t="shared" si="2"/>
-        <v>16.74204307</v>
+        <v>14.99983348</v>
       </c>
       <c r="D20" s="10">
         <f t="shared" si="3"/>
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="E20" s="10">
         <f t="shared" si="4"/>
@@ -2463,19 +2463,19 @@
       </c>
       <c r="I20" s="10">
         <f t="shared" si="5"/>
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J20" s="10">
         <f t="shared" si="6"/>
-        <v>0.4840861454</v>
+        <v>0.999666969</v>
       </c>
       <c r="K20" s="10">
         <f t="shared" si="10"/>
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="L20" s="11">
         <f t="shared" si="7"/>
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="M20" s="7"/>
       <c r="N20" s="7"/>
@@ -2501,15 +2501,15 @@
         <v>2.08</v>
       </c>
       <c r="B21" s="9">
-        <v>2901.0</v>
+        <v>2081.0</v>
       </c>
       <c r="C21" s="10">
         <f t="shared" si="2"/>
-        <v>15.11863921</v>
+        <v>13.70865748</v>
       </c>
       <c r="D21" s="10">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="E21" s="10">
         <f t="shared" si="4"/>
@@ -2526,19 +2526,19 @@
       </c>
       <c r="I21" s="10">
         <f t="shared" si="5"/>
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J21" s="10">
         <f t="shared" si="6"/>
-        <v>0.2372784142</v>
+        <v>0.4173149644</v>
       </c>
       <c r="K21" s="10">
         <f t="shared" si="10"/>
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L21" s="11">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="M21" s="7"/>
       <c r="N21" s="7"/>
@@ -2564,15 +2564,15 @@
         <v>2.09</v>
       </c>
       <c r="B22" s="9">
-        <v>2887.0</v>
+        <v>2077.0</v>
       </c>
       <c r="C22" s="10">
         <f t="shared" si="2"/>
-        <v>13.85976068</v>
+        <v>12.58031062</v>
       </c>
       <c r="D22" s="10">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="E22" s="10">
         <f t="shared" si="4"/>
@@ -2589,19 +2589,19 @@
       </c>
       <c r="I22" s="10">
         <f t="shared" si="5"/>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J22" s="10">
         <f t="shared" si="6"/>
-        <v>0.719521356</v>
+        <v>0.1606212337</v>
       </c>
       <c r="K22" s="10">
         <f t="shared" si="10"/>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L22" s="11">
         <f t="shared" si="7"/>
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
@@ -2627,15 +2627,15 @@
         <v>2.1</v>
       </c>
       <c r="B23" s="9">
-        <v>2769.0</v>
+        <v>1935.0</v>
       </c>
       <c r="C23" s="10">
         <f t="shared" si="2"/>
-        <v>12.29417089</v>
+        <v>10.99372871</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="E23" s="10">
         <f t="shared" si="4"/>
@@ -2652,19 +2652,19 @@
       </c>
       <c r="I23" s="10">
         <f t="shared" si="5"/>
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J23" s="10">
         <f t="shared" si="6"/>
-        <v>0.5883417803</v>
+        <v>0.9874574247</v>
       </c>
       <c r="K23" s="10">
         <f t="shared" si="10"/>
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L23" s="11">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="M23" s="7"/>
       <c r="N23" s="7"/>
@@ -2690,15 +2690,15 @@
         <v>2.11</v>
       </c>
       <c r="B24" s="9">
-        <v>2446.0</v>
+        <v>1881.0</v>
       </c>
       <c r="C24" s="10">
         <f t="shared" si="2"/>
-        <v>10.63754613</v>
+        <v>10.03474313</v>
       </c>
       <c r="D24" s="10">
         <f t="shared" si="3"/>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="E24" s="10">
         <f t="shared" si="4"/>
@@ -2715,19 +2715,19 @@
       </c>
       <c r="I24" s="10">
         <f t="shared" si="5"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J24" s="10">
         <f t="shared" si="6"/>
-        <v>0.2750922692</v>
+        <v>0.06948625293</v>
       </c>
       <c r="K24" s="10">
         <f t="shared" si="10"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L24" s="11">
         <f t="shared" si="7"/>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="M24" s="7"/>
       <c r="N24" s="7"/>
@@ -2753,15 +2753,15 @@
         <v>2.12</v>
       </c>
       <c r="B25" s="9">
-        <v>2436.0</v>
+        <v>1853.0</v>
       </c>
       <c r="C25" s="10">
         <f t="shared" si="2"/>
-        <v>9.961820154</v>
+        <v>9.356469288</v>
       </c>
       <c r="D25" s="10">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="E25" s="10">
         <f t="shared" si="4"/>
@@ -2778,19 +2778,19 @@
       </c>
       <c r="I25" s="10">
         <f t="shared" si="5"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J25" s="10">
         <f t="shared" si="6"/>
-        <v>0.923640308</v>
+        <v>0.7129385758</v>
       </c>
       <c r="K25" s="10">
         <f t="shared" si="10"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L25" s="11">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
@@ -2816,15 +2816,15 @@
         <v>3.01</v>
       </c>
       <c r="B26" s="9">
-        <v>2412.0</v>
+        <v>1660.0</v>
       </c>
       <c r="C26" s="10">
         <f t="shared" si="2"/>
-        <v>9.128907957</v>
+        <v>8.175029908</v>
       </c>
       <c r="D26" s="10">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26" s="10">
         <f t="shared" si="4"/>
@@ -2841,19 +2841,19 @@
       </c>
       <c r="I26" s="10">
         <f t="shared" si="5"/>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J26" s="10">
         <f t="shared" si="6"/>
-        <v>0.2578159146</v>
+        <v>0.3500598154</v>
       </c>
       <c r="K26" s="10">
         <f t="shared" si="10"/>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L26" s="11">
         <f t="shared" si="7"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M26" s="7"/>
       <c r="N26" s="7"/>
@@ -2879,15 +2879,15 @@
         <v>3.02</v>
       </c>
       <c r="B27" s="9">
-        <v>2367.0</v>
+        <v>1642.0</v>
       </c>
       <c r="C27" s="10">
         <f t="shared" si="2"/>
-        <v>8.424966136</v>
+        <v>7.58717066</v>
       </c>
       <c r="D27" s="10">
         <f t="shared" si="3"/>
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="E27" s="10">
         <f t="shared" si="4"/>
@@ -2904,19 +2904,19 @@
       </c>
       <c r="I27" s="10">
         <f t="shared" si="5"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J27" s="10">
         <f t="shared" si="6"/>
-        <v>0.8499322724</v>
+        <v>0.1743413199</v>
       </c>
       <c r="K27" s="10">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L27" s="11">
         <f t="shared" si="7"/>
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
@@ -2942,15 +2942,15 @@
         <v>3.03</v>
       </c>
       <c r="B28" s="9">
-        <v>2319.0</v>
+        <v>1579.0</v>
       </c>
       <c r="C28" s="10">
         <f t="shared" si="2"/>
-        <v>7.656667123</v>
+        <v>6.840061315</v>
       </c>
       <c r="D28" s="10">
         <f t="shared" si="3"/>
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="E28" s="10">
         <f t="shared" si="4"/>
@@ -2967,19 +2967,19 @@
       </c>
       <c r="I28" s="10">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J28" s="10">
         <f t="shared" si="6"/>
-        <v>0.3133342455</v>
+        <v>0.6801226303</v>
       </c>
       <c r="K28" s="10">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L28" s="11">
         <f t="shared" si="7"/>
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="M28" s="7"/>
       <c r="N28" s="7"/>
@@ -3005,15 +3005,15 @@
         <v>3.04</v>
       </c>
       <c r="B29" s="9">
-        <v>2190.0</v>
+        <v>1544.0</v>
       </c>
       <c r="C29" s="10">
         <f t="shared" si="2"/>
-        <v>6.864574946</v>
+        <v>6.247379098</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E29" s="10">
         <f t="shared" si="4"/>
@@ -3030,19 +3030,19 @@
       </c>
       <c r="I29" s="10">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J29" s="10">
         <f t="shared" si="6"/>
-        <v>0.729149893</v>
+        <v>0.4947581954</v>
       </c>
       <c r="K29" s="10">
         <f t="shared" si="10"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L29" s="11">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M29" s="7"/>
       <c r="N29" s="7"/>
@@ -3086,15 +3086,15 @@
         <v>3.05</v>
       </c>
       <c r="B30" s="9">
-        <v>2125.0</v>
+        <v>1224.0</v>
       </c>
       <c r="C30" s="10">
         <f t="shared" si="2"/>
-        <v>6.315443152</v>
+        <v>5.304672514</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="3"/>
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="E30" s="10">
         <f t="shared" si="4"/>
@@ -3111,19 +3111,19 @@
       </c>
       <c r="I30" s="10">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J30" s="10">
         <f t="shared" si="6"/>
-        <v>0.6308863033</v>
+        <v>0.6093450284</v>
       </c>
       <c r="K30" s="10">
         <f t="shared" si="10"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L30" s="11">
         <f t="shared" si="7"/>
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="M30" s="7"/>
       <c r="N30" s="7"/>
@@ -3167,15 +3167,15 @@
         <v>3.06</v>
       </c>
       <c r="B31" s="9">
-        <v>2094.0</v>
+        <v>1146.0</v>
       </c>
       <c r="C31" s="10">
         <f t="shared" si="2"/>
-        <v>5.845066575</v>
+        <v>4.832186763</v>
       </c>
       <c r="D31" s="10">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31" s="10">
         <f t="shared" si="4"/>
@@ -3192,19 +3192,19 @@
       </c>
       <c r="I31" s="10">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J31" s="10">
         <f t="shared" si="6"/>
-        <v>0.6901331501</v>
+        <v>0.6643735259</v>
       </c>
       <c r="K31" s="10">
         <f t="shared" si="10"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L31" s="11">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M31" s="7"/>
       <c r="N31" s="7"/>
@@ -3248,15 +3248,15 @@
         <v>3.07</v>
       </c>
       <c r="B32" s="9">
-        <v>2061.0</v>
+        <v>1118.0</v>
       </c>
       <c r="C32" s="10">
         <f t="shared" si="2"/>
-        <v>5.23203327</v>
+        <v>4.296964141</v>
       </c>
       <c r="D32" s="10">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="E32" s="10">
         <f t="shared" si="4"/>
@@ -3273,19 +3273,19 @@
       </c>
       <c r="I32" s="10">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J32" s="10">
         <f t="shared" si="6"/>
-        <v>0.4640665396</v>
+        <v>0.5939282828</v>
       </c>
       <c r="K32" s="10">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L32" s="11">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="M32" s="7"/>
       <c r="N32" s="7"/>
@@ -3329,15 +3329,15 @@
         <v>3.08</v>
       </c>
       <c r="B33" s="9">
-        <v>1957.0</v>
+        <v>1078.0</v>
       </c>
       <c r="C33" s="10">
         <f t="shared" si="2"/>
-        <v>4.757468998</v>
+        <v>3.958928692</v>
       </c>
       <c r="D33" s="10">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E33" s="10">
         <f t="shared" si="4"/>
@@ -3354,19 +3354,19 @@
       </c>
       <c r="I33" s="10">
         <f t="shared" si="5"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J33" s="10">
         <f t="shared" si="6"/>
-        <v>0.5149379963</v>
+        <v>0.9178573833</v>
       </c>
       <c r="K33" s="10">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L33" s="11">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -3410,15 +3410,15 @@
         <v>3.09</v>
       </c>
       <c r="B34" s="9">
-        <v>1907.0</v>
+        <v>1050.0</v>
       </c>
       <c r="C34" s="10">
         <f t="shared" si="2"/>
-        <v>4.339154724</v>
+        <v>3.619890895</v>
       </c>
       <c r="D34" s="10">
         <f t="shared" si="3"/>
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="E34" s="10">
         <f t="shared" si="4"/>
@@ -3435,19 +3435,19 @@
       </c>
       <c r="I34" s="10">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J34" s="10">
         <f t="shared" si="6"/>
-        <v>0.678309448</v>
+        <v>0.2397817903</v>
       </c>
       <c r="K34" s="10">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L34" s="11">
         <f t="shared" si="7"/>
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="M34" s="7"/>
       <c r="N34" s="7"/>
@@ -3491,15 +3491,15 @@
         <v>3.1</v>
       </c>
       <c r="B35" s="9">
-        <v>1865.0</v>
+        <v>1023.0</v>
       </c>
       <c r="C35" s="10">
         <f t="shared" si="2"/>
-        <v>4.113323206</v>
+        <v>3.459318147</v>
       </c>
       <c r="D35" s="10">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E35" s="10">
         <f t="shared" si="4"/>
@@ -3516,19 +3516,19 @@
       </c>
       <c r="I35" s="10">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J35" s="10">
         <f t="shared" si="6"/>
-        <v>0.2266464123</v>
+        <v>0.9186362948</v>
       </c>
       <c r="K35" s="10">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L35" s="11">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="M35" s="7"/>
       <c r="N35" s="7"/>
@@ -3572,15 +3572,15 @@
         <v>3.11</v>
       </c>
       <c r="B36" s="9">
-        <v>1837.0</v>
+        <v>992.0</v>
       </c>
       <c r="C36" s="10">
         <f t="shared" si="2"/>
-        <v>3.753799375</v>
+        <v>3.142677043</v>
       </c>
       <c r="D36" s="10">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" s="10">
         <f t="shared" si="4"/>
@@ -3597,19 +3597,19 @@
       </c>
       <c r="I36" s="10">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J36" s="10">
         <f t="shared" si="6"/>
-        <v>0.5075987505</v>
+        <v>0.2853540857</v>
       </c>
       <c r="K36" s="10">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L36" s="11">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M36" s="7"/>
       <c r="N36" s="7"/>
@@ -3653,15 +3653,15 @@
         <v>3.12</v>
       </c>
       <c r="B37" s="9">
-        <v>1782.0</v>
+        <v>925.0</v>
       </c>
       <c r="C37" s="10">
         <f t="shared" si="2"/>
-        <v>3.58305667</v>
+        <v>2.999911193</v>
       </c>
       <c r="D37" s="10">
         <f t="shared" si="3"/>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="E37" s="10">
         <f t="shared" si="4"/>
@@ -3678,19 +3678,19 @@
       </c>
       <c r="I37" s="10">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J37" s="10">
         <f t="shared" si="6"/>
-        <v>0.1661133392</v>
+        <v>0.9998223863</v>
       </c>
       <c r="K37" s="10">
         <f t="shared" si="10"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L37" s="11">
         <f t="shared" si="7"/>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="M37" s="7"/>
       <c r="N37" s="7"/>
@@ -3734,15 +3734,15 @@
         <v>4.01</v>
       </c>
       <c r="B38" s="9">
-        <v>1771.0</v>
+        <v>905.0</v>
       </c>
       <c r="C38" s="10">
         <f t="shared" si="2"/>
-        <v>3.298318867</v>
+        <v>2.750522535</v>
       </c>
       <c r="D38" s="10">
         <f t="shared" si="3"/>
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="E38" s="10">
         <f t="shared" si="4"/>
@@ -3759,19 +3759,19 @@
       </c>
       <c r="I38" s="10">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J38" s="10">
         <f t="shared" si="6"/>
-        <v>0.5966377345</v>
+        <v>0.5010450695</v>
       </c>
       <c r="K38" s="10">
         <f t="shared" si="10"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L38" s="11">
         <f t="shared" si="7"/>
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="M38" s="7"/>
       <c r="N38" s="7"/>
@@ -3815,15 +3815,15 @@
         <v>4.02</v>
       </c>
       <c r="B39" s="9">
-        <v>1714.0</v>
+        <v>884.0</v>
       </c>
       <c r="C39" s="10">
         <f t="shared" si="2"/>
-        <v>3.122265286</v>
+        <v>2.639344433</v>
       </c>
       <c r="D39" s="10">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="E39" s="10">
         <f t="shared" si="4"/>
@@ -3840,19 +3840,19 @@
       </c>
       <c r="I39" s="10">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J39" s="10">
         <f t="shared" si="6"/>
-        <v>0.2445305714</v>
+        <v>0.2786888661</v>
       </c>
       <c r="K39" s="10">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L39" s="11">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M39" s="7"/>
       <c r="N39" s="7"/>
@@ -3896,15 +3896,15 @@
         <v>4.03</v>
       </c>
       <c r="B40" s="9">
-        <v>1683.0</v>
+        <v>725.0</v>
       </c>
       <c r="C40" s="10">
         <f t="shared" si="2"/>
-        <v>2.845924425</v>
+        <v>2.300340716</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="E40" s="10">
         <f t="shared" si="4"/>
@@ -3921,19 +3921,19 @@
       </c>
       <c r="I40" s="10">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="6"/>
-        <v>0.6918488493</v>
+        <v>0.6006814316</v>
       </c>
       <c r="K40" s="10">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L40" s="11">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M40" s="7"/>
       <c r="N40" s="7"/>
@@ -3977,15 +3977,15 @@
         <v>4.04</v>
       </c>
       <c r="B41" s="9">
-        <v>1672.0</v>
+        <v>693.0</v>
       </c>
       <c r="C41" s="10">
         <f t="shared" si="2"/>
-        <v>2.75563629</v>
+        <v>2.236209353</v>
       </c>
       <c r="D41" s="10">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" s="10">
         <f t="shared" si="4"/>
@@ -4002,19 +4002,19 @@
       </c>
       <c r="I41" s="10">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J41" s="10">
         <f t="shared" si="6"/>
-        <v>0.5112725794</v>
+        <v>0.4724187054</v>
       </c>
       <c r="K41" s="10">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L41" s="11">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
@@ -4058,15 +4058,15 @@
         <v>4.05</v>
       </c>
       <c r="B42" s="13">
-        <v>1619.0</v>
+        <v>681.0</v>
       </c>
       <c r="C42" s="10">
         <f t="shared" si="2"/>
-        <v>2.485574312</v>
+        <v>2.027585731</v>
       </c>
       <c r="D42" s="10">
         <f t="shared" si="3"/>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E42" s="10">
         <f t="shared" si="4"/>
@@ -4087,15 +4087,15 @@
       </c>
       <c r="J42" s="10">
         <f t="shared" si="6"/>
-        <v>0.9711486246</v>
+        <v>0.05517146174</v>
       </c>
       <c r="K42" s="10">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L42" s="11">
         <f t="shared" si="7"/>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
@@ -4130,15 +4130,15 @@
         <v>4.06</v>
       </c>
       <c r="B43" s="9">
-        <v>1601.0</v>
+        <v>643.0</v>
       </c>
       <c r="C43" s="10">
         <f t="shared" si="2"/>
-        <v>2.374909263</v>
+        <v>1.93871145</v>
       </c>
       <c r="D43" s="10">
         <f t="shared" si="3"/>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E43" s="10">
         <f t="shared" si="4"/>
@@ -4155,19 +4155,19 @@
       </c>
       <c r="I43" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J43" s="10">
         <f t="shared" si="6"/>
-        <v>0.7498185261</v>
+        <v>0.8774229009</v>
       </c>
       <c r="K43" s="10">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L43" s="11">
         <f t="shared" si="7"/>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="M43" s="7"/>
       <c r="N43" s="7"/>
@@ -4202,15 +4202,15 @@
         <v>4.07</v>
       </c>
       <c r="B44" s="9">
-        <v>1596.0</v>
+        <v>608.0</v>
       </c>
       <c r="C44" s="10">
         <f t="shared" si="2"/>
-        <v>2.309825789</v>
+        <v>1.890293276</v>
       </c>
       <c r="D44" s="10">
         <f t="shared" si="3"/>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E44" s="10">
         <f t="shared" si="4"/>
@@ -4227,19 +4227,19 @@
       </c>
       <c r="I44" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J44" s="10">
         <f t="shared" si="6"/>
-        <v>0.6196515786</v>
+        <v>0.780586551</v>
       </c>
       <c r="K44" s="10">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L44" s="11">
         <f t="shared" si="7"/>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
@@ -4282,15 +4282,15 @@
         <v>4.08</v>
       </c>
       <c r="B45" s="9">
-        <v>1593.0</v>
+        <v>574.0</v>
       </c>
       <c r="C45" s="10">
         <f t="shared" si="2"/>
-        <v>2.250774638</v>
+        <v>1.84756062</v>
       </c>
       <c r="D45" s="10">
         <f t="shared" si="3"/>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E45" s="10">
         <f t="shared" si="4"/>
@@ -4307,19 +4307,19 @@
       </c>
       <c r="I45" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J45" s="10">
         <f t="shared" si="6"/>
-        <v>0.5015492767</v>
+        <v>0.6951212392</v>
       </c>
       <c r="K45" s="10">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L45" s="11">
         <f t="shared" si="7"/>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
@@ -4338,7 +4338,7 @@
    INDEX($P$2:$AA$7,O45,P45) * $AD$1
 )
 </f>
-        <v>118</v>
+        <v>129.5</v>
       </c>
       <c r="R45" s="7" t="str">
         <f t="shared" ref="R45:R116" si="21">IF(
@@ -4382,15 +4382,15 @@
         <v>4.09</v>
       </c>
       <c r="B46" s="9">
-        <v>1506.0</v>
+        <v>543.0</v>
       </c>
       <c r="C46" s="10">
         <f t="shared" si="2"/>
-        <v>1.998642088</v>
+        <v>1.646873516</v>
       </c>
       <c r="D46" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E46" s="10">
         <f t="shared" si="4"/>
@@ -4411,15 +4411,15 @@
       </c>
       <c r="J46" s="10">
         <f t="shared" si="6"/>
-        <v>0.9972841761</v>
+        <v>0.2937470312</v>
       </c>
       <c r="K46" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L46" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Q46" s="10">
         <f t="shared" si="20"/>
-        <v>118</v>
+        <v>129.5</v>
       </c>
       <c r="R46" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4466,15 +4466,15 @@
         <v>4.1</v>
       </c>
       <c r="B47" s="9">
-        <v>1502.0</v>
+        <v>513.0</v>
       </c>
       <c r="C47" s="10">
         <f t="shared" si="2"/>
-        <v>1.917905501</v>
+        <v>1.581703755</v>
       </c>
       <c r="D47" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E47" s="10">
         <f t="shared" si="4"/>
@@ -4495,15 +4495,15 @@
       </c>
       <c r="J47" s="10">
         <f t="shared" si="6"/>
-        <v>0.8358110019</v>
+        <v>0.1634075109</v>
       </c>
       <c r="K47" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L47" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
@@ -4517,7 +4517,7 @@
       </c>
       <c r="Q47" s="10">
         <f t="shared" si="20"/>
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="R47" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4550,15 +4550,15 @@
         <v>4.11</v>
       </c>
       <c r="B48" s="9">
-        <v>1359.0</v>
+        <v>485.0</v>
       </c>
       <c r="C48" s="10">
         <f t="shared" si="2"/>
-        <v>1.82614015</v>
+        <v>1.553595145</v>
       </c>
       <c r="D48" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E48" s="10">
         <f t="shared" si="4"/>
@@ -4579,15 +4579,15 @@
       </c>
       <c r="J48" s="10">
         <f t="shared" si="6"/>
-        <v>0.6522802998</v>
+        <v>0.1071902898</v>
       </c>
       <c r="K48" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L48" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M48" s="7"/>
       <c r="N48" s="7"/>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="Q48" s="10">
         <f t="shared" si="20"/>
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="R48" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4634,15 +4634,15 @@
         <v>4.12</v>
       </c>
       <c r="B49" s="9">
-        <v>1327.0</v>
+        <v>458.0</v>
       </c>
       <c r="C49" s="10">
         <f t="shared" si="2"/>
-        <v>1.780275243</v>
+        <v>1.528865431</v>
       </c>
       <c r="D49" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E49" s="10">
         <f t="shared" si="4"/>
@@ -4663,15 +4663,15 @@
       </c>
       <c r="J49" s="10">
         <f t="shared" si="6"/>
-        <v>0.5605504851</v>
+        <v>0.05773086105</v>
       </c>
       <c r="K49" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L49" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M49" s="7"/>
       <c r="N49" s="7"/>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="Q49" s="10">
         <f t="shared" si="20"/>
-        <v>72.5</v>
+        <v>80</v>
       </c>
       <c r="R49" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4718,15 +4718,15 @@
         <v>5.01</v>
       </c>
       <c r="B50" s="9">
-        <v>1326.0</v>
+        <v>433.0</v>
       </c>
       <c r="C50" s="10">
         <f t="shared" si="2"/>
-        <v>2.747755044</v>
+        <v>2.507472877</v>
       </c>
       <c r="D50" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E50" s="10">
         <f t="shared" si="4"/>
@@ -4747,15 +4747,15 @@
       </c>
       <c r="J50" s="10">
         <f t="shared" si="6"/>
-        <v>0.4955100887</v>
+        <v>0.0149457548</v>
       </c>
       <c r="K50" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L50" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M50" s="7"/>
       <c r="N50" s="7"/>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="Q50" s="10">
         <f t="shared" si="20"/>
-        <v>65.5</v>
+        <v>73.5</v>
       </c>
       <c r="R50" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4802,15 +4802,15 @@
         <v>5.02</v>
       </c>
       <c r="B51" s="9">
-        <v>1314.0</v>
+        <v>409.0</v>
       </c>
       <c r="C51" s="10">
         <f t="shared" si="2"/>
-        <v>2.714787569</v>
+        <v>2.48868622</v>
       </c>
       <c r="D51" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E51" s="10">
         <f t="shared" si="4"/>
@@ -4827,19 +4827,19 @@
       </c>
       <c r="I51" s="10">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J51" s="10">
         <f t="shared" si="6"/>
-        <v>0.4295751377</v>
+        <v>0.9773724404</v>
       </c>
       <c r="K51" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L51" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M51" s="7"/>
       <c r="N51" s="7"/>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="Q51" s="10">
         <f t="shared" si="20"/>
-        <v>60.5</v>
+        <v>63</v>
       </c>
       <c r="R51" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4886,15 +4886,15 @@
         <v>5.03</v>
       </c>
       <c r="B52" s="9">
-        <v>1300.0</v>
+        <v>387.0</v>
       </c>
       <c r="C52" s="10">
         <f t="shared" si="2"/>
-        <v>2.684100824</v>
+        <v>2.472496614</v>
       </c>
       <c r="D52" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E52" s="10">
         <f t="shared" si="4"/>
@@ -4911,19 +4911,19 @@
       </c>
       <c r="I52" s="10">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J52" s="10">
         <f t="shared" si="6"/>
-        <v>0.3682016476</v>
+        <v>0.944993227</v>
       </c>
       <c r="K52" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L52" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="Q52" s="10">
         <f t="shared" si="20"/>
-        <v>55</v>
+        <v>54.5</v>
       </c>
       <c r="R52" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4970,15 +4970,15 @@
         <v>5.04</v>
       </c>
       <c r="B53" s="9">
-        <v>1292.0</v>
+        <v>366.0</v>
       </c>
       <c r="C53" s="10">
         <f t="shared" si="2"/>
-        <v>2.65741505</v>
+        <v>2.458305103</v>
       </c>
       <c r="D53" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E53" s="10">
         <f t="shared" si="4"/>
@@ -4995,19 +4995,19 @@
       </c>
       <c r="I53" s="10">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J53" s="10">
         <f t="shared" si="6"/>
-        <v>0.314830101</v>
+        <v>0.9166102059</v>
       </c>
       <c r="K53" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L53" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M53" s="7"/>
       <c r="N53" s="7"/>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="Q53" s="10">
         <f t="shared" si="20"/>
-        <v>50.5</v>
+        <v>48.5</v>
       </c>
       <c r="R53" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5054,15 +5054,15 @@
         <v>5.05</v>
       </c>
       <c r="B54" s="9">
-        <v>1291.0</v>
+        <v>346.0</v>
       </c>
       <c r="C54" s="10">
         <f t="shared" si="2"/>
-        <v>2.634403161</v>
+        <v>2.445879971</v>
       </c>
       <c r="D54" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E54" s="10">
         <f t="shared" si="4"/>
@@ -5079,19 +5079,19 @@
       </c>
       <c r="I54" s="10">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J54" s="10">
         <f t="shared" si="6"/>
-        <v>0.2688063222</v>
+        <v>0.8917599416</v>
       </c>
       <c r="K54" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L54" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M54" s="7"/>
       <c r="N54" s="7"/>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="Q54" s="10">
         <f t="shared" si="20"/>
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="R54" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5138,15 +5138,15 @@
         <v>5.06</v>
       </c>
       <c r="B55" s="9">
-        <v>1285.0</v>
+        <v>327.0</v>
       </c>
       <c r="C55" s="10">
         <f t="shared" si="2"/>
-        <v>2.612195693</v>
+        <v>2.435014822</v>
       </c>
       <c r="D55" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E55" s="10">
         <f t="shared" si="4"/>
@@ -5163,19 +5163,19 @@
       </c>
       <c r="I55" s="10">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J55" s="10">
         <f t="shared" si="6"/>
-        <v>0.2243913851</v>
+        <v>0.8700296449</v>
       </c>
       <c r="K55" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L55" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="Q55" s="10">
         <f t="shared" si="20"/>
-        <v>40.5</v>
+        <v>40</v>
       </c>
       <c r="R55" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5222,15 +5222,15 @@
         <v>5.07</v>
       </c>
       <c r="B56" s="9">
-        <v>1279.0</v>
+        <v>309.0</v>
       </c>
       <c r="C56" s="10">
         <f t="shared" si="2"/>
-        <v>2.591783799</v>
+        <v>2.425525957</v>
       </c>
       <c r="D56" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E56" s="10">
         <f t="shared" si="4"/>
@@ -5247,19 +5247,19 @@
       </c>
       <c r="I56" s="10">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J56" s="10">
         <f t="shared" si="6"/>
-        <v>0.1835675977</v>
+        <v>0.8510519141</v>
       </c>
       <c r="K56" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L56" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M56" s="7"/>
       <c r="N56" s="7"/>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="Q56" s="10">
         <f t="shared" si="20"/>
-        <v>36</v>
+        <v>34.5</v>
       </c>
       <c r="R56" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5306,15 +5306,15 @@
         <v>5.08</v>
       </c>
       <c r="B57" s="9">
-        <v>1262.0</v>
+        <v>292.0</v>
       </c>
       <c r="C57" s="10">
         <f t="shared" si="2"/>
-        <v>2.571188089</v>
+        <v>2.417249998</v>
       </c>
       <c r="D57" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E57" s="10">
         <f t="shared" si="4"/>
@@ -5331,19 +5331,19 @@
       </c>
       <c r="I57" s="10">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J57" s="10">
         <f t="shared" si="6"/>
-        <v>0.1423761789</v>
+        <v>0.834499996</v>
       </c>
       <c r="K57" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L57" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M57" s="7"/>
       <c r="N57" s="7"/>
@@ -5357,7 +5357,7 @@
       </c>
       <c r="Q57" s="10">
         <f t="shared" si="20"/>
-        <v>30.5</v>
+        <v>26.75</v>
       </c>
       <c r="R57" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5390,15 +5390,15 @@
         <v>5.09</v>
       </c>
       <c r="B58" s="9">
-        <v>1236.0</v>
+        <v>276.0</v>
       </c>
       <c r="C58" s="10">
         <f t="shared" si="2"/>
-        <v>2.551006543</v>
+        <v>2.410041761</v>
       </c>
       <c r="D58" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E58" s="10">
         <f t="shared" si="4"/>
@@ -5415,19 +5415,19 @@
       </c>
       <c r="I58" s="10">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J58" s="10">
         <f t="shared" si="6"/>
-        <v>0.1020130854</v>
+        <v>0.820083521</v>
       </c>
       <c r="K58" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L58" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="Q58" s="10">
         <f t="shared" si="20"/>
-        <v>30.5</v>
+        <v>26.75</v>
       </c>
       <c r="R58" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5474,15 +5474,15 @@
         <v>5.1</v>
       </c>
       <c r="B59" s="9">
-        <v>1231.0</v>
+        <v>261.0</v>
       </c>
       <c r="C59" s="10">
         <f t="shared" si="2"/>
-        <v>2.535668191</v>
+        <v>2.403772332</v>
       </c>
       <c r="D59" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E59" s="10">
         <f t="shared" si="4"/>
@@ -5499,19 +5499,19 @@
       </c>
       <c r="I59" s="10">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J59" s="10">
         <f t="shared" si="6"/>
-        <v>0.0713363818</v>
+        <v>0.8075446641</v>
       </c>
       <c r="K59" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L59" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M59" s="7"/>
       <c r="N59" s="7"/>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="Q59" s="10">
         <f t="shared" si="20"/>
-        <v>26</v>
+        <v>22.5</v>
       </c>
       <c r="R59" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5558,15 +5558,15 @@
         <v>5.11</v>
       </c>
       <c r="B60" s="9">
-        <v>1229.0</v>
+        <v>247.0</v>
       </c>
       <c r="C60" s="10">
         <f t="shared" si="2"/>
-        <v>2.521956509</v>
+        <v>2.398327347</v>
       </c>
       <c r="D60" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E60" s="10">
         <f t="shared" si="4"/>
@@ -5583,19 +5583,19 @@
       </c>
       <c r="I60" s="10">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J60" s="10">
         <f t="shared" si="6"/>
-        <v>0.04391301772</v>
+        <v>0.7966546932</v>
       </c>
       <c r="K60" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L60" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M60" s="7"/>
       <c r="N60" s="7"/>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="Q60" s="10">
         <f t="shared" si="20"/>
-        <v>23.5</v>
+        <v>20.5</v>
       </c>
       <c r="R60" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5642,15 +5642,15 @@
         <v>5.12</v>
       </c>
       <c r="B61" s="9">
-        <v>1226.0</v>
+        <v>234.0</v>
       </c>
       <c r="C61" s="10">
         <f t="shared" si="2"/>
-        <v>2.509197356</v>
+        <v>2.393605433</v>
       </c>
       <c r="D61" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E61" s="10">
         <f t="shared" si="4"/>
@@ -5667,19 +5667,19 @@
       </c>
       <c r="I61" s="10">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J61" s="10">
         <f t="shared" si="6"/>
-        <v>0.01839471107</v>
+        <v>0.7872108664</v>
       </c>
       <c r="K61" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L61" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M61" s="7"/>
       <c r="N61" s="7"/>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="Q61" s="10">
         <f t="shared" si="20"/>
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="R61" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5726,11 +5726,11 @@
         <v>6.01</v>
       </c>
       <c r="B62" s="9">
-        <v>1220.0</v>
+        <v>221.0</v>
       </c>
       <c r="C62" s="10">
         <f t="shared" si="2"/>
-        <v>1.136423525</v>
+        <v>1.028699433</v>
       </c>
       <c r="D62" s="10">
         <f t="shared" si="3"/>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="J62" s="10">
         <f t="shared" si="6"/>
-        <v>0.2728470495</v>
+        <v>0.05739886682</v>
       </c>
       <c r="K62" s="10">
         <f t="shared" si="10"/>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="Q62" s="10">
         <f t="shared" si="20"/>
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="R62" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5814,11 +5814,11 @@
         <v>6.02</v>
       </c>
       <c r="B63" s="9">
-        <v>1171.0</v>
+        <v>209.0</v>
       </c>
       <c r="C63" s="10">
         <f t="shared" si="2"/>
-        <v>1.120878791</v>
+        <v>1.02505481</v>
       </c>
       <c r="D63" s="10">
         <f t="shared" si="3"/>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="J63" s="10">
         <f t="shared" si="6"/>
-        <v>0.2417575811</v>
+        <v>0.05010961966</v>
       </c>
       <c r="K63" s="10">
         <f t="shared" si="10"/>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="Q63" s="10">
         <f t="shared" si="20"/>
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="R63" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="U63" s="10">
         <f t="shared" ref="U63:U74" si="22">SUMIF($R$45:$R$116, T63, $Q$45:$Q$116)</f>
-        <v>416.5</v>
+        <v>412.75</v>
       </c>
       <c r="V63" s="13">
         <v>1.0</v>
@@ -5903,11 +5903,11 @@
         <v>6.03</v>
       </c>
       <c r="B64" s="9">
-        <v>1154.0</v>
+        <v>198.0</v>
       </c>
       <c r="C64" s="10">
         <f t="shared" si="2"/>
-        <v>1.109966896</v>
+        <v>1.021911543</v>
       </c>
       <c r="D64" s="10">
         <f t="shared" si="3"/>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="J64" s="10">
         <f t="shared" si="6"/>
-        <v>0.2199337916</v>
+        <v>0.04382308594</v>
       </c>
       <c r="K64" s="10">
         <f t="shared" si="10"/>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="Q64" s="10">
         <f t="shared" si="20"/>
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="R64" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="U64" s="10">
         <f t="shared" si="22"/>
-        <v>163.5</v>
+        <v>169</v>
       </c>
       <c r="V64" s="12">
         <v>1.0</v>
@@ -5992,11 +5992,11 @@
         <v>6.04</v>
       </c>
       <c r="B65" s="9">
-        <v>1142.0</v>
+        <v>187.0</v>
       </c>
       <c r="C65" s="10">
         <f t="shared" si="2"/>
-        <v>1.100457987</v>
+        <v>1.01910344</v>
       </c>
       <c r="D65" s="10">
         <f t="shared" si="3"/>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="J65" s="10">
         <f t="shared" si="6"/>
-        <v>0.2009159739</v>
+        <v>0.03820688078</v>
       </c>
       <c r="K65" s="10">
         <f t="shared" si="10"/>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="Q65" s="10">
         <f t="shared" si="20"/>
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="R65" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="U65" s="10">
         <f t="shared" si="22"/>
-        <v>155</v>
+        <v>158.5</v>
       </c>
       <c r="V65" s="13">
         <v>3.0</v>
@@ -6081,11 +6081,11 @@
         <v>6.05</v>
       </c>
       <c r="B66" s="9">
-        <v>1140.0</v>
+        <v>177.0</v>
       </c>
       <c r="C66" s="10">
         <f t="shared" si="2"/>
-        <v>1.092573093</v>
+        <v>1.016691863</v>
       </c>
       <c r="D66" s="10">
         <f t="shared" si="3"/>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="J66" s="10">
         <f t="shared" si="6"/>
-        <v>0.185146187</v>
+        <v>0.03338372552</v>
       </c>
       <c r="K66" s="10">
         <f t="shared" si="10"/>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="Q66" s="10">
         <f t="shared" si="20"/>
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="R66" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="U66" s="10">
         <f t="shared" si="22"/>
-        <v>139.5</v>
+        <v>138.5</v>
       </c>
       <c r="V66" s="14">
         <v>1.0</v>
@@ -6170,11 +6170,11 @@
         <v>6.06</v>
       </c>
       <c r="B67" s="9">
-        <v>1126.0</v>
+        <v>168.0</v>
       </c>
       <c r="C67" s="10">
         <f t="shared" si="2"/>
-        <v>1.084407161</v>
+        <v>1.0146252</v>
       </c>
       <c r="D67" s="10">
         <f t="shared" si="3"/>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="J67" s="10">
         <f t="shared" si="6"/>
-        <v>0.1688143228</v>
+        <v>0.02925039908</v>
       </c>
       <c r="K67" s="10">
         <f t="shared" si="10"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="Q67" s="10">
         <f t="shared" si="20"/>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="R67" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="U67" s="10">
         <f t="shared" si="22"/>
-        <v>125</v>
+        <v>129.5</v>
       </c>
       <c r="V67" s="14">
         <v>5.0</v>
@@ -6259,11 +6259,11 @@
         <v>6.07</v>
       </c>
       <c r="B68" s="9">
-        <v>1096.0</v>
+        <v>159.0</v>
       </c>
       <c r="C68" s="10">
         <f t="shared" si="2"/>
-        <v>1.075842375</v>
+        <v>1.012777624</v>
       </c>
       <c r="D68" s="10">
         <f t="shared" si="3"/>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="J68" s="10">
         <f t="shared" si="6"/>
-        <v>0.1516847502</v>
+        <v>0.02555524827</v>
       </c>
       <c r="K68" s="10">
         <f t="shared" si="10"/>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="Q68" s="10">
         <f t="shared" si="20"/>
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="R68" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="U68" s="10">
         <f t="shared" si="22"/>
-        <v>67</v>
+        <v>68.5</v>
       </c>
       <c r="V68" s="14">
         <v>6.0</v>
@@ -6348,11 +6348,11 @@
         <v>6.08</v>
       </c>
       <c r="B69" s="13">
-        <v>1026.0</v>
+        <v>150.0</v>
       </c>
       <c r="C69" s="10">
         <f t="shared" si="2"/>
-        <v>1.065540348</v>
+        <v>1.01112767</v>
       </c>
       <c r="D69" s="10">
         <f t="shared" si="3"/>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="J69" s="10">
         <f t="shared" si="6"/>
-        <v>0.1310806959</v>
+        <v>0.02225534086</v>
       </c>
       <c r="K69" s="10">
         <f t="shared" si="10"/>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="Q69" s="10">
         <f t="shared" si="20"/>
-        <v>8.75</v>
+        <v>7.75</v>
       </c>
       <c r="R69" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="U69" s="10">
         <f t="shared" si="22"/>
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="V69" s="12"/>
       <c r="W69" s="12"/>
@@ -6431,11 +6431,11 @@
         <v>6.09</v>
       </c>
       <c r="B70" s="9">
-        <v>1021.0</v>
+        <v>142.0</v>
       </c>
       <c r="C70" s="10">
         <f t="shared" si="2"/>
-        <v>1.060206964</v>
+        <v>1.009724358</v>
       </c>
       <c r="D70" s="10">
         <f t="shared" si="3"/>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="J70" s="10">
         <f t="shared" si="6"/>
-        <v>0.1204139289</v>
+        <v>0.01944871637</v>
       </c>
       <c r="K70" s="10">
         <f t="shared" si="10"/>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="Q70" s="10">
         <f t="shared" si="20"/>
-        <v>8.75</v>
+        <v>7.75</v>
       </c>
       <c r="R70" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="U70" s="10">
         <f t="shared" si="22"/>
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="V70" s="3"/>
       <c r="W70" s="3"/>
@@ -6514,11 +6514,11 @@
         <v>6.1</v>
       </c>
       <c r="B71" s="9">
-        <v>1011.0</v>
+        <v>134.0</v>
       </c>
       <c r="C71" s="10">
         <f t="shared" si="2"/>
-        <v>1.05503404</v>
+        <v>1.008471038</v>
       </c>
       <c r="D71" s="10">
         <f t="shared" si="3"/>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="J71" s="10">
         <f t="shared" si="6"/>
-        <v>0.1100680797</v>
+        <v>0.0169420768</v>
       </c>
       <c r="K71" s="10">
         <f t="shared" si="10"/>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="Q71" s="10">
         <f t="shared" si="20"/>
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="R71" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6577,7 +6577,7 @@
       </c>
       <c r="U71" s="10">
         <f t="shared" si="22"/>
-        <v>19.5</v>
+        <v>16.25</v>
       </c>
       <c r="V71" s="3"/>
       <c r="W71" s="3"/>
@@ -6597,11 +6597,11 @@
         <v>6.11</v>
       </c>
       <c r="B72" s="13">
-        <v>1004.0</v>
+        <v>127.0</v>
       </c>
       <c r="C72" s="10">
         <f t="shared" si="2"/>
-        <v>1.050451361</v>
+        <v>1.007411302</v>
       </c>
       <c r="D72" s="10">
         <f t="shared" si="3"/>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="J72" s="10">
         <f t="shared" si="6"/>
-        <v>0.1009027212</v>
+        <v>0.01482260381</v>
       </c>
       <c r="K72" s="10">
         <f t="shared" si="10"/>
@@ -6648,7 +6648,7 @@
       </c>
       <c r="Q72" s="10">
         <f t="shared" si="20"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R72" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="U72" s="10">
         <f t="shared" si="22"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V72" s="3"/>
       <c r="W72" s="3"/>
@@ -6680,11 +6680,11 @@
         <v>6.12</v>
       </c>
       <c r="B73" s="9">
-        <v>946.0</v>
+        <v>118.0</v>
       </c>
       <c r="C73" s="10">
         <f t="shared" si="2"/>
-        <v>1.043882257</v>
+        <v>1.006356696</v>
       </c>
       <c r="D73" s="10">
         <f t="shared" si="3"/>
@@ -6709,7 +6709,7 @@
       </c>
       <c r="J73" s="10">
         <f t="shared" si="6"/>
-        <v>0.08776451406</v>
+        <v>0.01271339197</v>
       </c>
       <c r="K73" s="10">
         <f t="shared" si="10"/>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="Q73" s="10">
         <f t="shared" si="20"/>
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="R73" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6760,9 +6760,6 @@
     </row>
     <row r="74">
       <c r="A74" s="3"/>
-      <c r="B74" s="9">
-        <v>836.0</v>
-      </c>
       <c r="C74" s="3"/>
       <c r="D74" s="10">
         <f>Sum(D2:D73)</f>
@@ -6797,7 +6794,7 @@
       </c>
       <c r="Q74" s="10">
         <f t="shared" si="20"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R74" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6826,9 +6823,7 @@
     </row>
     <row r="75">
       <c r="A75" s="3"/>
-      <c r="B75" s="13">
-        <v>786.0</v>
-      </c>
+      <c r="B75" s="13"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -6851,7 +6846,7 @@
       </c>
       <c r="Q75" s="10">
         <f t="shared" si="20"/>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="R75" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6878,9 +6873,6 @@
     </row>
     <row r="76">
       <c r="A76" s="3"/>
-      <c r="B76" s="9">
-        <v>577.0</v>
-      </c>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -6903,7 +6895,7 @@
       </c>
       <c r="Q76" s="10">
         <f t="shared" si="20"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R76" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6927,9 +6919,7 @@
     </row>
     <row r="77">
       <c r="A77" s="3"/>
-      <c r="B77" s="13">
-        <v>542.0</v>
-      </c>
+      <c r="B77" s="13"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -6952,7 +6942,7 @@
       </c>
       <c r="Q77" s="10">
         <f t="shared" si="20"/>
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="R77" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6976,9 +6966,7 @@
     </row>
     <row r="78">
       <c r="A78" s="3"/>
-      <c r="B78" s="13">
-        <v>449.0</v>
-      </c>
+      <c r="B78" s="13"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -7001,7 +6989,7 @@
       </c>
       <c r="Q78" s="10">
         <f t="shared" si="20"/>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R78" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7025,9 +7013,7 @@
     </row>
     <row r="79">
       <c r="A79" s="3"/>
-      <c r="B79" s="13">
-        <v>351.0</v>
-      </c>
+      <c r="B79" s="13"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -7050,7 +7036,7 @@
       </c>
       <c r="Q79" s="10">
         <f t="shared" si="20"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R79" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7074,9 +7060,7 @@
     </row>
     <row r="80">
       <c r="A80" s="3"/>
-      <c r="B80" s="13">
-        <v>310.0</v>
-      </c>
+      <c r="B80" s="13"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -7099,7 +7083,7 @@
       </c>
       <c r="Q80" s="10">
         <f t="shared" si="20"/>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R80" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7123,9 +7107,7 @@
     </row>
     <row r="81">
       <c r="A81" s="3"/>
-      <c r="B81" s="13">
-        <v>243.0</v>
-      </c>
+      <c r="B81" s="13"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -7148,7 +7130,7 @@
       </c>
       <c r="Q81" s="10">
         <f t="shared" si="20"/>
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="R81" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7172,9 +7154,7 @@
     </row>
     <row r="82">
       <c r="A82" s="3"/>
-      <c r="B82" s="13">
-        <v>214.0</v>
-      </c>
+      <c r="B82" s="13"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -7197,7 +7177,7 @@
       </c>
       <c r="Q82" s="10">
         <f t="shared" si="20"/>
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="R82" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7218,9 +7198,7 @@
     </row>
     <row r="83">
       <c r="A83" s="7"/>
-      <c r="B83" s="13">
-        <v>201.0</v>
-      </c>
+      <c r="B83" s="13"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -7243,7 +7221,7 @@
       </c>
       <c r="Q83" s="10">
         <f t="shared" si="20"/>
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R83" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7264,9 +7242,7 @@
     </row>
     <row r="84">
       <c r="A84" s="7"/>
-      <c r="B84" s="13">
-        <v>157.0</v>
-      </c>
+      <c r="B84" s="13"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -7289,7 +7265,7 @@
       </c>
       <c r="Q84" s="10">
         <f t="shared" si="20"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R84" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7310,9 +7286,6 @@
     </row>
     <row r="85">
       <c r="A85" s="7"/>
-      <c r="B85" s="9">
-        <v>148.0</v>
-      </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -7335,7 +7308,7 @@
       </c>
       <c r="Q85" s="10">
         <f t="shared" si="20"/>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="R85" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7356,9 +7329,7 @@
     </row>
     <row r="86">
       <c r="A86" s="7"/>
-      <c r="B86" s="13">
-        <v>116.0</v>
-      </c>
+      <c r="B86" s="13"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -7381,7 +7352,7 @@
       </c>
       <c r="Q86" s="10">
         <f t="shared" si="20"/>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="R86" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7402,9 +7373,7 @@
     </row>
     <row r="87">
       <c r="A87" s="7"/>
-      <c r="B87" s="13">
-        <v>102.0</v>
-      </c>
+      <c r="B87" s="13"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -7427,7 +7396,7 @@
       </c>
       <c r="Q87" s="10">
         <f t="shared" si="20"/>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="R87" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7448,9 +7417,7 @@
     </row>
     <row r="88">
       <c r="A88" s="7"/>
-      <c r="B88" s="13">
-        <v>90.0</v>
-      </c>
+      <c r="B88" s="13"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -7473,7 +7440,7 @@
       </c>
       <c r="Q88" s="10">
         <f t="shared" si="20"/>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="R88" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7494,9 +7461,7 @@
     </row>
     <row r="89">
       <c r="A89" s="7"/>
-      <c r="B89" s="13">
-        <v>75.0</v>
-      </c>
+      <c r="B89" s="13"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -7519,7 +7484,7 @@
       </c>
       <c r="Q89" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R89" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7540,9 +7505,7 @@
     </row>
     <row r="90">
       <c r="A90" s="3"/>
-      <c r="B90" s="13">
-        <v>70.0</v>
-      </c>
+      <c r="B90" s="13"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -7565,7 +7528,7 @@
       </c>
       <c r="Q90" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R90" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7586,9 +7549,7 @@
     </row>
     <row r="91">
       <c r="A91" s="3"/>
-      <c r="B91" s="13">
-        <v>58.0</v>
-      </c>
+      <c r="B91" s="13"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -7611,7 +7572,7 @@
       </c>
       <c r="Q91" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R91" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7632,9 +7593,7 @@
     </row>
     <row r="92">
       <c r="A92" s="3"/>
-      <c r="B92" s="13">
-        <v>52.0</v>
-      </c>
+      <c r="B92" s="13"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -7657,7 +7616,7 @@
       </c>
       <c r="Q92" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R92" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7678,9 +7637,7 @@
     </row>
     <row r="93">
       <c r="A93" s="3"/>
-      <c r="B93" s="13">
-        <v>49.0</v>
-      </c>
+      <c r="B93" s="13"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -7703,7 +7660,7 @@
       </c>
       <c r="Q93" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R93" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7724,9 +7681,7 @@
     </row>
     <row r="94">
       <c r="A94" s="7"/>
-      <c r="B94" s="13">
-        <v>46.0</v>
-      </c>
+      <c r="B94" s="13"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -7749,7 +7704,7 @@
       </c>
       <c r="Q94" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R94" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7770,9 +7725,7 @@
     </row>
     <row r="95">
       <c r="A95" s="7"/>
-      <c r="B95" s="13">
-        <v>43.0</v>
-      </c>
+      <c r="B95" s="13"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -7795,7 +7748,7 @@
       </c>
       <c r="Q95" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R95" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7816,9 +7769,7 @@
     </row>
     <row r="96">
       <c r="A96" s="7"/>
-      <c r="B96" s="13">
-        <v>40.0</v>
-      </c>
+      <c r="B96" s="13"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -7841,7 +7792,7 @@
       </c>
       <c r="Q96" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R96" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7862,9 +7813,7 @@
     </row>
     <row r="97">
       <c r="A97" s="7"/>
-      <c r="B97" s="13">
-        <v>36.0</v>
-      </c>
+      <c r="B97" s="13"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -7887,7 +7836,7 @@
       </c>
       <c r="Q97" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R97" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7908,9 +7857,7 @@
     </row>
     <row r="98">
       <c r="A98" s="7"/>
-      <c r="B98" s="13">
-        <v>32.0</v>
-      </c>
+      <c r="B98" s="13"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -7933,7 +7880,7 @@
       </c>
       <c r="Q98" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R98" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7954,9 +7901,7 @@
     </row>
     <row r="99">
       <c r="A99" s="7"/>
-      <c r="B99" s="13">
-        <v>30.0</v>
-      </c>
+      <c r="B99" s="13"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -7979,7 +7924,7 @@
       </c>
       <c r="Q99" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R99" s="7" t="str">
         <f t="shared" si="21"/>
@@ -8000,9 +7945,7 @@
     </row>
     <row r="100">
       <c r="A100" s="7"/>
-      <c r="B100" s="13">
-        <v>16.0</v>
-      </c>
+      <c r="B100" s="13"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -8025,7 +7968,7 @@
       </c>
       <c r="Q100" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R100" s="7" t="str">
         <f t="shared" si="21"/>
@@ -8046,9 +7989,7 @@
     </row>
     <row r="101">
       <c r="A101" s="3"/>
-      <c r="B101" s="13">
-        <v>14.0</v>
-      </c>
+      <c r="B101" s="13"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
@@ -8071,7 +8012,7 @@
       </c>
       <c r="Q101" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R101" s="7" t="str">
         <f t="shared" si="21"/>
@@ -8092,9 +8033,7 @@
     </row>
     <row r="102">
       <c r="A102" s="3"/>
-      <c r="B102" s="13">
-        <v>8.0</v>
-      </c>
+      <c r="B102" s="13"/>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
@@ -8117,7 +8056,7 @@
       </c>
       <c r="Q102" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R102" s="7" t="str">
         <f t="shared" si="21"/>
@@ -8161,7 +8100,7 @@
       </c>
       <c r="Q103" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R103" s="7" t="str">
         <f t="shared" si="21"/>
@@ -8205,7 +8144,7 @@
       </c>
       <c r="Q104" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R104" s="7" t="str">
         <f t="shared" si="21"/>
@@ -8968,7 +8907,7 @@
      )
      &lt;= 1200 - SUMPRODUCT(ROUNDDOWN($C$2:$C$73,0)) )
 </f>
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="N123" s="7"/>
       <c r="O123" s="7"/>
@@ -37779,7 +37718,7 @@
       </c>
       <c r="G2" s="17">
         <f t="shared" ref="G2:G73" si="2">IF($D2&gt;0,"",MIN($L$8, $C2*$L$14*(1+($L$11-1)*$L$16)))</f>
-        <v>193.1787364</v>
+        <v>192.2072912</v>
       </c>
       <c r="H2" s="20">
         <f t="shared" ref="H2:H73" si="3">IF($D2&lt;&gt;"","",
@@ -37833,7 +37772,7 @@
       </c>
       <c r="G3" s="17">
         <f t="shared" si="2"/>
-        <v>145.781723</v>
+        <v>145.048625</v>
       </c>
       <c r="H3" s="20">
         <f t="shared" si="3"/>
@@ -37875,7 +37814,7 @@
       </c>
       <c r="G4" s="17">
         <f t="shared" si="2"/>
-        <v>129.264582</v>
+        <v>128.6145443</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" si="3"/>
@@ -37890,7 +37829,7 @@
       </c>
       <c r="L4" s="19">
         <f>'Draft Data'!U63</f>
-        <v>416.5</v>
+        <v>412.75</v>
       </c>
     </row>
     <row r="5">
@@ -37912,7 +37851,7 @@
       </c>
       <c r="G5" s="17">
         <f t="shared" si="2"/>
-        <v>119.2106701</v>
+        <v>118.6111909</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="3"/>
@@ -37950,7 +37889,7 @@
       </c>
       <c r="G6" s="17">
         <f t="shared" si="2"/>
-        <v>104.1298022</v>
+        <v>103.6061607</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="3"/>
@@ -37988,7 +37927,7 @@
       </c>
       <c r="G7" s="17">
         <f t="shared" si="2"/>
-        <v>94.07589024</v>
+        <v>93.60280724</v>
       </c>
       <c r="H7" s="20">
         <f t="shared" si="3"/>
@@ -38025,7 +37964,7 @@
       </c>
       <c r="G8" s="17">
         <f t="shared" si="2"/>
-        <v>86.89452457</v>
+        <v>86.45755478</v>
       </c>
       <c r="H8" s="20">
         <f t="shared" si="3"/>
@@ -38041,7 +37980,7 @@
       <c r="L8" s="17">
         <f>L4-L7
 </f>
-        <v>416.5</v>
+        <v>412.75</v>
       </c>
     </row>
     <row r="9">
@@ -38063,7 +38002,7 @@
       </c>
       <c r="G9" s="17">
         <f t="shared" si="2"/>
-        <v>78.99502234</v>
+        <v>78.59777707</v>
       </c>
       <c r="H9" s="20">
         <f t="shared" si="3"/>
@@ -38079,7 +38018,7 @@
       <c r="L9" s="17">
         <f>L6-L8
 </f>
-        <v>783.5</v>
+        <v>787.25</v>
       </c>
     </row>
     <row r="10">
@@ -38101,7 +38040,7 @@
       </c>
       <c r="G10" s="17">
         <f t="shared" si="2"/>
-        <v>72.53179324</v>
+        <v>72.16704986</v>
       </c>
       <c r="H10" s="20">
         <f t="shared" si="3"/>
@@ -38116,7 +38055,7 @@
       </c>
       <c r="L10" s="17">
         <f>IF(L3&gt;1,L9/(L3-1),0)</f>
-        <v>71.22727273</v>
+        <v>71.56818182</v>
       </c>
     </row>
     <row r="11">
@@ -38138,7 +38077,7 @@
       </c>
       <c r="G11" s="17">
         <f t="shared" si="2"/>
-        <v>64.632291</v>
+        <v>64.30727215</v>
       </c>
       <c r="H11" s="20">
         <f t="shared" si="3"/>
@@ -38153,7 +38092,7 @@
       </c>
       <c r="L11" s="23">
         <f>IF(L10&gt;0,L8/L10,1)</f>
-        <v>5.84747926</v>
+        <v>5.767227691</v>
       </c>
     </row>
     <row r="12">
@@ -38175,7 +38114,7 @@
       </c>
       <c r="G12" s="17">
         <f t="shared" si="2"/>
-        <v>58.1690619</v>
+        <v>57.87654493</v>
       </c>
       <c r="H12" s="20">
         <f t="shared" si="3"/>
@@ -38205,7 +38144,7 @@
       </c>
       <c r="G13" s="17">
         <f t="shared" si="2"/>
-        <v>51.7058328</v>
+        <v>51.44581772</v>
       </c>
       <c r="H13" s="20">
         <f t="shared" si="3"/>
@@ -38242,7 +38181,7 @@
       </c>
       <c r="G14" s="17">
         <f t="shared" si="2"/>
-        <v>45.96074027</v>
+        <v>45.72961575</v>
       </c>
       <c r="H14" s="20">
         <f t="shared" si="3"/>
@@ -38279,7 +38218,7 @@
       </c>
       <c r="G15" s="17">
         <f t="shared" si="2"/>
-        <v>41.65192087</v>
+        <v>41.44246427</v>
       </c>
       <c r="H15" s="20">
         <f t="shared" si="3"/>
@@ -38309,7 +38248,7 @@
       </c>
       <c r="G16" s="17">
         <f t="shared" si="2"/>
-        <v>37.34310147</v>
+        <v>37.1553128</v>
       </c>
       <c r="H16" s="20">
         <f t="shared" si="3"/>
@@ -38356,7 +38295,7 @@
       </c>
       <c r="G17" s="17">
         <f t="shared" si="2"/>
-        <v>33.75241863</v>
+        <v>33.58268657</v>
       </c>
       <c r="H17" s="20">
         <f t="shared" si="3"/>
@@ -38386,7 +38325,7 @@
       </c>
       <c r="G18" s="17">
         <f t="shared" si="2"/>
-        <v>30.1617358</v>
+        <v>30.01006034</v>
       </c>
       <c r="H18" s="20">
         <f t="shared" si="3"/>
@@ -38423,7 +38362,7 @@
       </c>
       <c r="G19" s="17">
         <f t="shared" si="2"/>
-        <v>26.57105297</v>
+        <v>26.43743411</v>
       </c>
       <c r="H19" s="20">
         <f t="shared" si="3"/>
@@ -38453,7 +38392,7 @@
       </c>
       <c r="G20" s="17">
         <f t="shared" si="2"/>
-        <v>23.6985067</v>
+        <v>23.57933312</v>
       </c>
       <c r="H20" s="20">
         <f t="shared" si="3"/>
@@ -38483,7 +38422,7 @@
       </c>
       <c r="G21" s="17">
         <f t="shared" si="2"/>
-        <v>21.544097</v>
+        <v>21.43575738</v>
       </c>
       <c r="H21" s="20">
         <f t="shared" si="3"/>
@@ -38513,7 +38452,7 @@
       </c>
       <c r="G22" s="17">
         <f t="shared" si="2"/>
-        <v>20.10782387</v>
+        <v>20.00670689</v>
       </c>
       <c r="H22" s="20">
         <f t="shared" si="3"/>
@@ -38543,7 +38482,7 @@
       </c>
       <c r="G23" s="17">
         <f t="shared" si="2"/>
-        <v>17.95341417</v>
+        <v>17.86313115</v>
       </c>
       <c r="H23" s="20">
         <f t="shared" si="3"/>
@@ -38573,7 +38512,7 @@
       </c>
       <c r="G24" s="17">
         <f t="shared" si="2"/>
-        <v>15.0808679</v>
+        <v>15.00503017</v>
       </c>
       <c r="H24" s="20">
         <f t="shared" si="3"/>
@@ -38603,7 +38542,7 @@
       </c>
       <c r="G25" s="17">
         <f t="shared" si="2"/>
-        <v>14.36273133</v>
+        <v>14.29050492</v>
       </c>
       <c r="H25" s="20">
         <f t="shared" si="3"/>
@@ -38633,7 +38572,7 @@
       </c>
       <c r="G26" s="17">
         <f t="shared" si="2"/>
-        <v>12.9264582</v>
+        <v>12.86145443</v>
       </c>
       <c r="H26" s="20">
         <f t="shared" si="3"/>
@@ -38663,7 +38602,7 @@
       </c>
       <c r="G27" s="17">
         <f t="shared" si="2"/>
-        <v>12.20832163</v>
+        <v>12.14692918</v>
       </c>
       <c r="H27" s="20">
         <f t="shared" si="3"/>
@@ -38699,7 +38638,7 @@
       </c>
       <c r="G28" s="17">
         <f t="shared" si="2"/>
-        <v>10.7720485</v>
+        <v>10.71787869</v>
       </c>
       <c r="H28" s="20">
         <f t="shared" si="3"/>
@@ -38729,7 +38668,7 @@
       </c>
       <c r="G29" s="17">
         <f t="shared" si="2"/>
-        <v>10.05391193</v>
+        <v>10.00335345</v>
       </c>
       <c r="H29" s="20">
         <f t="shared" si="3"/>
@@ -38759,7 +38698,7 @@
       </c>
       <c r="G30" s="17">
         <f t="shared" si="2"/>
-        <v>9.335775367</v>
+        <v>9.288828199</v>
       </c>
       <c r="H30" s="20">
         <f t="shared" si="3"/>
@@ -38789,7 +38728,7 @@
       </c>
       <c r="G31" s="17">
         <f t="shared" si="2"/>
-        <v>8.6176388</v>
+        <v>8.574302953</v>
       </c>
       <c r="H31" s="20">
         <f t="shared" si="3"/>
@@ -38819,7 +38758,7 @@
       </c>
       <c r="G32" s="17">
         <f t="shared" si="2"/>
-        <v>7.181365667</v>
+        <v>7.145252461</v>
       </c>
       <c r="H32" s="20">
         <f t="shared" si="3"/>
@@ -38849,7 +38788,7 @@
       </c>
       <c r="G33" s="17">
         <f t="shared" si="2"/>
-        <v>7.181365667</v>
+        <v>7.145252461</v>
       </c>
       <c r="H33" s="20">
         <f t="shared" si="3"/>
@@ -38879,7 +38818,7 @@
       </c>
       <c r="G34" s="17">
         <f t="shared" si="2"/>
-        <v>6.4632291</v>
+        <v>6.430727215</v>
       </c>
       <c r="H34" s="20">
         <f t="shared" si="3"/>
@@ -38909,7 +38848,7 @@
       </c>
       <c r="G35" s="17">
         <f t="shared" si="2"/>
-        <v>5.745092534</v>
+        <v>5.716201969</v>
       </c>
       <c r="H35" s="20">
         <f t="shared" si="3"/>
@@ -38939,7 +38878,7 @@
       </c>
       <c r="G36" s="17">
         <f t="shared" si="2"/>
-        <v>5.745092534</v>
+        <v>5.716201969</v>
       </c>
       <c r="H36" s="20">
         <f t="shared" si="3"/>
@@ -38969,7 +38908,7 @@
       </c>
       <c r="G37" s="17">
         <f t="shared" si="2"/>
-        <v>5.026955967</v>
+        <v>5.001676723</v>
       </c>
       <c r="H37" s="20">
         <f t="shared" si="3"/>
@@ -38999,7 +38938,7 @@
       </c>
       <c r="G38" s="17">
         <f t="shared" si="2"/>
-        <v>5.026955967</v>
+        <v>5.001676723</v>
       </c>
       <c r="H38" s="20">
         <f t="shared" si="3"/>
@@ -39029,7 +38968,7 @@
       </c>
       <c r="G39" s="17">
         <f t="shared" si="2"/>
-        <v>4.3088194</v>
+        <v>4.287151477</v>
       </c>
       <c r="H39" s="20">
         <f t="shared" si="3"/>
@@ -39059,7 +38998,7 @@
       </c>
       <c r="G40" s="17">
         <f t="shared" si="2"/>
-        <v>4.3088194</v>
+        <v>4.287151477</v>
       </c>
       <c r="H40" s="20">
         <f t="shared" si="3"/>
@@ -39089,7 +39028,7 @@
       </c>
       <c r="G41" s="17">
         <f t="shared" si="2"/>
-        <v>4.3088194</v>
+        <v>4.287151477</v>
       </c>
       <c r="H41" s="20">
         <f t="shared" si="3"/>
@@ -39119,7 +39058,7 @@
       </c>
       <c r="G42" s="17">
         <f t="shared" si="2"/>
-        <v>3.590682833</v>
+        <v>3.572626231</v>
       </c>
       <c r="H42" s="20">
         <f t="shared" si="3"/>
@@ -39149,7 +39088,7 @@
       </c>
       <c r="G43" s="17">
         <f t="shared" si="2"/>
-        <v>3.590682833</v>
+        <v>3.572626231</v>
       </c>
       <c r="H43" s="20">
         <f t="shared" si="3"/>
@@ -39179,7 +39118,7 @@
       </c>
       <c r="G44" s="17">
         <f t="shared" si="2"/>
-        <v>3.590682833</v>
+        <v>3.572626231</v>
       </c>
       <c r="H44" s="20">
         <f t="shared" si="3"/>
@@ -39209,7 +39148,7 @@
       </c>
       <c r="G45" s="17">
         <f t="shared" si="2"/>
-        <v>3.590682833</v>
+        <v>3.572626231</v>
       </c>
       <c r="H45" s="20">
         <f t="shared" si="3"/>
@@ -39239,7 +39178,7 @@
       </c>
       <c r="G46" s="17">
         <f t="shared" si="2"/>
-        <v>2.872546267</v>
+        <v>2.858100984</v>
       </c>
       <c r="H46" s="20">
         <f t="shared" si="3"/>
@@ -39269,7 +39208,7 @@
       </c>
       <c r="G47" s="17">
         <f t="shared" si="2"/>
-        <v>2.872546267</v>
+        <v>2.858100984</v>
       </c>
       <c r="H47" s="20">
         <f t="shared" si="3"/>
@@ -39299,7 +39238,7 @@
       </c>
       <c r="G48" s="17">
         <f t="shared" si="2"/>
-        <v>2.872546267</v>
+        <v>2.858100984</v>
       </c>
       <c r="H48" s="20">
         <f t="shared" si="3"/>
@@ -39329,7 +39268,7 @@
       </c>
       <c r="G49" s="17">
         <f t="shared" si="2"/>
-        <v>2.872546267</v>
+        <v>2.858100984</v>
       </c>
       <c r="H49" s="20">
         <f t="shared" si="3"/>
@@ -39359,7 +39298,7 @@
       </c>
       <c r="G50" s="17">
         <f t="shared" si="2"/>
-        <v>2.872546267</v>
+        <v>2.858100984</v>
       </c>
       <c r="H50" s="20">
         <f t="shared" si="3"/>
@@ -39389,7 +39328,7 @@
       </c>
       <c r="G51" s="17">
         <f t="shared" si="2"/>
-        <v>2.872546267</v>
+        <v>2.858100984</v>
       </c>
       <c r="H51" s="20">
         <f t="shared" si="3"/>
@@ -39419,7 +39358,7 @@
       </c>
       <c r="G52" s="17">
         <f t="shared" si="2"/>
-        <v>2.872546267</v>
+        <v>2.858100984</v>
       </c>
       <c r="H52" s="20">
         <f t="shared" si="3"/>
@@ -39449,7 +39388,7 @@
       </c>
       <c r="G53" s="17">
         <f t="shared" si="2"/>
-        <v>2.872546267</v>
+        <v>2.858100984</v>
       </c>
       <c r="H53" s="20">
         <f t="shared" si="3"/>
@@ -39479,7 +39418,7 @@
       </c>
       <c r="G54" s="17">
         <f t="shared" si="2"/>
-        <v>2.872546267</v>
+        <v>2.858100984</v>
       </c>
       <c r="H54" s="20">
         <f t="shared" si="3"/>
@@ -39509,7 +39448,7 @@
       </c>
       <c r="G55" s="17">
         <f t="shared" si="2"/>
-        <v>2.872546267</v>
+        <v>2.858100984</v>
       </c>
       <c r="H55" s="20">
         <f t="shared" si="3"/>
@@ -39539,7 +39478,7 @@
       </c>
       <c r="G56" s="17">
         <f t="shared" si="2"/>
-        <v>2.872546267</v>
+        <v>2.858100984</v>
       </c>
       <c r="H56" s="20">
         <f t="shared" si="3"/>
@@ -39569,7 +39508,7 @@
       </c>
       <c r="G57" s="17">
         <f t="shared" si="2"/>
-        <v>2.872546267</v>
+        <v>2.858100984</v>
       </c>
       <c r="H57" s="20">
         <f t="shared" si="3"/>
@@ -39599,7 +39538,7 @@
       </c>
       <c r="G58" s="17">
         <f t="shared" si="2"/>
-        <v>2.872546267</v>
+        <v>2.858100984</v>
       </c>
       <c r="H58" s="20">
         <f t="shared" si="3"/>
@@ -39629,7 +39568,7 @@
       </c>
       <c r="G59" s="17">
         <f t="shared" si="2"/>
-        <v>2.872546267</v>
+        <v>2.858100984</v>
       </c>
       <c r="H59" s="20">
         <f t="shared" si="3"/>
@@ -39659,7 +39598,7 @@
       </c>
       <c r="G60" s="17">
         <f t="shared" si="2"/>
-        <v>2.872546267</v>
+        <v>2.858100984</v>
       </c>
       <c r="H60" s="20">
         <f t="shared" si="3"/>
@@ -39689,7 +39628,7 @@
       </c>
       <c r="G61" s="17">
         <f t="shared" si="2"/>
-        <v>2.872546267</v>
+        <v>2.858100984</v>
       </c>
       <c r="H61" s="20">
         <f t="shared" si="3"/>
@@ -39719,7 +39658,7 @@
       </c>
       <c r="G62" s="17">
         <f t="shared" si="2"/>
-        <v>1.436273133</v>
+        <v>1.429050492</v>
       </c>
       <c r="H62" s="20">
         <f t="shared" si="3"/>
@@ -39749,7 +39688,7 @@
       </c>
       <c r="G63" s="17">
         <f t="shared" si="2"/>
-        <v>1.436273133</v>
+        <v>1.429050492</v>
       </c>
       <c r="H63" s="20">
         <f t="shared" si="3"/>
@@ -39779,7 +39718,7 @@
       </c>
       <c r="G64" s="17">
         <f t="shared" si="2"/>
-        <v>1.436273133</v>
+        <v>1.429050492</v>
       </c>
       <c r="H64" s="20">
         <f t="shared" si="3"/>
@@ -39809,7 +39748,7 @@
       </c>
       <c r="G65" s="17">
         <f t="shared" si="2"/>
-        <v>1.436273133</v>
+        <v>1.429050492</v>
       </c>
       <c r="H65" s="20">
         <f t="shared" si="3"/>
@@ -39839,7 +39778,7 @@
       </c>
       <c r="G66" s="17">
         <f t="shared" si="2"/>
-        <v>1.436273133</v>
+        <v>1.429050492</v>
       </c>
       <c r="H66" s="20">
         <f t="shared" si="3"/>
@@ -39869,7 +39808,7 @@
       </c>
       <c r="G67" s="17">
         <f t="shared" si="2"/>
-        <v>1.436273133</v>
+        <v>1.429050492</v>
       </c>
       <c r="H67" s="20">
         <f t="shared" si="3"/>
@@ -39899,7 +39838,7 @@
       </c>
       <c r="G68" s="17">
         <f t="shared" si="2"/>
-        <v>1.436273133</v>
+        <v>1.429050492</v>
       </c>
       <c r="H68" s="20">
         <f t="shared" si="3"/>
@@ -39929,7 +39868,7 @@
       </c>
       <c r="G69" s="17">
         <f t="shared" si="2"/>
-        <v>1.436273133</v>
+        <v>1.429050492</v>
       </c>
       <c r="H69" s="20">
         <f t="shared" si="3"/>
@@ -39959,7 +39898,7 @@
       </c>
       <c r="G70" s="17">
         <f t="shared" si="2"/>
-        <v>1.436273133</v>
+        <v>1.429050492</v>
       </c>
       <c r="H70" s="20">
         <f t="shared" si="3"/>
@@ -39989,7 +39928,7 @@
       </c>
       <c r="G71" s="17">
         <f t="shared" si="2"/>
-        <v>1.436273133</v>
+        <v>1.429050492</v>
       </c>
       <c r="H71" s="20">
         <f t="shared" si="3"/>
@@ -40019,7 +39958,7 @@
       </c>
       <c r="G72" s="17">
         <f t="shared" si="2"/>
-        <v>1.436273133</v>
+        <v>1.429050492</v>
       </c>
       <c r="H72" s="20">
         <f t="shared" si="3"/>
@@ -40049,7 +39988,7 @@
       </c>
       <c r="G73" s="17">
         <f t="shared" si="2"/>
-        <v>1.436273133</v>
+        <v>1.429050492</v>
       </c>
       <c r="H73" s="20">
         <f t="shared" si="3"/>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -6997,7 +6997,7 @@
       </c>
       <c r="S78" s="7"/>
       <c r="T78" s="7"/>
-      <c r="U78" s="7"/>
+      <c r="U78" s="3"/>
       <c r="V78" s="7"/>
       <c r="W78" s="7"/>
       <c r="X78" s="7"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="S79" s="7"/>
       <c r="T79" s="7"/>
-      <c r="U79" s="7"/>
+      <c r="U79" s="10"/>
       <c r="V79" s="7"/>
       <c r="W79" s="7"/>
       <c r="X79" s="7"/>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="S80" s="7"/>
       <c r="T80" s="7"/>
-      <c r="U80" s="7"/>
+      <c r="U80" s="10"/>
       <c r="V80" s="7"/>
       <c r="W80" s="7"/>
       <c r="X80" s="7"/>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="S81" s="7"/>
       <c r="T81" s="7"/>
-      <c r="U81" s="7"/>
+      <c r="U81" s="10"/>
       <c r="V81" s="7"/>
       <c r="W81" s="7"/>
       <c r="X81" s="7"/>
@@ -7185,7 +7185,7 @@
       </c>
       <c r="S82" s="7"/>
       <c r="T82" s="7"/>
-      <c r="U82" s="7"/>
+      <c r="U82" s="10"/>
       <c r="V82" s="7"/>
       <c r="W82" s="7"/>
       <c r="X82" s="7"/>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="S83" s="7"/>
       <c r="T83" s="7"/>
-      <c r="U83" s="7"/>
+      <c r="U83" s="10"/>
       <c r="V83" s="7"/>
       <c r="W83" s="7"/>
       <c r="X83" s="7"/>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="S84" s="7"/>
       <c r="T84" s="7"/>
-      <c r="U84" s="7"/>
+      <c r="U84" s="10"/>
       <c r="V84" s="7"/>
       <c r="W84" s="7"/>
       <c r="X84" s="7"/>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="S85" s="7"/>
       <c r="T85" s="7"/>
-      <c r="U85" s="7"/>
+      <c r="U85" s="10"/>
       <c r="V85" s="7"/>
       <c r="W85" s="7"/>
       <c r="X85" s="7"/>
@@ -7360,7 +7360,7 @@
       </c>
       <c r="S86" s="7"/>
       <c r="T86" s="7"/>
-      <c r="U86" s="7"/>
+      <c r="U86" s="10"/>
       <c r="V86" s="7"/>
       <c r="W86" s="7"/>
       <c r="X86" s="7"/>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="S87" s="7"/>
       <c r="T87" s="7"/>
-      <c r="U87" s="7"/>
+      <c r="U87" s="10"/>
       <c r="V87" s="7"/>
       <c r="W87" s="7"/>
       <c r="X87" s="7"/>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="S88" s="7"/>
       <c r="T88" s="7"/>
-      <c r="U88" s="7"/>
+      <c r="U88" s="10"/>
       <c r="V88" s="7"/>
       <c r="W88" s="7"/>
       <c r="X88" s="7"/>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="S89" s="7"/>
       <c r="T89" s="7"/>
-      <c r="U89" s="7"/>
+      <c r="U89" s="10"/>
       <c r="V89" s="7"/>
       <c r="W89" s="7"/>
       <c r="X89" s="7"/>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S90" s="7"/>
       <c r="T90" s="7"/>
-      <c r="U90" s="7"/>
+      <c r="U90" s="10"/>
       <c r="V90" s="7"/>
       <c r="W90" s="7"/>
       <c r="X90" s="7"/>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -4773,7 +4773,7 @@
       </c>
       <c r="R50" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>Roy</v>
+        <v>Jason</v>
       </c>
       <c r="S50" s="7"/>
       <c r="T50" s="7"/>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="R53" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>Roy</v>
+        <v>Jason</v>
       </c>
       <c r="S53" s="7"/>
       <c r="T53" s="7"/>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="U63" s="10">
         <f t="shared" ref="U63:U74" si="22">SUMIF($R$45:$R$116, T63, $Q$45:$Q$116)</f>
-        <v>412.75</v>
+        <v>534.75</v>
       </c>
       <c r="V63" s="13">
         <v>1.0</v>
@@ -5886,7 +5886,7 @@
         <v>32</v>
       </c>
       <c r="X63" s="13" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="Y63" s="7" t="str">
         <f t="shared" si="17"/>
@@ -5975,7 +5975,7 @@
         <v>33</v>
       </c>
       <c r="X64" s="13" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="Y64" s="7" t="str">
         <f t="shared" si="17"/>
@@ -6229,11 +6229,11 @@
       </c>
       <c r="S67" s="7"/>
       <c r="T67" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="U67" s="10">
         <f t="shared" si="22"/>
-        <v>129.5</v>
+        <v>68.5</v>
       </c>
       <c r="V67" s="14">
         <v>5.0</v>
@@ -6318,11 +6318,11 @@
       </c>
       <c r="S68" s="7"/>
       <c r="T68" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="U68" s="10">
         <f t="shared" si="22"/>
-        <v>68.5</v>
+        <v>51</v>
       </c>
       <c r="V68" s="14">
         <v>6.0</v>
@@ -6490,11 +6490,11 @@
       </c>
       <c r="S70" s="7"/>
       <c r="T70" s="7" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="U70" s="10">
         <f t="shared" si="22"/>
-        <v>51</v>
+        <v>16.25</v>
       </c>
       <c r="V70" s="3"/>
       <c r="W70" s="3"/>
@@ -6573,11 +6573,11 @@
       </c>
       <c r="S71" s="7"/>
       <c r="T71" s="7" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="U71" s="10">
         <f t="shared" si="22"/>
-        <v>16.25</v>
+        <v>7.5</v>
       </c>
       <c r="V71" s="3"/>
       <c r="W71" s="3"/>
@@ -37718,7 +37718,7 @@
       </c>
       <c r="G2" s="17">
         <f t="shared" ref="G2:G73" si="2">IF($D2&gt;0,"",MIN($L$8, $C2*$L$14*(1+($L$11-1)*$L$16)))</f>
-        <v>192.2072912</v>
+        <v>229.4294025</v>
       </c>
       <c r="H2" s="20">
         <f t="shared" ref="H2:H73" si="3">IF($D2&lt;&gt;"","",
@@ -37772,7 +37772,7 @@
       </c>
       <c r="G3" s="17">
         <f t="shared" si="2"/>
-        <v>145.048625</v>
+        <v>173.1381736</v>
       </c>
       <c r="H3" s="20">
         <f t="shared" si="3"/>
@@ -37814,7 +37814,7 @@
       </c>
       <c r="G4" s="17">
         <f t="shared" si="2"/>
-        <v>128.6145443</v>
+        <v>153.5215333</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" si="3"/>
@@ -37829,7 +37829,7 @@
       </c>
       <c r="L4" s="19">
         <f>'Draft Data'!U63</f>
-        <v>412.75</v>
+        <v>534.75</v>
       </c>
     </row>
     <row r="5">
@@ -37851,7 +37851,7 @@
       </c>
       <c r="G5" s="17">
         <f t="shared" si="2"/>
-        <v>118.6111909</v>
+        <v>141.5809696</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="3"/>
@@ -37889,7 +37889,7 @@
       </c>
       <c r="G6" s="17">
         <f t="shared" si="2"/>
-        <v>103.6061607</v>
+        <v>123.670124</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="3"/>
@@ -37927,7 +37927,7 @@
       </c>
       <c r="G7" s="17">
         <f t="shared" si="2"/>
-        <v>93.60280724</v>
+        <v>111.7295603</v>
       </c>
       <c r="H7" s="20">
         <f t="shared" si="3"/>
@@ -37964,7 +37964,7 @@
       </c>
       <c r="G8" s="17">
         <f t="shared" si="2"/>
-        <v>86.45755478</v>
+        <v>103.2005862</v>
       </c>
       <c r="H8" s="20">
         <f t="shared" si="3"/>
@@ -37980,7 +37980,7 @@
       <c r="L8" s="17">
         <f>L4-L7
 </f>
-        <v>412.75</v>
+        <v>534.75</v>
       </c>
     </row>
     <row r="9">
@@ -38002,7 +38002,7 @@
       </c>
       <c r="G9" s="17">
         <f t="shared" si="2"/>
-        <v>78.59777707</v>
+        <v>93.81871477</v>
       </c>
       <c r="H9" s="20">
         <f t="shared" si="3"/>
@@ -38018,7 +38018,7 @@
       <c r="L9" s="17">
         <f>L6-L8
 </f>
-        <v>787.25</v>
+        <v>665.25</v>
       </c>
     </row>
     <row r="10">
@@ -38040,7 +38040,7 @@
       </c>
       <c r="G10" s="17">
         <f t="shared" si="2"/>
-        <v>72.16704986</v>
+        <v>86.14263811</v>
       </c>
       <c r="H10" s="20">
         <f t="shared" si="3"/>
@@ -38055,7 +38055,7 @@
       </c>
       <c r="L10" s="17">
         <f>IF(L3&gt;1,L9/(L3-1),0)</f>
-        <v>71.56818182</v>
+        <v>60.47727273</v>
       </c>
     </row>
     <row r="11">
@@ -38077,7 +38077,7 @@
       </c>
       <c r="G11" s="17">
         <f t="shared" si="2"/>
-        <v>64.30727215</v>
+        <v>76.76076663</v>
       </c>
       <c r="H11" s="20">
         <f t="shared" si="3"/>
@@ -38092,7 +38092,7 @@
       </c>
       <c r="L11" s="23">
         <f>IF(L10&gt;0,L8/L10,1)</f>
-        <v>5.767227691</v>
+        <v>8.8421646</v>
       </c>
     </row>
     <row r="12">
@@ -38114,7 +38114,7 @@
       </c>
       <c r="G12" s="17">
         <f t="shared" si="2"/>
-        <v>57.87654493</v>
+        <v>69.08468997</v>
       </c>
       <c r="H12" s="20">
         <f t="shared" si="3"/>
@@ -38144,7 +38144,7 @@
       </c>
       <c r="G13" s="17">
         <f t="shared" si="2"/>
-        <v>51.44581772</v>
+        <v>61.4086133</v>
       </c>
       <c r="H13" s="20">
         <f t="shared" si="3"/>
@@ -38181,7 +38181,7 @@
       </c>
       <c r="G14" s="17">
         <f t="shared" si="2"/>
-        <v>45.72961575</v>
+        <v>54.58543405</v>
       </c>
       <c r="H14" s="20">
         <f t="shared" si="3"/>
@@ -38218,7 +38218,7 @@
       </c>
       <c r="G15" s="17">
         <f t="shared" si="2"/>
-        <v>41.44246427</v>
+        <v>49.46804961</v>
       </c>
       <c r="H15" s="20">
         <f t="shared" si="3"/>
@@ -38248,7 +38248,7 @@
       </c>
       <c r="G16" s="17">
         <f t="shared" si="2"/>
-        <v>37.1553128</v>
+        <v>44.35066516</v>
       </c>
       <c r="H16" s="20">
         <f t="shared" si="3"/>
@@ -38295,7 +38295,7 @@
       </c>
       <c r="G17" s="17">
         <f t="shared" si="2"/>
-        <v>33.58268657</v>
+        <v>40.08617813</v>
       </c>
       <c r="H17" s="20">
         <f t="shared" si="3"/>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="G18" s="17">
         <f t="shared" si="2"/>
-        <v>30.01006034</v>
+        <v>35.82169109</v>
       </c>
       <c r="H18" s="20">
         <f t="shared" si="3"/>
@@ -38362,7 +38362,7 @@
       </c>
       <c r="G19" s="17">
         <f t="shared" si="2"/>
-        <v>26.43743411</v>
+        <v>31.55720406</v>
       </c>
       <c r="H19" s="20">
         <f t="shared" si="3"/>
@@ -38392,7 +38392,7 @@
       </c>
       <c r="G20" s="17">
         <f t="shared" si="2"/>
-        <v>23.57933312</v>
+        <v>28.14561443</v>
       </c>
       <c r="H20" s="20">
         <f t="shared" si="3"/>
@@ -38422,7 +38422,7 @@
       </c>
       <c r="G21" s="17">
         <f t="shared" si="2"/>
-        <v>21.43575738</v>
+        <v>25.58692221</v>
       </c>
       <c r="H21" s="20">
         <f t="shared" si="3"/>
@@ -38452,7 +38452,7 @@
       </c>
       <c r="G22" s="17">
         <f t="shared" si="2"/>
-        <v>20.00670689</v>
+        <v>23.8811274</v>
       </c>
       <c r="H22" s="20">
         <f t="shared" si="3"/>
@@ -38482,7 +38482,7 @@
       </c>
       <c r="G23" s="17">
         <f t="shared" si="2"/>
-        <v>17.86313115</v>
+        <v>21.32243517</v>
       </c>
       <c r="H23" s="20">
         <f t="shared" si="3"/>
@@ -38512,7 +38512,7 @@
       </c>
       <c r="G24" s="17">
         <f t="shared" si="2"/>
-        <v>15.00503017</v>
+        <v>17.91084555</v>
       </c>
       <c r="H24" s="20">
         <f t="shared" si="3"/>
@@ -38542,7 +38542,7 @@
       </c>
       <c r="G25" s="17">
         <f t="shared" si="2"/>
-        <v>14.29050492</v>
+        <v>17.05794814</v>
       </c>
       <c r="H25" s="20">
         <f t="shared" si="3"/>
@@ -38572,7 +38572,7 @@
       </c>
       <c r="G26" s="17">
         <f t="shared" si="2"/>
-        <v>12.86145443</v>
+        <v>15.35215333</v>
       </c>
       <c r="H26" s="20">
         <f t="shared" si="3"/>
@@ -38602,7 +38602,7 @@
       </c>
       <c r="G27" s="17">
         <f t="shared" si="2"/>
-        <v>12.14692918</v>
+        <v>14.49925592</v>
       </c>
       <c r="H27" s="20">
         <f t="shared" si="3"/>
@@ -38638,7 +38638,7 @@
       </c>
       <c r="G28" s="17">
         <f t="shared" si="2"/>
-        <v>10.71787869</v>
+        <v>12.7934611</v>
       </c>
       <c r="H28" s="20">
         <f t="shared" si="3"/>
@@ -38668,7 +38668,7 @@
       </c>
       <c r="G29" s="17">
         <f t="shared" si="2"/>
-        <v>10.00335345</v>
+        <v>11.9405637</v>
       </c>
       <c r="H29" s="20">
         <f t="shared" si="3"/>
@@ -38698,7 +38698,7 @@
       </c>
       <c r="G30" s="17">
         <f t="shared" si="2"/>
-        <v>9.288828199</v>
+        <v>11.08766629</v>
       </c>
       <c r="H30" s="20">
         <f t="shared" si="3"/>
@@ -38728,7 +38728,7 @@
       </c>
       <c r="G31" s="17">
         <f t="shared" si="2"/>
-        <v>8.574302953</v>
+        <v>10.23476888</v>
       </c>
       <c r="H31" s="20">
         <f t="shared" si="3"/>
@@ -38758,7 +38758,7 @@
       </c>
       <c r="G32" s="17">
         <f t="shared" si="2"/>
-        <v>7.145252461</v>
+        <v>8.52897407</v>
       </c>
       <c r="H32" s="20">
         <f t="shared" si="3"/>
@@ -38788,7 +38788,7 @@
       </c>
       <c r="G33" s="17">
         <f t="shared" si="2"/>
-        <v>7.145252461</v>
+        <v>8.52897407</v>
       </c>
       <c r="H33" s="20">
         <f t="shared" si="3"/>
@@ -38818,7 +38818,7 @@
       </c>
       <c r="G34" s="17">
         <f t="shared" si="2"/>
-        <v>6.430727215</v>
+        <v>7.676076663</v>
       </c>
       <c r="H34" s="20">
         <f t="shared" si="3"/>
@@ -38848,7 +38848,7 @@
       </c>
       <c r="G35" s="17">
         <f t="shared" si="2"/>
-        <v>5.716201969</v>
+        <v>6.823179256</v>
       </c>
       <c r="H35" s="20">
         <f t="shared" si="3"/>
@@ -38878,7 +38878,7 @@
       </c>
       <c r="G36" s="17">
         <f t="shared" si="2"/>
-        <v>5.716201969</v>
+        <v>6.823179256</v>
       </c>
       <c r="H36" s="20">
         <f t="shared" si="3"/>
@@ -38908,7 +38908,7 @@
       </c>
       <c r="G37" s="17">
         <f t="shared" si="2"/>
-        <v>5.001676723</v>
+        <v>5.970281849</v>
       </c>
       <c r="H37" s="20">
         <f t="shared" si="3"/>
@@ -38938,7 +38938,7 @@
       </c>
       <c r="G38" s="17">
         <f t="shared" si="2"/>
-        <v>5.001676723</v>
+        <v>5.970281849</v>
       </c>
       <c r="H38" s="20">
         <f t="shared" si="3"/>
@@ -38968,7 +38968,7 @@
       </c>
       <c r="G39" s="17">
         <f t="shared" si="2"/>
-        <v>4.287151477</v>
+        <v>5.117384442</v>
       </c>
       <c r="H39" s="20">
         <f t="shared" si="3"/>
@@ -38998,7 +38998,7 @@
       </c>
       <c r="G40" s="17">
         <f t="shared" si="2"/>
-        <v>4.287151477</v>
+        <v>5.117384442</v>
       </c>
       <c r="H40" s="20">
         <f t="shared" si="3"/>
@@ -39028,7 +39028,7 @@
       </c>
       <c r="G41" s="17">
         <f t="shared" si="2"/>
-        <v>4.287151477</v>
+        <v>5.117384442</v>
       </c>
       <c r="H41" s="20">
         <f t="shared" si="3"/>
@@ -39058,7 +39058,7 @@
       </c>
       <c r="G42" s="17">
         <f t="shared" si="2"/>
-        <v>3.572626231</v>
+        <v>4.264487035</v>
       </c>
       <c r="H42" s="20">
         <f t="shared" si="3"/>
@@ -39088,7 +39088,7 @@
       </c>
       <c r="G43" s="17">
         <f t="shared" si="2"/>
-        <v>3.572626231</v>
+        <v>4.264487035</v>
       </c>
       <c r="H43" s="20">
         <f t="shared" si="3"/>
@@ -39118,7 +39118,7 @@
       </c>
       <c r="G44" s="17">
         <f t="shared" si="2"/>
-        <v>3.572626231</v>
+        <v>4.264487035</v>
       </c>
       <c r="H44" s="20">
         <f t="shared" si="3"/>
@@ -39148,7 +39148,7 @@
       </c>
       <c r="G45" s="17">
         <f t="shared" si="2"/>
-        <v>3.572626231</v>
+        <v>4.264487035</v>
       </c>
       <c r="H45" s="20">
         <f t="shared" si="3"/>
@@ -39178,7 +39178,7 @@
       </c>
       <c r="G46" s="17">
         <f t="shared" si="2"/>
-        <v>2.858100984</v>
+        <v>3.411589628</v>
       </c>
       <c r="H46" s="20">
         <f t="shared" si="3"/>
@@ -39208,7 +39208,7 @@
       </c>
       <c r="G47" s="17">
         <f t="shared" si="2"/>
-        <v>2.858100984</v>
+        <v>3.411589628</v>
       </c>
       <c r="H47" s="20">
         <f t="shared" si="3"/>
@@ -39238,7 +39238,7 @@
       </c>
       <c r="G48" s="17">
         <f t="shared" si="2"/>
-        <v>2.858100984</v>
+        <v>3.411589628</v>
       </c>
       <c r="H48" s="20">
         <f t="shared" si="3"/>
@@ -39268,7 +39268,7 @@
       </c>
       <c r="G49" s="17">
         <f t="shared" si="2"/>
-        <v>2.858100984</v>
+        <v>3.411589628</v>
       </c>
       <c r="H49" s="20">
         <f t="shared" si="3"/>
@@ -39298,7 +39298,7 @@
       </c>
       <c r="G50" s="17">
         <f t="shared" si="2"/>
-        <v>2.858100984</v>
+        <v>3.411589628</v>
       </c>
       <c r="H50" s="20">
         <f t="shared" si="3"/>
@@ -39328,7 +39328,7 @@
       </c>
       <c r="G51" s="17">
         <f t="shared" si="2"/>
-        <v>2.858100984</v>
+        <v>3.411589628</v>
       </c>
       <c r="H51" s="20">
         <f t="shared" si="3"/>
@@ -39358,7 +39358,7 @@
       </c>
       <c r="G52" s="17">
         <f t="shared" si="2"/>
-        <v>2.858100984</v>
+        <v>3.411589628</v>
       </c>
       <c r="H52" s="20">
         <f t="shared" si="3"/>
@@ -39388,7 +39388,7 @@
       </c>
       <c r="G53" s="17">
         <f t="shared" si="2"/>
-        <v>2.858100984</v>
+        <v>3.411589628</v>
       </c>
       <c r="H53" s="20">
         <f t="shared" si="3"/>
@@ -39418,7 +39418,7 @@
       </c>
       <c r="G54" s="17">
         <f t="shared" si="2"/>
-        <v>2.858100984</v>
+        <v>3.411589628</v>
       </c>
       <c r="H54" s="20">
         <f t="shared" si="3"/>
@@ -39448,7 +39448,7 @@
       </c>
       <c r="G55" s="17">
         <f t="shared" si="2"/>
-        <v>2.858100984</v>
+        <v>3.411589628</v>
       </c>
       <c r="H55" s="20">
         <f t="shared" si="3"/>
@@ -39478,7 +39478,7 @@
       </c>
       <c r="G56" s="17">
         <f t="shared" si="2"/>
-        <v>2.858100984</v>
+        <v>3.411589628</v>
       </c>
       <c r="H56" s="20">
         <f t="shared" si="3"/>
@@ -39508,7 +39508,7 @@
       </c>
       <c r="G57" s="17">
         <f t="shared" si="2"/>
-        <v>2.858100984</v>
+        <v>3.411589628</v>
       </c>
       <c r="H57" s="20">
         <f t="shared" si="3"/>
@@ -39538,7 +39538,7 @@
       </c>
       <c r="G58" s="17">
         <f t="shared" si="2"/>
-        <v>2.858100984</v>
+        <v>3.411589628</v>
       </c>
       <c r="H58" s="20">
         <f t="shared" si="3"/>
@@ -39568,7 +39568,7 @@
       </c>
       <c r="G59" s="17">
         <f t="shared" si="2"/>
-        <v>2.858100984</v>
+        <v>3.411589628</v>
       </c>
       <c r="H59" s="20">
         <f t="shared" si="3"/>
@@ -39598,7 +39598,7 @@
       </c>
       <c r="G60" s="17">
         <f t="shared" si="2"/>
-        <v>2.858100984</v>
+        <v>3.411589628</v>
       </c>
       <c r="H60" s="20">
         <f t="shared" si="3"/>
@@ -39628,7 +39628,7 @@
       </c>
       <c r="G61" s="17">
         <f t="shared" si="2"/>
-        <v>2.858100984</v>
+        <v>3.411589628</v>
       </c>
       <c r="H61" s="20">
         <f t="shared" si="3"/>
@@ -39658,7 +39658,7 @@
       </c>
       <c r="G62" s="17">
         <f t="shared" si="2"/>
-        <v>1.429050492</v>
+        <v>1.705794814</v>
       </c>
       <c r="H62" s="20">
         <f t="shared" si="3"/>
@@ -39688,7 +39688,7 @@
       </c>
       <c r="G63" s="17">
         <f t="shared" si="2"/>
-        <v>1.429050492</v>
+        <v>1.705794814</v>
       </c>
       <c r="H63" s="20">
         <f t="shared" si="3"/>
@@ -39718,7 +39718,7 @@
       </c>
       <c r="G64" s="17">
         <f t="shared" si="2"/>
-        <v>1.429050492</v>
+        <v>1.705794814</v>
       </c>
       <c r="H64" s="20">
         <f t="shared" si="3"/>
@@ -39748,7 +39748,7 @@
       </c>
       <c r="G65" s="17">
         <f t="shared" si="2"/>
-        <v>1.429050492</v>
+        <v>1.705794814</v>
       </c>
       <c r="H65" s="20">
         <f t="shared" si="3"/>
@@ -39778,7 +39778,7 @@
       </c>
       <c r="G66" s="17">
         <f t="shared" si="2"/>
-        <v>1.429050492</v>
+        <v>1.705794814</v>
       </c>
       <c r="H66" s="20">
         <f t="shared" si="3"/>
@@ -39808,7 +39808,7 @@
       </c>
       <c r="G67" s="17">
         <f t="shared" si="2"/>
-        <v>1.429050492</v>
+        <v>1.705794814</v>
       </c>
       <c r="H67" s="20">
         <f t="shared" si="3"/>
@@ -39838,7 +39838,7 @@
       </c>
       <c r="G68" s="17">
         <f t="shared" si="2"/>
-        <v>1.429050492</v>
+        <v>1.705794814</v>
       </c>
       <c r="H68" s="20">
         <f t="shared" si="3"/>
@@ -39868,7 +39868,7 @@
       </c>
       <c r="G69" s="17">
         <f t="shared" si="2"/>
-        <v>1.429050492</v>
+        <v>1.705794814</v>
       </c>
       <c r="H69" s="20">
         <f t="shared" si="3"/>
@@ -39898,7 +39898,7 @@
       </c>
       <c r="G70" s="17">
         <f t="shared" si="2"/>
-        <v>1.429050492</v>
+        <v>1.705794814</v>
       </c>
       <c r="H70" s="20">
         <f t="shared" si="3"/>
@@ -39928,7 +39928,7 @@
       </c>
       <c r="G71" s="17">
         <f t="shared" si="2"/>
-        <v>1.429050492</v>
+        <v>1.705794814</v>
       </c>
       <c r="H71" s="20">
         <f t="shared" si="3"/>
@@ -39958,7 +39958,7 @@
       </c>
       <c r="G72" s="17">
         <f t="shared" si="2"/>
-        <v>1.429050492</v>
+        <v>1.705794814</v>
       </c>
       <c r="H72" s="20">
         <f t="shared" si="3"/>
@@ -39988,7 +39988,7 @@
       </c>
       <c r="G73" s="17">
         <f t="shared" si="2"/>
-        <v>1.429050492</v>
+        <v>1.705794814</v>
       </c>
       <c r="H73" s="20">
         <f t="shared" si="3"/>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="172">
   <si>
     <t>PICK</t>
   </si>
@@ -92,34 +92,31 @@
     <t>Ed</t>
   </si>
   <si>
-    <t>Makayla</t>
+    <t>Blaine</t>
   </si>
   <si>
-    <t>Blaine</t>
+    <t>Jason</t>
   </si>
   <si>
     <t>Brent</t>
   </si>
   <si>
-    <t>Jason</t>
+    <t>Joey</t>
+  </si>
+  <si>
+    <t>MaKayla</t>
   </si>
   <si>
     <t>Collin</t>
-  </si>
-  <si>
-    <t>Joey</t>
-  </si>
-  <si>
-    <t>Eric</t>
-  </si>
-  <si>
-    <t>MaKayla</t>
   </si>
   <si>
     <t>Ty</t>
   </si>
   <si>
     <t>Kich</t>
+  </si>
+  <si>
+    <t>Eric</t>
   </si>
   <si>
     <t>Roy</t>
@@ -989,7 +986,7 @@
         <v>1.01</v>
       </c>
       <c r="B2" s="9">
-        <v>7552.0</v>
+        <v>7651.0</v>
       </c>
       <c r="C2" s="10">
         <f t="shared" ref="C2:C73" si="2">1 + --(INT((ROW()-ROW($B$2))/12)=4)
@@ -1009,7 +1006,7 @@
         )
     )
 </f>
-        <v>146.0244645</v>
+        <v>139.1284418</v>
       </c>
       <c r="D2" s="10">
         <f t="shared" ref="D2:D73" si="3">( K2
@@ -1021,7 +1018,7 @@
      )
   ) / 2
 </f>
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E2" s="10">
         <f t="shared" ref="E2:E73" si="4">(MEDIAN(F2:H2)+AVERAGE(F2:H2))/2
@@ -1039,19 +1036,19 @@
       </c>
       <c r="I2" s="10">
         <f t="shared" ref="I2:I73" si="5">ROUNDDOWN(C2*2,0)</f>
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="J2" s="10">
         <f t="shared" ref="J2:J73" si="6">C2*2 - I2</f>
-        <v>0.04892906141</v>
+        <v>0.2568836805</v>
       </c>
       <c r="K2" s="10">
         <f>I2 + --(RANK(J2,$J$2:$J$73,0) &lt;= 1200*2 - SUM($I$2:$I$73))</f>
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="L2" s="11">
         <f t="shared" ref="L2:L74" si="7">D2</f>
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
@@ -1060,27 +1057,27 @@
       </c>
       <c r="P2" s="10">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="Q2" s="10">
         <f t="shared" si="1"/>
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="R2" s="10">
         <f t="shared" si="1"/>
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="S2" s="10">
         <f t="shared" si="1"/>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="T2" s="10">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="U2" s="10">
         <f t="shared" si="1"/>
-        <v>73.5</v>
+        <v>69</v>
       </c>
       <c r="V2" s="10">
         <f t="shared" si="1"/>
@@ -1088,15 +1085,15 @@
       </c>
       <c r="W2" s="10">
         <f t="shared" si="1"/>
-        <v>54.5</v>
+        <v>58</v>
       </c>
       <c r="X2" s="10">
         <f t="shared" si="1"/>
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="Y2" s="10">
         <f t="shared" si="1"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Z2" s="10">
         <f t="shared" si="1"/>
@@ -1104,11 +1101,11 @@
       </c>
       <c r="AA2" s="10">
         <f t="shared" si="1"/>
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="AB2" s="10">
         <f t="shared" ref="AB2:AB7" si="9">SUM(P2:AA2)</f>
-        <v>883</v>
+        <v>866</v>
       </c>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
@@ -1118,15 +1115,15 @@
         <v>1.02</v>
       </c>
       <c r="B3" s="9">
-        <v>5610.0</v>
+        <v>5748.0</v>
       </c>
       <c r="C3" s="10">
         <f t="shared" si="2"/>
-        <v>111.0226246</v>
+        <v>106.8674263</v>
       </c>
       <c r="D3" s="10">
         <f t="shared" si="3"/>
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E3" s="10">
         <f t="shared" si="4"/>
@@ -1143,11 +1140,11 @@
       </c>
       <c r="I3" s="10">
         <f t="shared" si="5"/>
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="J3" s="10">
         <f t="shared" si="6"/>
-        <v>0.04524926955</v>
+        <v>0.7348525498</v>
       </c>
       <c r="K3" s="10">
         <f t="shared" ref="K3:K73" si="10">MIN(
@@ -1156,11 +1153,11 @@
   K2
 )
 </f>
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="L3" s="11">
         <f t="shared" si="7"/>
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
@@ -1169,55 +1166,55 @@
       </c>
       <c r="P3" s="10">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
-        <v>29</v>
+        <v>28.5</v>
       </c>
       <c r="Q3" s="10">
         <f t="shared" si="8"/>
-        <v>24.5</v>
+        <v>25.5</v>
       </c>
       <c r="R3" s="10">
         <f t="shared" si="8"/>
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
       <c r="S3" s="10">
         <f t="shared" si="8"/>
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="T3" s="10">
         <f t="shared" si="8"/>
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="U3" s="10">
         <f t="shared" si="8"/>
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="V3" s="10">
         <f t="shared" si="8"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W3" s="10">
         <f t="shared" si="8"/>
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="X3" s="10">
         <f t="shared" si="8"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y3" s="10">
         <f t="shared" si="8"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z3" s="10">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA3" s="10">
         <f t="shared" si="8"/>
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AB3" s="10">
         <f t="shared" si="9"/>
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="AC3" s="5"/>
       <c r="AD3" s="5"/>
@@ -1227,15 +1224,15 @@
         <v>1.03</v>
       </c>
       <c r="B4" s="9">
-        <v>5328.0</v>
+        <v>5655.0</v>
       </c>
       <c r="C4" s="10">
         <f t="shared" si="2"/>
-        <v>96.79340493</v>
+        <v>95.09489457</v>
       </c>
       <c r="D4" s="10">
         <f t="shared" si="3"/>
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E4" s="10">
         <f t="shared" si="4"/>
@@ -1252,19 +1249,19 @@
       </c>
       <c r="I4" s="10">
         <f t="shared" si="5"/>
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="J4" s="10">
         <f t="shared" si="6"/>
-        <v>0.5868098528</v>
+        <v>0.1897891409</v>
       </c>
       <c r="K4" s="10">
         <f t="shared" si="10"/>
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="L4" s="11">
         <f t="shared" si="7"/>
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
@@ -1273,47 +1270,47 @@
       </c>
       <c r="P4" s="10">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q4" s="10">
         <f t="shared" si="11"/>
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="R4" s="10">
         <f t="shared" si="11"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S4" s="10">
         <f t="shared" si="11"/>
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="T4" s="10">
         <f t="shared" si="11"/>
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="U4" s="10">
         <f t="shared" si="11"/>
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="V4" s="10">
         <f t="shared" si="11"/>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="W4" s="10">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="X4" s="10">
         <f t="shared" si="11"/>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="Y4" s="10">
         <f t="shared" si="11"/>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="Z4" s="10">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AA4" s="10">
         <f t="shared" si="11"/>
@@ -1321,7 +1318,7 @@
       </c>
       <c r="AB4" s="10">
         <f t="shared" si="9"/>
-        <v>60.5</v>
+        <v>67.5</v>
       </c>
       <c r="AC4" s="5"/>
       <c r="AD4" s="5"/>
@@ -1331,15 +1328,15 @@
         <v>1.04</v>
       </c>
       <c r="B5" s="9">
-        <v>5124.0</v>
+        <v>5263.0</v>
       </c>
       <c r="C5" s="10">
         <f t="shared" si="2"/>
-        <v>88.1976102</v>
+        <v>84.94144699</v>
       </c>
       <c r="D5" s="10">
         <f t="shared" si="3"/>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E5" s="10">
         <f t="shared" si="4"/>
@@ -1356,19 +1353,19 @@
       </c>
       <c r="I5" s="10">
         <f t="shared" si="5"/>
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="J5" s="10">
         <f t="shared" si="6"/>
-        <v>0.3952204032</v>
+        <v>0.8828939733</v>
       </c>
       <c r="K5" s="10">
         <f t="shared" si="10"/>
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="L5" s="11">
         <f t="shared" si="7"/>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
@@ -1377,7 +1374,7 @@
       </c>
       <c r="P5" s="10">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="Q5" s="10">
         <f t="shared" si="12"/>
@@ -1389,7 +1386,7 @@
       </c>
       <c r="S5" s="10">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="T5" s="10">
         <f t="shared" si="12"/>
@@ -1425,7 +1422,7 @@
       </c>
       <c r="AB5" s="10">
         <f t="shared" si="9"/>
-        <v>23.5</v>
+        <v>24.5</v>
       </c>
       <c r="AC5" s="5"/>
       <c r="AD5" s="5"/>
@@ -1435,15 +1432,15 @@
         <v>1.05</v>
       </c>
       <c r="B6" s="9">
-        <v>4886.0</v>
+        <v>5012.0</v>
       </c>
       <c r="C6" s="10">
         <f t="shared" si="2"/>
-        <v>78.82067948</v>
+        <v>75.84174891</v>
       </c>
       <c r="D6" s="10">
         <f t="shared" si="3"/>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E6" s="10">
         <f t="shared" si="4"/>
@@ -1460,19 +1457,19 @@
       </c>
       <c r="I6" s="10">
         <f t="shared" si="5"/>
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="J6" s="10">
         <f t="shared" si="6"/>
-        <v>0.6413589668</v>
+        <v>0.6834978222</v>
       </c>
       <c r="K6" s="10">
         <f t="shared" si="10"/>
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="L6" s="11">
         <f t="shared" si="7"/>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
@@ -1539,15 +1536,15 @@
         <v>1.06</v>
       </c>
       <c r="B7" s="9">
-        <v>4811.0</v>
+        <v>4716.0</v>
       </c>
       <c r="C7" s="10">
         <f t="shared" si="2"/>
-        <v>72.47508107</v>
+        <v>67.83501727</v>
       </c>
       <c r="D7" s="10">
         <f t="shared" si="3"/>
-        <v>73.5</v>
+        <v>69</v>
       </c>
       <c r="E7" s="10">
         <f t="shared" si="4"/>
@@ -1564,19 +1561,19 @@
       </c>
       <c r="I7" s="10">
         <f t="shared" si="5"/>
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="J7" s="10">
         <f t="shared" si="6"/>
-        <v>0.9501621308</v>
+        <v>0.6700345437</v>
       </c>
       <c r="K7" s="10">
         <f t="shared" si="10"/>
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="L7" s="11">
         <f t="shared" si="7"/>
-        <v>73.5</v>
+        <v>69</v>
       </c>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
@@ -1643,11 +1640,11 @@
         <v>1.07</v>
       </c>
       <c r="B8" s="9">
-        <v>4211.0</v>
+        <v>4608.0</v>
       </c>
       <c r="C8" s="10">
         <f t="shared" si="2"/>
-        <v>61.85932775</v>
+        <v>61.93350077</v>
       </c>
       <c r="D8" s="10">
         <f t="shared" si="3"/>
@@ -1672,7 +1669,7 @@
       </c>
       <c r="J8" s="10">
         <f t="shared" si="6"/>
-        <v>0.7186555071</v>
+        <v>0.8670015458</v>
       </c>
       <c r="K8" s="10">
         <f t="shared" si="10"/>
@@ -1687,11 +1684,11 @@
       <c r="O8" s="7"/>
       <c r="P8" s="10">
         <f t="shared" ref="P8:AB8" si="15">SUM(P2:P7)</f>
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="Q8" s="10">
         <f t="shared" si="15"/>
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="R8" s="10">
         <f t="shared" si="15"/>
@@ -1699,39 +1696,39 @@
       </c>
       <c r="S8" s="10">
         <f t="shared" si="15"/>
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="T8" s="10">
         <f t="shared" si="15"/>
-        <v>108.5</v>
+        <v>106.5</v>
       </c>
       <c r="U8" s="10">
         <f t="shared" si="15"/>
-        <v>99.5</v>
+        <v>96.5</v>
       </c>
       <c r="V8" s="10">
         <f t="shared" si="15"/>
-        <v>87</v>
+        <v>88.5</v>
       </c>
       <c r="W8" s="10">
         <f t="shared" si="15"/>
-        <v>76.5</v>
+        <v>81.5</v>
       </c>
       <c r="X8" s="10">
         <f t="shared" si="15"/>
-        <v>68.5</v>
+        <v>71</v>
       </c>
       <c r="Y8" s="10">
         <f t="shared" si="15"/>
-        <v>61.5</v>
+        <v>64</v>
       </c>
       <c r="Z8" s="10">
         <f t="shared" si="15"/>
-        <v>57</v>
+        <v>58.5</v>
       </c>
       <c r="AA8" s="10">
         <f t="shared" si="15"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AB8" s="10">
         <f t="shared" si="15"/>
@@ -1745,15 +1742,15 @@
         <v>1.08</v>
       </c>
       <c r="B9" s="9">
-        <v>3731.0</v>
+        <v>4496.0</v>
       </c>
       <c r="C9" s="10">
         <f t="shared" si="2"/>
-        <v>53.60083706</v>
+        <v>56.77893357</v>
       </c>
       <c r="D9" s="10">
         <f t="shared" si="3"/>
-        <v>54.5</v>
+        <v>58</v>
       </c>
       <c r="E9" s="10">
         <f t="shared" si="4"/>
@@ -1770,19 +1767,19 @@
       </c>
       <c r="I9" s="10">
         <f t="shared" si="5"/>
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="J9" s="10">
         <f t="shared" si="6"/>
-        <v>0.2016741119</v>
+        <v>0.5578671413</v>
       </c>
       <c r="K9" s="10">
         <f t="shared" si="10"/>
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L9" s="11">
         <f t="shared" si="7"/>
-        <v>54.5</v>
+        <v>58</v>
       </c>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
@@ -1808,15 +1805,15 @@
         <v>1.09</v>
       </c>
       <c r="B10" s="9">
-        <v>3458.0</v>
+        <v>3962.0</v>
       </c>
       <c r="C10" s="10">
         <f t="shared" si="2"/>
-        <v>47.54168514</v>
+        <v>48.84719592</v>
       </c>
       <c r="D10" s="10">
         <f t="shared" si="3"/>
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="E10" s="10">
         <f t="shared" si="4"/>
@@ -1833,19 +1830,19 @@
       </c>
       <c r="I10" s="10">
         <f t="shared" si="5"/>
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J10" s="10">
         <f t="shared" si="6"/>
-        <v>0.08337028504</v>
+        <v>0.6943918419</v>
       </c>
       <c r="K10" s="10">
         <f t="shared" si="10"/>
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L10" s="11">
         <f t="shared" si="7"/>
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
@@ -1871,15 +1868,15 @@
         <v>1.1</v>
       </c>
       <c r="B11" s="9">
-        <v>3375.0</v>
+        <v>3852.0</v>
       </c>
       <c r="C11" s="10">
         <f t="shared" si="2"/>
-        <v>42.18333691</v>
+        <v>43.27287131</v>
       </c>
       <c r="D11" s="10">
         <f t="shared" si="3"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E11" s="10">
         <f t="shared" si="4"/>
@@ -1896,19 +1893,19 @@
       </c>
       <c r="I11" s="10">
         <f t="shared" si="5"/>
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J11" s="10">
         <f t="shared" si="6"/>
-        <v>0.3666738246</v>
+        <v>0.5457426166</v>
       </c>
       <c r="K11" s="10">
         <f t="shared" si="10"/>
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L11" s="11">
         <f t="shared" si="7"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -1934,11 +1931,11 @@
         <v>1.11</v>
       </c>
       <c r="B12" s="9">
-        <v>3348.0</v>
+        <v>3655.0</v>
       </c>
       <c r="C12" s="10">
         <f t="shared" si="2"/>
-        <v>38.95212006</v>
+        <v>38.94398666</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="3"/>
@@ -1963,7 +1960,7 @@
       </c>
       <c r="J12" s="10">
         <f t="shared" si="6"/>
-        <v>0.9042401243</v>
+        <v>0.8879733251</v>
       </c>
       <c r="K12" s="10">
         <f t="shared" si="10"/>
@@ -1997,15 +1994,15 @@
         <v>1.12</v>
       </c>
       <c r="B13" s="9">
-        <v>3060.0</v>
+        <v>3490.0</v>
       </c>
       <c r="C13" s="10">
         <f t="shared" si="2"/>
-        <v>33.33899008</v>
+        <v>34.17979276</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="3"/>
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E13" s="10">
         <f t="shared" si="4"/>
@@ -2022,19 +2019,19 @@
       </c>
       <c r="I13" s="10">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J13" s="10">
         <f t="shared" si="6"/>
-        <v>0.6779801635</v>
+        <v>0.3595855109</v>
       </c>
       <c r="K13" s="10">
         <f t="shared" si="10"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L13" s="11">
         <f t="shared" si="7"/>
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
@@ -2060,15 +2057,15 @@
         <v>2.01</v>
       </c>
       <c r="B14" s="9">
-        <v>2817.0</v>
+        <v>2956.0</v>
       </c>
       <c r="C14" s="10">
         <f t="shared" si="2"/>
-        <v>28.95462706</v>
+        <v>28.3198364</v>
       </c>
       <c r="D14" s="10">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>28.5</v>
       </c>
       <c r="E14" s="10">
         <f t="shared" si="4"/>
@@ -2085,19 +2082,19 @@
       </c>
       <c r="I14" s="10">
         <f t="shared" si="5"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J14" s="10">
         <f t="shared" si="6"/>
-        <v>0.9092541106</v>
+        <v>0.6396727915</v>
       </c>
       <c r="K14" s="10">
         <f t="shared" si="10"/>
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L14" s="11">
         <f t="shared" si="7"/>
-        <v>29</v>
+        <v>28.5</v>
       </c>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
@@ -2123,15 +2120,15 @@
         <v>2.02</v>
       </c>
       <c r="B15" s="9">
-        <v>2486.0</v>
+        <v>2916.0</v>
       </c>
       <c r="C15" s="10">
         <f t="shared" si="2"/>
-        <v>24.64613739</v>
+        <v>25.62991281</v>
       </c>
       <c r="D15" s="10">
         <f t="shared" si="3"/>
-        <v>24.5</v>
+        <v>25.5</v>
       </c>
       <c r="E15" s="10">
         <f t="shared" si="4"/>
@@ -2148,19 +2145,19 @@
       </c>
       <c r="I15" s="10">
         <f t="shared" si="5"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J15" s="10">
         <f t="shared" si="6"/>
-        <v>0.2922747722</v>
+        <v>0.2598256233</v>
       </c>
       <c r="K15" s="10">
         <f t="shared" si="10"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L15" s="11">
         <f t="shared" si="7"/>
-        <v>24.5</v>
+        <v>25.5</v>
       </c>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
@@ -2186,15 +2183,15 @@
         <v>2.03</v>
       </c>
       <c r="B16" s="9">
-        <v>2454.0</v>
+        <v>2874.0</v>
       </c>
       <c r="C16" s="10">
         <f t="shared" si="2"/>
-        <v>22.67443769</v>
+        <v>23.5550663</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" si="3"/>
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
       <c r="E16" s="10">
         <f t="shared" si="4"/>
@@ -2211,19 +2208,19 @@
       </c>
       <c r="I16" s="10">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J16" s="10">
         <f t="shared" si="6"/>
-        <v>0.3488753704</v>
+        <v>0.1101326074</v>
       </c>
       <c r="K16" s="10">
         <f t="shared" si="10"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L16" s="11">
         <f t="shared" si="7"/>
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
@@ -2249,15 +2246,15 @@
         <v>2.04</v>
       </c>
       <c r="B17" s="9">
-        <v>2382.0</v>
+        <v>2870.0</v>
       </c>
       <c r="C17" s="10">
         <f t="shared" si="2"/>
-        <v>20.53923953</v>
+        <v>21.66981819</v>
       </c>
       <c r="D17" s="10">
         <f t="shared" si="3"/>
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="E17" s="10">
         <f t="shared" si="4"/>
@@ -2274,19 +2271,19 @@
       </c>
       <c r="I17" s="10">
         <f t="shared" si="5"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J17" s="10">
         <f t="shared" si="6"/>
-        <v>0.07847905937</v>
+        <v>0.3396363836</v>
       </c>
       <c r="K17" s="10">
         <f t="shared" si="10"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L17" s="11">
         <f t="shared" si="7"/>
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
@@ -2312,15 +2309,15 @@
         <v>2.05</v>
       </c>
       <c r="B18" s="9">
-        <v>2314.0</v>
+        <v>2724.0</v>
       </c>
       <c r="C18" s="10">
         <f t="shared" si="2"/>
-        <v>18.43045161</v>
+        <v>19.19835733</v>
       </c>
       <c r="D18" s="10">
         <f t="shared" si="3"/>
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="E18" s="10">
         <f t="shared" si="4"/>
@@ -2337,19 +2334,19 @@
       </c>
       <c r="I18" s="10">
         <f t="shared" si="5"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J18" s="10">
         <f t="shared" si="6"/>
-        <v>0.8609032195</v>
+        <v>0.396714658</v>
       </c>
       <c r="K18" s="10">
         <f t="shared" si="10"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L18" s="11">
         <f t="shared" si="7"/>
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="M18" s="7"/>
       <c r="N18" s="7"/>
@@ -2375,15 +2372,15 @@
         <v>2.06</v>
       </c>
       <c r="B19" s="9">
-        <v>2140.0</v>
+        <v>2635.0</v>
       </c>
       <c r="C19" s="10">
         <f t="shared" si="2"/>
-        <v>16.42707243</v>
+        <v>17.50331703</v>
       </c>
       <c r="D19" s="10">
         <f t="shared" si="3"/>
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="E19" s="10">
         <f t="shared" si="4"/>
@@ -2400,19 +2397,19 @@
       </c>
       <c r="I19" s="10">
         <f t="shared" si="5"/>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J19" s="10">
         <f t="shared" si="6"/>
-        <v>0.8541448641</v>
+        <v>0.006634064342</v>
       </c>
       <c r="K19" s="10">
         <f t="shared" si="10"/>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L19" s="11">
         <f t="shared" si="7"/>
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="M19" s="7"/>
       <c r="N19" s="7"/>
@@ -2438,15 +2435,15 @@
         <v>2.07</v>
       </c>
       <c r="B20" s="9">
-        <v>2127.0</v>
+        <v>2614.0</v>
       </c>
       <c r="C20" s="10">
         <f t="shared" si="2"/>
-        <v>14.99983348</v>
+        <v>15.97357762</v>
       </c>
       <c r="D20" s="10">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E20" s="10">
         <f t="shared" si="4"/>
@@ -2463,19 +2460,19 @@
       </c>
       <c r="I20" s="10">
         <f t="shared" si="5"/>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J20" s="10">
         <f t="shared" si="6"/>
-        <v>0.999666969</v>
+        <v>0.9471552331</v>
       </c>
       <c r="K20" s="10">
         <f t="shared" si="10"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L20" s="11">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M20" s="7"/>
       <c r="N20" s="7"/>
@@ -2501,15 +2498,15 @@
         <v>2.08</v>
       </c>
       <c r="B21" s="9">
-        <v>2081.0</v>
+        <v>2551.0</v>
       </c>
       <c r="C21" s="10">
         <f t="shared" si="2"/>
-        <v>13.70865748</v>
+        <v>14.57042068</v>
       </c>
       <c r="D21" s="10">
         <f t="shared" si="3"/>
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="E21" s="10">
         <f t="shared" si="4"/>
@@ -2526,19 +2523,19 @@
       </c>
       <c r="I21" s="10">
         <f t="shared" si="5"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J21" s="10">
         <f t="shared" si="6"/>
-        <v>0.4173149644</v>
+        <v>0.1408413679</v>
       </c>
       <c r="K21" s="10">
         <f t="shared" si="10"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L21" s="11">
         <f t="shared" si="7"/>
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="M21" s="7"/>
       <c r="N21" s="7"/>
@@ -2564,15 +2561,15 @@
         <v>2.09</v>
       </c>
       <c r="B22" s="9">
-        <v>2077.0</v>
+        <v>2485.0</v>
       </c>
       <c r="C22" s="10">
         <f t="shared" si="2"/>
-        <v>12.58031062</v>
+        <v>13.20114215</v>
       </c>
       <c r="D22" s="10">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="E22" s="10">
         <f t="shared" si="4"/>
@@ -2589,19 +2586,19 @@
       </c>
       <c r="I22" s="10">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J22" s="10">
         <f t="shared" si="6"/>
-        <v>0.1606212337</v>
+        <v>0.4022843027</v>
       </c>
       <c r="K22" s="10">
         <f t="shared" si="10"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L22" s="11">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
@@ -2627,15 +2624,15 @@
         <v>2.1</v>
       </c>
       <c r="B23" s="9">
-        <v>1935.0</v>
+        <v>2449.0</v>
       </c>
       <c r="C23" s="10">
         <f t="shared" si="2"/>
-        <v>10.99372871</v>
+        <v>11.88357616</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E23" s="10">
         <f t="shared" si="4"/>
@@ -2652,19 +2649,19 @@
       </c>
       <c r="I23" s="10">
         <f t="shared" si="5"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J23" s="10">
         <f t="shared" si="6"/>
-        <v>0.9874574247</v>
+        <v>0.7671523235</v>
       </c>
       <c r="K23" s="10">
         <f t="shared" si="10"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L23" s="11">
         <f t="shared" si="7"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M23" s="7"/>
       <c r="N23" s="7"/>
@@ -2690,15 +2687,15 @@
         <v>2.11</v>
       </c>
       <c r="B24" s="9">
-        <v>1881.0</v>
+        <v>2393.0</v>
       </c>
       <c r="C24" s="10">
         <f t="shared" si="2"/>
-        <v>10.03474313</v>
+        <v>10.86498137</v>
       </c>
       <c r="D24" s="10">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E24" s="10">
         <f t="shared" si="4"/>
@@ -2715,19 +2712,19 @@
       </c>
       <c r="I24" s="10">
         <f t="shared" si="5"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J24" s="10">
         <f t="shared" si="6"/>
-        <v>0.06948625293</v>
+        <v>0.7299627311</v>
       </c>
       <c r="K24" s="10">
         <f t="shared" si="10"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L24" s="11">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M24" s="7"/>
       <c r="N24" s="7"/>
@@ -2753,15 +2750,15 @@
         <v>2.12</v>
       </c>
       <c r="B25" s="9">
-        <v>1853.0</v>
+        <v>2349.0</v>
       </c>
       <c r="C25" s="10">
         <f t="shared" si="2"/>
-        <v>9.356469288</v>
+        <v>10.09371747</v>
       </c>
       <c r="D25" s="10">
         <f t="shared" si="3"/>
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="E25" s="10">
         <f t="shared" si="4"/>
@@ -2778,19 +2775,19 @@
       </c>
       <c r="I25" s="10">
         <f t="shared" si="5"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J25" s="10">
         <f t="shared" si="6"/>
-        <v>0.7129385758</v>
+        <v>0.1874349454</v>
       </c>
       <c r="K25" s="10">
         <f t="shared" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L25" s="11">
         <f t="shared" si="7"/>
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
@@ -2816,15 +2813,15 @@
         <v>3.01</v>
       </c>
       <c r="B26" s="9">
-        <v>1660.0</v>
+        <v>2331.0</v>
       </c>
       <c r="C26" s="10">
         <f t="shared" si="2"/>
-        <v>8.175029908</v>
+        <v>9.260413184</v>
       </c>
       <c r="D26" s="10">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E26" s="10">
         <f t="shared" si="4"/>
@@ -2841,19 +2838,19 @@
       </c>
       <c r="I26" s="10">
         <f t="shared" si="5"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J26" s="10">
         <f t="shared" si="6"/>
-        <v>0.3500598154</v>
+        <v>0.5208263684</v>
       </c>
       <c r="K26" s="10">
         <f t="shared" si="10"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L26" s="11">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M26" s="7"/>
       <c r="N26" s="7"/>
@@ -2879,15 +2876,15 @@
         <v>3.02</v>
       </c>
       <c r="B27" s="9">
-        <v>1642.0</v>
+        <v>2321.0</v>
       </c>
       <c r="C27" s="10">
         <f t="shared" si="2"/>
-        <v>7.58717066</v>
+        <v>8.609091984</v>
       </c>
       <c r="D27" s="10">
         <f t="shared" si="3"/>
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="E27" s="10">
         <f t="shared" si="4"/>
@@ -2904,19 +2901,19 @@
       </c>
       <c r="I27" s="10">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J27" s="10">
         <f t="shared" si="6"/>
-        <v>0.1743413199</v>
+        <v>0.2181839685</v>
       </c>
       <c r="K27" s="10">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L27" s="11">
         <f t="shared" si="7"/>
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
@@ -2942,15 +2939,15 @@
         <v>3.03</v>
       </c>
       <c r="B28" s="9">
-        <v>1579.0</v>
+        <v>2300.0</v>
       </c>
       <c r="C28" s="10">
         <f t="shared" si="2"/>
-        <v>6.840061315</v>
+        <v>7.870024625</v>
       </c>
       <c r="D28" s="10">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E28" s="10">
         <f t="shared" si="4"/>
@@ -2967,19 +2964,19 @@
       </c>
       <c r="I28" s="10">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J28" s="10">
         <f t="shared" si="6"/>
-        <v>0.6801226303</v>
+        <v>0.7400492507</v>
       </c>
       <c r="K28" s="10">
         <f t="shared" si="10"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L28" s="11">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M28" s="7"/>
       <c r="N28" s="7"/>
@@ -3005,15 +3002,15 @@
         <v>3.04</v>
       </c>
       <c r="B29" s="9">
-        <v>1544.0</v>
+        <v>1855.0</v>
       </c>
       <c r="C29" s="10">
         <f t="shared" si="2"/>
-        <v>6.247379098</v>
+        <v>6.526501992</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="E29" s="10">
         <f t="shared" si="4"/>
@@ -3030,19 +3027,19 @@
       </c>
       <c r="I29" s="10">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J29" s="10">
         <f t="shared" si="6"/>
-        <v>0.4947581954</v>
+        <v>0.05300398382</v>
       </c>
       <c r="K29" s="10">
         <f t="shared" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L29" s="11">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="M29" s="7"/>
       <c r="N29" s="7"/>
@@ -3086,15 +3083,15 @@
         <v>3.05</v>
       </c>
       <c r="B30" s="9">
-        <v>1224.0</v>
+        <v>1742.0</v>
       </c>
       <c r="C30" s="10">
         <f t="shared" si="2"/>
-        <v>5.304672514</v>
+        <v>5.923832598</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="3"/>
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="E30" s="10">
         <f t="shared" si="4"/>
@@ -3111,19 +3108,19 @@
       </c>
       <c r="I30" s="10">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J30" s="10">
         <f t="shared" si="6"/>
-        <v>0.6093450284</v>
+        <v>0.8476651953</v>
       </c>
       <c r="K30" s="10">
         <f t="shared" si="10"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L30" s="11">
         <f t="shared" si="7"/>
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="M30" s="7"/>
       <c r="N30" s="7"/>
@@ -3144,7 +3141,7 @@
       </c>
       <c r="U30" s="7"/>
       <c r="V30" s="12">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="W30" s="12" t="s">
         <v>26</v>
@@ -3154,7 +3151,7 @@
       </c>
       <c r="Y30" s="7" t="str">
         <f t="shared" ref="Y30:Y81" si="17">TEXT(V30,"0")&amp;"|"&amp;TRIM(W30)</f>
-        <v>3|Makayla</v>
+        <v>1|Blaine</v>
       </c>
       <c r="Z30" s="7"/>
       <c r="AA30" s="7"/>
@@ -3167,15 +3164,15 @@
         <v>3.06</v>
       </c>
       <c r="B31" s="9">
-        <v>1146.0</v>
+        <v>1653.0</v>
       </c>
       <c r="C31" s="10">
         <f t="shared" si="2"/>
-        <v>4.832186763</v>
+        <v>5.398808901</v>
       </c>
       <c r="D31" s="10">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="E31" s="10">
         <f t="shared" si="4"/>
@@ -3192,19 +3189,19 @@
       </c>
       <c r="I31" s="10">
         <f t="shared" si="5"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J31" s="10">
         <f t="shared" si="6"/>
-        <v>0.6643735259</v>
+        <v>0.7976178026</v>
       </c>
       <c r="K31" s="10">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L31" s="11">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="M31" s="7"/>
       <c r="N31" s="7"/>
@@ -3225,17 +3222,17 @@
       </c>
       <c r="U31" s="7"/>
       <c r="V31" s="14">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="W31" s="13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="X31" s="13" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Y31" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>2|Jason</v>
+        <v>1|Ed</v>
       </c>
       <c r="Z31" s="7"/>
       <c r="AA31" s="7"/>
@@ -3248,15 +3245,15 @@
         <v>3.07</v>
       </c>
       <c r="B32" s="9">
-        <v>1118.0</v>
+        <v>1615.0</v>
       </c>
       <c r="C32" s="10">
         <f t="shared" si="2"/>
-        <v>4.296964141</v>
+        <v>4.810713002</v>
       </c>
       <c r="D32" s="10">
         <f t="shared" si="3"/>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="E32" s="10">
         <f t="shared" si="4"/>
@@ -3273,19 +3270,19 @@
       </c>
       <c r="I32" s="10">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J32" s="10">
         <f t="shared" si="6"/>
-        <v>0.5939282828</v>
+        <v>0.6214260039</v>
       </c>
       <c r="K32" s="10">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L32" s="11">
         <f t="shared" si="7"/>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="M32" s="7"/>
       <c r="N32" s="7"/>
@@ -3293,7 +3290,7 @@
         <v>3.0</v>
       </c>
       <c r="P32" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q32" s="7"/>
       <c r="R32" s="4">
@@ -3309,14 +3306,14 @@
         <v>2.0</v>
       </c>
       <c r="W32" s="13" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="X32" s="13" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Y32" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>2|Eric</v>
+        <v>2|Blaine</v>
       </c>
       <c r="Z32" s="7"/>
       <c r="AA32" s="7"/>
@@ -3329,15 +3326,15 @@
         <v>3.08</v>
       </c>
       <c r="B33" s="9">
-        <v>1078.0</v>
+        <v>1606.0</v>
       </c>
       <c r="C33" s="10">
         <f t="shared" si="2"/>
-        <v>3.958928692</v>
+        <v>4.475243412</v>
       </c>
       <c r="D33" s="10">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="E33" s="10">
         <f t="shared" si="4"/>
@@ -3354,19 +3351,19 @@
       </c>
       <c r="I33" s="10">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J33" s="10">
         <f t="shared" si="6"/>
-        <v>0.9178573833</v>
+        <v>0.9504868244</v>
       </c>
       <c r="K33" s="10">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L33" s="11">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -3374,7 +3371,7 @@
         <v>4.0</v>
       </c>
       <c r="P33" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Q33" s="7"/>
       <c r="R33" s="4">
@@ -3390,14 +3387,14 @@
         <v>2.0</v>
       </c>
       <c r="W33" s="13" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="X33" s="13" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Y33" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>2|Ed</v>
+        <v>2|Collin</v>
       </c>
       <c r="Z33" s="7"/>
       <c r="AA33" s="7"/>
@@ -3410,15 +3407,15 @@
         <v>3.09</v>
       </c>
       <c r="B34" s="9">
-        <v>1050.0</v>
+        <v>1550.0</v>
       </c>
       <c r="C34" s="10">
         <f t="shared" si="2"/>
-        <v>3.619890895</v>
+        <v>4.068494974</v>
       </c>
       <c r="D34" s="10">
         <f t="shared" si="3"/>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E34" s="10">
         <f t="shared" si="4"/>
@@ -3435,19 +3432,19 @@
       </c>
       <c r="I34" s="10">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J34" s="10">
         <f t="shared" si="6"/>
-        <v>0.2397817903</v>
+        <v>0.1369899471</v>
       </c>
       <c r="K34" s="10">
         <f t="shared" si="10"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L34" s="11">
         <f t="shared" si="7"/>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="M34" s="7"/>
       <c r="N34" s="7"/>
@@ -3455,7 +3452,7 @@
         <v>5.0</v>
       </c>
       <c r="P34" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q34" s="7"/>
       <c r="R34" s="4">
@@ -3468,17 +3465,17 @@
       </c>
       <c r="U34" s="7"/>
       <c r="V34" s="14">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="W34" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="X34" s="13" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Y34" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>4|Joey</v>
+        <v>2|Kich</v>
       </c>
       <c r="Z34" s="7"/>
       <c r="AA34" s="7"/>
@@ -3491,15 +3488,15 @@
         <v>3.1</v>
       </c>
       <c r="B35" s="9">
-        <v>1023.0</v>
+        <v>1498.0</v>
       </c>
       <c r="C35" s="10">
         <f t="shared" si="2"/>
-        <v>3.459318147</v>
+        <v>3.850505722</v>
       </c>
       <c r="D35" s="10">
         <f t="shared" si="3"/>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E35" s="10">
         <f t="shared" si="4"/>
@@ -3516,19 +3513,19 @@
       </c>
       <c r="I35" s="10">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J35" s="10">
         <f t="shared" si="6"/>
-        <v>0.9186362948</v>
+        <v>0.7010114442</v>
       </c>
       <c r="K35" s="10">
         <f t="shared" si="10"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L35" s="11">
         <f t="shared" si="7"/>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="M35" s="7"/>
       <c r="N35" s="7"/>
@@ -3536,7 +3533,7 @@
         <v>6.0</v>
       </c>
       <c r="P35" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q35" s="7"/>
       <c r="R35" s="4">
@@ -3549,17 +3546,17 @@
       </c>
       <c r="U35" s="7"/>
       <c r="V35" s="14">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="W35" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X35" s="13" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Y35" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>5|Joey</v>
+        <v>2|Ty</v>
       </c>
       <c r="Z35" s="7"/>
       <c r="AA35" s="7"/>
@@ -3572,15 +3569,15 @@
         <v>3.11</v>
       </c>
       <c r="B36" s="9">
-        <v>992.0</v>
+        <v>1270.0</v>
       </c>
       <c r="C36" s="10">
         <f t="shared" si="2"/>
-        <v>3.142677043</v>
+        <v>3.31975183</v>
       </c>
       <c r="D36" s="10">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E36" s="10">
         <f t="shared" si="4"/>
@@ -3601,15 +3598,15 @@
       </c>
       <c r="J36" s="10">
         <f t="shared" si="6"/>
-        <v>0.2853540857</v>
+        <v>0.6395036593</v>
       </c>
       <c r="K36" s="10">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L36" s="11">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="M36" s="7"/>
       <c r="N36" s="7"/>
@@ -3617,7 +3614,7 @@
         <v>7.0</v>
       </c>
       <c r="P36" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q36" s="7"/>
       <c r="R36" s="4">
@@ -3630,17 +3627,17 @@
       </c>
       <c r="U36" s="7"/>
       <c r="V36" s="14">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="W36" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="X36" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Y36" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>5|Brent</v>
+        <v>2|Joey</v>
       </c>
       <c r="Z36" s="7"/>
       <c r="AA36" s="7"/>
@@ -3653,11 +3650,11 @@
         <v>3.12</v>
       </c>
       <c r="B37" s="9">
-        <v>925.0</v>
+        <v>1242.0</v>
       </c>
       <c r="C37" s="10">
         <f t="shared" si="2"/>
-        <v>2.999911193</v>
+        <v>3.203009774</v>
       </c>
       <c r="D37" s="10">
         <f t="shared" si="3"/>
@@ -3678,11 +3675,11 @@
       </c>
       <c r="I37" s="10">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J37" s="10">
         <f t="shared" si="6"/>
-        <v>0.9998223863</v>
+        <v>0.4060195486</v>
       </c>
       <c r="K37" s="10">
         <f t="shared" si="10"/>
@@ -3698,7 +3695,7 @@
         <v>8.0</v>
       </c>
       <c r="P37" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q37" s="7"/>
       <c r="R37" s="4">
@@ -3711,17 +3708,17 @@
       </c>
       <c r="U37" s="7"/>
       <c r="V37" s="14">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="W37" s="13" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="X37" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Y37" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>6|Brent</v>
+        <v>3|Roy</v>
       </c>
       <c r="Z37" s="7"/>
       <c r="AA37" s="7"/>
@@ -3734,15 +3731,15 @@
         <v>4.01</v>
       </c>
       <c r="B38" s="9">
-        <v>905.0</v>
+        <v>1055.0</v>
       </c>
       <c r="C38" s="10">
         <f t="shared" si="2"/>
-        <v>2.750522535</v>
+        <v>2.804449097</v>
       </c>
       <c r="D38" s="10">
         <f t="shared" si="3"/>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E38" s="10">
         <f t="shared" si="4"/>
@@ -3763,15 +3760,15 @@
       </c>
       <c r="J38" s="10">
         <f t="shared" si="6"/>
-        <v>0.5010450695</v>
+        <v>0.6088981937</v>
       </c>
       <c r="K38" s="10">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L38" s="11">
         <f t="shared" si="7"/>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M38" s="7"/>
       <c r="N38" s="7"/>
@@ -3779,7 +3776,7 @@
         <v>9.0</v>
       </c>
       <c r="P38" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q38" s="7"/>
       <c r="R38" s="4">
@@ -3792,17 +3789,17 @@
       </c>
       <c r="U38" s="7"/>
       <c r="V38" s="14">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="W38" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="X38" s="13" t="s">
         <v>27</v>
-      </c>
-      <c r="X38" s="13" t="s">
-        <v>29</v>
       </c>
       <c r="Y38" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1|Blaine</v>
+        <v>3|Brent</v>
       </c>
       <c r="Z38" s="7"/>
       <c r="AA38" s="7"/>
@@ -3815,11 +3812,11 @@
         <v>4.02</v>
       </c>
       <c r="B39" s="9">
-        <v>884.0</v>
+        <v>1050.0</v>
       </c>
       <c r="C39" s="10">
         <f t="shared" si="2"/>
-        <v>2.639344433</v>
+        <v>2.702537893</v>
       </c>
       <c r="D39" s="10">
         <f t="shared" si="3"/>
@@ -3844,7 +3841,7 @@
       </c>
       <c r="J39" s="10">
         <f t="shared" si="6"/>
-        <v>0.2786888661</v>
+        <v>0.4050757865</v>
       </c>
       <c r="K39" s="10">
         <f t="shared" si="10"/>
@@ -3860,7 +3857,7 @@
         <v>10.0</v>
       </c>
       <c r="P39" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Q39" s="7"/>
       <c r="R39" s="4">
@@ -3873,17 +3870,17 @@
       </c>
       <c r="U39" s="7"/>
       <c r="V39" s="14">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="W39" s="13" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="X39" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y39" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1|Ed</v>
+        <v>4|Roy</v>
       </c>
       <c r="Z39" s="7"/>
       <c r="AA39" s="7"/>
@@ -3896,11 +3893,11 @@
         <v>4.03</v>
       </c>
       <c r="B40" s="9">
-        <v>725.0</v>
+        <v>996.0</v>
       </c>
       <c r="C40" s="10">
         <f t="shared" si="2"/>
-        <v>2.300340716</v>
+        <v>2.441223105</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="3"/>
@@ -3925,7 +3922,7 @@
       </c>
       <c r="J40" s="10">
         <f t="shared" si="6"/>
-        <v>0.6006814316</v>
+        <v>0.8824462108</v>
       </c>
       <c r="K40" s="10">
         <f t="shared" si="10"/>
@@ -3941,7 +3938,7 @@
         <v>11.0</v>
       </c>
       <c r="P40" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q40" s="7"/>
       <c r="R40" s="4">
@@ -3954,17 +3951,17 @@
       </c>
       <c r="U40" s="7"/>
       <c r="V40" s="14">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="W40" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="X40" s="13" t="s">
         <v>27</v>
-      </c>
-      <c r="X40" s="13" t="s">
-        <v>29</v>
       </c>
       <c r="Y40" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>2|Blaine</v>
+        <v>4|Collin</v>
       </c>
       <c r="Z40" s="7"/>
       <c r="AA40" s="7"/>
@@ -3977,15 +3974,15 @@
         <v>4.04</v>
       </c>
       <c r="B41" s="9">
-        <v>693.0</v>
+        <v>980.0</v>
       </c>
       <c r="C41" s="10">
         <f t="shared" si="2"/>
-        <v>2.236209353</v>
+        <v>2.37835901</v>
       </c>
       <c r="D41" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E41" s="10">
         <f t="shared" si="4"/>
@@ -4006,15 +4003,15 @@
       </c>
       <c r="J41" s="10">
         <f t="shared" si="6"/>
-        <v>0.4724187054</v>
+        <v>0.7567180198</v>
       </c>
       <c r="K41" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L41" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
@@ -4022,7 +4019,7 @@
         <v>12.0</v>
       </c>
       <c r="P41" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q41" s="7"/>
       <c r="R41" s="4">
@@ -4035,17 +4032,17 @@
       </c>
       <c r="U41" s="7"/>
       <c r="V41" s="14">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="W41" s="13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="X41" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y41" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>2|Roy</v>
+        <v>4|Eric</v>
       </c>
       <c r="Z41" s="7"/>
       <c r="AA41" s="7"/>
@@ -4058,11 +4055,11 @@
         <v>4.05</v>
       </c>
       <c r="B42" s="13">
-        <v>681.0</v>
+        <v>961.0</v>
       </c>
       <c r="C42" s="10">
         <f t="shared" si="2"/>
-        <v>2.027585731</v>
+        <v>2.1553673</v>
       </c>
       <c r="D42" s="10">
         <f t="shared" si="3"/>
@@ -4087,7 +4084,7 @@
       </c>
       <c r="J42" s="10">
         <f t="shared" si="6"/>
-        <v>0.05517146174</v>
+        <v>0.3107345999</v>
       </c>
       <c r="K42" s="10">
         <f t="shared" si="10"/>
@@ -4107,17 +4104,17 @@
       <c r="T42" s="7"/>
       <c r="U42" s="7"/>
       <c r="V42" s="14">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="W42" s="13" t="s">
         <v>30</v>
       </c>
       <c r="X42" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y42" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>2|Collin</v>
+        <v>4|MaKayla</v>
       </c>
       <c r="Z42" s="7"/>
       <c r="AA42" s="7"/>
@@ -4130,11 +4127,11 @@
         <v>4.06</v>
       </c>
       <c r="B43" s="9">
-        <v>643.0</v>
+        <v>959.0</v>
       </c>
       <c r="C43" s="10">
         <f t="shared" si="2"/>
-        <v>1.93871145</v>
+        <v>2.078137938</v>
       </c>
       <c r="D43" s="10">
         <f t="shared" si="3"/>
@@ -4155,11 +4152,11 @@
       </c>
       <c r="I43" s="10">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J43" s="10">
         <f t="shared" si="6"/>
-        <v>0.8774229009</v>
+        <v>0.1562758754</v>
       </c>
       <c r="K43" s="10">
         <f t="shared" si="10"/>
@@ -4179,17 +4176,17 @@
       <c r="T43" s="7"/>
       <c r="U43" s="7"/>
       <c r="V43" s="14">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="W43" s="13" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="X43" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y43" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>2|Kich</v>
+        <v>4|Brent</v>
       </c>
       <c r="Z43" s="7"/>
       <c r="AA43" s="7"/>
@@ -4202,11 +4199,11 @@
         <v>4.07</v>
       </c>
       <c r="B44" s="9">
-        <v>608.0</v>
+        <v>930.0</v>
       </c>
       <c r="C44" s="10">
         <f t="shared" si="2"/>
-        <v>1.890293276</v>
+        <v>2.023645168</v>
       </c>
       <c r="D44" s="10">
         <f t="shared" si="3"/>
@@ -4227,11 +4224,11 @@
       </c>
       <c r="I44" s="10">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J44" s="10">
         <f t="shared" si="6"/>
-        <v>0.780586551</v>
+        <v>0.04729033657</v>
       </c>
       <c r="K44" s="10">
         <f t="shared" si="10"/>
@@ -4250,7 +4247,7 @@
         <v>9</v>
       </c>
       <c r="Q44" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R44" s="5" t="s">
         <v>17</v>
@@ -4259,17 +4256,17 @@
       <c r="T44" s="7"/>
       <c r="U44" s="7"/>
       <c r="V44" s="14">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="W44" s="13" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="X44" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y44" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>2|Ty</v>
+        <v>4|Ed</v>
       </c>
       <c r="Z44" s="7"/>
       <c r="AA44" s="7"/>
@@ -4282,11 +4279,11 @@
         <v>4.08</v>
       </c>
       <c r="B45" s="9">
-        <v>574.0</v>
+        <v>913.0</v>
       </c>
       <c r="C45" s="10">
         <f t="shared" si="2"/>
-        <v>1.84756062</v>
+        <v>1.97999543</v>
       </c>
       <c r="D45" s="10">
         <f t="shared" si="3"/>
@@ -4311,7 +4308,7 @@
       </c>
       <c r="J45" s="10">
         <f t="shared" si="6"/>
-        <v>0.6951212392</v>
+        <v>0.95999086</v>
       </c>
       <c r="K45" s="10">
         <f t="shared" si="10"/>
@@ -4338,7 +4335,7 @@
    INDEX($P$2:$AA$7,O45,P45) * $AD$1
 )
 </f>
-        <v>129.5</v>
+        <v>124</v>
       </c>
       <c r="R45" s="7" t="str">
         <f t="shared" ref="R45:R116" si="21">IF(
@@ -4359,17 +4356,17 @@
       <c r="T45" s="7"/>
       <c r="U45" s="7"/>
       <c r="V45" s="14">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="W45" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="X45" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y45" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>2|Joey</v>
+        <v>5|Eric</v>
       </c>
       <c r="Z45" s="7"/>
       <c r="AA45" s="7"/>
@@ -4382,11 +4379,11 @@
         <v>4.09</v>
       </c>
       <c r="B46" s="9">
-        <v>543.0</v>
+        <v>888.0</v>
       </c>
       <c r="C46" s="10">
         <f t="shared" si="2"/>
-        <v>1.646873516</v>
+        <v>1.772925922</v>
       </c>
       <c r="D46" s="10">
         <f t="shared" si="3"/>
@@ -4411,7 +4408,7 @@
       </c>
       <c r="J46" s="10">
         <f t="shared" si="6"/>
-        <v>0.2937470312</v>
+        <v>0.545851845</v>
       </c>
       <c r="K46" s="10">
         <f t="shared" si="10"/>
@@ -4433,7 +4430,7 @@
       </c>
       <c r="Q46" s="10">
         <f t="shared" si="20"/>
-        <v>129.5</v>
+        <v>124</v>
       </c>
       <c r="R46" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4443,17 +4440,17 @@
       <c r="T46" s="7"/>
       <c r="U46" s="7"/>
       <c r="V46" s="14">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="W46" s="13" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="X46" s="13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Y46" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>2|Brent</v>
+        <v>1|Eric</v>
       </c>
       <c r="Z46" s="7"/>
       <c r="AA46" s="7"/>
@@ -4466,11 +4463,11 @@
         <v>4.1</v>
       </c>
       <c r="B47" s="9">
-        <v>513.0</v>
+        <v>843.0</v>
       </c>
       <c r="C47" s="10">
         <f t="shared" si="2"/>
-        <v>1.581703755</v>
+        <v>1.693250653</v>
       </c>
       <c r="D47" s="10">
         <f t="shared" si="3"/>
@@ -4495,7 +4492,7 @@
       </c>
       <c r="J47" s="10">
         <f t="shared" si="6"/>
-        <v>0.1634075109</v>
+        <v>0.3865013066</v>
       </c>
       <c r="K47" s="10">
         <f t="shared" si="10"/>
@@ -4517,7 +4514,7 @@
       </c>
       <c r="Q47" s="10">
         <f t="shared" si="20"/>
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="R47" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4527,17 +4524,17 @@
       <c r="T47" s="7"/>
       <c r="U47" s="7"/>
       <c r="V47" s="14">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="W47" s="13" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="X47" s="13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Y47" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>3|Roy</v>
+        <v>1|MaKayla</v>
       </c>
       <c r="Z47" s="7"/>
       <c r="AA47" s="7"/>
@@ -4550,11 +4547,11 @@
         <v>4.11</v>
       </c>
       <c r="B48" s="9">
-        <v>485.0</v>
+        <v>781.0</v>
       </c>
       <c r="C48" s="10">
         <f t="shared" si="2"/>
-        <v>1.553595145</v>
+        <v>1.645132586</v>
       </c>
       <c r="D48" s="10">
         <f t="shared" si="3"/>
@@ -4579,7 +4576,7 @@
       </c>
       <c r="J48" s="10">
         <f t="shared" si="6"/>
-        <v>0.1071902898</v>
+        <v>0.2902651724</v>
       </c>
       <c r="K48" s="10">
         <f t="shared" si="10"/>
@@ -4601,7 +4598,7 @@
       </c>
       <c r="Q48" s="10">
         <f t="shared" si="20"/>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="R48" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4611,17 +4608,17 @@
       <c r="T48" s="7"/>
       <c r="U48" s="7"/>
       <c r="V48" s="14">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="W48" s="13" t="s">
         <v>35</v>
       </c>
       <c r="X48" s="13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Y48" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>3|Kich</v>
+        <v>2|Roy</v>
       </c>
       <c r="Z48" s="7"/>
       <c r="AA48" s="7"/>
@@ -4634,11 +4631,11 @@
         <v>4.12</v>
       </c>
       <c r="B49" s="9">
-        <v>458.0</v>
+        <v>666.0</v>
       </c>
       <c r="C49" s="10">
         <f t="shared" si="2"/>
-        <v>1.528865431</v>
+        <v>1.58462017</v>
       </c>
       <c r="D49" s="10">
         <f t="shared" si="3"/>
@@ -4663,7 +4660,7 @@
       </c>
       <c r="J49" s="10">
         <f t="shared" si="6"/>
-        <v>0.05773086105</v>
+        <v>0.1692403406</v>
       </c>
       <c r="K49" s="10">
         <f t="shared" si="10"/>
@@ -4685,7 +4682,7 @@
       </c>
       <c r="Q49" s="10">
         <f t="shared" si="20"/>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="R49" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4695,17 +4692,17 @@
       <c r="T49" s="7"/>
       <c r="U49" s="7"/>
       <c r="V49" s="14">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="W49" s="13" t="s">
         <v>28</v>
       </c>
       <c r="X49" s="13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Y49" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>3|Brent</v>
+        <v>5|Brent</v>
       </c>
       <c r="Z49" s="7"/>
       <c r="AA49" s="7"/>
@@ -4718,11 +4715,11 @@
         <v>5.01</v>
       </c>
       <c r="B50" s="9">
-        <v>433.0</v>
+        <v>637.0</v>
       </c>
       <c r="C50" s="10">
         <f t="shared" si="2"/>
-        <v>2.507472877</v>
+        <v>2.558418166</v>
       </c>
       <c r="D50" s="10">
         <f t="shared" si="3"/>
@@ -4747,7 +4744,7 @@
       </c>
       <c r="J50" s="10">
         <f t="shared" si="6"/>
-        <v>0.0149457548</v>
+        <v>0.1168363329</v>
       </c>
       <c r="K50" s="10">
         <f t="shared" si="10"/>
@@ -4769,27 +4766,27 @@
       </c>
       <c r="Q50" s="10">
         <f t="shared" si="20"/>
-        <v>73.5</v>
+        <v>69</v>
       </c>
       <c r="R50" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>Ed</v>
       </c>
       <c r="S50" s="7"/>
       <c r="T50" s="7"/>
       <c r="U50" s="7"/>
       <c r="V50" s="14">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="W50" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="X50" s="13" t="s">
         <v>25</v>
-      </c>
-      <c r="X50" s="13" t="s">
-        <v>29</v>
       </c>
       <c r="Y50" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>3|Ed</v>
+        <v>6|Brent</v>
       </c>
       <c r="Z50" s="7"/>
       <c r="AA50" s="7"/>
@@ -4802,11 +4799,11 @@
         <v>5.02</v>
       </c>
       <c r="B51" s="9">
-        <v>409.0</v>
+        <v>590.0</v>
       </c>
       <c r="C51" s="10">
         <f t="shared" si="2"/>
-        <v>2.48868622</v>
+        <v>2.529760411</v>
       </c>
       <c r="D51" s="10">
         <f t="shared" si="3"/>
@@ -4827,11 +4824,11 @@
       </c>
       <c r="I51" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J51" s="10">
         <f t="shared" si="6"/>
-        <v>0.9773724404</v>
+        <v>0.05952082165</v>
       </c>
       <c r="K51" s="10">
         <f t="shared" si="10"/>
@@ -4863,17 +4860,17 @@
       <c r="T51" s="7"/>
       <c r="U51" s="7"/>
       <c r="V51" s="14">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="W51" s="13" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="X51" s="13" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y51" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>4|Roy</v>
+        <v>1|Brent</v>
       </c>
       <c r="Z51" s="7"/>
       <c r="AA51" s="7"/>
@@ -4886,11 +4883,11 @@
         <v>5.03</v>
       </c>
       <c r="B52" s="9">
-        <v>387.0</v>
+        <v>552.0</v>
       </c>
       <c r="C52" s="10">
         <f t="shared" si="2"/>
-        <v>2.472496614</v>
+        <v>2.506718485</v>
       </c>
       <c r="D52" s="10">
         <f t="shared" si="3"/>
@@ -4911,11 +4908,11 @@
       </c>
       <c r="I52" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J52" s="10">
         <f t="shared" si="6"/>
-        <v>0.944993227</v>
+        <v>0.01343696904</v>
       </c>
       <c r="K52" s="10">
         <f t="shared" si="10"/>
@@ -4937,7 +4934,7 @@
       </c>
       <c r="Q52" s="10">
         <f t="shared" si="20"/>
-        <v>54.5</v>
+        <v>58</v>
       </c>
       <c r="R52" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4947,17 +4944,17 @@
       <c r="T52" s="7"/>
       <c r="U52" s="7"/>
       <c r="V52" s="14">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="W52" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="X52" s="13" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y52" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>4|Collin</v>
+        <v>2|Brent</v>
       </c>
       <c r="Z52" s="7"/>
       <c r="AA52" s="7"/>
@@ -4970,11 +4967,11 @@
         <v>5.04</v>
       </c>
       <c r="B53" s="9">
-        <v>366.0</v>
+        <v>538.0</v>
       </c>
       <c r="C53" s="10">
         <f t="shared" si="2"/>
-        <v>2.458305103</v>
+        <v>2.492079529</v>
       </c>
       <c r="D53" s="10">
         <f t="shared" si="3"/>
@@ -4999,7 +4996,7 @@
       </c>
       <c r="J53" s="10">
         <f t="shared" si="6"/>
-        <v>0.9166102059</v>
+        <v>0.9841590581</v>
       </c>
       <c r="K53" s="10">
         <f t="shared" si="10"/>
@@ -5021,27 +5018,27 @@
       </c>
       <c r="Q53" s="10">
         <f t="shared" si="20"/>
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="R53" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>Ed</v>
       </c>
       <c r="S53" s="7"/>
       <c r="T53" s="7"/>
       <c r="U53" s="7"/>
       <c r="V53" s="14">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="W53" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="X53" s="13" t="s">
         <v>32</v>
-      </c>
-      <c r="X53" s="13" t="s">
-        <v>29</v>
       </c>
       <c r="Y53" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>4|Eric</v>
+        <v>5|Jason</v>
       </c>
       <c r="Z53" s="7"/>
       <c r="AA53" s="7"/>
@@ -5054,11 +5051,11 @@
         <v>5.05</v>
       </c>
       <c r="B54" s="9">
-        <v>346.0</v>
+        <v>486.0</v>
       </c>
       <c r="C54" s="10">
         <f t="shared" si="2"/>
-        <v>2.445879971</v>
+        <v>2.470259875</v>
       </c>
       <c r="D54" s="10">
         <f t="shared" si="3"/>
@@ -5083,7 +5080,7 @@
       </c>
       <c r="J54" s="10">
         <f t="shared" si="6"/>
-        <v>0.8917599416</v>
+        <v>0.9405197497</v>
       </c>
       <c r="K54" s="10">
         <f t="shared" si="10"/>
@@ -5105,7 +5102,7 @@
       </c>
       <c r="Q54" s="10">
         <f t="shared" si="20"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R54" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5115,17 +5112,17 @@
       <c r="T54" s="7"/>
       <c r="U54" s="7"/>
       <c r="V54" s="14">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="W54" s="13" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="X54" s="13" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y54" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>4|MaKayla</v>
+        <v>6|Jason</v>
       </c>
       <c r="Z54" s="7"/>
       <c r="AA54" s="7"/>
@@ -5138,11 +5135,11 @@
         <v>5.06</v>
       </c>
       <c r="B55" s="9">
-        <v>327.0</v>
+        <v>456.0</v>
       </c>
       <c r="C55" s="10">
         <f t="shared" si="2"/>
-        <v>2.435014822</v>
+        <v>2.455596034</v>
       </c>
       <c r="D55" s="10">
         <f t="shared" si="3"/>
@@ -5167,7 +5164,7 @@
       </c>
       <c r="J55" s="10">
         <f t="shared" si="6"/>
-        <v>0.8700296449</v>
+        <v>0.9111920678</v>
       </c>
       <c r="K55" s="10">
         <f t="shared" si="10"/>
@@ -5199,17 +5196,17 @@
       <c r="T55" s="7"/>
       <c r="U55" s="7"/>
       <c r="V55" s="14">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="W55" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X55" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Y55" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>4|Brent</v>
+        <v>2|Jason</v>
       </c>
       <c r="Z55" s="7"/>
       <c r="AA55" s="7"/>
@@ -5222,11 +5219,11 @@
         <v>5.07</v>
       </c>
       <c r="B56" s="9">
-        <v>309.0</v>
+        <v>347.0</v>
       </c>
       <c r="C56" s="10">
         <f t="shared" si="2"/>
-        <v>2.425525957</v>
+        <v>2.427359485</v>
       </c>
       <c r="D56" s="10">
         <f t="shared" si="3"/>
@@ -5251,7 +5248,7 @@
       </c>
       <c r="J56" s="10">
         <f t="shared" si="6"/>
-        <v>0.8510519141</v>
+        <v>0.8547189693</v>
       </c>
       <c r="K56" s="10">
         <f t="shared" si="10"/>
@@ -5273,7 +5270,7 @@
       </c>
       <c r="Q56" s="10">
         <f t="shared" si="20"/>
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="R56" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5283,17 +5280,17 @@
       <c r="T56" s="7"/>
       <c r="U56" s="7"/>
       <c r="V56" s="14">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="W56" s="13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="X56" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Y56" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>4|Ed</v>
+        <v>2|Eric</v>
       </c>
       <c r="Z56" s="7"/>
       <c r="AA56" s="7"/>
@@ -5306,11 +5303,11 @@
         <v>5.08</v>
       </c>
       <c r="B57" s="9">
-        <v>292.0</v>
+        <v>147.0</v>
       </c>
       <c r="C57" s="10">
         <f t="shared" si="2"/>
-        <v>2.417249998</v>
+        <v>2.386761222</v>
       </c>
       <c r="D57" s="10">
         <f t="shared" si="3"/>
@@ -5335,7 +5332,7 @@
       </c>
       <c r="J57" s="10">
         <f t="shared" si="6"/>
-        <v>0.834499996</v>
+        <v>0.7735224443</v>
       </c>
       <c r="K57" s="10">
         <f t="shared" si="10"/>
@@ -5357,7 +5354,7 @@
       </c>
       <c r="Q57" s="10">
         <f t="shared" si="20"/>
-        <v>26.75</v>
+        <v>27</v>
       </c>
       <c r="R57" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5367,17 +5364,17 @@
       <c r="T57" s="7"/>
       <c r="U57" s="7"/>
       <c r="V57" s="14">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="W57" s="13" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="X57" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Y57" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>5|Eric</v>
+        <v>2|Ed</v>
       </c>
       <c r="Z57" s="7"/>
       <c r="AA57" s="7"/>
@@ -5390,11 +5387,11 @@
         <v>5.09</v>
       </c>
       <c r="B58" s="9">
-        <v>276.0</v>
+        <v>146.0</v>
       </c>
       <c r="C58" s="10">
         <f t="shared" si="2"/>
-        <v>2.410041761</v>
+        <v>2.384593582</v>
       </c>
       <c r="D58" s="10">
         <f t="shared" si="3"/>
@@ -5419,7 +5416,7 @@
       </c>
       <c r="J58" s="10">
         <f t="shared" si="6"/>
-        <v>0.820083521</v>
+        <v>0.7691871637</v>
       </c>
       <c r="K58" s="10">
         <f t="shared" si="10"/>
@@ -5441,7 +5438,7 @@
       </c>
       <c r="Q58" s="10">
         <f t="shared" si="20"/>
-        <v>26.75</v>
+        <v>27</v>
       </c>
       <c r="R58" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5461,7 +5458,7 @@
       </c>
       <c r="Y58" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>4|Jason</v>
+        <v>4|Joey</v>
       </c>
       <c r="Z58" s="7"/>
       <c r="AA58" s="7"/>
@@ -5474,11 +5471,11 @@
         <v>5.1</v>
       </c>
       <c r="B59" s="9">
-        <v>261.0</v>
+        <v>1.0</v>
       </c>
       <c r="C59" s="10">
         <f t="shared" si="2"/>
-        <v>2.403772332</v>
+        <v>2.360838683</v>
       </c>
       <c r="D59" s="10">
         <f t="shared" si="3"/>
@@ -5503,7 +5500,7 @@
       </c>
       <c r="J59" s="10">
         <f t="shared" si="6"/>
-        <v>0.8075446641</v>
+        <v>0.7216773657</v>
       </c>
       <c r="K59" s="10">
         <f t="shared" si="10"/>
@@ -5525,7 +5522,7 @@
       </c>
       <c r="Q59" s="10">
         <f t="shared" si="20"/>
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
       <c r="R59" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5535,17 +5532,17 @@
       <c r="T59" s="7"/>
       <c r="U59" s="7"/>
       <c r="V59" s="12">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="W59" s="12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="X59" s="13" t="s">
         <v>31</v>
       </c>
       <c r="Y59" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>6|Eric</v>
+        <v>5|Joey</v>
       </c>
       <c r="Z59" s="7"/>
       <c r="AA59" s="7"/>
@@ -5558,11 +5555,11 @@
         <v>5.11</v>
       </c>
       <c r="B60" s="9">
-        <v>247.0</v>
+        <v>1.0</v>
       </c>
       <c r="C60" s="10">
         <f t="shared" si="2"/>
-        <v>2.398327347</v>
+        <v>2.360827065</v>
       </c>
       <c r="D60" s="10">
         <f t="shared" si="3"/>
@@ -5587,7 +5584,7 @@
       </c>
       <c r="J60" s="10">
         <f t="shared" si="6"/>
-        <v>0.7966546932</v>
+        <v>0.7216541297</v>
       </c>
       <c r="K60" s="10">
         <f t="shared" si="10"/>
@@ -5609,27 +5606,27 @@
       </c>
       <c r="Q60" s="10">
         <f t="shared" si="20"/>
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="R60" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>Ed</v>
       </c>
       <c r="S60" s="7"/>
       <c r="T60" s="7"/>
       <c r="U60" s="7"/>
       <c r="V60" s="12">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="W60" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="X60" s="13" t="s">
         <v>30</v>
-      </c>
-      <c r="X60" s="13" t="s">
-        <v>35</v>
       </c>
       <c r="Y60" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>6|Collin</v>
+        <v>1|Roy</v>
       </c>
       <c r="Z60" s="7"/>
       <c r="AA60" s="7"/>
@@ -5642,11 +5639,11 @@
         <v>5.12</v>
       </c>
       <c r="B61" s="9">
-        <v>234.0</v>
+        <v>1.0</v>
       </c>
       <c r="C61" s="10">
         <f t="shared" si="2"/>
-        <v>2.393605433</v>
+        <v>2.360816339</v>
       </c>
       <c r="D61" s="10">
         <f t="shared" si="3"/>
@@ -5671,7 +5668,7 @@
       </c>
       <c r="J61" s="10">
         <f t="shared" si="6"/>
-        <v>0.7872108664</v>
+        <v>0.7216326789</v>
       </c>
       <c r="K61" s="10">
         <f t="shared" si="10"/>
@@ -5693,7 +5690,7 @@
       </c>
       <c r="Q61" s="10">
         <f t="shared" si="20"/>
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="R61" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5706,10 +5703,10 @@
         <v>1.0</v>
       </c>
       <c r="W61" s="13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="X61" s="13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Y61" s="7" t="str">
         <f t="shared" si="17"/>
@@ -5726,11 +5723,11 @@
         <v>6.01</v>
       </c>
       <c r="B62" s="9">
-        <v>221.0</v>
+        <v>1.0</v>
       </c>
       <c r="C62" s="10">
         <f t="shared" si="2"/>
-        <v>1.028699433</v>
+        <v>1.000118911</v>
       </c>
       <c r="D62" s="10">
         <f t="shared" si="3"/>
@@ -5755,7 +5752,7 @@
       </c>
       <c r="J62" s="10">
         <f t="shared" si="6"/>
-        <v>0.05739886682</v>
+        <v>0.0002378213096</v>
       </c>
       <c r="K62" s="10">
         <f t="shared" si="10"/>
@@ -5777,7 +5774,7 @@
       </c>
       <c r="Q62" s="10">
         <f t="shared" si="20"/>
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="R62" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5785,23 +5782,23 @@
       </c>
       <c r="S62" s="7"/>
       <c r="T62" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="U62" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="U62" s="7" t="s">
-        <v>40</v>
-      </c>
       <c r="V62" s="13">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="W62" s="13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="X62" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Y62" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1|Roy</v>
+        <v>3|Eric</v>
       </c>
       <c r="Z62" s="7"/>
       <c r="AA62" s="7"/>
@@ -5814,11 +5811,11 @@
         <v>6.02</v>
       </c>
       <c r="B63" s="9">
-        <v>209.0</v>
+        <v>1.0</v>
       </c>
       <c r="C63" s="10">
         <f t="shared" si="2"/>
-        <v>1.02505481</v>
+        <v>1.00010977</v>
       </c>
       <c r="D63" s="10">
         <f t="shared" si="3"/>
@@ -5843,7 +5840,7 @@
       </c>
       <c r="J63" s="10">
         <f t="shared" si="6"/>
-        <v>0.05010961966</v>
+        <v>0.0002195404458</v>
       </c>
       <c r="K63" s="10">
         <f t="shared" si="10"/>
@@ -5865,7 +5862,7 @@
       </c>
       <c r="Q63" s="10">
         <f t="shared" si="20"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R63" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5873,24 +5870,24 @@
       </c>
       <c r="S63" s="7"/>
       <c r="T63" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U63" s="10">
         <f t="shared" ref="U63:U74" si="22">SUMIF($R$45:$R$116, T63, $Q$45:$Q$116)</f>
-        <v>534.75</v>
+        <v>374</v>
       </c>
       <c r="V63" s="13">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="W63" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X63" s="13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="Y63" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1|Eric</v>
+        <v>3|Kich</v>
       </c>
       <c r="Z63" s="7"/>
       <c r="AA63" s="7"/>
@@ -5903,11 +5900,11 @@
         <v>6.03</v>
       </c>
       <c r="B64" s="9">
-        <v>198.0</v>
+        <v>1.0</v>
       </c>
       <c r="C64" s="10">
         <f t="shared" si="2"/>
-        <v>1.021911543</v>
+        <v>1.000101332</v>
       </c>
       <c r="D64" s="10">
         <f t="shared" si="3"/>
@@ -5932,7 +5929,7 @@
       </c>
       <c r="J64" s="10">
         <f t="shared" si="6"/>
-        <v>0.04382308594</v>
+        <v>0.0002026644095</v>
       </c>
       <c r="K64" s="10">
         <f t="shared" si="10"/>
@@ -5954,7 +5951,7 @@
       </c>
       <c r="Q64" s="10">
         <f t="shared" si="20"/>
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="R64" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5962,24 +5959,24 @@
       </c>
       <c r="S64" s="7"/>
       <c r="T64" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U64" s="10">
         <f t="shared" si="22"/>
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="V64" s="12">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="W64" s="12" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="X64" s="13" t="s">
         <v>29</v>
       </c>
       <c r="Y64" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1|MaKayla</v>
+        <v>4|Jason</v>
       </c>
       <c r="Z64" s="7"/>
       <c r="AA64" s="7"/>
@@ -5992,11 +5989,11 @@
         <v>6.04</v>
       </c>
       <c r="B65" s="9">
-        <v>187.0</v>
+        <v>1.0</v>
       </c>
       <c r="C65" s="10">
         <f t="shared" si="2"/>
-        <v>1.01910344</v>
+        <v>1.000093543</v>
       </c>
       <c r="D65" s="10">
         <f t="shared" si="3"/>
@@ -6021,7 +6018,7 @@
       </c>
       <c r="J65" s="10">
         <f t="shared" si="6"/>
-        <v>0.03820688078</v>
+        <v>0.0001870853144</v>
       </c>
       <c r="K65" s="10">
         <f t="shared" si="10"/>
@@ -6043,7 +6040,7 @@
       </c>
       <c r="Q65" s="10">
         <f t="shared" si="20"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="R65" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6051,24 +6048,24 @@
       </c>
       <c r="S65" s="7"/>
       <c r="T65" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="U65" s="10">
         <f t="shared" si="22"/>
-        <v>158.5</v>
+        <v>159.5</v>
       </c>
       <c r="V65" s="13">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="W65" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="X65" s="13" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="Y65" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>3|Eric</v>
+        <v>6|Eric</v>
       </c>
       <c r="Z65" s="7"/>
       <c r="AA65" s="7"/>
@@ -6081,11 +6078,11 @@
         <v>6.05</v>
       </c>
       <c r="B66" s="9">
-        <v>177.0</v>
+        <v>1.0</v>
       </c>
       <c r="C66" s="10">
         <f t="shared" si="2"/>
-        <v>1.016691863</v>
+        <v>1.000086352</v>
       </c>
       <c r="D66" s="10">
         <f t="shared" si="3"/>
@@ -6110,7 +6107,7 @@
       </c>
       <c r="J66" s="10">
         <f t="shared" si="6"/>
-        <v>0.03338372552</v>
+        <v>0.0001727035465</v>
       </c>
       <c r="K66" s="10">
         <f t="shared" si="10"/>
@@ -6132,7 +6129,7 @@
       </c>
       <c r="Q66" s="10">
         <f t="shared" si="20"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R66" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6140,24 +6137,24 @@
       </c>
       <c r="S66" s="7"/>
       <c r="T66" s="7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="U66" s="10">
         <f t="shared" si="22"/>
-        <v>138.5</v>
+        <v>148.5</v>
       </c>
       <c r="V66" s="14">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="W66" s="13" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="X66" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Y66" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>1|Brent</v>
+        <v>6|Collin</v>
       </c>
       <c r="Z66" s="7"/>
       <c r="AA66" s="7"/>
@@ -6170,11 +6167,11 @@
         <v>6.06</v>
       </c>
       <c r="B67" s="9">
-        <v>168.0</v>
+        <v>1.0</v>
       </c>
       <c r="C67" s="10">
         <f t="shared" si="2"/>
-        <v>1.0146252</v>
+        <v>1.000079714</v>
       </c>
       <c r="D67" s="10">
         <f t="shared" si="3"/>
@@ -6199,7 +6196,7 @@
       </c>
       <c r="J67" s="10">
         <f t="shared" si="6"/>
-        <v>0.02925039908</v>
+        <v>0.0001594271327</v>
       </c>
       <c r="K67" s="10">
         <f t="shared" si="10"/>
@@ -6221,32 +6218,32 @@
       </c>
       <c r="Q67" s="10">
         <f t="shared" si="20"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R67" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>Ty</v>
       </c>
       <c r="S67" s="7"/>
       <c r="T67" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="U67" s="10">
         <f t="shared" si="22"/>
-        <v>68.5</v>
+        <v>138.5</v>
       </c>
       <c r="V67" s="14">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="W67" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X67" s="13" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="Y67" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>5|Jason</v>
+        <v>3|MaKayla</v>
       </c>
       <c r="Z67" s="7"/>
       <c r="AA67" s="7"/>
@@ -6259,11 +6256,11 @@
         <v>6.07</v>
       </c>
       <c r="B68" s="9">
-        <v>159.0</v>
+        <v>1.0</v>
       </c>
       <c r="C68" s="10">
         <f t="shared" si="2"/>
-        <v>1.012777624</v>
+        <v>1.000073586</v>
       </c>
       <c r="D68" s="10">
         <f t="shared" si="3"/>
@@ -6288,7 +6285,7 @@
       </c>
       <c r="J68" s="10">
         <f t="shared" si="6"/>
-        <v>0.02555524827</v>
+        <v>0.0001471711561</v>
       </c>
       <c r="K68" s="10">
         <f t="shared" si="10"/>
@@ -6310,7 +6307,7 @@
       </c>
       <c r="Q68" s="10">
         <f t="shared" si="20"/>
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="R68" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6318,24 +6315,18 @@
       </c>
       <c r="S68" s="7"/>
       <c r="T68" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U68" s="10">
         <f t="shared" si="22"/>
-        <v>51</v>
-      </c>
-      <c r="V68" s="14">
-        <v>6.0</v>
-      </c>
-      <c r="W68" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="X68" s="13" t="s">
-        <v>34</v>
-      </c>
+        <v>68.5</v>
+      </c>
+      <c r="V68" s="14"/>
+      <c r="W68" s="13"/>
+      <c r="X68" s="13"/>
       <c r="Y68" s="7" t="str">
         <f t="shared" si="17"/>
-        <v>6|Jason</v>
+        <v>0|</v>
       </c>
       <c r="Z68" s="7"/>
       <c r="AA68" s="7"/>
@@ -6348,11 +6339,11 @@
         <v>6.08</v>
       </c>
       <c r="B69" s="13">
-        <v>150.0</v>
+        <v>1.0</v>
       </c>
       <c r="C69" s="10">
         <f t="shared" si="2"/>
-        <v>1.01112767</v>
+        <v>1.000067929</v>
       </c>
       <c r="D69" s="10">
         <f t="shared" si="3"/>
@@ -6377,7 +6368,7 @@
       </c>
       <c r="J69" s="10">
         <f t="shared" si="6"/>
-        <v>0.02225534086</v>
+        <v>0.0001358572166</v>
       </c>
       <c r="K69" s="10">
         <f t="shared" si="10"/>
@@ -6399,7 +6390,7 @@
       </c>
       <c r="Q69" s="10">
         <f t="shared" si="20"/>
-        <v>7.75</v>
+        <v>8.75</v>
       </c>
       <c r="R69" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6407,11 +6398,11 @@
       </c>
       <c r="S69" s="7"/>
       <c r="T69" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="U69" s="10">
         <f t="shared" si="22"/>
-        <v>51</v>
+        <v>62.5</v>
       </c>
       <c r="V69" s="12"/>
       <c r="W69" s="12"/>
@@ -6431,11 +6422,11 @@
         <v>6.09</v>
       </c>
       <c r="B70" s="9">
-        <v>142.0</v>
+        <v>1.0</v>
       </c>
       <c r="C70" s="10">
         <f t="shared" si="2"/>
-        <v>1.009724358</v>
+        <v>1.000062706</v>
       </c>
       <c r="D70" s="10">
         <f t="shared" si="3"/>
@@ -6460,7 +6451,7 @@
       </c>
       <c r="J70" s="10">
         <f t="shared" si="6"/>
-        <v>0.01944871637</v>
+        <v>0.0001254129316</v>
       </c>
       <c r="K70" s="10">
         <f t="shared" si="10"/>
@@ -6482,7 +6473,7 @@
       </c>
       <c r="Q70" s="10">
         <f t="shared" si="20"/>
-        <v>7.75</v>
+        <v>8.75</v>
       </c>
       <c r="R70" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6490,11 +6481,11 @@
       </c>
       <c r="S70" s="7"/>
       <c r="T70" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="U70" s="10">
         <f t="shared" si="22"/>
-        <v>16.25</v>
+        <v>52.5</v>
       </c>
       <c r="V70" s="3"/>
       <c r="W70" s="3"/>
@@ -6514,11 +6505,11 @@
         <v>6.1</v>
       </c>
       <c r="B71" s="9">
-        <v>134.0</v>
+        <v>1.0</v>
       </c>
       <c r="C71" s="10">
         <f t="shared" si="2"/>
-        <v>1.008471038</v>
+        <v>1.000057886</v>
       </c>
       <c r="D71" s="10">
         <f t="shared" si="3"/>
@@ -6543,7 +6534,7 @@
       </c>
       <c r="J71" s="10">
         <f t="shared" si="6"/>
-        <v>0.0169420768</v>
+        <v>0.0001157714757</v>
       </c>
       <c r="K71" s="10">
         <f t="shared" si="10"/>
@@ -6565,7 +6556,7 @@
       </c>
       <c r="Q71" s="10">
         <f t="shared" si="20"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R71" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6573,11 +6564,11 @@
       </c>
       <c r="S71" s="7"/>
       <c r="T71" s="7" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="U71" s="10">
         <f t="shared" si="22"/>
-        <v>7.5</v>
+        <v>18</v>
       </c>
       <c r="V71" s="3"/>
       <c r="W71" s="3"/>
@@ -6597,11 +6588,11 @@
         <v>6.11</v>
       </c>
       <c r="B72" s="13">
-        <v>127.0</v>
+        <v>1.0</v>
       </c>
       <c r="C72" s="10">
         <f t="shared" si="2"/>
-        <v>1.007411302</v>
+        <v>1.000053436</v>
       </c>
       <c r="D72" s="10">
         <f t="shared" si="3"/>
@@ -6626,7 +6617,7 @@
       </c>
       <c r="J72" s="10">
         <f t="shared" si="6"/>
-        <v>0.01482260381</v>
+        <v>0.0001068711545</v>
       </c>
       <c r="K72" s="10">
         <f t="shared" si="10"/>
@@ -6648,7 +6639,7 @@
       </c>
       <c r="Q72" s="10">
         <f t="shared" si="20"/>
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="R72" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6656,11 +6647,11 @@
       </c>
       <c r="S72" s="7"/>
       <c r="T72" s="7" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="U72" s="10">
         <f t="shared" si="22"/>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="V72" s="3"/>
       <c r="W72" s="3"/>
@@ -6680,11 +6671,11 @@
         <v>6.12</v>
       </c>
       <c r="B73" s="9">
-        <v>118.0</v>
+        <v>1.0</v>
       </c>
       <c r="C73" s="10">
         <f t="shared" si="2"/>
-        <v>1.006356696</v>
+        <v>1.000049328</v>
       </c>
       <c r="D73" s="10">
         <f t="shared" si="3"/>
@@ -6709,7 +6700,7 @@
       </c>
       <c r="J73" s="10">
         <f t="shared" si="6"/>
-        <v>0.01271339197</v>
+        <v>0.00009865501143</v>
       </c>
       <c r="K73" s="10">
         <f t="shared" si="10"/>
@@ -6731,7 +6722,7 @@
       </c>
       <c r="Q73" s="10">
         <f t="shared" si="20"/>
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="R73" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6739,7 +6730,7 @@
       </c>
       <c r="S73" s="7"/>
       <c r="T73" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="U73" s="10">
         <f t="shared" si="22"/>
@@ -6794,7 +6785,7 @@
       </c>
       <c r="Q74" s="10">
         <f t="shared" si="20"/>
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R74" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6846,11 +6837,11 @@
       </c>
       <c r="Q75" s="10">
         <f t="shared" si="20"/>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="R75" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>Roy</v>
       </c>
       <c r="S75" s="7"/>
       <c r="T75" s="7"/>
@@ -6895,7 +6886,7 @@
       </c>
       <c r="Q76" s="10">
         <f t="shared" si="20"/>
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R76" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6942,7 +6933,7 @@
       </c>
       <c r="Q77" s="10">
         <f t="shared" si="20"/>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R77" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6989,7 +6980,7 @@
       </c>
       <c r="Q78" s="10">
         <f t="shared" si="20"/>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R78" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7036,7 +7027,7 @@
       </c>
       <c r="Q79" s="10">
         <f t="shared" si="20"/>
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="R79" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7087,7 +7078,7 @@
       </c>
       <c r="R80" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>Ed</v>
       </c>
       <c r="S80" s="7"/>
       <c r="T80" s="7"/>
@@ -7130,7 +7121,7 @@
       </c>
       <c r="Q81" s="10">
         <f t="shared" si="20"/>
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="R81" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7177,7 +7168,7 @@
       </c>
       <c r="Q82" s="10">
         <f t="shared" si="20"/>
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="R82" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7265,7 +7256,7 @@
       </c>
       <c r="Q84" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="R84" s="7" t="str">
         <f t="shared" si="21"/>
@@ -8907,7 +8898,7 @@
      )
      &lt;= 1200 - SUMPRODUCT(ROUNDDOWN($C$2:$C$73,0)) )
 </f>
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="N123" s="7"/>
       <c r="O123" s="7"/>
@@ -9370,7 +9361,7 @@
       <c r="X137" s="7"/>
       <c r="Y137" s="7"/>
       <c r="Z137" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA137" s="7"/>
       <c r="AB137" s="7"/>
@@ -9435,13 +9426,13 @@
       <c r="U139" s="7"/>
       <c r="V139" s="7"/>
       <c r="W139" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="X139" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="X139" s="13" t="s">
+      <c r="Y139" s="13" t="s">
         <v>43</v>
-      </c>
-      <c r="Y139" s="13" t="s">
-        <v>44</v>
       </c>
       <c r="Z139" s="13">
         <v>5203.0</v>
@@ -9478,10 +9469,10 @@
         <v>1.0</v>
       </c>
       <c r="X140" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y140" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="Y140" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="Z140" s="13">
         <v>5103.0</v>
@@ -9518,10 +9509,10 @@
         <v>3.0</v>
       </c>
       <c r="X141" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y141" s="13" t="s">
         <v>47</v>
-      </c>
-      <c r="Y141" s="13" t="s">
-        <v>48</v>
       </c>
       <c r="Z141" s="13">
         <v>5020.0</v>
@@ -9558,10 +9549,10 @@
         <v>4.0</v>
       </c>
       <c r="X142" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y142" s="13" t="s">
         <v>49</v>
-      </c>
-      <c r="Y142" s="13" t="s">
-        <v>50</v>
       </c>
       <c r="Z142" s="13">
         <v>4517.0</v>
@@ -9598,10 +9589,10 @@
         <v>5.0</v>
       </c>
       <c r="X143" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Y143" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z143" s="13">
         <v>4164.0</v>
@@ -9638,10 +9629,10 @@
         <v>6.0</v>
       </c>
       <c r="X144" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y144" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z144" s="13">
         <v>4025.0</v>
@@ -9678,10 +9669,10 @@
         <v>7.0</v>
       </c>
       <c r="X145" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y145" s="13" t="s">
         <v>53</v>
-      </c>
-      <c r="Y145" s="13" t="s">
-        <v>54</v>
       </c>
       <c r="Z145" s="13">
         <v>3650.0</v>
@@ -9718,10 +9709,10 @@
         <v>8.0</v>
       </c>
       <c r="X146" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y146" s="13" t="s">
         <v>55</v>
-      </c>
-      <c r="Y146" s="13" t="s">
-        <v>56</v>
       </c>
       <c r="Z146" s="13">
         <v>3611.0</v>
@@ -9758,10 +9749,10 @@
         <v>9.0</v>
       </c>
       <c r="X147" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Y147" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z147" s="13">
         <v>3608.0</v>
@@ -9798,10 +9789,10 @@
         <v>10.0</v>
       </c>
       <c r="X148" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y148" s="13" t="s">
         <v>58</v>
-      </c>
-      <c r="Y148" s="13" t="s">
-        <v>59</v>
       </c>
       <c r="Z148" s="13">
         <v>3596.0</v>
@@ -9838,10 +9829,10 @@
         <v>11.0</v>
       </c>
       <c r="X149" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Y149" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Z149" s="13">
         <v>3426.0</v>
@@ -9878,10 +9869,10 @@
         <v>12.0</v>
       </c>
       <c r="X150" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y150" s="13" t="s">
         <v>61</v>
-      </c>
-      <c r="Y150" s="13" t="s">
-        <v>62</v>
       </c>
       <c r="Z150" s="13">
         <v>3264.0</v>
@@ -9918,10 +9909,10 @@
         <v>13.0</v>
       </c>
       <c r="X151" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y151" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Z151" s="13">
         <v>3179.0</v>
@@ -9958,10 +9949,10 @@
         <v>14.0</v>
       </c>
       <c r="X152" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Y152" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Z152" s="13">
         <v>3162.0</v>
@@ -9998,10 +9989,10 @@
         <v>15.0</v>
       </c>
       <c r="X153" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Y153" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z153" s="13">
         <v>3125.0</v>
@@ -10038,10 +10029,10 @@
         <v>16.0</v>
       </c>
       <c r="X154" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Y154" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Z154" s="13">
         <v>2971.0</v>
@@ -10078,10 +10069,10 @@
         <v>17.0</v>
       </c>
       <c r="X155" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Y155" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Z155" s="13">
         <v>2963.0</v>
@@ -10118,10 +10109,10 @@
         <v>18.0</v>
       </c>
       <c r="X156" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y156" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Z156" s="13">
         <v>2953.0</v>
@@ -10158,10 +10149,10 @@
         <v>19.0</v>
       </c>
       <c r="X157" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Y157" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Z157" s="13">
         <v>2807.0</v>
@@ -10198,10 +10189,10 @@
         <v>20.0</v>
       </c>
       <c r="X158" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y158" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Z158" s="13">
         <v>2696.0</v>
@@ -10238,10 +10229,10 @@
         <v>21.0</v>
       </c>
       <c r="X159" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Y159" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z159" s="13">
         <v>2672.0</v>
@@ -10278,10 +10269,10 @@
         <v>22.0</v>
       </c>
       <c r="X160" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y160" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z160" s="13">
         <v>2480.0</v>
@@ -10318,10 +10309,10 @@
         <v>23.0</v>
       </c>
       <c r="X161" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Y161" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Z161" s="13">
         <v>2416.0</v>
@@ -10358,10 +10349,10 @@
         <v>24.0</v>
       </c>
       <c r="X162" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y162" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z162" s="13">
         <v>2416.0</v>
@@ -10398,10 +10389,10 @@
         <v>25.0</v>
       </c>
       <c r="X163" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Y163" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Z163" s="13">
         <v>2109.0</v>
@@ -10438,10 +10429,10 @@
         <v>26.0</v>
       </c>
       <c r="X164" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Y164" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Z164" s="13">
         <v>2106.0</v>
@@ -10478,10 +10469,10 @@
         <v>27.0</v>
       </c>
       <c r="X165" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y165" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Z165" s="13">
         <v>2098.0</v>
@@ -10518,10 +10509,10 @@
         <v>28.0</v>
       </c>
       <c r="X166" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Y166" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z166" s="13">
         <v>2078.0</v>
@@ -10558,10 +10549,10 @@
         <v>29.0</v>
       </c>
       <c r="X167" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Y167" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Z167" s="13">
         <v>2074.0</v>
@@ -10598,10 +10589,10 @@
         <v>30.0</v>
       </c>
       <c r="X168" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y168" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z168" s="13">
         <v>2066.0</v>
@@ -10638,10 +10629,10 @@
         <v>31.0</v>
       </c>
       <c r="X169" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Y169" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z169" s="13">
         <v>2045.0</v>
@@ -10678,10 +10669,10 @@
         <v>32.0</v>
       </c>
       <c r="X170" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Y170" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Z170" s="13">
         <v>1977.0</v>
@@ -10718,10 +10709,10 @@
         <v>33.0</v>
       </c>
       <c r="X171" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y171" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z171" s="13">
         <v>1967.0</v>
@@ -10758,10 +10749,10 @@
         <v>34.0</v>
       </c>
       <c r="X172" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y172" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Z172" s="13">
         <v>1962.0</v>
@@ -10798,10 +10789,10 @@
         <v>35.0</v>
       </c>
       <c r="X173" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y173" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Z173" s="13">
         <v>1961.0</v>
@@ -10838,10 +10829,10 @@
         <v>36.0</v>
       </c>
       <c r="X174" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Y174" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z174" s="13">
         <v>1910.0</v>
@@ -10878,10 +10869,10 @@
         <v>37.0</v>
       </c>
       <c r="X175" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Y175" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Z175" s="13">
         <v>1873.0</v>
@@ -10918,10 +10909,10 @@
         <v>38.0</v>
       </c>
       <c r="X176" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y176" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z176" s="13">
         <v>1822.0</v>
@@ -10958,10 +10949,10 @@
         <v>39.0</v>
       </c>
       <c r="X177" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y177" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z177" s="13">
         <v>1741.0</v>
@@ -10998,10 +10989,10 @@
         <v>40.0</v>
       </c>
       <c r="X178" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Y178" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z178" s="13">
         <v>1724.0</v>
@@ -11038,10 +11029,10 @@
         <v>41.0</v>
       </c>
       <c r="X179" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Y179" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z179" s="13">
         <v>1660.0</v>
@@ -11078,10 +11069,10 @@
         <v>42.0</v>
       </c>
       <c r="X180" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Y180" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Z180" s="13">
         <v>1640.0</v>
@@ -11118,10 +11109,10 @@
         <v>43.0</v>
       </c>
       <c r="X181" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y181" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z181" s="13">
         <v>1577.0</v>
@@ -11158,10 +11149,10 @@
         <v>44.0</v>
       </c>
       <c r="X182" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y182" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Z182" s="13">
         <v>1565.0</v>
@@ -11198,10 +11189,10 @@
         <v>45.0</v>
       </c>
       <c r="X183" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Y183" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Z183" s="13">
         <v>1552.0</v>
@@ -11238,10 +11229,10 @@
         <v>46.0</v>
       </c>
       <c r="X184" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y184" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z184" s="13">
         <v>1404.0</v>
@@ -11278,10 +11269,10 @@
         <v>47.0</v>
       </c>
       <c r="X185" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Y185" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z185" s="13">
         <v>1351.0</v>
@@ -11318,10 +11309,10 @@
         <v>48.0</v>
       </c>
       <c r="X186" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Y186" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z186" s="13">
         <v>1344.0</v>
@@ -11358,10 +11349,10 @@
         <v>49.0</v>
       </c>
       <c r="X187" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Y187" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Z187" s="13">
         <v>1299.0</v>
@@ -11398,10 +11389,10 @@
         <v>50.0</v>
       </c>
       <c r="X188" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Y188" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Z188" s="13">
         <v>1261.0</v>
@@ -11438,10 +11429,10 @@
         <v>51.0</v>
       </c>
       <c r="X189" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Y189" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Z189" s="13">
         <v>1247.0</v>
@@ -11478,10 +11469,10 @@
         <v>52.0</v>
       </c>
       <c r="X190" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Y190" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Z190" s="13">
         <v>1226.0</v>
@@ -11518,10 +11509,10 @@
         <v>53.0</v>
       </c>
       <c r="X191" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Y191" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z191" s="13">
         <v>1211.0</v>
@@ -11558,10 +11549,10 @@
         <v>54.0</v>
       </c>
       <c r="X192" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Y192" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z192" s="13">
         <v>1197.0</v>
@@ -11598,10 +11589,10 @@
         <v>55.0</v>
       </c>
       <c r="X193" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Y193" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z193" s="13">
         <v>1184.0</v>
@@ -11638,10 +11629,10 @@
         <v>56.0</v>
       </c>
       <c r="X194" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Y194" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Z194" s="13">
         <v>1157.0</v>
@@ -11678,10 +11669,10 @@
         <v>57.0</v>
       </c>
       <c r="X195" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Y195" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z195" s="13">
         <v>1143.0</v>
@@ -11718,10 +11709,10 @@
         <v>58.0</v>
       </c>
       <c r="X196" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Y196" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z196" s="13">
         <v>1078.0</v>
@@ -11758,10 +11749,10 @@
         <v>59.0</v>
       </c>
       <c r="X197" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y197" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z197" s="13">
         <v>1069.0</v>
@@ -11798,10 +11789,10 @@
         <v>60.0</v>
       </c>
       <c r="X198" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Y198" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z198" s="13">
         <v>1000.0</v>
@@ -11838,10 +11829,10 @@
         <v>61.0</v>
       </c>
       <c r="X199" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Y199" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Z199" s="13">
         <v>987.0</v>
@@ -11878,10 +11869,10 @@
         <v>62.0</v>
       </c>
       <c r="X200" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y200" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z200" s="13">
         <v>952.0</v>
@@ -11918,10 +11909,10 @@
         <v>63.0</v>
       </c>
       <c r="X201" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Y201" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Z201" s="13">
         <v>913.0</v>
@@ -11958,10 +11949,10 @@
         <v>64.0</v>
       </c>
       <c r="X202" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y202" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Z202" s="13">
         <v>905.0</v>
@@ -11998,10 +11989,10 @@
         <v>65.0</v>
       </c>
       <c r="X203" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Y203" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Z203" s="13">
         <v>842.0</v>
@@ -12038,10 +12029,10 @@
         <v>66.0</v>
       </c>
       <c r="X204" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Y204" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z204" s="13">
         <v>823.0</v>
@@ -12078,10 +12069,10 @@
         <v>67.0</v>
       </c>
       <c r="X205" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y205" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z205" s="13">
         <v>820.0</v>
@@ -12118,10 +12109,10 @@
         <v>68.0</v>
       </c>
       <c r="X206" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y206" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Z206" s="13">
         <v>805.0</v>
@@ -12158,10 +12149,10 @@
         <v>69.0</v>
       </c>
       <c r="X207" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y207" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z207" s="13">
         <v>782.0</v>
@@ -12198,10 +12189,10 @@
         <v>70.0</v>
       </c>
       <c r="X208" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Y208" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z208" s="13">
         <v>736.0</v>
@@ -12238,10 +12229,10 @@
         <v>71.0</v>
       </c>
       <c r="X209" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Y209" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z209" s="13">
         <v>733.0</v>
@@ -12278,10 +12269,10 @@
         <v>72.0</v>
       </c>
       <c r="X210" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Y210" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z210" s="13">
         <v>700.0</v>
@@ -12318,10 +12309,10 @@
         <v>73.0</v>
       </c>
       <c r="X211" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y211" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z211" s="13">
         <v>649.0</v>
@@ -12358,10 +12349,10 @@
         <v>74.0</v>
       </c>
       <c r="X212" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y212" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Z212" s="13">
         <v>636.0</v>
@@ -12398,10 +12389,10 @@
         <v>75.0</v>
       </c>
       <c r="X213" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Y213" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z213" s="13">
         <v>528.0</v>
@@ -12438,10 +12429,10 @@
         <v>76.0</v>
       </c>
       <c r="X214" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Y214" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Z214" s="13">
         <v>473.0</v>
@@ -12478,10 +12469,10 @@
         <v>78.0</v>
       </c>
       <c r="X215" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y215" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z215" s="13">
         <v>435.0</v>
@@ -12518,10 +12509,10 @@
         <v>79.0</v>
       </c>
       <c r="X216" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y216" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Z216" s="7"/>
       <c r="AA216" s="7"/>
@@ -12556,10 +12547,10 @@
         <v>80.0</v>
       </c>
       <c r="X217" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y217" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Z217" s="7"/>
       <c r="AA217" s="7"/>
@@ -37667,34 +37658,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="G1" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="H1" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="I1" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>137</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="2">
@@ -37702,7 +37693,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" s="17">
         <v>134.5</v>
@@ -37718,7 +37709,7 @@
       </c>
       <c r="G2" s="17">
         <f t="shared" ref="G2:G73" si="2">IF($D2&gt;0,"",MIN($L$8, $C2*$L$14*(1+($L$11-1)*$L$16)))</f>
-        <v>229.4294025</v>
+        <v>182.6855206</v>
       </c>
       <c r="H2" s="20">
         <f t="shared" ref="H2:H73" si="3">IF($D2&lt;&gt;"","",
@@ -37746,7 +37737,7 @@
         <v/>
       </c>
       <c r="K2" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L2" s="9">
         <v>1200.0</v>
@@ -37757,7 +37748,7 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C3" s="17">
         <v>101.5</v>
@@ -37772,7 +37763,7 @@
       </c>
       <c r="G3" s="17">
         <f t="shared" si="2"/>
-        <v>173.1381736</v>
+        <v>137.8630508</v>
       </c>
       <c r="H3" s="20">
         <f t="shared" si="3"/>
@@ -37788,7 +37779,7 @@
         <v/>
       </c>
       <c r="K3" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L3" s="9">
         <v>12.0</v>
@@ -37799,7 +37790,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4" s="17">
         <v>90.0</v>
@@ -37814,7 +37805,7 @@
       </c>
       <c r="G4" s="17">
         <f t="shared" si="2"/>
-        <v>153.5215333</v>
+        <v>122.2430993</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" si="3"/>
@@ -37825,11 +37816,11 @@
         <v/>
       </c>
       <c r="K4" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L4" s="19">
         <f>'Draft Data'!U63</f>
-        <v>534.75</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5">
@@ -37837,7 +37828,7 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="17">
         <v>83.0</v>
@@ -37851,7 +37842,7 @@
       </c>
       <c r="G5" s="17">
         <f t="shared" si="2"/>
-        <v>141.5809696</v>
+        <v>112.7353027</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="3"/>
@@ -37862,7 +37853,7 @@
         <v/>
       </c>
       <c r="K5" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L5" s="22">
         <f>SUM($D$2:$D$500)
@@ -37875,7 +37866,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6" s="17">
         <v>72.5</v>
@@ -37889,7 +37880,7 @@
       </c>
       <c r="G6" s="17">
         <f t="shared" si="2"/>
-        <v>123.670124</v>
+        <v>98.47360775</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="3"/>
@@ -37900,7 +37891,7 @@
         <v/>
       </c>
       <c r="K6" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L6" s="22">
         <f>L2-L5
@@ -37913,7 +37904,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="17">
         <v>65.5</v>
@@ -37927,7 +37918,7 @@
       </c>
       <c r="G7" s="17">
         <f t="shared" si="2"/>
-        <v>111.7295603</v>
+        <v>88.96581114</v>
       </c>
       <c r="H7" s="20">
         <f t="shared" si="3"/>
@@ -37938,7 +37929,7 @@
         <v/>
       </c>
       <c r="K7" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L7" s="22">
         <f>SUMIF($E$2:$E$500,TRUE,$D$2:$D$500)</f>
@@ -37950,7 +37941,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" s="17">
         <v>60.5</v>
@@ -37964,7 +37955,7 @@
       </c>
       <c r="G8" s="17">
         <f t="shared" si="2"/>
-        <v>103.2005862</v>
+        <v>82.17452785</v>
       </c>
       <c r="H8" s="20">
         <f t="shared" si="3"/>
@@ -37975,12 +37966,12 @@
         <v/>
       </c>
       <c r="K8" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L8" s="17">
         <f>L4-L7
 </f>
-        <v>534.75</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -37988,7 +37979,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" s="17">
         <v>55.0</v>
@@ -38002,7 +37993,7 @@
       </c>
       <c r="G9" s="17">
         <f t="shared" si="2"/>
-        <v>93.81871477</v>
+        <v>74.70411622</v>
       </c>
       <c r="H9" s="20">
         <f t="shared" si="3"/>
@@ -38013,12 +38004,12 @@
         <v/>
       </c>
       <c r="K9" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L9" s="17">
         <f>L6-L8
 </f>
-        <v>665.25</v>
+        <v>826</v>
       </c>
     </row>
     <row r="10">
@@ -38026,7 +38017,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C10" s="17">
         <v>50.5</v>
@@ -38040,7 +38031,7 @@
       </c>
       <c r="G10" s="17">
         <f t="shared" si="2"/>
-        <v>86.14263811</v>
+        <v>68.59196126</v>
       </c>
       <c r="H10" s="20">
         <f t="shared" si="3"/>
@@ -38051,11 +38042,11 @@
         <v/>
       </c>
       <c r="K10" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L10" s="17">
         <f>IF(L3&gt;1,L9/(L3-1),0)</f>
-        <v>60.47727273</v>
+        <v>75.09090909</v>
       </c>
     </row>
     <row r="11">
@@ -38063,7 +38054,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C11" s="17">
         <v>45.0</v>
@@ -38077,7 +38068,7 @@
       </c>
       <c r="G11" s="17">
         <f t="shared" si="2"/>
-        <v>76.76076663</v>
+        <v>61.12154964</v>
       </c>
       <c r="H11" s="20">
         <f t="shared" si="3"/>
@@ -38088,11 +38079,11 @@
         <v/>
       </c>
       <c r="K11" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L11" s="23">
         <f>IF(L10&gt;0,L8/L10,1)</f>
-        <v>8.8421646</v>
+        <v>4.98062954</v>
       </c>
     </row>
     <row r="12">
@@ -38100,7 +38091,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C12" s="17">
         <v>40.5</v>
@@ -38114,7 +38105,7 @@
       </c>
       <c r="G12" s="17">
         <f t="shared" si="2"/>
-        <v>69.08468997</v>
+        <v>55.00939467</v>
       </c>
       <c r="H12" s="20">
         <f t="shared" si="3"/>
@@ -38130,7 +38121,7 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C13" s="17">
         <v>36.0</v>
@@ -38144,7 +38135,7 @@
       </c>
       <c r="G13" s="17">
         <f t="shared" si="2"/>
-        <v>61.4086133</v>
+        <v>48.89723971</v>
       </c>
       <c r="H13" s="20">
         <f t="shared" si="3"/>
@@ -38155,7 +38146,7 @@
         <v/>
       </c>
       <c r="K13" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L13" s="22">
         <f>SUMIF($D$2:$D$73,"",$C$2:$C$73)</f>
@@ -38167,7 +38158,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C14" s="17">
         <v>32.0</v>
@@ -38181,7 +38172,7 @@
       </c>
       <c r="G14" s="17">
         <f t="shared" si="2"/>
-        <v>54.58543405</v>
+        <v>43.46421308</v>
       </c>
       <c r="H14" s="20">
         <f t="shared" si="3"/>
@@ -38192,7 +38183,7 @@
         <v/>
       </c>
       <c r="K14" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L14" s="23">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -38204,7 +38195,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C15" s="17">
         <v>29.0</v>
@@ -38218,7 +38209,7 @@
       </c>
       <c r="G15" s="17">
         <f t="shared" si="2"/>
-        <v>49.46804961</v>
+        <v>39.3894431</v>
       </c>
       <c r="H15" s="20">
         <f t="shared" si="3"/>
@@ -38234,7 +38225,7 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C16" s="17">
         <v>26.0</v>
@@ -38248,7 +38239,7 @@
       </c>
       <c r="G16" s="17">
         <f t="shared" si="2"/>
-        <v>44.35066516</v>
+        <v>35.31467312</v>
       </c>
       <c r="H16" s="20">
         <f t="shared" si="3"/>
@@ -38259,7 +38250,7 @@
         <v/>
       </c>
       <c r="K16" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L16" s="9">
         <f>IF($L$18&lt;0.3,
@@ -38281,7 +38272,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C17" s="17">
         <v>23.5</v>
@@ -38295,7 +38286,7 @@
       </c>
       <c r="G17" s="17">
         <f t="shared" si="2"/>
-        <v>40.08617813</v>
+        <v>31.91903148</v>
       </c>
       <c r="H17" s="20">
         <f t="shared" si="3"/>
@@ -38311,7 +38302,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C18" s="17">
         <v>21.0</v>
@@ -38325,7 +38316,7 @@
       </c>
       <c r="G18" s="17">
         <f t="shared" si="2"/>
-        <v>35.82169109</v>
+        <v>28.52338983</v>
       </c>
       <c r="H18" s="20">
         <f t="shared" si="3"/>
@@ -38336,7 +38327,7 @@
         <v/>
       </c>
       <c r="K18" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L18" s="24">
         <f>L5/L2</f>
@@ -38348,7 +38339,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C19" s="17">
         <v>18.5</v>
@@ -38362,7 +38353,7 @@
       </c>
       <c r="G19" s="17">
         <f t="shared" si="2"/>
-        <v>31.55720406</v>
+        <v>25.12774818</v>
       </c>
       <c r="H19" s="20">
         <f t="shared" si="3"/>
@@ -38378,7 +38369,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C20" s="17">
         <v>16.5</v>
@@ -38392,7 +38383,7 @@
       </c>
       <c r="G20" s="17">
         <f t="shared" si="2"/>
-        <v>28.14561443</v>
+        <v>22.41123487</v>
       </c>
       <c r="H20" s="20">
         <f t="shared" si="3"/>
@@ -38408,7 +38399,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C21" s="17">
         <v>15.0</v>
@@ -38422,7 +38413,7 @@
       </c>
       <c r="G21" s="17">
         <f t="shared" si="2"/>
-        <v>25.58692221</v>
+        <v>20.37384988</v>
       </c>
       <c r="H21" s="20">
         <f t="shared" si="3"/>
@@ -38438,7 +38429,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C22" s="17">
         <v>14.0</v>
@@ -38452,7 +38443,7 @@
       </c>
       <c r="G22" s="17">
         <f t="shared" si="2"/>
-        <v>23.8811274</v>
+        <v>19.01559322</v>
       </c>
       <c r="H22" s="20">
         <f t="shared" si="3"/>
@@ -38468,7 +38459,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C23" s="17">
         <v>12.5</v>
@@ -38482,7 +38473,7 @@
       </c>
       <c r="G23" s="17">
         <f t="shared" si="2"/>
-        <v>21.32243517</v>
+        <v>16.97820823</v>
       </c>
       <c r="H23" s="20">
         <f t="shared" si="3"/>
@@ -38498,7 +38489,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C24" s="17">
         <v>10.5</v>
@@ -38512,7 +38503,7 @@
       </c>
       <c r="G24" s="17">
         <f t="shared" si="2"/>
-        <v>17.91084555</v>
+        <v>14.26169492</v>
       </c>
       <c r="H24" s="20">
         <f t="shared" si="3"/>
@@ -38528,7 +38519,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C25" s="17">
         <v>10.0</v>
@@ -38542,7 +38533,7 @@
       </c>
       <c r="G25" s="17">
         <f t="shared" si="2"/>
-        <v>17.05794814</v>
+        <v>13.58256659</v>
       </c>
       <c r="H25" s="20">
         <f t="shared" si="3"/>
@@ -38558,7 +38549,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C26" s="17">
         <v>9.0</v>
@@ -38572,7 +38563,7 @@
       </c>
       <c r="G26" s="17">
         <f t="shared" si="2"/>
-        <v>15.35215333</v>
+        <v>12.22430993</v>
       </c>
       <c r="H26" s="20">
         <f t="shared" si="3"/>
@@ -38588,7 +38579,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C27" s="17">
         <v>8.5</v>
@@ -38602,7 +38593,7 @@
       </c>
       <c r="G27" s="17">
         <f t="shared" si="2"/>
-        <v>14.49925592</v>
+        <v>11.5451816</v>
       </c>
       <c r="H27" s="20">
         <f t="shared" si="3"/>
@@ -38613,7 +38604,7 @@
         <v/>
       </c>
       <c r="K27" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L27" s="9">
         <v>0.8</v>
@@ -38624,7 +38615,7 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C28" s="17">
         <v>7.5</v>
@@ -38638,7 +38629,7 @@
       </c>
       <c r="G28" s="17">
         <f t="shared" si="2"/>
-        <v>12.7934611</v>
+        <v>10.18692494</v>
       </c>
       <c r="H28" s="20">
         <f t="shared" si="3"/>
@@ -38654,7 +38645,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C29" s="17">
         <v>7.0</v>
@@ -38668,7 +38659,7 @@
       </c>
       <c r="G29" s="17">
         <f t="shared" si="2"/>
-        <v>11.9405637</v>
+        <v>9.50779661</v>
       </c>
       <c r="H29" s="20">
         <f t="shared" si="3"/>
@@ -38684,7 +38675,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C30" s="17">
         <v>6.5</v>
@@ -38698,7 +38689,7 @@
       </c>
       <c r="G30" s="17">
         <f t="shared" si="2"/>
-        <v>11.08766629</v>
+        <v>8.828668281</v>
       </c>
       <c r="H30" s="20">
         <f t="shared" si="3"/>
@@ -38714,7 +38705,7 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C31" s="17">
         <v>6.0</v>
@@ -38728,7 +38719,7 @@
       </c>
       <c r="G31" s="17">
         <f t="shared" si="2"/>
-        <v>10.23476888</v>
+        <v>8.149539952</v>
       </c>
       <c r="H31" s="20">
         <f t="shared" si="3"/>
@@ -38744,7 +38735,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C32" s="17">
         <v>5.0</v>
@@ -38758,7 +38749,7 @@
       </c>
       <c r="G32" s="17">
         <f t="shared" si="2"/>
-        <v>8.52897407</v>
+        <v>6.791283293</v>
       </c>
       <c r="H32" s="20">
         <f t="shared" si="3"/>
@@ -38774,7 +38765,7 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C33" s="17">
         <v>5.0</v>
@@ -38788,7 +38779,7 @@
       </c>
       <c r="G33" s="17">
         <f t="shared" si="2"/>
-        <v>8.52897407</v>
+        <v>6.791283293</v>
       </c>
       <c r="H33" s="20">
         <f t="shared" si="3"/>
@@ -38804,7 +38795,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C34" s="17">
         <v>4.5</v>
@@ -38818,7 +38809,7 @@
       </c>
       <c r="G34" s="17">
         <f t="shared" si="2"/>
-        <v>7.676076663</v>
+        <v>6.112154964</v>
       </c>
       <c r="H34" s="20">
         <f t="shared" si="3"/>
@@ -38834,7 +38825,7 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C35" s="17">
         <v>4.0</v>
@@ -38848,7 +38839,7 @@
       </c>
       <c r="G35" s="17">
         <f t="shared" si="2"/>
-        <v>6.823179256</v>
+        <v>5.433026634</v>
       </c>
       <c r="H35" s="20">
         <f t="shared" si="3"/>
@@ -38864,7 +38855,7 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C36" s="17">
         <v>4.0</v>
@@ -38878,7 +38869,7 @@
       </c>
       <c r="G36" s="17">
         <f t="shared" si="2"/>
-        <v>6.823179256</v>
+        <v>5.433026634</v>
       </c>
       <c r="H36" s="20">
         <f t="shared" si="3"/>
@@ -38894,7 +38885,7 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C37" s="17">
         <v>3.5</v>
@@ -38908,7 +38899,7 @@
       </c>
       <c r="G37" s="17">
         <f t="shared" si="2"/>
-        <v>5.970281849</v>
+        <v>4.753898305</v>
       </c>
       <c r="H37" s="20">
         <f t="shared" si="3"/>
@@ -38924,7 +38915,7 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C38" s="17">
         <v>3.5</v>
@@ -38938,7 +38929,7 @@
       </c>
       <c r="G38" s="17">
         <f t="shared" si="2"/>
-        <v>5.970281849</v>
+        <v>4.753898305</v>
       </c>
       <c r="H38" s="20">
         <f t="shared" si="3"/>
@@ -38954,7 +38945,7 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C39" s="17">
         <v>3.0</v>
@@ -38968,7 +38959,7 @@
       </c>
       <c r="G39" s="17">
         <f t="shared" si="2"/>
-        <v>5.117384442</v>
+        <v>4.074769976</v>
       </c>
       <c r="H39" s="20">
         <f t="shared" si="3"/>
@@ -38984,7 +38975,7 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C40" s="17">
         <v>3.0</v>
@@ -38998,7 +38989,7 @@
       </c>
       <c r="G40" s="17">
         <f t="shared" si="2"/>
-        <v>5.117384442</v>
+        <v>4.074769976</v>
       </c>
       <c r="H40" s="20">
         <f t="shared" si="3"/>
@@ -39014,7 +39005,7 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C41" s="17">
         <v>3.0</v>
@@ -39028,7 +39019,7 @@
       </c>
       <c r="G41" s="17">
         <f t="shared" si="2"/>
-        <v>5.117384442</v>
+        <v>4.074769976</v>
       </c>
       <c r="H41" s="20">
         <f t="shared" si="3"/>
@@ -39044,7 +39035,7 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C42" s="17">
         <v>2.5</v>
@@ -39058,7 +39049,7 @@
       </c>
       <c r="G42" s="17">
         <f t="shared" si="2"/>
-        <v>4.264487035</v>
+        <v>3.395641646</v>
       </c>
       <c r="H42" s="20">
         <f t="shared" si="3"/>
@@ -39074,7 +39065,7 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C43" s="17">
         <v>2.5</v>
@@ -39088,7 +39079,7 @@
       </c>
       <c r="G43" s="17">
         <f t="shared" si="2"/>
-        <v>4.264487035</v>
+        <v>3.395641646</v>
       </c>
       <c r="H43" s="20">
         <f t="shared" si="3"/>
@@ -39104,7 +39095,7 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C44" s="17">
         <v>2.5</v>
@@ -39118,7 +39109,7 @@
       </c>
       <c r="G44" s="17">
         <f t="shared" si="2"/>
-        <v>4.264487035</v>
+        <v>3.395641646</v>
       </c>
       <c r="H44" s="20">
         <f t="shared" si="3"/>
@@ -39134,7 +39125,7 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C45" s="17">
         <v>2.5</v>
@@ -39148,7 +39139,7 @@
       </c>
       <c r="G45" s="17">
         <f t="shared" si="2"/>
-        <v>4.264487035</v>
+        <v>3.395641646</v>
       </c>
       <c r="H45" s="20">
         <f t="shared" si="3"/>
@@ -39164,7 +39155,7 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C46" s="17">
         <v>2.0</v>
@@ -39178,7 +39169,7 @@
       </c>
       <c r="G46" s="17">
         <f t="shared" si="2"/>
-        <v>3.411589628</v>
+        <v>2.716513317</v>
       </c>
       <c r="H46" s="20">
         <f t="shared" si="3"/>
@@ -39194,7 +39185,7 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C47" s="17">
         <v>2.0</v>
@@ -39208,7 +39199,7 @@
       </c>
       <c r="G47" s="17">
         <f t="shared" si="2"/>
-        <v>3.411589628</v>
+        <v>2.716513317</v>
       </c>
       <c r="H47" s="20">
         <f t="shared" si="3"/>
@@ -39224,7 +39215,7 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C48" s="17">
         <v>2.0</v>
@@ -39238,7 +39229,7 @@
       </c>
       <c r="G48" s="17">
         <f t="shared" si="2"/>
-        <v>3.411589628</v>
+        <v>2.716513317</v>
       </c>
       <c r="H48" s="20">
         <f t="shared" si="3"/>
@@ -39254,7 +39245,7 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C49" s="17">
         <v>2.0</v>
@@ -39268,7 +39259,7 @@
       </c>
       <c r="G49" s="17">
         <f t="shared" si="2"/>
-        <v>3.411589628</v>
+        <v>2.716513317</v>
       </c>
       <c r="H49" s="20">
         <f t="shared" si="3"/>
@@ -39284,7 +39275,7 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C50" s="17">
         <v>2.0</v>
@@ -39298,7 +39289,7 @@
       </c>
       <c r="G50" s="17">
         <f t="shared" si="2"/>
-        <v>3.411589628</v>
+        <v>2.716513317</v>
       </c>
       <c r="H50" s="20">
         <f t="shared" si="3"/>
@@ -39314,7 +39305,7 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C51" s="17">
         <v>2.0</v>
@@ -39328,7 +39319,7 @@
       </c>
       <c r="G51" s="17">
         <f t="shared" si="2"/>
-        <v>3.411589628</v>
+        <v>2.716513317</v>
       </c>
       <c r="H51" s="20">
         <f t="shared" si="3"/>
@@ -39344,7 +39335,7 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C52" s="17">
         <v>2.0</v>
@@ -39358,7 +39349,7 @@
       </c>
       <c r="G52" s="17">
         <f t="shared" si="2"/>
-        <v>3.411589628</v>
+        <v>2.716513317</v>
       </c>
       <c r="H52" s="20">
         <f t="shared" si="3"/>
@@ -39374,7 +39365,7 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C53" s="17">
         <v>2.0</v>
@@ -39388,7 +39379,7 @@
       </c>
       <c r="G53" s="17">
         <f t="shared" si="2"/>
-        <v>3.411589628</v>
+        <v>2.716513317</v>
       </c>
       <c r="H53" s="20">
         <f t="shared" si="3"/>
@@ -39404,7 +39395,7 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C54" s="17">
         <v>2.0</v>
@@ -39418,7 +39409,7 @@
       </c>
       <c r="G54" s="17">
         <f t="shared" si="2"/>
-        <v>3.411589628</v>
+        <v>2.716513317</v>
       </c>
       <c r="H54" s="20">
         <f t="shared" si="3"/>
@@ -39434,7 +39425,7 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C55" s="17">
         <v>2.0</v>
@@ -39448,7 +39439,7 @@
       </c>
       <c r="G55" s="17">
         <f t="shared" si="2"/>
-        <v>3.411589628</v>
+        <v>2.716513317</v>
       </c>
       <c r="H55" s="20">
         <f t="shared" si="3"/>
@@ -39464,7 +39455,7 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C56" s="17">
         <v>2.0</v>
@@ -39478,7 +39469,7 @@
       </c>
       <c r="G56" s="17">
         <f t="shared" si="2"/>
-        <v>3.411589628</v>
+        <v>2.716513317</v>
       </c>
       <c r="H56" s="20">
         <f t="shared" si="3"/>
@@ -39494,7 +39485,7 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C57" s="17">
         <v>2.0</v>
@@ -39508,7 +39499,7 @@
       </c>
       <c r="G57" s="17">
         <f t="shared" si="2"/>
-        <v>3.411589628</v>
+        <v>2.716513317</v>
       </c>
       <c r="H57" s="20">
         <f t="shared" si="3"/>
@@ -39524,7 +39515,7 @@
         <v>57.0</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C58" s="17">
         <v>2.0</v>
@@ -39538,7 +39529,7 @@
       </c>
       <c r="G58" s="17">
         <f t="shared" si="2"/>
-        <v>3.411589628</v>
+        <v>2.716513317</v>
       </c>
       <c r="H58" s="20">
         <f t="shared" si="3"/>
@@ -39554,7 +39545,7 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C59" s="17">
         <v>2.0</v>
@@ -39568,7 +39559,7 @@
       </c>
       <c r="G59" s="17">
         <f t="shared" si="2"/>
-        <v>3.411589628</v>
+        <v>2.716513317</v>
       </c>
       <c r="H59" s="20">
         <f t="shared" si="3"/>
@@ -39584,7 +39575,7 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C60" s="17">
         <v>2.0</v>
@@ -39598,7 +39589,7 @@
       </c>
       <c r="G60" s="17">
         <f t="shared" si="2"/>
-        <v>3.411589628</v>
+        <v>2.716513317</v>
       </c>
       <c r="H60" s="20">
         <f t="shared" si="3"/>
@@ -39614,7 +39605,7 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C61" s="17">
         <v>2.0</v>
@@ -39628,7 +39619,7 @@
       </c>
       <c r="G61" s="17">
         <f t="shared" si="2"/>
-        <v>3.411589628</v>
+        <v>2.716513317</v>
       </c>
       <c r="H61" s="20">
         <f t="shared" si="3"/>
@@ -39644,7 +39635,7 @@
         <v>61.0</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C62" s="17">
         <v>1.0</v>
@@ -39658,7 +39649,7 @@
       </c>
       <c r="G62" s="17">
         <f t="shared" si="2"/>
-        <v>1.705794814</v>
+        <v>1.358256659</v>
       </c>
       <c r="H62" s="20">
         <f t="shared" si="3"/>
@@ -39674,7 +39665,7 @@
         <v>62.0</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C63" s="17">
         <v>1.0</v>
@@ -39688,7 +39679,7 @@
       </c>
       <c r="G63" s="17">
         <f t="shared" si="2"/>
-        <v>1.705794814</v>
+        <v>1.358256659</v>
       </c>
       <c r="H63" s="20">
         <f t="shared" si="3"/>
@@ -39704,7 +39695,7 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C64" s="17">
         <v>1.0</v>
@@ -39718,7 +39709,7 @@
       </c>
       <c r="G64" s="17">
         <f t="shared" si="2"/>
-        <v>1.705794814</v>
+        <v>1.358256659</v>
       </c>
       <c r="H64" s="20">
         <f t="shared" si="3"/>
@@ -39734,7 +39725,7 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C65" s="17">
         <v>1.0</v>
@@ -39748,7 +39739,7 @@
       </c>
       <c r="G65" s="17">
         <f t="shared" si="2"/>
-        <v>1.705794814</v>
+        <v>1.358256659</v>
       </c>
       <c r="H65" s="20">
         <f t="shared" si="3"/>
@@ -39764,7 +39755,7 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C66" s="17">
         <v>1.0</v>
@@ -39778,7 +39769,7 @@
       </c>
       <c r="G66" s="17">
         <f t="shared" si="2"/>
-        <v>1.705794814</v>
+        <v>1.358256659</v>
       </c>
       <c r="H66" s="20">
         <f t="shared" si="3"/>
@@ -39794,7 +39785,7 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C67" s="17">
         <v>1.0</v>
@@ -39808,7 +39799,7 @@
       </c>
       <c r="G67" s="17">
         <f t="shared" si="2"/>
-        <v>1.705794814</v>
+        <v>1.358256659</v>
       </c>
       <c r="H67" s="20">
         <f t="shared" si="3"/>
@@ -39824,7 +39815,7 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C68" s="17">
         <v>1.0</v>
@@ -39838,7 +39829,7 @@
       </c>
       <c r="G68" s="17">
         <f t="shared" si="2"/>
-        <v>1.705794814</v>
+        <v>1.358256659</v>
       </c>
       <c r="H68" s="20">
         <f t="shared" si="3"/>
@@ -39854,7 +39845,7 @@
         <v>68.0</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C69" s="17">
         <v>1.0</v>
@@ -39868,7 +39859,7 @@
       </c>
       <c r="G69" s="17">
         <f t="shared" si="2"/>
-        <v>1.705794814</v>
+        <v>1.358256659</v>
       </c>
       <c r="H69" s="20">
         <f t="shared" si="3"/>
@@ -39884,7 +39875,7 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C70" s="17">
         <v>1.0</v>
@@ -39898,7 +39889,7 @@
       </c>
       <c r="G70" s="17">
         <f t="shared" si="2"/>
-        <v>1.705794814</v>
+        <v>1.358256659</v>
       </c>
       <c r="H70" s="20">
         <f t="shared" si="3"/>
@@ -39914,7 +39905,7 @@
         <v>70.0</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C71" s="17">
         <v>1.0</v>
@@ -39928,7 +39919,7 @@
       </c>
       <c r="G71" s="17">
         <f t="shared" si="2"/>
-        <v>1.705794814</v>
+        <v>1.358256659</v>
       </c>
       <c r="H71" s="20">
         <f t="shared" si="3"/>
@@ -39944,7 +39935,7 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C72" s="17">
         <v>1.0</v>
@@ -39958,7 +39949,7 @@
       </c>
       <c r="G72" s="17">
         <f t="shared" si="2"/>
-        <v>1.705794814</v>
+        <v>1.358256659</v>
       </c>
       <c r="H72" s="20">
         <f t="shared" si="3"/>
@@ -39974,7 +39965,7 @@
         <v>72.0</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C73" s="17">
         <v>1.0</v>
@@ -39988,7 +39979,7 @@
       </c>
       <c r="G73" s="17">
         <f t="shared" si="2"/>
-        <v>1.705794814</v>
+        <v>1.358256659</v>
       </c>
       <c r="H73" s="20">
         <f t="shared" si="3"/>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="178">
   <si>
     <t>PICK</t>
   </si>
@@ -458,16 +458,16 @@
     <t>Budget Advantage Factor</t>
   </si>
   <si>
-    <t>Undrafted Predraft$</t>
+    <t>Omar Cooper</t>
   </si>
   <si>
     <t>CJ Allen</t>
   </si>
   <si>
-    <t>Inflation Factor</t>
+    <t>Undrafted Predraft$</t>
   </si>
   <si>
-    <t>Omar Cooper</t>
+    <t>Inflation Factor</t>
   </si>
   <si>
     <t>Aggression</t>
@@ -482,52 +482,70 @@
     <t>Mike Washington</t>
   </si>
   <si>
+    <t>Enforce % of Fair</t>
+  </si>
+  <si>
     <t>Chris Brazzell</t>
   </si>
   <si>
-    <t>Enforce % of Fair</t>
+    <t>De'Zhaun Stribling</t>
   </si>
   <si>
     <t>Anthony Hill</t>
   </si>
   <si>
+    <t>A.J. Haulcy</t>
+  </si>
+  <si>
+    <t>Dani Dennis-Sutton</t>
+  </si>
+  <si>
+    <t>R Mason Thomas</t>
+  </si>
+  <si>
+    <t>Malachi Lawrence</t>
+  </si>
+  <si>
+    <t>CJ Donaldson</t>
+  </si>
+  <si>
     <t>Cashius Howell</t>
   </si>
   <si>
-    <t>Vinny Anthony</t>
+    <t>Keldric Faulk</t>
   </si>
   <si>
     <t>Akheem Mesidor</t>
   </si>
   <si>
+    <t>DJ Rogers</t>
+  </si>
+  <si>
+    <t>Lake McRee</t>
+  </si>
+  <si>
     <t>Sam Roush</t>
   </si>
   <si>
-    <t>A.J. Haulcy</t>
+    <t>Tanner Koziol</t>
   </si>
   <si>
-    <t>Keldric Faulk</t>
+    <t>Matthew Hibner</t>
   </si>
   <si>
-    <t>Peter Woods</t>
+    <t>Tyren Montgomery</t>
   </si>
   <si>
     <t>Kevin Coleman</t>
   </si>
   <si>
-    <t>Tanner Koziol</t>
+    <t>Nate Boerkircher</t>
   </si>
   <si>
-    <t>John Michael Gyllenborg</t>
+    <t>Will Kacmarek</t>
   </si>
   <si>
-    <t>De'Zhaun Stribling</t>
-  </si>
-  <si>
-    <t>Jeff Caldwell</t>
-  </si>
-  <si>
-    <t>CJ Daniels</t>
+    <t>Noah Whittington</t>
   </si>
 </sst>
 </file>
@@ -37696,7 +37714,7 @@
         <v>44</v>
       </c>
       <c r="C2" s="17">
-        <v>134.5</v>
+        <v>139.0</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="b">
@@ -37705,11 +37723,11 @@
       <c r="F2" s="17">
         <f t="shared" ref="F2:F73" si="1">IF($D2&gt;0,"",$C2*$L$14)
 </f>
-        <v>134.5</v>
+        <v>139</v>
       </c>
       <c r="G2" s="17">
         <f t="shared" ref="G2:G73" si="2">IF($D2&gt;0,"",MIN($L$8, $C2*$L$14*(1+($L$11-1)*$L$16)))</f>
-        <v>182.6855206</v>
+        <v>188.7976755</v>
       </c>
       <c r="H2" s="20">
         <f t="shared" ref="H2:H73" si="3">IF($D2&lt;&gt;"","",
@@ -37719,7 +37737,7 @@
    )
 )
 </f>
-        <v>107.6</v>
+        <v>111.2</v>
       </c>
       <c r="I2" s="21" t="str">
         <f>IF($D2="","",
@@ -37748,10 +37766,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C3" s="17">
-        <v>101.5</v>
+        <v>106.5</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9" t="b">
@@ -37759,15 +37777,15 @@
       </c>
       <c r="F3" s="17">
         <f t="shared" si="1"/>
-        <v>101.5</v>
+        <v>106.5</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" si="2"/>
-        <v>137.8630508</v>
+        <v>144.6543341</v>
       </c>
       <c r="H3" s="20">
         <f t="shared" si="3"/>
-        <v>81.2</v>
+        <v>85.2</v>
       </c>
       <c r="I3" s="21" t="str">
         <f t="shared" ref="I3:I73" si="4">IF($D3="","",
@@ -37790,10 +37808,10 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C4" s="17">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9" t="b">
@@ -37801,15 +37819,15 @@
       </c>
       <c r="F4" s="17">
         <f t="shared" si="1"/>
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" si="2"/>
-        <v>122.2430993</v>
+        <v>126.3178692</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" si="3"/>
-        <v>72</v>
+        <v>74.4</v>
       </c>
       <c r="I4" s="21" t="str">
         <f t="shared" si="4"/>
@@ -37828,25 +37846,25 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C5" s="17">
-        <v>83.0</v>
+        <v>82.5</v>
       </c>
       <c r="E5" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F5" s="17">
         <f t="shared" si="1"/>
-        <v>83</v>
+        <v>82.5</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" si="2"/>
-        <v>112.7353027</v>
+        <v>112.0561743</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="3"/>
-        <v>66.4</v>
+        <v>66</v>
       </c>
       <c r="I5" s="21" t="str">
         <f t="shared" si="4"/>
@@ -37866,25 +37884,25 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="17">
-        <v>72.5</v>
+        <v>76.0</v>
       </c>
       <c r="E6" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F6" s="17">
         <f t="shared" si="1"/>
-        <v>72.5</v>
+        <v>76</v>
       </c>
       <c r="G6" s="17">
         <f t="shared" si="2"/>
-        <v>98.47360775</v>
+        <v>103.2275061</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="3"/>
-        <v>58</v>
+        <v>60.8</v>
       </c>
       <c r="I6" s="21" t="str">
         <f t="shared" si="4"/>
@@ -37904,25 +37922,25 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C7" s="17">
-        <v>65.5</v>
+        <v>66.5</v>
       </c>
       <c r="E7" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F7" s="17">
         <f t="shared" si="1"/>
-        <v>65.5</v>
+        <v>66.5</v>
       </c>
       <c r="G7" s="17">
         <f t="shared" si="2"/>
-        <v>88.96581114</v>
+        <v>90.3240678</v>
       </c>
       <c r="H7" s="20">
         <f t="shared" si="3"/>
-        <v>52.4</v>
+        <v>53.2</v>
       </c>
       <c r="I7" s="21" t="str">
         <f t="shared" si="4"/>
@@ -37941,25 +37959,25 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C8" s="17">
-        <v>60.5</v>
+        <v>57.5</v>
       </c>
       <c r="E8" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F8" s="17">
         <f t="shared" si="1"/>
-        <v>60.5</v>
+        <v>57.5</v>
       </c>
       <c r="G8" s="17">
         <f t="shared" si="2"/>
-        <v>82.17452785</v>
+        <v>78.09975787</v>
       </c>
       <c r="H8" s="20">
         <f t="shared" si="3"/>
-        <v>48.4</v>
+        <v>46</v>
       </c>
       <c r="I8" s="21" t="str">
         <f t="shared" si="4"/>
@@ -37979,25 +37997,25 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C9" s="17">
-        <v>55.0</v>
+        <v>53.0</v>
       </c>
       <c r="E9" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F9" s="17">
         <f t="shared" si="1"/>
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G9" s="17">
         <f t="shared" si="2"/>
-        <v>74.70411622</v>
+        <v>71.98760291</v>
       </c>
       <c r="H9" s="20">
         <f t="shared" si="3"/>
-        <v>44</v>
+        <v>42.4</v>
       </c>
       <c r="I9" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38017,25 +38035,25 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C10" s="17">
-        <v>50.5</v>
+        <v>48.0</v>
       </c>
       <c r="E10" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F10" s="17">
         <f t="shared" si="1"/>
-        <v>50.5</v>
+        <v>48</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" si="2"/>
-        <v>68.59196126</v>
+        <v>65.19631961</v>
       </c>
       <c r="H10" s="20">
         <f t="shared" si="3"/>
-        <v>40.4</v>
+        <v>38.4</v>
       </c>
       <c r="I10" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38054,25 +38072,25 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C11" s="17">
-        <v>45.0</v>
+        <v>43.0</v>
       </c>
       <c r="E11" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F11" s="17">
         <f t="shared" si="1"/>
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G11" s="17">
         <f t="shared" si="2"/>
-        <v>61.12154964</v>
+        <v>58.40503632</v>
       </c>
       <c r="H11" s="20">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>34.4</v>
       </c>
       <c r="I11" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38091,25 +38109,25 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="C12" s="17">
-        <v>40.5</v>
+        <v>39.0</v>
       </c>
       <c r="E12" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F12" s="17">
         <f t="shared" si="1"/>
-        <v>40.5</v>
+        <v>39</v>
       </c>
       <c r="G12" s="17">
         <f t="shared" si="2"/>
-        <v>55.00939467</v>
+        <v>52.97200969</v>
       </c>
       <c r="H12" s="20">
         <f t="shared" si="3"/>
-        <v>32.4</v>
+        <v>31.2</v>
       </c>
       <c r="I12" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38121,32 +38139,32 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="C13" s="17">
-        <v>36.0</v>
+        <v>34.0</v>
       </c>
       <c r="E13" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F13" s="17">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G13" s="17">
         <f t="shared" si="2"/>
-        <v>48.89723971</v>
+        <v>46.18072639</v>
       </c>
       <c r="H13" s="20">
         <f t="shared" si="3"/>
-        <v>28.8</v>
+        <v>27.2</v>
       </c>
       <c r="I13" s="21" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K13" s="9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="L13" s="22">
         <f>SUMIF($D$2:$D$73,"",$C$2:$C$73)</f>
@@ -38158,32 +38176,32 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>149</v>
+        <v>59</v>
       </c>
       <c r="C14" s="17">
-        <v>32.0</v>
+        <v>30.5</v>
       </c>
       <c r="E14" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F14" s="17">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>30.5</v>
       </c>
       <c r="G14" s="17">
         <f t="shared" si="2"/>
-        <v>43.46421308</v>
+        <v>41.42682809</v>
       </c>
       <c r="H14" s="20">
         <f t="shared" si="3"/>
-        <v>25.6</v>
+        <v>24.4</v>
       </c>
       <c r="I14" s="21" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K14" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L14" s="23">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -38195,25 +38213,25 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C15" s="17">
-        <v>29.0</v>
+        <v>27.5</v>
       </c>
       <c r="E15" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" si="1"/>
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="G15" s="17">
         <f t="shared" si="2"/>
-        <v>39.3894431</v>
+        <v>37.35205811</v>
       </c>
       <c r="H15" s="20">
         <f t="shared" si="3"/>
-        <v>23.2</v>
+        <v>22</v>
       </c>
       <c r="I15" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38225,25 +38243,25 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>151</v>
+        <v>56</v>
       </c>
       <c r="C16" s="17">
-        <v>26.0</v>
+        <v>25.5</v>
       </c>
       <c r="E16" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F16" s="17">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>25.5</v>
       </c>
       <c r="G16" s="17">
         <f t="shared" si="2"/>
-        <v>35.31467312</v>
+        <v>34.63554479</v>
       </c>
       <c r="H16" s="20">
         <f t="shared" si="3"/>
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
       <c r="I16" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38272,25 +38290,25 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C17" s="17">
-        <v>23.5</v>
+        <v>22.5</v>
       </c>
       <c r="E17" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F17" s="17">
         <f t="shared" si="1"/>
-        <v>23.5</v>
+        <v>22.5</v>
       </c>
       <c r="G17" s="17">
         <f t="shared" si="2"/>
-        <v>31.91903148</v>
+        <v>30.56077482</v>
       </c>
       <c r="H17" s="20">
         <f t="shared" si="3"/>
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="I17" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38302,25 +38320,25 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C18" s="17">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="E18" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F18" s="17">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G18" s="17">
         <f t="shared" si="2"/>
-        <v>28.52338983</v>
+        <v>27.16513317</v>
       </c>
       <c r="H18" s="20">
         <f t="shared" si="3"/>
-        <v>16.8</v>
+        <v>16</v>
       </c>
       <c r="I18" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38339,7 +38357,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C19" s="17">
         <v>18.5</v>
@@ -38369,7 +38387,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C20" s="17">
         <v>16.5</v>
@@ -38399,25 +38417,25 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="C21" s="17">
-        <v>15.0</v>
+        <v>14.5</v>
       </c>
       <c r="E21" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F21" s="17">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="G21" s="17">
         <f t="shared" si="2"/>
-        <v>20.37384988</v>
+        <v>19.69472155</v>
       </c>
       <c r="H21" s="20">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="I21" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38429,25 +38447,25 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C22" s="17">
-        <v>14.0</v>
+        <v>13.5</v>
       </c>
       <c r="E22" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F22" s="17">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="G22" s="17">
         <f t="shared" si="2"/>
-        <v>19.01559322</v>
+        <v>18.33646489</v>
       </c>
       <c r="H22" s="20">
         <f t="shared" si="3"/>
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="I22" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38459,25 +38477,25 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C23" s="17">
-        <v>12.5</v>
+        <v>12.0</v>
       </c>
       <c r="E23" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F23" s="17">
         <f t="shared" si="1"/>
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="G23" s="17">
         <f t="shared" si="2"/>
-        <v>16.97820823</v>
+        <v>16.2990799</v>
       </c>
       <c r="H23" s="20">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="I23" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38489,25 +38507,25 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C24" s="17">
-        <v>10.5</v>
+        <v>11.0</v>
       </c>
       <c r="E24" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F24" s="17">
         <f t="shared" si="1"/>
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G24" s="17">
         <f t="shared" si="2"/>
-        <v>14.26169492</v>
+        <v>14.94082324</v>
       </c>
       <c r="H24" s="20">
         <f t="shared" si="3"/>
-        <v>8.4</v>
+        <v>8.8</v>
       </c>
       <c r="I24" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38519,7 +38537,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="C25" s="17">
         <v>10.0</v>
@@ -38549,25 +38567,25 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C26" s="17">
-        <v>9.0</v>
+        <v>9.5</v>
       </c>
       <c r="E26" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F26" s="17">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G26" s="17">
         <f t="shared" si="2"/>
-        <v>12.22430993</v>
+        <v>12.90343826</v>
       </c>
       <c r="H26" s="20">
         <f t="shared" si="3"/>
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="I26" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38579,7 +38597,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C27" s="17">
         <v>8.5</v>
@@ -38604,7 +38622,7 @@
         <v/>
       </c>
       <c r="K27" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L27" s="9">
         <v>0.8</v>
@@ -38615,25 +38633,25 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C28" s="17">
-        <v>7.5</v>
+        <v>8.0</v>
       </c>
       <c r="E28" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F28" s="17">
         <f t="shared" si="1"/>
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G28" s="17">
         <f t="shared" si="2"/>
-        <v>10.18692494</v>
+        <v>10.86605327</v>
       </c>
       <c r="H28" s="20">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I28" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38645,7 +38663,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C29" s="17">
         <v>7.0</v>
@@ -38675,7 +38693,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="C30" s="17">
         <v>6.5</v>
@@ -38705,7 +38723,7 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="C31" s="17">
         <v>6.0</v>
@@ -38738,22 +38756,22 @@
         <v>88</v>
       </c>
       <c r="C32" s="17">
-        <v>5.0</v>
+        <v>5.5</v>
       </c>
       <c r="E32" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F32" s="17">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G32" s="17">
         <f t="shared" si="2"/>
-        <v>6.791283293</v>
+        <v>7.470411622</v>
       </c>
       <c r="H32" s="20">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I32" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38765,7 +38783,7 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C33" s="17">
         <v>5.0</v>
@@ -38795,7 +38813,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>89</v>
+        <v>158</v>
       </c>
       <c r="C34" s="17">
         <v>4.5</v>
@@ -38825,25 +38843,25 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C35" s="17">
-        <v>4.0</v>
+        <v>4.5</v>
       </c>
       <c r="E35" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F35" s="17">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G35" s="17">
         <f t="shared" si="2"/>
-        <v>5.433026634</v>
+        <v>6.112154964</v>
       </c>
       <c r="H35" s="20">
         <f t="shared" si="3"/>
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="I35" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38855,7 +38873,7 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C36" s="17">
         <v>4.0</v>
@@ -38885,25 +38903,25 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C37" s="17">
-        <v>3.5</v>
+        <v>4.0</v>
       </c>
       <c r="E37" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F37" s="17">
         <f t="shared" si="1"/>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G37" s="17">
         <f t="shared" si="2"/>
-        <v>4.753898305</v>
+        <v>5.433026634</v>
       </c>
       <c r="H37" s="20">
         <f t="shared" si="3"/>
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="I37" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38915,7 +38933,7 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C38" s="17">
         <v>3.5</v>
@@ -38945,25 +38963,25 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>85</v>
+        <v>159</v>
       </c>
       <c r="C39" s="17">
-        <v>3.0</v>
+        <v>3.5</v>
       </c>
       <c r="E39" s="22" t="b">
         <v>0</v>
       </c>
       <c r="F39" s="17">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G39" s="17">
         <f t="shared" si="2"/>
-        <v>4.074769976</v>
+        <v>4.753898305</v>
       </c>
       <c r="H39" s="20">
         <f t="shared" si="3"/>
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="I39" s="21" t="str">
         <f t="shared" si="4"/>
@@ -38975,7 +38993,7 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>158</v>
+        <v>96</v>
       </c>
       <c r="C40" s="17">
         <v>3.0</v>
@@ -39005,7 +39023,7 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="C41" s="17">
         <v>3.0</v>
@@ -39035,7 +39053,7 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="C42" s="17">
         <v>2.5</v>
@@ -39065,7 +39083,7 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>101</v>
+        <v>161</v>
       </c>
       <c r="C43" s="17">
         <v>2.5</v>
@@ -39095,7 +39113,7 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="C44" s="17">
         <v>2.5</v>
@@ -39125,7 +39143,7 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>94</v>
+        <v>162</v>
       </c>
       <c r="C45" s="17">
         <v>2.5</v>
@@ -39155,7 +39173,7 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C46" s="17">
         <v>2.0</v>
@@ -39185,7 +39203,7 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="C47" s="17">
         <v>2.0</v>
@@ -39215,7 +39233,7 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C48" s="17">
         <v>2.0</v>
@@ -39245,7 +39263,7 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="C49" s="17">
         <v>2.0</v>
@@ -39275,7 +39293,7 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C50" s="17">
         <v>2.0</v>
@@ -39305,7 +39323,7 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>161</v>
+        <v>83</v>
       </c>
       <c r="C51" s="17">
         <v>2.0</v>
@@ -39335,7 +39353,7 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C52" s="17">
         <v>2.0</v>
@@ -39365,7 +39383,7 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C53" s="17">
         <v>2.0</v>
@@ -39395,7 +39413,7 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C54" s="17">
         <v>2.0</v>
@@ -39425,7 +39443,7 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>165</v>
+        <v>111</v>
       </c>
       <c r="C55" s="17">
         <v>2.0</v>
@@ -39455,7 +39473,7 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>166</v>
+        <v>109</v>
       </c>
       <c r="C56" s="17">
         <v>2.0</v>
@@ -39485,7 +39503,7 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C57" s="17">
         <v>2.0</v>
@@ -39515,7 +39533,7 @@
         <v>57.0</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="C58" s="17">
         <v>2.0</v>
@@ -39545,7 +39563,7 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="C59" s="17">
         <v>2.0</v>
@@ -39575,7 +39593,7 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="C60" s="17">
         <v>2.0</v>
@@ -39605,7 +39623,7 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>168</v>
+        <v>99</v>
       </c>
       <c r="C61" s="17">
         <v>2.0</v>
@@ -39635,7 +39653,7 @@
         <v>61.0</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="C62" s="17">
         <v>1.0</v>
@@ -39665,7 +39683,7 @@
         <v>62.0</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>114</v>
+        <v>170</v>
       </c>
       <c r="C63" s="17">
         <v>1.0</v>
@@ -39695,7 +39713,7 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>117</v>
+        <v>171</v>
       </c>
       <c r="C64" s="17">
         <v>1.0</v>
@@ -39725,7 +39743,7 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>170</v>
+        <v>92</v>
       </c>
       <c r="C65" s="17">
         <v>1.0</v>
@@ -39755,7 +39773,7 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="C66" s="17">
         <v>1.0</v>
@@ -39785,7 +39803,7 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="C67" s="17">
         <v>1.0</v>
@@ -39815,7 +39833,7 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C68" s="17">
         <v>1.0</v>
@@ -39845,7 +39863,7 @@
         <v>68.0</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="C69" s="17">
         <v>1.0</v>
@@ -39875,7 +39893,7 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="C70" s="17">
         <v>1.0</v>
@@ -39905,7 +39923,7 @@
         <v>70.0</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C71" s="17">
         <v>1.0</v>
@@ -39935,7 +39953,7 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="C72" s="17">
         <v>1.0</v>
@@ -39965,7 +39983,7 @@
         <v>72.0</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>124</v>
+        <v>177</v>
       </c>
       <c r="C73" s="17">
         <v>1.0</v>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -1004,7 +1004,7 @@
         <v>1.01</v>
       </c>
       <c r="B2" s="9">
-        <v>7651.0</v>
+        <v>7581.0</v>
       </c>
       <c r="C2" s="10">
         <f t="shared" ref="C2:C73" si="2">1 + --(INT((ROW()-ROW($B$2))/12)=4)
@@ -1024,7 +1024,7 @@
         )
     )
 </f>
-        <v>139.1284418</v>
+        <v>133.2988864</v>
       </c>
       <c r="D2" s="10">
         <f t="shared" ref="D2:D73" si="3">( K2
@@ -1036,7 +1036,7 @@
      )
   ) / 2
 </f>
-        <v>140</v>
+        <v>134.5</v>
       </c>
       <c r="E2" s="10">
         <f t="shared" ref="E2:E73" si="4">(MEDIAN(F2:H2)+AVERAGE(F2:H2))/2
@@ -1054,19 +1054,19 @@
       </c>
       <c r="I2" s="10">
         <f t="shared" ref="I2:I73" si="5">ROUNDDOWN(C2*2,0)</f>
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="J2" s="10">
         <f t="shared" ref="J2:J73" si="6">C2*2 - I2</f>
-        <v>0.2568836805</v>
+        <v>0.5977727823</v>
       </c>
       <c r="K2" s="10">
         <f>I2 + --(RANK(J2,$J$2:$J$73,0) &lt;= 1200*2 - SUM($I$2:$I$73))</f>
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="L2" s="11">
         <f t="shared" ref="L2:L74" si="7">D2</f>
-        <v>140</v>
+        <v>134.5</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
@@ -1075,47 +1075,47 @@
       </c>
       <c r="P2" s="10">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
-        <v>140</v>
+        <v>134.5</v>
       </c>
       <c r="Q2" s="10">
         <f t="shared" si="1"/>
-        <v>108</v>
+        <v>102.5</v>
       </c>
       <c r="R2" s="10">
         <f t="shared" si="1"/>
-        <v>96</v>
+        <v>92.5</v>
       </c>
       <c r="S2" s="10">
         <f t="shared" si="1"/>
-        <v>86</v>
+        <v>81.5</v>
       </c>
       <c r="T2" s="10">
         <f t="shared" si="1"/>
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U2" s="10">
         <f t="shared" si="1"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V2" s="10">
         <f t="shared" si="1"/>
-        <v>63</v>
+        <v>55.5</v>
       </c>
       <c r="W2" s="10">
         <f t="shared" si="1"/>
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="X2" s="10">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Y2" s="10">
         <f t="shared" si="1"/>
-        <v>44</v>
+        <v>44.5</v>
       </c>
       <c r="Z2" s="10">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AA2" s="10">
         <f t="shared" si="1"/>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="AB2" s="10">
         <f t="shared" ref="AB2:AB7" si="9">SUM(P2:AA2)</f>
-        <v>866</v>
+        <v>830</v>
       </c>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
@@ -1133,15 +1133,15 @@
         <v>1.02</v>
       </c>
       <c r="B3" s="9">
-        <v>5748.0</v>
+        <v>5595.5</v>
       </c>
       <c r="C3" s="10">
         <f t="shared" si="2"/>
-        <v>106.8674263</v>
+        <v>101.6766712</v>
       </c>
       <c r="D3" s="10">
         <f t="shared" si="3"/>
-        <v>108</v>
+        <v>102.5</v>
       </c>
       <c r="E3" s="10">
         <f t="shared" si="4"/>
@@ -1158,11 +1158,11 @@
       </c>
       <c r="I3" s="10">
         <f t="shared" si="5"/>
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="J3" s="10">
         <f t="shared" si="6"/>
-        <v>0.7348525498</v>
+        <v>0.3533423145</v>
       </c>
       <c r="K3" s="10">
         <f t="shared" ref="K3:K73" si="10">MIN(
@@ -1171,11 +1171,11 @@
   K2
 )
 </f>
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="L3" s="11">
         <f t="shared" si="7"/>
-        <v>108</v>
+        <v>102.5</v>
       </c>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
@@ -1184,43 +1184,43 @@
       </c>
       <c r="P3" s="10">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
-        <v>28.5</v>
+        <v>29.5</v>
       </c>
       <c r="Q3" s="10">
         <f t="shared" si="8"/>
-        <v>25.5</v>
+        <v>28</v>
       </c>
       <c r="R3" s="10">
         <f t="shared" si="8"/>
-        <v>23.5</v>
+        <v>26</v>
       </c>
       <c r="S3" s="10">
         <f t="shared" si="8"/>
-        <v>21.5</v>
+        <v>24</v>
       </c>
       <c r="T3" s="10">
         <f t="shared" si="8"/>
-        <v>19</v>
+        <v>21.5</v>
       </c>
       <c r="U3" s="10">
         <f t="shared" si="8"/>
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="V3" s="10">
         <f t="shared" si="8"/>
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="W3" s="10">
         <f t="shared" si="8"/>
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="X3" s="10">
         <f t="shared" si="8"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y3" s="10">
         <f t="shared" si="8"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z3" s="10">
         <f t="shared" si="8"/>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="AB3" s="10">
         <f t="shared" si="9"/>
-        <v>212</v>
+        <v>229.5</v>
       </c>
       <c r="AC3" s="5"/>
       <c r="AD3" s="5"/>
@@ -1242,15 +1242,15 @@
         <v>1.03</v>
       </c>
       <c r="B4" s="9">
-        <v>5655.0</v>
+        <v>5651.0</v>
       </c>
       <c r="C4" s="10">
         <f t="shared" si="2"/>
-        <v>95.09489457</v>
+        <v>91.69437929</v>
       </c>
       <c r="D4" s="10">
         <f t="shared" si="3"/>
-        <v>96</v>
+        <v>92.5</v>
       </c>
       <c r="E4" s="10">
         <f t="shared" si="4"/>
@@ -1267,19 +1267,19 @@
       </c>
       <c r="I4" s="10">
         <f t="shared" si="5"/>
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="J4" s="10">
         <f t="shared" si="6"/>
-        <v>0.1897891409</v>
+        <v>0.3887585817</v>
       </c>
       <c r="K4" s="10">
         <f t="shared" si="10"/>
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="L4" s="11">
         <f t="shared" si="7"/>
-        <v>96</v>
+        <v>92.5</v>
       </c>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
@@ -1288,15 +1288,15 @@
       </c>
       <c r="P4" s="10">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Q4" s="10">
         <f t="shared" si="11"/>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="R4" s="10">
         <f t="shared" si="11"/>
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="S4" s="10">
         <f t="shared" si="11"/>
@@ -1304,39 +1304,39 @@
       </c>
       <c r="T4" s="10">
         <f t="shared" si="11"/>
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="U4" s="10">
         <f t="shared" si="11"/>
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="V4" s="10">
         <f t="shared" si="11"/>
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W4" s="10">
         <f t="shared" si="11"/>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="X4" s="10">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y4" s="10">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Z4" s="10">
         <f t="shared" si="11"/>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AA4" s="10">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB4" s="10">
         <f t="shared" si="9"/>
-        <v>67.5</v>
+        <v>73</v>
       </c>
       <c r="AC4" s="5"/>
       <c r="AD4" s="5"/>
@@ -1346,15 +1346,15 @@
         <v>1.04</v>
       </c>
       <c r="B5" s="9">
-        <v>5263.0</v>
+        <v>5084.5</v>
       </c>
       <c r="C5" s="10">
         <f t="shared" si="2"/>
-        <v>84.94144699</v>
+        <v>80.34665431</v>
       </c>
       <c r="D5" s="10">
         <f t="shared" si="3"/>
-        <v>86</v>
+        <v>81.5</v>
       </c>
       <c r="E5" s="10">
         <f t="shared" si="4"/>
@@ -1371,19 +1371,19 @@
       </c>
       <c r="I5" s="10">
         <f t="shared" si="5"/>
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="J5" s="10">
         <f t="shared" si="6"/>
-        <v>0.8828939733</v>
+        <v>0.6933086157</v>
       </c>
       <c r="K5" s="10">
         <f t="shared" si="10"/>
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="L5" s="11">
         <f t="shared" si="7"/>
-        <v>86</v>
+        <v>81.5</v>
       </c>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
@@ -1392,55 +1392,55 @@
       </c>
       <c r="P5" s="10">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q5" s="10">
         <f t="shared" si="12"/>
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="R5" s="10">
         <f t="shared" si="12"/>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="S5" s="10">
         <f t="shared" si="12"/>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T5" s="10">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U5" s="10">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="V5" s="10">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="W5" s="10">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="X5" s="10">
         <f t="shared" si="12"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Y5" s="10">
         <f t="shared" si="12"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Z5" s="10">
         <f t="shared" si="12"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AA5" s="10">
         <f t="shared" si="12"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AB5" s="10">
         <f t="shared" si="9"/>
-        <v>24.5</v>
+        <v>31.5</v>
       </c>
       <c r="AC5" s="5"/>
       <c r="AD5" s="5"/>
@@ -1450,15 +1450,15 @@
         <v>1.05</v>
       </c>
       <c r="B6" s="9">
-        <v>5012.0</v>
+        <v>5065.5</v>
       </c>
       <c r="C6" s="10">
         <f t="shared" si="2"/>
-        <v>75.84174891</v>
+        <v>73.66567951</v>
       </c>
       <c r="D6" s="10">
         <f t="shared" si="3"/>
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E6" s="10">
         <f t="shared" si="4"/>
@@ -1475,19 +1475,19 @@
       </c>
       <c r="I6" s="10">
         <f t="shared" si="5"/>
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="J6" s="10">
         <f t="shared" si="6"/>
-        <v>0.6834978222</v>
+        <v>0.3313590109</v>
       </c>
       <c r="K6" s="10">
         <f t="shared" si="10"/>
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="L6" s="11">
         <f t="shared" si="7"/>
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
@@ -1496,55 +1496,55 @@
       </c>
       <c r="P6" s="10">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="S6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="U6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="V6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="W6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="X6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Y6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Z6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AA6" s="10">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AB6" s="10">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AC6" s="5"/>
       <c r="AD6" s="5"/>
@@ -1554,15 +1554,15 @@
         <v>1.06</v>
       </c>
       <c r="B7" s="9">
-        <v>4716.0</v>
+        <v>4959.5</v>
       </c>
       <c r="C7" s="10">
         <f t="shared" si="2"/>
-        <v>67.83501727</v>
+        <v>67.48501036</v>
       </c>
       <c r="D7" s="10">
         <f t="shared" si="3"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E7" s="10">
         <f t="shared" si="4"/>
@@ -1579,19 +1579,19 @@
       </c>
       <c r="I7" s="10">
         <f t="shared" si="5"/>
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J7" s="10">
         <f t="shared" si="6"/>
-        <v>0.6700345437</v>
+        <v>0.9700207102</v>
       </c>
       <c r="K7" s="10">
         <f t="shared" si="10"/>
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L7" s="11">
         <f t="shared" si="7"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
@@ -1658,15 +1658,15 @@
         <v>1.07</v>
       </c>
       <c r="B8" s="9">
-        <v>4608.0</v>
+        <v>3998.0</v>
       </c>
       <c r="C8" s="10">
         <f t="shared" si="2"/>
-        <v>61.93350077</v>
+        <v>55.16138027</v>
       </c>
       <c r="D8" s="10">
         <f t="shared" si="3"/>
-        <v>63</v>
+        <v>55.5</v>
       </c>
       <c r="E8" s="10">
         <f t="shared" si="4"/>
@@ -1683,54 +1683,54 @@
       </c>
       <c r="I8" s="10">
         <f t="shared" si="5"/>
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="J8" s="10">
         <f t="shared" si="6"/>
-        <v>0.8670015458</v>
+        <v>0.3227605389</v>
       </c>
       <c r="K8" s="10">
         <f t="shared" si="10"/>
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="L8" s="11">
         <f t="shared" si="7"/>
-        <v>63</v>
+        <v>55.5</v>
       </c>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
       <c r="P8" s="10">
         <f t="shared" ref="P8:AB8" si="15">SUM(P2:P7)</f>
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="Q8" s="10">
         <f t="shared" si="15"/>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R8" s="10">
         <f t="shared" si="15"/>
-        <v>132.5</v>
+        <v>132</v>
       </c>
       <c r="S8" s="10">
         <f t="shared" si="15"/>
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="T8" s="10">
         <f t="shared" si="15"/>
-        <v>106.5</v>
+        <v>108</v>
       </c>
       <c r="U8" s="10">
         <f t="shared" si="15"/>
-        <v>96.5</v>
+        <v>98.5</v>
       </c>
       <c r="V8" s="10">
         <f t="shared" si="15"/>
-        <v>88.5</v>
+        <v>84</v>
       </c>
       <c r="W8" s="10">
         <f t="shared" si="15"/>
-        <v>81.5</v>
+        <v>80.5</v>
       </c>
       <c r="X8" s="10">
         <f t="shared" si="15"/>
@@ -1738,15 +1738,15 @@
       </c>
       <c r="Y8" s="10">
         <f t="shared" si="15"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="Z8" s="10">
         <f t="shared" si="15"/>
-        <v>58.5</v>
+        <v>61</v>
       </c>
       <c r="AA8" s="10">
         <f t="shared" si="15"/>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AB8" s="10">
         <f t="shared" si="15"/>
@@ -1760,15 +1760,15 @@
         <v>1.08</v>
       </c>
       <c r="B9" s="9">
-        <v>4496.0</v>
+        <v>4293.5</v>
       </c>
       <c r="C9" s="10">
         <f t="shared" si="2"/>
-        <v>56.77893357</v>
+        <v>53.39688341</v>
       </c>
       <c r="D9" s="10">
         <f t="shared" si="3"/>
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E9" s="10">
         <f t="shared" si="4"/>
@@ -1785,19 +1785,19 @@
       </c>
       <c r="I9" s="10">
         <f t="shared" si="5"/>
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="J9" s="10">
         <f t="shared" si="6"/>
-        <v>0.5578671413</v>
+        <v>0.7937668276</v>
       </c>
       <c r="K9" s="10">
         <f t="shared" si="10"/>
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L9" s="11">
         <f t="shared" si="7"/>
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
@@ -1823,15 +1823,15 @@
         <v>1.09</v>
       </c>
       <c r="B10" s="9">
-        <v>3962.0</v>
+        <v>3868.0</v>
       </c>
       <c r="C10" s="10">
         <f t="shared" si="2"/>
-        <v>48.84719592</v>
+        <v>46.62675706</v>
       </c>
       <c r="D10" s="10">
         <f t="shared" si="3"/>
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E10" s="10">
         <f t="shared" si="4"/>
@@ -1848,19 +1848,19 @@
       </c>
       <c r="I10" s="10">
         <f t="shared" si="5"/>
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="J10" s="10">
         <f t="shared" si="6"/>
-        <v>0.6943918419</v>
+        <v>0.2535141299</v>
       </c>
       <c r="K10" s="10">
         <f t="shared" si="10"/>
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="L10" s="11">
         <f t="shared" si="7"/>
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
@@ -1886,15 +1886,15 @@
         <v>1.1</v>
       </c>
       <c r="B11" s="9">
-        <v>3852.0</v>
+        <v>4169.0</v>
       </c>
       <c r="C11" s="10">
         <f t="shared" si="2"/>
-        <v>43.27287131</v>
+        <v>43.7855352</v>
       </c>
       <c r="D11" s="10">
         <f t="shared" si="3"/>
-        <v>44</v>
+        <v>44.5</v>
       </c>
       <c r="E11" s="10">
         <f t="shared" si="4"/>
@@ -1911,19 +1911,19 @@
       </c>
       <c r="I11" s="10">
         <f t="shared" si="5"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J11" s="10">
         <f t="shared" si="6"/>
-        <v>0.5457426166</v>
+        <v>0.5710703924</v>
       </c>
       <c r="K11" s="10">
         <f t="shared" si="10"/>
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L11" s="11">
         <f t="shared" si="7"/>
-        <v>44</v>
+        <v>44.5</v>
       </c>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -1949,15 +1949,15 @@
         <v>1.11</v>
       </c>
       <c r="B12" s="9">
-        <v>3655.0</v>
+        <v>4164.0</v>
       </c>
       <c r="C12" s="10">
         <f t="shared" si="2"/>
-        <v>38.94398666</v>
+        <v>40.59449014</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="3"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E12" s="10">
         <f t="shared" si="4"/>
@@ -1974,19 +1974,19 @@
       </c>
       <c r="I12" s="10">
         <f t="shared" si="5"/>
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J12" s="10">
         <f t="shared" si="6"/>
-        <v>0.8879733251</v>
+        <v>0.1889802728</v>
       </c>
       <c r="K12" s="10">
         <f t="shared" si="10"/>
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L12" s="11">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
@@ -2012,11 +2012,11 @@
         <v>1.12</v>
       </c>
       <c r="B13" s="9">
-        <v>3490.0</v>
+        <v>3804.0</v>
       </c>
       <c r="C13" s="10">
         <f t="shared" si="2"/>
-        <v>34.17979276</v>
+        <v>34.72505331</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="3"/>
@@ -2037,15 +2037,15 @@
       </c>
       <c r="I13" s="10">
         <f t="shared" si="5"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J13" s="10">
         <f t="shared" si="6"/>
-        <v>0.3595855109</v>
+        <v>0.450106622</v>
       </c>
       <c r="K13" s="10">
         <f t="shared" si="10"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L13" s="11">
         <f t="shared" si="7"/>
@@ -2075,15 +2075,15 @@
         <v>2.01</v>
       </c>
       <c r="B14" s="9">
-        <v>2956.0</v>
+        <v>3370.0</v>
       </c>
       <c r="C14" s="10">
         <f t="shared" si="2"/>
-        <v>28.3198364</v>
+        <v>29.48452656</v>
       </c>
       <c r="D14" s="10">
         <f t="shared" si="3"/>
-        <v>28.5</v>
+        <v>29.5</v>
       </c>
       <c r="E14" s="10">
         <f t="shared" si="4"/>
@@ -2100,19 +2100,19 @@
       </c>
       <c r="I14" s="10">
         <f t="shared" si="5"/>
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J14" s="10">
         <f t="shared" si="6"/>
-        <v>0.6396727915</v>
+        <v>0.96905312</v>
       </c>
       <c r="K14" s="10">
         <f t="shared" si="10"/>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L14" s="11">
         <f t="shared" si="7"/>
-        <v>28.5</v>
+        <v>29.5</v>
       </c>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
@@ -2138,15 +2138,15 @@
         <v>2.02</v>
       </c>
       <c r="B15" s="9">
-        <v>2916.0</v>
+        <v>3611.0</v>
       </c>
       <c r="C15" s="10">
         <f t="shared" si="2"/>
-        <v>25.62991281</v>
+        <v>28.0185235</v>
       </c>
       <c r="D15" s="10">
         <f t="shared" si="3"/>
-        <v>25.5</v>
+        <v>28</v>
       </c>
       <c r="E15" s="10">
         <f t="shared" si="4"/>
@@ -2163,19 +2163,19 @@
       </c>
       <c r="I15" s="10">
         <f t="shared" si="5"/>
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J15" s="10">
         <f t="shared" si="6"/>
-        <v>0.2598256233</v>
+        <v>0.03704700192</v>
       </c>
       <c r="K15" s="10">
         <f t="shared" si="10"/>
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="L15" s="11">
         <f t="shared" si="7"/>
-        <v>25.5</v>
+        <v>28</v>
       </c>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
@@ -2201,15 +2201,15 @@
         <v>2.03</v>
       </c>
       <c r="B16" s="9">
-        <v>2874.0</v>
+        <v>3605.0</v>
       </c>
       <c r="C16" s="10">
         <f t="shared" si="2"/>
-        <v>23.5550663</v>
+        <v>25.93594648</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" si="3"/>
-        <v>23.5</v>
+        <v>26</v>
       </c>
       <c r="E16" s="10">
         <f t="shared" si="4"/>
@@ -2226,19 +2226,19 @@
       </c>
       <c r="I16" s="10">
         <f t="shared" si="5"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J16" s="10">
         <f t="shared" si="6"/>
-        <v>0.1101326074</v>
+        <v>0.8718929514</v>
       </c>
       <c r="K16" s="10">
         <f t="shared" si="10"/>
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="L16" s="11">
         <f t="shared" si="7"/>
-        <v>23.5</v>
+        <v>26</v>
       </c>
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
@@ -2264,15 +2264,15 @@
         <v>2.04</v>
       </c>
       <c r="B17" s="9">
-        <v>2870.0</v>
+        <v>3603.0</v>
       </c>
       <c r="C17" s="10">
         <f t="shared" si="2"/>
-        <v>21.66981819</v>
+        <v>23.88616967</v>
       </c>
       <c r="D17" s="10">
         <f t="shared" si="3"/>
-        <v>21.5</v>
+        <v>24</v>
       </c>
       <c r="E17" s="10">
         <f t="shared" si="4"/>
@@ -2289,19 +2289,19 @@
       </c>
       <c r="I17" s="10">
         <f t="shared" si="5"/>
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J17" s="10">
         <f t="shared" si="6"/>
-        <v>0.3396363836</v>
+        <v>0.7723393477</v>
       </c>
       <c r="K17" s="10">
         <f t="shared" si="10"/>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L17" s="11">
         <f t="shared" si="7"/>
-        <v>21.5</v>
+        <v>24</v>
       </c>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
@@ -2327,15 +2327,15 @@
         <v>2.05</v>
       </c>
       <c r="B18" s="9">
-        <v>2724.0</v>
+        <v>3445.0</v>
       </c>
       <c r="C18" s="10">
         <f t="shared" si="2"/>
-        <v>19.19835733</v>
+        <v>21.24071413</v>
       </c>
       <c r="D18" s="10">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21.5</v>
       </c>
       <c r="E18" s="10">
         <f t="shared" si="4"/>
@@ -2352,19 +2352,19 @@
       </c>
       <c r="I18" s="10">
         <f t="shared" si="5"/>
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J18" s="10">
         <f t="shared" si="6"/>
-        <v>0.396714658</v>
+        <v>0.481428268</v>
       </c>
       <c r="K18" s="10">
         <f t="shared" si="10"/>
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L18" s="11">
         <f t="shared" si="7"/>
-        <v>19</v>
+        <v>21.5</v>
       </c>
       <c r="M18" s="7"/>
       <c r="N18" s="7"/>
@@ -2390,15 +2390,15 @@
         <v>2.06</v>
       </c>
       <c r="B19" s="9">
-        <v>2635.0</v>
+        <v>3220.0</v>
       </c>
       <c r="C19" s="10">
         <f t="shared" si="2"/>
-        <v>17.50331703</v>
+        <v>18.95034162</v>
       </c>
       <c r="D19" s="10">
         <f t="shared" si="3"/>
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="E19" s="10">
         <f t="shared" si="4"/>
@@ -2415,19 +2415,19 @@
       </c>
       <c r="I19" s="10">
         <f t="shared" si="5"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J19" s="10">
         <f t="shared" si="6"/>
-        <v>0.006634064342</v>
+        <v>0.9006832386</v>
       </c>
       <c r="K19" s="10">
         <f t="shared" si="10"/>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L19" s="11">
         <f t="shared" si="7"/>
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="M19" s="7"/>
       <c r="N19" s="7"/>
@@ -2453,15 +2453,15 @@
         <v>2.07</v>
       </c>
       <c r="B20" s="9">
-        <v>2614.0</v>
+        <v>3200.0</v>
       </c>
       <c r="C20" s="10">
         <f t="shared" si="2"/>
-        <v>15.97357762</v>
+        <v>17.32055955</v>
       </c>
       <c r="D20" s="10">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="E20" s="10">
         <f t="shared" si="4"/>
@@ -2478,19 +2478,19 @@
       </c>
       <c r="I20" s="10">
         <f t="shared" si="5"/>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J20" s="10">
         <f t="shared" si="6"/>
-        <v>0.9471552331</v>
+        <v>0.6411190999</v>
       </c>
       <c r="K20" s="10">
         <f t="shared" si="10"/>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L20" s="11">
         <f t="shared" si="7"/>
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="M20" s="7"/>
       <c r="N20" s="7"/>
@@ -2516,15 +2516,15 @@
         <v>2.08</v>
       </c>
       <c r="B21" s="9">
-        <v>2551.0</v>
+        <v>3127.0</v>
       </c>
       <c r="C21" s="10">
         <f t="shared" si="2"/>
-        <v>14.57042068</v>
+        <v>15.79914766</v>
       </c>
       <c r="D21" s="10">
         <f t="shared" si="3"/>
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="E21" s="10">
         <f t="shared" si="4"/>
@@ -2541,19 +2541,19 @@
       </c>
       <c r="I21" s="10">
         <f t="shared" si="5"/>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J21" s="10">
         <f t="shared" si="6"/>
-        <v>0.1408413679</v>
+        <v>0.5982953293</v>
       </c>
       <c r="K21" s="10">
         <f t="shared" si="10"/>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L21" s="11">
         <f t="shared" si="7"/>
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="M21" s="7"/>
       <c r="N21" s="7"/>
@@ -2579,15 +2579,15 @@
         <v>2.09</v>
       </c>
       <c r="B22" s="9">
-        <v>2485.0</v>
+        <v>2924.0</v>
       </c>
       <c r="C22" s="10">
         <f t="shared" si="2"/>
-        <v>13.20114215</v>
+        <v>13.97892858</v>
       </c>
       <c r="D22" s="10">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E22" s="10">
         <f t="shared" si="4"/>
@@ -2604,19 +2604,19 @@
       </c>
       <c r="I22" s="10">
         <f t="shared" si="5"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J22" s="10">
         <f t="shared" si="6"/>
-        <v>0.4022843027</v>
+        <v>0.9578571639</v>
       </c>
       <c r="K22" s="10">
         <f t="shared" si="10"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L22" s="11">
         <f t="shared" si="7"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
@@ -2642,15 +2642,15 @@
         <v>2.1</v>
       </c>
       <c r="B23" s="9">
-        <v>2449.0</v>
+        <v>3020.0</v>
       </c>
       <c r="C23" s="10">
         <f t="shared" si="2"/>
-        <v>11.88357616</v>
+        <v>12.93828607</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E23" s="10">
         <f t="shared" si="4"/>
@@ -2667,19 +2667,19 @@
       </c>
       <c r="I23" s="10">
         <f t="shared" si="5"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J23" s="10">
         <f t="shared" si="6"/>
-        <v>0.7671523235</v>
+        <v>0.8765721429</v>
       </c>
       <c r="K23" s="10">
         <f t="shared" si="10"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L23" s="11">
         <f t="shared" si="7"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M23" s="7"/>
       <c r="N23" s="7"/>
@@ -2705,11 +2705,11 @@
         <v>2.11</v>
       </c>
       <c r="B24" s="9">
-        <v>2393.0</v>
+        <v>2543.5</v>
       </c>
       <c r="C24" s="10">
         <f t="shared" si="2"/>
-        <v>10.86498137</v>
+        <v>10.87675645</v>
       </c>
       <c r="D24" s="10">
         <f t="shared" si="3"/>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="J24" s="10">
         <f t="shared" si="6"/>
-        <v>0.7299627311</v>
+        <v>0.7535128983</v>
       </c>
       <c r="K24" s="10">
         <f t="shared" si="10"/>
@@ -2768,11 +2768,11 @@
         <v>2.12</v>
       </c>
       <c r="B25" s="9">
-        <v>2349.0</v>
+        <v>2391.0</v>
       </c>
       <c r="C25" s="10">
         <f t="shared" si="2"/>
-        <v>10.09371747</v>
+        <v>9.878535977</v>
       </c>
       <c r="D25" s="10">
         <f t="shared" si="3"/>
@@ -2793,11 +2793,11 @@
       </c>
       <c r="I25" s="10">
         <f t="shared" si="5"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J25" s="10">
         <f t="shared" si="6"/>
-        <v>0.1874349454</v>
+        <v>0.7570719546</v>
       </c>
       <c r="K25" s="10">
         <f t="shared" si="10"/>
@@ -2831,15 +2831,15 @@
         <v>3.01</v>
       </c>
       <c r="B26" s="9">
-        <v>2331.0</v>
+        <v>2669.5</v>
       </c>
       <c r="C26" s="10">
         <f t="shared" si="2"/>
-        <v>9.260413184</v>
+        <v>9.649188303</v>
       </c>
       <c r="D26" s="10">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="E26" s="10">
         <f t="shared" si="4"/>
@@ -2856,19 +2856,19 @@
       </c>
       <c r="I26" s="10">
         <f t="shared" si="5"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J26" s="10">
         <f t="shared" si="6"/>
-        <v>0.5208263684</v>
+        <v>0.2983766053</v>
       </c>
       <c r="K26" s="10">
         <f t="shared" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L26" s="11">
         <f t="shared" si="7"/>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="M26" s="7"/>
       <c r="N26" s="7"/>
@@ -2894,15 +2894,15 @@
         <v>3.02</v>
       </c>
       <c r="B27" s="9">
-        <v>2321.0</v>
+        <v>2632.0</v>
       </c>
       <c r="C27" s="10">
         <f t="shared" si="2"/>
-        <v>8.609091984</v>
+        <v>8.91934944</v>
       </c>
       <c r="D27" s="10">
         <f t="shared" si="3"/>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="E27" s="10">
         <f t="shared" si="4"/>
@@ -2923,15 +2923,15 @@
       </c>
       <c r="J27" s="10">
         <f t="shared" si="6"/>
-        <v>0.2181839685</v>
+        <v>0.83869888</v>
       </c>
       <c r="K27" s="10">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L27" s="11">
         <f t="shared" si="7"/>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
@@ -2957,15 +2957,15 @@
         <v>3.03</v>
       </c>
       <c r="B28" s="9">
-        <v>2300.0</v>
+        <v>2194.0</v>
       </c>
       <c r="C28" s="10">
         <f t="shared" si="2"/>
-        <v>7.870024625</v>
+        <v>7.45545819</v>
       </c>
       <c r="D28" s="10">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="E28" s="10">
         <f t="shared" si="4"/>
@@ -2982,19 +2982,19 @@
       </c>
       <c r="I28" s="10">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J28" s="10">
         <f t="shared" si="6"/>
-        <v>0.7400492507</v>
+        <v>0.9109163795</v>
       </c>
       <c r="K28" s="10">
         <f t="shared" si="10"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L28" s="11">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="M28" s="7"/>
       <c r="N28" s="7"/>
@@ -3020,11 +3020,11 @@
         <v>3.04</v>
       </c>
       <c r="B29" s="9">
-        <v>1855.0</v>
+        <v>1964.5</v>
       </c>
       <c r="C29" s="10">
         <f t="shared" si="2"/>
-        <v>6.526501992</v>
+        <v>6.521492907</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="3"/>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="J29" s="10">
         <f t="shared" si="6"/>
-        <v>0.05300398382</v>
+        <v>0.04298581461</v>
       </c>
       <c r="K29" s="10">
         <f t="shared" si="10"/>
@@ -3101,15 +3101,15 @@
         <v>3.05</v>
       </c>
       <c r="B30" s="9">
-        <v>1742.0</v>
+        <v>2468.0</v>
       </c>
       <c r="C30" s="10">
         <f t="shared" si="2"/>
-        <v>5.923832598</v>
+        <v>6.816999431</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="E30" s="10">
         <f t="shared" si="4"/>
@@ -3126,19 +3126,19 @@
       </c>
       <c r="I30" s="10">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J30" s="10">
         <f t="shared" si="6"/>
-        <v>0.8476651953</v>
+        <v>0.6339988621</v>
       </c>
       <c r="K30" s="10">
         <f t="shared" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L30" s="11">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="M30" s="7"/>
       <c r="N30" s="7"/>
@@ -3182,15 +3182,15 @@
         <v>3.06</v>
       </c>
       <c r="B31" s="9">
-        <v>1653.0</v>
+        <v>2329.0</v>
       </c>
       <c r="C31" s="10">
         <f t="shared" si="2"/>
-        <v>5.398808901</v>
+        <v>6.164625544</v>
       </c>
       <c r="D31" s="10">
         <f t="shared" si="3"/>
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="E31" s="10">
         <f t="shared" si="4"/>
@@ -3207,19 +3207,19 @@
       </c>
       <c r="I31" s="10">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J31" s="10">
         <f t="shared" si="6"/>
-        <v>0.7976178026</v>
+        <v>0.3292510877</v>
       </c>
       <c r="K31" s="10">
         <f t="shared" si="10"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L31" s="11">
         <f t="shared" si="7"/>
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="M31" s="7"/>
       <c r="N31" s="7"/>
@@ -3263,15 +3263,15 @@
         <v>3.07</v>
       </c>
       <c r="B32" s="9">
-        <v>1615.0</v>
+        <v>2237.5</v>
       </c>
       <c r="C32" s="10">
         <f t="shared" si="2"/>
-        <v>4.810713002</v>
+        <v>5.455226479</v>
       </c>
       <c r="D32" s="10">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="E32" s="10">
         <f t="shared" si="4"/>
@@ -3288,19 +3288,19 @@
       </c>
       <c r="I32" s="10">
         <f t="shared" si="5"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J32" s="10">
         <f t="shared" si="6"/>
-        <v>0.6214260039</v>
+        <v>0.9104529585</v>
       </c>
       <c r="K32" s="10">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L32" s="11">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="M32" s="7"/>
       <c r="N32" s="7"/>
@@ -3344,15 +3344,15 @@
         <v>3.08</v>
       </c>
       <c r="B33" s="9">
-        <v>1606.0</v>
+        <v>2311.0</v>
       </c>
       <c r="C33" s="10">
         <f t="shared" si="2"/>
-        <v>4.475243412</v>
+        <v>5.164859326</v>
       </c>
       <c r="D33" s="10">
         <f t="shared" si="3"/>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="E33" s="10">
         <f t="shared" si="4"/>
@@ -3369,19 +3369,19 @@
       </c>
       <c r="I33" s="10">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J33" s="10">
         <f t="shared" si="6"/>
-        <v>0.9504868244</v>
+        <v>0.3297186522</v>
       </c>
       <c r="K33" s="10">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L33" s="11">
         <f t="shared" si="7"/>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
@@ -3425,15 +3425,15 @@
         <v>3.09</v>
       </c>
       <c r="B34" s="9">
-        <v>1550.0</v>
+        <v>2434.0</v>
       </c>
       <c r="C34" s="10">
         <f t="shared" si="2"/>
-        <v>4.068494974</v>
+        <v>4.896711616</v>
       </c>
       <c r="D34" s="10">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E34" s="10">
         <f t="shared" si="4"/>
@@ -3450,19 +3450,19 @@
       </c>
       <c r="I34" s="10">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J34" s="10">
         <f t="shared" si="6"/>
-        <v>0.1369899471</v>
+        <v>0.7934232321</v>
       </c>
       <c r="K34" s="10">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L34" s="11">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M34" s="7"/>
       <c r="N34" s="7"/>
@@ -3506,15 +3506,15 @@
         <v>3.1</v>
       </c>
       <c r="B35" s="9">
-        <v>1498.0</v>
+        <v>1984.5</v>
       </c>
       <c r="C35" s="10">
         <f t="shared" si="2"/>
-        <v>3.850505722</v>
+        <v>4.233513666</v>
       </c>
       <c r="D35" s="10">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="E35" s="10">
         <f t="shared" si="4"/>
@@ -3531,19 +3531,19 @@
       </c>
       <c r="I35" s="10">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J35" s="10">
         <f t="shared" si="6"/>
-        <v>0.7010114442</v>
+        <v>0.4670273326</v>
       </c>
       <c r="K35" s="10">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L35" s="11">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="M35" s="7"/>
       <c r="N35" s="7"/>
@@ -3587,15 +3587,15 @@
         <v>3.11</v>
       </c>
       <c r="B36" s="9">
-        <v>1270.0</v>
+        <v>2159.0</v>
       </c>
       <c r="C36" s="10">
         <f t="shared" si="2"/>
-        <v>3.31975183</v>
+        <v>4.045850253</v>
       </c>
       <c r="D36" s="10">
         <f t="shared" si="3"/>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E36" s="10">
         <f t="shared" si="4"/>
@@ -3612,19 +3612,19 @@
       </c>
       <c r="I36" s="10">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J36" s="10">
         <f t="shared" si="6"/>
-        <v>0.6395036593</v>
+        <v>0.09170050551</v>
       </c>
       <c r="K36" s="10">
         <f t="shared" si="10"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L36" s="11">
         <f t="shared" si="7"/>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="M36" s="7"/>
       <c r="N36" s="7"/>
@@ -3668,15 +3668,15 @@
         <v>3.12</v>
       </c>
       <c r="B37" s="9">
-        <v>1242.0</v>
+        <v>2012.5</v>
       </c>
       <c r="C37" s="10">
         <f t="shared" si="2"/>
-        <v>3.203009774</v>
+        <v>3.777070754</v>
       </c>
       <c r="D37" s="10">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="10">
         <f t="shared" si="4"/>
@@ -3693,19 +3693,19 @@
       </c>
       <c r="I37" s="10">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J37" s="10">
         <f t="shared" si="6"/>
-        <v>0.4060195486</v>
+        <v>0.5541415087</v>
       </c>
       <c r="K37" s="10">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L37" s="11">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M37" s="7"/>
       <c r="N37" s="7"/>
@@ -3749,15 +3749,15 @@
         <v>4.01</v>
       </c>
       <c r="B38" s="9">
-        <v>1055.0</v>
+        <v>1908.5</v>
       </c>
       <c r="C38" s="10">
         <f t="shared" si="2"/>
-        <v>2.804449097</v>
+        <v>3.406525128</v>
       </c>
       <c r="D38" s="10">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E38" s="10">
         <f t="shared" si="4"/>
@@ -3774,19 +3774,19 @@
       </c>
       <c r="I38" s="10">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J38" s="10">
         <f t="shared" si="6"/>
-        <v>0.6088981937</v>
+        <v>0.8130502555</v>
       </c>
       <c r="K38" s="10">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L38" s="11">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="M38" s="7"/>
       <c r="N38" s="7"/>
@@ -3830,15 +3830,15 @@
         <v>4.02</v>
       </c>
       <c r="B39" s="9">
-        <v>1050.0</v>
+        <v>2089.0</v>
       </c>
       <c r="C39" s="10">
         <f t="shared" si="2"/>
-        <v>2.702537893</v>
+        <v>3.38934916</v>
       </c>
       <c r="D39" s="10">
         <f t="shared" si="3"/>
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="E39" s="10">
         <f t="shared" si="4"/>
@@ -3855,19 +3855,19 @@
       </c>
       <c r="I39" s="10">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J39" s="10">
         <f t="shared" si="6"/>
-        <v>0.4050757865</v>
+        <v>0.7786983208</v>
       </c>
       <c r="K39" s="10">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L39" s="11">
         <f t="shared" si="7"/>
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="M39" s="7"/>
       <c r="N39" s="7"/>
@@ -3911,15 +3911,15 @@
         <v>4.03</v>
       </c>
       <c r="B40" s="9">
-        <v>996.0</v>
+        <v>2080.0</v>
       </c>
       <c r="C40" s="10">
         <f t="shared" si="2"/>
-        <v>2.441223105</v>
+        <v>3.106796764</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="3"/>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E40" s="10">
         <f t="shared" si="4"/>
@@ -3936,19 +3936,19 @@
       </c>
       <c r="I40" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="6"/>
-        <v>0.8824462108</v>
+        <v>0.2135935275</v>
       </c>
       <c r="K40" s="10">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L40" s="11">
         <f t="shared" si="7"/>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M40" s="7"/>
       <c r="N40" s="7"/>
@@ -3992,15 +3992,15 @@
         <v>4.04</v>
       </c>
       <c r="B41" s="9">
-        <v>980.0</v>
+        <v>2063.0</v>
       </c>
       <c r="C41" s="10">
         <f t="shared" si="2"/>
-        <v>2.37835901</v>
+        <v>2.992889914</v>
       </c>
       <c r="D41" s="10">
         <f t="shared" si="3"/>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E41" s="10">
         <f t="shared" si="4"/>
@@ -4017,19 +4017,19 @@
       </c>
       <c r="I41" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J41" s="10">
         <f t="shared" si="6"/>
-        <v>0.7567180198</v>
+        <v>0.9857798276</v>
       </c>
       <c r="K41" s="10">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L41" s="11">
         <f t="shared" si="7"/>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
@@ -4073,15 +4073,15 @@
         <v>4.05</v>
       </c>
       <c r="B42" s="13">
-        <v>961.0</v>
+        <v>2048.0</v>
       </c>
       <c r="C42" s="10">
         <f t="shared" si="2"/>
-        <v>2.1553673</v>
+        <v>2.725627734</v>
       </c>
       <c r="D42" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42" s="10">
         <f t="shared" si="4"/>
@@ -4098,19 +4098,19 @@
       </c>
       <c r="I42" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J42" s="10">
         <f t="shared" si="6"/>
-        <v>0.3107345999</v>
+        <v>0.451255468</v>
       </c>
       <c r="K42" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L42" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
@@ -4145,15 +4145,15 @@
         <v>4.06</v>
       </c>
       <c r="B43" s="9">
-        <v>959.0</v>
+        <v>1518.0</v>
       </c>
       <c r="C43" s="10">
         <f t="shared" si="2"/>
-        <v>2.078137938</v>
+        <v>2.334446925</v>
       </c>
       <c r="D43" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E43" s="10">
         <f t="shared" si="4"/>
@@ -4174,15 +4174,15 @@
       </c>
       <c r="J43" s="10">
         <f t="shared" si="6"/>
-        <v>0.1562758754</v>
+        <v>0.66889385</v>
       </c>
       <c r="K43" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L43" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M43" s="7"/>
       <c r="N43" s="7"/>
@@ -4217,15 +4217,15 @@
         <v>4.07</v>
       </c>
       <c r="B44" s="9">
-        <v>930.0</v>
+        <v>1956.0</v>
       </c>
       <c r="C44" s="10">
         <f t="shared" si="2"/>
-        <v>2.023645168</v>
+        <v>2.481821898</v>
       </c>
       <c r="D44" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E44" s="10">
         <f t="shared" si="4"/>
@@ -4246,15 +4246,15 @@
       </c>
       <c r="J44" s="10">
         <f t="shared" si="6"/>
-        <v>0.04729033657</v>
+        <v>0.9636437955</v>
       </c>
       <c r="K44" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L44" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
@@ -4297,15 +4297,15 @@
         <v>4.08</v>
       </c>
       <c r="B45" s="9">
-        <v>913.0</v>
+        <v>1953.0</v>
       </c>
       <c r="C45" s="10">
         <f t="shared" si="2"/>
-        <v>1.97999543</v>
+        <v>2.409567102</v>
       </c>
       <c r="D45" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E45" s="10">
         <f t="shared" si="4"/>
@@ -4322,19 +4322,19 @@
       </c>
       <c r="I45" s="10">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J45" s="10">
         <f t="shared" si="6"/>
-        <v>0.95999086</v>
+        <v>0.8191342046</v>
       </c>
       <c r="K45" s="10">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L45" s="11">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
@@ -4353,7 +4353,7 @@
    INDEX($P$2:$AA$7,O45,P45) * $AD$1
 )
 </f>
-        <v>124</v>
+        <v>118.5</v>
       </c>
       <c r="R45" s="7" t="str">
         <f t="shared" ref="R45:R116" si="21">IF(
@@ -4397,15 +4397,15 @@
         <v>4.09</v>
       </c>
       <c r="B46" s="9">
-        <v>888.0</v>
+        <v>1945.0</v>
       </c>
       <c r="C46" s="10">
         <f t="shared" si="2"/>
-        <v>1.772925922</v>
+        <v>2.17698214</v>
       </c>
       <c r="D46" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E46" s="10">
         <f t="shared" si="4"/>
@@ -4422,19 +4422,19 @@
       </c>
       <c r="I46" s="10">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J46" s="10">
         <f t="shared" si="6"/>
-        <v>0.545851845</v>
+        <v>0.3539642805</v>
       </c>
       <c r="K46" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L46" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="Q46" s="10">
         <f t="shared" si="20"/>
-        <v>124</v>
+        <v>118.5</v>
       </c>
       <c r="R46" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4481,15 +4481,15 @@
         <v>4.1</v>
       </c>
       <c r="B47" s="9">
-        <v>843.0</v>
+        <v>1917.0</v>
       </c>
       <c r="C47" s="10">
         <f t="shared" si="2"/>
-        <v>1.693250653</v>
+        <v>2.073623776</v>
       </c>
       <c r="D47" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E47" s="10">
         <f t="shared" si="4"/>
@@ -4506,19 +4506,19 @@
       </c>
       <c r="I47" s="10">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J47" s="10">
         <f t="shared" si="6"/>
-        <v>0.3865013066</v>
+        <v>0.1472475525</v>
       </c>
       <c r="K47" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L47" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="Q47" s="10">
         <f t="shared" si="20"/>
-        <v>96</v>
+        <v>92.5</v>
       </c>
       <c r="R47" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4565,15 +4565,15 @@
         <v>4.11</v>
       </c>
       <c r="B48" s="9">
-        <v>781.0</v>
+        <v>1917.0</v>
       </c>
       <c r="C48" s="10">
         <f t="shared" si="2"/>
-        <v>1.645132586</v>
+        <v>2.018877918</v>
       </c>
       <c r="D48" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E48" s="10">
         <f t="shared" si="4"/>
@@ -4590,19 +4590,19 @@
       </c>
       <c r="I48" s="10">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J48" s="10">
         <f t="shared" si="6"/>
-        <v>0.2902651724</v>
+        <v>0.03775583696</v>
       </c>
       <c r="K48" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L48" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M48" s="7"/>
       <c r="N48" s="7"/>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Q48" s="10">
         <f t="shared" si="20"/>
-        <v>86</v>
+        <v>81.5</v>
       </c>
       <c r="R48" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4649,15 +4649,15 @@
         <v>4.12</v>
       </c>
       <c r="B49" s="9">
-        <v>666.0</v>
+        <v>1916.0</v>
       </c>
       <c r="C49" s="10">
         <f t="shared" si="2"/>
-        <v>1.58462017</v>
+        <v>1.96801195</v>
       </c>
       <c r="D49" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E49" s="10">
         <f t="shared" si="4"/>
@@ -4678,15 +4678,15 @@
       </c>
       <c r="J49" s="10">
         <f t="shared" si="6"/>
-        <v>0.1692403406</v>
+        <v>0.9360239005</v>
       </c>
       <c r="K49" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L49" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M49" s="7"/>
       <c r="N49" s="7"/>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="Q49" s="10">
         <f t="shared" si="20"/>
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="R49" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4733,15 +4733,15 @@
         <v>5.01</v>
       </c>
       <c r="B50" s="9">
-        <v>637.0</v>
+        <v>1898.0</v>
       </c>
       <c r="C50" s="10">
         <f t="shared" si="2"/>
-        <v>2.558418166</v>
+        <v>2.916096396</v>
       </c>
       <c r="D50" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E50" s="10">
         <f t="shared" si="4"/>
@@ -4762,15 +4762,15 @@
       </c>
       <c r="J50" s="10">
         <f t="shared" si="6"/>
-        <v>0.1168363329</v>
+        <v>0.8321927929</v>
       </c>
       <c r="K50" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L50" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M50" s="7"/>
       <c r="N50" s="7"/>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="Q50" s="10">
         <f t="shared" si="20"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R50" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4817,15 +4817,15 @@
         <v>5.02</v>
       </c>
       <c r="B51" s="9">
-        <v>590.0</v>
+        <v>1872.0</v>
       </c>
       <c r="C51" s="10">
         <f t="shared" si="2"/>
-        <v>2.529760411</v>
+        <v>2.86640721</v>
       </c>
       <c r="D51" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E51" s="10">
         <f t="shared" si="4"/>
@@ -4846,15 +4846,15 @@
       </c>
       <c r="J51" s="10">
         <f t="shared" si="6"/>
-        <v>0.05952082165</v>
+        <v>0.7328144202</v>
       </c>
       <c r="K51" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L51" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M51" s="7"/>
       <c r="N51" s="7"/>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="Q51" s="10">
         <f t="shared" si="20"/>
-        <v>63</v>
+        <v>55.5</v>
       </c>
       <c r="R51" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4901,15 +4901,15 @@
         <v>5.03</v>
       </c>
       <c r="B52" s="9">
-        <v>552.0</v>
+        <v>1652.5</v>
       </c>
       <c r="C52" s="10">
         <f t="shared" si="2"/>
-        <v>2.506718485</v>
+        <v>2.772812932</v>
       </c>
       <c r="D52" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E52" s="10">
         <f t="shared" si="4"/>
@@ -4930,15 +4930,15 @@
       </c>
       <c r="J52" s="10">
         <f t="shared" si="6"/>
-        <v>0.01343696904</v>
+        <v>0.5456258645</v>
       </c>
       <c r="K52" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L52" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="Q52" s="10">
         <f t="shared" si="20"/>
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="R52" s="7" t="str">
         <f t="shared" si="21"/>
@@ -4985,15 +4985,15 @@
         <v>5.04</v>
       </c>
       <c r="B53" s="9">
-        <v>538.0</v>
+        <v>1421.0</v>
       </c>
       <c r="C53" s="10">
         <f t="shared" si="2"/>
-        <v>2.492079529</v>
+        <v>2.687849483</v>
       </c>
       <c r="D53" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E53" s="10">
         <f t="shared" si="4"/>
@@ -5010,19 +5010,19 @@
       </c>
       <c r="I53" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J53" s="10">
         <f t="shared" si="6"/>
-        <v>0.9841590581</v>
+        <v>0.3756989662</v>
       </c>
       <c r="K53" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L53" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M53" s="7"/>
       <c r="N53" s="7"/>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="Q53" s="10">
         <f t="shared" si="20"/>
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="R53" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5069,15 +5069,15 @@
         <v>5.05</v>
       </c>
       <c r="B54" s="9">
-        <v>486.0</v>
+        <v>1363.5</v>
       </c>
       <c r="C54" s="10">
         <f t="shared" si="2"/>
-        <v>2.470259875</v>
+        <v>2.650489878</v>
       </c>
       <c r="D54" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E54" s="10">
         <f t="shared" si="4"/>
@@ -5094,19 +5094,19 @@
       </c>
       <c r="I54" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J54" s="10">
         <f t="shared" si="6"/>
-        <v>0.9405197497</v>
+        <v>0.3009797558</v>
       </c>
       <c r="K54" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L54" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M54" s="7"/>
       <c r="N54" s="7"/>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="Q54" s="10">
         <f t="shared" si="20"/>
-        <v>44</v>
+        <v>44.5</v>
       </c>
       <c r="R54" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5153,15 +5153,15 @@
         <v>5.06</v>
       </c>
       <c r="B55" s="9">
-        <v>456.0</v>
+        <v>1630.0</v>
       </c>
       <c r="C55" s="10">
         <f t="shared" si="2"/>
-        <v>2.455596034</v>
+        <v>2.680510728</v>
       </c>
       <c r="D55" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E55" s="10">
         <f t="shared" si="4"/>
@@ -5178,19 +5178,19 @@
       </c>
       <c r="I55" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J55" s="10">
         <f t="shared" si="6"/>
-        <v>0.9111920678</v>
+        <v>0.3610214567</v>
       </c>
       <c r="K55" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L55" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="Q55" s="10">
         <f t="shared" si="20"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R55" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5237,15 +5237,15 @@
         <v>5.07</v>
       </c>
       <c r="B56" s="9">
-        <v>347.0</v>
+        <v>1345.0</v>
       </c>
       <c r="C56" s="10">
         <f t="shared" si="2"/>
-        <v>2.427359485</v>
+        <v>2.60431041</v>
       </c>
       <c r="D56" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E56" s="10">
         <f t="shared" si="4"/>
@@ -5262,19 +5262,19 @@
       </c>
       <c r="I56" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J56" s="10">
         <f t="shared" si="6"/>
-        <v>0.8547189693</v>
+        <v>0.2086208209</v>
       </c>
       <c r="K56" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L56" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M56" s="7"/>
       <c r="N56" s="7"/>
@@ -5321,15 +5321,15 @@
         <v>5.08</v>
       </c>
       <c r="B57" s="9">
-        <v>147.0</v>
+        <v>1585.0</v>
       </c>
       <c r="C57" s="10">
         <f t="shared" si="2"/>
-        <v>2.386761222</v>
+        <v>2.625718464</v>
       </c>
       <c r="D57" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E57" s="10">
         <f t="shared" si="4"/>
@@ -5346,19 +5346,19 @@
       </c>
       <c r="I57" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J57" s="10">
         <f t="shared" si="6"/>
-        <v>0.7735224443</v>
+        <v>0.2514369281</v>
       </c>
       <c r="K57" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L57" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M57" s="7"/>
       <c r="N57" s="7"/>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="Q57" s="10">
         <f t="shared" si="20"/>
-        <v>27</v>
+        <v>28.75</v>
       </c>
       <c r="R57" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5405,15 +5405,15 @@
         <v>5.09</v>
       </c>
       <c r="B58" s="9">
-        <v>146.0</v>
+        <v>1284.0</v>
       </c>
       <c r="C58" s="10">
         <f t="shared" si="2"/>
-        <v>2.384593582</v>
+        <v>2.558886836</v>
       </c>
       <c r="D58" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E58" s="10">
         <f t="shared" si="4"/>
@@ -5430,19 +5430,19 @@
       </c>
       <c r="I58" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J58" s="10">
         <f t="shared" si="6"/>
-        <v>0.7691871637</v>
+        <v>0.1177736719</v>
       </c>
       <c r="K58" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L58" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="Q58" s="10">
         <f t="shared" si="20"/>
-        <v>27</v>
+        <v>28.75</v>
       </c>
       <c r="R58" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5489,15 +5489,15 @@
         <v>5.1</v>
       </c>
       <c r="B59" s="9">
-        <v>1.0</v>
+        <v>1254.0</v>
       </c>
       <c r="C59" s="10">
         <f t="shared" si="2"/>
-        <v>2.360838683</v>
+        <v>2.539378636</v>
       </c>
       <c r="D59" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E59" s="10">
         <f t="shared" si="4"/>
@@ -5514,19 +5514,19 @@
       </c>
       <c r="I59" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J59" s="10">
         <f t="shared" si="6"/>
-        <v>0.7216773657</v>
+        <v>0.07875727148</v>
       </c>
       <c r="K59" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L59" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M59" s="7"/>
       <c r="N59" s="7"/>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="Q59" s="10">
         <f t="shared" si="20"/>
-        <v>23.5</v>
+        <v>26</v>
       </c>
       <c r="R59" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5573,15 +5573,15 @@
         <v>5.11</v>
       </c>
       <c r="B60" s="9">
-        <v>1.0</v>
+        <v>1253.0</v>
       </c>
       <c r="C60" s="10">
         <f t="shared" si="2"/>
-        <v>2.360827065</v>
+        <v>2.525512659</v>
       </c>
       <c r="D60" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E60" s="10">
         <f t="shared" si="4"/>
@@ -5598,19 +5598,19 @@
       </c>
       <c r="I60" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J60" s="10">
         <f t="shared" si="6"/>
-        <v>0.7216541297</v>
+        <v>0.05102531802</v>
       </c>
       <c r="K60" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L60" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M60" s="7"/>
       <c r="N60" s="7"/>
@@ -5624,7 +5624,7 @@
       </c>
       <c r="Q60" s="10">
         <f t="shared" si="20"/>
-        <v>21.5</v>
+        <v>24</v>
       </c>
       <c r="R60" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5657,15 +5657,15 @@
         <v>5.12</v>
       </c>
       <c r="B61" s="9">
-        <v>1.0</v>
+        <v>1251.0</v>
       </c>
       <c r="C61" s="10">
         <f t="shared" si="2"/>
-        <v>2.360816339</v>
+        <v>2.5126007</v>
       </c>
       <c r="D61" s="10">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E61" s="10">
         <f t="shared" si="4"/>
@@ -5682,19 +5682,19 @@
       </c>
       <c r="I61" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J61" s="10">
         <f t="shared" si="6"/>
-        <v>0.7216326789</v>
+        <v>0.02520140089</v>
       </c>
       <c r="K61" s="10">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L61" s="11">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M61" s="7"/>
       <c r="N61" s="7"/>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="Q61" s="10">
         <f t="shared" si="20"/>
-        <v>19</v>
+        <v>21.5</v>
       </c>
       <c r="R61" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5741,11 +5741,11 @@
         <v>6.01</v>
       </c>
       <c r="B62" s="9">
-        <v>1.0</v>
+        <v>1251.0</v>
       </c>
       <c r="C62" s="10">
         <f t="shared" si="2"/>
-        <v>1.000118911</v>
+        <v>1.140236203</v>
       </c>
       <c r="D62" s="10">
         <f t="shared" si="3"/>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="J62" s="10">
         <f t="shared" si="6"/>
-        <v>0.0002378213096</v>
+        <v>0.2804724066</v>
       </c>
       <c r="K62" s="10">
         <f t="shared" si="10"/>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="Q62" s="10">
         <f t="shared" si="20"/>
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="R62" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5829,11 +5829,11 @@
         <v>6.02</v>
       </c>
       <c r="B63" s="9">
-        <v>1.0</v>
+        <v>1250.0</v>
       </c>
       <c r="C63" s="10">
         <f t="shared" si="2"/>
-        <v>1.00010977</v>
+        <v>1.129353035</v>
       </c>
       <c r="D63" s="10">
         <f t="shared" si="3"/>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="J63" s="10">
         <f t="shared" si="6"/>
-        <v>0.0002195404458</v>
+        <v>0.2587060706</v>
       </c>
       <c r="K63" s="10">
         <f t="shared" si="10"/>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="Q63" s="10">
         <f t="shared" si="20"/>
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="R63" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="U63" s="10">
         <f t="shared" ref="U63:U74" si="22">SUMIF($R$45:$R$116, T63, $Q$45:$Q$116)</f>
-        <v>374</v>
+        <v>377.25</v>
       </c>
       <c r="V63" s="13">
         <v>3.0</v>
@@ -5918,11 +5918,11 @@
         <v>6.03</v>
       </c>
       <c r="B64" s="9">
-        <v>1.0</v>
+        <v>1249.0</v>
       </c>
       <c r="C64" s="10">
         <f t="shared" si="2"/>
-        <v>1.000101332</v>
+        <v>1.119314162</v>
       </c>
       <c r="D64" s="10">
         <f t="shared" si="3"/>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="J64" s="10">
         <f t="shared" si="6"/>
-        <v>0.0002026644095</v>
+        <v>0.238628324</v>
       </c>
       <c r="K64" s="10">
         <f t="shared" si="10"/>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="Q64" s="10">
         <f t="shared" si="20"/>
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="R64" s="7" t="str">
         <f t="shared" si="21"/>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="U64" s="10">
         <f t="shared" si="22"/>
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="V64" s="12">
         <v>4.0</v>
@@ -6007,11 +6007,11 @@
         <v>6.04</v>
       </c>
       <c r="B65" s="9">
-        <v>1.0</v>
+        <v>1246.0</v>
       </c>
       <c r="C65" s="10">
         <f t="shared" si="2"/>
-        <v>1.000093543</v>
+        <v>1.109877763</v>
       </c>
       <c r="D65" s="10">
         <f t="shared" si="3"/>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="J65" s="10">
         <f t="shared" si="6"/>
-        <v>0.0001870853144</v>
+        <v>0.2197555263</v>
       </c>
       <c r="K65" s="10">
         <f t="shared" si="10"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="Q65" s="10">
         <f t="shared" si="20"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R65" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="U65" s="10">
         <f t="shared" si="22"/>
-        <v>159.5</v>
+        <v>152.5</v>
       </c>
       <c r="V65" s="13">
         <v>6.0</v>
@@ -6096,11 +6096,11 @@
         <v>6.05</v>
       </c>
       <c r="B66" s="9">
-        <v>1.0</v>
+        <v>1245.0</v>
       </c>
       <c r="C66" s="10">
         <f t="shared" si="2"/>
-        <v>1.000086352</v>
+        <v>1.101349749</v>
       </c>
       <c r="D66" s="10">
         <f t="shared" si="3"/>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="J66" s="10">
         <f t="shared" si="6"/>
-        <v>0.0001727035465</v>
+        <v>0.2026994977</v>
       </c>
       <c r="K66" s="10">
         <f t="shared" si="10"/>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="Q66" s="10">
         <f t="shared" si="20"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R66" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="U66" s="10">
         <f t="shared" si="22"/>
-        <v>148.5</v>
+        <v>149</v>
       </c>
       <c r="V66" s="14">
         <v>6.0</v>
@@ -6185,11 +6185,11 @@
         <v>6.06</v>
       </c>
       <c r="B67" s="9">
-        <v>1.0</v>
+        <v>1244.0</v>
       </c>
       <c r="C67" s="10">
         <f t="shared" si="2"/>
-        <v>1.000079714</v>
+        <v>1.09348344</v>
       </c>
       <c r="D67" s="10">
         <f t="shared" si="3"/>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="J67" s="10">
         <f t="shared" si="6"/>
-        <v>0.0001594271327</v>
+        <v>0.1869668799</v>
       </c>
       <c r="K67" s="10">
         <f t="shared" si="10"/>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="U67" s="10">
         <f t="shared" si="22"/>
-        <v>138.5</v>
+        <v>141.5</v>
       </c>
       <c r="V67" s="14">
         <v>3.0</v>
@@ -6274,11 +6274,11 @@
         <v>6.07</v>
       </c>
       <c r="B68" s="9">
-        <v>1.0</v>
+        <v>1243.0</v>
       </c>
       <c r="C68" s="10">
         <f t="shared" si="2"/>
-        <v>1.000073586</v>
+        <v>1.086227521</v>
       </c>
       <c r="D68" s="10">
         <f t="shared" si="3"/>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="J68" s="10">
         <f t="shared" si="6"/>
-        <v>0.0001471711561</v>
+        <v>0.1724550416</v>
       </c>
       <c r="K68" s="10">
         <f t="shared" si="10"/>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="U68" s="10">
         <f t="shared" si="22"/>
-        <v>68.5</v>
+        <v>62</v>
       </c>
       <c r="V68" s="14"/>
       <c r="W68" s="13"/>
@@ -6357,11 +6357,11 @@
         <v>6.08</v>
       </c>
       <c r="B69" s="13">
-        <v>1.0</v>
+        <v>1242.0</v>
       </c>
       <c r="C69" s="10">
         <f t="shared" si="2"/>
-        <v>1.000067929</v>
+        <v>1.079534651</v>
       </c>
       <c r="D69" s="10">
         <f t="shared" si="3"/>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="J69" s="10">
         <f t="shared" si="6"/>
-        <v>0.0001358572166</v>
+        <v>0.1590693013</v>
       </c>
       <c r="K69" s="10">
         <f t="shared" si="10"/>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="Q69" s="10">
         <f t="shared" si="20"/>
-        <v>8.75</v>
+        <v>9.25</v>
       </c>
       <c r="R69" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="U69" s="10">
         <f t="shared" si="22"/>
-        <v>62.5</v>
+        <v>65.5</v>
       </c>
       <c r="V69" s="12"/>
       <c r="W69" s="12"/>
@@ -6440,11 +6440,11 @@
         <v>6.09</v>
       </c>
       <c r="B70" s="9">
-        <v>1.0</v>
+        <v>1221.0</v>
       </c>
       <c r="C70" s="10">
         <f t="shared" si="2"/>
-        <v>1.000062706</v>
+        <v>1.072178866</v>
       </c>
       <c r="D70" s="10">
         <f t="shared" si="3"/>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="J70" s="10">
         <f t="shared" si="6"/>
-        <v>0.0001254129316</v>
+        <v>0.1443577315</v>
       </c>
       <c r="K70" s="10">
         <f t="shared" si="10"/>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="Q70" s="10">
         <f t="shared" si="20"/>
-        <v>8.75</v>
+        <v>9.25</v>
       </c>
       <c r="R70" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="U70" s="10">
         <f t="shared" si="22"/>
-        <v>52.5</v>
+        <v>54</v>
       </c>
       <c r="V70" s="3"/>
       <c r="W70" s="3"/>
@@ -6523,11 +6523,11 @@
         <v>6.1</v>
       </c>
       <c r="B71" s="9">
-        <v>1.0</v>
+        <v>1190.0</v>
       </c>
       <c r="C71" s="10">
         <f t="shared" si="2"/>
-        <v>1.000057886</v>
+        <v>1.064938253</v>
       </c>
       <c r="D71" s="10">
         <f t="shared" si="3"/>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="J71" s="10">
         <f t="shared" si="6"/>
-        <v>0.0001157714757</v>
+        <v>0.1298765057</v>
       </c>
       <c r="K71" s="10">
         <f t="shared" si="10"/>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="Q71" s="10">
         <f t="shared" si="20"/>
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="R71" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="U71" s="10">
         <f t="shared" si="22"/>
-        <v>18</v>
+        <v>20.75</v>
       </c>
       <c r="V71" s="3"/>
       <c r="W71" s="3"/>
@@ -6606,11 +6606,11 @@
         <v>6.11</v>
       </c>
       <c r="B72" s="13">
-        <v>1.0</v>
+        <v>1163.0</v>
       </c>
       <c r="C72" s="10">
         <f t="shared" si="2"/>
-        <v>1.000053436</v>
+        <v>1.058585789</v>
       </c>
       <c r="D72" s="10">
         <f t="shared" si="3"/>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="J72" s="10">
         <f t="shared" si="6"/>
-        <v>0.0001068711545</v>
+        <v>0.1171715785</v>
       </c>
       <c r="K72" s="10">
         <f t="shared" si="10"/>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="U72" s="10">
         <f t="shared" si="22"/>
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="V72" s="3"/>
       <c r="W72" s="3"/>
@@ -6689,11 +6689,11 @@
         <v>6.12</v>
       </c>
       <c r="B73" s="9">
-        <v>1.0</v>
+        <v>1154.0</v>
       </c>
       <c r="C73" s="10">
         <f t="shared" si="2"/>
-        <v>1.000049328</v>
+        <v>1.053663257</v>
       </c>
       <c r="D73" s="10">
         <f t="shared" si="3"/>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="J73" s="10">
         <f t="shared" si="6"/>
-        <v>0.00009865501143</v>
+        <v>0.1073265144</v>
       </c>
       <c r="K73" s="10">
         <f t="shared" si="10"/>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="Q73" s="10">
         <f t="shared" si="20"/>
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="R73" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6769,6 +6769,9 @@
     </row>
     <row r="74">
       <c r="A74" s="3"/>
+      <c r="B74" s="9">
+        <v>1088.0</v>
+      </c>
       <c r="C74" s="3"/>
       <c r="D74" s="10">
         <f>Sum(D2:D73)</f>
@@ -6803,7 +6806,7 @@
       </c>
       <c r="Q74" s="10">
         <f t="shared" si="20"/>
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="R74" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6832,7 +6835,9 @@
     </row>
     <row r="75">
       <c r="A75" s="3"/>
-      <c r="B75" s="13"/>
+      <c r="B75" s="13">
+        <v>1052.0</v>
+      </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -6855,7 +6860,7 @@
       </c>
       <c r="Q75" s="10">
         <f t="shared" si="20"/>
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R75" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6882,6 +6887,9 @@
     </row>
     <row r="76">
       <c r="A76" s="3"/>
+      <c r="B76" s="9">
+        <v>953.5</v>
+      </c>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -6904,7 +6912,7 @@
       </c>
       <c r="Q76" s="10">
         <f t="shared" si="20"/>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="R76" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6928,7 +6936,9 @@
     </row>
     <row r="77">
       <c r="A77" s="3"/>
-      <c r="B77" s="13"/>
+      <c r="B77" s="13">
+        <v>997.0</v>
+      </c>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -6951,7 +6961,7 @@
       </c>
       <c r="Q77" s="10">
         <f t="shared" si="20"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R77" s="7" t="str">
         <f t="shared" si="21"/>
@@ -6975,7 +6985,9 @@
     </row>
     <row r="78">
       <c r="A78" s="3"/>
-      <c r="B78" s="13"/>
+      <c r="B78" s="13">
+        <v>832.0</v>
+      </c>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -6998,7 +7010,7 @@
       </c>
       <c r="Q78" s="10">
         <f t="shared" si="20"/>
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R78" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7022,7 +7034,9 @@
     </row>
     <row r="79">
       <c r="A79" s="3"/>
-      <c r="B79" s="13"/>
+      <c r="B79" s="13">
+        <v>848.0</v>
+      </c>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -7045,7 +7059,7 @@
       </c>
       <c r="Q79" s="10">
         <f t="shared" si="20"/>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R79" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7069,7 +7083,9 @@
     </row>
     <row r="80">
       <c r="A80" s="3"/>
-      <c r="B80" s="13"/>
+      <c r="B80" s="13">
+        <v>872.0</v>
+      </c>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -7092,7 +7108,7 @@
       </c>
       <c r="Q80" s="10">
         <f t="shared" si="20"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R80" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7116,7 +7132,9 @@
     </row>
     <row r="81">
       <c r="A81" s="3"/>
-      <c r="B81" s="13"/>
+      <c r="B81" s="13">
+        <v>861.0</v>
+      </c>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -7139,7 +7157,7 @@
       </c>
       <c r="Q81" s="10">
         <f t="shared" si="20"/>
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="R81" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7163,7 +7181,9 @@
     </row>
     <row r="82">
       <c r="A82" s="3"/>
-      <c r="B82" s="13"/>
+      <c r="B82" s="13">
+        <v>812.5</v>
+      </c>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -7186,7 +7206,7 @@
       </c>
       <c r="Q82" s="10">
         <f t="shared" si="20"/>
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="R82" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7207,7 +7227,9 @@
     </row>
     <row r="83">
       <c r="A83" s="7"/>
-      <c r="B83" s="13"/>
+      <c r="B83" s="13">
+        <v>829.0</v>
+      </c>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -7230,7 +7252,7 @@
       </c>
       <c r="Q83" s="10">
         <f t="shared" si="20"/>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R83" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7251,7 +7273,9 @@
     </row>
     <row r="84">
       <c r="A84" s="7"/>
-      <c r="B84" s="13"/>
+      <c r="B84" s="13">
+        <v>820.0</v>
+      </c>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -7274,7 +7298,7 @@
       </c>
       <c r="Q84" s="10">
         <f t="shared" si="20"/>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R84" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7295,6 +7319,9 @@
     </row>
     <row r="85">
       <c r="A85" s="7"/>
+      <c r="B85" s="9">
+        <v>680.5</v>
+      </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -7317,7 +7344,7 @@
       </c>
       <c r="Q85" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R85" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7338,7 +7365,9 @@
     </row>
     <row r="86">
       <c r="A86" s="7"/>
-      <c r="B86" s="13"/>
+      <c r="B86" s="13">
+        <v>709.0</v>
+      </c>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -7361,7 +7390,7 @@
       </c>
       <c r="Q86" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="R86" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7405,7 +7434,7 @@
       </c>
       <c r="Q87" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="R87" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7449,7 +7478,7 @@
       </c>
       <c r="Q88" s="10">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="R88" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7493,7 +7522,7 @@
       </c>
       <c r="Q89" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R89" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7537,7 +7566,7 @@
       </c>
       <c r="Q90" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R90" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7581,7 +7610,7 @@
       </c>
       <c r="Q91" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R91" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7625,7 +7654,7 @@
       </c>
       <c r="Q92" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R92" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7669,7 +7698,7 @@
       </c>
       <c r="Q93" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R93" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7713,7 +7742,7 @@
       </c>
       <c r="Q94" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R94" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7757,7 +7786,7 @@
       </c>
       <c r="Q95" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R95" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7801,7 +7830,7 @@
       </c>
       <c r="Q96" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R96" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7845,7 +7874,7 @@
       </c>
       <c r="Q97" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R97" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7889,7 +7918,7 @@
       </c>
       <c r="Q98" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R98" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7933,7 +7962,7 @@
       </c>
       <c r="Q99" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R99" s="7" t="str">
         <f t="shared" si="21"/>
@@ -7977,7 +8006,7 @@
       </c>
       <c r="Q100" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R100" s="7" t="str">
         <f t="shared" si="21"/>
@@ -8021,7 +8050,7 @@
       </c>
       <c r="Q101" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R101" s="7" t="str">
         <f t="shared" si="21"/>
@@ -8065,7 +8094,7 @@
       </c>
       <c r="Q102" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R102" s="7" t="str">
         <f t="shared" si="21"/>
@@ -8109,7 +8138,7 @@
       </c>
       <c r="Q103" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R103" s="7" t="str">
         <f t="shared" si="21"/>
@@ -8153,7 +8182,7 @@
       </c>
       <c r="Q104" s="10">
         <f t="shared" si="20"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R104" s="7" t="str">
         <f t="shared" si="21"/>
@@ -8916,7 +8945,7 @@
      )
      &lt;= 1200 - SUMPRODUCT(ROUNDDOWN($C$2:$C$73,0)) )
 </f>
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="N123" s="7"/>
       <c r="O123" s="7"/>
@@ -37727,7 +37756,7 @@
       </c>
       <c r="G2" s="17">
         <f t="shared" ref="G2:G73" si="2">IF($D2&gt;0,"",MIN($L$8, $C2*$L$14*(1+($L$11-1)*$L$16)))</f>
-        <v>188.7976755</v>
+        <v>189.5873838</v>
       </c>
       <c r="H2" s="20">
         <f t="shared" ref="H2:H73" si="3">IF($D2&lt;&gt;"","",
@@ -37781,7 +37810,7 @@
       </c>
       <c r="G3" s="17">
         <f t="shared" si="2"/>
-        <v>144.6543341</v>
+        <v>145.2593984</v>
       </c>
       <c r="H3" s="20">
         <f t="shared" si="3"/>
@@ -37823,7 +37852,7 @@
       </c>
       <c r="G4" s="17">
         <f t="shared" si="2"/>
-        <v>126.3178692</v>
+        <v>126.8462352</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" si="3"/>
@@ -37838,7 +37867,7 @@
       </c>
       <c r="L4" s="19">
         <f>'Draft Data'!U63</f>
-        <v>374</v>
+        <v>377.25</v>
       </c>
     </row>
     <row r="5">
@@ -37860,7 +37889,7 @@
       </c>
       <c r="G5" s="17">
         <f t="shared" si="2"/>
-        <v>112.0561743</v>
+        <v>112.5248861</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="3"/>
@@ -37898,7 +37927,7 @@
       </c>
       <c r="G6" s="17">
         <f t="shared" si="2"/>
-        <v>103.2275061</v>
+        <v>103.659289</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="3"/>
@@ -37936,7 +37965,7 @@
       </c>
       <c r="G7" s="17">
         <f t="shared" si="2"/>
-        <v>90.3240678</v>
+        <v>90.70187785</v>
       </c>
       <c r="H7" s="20">
         <f t="shared" si="3"/>
@@ -37973,7 +38002,7 @@
       </c>
       <c r="G8" s="17">
         <f t="shared" si="2"/>
-        <v>78.09975787</v>
+        <v>78.42643573</v>
       </c>
       <c r="H8" s="20">
         <f t="shared" si="3"/>
@@ -37989,7 +38018,7 @@
       <c r="L8" s="17">
         <f>L4-L7
 </f>
-        <v>374</v>
+        <v>377.25</v>
       </c>
     </row>
     <row r="9">
@@ -38011,7 +38040,7 @@
       </c>
       <c r="G9" s="17">
         <f t="shared" si="2"/>
-        <v>71.98760291</v>
+        <v>72.28871468</v>
       </c>
       <c r="H9" s="20">
         <f t="shared" si="3"/>
@@ -38027,7 +38056,7 @@
       <c r="L9" s="17">
         <f>L6-L8
 </f>
-        <v>826</v>
+        <v>822.75</v>
       </c>
     </row>
     <row r="10">
@@ -38049,7 +38078,7 @@
       </c>
       <c r="G10" s="17">
         <f t="shared" si="2"/>
-        <v>65.19631961</v>
+        <v>65.46902461</v>
       </c>
       <c r="H10" s="20">
         <f t="shared" si="3"/>
@@ -38064,7 +38093,7 @@
       </c>
       <c r="L10" s="17">
         <f>IF(L3&gt;1,L9/(L3-1),0)</f>
-        <v>75.09090909</v>
+        <v>74.79545455</v>
       </c>
     </row>
     <row r="11">
@@ -38086,7 +38115,7 @@
       </c>
       <c r="G11" s="17">
         <f t="shared" si="2"/>
-        <v>58.40503632</v>
+        <v>58.64933455</v>
       </c>
       <c r="H11" s="20">
         <f t="shared" si="3"/>
@@ -38101,7 +38130,7 @@
       </c>
       <c r="L11" s="23">
         <f>IF(L10&gt;0,L8/L10,1)</f>
-        <v>4.98062954</v>
+        <v>5.043755697</v>
       </c>
     </row>
     <row r="12">
@@ -38123,7 +38152,7 @@
       </c>
       <c r="G12" s="17">
         <f t="shared" si="2"/>
-        <v>52.97200969</v>
+        <v>53.1935825</v>
       </c>
       <c r="H12" s="20">
         <f t="shared" si="3"/>
@@ -38153,7 +38182,7 @@
       </c>
       <c r="G13" s="17">
         <f t="shared" si="2"/>
-        <v>46.18072639</v>
+        <v>46.37389243</v>
       </c>
       <c r="H13" s="20">
         <f t="shared" si="3"/>
@@ -38190,7 +38219,7 @@
       </c>
       <c r="G14" s="17">
         <f t="shared" si="2"/>
-        <v>41.42682809</v>
+        <v>41.60010939</v>
       </c>
       <c r="H14" s="20">
         <f t="shared" si="3"/>
@@ -38227,7 +38256,7 @@
       </c>
       <c r="G15" s="17">
         <f t="shared" si="2"/>
-        <v>37.35205811</v>
+        <v>37.50829535</v>
       </c>
       <c r="H15" s="20">
         <f t="shared" si="3"/>
@@ -38257,7 +38286,7 @@
       </c>
       <c r="G16" s="17">
         <f t="shared" si="2"/>
-        <v>34.63554479</v>
+        <v>34.78041933</v>
       </c>
       <c r="H16" s="20">
         <f t="shared" si="3"/>
@@ -38304,7 +38333,7 @@
       </c>
       <c r="G17" s="17">
         <f t="shared" si="2"/>
-        <v>30.56077482</v>
+        <v>30.68860529</v>
       </c>
       <c r="H17" s="20">
         <f t="shared" si="3"/>
@@ -38334,7 +38363,7 @@
       </c>
       <c r="G18" s="17">
         <f t="shared" si="2"/>
-        <v>27.16513317</v>
+        <v>27.27876026</v>
       </c>
       <c r="H18" s="20">
         <f t="shared" si="3"/>
@@ -38371,7 +38400,7 @@
       </c>
       <c r="G19" s="17">
         <f t="shared" si="2"/>
-        <v>25.12774818</v>
+        <v>25.23285324</v>
       </c>
       <c r="H19" s="20">
         <f t="shared" si="3"/>
@@ -38401,7 +38430,7 @@
       </c>
       <c r="G20" s="17">
         <f t="shared" si="2"/>
-        <v>22.41123487</v>
+        <v>22.50497721</v>
       </c>
       <c r="H20" s="20">
         <f t="shared" si="3"/>
@@ -38431,7 +38460,7 @@
       </c>
       <c r="G21" s="17">
         <f t="shared" si="2"/>
-        <v>19.69472155</v>
+        <v>19.77710119</v>
       </c>
       <c r="H21" s="20">
         <f t="shared" si="3"/>
@@ -38461,7 +38490,7 @@
       </c>
       <c r="G22" s="17">
         <f t="shared" si="2"/>
-        <v>18.33646489</v>
+        <v>18.41316317</v>
       </c>
       <c r="H22" s="20">
         <f t="shared" si="3"/>
@@ -38491,7 +38520,7 @@
       </c>
       <c r="G23" s="17">
         <f t="shared" si="2"/>
-        <v>16.2990799</v>
+        <v>16.36725615</v>
       </c>
       <c r="H23" s="20">
         <f t="shared" si="3"/>
@@ -38521,7 +38550,7 @@
       </c>
       <c r="G24" s="17">
         <f t="shared" si="2"/>
-        <v>14.94082324</v>
+        <v>15.00331814</v>
       </c>
       <c r="H24" s="20">
         <f t="shared" si="3"/>
@@ -38551,7 +38580,7 @@
       </c>
       <c r="G25" s="17">
         <f t="shared" si="2"/>
-        <v>13.58256659</v>
+        <v>13.63938013</v>
       </c>
       <c r="H25" s="20">
         <f t="shared" si="3"/>
@@ -38581,7 +38610,7 @@
       </c>
       <c r="G26" s="17">
         <f t="shared" si="2"/>
-        <v>12.90343826</v>
+        <v>12.95741112</v>
       </c>
       <c r="H26" s="20">
         <f t="shared" si="3"/>
@@ -38611,7 +38640,7 @@
       </c>
       <c r="G27" s="17">
         <f t="shared" si="2"/>
-        <v>11.5451816</v>
+        <v>11.59347311</v>
       </c>
       <c r="H27" s="20">
         <f t="shared" si="3"/>
@@ -38647,7 +38676,7 @@
       </c>
       <c r="G28" s="17">
         <f t="shared" si="2"/>
-        <v>10.86605327</v>
+        <v>10.9115041</v>
       </c>
       <c r="H28" s="20">
         <f t="shared" si="3"/>
@@ -38677,7 +38706,7 @@
       </c>
       <c r="G29" s="17">
         <f t="shared" si="2"/>
-        <v>9.50779661</v>
+        <v>9.547566089</v>
       </c>
       <c r="H29" s="20">
         <f t="shared" si="3"/>
@@ -38707,7 +38736,7 @@
       </c>
       <c r="G30" s="17">
         <f t="shared" si="2"/>
-        <v>8.828668281</v>
+        <v>8.865597083</v>
       </c>
       <c r="H30" s="20">
         <f t="shared" si="3"/>
@@ -38737,7 +38766,7 @@
       </c>
       <c r="G31" s="17">
         <f t="shared" si="2"/>
-        <v>8.149539952</v>
+        <v>8.183628077</v>
       </c>
       <c r="H31" s="20">
         <f t="shared" si="3"/>
@@ -38767,7 +38796,7 @@
       </c>
       <c r="G32" s="17">
         <f t="shared" si="2"/>
-        <v>7.470411622</v>
+        <v>7.50165907</v>
       </c>
       <c r="H32" s="20">
         <f t="shared" si="3"/>
@@ -38797,7 +38826,7 @@
       </c>
       <c r="G33" s="17">
         <f t="shared" si="2"/>
-        <v>6.791283293</v>
+        <v>6.819690064</v>
       </c>
       <c r="H33" s="20">
         <f t="shared" si="3"/>
@@ -38827,7 +38856,7 @@
       </c>
       <c r="G34" s="17">
         <f t="shared" si="2"/>
-        <v>6.112154964</v>
+        <v>6.137721057</v>
       </c>
       <c r="H34" s="20">
         <f t="shared" si="3"/>
@@ -38857,7 +38886,7 @@
       </c>
       <c r="G35" s="17">
         <f t="shared" si="2"/>
-        <v>6.112154964</v>
+        <v>6.137721057</v>
       </c>
       <c r="H35" s="20">
         <f t="shared" si="3"/>
@@ -38887,7 +38916,7 @@
       </c>
       <c r="G36" s="17">
         <f t="shared" si="2"/>
-        <v>5.433026634</v>
+        <v>5.455752051</v>
       </c>
       <c r="H36" s="20">
         <f t="shared" si="3"/>
@@ -38917,7 +38946,7 @@
       </c>
       <c r="G37" s="17">
         <f t="shared" si="2"/>
-        <v>5.433026634</v>
+        <v>5.455752051</v>
       </c>
       <c r="H37" s="20">
         <f t="shared" si="3"/>
@@ -38947,7 +38976,7 @@
       </c>
       <c r="G38" s="17">
         <f t="shared" si="2"/>
-        <v>4.753898305</v>
+        <v>4.773783045</v>
       </c>
       <c r="H38" s="20">
         <f t="shared" si="3"/>
@@ -38977,7 +39006,7 @@
       </c>
       <c r="G39" s="17">
         <f t="shared" si="2"/>
-        <v>4.753898305</v>
+        <v>4.773783045</v>
       </c>
       <c r="H39" s="20">
         <f t="shared" si="3"/>
@@ -39007,7 +39036,7 @@
       </c>
       <c r="G40" s="17">
         <f t="shared" si="2"/>
-        <v>4.074769976</v>
+        <v>4.091814038</v>
       </c>
       <c r="H40" s="20">
         <f t="shared" si="3"/>
@@ -39037,7 +39066,7 @@
       </c>
       <c r="G41" s="17">
         <f t="shared" si="2"/>
-        <v>4.074769976</v>
+        <v>4.091814038</v>
       </c>
       <c r="H41" s="20">
         <f t="shared" si="3"/>
@@ -39067,7 +39096,7 @@
       </c>
       <c r="G42" s="17">
         <f t="shared" si="2"/>
-        <v>3.395641646</v>
+        <v>3.409845032</v>
       </c>
       <c r="H42" s="20">
         <f t="shared" si="3"/>
@@ -39097,7 +39126,7 @@
       </c>
       <c r="G43" s="17">
         <f t="shared" si="2"/>
-        <v>3.395641646</v>
+        <v>3.409845032</v>
       </c>
       <c r="H43" s="20">
         <f t="shared" si="3"/>
@@ -39127,7 +39156,7 @@
       </c>
       <c r="G44" s="17">
         <f t="shared" si="2"/>
-        <v>3.395641646</v>
+        <v>3.409845032</v>
       </c>
       <c r="H44" s="20">
         <f t="shared" si="3"/>
@@ -39157,7 +39186,7 @@
       </c>
       <c r="G45" s="17">
         <f t="shared" si="2"/>
-        <v>3.395641646</v>
+        <v>3.409845032</v>
       </c>
       <c r="H45" s="20">
         <f t="shared" si="3"/>
@@ -39187,7 +39216,7 @@
       </c>
       <c r="G46" s="17">
         <f t="shared" si="2"/>
-        <v>2.716513317</v>
+        <v>2.727876026</v>
       </c>
       <c r="H46" s="20">
         <f t="shared" si="3"/>
@@ -39217,7 +39246,7 @@
       </c>
       <c r="G47" s="17">
         <f t="shared" si="2"/>
-        <v>2.716513317</v>
+        <v>2.727876026</v>
       </c>
       <c r="H47" s="20">
         <f t="shared" si="3"/>
@@ -39247,7 +39276,7 @@
       </c>
       <c r="G48" s="17">
         <f t="shared" si="2"/>
-        <v>2.716513317</v>
+        <v>2.727876026</v>
       </c>
       <c r="H48" s="20">
         <f t="shared" si="3"/>
@@ -39277,7 +39306,7 @@
       </c>
       <c r="G49" s="17">
         <f t="shared" si="2"/>
-        <v>2.716513317</v>
+        <v>2.727876026</v>
       </c>
       <c r="H49" s="20">
         <f t="shared" si="3"/>
@@ -39307,7 +39336,7 @@
       </c>
       <c r="G50" s="17">
         <f t="shared" si="2"/>
-        <v>2.716513317</v>
+        <v>2.727876026</v>
       </c>
       <c r="H50" s="20">
         <f t="shared" si="3"/>
@@ -39337,7 +39366,7 @@
       </c>
       <c r="G51" s="17">
         <f t="shared" si="2"/>
-        <v>2.716513317</v>
+        <v>2.727876026</v>
       </c>
       <c r="H51" s="20">
         <f t="shared" si="3"/>
@@ -39367,7 +39396,7 @@
       </c>
       <c r="G52" s="17">
         <f t="shared" si="2"/>
-        <v>2.716513317</v>
+        <v>2.727876026</v>
       </c>
       <c r="H52" s="20">
         <f t="shared" si="3"/>
@@ -39397,7 +39426,7 @@
       </c>
       <c r="G53" s="17">
         <f t="shared" si="2"/>
-        <v>2.716513317</v>
+        <v>2.727876026</v>
       </c>
       <c r="H53" s="20">
         <f t="shared" si="3"/>
@@ -39427,7 +39456,7 @@
       </c>
       <c r="G54" s="17">
         <f t="shared" si="2"/>
-        <v>2.716513317</v>
+        <v>2.727876026</v>
       </c>
       <c r="H54" s="20">
         <f t="shared" si="3"/>
@@ -39457,7 +39486,7 @@
       </c>
       <c r="G55" s="17">
         <f t="shared" si="2"/>
-        <v>2.716513317</v>
+        <v>2.727876026</v>
       </c>
       <c r="H55" s="20">
         <f t="shared" si="3"/>
@@ -39487,7 +39516,7 @@
       </c>
       <c r="G56" s="17">
         <f t="shared" si="2"/>
-        <v>2.716513317</v>
+        <v>2.727876026</v>
       </c>
       <c r="H56" s="20">
         <f t="shared" si="3"/>
@@ -39517,7 +39546,7 @@
       </c>
       <c r="G57" s="17">
         <f t="shared" si="2"/>
-        <v>2.716513317</v>
+        <v>2.727876026</v>
       </c>
       <c r="H57" s="20">
         <f t="shared" si="3"/>
@@ -39547,7 +39576,7 @@
       </c>
       <c r="G58" s="17">
         <f t="shared" si="2"/>
-        <v>2.716513317</v>
+        <v>2.727876026</v>
       </c>
       <c r="H58" s="20">
         <f t="shared" si="3"/>
@@ -39577,7 +39606,7 @@
       </c>
       <c r="G59" s="17">
         <f t="shared" si="2"/>
-        <v>2.716513317</v>
+        <v>2.727876026</v>
       </c>
       <c r="H59" s="20">
         <f t="shared" si="3"/>
@@ -39607,7 +39636,7 @@
       </c>
       <c r="G60" s="17">
         <f t="shared" si="2"/>
-        <v>2.716513317</v>
+        <v>2.727876026</v>
       </c>
       <c r="H60" s="20">
         <f t="shared" si="3"/>
@@ -39637,7 +39666,7 @@
       </c>
       <c r="G61" s="17">
         <f t="shared" si="2"/>
-        <v>2.716513317</v>
+        <v>2.727876026</v>
       </c>
       <c r="H61" s="20">
         <f t="shared" si="3"/>
@@ -39667,7 +39696,7 @@
       </c>
       <c r="G62" s="17">
         <f t="shared" si="2"/>
-        <v>1.358256659</v>
+        <v>1.363938013</v>
       </c>
       <c r="H62" s="20">
         <f t="shared" si="3"/>
@@ -39697,7 +39726,7 @@
       </c>
       <c r="G63" s="17">
         <f t="shared" si="2"/>
-        <v>1.358256659</v>
+        <v>1.363938013</v>
       </c>
       <c r="H63" s="20">
         <f t="shared" si="3"/>
@@ -39727,7 +39756,7 @@
       </c>
       <c r="G64" s="17">
         <f t="shared" si="2"/>
-        <v>1.358256659</v>
+        <v>1.363938013</v>
       </c>
       <c r="H64" s="20">
         <f t="shared" si="3"/>
@@ -39757,7 +39786,7 @@
       </c>
       <c r="G65" s="17">
         <f t="shared" si="2"/>
-        <v>1.358256659</v>
+        <v>1.363938013</v>
       </c>
       <c r="H65" s="20">
         <f t="shared" si="3"/>
@@ -39787,7 +39816,7 @@
       </c>
       <c r="G66" s="17">
         <f t="shared" si="2"/>
-        <v>1.358256659</v>
+        <v>1.363938013</v>
       </c>
       <c r="H66" s="20">
         <f t="shared" si="3"/>
@@ -39817,7 +39846,7 @@
       </c>
       <c r="G67" s="17">
         <f t="shared" si="2"/>
-        <v>1.358256659</v>
+        <v>1.363938013</v>
       </c>
       <c r="H67" s="20">
         <f t="shared" si="3"/>
@@ -39847,7 +39876,7 @@
       </c>
       <c r="G68" s="17">
         <f t="shared" si="2"/>
-        <v>1.358256659</v>
+        <v>1.363938013</v>
       </c>
       <c r="H68" s="20">
         <f t="shared" si="3"/>
@@ -39877,7 +39906,7 @@
       </c>
       <c r="G69" s="17">
         <f t="shared" si="2"/>
-        <v>1.358256659</v>
+        <v>1.363938013</v>
       </c>
       <c r="H69" s="20">
         <f t="shared" si="3"/>
@@ -39907,7 +39936,7 @@
       </c>
       <c r="G70" s="17">
         <f t="shared" si="2"/>
-        <v>1.358256659</v>
+        <v>1.363938013</v>
       </c>
       <c r="H70" s="20">
         <f t="shared" si="3"/>
@@ -39937,7 +39966,7 @@
       </c>
       <c r="G71" s="17">
         <f t="shared" si="2"/>
-        <v>1.358256659</v>
+        <v>1.363938013</v>
       </c>
       <c r="H71" s="20">
         <f t="shared" si="3"/>
@@ -39967,7 +39996,7 @@
       </c>
       <c r="G72" s="17">
         <f t="shared" si="2"/>
-        <v>1.358256659</v>
+        <v>1.363938013</v>
       </c>
       <c r="H72" s="20">
         <f t="shared" si="3"/>
@@ -39997,7 +40026,7 @@
       </c>
       <c r="G73" s="17">
         <f t="shared" si="2"/>
-        <v>1.358256659</v>
+        <v>1.363938013</v>
       </c>
       <c r="H73" s="20">
         <f t="shared" si="3"/>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="178">
   <si>
     <t>PICK</t>
   </si>
@@ -92,12 +92,6 @@
     <t>Ed</t>
   </si>
   <si>
-    <t>Blaine</t>
-  </si>
-  <si>
-    <t>Jason</t>
-  </si>
-  <si>
     <t>Brent</t>
   </si>
   <si>
@@ -105,9 +99,6 @@
   </si>
   <si>
     <t>MaKayla</t>
-  </si>
-  <si>
-    <t>Collin</t>
   </si>
   <si>
     <t>Ty</t>
@@ -119,7 +110,16 @@
     <t>Eric</t>
   </si>
   <si>
+    <t>Collin</t>
+  </si>
+  <si>
     <t>Roy</t>
+  </si>
+  <si>
+    <t>Jason</t>
+  </si>
+  <si>
+    <t>Blaine</t>
   </si>
   <si>
     <t>Joel</t>
@@ -3158,18 +3158,12 @@
         <v>Ed</v>
       </c>
       <c r="U30" s="8"/>
-      <c r="V30" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="W30" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="X30" s="14" t="s">
-        <v>27</v>
-      </c>
+      <c r="V30" s="13"/>
+      <c r="W30" s="13"/>
+      <c r="X30" s="14"/>
       <c r="Y30" s="8" t="str">
         <f t="shared" ref="Y30:Y81" si="17">TEXT(V30,"0")&amp;"|"&amp;TRIM(W30)</f>
-        <v>1|Blaine</v>
+        <v>0|</v>
       </c>
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
@@ -3227,7 +3221,7 @@
         <v>2.0</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Q31" s="8"/>
       <c r="R31" s="4">
@@ -3239,18 +3233,12 @@
         <v>Brent</v>
       </c>
       <c r="U31" s="8"/>
-      <c r="V31" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="W31" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="X31" s="14" t="s">
-        <v>27</v>
-      </c>
+      <c r="V31" s="5"/>
+      <c r="W31" s="14"/>
+      <c r="X31" s="14"/>
       <c r="Y31" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>1|Ed</v>
+        <v>0|</v>
       </c>
       <c r="Z31" s="8"/>
       <c r="AA31" s="8"/>
@@ -3308,7 +3296,7 @@
         <v>3.0</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Q32" s="8"/>
       <c r="R32" s="4">
@@ -3320,18 +3308,12 @@
         <v>Joey</v>
       </c>
       <c r="U32" s="8"/>
-      <c r="V32" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="W32" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="X32" s="14" t="s">
-        <v>27</v>
-      </c>
+      <c r="V32" s="5"/>
+      <c r="W32" s="14"/>
+      <c r="X32" s="14"/>
       <c r="Y32" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>2|Blaine</v>
+        <v>0|</v>
       </c>
       <c r="Z32" s="8"/>
       <c r="AA32" s="8"/>
@@ -3389,7 +3371,7 @@
         <v>4.0</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Q33" s="8"/>
       <c r="R33" s="4">
@@ -3401,18 +3383,12 @@
         <v>MaKayla</v>
       </c>
       <c r="U33" s="8"/>
-      <c r="V33" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="W33" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="X33" s="14" t="s">
-        <v>27</v>
-      </c>
+      <c r="V33" s="5"/>
+      <c r="W33" s="14"/>
+      <c r="X33" s="14"/>
       <c r="Y33" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>2|Collin</v>
+        <v>0|</v>
       </c>
       <c r="Z33" s="8"/>
       <c r="AA33" s="8"/>
@@ -3470,7 +3446,7 @@
         <v>5.0</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Q34" s="8"/>
       <c r="R34" s="4">
@@ -3482,18 +3458,12 @@
         <v>Ty</v>
       </c>
       <c r="U34" s="8"/>
-      <c r="V34" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="W34" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="X34" s="14" t="s">
-        <v>27</v>
-      </c>
+      <c r="V34" s="5"/>
+      <c r="W34" s="14"/>
+      <c r="X34" s="14"/>
       <c r="Y34" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>2|Kich</v>
+        <v>0|</v>
       </c>
       <c r="Z34" s="8"/>
       <c r="AA34" s="8"/>
@@ -3551,7 +3521,7 @@
         <v>6.0</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Q35" s="8"/>
       <c r="R35" s="4">
@@ -3563,18 +3533,12 @@
         <v>Kich</v>
       </c>
       <c r="U35" s="8"/>
-      <c r="V35" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="W35" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="X35" s="14" t="s">
-        <v>27</v>
-      </c>
+      <c r="V35" s="5"/>
+      <c r="W35" s="14"/>
+      <c r="X35" s="14"/>
       <c r="Y35" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>2|Ty</v>
+        <v>0|</v>
       </c>
       <c r="Z35" s="8"/>
       <c r="AA35" s="8"/>
@@ -3632,7 +3596,7 @@
         <v>7.0</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Q36" s="8"/>
       <c r="R36" s="4">
@@ -3644,18 +3608,12 @@
         <v>Eric</v>
       </c>
       <c r="U36" s="8"/>
-      <c r="V36" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="W36" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="X36" s="14" t="s">
-        <v>27</v>
-      </c>
+      <c r="V36" s="5"/>
+      <c r="W36" s="14"/>
+      <c r="X36" s="14"/>
       <c r="Y36" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>2|Joey</v>
+        <v>0|</v>
       </c>
       <c r="Z36" s="8"/>
       <c r="AA36" s="8"/>
@@ -3713,7 +3671,7 @@
         <v>8.0</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q37" s="8"/>
       <c r="R37" s="4">
@@ -3725,18 +3683,12 @@
         <v>Collin</v>
       </c>
       <c r="U37" s="8"/>
-      <c r="V37" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="W37" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="X37" s="14" t="s">
-        <v>27</v>
-      </c>
+      <c r="V37" s="5"/>
+      <c r="W37" s="14"/>
+      <c r="X37" s="14"/>
       <c r="Y37" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>3|Roy</v>
+        <v>0|</v>
       </c>
       <c r="Z37" s="8"/>
       <c r="AA37" s="8"/>
@@ -3794,7 +3746,7 @@
         <v>9.0</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q38" s="8"/>
       <c r="R38" s="4">
@@ -3806,18 +3758,12 @@
         <v>Roy</v>
       </c>
       <c r="U38" s="8"/>
-      <c r="V38" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="W38" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="X38" s="14" t="s">
-        <v>27</v>
-      </c>
+      <c r="V38" s="5"/>
+      <c r="W38" s="14"/>
+      <c r="X38" s="14"/>
       <c r="Y38" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>3|Brent</v>
+        <v>0|</v>
       </c>
       <c r="Z38" s="8"/>
       <c r="AA38" s="8"/>
@@ -3875,7 +3821,7 @@
         <v>10.0</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="Q39" s="8"/>
       <c r="R39" s="4">
@@ -3887,18 +3833,12 @@
         <v>Jason</v>
       </c>
       <c r="U39" s="8"/>
-      <c r="V39" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="W39" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="X39" s="14" t="s">
-        <v>27</v>
-      </c>
+      <c r="V39" s="5"/>
+      <c r="W39" s="14"/>
+      <c r="X39" s="14"/>
       <c r="Y39" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>4|Roy</v>
+        <v>0|</v>
       </c>
       <c r="Z39" s="8"/>
       <c r="AA39" s="8"/>
@@ -3956,7 +3896,7 @@
         <v>11.0</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q40" s="8"/>
       <c r="R40" s="4">
@@ -3968,18 +3908,12 @@
         <v>Blaine</v>
       </c>
       <c r="U40" s="8"/>
-      <c r="V40" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="W40" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="X40" s="14" t="s">
-        <v>27</v>
-      </c>
+      <c r="V40" s="5"/>
+      <c r="W40" s="14"/>
+      <c r="X40" s="14"/>
       <c r="Y40" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>4|Collin</v>
+        <v>0|</v>
       </c>
       <c r="Z40" s="8"/>
       <c r="AA40" s="8"/>
@@ -4049,18 +3983,12 @@
         <v>Joel</v>
       </c>
       <c r="U41" s="8"/>
-      <c r="V41" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="W41" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="X41" s="14" t="s">
-        <v>27</v>
-      </c>
+      <c r="V41" s="5"/>
+      <c r="W41" s="14"/>
+      <c r="X41" s="14"/>
       <c r="Y41" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>4|Eric</v>
+        <v>0|</v>
       </c>
       <c r="Z41" s="8"/>
       <c r="AA41" s="8"/>
@@ -4121,18 +4049,12 @@
       <c r="S42" s="8"/>
       <c r="T42" s="8"/>
       <c r="U42" s="8"/>
-      <c r="V42" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="W42" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="X42" s="14" t="s">
-        <v>27</v>
-      </c>
+      <c r="V42" s="5"/>
+      <c r="W42" s="14"/>
+      <c r="X42" s="14"/>
       <c r="Y42" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>4|MaKayla</v>
+        <v>0|</v>
       </c>
       <c r="Z42" s="8"/>
       <c r="AA42" s="8"/>
@@ -4193,18 +4115,12 @@
       <c r="S43" s="8"/>
       <c r="T43" s="8"/>
       <c r="U43" s="8"/>
-      <c r="V43" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="W43" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="X43" s="14" t="s">
-        <v>27</v>
-      </c>
+      <c r="V43" s="5"/>
+      <c r="W43" s="14"/>
+      <c r="X43" s="14"/>
       <c r="Y43" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>4|Brent</v>
+        <v>0|</v>
       </c>
       <c r="Z43" s="8"/>
       <c r="AA43" s="8"/>
@@ -4273,18 +4189,12 @@
       <c r="S44" s="8"/>
       <c r="T44" s="8"/>
       <c r="U44" s="8"/>
-      <c r="V44" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="W44" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="X44" s="14" t="s">
-        <v>27</v>
-      </c>
+      <c r="V44" s="5"/>
+      <c r="W44" s="14"/>
+      <c r="X44" s="14"/>
       <c r="Y44" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>4|Ed</v>
+        <v>0|</v>
       </c>
       <c r="Z44" s="8"/>
       <c r="AA44" s="8"/>
@@ -4369,18 +4279,12 @@
       <c r="S45" s="8"/>
       <c r="T45" s="8"/>
       <c r="U45" s="8"/>
-      <c r="V45" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="W45" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="X45" s="14" t="s">
-        <v>27</v>
-      </c>
+      <c r="V45" s="5"/>
+      <c r="W45" s="14"/>
+      <c r="X45" s="14"/>
       <c r="Y45" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>5|Eric</v>
+        <v>0|</v>
       </c>
       <c r="Z45" s="8"/>
       <c r="AA45" s="8"/>
@@ -4448,23 +4352,17 @@
       </c>
       <c r="R46" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>Blaine</v>
       </c>
       <c r="S46" s="8"/>
       <c r="T46" s="8"/>
       <c r="U46" s="8"/>
-      <c r="V46" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="W46" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="X46" s="14" t="s">
-        <v>25</v>
-      </c>
+      <c r="V46" s="5"/>
+      <c r="W46" s="14"/>
+      <c r="X46" s="14"/>
       <c r="Y46" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>1|Eric</v>
+        <v>0|</v>
       </c>
       <c r="Z46" s="8"/>
       <c r="AA46" s="8"/>
@@ -4537,18 +4435,12 @@
       <c r="S47" s="8"/>
       <c r="T47" s="8"/>
       <c r="U47" s="8"/>
-      <c r="V47" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="W47" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="X47" s="14" t="s">
-        <v>25</v>
-      </c>
+      <c r="V47" s="5"/>
+      <c r="W47" s="14"/>
+      <c r="X47" s="14"/>
       <c r="Y47" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>1|MaKayla</v>
+        <v>0|</v>
       </c>
       <c r="Z47" s="8"/>
       <c r="AA47" s="8"/>
@@ -4616,23 +4508,17 @@
       </c>
       <c r="R48" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>MaKayla</v>
+        <v>Roy</v>
       </c>
       <c r="S48" s="8"/>
       <c r="T48" s="8"/>
       <c r="U48" s="8"/>
-      <c r="V48" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="W48" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="X48" s="14" t="s">
-        <v>25</v>
-      </c>
+      <c r="V48" s="5"/>
+      <c r="W48" s="14"/>
+      <c r="X48" s="14"/>
       <c r="Y48" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>2|Roy</v>
+        <v>0|</v>
       </c>
       <c r="Z48" s="8"/>
       <c r="AA48" s="8"/>
@@ -4705,18 +4591,12 @@
       <c r="S49" s="8"/>
       <c r="T49" s="8"/>
       <c r="U49" s="8"/>
-      <c r="V49" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="W49" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="X49" s="14" t="s">
-        <v>25</v>
-      </c>
+      <c r="V49" s="5"/>
+      <c r="W49" s="14"/>
+      <c r="X49" s="14"/>
       <c r="Y49" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>5|Brent</v>
+        <v>0|</v>
       </c>
       <c r="Z49" s="8"/>
       <c r="AA49" s="8"/>
@@ -4784,23 +4664,17 @@
       </c>
       <c r="R50" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Ed</v>
+        <v>Eric</v>
       </c>
       <c r="S50" s="8"/>
       <c r="T50" s="8"/>
       <c r="U50" s="8"/>
-      <c r="V50" s="5">
-        <v>6.0</v>
-      </c>
-      <c r="W50" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="X50" s="14" t="s">
-        <v>25</v>
-      </c>
+      <c r="V50" s="5"/>
+      <c r="W50" s="14"/>
+      <c r="X50" s="14"/>
       <c r="Y50" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>6|Brent</v>
+        <v>0|</v>
       </c>
       <c r="Z50" s="8"/>
       <c r="AA50" s="8"/>
@@ -4873,18 +4747,12 @@
       <c r="S51" s="8"/>
       <c r="T51" s="8"/>
       <c r="U51" s="8"/>
-      <c r="V51" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="W51" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="X51" s="14" t="s">
-        <v>32</v>
-      </c>
+      <c r="V51" s="5"/>
+      <c r="W51" s="14"/>
+      <c r="X51" s="14"/>
       <c r="Y51" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>1|Brent</v>
+        <v>0|</v>
       </c>
       <c r="Z51" s="8"/>
       <c r="AA51" s="8"/>
@@ -4952,23 +4820,17 @@
       </c>
       <c r="R52" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>MaKayla</v>
+        <v>Ty</v>
       </c>
       <c r="S52" s="8"/>
       <c r="T52" s="8"/>
       <c r="U52" s="8"/>
-      <c r="V52" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="W52" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="X52" s="14" t="s">
-        <v>32</v>
-      </c>
+      <c r="V52" s="5"/>
+      <c r="W52" s="14"/>
+      <c r="X52" s="14"/>
       <c r="Y52" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>2|Brent</v>
+        <v>0|</v>
       </c>
       <c r="Z52" s="8"/>
       <c r="AA52" s="8"/>
@@ -5036,23 +4898,17 @@
       </c>
       <c r="R53" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Ed</v>
+        <v>MaKayla</v>
       </c>
       <c r="S53" s="8"/>
       <c r="T53" s="8"/>
       <c r="U53" s="8"/>
-      <c r="V53" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="W53" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="X53" s="14" t="s">
-        <v>32</v>
-      </c>
+      <c r="V53" s="5"/>
+      <c r="W53" s="14"/>
+      <c r="X53" s="14"/>
       <c r="Y53" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>5|Jason</v>
+        <v>0|</v>
       </c>
       <c r="Z53" s="8"/>
       <c r="AA53" s="8"/>
@@ -5125,18 +4981,12 @@
       <c r="S54" s="8"/>
       <c r="T54" s="8"/>
       <c r="U54" s="8"/>
-      <c r="V54" s="5">
-        <v>6.0</v>
-      </c>
-      <c r="W54" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="X54" s="14" t="s">
-        <v>32</v>
-      </c>
+      <c r="V54" s="5"/>
+      <c r="W54" s="14"/>
+      <c r="X54" s="14"/>
       <c r="Y54" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>6|Jason</v>
+        <v>0|</v>
       </c>
       <c r="Z54" s="8"/>
       <c r="AA54" s="8"/>
@@ -5204,23 +5054,17 @@
       </c>
       <c r="R55" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Ty</v>
+        <v>Brent</v>
       </c>
       <c r="S55" s="8"/>
       <c r="T55" s="8"/>
       <c r="U55" s="8"/>
-      <c r="V55" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="W55" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="X55" s="14" t="s">
-        <v>31</v>
-      </c>
+      <c r="V55" s="5"/>
+      <c r="W55" s="14"/>
+      <c r="X55" s="14"/>
       <c r="Y55" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>2|Jason</v>
+        <v>0|</v>
       </c>
       <c r="Z55" s="8"/>
       <c r="AA55" s="8"/>
@@ -5288,23 +5132,17 @@
       </c>
       <c r="R56" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>Ed</v>
       </c>
       <c r="S56" s="8"/>
       <c r="T56" s="8"/>
       <c r="U56" s="8"/>
-      <c r="V56" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="W56" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="X56" s="14" t="s">
-        <v>31</v>
-      </c>
+      <c r="V56" s="5"/>
+      <c r="W56" s="14"/>
+      <c r="X56" s="14"/>
       <c r="Y56" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>2|Eric</v>
+        <v>0|</v>
       </c>
       <c r="Z56" s="8"/>
       <c r="AA56" s="8"/>
@@ -5377,18 +5215,12 @@
       <c r="S57" s="8"/>
       <c r="T57" s="8"/>
       <c r="U57" s="8"/>
-      <c r="V57" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="W57" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="X57" s="14" t="s">
-        <v>31</v>
-      </c>
+      <c r="V57" s="5"/>
+      <c r="W57" s="14"/>
+      <c r="X57" s="14"/>
       <c r="Y57" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>2|Ed</v>
+        <v>0|</v>
       </c>
       <c r="Z57" s="8"/>
       <c r="AA57" s="8"/>
@@ -5456,23 +5288,17 @@
       </c>
       <c r="R58" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>Blaine</v>
       </c>
       <c r="S58" s="8"/>
       <c r="T58" s="8"/>
       <c r="U58" s="8"/>
-      <c r="V58" s="13">
-        <v>4.0</v>
-      </c>
-      <c r="W58" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="X58" s="14" t="s">
-        <v>31</v>
-      </c>
+      <c r="V58" s="13"/>
+      <c r="W58" s="13"/>
+      <c r="X58" s="14"/>
       <c r="Y58" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>4|Joey</v>
+        <v>0|</v>
       </c>
       <c r="Z58" s="8"/>
       <c r="AA58" s="8"/>
@@ -5540,23 +5366,17 @@
       </c>
       <c r="R59" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Collin</v>
+        <v>Jason</v>
       </c>
       <c r="S59" s="8"/>
       <c r="T59" s="8"/>
       <c r="U59" s="8"/>
-      <c r="V59" s="13">
-        <v>5.0</v>
-      </c>
-      <c r="W59" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="X59" s="14" t="s">
-        <v>31</v>
-      </c>
+      <c r="V59" s="13"/>
+      <c r="W59" s="13"/>
+      <c r="X59" s="14"/>
       <c r="Y59" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>5|Joey</v>
+        <v>0|</v>
       </c>
       <c r="Z59" s="8"/>
       <c r="AA59" s="8"/>
@@ -5624,23 +5444,17 @@
       </c>
       <c r="R60" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Ed</v>
+        <v>Roy</v>
       </c>
       <c r="S60" s="8"/>
       <c r="T60" s="8"/>
       <c r="U60" s="8"/>
-      <c r="V60" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="W60" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="X60" s="14" t="s">
-        <v>30</v>
-      </c>
+      <c r="V60" s="13"/>
+      <c r="W60" s="13"/>
+      <c r="X60" s="14"/>
       <c r="Y60" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>1|Roy</v>
+        <v>0|</v>
       </c>
       <c r="Z60" s="8"/>
       <c r="AA60" s="8"/>
@@ -5708,23 +5522,17 @@
       </c>
       <c r="R61" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>Collin</v>
       </c>
       <c r="S61" s="8"/>
       <c r="T61" s="8"/>
       <c r="U61" s="8"/>
-      <c r="V61" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="W61" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="X61" s="14" t="s">
-        <v>30</v>
-      </c>
+      <c r="V61" s="5"/>
+      <c r="W61" s="14"/>
+      <c r="X61" s="14"/>
       <c r="Y61" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>1|Ty</v>
+        <v>0|</v>
       </c>
       <c r="Z61" s="8"/>
       <c r="AA61" s="8"/>
@@ -5792,7 +5600,7 @@
       </c>
       <c r="R62" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Collin</v>
+        <v>Eric</v>
       </c>
       <c r="S62" s="8"/>
       <c r="T62" s="8" t="s">
@@ -5801,18 +5609,12 @@
       <c r="U62" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="V62" s="14">
-        <v>3.0</v>
-      </c>
-      <c r="W62" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="X62" s="14" t="s">
-        <v>35</v>
-      </c>
+      <c r="V62" s="14"/>
+      <c r="W62" s="14"/>
+      <c r="X62" s="14"/>
       <c r="Y62" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>3|Eric</v>
+        <v>0|</v>
       </c>
       <c r="Z62" s="8"/>
       <c r="AA62" s="8"/>
@@ -5880,28 +5682,22 @@
       </c>
       <c r="R63" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>Kich</v>
       </c>
       <c r="S63" s="8"/>
-      <c r="T63" s="6" t="s">
-        <v>27</v>
+      <c r="T63" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="U63" s="11">
         <f t="shared" ref="U63:U74" si="22">SUMIF($R$45:$R$116, T63, $Q$45:$Q$116)</f>
-        <v>361</v>
-      </c>
-      <c r="V63" s="14">
-        <v>3.0</v>
-      </c>
-      <c r="W63" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="X63" s="14" t="s">
-        <v>35</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="V63" s="14"/>
+      <c r="W63" s="14"/>
+      <c r="X63" s="14"/>
       <c r="Y63" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>3|Kich</v>
+        <v>0|</v>
       </c>
       <c r="Z63" s="8"/>
       <c r="AA63" s="8"/>
@@ -5969,28 +5765,22 @@
       </c>
       <c r="R64" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>Ty</v>
       </c>
       <c r="S64" s="8"/>
       <c r="T64" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="U64" s="11">
         <f t="shared" si="22"/>
-        <v>180</v>
-      </c>
-      <c r="V64" s="13">
-        <v>4.0</v>
-      </c>
-      <c r="W64" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="X64" s="14" t="s">
-        <v>29</v>
-      </c>
+        <v>144.5</v>
+      </c>
+      <c r="V64" s="13"/>
+      <c r="W64" s="13"/>
+      <c r="X64" s="14"/>
       <c r="Y64" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>4|Jason</v>
+        <v>0|</v>
       </c>
       <c r="Z64" s="8"/>
       <c r="AA64" s="8"/>
@@ -6061,25 +5851,19 @@
         <v>MaKayla</v>
       </c>
       <c r="S65" s="8"/>
-      <c r="T65" s="8" t="s">
-        <v>30</v>
+      <c r="T65" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="U65" s="11">
         <f t="shared" si="22"/>
-        <v>151</v>
-      </c>
-      <c r="V65" s="14">
-        <v>6.0</v>
-      </c>
-      <c r="W65" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="X65" s="14" t="s">
-        <v>29</v>
-      </c>
+        <v>132.5</v>
+      </c>
+      <c r="V65" s="14"/>
+      <c r="W65" s="14"/>
+      <c r="X65" s="14"/>
       <c r="Y65" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>6|Eric</v>
+        <v>0|</v>
       </c>
       <c r="Z65" s="8"/>
       <c r="AA65" s="8"/>
@@ -6147,28 +5931,22 @@
       </c>
       <c r="R66" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>Joey</v>
       </c>
       <c r="S66" s="8"/>
       <c r="T66" s="8" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="U66" s="11">
         <f t="shared" si="22"/>
-        <v>148.5</v>
-      </c>
-      <c r="V66" s="5">
-        <v>6.0</v>
-      </c>
-      <c r="W66" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="X66" s="14" t="s">
-        <v>33</v>
-      </c>
+        <v>117.5</v>
+      </c>
+      <c r="V66" s="5"/>
+      <c r="W66" s="14"/>
+      <c r="X66" s="14"/>
       <c r="Y66" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>6|Collin</v>
+        <v>0|</v>
       </c>
       <c r="Z66" s="8"/>
       <c r="AA66" s="8"/>
@@ -6236,28 +6014,22 @@
       </c>
       <c r="R67" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Ty</v>
+        <v>Brent</v>
       </c>
       <c r="S67" s="8"/>
       <c r="T67" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="U67" s="11">
         <f t="shared" si="22"/>
-        <v>143.5</v>
-      </c>
-      <c r="V67" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="W67" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="X67" s="14" t="s">
-        <v>26</v>
-      </c>
+        <v>109.5</v>
+      </c>
+      <c r="V67" s="5"/>
+      <c r="W67" s="14"/>
+      <c r="X67" s="14"/>
       <c r="Y67" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>3|MaKayla</v>
+        <v>0|</v>
       </c>
       <c r="Z67" s="8"/>
       <c r="AA67" s="8"/>
@@ -6325,15 +6097,15 @@
       </c>
       <c r="R68" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Collin</v>
+        <v>Ed</v>
       </c>
       <c r="S68" s="8"/>
       <c r="T68" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="U68" s="11">
         <f t="shared" si="22"/>
-        <v>61</v>
+        <v>99.5</v>
       </c>
       <c r="V68" s="5"/>
       <c r="W68" s="14"/>
@@ -6412,11 +6184,11 @@
       </c>
       <c r="S69" s="8"/>
       <c r="T69" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="U69" s="11">
         <f t="shared" si="22"/>
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="V69" s="13"/>
       <c r="W69" s="13"/>
@@ -6499,7 +6271,7 @@
       </c>
       <c r="U70" s="11">
         <f t="shared" si="22"/>
-        <v>54</v>
+        <v>80.5</v>
       </c>
       <c r="V70" s="3"/>
       <c r="W70" s="3"/>
@@ -6578,11 +6350,11 @@
       </c>
       <c r="S71" s="8"/>
       <c r="T71" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="U71" s="11">
         <f t="shared" si="22"/>
-        <v>20</v>
+        <v>69.5</v>
       </c>
       <c r="V71" s="3"/>
       <c r="W71" s="3"/>
@@ -6657,15 +6429,15 @@
       </c>
       <c r="R72" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>Roy</v>
       </c>
       <c r="S72" s="8"/>
       <c r="T72" s="8" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="U72" s="11">
         <f t="shared" si="22"/>
-        <v>15</v>
+        <v>67.5</v>
       </c>
       <c r="V72" s="3"/>
       <c r="W72" s="3"/>
@@ -6744,11 +6516,11 @@
       </c>
       <c r="S73" s="8"/>
       <c r="T73" s="8" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U73" s="11">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>61.5</v>
       </c>
       <c r="V73" s="3"/>
       <c r="W73" s="3"/>
@@ -6803,15 +6575,15 @@
       </c>
       <c r="R74" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Roy</v>
+        <v>Eric</v>
       </c>
       <c r="S74" s="8"/>
       <c r="T74" s="8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="U74" s="11">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>54.5</v>
       </c>
       <c r="V74" s="3"/>
       <c r="W74" s="3"/>
@@ -6855,7 +6627,7 @@
       </c>
       <c r="R75" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Roy</v>
+        <v>Kich</v>
       </c>
       <c r="S75" s="8"/>
       <c r="T75" s="8"/>
@@ -6951,7 +6723,7 @@
       </c>
       <c r="R77" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Blaine</v>
+        <v>MaKayla</v>
       </c>
       <c r="S77" s="8"/>
       <c r="T77" s="8"/>
@@ -7045,7 +6817,7 @@
       </c>
       <c r="R79" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>Brent</v>
       </c>
       <c r="S79" s="8"/>
       <c r="T79" s="8"/>
@@ -7230,7 +7002,7 @@
       </c>
       <c r="R83" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Joey</v>
+        <v>Jason</v>
       </c>
       <c r="S83" s="8"/>
       <c r="T83" s="8"/>
@@ -7274,7 +7046,7 @@
       </c>
       <c r="R84" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>Roy</v>
       </c>
       <c r="S84" s="8"/>
       <c r="T84" s="8"/>
@@ -7317,7 +7089,7 @@
       </c>
       <c r="R85" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>Collin</v>
       </c>
       <c r="S85" s="8"/>
       <c r="T85" s="8"/>
@@ -7361,7 +7133,7 @@
       </c>
       <c r="R86" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>Eric</v>
       </c>
       <c r="S86" s="8"/>
       <c r="T86" s="8"/>
@@ -7493,7 +7265,7 @@
       </c>
       <c r="R89" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>MaKayla</v>
       </c>
       <c r="S89" s="8"/>
       <c r="T89" s="8"/>
@@ -7537,7 +7309,7 @@
       </c>
       <c r="R90" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Collin</v>
+        <v>Joey</v>
       </c>
       <c r="S90" s="8"/>
       <c r="T90" s="8"/>
@@ -7581,7 +7353,7 @@
       </c>
       <c r="R91" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>Brent</v>
       </c>
       <c r="S91" s="8"/>
       <c r="T91" s="8"/>
@@ -7625,7 +7397,7 @@
       </c>
       <c r="R92" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>Ed</v>
       </c>
       <c r="S92" s="8"/>
       <c r="T92" s="8"/>
@@ -7757,7 +7529,7 @@
       </c>
       <c r="R95" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Ty</v>
+        <v>Jason</v>
       </c>
       <c r="S95" s="8"/>
       <c r="T95" s="8"/>
@@ -7889,7 +7661,7 @@
       </c>
       <c r="R98" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Jason</v>
+        <v>Eric</v>
       </c>
       <c r="S98" s="8"/>
       <c r="T98" s="8"/>
@@ -8065,7 +7837,7 @@
       </c>
       <c r="R102" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Collin</v>
+        <v>Joey</v>
       </c>
       <c r="S102" s="8"/>
       <c r="T102" s="8"/>
@@ -8109,7 +7881,7 @@
       </c>
       <c r="R103" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Ed</v>
+        <v>Brent</v>
       </c>
       <c r="S103" s="8"/>
       <c r="T103" s="8"/>
@@ -8285,7 +8057,7 @@
       </c>
       <c r="R107" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Ty</v>
+        <v>Jason</v>
       </c>
       <c r="S107" s="8"/>
       <c r="T107" s="8"/>
@@ -8373,7 +8145,7 @@
       </c>
       <c r="R109" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Kich</v>
+        <v>Collin</v>
       </c>
       <c r="S109" s="8"/>
       <c r="T109" s="8"/>
@@ -8417,7 +8189,7 @@
       </c>
       <c r="R110" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Joey</v>
+        <v>Eric</v>
       </c>
       <c r="S110" s="8"/>
       <c r="T110" s="8"/>
@@ -8637,7 +8409,7 @@
       </c>
       <c r="R115" s="8" t="str">
         <f t="shared" si="21"/>
-        <v>Ed</v>
+        <v>Brent</v>
       </c>
       <c r="S115" s="8"/>
       <c r="T115" s="8"/>
@@ -37723,7 +37495,7 @@
       </c>
       <c r="G2" s="17">
         <f t="shared" ref="G2:G73" si="2">IF($D2&gt;0,"",MIN($L$8, $C2*$L$14*(1+($L$11-1)*$L$16)))</f>
-        <v>185.7000238</v>
+        <v>150.7741176</v>
       </c>
       <c r="H2" s="20">
         <f t="shared" ref="H2:H73" si="3">IF($D2&lt;&gt;"","",
@@ -37777,7 +37549,7 @@
       </c>
       <c r="G3" s="17">
         <f t="shared" si="2"/>
-        <v>142.2809535</v>
+        <v>115.5211765</v>
       </c>
       <c r="H3" s="20">
         <f t="shared" si="3"/>
@@ -37819,7 +37591,7 @@
       </c>
       <c r="G4" s="17">
         <f t="shared" si="2"/>
-        <v>124.2453397</v>
+        <v>100.8776471</v>
       </c>
       <c r="H4" s="20">
         <f t="shared" si="3"/>
@@ -37834,7 +37606,7 @@
       </c>
       <c r="L4" s="10">
         <f>'Draft Data'!U63</f>
-        <v>361</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5">
@@ -37856,7 +37628,7 @@
       </c>
       <c r="G5" s="17">
         <f t="shared" si="2"/>
-        <v>110.21764</v>
+        <v>89.48823529</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" si="3"/>
@@ -37894,7 +37666,7 @@
       </c>
       <c r="G6" s="17">
         <f t="shared" si="2"/>
-        <v>101.533826</v>
+        <v>82.43764706</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="3"/>
@@ -37932,7 +37704,7 @@
       </c>
       <c r="G7" s="17">
         <f t="shared" si="2"/>
-        <v>88.84209774</v>
+        <v>72.13294118</v>
       </c>
       <c r="H7" s="20">
         <f t="shared" si="3"/>
@@ -37969,7 +37741,7 @@
       </c>
       <c r="G8" s="17">
         <f t="shared" si="2"/>
-        <v>76.81835518</v>
+        <v>62.37058824</v>
       </c>
       <c r="H8" s="20">
         <f t="shared" si="3"/>
@@ -37985,7 +37757,7 @@
       <c r="L8" s="17">
         <f>L4-L7
 </f>
-        <v>361</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9">
@@ -38007,7 +37779,7 @@
       </c>
       <c r="G9" s="17">
         <f t="shared" si="2"/>
-        <v>70.80648391</v>
+        <v>57.48941176</v>
       </c>
       <c r="H9" s="20">
         <f t="shared" si="3"/>
@@ -38023,7 +37795,7 @@
       <c r="L9" s="17">
         <f>L6-L8
 </f>
-        <v>839</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="10">
@@ -38045,7 +37817,7 @@
       </c>
       <c r="G10" s="17">
         <f t="shared" si="2"/>
-        <v>64.12662694</v>
+        <v>52.06588235</v>
       </c>
       <c r="H10" s="20">
         <f t="shared" si="3"/>
@@ -38060,7 +37832,7 @@
       </c>
       <c r="L10" s="17">
         <f>IF(L3&gt;1,L9/(L3-1),0)</f>
-        <v>76.27272727</v>
+        <v>92.72727273</v>
       </c>
     </row>
     <row r="11">
@@ -38082,7 +37854,7 @@
       </c>
       <c r="G11" s="17">
         <f t="shared" si="2"/>
-        <v>57.44676996</v>
+        <v>46.64235294</v>
       </c>
       <c r="H11" s="20">
         <f t="shared" si="3"/>
@@ -38097,7 +37869,7 @@
       </c>
       <c r="L11" s="23">
         <f>IF(L10&gt;0,L8/L10,1)</f>
-        <v>4.733015495</v>
+        <v>1.941176471</v>
       </c>
     </row>
     <row r="12">
@@ -38119,7 +37891,7 @@
       </c>
       <c r="G12" s="17">
         <f t="shared" si="2"/>
-        <v>52.10288439</v>
+        <v>42.30352941</v>
       </c>
       <c r="H12" s="20">
         <f t="shared" si="3"/>
@@ -38149,7 +37921,7 @@
       </c>
       <c r="G13" s="17">
         <f t="shared" si="2"/>
-        <v>45.42302741</v>
+        <v>36.88</v>
       </c>
       <c r="H13" s="20">
         <f t="shared" si="3"/>
@@ -38186,7 +37958,7 @@
       </c>
       <c r="G14" s="17">
         <f t="shared" si="2"/>
-        <v>40.74712753</v>
+        <v>33.08352941</v>
       </c>
       <c r="H14" s="20">
         <f t="shared" si="3"/>
@@ -38223,7 +37995,7 @@
       </c>
       <c r="G15" s="17">
         <f t="shared" si="2"/>
-        <v>36.73921335</v>
+        <v>29.82941176</v>
       </c>
       <c r="H15" s="20">
         <f t="shared" si="3"/>
@@ -38253,7 +38025,7 @@
       </c>
       <c r="G16" s="17">
         <f t="shared" si="2"/>
-        <v>34.06727056</v>
+        <v>27.66</v>
       </c>
       <c r="H16" s="20">
         <f t="shared" si="3"/>
@@ -38300,7 +38072,7 @@
       </c>
       <c r="G17" s="17">
         <f t="shared" si="2"/>
-        <v>30.05935638</v>
+        <v>24.40588235</v>
       </c>
       <c r="H17" s="20">
         <f t="shared" si="3"/>
@@ -38330,7 +38102,7 @@
       </c>
       <c r="G18" s="17">
         <f t="shared" si="2"/>
-        <v>26.71942789</v>
+        <v>21.69411765</v>
       </c>
       <c r="H18" s="20">
         <f t="shared" si="3"/>
@@ -38367,7 +38139,7 @@
       </c>
       <c r="G19" s="17">
         <f t="shared" si="2"/>
-        <v>24.7154708</v>
+        <v>20.06705882</v>
       </c>
       <c r="H19" s="20">
         <f t="shared" si="3"/>
@@ -38397,7 +38169,7 @@
       </c>
       <c r="G20" s="17">
         <f t="shared" si="2"/>
-        <v>22.04352801</v>
+        <v>17.89764706</v>
       </c>
       <c r="H20" s="20">
         <f t="shared" si="3"/>
@@ -38427,7 +38199,7 @@
       </c>
       <c r="G21" s="17">
         <f t="shared" si="2"/>
-        <v>19.37158522</v>
+        <v>15.72823529</v>
       </c>
       <c r="H21" s="20">
         <f t="shared" si="3"/>
@@ -38457,7 +38229,7 @@
       </c>
       <c r="G22" s="17">
         <f t="shared" si="2"/>
-        <v>18.03561383</v>
+        <v>14.64352941</v>
       </c>
       <c r="H22" s="20">
         <f t="shared" si="3"/>
@@ -38487,7 +38259,7 @@
       </c>
       <c r="G23" s="17">
         <f t="shared" si="2"/>
-        <v>16.03165673</v>
+        <v>13.01647059</v>
       </c>
       <c r="H23" s="20">
         <f t="shared" si="3"/>
@@ -38517,7 +38289,7 @@
       </c>
       <c r="G24" s="17">
         <f t="shared" si="2"/>
-        <v>14.69568534</v>
+        <v>11.93176471</v>
       </c>
       <c r="H24" s="20">
         <f t="shared" si="3"/>
@@ -38547,7 +38319,7 @@
       </c>
       <c r="G25" s="17">
         <f t="shared" si="2"/>
-        <v>13.35971395</v>
+        <v>10.84705882</v>
       </c>
       <c r="H25" s="20">
         <f t="shared" si="3"/>
@@ -38577,7 +38349,7 @@
       </c>
       <c r="G26" s="17">
         <f t="shared" si="2"/>
-        <v>12.69172825</v>
+        <v>10.30470588</v>
       </c>
       <c r="H26" s="20">
         <f t="shared" si="3"/>
@@ -38607,7 +38379,7 @@
       </c>
       <c r="G27" s="17">
         <f t="shared" si="2"/>
-        <v>11.35575685</v>
+        <v>9.22</v>
       </c>
       <c r="H27" s="20">
         <f t="shared" si="3"/>
@@ -38643,7 +38415,7 @@
       </c>
       <c r="G28" s="17">
         <f t="shared" si="2"/>
-        <v>10.68777116</v>
+        <v>8.677647059</v>
       </c>
       <c r="H28" s="20">
         <f t="shared" si="3"/>
@@ -38673,7 +38445,7 @@
       </c>
       <c r="G29" s="17">
         <f t="shared" si="2"/>
-        <v>9.351799762</v>
+        <v>7.592941176</v>
       </c>
       <c r="H29" s="20">
         <f t="shared" si="3"/>
@@ -38703,7 +38475,7 @@
       </c>
       <c r="G30" s="17">
         <f t="shared" si="2"/>
-        <v>8.683814064</v>
+        <v>7.050588235</v>
       </c>
       <c r="H30" s="20">
         <f t="shared" si="3"/>
@@ -38733,7 +38505,7 @@
       </c>
       <c r="G31" s="17">
         <f t="shared" si="2"/>
-        <v>8.015828367</v>
+        <v>6.508235294</v>
       </c>
       <c r="H31" s="20">
         <f t="shared" si="3"/>
@@ -38763,7 +38535,7 @@
       </c>
       <c r="G32" s="17">
         <f t="shared" si="2"/>
-        <v>7.34784267</v>
+        <v>5.965882353</v>
       </c>
       <c r="H32" s="20">
         <f t="shared" si="3"/>
@@ -38793,7 +38565,7 @@
       </c>
       <c r="G33" s="17">
         <f t="shared" si="2"/>
-        <v>6.679856973</v>
+        <v>5.423529412</v>
       </c>
       <c r="H33" s="20">
         <f t="shared" si="3"/>
@@ -38823,7 +38595,7 @@
       </c>
       <c r="G34" s="17">
         <f t="shared" si="2"/>
-        <v>6.011871275</v>
+        <v>4.881176471</v>
       </c>
       <c r="H34" s="20">
         <f t="shared" si="3"/>
@@ -38853,7 +38625,7 @@
       </c>
       <c r="G35" s="17">
         <f t="shared" si="2"/>
-        <v>6.011871275</v>
+        <v>4.881176471</v>
       </c>
       <c r="H35" s="20">
         <f t="shared" si="3"/>
@@ -38883,7 +38655,7 @@
       </c>
       <c r="G36" s="17">
         <f t="shared" si="2"/>
-        <v>5.343885578</v>
+        <v>4.338823529</v>
       </c>
       <c r="H36" s="20">
         <f t="shared" si="3"/>
@@ -38913,7 +38685,7 @@
       </c>
       <c r="G37" s="17">
         <f t="shared" si="2"/>
-        <v>5.343885578</v>
+        <v>4.338823529</v>
       </c>
       <c r="H37" s="20">
         <f t="shared" si="3"/>
@@ -38943,7 +38715,7 @@
       </c>
       <c r="G38" s="17">
         <f t="shared" si="2"/>
-        <v>4.675899881</v>
+        <v>3.796470588</v>
       </c>
       <c r="H38" s="20">
         <f t="shared" si="3"/>
@@ -38973,7 +38745,7 @@
       </c>
       <c r="G39" s="17">
         <f t="shared" si="2"/>
-        <v>4.675899881</v>
+        <v>3.796470588</v>
       </c>
       <c r="H39" s="20">
         <f t="shared" si="3"/>
@@ -39003,7 +38775,7 @@
       </c>
       <c r="G40" s="17">
         <f t="shared" si="2"/>
-        <v>4.007914184</v>
+        <v>3.254117647</v>
       </c>
       <c r="H40" s="20">
         <f t="shared" si="3"/>
@@ -39033,7 +38805,7 @@
       </c>
       <c r="G41" s="17">
         <f t="shared" si="2"/>
-        <v>4.007914184</v>
+        <v>3.254117647</v>
       </c>
       <c r="H41" s="20">
         <f t="shared" si="3"/>
@@ -39063,7 +38835,7 @@
       </c>
       <c r="G42" s="17">
         <f t="shared" si="2"/>
-        <v>3.339928486</v>
+        <v>2.711764706</v>
       </c>
       <c r="H42" s="20">
         <f t="shared" si="3"/>
@@ -39093,7 +38865,7 @@
       </c>
       <c r="G43" s="17">
         <f t="shared" si="2"/>
-        <v>3.339928486</v>
+        <v>2.711764706</v>
       </c>
       <c r="H43" s="20">
         <f t="shared" si="3"/>
@@ -39123,7 +38895,7 @@
       </c>
       <c r="G44" s="17">
         <f t="shared" si="2"/>
-        <v>3.339928486</v>
+        <v>2.711764706</v>
       </c>
       <c r="H44" s="20">
         <f t="shared" si="3"/>
@@ -39153,7 +38925,7 @@
       </c>
       <c r="G45" s="17">
         <f t="shared" si="2"/>
-        <v>3.339928486</v>
+        <v>2.711764706</v>
       </c>
       <c r="H45" s="20">
         <f t="shared" si="3"/>
@@ -39183,7 +38955,7 @@
       </c>
       <c r="G46" s="17">
         <f t="shared" si="2"/>
-        <v>2.671942789</v>
+        <v>2.169411765</v>
       </c>
       <c r="H46" s="20">
         <f t="shared" si="3"/>
@@ -39213,7 +38985,7 @@
       </c>
       <c r="G47" s="17">
         <f t="shared" si="2"/>
-        <v>2.671942789</v>
+        <v>2.169411765</v>
       </c>
       <c r="H47" s="20">
         <f t="shared" si="3"/>
@@ -39243,7 +39015,7 @@
       </c>
       <c r="G48" s="17">
         <f t="shared" si="2"/>
-        <v>2.671942789</v>
+        <v>2.169411765</v>
       </c>
       <c r="H48" s="20">
         <f t="shared" si="3"/>
@@ -39273,7 +39045,7 @@
       </c>
       <c r="G49" s="17">
         <f t="shared" si="2"/>
-        <v>2.671942789</v>
+        <v>2.169411765</v>
       </c>
       <c r="H49" s="20">
         <f t="shared" si="3"/>
@@ -39303,7 +39075,7 @@
       </c>
       <c r="G50" s="17">
         <f t="shared" si="2"/>
-        <v>2.671942789</v>
+        <v>2.169411765</v>
       </c>
       <c r="H50" s="20">
         <f t="shared" si="3"/>
@@ -39333,7 +39105,7 @@
       </c>
       <c r="G51" s="17">
         <f t="shared" si="2"/>
-        <v>2.671942789</v>
+        <v>2.169411765</v>
       </c>
       <c r="H51" s="20">
         <f t="shared" si="3"/>
@@ -39363,7 +39135,7 @@
       </c>
       <c r="G52" s="17">
         <f t="shared" si="2"/>
-        <v>2.671942789</v>
+        <v>2.169411765</v>
       </c>
       <c r="H52" s="20">
         <f t="shared" si="3"/>
@@ -39393,7 +39165,7 @@
       </c>
       <c r="G53" s="17">
         <f t="shared" si="2"/>
-        <v>2.671942789</v>
+        <v>2.169411765</v>
       </c>
       <c r="H53" s="20">
         <f t="shared" si="3"/>
@@ -39423,7 +39195,7 @@
       </c>
       <c r="G54" s="17">
         <f t="shared" si="2"/>
-        <v>2.671942789</v>
+        <v>2.169411765</v>
       </c>
       <c r="H54" s="20">
         <f t="shared" si="3"/>
@@ -39453,7 +39225,7 @@
       </c>
       <c r="G55" s="17">
         <f t="shared" si="2"/>
-        <v>2.671942789</v>
+        <v>2.169411765</v>
       </c>
       <c r="H55" s="20">
         <f t="shared" si="3"/>
@@ -39483,7 +39255,7 @@
       </c>
       <c r="G56" s="17">
         <f t="shared" si="2"/>
-        <v>2.671942789</v>
+        <v>2.169411765</v>
       </c>
       <c r="H56" s="20">
         <f t="shared" si="3"/>
@@ -39513,7 +39285,7 @@
       </c>
       <c r="G57" s="17">
         <f t="shared" si="2"/>
-        <v>2.671942789</v>
+        <v>2.169411765</v>
       </c>
       <c r="H57" s="20">
         <f t="shared" si="3"/>
@@ -39543,7 +39315,7 @@
       </c>
       <c r="G58" s="17">
         <f t="shared" si="2"/>
-        <v>2.671942789</v>
+        <v>2.169411765</v>
       </c>
       <c r="H58" s="20">
         <f t="shared" si="3"/>
@@ -39573,7 +39345,7 @@
       </c>
       <c r="G59" s="17">
         <f t="shared" si="2"/>
-        <v>2.671942789</v>
+        <v>2.169411765</v>
       </c>
       <c r="H59" s="20">
         <f t="shared" si="3"/>
@@ -39603,7 +39375,7 @@
       </c>
       <c r="G60" s="17">
         <f t="shared" si="2"/>
-        <v>2.671942789</v>
+        <v>2.169411765</v>
       </c>
       <c r="H60" s="20">
         <f t="shared" si="3"/>
@@ -39633,7 +39405,7 @@
       </c>
       <c r="G61" s="17">
         <f t="shared" si="2"/>
-        <v>2.671942789</v>
+        <v>2.169411765</v>
       </c>
       <c r="H61" s="20">
         <f t="shared" si="3"/>
@@ -39663,7 +39435,7 @@
       </c>
       <c r="G62" s="17">
         <f t="shared" si="2"/>
-        <v>1.335971395</v>
+        <v>1.084705882</v>
       </c>
       <c r="H62" s="20">
         <f t="shared" si="3"/>
@@ -39693,7 +39465,7 @@
       </c>
       <c r="G63" s="17">
         <f t="shared" si="2"/>
-        <v>1.335971395</v>
+        <v>1.084705882</v>
       </c>
       <c r="H63" s="20">
         <f t="shared" si="3"/>
@@ -39723,7 +39495,7 @@
       </c>
       <c r="G64" s="17">
         <f t="shared" si="2"/>
-        <v>1.335971395</v>
+        <v>1.084705882</v>
       </c>
       <c r="H64" s="20">
         <f t="shared" si="3"/>
@@ -39753,7 +39525,7 @@
       </c>
       <c r="G65" s="17">
         <f t="shared" si="2"/>
-        <v>1.335971395</v>
+        <v>1.084705882</v>
       </c>
       <c r="H65" s="20">
         <f t="shared" si="3"/>
@@ -39783,7 +39555,7 @@
       </c>
       <c r="G66" s="17">
         <f t="shared" si="2"/>
-        <v>1.335971395</v>
+        <v>1.084705882</v>
       </c>
       <c r="H66" s="20">
         <f t="shared" si="3"/>
@@ -39813,7 +39585,7 @@
       </c>
       <c r="G67" s="17">
         <f t="shared" si="2"/>
-        <v>1.335971395</v>
+        <v>1.084705882</v>
       </c>
       <c r="H67" s="20">
         <f t="shared" si="3"/>
@@ -39843,7 +39615,7 @@
       </c>
       <c r="G68" s="17">
         <f t="shared" si="2"/>
-        <v>1.335971395</v>
+        <v>1.084705882</v>
       </c>
       <c r="H68" s="20">
         <f t="shared" si="3"/>
@@ -39873,7 +39645,7 @@
       </c>
       <c r="G69" s="17">
         <f t="shared" si="2"/>
-        <v>1.335971395</v>
+        <v>1.084705882</v>
       </c>
       <c r="H69" s="20">
         <f t="shared" si="3"/>
@@ -39903,7 +39675,7 @@
       </c>
       <c r="G70" s="17">
         <f t="shared" si="2"/>
-        <v>1.335971395</v>
+        <v>1.084705882</v>
       </c>
       <c r="H70" s="20">
         <f t="shared" si="3"/>
@@ -39933,7 +39705,7 @@
       </c>
       <c r="G71" s="17">
         <f t="shared" si="2"/>
-        <v>1.335971395</v>
+        <v>1.084705882</v>
       </c>
       <c r="H71" s="20">
         <f t="shared" si="3"/>
@@ -39963,7 +39735,7 @@
       </c>
       <c r="G72" s="17">
         <f t="shared" si="2"/>
-        <v>1.335971395</v>
+        <v>1.084705882</v>
       </c>
       <c r="H72" s="20">
         <f t="shared" si="3"/>
@@ -39993,7 +39765,7 @@
       </c>
       <c r="G73" s="17">
         <f t="shared" si="2"/>
-        <v>1.335971395</v>
+        <v>1.084705882</v>
       </c>
       <c r="H73" s="20">
         <f t="shared" si="3"/>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -17,13 +17,10 @@
     <t>PICK</t>
   </si>
   <si>
-    <t>VALUE</t>
-  </si>
-  <si>
     <t>Rank</t>
   </si>
   <si>
-    <t>Decay</t>
+    <t>VALUE</t>
   </si>
   <si>
     <t>PLAYER NAME</t>
@@ -32,7 +29,7 @@
     <t>PreDraft$</t>
   </si>
   <si>
-    <t>New Values</t>
+    <t>Decay</t>
   </si>
   <si>
     <t>Final Price</t>
@@ -41,10 +38,13 @@
     <t>Mine?</t>
   </si>
   <si>
-    <t>Spine</t>
+    <t>New Values</t>
   </si>
   <si>
     <t>Inflated Fair Price</t>
+  </si>
+  <si>
+    <t>Spine</t>
   </si>
   <si>
     <t>My Max Bid</t>
@@ -62,10 +62,10 @@
     <t>Floors</t>
   </si>
   <si>
-    <t>Fractions</t>
+    <t>Jeremiyah Love</t>
   </si>
   <si>
-    <t>Jeremiyah Love</t>
+    <t>Fractions</t>
   </si>
   <si>
     <t>Monotone Rounded</t>
@@ -143,9 +143,6 @@
     <t>CJ Allen</t>
   </si>
   <si>
-    <t>Round 2</t>
-  </si>
-  <si>
     <t>Undrafted Predraft$</t>
   </si>
   <si>
@@ -153,6 +150,9 @@
   </si>
   <si>
     <t>Inflation Factor</t>
+  </si>
+  <si>
+    <t>Round 2</t>
   </si>
   <si>
     <t>Ty Simpson</t>
@@ -164,13 +164,16 @@
     <t>Aggression</t>
   </si>
   <si>
+    <t>Round 3</t>
+  </si>
+  <si>
     <t>Caleb Downs</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>David Bailey</t>
   </si>
   <si>
-    <t>David Bailey</t>
+    <t>Round 4</t>
   </si>
   <si>
     <t>League Spent %</t>
@@ -182,6 +185,9 @@
     <t>Jonah Coleman</t>
   </si>
   <si>
+    <t>Round 5</t>
+  </si>
+  <si>
     <t>Jake Golday</t>
   </si>
   <si>
@@ -191,13 +197,13 @@
     <t>Rueben Bain</t>
   </si>
   <si>
+    <t>Round 6</t>
+  </si>
+  <si>
     <t>Chris Bell</t>
   </si>
   <si>
     <t>Germie Bernard</t>
-  </si>
-  <si>
-    <t>Round 4</t>
   </si>
   <si>
     <t>Nicholas Singleton</t>
@@ -227,9 +233,6 @@
     <t>Zachariah Branch</t>
   </si>
   <si>
-    <t>Round 5</t>
-  </si>
-  <si>
     <t>De'Zhaun Stribling</t>
   </si>
   <si>
@@ -255,9 +258,6 @@
   </si>
   <si>
     <t>Josiah Trotter</t>
-  </si>
-  <si>
-    <t>Round 6</t>
   </si>
   <si>
     <t>Dani Dennis-Sutton</t>
@@ -344,15 +344,6 @@
     <t>Garrett Nussmeier</t>
   </si>
   <si>
-    <t>Nate Boerkircher</t>
-  </si>
-  <si>
-    <t>Will Kacmarek</t>
-  </si>
-  <si>
-    <t>Noah Whittington</t>
-  </si>
-  <si>
     <t>Standings</t>
   </si>
   <si>
@@ -368,6 +359,9 @@
     <t>Owner (Final)</t>
   </si>
   <si>
+    <t>Nate Boerkircher</t>
+  </si>
+  <si>
     <t>Round</t>
   </si>
   <si>
@@ -378,6 +372,12 @@
   </si>
   <si>
     <t>Key</t>
+  </si>
+  <si>
+    <t>Will Kacmarek</t>
+  </si>
+  <si>
+    <t>Noah Whittington</t>
   </si>
   <si>
     <t>Ed</t>
@@ -568,13 +568,13 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF1B1C1D"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FF1B1C1D"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -614,16 +614,16 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -638,7 +638,7 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -648,25 +648,25 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
@@ -916,17 +916,17 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
+      <c r="B1" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F1" s="6">
         <v>2025.0</v>
@@ -941,7 +941,7 @@
         <v>15</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>18</v>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="8" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="8" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="8" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -3062,33 +3062,33 @@
       <c r="M29" s="12"/>
       <c r="N29" s="12"/>
       <c r="O29" s="8" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P29" s="8" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Q29" s="12"/>
       <c r="R29" s="8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="S29" s="8" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="T29" s="8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="U29" s="12"/>
       <c r="V29" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="W29" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="X29" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="W29" s="8" t="s">
+      <c r="Y29" s="8" t="s">
         <v>119</v>
-      </c>
-      <c r="X29" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="Y29" s="8" t="s">
-        <v>121</v>
       </c>
       <c r="Z29" s="12"/>
       <c r="AA29" s="12"/>
@@ -4175,7 +4175,7 @@
       <c r="M44" s="12"/>
       <c r="N44" s="12"/>
       <c r="O44" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="P44" s="8" t="s">
         <v>20</v>
@@ -4184,7 +4184,7 @@
         <v>134</v>
       </c>
       <c r="R44" s="8" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="S44" s="12"/>
       <c r="T44" s="12"/>
@@ -9212,7 +9212,7 @@
       <c r="U139" s="12"/>
       <c r="V139" s="12"/>
       <c r="W139" s="9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X139" s="9" t="s">
         <v>138</v>
@@ -9255,7 +9255,7 @@
         <v>1.0</v>
       </c>
       <c r="X140" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y140" s="9" t="s">
         <v>140</v>
@@ -9575,7 +9575,7 @@
         <v>10.0</v>
       </c>
       <c r="X148" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Y148" s="9" t="s">
         <v>145</v>
@@ -9615,7 +9615,7 @@
         <v>11.0</v>
       </c>
       <c r="X149" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Y149" s="9" t="s">
         <v>143</v>
@@ -9815,7 +9815,7 @@
         <v>16.0</v>
       </c>
       <c r="X154" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Y154" s="9" t="s">
         <v>143</v>
@@ -9855,7 +9855,7 @@
         <v>17.0</v>
       </c>
       <c r="X155" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Y155" s="9" t="s">
         <v>140</v>
@@ -9895,7 +9895,7 @@
         <v>18.0</v>
       </c>
       <c r="X156" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Y156" s="9" t="s">
         <v>145</v>
@@ -10135,7 +10135,7 @@
         <v>24.0</v>
       </c>
       <c r="X162" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Y162" s="9" t="s">
         <v>141</v>
@@ -10175,7 +10175,7 @@
         <v>25.0</v>
       </c>
       <c r="X163" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y163" s="9" t="s">
         <v>140</v>
@@ -10215,7 +10215,7 @@
         <v>26.0</v>
       </c>
       <c r="X164" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Y164" s="9" t="s">
         <v>140</v>
@@ -10335,7 +10335,7 @@
         <v>29.0</v>
       </c>
       <c r="X167" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Y167" s="9" t="s">
         <v>143</v>
@@ -10375,7 +10375,7 @@
         <v>30.0</v>
       </c>
       <c r="X168" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="Y168" s="9" t="s">
         <v>141</v>
@@ -10415,7 +10415,7 @@
         <v>31.0</v>
       </c>
       <c r="X169" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Y169" s="9" t="s">
         <v>141</v>
@@ -10495,7 +10495,7 @@
         <v>33.0</v>
       </c>
       <c r="X171" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y171" s="9" t="s">
         <v>141</v>
@@ -10575,7 +10575,7 @@
         <v>35.0</v>
       </c>
       <c r="X173" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Y173" s="9" t="s">
         <v>143</v>
@@ -10695,7 +10695,7 @@
         <v>38.0</v>
       </c>
       <c r="X176" s="9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="Y176" s="9" t="s">
         <v>141</v>
@@ -10735,7 +10735,7 @@
         <v>39.0</v>
       </c>
       <c r="X177" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Y177" s="9" t="s">
         <v>144</v>
@@ -10775,7 +10775,7 @@
         <v>40.0</v>
       </c>
       <c r="X178" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y178" s="9" t="s">
         <v>141</v>
@@ -10815,7 +10815,7 @@
         <v>41.0</v>
       </c>
       <c r="X179" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Y179" s="9" t="s">
         <v>141</v>
@@ -10855,7 +10855,7 @@
         <v>42.0</v>
       </c>
       <c r="X180" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Y180" s="9" t="s">
         <v>140</v>
@@ -11055,7 +11055,7 @@
         <v>47.0</v>
       </c>
       <c r="X185" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y185" s="9" t="s">
         <v>141</v>
@@ -11375,7 +11375,7 @@
         <v>55.0</v>
       </c>
       <c r="X193" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Y193" s="9" t="s">
         <v>141</v>
@@ -37443,23 +37443,23 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F1" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>11</v>
@@ -37467,25 +37467,25 @@
       <c r="H1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>1.0</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" s="10">
         <v>139.0</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3" t="b">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F2" s="10">
@@ -37522,15 +37522,15 @@
 </f>
         <v/>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="2">
         <v>1200.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>2.0</v>
       </c>
       <c r="B3" s="9" t="s">
@@ -37539,8 +37539,8 @@
       <c r="C3" s="10">
         <v>106.5</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3" t="b">
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F3" s="10">
@@ -37564,15 +37564,15 @@
 </f>
         <v/>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="2">
         <v>12.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>3.0</v>
       </c>
       <c r="B4" s="9" t="s">
@@ -37581,8 +37581,8 @@
       <c r="C4" s="10">
         <v>93.0</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3" t="b">
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F4" s="10">
@@ -37601,7 +37601,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L4" s="5">
@@ -37610,7 +37610,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>4.0</v>
       </c>
       <c r="B5" s="9" t="s">
@@ -37638,7 +37638,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="2" t="s">
         <v>27</v>
       </c>
       <c r="L5" s="17">
@@ -37648,7 +37648,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>5.0</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -37676,7 +37676,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="L6" s="17">
@@ -37686,7 +37686,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>6.0</v>
       </c>
       <c r="B7" s="9" t="s">
@@ -37714,7 +37714,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="L7" s="17">
@@ -37723,7 +37723,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <v>7.0</v>
       </c>
       <c r="B8" s="9" t="s">
@@ -37751,7 +37751,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="2" t="s">
         <v>34</v>
       </c>
       <c r="L8" s="10">
@@ -37761,7 +37761,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>8.0</v>
       </c>
       <c r="B9" s="9" t="s">
@@ -37789,7 +37789,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="2" t="s">
         <v>36</v>
       </c>
       <c r="L9" s="10">
@@ -37799,7 +37799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3">
+      <c r="A10" s="2">
         <v>9.0</v>
       </c>
       <c r="B10" s="9" t="s">
@@ -37827,7 +37827,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="K10" s="2" t="s">
         <v>38</v>
       </c>
       <c r="L10" s="10">
@@ -37836,7 +37836,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>10.0</v>
       </c>
       <c r="B11" s="9" t="s">
@@ -37864,7 +37864,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="K11" s="2" t="s">
         <v>40</v>
       </c>
       <c r="L11" s="19">
@@ -37873,7 +37873,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <v>11.0</v>
       </c>
       <c r="B12" s="9" t="s">
@@ -37903,7 +37903,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3">
+      <c r="A13" s="2">
         <v>12.0</v>
       </c>
       <c r="B13" s="9" t="s">
@@ -37931,8 +37931,8 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>44</v>
+      <c r="K13" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L13" s="17">
         <f>SUMIF($D$2:$D$73,"",$C$2:$C$73)</f>
@@ -37940,11 +37940,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3">
+      <c r="A14" s="2">
         <v>13.0</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" s="10">
         <v>30.5</v>
@@ -37968,8 +37968,8 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>46</v>
+      <c r="K14" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="L14" s="19">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -37977,7 +37977,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3">
+      <c r="A15" s="2">
         <v>14.0</v>
       </c>
       <c r="B15" s="9" t="s">
@@ -38007,7 +38007,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3">
+      <c r="A16" s="2">
         <v>15.0</v>
       </c>
       <c r="B16" s="9" t="s">
@@ -38035,10 +38035,10 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K16" s="3" t="s">
+      <c r="K16" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L16" s="3">
+      <c r="L16" s="2">
         <f>IF($L$18&lt;0.3,
      IF($L$11&gt;=1.3,0.09,
         IF($L$11&gt;=1.1,0.07,0.05)),
@@ -38054,11 +38054,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3">
+      <c r="A17" s="2">
         <v>16.0</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C17" s="10">
         <v>22.5</v>
@@ -38084,7 +38084,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3">
+      <c r="A18" s="2">
         <v>17.0</v>
       </c>
       <c r="B18" s="9" t="s">
@@ -38112,8 +38112,8 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>53</v>
+      <c r="K18" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="L18" s="20">
         <f>L5/L2</f>
@@ -38121,11 +38121,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3">
+      <c r="A19" s="2">
         <v>18.0</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" s="10">
         <v>18.5</v>
@@ -38151,11 +38151,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3">
+      <c r="A20" s="2">
         <v>19.0</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C20" s="10">
         <v>16.5</v>
@@ -38181,11 +38181,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3">
+      <c r="A21" s="2">
         <v>20.0</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C21" s="10">
         <v>14.5</v>
@@ -38211,11 +38211,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3">
+      <c r="A22" s="2">
         <v>21.0</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C22" s="10">
         <v>13.5</v>
@@ -38241,11 +38241,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3">
+      <c r="A23" s="2">
         <v>22.0</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C23" s="10">
         <v>12.0</v>
@@ -38271,11 +38271,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3">
+      <c r="A24" s="2">
         <v>23.0</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C24" s="10">
         <v>11.0</v>
@@ -38301,11 +38301,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3">
+      <c r="A25" s="2">
         <v>24.0</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C25" s="10">
         <v>10.0</v>
@@ -38331,11 +38331,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3">
+      <c r="A26" s="2">
         <v>25.0</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C26" s="10">
         <v>9.5</v>
@@ -38361,11 +38361,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3">
+      <c r="A27" s="2">
         <v>26.0</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C27" s="10">
         <v>8.5</v>
@@ -38389,19 +38389,19 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="K27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L27" s="2">
         <v>0.8</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3">
+      <c r="A28" s="2">
         <v>27.0</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C28" s="10">
         <v>8.0</v>
@@ -38427,11 +38427,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3">
+      <c r="A29" s="2">
         <v>28.0</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C29" s="10">
         <v>7.0</v>
@@ -38457,11 +38457,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3">
+      <c r="A30" s="2">
         <v>29.0</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C30" s="10">
         <v>6.5</v>
@@ -38487,11 +38487,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3">
+      <c r="A31" s="2">
         <v>30.0</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C31" s="10">
         <v>6.0</v>
@@ -38517,11 +38517,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3">
+      <c r="A32" s="2">
         <v>31.0</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C32" s="10">
         <v>5.5</v>
@@ -38547,11 +38547,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3">
+      <c r="A33" s="2">
         <v>32.0</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C33" s="10">
         <v>5.0</v>
@@ -38577,11 +38577,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3">
+      <c r="A34" s="2">
         <v>33.0</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C34" s="10">
         <v>4.5</v>
@@ -38607,11 +38607,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3">
+      <c r="A35" s="2">
         <v>34.0</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C35" s="10">
         <v>4.5</v>
@@ -38637,11 +38637,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3">
+      <c r="A36" s="2">
         <v>35.0</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C36" s="10">
         <v>4.0</v>
@@ -38667,11 +38667,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3">
+      <c r="A37" s="2">
         <v>36.0</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C37" s="10">
         <v>4.0</v>
@@ -38697,11 +38697,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3">
+      <c r="A38" s="2">
         <v>37.0</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C38" s="10">
         <v>3.5</v>
@@ -38727,11 +38727,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3">
+      <c r="A39" s="2">
         <v>38.0</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C39" s="10">
         <v>3.5</v>
@@ -38757,11 +38757,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3">
+      <c r="A40" s="2">
         <v>39.0</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C40" s="10">
         <v>3.0</v>
@@ -38787,11 +38787,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3">
+      <c r="A41" s="2">
         <v>40.0</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C41" s="10">
         <v>3.0</v>
@@ -38817,11 +38817,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3">
+      <c r="A42" s="2">
         <v>41.0</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C42" s="10">
         <v>2.5</v>
@@ -38847,7 +38847,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3">
+      <c r="A43" s="2">
         <v>42.0</v>
       </c>
       <c r="B43" s="9" t="s">
@@ -38877,7 +38877,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3">
+      <c r="A44" s="2">
         <v>43.0</v>
       </c>
       <c r="B44" s="9" t="s">
@@ -38907,7 +38907,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3">
+      <c r="A45" s="2">
         <v>44.0</v>
       </c>
       <c r="B45" s="9" t="s">
@@ -38937,7 +38937,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3">
+      <c r="A46" s="2">
         <v>45.0</v>
       </c>
       <c r="B46" s="9" t="s">
@@ -38967,7 +38967,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3">
+      <c r="A47" s="2">
         <v>46.0</v>
       </c>
       <c r="B47" s="9" t="s">
@@ -38997,7 +38997,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3">
+      <c r="A48" s="2">
         <v>47.0</v>
       </c>
       <c r="B48" s="9" t="s">
@@ -39027,7 +39027,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3">
+      <c r="A49" s="2">
         <v>48.0</v>
       </c>
       <c r="B49" s="9" t="s">
@@ -39057,7 +39057,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3">
+      <c r="A50" s="2">
         <v>49.0</v>
       </c>
       <c r="B50" s="9" t="s">
@@ -39087,7 +39087,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3">
+      <c r="A51" s="2">
         <v>50.0</v>
       </c>
       <c r="B51" s="9" t="s">
@@ -39117,7 +39117,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3">
+      <c r="A52" s="2">
         <v>51.0</v>
       </c>
       <c r="B52" s="9" t="s">
@@ -39147,7 +39147,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3">
+      <c r="A53" s="2">
         <v>52.0</v>
       </c>
       <c r="B53" s="9" t="s">
@@ -39177,7 +39177,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3">
+      <c r="A54" s="2">
         <v>53.0</v>
       </c>
       <c r="B54" s="9" t="s">
@@ -39207,7 +39207,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3">
+      <c r="A55" s="2">
         <v>54.0</v>
       </c>
       <c r="B55" s="9" t="s">
@@ -39237,7 +39237,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3">
+      <c r="A56" s="2">
         <v>55.0</v>
       </c>
       <c r="B56" s="9" t="s">
@@ -39267,7 +39267,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3">
+      <c r="A57" s="2">
         <v>56.0</v>
       </c>
       <c r="B57" s="9" t="s">
@@ -39297,7 +39297,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3">
+      <c r="A58" s="2">
         <v>57.0</v>
       </c>
       <c r="B58" s="9" t="s">
@@ -39327,7 +39327,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3">
+      <c r="A59" s="2">
         <v>58.0</v>
       </c>
       <c r="B59" s="9" t="s">
@@ -39357,7 +39357,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3">
+      <c r="A60" s="2">
         <v>59.0</v>
       </c>
       <c r="B60" s="9" t="s">
@@ -39387,7 +39387,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3">
+      <c r="A61" s="2">
         <v>60.0</v>
       </c>
       <c r="B61" s="9" t="s">
@@ -39417,7 +39417,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3">
+      <c r="A62" s="2">
         <v>61.0</v>
       </c>
       <c r="B62" s="9" t="s">
@@ -39447,7 +39447,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3">
+      <c r="A63" s="2">
         <v>62.0</v>
       </c>
       <c r="B63" s="9" t="s">
@@ -39477,7 +39477,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3">
+      <c r="A64" s="2">
         <v>63.0</v>
       </c>
       <c r="B64" s="9" t="s">
@@ -39507,7 +39507,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3">
+      <c r="A65" s="2">
         <v>64.0</v>
       </c>
       <c r="B65" s="9" t="s">
@@ -39537,7 +39537,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3">
+      <c r="A66" s="2">
         <v>65.0</v>
       </c>
       <c r="B66" s="9" t="s">
@@ -39567,7 +39567,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3">
+      <c r="A67" s="2">
         <v>66.0</v>
       </c>
       <c r="B67" s="9" t="s">
@@ -39597,7 +39597,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3">
+      <c r="A68" s="2">
         <v>67.0</v>
       </c>
       <c r="B68" s="9" t="s">
@@ -39627,7 +39627,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3">
+      <c r="A69" s="2">
         <v>68.0</v>
       </c>
       <c r="B69" s="9" t="s">
@@ -39657,7 +39657,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3">
+      <c r="A70" s="2">
         <v>69.0</v>
       </c>
       <c r="B70" s="9" t="s">
@@ -39687,11 +39687,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3">
+      <c r="A71" s="2">
         <v>70.0</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C71" s="10">
         <v>1.0</v>
@@ -39717,11 +39717,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3">
+      <c r="A72" s="2">
         <v>71.0</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="C72" s="10">
         <v>1.0</v>
@@ -39747,11 +39747,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3">
+      <c r="A73" s="2">
         <v>72.0</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>112</v>
+      <c r="B73" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="C73" s="10">
         <v>1.0</v>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -29,19 +29,19 @@
     <t>PreDraft$</t>
   </si>
   <si>
-    <t>Decay</t>
+    <t>Final Price</t>
   </si>
   <si>
-    <t>Final Price</t>
+    <t>Decay</t>
   </si>
   <si>
     <t>Mine?</t>
   </si>
   <si>
-    <t>New Values</t>
+    <t>Inflated Fair Price</t>
   </si>
   <si>
-    <t>Inflated Fair Price</t>
+    <t>New Values</t>
   </si>
   <si>
     <t>Spine</t>
@@ -56,19 +56,19 @@
     <t>Value vs Fair</t>
   </si>
   <si>
+    <t>Settings</t>
+  </si>
+  <si>
     <t>Floors</t>
   </si>
   <si>
-    <t>Settings</t>
+    <t>Jeremiyah Love</t>
   </si>
   <si>
     <t>Fractions</t>
   </si>
   <si>
     <t>Monotone Rounded</t>
-  </si>
-  <si>
-    <t>Jeremiyah Love</t>
   </si>
   <si>
     <t>Final Dollar Per Pick</t>
@@ -101,9 +101,6 @@
     <t>Makai Lemon</t>
   </si>
   <si>
-    <t>Round 1</t>
-  </si>
-  <si>
     <t>Remaining Leage $</t>
   </si>
   <si>
@@ -111,6 +108,9 @@
   </si>
   <si>
     <t>My Spent</t>
+  </si>
+  <si>
+    <t>Round 1</t>
   </si>
   <si>
     <t>Sonny Styles</t>
@@ -137,9 +137,6 @@
     <t>Budget Advantage Factor</t>
   </si>
   <si>
-    <t>Round 2</t>
-  </si>
-  <si>
     <t>Omar Cooper</t>
   </si>
   <si>
@@ -149,13 +146,13 @@
     <t>Undrafted Predraft$</t>
   </si>
   <si>
+    <t>Round 2</t>
+  </si>
+  <si>
     <t>Arvell Reese</t>
   </si>
   <si>
     <t>Inflation Factor</t>
-  </si>
-  <si>
-    <t>Round 3</t>
   </si>
   <si>
     <t>Ty Simpson</t>
@@ -167,7 +164,7 @@
     <t>Aggression</t>
   </si>
   <si>
-    <t>Round 4</t>
+    <t>Round 3</t>
   </si>
   <si>
     <t>Caleb Downs</t>
@@ -185,13 +182,13 @@
     <t>Jonah Coleman</t>
   </si>
   <si>
-    <t>Round 5</t>
-  </si>
-  <si>
     <t>Jake Golday</t>
   </si>
   <si>
     <t>Dillon Thieneman</t>
+  </si>
+  <si>
+    <t>Round 4</t>
   </si>
   <si>
     <t>Rueben Bain</t>
@@ -201,9 +198,6 @@
   </si>
   <si>
     <t>Germie Bernard</t>
-  </si>
-  <si>
-    <t>Round 6</t>
   </si>
   <si>
     <t>Nicholas Singleton</t>
@@ -225,6 +219,9 @@
   </si>
   <si>
     <t>Chris Brazzell</t>
+  </si>
+  <si>
+    <t>Round 5</t>
   </si>
   <si>
     <t>Max Klare</t>
@@ -255,6 +252,9 @@
   </si>
   <si>
     <t>A.J. Haulcy</t>
+  </si>
+  <si>
+    <t>Round 6</t>
   </si>
   <si>
     <t>Josiah Trotter</t>
@@ -920,10 +920,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>10</v>
@@ -938,13 +938,13 @@
         <v>2026.0</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L1" s="10" t="s">
         <v>19</v>
@@ -1071,7 +1071,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="8" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="8" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="8" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="8" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -9255,7 +9255,7 @@
         <v>1.0</v>
       </c>
       <c r="X140" s="9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y140" s="9" t="s">
         <v>140</v>
@@ -9495,7 +9495,7 @@
         <v>8.0</v>
       </c>
       <c r="X146" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Y146" s="9" t="s">
         <v>144</v>
@@ -9535,7 +9535,7 @@
         <v>9.0</v>
       </c>
       <c r="X147" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Y147" s="9" t="s">
         <v>141</v>
@@ -9575,7 +9575,7 @@
         <v>10.0</v>
       </c>
       <c r="X148" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y148" s="9" t="s">
         <v>145</v>
@@ -9655,7 +9655,7 @@
         <v>12.0</v>
       </c>
       <c r="X150" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Y150" s="9" t="s">
         <v>146</v>
@@ -9815,7 +9815,7 @@
         <v>16.0</v>
       </c>
       <c r="X154" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Y154" s="9" t="s">
         <v>143</v>
@@ -9855,7 +9855,7 @@
         <v>17.0</v>
       </c>
       <c r="X155" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Y155" s="9" t="s">
         <v>140</v>
@@ -9895,7 +9895,7 @@
         <v>18.0</v>
       </c>
       <c r="X156" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Y156" s="9" t="s">
         <v>145</v>
@@ -10095,7 +10095,7 @@
         <v>23.0</v>
       </c>
       <c r="X161" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Y161" s="9" t="s">
         <v>142</v>
@@ -10135,7 +10135,7 @@
         <v>24.0</v>
       </c>
       <c r="X162" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="Y162" s="9" t="s">
         <v>141</v>
@@ -10175,7 +10175,7 @@
         <v>25.0</v>
       </c>
       <c r="X163" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Y163" s="9" t="s">
         <v>140</v>
@@ -10215,7 +10215,7 @@
         <v>26.0</v>
       </c>
       <c r="X164" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Y164" s="9" t="s">
         <v>140</v>
@@ -10335,7 +10335,7 @@
         <v>29.0</v>
       </c>
       <c r="X167" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Y167" s="9" t="s">
         <v>143</v>
@@ -10375,7 +10375,7 @@
         <v>30.0</v>
       </c>
       <c r="X168" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Y168" s="9" t="s">
         <v>141</v>
@@ -10415,7 +10415,7 @@
         <v>31.0</v>
       </c>
       <c r="X169" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y169" s="9" t="s">
         <v>141</v>
@@ -10495,7 +10495,7 @@
         <v>33.0</v>
       </c>
       <c r="X171" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y171" s="9" t="s">
         <v>141</v>
@@ -10695,7 +10695,7 @@
         <v>38.0</v>
       </c>
       <c r="X176" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Y176" s="9" t="s">
         <v>141</v>
@@ -10735,7 +10735,7 @@
         <v>39.0</v>
       </c>
       <c r="X177" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Y177" s="9" t="s">
         <v>144</v>
@@ -10775,7 +10775,7 @@
         <v>40.0</v>
       </c>
       <c r="X178" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y178" s="9" t="s">
         <v>141</v>
@@ -10815,7 +10815,7 @@
         <v>41.0</v>
       </c>
       <c r="X179" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Y179" s="9" t="s">
         <v>141</v>
@@ -10855,7 +10855,7 @@
         <v>42.0</v>
       </c>
       <c r="X180" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Y180" s="9" t="s">
         <v>140</v>
@@ -11055,7 +11055,7 @@
         <v>47.0</v>
       </c>
       <c r="X185" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Y185" s="9" t="s">
         <v>141</v>
@@ -11375,7 +11375,7 @@
         <v>55.0</v>
       </c>
       <c r="X193" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Y193" s="9" t="s">
         <v>141</v>
@@ -37453,13 +37453,13 @@
         <v>4</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>11</v>
@@ -37471,7 +37471,7 @@
         <v>13</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
@@ -37479,7 +37479,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C2" s="11">
         <v>139.0</v>
@@ -37677,7 +37677,7 @@
         <v/>
       </c>
       <c r="K6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L6" s="17">
         <f>L2-L5
@@ -37690,7 +37690,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" s="11">
         <v>66.5</v>
@@ -37715,7 +37715,7 @@
         <v/>
       </c>
       <c r="K7" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L7" s="17">
         <f>SUMIF($E$2:$E$500,TRUE,$D$2:$D$500)</f>
@@ -37877,7 +37877,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="11">
         <v>39.0</v>
@@ -37907,7 +37907,7 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11">
         <v>34.0</v>
@@ -37932,7 +37932,7 @@
         <v/>
       </c>
       <c r="K13" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L13" s="17">
         <f>SUMIF($D$2:$D$73,"",$C$2:$C$73)</f>
@@ -37981,7 +37981,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" s="11">
         <v>27.5</v>
@@ -38011,7 +38011,7 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C16" s="11">
         <v>25.5</v>
@@ -38036,7 +38036,7 @@
         <v/>
       </c>
       <c r="K16" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L16" s="2">
         <f>IF($L$18&lt;0.3,
@@ -38058,7 +38058,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" s="11">
         <v>22.5</v>
@@ -38088,7 +38088,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="11">
         <v>20.0</v>
@@ -38113,7 +38113,7 @@
         <v/>
       </c>
       <c r="K18" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L18" s="20">
         <f>L5/L2</f>
@@ -38125,7 +38125,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C19" s="11">
         <v>18.5</v>
@@ -38155,7 +38155,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C20" s="11">
         <v>16.5</v>
@@ -38185,7 +38185,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C21" s="11">
         <v>14.5</v>
@@ -38215,7 +38215,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C22" s="11">
         <v>13.5</v>
@@ -38245,7 +38245,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C23" s="11">
         <v>12.0</v>
@@ -38275,7 +38275,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C24" s="11">
         <v>11.0</v>
@@ -38305,7 +38305,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C25" s="11">
         <v>10.0</v>
@@ -38335,7 +38335,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C26" s="11">
         <v>9.5</v>
@@ -38365,7 +38365,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C27" s="11">
         <v>8.5</v>
@@ -38390,7 +38390,7 @@
         <v/>
       </c>
       <c r="K27" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L27" s="2">
         <v>0.8</v>
@@ -38401,7 +38401,7 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C28" s="11">
         <v>8.0</v>
@@ -38431,7 +38431,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C29" s="11">
         <v>7.0</v>
@@ -38461,7 +38461,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C30" s="11">
         <v>6.5</v>
@@ -38491,7 +38491,7 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C31" s="11">
         <v>6.0</v>
@@ -38521,7 +38521,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C32" s="11">
         <v>5.5</v>
@@ -38551,7 +38551,7 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C33" s="11">
         <v>5.0</v>
@@ -38581,7 +38581,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C34" s="11">
         <v>4.5</v>
@@ -38611,7 +38611,7 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C35" s="11">
         <v>4.5</v>
@@ -38641,7 +38641,7 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C36" s="11">
         <v>4.0</v>
@@ -38671,7 +38671,7 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C37" s="11">
         <v>4.0</v>
@@ -38701,7 +38701,7 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C38" s="11">
         <v>3.5</v>
@@ -38731,7 +38731,7 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C39" s="11">
         <v>3.5</v>
@@ -38761,7 +38761,7 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C40" s="11">
         <v>3.0</v>
@@ -38791,7 +38791,7 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C41" s="11">
         <v>3.0</v>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -14,10 +14,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="178">
   <si>
-    <t>Rank</t>
+    <t>PICK</t>
   </si>
   <si>
-    <t>PICK</t>
+    <t>Rank</t>
   </si>
   <si>
     <t>PLAYER NAME</t>
@@ -98,6 +98,9 @@
     <t>Total Spent $</t>
   </si>
   <si>
+    <t>Round 1</t>
+  </si>
+  <si>
     <t>Makai Lemon</t>
   </si>
   <si>
@@ -105,9 +108,6 @@
   </si>
   <si>
     <t>Kenyon Sadiq</t>
-  </si>
-  <si>
-    <t>Round 1</t>
   </si>
   <si>
     <t>My Spent</t>
@@ -125,6 +125,9 @@
     <t>Other Teams Remaining</t>
   </si>
   <si>
+    <t>Round 2</t>
+  </si>
+  <si>
     <t>Jadarian Price</t>
   </si>
   <si>
@@ -137,19 +140,16 @@
     <t>Budget Advantage Factor</t>
   </si>
   <si>
-    <t>Round 2</t>
-  </si>
-  <si>
     <t>Omar Cooper</t>
   </si>
   <si>
     <t>CJ Allen</t>
   </si>
   <si>
-    <t>Undrafted Predraft$</t>
+    <t>Round 3</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>Undrafted Predraft$</t>
   </si>
   <si>
     <t>Arvell Reese</t>
@@ -164,10 +164,10 @@
     <t>Denzel Boston</t>
   </si>
   <si>
-    <t>Aggression</t>
+    <t>Round 4</t>
   </si>
   <si>
-    <t>Round 4</t>
+    <t>Aggression</t>
   </si>
   <si>
     <t>Caleb Downs</t>
@@ -176,13 +176,13 @@
     <t>David Bailey</t>
   </si>
   <si>
+    <t>Round 5</t>
+  </si>
+  <si>
     <t>League Spent %</t>
   </si>
   <si>
     <t>Jacob Rodriguez</t>
-  </si>
-  <si>
-    <t>Round 5</t>
   </si>
   <si>
     <t>Jonah Coleman</t>
@@ -194,6 +194,9 @@
     <t>Dillon Thieneman</t>
   </si>
   <si>
+    <t>Round 6</t>
+  </si>
+  <si>
     <t>Rueben Bain</t>
   </si>
   <si>
@@ -201,9 +204,6 @@
   </si>
   <si>
     <t>Germie Bernard</t>
-  </si>
-  <si>
-    <t>Round 6</t>
   </si>
   <si>
     <t>Nicholas Singleton</t>
@@ -914,7 +914,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>6</v>
@@ -1071,7 +1071,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="10" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -9212,7 +9212,7 @@
       <c r="U139" s="12"/>
       <c r="V139" s="12"/>
       <c r="W139" s="7" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X139" s="7" t="s">
         <v>138</v>
@@ -9375,7 +9375,7 @@
         <v>5.0</v>
       </c>
       <c r="X143" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y143" s="7" t="s">
         <v>141</v>
@@ -9495,7 +9495,7 @@
         <v>8.0</v>
       </c>
       <c r="X146" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Y146" s="7" t="s">
         <v>144</v>
@@ -9815,7 +9815,7 @@
         <v>16.0</v>
       </c>
       <c r="X154" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Y154" s="7" t="s">
         <v>143</v>
@@ -9975,7 +9975,7 @@
         <v>20.0</v>
       </c>
       <c r="X158" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Y158" s="7" t="s">
         <v>140</v>
@@ -10055,7 +10055,7 @@
         <v>22.0</v>
       </c>
       <c r="X160" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y160" s="7" t="s">
         <v>144</v>
@@ -10375,7 +10375,7 @@
         <v>30.0</v>
       </c>
       <c r="X168" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Y168" s="7" t="s">
         <v>141</v>
@@ -10695,7 +10695,7 @@
         <v>38.0</v>
       </c>
       <c r="X176" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Y176" s="7" t="s">
         <v>141</v>
@@ -37444,7 +37444,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -37652,7 +37652,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="9">
         <v>76.0</v>
@@ -37677,7 +37677,7 @@
         <v/>
       </c>
       <c r="K6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L6" s="17">
         <f>L2-L5
@@ -37690,7 +37690,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" s="9">
         <v>66.5</v>
@@ -37803,7 +37803,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" s="9">
         <v>48.0</v>
@@ -37828,7 +37828,7 @@
         <v/>
       </c>
       <c r="K10" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L10" s="9">
         <f>IF(L3&gt;1,L9/(L3-1),0)</f>
@@ -37840,7 +37840,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" s="9">
         <v>43.0</v>
@@ -37865,7 +37865,7 @@
         <v/>
       </c>
       <c r="K11" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L11" s="19">
         <f>IF(L10&gt;0,L8/L10,1)</f>
@@ -37932,7 +37932,7 @@
         <v/>
       </c>
       <c r="K13" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L13" s="17">
         <f>SUMIF($D$2:$D$73,"",$C$2:$C$73)</f>
@@ -38036,7 +38036,7 @@
         <v/>
       </c>
       <c r="K16" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L16" s="1">
         <f>IF($L$18&lt;0.3,
@@ -38113,7 +38113,7 @@
         <v/>
       </c>
       <c r="K18" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L18" s="20">
         <f>L5/L2</f>
@@ -38125,7 +38125,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C19" s="9">
         <v>18.5</v>
@@ -38245,7 +38245,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23" s="9">
         <v>12.0</v>
@@ -38275,7 +38275,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C24" s="9">
         <v>11.0</v>
@@ -38305,7 +38305,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C25" s="9">
         <v>10.0</v>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -14,10 +14,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="178">
   <si>
-    <t>Rank</t>
+    <t>PICK</t>
   </si>
   <si>
-    <t>PICK</t>
+    <t>Rank</t>
   </si>
   <si>
     <t>PLAYER NAME</t>
@@ -32,16 +32,25 @@
     <t>Mine?</t>
   </si>
   <si>
+    <t>VALUE</t>
+  </si>
+  <si>
     <t>Inflated Fair Price</t>
   </si>
   <si>
-    <t>VALUE</t>
+    <t>Decay</t>
   </si>
   <si>
     <t>My Max Bid</t>
   </si>
   <si>
+    <t>New Values</t>
+  </si>
+  <si>
     <t>EnforceUpTo</t>
+  </si>
+  <si>
+    <t>Spine</t>
   </si>
   <si>
     <t>Value vs Fair</t>
@@ -50,16 +59,7 @@
     <t>Settings</t>
   </si>
   <si>
-    <t>Decay</t>
-  </si>
-  <si>
     <t>Jeremiyah Love</t>
-  </si>
-  <si>
-    <t>New Values</t>
-  </si>
-  <si>
-    <t>Spine</t>
   </si>
   <si>
     <t>Floors</t>
@@ -107,10 +107,10 @@
     <t>Kenyon Sadiq</t>
   </si>
   <si>
-    <t>My Spent</t>
+    <t>Round 1</t>
   </si>
   <si>
-    <t>Round 1</t>
+    <t>My Spent</t>
   </si>
   <si>
     <t>Sonny Styles</t>
@@ -140,13 +140,13 @@
     <t>Omar Cooper</t>
   </si>
   <si>
+    <t>Round 2</t>
+  </si>
+  <si>
     <t>CJ Allen</t>
   </si>
   <si>
     <t>Undrafted Predraft$</t>
-  </si>
-  <si>
-    <t>Round 2</t>
   </si>
   <si>
     <t>Arvell Reese</t>
@@ -161,16 +161,16 @@
     <t>Denzel Boston</t>
   </si>
   <si>
+    <t>Round 3</t>
+  </si>
+  <si>
     <t>Aggression</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>Round 4</t>
   </si>
   <si>
     <t>Caleb Downs</t>
-  </si>
-  <si>
-    <t>Round 4</t>
   </si>
   <si>
     <t>David Bailey</t>
@@ -185,10 +185,10 @@
     <t>Jonah Coleman</t>
   </si>
   <si>
-    <t>Jake Golday</t>
+    <t>Round 5</t>
   </si>
   <si>
-    <t>Round 5</t>
+    <t>Jake Golday</t>
   </si>
   <si>
     <t>Dillon Thieneman</t>
@@ -198,6 +198,9 @@
   </si>
   <si>
     <t>Chris Bell</t>
+  </si>
+  <si>
+    <t>Round 6</t>
   </si>
   <si>
     <t>Germie Bernard</t>
@@ -213,9 +216,6 @@
   </si>
   <si>
     <t>Antonio Williams</t>
-  </si>
-  <si>
-    <t>Round 6</t>
   </si>
   <si>
     <t>Elijah Sarratt</t>
@@ -617,20 +617,20 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -914,24 +914,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="7">
+      <c r="F1" s="6">
         <v>2025.0</v>
       </c>
-      <c r="G1" s="7">
+      <c r="G1" s="6">
         <v>2024.0</v>
       </c>
       <c r="H1" s="9">
@@ -949,52 +949,52 @@
       <c r="L1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="7">
+      <c r="M1" s="6">
         <v>12.0</v>
       </c>
       <c r="N1" s="12"/>
       <c r="O1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="7">
+      <c r="P1" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q1" s="7">
+      <c r="Q1" s="6">
         <v>2.0</v>
       </c>
-      <c r="R1" s="7">
+      <c r="R1" s="6">
         <v>3.0</v>
       </c>
-      <c r="S1" s="7">
+      <c r="S1" s="6">
         <v>4.0</v>
       </c>
-      <c r="T1" s="7">
+      <c r="T1" s="6">
         <v>5.0</v>
       </c>
-      <c r="U1" s="7">
+      <c r="U1" s="6">
         <v>6.0</v>
       </c>
-      <c r="V1" s="7">
+      <c r="V1" s="6">
         <v>7.0</v>
       </c>
-      <c r="W1" s="7">
+      <c r="W1" s="6">
         <v>8.0</v>
       </c>
-      <c r="X1" s="7">
+      <c r="X1" s="6">
         <v>9.0</v>
       </c>
-      <c r="Y1" s="7">
+      <c r="Y1" s="6">
         <v>10.0</v>
       </c>
-      <c r="Z1" s="7">
+      <c r="Z1" s="6">
         <v>11.0</v>
       </c>
-      <c r="AA1" s="7">
+      <c r="AA1" s="6">
         <v>12.0</v>
       </c>
       <c r="AB1" s="10"/>
       <c r="AC1" s="10"/>
-      <c r="AD1" s="7">
+      <c r="AD1" s="6">
         <f>1200 / SUM($P$2:$AA$7)</f>
         <v>1</v>
       </c>
@@ -1003,7 +1003,7 @@
       <c r="A2" s="13">
         <v>1.01</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="4">
         <v>7580.0</v>
       </c>
       <c r="C2" s="16">
@@ -1071,7 +1071,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1132,7 +1132,7 @@
       <c r="A3" s="13">
         <v>1.02</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>5598.5</v>
       </c>
       <c r="C3" s="16">
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1241,7 +1241,7 @@
       <c r="A4" s="13">
         <v>1.03</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>5649.0</v>
       </c>
       <c r="C4" s="16">
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1345,7 +1345,7 @@
       <c r="A5" s="13">
         <v>1.04</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>5074.5</v>
       </c>
       <c r="C5" s="16">
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1449,7 +1449,7 @@
       <c r="A6" s="13">
         <v>1.05</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="4">
         <v>5076.0</v>
       </c>
       <c r="C6" s="16">
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1553,7 +1553,7 @@
       <c r="A7" s="13">
         <v>1.06</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>4965.0</v>
       </c>
       <c r="C7" s="16">
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="10" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1657,7 +1657,7 @@
       <c r="A8" s="13">
         <v>1.07</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="4">
         <v>4014.5</v>
       </c>
       <c r="C8" s="16">
@@ -1759,7 +1759,7 @@
       <c r="A9" s="13">
         <v>1.08</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="4">
         <v>4308.0</v>
       </c>
       <c r="C9" s="16">
@@ -1822,7 +1822,7 @@
       <c r="A10" s="13">
         <v>1.09</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="4">
         <v>3869.0</v>
       </c>
       <c r="C10" s="16">
@@ -1885,7 +1885,7 @@
       <c r="A11" s="13">
         <v>1.1</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="4">
         <v>4169.0</v>
       </c>
       <c r="C11" s="16">
@@ -1948,7 +1948,7 @@
       <c r="A12" s="13">
         <v>1.11</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="4">
         <v>4164.0</v>
       </c>
       <c r="C12" s="16">
@@ -2011,7 +2011,7 @@
       <c r="A13" s="13">
         <v>1.12</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="4">
         <v>3809.5</v>
       </c>
       <c r="C13" s="16">
@@ -2074,7 +2074,7 @@
       <c r="A14" s="13">
         <v>2.01</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="4">
         <v>3397.5</v>
       </c>
       <c r="C14" s="16">
@@ -2137,7 +2137,7 @@
       <c r="A15" s="13">
         <v>2.02</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="4">
         <v>3611.0</v>
       </c>
       <c r="C15" s="16">
@@ -2200,7 +2200,7 @@
       <c r="A16" s="13">
         <v>2.03</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="4">
         <v>3605.0</v>
       </c>
       <c r="C16" s="16">
@@ -2263,7 +2263,7 @@
       <c r="A17" s="13">
         <v>2.04</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="4">
         <v>3603.0</v>
       </c>
       <c r="C17" s="16">
@@ -2326,7 +2326,7 @@
       <c r="A18" s="13">
         <v>2.05</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="4">
         <v>3440.5</v>
       </c>
       <c r="C18" s="16">
@@ -2389,7 +2389,7 @@
       <c r="A19" s="13">
         <v>2.06</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="4">
         <v>3220.0</v>
       </c>
       <c r="C19" s="16">
@@ -2452,7 +2452,7 @@
       <c r="A20" s="13">
         <v>2.07</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="4">
         <v>3200.0</v>
       </c>
       <c r="C20" s="16">
@@ -2515,7 +2515,7 @@
       <c r="A21" s="13">
         <v>2.08</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="4">
         <v>3127.0</v>
       </c>
       <c r="C21" s="16">
@@ -2578,7 +2578,7 @@
       <c r="A22" s="13">
         <v>2.09</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="4">
         <v>2943.0</v>
       </c>
       <c r="C22" s="16">
@@ -2641,7 +2641,7 @@
       <c r="A23" s="13">
         <v>2.1</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="4">
         <v>3020.0</v>
       </c>
       <c r="C23" s="16">
@@ -2704,7 +2704,7 @@
       <c r="A24" s="13">
         <v>2.11</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="4">
         <v>2537.5</v>
       </c>
       <c r="C24" s="16">
@@ -2767,7 +2767,7 @@
       <c r="A25" s="13">
         <v>2.12</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="4">
         <v>2406.0</v>
       </c>
       <c r="C25" s="16">
@@ -2830,7 +2830,7 @@
       <c r="A26" s="13">
         <v>3.01</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="4">
         <v>2671.0</v>
       </c>
       <c r="C26" s="16">
@@ -2893,7 +2893,7 @@
       <c r="A27" s="13">
         <v>3.02</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="4">
         <v>2628.0</v>
       </c>
       <c r="C27" s="16">
@@ -2956,7 +2956,7 @@
       <c r="A28" s="13">
         <v>3.03</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="4">
         <v>1998.5</v>
       </c>
       <c r="C28" s="16">
@@ -3019,7 +3019,7 @@
       <c r="A29" s="13">
         <v>3.04</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="4">
         <v>2202.5</v>
       </c>
       <c r="C29" s="16">
@@ -3100,7 +3100,7 @@
       <c r="A30" s="13">
         <v>3.05</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="4">
         <v>2252.5</v>
       </c>
       <c r="C30" s="16">
@@ -3142,14 +3142,14 @@
       </c>
       <c r="M30" s="12"/>
       <c r="N30" s="12"/>
-      <c r="O30" s="7">
+      <c r="O30" s="6">
         <v>1.0</v>
       </c>
       <c r="P30" s="10" t="s">
         <v>122</v>
       </c>
       <c r="Q30" s="12"/>
-      <c r="R30" s="7">
+      <c r="R30" s="6">
         <v>12.0</v>
       </c>
       <c r="S30" s="12"/>
@@ -3160,7 +3160,7 @@
       <c r="U30" s="12"/>
       <c r="V30" s="23"/>
       <c r="W30" s="23"/>
-      <c r="X30" s="6"/>
+      <c r="X30" s="7"/>
       <c r="Y30" s="12" t="str">
         <f t="shared" ref="Y30:Y81" si="17">TEXT(V30,"0")&amp;"|"&amp;TRIM(W30)</f>
         <v>0|</v>
@@ -3175,7 +3175,7 @@
       <c r="A31" s="13">
         <v>3.06</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="4">
         <v>2458.0</v>
       </c>
       <c r="C31" s="16">
@@ -3217,14 +3217,14 @@
       </c>
       <c r="M31" s="12"/>
       <c r="N31" s="12"/>
-      <c r="O31" s="7">
+      <c r="O31" s="6">
         <v>2.0</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>123</v>
       </c>
       <c r="Q31" s="12"/>
-      <c r="R31" s="7">
+      <c r="R31" s="6">
         <v>11.0</v>
       </c>
       <c r="S31" s="12"/>
@@ -3234,8 +3234,8 @@
       </c>
       <c r="U31" s="12"/>
       <c r="V31" s="9"/>
-      <c r="W31" s="6"/>
-      <c r="X31" s="6"/>
+      <c r="W31" s="7"/>
+      <c r="X31" s="7"/>
       <c r="Y31" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3250,7 +3250,7 @@
       <c r="A32" s="13">
         <v>3.07</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="4">
         <v>2332.5</v>
       </c>
       <c r="C32" s="16">
@@ -3292,14 +3292,14 @@
       </c>
       <c r="M32" s="12"/>
       <c r="N32" s="12"/>
-      <c r="O32" s="7">
+      <c r="O32" s="6">
         <v>3.0</v>
       </c>
       <c r="P32" s="10" t="s">
         <v>124</v>
       </c>
       <c r="Q32" s="12"/>
-      <c r="R32" s="7">
+      <c r="R32" s="6">
         <v>10.0</v>
       </c>
       <c r="S32" s="12"/>
@@ -3309,8 +3309,8 @@
       </c>
       <c r="U32" s="12"/>
       <c r="V32" s="9"/>
-      <c r="W32" s="6"/>
-      <c r="X32" s="6"/>
+      <c r="W32" s="7"/>
+      <c r="X32" s="7"/>
       <c r="Y32" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3325,7 +3325,7 @@
       <c r="A33" s="13">
         <v>3.08</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="4">
         <v>2331.0</v>
       </c>
       <c r="C33" s="16">
@@ -3367,14 +3367,14 @@
       </c>
       <c r="M33" s="12"/>
       <c r="N33" s="12"/>
-      <c r="O33" s="7">
+      <c r="O33" s="6">
         <v>4.0</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>125</v>
       </c>
       <c r="Q33" s="12"/>
-      <c r="R33" s="7">
+      <c r="R33" s="6">
         <v>9.0</v>
       </c>
       <c r="S33" s="12"/>
@@ -3384,8 +3384,8 @@
       </c>
       <c r="U33" s="12"/>
       <c r="V33" s="9"/>
-      <c r="W33" s="6"/>
-      <c r="X33" s="6"/>
+      <c r="W33" s="7"/>
+      <c r="X33" s="7"/>
       <c r="Y33" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3400,7 +3400,7 @@
       <c r="A34" s="13">
         <v>3.09</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="4">
         <v>1991.0</v>
       </c>
       <c r="C34" s="16">
@@ -3442,14 +3442,14 @@
       </c>
       <c r="M34" s="12"/>
       <c r="N34" s="12"/>
-      <c r="O34" s="7">
+      <c r="O34" s="6">
         <v>5.0</v>
       </c>
       <c r="P34" s="10" t="s">
         <v>126</v>
       </c>
       <c r="Q34" s="12"/>
-      <c r="R34" s="7">
+      <c r="R34" s="6">
         <v>8.0</v>
       </c>
       <c r="S34" s="12"/>
@@ -3459,8 +3459,8 @@
       </c>
       <c r="U34" s="12"/>
       <c r="V34" s="9"/>
-      <c r="W34" s="6"/>
-      <c r="X34" s="6"/>
+      <c r="W34" s="7"/>
+      <c r="X34" s="7"/>
       <c r="Y34" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3475,7 +3475,7 @@
       <c r="A35" s="13">
         <v>3.1</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="4">
         <v>2180.5</v>
       </c>
       <c r="C35" s="16">
@@ -3517,14 +3517,14 @@
       </c>
       <c r="M35" s="12"/>
       <c r="N35" s="12"/>
-      <c r="O35" s="7">
+      <c r="O35" s="6">
         <v>6.0</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>127</v>
       </c>
       <c r="Q35" s="12"/>
-      <c r="R35" s="7">
+      <c r="R35" s="6">
         <v>7.0</v>
       </c>
       <c r="S35" s="12"/>
@@ -3534,8 +3534,8 @@
       </c>
       <c r="U35" s="12"/>
       <c r="V35" s="9"/>
-      <c r="W35" s="6"/>
-      <c r="X35" s="6"/>
+      <c r="W35" s="7"/>
+      <c r="X35" s="7"/>
       <c r="Y35" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3550,7 +3550,7 @@
       <c r="A36" s="13">
         <v>3.11</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="4">
         <v>2432.0</v>
       </c>
       <c r="C36" s="16">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="M36" s="12"/>
       <c r="N36" s="12"/>
-      <c r="O36" s="7">
+      <c r="O36" s="6">
         <v>7.0</v>
       </c>
       <c r="P36" s="10" t="s">
         <v>128</v>
       </c>
       <c r="Q36" s="12"/>
-      <c r="R36" s="7">
+      <c r="R36" s="6">
         <v>6.0</v>
       </c>
       <c r="S36" s="12"/>
@@ -3609,8 +3609,8 @@
       </c>
       <c r="U36" s="12"/>
       <c r="V36" s="9"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="6"/>
+      <c r="W36" s="7"/>
+      <c r="X36" s="7"/>
       <c r="Y36" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3625,7 +3625,7 @@
       <c r="A37" s="13">
         <v>3.12</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="4">
         <v>2014.0</v>
       </c>
       <c r="C37" s="16">
@@ -3667,14 +3667,14 @@
       </c>
       <c r="M37" s="12"/>
       <c r="N37" s="12"/>
-      <c r="O37" s="7">
+      <c r="O37" s="6">
         <v>8.0</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>129</v>
       </c>
       <c r="Q37" s="12"/>
-      <c r="R37" s="7">
+      <c r="R37" s="6">
         <v>5.0</v>
       </c>
       <c r="S37" s="12"/>
@@ -3684,8 +3684,8 @@
       </c>
       <c r="U37" s="12"/>
       <c r="V37" s="9"/>
-      <c r="W37" s="6"/>
-      <c r="X37" s="6"/>
+      <c r="W37" s="7"/>
+      <c r="X37" s="7"/>
       <c r="Y37" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3700,7 +3700,7 @@
       <c r="A38" s="13">
         <v>4.01</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="4">
         <v>1907.0</v>
       </c>
       <c r="C38" s="16">
@@ -3742,14 +3742,14 @@
       </c>
       <c r="M38" s="12"/>
       <c r="N38" s="12"/>
-      <c r="O38" s="7">
+      <c r="O38" s="6">
         <v>9.0</v>
       </c>
       <c r="P38" s="10" t="s">
         <v>130</v>
       </c>
       <c r="Q38" s="12"/>
-      <c r="R38" s="7">
+      <c r="R38" s="6">
         <v>4.0</v>
       </c>
       <c r="S38" s="12"/>
@@ -3759,8 +3759,8 @@
       </c>
       <c r="U38" s="12"/>
       <c r="V38" s="9"/>
-      <c r="W38" s="6"/>
-      <c r="X38" s="6"/>
+      <c r="W38" s="7"/>
+      <c r="X38" s="7"/>
       <c r="Y38" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3775,7 +3775,7 @@
       <c r="A39" s="13">
         <v>4.02</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39" s="4">
         <v>2089.0</v>
       </c>
       <c r="C39" s="16">
@@ -3817,14 +3817,14 @@
       </c>
       <c r="M39" s="12"/>
       <c r="N39" s="12"/>
-      <c r="O39" s="7">
+      <c r="O39" s="6">
         <v>10.0</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>131</v>
       </c>
       <c r="Q39" s="12"/>
-      <c r="R39" s="7">
+      <c r="R39" s="6">
         <v>3.0</v>
       </c>
       <c r="S39" s="12"/>
@@ -3834,8 +3834,8 @@
       </c>
       <c r="U39" s="12"/>
       <c r="V39" s="9"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="6"/>
+      <c r="W39" s="7"/>
+      <c r="X39" s="7"/>
       <c r="Y39" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3850,7 +3850,7 @@
       <c r="A40" s="13">
         <v>4.03</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40" s="4">
         <v>2080.0</v>
       </c>
       <c r="C40" s="16">
@@ -3892,14 +3892,14 @@
       </c>
       <c r="M40" s="12"/>
       <c r="N40" s="12"/>
-      <c r="O40" s="7">
+      <c r="O40" s="6">
         <v>11.0</v>
       </c>
       <c r="P40" s="10" t="s">
         <v>132</v>
       </c>
       <c r="Q40" s="12"/>
-      <c r="R40" s="7">
+      <c r="R40" s="6">
         <v>2.0</v>
       </c>
       <c r="S40" s="12"/>
@@ -3909,8 +3909,8 @@
       </c>
       <c r="U40" s="12"/>
       <c r="V40" s="9"/>
-      <c r="W40" s="6"/>
-      <c r="X40" s="6"/>
+      <c r="W40" s="7"/>
+      <c r="X40" s="7"/>
       <c r="Y40" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3925,7 +3925,7 @@
       <c r="A41" s="13">
         <v>4.04</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B41" s="4">
         <v>2063.0</v>
       </c>
       <c r="C41" s="16">
@@ -3967,14 +3967,14 @@
       </c>
       <c r="M41" s="12"/>
       <c r="N41" s="12"/>
-      <c r="O41" s="7">
+      <c r="O41" s="6">
         <v>12.0</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>133</v>
       </c>
       <c r="Q41" s="12"/>
-      <c r="R41" s="7">
+      <c r="R41" s="6">
         <v>1.0</v>
       </c>
       <c r="S41" s="12"/>
@@ -3984,8 +3984,8 @@
       </c>
       <c r="U41" s="12"/>
       <c r="V41" s="9"/>
-      <c r="W41" s="6"/>
-      <c r="X41" s="6"/>
+      <c r="W41" s="7"/>
+      <c r="X41" s="7"/>
       <c r="Y41" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4050,8 +4050,8 @@
       <c r="T42" s="12"/>
       <c r="U42" s="12"/>
       <c r="V42" s="9"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="6"/>
+      <c r="W42" s="7"/>
+      <c r="X42" s="7"/>
       <c r="Y42" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4066,7 +4066,7 @@
       <c r="A43" s="13">
         <v>4.06</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43" s="4">
         <v>1539.5</v>
       </c>
       <c r="C43" s="16">
@@ -4116,8 +4116,8 @@
       <c r="T43" s="12"/>
       <c r="U43" s="12"/>
       <c r="V43" s="9"/>
-      <c r="W43" s="6"/>
-      <c r="X43" s="6"/>
+      <c r="W43" s="7"/>
+      <c r="X43" s="7"/>
       <c r="Y43" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4132,7 +4132,7 @@
       <c r="A44" s="13">
         <v>4.07</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B44" s="4">
         <v>1956.0</v>
       </c>
       <c r="C44" s="16">
@@ -4190,8 +4190,8 @@
       <c r="T44" s="12"/>
       <c r="U44" s="12"/>
       <c r="V44" s="9"/>
-      <c r="W44" s="6"/>
-      <c r="X44" s="6"/>
+      <c r="W44" s="7"/>
+      <c r="X44" s="7"/>
       <c r="Y44" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4206,7 +4206,7 @@
       <c r="A45" s="13">
         <v>4.08</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45" s="4">
         <v>1953.0</v>
       </c>
       <c r="C45" s="16">
@@ -4280,8 +4280,8 @@
       <c r="T45" s="12"/>
       <c r="U45" s="12"/>
       <c r="V45" s="9"/>
-      <c r="W45" s="6"/>
-      <c r="X45" s="6"/>
+      <c r="W45" s="7"/>
+      <c r="X45" s="7"/>
       <c r="Y45" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4296,7 +4296,7 @@
       <c r="A46" s="13">
         <v>4.09</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B46" s="4">
         <v>1945.0</v>
       </c>
       <c r="C46" s="16">
@@ -4358,8 +4358,8 @@
       <c r="T46" s="12"/>
       <c r="U46" s="12"/>
       <c r="V46" s="9"/>
-      <c r="W46" s="6"/>
-      <c r="X46" s="6"/>
+      <c r="W46" s="7"/>
+      <c r="X46" s="7"/>
       <c r="Y46" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4374,7 +4374,7 @@
       <c r="A47" s="13">
         <v>4.1</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B47" s="4">
         <v>1938.0</v>
       </c>
       <c r="C47" s="16">
@@ -4436,8 +4436,8 @@
       <c r="T47" s="12"/>
       <c r="U47" s="12"/>
       <c r="V47" s="9"/>
-      <c r="W47" s="6"/>
-      <c r="X47" s="6"/>
+      <c r="W47" s="7"/>
+      <c r="X47" s="7"/>
       <c r="Y47" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4452,7 +4452,7 @@
       <c r="A48" s="13">
         <v>4.11</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48" s="4">
         <v>1926.0</v>
       </c>
       <c r="C48" s="16">
@@ -4514,8 +4514,8 @@
       <c r="T48" s="12"/>
       <c r="U48" s="12"/>
       <c r="V48" s="9"/>
-      <c r="W48" s="6"/>
-      <c r="X48" s="6"/>
+      <c r="W48" s="7"/>
+      <c r="X48" s="7"/>
       <c r="Y48" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4530,7 +4530,7 @@
       <c r="A49" s="13">
         <v>4.12</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B49" s="4">
         <v>1917.0</v>
       </c>
       <c r="C49" s="16">
@@ -4592,8 +4592,8 @@
       <c r="T49" s="12"/>
       <c r="U49" s="12"/>
       <c r="V49" s="9"/>
-      <c r="W49" s="6"/>
-      <c r="X49" s="6"/>
+      <c r="W49" s="7"/>
+      <c r="X49" s="7"/>
       <c r="Y49" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4608,7 +4608,7 @@
       <c r="A50" s="13">
         <v>5.01</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50" s="4">
         <v>1917.0</v>
       </c>
       <c r="C50" s="16">
@@ -4670,8 +4670,8 @@
       <c r="T50" s="12"/>
       <c r="U50" s="12"/>
       <c r="V50" s="9"/>
-      <c r="W50" s="6"/>
-      <c r="X50" s="6"/>
+      <c r="W50" s="7"/>
+      <c r="X50" s="7"/>
       <c r="Y50" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4686,7 +4686,7 @@
       <c r="A51" s="13">
         <v>5.02</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B51" s="4">
         <v>1916.0</v>
       </c>
       <c r="C51" s="16">
@@ -4748,8 +4748,8 @@
       <c r="T51" s="12"/>
       <c r="U51" s="12"/>
       <c r="V51" s="9"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="6"/>
+      <c r="W51" s="7"/>
+      <c r="X51" s="7"/>
       <c r="Y51" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4764,7 +4764,7 @@
       <c r="A52" s="13">
         <v>5.03</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52" s="4">
         <v>1647.5</v>
       </c>
       <c r="C52" s="16">
@@ -4826,8 +4826,8 @@
       <c r="T52" s="12"/>
       <c r="U52" s="12"/>
       <c r="V52" s="9"/>
-      <c r="W52" s="6"/>
-      <c r="X52" s="6"/>
+      <c r="W52" s="7"/>
+      <c r="X52" s="7"/>
       <c r="Y52" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4842,7 +4842,7 @@
       <c r="A53" s="13">
         <v>5.04</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B53" s="4">
         <v>1374.0</v>
       </c>
       <c r="C53" s="16">
@@ -4904,8 +4904,8 @@
       <c r="T53" s="12"/>
       <c r="U53" s="12"/>
       <c r="V53" s="9"/>
-      <c r="W53" s="6"/>
-      <c r="X53" s="6"/>
+      <c r="W53" s="7"/>
+      <c r="X53" s="7"/>
       <c r="Y53" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4920,7 +4920,7 @@
       <c r="A54" s="13">
         <v>5.05</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B54" s="4">
         <v>1424.0</v>
       </c>
       <c r="C54" s="16">
@@ -4982,8 +4982,8 @@
       <c r="T54" s="12"/>
       <c r="U54" s="12"/>
       <c r="V54" s="9"/>
-      <c r="W54" s="6"/>
-      <c r="X54" s="6"/>
+      <c r="W54" s="7"/>
+      <c r="X54" s="7"/>
       <c r="Y54" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4998,7 +4998,7 @@
       <c r="A55" s="13">
         <v>5.06</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B55" s="4">
         <v>1370.5</v>
       </c>
       <c r="C55" s="16">
@@ -5060,8 +5060,8 @@
       <c r="T55" s="12"/>
       <c r="U55" s="12"/>
       <c r="V55" s="9"/>
-      <c r="W55" s="6"/>
-      <c r="X55" s="6"/>
+      <c r="W55" s="7"/>
+      <c r="X55" s="7"/>
       <c r="Y55" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5076,7 +5076,7 @@
       <c r="A56" s="13">
         <v>5.07</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B56" s="4">
         <v>1643.0</v>
       </c>
       <c r="C56" s="16">
@@ -5138,8 +5138,8 @@
       <c r="T56" s="12"/>
       <c r="U56" s="12"/>
       <c r="V56" s="9"/>
-      <c r="W56" s="6"/>
-      <c r="X56" s="6"/>
+      <c r="W56" s="7"/>
+      <c r="X56" s="7"/>
       <c r="Y56" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5154,7 +5154,7 @@
       <c r="A57" s="13">
         <v>5.08</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B57" s="4">
         <v>1628.0</v>
       </c>
       <c r="C57" s="16">
@@ -5216,8 +5216,8 @@
       <c r="T57" s="12"/>
       <c r="U57" s="12"/>
       <c r="V57" s="9"/>
-      <c r="W57" s="6"/>
-      <c r="X57" s="6"/>
+      <c r="W57" s="7"/>
+      <c r="X57" s="7"/>
       <c r="Y57" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5232,7 +5232,7 @@
       <c r="A58" s="13">
         <v>5.09</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58" s="4">
         <v>1302.0</v>
       </c>
       <c r="C58" s="16">
@@ -5295,7 +5295,7 @@
       <c r="U58" s="12"/>
       <c r="V58" s="23"/>
       <c r="W58" s="23"/>
-      <c r="X58" s="6"/>
+      <c r="X58" s="7"/>
       <c r="Y58" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5310,7 +5310,7 @@
       <c r="A59" s="13">
         <v>5.1</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B59" s="4">
         <v>1284.0</v>
       </c>
       <c r="C59" s="16">
@@ -5373,7 +5373,7 @@
       <c r="U59" s="12"/>
       <c r="V59" s="23"/>
       <c r="W59" s="23"/>
-      <c r="X59" s="6"/>
+      <c r="X59" s="7"/>
       <c r="Y59" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5388,7 +5388,7 @@
       <c r="A60" s="13">
         <v>5.11</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B60" s="4">
         <v>1254.0</v>
       </c>
       <c r="C60" s="16">
@@ -5451,7 +5451,7 @@
       <c r="U60" s="12"/>
       <c r="V60" s="23"/>
       <c r="W60" s="23"/>
-      <c r="X60" s="6"/>
+      <c r="X60" s="7"/>
       <c r="Y60" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5466,7 +5466,7 @@
       <c r="A61" s="13">
         <v>5.12</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B61" s="4">
         <v>1253.0</v>
       </c>
       <c r="C61" s="16">
@@ -5528,8 +5528,8 @@
       <c r="T61" s="12"/>
       <c r="U61" s="12"/>
       <c r="V61" s="9"/>
-      <c r="W61" s="6"/>
-      <c r="X61" s="6"/>
+      <c r="W61" s="7"/>
+      <c r="X61" s="7"/>
       <c r="Y61" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5544,7 +5544,7 @@
       <c r="A62" s="13">
         <v>6.01</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B62" s="4">
         <v>1251.0</v>
       </c>
       <c r="C62" s="16">
@@ -5609,9 +5609,9 @@
       <c r="U62" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="V62" s="6"/>
-      <c r="W62" s="6"/>
-      <c r="X62" s="6"/>
+      <c r="V62" s="7"/>
+      <c r="W62" s="7"/>
+      <c r="X62" s="7"/>
       <c r="Y62" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5626,7 +5626,7 @@
       <c r="A63" s="13">
         <v>6.02</v>
       </c>
-      <c r="B63" s="3">
+      <c r="B63" s="4">
         <v>1250.0</v>
       </c>
       <c r="C63" s="16">
@@ -5692,9 +5692,9 @@
         <f t="shared" ref="U63:U74" si="22">SUMIF($R$45:$R$116, T63, $Q$45:$Q$116)</f>
         <v>180</v>
       </c>
-      <c r="V63" s="6"/>
-      <c r="W63" s="6"/>
-      <c r="X63" s="6"/>
+      <c r="V63" s="7"/>
+      <c r="W63" s="7"/>
+      <c r="X63" s="7"/>
       <c r="Y63" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5709,7 +5709,7 @@
       <c r="A64" s="13">
         <v>6.03</v>
       </c>
-      <c r="B64" s="3">
+      <c r="B64" s="4">
         <v>1249.0</v>
       </c>
       <c r="C64" s="16">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="V64" s="23"/>
       <c r="W64" s="23"/>
-      <c r="X64" s="6"/>
+      <c r="X64" s="7"/>
       <c r="Y64" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5792,7 +5792,7 @@
       <c r="A65" s="13">
         <v>6.04</v>
       </c>
-      <c r="B65" s="3">
+      <c r="B65" s="4">
         <v>1246.0</v>
       </c>
       <c r="C65" s="16">
@@ -5858,9 +5858,9 @@
         <f t="shared" si="22"/>
         <v>132.5</v>
       </c>
-      <c r="V65" s="6"/>
-      <c r="W65" s="6"/>
-      <c r="X65" s="6"/>
+      <c r="V65" s="7"/>
+      <c r="W65" s="7"/>
+      <c r="X65" s="7"/>
       <c r="Y65" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5875,7 +5875,7 @@
       <c r="A66" s="13">
         <v>6.05</v>
       </c>
-      <c r="B66" s="3">
+      <c r="B66" s="4">
         <v>1245.0</v>
       </c>
       <c r="C66" s="16">
@@ -5942,8 +5942,8 @@
         <v>117.5</v>
       </c>
       <c r="V66" s="9"/>
-      <c r="W66" s="6"/>
-      <c r="X66" s="6"/>
+      <c r="W66" s="7"/>
+      <c r="X66" s="7"/>
       <c r="Y66" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5958,7 +5958,7 @@
       <c r="A67" s="13">
         <v>6.06</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B67" s="4">
         <v>1244.0</v>
       </c>
       <c r="C67" s="16">
@@ -6025,8 +6025,8 @@
         <v>109.5</v>
       </c>
       <c r="V67" s="9"/>
-      <c r="W67" s="6"/>
-      <c r="X67" s="6"/>
+      <c r="W67" s="7"/>
+      <c r="X67" s="7"/>
       <c r="Y67" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -6041,7 +6041,7 @@
       <c r="A68" s="13">
         <v>6.07</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B68" s="4">
         <v>1243.0</v>
       </c>
       <c r="C68" s="16">
@@ -6108,8 +6108,8 @@
         <v>99.5</v>
       </c>
       <c r="V68" s="9"/>
-      <c r="W68" s="6"/>
-      <c r="X68" s="6"/>
+      <c r="W68" s="7"/>
+      <c r="X68" s="7"/>
       <c r="Y68" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="V69" s="23"/>
       <c r="W69" s="23"/>
-      <c r="X69" s="6"/>
+      <c r="X69" s="7"/>
       <c r="Y69" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -6207,7 +6207,7 @@
       <c r="A70" s="13">
         <v>6.09</v>
       </c>
-      <c r="B70" s="3">
+      <c r="B70" s="4">
         <v>1234.0</v>
       </c>
       <c r="C70" s="16">
@@ -6290,7 +6290,7 @@
       <c r="A71" s="13">
         <v>6.1</v>
       </c>
-      <c r="B71" s="3">
+      <c r="B71" s="4">
         <v>1223.0</v>
       </c>
       <c r="C71" s="16">
@@ -6456,7 +6456,7 @@
       <c r="A73" s="13">
         <v>6.12</v>
       </c>
-      <c r="B73" s="3">
+      <c r="B73" s="4">
         <v>1166.0</v>
       </c>
       <c r="C73" s="16">
@@ -6600,7 +6600,7 @@
     </row>
     <row r="75">
       <c r="A75" s="5"/>
-      <c r="B75" s="6"/>
+      <c r="B75" s="7"/>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
@@ -6696,7 +6696,7 @@
     </row>
     <row r="77">
       <c r="A77" s="5"/>
-      <c r="B77" s="6"/>
+      <c r="B77" s="7"/>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
@@ -6743,7 +6743,7 @@
     </row>
     <row r="78">
       <c r="A78" s="5"/>
-      <c r="B78" s="6"/>
+      <c r="B78" s="7"/>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
       <c r="E78" s="5"/>
@@ -6790,7 +6790,7 @@
     </row>
     <row r="79">
       <c r="A79" s="5"/>
-      <c r="B79" s="6"/>
+      <c r="B79" s="7"/>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
@@ -6837,7 +6837,7 @@
     </row>
     <row r="80">
       <c r="A80" s="5"/>
-      <c r="B80" s="6"/>
+      <c r="B80" s="7"/>
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
       <c r="E80" s="5"/>
@@ -6884,7 +6884,7 @@
     </row>
     <row r="81">
       <c r="A81" s="5"/>
-      <c r="B81" s="6"/>
+      <c r="B81" s="7"/>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
@@ -6931,7 +6931,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5"/>
-      <c r="B82" s="6"/>
+      <c r="B82" s="7"/>
       <c r="C82" s="5"/>
       <c r="D82" s="5"/>
       <c r="E82" s="5"/>
@@ -6975,7 +6975,7 @@
     </row>
     <row r="83">
       <c r="A83" s="12"/>
-      <c r="B83" s="6"/>
+      <c r="B83" s="7"/>
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
@@ -7019,7 +7019,7 @@
     </row>
     <row r="84">
       <c r="A84" s="12"/>
-      <c r="B84" s="6"/>
+      <c r="B84" s="7"/>
       <c r="C84" s="5"/>
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
@@ -7106,7 +7106,7 @@
     </row>
     <row r="86">
       <c r="A86" s="12"/>
-      <c r="B86" s="6"/>
+      <c r="B86" s="7"/>
       <c r="C86" s="5"/>
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
@@ -7150,7 +7150,7 @@
     </row>
     <row r="87">
       <c r="A87" s="12"/>
-      <c r="B87" s="6"/>
+      <c r="B87" s="7"/>
       <c r="C87" s="5"/>
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
@@ -7194,7 +7194,7 @@
     </row>
     <row r="88">
       <c r="A88" s="12"/>
-      <c r="B88" s="6"/>
+      <c r="B88" s="7"/>
       <c r="C88" s="5"/>
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
@@ -7238,7 +7238,7 @@
     </row>
     <row r="89">
       <c r="A89" s="12"/>
-      <c r="B89" s="6"/>
+      <c r="B89" s="7"/>
       <c r="C89" s="5"/>
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
@@ -7282,7 +7282,7 @@
     </row>
     <row r="90">
       <c r="A90" s="5"/>
-      <c r="B90" s="6"/>
+      <c r="B90" s="7"/>
       <c r="C90" s="5"/>
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
@@ -7326,7 +7326,7 @@
     </row>
     <row r="91">
       <c r="A91" s="5"/>
-      <c r="B91" s="6"/>
+      <c r="B91" s="7"/>
       <c r="C91" s="5"/>
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
@@ -7370,7 +7370,7 @@
     </row>
     <row r="92">
       <c r="A92" s="5"/>
-      <c r="B92" s="6"/>
+      <c r="B92" s="7"/>
       <c r="C92" s="5"/>
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
@@ -7414,7 +7414,7 @@
     </row>
     <row r="93">
       <c r="A93" s="5"/>
-      <c r="B93" s="6"/>
+      <c r="B93" s="7"/>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
@@ -7458,7 +7458,7 @@
     </row>
     <row r="94">
       <c r="A94" s="12"/>
-      <c r="B94" s="6"/>
+      <c r="B94" s="7"/>
       <c r="C94" s="5"/>
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
@@ -7502,7 +7502,7 @@
     </row>
     <row r="95">
       <c r="A95" s="12"/>
-      <c r="B95" s="6"/>
+      <c r="B95" s="7"/>
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
@@ -7546,7 +7546,7 @@
     </row>
     <row r="96">
       <c r="A96" s="12"/>
-      <c r="B96" s="6"/>
+      <c r="B96" s="7"/>
       <c r="C96" s="5"/>
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
@@ -7590,7 +7590,7 @@
     </row>
     <row r="97">
       <c r="A97" s="12"/>
-      <c r="B97" s="6"/>
+      <c r="B97" s="7"/>
       <c r="C97" s="5"/>
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
@@ -7634,7 +7634,7 @@
     </row>
     <row r="98">
       <c r="A98" s="12"/>
-      <c r="B98" s="6"/>
+      <c r="B98" s="7"/>
       <c r="C98" s="5"/>
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
@@ -7678,7 +7678,7 @@
     </row>
     <row r="99">
       <c r="A99" s="12"/>
-      <c r="B99" s="6"/>
+      <c r="B99" s="7"/>
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
       <c r="E99" s="5"/>
@@ -7722,7 +7722,7 @@
     </row>
     <row r="100">
       <c r="A100" s="12"/>
-      <c r="B100" s="6"/>
+      <c r="B100" s="7"/>
       <c r="C100" s="5"/>
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
@@ -7766,7 +7766,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5"/>
-      <c r="B101" s="6"/>
+      <c r="B101" s="7"/>
       <c r="C101" s="5"/>
       <c r="D101" s="5"/>
       <c r="E101" s="5"/>
@@ -7810,7 +7810,7 @@
     </row>
     <row r="102">
       <c r="A102" s="5"/>
-      <c r="B102" s="6"/>
+      <c r="B102" s="7"/>
       <c r="C102" s="5"/>
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
@@ -9146,7 +9146,7 @@
       <c r="W137" s="12"/>
       <c r="X137" s="12"/>
       <c r="Y137" s="12"/>
-      <c r="Z137" s="6" t="s">
+      <c r="Z137" s="7" t="s">
         <v>137</v>
       </c>
       <c r="AA137" s="12"/>
@@ -9180,7 +9180,7 @@
       <c r="W138" s="12"/>
       <c r="X138" s="12"/>
       <c r="Y138" s="12"/>
-      <c r="Z138" s="6">
+      <c r="Z138" s="7">
         <v>6817.0</v>
       </c>
       <c r="AA138" s="12"/>
@@ -9211,16 +9211,16 @@
       <c r="T139" s="12"/>
       <c r="U139" s="12"/>
       <c r="V139" s="12"/>
-      <c r="W139" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="X139" s="6" t="s">
+      <c r="W139" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="X139" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="Y139" s="6" t="s">
+      <c r="Y139" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="Z139" s="6">
+      <c r="Z139" s="7">
         <v>5203.0</v>
       </c>
       <c r="AA139" s="12"/>
@@ -9251,16 +9251,16 @@
       <c r="T140" s="12"/>
       <c r="U140" s="12"/>
       <c r="V140" s="12"/>
-      <c r="W140" s="6">
+      <c r="W140" s="7">
         <v>1.0</v>
       </c>
-      <c r="X140" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y140" s="6" t="s">
+      <c r="X140" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y140" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z140" s="6">
+      <c r="Z140" s="7">
         <v>5103.0</v>
       </c>
       <c r="AA140" s="12"/>
@@ -9291,16 +9291,16 @@
       <c r="T141" s="12"/>
       <c r="U141" s="12"/>
       <c r="V141" s="12"/>
-      <c r="W141" s="6">
+      <c r="W141" s="7">
         <v>3.0</v>
       </c>
-      <c r="X141" s="6" t="s">
+      <c r="X141" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="Y141" s="6" t="s">
+      <c r="Y141" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z141" s="6">
+      <c r="Z141" s="7">
         <v>5020.0</v>
       </c>
       <c r="AA141" s="12"/>
@@ -9331,16 +9331,16 @@
       <c r="T142" s="12"/>
       <c r="U142" s="12"/>
       <c r="V142" s="12"/>
-      <c r="W142" s="6">
+      <c r="W142" s="7">
         <v>4.0</v>
       </c>
-      <c r="X142" s="6" t="s">
+      <c r="X142" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="Y142" s="6" t="s">
+      <c r="Y142" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z142" s="6">
+      <c r="Z142" s="7">
         <v>4517.0</v>
       </c>
       <c r="AA142" s="12"/>
@@ -9371,16 +9371,16 @@
       <c r="T143" s="12"/>
       <c r="U143" s="12"/>
       <c r="V143" s="12"/>
-      <c r="W143" s="6">
+      <c r="W143" s="7">
         <v>5.0</v>
       </c>
-      <c r="X143" s="6" t="s">
+      <c r="X143" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="Y143" s="6" t="s">
+      <c r="Y143" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z143" s="6">
+      <c r="Z143" s="7">
         <v>4164.0</v>
       </c>
       <c r="AA143" s="12"/>
@@ -9411,16 +9411,16 @@
       <c r="T144" s="12"/>
       <c r="U144" s="12"/>
       <c r="V144" s="12"/>
-      <c r="W144" s="6">
+      <c r="W144" s="7">
         <v>6.0</v>
       </c>
-      <c r="X144" s="6" t="s">
+      <c r="X144" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="Y144" s="6" t="s">
+      <c r="Y144" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z144" s="6">
+      <c r="Z144" s="7">
         <v>4025.0</v>
       </c>
       <c r="AA144" s="12"/>
@@ -9451,16 +9451,16 @@
       <c r="T145" s="12"/>
       <c r="U145" s="12"/>
       <c r="V145" s="12"/>
-      <c r="W145" s="6">
+      <c r="W145" s="7">
         <v>7.0</v>
       </c>
-      <c r="X145" s="6" t="s">
+      <c r="X145" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="Y145" s="6" t="s">
+      <c r="Y145" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Z145" s="6">
+      <c r="Z145" s="7">
         <v>3650.0</v>
       </c>
       <c r="AA145" s="12"/>
@@ -9491,16 +9491,16 @@
       <c r="T146" s="12"/>
       <c r="U146" s="12"/>
       <c r="V146" s="12"/>
-      <c r="W146" s="6">
+      <c r="W146" s="7">
         <v>8.0</v>
       </c>
-      <c r="X146" s="6" t="s">
+      <c r="X146" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="Y146" s="6" t="s">
+      <c r="Y146" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z146" s="6">
+      <c r="Z146" s="7">
         <v>3611.0</v>
       </c>
       <c r="AA146" s="12"/>
@@ -9531,16 +9531,16 @@
       <c r="T147" s="12"/>
       <c r="U147" s="12"/>
       <c r="V147" s="12"/>
-      <c r="W147" s="6">
+      <c r="W147" s="7">
         <v>9.0</v>
       </c>
-      <c r="X147" s="6" t="s">
+      <c r="X147" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="Y147" s="6" t="s">
+      <c r="Y147" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z147" s="6">
+      <c r="Z147" s="7">
         <v>3608.0</v>
       </c>
       <c r="AA147" s="12"/>
@@ -9571,16 +9571,16 @@
       <c r="T148" s="12"/>
       <c r="U148" s="12"/>
       <c r="V148" s="12"/>
-      <c r="W148" s="6">
+      <c r="W148" s="7">
         <v>10.0</v>
       </c>
-      <c r="X148" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y148" s="6" t="s">
+      <c r="X148" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y148" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="Z148" s="6">
+      <c r="Z148" s="7">
         <v>3596.0</v>
       </c>
       <c r="AA148" s="12"/>
@@ -9611,16 +9611,16 @@
       <c r="T149" s="12"/>
       <c r="U149" s="12"/>
       <c r="V149" s="12"/>
-      <c r="W149" s="6">
+      <c r="W149" s="7">
         <v>11.0</v>
       </c>
-      <c r="X149" s="6" t="s">
+      <c r="X149" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="Y149" s="6" t="s">
+      <c r="Y149" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Z149" s="6">
+      <c r="Z149" s="7">
         <v>3426.0</v>
       </c>
       <c r="AA149" s="12"/>
@@ -9651,16 +9651,16 @@
       <c r="T150" s="12"/>
       <c r="U150" s="12"/>
       <c r="V150" s="12"/>
-      <c r="W150" s="6">
+      <c r="W150" s="7">
         <v>12.0</v>
       </c>
-      <c r="X150" s="6" t="s">
+      <c r="X150" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="Y150" s="6" t="s">
+      <c r="Y150" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="Z150" s="6">
+      <c r="Z150" s="7">
         <v>3264.0</v>
       </c>
       <c r="AA150" s="12"/>
@@ -9691,16 +9691,16 @@
       <c r="T151" s="12"/>
       <c r="U151" s="12"/>
       <c r="V151" s="12"/>
-      <c r="W151" s="6">
+      <c r="W151" s="7">
         <v>13.0</v>
       </c>
-      <c r="X151" s="6" t="s">
+      <c r="X151" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="Y151" s="6" t="s">
+      <c r="Y151" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="Z151" s="6">
+      <c r="Z151" s="7">
         <v>3179.0</v>
       </c>
       <c r="AA151" s="12"/>
@@ -9731,16 +9731,16 @@
       <c r="T152" s="12"/>
       <c r="U152" s="12"/>
       <c r="V152" s="12"/>
-      <c r="W152" s="6">
+      <c r="W152" s="7">
         <v>14.0</v>
       </c>
-      <c r="X152" s="6" t="s">
+      <c r="X152" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="Y152" s="6" t="s">
+      <c r="Y152" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Z152" s="6">
+      <c r="Z152" s="7">
         <v>3162.0</v>
       </c>
       <c r="AA152" s="12"/>
@@ -9771,16 +9771,16 @@
       <c r="T153" s="12"/>
       <c r="U153" s="12"/>
       <c r="V153" s="12"/>
-      <c r="W153" s="6">
+      <c r="W153" s="7">
         <v>15.0</v>
       </c>
-      <c r="X153" s="6" t="s">
+      <c r="X153" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="Y153" s="6" t="s">
+      <c r="Y153" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z153" s="6">
+      <c r="Z153" s="7">
         <v>3125.0</v>
       </c>
       <c r="AA153" s="12"/>
@@ -9811,16 +9811,16 @@
       <c r="T154" s="12"/>
       <c r="U154" s="12"/>
       <c r="V154" s="12"/>
-      <c r="W154" s="6">
+      <c r="W154" s="7">
         <v>16.0</v>
       </c>
-      <c r="X154" s="6" t="s">
+      <c r="X154" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="Y154" s="6" t="s">
+      <c r="Y154" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Z154" s="6">
+      <c r="Z154" s="7">
         <v>2971.0</v>
       </c>
       <c r="AA154" s="12"/>
@@ -9851,16 +9851,16 @@
       <c r="T155" s="12"/>
       <c r="U155" s="12"/>
       <c r="V155" s="12"/>
-      <c r="W155" s="6">
+      <c r="W155" s="7">
         <v>17.0</v>
       </c>
-      <c r="X155" s="6" t="s">
+      <c r="X155" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="Y155" s="6" t="s">
+      <c r="Y155" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z155" s="6">
+      <c r="Z155" s="7">
         <v>2963.0</v>
       </c>
       <c r="AA155" s="12"/>
@@ -9891,16 +9891,16 @@
       <c r="T156" s="12"/>
       <c r="U156" s="12"/>
       <c r="V156" s="12"/>
-      <c r="W156" s="6">
+      <c r="W156" s="7">
         <v>18.0</v>
       </c>
-      <c r="X156" s="6" t="s">
+      <c r="X156" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="Y156" s="6" t="s">
+      <c r="Y156" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="Z156" s="6">
+      <c r="Z156" s="7">
         <v>2953.0</v>
       </c>
       <c r="AA156" s="12"/>
@@ -9931,16 +9931,16 @@
       <c r="T157" s="12"/>
       <c r="U157" s="12"/>
       <c r="V157" s="12"/>
-      <c r="W157" s="6">
+      <c r="W157" s="7">
         <v>19.0</v>
       </c>
-      <c r="X157" s="6" t="s">
+      <c r="X157" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="Y157" s="6" t="s">
+      <c r="Y157" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="Z157" s="6">
+      <c r="Z157" s="7">
         <v>2807.0</v>
       </c>
       <c r="AA157" s="12"/>
@@ -9971,16 +9971,16 @@
       <c r="T158" s="12"/>
       <c r="U158" s="12"/>
       <c r="V158" s="12"/>
-      <c r="W158" s="6">
+      <c r="W158" s="7">
         <v>20.0</v>
       </c>
-      <c r="X158" s="6" t="s">
+      <c r="X158" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="Y158" s="6" t="s">
+      <c r="Y158" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z158" s="6">
+      <c r="Z158" s="7">
         <v>2696.0</v>
       </c>
       <c r="AA158" s="12"/>
@@ -10011,16 +10011,16 @@
       <c r="T159" s="12"/>
       <c r="U159" s="12"/>
       <c r="V159" s="12"/>
-      <c r="W159" s="6">
+      <c r="W159" s="7">
         <v>21.0</v>
       </c>
-      <c r="X159" s="6" t="s">
+      <c r="X159" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="Y159" s="6" t="s">
+      <c r="Y159" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z159" s="6">
+      <c r="Z159" s="7">
         <v>2672.0</v>
       </c>
       <c r="AA159" s="12"/>
@@ -10051,16 +10051,16 @@
       <c r="T160" s="12"/>
       <c r="U160" s="12"/>
       <c r="V160" s="12"/>
-      <c r="W160" s="6">
+      <c r="W160" s="7">
         <v>22.0</v>
       </c>
-      <c r="X160" s="6" t="s">
+      <c r="X160" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="Y160" s="6" t="s">
+      <c r="Y160" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z160" s="6">
+      <c r="Z160" s="7">
         <v>2480.0</v>
       </c>
       <c r="AA160" s="12"/>
@@ -10091,16 +10091,16 @@
       <c r="T161" s="12"/>
       <c r="U161" s="12"/>
       <c r="V161" s="12"/>
-      <c r="W161" s="6">
+      <c r="W161" s="7">
         <v>23.0</v>
       </c>
-      <c r="X161" s="6" t="s">
+      <c r="X161" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="Y161" s="6" t="s">
+      <c r="Y161" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z161" s="6">
+      <c r="Z161" s="7">
         <v>2416.0</v>
       </c>
       <c r="AA161" s="12"/>
@@ -10131,16 +10131,16 @@
       <c r="T162" s="12"/>
       <c r="U162" s="12"/>
       <c r="V162" s="12"/>
-      <c r="W162" s="6">
+      <c r="W162" s="7">
         <v>24.0</v>
       </c>
-      <c r="X162" s="6" t="s">
+      <c r="X162" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="Y162" s="6" t="s">
+      <c r="Y162" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z162" s="6">
+      <c r="Z162" s="7">
         <v>2416.0</v>
       </c>
       <c r="AA162" s="12"/>
@@ -10171,16 +10171,16 @@
       <c r="T163" s="12"/>
       <c r="U163" s="12"/>
       <c r="V163" s="12"/>
-      <c r="W163" s="6">
+      <c r="W163" s="7">
         <v>25.0</v>
       </c>
-      <c r="X163" s="6" t="s">
+      <c r="X163" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="Y163" s="6" t="s">
+      <c r="Y163" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z163" s="6">
+      <c r="Z163" s="7">
         <v>2109.0</v>
       </c>
       <c r="AA163" s="12"/>
@@ -10211,16 +10211,16 @@
       <c r="T164" s="12"/>
       <c r="U164" s="12"/>
       <c r="V164" s="12"/>
-      <c r="W164" s="6">
+      <c r="W164" s="7">
         <v>26.0</v>
       </c>
-      <c r="X164" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y164" s="6" t="s">
+      <c r="X164" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y164" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z164" s="6">
+      <c r="Z164" s="7">
         <v>2106.0</v>
       </c>
       <c r="AA164" s="12"/>
@@ -10251,16 +10251,16 @@
       <c r="T165" s="12"/>
       <c r="U165" s="12"/>
       <c r="V165" s="12"/>
-      <c r="W165" s="6">
+      <c r="W165" s="7">
         <v>27.0</v>
       </c>
-      <c r="X165" s="6" t="s">
+      <c r="X165" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="Y165" s="6" t="s">
+      <c r="Y165" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z165" s="6">
+      <c r="Z165" s="7">
         <v>2098.0</v>
       </c>
       <c r="AA165" s="12"/>
@@ -10291,16 +10291,16 @@
       <c r="T166" s="12"/>
       <c r="U166" s="12"/>
       <c r="V166" s="12"/>
-      <c r="W166" s="6">
+      <c r="W166" s="7">
         <v>28.0</v>
       </c>
-      <c r="X166" s="6" t="s">
+      <c r="X166" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="Y166" s="6" t="s">
+      <c r="Y166" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z166" s="6">
+      <c r="Z166" s="7">
         <v>2078.0</v>
       </c>
       <c r="AA166" s="12"/>
@@ -10331,16 +10331,16 @@
       <c r="T167" s="12"/>
       <c r="U167" s="12"/>
       <c r="V167" s="12"/>
-      <c r="W167" s="6">
+      <c r="W167" s="7">
         <v>29.0</v>
       </c>
-      <c r="X167" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y167" s="6" t="s">
+      <c r="X167" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y167" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Z167" s="6">
+      <c r="Z167" s="7">
         <v>2074.0</v>
       </c>
       <c r="AA167" s="12"/>
@@ -10371,16 +10371,16 @@
       <c r="T168" s="12"/>
       <c r="U168" s="12"/>
       <c r="V168" s="12"/>
-      <c r="W168" s="6">
+      <c r="W168" s="7">
         <v>30.0</v>
       </c>
-      <c r="X168" s="6" t="s">
+      <c r="X168" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="Y168" s="6" t="s">
+      <c r="Y168" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z168" s="6">
+      <c r="Z168" s="7">
         <v>2066.0</v>
       </c>
       <c r="AA168" s="12"/>
@@ -10411,16 +10411,16 @@
       <c r="T169" s="12"/>
       <c r="U169" s="12"/>
       <c r="V169" s="12"/>
-      <c r="W169" s="6">
+      <c r="W169" s="7">
         <v>31.0</v>
       </c>
-      <c r="X169" s="6" t="s">
+      <c r="X169" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="Y169" s="6" t="s">
+      <c r="Y169" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z169" s="6">
+      <c r="Z169" s="7">
         <v>2045.0</v>
       </c>
       <c r="AA169" s="12"/>
@@ -10451,16 +10451,16 @@
       <c r="T170" s="12"/>
       <c r="U170" s="12"/>
       <c r="V170" s="12"/>
-      <c r="W170" s="6">
+      <c r="W170" s="7">
         <v>32.0</v>
       </c>
-      <c r="X170" s="6" t="s">
+      <c r="X170" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="Y170" s="6" t="s">
+      <c r="Y170" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z170" s="6">
+      <c r="Z170" s="7">
         <v>1977.0</v>
       </c>
       <c r="AA170" s="12"/>
@@ -10491,16 +10491,16 @@
       <c r="T171" s="12"/>
       <c r="U171" s="12"/>
       <c r="V171" s="12"/>
-      <c r="W171" s="6">
+      <c r="W171" s="7">
         <v>33.0</v>
       </c>
-      <c r="X171" s="6" t="s">
+      <c r="X171" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="Y171" s="6" t="s">
+      <c r="Y171" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z171" s="6">
+      <c r="Z171" s="7">
         <v>1967.0</v>
       </c>
       <c r="AA171" s="12"/>
@@ -10531,16 +10531,16 @@
       <c r="T172" s="12"/>
       <c r="U172" s="12"/>
       <c r="V172" s="12"/>
-      <c r="W172" s="6">
+      <c r="W172" s="7">
         <v>34.0</v>
       </c>
-      <c r="X172" s="6" t="s">
+      <c r="X172" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="Y172" s="6" t="s">
+      <c r="Y172" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="Z172" s="6">
+      <c r="Z172" s="7">
         <v>1962.0</v>
       </c>
       <c r="AA172" s="12"/>
@@ -10571,16 +10571,16 @@
       <c r="T173" s="12"/>
       <c r="U173" s="12"/>
       <c r="V173" s="12"/>
-      <c r="W173" s="6">
+      <c r="W173" s="7">
         <v>35.0</v>
       </c>
-      <c r="X173" s="6" t="s">
+      <c r="X173" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="Y173" s="6" t="s">
+      <c r="Y173" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Z173" s="6">
+      <c r="Z173" s="7">
         <v>1961.0</v>
       </c>
       <c r="AA173" s="12"/>
@@ -10611,16 +10611,16 @@
       <c r="T174" s="12"/>
       <c r="U174" s="12"/>
       <c r="V174" s="12"/>
-      <c r="W174" s="6">
+      <c r="W174" s="7">
         <v>36.0</v>
       </c>
-      <c r="X174" s="6" t="s">
+      <c r="X174" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="Y174" s="6" t="s">
+      <c r="Y174" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z174" s="6">
+      <c r="Z174" s="7">
         <v>1910.0</v>
       </c>
       <c r="AA174" s="12"/>
@@ -10651,16 +10651,16 @@
       <c r="T175" s="12"/>
       <c r="U175" s="12"/>
       <c r="V175" s="12"/>
-      <c r="W175" s="6">
+      <c r="W175" s="7">
         <v>37.0</v>
       </c>
-      <c r="X175" s="6" t="s">
+      <c r="X175" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="Y175" s="6" t="s">
+      <c r="Y175" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Z175" s="6">
+      <c r="Z175" s="7">
         <v>1873.0</v>
       </c>
       <c r="AA175" s="12"/>
@@ -10691,16 +10691,16 @@
       <c r="T176" s="12"/>
       <c r="U176" s="12"/>
       <c r="V176" s="12"/>
-      <c r="W176" s="6">
+      <c r="W176" s="7">
         <v>38.0</v>
       </c>
-      <c r="X176" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y176" s="6" t="s">
+      <c r="X176" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y176" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z176" s="6">
+      <c r="Z176" s="7">
         <v>1822.0</v>
       </c>
       <c r="AA176" s="12"/>
@@ -10731,16 +10731,16 @@
       <c r="T177" s="12"/>
       <c r="U177" s="12"/>
       <c r="V177" s="12"/>
-      <c r="W177" s="6">
+      <c r="W177" s="7">
         <v>39.0</v>
       </c>
-      <c r="X177" s="6" t="s">
+      <c r="X177" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Y177" s="6" t="s">
+      <c r="Y177" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z177" s="6">
+      <c r="Z177" s="7">
         <v>1741.0</v>
       </c>
       <c r="AA177" s="12"/>
@@ -10771,16 +10771,16 @@
       <c r="T178" s="12"/>
       <c r="U178" s="12"/>
       <c r="V178" s="12"/>
-      <c r="W178" s="6">
+      <c r="W178" s="7">
         <v>40.0</v>
       </c>
-      <c r="X178" s="6" t="s">
+      <c r="X178" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="Y178" s="6" t="s">
+      <c r="Y178" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z178" s="6">
+      <c r="Z178" s="7">
         <v>1724.0</v>
       </c>
       <c r="AA178" s="12"/>
@@ -10811,16 +10811,16 @@
       <c r="T179" s="12"/>
       <c r="U179" s="12"/>
       <c r="V179" s="12"/>
-      <c r="W179" s="6">
+      <c r="W179" s="7">
         <v>41.0</v>
       </c>
-      <c r="X179" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y179" s="6" t="s">
+      <c r="X179" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y179" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z179" s="6">
+      <c r="Z179" s="7">
         <v>1660.0</v>
       </c>
       <c r="AA179" s="12"/>
@@ -10851,16 +10851,16 @@
       <c r="T180" s="12"/>
       <c r="U180" s="12"/>
       <c r="V180" s="12"/>
-      <c r="W180" s="6">
+      <c r="W180" s="7">
         <v>42.0</v>
       </c>
-      <c r="X180" s="6" t="s">
+      <c r="X180" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="Y180" s="6" t="s">
+      <c r="Y180" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z180" s="6">
+      <c r="Z180" s="7">
         <v>1640.0</v>
       </c>
       <c r="AA180" s="12"/>
@@ -10891,16 +10891,16 @@
       <c r="T181" s="12"/>
       <c r="U181" s="12"/>
       <c r="V181" s="12"/>
-      <c r="W181" s="6">
+      <c r="W181" s="7">
         <v>43.0</v>
       </c>
-      <c r="X181" s="6" t="s">
+      <c r="X181" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="Y181" s="6" t="s">
+      <c r="Y181" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z181" s="6">
+      <c r="Z181" s="7">
         <v>1577.0</v>
       </c>
       <c r="AA181" s="12"/>
@@ -10931,16 +10931,16 @@
       <c r="T182" s="12"/>
       <c r="U182" s="12"/>
       <c r="V182" s="12"/>
-      <c r="W182" s="6">
+      <c r="W182" s="7">
         <v>44.0</v>
       </c>
-      <c r="X182" s="6" t="s">
+      <c r="X182" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="Y182" s="6" t="s">
+      <c r="Y182" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z182" s="6">
+      <c r="Z182" s="7">
         <v>1565.0</v>
       </c>
       <c r="AA182" s="12"/>
@@ -10971,16 +10971,16 @@
       <c r="T183" s="12"/>
       <c r="U183" s="12"/>
       <c r="V183" s="12"/>
-      <c r="W183" s="6">
+      <c r="W183" s="7">
         <v>45.0</v>
       </c>
-      <c r="X183" s="6" t="s">
+      <c r="X183" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="Y183" s="6" t="s">
+      <c r="Y183" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z183" s="6">
+      <c r="Z183" s="7">
         <v>1552.0</v>
       </c>
       <c r="AA183" s="12"/>
@@ -11011,16 +11011,16 @@
       <c r="T184" s="12"/>
       <c r="U184" s="12"/>
       <c r="V184" s="12"/>
-      <c r="W184" s="6">
+      <c r="W184" s="7">
         <v>46.0</v>
       </c>
-      <c r="X184" s="6" t="s">
+      <c r="X184" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="Y184" s="6" t="s">
+      <c r="Y184" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z184" s="6">
+      <c r="Z184" s="7">
         <v>1404.0</v>
       </c>
       <c r="AA184" s="12"/>
@@ -11051,16 +11051,16 @@
       <c r="T185" s="12"/>
       <c r="U185" s="12"/>
       <c r="V185" s="12"/>
-      <c r="W185" s="6">
+      <c r="W185" s="7">
         <v>47.0</v>
       </c>
-      <c r="X185" s="6" t="s">
+      <c r="X185" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="Y185" s="6" t="s">
+      <c r="Y185" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z185" s="6">
+      <c r="Z185" s="7">
         <v>1351.0</v>
       </c>
       <c r="AA185" s="12"/>
@@ -11091,16 +11091,16 @@
       <c r="T186" s="12"/>
       <c r="U186" s="12"/>
       <c r="V186" s="12"/>
-      <c r="W186" s="6">
+      <c r="W186" s="7">
         <v>48.0</v>
       </c>
-      <c r="X186" s="6" t="s">
+      <c r="X186" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="Y186" s="6" t="s">
+      <c r="Y186" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z186" s="6">
+      <c r="Z186" s="7">
         <v>1344.0</v>
       </c>
       <c r="AA186" s="12"/>
@@ -11131,16 +11131,16 @@
       <c r="T187" s="12"/>
       <c r="U187" s="12"/>
       <c r="V187" s="12"/>
-      <c r="W187" s="6">
+      <c r="W187" s="7">
         <v>49.0</v>
       </c>
-      <c r="X187" s="6" t="s">
+      <c r="X187" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="Y187" s="6" t="s">
+      <c r="Y187" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z187" s="6">
+      <c r="Z187" s="7">
         <v>1299.0</v>
       </c>
       <c r="AA187" s="12"/>
@@ -11171,16 +11171,16 @@
       <c r="T188" s="12"/>
       <c r="U188" s="12"/>
       <c r="V188" s="12"/>
-      <c r="W188" s="6">
+      <c r="W188" s="7">
         <v>50.0</v>
       </c>
-      <c r="X188" s="6" t="s">
+      <c r="X188" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="Y188" s="6" t="s">
+      <c r="Y188" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z188" s="6">
+      <c r="Z188" s="7">
         <v>1261.0</v>
       </c>
       <c r="AA188" s="12"/>
@@ -11211,16 +11211,16 @@
       <c r="T189" s="12"/>
       <c r="U189" s="12"/>
       <c r="V189" s="12"/>
-      <c r="W189" s="6">
+      <c r="W189" s="7">
         <v>51.0</v>
       </c>
-      <c r="X189" s="6" t="s">
+      <c r="X189" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="Y189" s="6" t="s">
+      <c r="Y189" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z189" s="6">
+      <c r="Z189" s="7">
         <v>1247.0</v>
       </c>
       <c r="AA189" s="12"/>
@@ -11251,16 +11251,16 @@
       <c r="T190" s="12"/>
       <c r="U190" s="12"/>
       <c r="V190" s="12"/>
-      <c r="W190" s="6">
+      <c r="W190" s="7">
         <v>52.0</v>
       </c>
-      <c r="X190" s="6" t="s">
+      <c r="X190" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="Y190" s="6" t="s">
+      <c r="Y190" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z190" s="6">
+      <c r="Z190" s="7">
         <v>1226.0</v>
       </c>
       <c r="AA190" s="12"/>
@@ -11291,16 +11291,16 @@
       <c r="T191" s="12"/>
       <c r="U191" s="12"/>
       <c r="V191" s="12"/>
-      <c r="W191" s="6">
+      <c r="W191" s="7">
         <v>53.0</v>
       </c>
-      <c r="X191" s="6" t="s">
+      <c r="X191" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="Y191" s="6" t="s">
+      <c r="Y191" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z191" s="6">
+      <c r="Z191" s="7">
         <v>1211.0</v>
       </c>
       <c r="AA191" s="12"/>
@@ -11331,16 +11331,16 @@
       <c r="T192" s="12"/>
       <c r="U192" s="12"/>
       <c r="V192" s="12"/>
-      <c r="W192" s="6">
+      <c r="W192" s="7">
         <v>54.0</v>
       </c>
-      <c r="X192" s="6" t="s">
+      <c r="X192" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="Y192" s="6" t="s">
+      <c r="Y192" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z192" s="6">
+      <c r="Z192" s="7">
         <v>1197.0</v>
       </c>
       <c r="AA192" s="12"/>
@@ -11371,16 +11371,16 @@
       <c r="T193" s="12"/>
       <c r="U193" s="12"/>
       <c r="V193" s="12"/>
-      <c r="W193" s="6">
+      <c r="W193" s="7">
         <v>55.0</v>
       </c>
-      <c r="X193" s="6" t="s">
+      <c r="X193" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="Y193" s="6" t="s">
+      <c r="Y193" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z193" s="6">
+      <c r="Z193" s="7">
         <v>1184.0</v>
       </c>
       <c r="AA193" s="12"/>
@@ -11411,16 +11411,16 @@
       <c r="T194" s="12"/>
       <c r="U194" s="12"/>
       <c r="V194" s="12"/>
-      <c r="W194" s="6">
+      <c r="W194" s="7">
         <v>56.0</v>
       </c>
-      <c r="X194" s="6" t="s">
+      <c r="X194" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="Y194" s="6" t="s">
+      <c r="Y194" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z194" s="6">
+      <c r="Z194" s="7">
         <v>1157.0</v>
       </c>
       <c r="AA194" s="12"/>
@@ -11451,16 +11451,16 @@
       <c r="T195" s="12"/>
       <c r="U195" s="12"/>
       <c r="V195" s="12"/>
-      <c r="W195" s="6">
+      <c r="W195" s="7">
         <v>57.0</v>
       </c>
-      <c r="X195" s="6" t="s">
+      <c r="X195" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="Y195" s="6" t="s">
+      <c r="Y195" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z195" s="6">
+      <c r="Z195" s="7">
         <v>1143.0</v>
       </c>
       <c r="AA195" s="12"/>
@@ -11491,16 +11491,16 @@
       <c r="T196" s="12"/>
       <c r="U196" s="12"/>
       <c r="V196" s="12"/>
-      <c r="W196" s="6">
+      <c r="W196" s="7">
         <v>58.0</v>
       </c>
-      <c r="X196" s="6" t="s">
+      <c r="X196" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="Y196" s="6" t="s">
+      <c r="Y196" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z196" s="6">
+      <c r="Z196" s="7">
         <v>1078.0</v>
       </c>
       <c r="AA196" s="12"/>
@@ -11531,16 +11531,16 @@
       <c r="T197" s="12"/>
       <c r="U197" s="12"/>
       <c r="V197" s="12"/>
-      <c r="W197" s="6">
+      <c r="W197" s="7">
         <v>59.0</v>
       </c>
-      <c r="X197" s="6" t="s">
+      <c r="X197" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="Y197" s="6" t="s">
+      <c r="Y197" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z197" s="6">
+      <c r="Z197" s="7">
         <v>1069.0</v>
       </c>
       <c r="AA197" s="12"/>
@@ -11571,16 +11571,16 @@
       <c r="T198" s="12"/>
       <c r="U198" s="12"/>
       <c r="V198" s="12"/>
-      <c r="W198" s="6">
+      <c r="W198" s="7">
         <v>60.0</v>
       </c>
-      <c r="X198" s="6" t="s">
+      <c r="X198" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="Y198" s="6" t="s">
+      <c r="Y198" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z198" s="6">
+      <c r="Z198" s="7">
         <v>1000.0</v>
       </c>
       <c r="AA198" s="12"/>
@@ -11611,16 +11611,16 @@
       <c r="T199" s="12"/>
       <c r="U199" s="12"/>
       <c r="V199" s="12"/>
-      <c r="W199" s="6">
+      <c r="W199" s="7">
         <v>61.0</v>
       </c>
-      <c r="X199" s="6" t="s">
+      <c r="X199" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="Y199" s="6" t="s">
+      <c r="Y199" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z199" s="6">
+      <c r="Z199" s="7">
         <v>987.0</v>
       </c>
       <c r="AA199" s="12"/>
@@ -11651,16 +11651,16 @@
       <c r="T200" s="12"/>
       <c r="U200" s="12"/>
       <c r="V200" s="12"/>
-      <c r="W200" s="6">
+      <c r="W200" s="7">
         <v>62.0</v>
       </c>
-      <c r="X200" s="6" t="s">
+      <c r="X200" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="Y200" s="6" t="s">
+      <c r="Y200" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z200" s="6">
+      <c r="Z200" s="7">
         <v>952.0</v>
       </c>
       <c r="AA200" s="12"/>
@@ -11691,16 +11691,16 @@
       <c r="T201" s="12"/>
       <c r="U201" s="12"/>
       <c r="V201" s="12"/>
-      <c r="W201" s="6">
+      <c r="W201" s="7">
         <v>63.0</v>
       </c>
-      <c r="X201" s="6" t="s">
+      <c r="X201" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="Y201" s="6" t="s">
+      <c r="Y201" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z201" s="6">
+      <c r="Z201" s="7">
         <v>913.0</v>
       </c>
       <c r="AA201" s="12"/>
@@ -11731,16 +11731,16 @@
       <c r="T202" s="12"/>
       <c r="U202" s="12"/>
       <c r="V202" s="12"/>
-      <c r="W202" s="6">
+      <c r="W202" s="7">
         <v>64.0</v>
       </c>
-      <c r="X202" s="6" t="s">
+      <c r="X202" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="Y202" s="6" t="s">
+      <c r="Y202" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z202" s="6">
+      <c r="Z202" s="7">
         <v>905.0</v>
       </c>
       <c r="AA202" s="12"/>
@@ -11771,16 +11771,16 @@
       <c r="T203" s="12"/>
       <c r="U203" s="12"/>
       <c r="V203" s="12"/>
-      <c r="W203" s="6">
+      <c r="W203" s="7">
         <v>65.0</v>
       </c>
-      <c r="X203" s="6" t="s">
+      <c r="X203" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="Y203" s="6" t="s">
+      <c r="Y203" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z203" s="6">
+      <c r="Z203" s="7">
         <v>842.0</v>
       </c>
       <c r="AA203" s="12"/>
@@ -11811,16 +11811,16 @@
       <c r="T204" s="12"/>
       <c r="U204" s="12"/>
       <c r="V204" s="12"/>
-      <c r="W204" s="6">
+      <c r="W204" s="7">
         <v>66.0</v>
       </c>
-      <c r="X204" s="6" t="s">
+      <c r="X204" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="Y204" s="6" t="s">
+      <c r="Y204" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z204" s="6">
+      <c r="Z204" s="7">
         <v>823.0</v>
       </c>
       <c r="AA204" s="12"/>
@@ -11851,16 +11851,16 @@
       <c r="T205" s="12"/>
       <c r="U205" s="12"/>
       <c r="V205" s="12"/>
-      <c r="W205" s="6">
+      <c r="W205" s="7">
         <v>67.0</v>
       </c>
-      <c r="X205" s="6" t="s">
+      <c r="X205" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="Y205" s="6" t="s">
+      <c r="Y205" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z205" s="6">
+      <c r="Z205" s="7">
         <v>820.0</v>
       </c>
       <c r="AA205" s="12"/>
@@ -11891,16 +11891,16 @@
       <c r="T206" s="12"/>
       <c r="U206" s="12"/>
       <c r="V206" s="12"/>
-      <c r="W206" s="6">
+      <c r="W206" s="7">
         <v>68.0</v>
       </c>
-      <c r="X206" s="6" t="s">
+      <c r="X206" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="Y206" s="6" t="s">
+      <c r="Y206" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z206" s="6">
+      <c r="Z206" s="7">
         <v>805.0</v>
       </c>
       <c r="AA206" s="12"/>
@@ -11931,16 +11931,16 @@
       <c r="T207" s="12"/>
       <c r="U207" s="12"/>
       <c r="V207" s="12"/>
-      <c r="W207" s="6">
+      <c r="W207" s="7">
         <v>69.0</v>
       </c>
-      <c r="X207" s="6" t="s">
+      <c r="X207" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="Y207" s="6" t="s">
+      <c r="Y207" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z207" s="6">
+      <c r="Z207" s="7">
         <v>782.0</v>
       </c>
       <c r="AA207" s="12"/>
@@ -11971,16 +11971,16 @@
       <c r="T208" s="12"/>
       <c r="U208" s="12"/>
       <c r="V208" s="12"/>
-      <c r="W208" s="6">
+      <c r="W208" s="7">
         <v>70.0</v>
       </c>
-      <c r="X208" s="6" t="s">
+      <c r="X208" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="Y208" s="6" t="s">
+      <c r="Y208" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z208" s="6">
+      <c r="Z208" s="7">
         <v>736.0</v>
       </c>
       <c r="AA208" s="12"/>
@@ -12011,16 +12011,16 @@
       <c r="T209" s="12"/>
       <c r="U209" s="12"/>
       <c r="V209" s="12"/>
-      <c r="W209" s="6">
+      <c r="W209" s="7">
         <v>71.0</v>
       </c>
-      <c r="X209" s="6" t="s">
+      <c r="X209" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="Y209" s="6" t="s">
+      <c r="Y209" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z209" s="6">
+      <c r="Z209" s="7">
         <v>733.0</v>
       </c>
       <c r="AA209" s="12"/>
@@ -12051,16 +12051,16 @@
       <c r="T210" s="12"/>
       <c r="U210" s="12"/>
       <c r="V210" s="12"/>
-      <c r="W210" s="6">
+      <c r="W210" s="7">
         <v>72.0</v>
       </c>
-      <c r="X210" s="6" t="s">
+      <c r="X210" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="Y210" s="6" t="s">
+      <c r="Y210" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z210" s="6">
+      <c r="Z210" s="7">
         <v>700.0</v>
       </c>
       <c r="AA210" s="12"/>
@@ -12091,16 +12091,16 @@
       <c r="T211" s="12"/>
       <c r="U211" s="12"/>
       <c r="V211" s="12"/>
-      <c r="W211" s="6">
+      <c r="W211" s="7">
         <v>73.0</v>
       </c>
-      <c r="X211" s="6" t="s">
+      <c r="X211" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="Y211" s="6" t="s">
+      <c r="Y211" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z211" s="6">
+      <c r="Z211" s="7">
         <v>649.0</v>
       </c>
       <c r="AA211" s="12"/>
@@ -12131,16 +12131,16 @@
       <c r="T212" s="12"/>
       <c r="U212" s="12"/>
       <c r="V212" s="12"/>
-      <c r="W212" s="6">
+      <c r="W212" s="7">
         <v>74.0</v>
       </c>
-      <c r="X212" s="6" t="s">
+      <c r="X212" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="Y212" s="6" t="s">
+      <c r="Y212" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z212" s="6">
+      <c r="Z212" s="7">
         <v>636.0</v>
       </c>
       <c r="AA212" s="12"/>
@@ -12171,16 +12171,16 @@
       <c r="T213" s="12"/>
       <c r="U213" s="12"/>
       <c r="V213" s="12"/>
-      <c r="W213" s="6">
+      <c r="W213" s="7">
         <v>75.0</v>
       </c>
-      <c r="X213" s="6" t="s">
+      <c r="X213" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="Y213" s="6" t="s">
+      <c r="Y213" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z213" s="6">
+      <c r="Z213" s="7">
         <v>528.0</v>
       </c>
       <c r="AA213" s="12"/>
@@ -12211,16 +12211,16 @@
       <c r="T214" s="12"/>
       <c r="U214" s="12"/>
       <c r="V214" s="12"/>
-      <c r="W214" s="6">
+      <c r="W214" s="7">
         <v>76.0</v>
       </c>
-      <c r="X214" s="6" t="s">
+      <c r="X214" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="Y214" s="6" t="s">
+      <c r="Y214" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z214" s="6">
+      <c r="Z214" s="7">
         <v>473.0</v>
       </c>
       <c r="AA214" s="12"/>
@@ -12251,16 +12251,16 @@
       <c r="T215" s="12"/>
       <c r="U215" s="12"/>
       <c r="V215" s="12"/>
-      <c r="W215" s="6">
+      <c r="W215" s="7">
         <v>78.0</v>
       </c>
-      <c r="X215" s="6" t="s">
+      <c r="X215" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="Y215" s="6" t="s">
+      <c r="Y215" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z215" s="6">
+      <c r="Z215" s="7">
         <v>435.0</v>
       </c>
       <c r="AA215" s="12"/>
@@ -12291,13 +12291,13 @@
       <c r="T216" s="12"/>
       <c r="U216" s="12"/>
       <c r="V216" s="12"/>
-      <c r="W216" s="6">
+      <c r="W216" s="7">
         <v>79.0</v>
       </c>
-      <c r="X216" s="6" t="s">
+      <c r="X216" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="Y216" s="6" t="s">
+      <c r="Y216" s="7" t="s">
         <v>140</v>
       </c>
       <c r="Z216" s="12"/>
@@ -12329,13 +12329,13 @@
       <c r="T217" s="12"/>
       <c r="U217" s="12"/>
       <c r="V217" s="12"/>
-      <c r="W217" s="6">
+      <c r="W217" s="7">
         <v>80.0</v>
       </c>
-      <c r="X217" s="6" t="s">
+      <c r="X217" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="Y217" s="6" t="s">
+      <c r="Y217" s="7" t="s">
         <v>140</v>
       </c>
       <c r="Z217" s="12"/>
@@ -37444,7 +37444,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -37458,28 +37458,28 @@
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="F1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="H1" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="I1" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
         <v>1.0</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>13</v>
+      <c r="B2" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="C2" s="8">
         <v>139.0</v>
@@ -37533,7 +37533,7 @@
       <c r="A3" s="1">
         <v>2.0</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="8">
@@ -37575,7 +37575,7 @@
       <c r="A4" s="1">
         <v>3.0</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="8">
@@ -37604,7 +37604,7 @@
       <c r="K4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="4">
         <f>'Draft Data'!U63</f>
         <v>180</v>
       </c>
@@ -37613,7 +37613,7 @@
       <c r="A5" s="1">
         <v>4.0</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C5" s="8">
@@ -37651,7 +37651,7 @@
       <c r="A6" s="1">
         <v>5.0</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="8">
@@ -37689,7 +37689,7 @@
       <c r="A7" s="1">
         <v>6.0</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>30</v>
       </c>
       <c r="C7" s="8">
@@ -37715,7 +37715,7 @@
         <v/>
       </c>
       <c r="K7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L7" s="17">
         <f>SUMIF($E$2:$E$500,TRUE,$D$2:$D$500)</f>
@@ -37726,7 +37726,7 @@
       <c r="A8" s="1">
         <v>7.0</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="8">
@@ -37764,7 +37764,7 @@
       <c r="A9" s="1">
         <v>8.0</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>35</v>
       </c>
       <c r="C9" s="8">
@@ -37802,7 +37802,7 @@
       <c r="A10" s="1">
         <v>9.0</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C10" s="8">
@@ -37839,7 +37839,7 @@
       <c r="A11" s="1">
         <v>10.0</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="8">
@@ -37876,7 +37876,7 @@
       <c r="A12" s="1">
         <v>11.0</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="8">
@@ -37906,8 +37906,8 @@
       <c r="A13" s="1">
         <v>12.0</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>42</v>
+      <c r="B13" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="C13" s="8">
         <v>34.0</v>
@@ -37932,7 +37932,7 @@
         <v/>
       </c>
       <c r="K13" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L13" s="17">
         <f>SUMIF($D$2:$D$73,"",$C$2:$C$73)</f>
@@ -37943,7 +37943,7 @@
       <c r="A14" s="1">
         <v>13.0</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>45</v>
       </c>
       <c r="C14" s="8">
@@ -37980,7 +37980,7 @@
       <c r="A15" s="1">
         <v>14.0</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C15" s="8">
@@ -38010,7 +38010,7 @@
       <c r="A16" s="1">
         <v>15.0</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>48</v>
       </c>
       <c r="C16" s="8">
@@ -38036,7 +38036,7 @@
         <v/>
       </c>
       <c r="K16" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L16" s="1">
         <f>IF($L$18&lt;0.3,
@@ -38057,8 +38057,8 @@
       <c r="A17" s="1">
         <v>16.0</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>51</v>
+      <c r="B17" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="C17" s="8">
         <v>22.5</v>
@@ -38087,7 +38087,7 @@
       <c r="A18" s="1">
         <v>17.0</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>53</v>
       </c>
       <c r="C18" s="8">
@@ -38124,7 +38124,7 @@
       <c r="A19" s="1">
         <v>18.0</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>55</v>
       </c>
       <c r="C19" s="8">
@@ -38154,7 +38154,7 @@
       <c r="A20" s="1">
         <v>19.0</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="7" t="s">
         <v>56</v>
       </c>
       <c r="C20" s="8">
@@ -38184,8 +38184,8 @@
       <c r="A21" s="1">
         <v>20.0</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>57</v>
+      <c r="B21" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="C21" s="8">
         <v>14.5</v>
@@ -38214,7 +38214,7 @@
       <c r="A22" s="1">
         <v>21.0</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="7" t="s">
         <v>59</v>
       </c>
       <c r="C22" s="8">
@@ -38244,7 +38244,7 @@
       <c r="A23" s="1">
         <v>22.0</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="7" t="s">
         <v>60</v>
       </c>
       <c r="C23" s="8">
@@ -38274,7 +38274,7 @@
       <c r="A24" s="1">
         <v>23.0</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="7" t="s">
         <v>61</v>
       </c>
       <c r="C24" s="8">
@@ -38304,8 +38304,8 @@
       <c r="A25" s="1">
         <v>24.0</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>62</v>
+      <c r="B25" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="C25" s="8">
         <v>10.0</v>
@@ -38334,8 +38334,8 @@
       <c r="A26" s="1">
         <v>25.0</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>63</v>
+      <c r="B26" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="C26" s="8">
         <v>9.5</v>
@@ -38364,8 +38364,8 @@
       <c r="A27" s="1">
         <v>26.0</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>64</v>
+      <c r="B27" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="C27" s="8">
         <v>8.5</v>
@@ -38390,7 +38390,7 @@
         <v/>
       </c>
       <c r="K27" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L27" s="1">
         <v>0.8</v>
@@ -38400,8 +38400,8 @@
       <c r="A28" s="1">
         <v>27.0</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>66</v>
+      <c r="B28" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="C28" s="8">
         <v>8.0</v>
@@ -38430,7 +38430,7 @@
       <c r="A29" s="1">
         <v>28.0</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C29" s="8">
@@ -38460,7 +38460,7 @@
       <c r="A30" s="1">
         <v>29.0</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="7" t="s">
         <v>69</v>
       </c>
       <c r="C30" s="8">
@@ -38490,7 +38490,7 @@
       <c r="A31" s="1">
         <v>30.0</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C31" s="8">
@@ -38520,7 +38520,7 @@
       <c r="A32" s="1">
         <v>31.0</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="7" t="s">
         <v>71</v>
       </c>
       <c r="C32" s="8">
@@ -38550,7 +38550,7 @@
       <c r="A33" s="1">
         <v>32.0</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="7" t="s">
         <v>72</v>
       </c>
       <c r="C33" s="8">
@@ -38580,7 +38580,7 @@
       <c r="A34" s="1">
         <v>33.0</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="7" t="s">
         <v>73</v>
       </c>
       <c r="C34" s="8">
@@ -38610,7 +38610,7 @@
       <c r="A35" s="1">
         <v>34.0</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="7" t="s">
         <v>74</v>
       </c>
       <c r="C35" s="8">
@@ -38640,7 +38640,7 @@
       <c r="A36" s="1">
         <v>35.0</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C36" s="8">
@@ -38670,7 +38670,7 @@
       <c r="A37" s="1">
         <v>36.0</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="7" t="s">
         <v>76</v>
       </c>
       <c r="C37" s="8">
@@ -38700,7 +38700,7 @@
       <c r="A38" s="1">
         <v>37.0</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="7" t="s">
         <v>77</v>
       </c>
       <c r="C38" s="8">
@@ -38730,7 +38730,7 @@
       <c r="A39" s="1">
         <v>38.0</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="7" t="s">
         <v>78</v>
       </c>
       <c r="C39" s="8">
@@ -38760,7 +38760,7 @@
       <c r="A40" s="1">
         <v>39.0</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="7" t="s">
         <v>79</v>
       </c>
       <c r="C40" s="8">
@@ -38790,7 +38790,7 @@
       <c r="A41" s="1">
         <v>40.0</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="7" t="s">
         <v>80</v>
       </c>
       <c r="C41" s="8">
@@ -38820,7 +38820,7 @@
       <c r="A42" s="1">
         <v>41.0</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="7" t="s">
         <v>81</v>
       </c>
       <c r="C42" s="8">
@@ -38850,7 +38850,7 @@
       <c r="A43" s="1">
         <v>42.0</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="7" t="s">
         <v>82</v>
       </c>
       <c r="C43" s="8">
@@ -38880,7 +38880,7 @@
       <c r="A44" s="1">
         <v>43.0</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C44" s="8">
@@ -38910,7 +38910,7 @@
       <c r="A45" s="1">
         <v>44.0</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="7" t="s">
         <v>84</v>
       </c>
       <c r="C45" s="8">
@@ -38940,7 +38940,7 @@
       <c r="A46" s="1">
         <v>45.0</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="7" t="s">
         <v>85</v>
       </c>
       <c r="C46" s="8">
@@ -38970,7 +38970,7 @@
       <c r="A47" s="1">
         <v>46.0</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="7" t="s">
         <v>86</v>
       </c>
       <c r="C47" s="8">
@@ -39000,7 +39000,7 @@
       <c r="A48" s="1">
         <v>47.0</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="7" t="s">
         <v>87</v>
       </c>
       <c r="C48" s="8">
@@ -39030,7 +39030,7 @@
       <c r="A49" s="1">
         <v>48.0</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C49" s="8">
@@ -39060,7 +39060,7 @@
       <c r="A50" s="1">
         <v>49.0</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="7" t="s">
         <v>89</v>
       </c>
       <c r="C50" s="8">
@@ -39090,7 +39090,7 @@
       <c r="A51" s="1">
         <v>50.0</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="7" t="s">
         <v>90</v>
       </c>
       <c r="C51" s="8">
@@ -39120,7 +39120,7 @@
       <c r="A52" s="1">
         <v>51.0</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="7" t="s">
         <v>91</v>
       </c>
       <c r="C52" s="8">
@@ -39150,7 +39150,7 @@
       <c r="A53" s="1">
         <v>52.0</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="7" t="s">
         <v>92</v>
       </c>
       <c r="C53" s="8">
@@ -39180,7 +39180,7 @@
       <c r="A54" s="1">
         <v>53.0</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="7" t="s">
         <v>93</v>
       </c>
       <c r="C54" s="8">
@@ -39210,7 +39210,7 @@
       <c r="A55" s="1">
         <v>54.0</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="7" t="s">
         <v>94</v>
       </c>
       <c r="C55" s="8">
@@ -39240,7 +39240,7 @@
       <c r="A56" s="1">
         <v>55.0</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="7" t="s">
         <v>95</v>
       </c>
       <c r="C56" s="8">
@@ -39270,7 +39270,7 @@
       <c r="A57" s="1">
         <v>56.0</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="7" t="s">
         <v>96</v>
       </c>
       <c r="C57" s="8">
@@ -39300,7 +39300,7 @@
       <c r="A58" s="1">
         <v>57.0</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C58" s="8">
@@ -39330,7 +39330,7 @@
       <c r="A59" s="1">
         <v>58.0</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="7" t="s">
         <v>98</v>
       </c>
       <c r="C59" s="8">
@@ -39360,7 +39360,7 @@
       <c r="A60" s="1">
         <v>59.0</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="7" t="s">
         <v>99</v>
       </c>
       <c r="C60" s="8">
@@ -39390,7 +39390,7 @@
       <c r="A61" s="1">
         <v>60.0</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C61" s="8">
@@ -39420,7 +39420,7 @@
       <c r="A62" s="1">
         <v>61.0</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="7" t="s">
         <v>101</v>
       </c>
       <c r="C62" s="8">
@@ -39450,7 +39450,7 @@
       <c r="A63" s="1">
         <v>62.0</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="7" t="s">
         <v>102</v>
       </c>
       <c r="C63" s="8">
@@ -39480,7 +39480,7 @@
       <c r="A64" s="1">
         <v>63.0</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="7" t="s">
         <v>103</v>
       </c>
       <c r="C64" s="8">
@@ -39510,7 +39510,7 @@
       <c r="A65" s="1">
         <v>64.0</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="7" t="s">
         <v>104</v>
       </c>
       <c r="C65" s="8">
@@ -39540,7 +39540,7 @@
       <c r="A66" s="1">
         <v>65.0</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="7" t="s">
         <v>105</v>
       </c>
       <c r="C66" s="8">
@@ -39570,7 +39570,7 @@
       <c r="A67" s="1">
         <v>66.0</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="7" t="s">
         <v>106</v>
       </c>
       <c r="C67" s="8">
@@ -39600,7 +39600,7 @@
       <c r="A68" s="1">
         <v>67.0</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="7" t="s">
         <v>107</v>
       </c>
       <c r="C68" s="8">
@@ -39630,7 +39630,7 @@
       <c r="A69" s="1">
         <v>68.0</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="7" t="s">
         <v>108</v>
       </c>
       <c r="C69" s="8">
@@ -39660,7 +39660,7 @@
       <c r="A70" s="1">
         <v>69.0</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="7" t="s">
         <v>109</v>
       </c>
       <c r="C70" s="8">
@@ -39690,7 +39690,7 @@
       <c r="A71" s="1">
         <v>70.0</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="7" t="s">
         <v>110</v>
       </c>
       <c r="C71" s="8">
@@ -39720,7 +39720,7 @@
       <c r="A72" s="1">
         <v>71.0</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="7" t="s">
         <v>111</v>
       </c>
       <c r="C72" s="8">

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -14,10 +14,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="178">
   <si>
-    <t>PICK</t>
+    <t>Rank</t>
   </si>
   <si>
-    <t>Rank</t>
+    <t>PICK</t>
   </si>
   <si>
     <t>PLAYER NAME</t>
@@ -32,25 +32,16 @@
     <t>Mine?</t>
   </si>
   <si>
-    <t>VALUE</t>
-  </si>
-  <si>
     <t>Inflated Fair Price</t>
   </si>
   <si>
-    <t>Decay</t>
+    <t>VALUE</t>
   </si>
   <si>
     <t>My Max Bid</t>
   </si>
   <si>
-    <t>New Values</t>
-  </si>
-  <si>
     <t>EnforceUpTo</t>
-  </si>
-  <si>
-    <t>Spine</t>
   </si>
   <si>
     <t>Value vs Fair</t>
@@ -59,7 +50,16 @@
     <t>Settings</t>
   </si>
   <si>
+    <t>Decay</t>
+  </si>
+  <si>
     <t>Jeremiyah Love</t>
+  </si>
+  <si>
+    <t>New Values</t>
+  </si>
+  <si>
+    <t>Spine</t>
   </si>
   <si>
     <t>Floors</t>
@@ -107,9 +107,6 @@
     <t>Kenyon Sadiq</t>
   </si>
   <si>
-    <t>Round 1</t>
-  </si>
-  <si>
     <t>My Spent</t>
   </si>
   <si>
@@ -120,6 +117,9 @@
   </si>
   <si>
     <t>KC Concepcion</t>
+  </si>
+  <si>
+    <t>Round 1</t>
   </si>
   <si>
     <t>Other Teams Remaining</t>
@@ -140,9 +140,6 @@
     <t>Omar Cooper</t>
   </si>
   <si>
-    <t>Round 2</t>
-  </si>
-  <si>
     <t>CJ Allen</t>
   </si>
   <si>
@@ -161,13 +158,13 @@
     <t>Denzel Boston</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>Round 2</t>
   </si>
   <si>
     <t>Aggression</t>
   </si>
   <si>
-    <t>Round 4</t>
+    <t>Round 3</t>
   </si>
   <si>
     <t>Caleb Downs</t>
@@ -179,13 +176,13 @@
     <t>League Spent %</t>
   </si>
   <si>
+    <t>Round 4</t>
+  </si>
+  <si>
     <t>Jacob Rodriguez</t>
   </si>
   <si>
     <t>Jonah Coleman</t>
-  </si>
-  <si>
-    <t>Round 5</t>
   </si>
   <si>
     <t>Jake Golday</t>
@@ -200,7 +197,7 @@
     <t>Chris Bell</t>
   </si>
   <si>
-    <t>Round 6</t>
+    <t>Round 5</t>
   </si>
   <si>
     <t>Germie Bernard</t>
@@ -222,6 +219,9 @@
   </si>
   <si>
     <t>Emmett Johnson</t>
+  </si>
+  <si>
+    <t>Round 6</t>
   </si>
   <si>
     <t>Chris Brazzell</t>
@@ -617,20 +617,20 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -914,24 +914,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="6">
+        <v>15</v>
+      </c>
+      <c r="F1" s="7">
         <v>2025.0</v>
       </c>
-      <c r="G1" s="6">
+      <c r="G1" s="7">
         <v>2024.0</v>
       </c>
       <c r="H1" s="9">
@@ -949,52 +949,52 @@
       <c r="L1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="6">
+      <c r="M1" s="7">
         <v>12.0</v>
       </c>
       <c r="N1" s="12"/>
       <c r="O1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="6">
+      <c r="P1" s="7">
         <v>1.0</v>
       </c>
-      <c r="Q1" s="6">
+      <c r="Q1" s="7">
         <v>2.0</v>
       </c>
-      <c r="R1" s="6">
+      <c r="R1" s="7">
         <v>3.0</v>
       </c>
-      <c r="S1" s="6">
+      <c r="S1" s="7">
         <v>4.0</v>
       </c>
-      <c r="T1" s="6">
+      <c r="T1" s="7">
         <v>5.0</v>
       </c>
-      <c r="U1" s="6">
+      <c r="U1" s="7">
         <v>6.0</v>
       </c>
-      <c r="V1" s="6">
+      <c r="V1" s="7">
         <v>7.0</v>
       </c>
-      <c r="W1" s="6">
+      <c r="W1" s="7">
         <v>8.0</v>
       </c>
-      <c r="X1" s="6">
+      <c r="X1" s="7">
         <v>9.0</v>
       </c>
-      <c r="Y1" s="6">
+      <c r="Y1" s="7">
         <v>10.0</v>
       </c>
-      <c r="Z1" s="6">
+      <c r="Z1" s="7">
         <v>11.0</v>
       </c>
-      <c r="AA1" s="6">
+      <c r="AA1" s="7">
         <v>12.0</v>
       </c>
       <c r="AB1" s="10"/>
       <c r="AC1" s="10"/>
-      <c r="AD1" s="6">
+      <c r="AD1" s="7">
         <f>1200 / SUM($P$2:$AA$7)</f>
         <v>1</v>
       </c>
@@ -1003,7 +1003,7 @@
       <c r="A2" s="13">
         <v>1.01</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="3">
         <v>7580.0</v>
       </c>
       <c r="C2" s="16">
@@ -1071,7 +1071,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="10" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1132,7 +1132,7 @@
       <c r="A3" s="13">
         <v>1.02</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>5598.5</v>
       </c>
       <c r="C3" s="16">
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1241,7 +1241,7 @@
       <c r="A4" s="13">
         <v>1.03</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>5649.0</v>
       </c>
       <c r="C4" s="16">
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1345,7 +1345,7 @@
       <c r="A5" s="13">
         <v>1.04</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>5074.5</v>
       </c>
       <c r="C5" s="16">
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1449,7 +1449,7 @@
       <c r="A6" s="13">
         <v>1.05</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>5076.0</v>
       </c>
       <c r="C6" s="16">
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="10" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1553,7 +1553,7 @@
       <c r="A7" s="13">
         <v>1.06</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>4965.0</v>
       </c>
       <c r="C7" s="16">
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="10" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1657,7 +1657,7 @@
       <c r="A8" s="13">
         <v>1.07</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>4014.5</v>
       </c>
       <c r="C8" s="16">
@@ -1759,7 +1759,7 @@
       <c r="A9" s="13">
         <v>1.08</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="3">
         <v>4308.0</v>
       </c>
       <c r="C9" s="16">
@@ -1822,7 +1822,7 @@
       <c r="A10" s="13">
         <v>1.09</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="3">
         <v>3869.0</v>
       </c>
       <c r="C10" s="16">
@@ -1885,7 +1885,7 @@
       <c r="A11" s="13">
         <v>1.1</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="3">
         <v>4169.0</v>
       </c>
       <c r="C11" s="16">
@@ -1948,7 +1948,7 @@
       <c r="A12" s="13">
         <v>1.11</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="3">
         <v>4164.0</v>
       </c>
       <c r="C12" s="16">
@@ -2011,7 +2011,7 @@
       <c r="A13" s="13">
         <v>1.12</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="3">
         <v>3809.5</v>
       </c>
       <c r="C13" s="16">
@@ -2074,7 +2074,7 @@
       <c r="A14" s="13">
         <v>2.01</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="3">
         <v>3397.5</v>
       </c>
       <c r="C14" s="16">
@@ -2137,7 +2137,7 @@
       <c r="A15" s="13">
         <v>2.02</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="3">
         <v>3611.0</v>
       </c>
       <c r="C15" s="16">
@@ -2200,7 +2200,7 @@
       <c r="A16" s="13">
         <v>2.03</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="3">
         <v>3605.0</v>
       </c>
       <c r="C16" s="16">
@@ -2263,7 +2263,7 @@
       <c r="A17" s="13">
         <v>2.04</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="3">
         <v>3603.0</v>
       </c>
       <c r="C17" s="16">
@@ -2326,7 +2326,7 @@
       <c r="A18" s="13">
         <v>2.05</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="3">
         <v>3440.5</v>
       </c>
       <c r="C18" s="16">
@@ -2389,7 +2389,7 @@
       <c r="A19" s="13">
         <v>2.06</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="3">
         <v>3220.0</v>
       </c>
       <c r="C19" s="16">
@@ -2452,7 +2452,7 @@
       <c r="A20" s="13">
         <v>2.07</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="3">
         <v>3200.0</v>
       </c>
       <c r="C20" s="16">
@@ -2515,7 +2515,7 @@
       <c r="A21" s="13">
         <v>2.08</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="3">
         <v>3127.0</v>
       </c>
       <c r="C21" s="16">
@@ -2578,7 +2578,7 @@
       <c r="A22" s="13">
         <v>2.09</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="3">
         <v>2943.0</v>
       </c>
       <c r="C22" s="16">
@@ -2641,7 +2641,7 @@
       <c r="A23" s="13">
         <v>2.1</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="3">
         <v>3020.0</v>
       </c>
       <c r="C23" s="16">
@@ -2704,7 +2704,7 @@
       <c r="A24" s="13">
         <v>2.11</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="3">
         <v>2537.5</v>
       </c>
       <c r="C24" s="16">
@@ -2767,7 +2767,7 @@
       <c r="A25" s="13">
         <v>2.12</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="3">
         <v>2406.0</v>
       </c>
       <c r="C25" s="16">
@@ -2830,7 +2830,7 @@
       <c r="A26" s="13">
         <v>3.01</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="3">
         <v>2671.0</v>
       </c>
       <c r="C26" s="16">
@@ -2893,7 +2893,7 @@
       <c r="A27" s="13">
         <v>3.02</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="3">
         <v>2628.0</v>
       </c>
       <c r="C27" s="16">
@@ -2956,7 +2956,7 @@
       <c r="A28" s="13">
         <v>3.03</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="3">
         <v>1998.5</v>
       </c>
       <c r="C28" s="16">
@@ -3019,7 +3019,7 @@
       <c r="A29" s="13">
         <v>3.04</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="3">
         <v>2202.5</v>
       </c>
       <c r="C29" s="16">
@@ -3100,7 +3100,7 @@
       <c r="A30" s="13">
         <v>3.05</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="3">
         <v>2252.5</v>
       </c>
       <c r="C30" s="16">
@@ -3142,14 +3142,14 @@
       </c>
       <c r="M30" s="12"/>
       <c r="N30" s="12"/>
-      <c r="O30" s="6">
+      <c r="O30" s="7">
         <v>1.0</v>
       </c>
       <c r="P30" s="10" t="s">
         <v>122</v>
       </c>
       <c r="Q30" s="12"/>
-      <c r="R30" s="6">
+      <c r="R30" s="7">
         <v>12.0</v>
       </c>
       <c r="S30" s="12"/>
@@ -3160,7 +3160,7 @@
       <c r="U30" s="12"/>
       <c r="V30" s="23"/>
       <c r="W30" s="23"/>
-      <c r="X30" s="7"/>
+      <c r="X30" s="6"/>
       <c r="Y30" s="12" t="str">
         <f t="shared" ref="Y30:Y81" si="17">TEXT(V30,"0")&amp;"|"&amp;TRIM(W30)</f>
         <v>0|</v>
@@ -3175,7 +3175,7 @@
       <c r="A31" s="13">
         <v>3.06</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="3">
         <v>2458.0</v>
       </c>
       <c r="C31" s="16">
@@ -3217,14 +3217,14 @@
       </c>
       <c r="M31" s="12"/>
       <c r="N31" s="12"/>
-      <c r="O31" s="6">
+      <c r="O31" s="7">
         <v>2.0</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>123</v>
       </c>
       <c r="Q31" s="12"/>
-      <c r="R31" s="6">
+      <c r="R31" s="7">
         <v>11.0</v>
       </c>
       <c r="S31" s="12"/>
@@ -3234,8 +3234,8 @@
       </c>
       <c r="U31" s="12"/>
       <c r="V31" s="9"/>
-      <c r="W31" s="7"/>
-      <c r="X31" s="7"/>
+      <c r="W31" s="6"/>
+      <c r="X31" s="6"/>
       <c r="Y31" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3250,7 +3250,7 @@
       <c r="A32" s="13">
         <v>3.07</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="3">
         <v>2332.5</v>
       </c>
       <c r="C32" s="16">
@@ -3292,14 +3292,14 @@
       </c>
       <c r="M32" s="12"/>
       <c r="N32" s="12"/>
-      <c r="O32" s="6">
+      <c r="O32" s="7">
         <v>3.0</v>
       </c>
       <c r="P32" s="10" t="s">
         <v>124</v>
       </c>
       <c r="Q32" s="12"/>
-      <c r="R32" s="6">
+      <c r="R32" s="7">
         <v>10.0</v>
       </c>
       <c r="S32" s="12"/>
@@ -3309,8 +3309,8 @@
       </c>
       <c r="U32" s="12"/>
       <c r="V32" s="9"/>
-      <c r="W32" s="7"/>
-      <c r="X32" s="7"/>
+      <c r="W32" s="6"/>
+      <c r="X32" s="6"/>
       <c r="Y32" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3325,7 +3325,7 @@
       <c r="A33" s="13">
         <v>3.08</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="3">
         <v>2331.0</v>
       </c>
       <c r="C33" s="16">
@@ -3367,14 +3367,14 @@
       </c>
       <c r="M33" s="12"/>
       <c r="N33" s="12"/>
-      <c r="O33" s="6">
+      <c r="O33" s="7">
         <v>4.0</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>125</v>
       </c>
       <c r="Q33" s="12"/>
-      <c r="R33" s="6">
+      <c r="R33" s="7">
         <v>9.0</v>
       </c>
       <c r="S33" s="12"/>
@@ -3384,8 +3384,8 @@
       </c>
       <c r="U33" s="12"/>
       <c r="V33" s="9"/>
-      <c r="W33" s="7"/>
-      <c r="X33" s="7"/>
+      <c r="W33" s="6"/>
+      <c r="X33" s="6"/>
       <c r="Y33" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3400,7 +3400,7 @@
       <c r="A34" s="13">
         <v>3.09</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="3">
         <v>1991.0</v>
       </c>
       <c r="C34" s="16">
@@ -3442,14 +3442,14 @@
       </c>
       <c r="M34" s="12"/>
       <c r="N34" s="12"/>
-      <c r="O34" s="6">
+      <c r="O34" s="7">
         <v>5.0</v>
       </c>
       <c r="P34" s="10" t="s">
         <v>126</v>
       </c>
       <c r="Q34" s="12"/>
-      <c r="R34" s="6">
+      <c r="R34" s="7">
         <v>8.0</v>
       </c>
       <c r="S34" s="12"/>
@@ -3459,8 +3459,8 @@
       </c>
       <c r="U34" s="12"/>
       <c r="V34" s="9"/>
-      <c r="W34" s="7"/>
-      <c r="X34" s="7"/>
+      <c r="W34" s="6"/>
+      <c r="X34" s="6"/>
       <c r="Y34" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3475,7 +3475,7 @@
       <c r="A35" s="13">
         <v>3.1</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="3">
         <v>2180.5</v>
       </c>
       <c r="C35" s="16">
@@ -3517,14 +3517,14 @@
       </c>
       <c r="M35" s="12"/>
       <c r="N35" s="12"/>
-      <c r="O35" s="6">
+      <c r="O35" s="7">
         <v>6.0</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>127</v>
       </c>
       <c r="Q35" s="12"/>
-      <c r="R35" s="6">
+      <c r="R35" s="7">
         <v>7.0</v>
       </c>
       <c r="S35" s="12"/>
@@ -3534,8 +3534,8 @@
       </c>
       <c r="U35" s="12"/>
       <c r="V35" s="9"/>
-      <c r="W35" s="7"/>
-      <c r="X35" s="7"/>
+      <c r="W35" s="6"/>
+      <c r="X35" s="6"/>
       <c r="Y35" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3550,7 +3550,7 @@
       <c r="A36" s="13">
         <v>3.11</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="3">
         <v>2432.0</v>
       </c>
       <c r="C36" s="16">
@@ -3592,14 +3592,14 @@
       </c>
       <c r="M36" s="12"/>
       <c r="N36" s="12"/>
-      <c r="O36" s="6">
+      <c r="O36" s="7">
         <v>7.0</v>
       </c>
       <c r="P36" s="10" t="s">
         <v>128</v>
       </c>
       <c r="Q36" s="12"/>
-      <c r="R36" s="6">
+      <c r="R36" s="7">
         <v>6.0</v>
       </c>
       <c r="S36" s="12"/>
@@ -3609,8 +3609,8 @@
       </c>
       <c r="U36" s="12"/>
       <c r="V36" s="9"/>
-      <c r="W36" s="7"/>
-      <c r="X36" s="7"/>
+      <c r="W36" s="6"/>
+      <c r="X36" s="6"/>
       <c r="Y36" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3625,7 +3625,7 @@
       <c r="A37" s="13">
         <v>3.12</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" s="3">
         <v>2014.0</v>
       </c>
       <c r="C37" s="16">
@@ -3667,14 +3667,14 @@
       </c>
       <c r="M37" s="12"/>
       <c r="N37" s="12"/>
-      <c r="O37" s="6">
+      <c r="O37" s="7">
         <v>8.0</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>129</v>
       </c>
       <c r="Q37" s="12"/>
-      <c r="R37" s="6">
+      <c r="R37" s="7">
         <v>5.0</v>
       </c>
       <c r="S37" s="12"/>
@@ -3684,8 +3684,8 @@
       </c>
       <c r="U37" s="12"/>
       <c r="V37" s="9"/>
-      <c r="W37" s="7"/>
-      <c r="X37" s="7"/>
+      <c r="W37" s="6"/>
+      <c r="X37" s="6"/>
       <c r="Y37" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3700,7 +3700,7 @@
       <c r="A38" s="13">
         <v>4.01</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38" s="3">
         <v>1907.0</v>
       </c>
       <c r="C38" s="16">
@@ -3742,14 +3742,14 @@
       </c>
       <c r="M38" s="12"/>
       <c r="N38" s="12"/>
-      <c r="O38" s="6">
+      <c r="O38" s="7">
         <v>9.0</v>
       </c>
       <c r="P38" s="10" t="s">
         <v>130</v>
       </c>
       <c r="Q38" s="12"/>
-      <c r="R38" s="6">
+      <c r="R38" s="7">
         <v>4.0</v>
       </c>
       <c r="S38" s="12"/>
@@ -3759,8 +3759,8 @@
       </c>
       <c r="U38" s="12"/>
       <c r="V38" s="9"/>
-      <c r="W38" s="7"/>
-      <c r="X38" s="7"/>
+      <c r="W38" s="6"/>
+      <c r="X38" s="6"/>
       <c r="Y38" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3775,7 +3775,7 @@
       <c r="A39" s="13">
         <v>4.02</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B39" s="3">
         <v>2089.0</v>
       </c>
       <c r="C39" s="16">
@@ -3817,14 +3817,14 @@
       </c>
       <c r="M39" s="12"/>
       <c r="N39" s="12"/>
-      <c r="O39" s="6">
+      <c r="O39" s="7">
         <v>10.0</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>131</v>
       </c>
       <c r="Q39" s="12"/>
-      <c r="R39" s="6">
+      <c r="R39" s="7">
         <v>3.0</v>
       </c>
       <c r="S39" s="12"/>
@@ -3834,8 +3834,8 @@
       </c>
       <c r="U39" s="12"/>
       <c r="V39" s="9"/>
-      <c r="W39" s="7"/>
-      <c r="X39" s="7"/>
+      <c r="W39" s="6"/>
+      <c r="X39" s="6"/>
       <c r="Y39" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3850,7 +3850,7 @@
       <c r="A40" s="13">
         <v>4.03</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B40" s="3">
         <v>2080.0</v>
       </c>
       <c r="C40" s="16">
@@ -3892,14 +3892,14 @@
       </c>
       <c r="M40" s="12"/>
       <c r="N40" s="12"/>
-      <c r="O40" s="6">
+      <c r="O40" s="7">
         <v>11.0</v>
       </c>
       <c r="P40" s="10" t="s">
         <v>132</v>
       </c>
       <c r="Q40" s="12"/>
-      <c r="R40" s="6">
+      <c r="R40" s="7">
         <v>2.0</v>
       </c>
       <c r="S40" s="12"/>
@@ -3909,8 +3909,8 @@
       </c>
       <c r="U40" s="12"/>
       <c r="V40" s="9"/>
-      <c r="W40" s="7"/>
-      <c r="X40" s="7"/>
+      <c r="W40" s="6"/>
+      <c r="X40" s="6"/>
       <c r="Y40" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3925,7 +3925,7 @@
       <c r="A41" s="13">
         <v>4.04</v>
       </c>
-      <c r="B41" s="4">
+      <c r="B41" s="3">
         <v>2063.0</v>
       </c>
       <c r="C41" s="16">
@@ -3967,14 +3967,14 @@
       </c>
       <c r="M41" s="12"/>
       <c r="N41" s="12"/>
-      <c r="O41" s="6">
+      <c r="O41" s="7">
         <v>12.0</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>133</v>
       </c>
       <c r="Q41" s="12"/>
-      <c r="R41" s="6">
+      <c r="R41" s="7">
         <v>1.0</v>
       </c>
       <c r="S41" s="12"/>
@@ -3984,8 +3984,8 @@
       </c>
       <c r="U41" s="12"/>
       <c r="V41" s="9"/>
-      <c r="W41" s="7"/>
-      <c r="X41" s="7"/>
+      <c r="W41" s="6"/>
+      <c r="X41" s="6"/>
       <c r="Y41" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4050,8 +4050,8 @@
       <c r="T42" s="12"/>
       <c r="U42" s="12"/>
       <c r="V42" s="9"/>
-      <c r="W42" s="7"/>
-      <c r="X42" s="7"/>
+      <c r="W42" s="6"/>
+      <c r="X42" s="6"/>
       <c r="Y42" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4066,7 +4066,7 @@
       <c r="A43" s="13">
         <v>4.06</v>
       </c>
-      <c r="B43" s="4">
+      <c r="B43" s="3">
         <v>1539.5</v>
       </c>
       <c r="C43" s="16">
@@ -4116,8 +4116,8 @@
       <c r="T43" s="12"/>
       <c r="U43" s="12"/>
       <c r="V43" s="9"/>
-      <c r="W43" s="7"/>
-      <c r="X43" s="7"/>
+      <c r="W43" s="6"/>
+      <c r="X43" s="6"/>
       <c r="Y43" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4132,7 +4132,7 @@
       <c r="A44" s="13">
         <v>4.07</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B44" s="3">
         <v>1956.0</v>
       </c>
       <c r="C44" s="16">
@@ -4190,8 +4190,8 @@
       <c r="T44" s="12"/>
       <c r="U44" s="12"/>
       <c r="V44" s="9"/>
-      <c r="W44" s="7"/>
-      <c r="X44" s="7"/>
+      <c r="W44" s="6"/>
+      <c r="X44" s="6"/>
       <c r="Y44" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4206,7 +4206,7 @@
       <c r="A45" s="13">
         <v>4.08</v>
       </c>
-      <c r="B45" s="4">
+      <c r="B45" s="3">
         <v>1953.0</v>
       </c>
       <c r="C45" s="16">
@@ -4280,8 +4280,8 @@
       <c r="T45" s="12"/>
       <c r="U45" s="12"/>
       <c r="V45" s="9"/>
-      <c r="W45" s="7"/>
-      <c r="X45" s="7"/>
+      <c r="W45" s="6"/>
+      <c r="X45" s="6"/>
       <c r="Y45" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4296,7 +4296,7 @@
       <c r="A46" s="13">
         <v>4.09</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B46" s="3">
         <v>1945.0</v>
       </c>
       <c r="C46" s="16">
@@ -4358,8 +4358,8 @@
       <c r="T46" s="12"/>
       <c r="U46" s="12"/>
       <c r="V46" s="9"/>
-      <c r="W46" s="7"/>
-      <c r="X46" s="7"/>
+      <c r="W46" s="6"/>
+      <c r="X46" s="6"/>
       <c r="Y46" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4374,7 +4374,7 @@
       <c r="A47" s="13">
         <v>4.1</v>
       </c>
-      <c r="B47" s="4">
+      <c r="B47" s="3">
         <v>1938.0</v>
       </c>
       <c r="C47" s="16">
@@ -4436,8 +4436,8 @@
       <c r="T47" s="12"/>
       <c r="U47" s="12"/>
       <c r="V47" s="9"/>
-      <c r="W47" s="7"/>
-      <c r="X47" s="7"/>
+      <c r="W47" s="6"/>
+      <c r="X47" s="6"/>
       <c r="Y47" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4452,7 +4452,7 @@
       <c r="A48" s="13">
         <v>4.11</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48" s="3">
         <v>1926.0</v>
       </c>
       <c r="C48" s="16">
@@ -4514,8 +4514,8 @@
       <c r="T48" s="12"/>
       <c r="U48" s="12"/>
       <c r="V48" s="9"/>
-      <c r="W48" s="7"/>
-      <c r="X48" s="7"/>
+      <c r="W48" s="6"/>
+      <c r="X48" s="6"/>
       <c r="Y48" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4530,7 +4530,7 @@
       <c r="A49" s="13">
         <v>4.12</v>
       </c>
-      <c r="B49" s="4">
+      <c r="B49" s="3">
         <v>1917.0</v>
       </c>
       <c r="C49" s="16">
@@ -4592,8 +4592,8 @@
       <c r="T49" s="12"/>
       <c r="U49" s="12"/>
       <c r="V49" s="9"/>
-      <c r="W49" s="7"/>
-      <c r="X49" s="7"/>
+      <c r="W49" s="6"/>
+      <c r="X49" s="6"/>
       <c r="Y49" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4608,7 +4608,7 @@
       <c r="A50" s="13">
         <v>5.01</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50" s="3">
         <v>1917.0</v>
       </c>
       <c r="C50" s="16">
@@ -4670,8 +4670,8 @@
       <c r="T50" s="12"/>
       <c r="U50" s="12"/>
       <c r="V50" s="9"/>
-      <c r="W50" s="7"/>
-      <c r="X50" s="7"/>
+      <c r="W50" s="6"/>
+      <c r="X50" s="6"/>
       <c r="Y50" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4686,7 +4686,7 @@
       <c r="A51" s="13">
         <v>5.02</v>
       </c>
-      <c r="B51" s="4">
+      <c r="B51" s="3">
         <v>1916.0</v>
       </c>
       <c r="C51" s="16">
@@ -4748,8 +4748,8 @@
       <c r="T51" s="12"/>
       <c r="U51" s="12"/>
       <c r="V51" s="9"/>
-      <c r="W51" s="7"/>
-      <c r="X51" s="7"/>
+      <c r="W51" s="6"/>
+      <c r="X51" s="6"/>
       <c r="Y51" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4764,7 +4764,7 @@
       <c r="A52" s="13">
         <v>5.03</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52" s="3">
         <v>1647.5</v>
       </c>
       <c r="C52" s="16">
@@ -4826,8 +4826,8 @@
       <c r="T52" s="12"/>
       <c r="U52" s="12"/>
       <c r="V52" s="9"/>
-      <c r="W52" s="7"/>
-      <c r="X52" s="7"/>
+      <c r="W52" s="6"/>
+      <c r="X52" s="6"/>
       <c r="Y52" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4842,7 +4842,7 @@
       <c r="A53" s="13">
         <v>5.04</v>
       </c>
-      <c r="B53" s="4">
+      <c r="B53" s="3">
         <v>1374.0</v>
       </c>
       <c r="C53" s="16">
@@ -4904,8 +4904,8 @@
       <c r="T53" s="12"/>
       <c r="U53" s="12"/>
       <c r="V53" s="9"/>
-      <c r="W53" s="7"/>
-      <c r="X53" s="7"/>
+      <c r="W53" s="6"/>
+      <c r="X53" s="6"/>
       <c r="Y53" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4920,7 +4920,7 @@
       <c r="A54" s="13">
         <v>5.05</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54" s="3">
         <v>1424.0</v>
       </c>
       <c r="C54" s="16">
@@ -4982,8 +4982,8 @@
       <c r="T54" s="12"/>
       <c r="U54" s="12"/>
       <c r="V54" s="9"/>
-      <c r="W54" s="7"/>
-      <c r="X54" s="7"/>
+      <c r="W54" s="6"/>
+      <c r="X54" s="6"/>
       <c r="Y54" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4998,7 +4998,7 @@
       <c r="A55" s="13">
         <v>5.06</v>
       </c>
-      <c r="B55" s="4">
+      <c r="B55" s="3">
         <v>1370.5</v>
       </c>
       <c r="C55" s="16">
@@ -5060,8 +5060,8 @@
       <c r="T55" s="12"/>
       <c r="U55" s="12"/>
       <c r="V55" s="9"/>
-      <c r="W55" s="7"/>
-      <c r="X55" s="7"/>
+      <c r="W55" s="6"/>
+      <c r="X55" s="6"/>
       <c r="Y55" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5076,7 +5076,7 @@
       <c r="A56" s="13">
         <v>5.07</v>
       </c>
-      <c r="B56" s="4">
+      <c r="B56" s="3">
         <v>1643.0</v>
       </c>
       <c r="C56" s="16">
@@ -5138,8 +5138,8 @@
       <c r="T56" s="12"/>
       <c r="U56" s="12"/>
       <c r="V56" s="9"/>
-      <c r="W56" s="7"/>
-      <c r="X56" s="7"/>
+      <c r="W56" s="6"/>
+      <c r="X56" s="6"/>
       <c r="Y56" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5154,7 +5154,7 @@
       <c r="A57" s="13">
         <v>5.08</v>
       </c>
-      <c r="B57" s="4">
+      <c r="B57" s="3">
         <v>1628.0</v>
       </c>
       <c r="C57" s="16">
@@ -5216,8 +5216,8 @@
       <c r="T57" s="12"/>
       <c r="U57" s="12"/>
       <c r="V57" s="9"/>
-      <c r="W57" s="7"/>
-      <c r="X57" s="7"/>
+      <c r="W57" s="6"/>
+      <c r="X57" s="6"/>
       <c r="Y57" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5232,7 +5232,7 @@
       <c r="A58" s="13">
         <v>5.09</v>
       </c>
-      <c r="B58" s="4">
+      <c r="B58" s="3">
         <v>1302.0</v>
       </c>
       <c r="C58" s="16">
@@ -5295,7 +5295,7 @@
       <c r="U58" s="12"/>
       <c r="V58" s="23"/>
       <c r="W58" s="23"/>
-      <c r="X58" s="7"/>
+      <c r="X58" s="6"/>
       <c r="Y58" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5310,7 +5310,7 @@
       <c r="A59" s="13">
         <v>5.1</v>
       </c>
-      <c r="B59" s="4">
+      <c r="B59" s="3">
         <v>1284.0</v>
       </c>
       <c r="C59" s="16">
@@ -5373,7 +5373,7 @@
       <c r="U59" s="12"/>
       <c r="V59" s="23"/>
       <c r="W59" s="23"/>
-      <c r="X59" s="7"/>
+      <c r="X59" s="6"/>
       <c r="Y59" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5388,7 +5388,7 @@
       <c r="A60" s="13">
         <v>5.11</v>
       </c>
-      <c r="B60" s="4">
+      <c r="B60" s="3">
         <v>1254.0</v>
       </c>
       <c r="C60" s="16">
@@ -5451,7 +5451,7 @@
       <c r="U60" s="12"/>
       <c r="V60" s="23"/>
       <c r="W60" s="23"/>
-      <c r="X60" s="7"/>
+      <c r="X60" s="6"/>
       <c r="Y60" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5466,7 +5466,7 @@
       <c r="A61" s="13">
         <v>5.12</v>
       </c>
-      <c r="B61" s="4">
+      <c r="B61" s="3">
         <v>1253.0</v>
       </c>
       <c r="C61" s="16">
@@ -5528,8 +5528,8 @@
       <c r="T61" s="12"/>
       <c r="U61" s="12"/>
       <c r="V61" s="9"/>
-      <c r="W61" s="7"/>
-      <c r="X61" s="7"/>
+      <c r="W61" s="6"/>
+      <c r="X61" s="6"/>
       <c r="Y61" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5544,7 +5544,7 @@
       <c r="A62" s="13">
         <v>6.01</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B62" s="3">
         <v>1251.0</v>
       </c>
       <c r="C62" s="16">
@@ -5609,9 +5609,9 @@
       <c r="U62" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="V62" s="7"/>
-      <c r="W62" s="7"/>
-      <c r="X62" s="7"/>
+      <c r="V62" s="6"/>
+      <c r="W62" s="6"/>
+      <c r="X62" s="6"/>
       <c r="Y62" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5626,7 +5626,7 @@
       <c r="A63" s="13">
         <v>6.02</v>
       </c>
-      <c r="B63" s="4">
+      <c r="B63" s="3">
         <v>1250.0</v>
       </c>
       <c r="C63" s="16">
@@ -5692,9 +5692,9 @@
         <f t="shared" ref="U63:U74" si="22">SUMIF($R$45:$R$116, T63, $Q$45:$Q$116)</f>
         <v>180</v>
       </c>
-      <c r="V63" s="7"/>
-      <c r="W63" s="7"/>
-      <c r="X63" s="7"/>
+      <c r="V63" s="6"/>
+      <c r="W63" s="6"/>
+      <c r="X63" s="6"/>
       <c r="Y63" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5709,7 +5709,7 @@
       <c r="A64" s="13">
         <v>6.03</v>
       </c>
-      <c r="B64" s="4">
+      <c r="B64" s="3">
         <v>1249.0</v>
       </c>
       <c r="C64" s="16">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="V64" s="23"/>
       <c r="W64" s="23"/>
-      <c r="X64" s="7"/>
+      <c r="X64" s="6"/>
       <c r="Y64" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5792,7 +5792,7 @@
       <c r="A65" s="13">
         <v>6.04</v>
       </c>
-      <c r="B65" s="4">
+      <c r="B65" s="3">
         <v>1246.0</v>
       </c>
       <c r="C65" s="16">
@@ -5858,9 +5858,9 @@
         <f t="shared" si="22"/>
         <v>132.5</v>
       </c>
-      <c r="V65" s="7"/>
-      <c r="W65" s="7"/>
-      <c r="X65" s="7"/>
+      <c r="V65" s="6"/>
+      <c r="W65" s="6"/>
+      <c r="X65" s="6"/>
       <c r="Y65" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5875,7 +5875,7 @@
       <c r="A66" s="13">
         <v>6.05</v>
       </c>
-      <c r="B66" s="4">
+      <c r="B66" s="3">
         <v>1245.0</v>
       </c>
       <c r="C66" s="16">
@@ -5942,8 +5942,8 @@
         <v>117.5</v>
       </c>
       <c r="V66" s="9"/>
-      <c r="W66" s="7"/>
-      <c r="X66" s="7"/>
+      <c r="W66" s="6"/>
+      <c r="X66" s="6"/>
       <c r="Y66" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5958,7 +5958,7 @@
       <c r="A67" s="13">
         <v>6.06</v>
       </c>
-      <c r="B67" s="4">
+      <c r="B67" s="3">
         <v>1244.0</v>
       </c>
       <c r="C67" s="16">
@@ -6025,8 +6025,8 @@
         <v>109.5</v>
       </c>
       <c r="V67" s="9"/>
-      <c r="W67" s="7"/>
-      <c r="X67" s="7"/>
+      <c r="W67" s="6"/>
+      <c r="X67" s="6"/>
       <c r="Y67" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -6041,7 +6041,7 @@
       <c r="A68" s="13">
         <v>6.07</v>
       </c>
-      <c r="B68" s="4">
+      <c r="B68" s="3">
         <v>1243.0</v>
       </c>
       <c r="C68" s="16">
@@ -6108,8 +6108,8 @@
         <v>99.5</v>
       </c>
       <c r="V68" s="9"/>
-      <c r="W68" s="7"/>
-      <c r="X68" s="7"/>
+      <c r="W68" s="6"/>
+      <c r="X68" s="6"/>
       <c r="Y68" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="V69" s="23"/>
       <c r="W69" s="23"/>
-      <c r="X69" s="7"/>
+      <c r="X69" s="6"/>
       <c r="Y69" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -6207,7 +6207,7 @@
       <c r="A70" s="13">
         <v>6.09</v>
       </c>
-      <c r="B70" s="4">
+      <c r="B70" s="3">
         <v>1234.0</v>
       </c>
       <c r="C70" s="16">
@@ -6290,7 +6290,7 @@
       <c r="A71" s="13">
         <v>6.1</v>
       </c>
-      <c r="B71" s="4">
+      <c r="B71" s="3">
         <v>1223.0</v>
       </c>
       <c r="C71" s="16">
@@ -6456,7 +6456,7 @@
       <c r="A73" s="13">
         <v>6.12</v>
       </c>
-      <c r="B73" s="4">
+      <c r="B73" s="3">
         <v>1166.0</v>
       </c>
       <c r="C73" s="16">
@@ -6600,7 +6600,7 @@
     </row>
     <row r="75">
       <c r="A75" s="5"/>
-      <c r="B75" s="7"/>
+      <c r="B75" s="6"/>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
@@ -6696,7 +6696,7 @@
     </row>
     <row r="77">
       <c r="A77" s="5"/>
-      <c r="B77" s="7"/>
+      <c r="B77" s="6"/>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
@@ -6743,7 +6743,7 @@
     </row>
     <row r="78">
       <c r="A78" s="5"/>
-      <c r="B78" s="7"/>
+      <c r="B78" s="6"/>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
       <c r="E78" s="5"/>
@@ -6790,7 +6790,7 @@
     </row>
     <row r="79">
       <c r="A79" s="5"/>
-      <c r="B79" s="7"/>
+      <c r="B79" s="6"/>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
@@ -6837,7 +6837,7 @@
     </row>
     <row r="80">
       <c r="A80" s="5"/>
-      <c r="B80" s="7"/>
+      <c r="B80" s="6"/>
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
       <c r="E80" s="5"/>
@@ -6884,7 +6884,7 @@
     </row>
     <row r="81">
       <c r="A81" s="5"/>
-      <c r="B81" s="7"/>
+      <c r="B81" s="6"/>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
@@ -6931,7 +6931,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5"/>
-      <c r="B82" s="7"/>
+      <c r="B82" s="6"/>
       <c r="C82" s="5"/>
       <c r="D82" s="5"/>
       <c r="E82" s="5"/>
@@ -6975,7 +6975,7 @@
     </row>
     <row r="83">
       <c r="A83" s="12"/>
-      <c r="B83" s="7"/>
+      <c r="B83" s="6"/>
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
@@ -7019,7 +7019,7 @@
     </row>
     <row r="84">
       <c r="A84" s="12"/>
-      <c r="B84" s="7"/>
+      <c r="B84" s="6"/>
       <c r="C84" s="5"/>
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
@@ -7106,7 +7106,7 @@
     </row>
     <row r="86">
       <c r="A86" s="12"/>
-      <c r="B86" s="7"/>
+      <c r="B86" s="6"/>
       <c r="C86" s="5"/>
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
@@ -7150,7 +7150,7 @@
     </row>
     <row r="87">
       <c r="A87" s="12"/>
-      <c r="B87" s="7"/>
+      <c r="B87" s="6"/>
       <c r="C87" s="5"/>
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
@@ -7194,7 +7194,7 @@
     </row>
     <row r="88">
       <c r="A88" s="12"/>
-      <c r="B88" s="7"/>
+      <c r="B88" s="6"/>
       <c r="C88" s="5"/>
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
@@ -7238,7 +7238,7 @@
     </row>
     <row r="89">
       <c r="A89" s="12"/>
-      <c r="B89" s="7"/>
+      <c r="B89" s="6"/>
       <c r="C89" s="5"/>
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
@@ -7282,7 +7282,7 @@
     </row>
     <row r="90">
       <c r="A90" s="5"/>
-      <c r="B90" s="7"/>
+      <c r="B90" s="6"/>
       <c r="C90" s="5"/>
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
@@ -7326,7 +7326,7 @@
     </row>
     <row r="91">
       <c r="A91" s="5"/>
-      <c r="B91" s="7"/>
+      <c r="B91" s="6"/>
       <c r="C91" s="5"/>
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
@@ -7370,7 +7370,7 @@
     </row>
     <row r="92">
       <c r="A92" s="5"/>
-      <c r="B92" s="7"/>
+      <c r="B92" s="6"/>
       <c r="C92" s="5"/>
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
@@ -7414,7 +7414,7 @@
     </row>
     <row r="93">
       <c r="A93" s="5"/>
-      <c r="B93" s="7"/>
+      <c r="B93" s="6"/>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
@@ -7458,7 +7458,7 @@
     </row>
     <row r="94">
       <c r="A94" s="12"/>
-      <c r="B94" s="7"/>
+      <c r="B94" s="6"/>
       <c r="C94" s="5"/>
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
@@ -7502,7 +7502,7 @@
     </row>
     <row r="95">
       <c r="A95" s="12"/>
-      <c r="B95" s="7"/>
+      <c r="B95" s="6"/>
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
@@ -7546,7 +7546,7 @@
     </row>
     <row r="96">
       <c r="A96" s="12"/>
-      <c r="B96" s="7"/>
+      <c r="B96" s="6"/>
       <c r="C96" s="5"/>
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
@@ -7590,7 +7590,7 @@
     </row>
     <row r="97">
       <c r="A97" s="12"/>
-      <c r="B97" s="7"/>
+      <c r="B97" s="6"/>
       <c r="C97" s="5"/>
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
@@ -7634,7 +7634,7 @@
     </row>
     <row r="98">
       <c r="A98" s="12"/>
-      <c r="B98" s="7"/>
+      <c r="B98" s="6"/>
       <c r="C98" s="5"/>
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
@@ -7678,7 +7678,7 @@
     </row>
     <row r="99">
       <c r="A99" s="12"/>
-      <c r="B99" s="7"/>
+      <c r="B99" s="6"/>
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
       <c r="E99" s="5"/>
@@ -7722,7 +7722,7 @@
     </row>
     <row r="100">
       <c r="A100" s="12"/>
-      <c r="B100" s="7"/>
+      <c r="B100" s="6"/>
       <c r="C100" s="5"/>
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
@@ -7766,7 +7766,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5"/>
-      <c r="B101" s="7"/>
+      <c r="B101" s="6"/>
       <c r="C101" s="5"/>
       <c r="D101" s="5"/>
       <c r="E101" s="5"/>
@@ -7810,7 +7810,7 @@
     </row>
     <row r="102">
       <c r="A102" s="5"/>
-      <c r="B102" s="7"/>
+      <c r="B102" s="6"/>
       <c r="C102" s="5"/>
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
@@ -9146,7 +9146,7 @@
       <c r="W137" s="12"/>
       <c r="X137" s="12"/>
       <c r="Y137" s="12"/>
-      <c r="Z137" s="7" t="s">
+      <c r="Z137" s="6" t="s">
         <v>137</v>
       </c>
       <c r="AA137" s="12"/>
@@ -9180,7 +9180,7 @@
       <c r="W138" s="12"/>
       <c r="X138" s="12"/>
       <c r="Y138" s="12"/>
-      <c r="Z138" s="7">
+      <c r="Z138" s="6">
         <v>6817.0</v>
       </c>
       <c r="AA138" s="12"/>
@@ -9211,16 +9211,16 @@
       <c r="T139" s="12"/>
       <c r="U139" s="12"/>
       <c r="V139" s="12"/>
-      <c r="W139" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="X139" s="7" t="s">
+      <c r="W139" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="X139" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="Y139" s="7" t="s">
+      <c r="Y139" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="Z139" s="7">
+      <c r="Z139" s="6">
         <v>5203.0</v>
       </c>
       <c r="AA139" s="12"/>
@@ -9251,16 +9251,16 @@
       <c r="T140" s="12"/>
       <c r="U140" s="12"/>
       <c r="V140" s="12"/>
-      <c r="W140" s="7">
+      <c r="W140" s="6">
         <v>1.0</v>
       </c>
-      <c r="X140" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y140" s="7" t="s">
+      <c r="X140" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y140" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="Z140" s="7">
+      <c r="Z140" s="6">
         <v>5103.0</v>
       </c>
       <c r="AA140" s="12"/>
@@ -9291,16 +9291,16 @@
       <c r="T141" s="12"/>
       <c r="U141" s="12"/>
       <c r="V141" s="12"/>
-      <c r="W141" s="7">
+      <c r="W141" s="6">
         <v>3.0</v>
       </c>
-      <c r="X141" s="7" t="s">
+      <c r="X141" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="Y141" s="7" t="s">
+      <c r="Y141" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z141" s="7">
+      <c r="Z141" s="6">
         <v>5020.0</v>
       </c>
       <c r="AA141" s="12"/>
@@ -9331,16 +9331,16 @@
       <c r="T142" s="12"/>
       <c r="U142" s="12"/>
       <c r="V142" s="12"/>
-      <c r="W142" s="7">
+      <c r="W142" s="6">
         <v>4.0</v>
       </c>
-      <c r="X142" s="7" t="s">
+      <c r="X142" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Y142" s="7" t="s">
+      <c r="Y142" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="Z142" s="7">
+      <c r="Z142" s="6">
         <v>4517.0</v>
       </c>
       <c r="AA142" s="12"/>
@@ -9371,16 +9371,16 @@
       <c r="T143" s="12"/>
       <c r="U143" s="12"/>
       <c r="V143" s="12"/>
-      <c r="W143" s="7">
+      <c r="W143" s="6">
         <v>5.0</v>
       </c>
-      <c r="X143" s="7" t="s">
+      <c r="X143" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="Y143" s="7" t="s">
+      <c r="Y143" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z143" s="7">
+      <c r="Z143" s="6">
         <v>4164.0</v>
       </c>
       <c r="AA143" s="12"/>
@@ -9411,16 +9411,16 @@
       <c r="T144" s="12"/>
       <c r="U144" s="12"/>
       <c r="V144" s="12"/>
-      <c r="W144" s="7">
+      <c r="W144" s="6">
         <v>6.0</v>
       </c>
-      <c r="X144" s="7" t="s">
+      <c r="X144" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Y144" s="7" t="s">
+      <c r="Y144" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z144" s="7">
+      <c r="Z144" s="6">
         <v>4025.0</v>
       </c>
       <c r="AA144" s="12"/>
@@ -9451,16 +9451,16 @@
       <c r="T145" s="12"/>
       <c r="U145" s="12"/>
       <c r="V145" s="12"/>
-      <c r="W145" s="7">
+      <c r="W145" s="6">
         <v>7.0</v>
       </c>
-      <c r="X145" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y145" s="7" t="s">
+      <c r="X145" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y145" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="Z145" s="7">
+      <c r="Z145" s="6">
         <v>3650.0</v>
       </c>
       <c r="AA145" s="12"/>
@@ -9491,16 +9491,16 @@
       <c r="T146" s="12"/>
       <c r="U146" s="12"/>
       <c r="V146" s="12"/>
-      <c r="W146" s="7">
+      <c r="W146" s="6">
         <v>8.0</v>
       </c>
-      <c r="X146" s="7" t="s">
+      <c r="X146" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Y146" s="7" t="s">
+      <c r="Y146" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="Z146" s="7">
+      <c r="Z146" s="6">
         <v>3611.0</v>
       </c>
       <c r="AA146" s="12"/>
@@ -9531,16 +9531,16 @@
       <c r="T147" s="12"/>
       <c r="U147" s="12"/>
       <c r="V147" s="12"/>
-      <c r="W147" s="7">
+      <c r="W147" s="6">
         <v>9.0</v>
       </c>
-      <c r="X147" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y147" s="7" t="s">
+      <c r="X147" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y147" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z147" s="7">
+      <c r="Z147" s="6">
         <v>3608.0</v>
       </c>
       <c r="AA147" s="12"/>
@@ -9571,16 +9571,16 @@
       <c r="T148" s="12"/>
       <c r="U148" s="12"/>
       <c r="V148" s="12"/>
-      <c r="W148" s="7">
+      <c r="W148" s="6">
         <v>10.0</v>
       </c>
-      <c r="X148" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y148" s="7" t="s">
+      <c r="X148" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y148" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="Z148" s="7">
+      <c r="Z148" s="6">
         <v>3596.0</v>
       </c>
       <c r="AA148" s="12"/>
@@ -9611,16 +9611,16 @@
       <c r="T149" s="12"/>
       <c r="U149" s="12"/>
       <c r="V149" s="12"/>
-      <c r="W149" s="7">
+      <c r="W149" s="6">
         <v>11.0</v>
       </c>
-      <c r="X149" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y149" s="7" t="s">
+      <c r="X149" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y149" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="Z149" s="7">
+      <c r="Z149" s="6">
         <v>3426.0</v>
       </c>
       <c r="AA149" s="12"/>
@@ -9651,16 +9651,16 @@
       <c r="T150" s="12"/>
       <c r="U150" s="12"/>
       <c r="V150" s="12"/>
-      <c r="W150" s="7">
+      <c r="W150" s="6">
         <v>12.0</v>
       </c>
-      <c r="X150" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y150" s="7" t="s">
+      <c r="X150" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y150" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="Z150" s="7">
+      <c r="Z150" s="6">
         <v>3264.0</v>
       </c>
       <c r="AA150" s="12"/>
@@ -9691,16 +9691,16 @@
       <c r="T151" s="12"/>
       <c r="U151" s="12"/>
       <c r="V151" s="12"/>
-      <c r="W151" s="7">
+      <c r="W151" s="6">
         <v>13.0</v>
       </c>
-      <c r="X151" s="7" t="s">
+      <c r="X151" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="Y151" s="7" t="s">
+      <c r="Y151" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="Z151" s="7">
+      <c r="Z151" s="6">
         <v>3179.0</v>
       </c>
       <c r="AA151" s="12"/>
@@ -9731,16 +9731,16 @@
       <c r="T152" s="12"/>
       <c r="U152" s="12"/>
       <c r="V152" s="12"/>
-      <c r="W152" s="7">
+      <c r="W152" s="6">
         <v>14.0</v>
       </c>
-      <c r="X152" s="7" t="s">
+      <c r="X152" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="Y152" s="7" t="s">
+      <c r="Y152" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="Z152" s="7">
+      <c r="Z152" s="6">
         <v>3162.0</v>
       </c>
       <c r="AA152" s="12"/>
@@ -9771,16 +9771,16 @@
       <c r="T153" s="12"/>
       <c r="U153" s="12"/>
       <c r="V153" s="12"/>
-      <c r="W153" s="7">
+      <c r="W153" s="6">
         <v>15.0</v>
       </c>
-      <c r="X153" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y153" s="7" t="s">
+      <c r="X153" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y153" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z153" s="7">
+      <c r="Z153" s="6">
         <v>3125.0</v>
       </c>
       <c r="AA153" s="12"/>
@@ -9811,16 +9811,16 @@
       <c r="T154" s="12"/>
       <c r="U154" s="12"/>
       <c r="V154" s="12"/>
-      <c r="W154" s="7">
+      <c r="W154" s="6">
         <v>16.0</v>
       </c>
-      <c r="X154" s="7" t="s">
+      <c r="X154" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="Y154" s="7" t="s">
+      <c r="Y154" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="Z154" s="7">
+      <c r="Z154" s="6">
         <v>2971.0</v>
       </c>
       <c r="AA154" s="12"/>
@@ -9851,16 +9851,16 @@
       <c r="T155" s="12"/>
       <c r="U155" s="12"/>
       <c r="V155" s="12"/>
-      <c r="W155" s="7">
+      <c r="W155" s="6">
         <v>17.0</v>
       </c>
-      <c r="X155" s="7" t="s">
+      <c r="X155" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="Y155" s="7" t="s">
+      <c r="Y155" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="Z155" s="7">
+      <c r="Z155" s="6">
         <v>2963.0</v>
       </c>
       <c r="AA155" s="12"/>
@@ -9891,16 +9891,16 @@
       <c r="T156" s="12"/>
       <c r="U156" s="12"/>
       <c r="V156" s="12"/>
-      <c r="W156" s="7">
+      <c r="W156" s="6">
         <v>18.0</v>
       </c>
-      <c r="X156" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y156" s="7" t="s">
+      <c r="X156" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y156" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="Z156" s="7">
+      <c r="Z156" s="6">
         <v>2953.0</v>
       </c>
       <c r="AA156" s="12"/>
@@ -9931,16 +9931,16 @@
       <c r="T157" s="12"/>
       <c r="U157" s="12"/>
       <c r="V157" s="12"/>
-      <c r="W157" s="7">
+      <c r="W157" s="6">
         <v>19.0</v>
       </c>
-      <c r="X157" s="7" t="s">
+      <c r="X157" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="Y157" s="7" t="s">
+      <c r="Y157" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="Z157" s="7">
+      <c r="Z157" s="6">
         <v>2807.0</v>
       </c>
       <c r="AA157" s="12"/>
@@ -9971,16 +9971,16 @@
       <c r="T158" s="12"/>
       <c r="U158" s="12"/>
       <c r="V158" s="12"/>
-      <c r="W158" s="7">
+      <c r="W158" s="6">
         <v>20.0</v>
       </c>
-      <c r="X158" s="7" t="s">
+      <c r="X158" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="Y158" s="7" t="s">
+      <c r="Y158" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="Z158" s="7">
+      <c r="Z158" s="6">
         <v>2696.0</v>
       </c>
       <c r="AA158" s="12"/>
@@ -10011,16 +10011,16 @@
       <c r="T159" s="12"/>
       <c r="U159" s="12"/>
       <c r="V159" s="12"/>
-      <c r="W159" s="7">
+      <c r="W159" s="6">
         <v>21.0</v>
       </c>
-      <c r="X159" s="7" t="s">
+      <c r="X159" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="Y159" s="7" t="s">
+      <c r="Y159" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z159" s="7">
+      <c r="Z159" s="6">
         <v>2672.0</v>
       </c>
       <c r="AA159" s="12"/>
@@ -10051,16 +10051,16 @@
       <c r="T160" s="12"/>
       <c r="U160" s="12"/>
       <c r="V160" s="12"/>
-      <c r="W160" s="7">
+      <c r="W160" s="6">
         <v>22.0</v>
       </c>
-      <c r="X160" s="7" t="s">
+      <c r="X160" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="Y160" s="7" t="s">
+      <c r="Y160" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="Z160" s="7">
+      <c r="Z160" s="6">
         <v>2480.0</v>
       </c>
       <c r="AA160" s="12"/>
@@ -10091,16 +10091,16 @@
       <c r="T161" s="12"/>
       <c r="U161" s="12"/>
       <c r="V161" s="12"/>
-      <c r="W161" s="7">
+      <c r="W161" s="6">
         <v>23.0</v>
       </c>
-      <c r="X161" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y161" s="7" t="s">
+      <c r="X161" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y161" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="Z161" s="7">
+      <c r="Z161" s="6">
         <v>2416.0</v>
       </c>
       <c r="AA161" s="12"/>
@@ -10131,16 +10131,16 @@
       <c r="T162" s="12"/>
       <c r="U162" s="12"/>
       <c r="V162" s="12"/>
-      <c r="W162" s="7">
+      <c r="W162" s="6">
         <v>24.0</v>
       </c>
-      <c r="X162" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y162" s="7" t="s">
+      <c r="X162" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y162" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z162" s="7">
+      <c r="Z162" s="6">
         <v>2416.0</v>
       </c>
       <c r="AA162" s="12"/>
@@ -10171,16 +10171,16 @@
       <c r="T163" s="12"/>
       <c r="U163" s="12"/>
       <c r="V163" s="12"/>
-      <c r="W163" s="7">
+      <c r="W163" s="6">
         <v>25.0</v>
       </c>
-      <c r="X163" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y163" s="7" t="s">
+      <c r="X163" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y163" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="Z163" s="7">
+      <c r="Z163" s="6">
         <v>2109.0</v>
       </c>
       <c r="AA163" s="12"/>
@@ -10211,16 +10211,16 @@
       <c r="T164" s="12"/>
       <c r="U164" s="12"/>
       <c r="V164" s="12"/>
-      <c r="W164" s="7">
+      <c r="W164" s="6">
         <v>26.0</v>
       </c>
-      <c r="X164" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y164" s="7" t="s">
+      <c r="X164" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y164" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="Z164" s="7">
+      <c r="Z164" s="6">
         <v>2106.0</v>
       </c>
       <c r="AA164" s="12"/>
@@ -10251,16 +10251,16 @@
       <c r="T165" s="12"/>
       <c r="U165" s="12"/>
       <c r="V165" s="12"/>
-      <c r="W165" s="7">
+      <c r="W165" s="6">
         <v>27.0</v>
       </c>
-      <c r="X165" s="7" t="s">
+      <c r="X165" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="Y165" s="7" t="s">
+      <c r="Y165" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="Z165" s="7">
+      <c r="Z165" s="6">
         <v>2098.0</v>
       </c>
       <c r="AA165" s="12"/>
@@ -10291,16 +10291,16 @@
       <c r="T166" s="12"/>
       <c r="U166" s="12"/>
       <c r="V166" s="12"/>
-      <c r="W166" s="7">
+      <c r="W166" s="6">
         <v>28.0</v>
       </c>
-      <c r="X166" s="7" t="s">
+      <c r="X166" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="Y166" s="7" t="s">
+      <c r="Y166" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z166" s="7">
+      <c r="Z166" s="6">
         <v>2078.0</v>
       </c>
       <c r="AA166" s="12"/>
@@ -10331,16 +10331,16 @@
       <c r="T167" s="12"/>
       <c r="U167" s="12"/>
       <c r="V167" s="12"/>
-      <c r="W167" s="7">
+      <c r="W167" s="6">
         <v>29.0</v>
       </c>
-      <c r="X167" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y167" s="7" t="s">
+      <c r="X167" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y167" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="Z167" s="7">
+      <c r="Z167" s="6">
         <v>2074.0</v>
       </c>
       <c r="AA167" s="12"/>
@@ -10371,16 +10371,16 @@
       <c r="T168" s="12"/>
       <c r="U168" s="12"/>
       <c r="V168" s="12"/>
-      <c r="W168" s="7">
+      <c r="W168" s="6">
         <v>30.0</v>
       </c>
-      <c r="X168" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y168" s="7" t="s">
+      <c r="X168" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y168" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z168" s="7">
+      <c r="Z168" s="6">
         <v>2066.0</v>
       </c>
       <c r="AA168" s="12"/>
@@ -10411,16 +10411,16 @@
       <c r="T169" s="12"/>
       <c r="U169" s="12"/>
       <c r="V169" s="12"/>
-      <c r="W169" s="7">
+      <c r="W169" s="6">
         <v>31.0</v>
       </c>
-      <c r="X169" s="7" t="s">
+      <c r="X169" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="Y169" s="7" t="s">
+      <c r="Y169" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z169" s="7">
+      <c r="Z169" s="6">
         <v>2045.0</v>
       </c>
       <c r="AA169" s="12"/>
@@ -10451,16 +10451,16 @@
       <c r="T170" s="12"/>
       <c r="U170" s="12"/>
       <c r="V170" s="12"/>
-      <c r="W170" s="7">
+      <c r="W170" s="6">
         <v>32.0</v>
       </c>
-      <c r="X170" s="7" t="s">
+      <c r="X170" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="Y170" s="7" t="s">
+      <c r="Y170" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="Z170" s="7">
+      <c r="Z170" s="6">
         <v>1977.0</v>
       </c>
       <c r="AA170" s="12"/>
@@ -10491,16 +10491,16 @@
       <c r="T171" s="12"/>
       <c r="U171" s="12"/>
       <c r="V171" s="12"/>
-      <c r="W171" s="7">
+      <c r="W171" s="6">
         <v>33.0</v>
       </c>
-      <c r="X171" s="7" t="s">
+      <c r="X171" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="Y171" s="7" t="s">
+      <c r="Y171" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z171" s="7">
+      <c r="Z171" s="6">
         <v>1967.0</v>
       </c>
       <c r="AA171" s="12"/>
@@ -10531,16 +10531,16 @@
       <c r="T172" s="12"/>
       <c r="U172" s="12"/>
       <c r="V172" s="12"/>
-      <c r="W172" s="7">
+      <c r="W172" s="6">
         <v>34.0</v>
       </c>
-      <c r="X172" s="7" t="s">
+      <c r="X172" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="Y172" s="7" t="s">
+      <c r="Y172" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="Z172" s="7">
+      <c r="Z172" s="6">
         <v>1962.0</v>
       </c>
       <c r="AA172" s="12"/>
@@ -10571,16 +10571,16 @@
       <c r="T173" s="12"/>
       <c r="U173" s="12"/>
       <c r="V173" s="12"/>
-      <c r="W173" s="7">
+      <c r="W173" s="6">
         <v>35.0</v>
       </c>
-      <c r="X173" s="7" t="s">
+      <c r="X173" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="Y173" s="7" t="s">
+      <c r="Y173" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="Z173" s="7">
+      <c r="Z173" s="6">
         <v>1961.0</v>
       </c>
       <c r="AA173" s="12"/>
@@ -10611,16 +10611,16 @@
       <c r="T174" s="12"/>
       <c r="U174" s="12"/>
       <c r="V174" s="12"/>
-      <c r="W174" s="7">
+      <c r="W174" s="6">
         <v>36.0</v>
       </c>
-      <c r="X174" s="7" t="s">
+      <c r="X174" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="Y174" s="7" t="s">
+      <c r="Y174" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="Z174" s="7">
+      <c r="Z174" s="6">
         <v>1910.0</v>
       </c>
       <c r="AA174" s="12"/>
@@ -10651,16 +10651,16 @@
       <c r="T175" s="12"/>
       <c r="U175" s="12"/>
       <c r="V175" s="12"/>
-      <c r="W175" s="7">
+      <c r="W175" s="6">
         <v>37.0</v>
       </c>
-      <c r="X175" s="7" t="s">
+      <c r="X175" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="Y175" s="7" t="s">
+      <c r="Y175" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="Z175" s="7">
+      <c r="Z175" s="6">
         <v>1873.0</v>
       </c>
       <c r="AA175" s="12"/>
@@ -10691,16 +10691,16 @@
       <c r="T176" s="12"/>
       <c r="U176" s="12"/>
       <c r="V176" s="12"/>
-      <c r="W176" s="7">
+      <c r="W176" s="6">
         <v>38.0</v>
       </c>
-      <c r="X176" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y176" s="7" t="s">
+      <c r="X176" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y176" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z176" s="7">
+      <c r="Z176" s="6">
         <v>1822.0</v>
       </c>
       <c r="AA176" s="12"/>
@@ -10731,16 +10731,16 @@
       <c r="T177" s="12"/>
       <c r="U177" s="12"/>
       <c r="V177" s="12"/>
-      <c r="W177" s="7">
+      <c r="W177" s="6">
         <v>39.0</v>
       </c>
-      <c r="X177" s="7" t="s">
+      <c r="X177" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="Y177" s="7" t="s">
+      <c r="Y177" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="Z177" s="7">
+      <c r="Z177" s="6">
         <v>1741.0</v>
       </c>
       <c r="AA177" s="12"/>
@@ -10771,16 +10771,16 @@
       <c r="T178" s="12"/>
       <c r="U178" s="12"/>
       <c r="V178" s="12"/>
-      <c r="W178" s="7">
+      <c r="W178" s="6">
         <v>40.0</v>
       </c>
-      <c r="X178" s="7" t="s">
+      <c r="X178" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="Y178" s="7" t="s">
+      <c r="Y178" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z178" s="7">
+      <c r="Z178" s="6">
         <v>1724.0</v>
       </c>
       <c r="AA178" s="12"/>
@@ -10811,16 +10811,16 @@
       <c r="T179" s="12"/>
       <c r="U179" s="12"/>
       <c r="V179" s="12"/>
-      <c r="W179" s="7">
+      <c r="W179" s="6">
         <v>41.0</v>
       </c>
-      <c r="X179" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y179" s="7" t="s">
+      <c r="X179" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y179" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z179" s="7">
+      <c r="Z179" s="6">
         <v>1660.0</v>
       </c>
       <c r="AA179" s="12"/>
@@ -10851,16 +10851,16 @@
       <c r="T180" s="12"/>
       <c r="U180" s="12"/>
       <c r="V180" s="12"/>
-      <c r="W180" s="7">
+      <c r="W180" s="6">
         <v>42.0</v>
       </c>
-      <c r="X180" s="7" t="s">
+      <c r="X180" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="Y180" s="7" t="s">
+      <c r="Y180" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="Z180" s="7">
+      <c r="Z180" s="6">
         <v>1640.0</v>
       </c>
       <c r="AA180" s="12"/>
@@ -10891,16 +10891,16 @@
       <c r="T181" s="12"/>
       <c r="U181" s="12"/>
       <c r="V181" s="12"/>
-      <c r="W181" s="7">
+      <c r="W181" s="6">
         <v>43.0</v>
       </c>
-      <c r="X181" s="7" t="s">
+      <c r="X181" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="Y181" s="7" t="s">
+      <c r="Y181" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="Z181" s="7">
+      <c r="Z181" s="6">
         <v>1577.0</v>
       </c>
       <c r="AA181" s="12"/>
@@ -10931,16 +10931,16 @@
       <c r="T182" s="12"/>
       <c r="U182" s="12"/>
       <c r="V182" s="12"/>
-      <c r="W182" s="7">
+      <c r="W182" s="6">
         <v>44.0</v>
       </c>
-      <c r="X182" s="7" t="s">
+      <c r="X182" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="Y182" s="7" t="s">
+      <c r="Y182" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="Z182" s="7">
+      <c r="Z182" s="6">
         <v>1565.0</v>
       </c>
       <c r="AA182" s="12"/>
@@ -10971,16 +10971,16 @@
       <c r="T183" s="12"/>
       <c r="U183" s="12"/>
       <c r="V183" s="12"/>
-      <c r="W183" s="7">
+      <c r="W183" s="6">
         <v>45.0</v>
       </c>
-      <c r="X183" s="7" t="s">
+      <c r="X183" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="Y183" s="7" t="s">
+      <c r="Y183" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="Z183" s="7">
+      <c r="Z183" s="6">
         <v>1552.0</v>
       </c>
       <c r="AA183" s="12"/>
@@ -11011,16 +11011,16 @@
       <c r="T184" s="12"/>
       <c r="U184" s="12"/>
       <c r="V184" s="12"/>
-      <c r="W184" s="7">
+      <c r="W184" s="6">
         <v>46.0</v>
       </c>
-      <c r="X184" s="7" t="s">
+      <c r="X184" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="Y184" s="7" t="s">
+      <c r="Y184" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z184" s="7">
+      <c r="Z184" s="6">
         <v>1404.0</v>
       </c>
       <c r="AA184" s="12"/>
@@ -11051,16 +11051,16 @@
       <c r="T185" s="12"/>
       <c r="U185" s="12"/>
       <c r="V185" s="12"/>
-      <c r="W185" s="7">
+      <c r="W185" s="6">
         <v>47.0</v>
       </c>
-      <c r="X185" s="7" t="s">
+      <c r="X185" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="Y185" s="7" t="s">
+      <c r="Y185" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z185" s="7">
+      <c r="Z185" s="6">
         <v>1351.0</v>
       </c>
       <c r="AA185" s="12"/>
@@ -11091,16 +11091,16 @@
       <c r="T186" s="12"/>
       <c r="U186" s="12"/>
       <c r="V186" s="12"/>
-      <c r="W186" s="7">
+      <c r="W186" s="6">
         <v>48.0</v>
       </c>
-      <c r="X186" s="7" t="s">
+      <c r="X186" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="Y186" s="7" t="s">
+      <c r="Y186" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z186" s="7">
+      <c r="Z186" s="6">
         <v>1344.0</v>
       </c>
       <c r="AA186" s="12"/>
@@ -11131,16 +11131,16 @@
       <c r="T187" s="12"/>
       <c r="U187" s="12"/>
       <c r="V187" s="12"/>
-      <c r="W187" s="7">
+      <c r="W187" s="6">
         <v>49.0</v>
       </c>
-      <c r="X187" s="7" t="s">
+      <c r="X187" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="Y187" s="7" t="s">
+      <c r="Y187" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="Z187" s="7">
+      <c r="Z187" s="6">
         <v>1299.0</v>
       </c>
       <c r="AA187" s="12"/>
@@ -11171,16 +11171,16 @@
       <c r="T188" s="12"/>
       <c r="U188" s="12"/>
       <c r="V188" s="12"/>
-      <c r="W188" s="7">
+      <c r="W188" s="6">
         <v>50.0</v>
       </c>
-      <c r="X188" s="7" t="s">
+      <c r="X188" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="Y188" s="7" t="s">
+      <c r="Y188" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="Z188" s="7">
+      <c r="Z188" s="6">
         <v>1261.0</v>
       </c>
       <c r="AA188" s="12"/>
@@ -11211,16 +11211,16 @@
       <c r="T189" s="12"/>
       <c r="U189" s="12"/>
       <c r="V189" s="12"/>
-      <c r="W189" s="7">
+      <c r="W189" s="6">
         <v>51.0</v>
       </c>
-      <c r="X189" s="7" t="s">
+      <c r="X189" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="Y189" s="7" t="s">
+      <c r="Y189" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="Z189" s="7">
+      <c r="Z189" s="6">
         <v>1247.0</v>
       </c>
       <c r="AA189" s="12"/>
@@ -11251,16 +11251,16 @@
       <c r="T190" s="12"/>
       <c r="U190" s="12"/>
       <c r="V190" s="12"/>
-      <c r="W190" s="7">
+      <c r="W190" s="6">
         <v>52.0</v>
       </c>
-      <c r="X190" s="7" t="s">
+      <c r="X190" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="Y190" s="7" t="s">
+      <c r="Y190" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="Z190" s="7">
+      <c r="Z190" s="6">
         <v>1226.0</v>
       </c>
       <c r="AA190" s="12"/>
@@ -11291,16 +11291,16 @@
       <c r="T191" s="12"/>
       <c r="U191" s="12"/>
       <c r="V191" s="12"/>
-      <c r="W191" s="7">
+      <c r="W191" s="6">
         <v>53.0</v>
       </c>
-      <c r="X191" s="7" t="s">
+      <c r="X191" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="Y191" s="7" t="s">
+      <c r="Y191" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="Z191" s="7">
+      <c r="Z191" s="6">
         <v>1211.0</v>
       </c>
       <c r="AA191" s="12"/>
@@ -11331,16 +11331,16 @@
       <c r="T192" s="12"/>
       <c r="U192" s="12"/>
       <c r="V192" s="12"/>
-      <c r="W192" s="7">
+      <c r="W192" s="6">
         <v>54.0</v>
       </c>
-      <c r="X192" s="7" t="s">
+      <c r="X192" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="Y192" s="7" t="s">
+      <c r="Y192" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z192" s="7">
+      <c r="Z192" s="6">
         <v>1197.0</v>
       </c>
       <c r="AA192" s="12"/>
@@ -11371,16 +11371,16 @@
       <c r="T193" s="12"/>
       <c r="U193" s="12"/>
       <c r="V193" s="12"/>
-      <c r="W193" s="7">
+      <c r="W193" s="6">
         <v>55.0</v>
       </c>
-      <c r="X193" s="7" t="s">
+      <c r="X193" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="Y193" s="7" t="s">
+      <c r="Y193" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z193" s="7">
+      <c r="Z193" s="6">
         <v>1184.0</v>
       </c>
       <c r="AA193" s="12"/>
@@ -11411,16 +11411,16 @@
       <c r="T194" s="12"/>
       <c r="U194" s="12"/>
       <c r="V194" s="12"/>
-      <c r="W194" s="7">
+      <c r="W194" s="6">
         <v>56.0</v>
       </c>
-      <c r="X194" s="7" t="s">
+      <c r="X194" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Y194" s="7" t="s">
+      <c r="Y194" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="Z194" s="7">
+      <c r="Z194" s="6">
         <v>1157.0</v>
       </c>
       <c r="AA194" s="12"/>
@@ -11451,16 +11451,16 @@
       <c r="T195" s="12"/>
       <c r="U195" s="12"/>
       <c r="V195" s="12"/>
-      <c r="W195" s="7">
+      <c r="W195" s="6">
         <v>57.0</v>
       </c>
-      <c r="X195" s="7" t="s">
+      <c r="X195" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="Y195" s="7" t="s">
+      <c r="Y195" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z195" s="7">
+      <c r="Z195" s="6">
         <v>1143.0</v>
       </c>
       <c r="AA195" s="12"/>
@@ -11491,16 +11491,16 @@
       <c r="T196" s="12"/>
       <c r="U196" s="12"/>
       <c r="V196" s="12"/>
-      <c r="W196" s="7">
+      <c r="W196" s="6">
         <v>58.0</v>
       </c>
-      <c r="X196" s="7" t="s">
+      <c r="X196" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="Y196" s="7" t="s">
+      <c r="Y196" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z196" s="7">
+      <c r="Z196" s="6">
         <v>1078.0</v>
       </c>
       <c r="AA196" s="12"/>
@@ -11531,16 +11531,16 @@
       <c r="T197" s="12"/>
       <c r="U197" s="12"/>
       <c r="V197" s="12"/>
-      <c r="W197" s="7">
+      <c r="W197" s="6">
         <v>59.0</v>
       </c>
-      <c r="X197" s="7" t="s">
+      <c r="X197" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="Y197" s="7" t="s">
+      <c r="Y197" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z197" s="7">
+      <c r="Z197" s="6">
         <v>1069.0</v>
       </c>
       <c r="AA197" s="12"/>
@@ -11571,16 +11571,16 @@
       <c r="T198" s="12"/>
       <c r="U198" s="12"/>
       <c r="V198" s="12"/>
-      <c r="W198" s="7">
+      <c r="W198" s="6">
         <v>60.0</v>
       </c>
-      <c r="X198" s="7" t="s">
+      <c r="X198" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="Y198" s="7" t="s">
+      <c r="Y198" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="Z198" s="7">
+      <c r="Z198" s="6">
         <v>1000.0</v>
       </c>
       <c r="AA198" s="12"/>
@@ -11611,16 +11611,16 @@
       <c r="T199" s="12"/>
       <c r="U199" s="12"/>
       <c r="V199" s="12"/>
-      <c r="W199" s="7">
+      <c r="W199" s="6">
         <v>61.0</v>
       </c>
-      <c r="X199" s="7" t="s">
+      <c r="X199" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="Y199" s="7" t="s">
+      <c r="Y199" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="Z199" s="7">
+      <c r="Z199" s="6">
         <v>987.0</v>
       </c>
       <c r="AA199" s="12"/>
@@ -11651,16 +11651,16 @@
       <c r="T200" s="12"/>
       <c r="U200" s="12"/>
       <c r="V200" s="12"/>
-      <c r="W200" s="7">
+      <c r="W200" s="6">
         <v>62.0</v>
       </c>
-      <c r="X200" s="7" t="s">
+      <c r="X200" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="Y200" s="7" t="s">
+      <c r="Y200" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="Z200" s="7">
+      <c r="Z200" s="6">
         <v>952.0</v>
       </c>
       <c r="AA200" s="12"/>
@@ -11691,16 +11691,16 @@
       <c r="T201" s="12"/>
       <c r="U201" s="12"/>
       <c r="V201" s="12"/>
-      <c r="W201" s="7">
+      <c r="W201" s="6">
         <v>63.0</v>
       </c>
-      <c r="X201" s="7" t="s">
+      <c r="X201" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="Y201" s="7" t="s">
+      <c r="Y201" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="Z201" s="7">
+      <c r="Z201" s="6">
         <v>913.0</v>
       </c>
       <c r="AA201" s="12"/>
@@ -11731,16 +11731,16 @@
       <c r="T202" s="12"/>
       <c r="U202" s="12"/>
       <c r="V202" s="12"/>
-      <c r="W202" s="7">
+      <c r="W202" s="6">
         <v>64.0</v>
       </c>
-      <c r="X202" s="7" t="s">
+      <c r="X202" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="Y202" s="7" t="s">
+      <c r="Y202" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="Z202" s="7">
+      <c r="Z202" s="6">
         <v>905.0</v>
       </c>
       <c r="AA202" s="12"/>
@@ -11771,16 +11771,16 @@
       <c r="T203" s="12"/>
       <c r="U203" s="12"/>
       <c r="V203" s="12"/>
-      <c r="W203" s="7">
+      <c r="W203" s="6">
         <v>65.0</v>
       </c>
-      <c r="X203" s="7" t="s">
+      <c r="X203" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="Y203" s="7" t="s">
+      <c r="Y203" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="Z203" s="7">
+      <c r="Z203" s="6">
         <v>842.0</v>
       </c>
       <c r="AA203" s="12"/>
@@ -11811,16 +11811,16 @@
       <c r="T204" s="12"/>
       <c r="U204" s="12"/>
       <c r="V204" s="12"/>
-      <c r="W204" s="7">
+      <c r="W204" s="6">
         <v>66.0</v>
       </c>
-      <c r="X204" s="7" t="s">
+      <c r="X204" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y204" s="7" t="s">
+      <c r="Y204" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="Z204" s="7">
+      <c r="Z204" s="6">
         <v>823.0</v>
       </c>
       <c r="AA204" s="12"/>
@@ -11851,16 +11851,16 @@
       <c r="T205" s="12"/>
       <c r="U205" s="12"/>
       <c r="V205" s="12"/>
-      <c r="W205" s="7">
+      <c r="W205" s="6">
         <v>67.0</v>
       </c>
-      <c r="X205" s="7" t="s">
+      <c r="X205" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="Y205" s="7" t="s">
+      <c r="Y205" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z205" s="7">
+      <c r="Z205" s="6">
         <v>820.0</v>
       </c>
       <c r="AA205" s="12"/>
@@ -11891,16 +11891,16 @@
       <c r="T206" s="12"/>
       <c r="U206" s="12"/>
       <c r="V206" s="12"/>
-      <c r="W206" s="7">
+      <c r="W206" s="6">
         <v>68.0</v>
       </c>
-      <c r="X206" s="7" t="s">
+      <c r="X206" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="Y206" s="7" t="s">
+      <c r="Y206" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="Z206" s="7">
+      <c r="Z206" s="6">
         <v>805.0</v>
       </c>
       <c r="AA206" s="12"/>
@@ -11931,16 +11931,16 @@
       <c r="T207" s="12"/>
       <c r="U207" s="12"/>
       <c r="V207" s="12"/>
-      <c r="W207" s="7">
+      <c r="W207" s="6">
         <v>69.0</v>
       </c>
-      <c r="X207" s="7" t="s">
+      <c r="X207" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="Y207" s="7" t="s">
+      <c r="Y207" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="Z207" s="7">
+      <c r="Z207" s="6">
         <v>782.0</v>
       </c>
       <c r="AA207" s="12"/>
@@ -11971,16 +11971,16 @@
       <c r="T208" s="12"/>
       <c r="U208" s="12"/>
       <c r="V208" s="12"/>
-      <c r="W208" s="7">
+      <c r="W208" s="6">
         <v>70.0</v>
       </c>
-      <c r="X208" s="7" t="s">
+      <c r="X208" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="Y208" s="7" t="s">
+      <c r="Y208" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z208" s="7">
+      <c r="Z208" s="6">
         <v>736.0</v>
       </c>
       <c r="AA208" s="12"/>
@@ -12011,16 +12011,16 @@
       <c r="T209" s="12"/>
       <c r="U209" s="12"/>
       <c r="V209" s="12"/>
-      <c r="W209" s="7">
+      <c r="W209" s="6">
         <v>71.0</v>
       </c>
-      <c r="X209" s="7" t="s">
+      <c r="X209" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="Y209" s="7" t="s">
+      <c r="Y209" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z209" s="7">
+      <c r="Z209" s="6">
         <v>733.0</v>
       </c>
       <c r="AA209" s="12"/>
@@ -12051,16 +12051,16 @@
       <c r="T210" s="12"/>
       <c r="U210" s="12"/>
       <c r="V210" s="12"/>
-      <c r="W210" s="7">
+      <c r="W210" s="6">
         <v>72.0</v>
       </c>
-      <c r="X210" s="7" t="s">
+      <c r="X210" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="Y210" s="7" t="s">
+      <c r="Y210" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z210" s="7">
+      <c r="Z210" s="6">
         <v>700.0</v>
       </c>
       <c r="AA210" s="12"/>
@@ -12091,16 +12091,16 @@
       <c r="T211" s="12"/>
       <c r="U211" s="12"/>
       <c r="V211" s="12"/>
-      <c r="W211" s="7">
+      <c r="W211" s="6">
         <v>73.0</v>
       </c>
-      <c r="X211" s="7" t="s">
+      <c r="X211" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="Y211" s="7" t="s">
+      <c r="Y211" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z211" s="7">
+      <c r="Z211" s="6">
         <v>649.0</v>
       </c>
       <c r="AA211" s="12"/>
@@ -12131,16 +12131,16 @@
       <c r="T212" s="12"/>
       <c r="U212" s="12"/>
       <c r="V212" s="12"/>
-      <c r="W212" s="7">
+      <c r="W212" s="6">
         <v>74.0</v>
       </c>
-      <c r="X212" s="7" t="s">
+      <c r="X212" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Y212" s="7" t="s">
+      <c r="Y212" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="Z212" s="7">
+      <c r="Z212" s="6">
         <v>636.0</v>
       </c>
       <c r="AA212" s="12"/>
@@ -12171,16 +12171,16 @@
       <c r="T213" s="12"/>
       <c r="U213" s="12"/>
       <c r="V213" s="12"/>
-      <c r="W213" s="7">
+      <c r="W213" s="6">
         <v>75.0</v>
       </c>
-      <c r="X213" s="7" t="s">
+      <c r="X213" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="Y213" s="7" t="s">
+      <c r="Y213" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z213" s="7">
+      <c r="Z213" s="6">
         <v>528.0</v>
       </c>
       <c r="AA213" s="12"/>
@@ -12211,16 +12211,16 @@
       <c r="T214" s="12"/>
       <c r="U214" s="12"/>
       <c r="V214" s="12"/>
-      <c r="W214" s="7">
+      <c r="W214" s="6">
         <v>76.0</v>
       </c>
-      <c r="X214" s="7" t="s">
+      <c r="X214" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="Y214" s="7" t="s">
+      <c r="Y214" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="Z214" s="7">
+      <c r="Z214" s="6">
         <v>473.0</v>
       </c>
       <c r="AA214" s="12"/>
@@ -12251,16 +12251,16 @@
       <c r="T215" s="12"/>
       <c r="U215" s="12"/>
       <c r="V215" s="12"/>
-      <c r="W215" s="7">
+      <c r="W215" s="6">
         <v>78.0</v>
       </c>
-      <c r="X215" s="7" t="s">
+      <c r="X215" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="Y215" s="7" t="s">
+      <c r="Y215" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Z215" s="7">
+      <c r="Z215" s="6">
         <v>435.0</v>
       </c>
       <c r="AA215" s="12"/>
@@ -12291,13 +12291,13 @@
       <c r="T216" s="12"/>
       <c r="U216" s="12"/>
       <c r="V216" s="12"/>
-      <c r="W216" s="7">
+      <c r="W216" s="6">
         <v>79.0</v>
       </c>
-      <c r="X216" s="7" t="s">
+      <c r="X216" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="Y216" s="7" t="s">
+      <c r="Y216" s="6" t="s">
         <v>140</v>
       </c>
       <c r="Z216" s="12"/>
@@ -12329,13 +12329,13 @@
       <c r="T217" s="12"/>
       <c r="U217" s="12"/>
       <c r="V217" s="12"/>
-      <c r="W217" s="7">
+      <c r="W217" s="6">
         <v>80.0</v>
       </c>
-      <c r="X217" s="7" t="s">
+      <c r="X217" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="Y217" s="7" t="s">
+      <c r="Y217" s="6" t="s">
         <v>140</v>
       </c>
       <c r="Z217" s="12"/>
@@ -37444,7 +37444,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -37458,28 +37458,28 @@
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
         <v>1.0</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>15</v>
+      <c r="B2" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="C2" s="8">
         <v>139.0</v>
@@ -37533,7 +37533,7 @@
       <c r="A3" s="1">
         <v>2.0</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="8">
@@ -37575,7 +37575,7 @@
       <c r="A4" s="1">
         <v>3.0</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="8">
@@ -37604,7 +37604,7 @@
       <c r="K4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="3">
         <f>'Draft Data'!U63</f>
         <v>180</v>
       </c>
@@ -37613,7 +37613,7 @@
       <c r="A5" s="1">
         <v>4.0</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C5" s="8">
@@ -37651,7 +37651,7 @@
       <c r="A6" s="1">
         <v>5.0</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="8">
@@ -37689,7 +37689,7 @@
       <c r="A7" s="1">
         <v>6.0</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C7" s="8">
@@ -37715,7 +37715,7 @@
         <v/>
       </c>
       <c r="K7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L7" s="17">
         <f>SUMIF($E$2:$E$500,TRUE,$D$2:$D$500)</f>
@@ -37726,8 +37726,8 @@
       <c r="A8" s="1">
         <v>7.0</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>33</v>
+      <c r="B8" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="C8" s="8">
         <v>57.5</v>
@@ -37752,7 +37752,7 @@
         <v/>
       </c>
       <c r="K8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L8" s="8">
         <f>L4-L7
@@ -37764,8 +37764,8 @@
       <c r="A9" s="1">
         <v>8.0</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>35</v>
+      <c r="B9" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="C9" s="8">
         <v>53.0</v>
@@ -37802,7 +37802,7 @@
       <c r="A10" s="1">
         <v>9.0</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C10" s="8">
@@ -37839,7 +37839,7 @@
       <c r="A11" s="1">
         <v>10.0</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="8">
@@ -37876,7 +37876,7 @@
       <c r="A12" s="1">
         <v>11.0</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="8">
@@ -37906,8 +37906,8 @@
       <c r="A13" s="1">
         <v>12.0</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>43</v>
+      <c r="B13" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="C13" s="8">
         <v>34.0</v>
@@ -37932,7 +37932,7 @@
         <v/>
       </c>
       <c r="K13" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L13" s="17">
         <f>SUMIF($D$2:$D$73,"",$C$2:$C$73)</f>
@@ -37943,8 +37943,8 @@
       <c r="A14" s="1">
         <v>13.0</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>45</v>
+      <c r="B14" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="C14" s="8">
         <v>30.5</v>
@@ -37969,7 +37969,7 @@
         <v/>
       </c>
       <c r="K14" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L14" s="19">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -37980,8 +37980,8 @@
       <c r="A15" s="1">
         <v>14.0</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>47</v>
+      <c r="B15" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="C15" s="8">
         <v>27.5</v>
@@ -38010,8 +38010,8 @@
       <c r="A16" s="1">
         <v>15.0</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>48</v>
+      <c r="B16" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C16" s="8">
         <v>25.5</v>
@@ -38036,7 +38036,7 @@
         <v/>
       </c>
       <c r="K16" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L16" s="1">
         <f>IF($L$18&lt;0.3,
@@ -38057,8 +38057,8 @@
       <c r="A17" s="1">
         <v>16.0</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>52</v>
+      <c r="B17" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="C17" s="8">
         <v>22.5</v>
@@ -38087,8 +38087,8 @@
       <c r="A18" s="1">
         <v>17.0</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>53</v>
+      <c r="B18" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="C18" s="8">
         <v>20.0</v>
@@ -38113,7 +38113,7 @@
         <v/>
       </c>
       <c r="K18" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L18" s="20">
         <f>L5/L2</f>
@@ -38124,7 +38124,7 @@
       <c r="A19" s="1">
         <v>18.0</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>55</v>
       </c>
       <c r="C19" s="8">
@@ -38154,7 +38154,7 @@
       <c r="A20" s="1">
         <v>19.0</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>56</v>
       </c>
       <c r="C20" s="8">
@@ -38184,8 +38184,8 @@
       <c r="A21" s="1">
         <v>20.0</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>58</v>
+      <c r="B21" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="C21" s="8">
         <v>14.5</v>
@@ -38214,8 +38214,8 @@
       <c r="A22" s="1">
         <v>21.0</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>59</v>
+      <c r="B22" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="C22" s="8">
         <v>13.5</v>
@@ -38244,8 +38244,8 @@
       <c r="A23" s="1">
         <v>22.0</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>60</v>
+      <c r="B23" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="C23" s="8">
         <v>12.0</v>
@@ -38274,8 +38274,8 @@
       <c r="A24" s="1">
         <v>23.0</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>61</v>
+      <c r="B24" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="C24" s="8">
         <v>11.0</v>
@@ -38304,8 +38304,8 @@
       <c r="A25" s="1">
         <v>24.0</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>63</v>
+      <c r="B25" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="C25" s="8">
         <v>10.0</v>
@@ -38334,8 +38334,8 @@
       <c r="A26" s="1">
         <v>25.0</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>64</v>
+      <c r="B26" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="C26" s="8">
         <v>9.5</v>
@@ -38364,8 +38364,8 @@
       <c r="A27" s="1">
         <v>26.0</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>65</v>
+      <c r="B27" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="C27" s="8">
         <v>8.5</v>
@@ -38390,7 +38390,7 @@
         <v/>
       </c>
       <c r="K27" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L27" s="1">
         <v>0.8</v>
@@ -38400,8 +38400,8 @@
       <c r="A28" s="1">
         <v>27.0</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>67</v>
+      <c r="B28" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="C28" s="8">
         <v>8.0</v>
@@ -38430,8 +38430,8 @@
       <c r="A29" s="1">
         <v>28.0</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>68</v>
+      <c r="B29" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="C29" s="8">
         <v>7.0</v>
@@ -38460,8 +38460,8 @@
       <c r="A30" s="1">
         <v>29.0</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>69</v>
+      <c r="B30" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="C30" s="8">
         <v>6.5</v>
@@ -38490,7 +38490,7 @@
       <c r="A31" s="1">
         <v>30.0</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C31" s="8">
@@ -38520,7 +38520,7 @@
       <c r="A32" s="1">
         <v>31.0</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C32" s="8">
@@ -38550,7 +38550,7 @@
       <c r="A33" s="1">
         <v>32.0</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="6" t="s">
         <v>72</v>
       </c>
       <c r="C33" s="8">
@@ -38580,7 +38580,7 @@
       <c r="A34" s="1">
         <v>33.0</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C34" s="8">
@@ -38610,7 +38610,7 @@
       <c r="A35" s="1">
         <v>34.0</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="6" t="s">
         <v>74</v>
       </c>
       <c r="C35" s="8">
@@ -38640,7 +38640,7 @@
       <c r="A36" s="1">
         <v>35.0</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="6" t="s">
         <v>75</v>
       </c>
       <c r="C36" s="8">
@@ -38670,7 +38670,7 @@
       <c r="A37" s="1">
         <v>36.0</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="6" t="s">
         <v>76</v>
       </c>
       <c r="C37" s="8">
@@ -38700,7 +38700,7 @@
       <c r="A38" s="1">
         <v>37.0</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="6" t="s">
         <v>77</v>
       </c>
       <c r="C38" s="8">
@@ -38730,7 +38730,7 @@
       <c r="A39" s="1">
         <v>38.0</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="6" t="s">
         <v>78</v>
       </c>
       <c r="C39" s="8">
@@ -38760,7 +38760,7 @@
       <c r="A40" s="1">
         <v>39.0</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="6" t="s">
         <v>79</v>
       </c>
       <c r="C40" s="8">
@@ -38790,7 +38790,7 @@
       <c r="A41" s="1">
         <v>40.0</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="6" t="s">
         <v>80</v>
       </c>
       <c r="C41" s="8">
@@ -38820,7 +38820,7 @@
       <c r="A42" s="1">
         <v>41.0</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="6" t="s">
         <v>81</v>
       </c>
       <c r="C42" s="8">
@@ -38850,7 +38850,7 @@
       <c r="A43" s="1">
         <v>42.0</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="6" t="s">
         <v>82</v>
       </c>
       <c r="C43" s="8">
@@ -38880,7 +38880,7 @@
       <c r="A44" s="1">
         <v>43.0</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C44" s="8">
@@ -38910,7 +38910,7 @@
       <c r="A45" s="1">
         <v>44.0</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="6" t="s">
         <v>84</v>
       </c>
       <c r="C45" s="8">
@@ -38940,7 +38940,7 @@
       <c r="A46" s="1">
         <v>45.0</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="6" t="s">
         <v>85</v>
       </c>
       <c r="C46" s="8">
@@ -38970,7 +38970,7 @@
       <c r="A47" s="1">
         <v>46.0</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="6" t="s">
         <v>86</v>
       </c>
       <c r="C47" s="8">
@@ -39000,7 +39000,7 @@
       <c r="A48" s="1">
         <v>47.0</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="6" t="s">
         <v>87</v>
       </c>
       <c r="C48" s="8">
@@ -39030,7 +39030,7 @@
       <c r="A49" s="1">
         <v>48.0</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="6" t="s">
         <v>88</v>
       </c>
       <c r="C49" s="8">
@@ -39060,7 +39060,7 @@
       <c r="A50" s="1">
         <v>49.0</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="6" t="s">
         <v>89</v>
       </c>
       <c r="C50" s="8">
@@ -39090,7 +39090,7 @@
       <c r="A51" s="1">
         <v>50.0</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="6" t="s">
         <v>90</v>
       </c>
       <c r="C51" s="8">
@@ -39120,7 +39120,7 @@
       <c r="A52" s="1">
         <v>51.0</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="6" t="s">
         <v>91</v>
       </c>
       <c r="C52" s="8">
@@ -39150,7 +39150,7 @@
       <c r="A53" s="1">
         <v>52.0</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C53" s="8">
@@ -39180,7 +39180,7 @@
       <c r="A54" s="1">
         <v>53.0</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="6" t="s">
         <v>93</v>
       </c>
       <c r="C54" s="8">
@@ -39210,7 +39210,7 @@
       <c r="A55" s="1">
         <v>54.0</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="6" t="s">
         <v>94</v>
       </c>
       <c r="C55" s="8">
@@ -39240,7 +39240,7 @@
       <c r="A56" s="1">
         <v>55.0</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="6" t="s">
         <v>95</v>
       </c>
       <c r="C56" s="8">
@@ -39270,7 +39270,7 @@
       <c r="A57" s="1">
         <v>56.0</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="6" t="s">
         <v>96</v>
       </c>
       <c r="C57" s="8">
@@ -39300,7 +39300,7 @@
       <c r="A58" s="1">
         <v>57.0</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="6" t="s">
         <v>97</v>
       </c>
       <c r="C58" s="8">
@@ -39330,7 +39330,7 @@
       <c r="A59" s="1">
         <v>58.0</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="6" t="s">
         <v>98</v>
       </c>
       <c r="C59" s="8">
@@ -39360,7 +39360,7 @@
       <c r="A60" s="1">
         <v>59.0</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="6" t="s">
         <v>99</v>
       </c>
       <c r="C60" s="8">
@@ -39390,7 +39390,7 @@
       <c r="A61" s="1">
         <v>60.0</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="6" t="s">
         <v>100</v>
       </c>
       <c r="C61" s="8">
@@ -39420,7 +39420,7 @@
       <c r="A62" s="1">
         <v>61.0</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B62" s="6" t="s">
         <v>101</v>
       </c>
       <c r="C62" s="8">
@@ -39450,7 +39450,7 @@
       <c r="A63" s="1">
         <v>62.0</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="6" t="s">
         <v>102</v>
       </c>
       <c r="C63" s="8">
@@ -39480,7 +39480,7 @@
       <c r="A64" s="1">
         <v>63.0</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="6" t="s">
         <v>103</v>
       </c>
       <c r="C64" s="8">
@@ -39510,7 +39510,7 @@
       <c r="A65" s="1">
         <v>64.0</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="B65" s="6" t="s">
         <v>104</v>
       </c>
       <c r="C65" s="8">
@@ -39540,7 +39540,7 @@
       <c r="A66" s="1">
         <v>65.0</v>
       </c>
-      <c r="B66" s="7" t="s">
+      <c r="B66" s="6" t="s">
         <v>105</v>
       </c>
       <c r="C66" s="8">
@@ -39570,7 +39570,7 @@
       <c r="A67" s="1">
         <v>66.0</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="6" t="s">
         <v>106</v>
       </c>
       <c r="C67" s="8">
@@ -39600,7 +39600,7 @@
       <c r="A68" s="1">
         <v>67.0</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="B68" s="6" t="s">
         <v>107</v>
       </c>
       <c r="C68" s="8">
@@ -39630,7 +39630,7 @@
       <c r="A69" s="1">
         <v>68.0</v>
       </c>
-      <c r="B69" s="7" t="s">
+      <c r="B69" s="6" t="s">
         <v>108</v>
       </c>
       <c r="C69" s="8">
@@ -39660,7 +39660,7 @@
       <c r="A70" s="1">
         <v>69.0</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="B70" s="6" t="s">
         <v>109</v>
       </c>
       <c r="C70" s="8">
@@ -39690,7 +39690,7 @@
       <c r="A71" s="1">
         <v>70.0</v>
       </c>
-      <c r="B71" s="7" t="s">
+      <c r="B71" s="6" t="s">
         <v>110</v>
       </c>
       <c r="C71" s="8">
@@ -39720,7 +39720,7 @@
       <c r="A72" s="1">
         <v>71.0</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="B72" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C72" s="8">

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -14,13 +14,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="178">
   <si>
-    <t>PICK</t>
-  </si>
-  <si>
     <t>Rank</t>
   </si>
   <si>
-    <t>VALUE</t>
+    <t>PICK</t>
   </si>
   <si>
     <t>PLAYER NAME</t>
@@ -29,7 +26,7 @@
     <t>PreDraft$</t>
   </si>
   <si>
-    <t>Decay</t>
+    <t>VALUE</t>
   </si>
   <si>
     <t>Final Price</t>
@@ -38,10 +35,13 @@
     <t>Mine?</t>
   </si>
   <si>
-    <t>New Values</t>
+    <t>Decay</t>
   </si>
   <si>
     <t>Inflated Fair Price</t>
+  </si>
+  <si>
+    <t>New Values</t>
   </si>
   <si>
     <t>Spine</t>
@@ -107,10 +107,10 @@
     <t>Kenyon Sadiq</t>
   </si>
   <si>
-    <t>My Spent</t>
+    <t>Round 1</t>
   </si>
   <si>
-    <t>Round 1</t>
+    <t>My Spent</t>
   </si>
   <si>
     <t>Sonny Styles</t>
@@ -161,19 +161,19 @@
     <t>Denzel Boston</t>
   </si>
   <si>
-    <t>Aggression</t>
+    <t>Round 3</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>Aggression</t>
   </si>
   <si>
     <t>Caleb Downs</t>
   </si>
   <si>
-    <t>Round 4</t>
+    <t>David Bailey</t>
   </si>
   <si>
-    <t>David Bailey</t>
+    <t>Round 4</t>
   </si>
   <si>
     <t>League Spent %</t>
@@ -191,10 +191,10 @@
     <t>Dillon Thieneman</t>
   </si>
   <si>
-    <t>Round 5</t>
+    <t>Rueben Bain</t>
   </si>
   <si>
-    <t>Rueben Bain</t>
+    <t>Round 5</t>
   </si>
   <si>
     <t>Chris Bell</t>
@@ -209,13 +209,13 @@
     <t>Mike Washington</t>
   </si>
   <si>
-    <t>Round 6</t>
-  </si>
-  <si>
     <t>Enforce % of Fair</t>
   </si>
   <si>
     <t>Antonio Williams</t>
+  </si>
+  <si>
+    <t>Round 6</t>
   </si>
   <si>
     <t>Elijah Sarratt</t>
@@ -566,11 +566,11 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF1B1C1D"/>
@@ -611,66 +611,66 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -913,17 +913,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -9212,7 +9212,7 @@
       <c r="U139" s="12"/>
       <c r="V139" s="12"/>
       <c r="W139" s="9" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X139" s="9" t="s">
         <v>138</v>
@@ -9655,7 +9655,7 @@
         <v>12.0</v>
       </c>
       <c r="X150" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Y150" s="9" t="s">
         <v>146</v>
@@ -10815,7 +10815,7 @@
         <v>41.0</v>
       </c>
       <c r="X179" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Y179" s="9" t="s">
         <v>141</v>
@@ -37443,23 +37443,23 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="F1" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>11</v>
@@ -37467,15 +37467,15 @@
       <c r="H1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>1.0</v>
       </c>
       <c r="B2" s="9" t="s">
@@ -37484,8 +37484,8 @@
       <c r="C2" s="10">
         <v>139.0</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="b">
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F2" s="10">
@@ -37522,15 +37522,15 @@
 </f>
         <v/>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="1">
         <v>1200.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>2.0</v>
       </c>
       <c r="B3" s="9" t="s">
@@ -37539,8 +37539,8 @@
       <c r="C3" s="10">
         <v>106.5</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="b">
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F3" s="10">
@@ -37564,15 +37564,15 @@
 </f>
         <v/>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="1">
         <v>12.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>3.0</v>
       </c>
       <c r="B4" s="9" t="s">
@@ -37581,8 +37581,8 @@
       <c r="C4" s="10">
         <v>93.0</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="b">
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F4" s="10">
@@ -37601,7 +37601,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>25</v>
       </c>
       <c r="L4" s="5">
@@ -37610,7 +37610,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>4.0</v>
       </c>
       <c r="B5" s="9" t="s">
@@ -37638,7 +37638,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L5" s="17">
@@ -37648,7 +37648,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>5.0</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -37676,7 +37676,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="1" t="s">
         <v>29</v>
       </c>
       <c r="L6" s="17">
@@ -37686,7 +37686,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>6.0</v>
       </c>
       <c r="B7" s="9" t="s">
@@ -37714,8 +37714,8 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>31</v>
+      <c r="K7" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="L7" s="17">
         <f>SUMIF($E$2:$E$500,TRUE,$D$2:$D$500)</f>
@@ -37723,7 +37723,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>7.0</v>
       </c>
       <c r="B8" s="9" t="s">
@@ -37751,7 +37751,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="1" t="s">
         <v>34</v>
       </c>
       <c r="L8" s="10">
@@ -37761,7 +37761,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>8.0</v>
       </c>
       <c r="B9" s="9" t="s">
@@ -37789,7 +37789,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L9" s="10">
@@ -37799,7 +37799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>9.0</v>
       </c>
       <c r="B10" s="9" t="s">
@@ -37827,7 +37827,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" s="1" t="s">
         <v>38</v>
       </c>
       <c r="L10" s="10">
@@ -37836,7 +37836,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>10.0</v>
       </c>
       <c r="B11" s="9" t="s">
@@ -37864,7 +37864,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" s="1" t="s">
         <v>40</v>
       </c>
       <c r="L11" s="19">
@@ -37873,7 +37873,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>11.0</v>
       </c>
       <c r="B12" s="9" t="s">
@@ -37903,7 +37903,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>12.0</v>
       </c>
       <c r="B13" s="9" t="s">
@@ -37931,7 +37931,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="K13" s="1" t="s">
         <v>44</v>
       </c>
       <c r="L13" s="17">
@@ -37940,7 +37940,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>13.0</v>
       </c>
       <c r="B14" s="9" t="s">
@@ -37968,7 +37968,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="K14" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L14" s="19">
@@ -37977,7 +37977,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>14.0</v>
       </c>
       <c r="B15" s="9" t="s">
@@ -38007,7 +38007,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2">
+      <c r="A16" s="1">
         <v>15.0</v>
       </c>
       <c r="B16" s="9" t="s">
@@ -38035,10 +38035,10 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L16" s="2">
+      <c r="K16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L16" s="1">
         <f>IF($L$18&lt;0.3,
      IF($L$11&gt;=1.3,0.09,
         IF($L$11&gt;=1.1,0.07,0.05)),
@@ -38054,7 +38054,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>16.0</v>
       </c>
       <c r="B17" s="9" t="s">
@@ -38084,11 +38084,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2">
+      <c r="A18" s="1">
         <v>17.0</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="10">
         <v>20.0</v>
@@ -38112,7 +38112,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="K18" s="1" t="s">
         <v>54</v>
       </c>
       <c r="L18" s="20">
@@ -38121,7 +38121,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2">
+      <c r="A19" s="1">
         <v>18.0</v>
       </c>
       <c r="B19" s="9" t="s">
@@ -38151,7 +38151,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2">
+      <c r="A20" s="1">
         <v>19.0</v>
       </c>
       <c r="B20" s="9" t="s">
@@ -38181,7 +38181,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2">
+      <c r="A21" s="1">
         <v>20.0</v>
       </c>
       <c r="B21" s="9" t="s">
@@ -38211,7 +38211,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2">
+      <c r="A22" s="1">
         <v>21.0</v>
       </c>
       <c r="B22" s="9" t="s">
@@ -38241,11 +38241,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2">
+      <c r="A23" s="1">
         <v>22.0</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C23" s="10">
         <v>12.0</v>
@@ -38271,7 +38271,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2">
+      <c r="A24" s="1">
         <v>23.0</v>
       </c>
       <c r="B24" s="9" t="s">
@@ -38301,7 +38301,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2">
+      <c r="A25" s="1">
         <v>24.0</v>
       </c>
       <c r="B25" s="9" t="s">
@@ -38331,7 +38331,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2">
+      <c r="A26" s="1">
         <v>25.0</v>
       </c>
       <c r="B26" s="9" t="s">
@@ -38361,7 +38361,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2">
+      <c r="A27" s="1">
         <v>26.0</v>
       </c>
       <c r="B27" s="9" t="s">
@@ -38389,19 +38389,19 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K27" s="2" t="s">
+      <c r="K27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1">
+        <v>27.0</v>
+      </c>
+      <c r="B28" s="9" t="s">
         <v>66</v>
-      </c>
-      <c r="L27" s="2">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2">
-        <v>27.0</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>67</v>
       </c>
       <c r="C28" s="10">
         <v>8.0</v>
@@ -38427,7 +38427,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2">
+      <c r="A29" s="1">
         <v>28.0</v>
       </c>
       <c r="B29" s="9" t="s">
@@ -38457,7 +38457,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2">
+      <c r="A30" s="1">
         <v>29.0</v>
       </c>
       <c r="B30" s="9" t="s">
@@ -38487,7 +38487,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2">
+      <c r="A31" s="1">
         <v>30.0</v>
       </c>
       <c r="B31" s="9" t="s">
@@ -38517,7 +38517,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2">
+      <c r="A32" s="1">
         <v>31.0</v>
       </c>
       <c r="B32" s="9" t="s">
@@ -38547,7 +38547,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2">
+      <c r="A33" s="1">
         <v>32.0</v>
       </c>
       <c r="B33" s="9" t="s">
@@ -38577,7 +38577,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2">
+      <c r="A34" s="1">
         <v>33.0</v>
       </c>
       <c r="B34" s="9" t="s">
@@ -38607,7 +38607,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2">
+      <c r="A35" s="1">
         <v>34.0</v>
       </c>
       <c r="B35" s="9" t="s">
@@ -38637,7 +38637,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2">
+      <c r="A36" s="1">
         <v>35.0</v>
       </c>
       <c r="B36" s="9" t="s">
@@ -38667,7 +38667,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2">
+      <c r="A37" s="1">
         <v>36.0</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -38697,7 +38697,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2">
+      <c r="A38" s="1">
         <v>37.0</v>
       </c>
       <c r="B38" s="9" t="s">
@@ -38727,7 +38727,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2">
+      <c r="A39" s="1">
         <v>38.0</v>
       </c>
       <c r="B39" s="9" t="s">
@@ -38757,7 +38757,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2">
+      <c r="A40" s="1">
         <v>39.0</v>
       </c>
       <c r="B40" s="9" t="s">
@@ -38787,7 +38787,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2">
+      <c r="A41" s="1">
         <v>40.0</v>
       </c>
       <c r="B41" s="9" t="s">
@@ -38817,7 +38817,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2">
+      <c r="A42" s="1">
         <v>41.0</v>
       </c>
       <c r="B42" s="9" t="s">
@@ -38847,7 +38847,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2">
+      <c r="A43" s="1">
         <v>42.0</v>
       </c>
       <c r="B43" s="9" t="s">
@@ -38877,7 +38877,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2">
+      <c r="A44" s="1">
         <v>43.0</v>
       </c>
       <c r="B44" s="9" t="s">
@@ -38907,7 +38907,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2">
+      <c r="A45" s="1">
         <v>44.0</v>
       </c>
       <c r="B45" s="9" t="s">
@@ -38937,7 +38937,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2">
+      <c r="A46" s="1">
         <v>45.0</v>
       </c>
       <c r="B46" s="9" t="s">
@@ -38967,7 +38967,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2">
+      <c r="A47" s="1">
         <v>46.0</v>
       </c>
       <c r="B47" s="9" t="s">
@@ -38997,7 +38997,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2">
+      <c r="A48" s="1">
         <v>47.0</v>
       </c>
       <c r="B48" s="9" t="s">
@@ -39027,7 +39027,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2">
+      <c r="A49" s="1">
         <v>48.0</v>
       </c>
       <c r="B49" s="9" t="s">
@@ -39057,7 +39057,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2">
+      <c r="A50" s="1">
         <v>49.0</v>
       </c>
       <c r="B50" s="9" t="s">
@@ -39087,7 +39087,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2">
+      <c r="A51" s="1">
         <v>50.0</v>
       </c>
       <c r="B51" s="9" t="s">
@@ -39117,7 +39117,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2">
+      <c r="A52" s="1">
         <v>51.0</v>
       </c>
       <c r="B52" s="9" t="s">
@@ -39147,7 +39147,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2">
+      <c r="A53" s="1">
         <v>52.0</v>
       </c>
       <c r="B53" s="9" t="s">
@@ -39177,7 +39177,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2">
+      <c r="A54" s="1">
         <v>53.0</v>
       </c>
       <c r="B54" s="9" t="s">
@@ -39207,7 +39207,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2">
+      <c r="A55" s="1">
         <v>54.0</v>
       </c>
       <c r="B55" s="9" t="s">
@@ -39237,7 +39237,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2">
+      <c r="A56" s="1">
         <v>55.0</v>
       </c>
       <c r="B56" s="9" t="s">
@@ -39267,7 +39267,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2">
+      <c r="A57" s="1">
         <v>56.0</v>
       </c>
       <c r="B57" s="9" t="s">
@@ -39297,7 +39297,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2">
+      <c r="A58" s="1">
         <v>57.0</v>
       </c>
       <c r="B58" s="9" t="s">
@@ -39327,7 +39327,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2">
+      <c r="A59" s="1">
         <v>58.0</v>
       </c>
       <c r="B59" s="9" t="s">
@@ -39357,7 +39357,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2">
+      <c r="A60" s="1">
         <v>59.0</v>
       </c>
       <c r="B60" s="9" t="s">
@@ -39387,7 +39387,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2">
+      <c r="A61" s="1">
         <v>60.0</v>
       </c>
       <c r="B61" s="9" t="s">
@@ -39417,7 +39417,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2">
+      <c r="A62" s="1">
         <v>61.0</v>
       </c>
       <c r="B62" s="9" t="s">
@@ -39447,7 +39447,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2">
+      <c r="A63" s="1">
         <v>62.0</v>
       </c>
       <c r="B63" s="9" t="s">
@@ -39477,7 +39477,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2">
+      <c r="A64" s="1">
         <v>63.0</v>
       </c>
       <c r="B64" s="9" t="s">
@@ -39507,7 +39507,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2">
+      <c r="A65" s="1">
         <v>64.0</v>
       </c>
       <c r="B65" s="9" t="s">
@@ -39537,7 +39537,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2">
+      <c r="A66" s="1">
         <v>65.0</v>
       </c>
       <c r="B66" s="9" t="s">
@@ -39567,7 +39567,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2">
+      <c r="A67" s="1">
         <v>66.0</v>
       </c>
       <c r="B67" s="9" t="s">
@@ -39597,7 +39597,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2">
+      <c r="A68" s="1">
         <v>67.0</v>
       </c>
       <c r="B68" s="9" t="s">
@@ -39627,7 +39627,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2">
+      <c r="A69" s="1">
         <v>68.0</v>
       </c>
       <c r="B69" s="9" t="s">
@@ -39657,7 +39657,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2">
+      <c r="A70" s="1">
         <v>69.0</v>
       </c>
       <c r="B70" s="9" t="s">
@@ -39687,7 +39687,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2">
+      <c r="A71" s="1">
         <v>70.0</v>
       </c>
       <c r="B71" s="9" t="s">
@@ -39717,7 +39717,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2">
+      <c r="A72" s="1">
         <v>71.0</v>
       </c>
       <c r="B72" s="9" t="s">
@@ -39747,10 +39747,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2">
+      <c r="A73" s="1">
         <v>72.0</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="1" t="s">
         <v>112</v>
       </c>
       <c r="C73" s="10">

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -14,13 +14,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="178">
   <si>
-    <t>PICK</t>
-  </si>
-  <si>
     <t>Rank</t>
   </si>
   <si>
-    <t>VALUE</t>
+    <t>PICK</t>
   </si>
   <si>
     <t>PLAYER NAME</t>
@@ -33,6 +30,9 @@
   </si>
   <si>
     <t>Mine?</t>
+  </si>
+  <si>
+    <t>VALUE</t>
   </si>
   <si>
     <t>Inflated Fair Price</t>
@@ -50,10 +50,10 @@
     <t>Value vs Fair</t>
   </si>
   <si>
-    <t>Settings</t>
+    <t>New Values</t>
   </si>
   <si>
-    <t>New Values</t>
+    <t>Settings</t>
   </si>
   <si>
     <t>Spine</t>
@@ -104,6 +104,9 @@
     <t>Remaining Leage $</t>
   </si>
   <si>
+    <t>Round 1</t>
+  </si>
+  <si>
     <t>Kenyon Sadiq</t>
   </si>
   <si>
@@ -114,9 +117,6 @@
   </si>
   <si>
     <t>My Remaining</t>
-  </si>
-  <si>
-    <t>Round 1</t>
   </si>
   <si>
     <t>KC Concepcion</t>
@@ -146,6 +146,9 @@
     <t>Undrafted Predraft$</t>
   </si>
   <si>
+    <t>Round 2</t>
+  </si>
+  <si>
     <t>Arvell Reese</t>
   </si>
   <si>
@@ -161,13 +164,10 @@
     <t>Aggression</t>
   </si>
   <si>
-    <t>Round 2</t>
+    <t>Caleb Downs</t>
   </si>
   <si>
     <t>Round 3</t>
-  </si>
-  <si>
-    <t>Caleb Downs</t>
   </si>
   <si>
     <t>David Bailey</t>
@@ -188,13 +188,13 @@
     <t>Dillon Thieneman</t>
   </si>
   <si>
+    <t>Round 4</t>
+  </si>
+  <si>
     <t>Rueben Bain</t>
   </si>
   <si>
     <t>Chris Bell</t>
-  </si>
-  <si>
-    <t>Round 4</t>
   </si>
   <si>
     <t>Germie Bernard</t>
@@ -204,6 +204,9 @@
   </si>
   <si>
     <t>Mike Washington</t>
+  </si>
+  <si>
+    <t>Round 5</t>
   </si>
   <si>
     <t>Enforce % of Fair</t>
@@ -227,13 +230,13 @@
     <t>Zachariah Branch</t>
   </si>
   <si>
+    <t>Round 6</t>
+  </si>
+  <si>
     <t>De'Zhaun Stribling</t>
   </si>
   <si>
     <t>Malachi Fields</t>
-  </si>
-  <si>
-    <t>Round 5</t>
   </si>
   <si>
     <t>Kaytron Allen</t>
@@ -264,9 +267,6 @@
   </si>
   <si>
     <t>R Mason Thomas</t>
-  </si>
-  <si>
-    <t>Round 6</t>
   </si>
   <si>
     <t>Oscar Delp</t>
@@ -566,11 +566,11 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF1B1C1D"/>
@@ -611,66 +611,66 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -913,17 +913,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>14</v>
@@ -1071,7 +1071,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="10" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="10" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="10" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -9212,7 +9212,7 @@
       <c r="U139" s="12"/>
       <c r="V139" s="12"/>
       <c r="W139" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X139" s="6" t="s">
         <v>138</v>
@@ -9455,7 +9455,7 @@
         <v>7.0</v>
       </c>
       <c r="X145" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y145" s="6" t="s">
         <v>143</v>
@@ -9495,7 +9495,7 @@
         <v>8.0</v>
       </c>
       <c r="X146" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Y146" s="6" t="s">
         <v>144</v>
@@ -9535,7 +9535,7 @@
         <v>9.0</v>
       </c>
       <c r="X147" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Y147" s="6" t="s">
         <v>141</v>
@@ -9575,7 +9575,7 @@
         <v>10.0</v>
       </c>
       <c r="X148" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Y148" s="6" t="s">
         <v>145</v>
@@ -9615,7 +9615,7 @@
         <v>11.0</v>
       </c>
       <c r="X149" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Y149" s="6" t="s">
         <v>143</v>
@@ -9935,7 +9935,7 @@
         <v>19.0</v>
       </c>
       <c r="X157" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y157" s="6" t="s">
         <v>145</v>
@@ -10095,7 +10095,7 @@
         <v>23.0</v>
       </c>
       <c r="X161" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y161" s="6" t="s">
         <v>142</v>
@@ -10135,7 +10135,7 @@
         <v>24.0</v>
       </c>
       <c r="X162" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Y162" s="6" t="s">
         <v>141</v>
@@ -10175,7 +10175,7 @@
         <v>25.0</v>
       </c>
       <c r="X163" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y163" s="6" t="s">
         <v>140</v>
@@ -10375,7 +10375,7 @@
         <v>30.0</v>
       </c>
       <c r="X168" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Y168" s="6" t="s">
         <v>141</v>
@@ -10415,7 +10415,7 @@
         <v>31.0</v>
       </c>
       <c r="X169" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Y169" s="6" t="s">
         <v>141</v>
@@ -10495,7 +10495,7 @@
         <v>33.0</v>
       </c>
       <c r="X171" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y171" s="6" t="s">
         <v>141</v>
@@ -10575,7 +10575,7 @@
         <v>35.0</v>
       </c>
       <c r="X173" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Y173" s="6" t="s">
         <v>143</v>
@@ -10735,7 +10735,7 @@
         <v>39.0</v>
       </c>
       <c r="X177" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Y177" s="6" t="s">
         <v>144</v>
@@ -10775,7 +10775,7 @@
         <v>40.0</v>
       </c>
       <c r="X178" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y178" s="6" t="s">
         <v>141</v>
@@ -10815,7 +10815,7 @@
         <v>41.0</v>
       </c>
       <c r="X179" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Y179" s="6" t="s">
         <v>141</v>
@@ -10855,7 +10855,7 @@
         <v>42.0</v>
       </c>
       <c r="X180" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Y180" s="6" t="s">
         <v>140</v>
@@ -11055,7 +11055,7 @@
         <v>47.0</v>
       </c>
       <c r="X185" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y185" s="6" t="s">
         <v>141</v>
@@ -11375,7 +11375,7 @@
         <v>55.0</v>
       </c>
       <c r="X193" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Y193" s="6" t="s">
         <v>141</v>
@@ -37443,20 +37443,20 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>7</v>
@@ -37467,15 +37467,15 @@
       <c r="H1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>12</v>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>1.0</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -37484,8 +37484,8 @@
       <c r="C2" s="8">
         <v>139.0</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="b">
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F2" s="8">
@@ -37522,15 +37522,15 @@
 </f>
         <v/>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="1">
         <v>1200.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>2.0</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -37539,8 +37539,8 @@
       <c r="C3" s="8">
         <v>106.5</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="b">
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F3" s="8">
@@ -37564,15 +37564,15 @@
 </f>
         <v/>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="1">
         <v>12.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>3.0</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -37581,8 +37581,8 @@
       <c r="C4" s="8">
         <v>93.0</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="b">
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F4" s="8">
@@ -37601,7 +37601,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>25</v>
       </c>
       <c r="L4" s="4">
@@ -37610,7 +37610,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>4.0</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -37638,7 +37638,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L5" s="17">
@@ -37648,7 +37648,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>5.0</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -37676,7 +37676,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="1" t="s">
         <v>29</v>
       </c>
       <c r="L6" s="17">
@@ -37686,11 +37686,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>6.0</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" s="8">
         <v>66.5</v>
@@ -37714,8 +37714,8 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>31</v>
+      <c r="K7" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="L7" s="17">
         <f>SUMIF($E$2:$E$500,TRUE,$D$2:$D$500)</f>
@@ -37723,11 +37723,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>7.0</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="8">
         <v>57.5</v>
@@ -37751,8 +37751,8 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>33</v>
+      <c r="K8" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="L8" s="8">
         <f>L4-L7
@@ -37761,7 +37761,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>8.0</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -37789,7 +37789,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L9" s="8">
@@ -37799,7 +37799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>9.0</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -37827,7 +37827,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" s="1" t="s">
         <v>38</v>
       </c>
       <c r="L10" s="8">
@@ -37836,7 +37836,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>10.0</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -37864,7 +37864,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" s="1" t="s">
         <v>40</v>
       </c>
       <c r="L11" s="19">
@@ -37873,7 +37873,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>11.0</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -37903,7 +37903,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>12.0</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -37931,7 +37931,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="K13" s="1" t="s">
         <v>43</v>
       </c>
       <c r="L13" s="17">
@@ -37940,11 +37940,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>13.0</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" s="8">
         <v>30.5</v>
@@ -37968,8 +37968,8 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>45</v>
+      <c r="K14" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="L14" s="19">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -37977,11 +37977,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>14.0</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C15" s="8">
         <v>27.5</v>
@@ -38007,11 +38007,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2">
+      <c r="A16" s="1">
         <v>15.0</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C16" s="8">
         <v>25.5</v>
@@ -38035,10 +38035,10 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L16" s="2">
+      <c r="K16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="1">
         <f>IF($L$18&lt;0.3,
      IF($L$11&gt;=1.3,0.09,
         IF($L$11&gt;=1.1,0.07,0.05)),
@@ -38054,11 +38054,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>16.0</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C17" s="8">
         <v>22.5</v>
@@ -38084,7 +38084,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2">
+      <c r="A18" s="1">
         <v>17.0</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -38112,7 +38112,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="K18" s="1" t="s">
         <v>53</v>
       </c>
       <c r="L18" s="20">
@@ -38121,7 +38121,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2">
+      <c r="A19" s="1">
         <v>18.0</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -38151,7 +38151,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2">
+      <c r="A20" s="1">
         <v>19.0</v>
       </c>
       <c r="B20" s="6" t="s">
@@ -38181,7 +38181,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2">
+      <c r="A21" s="1">
         <v>20.0</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -38211,7 +38211,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2">
+      <c r="A22" s="1">
         <v>21.0</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -38241,11 +38241,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2">
+      <c r="A23" s="1">
         <v>22.0</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C23" s="8">
         <v>12.0</v>
@@ -38271,11 +38271,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2">
+      <c r="A24" s="1">
         <v>23.0</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C24" s="8">
         <v>11.0</v>
@@ -38301,7 +38301,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2">
+      <c r="A25" s="1">
         <v>24.0</v>
       </c>
       <c r="B25" s="6" t="s">
@@ -38331,7 +38331,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2">
+      <c r="A26" s="1">
         <v>25.0</v>
       </c>
       <c r="B26" s="6" t="s">
@@ -38361,7 +38361,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2">
+      <c r="A27" s="1">
         <v>26.0</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -38389,19 +38389,19 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K27" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="L27" s="2">
+      <c r="K27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L27" s="1">
         <v>0.8</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2">
+      <c r="A28" s="1">
         <v>27.0</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C28" s="8">
         <v>8.0</v>
@@ -38427,11 +38427,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2">
+      <c r="A29" s="1">
         <v>28.0</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C29" s="8">
         <v>7.0</v>
@@ -38457,11 +38457,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2">
+      <c r="A30" s="1">
         <v>29.0</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C30" s="8">
         <v>6.5</v>
@@ -38487,11 +38487,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2">
+      <c r="A31" s="1">
         <v>30.0</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C31" s="8">
         <v>6.0</v>
@@ -38517,11 +38517,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2">
+      <c r="A32" s="1">
         <v>31.0</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C32" s="8">
         <v>5.5</v>
@@ -38547,11 +38547,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2">
+      <c r="A33" s="1">
         <v>32.0</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C33" s="8">
         <v>5.0</v>
@@ -38577,11 +38577,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2">
+      <c r="A34" s="1">
         <v>33.0</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C34" s="8">
         <v>4.5</v>
@@ -38607,11 +38607,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2">
+      <c r="A35" s="1">
         <v>34.0</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C35" s="8">
         <v>4.5</v>
@@ -38637,11 +38637,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2">
+      <c r="A36" s="1">
         <v>35.0</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C36" s="8">
         <v>4.0</v>
@@ -38667,11 +38667,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2">
+      <c r="A37" s="1">
         <v>36.0</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C37" s="8">
         <v>4.0</v>
@@ -38697,11 +38697,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2">
+      <c r="A38" s="1">
         <v>37.0</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C38" s="8">
         <v>3.5</v>
@@ -38727,11 +38727,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2">
+      <c r="A39" s="1">
         <v>38.0</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C39" s="8">
         <v>3.5</v>
@@ -38757,11 +38757,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2">
+      <c r="A40" s="1">
         <v>39.0</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C40" s="8">
         <v>3.0</v>
@@ -38787,11 +38787,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2">
+      <c r="A41" s="1">
         <v>40.0</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C41" s="8">
         <v>3.0</v>
@@ -38817,11 +38817,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2">
+      <c r="A42" s="1">
         <v>41.0</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C42" s="8">
         <v>2.5</v>
@@ -38847,11 +38847,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2">
+      <c r="A43" s="1">
         <v>42.0</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C43" s="8">
         <v>2.5</v>
@@ -38877,11 +38877,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2">
+      <c r="A44" s="1">
         <v>43.0</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C44" s="8">
         <v>2.5</v>
@@ -38907,11 +38907,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2">
+      <c r="A45" s="1">
         <v>44.0</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C45" s="8">
         <v>2.5</v>
@@ -38937,7 +38937,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2">
+      <c r="A46" s="1">
         <v>45.0</v>
       </c>
       <c r="B46" s="6" t="s">
@@ -38967,7 +38967,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2">
+      <c r="A47" s="1">
         <v>46.0</v>
       </c>
       <c r="B47" s="6" t="s">
@@ -38997,7 +38997,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2">
+      <c r="A48" s="1">
         <v>47.0</v>
       </c>
       <c r="B48" s="6" t="s">
@@ -39027,7 +39027,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2">
+      <c r="A49" s="1">
         <v>48.0</v>
       </c>
       <c r="B49" s="6" t="s">
@@ -39057,7 +39057,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2">
+      <c r="A50" s="1">
         <v>49.0</v>
       </c>
       <c r="B50" s="6" t="s">
@@ -39087,7 +39087,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2">
+      <c r="A51" s="1">
         <v>50.0</v>
       </c>
       <c r="B51" s="6" t="s">
@@ -39117,7 +39117,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2">
+      <c r="A52" s="1">
         <v>51.0</v>
       </c>
       <c r="B52" s="6" t="s">
@@ -39147,7 +39147,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2">
+      <c r="A53" s="1">
         <v>52.0</v>
       </c>
       <c r="B53" s="6" t="s">
@@ -39177,7 +39177,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2">
+      <c r="A54" s="1">
         <v>53.0</v>
       </c>
       <c r="B54" s="6" t="s">
@@ -39207,7 +39207,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2">
+      <c r="A55" s="1">
         <v>54.0</v>
       </c>
       <c r="B55" s="6" t="s">
@@ -39237,7 +39237,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2">
+      <c r="A56" s="1">
         <v>55.0</v>
       </c>
       <c r="B56" s="6" t="s">
@@ -39267,7 +39267,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2">
+      <c r="A57" s="1">
         <v>56.0</v>
       </c>
       <c r="B57" s="6" t="s">
@@ -39297,7 +39297,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2">
+      <c r="A58" s="1">
         <v>57.0</v>
       </c>
       <c r="B58" s="6" t="s">
@@ -39327,7 +39327,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2">
+      <c r="A59" s="1">
         <v>58.0</v>
       </c>
       <c r="B59" s="6" t="s">
@@ -39357,7 +39357,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2">
+      <c r="A60" s="1">
         <v>59.0</v>
       </c>
       <c r="B60" s="6" t="s">
@@ -39387,7 +39387,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2">
+      <c r="A61" s="1">
         <v>60.0</v>
       </c>
       <c r="B61" s="6" t="s">
@@ -39417,7 +39417,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2">
+      <c r="A62" s="1">
         <v>61.0</v>
       </c>
       <c r="B62" s="6" t="s">
@@ -39447,7 +39447,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2">
+      <c r="A63" s="1">
         <v>62.0</v>
       </c>
       <c r="B63" s="6" t="s">
@@ -39477,7 +39477,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2">
+      <c r="A64" s="1">
         <v>63.0</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -39507,7 +39507,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2">
+      <c r="A65" s="1">
         <v>64.0</v>
       </c>
       <c r="B65" s="6" t="s">
@@ -39537,7 +39537,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2">
+      <c r="A66" s="1">
         <v>65.0</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -39567,7 +39567,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2">
+      <c r="A67" s="1">
         <v>66.0</v>
       </c>
       <c r="B67" s="6" t="s">
@@ -39597,7 +39597,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2">
+      <c r="A68" s="1">
         <v>67.0</v>
       </c>
       <c r="B68" s="6" t="s">
@@ -39627,7 +39627,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2">
+      <c r="A69" s="1">
         <v>68.0</v>
       </c>
       <c r="B69" s="6" t="s">
@@ -39657,7 +39657,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2">
+      <c r="A70" s="1">
         <v>69.0</v>
       </c>
       <c r="B70" s="6" t="s">
@@ -39687,7 +39687,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2">
+      <c r="A71" s="1">
         <v>70.0</v>
       </c>
       <c r="B71" s="6" t="s">
@@ -39717,7 +39717,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2">
+      <c r="A72" s="1">
         <v>71.0</v>
       </c>
       <c r="B72" s="6" t="s">
@@ -39747,10 +39747,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2">
+      <c r="A73" s="1">
         <v>72.0</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="1" t="s">
         <v>112</v>
       </c>
       <c r="C73" s="8">

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -110,10 +110,10 @@
     <t>My Spent</t>
   </si>
   <si>
-    <t>Round 1</t>
+    <t>Sonny Styles</t>
   </si>
   <si>
-    <t>Sonny Styles</t>
+    <t>Round 1</t>
   </si>
   <si>
     <t>My Remaining</t>
@@ -140,16 +140,19 @@
     <t>Omar Cooper</t>
   </si>
   <si>
-    <t>Round 2</t>
-  </si>
-  <si>
     <t>CJ Allen</t>
   </si>
   <si>
     <t>Undrafted Predraft$</t>
   </si>
   <si>
+    <t>Round 2</t>
+  </si>
+  <si>
     <t>Arvell Reese</t>
+  </si>
+  <si>
+    <t>Round 3</t>
   </si>
   <si>
     <t>Inflation Factor</t>
@@ -158,16 +161,22 @@
     <t>Ty Simpson</t>
   </si>
   <si>
+    <t>Round 4</t>
+  </si>
+  <si>
     <t>Denzel Boston</t>
   </si>
   <si>
     <t>Aggression</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>Round 5</t>
   </si>
   <si>
     <t>Caleb Downs</t>
+  </si>
+  <si>
+    <t>Round 6</t>
   </si>
   <si>
     <t>David Bailey</t>
@@ -180,9 +189,6 @@
   </si>
   <si>
     <t>Jonah Coleman</t>
-  </si>
-  <si>
-    <t>Round 4</t>
   </si>
   <si>
     <t>Jake Golday</t>
@@ -204,9 +210,6 @@
   </si>
   <si>
     <t>Mike Washington</t>
-  </si>
-  <si>
-    <t>Round 5</t>
   </si>
   <si>
     <t>Enforce % of Fair</t>
@@ -231,9 +234,6 @@
   </si>
   <si>
     <t>De'Zhaun Stribling</t>
-  </si>
-  <si>
-    <t>Round 6</t>
   </si>
   <si>
     <t>Malachi Fields</t>
@@ -308,51 +308,6 @@
     <t>Lake McRee</t>
   </si>
   <si>
-    <t>Cade Klubnik</t>
-  </si>
-  <si>
-    <t>Drew Allar</t>
-  </si>
-  <si>
-    <t>Carson Beck</t>
-  </si>
-  <si>
-    <t>Joe Royer</t>
-  </si>
-  <si>
-    <t>Sam Roush</t>
-  </si>
-  <si>
-    <t>Tanner Koziol</t>
-  </si>
-  <si>
-    <t>Jack Endries</t>
-  </si>
-  <si>
-    <t>Matthew Hibner</t>
-  </si>
-  <si>
-    <t>Tyren Montgomery</t>
-  </si>
-  <si>
-    <t>Bryce Lance</t>
-  </si>
-  <si>
-    <t>Kevin Coleman</t>
-  </si>
-  <si>
-    <t>Garrett Nussmeier</t>
-  </si>
-  <si>
-    <t>Nate Boerkircher</t>
-  </si>
-  <si>
-    <t>Will Kacmarek</t>
-  </si>
-  <si>
-    <t>Noah Whittington</t>
-  </si>
-  <si>
     <t>Standings</t>
   </si>
   <si>
@@ -380,22 +335,67 @@
     <t>Key</t>
   </si>
   <si>
+    <t>Cade Klubnik</t>
+  </si>
+  <si>
+    <t>Drew Allar</t>
+  </si>
+  <si>
     <t>Ed</t>
+  </si>
+  <si>
+    <t>Carson Beck</t>
+  </si>
+  <si>
+    <t>Joe Royer</t>
+  </si>
+  <si>
+    <t>Sam Roush</t>
+  </si>
+  <si>
+    <t>Tanner Koziol</t>
   </si>
   <si>
     <t>Brent</t>
   </si>
   <si>
+    <t>Jack Endries</t>
+  </si>
+  <si>
+    <t>Matthew Hibner</t>
+  </si>
+  <si>
     <t>Joey</t>
+  </si>
+  <si>
+    <t>Tyren Montgomery</t>
+  </si>
+  <si>
+    <t>Bryce Lance</t>
   </si>
   <si>
     <t>MaKayla</t>
   </si>
   <si>
+    <t>Kevin Coleman</t>
+  </si>
+  <si>
+    <t>Garrett Nussmeier</t>
+  </si>
+  <si>
     <t>Ty</t>
   </si>
   <si>
+    <t>Nate Boerkircher</t>
+  </si>
+  <si>
+    <t>Will Kacmarek</t>
+  </si>
+  <si>
     <t>Kich</t>
+  </si>
+  <si>
+    <t>Noah Whittington</t>
   </si>
   <si>
     <t>Eric</t>
@@ -663,13 +663,13 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
@@ -1071,7 +1071,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="10" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="10" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="10" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="10" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -3062,33 +3062,33 @@
       <c r="M29" s="12"/>
       <c r="N29" s="12"/>
       <c r="O29" s="10" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="Q29" s="12"/>
       <c r="R29" s="10" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="S29" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="T29" s="10" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="U29" s="12"/>
       <c r="V29" s="10" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="W29" s="10" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="X29" s="10" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="Y29" s="10" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="Z29" s="12"/>
       <c r="AA29" s="12"/>
@@ -3146,7 +3146,7 @@
         <v>1.0</v>
       </c>
       <c r="P30" s="10" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="Q30" s="12"/>
       <c r="R30" s="6">
@@ -3158,8 +3158,8 @@
         <v>Ed</v>
       </c>
       <c r="U30" s="12"/>
-      <c r="V30" s="23"/>
-      <c r="W30" s="23"/>
+      <c r="V30" s="21"/>
+      <c r="W30" s="21"/>
       <c r="X30" s="7"/>
       <c r="Y30" s="12" t="str">
         <f t="shared" ref="Y30:Y81" si="17">TEXT(V30,"0")&amp;"|"&amp;TRIM(W30)</f>
@@ -3221,7 +3221,7 @@
         <v>2.0</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="Q31" s="12"/>
       <c r="R31" s="6">
@@ -3296,7 +3296,7 @@
         <v>3.0</v>
       </c>
       <c r="P32" s="10" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="Q32" s="12"/>
       <c r="R32" s="6">
@@ -3371,7 +3371,7 @@
         <v>4.0</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="Q33" s="12"/>
       <c r="R33" s="6">
@@ -3446,7 +3446,7 @@
         <v>5.0</v>
       </c>
       <c r="P34" s="10" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Q34" s="12"/>
       <c r="R34" s="6">
@@ -3521,7 +3521,7 @@
         <v>6.0</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q35" s="12"/>
       <c r="R35" s="6">
@@ -4000,7 +4000,7 @@
       <c r="A42" s="13">
         <v>4.05</v>
       </c>
-      <c r="B42" s="23">
+      <c r="B42" s="21">
         <v>2048.0</v>
       </c>
       <c r="C42" s="16">
@@ -4175,7 +4175,7 @@
       <c r="M44" s="12"/>
       <c r="N44" s="12"/>
       <c r="O44" s="10" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="P44" s="10" t="s">
         <v>20</v>
@@ -4184,7 +4184,7 @@
         <v>134</v>
       </c>
       <c r="R44" s="10" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="S44" s="12"/>
       <c r="T44" s="12"/>
@@ -5293,8 +5293,8 @@
       <c r="S58" s="12"/>
       <c r="T58" s="12"/>
       <c r="U58" s="12"/>
-      <c r="V58" s="23"/>
-      <c r="W58" s="23"/>
+      <c r="V58" s="21"/>
+      <c r="W58" s="21"/>
       <c r="X58" s="7"/>
       <c r="Y58" s="12" t="str">
         <f t="shared" si="17"/>
@@ -5371,8 +5371,8 @@
       <c r="S59" s="12"/>
       <c r="T59" s="12"/>
       <c r="U59" s="12"/>
-      <c r="V59" s="23"/>
-      <c r="W59" s="23"/>
+      <c r="V59" s="21"/>
+      <c r="W59" s="21"/>
       <c r="X59" s="7"/>
       <c r="Y59" s="12" t="str">
         <f t="shared" si="17"/>
@@ -5449,8 +5449,8 @@
       <c r="S60" s="12"/>
       <c r="T60" s="12"/>
       <c r="U60" s="12"/>
-      <c r="V60" s="23"/>
-      <c r="W60" s="23"/>
+      <c r="V60" s="21"/>
+      <c r="W60" s="21"/>
       <c r="X60" s="7"/>
       <c r="Y60" s="12" t="str">
         <f t="shared" si="17"/>
@@ -5775,8 +5775,8 @@
         <f t="shared" si="22"/>
         <v>144.5</v>
       </c>
-      <c r="V64" s="23"/>
-      <c r="W64" s="23"/>
+      <c r="V64" s="21"/>
+      <c r="W64" s="21"/>
       <c r="X64" s="7"/>
       <c r="Y64" s="12" t="str">
         <f t="shared" si="17"/>
@@ -6124,7 +6124,7 @@
       <c r="A69" s="13">
         <v>6.08</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B69" s="21">
         <v>1242.0</v>
       </c>
       <c r="C69" s="16">
@@ -6184,14 +6184,14 @@
       </c>
       <c r="S69" s="12"/>
       <c r="T69" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U69" s="16">
         <f t="shared" si="22"/>
         <v>83</v>
       </c>
-      <c r="V69" s="23"/>
-      <c r="W69" s="23"/>
+      <c r="V69" s="21"/>
+      <c r="W69" s="21"/>
       <c r="X69" s="7"/>
       <c r="Y69" s="12" t="str">
         <f t="shared" si="17"/>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="S70" s="12"/>
       <c r="T70" s="12" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="U70" s="16">
         <f t="shared" si="22"/>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="S71" s="12"/>
       <c r="T71" s="12" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="U71" s="16">
         <f t="shared" si="22"/>
@@ -6373,7 +6373,7 @@
       <c r="A72" s="13">
         <v>6.11</v>
       </c>
-      <c r="B72" s="23">
+      <c r="B72" s="21">
         <v>1190.0</v>
       </c>
       <c r="C72" s="16">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="S72" s="12"/>
       <c r="T72" s="12" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="U72" s="16">
         <f t="shared" si="22"/>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S73" s="12"/>
       <c r="T73" s="12" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="U73" s="16">
         <f t="shared" si="22"/>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="S74" s="12"/>
       <c r="T74" s="12" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="U74" s="16">
         <f t="shared" si="22"/>
@@ -9455,7 +9455,7 @@
         <v>7.0</v>
       </c>
       <c r="X145" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y145" s="7" t="s">
         <v>143</v>
@@ -9535,7 +9535,7 @@
         <v>9.0</v>
       </c>
       <c r="X147" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Y147" s="7" t="s">
         <v>141</v>
@@ -9575,7 +9575,7 @@
         <v>10.0</v>
       </c>
       <c r="X148" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Y148" s="7" t="s">
         <v>145</v>
@@ -9655,7 +9655,7 @@
         <v>12.0</v>
       </c>
       <c r="X150" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Y150" s="7" t="s">
         <v>146</v>
@@ -9815,7 +9815,7 @@
         <v>16.0</v>
       </c>
       <c r="X154" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="Y154" s="7" t="s">
         <v>143</v>
@@ -9855,7 +9855,7 @@
         <v>17.0</v>
       </c>
       <c r="X155" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="Y155" s="7" t="s">
         <v>140</v>
@@ -9895,7 +9895,7 @@
         <v>18.0</v>
       </c>
       <c r="X156" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Y156" s="7" t="s">
         <v>145</v>
@@ -10095,7 +10095,7 @@
         <v>23.0</v>
       </c>
       <c r="X161" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Y161" s="7" t="s">
         <v>142</v>
@@ -10135,7 +10135,7 @@
         <v>24.0</v>
       </c>
       <c r="X162" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y162" s="7" t="s">
         <v>141</v>
@@ -10175,7 +10175,7 @@
         <v>25.0</v>
       </c>
       <c r="X163" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Y163" s="7" t="s">
         <v>140</v>
@@ -10215,7 +10215,7 @@
         <v>26.0</v>
       </c>
       <c r="X164" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Y164" s="7" t="s">
         <v>140</v>
@@ -10335,7 +10335,7 @@
         <v>29.0</v>
       </c>
       <c r="X167" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Y167" s="7" t="s">
         <v>143</v>
@@ -10375,7 +10375,7 @@
         <v>30.0</v>
       </c>
       <c r="X168" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Y168" s="7" t="s">
         <v>141</v>
@@ -10415,7 +10415,7 @@
         <v>31.0</v>
       </c>
       <c r="X169" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y169" s="7" t="s">
         <v>141</v>
@@ -10615,7 +10615,7 @@
         <v>36.0</v>
       </c>
       <c r="X174" s="7" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="Y174" s="7" t="s">
         <v>144</v>
@@ -10695,7 +10695,7 @@
         <v>38.0</v>
       </c>
       <c r="X176" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="Y176" s="7" t="s">
         <v>141</v>
@@ -10735,7 +10735,7 @@
         <v>39.0</v>
       </c>
       <c r="X177" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Y177" s="7" t="s">
         <v>144</v>
@@ -10815,7 +10815,7 @@
         <v>41.0</v>
       </c>
       <c r="X179" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Y179" s="7" t="s">
         <v>141</v>
@@ -10895,7 +10895,7 @@
         <v>43.0</v>
       </c>
       <c r="X181" s="7" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="Y181" s="7" t="s">
         <v>144</v>
@@ -10935,7 +10935,7 @@
         <v>44.0</v>
       </c>
       <c r="X182" s="7" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="Y182" s="7" t="s">
         <v>142</v>
@@ -11015,7 +11015,7 @@
         <v>46.0</v>
       </c>
       <c r="X184" s="7" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="Y184" s="7" t="s">
         <v>141</v>
@@ -11175,7 +11175,7 @@
         <v>50.0</v>
       </c>
       <c r="X188" s="7" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Y188" s="7" t="s">
         <v>142</v>
@@ -11775,7 +11775,7 @@
         <v>65.0</v>
       </c>
       <c r="X203" s="7" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="Y203" s="7" t="s">
         <v>142</v>
@@ -12135,7 +12135,7 @@
         <v>74.0</v>
       </c>
       <c r="X212" s="7" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="Y212" s="7" t="s">
         <v>142</v>
@@ -37727,7 +37727,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="9">
         <v>57.5</v>
@@ -37907,7 +37907,7 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="9">
         <v>34.0</v>
@@ -37932,7 +37932,7 @@
         <v/>
       </c>
       <c r="K13" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L13" s="17">
         <f>SUMIF($D$2:$D$73,"",$C$2:$C$73)</f>
@@ -37969,7 +37969,7 @@
         <v/>
       </c>
       <c r="K14" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L14" s="19">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -37981,7 +37981,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C15" s="9">
         <v>27.5</v>
@@ -38011,7 +38011,7 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C16" s="9">
         <v>25.5</v>
@@ -38036,7 +38036,7 @@
         <v/>
       </c>
       <c r="K16" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L16" s="1">
         <f>IF($L$18&lt;0.3,
@@ -38058,7 +38058,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C17" s="9">
         <v>22.5</v>
@@ -38088,7 +38088,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C18" s="9">
         <v>20.0</v>
@@ -38113,7 +38113,7 @@
         <v/>
       </c>
       <c r="K18" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="L18" s="20">
         <f>L5/L2</f>
@@ -38125,7 +38125,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C19" s="9">
         <v>18.5</v>
@@ -38155,7 +38155,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C20" s="9">
         <v>16.5</v>
@@ -38185,7 +38185,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C21" s="9">
         <v>14.5</v>
@@ -38215,7 +38215,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C22" s="9">
         <v>13.5</v>
@@ -38245,7 +38245,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C23" s="9">
         <v>12.0</v>
@@ -38275,7 +38275,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C24" s="9">
         <v>11.0</v>
@@ -38305,7 +38305,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C25" s="9">
         <v>10.0</v>
@@ -38335,7 +38335,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C26" s="9">
         <v>9.5</v>
@@ -38365,7 +38365,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C27" s="9">
         <v>8.5</v>
@@ -38390,7 +38390,7 @@
         <v/>
       </c>
       <c r="K27" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L27" s="1">
         <v>0.8</v>
@@ -38401,7 +38401,7 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C28" s="9">
         <v>8.0</v>
@@ -38431,7 +38431,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29" s="9">
         <v>7.0</v>
@@ -38461,7 +38461,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C30" s="9">
         <v>6.5</v>
@@ -38491,7 +38491,7 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C31" s="9">
         <v>6.0</v>
@@ -38521,7 +38521,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C32" s="9">
         <v>5.5</v>
@@ -38551,7 +38551,7 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C33" s="9">
         <v>5.0</v>
@@ -38581,7 +38581,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C34" s="9">
         <v>4.5</v>
@@ -39331,7 +39331,7 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C59" s="9">
         <v>2.0</v>
@@ -39361,7 +39361,7 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C60" s="9">
         <v>2.0</v>
@@ -39391,7 +39391,7 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C61" s="9">
         <v>2.0</v>
@@ -39421,7 +39421,7 @@
         <v>61.0</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C62" s="9">
         <v>1.0</v>
@@ -39451,7 +39451,7 @@
         <v>62.0</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C63" s="9">
         <v>1.0</v>
@@ -39481,7 +39481,7 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C64" s="9">
         <v>1.0</v>
@@ -39511,7 +39511,7 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="C65" s="9">
         <v>1.0</v>
@@ -39541,7 +39541,7 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C66" s="9">
         <v>1.0</v>
@@ -39571,7 +39571,7 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="C67" s="9">
         <v>1.0</v>
@@ -39601,7 +39601,7 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C68" s="9">
         <v>1.0</v>
@@ -39631,7 +39631,7 @@
         <v>68.0</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C69" s="9">
         <v>1.0</v>
@@ -39661,7 +39661,7 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="C70" s="9">
         <v>1.0</v>
@@ -39691,7 +39691,7 @@
         <v>70.0</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="C71" s="9">
         <v>1.0</v>
@@ -39721,7 +39721,7 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="C72" s="9">
         <v>1.0</v>
@@ -39751,7 +39751,7 @@
         <v>72.0</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="C73" s="9">
         <v>1.0</v>
@@ -39783,6496 +39783,6496 @@
       <c r="F74" s="9"/>
       <c r="G74" s="9"/>
       <c r="H74" s="14"/>
-      <c r="I74" s="21"/>
+      <c r="I74" s="22"/>
     </row>
     <row r="75">
-      <c r="C75" s="22"/>
+      <c r="C75" s="23"/>
       <c r="F75" s="9"/>
       <c r="G75" s="9"/>
       <c r="H75" s="14"/>
-      <c r="I75" s="21"/>
+      <c r="I75" s="22"/>
     </row>
     <row r="76">
-      <c r="C76" s="22"/>
+      <c r="C76" s="23"/>
       <c r="F76" s="9"/>
       <c r="G76" s="9"/>
       <c r="H76" s="14"/>
-      <c r="I76" s="21"/>
+      <c r="I76" s="22"/>
     </row>
     <row r="77">
-      <c r="C77" s="22"/>
+      <c r="C77" s="23"/>
       <c r="F77" s="9"/>
       <c r="G77" s="9"/>
       <c r="H77" s="14"/>
-      <c r="I77" s="21"/>
+      <c r="I77" s="22"/>
     </row>
     <row r="78">
-      <c r="C78" s="22"/>
+      <c r="C78" s="23"/>
       <c r="F78" s="9"/>
       <c r="G78" s="9"/>
       <c r="H78" s="14"/>
-      <c r="I78" s="21"/>
+      <c r="I78" s="22"/>
     </row>
     <row r="79">
-      <c r="C79" s="22"/>
+      <c r="C79" s="23"/>
       <c r="F79" s="9"/>
       <c r="G79" s="9"/>
       <c r="H79" s="14"/>
-      <c r="I79" s="21"/>
+      <c r="I79" s="22"/>
     </row>
     <row r="80">
-      <c r="C80" s="22"/>
+      <c r="C80" s="23"/>
       <c r="F80" s="9"/>
       <c r="G80" s="9"/>
       <c r="H80" s="14"/>
-      <c r="I80" s="21"/>
+      <c r="I80" s="22"/>
     </row>
     <row r="81">
-      <c r="C81" s="22"/>
+      <c r="C81" s="23"/>
       <c r="F81" s="9"/>
       <c r="G81" s="9"/>
       <c r="H81" s="14"/>
-      <c r="I81" s="21"/>
+      <c r="I81" s="22"/>
     </row>
     <row r="82">
-      <c r="C82" s="22"/>
+      <c r="C82" s="23"/>
       <c r="F82" s="9"/>
       <c r="G82" s="9"/>
       <c r="H82" s="14"/>
-      <c r="I82" s="21"/>
+      <c r="I82" s="22"/>
     </row>
     <row r="83">
-      <c r="C83" s="22"/>
+      <c r="C83" s="23"/>
       <c r="F83" s="9"/>
       <c r="G83" s="9"/>
       <c r="H83" s="14"/>
-      <c r="I83" s="21"/>
+      <c r="I83" s="22"/>
     </row>
     <row r="84">
-      <c r="C84" s="22"/>
+      <c r="C84" s="23"/>
       <c r="F84" s="9"/>
       <c r="G84" s="9"/>
       <c r="H84" s="14"/>
-      <c r="I84" s="21"/>
+      <c r="I84" s="22"/>
     </row>
     <row r="85">
-      <c r="C85" s="22"/>
+      <c r="C85" s="23"/>
       <c r="F85" s="9"/>
       <c r="G85" s="9"/>
       <c r="H85" s="14"/>
-      <c r="I85" s="21"/>
+      <c r="I85" s="22"/>
     </row>
     <row r="86">
-      <c r="C86" s="22"/>
+      <c r="C86" s="23"/>
       <c r="F86" s="9"/>
       <c r="G86" s="9"/>
       <c r="H86" s="14"/>
-      <c r="I86" s="21"/>
+      <c r="I86" s="22"/>
     </row>
     <row r="87">
-      <c r="C87" s="22"/>
+      <c r="C87" s="23"/>
       <c r="F87" s="9"/>
       <c r="G87" s="9"/>
       <c r="H87" s="14"/>
-      <c r="I87" s="21"/>
+      <c r="I87" s="22"/>
     </row>
     <row r="88">
-      <c r="C88" s="22"/>
+      <c r="C88" s="23"/>
       <c r="F88" s="9"/>
       <c r="G88" s="9"/>
       <c r="H88" s="14"/>
-      <c r="I88" s="21"/>
+      <c r="I88" s="22"/>
     </row>
     <row r="89">
-      <c r="C89" s="22"/>
+      <c r="C89" s="23"/>
       <c r="F89" s="9"/>
       <c r="G89" s="9"/>
       <c r="H89" s="14"/>
-      <c r="I89" s="21"/>
+      <c r="I89" s="22"/>
     </row>
     <row r="90">
-      <c r="C90" s="22"/>
+      <c r="C90" s="23"/>
       <c r="F90" s="9"/>
       <c r="G90" s="9"/>
       <c r="H90" s="14"/>
-      <c r="I90" s="21"/>
+      <c r="I90" s="22"/>
     </row>
     <row r="91">
-      <c r="C91" s="22"/>
+      <c r="C91" s="23"/>
       <c r="F91" s="9"/>
       <c r="G91" s="9"/>
       <c r="H91" s="14"/>
-      <c r="I91" s="21"/>
+      <c r="I91" s="22"/>
     </row>
     <row r="92">
-      <c r="C92" s="22"/>
+      <c r="C92" s="23"/>
       <c r="F92" s="9"/>
       <c r="G92" s="9"/>
       <c r="H92" s="14"/>
-      <c r="I92" s="21"/>
+      <c r="I92" s="22"/>
     </row>
     <row r="93">
-      <c r="C93" s="22"/>
+      <c r="C93" s="23"/>
       <c r="F93" s="9"/>
       <c r="G93" s="9"/>
       <c r="H93" s="14"/>
-      <c r="I93" s="21"/>
+      <c r="I93" s="22"/>
     </row>
     <row r="94">
-      <c r="C94" s="22"/>
+      <c r="C94" s="23"/>
       <c r="F94" s="9"/>
       <c r="G94" s="9"/>
       <c r="H94" s="14"/>
-      <c r="I94" s="21"/>
+      <c r="I94" s="22"/>
     </row>
     <row r="95">
-      <c r="C95" s="22"/>
+      <c r="C95" s="23"/>
       <c r="F95" s="9"/>
       <c r="G95" s="9"/>
       <c r="H95" s="14"/>
-      <c r="I95" s="21"/>
+      <c r="I95" s="22"/>
     </row>
     <row r="96">
-      <c r="C96" s="22"/>
+      <c r="C96" s="23"/>
       <c r="F96" s="9"/>
       <c r="G96" s="9"/>
       <c r="H96" s="14"/>
-      <c r="I96" s="21"/>
+      <c r="I96" s="22"/>
     </row>
     <row r="97">
-      <c r="C97" s="22"/>
+      <c r="C97" s="23"/>
       <c r="F97" s="9"/>
       <c r="G97" s="9"/>
       <c r="H97" s="14"/>
-      <c r="I97" s="21"/>
+      <c r="I97" s="22"/>
     </row>
     <row r="98">
-      <c r="C98" s="22"/>
+      <c r="C98" s="23"/>
       <c r="F98" s="9"/>
       <c r="G98" s="9"/>
       <c r="H98" s="14"/>
-      <c r="I98" s="21"/>
+      <c r="I98" s="22"/>
     </row>
     <row r="99">
-      <c r="C99" s="22"/>
+      <c r="C99" s="23"/>
       <c r="F99" s="9"/>
       <c r="G99" s="9"/>
       <c r="H99" s="14"/>
-      <c r="I99" s="21"/>
+      <c r="I99" s="22"/>
     </row>
     <row r="100">
-      <c r="C100" s="22"/>
+      <c r="C100" s="23"/>
       <c r="F100" s="9"/>
       <c r="G100" s="9"/>
       <c r="H100" s="14"/>
-      <c r="I100" s="21"/>
+      <c r="I100" s="22"/>
     </row>
     <row r="101">
-      <c r="C101" s="22"/>
+      <c r="C101" s="23"/>
       <c r="F101" s="9"/>
       <c r="G101" s="9"/>
       <c r="H101" s="14"/>
-      <c r="I101" s="21"/>
+      <c r="I101" s="22"/>
     </row>
     <row r="102">
-      <c r="C102" s="22"/>
+      <c r="C102" s="23"/>
       <c r="F102" s="9"/>
       <c r="G102" s="9"/>
       <c r="H102" s="14"/>
-      <c r="I102" s="21"/>
+      <c r="I102" s="22"/>
     </row>
     <row r="103">
-      <c r="C103" s="22"/>
+      <c r="C103" s="23"/>
       <c r="F103" s="9"/>
       <c r="G103" s="9"/>
       <c r="H103" s="14"/>
-      <c r="I103" s="21"/>
+      <c r="I103" s="22"/>
     </row>
     <row r="104">
-      <c r="C104" s="22"/>
+      <c r="C104" s="23"/>
       <c r="F104" s="9"/>
       <c r="G104" s="9"/>
       <c r="H104" s="14"/>
-      <c r="I104" s="21"/>
+      <c r="I104" s="22"/>
     </row>
     <row r="105">
-      <c r="C105" s="22"/>
+      <c r="C105" s="23"/>
       <c r="F105" s="9"/>
       <c r="G105" s="9"/>
       <c r="H105" s="14"/>
-      <c r="I105" s="21"/>
+      <c r="I105" s="22"/>
     </row>
     <row r="106">
-      <c r="C106" s="22"/>
+      <c r="C106" s="23"/>
       <c r="F106" s="9"/>
       <c r="G106" s="9"/>
       <c r="H106" s="14"/>
-      <c r="I106" s="21"/>
+      <c r="I106" s="22"/>
     </row>
     <row r="107">
-      <c r="C107" s="22"/>
+      <c r="C107" s="23"/>
       <c r="F107" s="9"/>
       <c r="G107" s="9"/>
       <c r="H107" s="14"/>
-      <c r="I107" s="21"/>
+      <c r="I107" s="22"/>
     </row>
     <row r="108">
-      <c r="C108" s="22"/>
+      <c r="C108" s="23"/>
       <c r="F108" s="9"/>
       <c r="G108" s="9"/>
       <c r="H108" s="14"/>
-      <c r="I108" s="21"/>
+      <c r="I108" s="22"/>
     </row>
     <row r="109">
-      <c r="C109" s="22"/>
+      <c r="C109" s="23"/>
       <c r="F109" s="9"/>
       <c r="G109" s="9"/>
       <c r="H109" s="14"/>
-      <c r="I109" s="21"/>
+      <c r="I109" s="22"/>
     </row>
     <row r="110">
-      <c r="C110" s="22"/>
+      <c r="C110" s="23"/>
       <c r="F110" s="9"/>
       <c r="G110" s="9"/>
       <c r="H110" s="14"/>
-      <c r="I110" s="21"/>
+      <c r="I110" s="22"/>
     </row>
     <row r="111">
-      <c r="C111" s="22"/>
+      <c r="C111" s="23"/>
       <c r="F111" s="9"/>
       <c r="G111" s="9"/>
       <c r="H111" s="14"/>
-      <c r="I111" s="21"/>
+      <c r="I111" s="22"/>
     </row>
     <row r="112">
-      <c r="C112" s="22"/>
+      <c r="C112" s="23"/>
       <c r="F112" s="9"/>
       <c r="G112" s="9"/>
       <c r="H112" s="14"/>
-      <c r="I112" s="21"/>
+      <c r="I112" s="22"/>
     </row>
     <row r="113">
-      <c r="C113" s="22"/>
+      <c r="C113" s="23"/>
       <c r="F113" s="9"/>
       <c r="G113" s="9"/>
       <c r="H113" s="14"/>
-      <c r="I113" s="21"/>
+      <c r="I113" s="22"/>
     </row>
     <row r="114">
-      <c r="C114" s="22"/>
+      <c r="C114" s="23"/>
       <c r="F114" s="9"/>
       <c r="G114" s="9"/>
       <c r="H114" s="14"/>
-      <c r="I114" s="21"/>
+      <c r="I114" s="22"/>
     </row>
     <row r="115">
-      <c r="C115" s="22"/>
+      <c r="C115" s="23"/>
       <c r="F115" s="9"/>
       <c r="G115" s="9"/>
       <c r="H115" s="14"/>
-      <c r="I115" s="21"/>
+      <c r="I115" s="22"/>
     </row>
     <row r="116">
-      <c r="C116" s="22"/>
+      <c r="C116" s="23"/>
       <c r="F116" s="9"/>
       <c r="G116" s="9"/>
       <c r="H116" s="14"/>
-      <c r="I116" s="21"/>
+      <c r="I116" s="22"/>
     </row>
     <row r="117">
-      <c r="C117" s="22"/>
+      <c r="C117" s="23"/>
       <c r="F117" s="9"/>
       <c r="G117" s="9"/>
       <c r="H117" s="14"/>
-      <c r="I117" s="21"/>
+      <c r="I117" s="22"/>
     </row>
     <row r="118">
-      <c r="C118" s="22"/>
+      <c r="C118" s="23"/>
       <c r="F118" s="9"/>
       <c r="G118" s="9"/>
       <c r="H118" s="14"/>
-      <c r="I118" s="21"/>
+      <c r="I118" s="22"/>
     </row>
     <row r="119">
-      <c r="C119" s="22"/>
+      <c r="C119" s="23"/>
       <c r="F119" s="9"/>
       <c r="G119" s="9"/>
       <c r="H119" s="14"/>
-      <c r="I119" s="21"/>
+      <c r="I119" s="22"/>
     </row>
     <row r="120">
-      <c r="C120" s="22"/>
+      <c r="C120" s="23"/>
       <c r="F120" s="9"/>
       <c r="G120" s="9"/>
       <c r="H120" s="14"/>
-      <c r="I120" s="21"/>
+      <c r="I120" s="22"/>
     </row>
     <row r="121">
-      <c r="C121" s="22"/>
+      <c r="C121" s="23"/>
       <c r="F121" s="9"/>
       <c r="G121" s="9"/>
       <c r="H121" s="14"/>
-      <c r="I121" s="21"/>
+      <c r="I121" s="22"/>
     </row>
     <row r="122">
-      <c r="C122" s="22"/>
+      <c r="C122" s="23"/>
       <c r="F122" s="9"/>
       <c r="G122" s="9"/>
       <c r="H122" s="14"/>
-      <c r="I122" s="21"/>
+      <c r="I122" s="22"/>
     </row>
     <row r="123">
-      <c r="C123" s="22"/>
+      <c r="C123" s="23"/>
       <c r="F123" s="9"/>
       <c r="G123" s="9"/>
       <c r="H123" s="14"/>
-      <c r="I123" s="21"/>
+      <c r="I123" s="22"/>
     </row>
     <row r="124">
-      <c r="C124" s="22"/>
+      <c r="C124" s="23"/>
       <c r="F124" s="9"/>
       <c r="G124" s="9"/>
       <c r="H124" s="14"/>
-      <c r="I124" s="21"/>
+      <c r="I124" s="22"/>
     </row>
     <row r="125">
-      <c r="C125" s="22"/>
+      <c r="C125" s="23"/>
       <c r="F125" s="9"/>
       <c r="G125" s="9"/>
       <c r="H125" s="14"/>
-      <c r="I125" s="21"/>
+      <c r="I125" s="22"/>
     </row>
     <row r="126">
-      <c r="C126" s="22"/>
+      <c r="C126" s="23"/>
       <c r="F126" s="9"/>
       <c r="G126" s="9"/>
       <c r="H126" s="14"/>
-      <c r="I126" s="21"/>
+      <c r="I126" s="22"/>
     </row>
     <row r="127">
-      <c r="C127" s="22"/>
+      <c r="C127" s="23"/>
       <c r="F127" s="9"/>
       <c r="G127" s="9"/>
       <c r="H127" s="14"/>
-      <c r="I127" s="21"/>
+      <c r="I127" s="22"/>
     </row>
     <row r="128">
-      <c r="C128" s="22"/>
+      <c r="C128" s="23"/>
       <c r="F128" s="9"/>
       <c r="G128" s="9"/>
       <c r="H128" s="14"/>
-      <c r="I128" s="21"/>
+      <c r="I128" s="22"/>
     </row>
     <row r="129">
-      <c r="C129" s="22"/>
+      <c r="C129" s="23"/>
       <c r="F129" s="9"/>
       <c r="G129" s="9"/>
       <c r="H129" s="14"/>
-      <c r="I129" s="21"/>
+      <c r="I129" s="22"/>
     </row>
     <row r="130">
-      <c r="C130" s="22"/>
+      <c r="C130" s="23"/>
       <c r="F130" s="9"/>
       <c r="G130" s="9"/>
       <c r="H130" s="14"/>
-      <c r="I130" s="21"/>
+      <c r="I130" s="22"/>
     </row>
     <row r="131">
-      <c r="C131" s="22"/>
+      <c r="C131" s="23"/>
       <c r="F131" s="9"/>
       <c r="G131" s="9"/>
       <c r="H131" s="14"/>
-      <c r="I131" s="21"/>
+      <c r="I131" s="22"/>
     </row>
     <row r="132">
-      <c r="C132" s="22"/>
+      <c r="C132" s="23"/>
       <c r="F132" s="9"/>
       <c r="G132" s="9"/>
       <c r="H132" s="14"/>
-      <c r="I132" s="21"/>
+      <c r="I132" s="22"/>
     </row>
     <row r="133">
-      <c r="C133" s="22"/>
+      <c r="C133" s="23"/>
       <c r="F133" s="9"/>
       <c r="G133" s="9"/>
       <c r="H133" s="14"/>
-      <c r="I133" s="21"/>
+      <c r="I133" s="22"/>
     </row>
     <row r="134">
-      <c r="C134" s="22"/>
+      <c r="C134" s="23"/>
       <c r="F134" s="9"/>
       <c r="G134" s="9"/>
       <c r="H134" s="14"/>
-      <c r="I134" s="21"/>
+      <c r="I134" s="22"/>
     </row>
     <row r="135">
-      <c r="C135" s="22"/>
+      <c r="C135" s="23"/>
       <c r="F135" s="9"/>
       <c r="G135" s="9"/>
       <c r="H135" s="14"/>
-      <c r="I135" s="21"/>
+      <c r="I135" s="22"/>
     </row>
     <row r="136">
-      <c r="C136" s="22"/>
+      <c r="C136" s="23"/>
       <c r="F136" s="9"/>
       <c r="G136" s="9"/>
       <c r="H136" s="14"/>
-      <c r="I136" s="21"/>
+      <c r="I136" s="22"/>
     </row>
     <row r="137">
-      <c r="C137" s="22"/>
+      <c r="C137" s="23"/>
       <c r="F137" s="9"/>
       <c r="G137" s="9"/>
       <c r="H137" s="14"/>
-      <c r="I137" s="21"/>
+      <c r="I137" s="22"/>
     </row>
     <row r="138">
-      <c r="C138" s="22"/>
+      <c r="C138" s="23"/>
       <c r="F138" s="9"/>
       <c r="G138" s="9"/>
       <c r="H138" s="14"/>
-      <c r="I138" s="21"/>
+      <c r="I138" s="22"/>
     </row>
     <row r="139">
-      <c r="C139" s="22"/>
+      <c r="C139" s="23"/>
       <c r="F139" s="9"/>
       <c r="G139" s="9"/>
       <c r="H139" s="14"/>
-      <c r="I139" s="21"/>
+      <c r="I139" s="22"/>
     </row>
     <row r="140">
-      <c r="C140" s="22"/>
+      <c r="C140" s="23"/>
       <c r="F140" s="9"/>
       <c r="G140" s="9"/>
       <c r="H140" s="14"/>
-      <c r="I140" s="21"/>
+      <c r="I140" s="22"/>
     </row>
     <row r="141">
-      <c r="C141" s="22"/>
+      <c r="C141" s="23"/>
       <c r="F141" s="9"/>
       <c r="G141" s="9"/>
       <c r="H141" s="14"/>
-      <c r="I141" s="21"/>
+      <c r="I141" s="22"/>
     </row>
     <row r="142">
-      <c r="C142" s="22"/>
+      <c r="C142" s="23"/>
       <c r="F142" s="9"/>
       <c r="G142" s="9"/>
       <c r="H142" s="14"/>
-      <c r="I142" s="21"/>
+      <c r="I142" s="22"/>
     </row>
     <row r="143">
-      <c r="C143" s="22"/>
+      <c r="C143" s="23"/>
       <c r="F143" s="9"/>
       <c r="G143" s="9"/>
       <c r="H143" s="14"/>
-      <c r="I143" s="21"/>
+      <c r="I143" s="22"/>
     </row>
     <row r="144">
-      <c r="C144" s="22"/>
+      <c r="C144" s="23"/>
       <c r="F144" s="9"/>
       <c r="G144" s="9"/>
       <c r="H144" s="14"/>
-      <c r="I144" s="21"/>
+      <c r="I144" s="22"/>
     </row>
     <row r="145">
-      <c r="C145" s="22"/>
+      <c r="C145" s="23"/>
       <c r="F145" s="9"/>
       <c r="G145" s="9"/>
       <c r="H145" s="14"/>
-      <c r="I145" s="21"/>
+      <c r="I145" s="22"/>
     </row>
     <row r="146">
-      <c r="C146" s="22"/>
+      <c r="C146" s="23"/>
       <c r="F146" s="9"/>
       <c r="G146" s="9"/>
       <c r="H146" s="14"/>
-      <c r="I146" s="21"/>
+      <c r="I146" s="22"/>
     </row>
     <row r="147">
-      <c r="C147" s="22"/>
+      <c r="C147" s="23"/>
       <c r="F147" s="9"/>
       <c r="G147" s="9"/>
       <c r="H147" s="14"/>
-      <c r="I147" s="21"/>
+      <c r="I147" s="22"/>
     </row>
     <row r="148">
-      <c r="C148" s="22"/>
+      <c r="C148" s="23"/>
       <c r="F148" s="9"/>
       <c r="G148" s="9"/>
       <c r="H148" s="14"/>
-      <c r="I148" s="21"/>
+      <c r="I148" s="22"/>
     </row>
     <row r="149">
-      <c r="C149" s="22"/>
+      <c r="C149" s="23"/>
       <c r="F149" s="9"/>
       <c r="G149" s="9"/>
       <c r="H149" s="14"/>
-      <c r="I149" s="21"/>
+      <c r="I149" s="22"/>
     </row>
     <row r="150">
-      <c r="C150" s="22"/>
+      <c r="C150" s="23"/>
       <c r="F150" s="9"/>
       <c r="G150" s="9"/>
       <c r="H150" s="14"/>
-      <c r="I150" s="21"/>
+      <c r="I150" s="22"/>
     </row>
     <row r="151">
-      <c r="C151" s="22"/>
+      <c r="C151" s="23"/>
       <c r="F151" s="9"/>
       <c r="G151" s="9"/>
       <c r="H151" s="14"/>
-      <c r="I151" s="21"/>
+      <c r="I151" s="22"/>
     </row>
     <row r="152">
-      <c r="C152" s="22"/>
+      <c r="C152" s="23"/>
       <c r="F152" s="9"/>
       <c r="G152" s="9"/>
       <c r="H152" s="14"/>
-      <c r="I152" s="21"/>
+      <c r="I152" s="22"/>
     </row>
     <row r="153">
-      <c r="C153" s="22"/>
+      <c r="C153" s="23"/>
       <c r="F153" s="9"/>
       <c r="G153" s="9"/>
       <c r="H153" s="14"/>
-      <c r="I153" s="21"/>
+      <c r="I153" s="22"/>
     </row>
     <row r="154">
-      <c r="C154" s="22"/>
+      <c r="C154" s="23"/>
       <c r="F154" s="9"/>
       <c r="G154" s="9"/>
       <c r="H154" s="14"/>
-      <c r="I154" s="21"/>
+      <c r="I154" s="22"/>
     </row>
     <row r="155">
-      <c r="C155" s="22"/>
+      <c r="C155" s="23"/>
       <c r="F155" s="9"/>
       <c r="G155" s="9"/>
       <c r="H155" s="14"/>
-      <c r="I155" s="21"/>
+      <c r="I155" s="22"/>
     </row>
     <row r="156">
-      <c r="C156" s="22"/>
+      <c r="C156" s="23"/>
       <c r="F156" s="9"/>
       <c r="G156" s="9"/>
       <c r="H156" s="14"/>
-      <c r="I156" s="21"/>
+      <c r="I156" s="22"/>
     </row>
     <row r="157">
-      <c r="C157" s="22"/>
+      <c r="C157" s="23"/>
       <c r="F157" s="9"/>
       <c r="G157" s="9"/>
       <c r="H157" s="14"/>
-      <c r="I157" s="21"/>
+      <c r="I157" s="22"/>
     </row>
     <row r="158">
-      <c r="C158" s="22"/>
+      <c r="C158" s="23"/>
       <c r="F158" s="9"/>
       <c r="G158" s="9"/>
       <c r="H158" s="14"/>
-      <c r="I158" s="21"/>
+      <c r="I158" s="22"/>
     </row>
     <row r="159">
-      <c r="C159" s="22"/>
+      <c r="C159" s="23"/>
       <c r="F159" s="9"/>
       <c r="G159" s="9"/>
       <c r="H159" s="14"/>
-      <c r="I159" s="21"/>
+      <c r="I159" s="22"/>
     </row>
     <row r="160">
-      <c r="C160" s="22"/>
+      <c r="C160" s="23"/>
       <c r="F160" s="9"/>
       <c r="G160" s="9"/>
       <c r="H160" s="14"/>
-      <c r="I160" s="21"/>
+      <c r="I160" s="22"/>
     </row>
     <row r="161">
-      <c r="C161" s="22"/>
+      <c r="C161" s="23"/>
       <c r="F161" s="9"/>
       <c r="G161" s="9"/>
       <c r="H161" s="14"/>
-      <c r="I161" s="21"/>
+      <c r="I161" s="22"/>
     </row>
     <row r="162">
-      <c r="C162" s="22"/>
+      <c r="C162" s="23"/>
       <c r="F162" s="9"/>
       <c r="G162" s="9"/>
       <c r="H162" s="14"/>
-      <c r="I162" s="21"/>
+      <c r="I162" s="22"/>
     </row>
     <row r="163">
-      <c r="C163" s="22"/>
+      <c r="C163" s="23"/>
       <c r="F163" s="9"/>
       <c r="G163" s="9"/>
       <c r="H163" s="14"/>
-      <c r="I163" s="21"/>
+      <c r="I163" s="22"/>
     </row>
     <row r="164">
-      <c r="C164" s="22"/>
+      <c r="C164" s="23"/>
       <c r="F164" s="9"/>
       <c r="G164" s="9"/>
       <c r="H164" s="14"/>
-      <c r="I164" s="21"/>
+      <c r="I164" s="22"/>
     </row>
     <row r="165">
-      <c r="C165" s="22"/>
+      <c r="C165" s="23"/>
       <c r="F165" s="9"/>
       <c r="G165" s="9"/>
       <c r="H165" s="14"/>
-      <c r="I165" s="21"/>
+      <c r="I165" s="22"/>
     </row>
     <row r="166">
-      <c r="C166" s="22"/>
+      <c r="C166" s="23"/>
       <c r="F166" s="9"/>
       <c r="G166" s="9"/>
       <c r="H166" s="14"/>
-      <c r="I166" s="21"/>
+      <c r="I166" s="22"/>
     </row>
     <row r="167">
-      <c r="C167" s="22"/>
+      <c r="C167" s="23"/>
       <c r="F167" s="9"/>
       <c r="G167" s="9"/>
       <c r="H167" s="14"/>
-      <c r="I167" s="21"/>
+      <c r="I167" s="22"/>
     </row>
     <row r="168">
-      <c r="C168" s="22"/>
+      <c r="C168" s="23"/>
       <c r="F168" s="9"/>
       <c r="G168" s="9"/>
       <c r="H168" s="14"/>
-      <c r="I168" s="21"/>
+      <c r="I168" s="22"/>
     </row>
     <row r="169">
-      <c r="C169" s="22"/>
+      <c r="C169" s="23"/>
       <c r="F169" s="9"/>
       <c r="G169" s="9"/>
       <c r="H169" s="14"/>
-      <c r="I169" s="21"/>
+      <c r="I169" s="22"/>
     </row>
     <row r="170">
-      <c r="C170" s="22"/>
+      <c r="C170" s="23"/>
       <c r="F170" s="9"/>
       <c r="G170" s="9"/>
       <c r="H170" s="14"/>
-      <c r="I170" s="21"/>
+      <c r="I170" s="22"/>
     </row>
     <row r="171">
-      <c r="C171" s="22"/>
+      <c r="C171" s="23"/>
       <c r="F171" s="9"/>
       <c r="G171" s="9"/>
       <c r="H171" s="14"/>
-      <c r="I171" s="21"/>
+      <c r="I171" s="22"/>
     </row>
     <row r="172">
-      <c r="C172" s="22"/>
+      <c r="C172" s="23"/>
       <c r="F172" s="9"/>
       <c r="G172" s="9"/>
       <c r="H172" s="14"/>
-      <c r="I172" s="21"/>
+      <c r="I172" s="22"/>
     </row>
     <row r="173">
-      <c r="C173" s="22"/>
+      <c r="C173" s="23"/>
       <c r="F173" s="9"/>
       <c r="G173" s="9"/>
       <c r="H173" s="14"/>
-      <c r="I173" s="21"/>
+      <c r="I173" s="22"/>
     </row>
     <row r="174">
-      <c r="C174" s="22"/>
+      <c r="C174" s="23"/>
       <c r="F174" s="9"/>
       <c r="G174" s="9"/>
       <c r="H174" s="14"/>
-      <c r="I174" s="21"/>
+      <c r="I174" s="22"/>
     </row>
     <row r="175">
-      <c r="C175" s="22"/>
+      <c r="C175" s="23"/>
       <c r="F175" s="9"/>
       <c r="G175" s="9"/>
       <c r="H175" s="14"/>
-      <c r="I175" s="21"/>
+      <c r="I175" s="22"/>
     </row>
     <row r="176">
-      <c r="C176" s="22"/>
+      <c r="C176" s="23"/>
       <c r="F176" s="9"/>
       <c r="G176" s="9"/>
       <c r="H176" s="14"/>
-      <c r="I176" s="21"/>
+      <c r="I176" s="22"/>
     </row>
     <row r="177">
-      <c r="C177" s="22"/>
+      <c r="C177" s="23"/>
       <c r="F177" s="9"/>
       <c r="G177" s="9"/>
       <c r="H177" s="14"/>
-      <c r="I177" s="21"/>
+      <c r="I177" s="22"/>
     </row>
     <row r="178">
-      <c r="C178" s="22"/>
+      <c r="C178" s="23"/>
       <c r="F178" s="9"/>
       <c r="G178" s="9"/>
       <c r="H178" s="14"/>
-      <c r="I178" s="21"/>
+      <c r="I178" s="22"/>
     </row>
     <row r="179">
-      <c r="C179" s="22"/>
+      <c r="C179" s="23"/>
       <c r="F179" s="9"/>
       <c r="G179" s="9"/>
       <c r="H179" s="14"/>
-      <c r="I179" s="21"/>
+      <c r="I179" s="22"/>
     </row>
     <row r="180">
-      <c r="C180" s="22"/>
+      <c r="C180" s="23"/>
       <c r="F180" s="9"/>
       <c r="G180" s="9"/>
       <c r="H180" s="14"/>
-      <c r="I180" s="21"/>
+      <c r="I180" s="22"/>
     </row>
     <row r="181">
-      <c r="C181" s="22"/>
+      <c r="C181" s="23"/>
       <c r="F181" s="9"/>
       <c r="G181" s="9"/>
       <c r="H181" s="14"/>
-      <c r="I181" s="21"/>
+      <c r="I181" s="22"/>
     </row>
     <row r="182">
-      <c r="C182" s="22"/>
+      <c r="C182" s="23"/>
       <c r="F182" s="9"/>
       <c r="G182" s="9"/>
       <c r="H182" s="14"/>
-      <c r="I182" s="21"/>
+      <c r="I182" s="22"/>
     </row>
     <row r="183">
-      <c r="C183" s="22"/>
+      <c r="C183" s="23"/>
       <c r="F183" s="9"/>
       <c r="G183" s="9"/>
       <c r="H183" s="14"/>
-      <c r="I183" s="21"/>
+      <c r="I183" s="22"/>
     </row>
     <row r="184">
-      <c r="C184" s="22"/>
+      <c r="C184" s="23"/>
       <c r="F184" s="9"/>
       <c r="G184" s="9"/>
       <c r="H184" s="14"/>
-      <c r="I184" s="21"/>
+      <c r="I184" s="22"/>
     </row>
     <row r="185">
-      <c r="C185" s="22"/>
+      <c r="C185" s="23"/>
       <c r="F185" s="9"/>
       <c r="G185" s="9"/>
       <c r="H185" s="14"/>
-      <c r="I185" s="21"/>
+      <c r="I185" s="22"/>
     </row>
     <row r="186">
-      <c r="C186" s="22"/>
+      <c r="C186" s="23"/>
       <c r="F186" s="9"/>
       <c r="G186" s="9"/>
       <c r="H186" s="14"/>
-      <c r="I186" s="21"/>
+      <c r="I186" s="22"/>
     </row>
     <row r="187">
-      <c r="C187" s="22"/>
+      <c r="C187" s="23"/>
       <c r="F187" s="9"/>
       <c r="G187" s="9"/>
       <c r="H187" s="14"/>
-      <c r="I187" s="21"/>
+      <c r="I187" s="22"/>
     </row>
     <row r="188">
-      <c r="C188" s="22"/>
+      <c r="C188" s="23"/>
       <c r="F188" s="9"/>
       <c r="G188" s="9"/>
       <c r="H188" s="14"/>
-      <c r="I188" s="21"/>
+      <c r="I188" s="22"/>
     </row>
     <row r="189">
-      <c r="C189" s="22"/>
+      <c r="C189" s="23"/>
       <c r="F189" s="9"/>
       <c r="G189" s="9"/>
       <c r="H189" s="14"/>
-      <c r="I189" s="21"/>
+      <c r="I189" s="22"/>
     </row>
     <row r="190">
-      <c r="C190" s="22"/>
+      <c r="C190" s="23"/>
       <c r="F190" s="9"/>
       <c r="G190" s="9"/>
       <c r="H190" s="14"/>
-      <c r="I190" s="21"/>
+      <c r="I190" s="22"/>
     </row>
     <row r="191">
-      <c r="C191" s="22"/>
+      <c r="C191" s="23"/>
       <c r="F191" s="9"/>
       <c r="G191" s="9"/>
       <c r="H191" s="14"/>
-      <c r="I191" s="21"/>
+      <c r="I191" s="22"/>
     </row>
     <row r="192">
-      <c r="C192" s="22"/>
+      <c r="C192" s="23"/>
       <c r="F192" s="9"/>
       <c r="G192" s="9"/>
       <c r="H192" s="14"/>
-      <c r="I192" s="21"/>
+      <c r="I192" s="22"/>
     </row>
     <row r="193">
-      <c r="C193" s="22"/>
+      <c r="C193" s="23"/>
       <c r="F193" s="9"/>
       <c r="G193" s="9"/>
       <c r="H193" s="14"/>
-      <c r="I193" s="21"/>
+      <c r="I193" s="22"/>
     </row>
     <row r="194">
-      <c r="C194" s="22"/>
+      <c r="C194" s="23"/>
       <c r="F194" s="9"/>
       <c r="G194" s="9"/>
       <c r="H194" s="14"/>
-      <c r="I194" s="21"/>
+      <c r="I194" s="22"/>
     </row>
     <row r="195">
-      <c r="C195" s="22"/>
+      <c r="C195" s="23"/>
       <c r="F195" s="9"/>
       <c r="G195" s="9"/>
       <c r="H195" s="14"/>
-      <c r="I195" s="21"/>
+      <c r="I195" s="22"/>
     </row>
     <row r="196">
-      <c r="C196" s="22"/>
+      <c r="C196" s="23"/>
       <c r="F196" s="9"/>
       <c r="G196" s="9"/>
       <c r="H196" s="14"/>
-      <c r="I196" s="21"/>
+      <c r="I196" s="22"/>
     </row>
     <row r="197">
-      <c r="C197" s="22"/>
+      <c r="C197" s="23"/>
       <c r="F197" s="9"/>
       <c r="G197" s="9"/>
       <c r="H197" s="14"/>
-      <c r="I197" s="21"/>
+      <c r="I197" s="22"/>
     </row>
     <row r="198">
-      <c r="C198" s="22"/>
+      <c r="C198" s="23"/>
       <c r="F198" s="9"/>
       <c r="G198" s="9"/>
       <c r="H198" s="14"/>
-      <c r="I198" s="21"/>
+      <c r="I198" s="22"/>
     </row>
     <row r="199">
-      <c r="C199" s="22"/>
+      <c r="C199" s="23"/>
       <c r="F199" s="9"/>
       <c r="G199" s="9"/>
       <c r="H199" s="14"/>
-      <c r="I199" s="21"/>
+      <c r="I199" s="22"/>
     </row>
     <row r="200">
-      <c r="C200" s="22"/>
+      <c r="C200" s="23"/>
       <c r="F200" s="9"/>
       <c r="G200" s="9"/>
       <c r="H200" s="14"/>
-      <c r="I200" s="21"/>
+      <c r="I200" s="22"/>
     </row>
     <row r="201">
-      <c r="C201" s="22"/>
+      <c r="C201" s="23"/>
       <c r="F201" s="9"/>
       <c r="G201" s="9"/>
       <c r="H201" s="14"/>
-      <c r="I201" s="21"/>
+      <c r="I201" s="22"/>
     </row>
     <row r="202">
-      <c r="C202" s="22"/>
+      <c r="C202" s="23"/>
       <c r="F202" s="9"/>
       <c r="G202" s="9"/>
       <c r="H202" s="14"/>
-      <c r="I202" s="21"/>
+      <c r="I202" s="22"/>
     </row>
     <row r="203">
-      <c r="C203" s="22"/>
+      <c r="C203" s="23"/>
       <c r="F203" s="9"/>
       <c r="G203" s="9"/>
       <c r="H203" s="14"/>
-      <c r="I203" s="21"/>
+      <c r="I203" s="22"/>
     </row>
     <row r="204">
-      <c r="C204" s="22"/>
+      <c r="C204" s="23"/>
       <c r="F204" s="9"/>
       <c r="G204" s="9"/>
       <c r="H204" s="14"/>
-      <c r="I204" s="21"/>
+      <c r="I204" s="22"/>
     </row>
     <row r="205">
-      <c r="C205" s="22"/>
+      <c r="C205" s="23"/>
       <c r="F205" s="9"/>
       <c r="G205" s="9"/>
       <c r="H205" s="14"/>
-      <c r="I205" s="21"/>
+      <c r="I205" s="22"/>
     </row>
     <row r="206">
-      <c r="C206" s="22"/>
+      <c r="C206" s="23"/>
       <c r="F206" s="9"/>
       <c r="G206" s="9"/>
       <c r="H206" s="14"/>
-      <c r="I206" s="21"/>
+      <c r="I206" s="22"/>
     </row>
     <row r="207">
-      <c r="C207" s="22"/>
+      <c r="C207" s="23"/>
       <c r="F207" s="9"/>
       <c r="G207" s="9"/>
       <c r="H207" s="14"/>
-      <c r="I207" s="21"/>
+      <c r="I207" s="22"/>
     </row>
     <row r="208">
-      <c r="C208" s="22"/>
+      <c r="C208" s="23"/>
       <c r="F208" s="9"/>
       <c r="G208" s="9"/>
       <c r="H208" s="14"/>
-      <c r="I208" s="21"/>
+      <c r="I208" s="22"/>
     </row>
     <row r="209">
-      <c r="C209" s="22"/>
+      <c r="C209" s="23"/>
       <c r="F209" s="9"/>
       <c r="G209" s="9"/>
       <c r="H209" s="14"/>
-      <c r="I209" s="21"/>
+      <c r="I209" s="22"/>
     </row>
     <row r="210">
-      <c r="C210" s="22"/>
+      <c r="C210" s="23"/>
       <c r="F210" s="9"/>
       <c r="G210" s="9"/>
       <c r="H210" s="14"/>
-      <c r="I210" s="21"/>
+      <c r="I210" s="22"/>
     </row>
     <row r="211">
-      <c r="C211" s="22"/>
+      <c r="C211" s="23"/>
       <c r="F211" s="9"/>
       <c r="G211" s="9"/>
       <c r="H211" s="14"/>
-      <c r="I211" s="21"/>
+      <c r="I211" s="22"/>
     </row>
     <row r="212">
-      <c r="C212" s="22"/>
+      <c r="C212" s="23"/>
       <c r="F212" s="9"/>
       <c r="G212" s="9"/>
       <c r="H212" s="14"/>
-      <c r="I212" s="21"/>
+      <c r="I212" s="22"/>
     </row>
     <row r="213">
-      <c r="C213" s="22"/>
+      <c r="C213" s="23"/>
       <c r="F213" s="9"/>
       <c r="G213" s="9"/>
       <c r="H213" s="14"/>
-      <c r="I213" s="21"/>
+      <c r="I213" s="22"/>
     </row>
     <row r="214">
-      <c r="C214" s="22"/>
+      <c r="C214" s="23"/>
       <c r="F214" s="9"/>
       <c r="G214" s="9"/>
       <c r="H214" s="14"/>
-      <c r="I214" s="21"/>
+      <c r="I214" s="22"/>
     </row>
     <row r="215">
-      <c r="C215" s="22"/>
+      <c r="C215" s="23"/>
       <c r="F215" s="9"/>
       <c r="G215" s="9"/>
       <c r="H215" s="14"/>
-      <c r="I215" s="21"/>
+      <c r="I215" s="22"/>
     </row>
     <row r="216">
-      <c r="C216" s="22"/>
+      <c r="C216" s="23"/>
       <c r="F216" s="9"/>
       <c r="G216" s="9"/>
       <c r="H216" s="14"/>
-      <c r="I216" s="21"/>
+      <c r="I216" s="22"/>
     </row>
     <row r="217">
-      <c r="C217" s="22"/>
+      <c r="C217" s="23"/>
       <c r="F217" s="9"/>
       <c r="G217" s="9"/>
       <c r="H217" s="14"/>
-      <c r="I217" s="21"/>
+      <c r="I217" s="22"/>
     </row>
     <row r="218">
-      <c r="C218" s="22"/>
+      <c r="C218" s="23"/>
       <c r="F218" s="9"/>
       <c r="G218" s="9"/>
       <c r="H218" s="14"/>
-      <c r="I218" s="21"/>
+      <c r="I218" s="22"/>
     </row>
     <row r="219">
-      <c r="C219" s="22"/>
+      <c r="C219" s="23"/>
       <c r="F219" s="9"/>
       <c r="G219" s="9"/>
       <c r="H219" s="14"/>
-      <c r="I219" s="21"/>
+      <c r="I219" s="22"/>
     </row>
     <row r="220">
-      <c r="C220" s="22"/>
+      <c r="C220" s="23"/>
       <c r="F220" s="9"/>
       <c r="G220" s="9"/>
       <c r="H220" s="14"/>
-      <c r="I220" s="21"/>
+      <c r="I220" s="22"/>
     </row>
     <row r="221">
-      <c r="C221" s="22"/>
+      <c r="C221" s="23"/>
       <c r="F221" s="9"/>
       <c r="G221" s="9"/>
       <c r="H221" s="14"/>
-      <c r="I221" s="21"/>
+      <c r="I221" s="22"/>
     </row>
     <row r="222">
-      <c r="C222" s="22"/>
+      <c r="C222" s="23"/>
       <c r="F222" s="9"/>
       <c r="G222" s="9"/>
       <c r="H222" s="14"/>
-      <c r="I222" s="21"/>
+      <c r="I222" s="22"/>
     </row>
     <row r="223">
-      <c r="C223" s="22"/>
+      <c r="C223" s="23"/>
       <c r="F223" s="9"/>
       <c r="G223" s="9"/>
       <c r="H223" s="14"/>
-      <c r="I223" s="21"/>
+      <c r="I223" s="22"/>
     </row>
     <row r="224">
-      <c r="C224" s="22"/>
+      <c r="C224" s="23"/>
       <c r="F224" s="9"/>
       <c r="G224" s="9"/>
       <c r="H224" s="14"/>
-      <c r="I224" s="21"/>
+      <c r="I224" s="22"/>
     </row>
     <row r="225">
-      <c r="C225" s="22"/>
+      <c r="C225" s="23"/>
       <c r="F225" s="9"/>
       <c r="G225" s="9"/>
       <c r="H225" s="14"/>
-      <c r="I225" s="21"/>
+      <c r="I225" s="22"/>
     </row>
     <row r="226">
-      <c r="C226" s="22"/>
+      <c r="C226" s="23"/>
       <c r="F226" s="9"/>
       <c r="G226" s="9"/>
       <c r="H226" s="14"/>
-      <c r="I226" s="21"/>
+      <c r="I226" s="22"/>
     </row>
     <row r="227">
-      <c r="C227" s="22"/>
+      <c r="C227" s="23"/>
       <c r="F227" s="9"/>
       <c r="G227" s="9"/>
       <c r="H227" s="14"/>
-      <c r="I227" s="21"/>
+      <c r="I227" s="22"/>
     </row>
     <row r="228">
-      <c r="C228" s="22"/>
+      <c r="C228" s="23"/>
       <c r="F228" s="9"/>
       <c r="G228" s="9"/>
       <c r="H228" s="14"/>
-      <c r="I228" s="21"/>
+      <c r="I228" s="22"/>
     </row>
     <row r="229">
-      <c r="C229" s="22"/>
+      <c r="C229" s="23"/>
       <c r="F229" s="9"/>
       <c r="G229" s="9"/>
       <c r="H229" s="14"/>
-      <c r="I229" s="21"/>
+      <c r="I229" s="22"/>
     </row>
     <row r="230">
-      <c r="C230" s="22"/>
+      <c r="C230" s="23"/>
       <c r="F230" s="9"/>
       <c r="G230" s="9"/>
       <c r="H230" s="14"/>
-      <c r="I230" s="21"/>
+      <c r="I230" s="22"/>
     </row>
     <row r="231">
-      <c r="C231" s="22"/>
+      <c r="C231" s="23"/>
       <c r="F231" s="9"/>
       <c r="G231" s="9"/>
       <c r="H231" s="14"/>
-      <c r="I231" s="21"/>
+      <c r="I231" s="22"/>
     </row>
     <row r="232">
-      <c r="C232" s="22"/>
+      <c r="C232" s="23"/>
       <c r="F232" s="9"/>
       <c r="G232" s="9"/>
       <c r="H232" s="14"/>
-      <c r="I232" s="21"/>
+      <c r="I232" s="22"/>
     </row>
     <row r="233">
-      <c r="C233" s="22"/>
+      <c r="C233" s="23"/>
       <c r="F233" s="9"/>
       <c r="G233" s="9"/>
       <c r="H233" s="14"/>
-      <c r="I233" s="21"/>
+      <c r="I233" s="22"/>
     </row>
     <row r="234">
-      <c r="C234" s="22"/>
+      <c r="C234" s="23"/>
       <c r="F234" s="9"/>
       <c r="G234" s="9"/>
       <c r="H234" s="14"/>
-      <c r="I234" s="21"/>
+      <c r="I234" s="22"/>
     </row>
     <row r="235">
-      <c r="C235" s="22"/>
+      <c r="C235" s="23"/>
       <c r="F235" s="9"/>
       <c r="G235" s="9"/>
       <c r="H235" s="14"/>
-      <c r="I235" s="21"/>
+      <c r="I235" s="22"/>
     </row>
     <row r="236">
-      <c r="C236" s="22"/>
+      <c r="C236" s="23"/>
       <c r="F236" s="9"/>
       <c r="G236" s="9"/>
       <c r="H236" s="14"/>
-      <c r="I236" s="21"/>
+      <c r="I236" s="22"/>
     </row>
     <row r="237">
-      <c r="C237" s="22"/>
+      <c r="C237" s="23"/>
       <c r="F237" s="9"/>
       <c r="G237" s="9"/>
       <c r="H237" s="14"/>
-      <c r="I237" s="21"/>
+      <c r="I237" s="22"/>
     </row>
     <row r="238">
-      <c r="C238" s="22"/>
+      <c r="C238" s="23"/>
       <c r="F238" s="9"/>
       <c r="G238" s="9"/>
       <c r="H238" s="14"/>
-      <c r="I238" s="21"/>
+      <c r="I238" s="22"/>
     </row>
     <row r="239">
-      <c r="C239" s="22"/>
+      <c r="C239" s="23"/>
       <c r="F239" s="9"/>
       <c r="G239" s="9"/>
       <c r="H239" s="14"/>
-      <c r="I239" s="21"/>
+      <c r="I239" s="22"/>
     </row>
     <row r="240">
-      <c r="C240" s="22"/>
+      <c r="C240" s="23"/>
       <c r="F240" s="9"/>
       <c r="G240" s="9"/>
       <c r="H240" s="14"/>
-      <c r="I240" s="21"/>
+      <c r="I240" s="22"/>
     </row>
     <row r="241">
-      <c r="C241" s="22"/>
+      <c r="C241" s="23"/>
       <c r="F241" s="9"/>
       <c r="G241" s="9"/>
       <c r="H241" s="14"/>
-      <c r="I241" s="21"/>
+      <c r="I241" s="22"/>
     </row>
     <row r="242">
-      <c r="C242" s="22"/>
+      <c r="C242" s="23"/>
       <c r="F242" s="9"/>
       <c r="G242" s="9"/>
       <c r="H242" s="14"/>
-      <c r="I242" s="21"/>
+      <c r="I242" s="22"/>
     </row>
     <row r="243">
-      <c r="C243" s="22"/>
+      <c r="C243" s="23"/>
       <c r="F243" s="9"/>
       <c r="G243" s="9"/>
       <c r="H243" s="14"/>
-      <c r="I243" s="21"/>
+      <c r="I243" s="22"/>
     </row>
     <row r="244">
-      <c r="C244" s="22"/>
+      <c r="C244" s="23"/>
       <c r="F244" s="9"/>
       <c r="G244" s="9"/>
       <c r="H244" s="14"/>
-      <c r="I244" s="21"/>
+      <c r="I244" s="22"/>
     </row>
     <row r="245">
-      <c r="C245" s="22"/>
+      <c r="C245" s="23"/>
       <c r="F245" s="9"/>
       <c r="G245" s="9"/>
       <c r="H245" s="14"/>
-      <c r="I245" s="21"/>
+      <c r="I245" s="22"/>
     </row>
     <row r="246">
-      <c r="C246" s="22"/>
+      <c r="C246" s="23"/>
       <c r="F246" s="9"/>
       <c r="G246" s="9"/>
       <c r="H246" s="14"/>
-      <c r="I246" s="21"/>
+      <c r="I246" s="22"/>
     </row>
     <row r="247">
-      <c r="C247" s="22"/>
+      <c r="C247" s="23"/>
       <c r="F247" s="9"/>
       <c r="G247" s="9"/>
       <c r="H247" s="14"/>
-      <c r="I247" s="21"/>
+      <c r="I247" s="22"/>
     </row>
     <row r="248">
-      <c r="C248" s="22"/>
+      <c r="C248" s="23"/>
       <c r="F248" s="9"/>
       <c r="G248" s="9"/>
       <c r="H248" s="14"/>
-      <c r="I248" s="21"/>
+      <c r="I248" s="22"/>
     </row>
     <row r="249">
-      <c r="C249" s="22"/>
+      <c r="C249" s="23"/>
       <c r="F249" s="9"/>
       <c r="G249" s="9"/>
       <c r="H249" s="14"/>
-      <c r="I249" s="21"/>
+      <c r="I249" s="22"/>
     </row>
     <row r="250">
-      <c r="C250" s="22"/>
+      <c r="C250" s="23"/>
       <c r="F250" s="9"/>
       <c r="G250" s="9"/>
       <c r="H250" s="14"/>
-      <c r="I250" s="21"/>
+      <c r="I250" s="22"/>
     </row>
     <row r="251">
-      <c r="C251" s="22"/>
+      <c r="C251" s="23"/>
       <c r="F251" s="9"/>
       <c r="G251" s="9"/>
       <c r="H251" s="14"/>
-      <c r="I251" s="21"/>
+      <c r="I251" s="22"/>
     </row>
     <row r="252">
-      <c r="C252" s="22"/>
+      <c r="C252" s="23"/>
       <c r="F252" s="9"/>
       <c r="G252" s="9"/>
       <c r="H252" s="14"/>
-      <c r="I252" s="21"/>
+      <c r="I252" s="22"/>
     </row>
     <row r="253">
-      <c r="C253" s="22"/>
+      <c r="C253" s="23"/>
       <c r="F253" s="9"/>
       <c r="G253" s="9"/>
       <c r="H253" s="14"/>
-      <c r="I253" s="21"/>
+      <c r="I253" s="22"/>
     </row>
     <row r="254">
-      <c r="C254" s="22"/>
+      <c r="C254" s="23"/>
       <c r="F254" s="9"/>
       <c r="G254" s="9"/>
       <c r="H254" s="14"/>
-      <c r="I254" s="21"/>
+      <c r="I254" s="22"/>
     </row>
     <row r="255">
-      <c r="C255" s="22"/>
+      <c r="C255" s="23"/>
       <c r="F255" s="9"/>
       <c r="G255" s="9"/>
       <c r="H255" s="14"/>
-      <c r="I255" s="21"/>
+      <c r="I255" s="22"/>
     </row>
     <row r="256">
-      <c r="C256" s="22"/>
+      <c r="C256" s="23"/>
       <c r="F256" s="9"/>
       <c r="G256" s="9"/>
       <c r="H256" s="14"/>
-      <c r="I256" s="21"/>
+      <c r="I256" s="22"/>
     </row>
     <row r="257">
-      <c r="C257" s="22"/>
+      <c r="C257" s="23"/>
       <c r="F257" s="9"/>
       <c r="G257" s="9"/>
       <c r="H257" s="14"/>
-      <c r="I257" s="21"/>
+      <c r="I257" s="22"/>
     </row>
     <row r="258">
-      <c r="C258" s="22"/>
+      <c r="C258" s="23"/>
       <c r="F258" s="9"/>
       <c r="G258" s="9"/>
       <c r="H258" s="14"/>
-      <c r="I258" s="21"/>
+      <c r="I258" s="22"/>
     </row>
     <row r="259">
-      <c r="C259" s="22"/>
+      <c r="C259" s="23"/>
       <c r="F259" s="9"/>
       <c r="G259" s="9"/>
       <c r="H259" s="14"/>
-      <c r="I259" s="21"/>
+      <c r="I259" s="22"/>
     </row>
     <row r="260">
-      <c r="C260" s="22"/>
+      <c r="C260" s="23"/>
       <c r="F260" s="9"/>
       <c r="G260" s="9"/>
       <c r="H260" s="14"/>
-      <c r="I260" s="21"/>
+      <c r="I260" s="22"/>
     </row>
     <row r="261">
-      <c r="C261" s="22"/>
+      <c r="C261" s="23"/>
       <c r="F261" s="9"/>
       <c r="G261" s="9"/>
       <c r="H261" s="14"/>
-      <c r="I261" s="21"/>
+      <c r="I261" s="22"/>
     </row>
     <row r="262">
-      <c r="C262" s="22"/>
+      <c r="C262" s="23"/>
       <c r="F262" s="9"/>
       <c r="G262" s="9"/>
       <c r="H262" s="14"/>
-      <c r="I262" s="21"/>
+      <c r="I262" s="22"/>
     </row>
     <row r="263">
-      <c r="C263" s="22"/>
+      <c r="C263" s="23"/>
       <c r="F263" s="9"/>
       <c r="G263" s="9"/>
       <c r="H263" s="14"/>
-      <c r="I263" s="21"/>
+      <c r="I263" s="22"/>
     </row>
     <row r="264">
-      <c r="C264" s="22"/>
+      <c r="C264" s="23"/>
       <c r="F264" s="9"/>
       <c r="G264" s="9"/>
       <c r="H264" s="14"/>
-      <c r="I264" s="21"/>
+      <c r="I264" s="22"/>
     </row>
     <row r="265">
-      <c r="C265" s="22"/>
+      <c r="C265" s="23"/>
       <c r="F265" s="9"/>
       <c r="G265" s="9"/>
       <c r="H265" s="14"/>
-      <c r="I265" s="21"/>
+      <c r="I265" s="22"/>
     </row>
     <row r="266">
-      <c r="C266" s="22"/>
+      <c r="C266" s="23"/>
       <c r="F266" s="9"/>
       <c r="G266" s="9"/>
       <c r="H266" s="14"/>
-      <c r="I266" s="21"/>
+      <c r="I266" s="22"/>
     </row>
     <row r="267">
-      <c r="C267" s="22"/>
+      <c r="C267" s="23"/>
       <c r="F267" s="9"/>
       <c r="G267" s="9"/>
       <c r="H267" s="14"/>
-      <c r="I267" s="21"/>
+      <c r="I267" s="22"/>
     </row>
     <row r="268">
-      <c r="C268" s="22"/>
+      <c r="C268" s="23"/>
       <c r="F268" s="9"/>
       <c r="G268" s="9"/>
       <c r="H268" s="14"/>
-      <c r="I268" s="21"/>
+      <c r="I268" s="22"/>
     </row>
     <row r="269">
-      <c r="C269" s="22"/>
+      <c r="C269" s="23"/>
       <c r="F269" s="9"/>
       <c r="G269" s="9"/>
       <c r="H269" s="14"/>
-      <c r="I269" s="21"/>
+      <c r="I269" s="22"/>
     </row>
     <row r="270">
-      <c r="C270" s="22"/>
+      <c r="C270" s="23"/>
       <c r="F270" s="9"/>
       <c r="G270" s="9"/>
       <c r="H270" s="14"/>
-      <c r="I270" s="21"/>
+      <c r="I270" s="22"/>
     </row>
     <row r="271">
-      <c r="C271" s="22"/>
+      <c r="C271" s="23"/>
       <c r="F271" s="9"/>
       <c r="G271" s="9"/>
       <c r="H271" s="14"/>
-      <c r="I271" s="21"/>
+      <c r="I271" s="22"/>
     </row>
     <row r="272">
-      <c r="C272" s="22"/>
+      <c r="C272" s="23"/>
       <c r="F272" s="9"/>
       <c r="G272" s="9"/>
       <c r="H272" s="14"/>
-      <c r="I272" s="21"/>
+      <c r="I272" s="22"/>
     </row>
     <row r="273">
-      <c r="C273" s="22"/>
+      <c r="C273" s="23"/>
       <c r="F273" s="9"/>
       <c r="G273" s="9"/>
       <c r="H273" s="14"/>
-      <c r="I273" s="21"/>
+      <c r="I273" s="22"/>
     </row>
     <row r="274">
-      <c r="C274" s="22"/>
+      <c r="C274" s="23"/>
       <c r="F274" s="9"/>
       <c r="G274" s="9"/>
       <c r="H274" s="14"/>
-      <c r="I274" s="21"/>
+      <c r="I274" s="22"/>
     </row>
     <row r="275">
-      <c r="C275" s="22"/>
+      <c r="C275" s="23"/>
       <c r="F275" s="9"/>
       <c r="G275" s="9"/>
       <c r="H275" s="14"/>
-      <c r="I275" s="21"/>
+      <c r="I275" s="22"/>
     </row>
     <row r="276">
-      <c r="C276" s="22"/>
+      <c r="C276" s="23"/>
       <c r="F276" s="9"/>
       <c r="G276" s="9"/>
       <c r="H276" s="14"/>
-      <c r="I276" s="21"/>
+      <c r="I276" s="22"/>
     </row>
     <row r="277">
-      <c r="C277" s="22"/>
+      <c r="C277" s="23"/>
       <c r="F277" s="9"/>
       <c r="G277" s="9"/>
       <c r="H277" s="14"/>
-      <c r="I277" s="21"/>
+      <c r="I277" s="22"/>
     </row>
     <row r="278">
-      <c r="C278" s="22"/>
+      <c r="C278" s="23"/>
       <c r="F278" s="9"/>
       <c r="G278" s="9"/>
       <c r="H278" s="14"/>
-      <c r="I278" s="21"/>
+      <c r="I278" s="22"/>
     </row>
     <row r="279">
-      <c r="C279" s="22"/>
+      <c r="C279" s="23"/>
       <c r="F279" s="9"/>
       <c r="G279" s="9"/>
       <c r="H279" s="14"/>
-      <c r="I279" s="21"/>
+      <c r="I279" s="22"/>
     </row>
     <row r="280">
-      <c r="C280" s="22"/>
+      <c r="C280" s="23"/>
       <c r="F280" s="9"/>
       <c r="G280" s="9"/>
       <c r="H280" s="14"/>
-      <c r="I280" s="21"/>
+      <c r="I280" s="22"/>
     </row>
     <row r="281">
-      <c r="C281" s="22"/>
+      <c r="C281" s="23"/>
       <c r="F281" s="9"/>
       <c r="G281" s="9"/>
       <c r="H281" s="14"/>
-      <c r="I281" s="21"/>
+      <c r="I281" s="22"/>
     </row>
     <row r="282">
-      <c r="C282" s="22"/>
+      <c r="C282" s="23"/>
       <c r="F282" s="9"/>
       <c r="G282" s="9"/>
       <c r="H282" s="14"/>
-      <c r="I282" s="21"/>
+      <c r="I282" s="22"/>
     </row>
     <row r="283">
-      <c r="C283" s="22"/>
+      <c r="C283" s="23"/>
       <c r="F283" s="9"/>
       <c r="G283" s="9"/>
       <c r="H283" s="14"/>
-      <c r="I283" s="21"/>
+      <c r="I283" s="22"/>
     </row>
     <row r="284">
-      <c r="C284" s="22"/>
+      <c r="C284" s="23"/>
       <c r="F284" s="9"/>
       <c r="G284" s="9"/>
       <c r="H284" s="14"/>
-      <c r="I284" s="21"/>
+      <c r="I284" s="22"/>
     </row>
     <row r="285">
-      <c r="C285" s="22"/>
+      <c r="C285" s="23"/>
       <c r="F285" s="9"/>
       <c r="G285" s="9"/>
       <c r="H285" s="14"/>
-      <c r="I285" s="21"/>
+      <c r="I285" s="22"/>
     </row>
     <row r="286">
-      <c r="C286" s="22"/>
+      <c r="C286" s="23"/>
       <c r="F286" s="9"/>
       <c r="G286" s="9"/>
       <c r="H286" s="14"/>
-      <c r="I286" s="21"/>
+      <c r="I286" s="22"/>
     </row>
     <row r="287">
-      <c r="C287" s="22"/>
+      <c r="C287" s="23"/>
       <c r="F287" s="9"/>
       <c r="G287" s="9"/>
       <c r="H287" s="14"/>
-      <c r="I287" s="21"/>
+      <c r="I287" s="22"/>
     </row>
     <row r="288">
-      <c r="C288" s="22"/>
+      <c r="C288" s="23"/>
       <c r="F288" s="9"/>
       <c r="G288" s="9"/>
       <c r="H288" s="14"/>
-      <c r="I288" s="21"/>
+      <c r="I288" s="22"/>
     </row>
     <row r="289">
-      <c r="C289" s="22"/>
+      <c r="C289" s="23"/>
       <c r="F289" s="9"/>
       <c r="G289" s="9"/>
       <c r="H289" s="14"/>
-      <c r="I289" s="21"/>
+      <c r="I289" s="22"/>
     </row>
     <row r="290">
-      <c r="C290" s="22"/>
+      <c r="C290" s="23"/>
       <c r="F290" s="9"/>
       <c r="G290" s="9"/>
       <c r="H290" s="14"/>
-      <c r="I290" s="21"/>
+      <c r="I290" s="22"/>
     </row>
     <row r="291">
-      <c r="C291" s="22"/>
+      <c r="C291" s="23"/>
       <c r="F291" s="9"/>
       <c r="G291" s="9"/>
       <c r="H291" s="14"/>
-      <c r="I291" s="21"/>
+      <c r="I291" s="22"/>
     </row>
     <row r="292">
-      <c r="C292" s="22"/>
+      <c r="C292" s="23"/>
       <c r="F292" s="9"/>
       <c r="G292" s="9"/>
       <c r="H292" s="14"/>
-      <c r="I292" s="21"/>
+      <c r="I292" s="22"/>
     </row>
     <row r="293">
-      <c r="C293" s="22"/>
+      <c r="C293" s="23"/>
       <c r="F293" s="9"/>
       <c r="G293" s="9"/>
       <c r="H293" s="14"/>
-      <c r="I293" s="21"/>
+      <c r="I293" s="22"/>
     </row>
     <row r="294">
-      <c r="C294" s="22"/>
+      <c r="C294" s="23"/>
       <c r="F294" s="9"/>
       <c r="G294" s="9"/>
       <c r="H294" s="14"/>
-      <c r="I294" s="21"/>
+      <c r="I294" s="22"/>
     </row>
     <row r="295">
-      <c r="C295" s="22"/>
+      <c r="C295" s="23"/>
       <c r="F295" s="9"/>
       <c r="G295" s="9"/>
       <c r="H295" s="14"/>
-      <c r="I295" s="21"/>
+      <c r="I295" s="22"/>
     </row>
     <row r="296">
-      <c r="C296" s="22"/>
+      <c r="C296" s="23"/>
       <c r="F296" s="9"/>
       <c r="G296" s="9"/>
       <c r="H296" s="14"/>
-      <c r="I296" s="21"/>
+      <c r="I296" s="22"/>
     </row>
     <row r="297">
-      <c r="C297" s="22"/>
+      <c r="C297" s="23"/>
       <c r="F297" s="9"/>
       <c r="G297" s="9"/>
       <c r="H297" s="14"/>
-      <c r="I297" s="21"/>
+      <c r="I297" s="22"/>
     </row>
     <row r="298">
-      <c r="C298" s="22"/>
+      <c r="C298" s="23"/>
       <c r="F298" s="9"/>
       <c r="G298" s="9"/>
       <c r="H298" s="14"/>
-      <c r="I298" s="21"/>
+      <c r="I298" s="22"/>
     </row>
     <row r="299">
-      <c r="C299" s="22"/>
+      <c r="C299" s="23"/>
       <c r="F299" s="9"/>
       <c r="G299" s="9"/>
       <c r="H299" s="14"/>
-      <c r="I299" s="21"/>
+      <c r="I299" s="22"/>
     </row>
     <row r="300">
-      <c r="C300" s="22"/>
+      <c r="C300" s="23"/>
       <c r="F300" s="9"/>
       <c r="G300" s="9"/>
       <c r="H300" s="14"/>
-      <c r="I300" s="21"/>
+      <c r="I300" s="22"/>
     </row>
     <row r="301">
-      <c r="C301" s="22"/>
+      <c r="C301" s="23"/>
       <c r="F301" s="9"/>
       <c r="G301" s="9"/>
       <c r="H301" s="14"/>
-      <c r="I301" s="21"/>
+      <c r="I301" s="22"/>
     </row>
     <row r="302">
-      <c r="C302" s="22"/>
+      <c r="C302" s="23"/>
       <c r="F302" s="9"/>
       <c r="G302" s="9"/>
       <c r="H302" s="14"/>
-      <c r="I302" s="21"/>
+      <c r="I302" s="22"/>
     </row>
     <row r="303">
-      <c r="C303" s="22"/>
+      <c r="C303" s="23"/>
       <c r="F303" s="9"/>
       <c r="G303" s="9"/>
       <c r="H303" s="14"/>
-      <c r="I303" s="21"/>
+      <c r="I303" s="22"/>
     </row>
     <row r="304">
-      <c r="C304" s="22"/>
+      <c r="C304" s="23"/>
       <c r="F304" s="9"/>
       <c r="G304" s="9"/>
       <c r="H304" s="14"/>
-      <c r="I304" s="21"/>
+      <c r="I304" s="22"/>
     </row>
     <row r="305">
-      <c r="C305" s="22"/>
+      <c r="C305" s="23"/>
       <c r="F305" s="9"/>
       <c r="G305" s="9"/>
       <c r="H305" s="14"/>
-      <c r="I305" s="21"/>
+      <c r="I305" s="22"/>
     </row>
     <row r="306">
-      <c r="C306" s="22"/>
+      <c r="C306" s="23"/>
       <c r="F306" s="9"/>
       <c r="G306" s="9"/>
       <c r="H306" s="14"/>
-      <c r="I306" s="21"/>
+      <c r="I306" s="22"/>
     </row>
     <row r="307">
-      <c r="C307" s="22"/>
+      <c r="C307" s="23"/>
       <c r="F307" s="9"/>
       <c r="G307" s="9"/>
       <c r="H307" s="14"/>
-      <c r="I307" s="21"/>
+      <c r="I307" s="22"/>
     </row>
     <row r="308">
-      <c r="C308" s="22"/>
+      <c r="C308" s="23"/>
       <c r="F308" s="9"/>
       <c r="G308" s="9"/>
       <c r="H308" s="14"/>
-      <c r="I308" s="21"/>
+      <c r="I308" s="22"/>
     </row>
     <row r="309">
-      <c r="C309" s="22"/>
+      <c r="C309" s="23"/>
       <c r="F309" s="9"/>
       <c r="G309" s="9"/>
       <c r="H309" s="14"/>
-      <c r="I309" s="21"/>
+      <c r="I309" s="22"/>
     </row>
     <row r="310">
-      <c r="C310" s="22"/>
+      <c r="C310" s="23"/>
       <c r="F310" s="9"/>
       <c r="G310" s="9"/>
       <c r="H310" s="14"/>
-      <c r="I310" s="21"/>
+      <c r="I310" s="22"/>
     </row>
     <row r="311">
-      <c r="C311" s="22"/>
+      <c r="C311" s="23"/>
       <c r="F311" s="9"/>
       <c r="G311" s="9"/>
       <c r="H311" s="14"/>
-      <c r="I311" s="21"/>
+      <c r="I311" s="22"/>
     </row>
     <row r="312">
-      <c r="C312" s="22"/>
+      <c r="C312" s="23"/>
       <c r="F312" s="9"/>
       <c r="G312" s="9"/>
       <c r="H312" s="14"/>
-      <c r="I312" s="21"/>
+      <c r="I312" s="22"/>
     </row>
     <row r="313">
-      <c r="C313" s="22"/>
+      <c r="C313" s="23"/>
       <c r="F313" s="9"/>
       <c r="G313" s="9"/>
       <c r="H313" s="14"/>
-      <c r="I313" s="21"/>
+      <c r="I313" s="22"/>
     </row>
     <row r="314">
-      <c r="C314" s="22"/>
+      <c r="C314" s="23"/>
       <c r="F314" s="9"/>
       <c r="G314" s="9"/>
       <c r="H314" s="14"/>
-      <c r="I314" s="21"/>
+      <c r="I314" s="22"/>
     </row>
     <row r="315">
-      <c r="C315" s="22"/>
+      <c r="C315" s="23"/>
       <c r="F315" s="9"/>
       <c r="G315" s="9"/>
       <c r="H315" s="14"/>
-      <c r="I315" s="21"/>
+      <c r="I315" s="22"/>
     </row>
     <row r="316">
-      <c r="C316" s="22"/>
+      <c r="C316" s="23"/>
       <c r="F316" s="9"/>
       <c r="G316" s="9"/>
       <c r="H316" s="14"/>
-      <c r="I316" s="21"/>
+      <c r="I316" s="22"/>
     </row>
     <row r="317">
-      <c r="C317" s="22"/>
+      <c r="C317" s="23"/>
       <c r="F317" s="9"/>
       <c r="G317" s="9"/>
       <c r="H317" s="14"/>
-      <c r="I317" s="21"/>
+      <c r="I317" s="22"/>
     </row>
     <row r="318">
-      <c r="C318" s="22"/>
+      <c r="C318" s="23"/>
       <c r="F318" s="9"/>
       <c r="G318" s="9"/>
       <c r="H318" s="14"/>
-      <c r="I318" s="21"/>
+      <c r="I318" s="22"/>
     </row>
     <row r="319">
-      <c r="C319" s="22"/>
+      <c r="C319" s="23"/>
       <c r="F319" s="9"/>
       <c r="G319" s="9"/>
       <c r="H319" s="14"/>
-      <c r="I319" s="21"/>
+      <c r="I319" s="22"/>
     </row>
     <row r="320">
-      <c r="C320" s="22"/>
+      <c r="C320" s="23"/>
       <c r="F320" s="9"/>
       <c r="G320" s="9"/>
       <c r="H320" s="14"/>
-      <c r="I320" s="21"/>
+      <c r="I320" s="22"/>
     </row>
     <row r="321">
-      <c r="C321" s="22"/>
+      <c r="C321" s="23"/>
       <c r="F321" s="9"/>
       <c r="G321" s="9"/>
       <c r="H321" s="14"/>
-      <c r="I321" s="21"/>
+      <c r="I321" s="22"/>
     </row>
     <row r="322">
-      <c r="C322" s="22"/>
+      <c r="C322" s="23"/>
       <c r="F322" s="9"/>
       <c r="G322" s="9"/>
       <c r="H322" s="14"/>
-      <c r="I322" s="21"/>
+      <c r="I322" s="22"/>
     </row>
     <row r="323">
-      <c r="C323" s="22"/>
+      <c r="C323" s="23"/>
       <c r="F323" s="9"/>
       <c r="G323" s="9"/>
       <c r="H323" s="14"/>
-      <c r="I323" s="21"/>
+      <c r="I323" s="22"/>
     </row>
     <row r="324">
-      <c r="C324" s="22"/>
+      <c r="C324" s="23"/>
       <c r="F324" s="9"/>
       <c r="G324" s="9"/>
       <c r="H324" s="14"/>
-      <c r="I324" s="21"/>
+      <c r="I324" s="22"/>
     </row>
     <row r="325">
-      <c r="C325" s="22"/>
+      <c r="C325" s="23"/>
       <c r="F325" s="9"/>
       <c r="G325" s="9"/>
       <c r="H325" s="14"/>
-      <c r="I325" s="21"/>
+      <c r="I325" s="22"/>
     </row>
     <row r="326">
-      <c r="C326" s="22"/>
+      <c r="C326" s="23"/>
       <c r="F326" s="9"/>
       <c r="G326" s="9"/>
       <c r="H326" s="14"/>
-      <c r="I326" s="21"/>
+      <c r="I326" s="22"/>
     </row>
     <row r="327">
-      <c r="C327" s="22"/>
+      <c r="C327" s="23"/>
       <c r="F327" s="9"/>
       <c r="G327" s="9"/>
       <c r="H327" s="14"/>
-      <c r="I327" s="21"/>
+      <c r="I327" s="22"/>
     </row>
     <row r="328">
-      <c r="C328" s="22"/>
+      <c r="C328" s="23"/>
       <c r="F328" s="9"/>
       <c r="G328" s="9"/>
       <c r="H328" s="14"/>
-      <c r="I328" s="21"/>
+      <c r="I328" s="22"/>
     </row>
     <row r="329">
-      <c r="C329" s="22"/>
+      <c r="C329" s="23"/>
       <c r="F329" s="9"/>
       <c r="G329" s="9"/>
       <c r="H329" s="14"/>
-      <c r="I329" s="21"/>
+      <c r="I329" s="22"/>
     </row>
     <row r="330">
-      <c r="C330" s="22"/>
+      <c r="C330" s="23"/>
       <c r="F330" s="9"/>
       <c r="G330" s="9"/>
       <c r="H330" s="14"/>
-      <c r="I330" s="21"/>
+      <c r="I330" s="22"/>
     </row>
     <row r="331">
-      <c r="C331" s="22"/>
+      <c r="C331" s="23"/>
       <c r="F331" s="9"/>
       <c r="G331" s="9"/>
       <c r="H331" s="14"/>
-      <c r="I331" s="21"/>
+      <c r="I331" s="22"/>
     </row>
     <row r="332">
-      <c r="C332" s="22"/>
+      <c r="C332" s="23"/>
       <c r="F332" s="9"/>
       <c r="G332" s="9"/>
       <c r="H332" s="14"/>
-      <c r="I332" s="21"/>
+      <c r="I332" s="22"/>
     </row>
     <row r="333">
-      <c r="C333" s="22"/>
+      <c r="C333" s="23"/>
       <c r="F333" s="9"/>
       <c r="G333" s="9"/>
       <c r="H333" s="14"/>
-      <c r="I333" s="21"/>
+      <c r="I333" s="22"/>
     </row>
     <row r="334">
-      <c r="C334" s="22"/>
+      <c r="C334" s="23"/>
       <c r="F334" s="9"/>
       <c r="G334" s="9"/>
       <c r="H334" s="14"/>
-      <c r="I334" s="21"/>
+      <c r="I334" s="22"/>
     </row>
     <row r="335">
-      <c r="C335" s="22"/>
+      <c r="C335" s="23"/>
       <c r="F335" s="9"/>
       <c r="G335" s="9"/>
       <c r="H335" s="14"/>
-      <c r="I335" s="21"/>
+      <c r="I335" s="22"/>
     </row>
     <row r="336">
-      <c r="C336" s="22"/>
+      <c r="C336" s="23"/>
       <c r="F336" s="9"/>
       <c r="G336" s="9"/>
       <c r="H336" s="14"/>
-      <c r="I336" s="21"/>
+      <c r="I336" s="22"/>
     </row>
     <row r="337">
-      <c r="C337" s="22"/>
+      <c r="C337" s="23"/>
       <c r="F337" s="9"/>
       <c r="G337" s="9"/>
       <c r="H337" s="14"/>
-      <c r="I337" s="21"/>
+      <c r="I337" s="22"/>
     </row>
     <row r="338">
-      <c r="C338" s="22"/>
+      <c r="C338" s="23"/>
       <c r="F338" s="9"/>
       <c r="G338" s="9"/>
       <c r="H338" s="14"/>
-      <c r="I338" s="21"/>
+      <c r="I338" s="22"/>
     </row>
     <row r="339">
-      <c r="C339" s="22"/>
+      <c r="C339" s="23"/>
       <c r="F339" s="9"/>
       <c r="G339" s="9"/>
       <c r="H339" s="14"/>
-      <c r="I339" s="21"/>
+      <c r="I339" s="22"/>
     </row>
     <row r="340">
-      <c r="C340" s="22"/>
+      <c r="C340" s="23"/>
       <c r="F340" s="9"/>
       <c r="G340" s="9"/>
       <c r="H340" s="14"/>
-      <c r="I340" s="21"/>
+      <c r="I340" s="22"/>
     </row>
     <row r="341">
-      <c r="C341" s="22"/>
+      <c r="C341" s="23"/>
       <c r="F341" s="9"/>
       <c r="G341" s="9"/>
       <c r="H341" s="14"/>
-      <c r="I341" s="21"/>
+      <c r="I341" s="22"/>
     </row>
     <row r="342">
-      <c r="C342" s="22"/>
+      <c r="C342" s="23"/>
       <c r="F342" s="9"/>
       <c r="G342" s="9"/>
       <c r="H342" s="14"/>
-      <c r="I342" s="21"/>
+      <c r="I342" s="22"/>
     </row>
     <row r="343">
-      <c r="C343" s="22"/>
+      <c r="C343" s="23"/>
       <c r="F343" s="9"/>
       <c r="G343" s="9"/>
       <c r="H343" s="14"/>
-      <c r="I343" s="21"/>
+      <c r="I343" s="22"/>
     </row>
     <row r="344">
-      <c r="C344" s="22"/>
+      <c r="C344" s="23"/>
       <c r="F344" s="9"/>
       <c r="G344" s="9"/>
       <c r="H344" s="14"/>
-      <c r="I344" s="21"/>
+      <c r="I344" s="22"/>
     </row>
     <row r="345">
-      <c r="C345" s="22"/>
+      <c r="C345" s="23"/>
       <c r="F345" s="9"/>
       <c r="G345" s="9"/>
       <c r="H345" s="14"/>
-      <c r="I345" s="21"/>
+      <c r="I345" s="22"/>
     </row>
     <row r="346">
-      <c r="C346" s="22"/>
+      <c r="C346" s="23"/>
       <c r="F346" s="9"/>
       <c r="G346" s="9"/>
       <c r="H346" s="14"/>
-      <c r="I346" s="21"/>
+      <c r="I346" s="22"/>
     </row>
     <row r="347">
-      <c r="C347" s="22"/>
+      <c r="C347" s="23"/>
       <c r="F347" s="9"/>
       <c r="G347" s="9"/>
       <c r="H347" s="14"/>
-      <c r="I347" s="21"/>
+      <c r="I347" s="22"/>
     </row>
     <row r="348">
-      <c r="C348" s="22"/>
+      <c r="C348" s="23"/>
       <c r="F348" s="9"/>
       <c r="G348" s="9"/>
       <c r="H348" s="14"/>
-      <c r="I348" s="21"/>
+      <c r="I348" s="22"/>
     </row>
     <row r="349">
-      <c r="C349" s="22"/>
+      <c r="C349" s="23"/>
       <c r="F349" s="9"/>
       <c r="G349" s="9"/>
       <c r="H349" s="14"/>
-      <c r="I349" s="21"/>
+      <c r="I349" s="22"/>
     </row>
     <row r="350">
-      <c r="C350" s="22"/>
+      <c r="C350" s="23"/>
       <c r="F350" s="9"/>
       <c r="G350" s="9"/>
       <c r="H350" s="14"/>
-      <c r="I350" s="21"/>
+      <c r="I350" s="22"/>
     </row>
     <row r="351">
-      <c r="C351" s="22"/>
+      <c r="C351" s="23"/>
       <c r="F351" s="9"/>
       <c r="G351" s="9"/>
       <c r="H351" s="14"/>
-      <c r="I351" s="21"/>
+      <c r="I351" s="22"/>
     </row>
     <row r="352">
-      <c r="C352" s="22"/>
+      <c r="C352" s="23"/>
       <c r="F352" s="9"/>
       <c r="G352" s="9"/>
       <c r="H352" s="14"/>
-      <c r="I352" s="21"/>
+      <c r="I352" s="22"/>
     </row>
     <row r="353">
-      <c r="C353" s="22"/>
+      <c r="C353" s="23"/>
       <c r="F353" s="9"/>
       <c r="G353" s="9"/>
       <c r="H353" s="14"/>
-      <c r="I353" s="21"/>
+      <c r="I353" s="22"/>
     </row>
     <row r="354">
-      <c r="C354" s="22"/>
+      <c r="C354" s="23"/>
       <c r="F354" s="9"/>
       <c r="G354" s="9"/>
       <c r="H354" s="14"/>
-      <c r="I354" s="21"/>
+      <c r="I354" s="22"/>
     </row>
     <row r="355">
-      <c r="C355" s="22"/>
+      <c r="C355" s="23"/>
       <c r="F355" s="9"/>
       <c r="G355" s="9"/>
       <c r="H355" s="14"/>
-      <c r="I355" s="21"/>
+      <c r="I355" s="22"/>
     </row>
     <row r="356">
-      <c r="C356" s="22"/>
+      <c r="C356" s="23"/>
       <c r="F356" s="9"/>
       <c r="G356" s="9"/>
       <c r="H356" s="14"/>
-      <c r="I356" s="21"/>
+      <c r="I356" s="22"/>
     </row>
     <row r="357">
-      <c r="C357" s="22"/>
+      <c r="C357" s="23"/>
       <c r="F357" s="9"/>
       <c r="G357" s="9"/>
       <c r="H357" s="14"/>
-      <c r="I357" s="21"/>
+      <c r="I357" s="22"/>
     </row>
     <row r="358">
-      <c r="C358" s="22"/>
+      <c r="C358" s="23"/>
       <c r="F358" s="9"/>
       <c r="G358" s="9"/>
       <c r="H358" s="14"/>
-      <c r="I358" s="21"/>
+      <c r="I358" s="22"/>
     </row>
     <row r="359">
-      <c r="C359" s="22"/>
+      <c r="C359" s="23"/>
       <c r="F359" s="9"/>
       <c r="G359" s="9"/>
       <c r="H359" s="14"/>
-      <c r="I359" s="21"/>
+      <c r="I359" s="22"/>
     </row>
     <row r="360">
-      <c r="C360" s="22"/>
+      <c r="C360" s="23"/>
       <c r="F360" s="9"/>
       <c r="G360" s="9"/>
       <c r="H360" s="14"/>
-      <c r="I360" s="21"/>
+      <c r="I360" s="22"/>
     </row>
     <row r="361">
-      <c r="C361" s="22"/>
+      <c r="C361" s="23"/>
       <c r="F361" s="9"/>
       <c r="G361" s="9"/>
       <c r="H361" s="14"/>
-      <c r="I361" s="21"/>
+      <c r="I361" s="22"/>
     </row>
     <row r="362">
-      <c r="C362" s="22"/>
+      <c r="C362" s="23"/>
       <c r="F362" s="9"/>
       <c r="G362" s="9"/>
       <c r="H362" s="14"/>
-      <c r="I362" s="21"/>
+      <c r="I362" s="22"/>
     </row>
     <row r="363">
-      <c r="C363" s="22"/>
+      <c r="C363" s="23"/>
       <c r="F363" s="9"/>
       <c r="G363" s="9"/>
       <c r="H363" s="14"/>
-      <c r="I363" s="21"/>
+      <c r="I363" s="22"/>
     </row>
     <row r="364">
-      <c r="C364" s="22"/>
+      <c r="C364" s="23"/>
       <c r="F364" s="9"/>
       <c r="G364" s="9"/>
       <c r="H364" s="14"/>
-      <c r="I364" s="21"/>
+      <c r="I364" s="22"/>
     </row>
     <row r="365">
-      <c r="C365" s="22"/>
+      <c r="C365" s="23"/>
       <c r="F365" s="9"/>
       <c r="G365" s="9"/>
       <c r="H365" s="14"/>
-      <c r="I365" s="21"/>
+      <c r="I365" s="22"/>
     </row>
     <row r="366">
-      <c r="C366" s="22"/>
+      <c r="C366" s="23"/>
       <c r="F366" s="9"/>
       <c r="G366" s="9"/>
       <c r="H366" s="14"/>
-      <c r="I366" s="21"/>
+      <c r="I366" s="22"/>
     </row>
     <row r="367">
-      <c r="C367" s="22"/>
+      <c r="C367" s="23"/>
       <c r="F367" s="9"/>
       <c r="G367" s="9"/>
       <c r="H367" s="14"/>
-      <c r="I367" s="21"/>
+      <c r="I367" s="22"/>
     </row>
     <row r="368">
-      <c r="C368" s="22"/>
+      <c r="C368" s="23"/>
       <c r="F368" s="9"/>
       <c r="G368" s="9"/>
       <c r="H368" s="14"/>
-      <c r="I368" s="21"/>
+      <c r="I368" s="22"/>
     </row>
     <row r="369">
-      <c r="C369" s="22"/>
+      <c r="C369" s="23"/>
       <c r="F369" s="9"/>
       <c r="G369" s="9"/>
       <c r="H369" s="14"/>
-      <c r="I369" s="21"/>
+      <c r="I369" s="22"/>
     </row>
     <row r="370">
-      <c r="C370" s="22"/>
+      <c r="C370" s="23"/>
       <c r="F370" s="9"/>
       <c r="G370" s="9"/>
       <c r="H370" s="14"/>
-      <c r="I370" s="21"/>
+      <c r="I370" s="22"/>
     </row>
     <row r="371">
-      <c r="C371" s="22"/>
+      <c r="C371" s="23"/>
       <c r="F371" s="9"/>
       <c r="G371" s="9"/>
       <c r="H371" s="14"/>
-      <c r="I371" s="21"/>
+      <c r="I371" s="22"/>
     </row>
     <row r="372">
-      <c r="C372" s="22"/>
+      <c r="C372" s="23"/>
       <c r="F372" s="9"/>
       <c r="G372" s="9"/>
       <c r="H372" s="14"/>
-      <c r="I372" s="21"/>
+      <c r="I372" s="22"/>
     </row>
     <row r="373">
-      <c r="C373" s="22"/>
+      <c r="C373" s="23"/>
       <c r="F373" s="9"/>
       <c r="G373" s="9"/>
       <c r="H373" s="14"/>
-      <c r="I373" s="21"/>
+      <c r="I373" s="22"/>
     </row>
     <row r="374">
-      <c r="C374" s="22"/>
+      <c r="C374" s="23"/>
       <c r="F374" s="9"/>
       <c r="G374" s="9"/>
       <c r="H374" s="14"/>
-      <c r="I374" s="21"/>
+      <c r="I374" s="22"/>
     </row>
     <row r="375">
-      <c r="C375" s="22"/>
+      <c r="C375" s="23"/>
       <c r="F375" s="9"/>
       <c r="G375" s="9"/>
       <c r="H375" s="14"/>
-      <c r="I375" s="21"/>
+      <c r="I375" s="22"/>
     </row>
     <row r="376">
-      <c r="C376" s="22"/>
+      <c r="C376" s="23"/>
       <c r="F376" s="9"/>
       <c r="G376" s="9"/>
       <c r="H376" s="14"/>
-      <c r="I376" s="21"/>
+      <c r="I376" s="22"/>
     </row>
     <row r="377">
-      <c r="C377" s="22"/>
+      <c r="C377" s="23"/>
       <c r="F377" s="9"/>
       <c r="G377" s="9"/>
       <c r="H377" s="14"/>
-      <c r="I377" s="21"/>
+      <c r="I377" s="22"/>
     </row>
     <row r="378">
-      <c r="C378" s="22"/>
+      <c r="C378" s="23"/>
       <c r="F378" s="9"/>
       <c r="G378" s="9"/>
       <c r="H378" s="14"/>
-      <c r="I378" s="21"/>
+      <c r="I378" s="22"/>
     </row>
     <row r="379">
-      <c r="C379" s="22"/>
+      <c r="C379" s="23"/>
       <c r="F379" s="9"/>
       <c r="G379" s="9"/>
       <c r="H379" s="14"/>
-      <c r="I379" s="21"/>
+      <c r="I379" s="22"/>
     </row>
     <row r="380">
-      <c r="C380" s="22"/>
+      <c r="C380" s="23"/>
       <c r="F380" s="9"/>
       <c r="G380" s="9"/>
       <c r="H380" s="14"/>
-      <c r="I380" s="21"/>
+      <c r="I380" s="22"/>
     </row>
     <row r="381">
-      <c r="C381" s="22"/>
+      <c r="C381" s="23"/>
       <c r="F381" s="9"/>
       <c r="G381" s="9"/>
       <c r="H381" s="14"/>
-      <c r="I381" s="21"/>
+      <c r="I381" s="22"/>
     </row>
     <row r="382">
-      <c r="C382" s="22"/>
+      <c r="C382" s="23"/>
       <c r="F382" s="9"/>
       <c r="G382" s="9"/>
       <c r="H382" s="14"/>
-      <c r="I382" s="21"/>
+      <c r="I382" s="22"/>
     </row>
     <row r="383">
-      <c r="C383" s="22"/>
+      <c r="C383" s="23"/>
       <c r="F383" s="9"/>
       <c r="G383" s="9"/>
       <c r="H383" s="14"/>
-      <c r="I383" s="21"/>
+      <c r="I383" s="22"/>
     </row>
     <row r="384">
-      <c r="C384" s="22"/>
+      <c r="C384" s="23"/>
       <c r="F384" s="9"/>
       <c r="G384" s="9"/>
       <c r="H384" s="14"/>
-      <c r="I384" s="21"/>
+      <c r="I384" s="22"/>
     </row>
     <row r="385">
-      <c r="C385" s="22"/>
+      <c r="C385" s="23"/>
       <c r="F385" s="9"/>
       <c r="G385" s="9"/>
       <c r="H385" s="14"/>
-      <c r="I385" s="21"/>
+      <c r="I385" s="22"/>
     </row>
     <row r="386">
-      <c r="C386" s="22"/>
+      <c r="C386" s="23"/>
       <c r="F386" s="9"/>
       <c r="G386" s="9"/>
       <c r="H386" s="14"/>
-      <c r="I386" s="21"/>
+      <c r="I386" s="22"/>
     </row>
     <row r="387">
-      <c r="C387" s="22"/>
+      <c r="C387" s="23"/>
       <c r="F387" s="9"/>
       <c r="G387" s="9"/>
       <c r="H387" s="14"/>
-      <c r="I387" s="21"/>
+      <c r="I387" s="22"/>
     </row>
     <row r="388">
-      <c r="C388" s="22"/>
+      <c r="C388" s="23"/>
       <c r="F388" s="9"/>
       <c r="G388" s="9"/>
       <c r="H388" s="14"/>
-      <c r="I388" s="21"/>
+      <c r="I388" s="22"/>
     </row>
     <row r="389">
-      <c r="C389" s="22"/>
+      <c r="C389" s="23"/>
       <c r="F389" s="9"/>
       <c r="G389" s="9"/>
       <c r="H389" s="14"/>
-      <c r="I389" s="21"/>
+      <c r="I389" s="22"/>
     </row>
     <row r="390">
-      <c r="C390" s="22"/>
+      <c r="C390" s="23"/>
       <c r="F390" s="9"/>
       <c r="G390" s="9"/>
       <c r="H390" s="14"/>
-      <c r="I390" s="21"/>
+      <c r="I390" s="22"/>
     </row>
     <row r="391">
-      <c r="C391" s="22"/>
+      <c r="C391" s="23"/>
       <c r="F391" s="9"/>
       <c r="G391" s="9"/>
       <c r="H391" s="14"/>
-      <c r="I391" s="21"/>
+      <c r="I391" s="22"/>
     </row>
     <row r="392">
-      <c r="C392" s="22"/>
+      <c r="C392" s="23"/>
       <c r="F392" s="9"/>
       <c r="G392" s="9"/>
       <c r="H392" s="14"/>
-      <c r="I392" s="21"/>
+      <c r="I392" s="22"/>
     </row>
     <row r="393">
-      <c r="C393" s="22"/>
+      <c r="C393" s="23"/>
       <c r="F393" s="9"/>
       <c r="G393" s="9"/>
       <c r="H393" s="14"/>
-      <c r="I393" s="21"/>
+      <c r="I393" s="22"/>
     </row>
     <row r="394">
-      <c r="C394" s="22"/>
+      <c r="C394" s="23"/>
       <c r="F394" s="9"/>
       <c r="G394" s="9"/>
       <c r="H394" s="14"/>
-      <c r="I394" s="21"/>
+      <c r="I394" s="22"/>
     </row>
     <row r="395">
-      <c r="C395" s="22"/>
+      <c r="C395" s="23"/>
       <c r="F395" s="9"/>
       <c r="G395" s="9"/>
       <c r="H395" s="14"/>
-      <c r="I395" s="21"/>
+      <c r="I395" s="22"/>
     </row>
     <row r="396">
-      <c r="C396" s="22"/>
+      <c r="C396" s="23"/>
       <c r="F396" s="9"/>
       <c r="G396" s="9"/>
       <c r="H396" s="14"/>
-      <c r="I396" s="21"/>
+      <c r="I396" s="22"/>
     </row>
     <row r="397">
-      <c r="C397" s="22"/>
+      <c r="C397" s="23"/>
       <c r="F397" s="9"/>
       <c r="G397" s="9"/>
       <c r="H397" s="14"/>
-      <c r="I397" s="21"/>
+      <c r="I397" s="22"/>
     </row>
     <row r="398">
-      <c r="C398" s="22"/>
+      <c r="C398" s="23"/>
       <c r="F398" s="9"/>
       <c r="G398" s="9"/>
       <c r="H398" s="14"/>
-      <c r="I398" s="21"/>
+      <c r="I398" s="22"/>
     </row>
     <row r="399">
-      <c r="C399" s="22"/>
+      <c r="C399" s="23"/>
       <c r="F399" s="9"/>
       <c r="G399" s="9"/>
       <c r="H399" s="14"/>
-      <c r="I399" s="21"/>
+      <c r="I399" s="22"/>
     </row>
     <row r="400">
-      <c r="C400" s="22"/>
+      <c r="C400" s="23"/>
       <c r="F400" s="9"/>
       <c r="G400" s="9"/>
       <c r="H400" s="14"/>
-      <c r="I400" s="21"/>
+      <c r="I400" s="22"/>
     </row>
     <row r="401">
-      <c r="C401" s="22"/>
+      <c r="C401" s="23"/>
       <c r="F401" s="9"/>
       <c r="G401" s="9"/>
       <c r="H401" s="14"/>
-      <c r="I401" s="21"/>
+      <c r="I401" s="22"/>
     </row>
     <row r="402">
-      <c r="C402" s="22"/>
+      <c r="C402" s="23"/>
       <c r="F402" s="9"/>
       <c r="G402" s="9"/>
       <c r="H402" s="14"/>
-      <c r="I402" s="21"/>
+      <c r="I402" s="22"/>
     </row>
     <row r="403">
-      <c r="C403" s="22"/>
+      <c r="C403" s="23"/>
       <c r="F403" s="9"/>
       <c r="G403" s="9"/>
       <c r="H403" s="14"/>
-      <c r="I403" s="21"/>
+      <c r="I403" s="22"/>
     </row>
     <row r="404">
-      <c r="C404" s="22"/>
+      <c r="C404" s="23"/>
       <c r="F404" s="9"/>
       <c r="G404" s="9"/>
       <c r="H404" s="14"/>
-      <c r="I404" s="21"/>
+      <c r="I404" s="22"/>
     </row>
     <row r="405">
-      <c r="C405" s="22"/>
+      <c r="C405" s="23"/>
       <c r="F405" s="9"/>
       <c r="G405" s="9"/>
       <c r="H405" s="14"/>
-      <c r="I405" s="21"/>
+      <c r="I405" s="22"/>
     </row>
     <row r="406">
-      <c r="C406" s="22"/>
+      <c r="C406" s="23"/>
       <c r="F406" s="9"/>
       <c r="G406" s="9"/>
       <c r="H406" s="14"/>
-      <c r="I406" s="21"/>
+      <c r="I406" s="22"/>
     </row>
     <row r="407">
-      <c r="C407" s="22"/>
+      <c r="C407" s="23"/>
       <c r="F407" s="9"/>
       <c r="G407" s="9"/>
       <c r="H407" s="14"/>
-      <c r="I407" s="21"/>
+      <c r="I407" s="22"/>
     </row>
     <row r="408">
-      <c r="C408" s="22"/>
+      <c r="C408" s="23"/>
       <c r="F408" s="9"/>
       <c r="G408" s="9"/>
       <c r="H408" s="14"/>
-      <c r="I408" s="21"/>
+      <c r="I408" s="22"/>
     </row>
     <row r="409">
-      <c r="C409" s="22"/>
+      <c r="C409" s="23"/>
       <c r="F409" s="9"/>
       <c r="G409" s="9"/>
       <c r="H409" s="14"/>
-      <c r="I409" s="21"/>
+      <c r="I409" s="22"/>
     </row>
     <row r="410">
-      <c r="C410" s="22"/>
+      <c r="C410" s="23"/>
       <c r="F410" s="9"/>
       <c r="G410" s="9"/>
       <c r="H410" s="14"/>
-      <c r="I410" s="21"/>
+      <c r="I410" s="22"/>
     </row>
     <row r="411">
-      <c r="C411" s="22"/>
+      <c r="C411" s="23"/>
       <c r="F411" s="9"/>
       <c r="G411" s="9"/>
       <c r="H411" s="14"/>
-      <c r="I411" s="21"/>
+      <c r="I411" s="22"/>
     </row>
     <row r="412">
-      <c r="C412" s="22"/>
+      <c r="C412" s="23"/>
       <c r="F412" s="9"/>
       <c r="G412" s="9"/>
       <c r="H412" s="14"/>
-      <c r="I412" s="21"/>
+      <c r="I412" s="22"/>
     </row>
     <row r="413">
-      <c r="C413" s="22"/>
+      <c r="C413" s="23"/>
       <c r="F413" s="9"/>
       <c r="G413" s="9"/>
       <c r="H413" s="14"/>
-      <c r="I413" s="21"/>
+      <c r="I413" s="22"/>
     </row>
     <row r="414">
-      <c r="C414" s="22"/>
+      <c r="C414" s="23"/>
       <c r="F414" s="9"/>
       <c r="G414" s="9"/>
       <c r="H414" s="14"/>
-      <c r="I414" s="21"/>
+      <c r="I414" s="22"/>
     </row>
     <row r="415">
-      <c r="C415" s="22"/>
+      <c r="C415" s="23"/>
       <c r="F415" s="9"/>
       <c r="G415" s="9"/>
       <c r="H415" s="14"/>
-      <c r="I415" s="21"/>
+      <c r="I415" s="22"/>
     </row>
     <row r="416">
-      <c r="C416" s="22"/>
+      <c r="C416" s="23"/>
       <c r="F416" s="9"/>
       <c r="G416" s="9"/>
       <c r="H416" s="14"/>
-      <c r="I416" s="21"/>
+      <c r="I416" s="22"/>
     </row>
     <row r="417">
-      <c r="C417" s="22"/>
+      <c r="C417" s="23"/>
       <c r="F417" s="9"/>
       <c r="G417" s="9"/>
       <c r="H417" s="14"/>
-      <c r="I417" s="21"/>
+      <c r="I417" s="22"/>
     </row>
     <row r="418">
-      <c r="C418" s="22"/>
+      <c r="C418" s="23"/>
       <c r="F418" s="9"/>
       <c r="G418" s="9"/>
       <c r="H418" s="14"/>
-      <c r="I418" s="21"/>
+      <c r="I418" s="22"/>
     </row>
     <row r="419">
-      <c r="C419" s="22"/>
+      <c r="C419" s="23"/>
       <c r="F419" s="9"/>
       <c r="G419" s="9"/>
       <c r="H419" s="14"/>
-      <c r="I419" s="21"/>
+      <c r="I419" s="22"/>
     </row>
     <row r="420">
-      <c r="C420" s="22"/>
+      <c r="C420" s="23"/>
       <c r="F420" s="9"/>
       <c r="G420" s="9"/>
       <c r="H420" s="14"/>
-      <c r="I420" s="21"/>
+      <c r="I420" s="22"/>
     </row>
     <row r="421">
-      <c r="C421" s="22"/>
+      <c r="C421" s="23"/>
       <c r="F421" s="9"/>
       <c r="G421" s="9"/>
       <c r="H421" s="14"/>
-      <c r="I421" s="21"/>
+      <c r="I421" s="22"/>
     </row>
     <row r="422">
-      <c r="C422" s="22"/>
+      <c r="C422" s="23"/>
       <c r="F422" s="9"/>
       <c r="G422" s="9"/>
       <c r="H422" s="14"/>
-      <c r="I422" s="21"/>
+      <c r="I422" s="22"/>
     </row>
     <row r="423">
-      <c r="C423" s="22"/>
+      <c r="C423" s="23"/>
       <c r="F423" s="9"/>
       <c r="G423" s="9"/>
       <c r="H423" s="14"/>
-      <c r="I423" s="21"/>
+      <c r="I423" s="22"/>
     </row>
     <row r="424">
-      <c r="C424" s="22"/>
+      <c r="C424" s="23"/>
       <c r="F424" s="9"/>
       <c r="G424" s="9"/>
       <c r="H424" s="14"/>
-      <c r="I424" s="21"/>
+      <c r="I424" s="22"/>
     </row>
     <row r="425">
-      <c r="C425" s="22"/>
+      <c r="C425" s="23"/>
       <c r="F425" s="9"/>
       <c r="G425" s="9"/>
       <c r="H425" s="14"/>
-      <c r="I425" s="21"/>
+      <c r="I425" s="22"/>
     </row>
     <row r="426">
-      <c r="C426" s="22"/>
+      <c r="C426" s="23"/>
       <c r="F426" s="9"/>
       <c r="G426" s="9"/>
       <c r="H426" s="14"/>
-      <c r="I426" s="21"/>
+      <c r="I426" s="22"/>
     </row>
     <row r="427">
-      <c r="C427" s="22"/>
+      <c r="C427" s="23"/>
       <c r="F427" s="9"/>
       <c r="G427" s="9"/>
       <c r="H427" s="14"/>
-      <c r="I427" s="21"/>
+      <c r="I427" s="22"/>
     </row>
     <row r="428">
-      <c r="C428" s="22"/>
+      <c r="C428" s="23"/>
       <c r="F428" s="9"/>
       <c r="G428" s="9"/>
       <c r="H428" s="14"/>
-      <c r="I428" s="21"/>
+      <c r="I428" s="22"/>
     </row>
     <row r="429">
-      <c r="C429" s="22"/>
+      <c r="C429" s="23"/>
       <c r="F429" s="9"/>
       <c r="G429" s="9"/>
       <c r="H429" s="14"/>
-      <c r="I429" s="21"/>
+      <c r="I429" s="22"/>
     </row>
     <row r="430">
-      <c r="C430" s="22"/>
+      <c r="C430" s="23"/>
       <c r="F430" s="9"/>
       <c r="G430" s="9"/>
       <c r="H430" s="14"/>
-      <c r="I430" s="21"/>
+      <c r="I430" s="22"/>
     </row>
     <row r="431">
-      <c r="C431" s="22"/>
+      <c r="C431" s="23"/>
       <c r="F431" s="9"/>
       <c r="G431" s="9"/>
       <c r="H431" s="14"/>
-      <c r="I431" s="21"/>
+      <c r="I431" s="22"/>
     </row>
     <row r="432">
-      <c r="C432" s="22"/>
+      <c r="C432" s="23"/>
       <c r="F432" s="9"/>
       <c r="G432" s="9"/>
       <c r="H432" s="14"/>
-      <c r="I432" s="21"/>
+      <c r="I432" s="22"/>
     </row>
     <row r="433">
-      <c r="C433" s="22"/>
+      <c r="C433" s="23"/>
       <c r="F433" s="9"/>
       <c r="G433" s="9"/>
       <c r="H433" s="14"/>
-      <c r="I433" s="21"/>
+      <c r="I433" s="22"/>
     </row>
     <row r="434">
-      <c r="C434" s="22"/>
+      <c r="C434" s="23"/>
       <c r="F434" s="9"/>
       <c r="G434" s="9"/>
       <c r="H434" s="14"/>
-      <c r="I434" s="21"/>
+      <c r="I434" s="22"/>
     </row>
     <row r="435">
-      <c r="C435" s="22"/>
+      <c r="C435" s="23"/>
       <c r="F435" s="9"/>
       <c r="G435" s="9"/>
       <c r="H435" s="14"/>
-      <c r="I435" s="21"/>
+      <c r="I435" s="22"/>
     </row>
     <row r="436">
-      <c r="C436" s="22"/>
+      <c r="C436" s="23"/>
       <c r="F436" s="9"/>
       <c r="G436" s="9"/>
       <c r="H436" s="14"/>
-      <c r="I436" s="21"/>
+      <c r="I436" s="22"/>
     </row>
     <row r="437">
-      <c r="C437" s="22"/>
+      <c r="C437" s="23"/>
       <c r="F437" s="9"/>
       <c r="G437" s="9"/>
       <c r="H437" s="14"/>
-      <c r="I437" s="21"/>
+      <c r="I437" s="22"/>
     </row>
     <row r="438">
-      <c r="C438" s="22"/>
+      <c r="C438" s="23"/>
       <c r="F438" s="9"/>
       <c r="G438" s="9"/>
       <c r="H438" s="14"/>
-      <c r="I438" s="21"/>
+      <c r="I438" s="22"/>
     </row>
     <row r="439">
-      <c r="C439" s="22"/>
+      <c r="C439" s="23"/>
       <c r="F439" s="9"/>
       <c r="G439" s="9"/>
       <c r="H439" s="14"/>
-      <c r="I439" s="21"/>
+      <c r="I439" s="22"/>
     </row>
     <row r="440">
-      <c r="C440" s="22"/>
+      <c r="C440" s="23"/>
       <c r="F440" s="9"/>
       <c r="G440" s="9"/>
       <c r="H440" s="14"/>
-      <c r="I440" s="21"/>
+      <c r="I440" s="22"/>
     </row>
     <row r="441">
-      <c r="C441" s="22"/>
+      <c r="C441" s="23"/>
       <c r="F441" s="9"/>
       <c r="G441" s="9"/>
       <c r="H441" s="14"/>
-      <c r="I441" s="21"/>
+      <c r="I441" s="22"/>
     </row>
     <row r="442">
-      <c r="C442" s="22"/>
+      <c r="C442" s="23"/>
       <c r="F442" s="9"/>
       <c r="G442" s="9"/>
       <c r="H442" s="14"/>
-      <c r="I442" s="21"/>
+      <c r="I442" s="22"/>
     </row>
     <row r="443">
-      <c r="C443" s="22"/>
+      <c r="C443" s="23"/>
       <c r="F443" s="9"/>
       <c r="G443" s="9"/>
       <c r="H443" s="14"/>
-      <c r="I443" s="21"/>
+      <c r="I443" s="22"/>
     </row>
     <row r="444">
-      <c r="C444" s="22"/>
+      <c r="C444" s="23"/>
       <c r="F444" s="9"/>
       <c r="G444" s="9"/>
       <c r="H444" s="14"/>
-      <c r="I444" s="21"/>
+      <c r="I444" s="22"/>
     </row>
     <row r="445">
-      <c r="C445" s="22"/>
+      <c r="C445" s="23"/>
       <c r="F445" s="9"/>
       <c r="G445" s="9"/>
       <c r="H445" s="14"/>
-      <c r="I445" s="21"/>
+      <c r="I445" s="22"/>
     </row>
     <row r="446">
-      <c r="C446" s="22"/>
+      <c r="C446" s="23"/>
       <c r="F446" s="9"/>
       <c r="G446" s="9"/>
       <c r="H446" s="14"/>
-      <c r="I446" s="21"/>
+      <c r="I446" s="22"/>
     </row>
     <row r="447">
-      <c r="C447" s="22"/>
+      <c r="C447" s="23"/>
       <c r="F447" s="9"/>
       <c r="G447" s="9"/>
       <c r="H447" s="14"/>
-      <c r="I447" s="21"/>
+      <c r="I447" s="22"/>
     </row>
     <row r="448">
-      <c r="C448" s="22"/>
+      <c r="C448" s="23"/>
       <c r="F448" s="9"/>
       <c r="G448" s="9"/>
       <c r="H448" s="14"/>
-      <c r="I448" s="21"/>
+      <c r="I448" s="22"/>
     </row>
     <row r="449">
-      <c r="C449" s="22"/>
+      <c r="C449" s="23"/>
       <c r="F449" s="9"/>
       <c r="G449" s="9"/>
       <c r="H449" s="14"/>
-      <c r="I449" s="21"/>
+      <c r="I449" s="22"/>
     </row>
     <row r="450">
-      <c r="C450" s="22"/>
+      <c r="C450" s="23"/>
       <c r="F450" s="9"/>
       <c r="G450" s="9"/>
       <c r="H450" s="14"/>
-      <c r="I450" s="21"/>
+      <c r="I450" s="22"/>
     </row>
     <row r="451">
-      <c r="C451" s="22"/>
+      <c r="C451" s="23"/>
       <c r="F451" s="9"/>
       <c r="G451" s="9"/>
       <c r="H451" s="14"/>
-      <c r="I451" s="21"/>
+      <c r="I451" s="22"/>
     </row>
     <row r="452">
-      <c r="C452" s="22"/>
+      <c r="C452" s="23"/>
       <c r="F452" s="9"/>
       <c r="G452" s="9"/>
       <c r="H452" s="14"/>
-      <c r="I452" s="21"/>
+      <c r="I452" s="22"/>
     </row>
     <row r="453">
-      <c r="C453" s="22"/>
+      <c r="C453" s="23"/>
       <c r="F453" s="9"/>
       <c r="G453" s="9"/>
       <c r="H453" s="14"/>
-      <c r="I453" s="21"/>
+      <c r="I453" s="22"/>
     </row>
     <row r="454">
-      <c r="C454" s="22"/>
+      <c r="C454" s="23"/>
       <c r="F454" s="9"/>
       <c r="G454" s="9"/>
       <c r="H454" s="14"/>
-      <c r="I454" s="21"/>
+      <c r="I454" s="22"/>
     </row>
     <row r="455">
-      <c r="C455" s="22"/>
+      <c r="C455" s="23"/>
       <c r="F455" s="9"/>
       <c r="G455" s="9"/>
       <c r="H455" s="14"/>
-      <c r="I455" s="21"/>
+      <c r="I455" s="22"/>
     </row>
     <row r="456">
-      <c r="C456" s="22"/>
+      <c r="C456" s="23"/>
       <c r="F456" s="9"/>
       <c r="G456" s="9"/>
       <c r="H456" s="14"/>
-      <c r="I456" s="21"/>
+      <c r="I456" s="22"/>
     </row>
     <row r="457">
-      <c r="C457" s="22"/>
+      <c r="C457" s="23"/>
       <c r="F457" s="9"/>
       <c r="G457" s="9"/>
       <c r="H457" s="14"/>
-      <c r="I457" s="21"/>
+      <c r="I457" s="22"/>
     </row>
     <row r="458">
-      <c r="C458" s="22"/>
+      <c r="C458" s="23"/>
       <c r="F458" s="9"/>
       <c r="G458" s="9"/>
       <c r="H458" s="14"/>
-      <c r="I458" s="21"/>
+      <c r="I458" s="22"/>
     </row>
     <row r="459">
-      <c r="C459" s="22"/>
+      <c r="C459" s="23"/>
       <c r="F459" s="9"/>
       <c r="G459" s="9"/>
       <c r="H459" s="14"/>
-      <c r="I459" s="21"/>
+      <c r="I459" s="22"/>
     </row>
     <row r="460">
-      <c r="C460" s="22"/>
+      <c r="C460" s="23"/>
       <c r="F460" s="9"/>
       <c r="G460" s="9"/>
       <c r="H460" s="14"/>
-      <c r="I460" s="21"/>
+      <c r="I460" s="22"/>
     </row>
     <row r="461">
-      <c r="C461" s="22"/>
+      <c r="C461" s="23"/>
       <c r="F461" s="9"/>
       <c r="G461" s="9"/>
       <c r="H461" s="14"/>
-      <c r="I461" s="21"/>
+      <c r="I461" s="22"/>
     </row>
     <row r="462">
-      <c r="C462" s="22"/>
+      <c r="C462" s="23"/>
       <c r="F462" s="9"/>
       <c r="G462" s="9"/>
       <c r="H462" s="14"/>
-      <c r="I462" s="21"/>
+      <c r="I462" s="22"/>
     </row>
     <row r="463">
-      <c r="C463" s="22"/>
+      <c r="C463" s="23"/>
       <c r="F463" s="9"/>
       <c r="G463" s="9"/>
       <c r="H463" s="14"/>
-      <c r="I463" s="21"/>
+      <c r="I463" s="22"/>
     </row>
     <row r="464">
-      <c r="C464" s="22"/>
+      <c r="C464" s="23"/>
       <c r="F464" s="9"/>
       <c r="G464" s="9"/>
       <c r="H464" s="14"/>
-      <c r="I464" s="21"/>
+      <c r="I464" s="22"/>
     </row>
     <row r="465">
-      <c r="C465" s="22"/>
+      <c r="C465" s="23"/>
       <c r="F465" s="9"/>
       <c r="G465" s="9"/>
       <c r="H465" s="14"/>
-      <c r="I465" s="21"/>
+      <c r="I465" s="22"/>
     </row>
     <row r="466">
-      <c r="C466" s="22"/>
+      <c r="C466" s="23"/>
       <c r="F466" s="9"/>
       <c r="G466" s="9"/>
       <c r="H466" s="14"/>
-      <c r="I466" s="21"/>
+      <c r="I466" s="22"/>
     </row>
     <row r="467">
-      <c r="C467" s="22"/>
+      <c r="C467" s="23"/>
       <c r="F467" s="9"/>
       <c r="G467" s="9"/>
       <c r="H467" s="14"/>
-      <c r="I467" s="21"/>
+      <c r="I467" s="22"/>
     </row>
     <row r="468">
-      <c r="C468" s="22"/>
+      <c r="C468" s="23"/>
       <c r="F468" s="9"/>
       <c r="G468" s="9"/>
       <c r="H468" s="14"/>
-      <c r="I468" s="21"/>
+      <c r="I468" s="22"/>
     </row>
     <row r="469">
-      <c r="C469" s="22"/>
+      <c r="C469" s="23"/>
       <c r="F469" s="9"/>
       <c r="G469" s="9"/>
       <c r="H469" s="14"/>
-      <c r="I469" s="21"/>
+      <c r="I469" s="22"/>
     </row>
     <row r="470">
-      <c r="C470" s="22"/>
+      <c r="C470" s="23"/>
       <c r="F470" s="9"/>
       <c r="G470" s="9"/>
       <c r="H470" s="14"/>
-      <c r="I470" s="21"/>
+      <c r="I470" s="22"/>
     </row>
     <row r="471">
-      <c r="C471" s="22"/>
+      <c r="C471" s="23"/>
       <c r="F471" s="9"/>
       <c r="G471" s="9"/>
       <c r="H471" s="14"/>
-      <c r="I471" s="21"/>
+      <c r="I471" s="22"/>
     </row>
     <row r="472">
-      <c r="C472" s="22"/>
+      <c r="C472" s="23"/>
       <c r="F472" s="9"/>
       <c r="G472" s="9"/>
       <c r="H472" s="14"/>
-      <c r="I472" s="21"/>
+      <c r="I472" s="22"/>
     </row>
     <row r="473">
-      <c r="C473" s="22"/>
+      <c r="C473" s="23"/>
       <c r="F473" s="9"/>
       <c r="G473" s="9"/>
       <c r="H473" s="14"/>
-      <c r="I473" s="21"/>
+      <c r="I473" s="22"/>
     </row>
     <row r="474">
-      <c r="C474" s="22"/>
+      <c r="C474" s="23"/>
       <c r="F474" s="9"/>
       <c r="G474" s="9"/>
       <c r="H474" s="14"/>
-      <c r="I474" s="21"/>
+      <c r="I474" s="22"/>
     </row>
     <row r="475">
-      <c r="C475" s="22"/>
+      <c r="C475" s="23"/>
       <c r="F475" s="9"/>
       <c r="G475" s="9"/>
       <c r="H475" s="14"/>
-      <c r="I475" s="21"/>
+      <c r="I475" s="22"/>
     </row>
     <row r="476">
-      <c r="C476" s="22"/>
+      <c r="C476" s="23"/>
       <c r="F476" s="9"/>
       <c r="G476" s="9"/>
       <c r="H476" s="14"/>
-      <c r="I476" s="21"/>
+      <c r="I476" s="22"/>
     </row>
     <row r="477">
-      <c r="C477" s="22"/>
+      <c r="C477" s="23"/>
       <c r="F477" s="9"/>
       <c r="G477" s="9"/>
       <c r="H477" s="14"/>
-      <c r="I477" s="21"/>
+      <c r="I477" s="22"/>
     </row>
     <row r="478">
-      <c r="C478" s="22"/>
+      <c r="C478" s="23"/>
       <c r="F478" s="9"/>
       <c r="G478" s="9"/>
       <c r="H478" s="14"/>
-      <c r="I478" s="21"/>
+      <c r="I478" s="22"/>
     </row>
     <row r="479">
-      <c r="C479" s="22"/>
+      <c r="C479" s="23"/>
       <c r="F479" s="9"/>
       <c r="G479" s="9"/>
       <c r="H479" s="14"/>
-      <c r="I479" s="21"/>
+      <c r="I479" s="22"/>
     </row>
     <row r="480">
-      <c r="C480" s="22"/>
+      <c r="C480" s="23"/>
       <c r="F480" s="9"/>
       <c r="G480" s="9"/>
       <c r="H480" s="14"/>
-      <c r="I480" s="21"/>
+      <c r="I480" s="22"/>
     </row>
     <row r="481">
-      <c r="C481" s="22"/>
+      <c r="C481" s="23"/>
       <c r="F481" s="9"/>
       <c r="G481" s="9"/>
       <c r="H481" s="14"/>
-      <c r="I481" s="21"/>
+      <c r="I481" s="22"/>
     </row>
     <row r="482">
-      <c r="C482" s="22"/>
+      <c r="C482" s="23"/>
       <c r="F482" s="9"/>
       <c r="G482" s="9"/>
       <c r="H482" s="14"/>
-      <c r="I482" s="21"/>
+      <c r="I482" s="22"/>
     </row>
     <row r="483">
-      <c r="C483" s="22"/>
+      <c r="C483" s="23"/>
       <c r="F483" s="9"/>
       <c r="G483" s="9"/>
       <c r="H483" s="14"/>
-      <c r="I483" s="21"/>
+      <c r="I483" s="22"/>
     </row>
     <row r="484">
-      <c r="C484" s="22"/>
+      <c r="C484" s="23"/>
       <c r="F484" s="9"/>
       <c r="G484" s="9"/>
       <c r="H484" s="14"/>
-      <c r="I484" s="21"/>
+      <c r="I484" s="22"/>
     </row>
     <row r="485">
-      <c r="C485" s="22"/>
+      <c r="C485" s="23"/>
       <c r="F485" s="9"/>
       <c r="G485" s="9"/>
       <c r="H485" s="14"/>
-      <c r="I485" s="21"/>
+      <c r="I485" s="22"/>
     </row>
     <row r="486">
-      <c r="C486" s="22"/>
+      <c r="C486" s="23"/>
       <c r="F486" s="9"/>
       <c r="G486" s="9"/>
       <c r="H486" s="14"/>
-      <c r="I486" s="21"/>
+      <c r="I486" s="22"/>
     </row>
     <row r="487">
-      <c r="C487" s="22"/>
+      <c r="C487" s="23"/>
       <c r="F487" s="9"/>
       <c r="G487" s="9"/>
       <c r="H487" s="14"/>
-      <c r="I487" s="21"/>
+      <c r="I487" s="22"/>
     </row>
     <row r="488">
-      <c r="C488" s="22"/>
+      <c r="C488" s="23"/>
       <c r="F488" s="9"/>
       <c r="G488" s="9"/>
       <c r="H488" s="14"/>
-      <c r="I488" s="21"/>
+      <c r="I488" s="22"/>
     </row>
     <row r="489">
-      <c r="C489" s="22"/>
+      <c r="C489" s="23"/>
       <c r="F489" s="9"/>
       <c r="G489" s="9"/>
       <c r="H489" s="14"/>
-      <c r="I489" s="21"/>
+      <c r="I489" s="22"/>
     </row>
     <row r="490">
-      <c r="C490" s="22"/>
+      <c r="C490" s="23"/>
       <c r="F490" s="9"/>
       <c r="G490" s="9"/>
       <c r="H490" s="14"/>
-      <c r="I490" s="21"/>
+      <c r="I490" s="22"/>
     </row>
     <row r="491">
-      <c r="C491" s="22"/>
+      <c r="C491" s="23"/>
       <c r="F491" s="9"/>
       <c r="G491" s="9"/>
       <c r="H491" s="14"/>
-      <c r="I491" s="21"/>
+      <c r="I491" s="22"/>
     </row>
     <row r="492">
-      <c r="C492" s="22"/>
+      <c r="C492" s="23"/>
       <c r="F492" s="9"/>
       <c r="G492" s="9"/>
       <c r="H492" s="14"/>
-      <c r="I492" s="21"/>
+      <c r="I492" s="22"/>
     </row>
     <row r="493">
-      <c r="C493" s="22"/>
+      <c r="C493" s="23"/>
       <c r="F493" s="9"/>
       <c r="G493" s="9"/>
       <c r="H493" s="14"/>
-      <c r="I493" s="21"/>
+      <c r="I493" s="22"/>
     </row>
     <row r="494">
-      <c r="C494" s="22"/>
+      <c r="C494" s="23"/>
       <c r="F494" s="9"/>
       <c r="G494" s="9"/>
       <c r="H494" s="14"/>
-      <c r="I494" s="21"/>
+      <c r="I494" s="22"/>
     </row>
     <row r="495">
-      <c r="C495" s="22"/>
+      <c r="C495" s="23"/>
       <c r="F495" s="9"/>
       <c r="G495" s="9"/>
       <c r="H495" s="14"/>
-      <c r="I495" s="21"/>
+      <c r="I495" s="22"/>
     </row>
     <row r="496">
-      <c r="C496" s="22"/>
+      <c r="C496" s="23"/>
       <c r="F496" s="9"/>
       <c r="G496" s="9"/>
       <c r="H496" s="14"/>
-      <c r="I496" s="21"/>
+      <c r="I496" s="22"/>
     </row>
     <row r="497">
-      <c r="C497" s="22"/>
+      <c r="C497" s="23"/>
       <c r="F497" s="9"/>
       <c r="G497" s="9"/>
       <c r="H497" s="14"/>
-      <c r="I497" s="21"/>
+      <c r="I497" s="22"/>
     </row>
     <row r="498">
-      <c r="C498" s="22"/>
+      <c r="C498" s="23"/>
       <c r="F498" s="9"/>
       <c r="G498" s="9"/>
       <c r="H498" s="14"/>
-      <c r="I498" s="21"/>
+      <c r="I498" s="22"/>
     </row>
     <row r="499">
-      <c r="C499" s="22"/>
+      <c r="C499" s="23"/>
       <c r="F499" s="9"/>
       <c r="G499" s="9"/>
       <c r="H499" s="14"/>
-      <c r="I499" s="21"/>
+      <c r="I499" s="22"/>
     </row>
     <row r="500">
-      <c r="C500" s="22"/>
+      <c r="C500" s="23"/>
       <c r="F500" s="9"/>
       <c r="G500" s="9"/>
       <c r="H500" s="14"/>
-      <c r="I500" s="21"/>
+      <c r="I500" s="22"/>
     </row>
     <row r="501">
-      <c r="C501" s="22"/>
+      <c r="C501" s="23"/>
       <c r="F501" s="9"/>
       <c r="G501" s="9"/>
       <c r="H501" s="14"/>
-      <c r="I501" s="21"/>
+      <c r="I501" s="22"/>
     </row>
     <row r="502">
-      <c r="C502" s="22"/>
+      <c r="C502" s="23"/>
       <c r="F502" s="9"/>
       <c r="G502" s="9"/>
       <c r="H502" s="14"/>
-      <c r="I502" s="21"/>
+      <c r="I502" s="22"/>
     </row>
     <row r="503">
-      <c r="C503" s="22"/>
+      <c r="C503" s="23"/>
       <c r="F503" s="9"/>
       <c r="G503" s="9"/>
       <c r="H503" s="14"/>
-      <c r="I503" s="21"/>
+      <c r="I503" s="22"/>
     </row>
     <row r="504">
-      <c r="C504" s="22"/>
+      <c r="C504" s="23"/>
       <c r="F504" s="9"/>
       <c r="G504" s="9"/>
       <c r="H504" s="14"/>
-      <c r="I504" s="21"/>
+      <c r="I504" s="22"/>
     </row>
     <row r="505">
-      <c r="C505" s="22"/>
+      <c r="C505" s="23"/>
       <c r="F505" s="9"/>
       <c r="G505" s="9"/>
       <c r="H505" s="14"/>
-      <c r="I505" s="21"/>
+      <c r="I505" s="22"/>
     </row>
     <row r="506">
-      <c r="C506" s="22"/>
+      <c r="C506" s="23"/>
       <c r="F506" s="9"/>
       <c r="G506" s="9"/>
       <c r="H506" s="14"/>
-      <c r="I506" s="21"/>
+      <c r="I506" s="22"/>
     </row>
     <row r="507">
-      <c r="C507" s="22"/>
+      <c r="C507" s="23"/>
       <c r="F507" s="9"/>
       <c r="G507" s="9"/>
       <c r="H507" s="14"/>
-      <c r="I507" s="21"/>
+      <c r="I507" s="22"/>
     </row>
     <row r="508">
-      <c r="C508" s="22"/>
+      <c r="C508" s="23"/>
       <c r="F508" s="9"/>
       <c r="G508" s="9"/>
       <c r="H508" s="14"/>
-      <c r="I508" s="21"/>
+      <c r="I508" s="22"/>
     </row>
     <row r="509">
-      <c r="C509" s="22"/>
+      <c r="C509" s="23"/>
       <c r="F509" s="9"/>
       <c r="G509" s="9"/>
       <c r="H509" s="14"/>
-      <c r="I509" s="21"/>
+      <c r="I509" s="22"/>
     </row>
     <row r="510">
-      <c r="C510" s="22"/>
+      <c r="C510" s="23"/>
       <c r="F510" s="9"/>
       <c r="G510" s="9"/>
       <c r="H510" s="14"/>
-      <c r="I510" s="21"/>
+      <c r="I510" s="22"/>
     </row>
     <row r="511">
-      <c r="C511" s="22"/>
+      <c r="C511" s="23"/>
       <c r="F511" s="9"/>
       <c r="G511" s="9"/>
       <c r="H511" s="14"/>
-      <c r="I511" s="21"/>
+      <c r="I511" s="22"/>
     </row>
     <row r="512">
-      <c r="C512" s="22"/>
+      <c r="C512" s="23"/>
       <c r="F512" s="9"/>
       <c r="G512" s="9"/>
       <c r="H512" s="14"/>
-      <c r="I512" s="21"/>
+      <c r="I512" s="22"/>
     </row>
     <row r="513">
-      <c r="C513" s="22"/>
+      <c r="C513" s="23"/>
       <c r="F513" s="9"/>
       <c r="G513" s="9"/>
       <c r="H513" s="14"/>
-      <c r="I513" s="21"/>
+      <c r="I513" s="22"/>
     </row>
     <row r="514">
-      <c r="C514" s="22"/>
+      <c r="C514" s="23"/>
       <c r="F514" s="9"/>
       <c r="G514" s="9"/>
       <c r="H514" s="14"/>
-      <c r="I514" s="21"/>
+      <c r="I514" s="22"/>
     </row>
     <row r="515">
-      <c r="C515" s="22"/>
+      <c r="C515" s="23"/>
       <c r="F515" s="9"/>
       <c r="G515" s="9"/>
       <c r="H515" s="14"/>
-      <c r="I515" s="21"/>
+      <c r="I515" s="22"/>
     </row>
     <row r="516">
-      <c r="C516" s="22"/>
+      <c r="C516" s="23"/>
       <c r="F516" s="9"/>
       <c r="G516" s="9"/>
       <c r="H516" s="14"/>
-      <c r="I516" s="21"/>
+      <c r="I516" s="22"/>
     </row>
     <row r="517">
-      <c r="C517" s="22"/>
+      <c r="C517" s="23"/>
       <c r="F517" s="9"/>
       <c r="G517" s="9"/>
       <c r="H517" s="14"/>
-      <c r="I517" s="21"/>
+      <c r="I517" s="22"/>
     </row>
     <row r="518">
-      <c r="C518" s="22"/>
+      <c r="C518" s="23"/>
       <c r="F518" s="9"/>
       <c r="G518" s="9"/>
       <c r="H518" s="14"/>
-      <c r="I518" s="21"/>
+      <c r="I518" s="22"/>
     </row>
     <row r="519">
-      <c r="C519" s="22"/>
+      <c r="C519" s="23"/>
       <c r="F519" s="9"/>
       <c r="G519" s="9"/>
       <c r="H519" s="14"/>
-      <c r="I519" s="21"/>
+      <c r="I519" s="22"/>
     </row>
     <row r="520">
-      <c r="C520" s="22"/>
+      <c r="C520" s="23"/>
       <c r="F520" s="9"/>
       <c r="G520" s="9"/>
       <c r="H520" s="14"/>
-      <c r="I520" s="21"/>
+      <c r="I520" s="22"/>
     </row>
     <row r="521">
-      <c r="C521" s="22"/>
+      <c r="C521" s="23"/>
       <c r="F521" s="9"/>
       <c r="G521" s="9"/>
       <c r="H521" s="14"/>
-      <c r="I521" s="21"/>
+      <c r="I521" s="22"/>
     </row>
     <row r="522">
-      <c r="C522" s="22"/>
+      <c r="C522" s="23"/>
       <c r="F522" s="9"/>
       <c r="G522" s="9"/>
       <c r="H522" s="14"/>
-      <c r="I522" s="21"/>
+      <c r="I522" s="22"/>
     </row>
     <row r="523">
-      <c r="C523" s="22"/>
+      <c r="C523" s="23"/>
       <c r="F523" s="9"/>
       <c r="G523" s="9"/>
       <c r="H523" s="14"/>
-      <c r="I523" s="21"/>
+      <c r="I523" s="22"/>
     </row>
     <row r="524">
-      <c r="C524" s="22"/>
+      <c r="C524" s="23"/>
       <c r="F524" s="9"/>
       <c r="G524" s="9"/>
       <c r="H524" s="14"/>
-      <c r="I524" s="21"/>
+      <c r="I524" s="22"/>
     </row>
     <row r="525">
-      <c r="C525" s="22"/>
+      <c r="C525" s="23"/>
       <c r="F525" s="9"/>
       <c r="G525" s="9"/>
       <c r="H525" s="14"/>
-      <c r="I525" s="21"/>
+      <c r="I525" s="22"/>
     </row>
     <row r="526">
-      <c r="C526" s="22"/>
+      <c r="C526" s="23"/>
       <c r="F526" s="9"/>
       <c r="G526" s="9"/>
       <c r="H526" s="14"/>
-      <c r="I526" s="21"/>
+      <c r="I526" s="22"/>
     </row>
     <row r="527">
-      <c r="C527" s="22"/>
+      <c r="C527" s="23"/>
       <c r="F527" s="9"/>
       <c r="G527" s="9"/>
       <c r="H527" s="14"/>
-      <c r="I527" s="21"/>
+      <c r="I527" s="22"/>
     </row>
     <row r="528">
-      <c r="C528" s="22"/>
+      <c r="C528" s="23"/>
       <c r="F528" s="9"/>
       <c r="G528" s="9"/>
       <c r="H528" s="14"/>
-      <c r="I528" s="21"/>
+      <c r="I528" s="22"/>
     </row>
     <row r="529">
-      <c r="C529" s="22"/>
+      <c r="C529" s="23"/>
       <c r="F529" s="9"/>
       <c r="G529" s="9"/>
       <c r="H529" s="14"/>
-      <c r="I529" s="21"/>
+      <c r="I529" s="22"/>
     </row>
     <row r="530">
-      <c r="C530" s="22"/>
+      <c r="C530" s="23"/>
       <c r="F530" s="9"/>
       <c r="G530" s="9"/>
       <c r="H530" s="14"/>
-      <c r="I530" s="21"/>
+      <c r="I530" s="22"/>
     </row>
     <row r="531">
-      <c r="C531" s="22"/>
+      <c r="C531" s="23"/>
       <c r="F531" s="9"/>
       <c r="G531" s="9"/>
       <c r="H531" s="14"/>
-      <c r="I531" s="21"/>
+      <c r="I531" s="22"/>
     </row>
     <row r="532">
-      <c r="C532" s="22"/>
+      <c r="C532" s="23"/>
       <c r="F532" s="9"/>
       <c r="G532" s="9"/>
       <c r="H532" s="14"/>
-      <c r="I532" s="21"/>
+      <c r="I532" s="22"/>
     </row>
     <row r="533">
-      <c r="C533" s="22"/>
+      <c r="C533" s="23"/>
       <c r="F533" s="9"/>
       <c r="G533" s="9"/>
       <c r="H533" s="14"/>
-      <c r="I533" s="21"/>
+      <c r="I533" s="22"/>
     </row>
     <row r="534">
-      <c r="C534" s="22"/>
+      <c r="C534" s="23"/>
       <c r="F534" s="9"/>
       <c r="G534" s="9"/>
       <c r="H534" s="14"/>
-      <c r="I534" s="21"/>
+      <c r="I534" s="22"/>
     </row>
     <row r="535">
-      <c r="C535" s="22"/>
+      <c r="C535" s="23"/>
       <c r="F535" s="9"/>
       <c r="G535" s="9"/>
       <c r="H535" s="14"/>
-      <c r="I535" s="21"/>
+      <c r="I535" s="22"/>
     </row>
     <row r="536">
-      <c r="C536" s="22"/>
+      <c r="C536" s="23"/>
       <c r="F536" s="9"/>
       <c r="G536" s="9"/>
       <c r="H536" s="14"/>
-      <c r="I536" s="21"/>
+      <c r="I536" s="22"/>
     </row>
     <row r="537">
-      <c r="C537" s="22"/>
+      <c r="C537" s="23"/>
       <c r="F537" s="9"/>
       <c r="G537" s="9"/>
       <c r="H537" s="14"/>
-      <c r="I537" s="21"/>
+      <c r="I537" s="22"/>
     </row>
     <row r="538">
-      <c r="C538" s="22"/>
+      <c r="C538" s="23"/>
       <c r="F538" s="9"/>
       <c r="G538" s="9"/>
       <c r="H538" s="14"/>
-      <c r="I538" s="21"/>
+      <c r="I538" s="22"/>
     </row>
     <row r="539">
-      <c r="C539" s="22"/>
+      <c r="C539" s="23"/>
       <c r="F539" s="9"/>
       <c r="G539" s="9"/>
       <c r="H539" s="14"/>
-      <c r="I539" s="21"/>
+      <c r="I539" s="22"/>
     </row>
     <row r="540">
-      <c r="C540" s="22"/>
+      <c r="C540" s="23"/>
       <c r="F540" s="9"/>
       <c r="G540" s="9"/>
       <c r="H540" s="14"/>
-      <c r="I540" s="21"/>
+      <c r="I540" s="22"/>
     </row>
     <row r="541">
-      <c r="C541" s="22"/>
+      <c r="C541" s="23"/>
       <c r="F541" s="9"/>
       <c r="G541" s="9"/>
       <c r="H541" s="14"/>
-      <c r="I541" s="21"/>
+      <c r="I541" s="22"/>
     </row>
     <row r="542">
-      <c r="C542" s="22"/>
+      <c r="C542" s="23"/>
       <c r="F542" s="9"/>
       <c r="G542" s="9"/>
       <c r="H542" s="14"/>
-      <c r="I542" s="21"/>
+      <c r="I542" s="22"/>
     </row>
     <row r="543">
-      <c r="C543" s="22"/>
+      <c r="C543" s="23"/>
       <c r="F543" s="9"/>
       <c r="G543" s="9"/>
       <c r="H543" s="14"/>
-      <c r="I543" s="21"/>
+      <c r="I543" s="22"/>
     </row>
     <row r="544">
-      <c r="C544" s="22"/>
+      <c r="C544" s="23"/>
       <c r="F544" s="9"/>
       <c r="G544" s="9"/>
       <c r="H544" s="14"/>
-      <c r="I544" s="21"/>
+      <c r="I544" s="22"/>
     </row>
     <row r="545">
-      <c r="C545" s="22"/>
+      <c r="C545" s="23"/>
       <c r="F545" s="9"/>
       <c r="G545" s="9"/>
       <c r="H545" s="14"/>
-      <c r="I545" s="21"/>
+      <c r="I545" s="22"/>
     </row>
     <row r="546">
-      <c r="C546" s="22"/>
+      <c r="C546" s="23"/>
       <c r="F546" s="9"/>
       <c r="G546" s="9"/>
       <c r="H546" s="14"/>
-      <c r="I546" s="21"/>
+      <c r="I546" s="22"/>
     </row>
     <row r="547">
-      <c r="C547" s="22"/>
+      <c r="C547" s="23"/>
       <c r="F547" s="9"/>
       <c r="G547" s="9"/>
       <c r="H547" s="14"/>
-      <c r="I547" s="21"/>
+      <c r="I547" s="22"/>
     </row>
     <row r="548">
-      <c r="C548" s="22"/>
+      <c r="C548" s="23"/>
       <c r="F548" s="9"/>
       <c r="G548" s="9"/>
       <c r="H548" s="14"/>
-      <c r="I548" s="21"/>
+      <c r="I548" s="22"/>
     </row>
     <row r="549">
-      <c r="C549" s="22"/>
+      <c r="C549" s="23"/>
       <c r="F549" s="9"/>
       <c r="G549" s="9"/>
       <c r="H549" s="14"/>
-      <c r="I549" s="21"/>
+      <c r="I549" s="22"/>
     </row>
     <row r="550">
-      <c r="C550" s="22"/>
+      <c r="C550" s="23"/>
       <c r="F550" s="9"/>
       <c r="G550" s="9"/>
       <c r="H550" s="14"/>
-      <c r="I550" s="21"/>
+      <c r="I550" s="22"/>
     </row>
     <row r="551">
-      <c r="C551" s="22"/>
+      <c r="C551" s="23"/>
       <c r="F551" s="9"/>
       <c r="G551" s="9"/>
       <c r="H551" s="14"/>
-      <c r="I551" s="21"/>
+      <c r="I551" s="22"/>
     </row>
     <row r="552">
-      <c r="C552" s="22"/>
+      <c r="C552" s="23"/>
       <c r="F552" s="9"/>
       <c r="G552" s="9"/>
       <c r="H552" s="14"/>
-      <c r="I552" s="21"/>
+      <c r="I552" s="22"/>
     </row>
     <row r="553">
-      <c r="C553" s="22"/>
+      <c r="C553" s="23"/>
       <c r="F553" s="9"/>
       <c r="G553" s="9"/>
       <c r="H553" s="14"/>
-      <c r="I553" s="21"/>
+      <c r="I553" s="22"/>
     </row>
     <row r="554">
-      <c r="C554" s="22"/>
+      <c r="C554" s="23"/>
       <c r="F554" s="9"/>
       <c r="G554" s="9"/>
       <c r="H554" s="14"/>
-      <c r="I554" s="21"/>
+      <c r="I554" s="22"/>
     </row>
     <row r="555">
-      <c r="C555" s="22"/>
+      <c r="C555" s="23"/>
       <c r="F555" s="9"/>
       <c r="G555" s="9"/>
       <c r="H555" s="14"/>
-      <c r="I555" s="21"/>
+      <c r="I555" s="22"/>
     </row>
     <row r="556">
-      <c r="C556" s="22"/>
+      <c r="C556" s="23"/>
       <c r="F556" s="9"/>
       <c r="G556" s="9"/>
       <c r="H556" s="14"/>
-      <c r="I556" s="21"/>
+      <c r="I556" s="22"/>
     </row>
     <row r="557">
-      <c r="C557" s="22"/>
+      <c r="C557" s="23"/>
       <c r="F557" s="9"/>
       <c r="G557" s="9"/>
       <c r="H557" s="14"/>
-      <c r="I557" s="21"/>
+      <c r="I557" s="22"/>
     </row>
     <row r="558">
-      <c r="C558" s="22"/>
+      <c r="C558" s="23"/>
       <c r="F558" s="9"/>
       <c r="G558" s="9"/>
       <c r="H558" s="14"/>
-      <c r="I558" s="21"/>
+      <c r="I558" s="22"/>
     </row>
     <row r="559">
-      <c r="C559" s="22"/>
+      <c r="C559" s="23"/>
       <c r="F559" s="9"/>
       <c r="G559" s="9"/>
       <c r="H559" s="14"/>
-      <c r="I559" s="21"/>
+      <c r="I559" s="22"/>
     </row>
     <row r="560">
-      <c r="C560" s="22"/>
+      <c r="C560" s="23"/>
       <c r="F560" s="9"/>
       <c r="G560" s="9"/>
       <c r="H560" s="14"/>
-      <c r="I560" s="21"/>
+      <c r="I560" s="22"/>
     </row>
     <row r="561">
-      <c r="C561" s="22"/>
+      <c r="C561" s="23"/>
       <c r="F561" s="9"/>
       <c r="G561" s="9"/>
       <c r="H561" s="14"/>
-      <c r="I561" s="21"/>
+      <c r="I561" s="22"/>
     </row>
     <row r="562">
-      <c r="C562" s="22"/>
+      <c r="C562" s="23"/>
       <c r="F562" s="9"/>
       <c r="G562" s="9"/>
       <c r="H562" s="14"/>
-      <c r="I562" s="21"/>
+      <c r="I562" s="22"/>
     </row>
     <row r="563">
-      <c r="C563" s="22"/>
+      <c r="C563" s="23"/>
       <c r="F563" s="9"/>
       <c r="G563" s="9"/>
       <c r="H563" s="14"/>
-      <c r="I563" s="21"/>
+      <c r="I563" s="22"/>
     </row>
     <row r="564">
-      <c r="C564" s="22"/>
+      <c r="C564" s="23"/>
       <c r="F564" s="9"/>
       <c r="G564" s="9"/>
       <c r="H564" s="14"/>
-      <c r="I564" s="21"/>
+      <c r="I564" s="22"/>
     </row>
     <row r="565">
-      <c r="C565" s="22"/>
+      <c r="C565" s="23"/>
       <c r="F565" s="9"/>
       <c r="G565" s="9"/>
       <c r="H565" s="14"/>
-      <c r="I565" s="21"/>
+      <c r="I565" s="22"/>
     </row>
     <row r="566">
-      <c r="C566" s="22"/>
+      <c r="C566" s="23"/>
       <c r="F566" s="9"/>
       <c r="G566" s="9"/>
       <c r="H566" s="14"/>
-      <c r="I566" s="21"/>
+      <c r="I566" s="22"/>
     </row>
     <row r="567">
-      <c r="C567" s="22"/>
+      <c r="C567" s="23"/>
       <c r="F567" s="9"/>
       <c r="G567" s="9"/>
       <c r="H567" s="14"/>
-      <c r="I567" s="21"/>
+      <c r="I567" s="22"/>
     </row>
     <row r="568">
-      <c r="C568" s="22"/>
+      <c r="C568" s="23"/>
       <c r="F568" s="9"/>
       <c r="G568" s="9"/>
       <c r="H568" s="14"/>
-      <c r="I568" s="21"/>
+      <c r="I568" s="22"/>
     </row>
     <row r="569">
-      <c r="C569" s="22"/>
+      <c r="C569" s="23"/>
       <c r="F569" s="9"/>
       <c r="G569" s="9"/>
       <c r="H569" s="14"/>
-      <c r="I569" s="21"/>
+      <c r="I569" s="22"/>
     </row>
     <row r="570">
-      <c r="C570" s="22"/>
+      <c r="C570" s="23"/>
       <c r="F570" s="9"/>
       <c r="G570" s="9"/>
       <c r="H570" s="14"/>
-      <c r="I570" s="21"/>
+      <c r="I570" s="22"/>
     </row>
     <row r="571">
-      <c r="C571" s="22"/>
+      <c r="C571" s="23"/>
       <c r="F571" s="9"/>
       <c r="G571" s="9"/>
       <c r="H571" s="14"/>
-      <c r="I571" s="21"/>
+      <c r="I571" s="22"/>
     </row>
     <row r="572">
-      <c r="C572" s="22"/>
+      <c r="C572" s="23"/>
       <c r="F572" s="9"/>
       <c r="G572" s="9"/>
       <c r="H572" s="14"/>
-      <c r="I572" s="21"/>
+      <c r="I572" s="22"/>
     </row>
     <row r="573">
-      <c r="C573" s="22"/>
+      <c r="C573" s="23"/>
       <c r="F573" s="9"/>
       <c r="G573" s="9"/>
       <c r="H573" s="14"/>
-      <c r="I573" s="21"/>
+      <c r="I573" s="22"/>
     </row>
     <row r="574">
-      <c r="C574" s="22"/>
+      <c r="C574" s="23"/>
       <c r="F574" s="9"/>
       <c r="G574" s="9"/>
       <c r="H574" s="14"/>
-      <c r="I574" s="21"/>
+      <c r="I574" s="22"/>
     </row>
     <row r="575">
-      <c r="C575" s="22"/>
+      <c r="C575" s="23"/>
       <c r="F575" s="9"/>
       <c r="G575" s="9"/>
       <c r="H575" s="14"/>
-      <c r="I575" s="21"/>
+      <c r="I575" s="22"/>
     </row>
     <row r="576">
-      <c r="C576" s="22"/>
+      <c r="C576" s="23"/>
       <c r="F576" s="9"/>
       <c r="G576" s="9"/>
       <c r="H576" s="14"/>
-      <c r="I576" s="21"/>
+      <c r="I576" s="22"/>
     </row>
     <row r="577">
-      <c r="C577" s="22"/>
+      <c r="C577" s="23"/>
       <c r="F577" s="9"/>
       <c r="G577" s="9"/>
       <c r="H577" s="14"/>
-      <c r="I577" s="21"/>
+      <c r="I577" s="22"/>
     </row>
     <row r="578">
-      <c r="C578" s="22"/>
+      <c r="C578" s="23"/>
       <c r="F578" s="9"/>
       <c r="G578" s="9"/>
       <c r="H578" s="14"/>
-      <c r="I578" s="21"/>
+      <c r="I578" s="22"/>
     </row>
     <row r="579">
-      <c r="C579" s="22"/>
+      <c r="C579" s="23"/>
       <c r="F579" s="9"/>
       <c r="G579" s="9"/>
       <c r="H579" s="14"/>
-      <c r="I579" s="21"/>
+      <c r="I579" s="22"/>
     </row>
     <row r="580">
-      <c r="C580" s="22"/>
+      <c r="C580" s="23"/>
       <c r="F580" s="9"/>
       <c r="G580" s="9"/>
       <c r="H580" s="14"/>
-      <c r="I580" s="21"/>
+      <c r="I580" s="22"/>
     </row>
     <row r="581">
-      <c r="C581" s="22"/>
+      <c r="C581" s="23"/>
       <c r="F581" s="9"/>
       <c r="G581" s="9"/>
       <c r="H581" s="14"/>
-      <c r="I581" s="21"/>
+      <c r="I581" s="22"/>
     </row>
     <row r="582">
-      <c r="C582" s="22"/>
+      <c r="C582" s="23"/>
       <c r="F582" s="9"/>
       <c r="G582" s="9"/>
       <c r="H582" s="14"/>
-      <c r="I582" s="21"/>
+      <c r="I582" s="22"/>
     </row>
     <row r="583">
-      <c r="C583" s="22"/>
+      <c r="C583" s="23"/>
       <c r="F583" s="9"/>
       <c r="G583" s="9"/>
       <c r="H583" s="14"/>
-      <c r="I583" s="21"/>
+      <c r="I583" s="22"/>
     </row>
     <row r="584">
-      <c r="C584" s="22"/>
+      <c r="C584" s="23"/>
       <c r="F584" s="9"/>
       <c r="G584" s="9"/>
       <c r="H584" s="14"/>
-      <c r="I584" s="21"/>
+      <c r="I584" s="22"/>
     </row>
     <row r="585">
-      <c r="C585" s="22"/>
+      <c r="C585" s="23"/>
       <c r="F585" s="9"/>
       <c r="G585" s="9"/>
       <c r="H585" s="14"/>
-      <c r="I585" s="21"/>
+      <c r="I585" s="22"/>
     </row>
     <row r="586">
-      <c r="C586" s="22"/>
+      <c r="C586" s="23"/>
       <c r="F586" s="9"/>
       <c r="G586" s="9"/>
       <c r="H586" s="14"/>
-      <c r="I586" s="21"/>
+      <c r="I586" s="22"/>
     </row>
     <row r="587">
-      <c r="C587" s="22"/>
+      <c r="C587" s="23"/>
       <c r="F587" s="9"/>
       <c r="G587" s="9"/>
       <c r="H587" s="14"/>
-      <c r="I587" s="21"/>
+      <c r="I587" s="22"/>
     </row>
     <row r="588">
-      <c r="C588" s="22"/>
+      <c r="C588" s="23"/>
       <c r="F588" s="9"/>
       <c r="G588" s="9"/>
       <c r="H588" s="14"/>
-      <c r="I588" s="21"/>
+      <c r="I588" s="22"/>
     </row>
     <row r="589">
-      <c r="C589" s="22"/>
+      <c r="C589" s="23"/>
       <c r="F589" s="9"/>
       <c r="G589" s="9"/>
       <c r="H589" s="14"/>
-      <c r="I589" s="21"/>
+      <c r="I589" s="22"/>
     </row>
     <row r="590">
-      <c r="C590" s="22"/>
+      <c r="C590" s="23"/>
       <c r="F590" s="9"/>
       <c r="G590" s="9"/>
       <c r="H590" s="14"/>
-      <c r="I590" s="21"/>
+      <c r="I590" s="22"/>
     </row>
     <row r="591">
-      <c r="C591" s="22"/>
+      <c r="C591" s="23"/>
       <c r="F591" s="9"/>
       <c r="G591" s="9"/>
       <c r="H591" s="14"/>
-      <c r="I591" s="21"/>
+      <c r="I591" s="22"/>
     </row>
     <row r="592">
-      <c r="C592" s="22"/>
+      <c r="C592" s="23"/>
       <c r="F592" s="9"/>
       <c r="G592" s="9"/>
       <c r="H592" s="14"/>
-      <c r="I592" s="21"/>
+      <c r="I592" s="22"/>
     </row>
     <row r="593">
-      <c r="C593" s="22"/>
+      <c r="C593" s="23"/>
       <c r="F593" s="9"/>
       <c r="G593" s="9"/>
       <c r="H593" s="14"/>
-      <c r="I593" s="21"/>
+      <c r="I593" s="22"/>
     </row>
     <row r="594">
-      <c r="C594" s="22"/>
+      <c r="C594" s="23"/>
       <c r="F594" s="9"/>
       <c r="G594" s="9"/>
       <c r="H594" s="14"/>
-      <c r="I594" s="21"/>
+      <c r="I594" s="22"/>
     </row>
     <row r="595">
-      <c r="C595" s="22"/>
+      <c r="C595" s="23"/>
       <c r="F595" s="9"/>
       <c r="G595" s="9"/>
       <c r="H595" s="14"/>
-      <c r="I595" s="21"/>
+      <c r="I595" s="22"/>
     </row>
     <row r="596">
-      <c r="C596" s="22"/>
+      <c r="C596" s="23"/>
       <c r="F596" s="9"/>
       <c r="G596" s="9"/>
       <c r="H596" s="14"/>
-      <c r="I596" s="21"/>
+      <c r="I596" s="22"/>
     </row>
     <row r="597">
-      <c r="C597" s="22"/>
+      <c r="C597" s="23"/>
       <c r="F597" s="9"/>
       <c r="G597" s="9"/>
       <c r="H597" s="14"/>
-      <c r="I597" s="21"/>
+      <c r="I597" s="22"/>
     </row>
     <row r="598">
-      <c r="C598" s="22"/>
+      <c r="C598" s="23"/>
       <c r="F598" s="9"/>
       <c r="G598" s="9"/>
       <c r="H598" s="14"/>
-      <c r="I598" s="21"/>
+      <c r="I598" s="22"/>
     </row>
     <row r="599">
-      <c r="C599" s="22"/>
+      <c r="C599" s="23"/>
       <c r="F599" s="9"/>
       <c r="G599" s="9"/>
       <c r="H599" s="14"/>
-      <c r="I599" s="21"/>
+      <c r="I599" s="22"/>
     </row>
     <row r="600">
-      <c r="C600" s="22"/>
+      <c r="C600" s="23"/>
       <c r="F600" s="9"/>
       <c r="G600" s="9"/>
       <c r="H600" s="14"/>
-      <c r="I600" s="21"/>
+      <c r="I600" s="22"/>
     </row>
     <row r="601">
-      <c r="C601" s="22"/>
+      <c r="C601" s="23"/>
       <c r="F601" s="9"/>
       <c r="G601" s="9"/>
       <c r="H601" s="14"/>
-      <c r="I601" s="21"/>
+      <c r="I601" s="22"/>
     </row>
     <row r="602">
-      <c r="C602" s="22"/>
+      <c r="C602" s="23"/>
       <c r="F602" s="9"/>
       <c r="G602" s="9"/>
       <c r="H602" s="14"/>
-      <c r="I602" s="21"/>
+      <c r="I602" s="22"/>
     </row>
     <row r="603">
-      <c r="C603" s="22"/>
+      <c r="C603" s="23"/>
       <c r="F603" s="9"/>
       <c r="G603" s="9"/>
       <c r="H603" s="14"/>
-      <c r="I603" s="21"/>
+      <c r="I603" s="22"/>
     </row>
     <row r="604">
-      <c r="C604" s="22"/>
+      <c r="C604" s="23"/>
       <c r="F604" s="9"/>
       <c r="G604" s="9"/>
       <c r="H604" s="14"/>
-      <c r="I604" s="21"/>
+      <c r="I604" s="22"/>
     </row>
     <row r="605">
-      <c r="C605" s="22"/>
+      <c r="C605" s="23"/>
       <c r="F605" s="9"/>
       <c r="G605" s="9"/>
       <c r="H605" s="14"/>
-      <c r="I605" s="21"/>
+      <c r="I605" s="22"/>
     </row>
     <row r="606">
-      <c r="C606" s="22"/>
+      <c r="C606" s="23"/>
       <c r="F606" s="9"/>
       <c r="G606" s="9"/>
       <c r="H606" s="14"/>
-      <c r="I606" s="21"/>
+      <c r="I606" s="22"/>
     </row>
     <row r="607">
-      <c r="C607" s="22"/>
+      <c r="C607" s="23"/>
       <c r="F607" s="9"/>
       <c r="G607" s="9"/>
       <c r="H607" s="14"/>
-      <c r="I607" s="21"/>
+      <c r="I607" s="22"/>
     </row>
     <row r="608">
-      <c r="C608" s="22"/>
+      <c r="C608" s="23"/>
       <c r="F608" s="9"/>
       <c r="G608" s="9"/>
       <c r="H608" s="14"/>
-      <c r="I608" s="21"/>
+      <c r="I608" s="22"/>
     </row>
     <row r="609">
-      <c r="C609" s="22"/>
+      <c r="C609" s="23"/>
       <c r="F609" s="9"/>
       <c r="G609" s="9"/>
       <c r="H609" s="14"/>
-      <c r="I609" s="21"/>
+      <c r="I609" s="22"/>
     </row>
     <row r="610">
-      <c r="C610" s="22"/>
+      <c r="C610" s="23"/>
       <c r="F610" s="9"/>
       <c r="G610" s="9"/>
       <c r="H610" s="14"/>
-      <c r="I610" s="21"/>
+      <c r="I610" s="22"/>
     </row>
     <row r="611">
-      <c r="C611" s="22"/>
+      <c r="C611" s="23"/>
       <c r="F611" s="9"/>
       <c r="G611" s="9"/>
       <c r="H611" s="14"/>
-      <c r="I611" s="21"/>
+      <c r="I611" s="22"/>
     </row>
     <row r="612">
-      <c r="C612" s="22"/>
+      <c r="C612" s="23"/>
       <c r="F612" s="9"/>
       <c r="G612" s="9"/>
       <c r="H612" s="14"/>
-      <c r="I612" s="21"/>
+      <c r="I612" s="22"/>
     </row>
     <row r="613">
-      <c r="C613" s="22"/>
+      <c r="C613" s="23"/>
       <c r="F613" s="9"/>
       <c r="G613" s="9"/>
       <c r="H613" s="14"/>
-      <c r="I613" s="21"/>
+      <c r="I613" s="22"/>
     </row>
     <row r="614">
-      <c r="C614" s="22"/>
+      <c r="C614" s="23"/>
       <c r="F614" s="9"/>
       <c r="G614" s="9"/>
       <c r="H614" s="14"/>
-      <c r="I614" s="21"/>
+      <c r="I614" s="22"/>
     </row>
     <row r="615">
-      <c r="C615" s="22"/>
+      <c r="C615" s="23"/>
       <c r="F615" s="9"/>
       <c r="G615" s="9"/>
       <c r="H615" s="14"/>
-      <c r="I615" s="21"/>
+      <c r="I615" s="22"/>
     </row>
     <row r="616">
-      <c r="C616" s="22"/>
+      <c r="C616" s="23"/>
       <c r="F616" s="9"/>
       <c r="G616" s="9"/>
       <c r="H616" s="14"/>
-      <c r="I616" s="21"/>
+      <c r="I616" s="22"/>
     </row>
     <row r="617">
-      <c r="C617" s="22"/>
+      <c r="C617" s="23"/>
       <c r="F617" s="9"/>
       <c r="G617" s="9"/>
       <c r="H617" s="14"/>
-      <c r="I617" s="21"/>
+      <c r="I617" s="22"/>
     </row>
     <row r="618">
-      <c r="C618" s="22"/>
+      <c r="C618" s="23"/>
       <c r="F618" s="9"/>
       <c r="G618" s="9"/>
       <c r="H618" s="14"/>
-      <c r="I618" s="21"/>
+      <c r="I618" s="22"/>
     </row>
     <row r="619">
-      <c r="C619" s="22"/>
+      <c r="C619" s="23"/>
       <c r="F619" s="9"/>
       <c r="G619" s="9"/>
       <c r="H619" s="14"/>
-      <c r="I619" s="21"/>
+      <c r="I619" s="22"/>
     </row>
     <row r="620">
-      <c r="C620" s="22"/>
+      <c r="C620" s="23"/>
       <c r="F620" s="9"/>
       <c r="G620" s="9"/>
       <c r="H620" s="14"/>
-      <c r="I620" s="21"/>
+      <c r="I620" s="22"/>
     </row>
     <row r="621">
-      <c r="C621" s="22"/>
+      <c r="C621" s="23"/>
       <c r="F621" s="9"/>
       <c r="G621" s="9"/>
       <c r="H621" s="14"/>
-      <c r="I621" s="21"/>
+      <c r="I621" s="22"/>
     </row>
     <row r="622">
-      <c r="C622" s="22"/>
+      <c r="C622" s="23"/>
       <c r="F622" s="9"/>
       <c r="G622" s="9"/>
       <c r="H622" s="14"/>
-      <c r="I622" s="21"/>
+      <c r="I622" s="22"/>
     </row>
     <row r="623">
-      <c r="C623" s="22"/>
+      <c r="C623" s="23"/>
       <c r="F623" s="9"/>
       <c r="G623" s="9"/>
       <c r="H623" s="14"/>
-      <c r="I623" s="21"/>
+      <c r="I623" s="22"/>
     </row>
     <row r="624">
-      <c r="C624" s="22"/>
+      <c r="C624" s="23"/>
       <c r="F624" s="9"/>
       <c r="G624" s="9"/>
       <c r="H624" s="14"/>
-      <c r="I624" s="21"/>
+      <c r="I624" s="22"/>
     </row>
     <row r="625">
-      <c r="C625" s="22"/>
+      <c r="C625" s="23"/>
       <c r="F625" s="9"/>
       <c r="G625" s="9"/>
       <c r="H625" s="14"/>
-      <c r="I625" s="21"/>
+      <c r="I625" s="22"/>
     </row>
     <row r="626">
-      <c r="C626" s="22"/>
+      <c r="C626" s="23"/>
       <c r="F626" s="9"/>
       <c r="G626" s="9"/>
       <c r="H626" s="14"/>
-      <c r="I626" s="21"/>
+      <c r="I626" s="22"/>
     </row>
     <row r="627">
-      <c r="C627" s="22"/>
+      <c r="C627" s="23"/>
       <c r="F627" s="9"/>
       <c r="G627" s="9"/>
       <c r="H627" s="14"/>
-      <c r="I627" s="21"/>
+      <c r="I627" s="22"/>
     </row>
     <row r="628">
-      <c r="C628" s="22"/>
+      <c r="C628" s="23"/>
       <c r="F628" s="9"/>
       <c r="G628" s="9"/>
       <c r="H628" s="14"/>
-      <c r="I628" s="21"/>
+      <c r="I628" s="22"/>
     </row>
     <row r="629">
-      <c r="C629" s="22"/>
+      <c r="C629" s="23"/>
       <c r="F629" s="9"/>
       <c r="G629" s="9"/>
       <c r="H629" s="14"/>
-      <c r="I629" s="21"/>
+      <c r="I629" s="22"/>
     </row>
     <row r="630">
-      <c r="C630" s="22"/>
+      <c r="C630" s="23"/>
       <c r="F630" s="9"/>
       <c r="G630" s="9"/>
       <c r="H630" s="14"/>
-      <c r="I630" s="21"/>
+      <c r="I630" s="22"/>
     </row>
     <row r="631">
-      <c r="C631" s="22"/>
+      <c r="C631" s="23"/>
       <c r="F631" s="9"/>
       <c r="G631" s="9"/>
       <c r="H631" s="14"/>
-      <c r="I631" s="21"/>
+      <c r="I631" s="22"/>
     </row>
     <row r="632">
-      <c r="C632" s="22"/>
+      <c r="C632" s="23"/>
       <c r="F632" s="9"/>
       <c r="G632" s="9"/>
       <c r="H632" s="14"/>
-      <c r="I632" s="21"/>
+      <c r="I632" s="22"/>
     </row>
     <row r="633">
-      <c r="C633" s="22"/>
+      <c r="C633" s="23"/>
       <c r="F633" s="9"/>
       <c r="G633" s="9"/>
       <c r="H633" s="14"/>
-      <c r="I633" s="21"/>
+      <c r="I633" s="22"/>
     </row>
     <row r="634">
-      <c r="C634" s="22"/>
+      <c r="C634" s="23"/>
       <c r="F634" s="9"/>
       <c r="G634" s="9"/>
       <c r="H634" s="14"/>
-      <c r="I634" s="21"/>
+      <c r="I634" s="22"/>
     </row>
     <row r="635">
-      <c r="C635" s="22"/>
+      <c r="C635" s="23"/>
       <c r="F635" s="9"/>
       <c r="G635" s="9"/>
       <c r="H635" s="14"/>
-      <c r="I635" s="21"/>
+      <c r="I635" s="22"/>
     </row>
     <row r="636">
-      <c r="C636" s="22"/>
+      <c r="C636" s="23"/>
       <c r="F636" s="9"/>
       <c r="G636" s="9"/>
       <c r="H636" s="14"/>
-      <c r="I636" s="21"/>
+      <c r="I636" s="22"/>
     </row>
     <row r="637">
-      <c r="C637" s="22"/>
+      <c r="C637" s="23"/>
       <c r="F637" s="9"/>
       <c r="G637" s="9"/>
       <c r="H637" s="14"/>
-      <c r="I637" s="21"/>
+      <c r="I637" s="22"/>
     </row>
     <row r="638">
-      <c r="C638" s="22"/>
+      <c r="C638" s="23"/>
       <c r="F638" s="9"/>
       <c r="G638" s="9"/>
       <c r="H638" s="14"/>
-      <c r="I638" s="21"/>
+      <c r="I638" s="22"/>
     </row>
     <row r="639">
-      <c r="C639" s="22"/>
+      <c r="C639" s="23"/>
       <c r="F639" s="9"/>
       <c r="G639" s="9"/>
       <c r="H639" s="14"/>
-      <c r="I639" s="21"/>
+      <c r="I639" s="22"/>
     </row>
     <row r="640">
-      <c r="C640" s="22"/>
+      <c r="C640" s="23"/>
       <c r="F640" s="9"/>
       <c r="G640" s="9"/>
       <c r="H640" s="14"/>
-      <c r="I640" s="21"/>
+      <c r="I640" s="22"/>
     </row>
     <row r="641">
-      <c r="C641" s="22"/>
+      <c r="C641" s="23"/>
       <c r="F641" s="9"/>
       <c r="G641" s="9"/>
       <c r="H641" s="14"/>
-      <c r="I641" s="21"/>
+      <c r="I641" s="22"/>
     </row>
     <row r="642">
-      <c r="C642" s="22"/>
+      <c r="C642" s="23"/>
       <c r="F642" s="9"/>
       <c r="G642" s="9"/>
       <c r="H642" s="14"/>
-      <c r="I642" s="21"/>
+      <c r="I642" s="22"/>
     </row>
     <row r="643">
-      <c r="C643" s="22"/>
+      <c r="C643" s="23"/>
       <c r="F643" s="9"/>
       <c r="G643" s="9"/>
       <c r="H643" s="14"/>
-      <c r="I643" s="21"/>
+      <c r="I643" s="22"/>
     </row>
     <row r="644">
-      <c r="C644" s="22"/>
+      <c r="C644" s="23"/>
       <c r="F644" s="9"/>
       <c r="G644" s="9"/>
       <c r="H644" s="14"/>
-      <c r="I644" s="21"/>
+      <c r="I644" s="22"/>
     </row>
     <row r="645">
-      <c r="C645" s="22"/>
+      <c r="C645" s="23"/>
       <c r="F645" s="9"/>
       <c r="G645" s="9"/>
       <c r="H645" s="14"/>
-      <c r="I645" s="21"/>
+      <c r="I645" s="22"/>
     </row>
     <row r="646">
-      <c r="C646" s="22"/>
+      <c r="C646" s="23"/>
       <c r="F646" s="9"/>
       <c r="G646" s="9"/>
       <c r="H646" s="14"/>
-      <c r="I646" s="21"/>
+      <c r="I646" s="22"/>
     </row>
     <row r="647">
-      <c r="C647" s="22"/>
+      <c r="C647" s="23"/>
       <c r="F647" s="9"/>
       <c r="G647" s="9"/>
       <c r="H647" s="14"/>
-      <c r="I647" s="21"/>
+      <c r="I647" s="22"/>
     </row>
     <row r="648">
-      <c r="C648" s="22"/>
+      <c r="C648" s="23"/>
       <c r="F648" s="9"/>
       <c r="G648" s="9"/>
       <c r="H648" s="14"/>
-      <c r="I648" s="21"/>
+      <c r="I648" s="22"/>
     </row>
     <row r="649">
-      <c r="C649" s="22"/>
+      <c r="C649" s="23"/>
       <c r="F649" s="9"/>
       <c r="G649" s="9"/>
       <c r="H649" s="14"/>
-      <c r="I649" s="21"/>
+      <c r="I649" s="22"/>
     </row>
     <row r="650">
-      <c r="C650" s="22"/>
+      <c r="C650" s="23"/>
       <c r="F650" s="9"/>
       <c r="G650" s="9"/>
       <c r="H650" s="14"/>
-      <c r="I650" s="21"/>
+      <c r="I650" s="22"/>
     </row>
     <row r="651">
-      <c r="C651" s="22"/>
+      <c r="C651" s="23"/>
       <c r="F651" s="9"/>
       <c r="G651" s="9"/>
       <c r="H651" s="14"/>
-      <c r="I651" s="21"/>
+      <c r="I651" s="22"/>
     </row>
     <row r="652">
-      <c r="C652" s="22"/>
+      <c r="C652" s="23"/>
       <c r="F652" s="9"/>
       <c r="G652" s="9"/>
       <c r="H652" s="14"/>
-      <c r="I652" s="21"/>
+      <c r="I652" s="22"/>
     </row>
     <row r="653">
-      <c r="C653" s="22"/>
+      <c r="C653" s="23"/>
       <c r="F653" s="9"/>
       <c r="G653" s="9"/>
       <c r="H653" s="14"/>
-      <c r="I653" s="21"/>
+      <c r="I653" s="22"/>
     </row>
     <row r="654">
-      <c r="C654" s="22"/>
+      <c r="C654" s="23"/>
       <c r="F654" s="9"/>
       <c r="G654" s="9"/>
       <c r="H654" s="14"/>
-      <c r="I654" s="21"/>
+      <c r="I654" s="22"/>
     </row>
     <row r="655">
-      <c r="C655" s="22"/>
+      <c r="C655" s="23"/>
       <c r="F655" s="9"/>
       <c r="G655" s="9"/>
       <c r="H655" s="14"/>
-      <c r="I655" s="21"/>
+      <c r="I655" s="22"/>
     </row>
     <row r="656">
-      <c r="C656" s="22"/>
+      <c r="C656" s="23"/>
       <c r="F656" s="9"/>
       <c r="G656" s="9"/>
       <c r="H656" s="14"/>
-      <c r="I656" s="21"/>
+      <c r="I656" s="22"/>
     </row>
     <row r="657">
-      <c r="C657" s="22"/>
+      <c r="C657" s="23"/>
       <c r="F657" s="9"/>
       <c r="G657" s="9"/>
       <c r="H657" s="14"/>
-      <c r="I657" s="21"/>
+      <c r="I657" s="22"/>
     </row>
     <row r="658">
-      <c r="C658" s="22"/>
+      <c r="C658" s="23"/>
       <c r="F658" s="9"/>
       <c r="G658" s="9"/>
       <c r="H658" s="14"/>
-      <c r="I658" s="21"/>
+      <c r="I658" s="22"/>
     </row>
     <row r="659">
-      <c r="C659" s="22"/>
+      <c r="C659" s="23"/>
       <c r="F659" s="9"/>
       <c r="G659" s="9"/>
       <c r="H659" s="14"/>
-      <c r="I659" s="21"/>
+      <c r="I659" s="22"/>
     </row>
     <row r="660">
-      <c r="C660" s="22"/>
+      <c r="C660" s="23"/>
       <c r="F660" s="9"/>
       <c r="G660" s="9"/>
       <c r="H660" s="14"/>
-      <c r="I660" s="21"/>
+      <c r="I660" s="22"/>
     </row>
     <row r="661">
-      <c r="C661" s="22"/>
+      <c r="C661" s="23"/>
       <c r="F661" s="9"/>
       <c r="G661" s="9"/>
       <c r="H661" s="14"/>
-      <c r="I661" s="21"/>
+      <c r="I661" s="22"/>
     </row>
     <row r="662">
-      <c r="C662" s="22"/>
+      <c r="C662" s="23"/>
       <c r="F662" s="9"/>
       <c r="G662" s="9"/>
       <c r="H662" s="14"/>
-      <c r="I662" s="21"/>
+      <c r="I662" s="22"/>
     </row>
     <row r="663">
-      <c r="C663" s="22"/>
+      <c r="C663" s="23"/>
       <c r="F663" s="9"/>
       <c r="G663" s="9"/>
       <c r="H663" s="14"/>
-      <c r="I663" s="21"/>
+      <c r="I663" s="22"/>
     </row>
     <row r="664">
-      <c r="C664" s="22"/>
+      <c r="C664" s="23"/>
       <c r="F664" s="9"/>
       <c r="G664" s="9"/>
       <c r="H664" s="14"/>
-      <c r="I664" s="21"/>
+      <c r="I664" s="22"/>
     </row>
     <row r="665">
-      <c r="C665" s="22"/>
+      <c r="C665" s="23"/>
       <c r="F665" s="9"/>
       <c r="G665" s="9"/>
       <c r="H665" s="14"/>
-      <c r="I665" s="21"/>
+      <c r="I665" s="22"/>
     </row>
     <row r="666">
-      <c r="C666" s="22"/>
+      <c r="C666" s="23"/>
       <c r="F666" s="9"/>
       <c r="G666" s="9"/>
       <c r="H666" s="14"/>
-      <c r="I666" s="21"/>
+      <c r="I666" s="22"/>
     </row>
     <row r="667">
-      <c r="C667" s="22"/>
+      <c r="C667" s="23"/>
       <c r="F667" s="9"/>
       <c r="G667" s="9"/>
       <c r="H667" s="14"/>
-      <c r="I667" s="21"/>
+      <c r="I667" s="22"/>
     </row>
     <row r="668">
-      <c r="C668" s="22"/>
+      <c r="C668" s="23"/>
       <c r="F668" s="9"/>
       <c r="G668" s="9"/>
       <c r="H668" s="14"/>
-      <c r="I668" s="21"/>
+      <c r="I668" s="22"/>
     </row>
     <row r="669">
-      <c r="C669" s="22"/>
+      <c r="C669" s="23"/>
       <c r="F669" s="9"/>
       <c r="G669" s="9"/>
       <c r="H669" s="14"/>
-      <c r="I669" s="21"/>
+      <c r="I669" s="22"/>
     </row>
     <row r="670">
-      <c r="C670" s="22"/>
+      <c r="C670" s="23"/>
       <c r="F670" s="9"/>
       <c r="G670" s="9"/>
       <c r="H670" s="14"/>
-      <c r="I670" s="21"/>
+      <c r="I670" s="22"/>
     </row>
     <row r="671">
-      <c r="C671" s="22"/>
+      <c r="C671" s="23"/>
       <c r="F671" s="9"/>
       <c r="G671" s="9"/>
       <c r="H671" s="14"/>
-      <c r="I671" s="21"/>
+      <c r="I671" s="22"/>
     </row>
     <row r="672">
-      <c r="C672" s="22"/>
+      <c r="C672" s="23"/>
       <c r="F672" s="9"/>
       <c r="G672" s="9"/>
       <c r="H672" s="14"/>
-      <c r="I672" s="21"/>
+      <c r="I672" s="22"/>
     </row>
     <row r="673">
-      <c r="C673" s="22"/>
+      <c r="C673" s="23"/>
       <c r="F673" s="9"/>
       <c r="G673" s="9"/>
       <c r="H673" s="14"/>
-      <c r="I673" s="21"/>
+      <c r="I673" s="22"/>
     </row>
     <row r="674">
-      <c r="C674" s="22"/>
+      <c r="C674" s="23"/>
       <c r="F674" s="9"/>
       <c r="G674" s="9"/>
       <c r="H674" s="14"/>
-      <c r="I674" s="21"/>
+      <c r="I674" s="22"/>
     </row>
     <row r="675">
-      <c r="C675" s="22"/>
+      <c r="C675" s="23"/>
       <c r="F675" s="9"/>
       <c r="G675" s="9"/>
       <c r="H675" s="14"/>
-      <c r="I675" s="21"/>
+      <c r="I675" s="22"/>
     </row>
     <row r="676">
-      <c r="C676" s="22"/>
+      <c r="C676" s="23"/>
       <c r="F676" s="9"/>
       <c r="G676" s="9"/>
       <c r="H676" s="14"/>
-      <c r="I676" s="21"/>
+      <c r="I676" s="22"/>
     </row>
     <row r="677">
-      <c r="C677" s="22"/>
+      <c r="C677" s="23"/>
       <c r="F677" s="9"/>
       <c r="G677" s="9"/>
       <c r="H677" s="14"/>
-      <c r="I677" s="21"/>
+      <c r="I677" s="22"/>
     </row>
     <row r="678">
-      <c r="C678" s="22"/>
+      <c r="C678" s="23"/>
       <c r="F678" s="9"/>
       <c r="G678" s="9"/>
       <c r="H678" s="14"/>
-      <c r="I678" s="21"/>
+      <c r="I678" s="22"/>
     </row>
     <row r="679">
-      <c r="C679" s="22"/>
+      <c r="C679" s="23"/>
       <c r="F679" s="9"/>
       <c r="G679" s="9"/>
       <c r="H679" s="14"/>
-      <c r="I679" s="21"/>
+      <c r="I679" s="22"/>
     </row>
     <row r="680">
-      <c r="C680" s="22"/>
+      <c r="C680" s="23"/>
       <c r="F680" s="9"/>
       <c r="G680" s="9"/>
       <c r="H680" s="14"/>
-      <c r="I680" s="21"/>
+      <c r="I680" s="22"/>
     </row>
     <row r="681">
-      <c r="C681" s="22"/>
+      <c r="C681" s="23"/>
       <c r="F681" s="9"/>
       <c r="G681" s="9"/>
       <c r="H681" s="14"/>
-      <c r="I681" s="21"/>
+      <c r="I681" s="22"/>
     </row>
     <row r="682">
-      <c r="C682" s="22"/>
+      <c r="C682" s="23"/>
       <c r="F682" s="9"/>
       <c r="G682" s="9"/>
       <c r="H682" s="14"/>
-      <c r="I682" s="21"/>
+      <c r="I682" s="22"/>
     </row>
     <row r="683">
-      <c r="C683" s="22"/>
+      <c r="C683" s="23"/>
       <c r="F683" s="9"/>
       <c r="G683" s="9"/>
       <c r="H683" s="14"/>
-      <c r="I683" s="21"/>
+      <c r="I683" s="22"/>
     </row>
     <row r="684">
-      <c r="C684" s="22"/>
+      <c r="C684" s="23"/>
       <c r="F684" s="9"/>
       <c r="G684" s="9"/>
       <c r="H684" s="14"/>
-      <c r="I684" s="21"/>
+      <c r="I684" s="22"/>
     </row>
     <row r="685">
-      <c r="C685" s="22"/>
+      <c r="C685" s="23"/>
       <c r="F685" s="9"/>
       <c r="G685" s="9"/>
       <c r="H685" s="14"/>
-      <c r="I685" s="21"/>
+      <c r="I685" s="22"/>
     </row>
     <row r="686">
-      <c r="C686" s="22"/>
+      <c r="C686" s="23"/>
       <c r="F686" s="9"/>
       <c r="G686" s="9"/>
       <c r="H686" s="14"/>
-      <c r="I686" s="21"/>
+      <c r="I686" s="22"/>
     </row>
     <row r="687">
-      <c r="C687" s="22"/>
+      <c r="C687" s="23"/>
       <c r="F687" s="9"/>
       <c r="G687" s="9"/>
       <c r="H687" s="14"/>
-      <c r="I687" s="21"/>
+      <c r="I687" s="22"/>
     </row>
     <row r="688">
-      <c r="C688" s="22"/>
+      <c r="C688" s="23"/>
       <c r="F688" s="9"/>
       <c r="G688" s="9"/>
       <c r="H688" s="14"/>
-      <c r="I688" s="21"/>
+      <c r="I688" s="22"/>
     </row>
     <row r="689">
-      <c r="C689" s="22"/>
+      <c r="C689" s="23"/>
       <c r="F689" s="9"/>
       <c r="G689" s="9"/>
       <c r="H689" s="14"/>
-      <c r="I689" s="21"/>
+      <c r="I689" s="22"/>
     </row>
     <row r="690">
-      <c r="C690" s="22"/>
+      <c r="C690" s="23"/>
       <c r="F690" s="9"/>
       <c r="G690" s="9"/>
       <c r="H690" s="14"/>
-      <c r="I690" s="21"/>
+      <c r="I690" s="22"/>
     </row>
     <row r="691">
-      <c r="C691" s="22"/>
+      <c r="C691" s="23"/>
       <c r="F691" s="9"/>
       <c r="G691" s="9"/>
       <c r="H691" s="14"/>
-      <c r="I691" s="21"/>
+      <c r="I691" s="22"/>
     </row>
     <row r="692">
-      <c r="C692" s="22"/>
+      <c r="C692" s="23"/>
       <c r="F692" s="9"/>
       <c r="G692" s="9"/>
       <c r="H692" s="14"/>
-      <c r="I692" s="21"/>
+      <c r="I692" s="22"/>
     </row>
     <row r="693">
-      <c r="C693" s="22"/>
+      <c r="C693" s="23"/>
       <c r="F693" s="9"/>
       <c r="G693" s="9"/>
       <c r="H693" s="14"/>
-      <c r="I693" s="21"/>
+      <c r="I693" s="22"/>
     </row>
     <row r="694">
-      <c r="C694" s="22"/>
+      <c r="C694" s="23"/>
       <c r="F694" s="9"/>
       <c r="G694" s="9"/>
       <c r="H694" s="14"/>
-      <c r="I694" s="21"/>
+      <c r="I694" s="22"/>
     </row>
     <row r="695">
-      <c r="C695" s="22"/>
+      <c r="C695" s="23"/>
       <c r="F695" s="9"/>
       <c r="G695" s="9"/>
       <c r="H695" s="14"/>
-      <c r="I695" s="21"/>
+      <c r="I695" s="22"/>
     </row>
     <row r="696">
-      <c r="C696" s="22"/>
+      <c r="C696" s="23"/>
       <c r="F696" s="9"/>
       <c r="G696" s="9"/>
       <c r="H696" s="14"/>
-      <c r="I696" s="21"/>
+      <c r="I696" s="22"/>
     </row>
     <row r="697">
-      <c r="C697" s="22"/>
+      <c r="C697" s="23"/>
       <c r="F697" s="9"/>
       <c r="G697" s="9"/>
       <c r="H697" s="14"/>
-      <c r="I697" s="21"/>
+      <c r="I697" s="22"/>
     </row>
     <row r="698">
-      <c r="C698" s="22"/>
+      <c r="C698" s="23"/>
       <c r="F698" s="9"/>
       <c r="G698" s="9"/>
       <c r="H698" s="14"/>
-      <c r="I698" s="21"/>
+      <c r="I698" s="22"/>
     </row>
     <row r="699">
-      <c r="C699" s="22"/>
+      <c r="C699" s="23"/>
       <c r="F699" s="9"/>
       <c r="G699" s="9"/>
       <c r="H699" s="14"/>
-      <c r="I699" s="21"/>
+      <c r="I699" s="22"/>
     </row>
     <row r="700">
-      <c r="C700" s="22"/>
+      <c r="C700" s="23"/>
       <c r="F700" s="9"/>
       <c r="G700" s="9"/>
       <c r="H700" s="14"/>
-      <c r="I700" s="21"/>
+      <c r="I700" s="22"/>
     </row>
     <row r="701">
-      <c r="C701" s="22"/>
+      <c r="C701" s="23"/>
       <c r="F701" s="9"/>
       <c r="G701" s="9"/>
       <c r="H701" s="14"/>
-      <c r="I701" s="21"/>
+      <c r="I701" s="22"/>
     </row>
     <row r="702">
-      <c r="C702" s="22"/>
+      <c r="C702" s="23"/>
       <c r="F702" s="9"/>
       <c r="G702" s="9"/>
       <c r="H702" s="14"/>
-      <c r="I702" s="21"/>
+      <c r="I702" s="22"/>
     </row>
     <row r="703">
-      <c r="C703" s="22"/>
+      <c r="C703" s="23"/>
       <c r="F703" s="9"/>
       <c r="G703" s="9"/>
       <c r="H703" s="14"/>
-      <c r="I703" s="21"/>
+      <c r="I703" s="22"/>
     </row>
     <row r="704">
-      <c r="C704" s="22"/>
+      <c r="C704" s="23"/>
       <c r="F704" s="9"/>
       <c r="G704" s="9"/>
       <c r="H704" s="14"/>
-      <c r="I704" s="21"/>
+      <c r="I704" s="22"/>
     </row>
     <row r="705">
-      <c r="C705" s="22"/>
+      <c r="C705" s="23"/>
       <c r="F705" s="9"/>
       <c r="G705" s="9"/>
       <c r="H705" s="14"/>
-      <c r="I705" s="21"/>
+      <c r="I705" s="22"/>
     </row>
     <row r="706">
-      <c r="C706" s="22"/>
+      <c r="C706" s="23"/>
       <c r="F706" s="9"/>
       <c r="G706" s="9"/>
       <c r="H706" s="14"/>
-      <c r="I706" s="21"/>
+      <c r="I706" s="22"/>
     </row>
     <row r="707">
-      <c r="C707" s="22"/>
+      <c r="C707" s="23"/>
       <c r="F707" s="9"/>
       <c r="G707" s="9"/>
       <c r="H707" s="14"/>
-      <c r="I707" s="21"/>
+      <c r="I707" s="22"/>
     </row>
     <row r="708">
-      <c r="C708" s="22"/>
+      <c r="C708" s="23"/>
       <c r="F708" s="9"/>
       <c r="G708" s="9"/>
       <c r="H708" s="14"/>
-      <c r="I708" s="21"/>
+      <c r="I708" s="22"/>
     </row>
     <row r="709">
-      <c r="C709" s="22"/>
+      <c r="C709" s="23"/>
       <c r="F709" s="9"/>
       <c r="G709" s="9"/>
       <c r="H709" s="14"/>
-      <c r="I709" s="21"/>
+      <c r="I709" s="22"/>
     </row>
     <row r="710">
-      <c r="C710" s="22"/>
+      <c r="C710" s="23"/>
       <c r="F710" s="9"/>
       <c r="G710" s="9"/>
       <c r="H710" s="14"/>
-      <c r="I710" s="21"/>
+      <c r="I710" s="22"/>
     </row>
     <row r="711">
-      <c r="C711" s="22"/>
+      <c r="C711" s="23"/>
       <c r="F711" s="9"/>
       <c r="G711" s="9"/>
       <c r="H711" s="14"/>
-      <c r="I711" s="21"/>
+      <c r="I711" s="22"/>
     </row>
     <row r="712">
-      <c r="C712" s="22"/>
+      <c r="C712" s="23"/>
       <c r="F712" s="9"/>
       <c r="G712" s="9"/>
       <c r="H712" s="14"/>
-      <c r="I712" s="21"/>
+      <c r="I712" s="22"/>
     </row>
     <row r="713">
-      <c r="C713" s="22"/>
+      <c r="C713" s="23"/>
       <c r="F713" s="9"/>
       <c r="G713" s="9"/>
       <c r="H713" s="14"/>
-      <c r="I713" s="21"/>
+      <c r="I713" s="22"/>
     </row>
     <row r="714">
-      <c r="C714" s="22"/>
+      <c r="C714" s="23"/>
       <c r="F714" s="9"/>
       <c r="G714" s="9"/>
       <c r="H714" s="14"/>
-      <c r="I714" s="21"/>
+      <c r="I714" s="22"/>
     </row>
     <row r="715">
-      <c r="C715" s="22"/>
+      <c r="C715" s="23"/>
       <c r="F715" s="9"/>
       <c r="G715" s="9"/>
       <c r="H715" s="14"/>
-      <c r="I715" s="21"/>
+      <c r="I715" s="22"/>
     </row>
     <row r="716">
-      <c r="C716" s="22"/>
+      <c r="C716" s="23"/>
       <c r="F716" s="9"/>
       <c r="G716" s="9"/>
       <c r="H716" s="14"/>
-      <c r="I716" s="21"/>
+      <c r="I716" s="22"/>
     </row>
     <row r="717">
-      <c r="C717" s="22"/>
+      <c r="C717" s="23"/>
       <c r="F717" s="9"/>
       <c r="G717" s="9"/>
       <c r="H717" s="14"/>
-      <c r="I717" s="21"/>
+      <c r="I717" s="22"/>
     </row>
     <row r="718">
-      <c r="C718" s="22"/>
+      <c r="C718" s="23"/>
       <c r="F718" s="9"/>
       <c r="G718" s="9"/>
       <c r="H718" s="14"/>
-      <c r="I718" s="21"/>
+      <c r="I718" s="22"/>
     </row>
     <row r="719">
-      <c r="C719" s="22"/>
+      <c r="C719" s="23"/>
       <c r="F719" s="9"/>
       <c r="G719" s="9"/>
       <c r="H719" s="14"/>
-      <c r="I719" s="21"/>
+      <c r="I719" s="22"/>
     </row>
     <row r="720">
-      <c r="C720" s="22"/>
+      <c r="C720" s="23"/>
       <c r="F720" s="9"/>
       <c r="G720" s="9"/>
       <c r="H720" s="14"/>
-      <c r="I720" s="21"/>
+      <c r="I720" s="22"/>
     </row>
     <row r="721">
-      <c r="C721" s="22"/>
+      <c r="C721" s="23"/>
       <c r="F721" s="9"/>
       <c r="G721" s="9"/>
       <c r="H721" s="14"/>
-      <c r="I721" s="21"/>
+      <c r="I721" s="22"/>
     </row>
     <row r="722">
-      <c r="C722" s="22"/>
+      <c r="C722" s="23"/>
       <c r="F722" s="9"/>
       <c r="G722" s="9"/>
       <c r="H722" s="14"/>
-      <c r="I722" s="21"/>
+      <c r="I722" s="22"/>
     </row>
     <row r="723">
-      <c r="C723" s="22"/>
+      <c r="C723" s="23"/>
       <c r="F723" s="9"/>
       <c r="G723" s="9"/>
       <c r="H723" s="14"/>
-      <c r="I723" s="21"/>
+      <c r="I723" s="22"/>
     </row>
     <row r="724">
-      <c r="C724" s="22"/>
+      <c r="C724" s="23"/>
       <c r="F724" s="9"/>
       <c r="G724" s="9"/>
       <c r="H724" s="14"/>
-      <c r="I724" s="21"/>
+      <c r="I724" s="22"/>
     </row>
     <row r="725">
-      <c r="C725" s="22"/>
+      <c r="C725" s="23"/>
       <c r="F725" s="9"/>
       <c r="G725" s="9"/>
       <c r="H725" s="14"/>
-      <c r="I725" s="21"/>
+      <c r="I725" s="22"/>
     </row>
     <row r="726">
-      <c r="C726" s="22"/>
+      <c r="C726" s="23"/>
       <c r="F726" s="9"/>
       <c r="G726" s="9"/>
       <c r="H726" s="14"/>
-      <c r="I726" s="21"/>
+      <c r="I726" s="22"/>
     </row>
     <row r="727">
-      <c r="C727" s="22"/>
+      <c r="C727" s="23"/>
       <c r="F727" s="9"/>
       <c r="G727" s="9"/>
       <c r="H727" s="14"/>
-      <c r="I727" s="21"/>
+      <c r="I727" s="22"/>
     </row>
     <row r="728">
-      <c r="C728" s="22"/>
+      <c r="C728" s="23"/>
       <c r="F728" s="9"/>
       <c r="G728" s="9"/>
       <c r="H728" s="14"/>
-      <c r="I728" s="21"/>
+      <c r="I728" s="22"/>
     </row>
     <row r="729">
-      <c r="C729" s="22"/>
+      <c r="C729" s="23"/>
       <c r="F729" s="9"/>
       <c r="G729" s="9"/>
       <c r="H729" s="14"/>
-      <c r="I729" s="21"/>
+      <c r="I729" s="22"/>
     </row>
     <row r="730">
-      <c r="C730" s="22"/>
+      <c r="C730" s="23"/>
       <c r="F730" s="9"/>
       <c r="G730" s="9"/>
       <c r="H730" s="14"/>
-      <c r="I730" s="21"/>
+      <c r="I730" s="22"/>
     </row>
     <row r="731">
-      <c r="C731" s="22"/>
+      <c r="C731" s="23"/>
       <c r="F731" s="9"/>
       <c r="G731" s="9"/>
       <c r="H731" s="14"/>
-      <c r="I731" s="21"/>
+      <c r="I731" s="22"/>
     </row>
     <row r="732">
-      <c r="C732" s="22"/>
+      <c r="C732" s="23"/>
       <c r="F732" s="9"/>
       <c r="G732" s="9"/>
       <c r="H732" s="14"/>
-      <c r="I732" s="21"/>
+      <c r="I732" s="22"/>
     </row>
     <row r="733">
-      <c r="C733" s="22"/>
+      <c r="C733" s="23"/>
       <c r="F733" s="9"/>
       <c r="G733" s="9"/>
       <c r="H733" s="14"/>
-      <c r="I733" s="21"/>
+      <c r="I733" s="22"/>
     </row>
     <row r="734">
-      <c r="C734" s="22"/>
+      <c r="C734" s="23"/>
       <c r="F734" s="9"/>
       <c r="G734" s="9"/>
       <c r="H734" s="14"/>
-      <c r="I734" s="21"/>
+      <c r="I734" s="22"/>
     </row>
     <row r="735">
-      <c r="C735" s="22"/>
+      <c r="C735" s="23"/>
       <c r="F735" s="9"/>
       <c r="G735" s="9"/>
       <c r="H735" s="14"/>
-      <c r="I735" s="21"/>
+      <c r="I735" s="22"/>
     </row>
     <row r="736">
-      <c r="C736" s="22"/>
+      <c r="C736" s="23"/>
       <c r="F736" s="9"/>
       <c r="G736" s="9"/>
       <c r="H736" s="14"/>
-      <c r="I736" s="21"/>
+      <c r="I736" s="22"/>
     </row>
     <row r="737">
-      <c r="C737" s="22"/>
+      <c r="C737" s="23"/>
       <c r="F737" s="9"/>
       <c r="G737" s="9"/>
       <c r="H737" s="14"/>
-      <c r="I737" s="21"/>
+      <c r="I737" s="22"/>
     </row>
     <row r="738">
-      <c r="C738" s="22"/>
+      <c r="C738" s="23"/>
       <c r="F738" s="9"/>
       <c r="G738" s="9"/>
       <c r="H738" s="14"/>
-      <c r="I738" s="21"/>
+      <c r="I738" s="22"/>
     </row>
     <row r="739">
-      <c r="C739" s="22"/>
+      <c r="C739" s="23"/>
       <c r="F739" s="9"/>
       <c r="G739" s="9"/>
       <c r="H739" s="14"/>
-      <c r="I739" s="21"/>
+      <c r="I739" s="22"/>
     </row>
     <row r="740">
-      <c r="C740" s="22"/>
+      <c r="C740" s="23"/>
       <c r="F740" s="9"/>
       <c r="G740" s="9"/>
       <c r="H740" s="14"/>
-      <c r="I740" s="21"/>
+      <c r="I740" s="22"/>
     </row>
     <row r="741">
-      <c r="C741" s="22"/>
+      <c r="C741" s="23"/>
       <c r="F741" s="9"/>
       <c r="G741" s="9"/>
       <c r="H741" s="14"/>
-      <c r="I741" s="21"/>
+      <c r="I741" s="22"/>
     </row>
     <row r="742">
-      <c r="C742" s="22"/>
+      <c r="C742" s="23"/>
       <c r="F742" s="9"/>
       <c r="G742" s="9"/>
       <c r="H742" s="14"/>
-      <c r="I742" s="21"/>
+      <c r="I742" s="22"/>
     </row>
     <row r="743">
-      <c r="C743" s="22"/>
+      <c r="C743" s="23"/>
       <c r="F743" s="9"/>
       <c r="G743" s="9"/>
       <c r="H743" s="14"/>
-      <c r="I743" s="21"/>
+      <c r="I743" s="22"/>
     </row>
     <row r="744">
-      <c r="C744" s="22"/>
+      <c r="C744" s="23"/>
       <c r="F744" s="9"/>
       <c r="G744" s="9"/>
       <c r="H744" s="14"/>
-      <c r="I744" s="21"/>
+      <c r="I744" s="22"/>
     </row>
     <row r="745">
-      <c r="C745" s="22"/>
+      <c r="C745" s="23"/>
       <c r="F745" s="9"/>
       <c r="G745" s="9"/>
       <c r="H745" s="14"/>
-      <c r="I745" s="21"/>
+      <c r="I745" s="22"/>
     </row>
     <row r="746">
-      <c r="C746" s="22"/>
+      <c r="C746" s="23"/>
       <c r="F746" s="9"/>
       <c r="G746" s="9"/>
       <c r="H746" s="14"/>
-      <c r="I746" s="21"/>
+      <c r="I746" s="22"/>
     </row>
     <row r="747">
-      <c r="C747" s="22"/>
+      <c r="C747" s="23"/>
       <c r="F747" s="9"/>
       <c r="G747" s="9"/>
       <c r="H747" s="14"/>
-      <c r="I747" s="21"/>
+      <c r="I747" s="22"/>
     </row>
     <row r="748">
-      <c r="C748" s="22"/>
+      <c r="C748" s="23"/>
       <c r="F748" s="9"/>
       <c r="G748" s="9"/>
       <c r="H748" s="14"/>
-      <c r="I748" s="21"/>
+      <c r="I748" s="22"/>
     </row>
     <row r="749">
-      <c r="C749" s="22"/>
+      <c r="C749" s="23"/>
       <c r="F749" s="9"/>
       <c r="G749" s="9"/>
       <c r="H749" s="14"/>
-      <c r="I749" s="21"/>
+      <c r="I749" s="22"/>
     </row>
     <row r="750">
-      <c r="C750" s="22"/>
+      <c r="C750" s="23"/>
       <c r="F750" s="9"/>
       <c r="G750" s="9"/>
       <c r="H750" s="14"/>
-      <c r="I750" s="21"/>
+      <c r="I750" s="22"/>
     </row>
     <row r="751">
-      <c r="C751" s="22"/>
+      <c r="C751" s="23"/>
       <c r="F751" s="9"/>
       <c r="G751" s="9"/>
       <c r="H751" s="14"/>
-      <c r="I751" s="21"/>
+      <c r="I751" s="22"/>
     </row>
     <row r="752">
-      <c r="C752" s="22"/>
+      <c r="C752" s="23"/>
       <c r="F752" s="9"/>
       <c r="G752" s="9"/>
       <c r="H752" s="14"/>
-      <c r="I752" s="21"/>
+      <c r="I752" s="22"/>
     </row>
     <row r="753">
-      <c r="C753" s="22"/>
+      <c r="C753" s="23"/>
       <c r="F753" s="9"/>
       <c r="G753" s="9"/>
       <c r="H753" s="14"/>
-      <c r="I753" s="21"/>
+      <c r="I753" s="22"/>
     </row>
     <row r="754">
-      <c r="C754" s="22"/>
+      <c r="C754" s="23"/>
       <c r="F754" s="9"/>
       <c r="G754" s="9"/>
       <c r="H754" s="14"/>
-      <c r="I754" s="21"/>
+      <c r="I754" s="22"/>
     </row>
     <row r="755">
-      <c r="C755" s="22"/>
+      <c r="C755" s="23"/>
       <c r="F755" s="9"/>
       <c r="G755" s="9"/>
       <c r="H755" s="14"/>
-      <c r="I755" s="21"/>
+      <c r="I755" s="22"/>
     </row>
     <row r="756">
-      <c r="C756" s="22"/>
+      <c r="C756" s="23"/>
       <c r="F756" s="9"/>
       <c r="G756" s="9"/>
       <c r="H756" s="14"/>
-      <c r="I756" s="21"/>
+      <c r="I756" s="22"/>
     </row>
     <row r="757">
-      <c r="C757" s="22"/>
+      <c r="C757" s="23"/>
       <c r="F757" s="9"/>
       <c r="G757" s="9"/>
       <c r="H757" s="14"/>
-      <c r="I757" s="21"/>
+      <c r="I757" s="22"/>
     </row>
     <row r="758">
-      <c r="C758" s="22"/>
+      <c r="C758" s="23"/>
       <c r="F758" s="9"/>
       <c r="G758" s="9"/>
       <c r="H758" s="14"/>
-      <c r="I758" s="21"/>
+      <c r="I758" s="22"/>
     </row>
     <row r="759">
-      <c r="C759" s="22"/>
+      <c r="C759" s="23"/>
       <c r="F759" s="9"/>
       <c r="G759" s="9"/>
       <c r="H759" s="14"/>
-      <c r="I759" s="21"/>
+      <c r="I759" s="22"/>
     </row>
     <row r="760">
-      <c r="C760" s="22"/>
+      <c r="C760" s="23"/>
       <c r="F760" s="9"/>
       <c r="G760" s="9"/>
       <c r="H760" s="14"/>
-      <c r="I760" s="21"/>
+      <c r="I760" s="22"/>
     </row>
     <row r="761">
-      <c r="C761" s="22"/>
+      <c r="C761" s="23"/>
       <c r="F761" s="9"/>
       <c r="G761" s="9"/>
       <c r="H761" s="14"/>
-      <c r="I761" s="21"/>
+      <c r="I761" s="22"/>
     </row>
     <row r="762">
-      <c r="C762" s="22"/>
+      <c r="C762" s="23"/>
       <c r="F762" s="9"/>
       <c r="G762" s="9"/>
       <c r="H762" s="14"/>
-      <c r="I762" s="21"/>
+      <c r="I762" s="22"/>
     </row>
     <row r="763">
-      <c r="C763" s="22"/>
+      <c r="C763" s="23"/>
       <c r="F763" s="9"/>
       <c r="G763" s="9"/>
       <c r="H763" s="14"/>
-      <c r="I763" s="21"/>
+      <c r="I763" s="22"/>
     </row>
     <row r="764">
-      <c r="C764" s="22"/>
+      <c r="C764" s="23"/>
       <c r="F764" s="9"/>
       <c r="G764" s="9"/>
       <c r="H764" s="14"/>
-      <c r="I764" s="21"/>
+      <c r="I764" s="22"/>
     </row>
     <row r="765">
-      <c r="C765" s="22"/>
+      <c r="C765" s="23"/>
       <c r="F765" s="9"/>
       <c r="G765" s="9"/>
       <c r="H765" s="14"/>
-      <c r="I765" s="21"/>
+      <c r="I765" s="22"/>
     </row>
     <row r="766">
-      <c r="C766" s="22"/>
+      <c r="C766" s="23"/>
       <c r="F766" s="9"/>
       <c r="G766" s="9"/>
       <c r="H766" s="14"/>
-      <c r="I766" s="21"/>
+      <c r="I766" s="22"/>
     </row>
     <row r="767">
-      <c r="C767" s="22"/>
+      <c r="C767" s="23"/>
       <c r="F767" s="9"/>
       <c r="G767" s="9"/>
       <c r="H767" s="14"/>
-      <c r="I767" s="21"/>
+      <c r="I767" s="22"/>
     </row>
     <row r="768">
-      <c r="C768" s="22"/>
+      <c r="C768" s="23"/>
       <c r="F768" s="9"/>
       <c r="G768" s="9"/>
       <c r="H768" s="14"/>
-      <c r="I768" s="21"/>
+      <c r="I768" s="22"/>
     </row>
     <row r="769">
-      <c r="C769" s="22"/>
+      <c r="C769" s="23"/>
       <c r="F769" s="9"/>
       <c r="G769" s="9"/>
       <c r="H769" s="14"/>
-      <c r="I769" s="21"/>
+      <c r="I769" s="22"/>
     </row>
     <row r="770">
-      <c r="C770" s="22"/>
+      <c r="C770" s="23"/>
       <c r="F770" s="9"/>
       <c r="G770" s="9"/>
       <c r="H770" s="14"/>
-      <c r="I770" s="21"/>
+      <c r="I770" s="22"/>
     </row>
     <row r="771">
-      <c r="C771" s="22"/>
+      <c r="C771" s="23"/>
       <c r="F771" s="9"/>
       <c r="G771" s="9"/>
       <c r="H771" s="14"/>
-      <c r="I771" s="21"/>
+      <c r="I771" s="22"/>
     </row>
     <row r="772">
-      <c r="C772" s="22"/>
+      <c r="C772" s="23"/>
       <c r="F772" s="9"/>
       <c r="G772" s="9"/>
       <c r="H772" s="14"/>
-      <c r="I772" s="21"/>
+      <c r="I772" s="22"/>
     </row>
     <row r="773">
-      <c r="C773" s="22"/>
+      <c r="C773" s="23"/>
       <c r="F773" s="9"/>
       <c r="G773" s="9"/>
       <c r="H773" s="14"/>
-      <c r="I773" s="21"/>
+      <c r="I773" s="22"/>
     </row>
     <row r="774">
-      <c r="C774" s="22"/>
+      <c r="C774" s="23"/>
       <c r="F774" s="9"/>
       <c r="G774" s="9"/>
       <c r="H774" s="14"/>
-      <c r="I774" s="21"/>
+      <c r="I774" s="22"/>
     </row>
     <row r="775">
-      <c r="C775" s="22"/>
+      <c r="C775" s="23"/>
       <c r="F775" s="9"/>
       <c r="G775" s="9"/>
       <c r="H775" s="14"/>
-      <c r="I775" s="21"/>
+      <c r="I775" s="22"/>
     </row>
     <row r="776">
-      <c r="C776" s="22"/>
+      <c r="C776" s="23"/>
       <c r="F776" s="9"/>
       <c r="G776" s="9"/>
       <c r="H776" s="14"/>
-      <c r="I776" s="21"/>
+      <c r="I776" s="22"/>
     </row>
     <row r="777">
-      <c r="C777" s="22"/>
+      <c r="C777" s="23"/>
       <c r="F777" s="9"/>
       <c r="G777" s="9"/>
       <c r="H777" s="14"/>
-      <c r="I777" s="21"/>
+      <c r="I777" s="22"/>
     </row>
     <row r="778">
-      <c r="C778" s="22"/>
+      <c r="C778" s="23"/>
       <c r="F778" s="9"/>
       <c r="G778" s="9"/>
       <c r="H778" s="14"/>
-      <c r="I778" s="21"/>
+      <c r="I778" s="22"/>
     </row>
     <row r="779">
-      <c r="C779" s="22"/>
+      <c r="C779" s="23"/>
       <c r="F779" s="9"/>
       <c r="G779" s="9"/>
       <c r="H779" s="14"/>
-      <c r="I779" s="21"/>
+      <c r="I779" s="22"/>
     </row>
     <row r="780">
-      <c r="C780" s="22"/>
+      <c r="C780" s="23"/>
       <c r="F780" s="9"/>
       <c r="G780" s="9"/>
       <c r="H780" s="14"/>
-      <c r="I780" s="21"/>
+      <c r="I780" s="22"/>
     </row>
     <row r="781">
-      <c r="C781" s="22"/>
+      <c r="C781" s="23"/>
       <c r="F781" s="9"/>
       <c r="G781" s="9"/>
       <c r="H781" s="14"/>
-      <c r="I781" s="21"/>
+      <c r="I781" s="22"/>
     </row>
     <row r="782">
-      <c r="C782" s="22"/>
+      <c r="C782" s="23"/>
       <c r="F782" s="9"/>
       <c r="G782" s="9"/>
       <c r="H782" s="14"/>
-      <c r="I782" s="21"/>
+      <c r="I782" s="22"/>
     </row>
     <row r="783">
-      <c r="C783" s="22"/>
+      <c r="C783" s="23"/>
       <c r="F783" s="9"/>
       <c r="G783" s="9"/>
       <c r="H783" s="14"/>
-      <c r="I783" s="21"/>
+      <c r="I783" s="22"/>
     </row>
     <row r="784">
-      <c r="C784" s="22"/>
+      <c r="C784" s="23"/>
       <c r="F784" s="9"/>
       <c r="G784" s="9"/>
       <c r="H784" s="14"/>
-      <c r="I784" s="21"/>
+      <c r="I784" s="22"/>
     </row>
     <row r="785">
-      <c r="C785" s="22"/>
+      <c r="C785" s="23"/>
       <c r="F785" s="9"/>
       <c r="G785" s="9"/>
       <c r="H785" s="14"/>
-      <c r="I785" s="21"/>
+      <c r="I785" s="22"/>
     </row>
     <row r="786">
-      <c r="C786" s="22"/>
+      <c r="C786" s="23"/>
       <c r="F786" s="9"/>
       <c r="G786" s="9"/>
       <c r="H786" s="14"/>
-      <c r="I786" s="21"/>
+      <c r="I786" s="22"/>
     </row>
     <row r="787">
-      <c r="C787" s="22"/>
+      <c r="C787" s="23"/>
       <c r="F787" s="9"/>
       <c r="G787" s="9"/>
       <c r="H787" s="14"/>
-      <c r="I787" s="21"/>
+      <c r="I787" s="22"/>
     </row>
     <row r="788">
-      <c r="C788" s="22"/>
+      <c r="C788" s="23"/>
       <c r="F788" s="9"/>
       <c r="G788" s="9"/>
       <c r="H788" s="14"/>
-      <c r="I788" s="21"/>
+      <c r="I788" s="22"/>
     </row>
     <row r="789">
-      <c r="C789" s="22"/>
+      <c r="C789" s="23"/>
       <c r="F789" s="9"/>
       <c r="G789" s="9"/>
       <c r="H789" s="14"/>
-      <c r="I789" s="21"/>
+      <c r="I789" s="22"/>
     </row>
     <row r="790">
-      <c r="C790" s="22"/>
+      <c r="C790" s="23"/>
       <c r="F790" s="9"/>
       <c r="G790" s="9"/>
       <c r="H790" s="14"/>
-      <c r="I790" s="21"/>
+      <c r="I790" s="22"/>
     </row>
     <row r="791">
-      <c r="C791" s="22"/>
+      <c r="C791" s="23"/>
       <c r="F791" s="9"/>
       <c r="G791" s="9"/>
       <c r="H791" s="14"/>
-      <c r="I791" s="21"/>
+      <c r="I791" s="22"/>
     </row>
     <row r="792">
-      <c r="C792" s="22"/>
+      <c r="C792" s="23"/>
       <c r="F792" s="9"/>
       <c r="G792" s="9"/>
       <c r="H792" s="14"/>
-      <c r="I792" s="21"/>
+      <c r="I792" s="22"/>
     </row>
     <row r="793">
-      <c r="C793" s="22"/>
+      <c r="C793" s="23"/>
       <c r="F793" s="9"/>
       <c r="G793" s="9"/>
       <c r="H793" s="14"/>
-      <c r="I793" s="21"/>
+      <c r="I793" s="22"/>
     </row>
     <row r="794">
-      <c r="C794" s="22"/>
+      <c r="C794" s="23"/>
       <c r="F794" s="9"/>
       <c r="G794" s="9"/>
       <c r="H794" s="14"/>
-      <c r="I794" s="21"/>
+      <c r="I794" s="22"/>
     </row>
     <row r="795">
-      <c r="C795" s="22"/>
+      <c r="C795" s="23"/>
       <c r="F795" s="9"/>
       <c r="G795" s="9"/>
       <c r="H795" s="14"/>
-      <c r="I795" s="21"/>
+      <c r="I795" s="22"/>
     </row>
     <row r="796">
-      <c r="C796" s="22"/>
+      <c r="C796" s="23"/>
       <c r="F796" s="9"/>
       <c r="G796" s="9"/>
       <c r="H796" s="14"/>
-      <c r="I796" s="21"/>
+      <c r="I796" s="22"/>
     </row>
     <row r="797">
-      <c r="C797" s="22"/>
+      <c r="C797" s="23"/>
       <c r="F797" s="9"/>
       <c r="G797" s="9"/>
       <c r="H797" s="14"/>
-      <c r="I797" s="21"/>
+      <c r="I797" s="22"/>
     </row>
     <row r="798">
-      <c r="C798" s="22"/>
+      <c r="C798" s="23"/>
       <c r="F798" s="9"/>
       <c r="G798" s="9"/>
       <c r="H798" s="14"/>
-      <c r="I798" s="21"/>
+      <c r="I798" s="22"/>
     </row>
     <row r="799">
-      <c r="C799" s="22"/>
+      <c r="C799" s="23"/>
       <c r="F799" s="9"/>
       <c r="G799" s="9"/>
       <c r="H799" s="14"/>
-      <c r="I799" s="21"/>
+      <c r="I799" s="22"/>
     </row>
     <row r="800">
-      <c r="C800" s="22"/>
+      <c r="C800" s="23"/>
       <c r="F800" s="9"/>
       <c r="G800" s="9"/>
       <c r="H800" s="14"/>
-      <c r="I800" s="21"/>
+      <c r="I800" s="22"/>
     </row>
     <row r="801">
-      <c r="C801" s="22"/>
+      <c r="C801" s="23"/>
       <c r="F801" s="9"/>
       <c r="G801" s="9"/>
       <c r="H801" s="14"/>
-      <c r="I801" s="21"/>
+      <c r="I801" s="22"/>
     </row>
     <row r="802">
-      <c r="C802" s="22"/>
+      <c r="C802" s="23"/>
       <c r="F802" s="9"/>
       <c r="G802" s="9"/>
       <c r="H802" s="14"/>
-      <c r="I802" s="21"/>
+      <c r="I802" s="22"/>
     </row>
     <row r="803">
-      <c r="C803" s="22"/>
+      <c r="C803" s="23"/>
       <c r="F803" s="9"/>
       <c r="G803" s="9"/>
       <c r="H803" s="14"/>
-      <c r="I803" s="21"/>
+      <c r="I803" s="22"/>
     </row>
     <row r="804">
-      <c r="C804" s="22"/>
+      <c r="C804" s="23"/>
       <c r="F804" s="9"/>
       <c r="G804" s="9"/>
       <c r="H804" s="14"/>
-      <c r="I804" s="21"/>
+      <c r="I804" s="22"/>
     </row>
     <row r="805">
-      <c r="C805" s="22"/>
+      <c r="C805" s="23"/>
       <c r="F805" s="9"/>
       <c r="G805" s="9"/>
       <c r="H805" s="14"/>
-      <c r="I805" s="21"/>
+      <c r="I805" s="22"/>
     </row>
     <row r="806">
-      <c r="C806" s="22"/>
+      <c r="C806" s="23"/>
       <c r="F806" s="9"/>
       <c r="G806" s="9"/>
       <c r="H806" s="14"/>
-      <c r="I806" s="21"/>
+      <c r="I806" s="22"/>
     </row>
     <row r="807">
-      <c r="C807" s="22"/>
+      <c r="C807" s="23"/>
       <c r="F807" s="9"/>
       <c r="G807" s="9"/>
       <c r="H807" s="14"/>
-      <c r="I807" s="21"/>
+      <c r="I807" s="22"/>
     </row>
     <row r="808">
-      <c r="C808" s="22"/>
+      <c r="C808" s="23"/>
       <c r="F808" s="9"/>
       <c r="G808" s="9"/>
       <c r="H808" s="14"/>
-      <c r="I808" s="21"/>
+      <c r="I808" s="22"/>
     </row>
     <row r="809">
-      <c r="C809" s="22"/>
+      <c r="C809" s="23"/>
       <c r="F809" s="9"/>
       <c r="G809" s="9"/>
       <c r="H809" s="14"/>
-      <c r="I809" s="21"/>
+      <c r="I809" s="22"/>
     </row>
     <row r="810">
-      <c r="C810" s="22"/>
+      <c r="C810" s="23"/>
       <c r="F810" s="9"/>
       <c r="G810" s="9"/>
       <c r="H810" s="14"/>
-      <c r="I810" s="21"/>
+      <c r="I810" s="22"/>
     </row>
     <row r="811">
-      <c r="C811" s="22"/>
+      <c r="C811" s="23"/>
       <c r="F811" s="9"/>
       <c r="G811" s="9"/>
       <c r="H811" s="14"/>
-      <c r="I811" s="21"/>
+      <c r="I811" s="22"/>
     </row>
     <row r="812">
-      <c r="C812" s="22"/>
+      <c r="C812" s="23"/>
       <c r="F812" s="9"/>
       <c r="G812" s="9"/>
       <c r="H812" s="14"/>
-      <c r="I812" s="21"/>
+      <c r="I812" s="22"/>
     </row>
     <row r="813">
-      <c r="C813" s="22"/>
+      <c r="C813" s="23"/>
       <c r="F813" s="9"/>
       <c r="G813" s="9"/>
       <c r="H813" s="14"/>
-      <c r="I813" s="21"/>
+      <c r="I813" s="22"/>
     </row>
     <row r="814">
-      <c r="C814" s="22"/>
+      <c r="C814" s="23"/>
       <c r="F814" s="9"/>
       <c r="G814" s="9"/>
       <c r="H814" s="14"/>
-      <c r="I814" s="21"/>
+      <c r="I814" s="22"/>
     </row>
     <row r="815">
-      <c r="C815" s="22"/>
+      <c r="C815" s="23"/>
       <c r="F815" s="9"/>
       <c r="G815" s="9"/>
       <c r="H815" s="14"/>
-      <c r="I815" s="21"/>
+      <c r="I815" s="22"/>
     </row>
     <row r="816">
-      <c r="C816" s="22"/>
+      <c r="C816" s="23"/>
       <c r="F816" s="9"/>
       <c r="G816" s="9"/>
       <c r="H816" s="14"/>
-      <c r="I816" s="21"/>
+      <c r="I816" s="22"/>
     </row>
     <row r="817">
-      <c r="C817" s="22"/>
+      <c r="C817" s="23"/>
       <c r="F817" s="9"/>
       <c r="G817" s="9"/>
       <c r="H817" s="14"/>
-      <c r="I817" s="21"/>
+      <c r="I817" s="22"/>
     </row>
     <row r="818">
-      <c r="C818" s="22"/>
+      <c r="C818" s="23"/>
       <c r="F818" s="9"/>
       <c r="G818" s="9"/>
       <c r="H818" s="14"/>
-      <c r="I818" s="21"/>
+      <c r="I818" s="22"/>
     </row>
     <row r="819">
-      <c r="C819" s="22"/>
+      <c r="C819" s="23"/>
       <c r="F819" s="9"/>
       <c r="G819" s="9"/>
       <c r="H819" s="14"/>
-      <c r="I819" s="21"/>
+      <c r="I819" s="22"/>
     </row>
     <row r="820">
-      <c r="C820" s="22"/>
+      <c r="C820" s="23"/>
       <c r="F820" s="9"/>
       <c r="G820" s="9"/>
       <c r="H820" s="14"/>
-      <c r="I820" s="21"/>
+      <c r="I820" s="22"/>
     </row>
     <row r="821">
-      <c r="C821" s="22"/>
+      <c r="C821" s="23"/>
       <c r="F821" s="9"/>
       <c r="G821" s="9"/>
       <c r="H821" s="14"/>
-      <c r="I821" s="21"/>
+      <c r="I821" s="22"/>
     </row>
     <row r="822">
-      <c r="C822" s="22"/>
+      <c r="C822" s="23"/>
       <c r="F822" s="9"/>
       <c r="G822" s="9"/>
       <c r="H822" s="14"/>
-      <c r="I822" s="21"/>
+      <c r="I822" s="22"/>
     </row>
     <row r="823">
-      <c r="C823" s="22"/>
+      <c r="C823" s="23"/>
       <c r="F823" s="9"/>
       <c r="G823" s="9"/>
       <c r="H823" s="14"/>
-      <c r="I823" s="21"/>
+      <c r="I823" s="22"/>
     </row>
     <row r="824">
-      <c r="C824" s="22"/>
+      <c r="C824" s="23"/>
       <c r="F824" s="9"/>
       <c r="G824" s="9"/>
       <c r="H824" s="14"/>
-      <c r="I824" s="21"/>
+      <c r="I824" s="22"/>
     </row>
     <row r="825">
-      <c r="C825" s="22"/>
+      <c r="C825" s="23"/>
       <c r="F825" s="9"/>
       <c r="G825" s="9"/>
       <c r="H825" s="14"/>
-      <c r="I825" s="21"/>
+      <c r="I825" s="22"/>
     </row>
     <row r="826">
-      <c r="C826" s="22"/>
+      <c r="C826" s="23"/>
       <c r="F826" s="9"/>
       <c r="G826" s="9"/>
       <c r="H826" s="14"/>
-      <c r="I826" s="21"/>
+      <c r="I826" s="22"/>
     </row>
     <row r="827">
-      <c r="C827" s="22"/>
+      <c r="C827" s="23"/>
       <c r="F827" s="9"/>
       <c r="G827" s="9"/>
       <c r="H827" s="14"/>
-      <c r="I827" s="21"/>
+      <c r="I827" s="22"/>
     </row>
     <row r="828">
-      <c r="C828" s="22"/>
+      <c r="C828" s="23"/>
       <c r="F828" s="9"/>
       <c r="G828" s="9"/>
       <c r="H828" s="14"/>
-      <c r="I828" s="21"/>
+      <c r="I828" s="22"/>
     </row>
     <row r="829">
-      <c r="C829" s="22"/>
+      <c r="C829" s="23"/>
       <c r="F829" s="9"/>
       <c r="G829" s="9"/>
       <c r="H829" s="14"/>
-      <c r="I829" s="21"/>
+      <c r="I829" s="22"/>
     </row>
     <row r="830">
-      <c r="C830" s="22"/>
+      <c r="C830" s="23"/>
       <c r="F830" s="9"/>
       <c r="G830" s="9"/>
       <c r="H830" s="14"/>
-      <c r="I830" s="21"/>
+      <c r="I830" s="22"/>
     </row>
     <row r="831">
-      <c r="C831" s="22"/>
+      <c r="C831" s="23"/>
       <c r="F831" s="9"/>
       <c r="G831" s="9"/>
       <c r="H831" s="14"/>
-      <c r="I831" s="21"/>
+      <c r="I831" s="22"/>
     </row>
     <row r="832">
-      <c r="C832" s="22"/>
+      <c r="C832" s="23"/>
       <c r="F832" s="9"/>
       <c r="G832" s="9"/>
       <c r="H832" s="14"/>
-      <c r="I832" s="21"/>
+      <c r="I832" s="22"/>
     </row>
     <row r="833">
-      <c r="C833" s="22"/>
+      <c r="C833" s="23"/>
       <c r="F833" s="9"/>
       <c r="G833" s="9"/>
       <c r="H833" s="14"/>
-      <c r="I833" s="21"/>
+      <c r="I833" s="22"/>
     </row>
     <row r="834">
-      <c r="C834" s="22"/>
+      <c r="C834" s="23"/>
       <c r="F834" s="9"/>
       <c r="G834" s="9"/>
       <c r="H834" s="14"/>
-      <c r="I834" s="21"/>
+      <c r="I834" s="22"/>
     </row>
     <row r="835">
-      <c r="C835" s="22"/>
+      <c r="C835" s="23"/>
       <c r="F835" s="9"/>
       <c r="G835" s="9"/>
       <c r="H835" s="14"/>
-      <c r="I835" s="21"/>
+      <c r="I835" s="22"/>
     </row>
     <row r="836">
-      <c r="C836" s="22"/>
+      <c r="C836" s="23"/>
       <c r="F836" s="9"/>
       <c r="G836" s="9"/>
       <c r="H836" s="14"/>
-      <c r="I836" s="21"/>
+      <c r="I836" s="22"/>
     </row>
     <row r="837">
-      <c r="C837" s="22"/>
+      <c r="C837" s="23"/>
       <c r="F837" s="9"/>
       <c r="G837" s="9"/>
       <c r="H837" s="14"/>
-      <c r="I837" s="21"/>
+      <c r="I837" s="22"/>
     </row>
     <row r="838">
-      <c r="C838" s="22"/>
+      <c r="C838" s="23"/>
       <c r="F838" s="9"/>
       <c r="G838" s="9"/>
       <c r="H838" s="14"/>
-      <c r="I838" s="21"/>
+      <c r="I838" s="22"/>
     </row>
     <row r="839">
-      <c r="C839" s="22"/>
+      <c r="C839" s="23"/>
       <c r="F839" s="9"/>
       <c r="G839" s="9"/>
       <c r="H839" s="14"/>
-      <c r="I839" s="21"/>
+      <c r="I839" s="22"/>
     </row>
     <row r="840">
-      <c r="C840" s="22"/>
+      <c r="C840" s="23"/>
       <c r="F840" s="9"/>
       <c r="G840" s="9"/>
       <c r="H840" s="14"/>
-      <c r="I840" s="21"/>
+      <c r="I840" s="22"/>
     </row>
     <row r="841">
-      <c r="C841" s="22"/>
+      <c r="C841" s="23"/>
       <c r="F841" s="9"/>
       <c r="G841" s="9"/>
       <c r="H841" s="14"/>
-      <c r="I841" s="21"/>
+      <c r="I841" s="22"/>
     </row>
     <row r="842">
-      <c r="C842" s="22"/>
+      <c r="C842" s="23"/>
       <c r="F842" s="9"/>
       <c r="G842" s="9"/>
       <c r="H842" s="14"/>
-      <c r="I842" s="21"/>
+      <c r="I842" s="22"/>
     </row>
     <row r="843">
-      <c r="C843" s="22"/>
+      <c r="C843" s="23"/>
       <c r="F843" s="9"/>
       <c r="G843" s="9"/>
       <c r="H843" s="14"/>
-      <c r="I843" s="21"/>
+      <c r="I843" s="22"/>
     </row>
     <row r="844">
-      <c r="C844" s="22"/>
+      <c r="C844" s="23"/>
       <c r="F844" s="9"/>
       <c r="G844" s="9"/>
       <c r="H844" s="14"/>
-      <c r="I844" s="21"/>
+      <c r="I844" s="22"/>
     </row>
     <row r="845">
-      <c r="C845" s="22"/>
+      <c r="C845" s="23"/>
       <c r="F845" s="9"/>
       <c r="G845" s="9"/>
       <c r="H845" s="14"/>
-      <c r="I845" s="21"/>
+      <c r="I845" s="22"/>
     </row>
     <row r="846">
-      <c r="C846" s="22"/>
+      <c r="C846" s="23"/>
       <c r="F846" s="9"/>
       <c r="G846" s="9"/>
       <c r="H846" s="14"/>
-      <c r="I846" s="21"/>
+      <c r="I846" s="22"/>
     </row>
     <row r="847">
-      <c r="C847" s="22"/>
+      <c r="C847" s="23"/>
       <c r="F847" s="9"/>
       <c r="G847" s="9"/>
       <c r="H847" s="14"/>
-      <c r="I847" s="21"/>
+      <c r="I847" s="22"/>
     </row>
     <row r="848">
-      <c r="C848" s="22"/>
+      <c r="C848" s="23"/>
       <c r="F848" s="9"/>
       <c r="G848" s="9"/>
       <c r="H848" s="14"/>
-      <c r="I848" s="21"/>
+      <c r="I848" s="22"/>
     </row>
     <row r="849">
-      <c r="C849" s="22"/>
+      <c r="C849" s="23"/>
       <c r="F849" s="9"/>
       <c r="G849" s="9"/>
       <c r="H849" s="14"/>
-      <c r="I849" s="21"/>
+      <c r="I849" s="22"/>
     </row>
     <row r="850">
-      <c r="C850" s="22"/>
+      <c r="C850" s="23"/>
       <c r="F850" s="9"/>
       <c r="G850" s="9"/>
       <c r="H850" s="14"/>
-      <c r="I850" s="21"/>
+      <c r="I850" s="22"/>
     </row>
     <row r="851">
-      <c r="C851" s="22"/>
+      <c r="C851" s="23"/>
       <c r="F851" s="9"/>
       <c r="G851" s="9"/>
       <c r="H851" s="14"/>
-      <c r="I851" s="21"/>
+      <c r="I851" s="22"/>
     </row>
     <row r="852">
-      <c r="C852" s="22"/>
+      <c r="C852" s="23"/>
       <c r="F852" s="9"/>
       <c r="G852" s="9"/>
       <c r="H852" s="14"/>
-      <c r="I852" s="21"/>
+      <c r="I852" s="22"/>
     </row>
     <row r="853">
-      <c r="C853" s="22"/>
+      <c r="C853" s="23"/>
       <c r="F853" s="9"/>
       <c r="G853" s="9"/>
       <c r="H853" s="14"/>
-      <c r="I853" s="21"/>
+      <c r="I853" s="22"/>
     </row>
     <row r="854">
-      <c r="C854" s="22"/>
+      <c r="C854" s="23"/>
       <c r="F854" s="9"/>
       <c r="G854" s="9"/>
       <c r="H854" s="14"/>
-      <c r="I854" s="21"/>
+      <c r="I854" s="22"/>
     </row>
     <row r="855">
-      <c r="C855" s="22"/>
+      <c r="C855" s="23"/>
       <c r="F855" s="9"/>
       <c r="G855" s="9"/>
       <c r="H855" s="14"/>
-      <c r="I855" s="21"/>
+      <c r="I855" s="22"/>
     </row>
     <row r="856">
-      <c r="C856" s="22"/>
+      <c r="C856" s="23"/>
       <c r="F856" s="9"/>
       <c r="G856" s="9"/>
       <c r="H856" s="14"/>
-      <c r="I856" s="21"/>
+      <c r="I856" s="22"/>
     </row>
     <row r="857">
-      <c r="C857" s="22"/>
+      <c r="C857" s="23"/>
       <c r="F857" s="9"/>
       <c r="G857" s="9"/>
       <c r="H857" s="14"/>
-      <c r="I857" s="21"/>
+      <c r="I857" s="22"/>
     </row>
     <row r="858">
-      <c r="C858" s="22"/>
+      <c r="C858" s="23"/>
       <c r="F858" s="9"/>
       <c r="G858" s="9"/>
       <c r="H858" s="14"/>
-      <c r="I858" s="21"/>
+      <c r="I858" s="22"/>
     </row>
     <row r="859">
-      <c r="C859" s="22"/>
+      <c r="C859" s="23"/>
       <c r="F859" s="9"/>
       <c r="G859" s="9"/>
       <c r="H859" s="14"/>
-      <c r="I859" s="21"/>
+      <c r="I859" s="22"/>
     </row>
     <row r="860">
-      <c r="C860" s="22"/>
+      <c r="C860" s="23"/>
       <c r="F860" s="9"/>
       <c r="G860" s="9"/>
       <c r="H860" s="14"/>
-      <c r="I860" s="21"/>
+      <c r="I860" s="22"/>
     </row>
     <row r="861">
-      <c r="C861" s="22"/>
+      <c r="C861" s="23"/>
       <c r="F861" s="9"/>
       <c r="G861" s="9"/>
       <c r="H861" s="14"/>
-      <c r="I861" s="21"/>
+      <c r="I861" s="22"/>
     </row>
     <row r="862">
-      <c r="C862" s="22"/>
+      <c r="C862" s="23"/>
       <c r="F862" s="9"/>
       <c r="G862" s="9"/>
       <c r="H862" s="14"/>
-      <c r="I862" s="21"/>
+      <c r="I862" s="22"/>
     </row>
     <row r="863">
-      <c r="C863" s="22"/>
+      <c r="C863" s="23"/>
       <c r="F863" s="9"/>
       <c r="G863" s="9"/>
       <c r="H863" s="14"/>
-      <c r="I863" s="21"/>
+      <c r="I863" s="22"/>
     </row>
     <row r="864">
-      <c r="C864" s="22"/>
+      <c r="C864" s="23"/>
       <c r="F864" s="9"/>
       <c r="G864" s="9"/>
       <c r="H864" s="14"/>
-      <c r="I864" s="21"/>
+      <c r="I864" s="22"/>
     </row>
     <row r="865">
-      <c r="C865" s="22"/>
+      <c r="C865" s="23"/>
       <c r="F865" s="9"/>
       <c r="G865" s="9"/>
       <c r="H865" s="14"/>
-      <c r="I865" s="21"/>
+      <c r="I865" s="22"/>
     </row>
     <row r="866">
-      <c r="C866" s="22"/>
+      <c r="C866" s="23"/>
       <c r="F866" s="9"/>
       <c r="G866" s="9"/>
       <c r="H866" s="14"/>
-      <c r="I866" s="21"/>
+      <c r="I866" s="22"/>
     </row>
     <row r="867">
-      <c r="C867" s="22"/>
+      <c r="C867" s="23"/>
       <c r="F867" s="9"/>
       <c r="G867" s="9"/>
       <c r="H867" s="14"/>
-      <c r="I867" s="21"/>
+      <c r="I867" s="22"/>
     </row>
     <row r="868">
-      <c r="C868" s="22"/>
+      <c r="C868" s="23"/>
       <c r="F868" s="9"/>
       <c r="G868" s="9"/>
       <c r="H868" s="14"/>
-      <c r="I868" s="21"/>
+      <c r="I868" s="22"/>
     </row>
     <row r="869">
-      <c r="C869" s="22"/>
+      <c r="C869" s="23"/>
       <c r="F869" s="9"/>
       <c r="G869" s="9"/>
       <c r="H869" s="14"/>
-      <c r="I869" s="21"/>
+      <c r="I869" s="22"/>
     </row>
     <row r="870">
-      <c r="C870" s="22"/>
+      <c r="C870" s="23"/>
       <c r="F870" s="9"/>
       <c r="G870" s="9"/>
       <c r="H870" s="14"/>
-      <c r="I870" s="21"/>
+      <c r="I870" s="22"/>
     </row>
     <row r="871">
-      <c r="C871" s="22"/>
+      <c r="C871" s="23"/>
       <c r="F871" s="9"/>
       <c r="G871" s="9"/>
       <c r="H871" s="14"/>
-      <c r="I871" s="21"/>
+      <c r="I871" s="22"/>
     </row>
     <row r="872">
-      <c r="C872" s="22"/>
+      <c r="C872" s="23"/>
       <c r="F872" s="9"/>
       <c r="G872" s="9"/>
       <c r="H872" s="14"/>
-      <c r="I872" s="21"/>
+      <c r="I872" s="22"/>
     </row>
     <row r="873">
-      <c r="C873" s="22"/>
+      <c r="C873" s="23"/>
       <c r="F873" s="9"/>
       <c r="G873" s="9"/>
       <c r="H873" s="14"/>
-      <c r="I873" s="21"/>
+      <c r="I873" s="22"/>
     </row>
     <row r="874">
-      <c r="C874" s="22"/>
+      <c r="C874" s="23"/>
       <c r="F874" s="9"/>
       <c r="G874" s="9"/>
       <c r="H874" s="14"/>
-      <c r="I874" s="21"/>
+      <c r="I874" s="22"/>
     </row>
     <row r="875">
-      <c r="C875" s="22"/>
+      <c r="C875" s="23"/>
       <c r="F875" s="9"/>
       <c r="G875" s="9"/>
       <c r="H875" s="14"/>
-      <c r="I875" s="21"/>
+      <c r="I875" s="22"/>
     </row>
     <row r="876">
-      <c r="C876" s="22"/>
+      <c r="C876" s="23"/>
       <c r="F876" s="9"/>
       <c r="G876" s="9"/>
       <c r="H876" s="14"/>
-      <c r="I876" s="21"/>
+      <c r="I876" s="22"/>
     </row>
     <row r="877">
-      <c r="C877" s="22"/>
+      <c r="C877" s="23"/>
       <c r="F877" s="9"/>
       <c r="G877" s="9"/>
       <c r="H877" s="14"/>
-      <c r="I877" s="21"/>
+      <c r="I877" s="22"/>
     </row>
     <row r="878">
-      <c r="C878" s="22"/>
+      <c r="C878" s="23"/>
       <c r="F878" s="9"/>
       <c r="G878" s="9"/>
       <c r="H878" s="14"/>
-      <c r="I878" s="21"/>
+      <c r="I878" s="22"/>
     </row>
     <row r="879">
-      <c r="C879" s="22"/>
+      <c r="C879" s="23"/>
       <c r="F879" s="9"/>
       <c r="G879" s="9"/>
       <c r="H879" s="14"/>
-      <c r="I879" s="21"/>
+      <c r="I879" s="22"/>
     </row>
     <row r="880">
-      <c r="C880" s="22"/>
+      <c r="C880" s="23"/>
       <c r="F880" s="9"/>
       <c r="G880" s="9"/>
       <c r="H880" s="14"/>
-      <c r="I880" s="21"/>
+      <c r="I880" s="22"/>
     </row>
     <row r="881">
-      <c r="C881" s="22"/>
+      <c r="C881" s="23"/>
       <c r="F881" s="9"/>
       <c r="G881" s="9"/>
       <c r="H881" s="14"/>
-      <c r="I881" s="21"/>
+      <c r="I881" s="22"/>
     </row>
     <row r="882">
-      <c r="C882" s="22"/>
+      <c r="C882" s="23"/>
       <c r="F882" s="9"/>
       <c r="G882" s="9"/>
       <c r="H882" s="14"/>
-      <c r="I882" s="21"/>
+      <c r="I882" s="22"/>
     </row>
     <row r="883">
-      <c r="C883" s="22"/>
+      <c r="C883" s="23"/>
       <c r="F883" s="9"/>
       <c r="G883" s="9"/>
       <c r="H883" s="14"/>
-      <c r="I883" s="21"/>
+      <c r="I883" s="22"/>
     </row>
     <row r="884">
-      <c r="C884" s="22"/>
+      <c r="C884" s="23"/>
       <c r="F884" s="9"/>
       <c r="G884" s="9"/>
       <c r="H884" s="14"/>
-      <c r="I884" s="21"/>
+      <c r="I884" s="22"/>
     </row>
     <row r="885">
-      <c r="C885" s="22"/>
+      <c r="C885" s="23"/>
       <c r="F885" s="9"/>
       <c r="G885" s="9"/>
       <c r="H885" s="14"/>
-      <c r="I885" s="21"/>
+      <c r="I885" s="22"/>
     </row>
     <row r="886">
-      <c r="C886" s="22"/>
+      <c r="C886" s="23"/>
       <c r="F886" s="9"/>
       <c r="G886" s="9"/>
       <c r="H886" s="14"/>
-      <c r="I886" s="21"/>
+      <c r="I886" s="22"/>
     </row>
     <row r="887">
-      <c r="C887" s="22"/>
+      <c r="C887" s="23"/>
       <c r="F887" s="9"/>
       <c r="G887" s="9"/>
       <c r="H887" s="14"/>
-      <c r="I887" s="21"/>
+      <c r="I887" s="22"/>
     </row>
     <row r="888">
-      <c r="C888" s="22"/>
+      <c r="C888" s="23"/>
       <c r="F888" s="9"/>
       <c r="G888" s="9"/>
       <c r="H888" s="14"/>
-      <c r="I888" s="21"/>
+      <c r="I888" s="22"/>
     </row>
     <row r="889">
-      <c r="C889" s="22"/>
+      <c r="C889" s="23"/>
       <c r="F889" s="9"/>
       <c r="G889" s="9"/>
       <c r="H889" s="14"/>
-      <c r="I889" s="21"/>
+      <c r="I889" s="22"/>
     </row>
     <row r="890">
-      <c r="C890" s="22"/>
+      <c r="C890" s="23"/>
       <c r="F890" s="9"/>
       <c r="G890" s="9"/>
       <c r="H890" s="14"/>
-      <c r="I890" s="21"/>
+      <c r="I890" s="22"/>
     </row>
     <row r="891">
-      <c r="C891" s="22"/>
+      <c r="C891" s="23"/>
       <c r="F891" s="9"/>
       <c r="G891" s="9"/>
       <c r="H891" s="14"/>
-      <c r="I891" s="21"/>
+      <c r="I891" s="22"/>
     </row>
     <row r="892">
-      <c r="C892" s="22"/>
+      <c r="C892" s="23"/>
       <c r="F892" s="9"/>
       <c r="G892" s="9"/>
       <c r="H892" s="14"/>
-      <c r="I892" s="21"/>
+      <c r="I892" s="22"/>
     </row>
     <row r="893">
-      <c r="C893" s="22"/>
+      <c r="C893" s="23"/>
       <c r="F893" s="9"/>
       <c r="G893" s="9"/>
       <c r="H893" s="14"/>
-      <c r="I893" s="21"/>
+      <c r="I893" s="22"/>
     </row>
     <row r="894">
-      <c r="C894" s="22"/>
+      <c r="C894" s="23"/>
       <c r="F894" s="9"/>
       <c r="G894" s="9"/>
       <c r="H894" s="14"/>
-      <c r="I894" s="21"/>
+      <c r="I894" s="22"/>
     </row>
     <row r="895">
-      <c r="C895" s="22"/>
+      <c r="C895" s="23"/>
       <c r="F895" s="9"/>
       <c r="G895" s="9"/>
       <c r="H895" s="14"/>
-      <c r="I895" s="21"/>
+      <c r="I895" s="22"/>
     </row>
     <row r="896">
-      <c r="C896" s="22"/>
+      <c r="C896" s="23"/>
       <c r="F896" s="9"/>
       <c r="G896" s="9"/>
       <c r="H896" s="14"/>
-      <c r="I896" s="21"/>
+      <c r="I896" s="22"/>
     </row>
     <row r="897">
-      <c r="C897" s="22"/>
+      <c r="C897" s="23"/>
       <c r="F897" s="9"/>
       <c r="G897" s="9"/>
       <c r="H897" s="14"/>
-      <c r="I897" s="21"/>
+      <c r="I897" s="22"/>
     </row>
     <row r="898">
-      <c r="C898" s="22"/>
+      <c r="C898" s="23"/>
       <c r="F898" s="9"/>
       <c r="G898" s="9"/>
       <c r="H898" s="14"/>
-      <c r="I898" s="21"/>
+      <c r="I898" s="22"/>
     </row>
     <row r="899">
-      <c r="C899" s="22"/>
+      <c r="C899" s="23"/>
       <c r="F899" s="9"/>
       <c r="G899" s="9"/>
       <c r="H899" s="14"/>
-      <c r="I899" s="21"/>
+      <c r="I899" s="22"/>
     </row>
     <row r="900">
-      <c r="C900" s="22"/>
+      <c r="C900" s="23"/>
       <c r="F900" s="9"/>
       <c r="G900" s="9"/>
       <c r="H900" s="14"/>
-      <c r="I900" s="21"/>
+      <c r="I900" s="22"/>
     </row>
     <row r="901">
-      <c r="C901" s="22"/>
+      <c r="C901" s="23"/>
       <c r="F901" s="9"/>
       <c r="G901" s="9"/>
       <c r="H901" s="14"/>
-      <c r="I901" s="21"/>
+      <c r="I901" s="22"/>
     </row>
     <row r="902">
-      <c r="C902" s="22"/>
+      <c r="C902" s="23"/>
       <c r="F902" s="9"/>
       <c r="G902" s="9"/>
       <c r="H902" s="14"/>
-      <c r="I902" s="21"/>
+      <c r="I902" s="22"/>
     </row>
     <row r="903">
-      <c r="C903" s="22"/>
+      <c r="C903" s="23"/>
       <c r="F903" s="9"/>
       <c r="G903" s="9"/>
       <c r="H903" s="14"/>
-      <c r="I903" s="21"/>
+      <c r="I903" s="22"/>
     </row>
     <row r="904">
-      <c r="C904" s="22"/>
+      <c r="C904" s="23"/>
       <c r="F904" s="9"/>
       <c r="G904" s="9"/>
       <c r="H904" s="14"/>
-      <c r="I904" s="21"/>
+      <c r="I904" s="22"/>
     </row>
     <row r="905">
-      <c r="C905" s="22"/>
+      <c r="C905" s="23"/>
       <c r="F905" s="9"/>
       <c r="G905" s="9"/>
       <c r="H905" s="14"/>
-      <c r="I905" s="21"/>
+      <c r="I905" s="22"/>
     </row>
     <row r="906">
-      <c r="C906" s="22"/>
+      <c r="C906" s="23"/>
       <c r="F906" s="9"/>
       <c r="G906" s="9"/>
       <c r="H906" s="14"/>
-      <c r="I906" s="21"/>
+      <c r="I906" s="22"/>
     </row>
     <row r="907">
-      <c r="C907" s="22"/>
+      <c r="C907" s="23"/>
       <c r="F907" s="9"/>
       <c r="G907" s="9"/>
       <c r="H907" s="14"/>
-      <c r="I907" s="21"/>
+      <c r="I907" s="22"/>
     </row>
     <row r="908">
-      <c r="C908" s="22"/>
+      <c r="C908" s="23"/>
       <c r="F908" s="9"/>
       <c r="G908" s="9"/>
       <c r="H908" s="14"/>
-      <c r="I908" s="21"/>
+      <c r="I908" s="22"/>
     </row>
     <row r="909">
-      <c r="C909" s="22"/>
+      <c r="C909" s="23"/>
       <c r="F909" s="9"/>
       <c r="G909" s="9"/>
       <c r="H909" s="14"/>
-      <c r="I909" s="21"/>
+      <c r="I909" s="22"/>
     </row>
     <row r="910">
-      <c r="C910" s="22"/>
+      <c r="C910" s="23"/>
       <c r="F910" s="9"/>
       <c r="G910" s="9"/>
       <c r="H910" s="14"/>
-      <c r="I910" s="21"/>
+      <c r="I910" s="22"/>
     </row>
     <row r="911">
-      <c r="C911" s="22"/>
+      <c r="C911" s="23"/>
       <c r="F911" s="9"/>
       <c r="G911" s="9"/>
       <c r="H911" s="14"/>
-      <c r="I911" s="21"/>
+      <c r="I911" s="22"/>
     </row>
     <row r="912">
-      <c r="C912" s="22"/>
+      <c r="C912" s="23"/>
       <c r="F912" s="9"/>
       <c r="G912" s="9"/>
       <c r="H912" s="14"/>
-      <c r="I912" s="21"/>
+      <c r="I912" s="22"/>
     </row>
     <row r="913">
-      <c r="C913" s="22"/>
+      <c r="C913" s="23"/>
       <c r="F913" s="9"/>
       <c r="G913" s="9"/>
       <c r="H913" s="14"/>
-      <c r="I913" s="21"/>
+      <c r="I913" s="22"/>
     </row>
     <row r="914">
-      <c r="C914" s="22"/>
+      <c r="C914" s="23"/>
       <c r="F914" s="9"/>
       <c r="G914" s="9"/>
       <c r="H914" s="14"/>
-      <c r="I914" s="21"/>
+      <c r="I914" s="22"/>
     </row>
     <row r="915">
-      <c r="C915" s="22"/>
+      <c r="C915" s="23"/>
       <c r="F915" s="9"/>
       <c r="G915" s="9"/>
       <c r="H915" s="14"/>
-      <c r="I915" s="21"/>
+      <c r="I915" s="22"/>
     </row>
     <row r="916">
-      <c r="C916" s="22"/>
+      <c r="C916" s="23"/>
       <c r="F916" s="9"/>
       <c r="G916" s="9"/>
       <c r="H916" s="14"/>
-      <c r="I916" s="21"/>
+      <c r="I916" s="22"/>
     </row>
     <row r="917">
-      <c r="C917" s="22"/>
+      <c r="C917" s="23"/>
       <c r="F917" s="9"/>
       <c r="G917" s="9"/>
       <c r="H917" s="14"/>
-      <c r="I917" s="21"/>
+      <c r="I917" s="22"/>
     </row>
     <row r="918">
-      <c r="C918" s="22"/>
+      <c r="C918" s="23"/>
       <c r="F918" s="9"/>
       <c r="G918" s="9"/>
       <c r="H918" s="14"/>
-      <c r="I918" s="21"/>
+      <c r="I918" s="22"/>
     </row>
     <row r="919">
-      <c r="C919" s="22"/>
+      <c r="C919" s="23"/>
       <c r="F919" s="9"/>
       <c r="G919" s="9"/>
       <c r="H919" s="14"/>
-      <c r="I919" s="21"/>
+      <c r="I919" s="22"/>
     </row>
     <row r="920">
-      <c r="C920" s="22"/>
+      <c r="C920" s="23"/>
       <c r="F920" s="9"/>
       <c r="G920" s="9"/>
       <c r="H920" s="14"/>
-      <c r="I920" s="21"/>
+      <c r="I920" s="22"/>
     </row>
     <row r="921">
-      <c r="C921" s="22"/>
+      <c r="C921" s="23"/>
       <c r="F921" s="9"/>
       <c r="G921" s="9"/>
       <c r="H921" s="14"/>
-      <c r="I921" s="21"/>
+      <c r="I921" s="22"/>
     </row>
     <row r="922">
-      <c r="C922" s="22"/>
+      <c r="C922" s="23"/>
       <c r="F922" s="9"/>
       <c r="G922" s="9"/>
       <c r="H922" s="14"/>
-      <c r="I922" s="21"/>
+      <c r="I922" s="22"/>
     </row>
     <row r="923">
-      <c r="C923" s="22"/>
+      <c r="C923" s="23"/>
       <c r="F923" s="9"/>
       <c r="G923" s="9"/>
       <c r="H923" s="14"/>
-      <c r="I923" s="21"/>
+      <c r="I923" s="22"/>
     </row>
     <row r="924">
-      <c r="C924" s="22"/>
+      <c r="C924" s="23"/>
       <c r="F924" s="9"/>
       <c r="G924" s="9"/>
       <c r="H924" s="14"/>
-      <c r="I924" s="21"/>
+      <c r="I924" s="22"/>
     </row>
     <row r="925">
-      <c r="C925" s="22"/>
+      <c r="C925" s="23"/>
       <c r="F925" s="9"/>
       <c r="G925" s="9"/>
       <c r="H925" s="14"/>
-      <c r="I925" s="21"/>
+      <c r="I925" s="22"/>
     </row>
     <row r="926">
-      <c r="C926" s="22"/>
+      <c r="C926" s="23"/>
       <c r="F926" s="9"/>
       <c r="G926" s="9"/>
       <c r="H926" s="14"/>
-      <c r="I926" s="21"/>
+      <c r="I926" s="22"/>
     </row>
     <row r="927">
-      <c r="C927" s="22"/>
+      <c r="C927" s="23"/>
       <c r="F927" s="9"/>
       <c r="G927" s="9"/>
       <c r="H927" s="14"/>
-      <c r="I927" s="21"/>
+      <c r="I927" s="22"/>
     </row>
     <row r="928">
-      <c r="C928" s="22"/>
+      <c r="C928" s="23"/>
       <c r="F928" s="9"/>
       <c r="G928" s="9"/>
       <c r="H928" s="14"/>
-      <c r="I928" s="21"/>
+      <c r="I928" s="22"/>
     </row>
     <row r="929">
-      <c r="C929" s="22"/>
+      <c r="C929" s="23"/>
       <c r="F929" s="9"/>
       <c r="G929" s="9"/>
       <c r="H929" s="14"/>
-      <c r="I929" s="21"/>
+      <c r="I929" s="22"/>
     </row>
     <row r="930">
-      <c r="C930" s="22"/>
+      <c r="C930" s="23"/>
       <c r="F930" s="9"/>
       <c r="G930" s="9"/>
       <c r="H930" s="14"/>
-      <c r="I930" s="21"/>
+      <c r="I930" s="22"/>
     </row>
     <row r="931">
-      <c r="C931" s="22"/>
+      <c r="C931" s="23"/>
       <c r="F931" s="9"/>
       <c r="G931" s="9"/>
       <c r="H931" s="14"/>
-      <c r="I931" s="21"/>
+      <c r="I931" s="22"/>
     </row>
     <row r="932">
-      <c r="C932" s="22"/>
+      <c r="C932" s="23"/>
       <c r="F932" s="9"/>
       <c r="G932" s="9"/>
       <c r="H932" s="14"/>
-      <c r="I932" s="21"/>
+      <c r="I932" s="22"/>
     </row>
     <row r="933">
-      <c r="C933" s="22"/>
+      <c r="C933" s="23"/>
       <c r="F933" s="9"/>
       <c r="G933" s="9"/>
       <c r="H933" s="14"/>
-      <c r="I933" s="21"/>
+      <c r="I933" s="22"/>
     </row>
     <row r="934">
-      <c r="C934" s="22"/>
+      <c r="C934" s="23"/>
       <c r="F934" s="9"/>
       <c r="G934" s="9"/>
       <c r="H934" s="14"/>
-      <c r="I934" s="21"/>
+      <c r="I934" s="22"/>
     </row>
     <row r="935">
-      <c r="C935" s="22"/>
+      <c r="C935" s="23"/>
       <c r="F935" s="9"/>
       <c r="G935" s="9"/>
       <c r="H935" s="14"/>
-      <c r="I935" s="21"/>
+      <c r="I935" s="22"/>
     </row>
     <row r="936">
-      <c r="C936" s="22"/>
+      <c r="C936" s="23"/>
       <c r="F936" s="9"/>
       <c r="G936" s="9"/>
       <c r="H936" s="14"/>
-      <c r="I936" s="21"/>
+      <c r="I936" s="22"/>
     </row>
     <row r="937">
-      <c r="C937" s="22"/>
+      <c r="C937" s="23"/>
       <c r="F937" s="9"/>
       <c r="G937" s="9"/>
       <c r="H937" s="14"/>
-      <c r="I937" s="21"/>
+      <c r="I937" s="22"/>
     </row>
     <row r="938">
-      <c r="C938" s="22"/>
+      <c r="C938" s="23"/>
       <c r="F938" s="9"/>
       <c r="G938" s="9"/>
       <c r="H938" s="14"/>
-      <c r="I938" s="21"/>
+      <c r="I938" s="22"/>
     </row>
     <row r="939">
-      <c r="C939" s="22"/>
+      <c r="C939" s="23"/>
       <c r="F939" s="9"/>
       <c r="G939" s="9"/>
       <c r="H939" s="14"/>
-      <c r="I939" s="21"/>
+      <c r="I939" s="22"/>
     </row>
     <row r="940">
-      <c r="C940" s="22"/>
+      <c r="C940" s="23"/>
       <c r="F940" s="9"/>
       <c r="G940" s="9"/>
       <c r="H940" s="14"/>
-      <c r="I940" s="21"/>
+      <c r="I940" s="22"/>
     </row>
     <row r="941">
-      <c r="C941" s="22"/>
+      <c r="C941" s="23"/>
       <c r="F941" s="9"/>
       <c r="G941" s="9"/>
       <c r="H941" s="14"/>
-      <c r="I941" s="21"/>
+      <c r="I941" s="22"/>
     </row>
     <row r="942">
-      <c r="C942" s="22"/>
+      <c r="C942" s="23"/>
       <c r="F942" s="9"/>
       <c r="G942" s="9"/>
       <c r="H942" s="14"/>
-      <c r="I942" s="21"/>
+      <c r="I942" s="22"/>
     </row>
     <row r="943">
-      <c r="C943" s="22"/>
+      <c r="C943" s="23"/>
       <c r="F943" s="9"/>
       <c r="G943" s="9"/>
       <c r="H943" s="14"/>
-      <c r="I943" s="21"/>
+      <c r="I943" s="22"/>
     </row>
     <row r="944">
-      <c r="C944" s="22"/>
+      <c r="C944" s="23"/>
       <c r="F944" s="9"/>
       <c r="G944" s="9"/>
       <c r="H944" s="14"/>
-      <c r="I944" s="21"/>
+      <c r="I944" s="22"/>
     </row>
     <row r="945">
-      <c r="C945" s="22"/>
+      <c r="C945" s="23"/>
       <c r="F945" s="9"/>
       <c r="G945" s="9"/>
       <c r="H945" s="14"/>
-      <c r="I945" s="21"/>
+      <c r="I945" s="22"/>
     </row>
     <row r="946">
-      <c r="C946" s="22"/>
+      <c r="C946" s="23"/>
       <c r="F946" s="9"/>
       <c r="G946" s="9"/>
       <c r="H946" s="14"/>
-      <c r="I946" s="21"/>
+      <c r="I946" s="22"/>
     </row>
     <row r="947">
-      <c r="C947" s="22"/>
+      <c r="C947" s="23"/>
       <c r="F947" s="9"/>
       <c r="G947" s="9"/>
       <c r="H947" s="14"/>
-      <c r="I947" s="21"/>
+      <c r="I947" s="22"/>
     </row>
     <row r="948">
-      <c r="C948" s="22"/>
+      <c r="C948" s="23"/>
       <c r="F948" s="9"/>
       <c r="G948" s="9"/>
       <c r="H948" s="14"/>
-      <c r="I948" s="21"/>
+      <c r="I948" s="22"/>
     </row>
     <row r="949">
-      <c r="C949" s="22"/>
+      <c r="C949" s="23"/>
       <c r="F949" s="9"/>
       <c r="G949" s="9"/>
       <c r="H949" s="14"/>
-      <c r="I949" s="21"/>
+      <c r="I949" s="22"/>
     </row>
     <row r="950">
-      <c r="C950" s="22"/>
+      <c r="C950" s="23"/>
       <c r="F950" s="9"/>
       <c r="G950" s="9"/>
       <c r="H950" s="14"/>
-      <c r="I950" s="21"/>
+      <c r="I950" s="22"/>
     </row>
     <row r="951">
-      <c r="C951" s="22"/>
+      <c r="C951" s="23"/>
       <c r="F951" s="9"/>
       <c r="G951" s="9"/>
       <c r="H951" s="14"/>
-      <c r="I951" s="21"/>
+      <c r="I951" s="22"/>
     </row>
     <row r="952">
-      <c r="C952" s="22"/>
+      <c r="C952" s="23"/>
       <c r="F952" s="9"/>
       <c r="G952" s="9"/>
       <c r="H952" s="14"/>
-      <c r="I952" s="21"/>
+      <c r="I952" s="22"/>
     </row>
     <row r="953">
-      <c r="C953" s="22"/>
+      <c r="C953" s="23"/>
       <c r="F953" s="9"/>
       <c r="G953" s="9"/>
       <c r="H953" s="14"/>
-      <c r="I953" s="21"/>
+      <c r="I953" s="22"/>
     </row>
     <row r="954">
-      <c r="C954" s="22"/>
+      <c r="C954" s="23"/>
       <c r="F954" s="9"/>
       <c r="G954" s="9"/>
       <c r="H954" s="14"/>
-      <c r="I954" s="21"/>
+      <c r="I954" s="22"/>
     </row>
     <row r="955">
-      <c r="C955" s="22"/>
+      <c r="C955" s="23"/>
       <c r="F955" s="9"/>
       <c r="G955" s="9"/>
       <c r="H955" s="14"/>
-      <c r="I955" s="21"/>
+      <c r="I955" s="22"/>
     </row>
     <row r="956">
-      <c r="C956" s="22"/>
+      <c r="C956" s="23"/>
       <c r="F956" s="9"/>
       <c r="G956" s="9"/>
       <c r="H956" s="14"/>
-      <c r="I956" s="21"/>
+      <c r="I956" s="22"/>
     </row>
     <row r="957">
-      <c r="C957" s="22"/>
+      <c r="C957" s="23"/>
       <c r="F957" s="9"/>
       <c r="G957" s="9"/>
       <c r="H957" s="14"/>
-      <c r="I957" s="21"/>
+      <c r="I957" s="22"/>
     </row>
     <row r="958">
-      <c r="C958" s="22"/>
+      <c r="C958" s="23"/>
       <c r="F958" s="9"/>
       <c r="G958" s="9"/>
       <c r="H958" s="14"/>
-      <c r="I958" s="21"/>
+      <c r="I958" s="22"/>
     </row>
     <row r="959">
-      <c r="C959" s="22"/>
+      <c r="C959" s="23"/>
       <c r="F959" s="9"/>
       <c r="G959" s="9"/>
       <c r="H959" s="14"/>
-      <c r="I959" s="21"/>
+      <c r="I959" s="22"/>
     </row>
     <row r="960">
-      <c r="C960" s="22"/>
+      <c r="C960" s="23"/>
       <c r="F960" s="9"/>
       <c r="G960" s="9"/>
       <c r="H960" s="14"/>
-      <c r="I960" s="21"/>
+      <c r="I960" s="22"/>
     </row>
     <row r="961">
-      <c r="C961" s="22"/>
+      <c r="C961" s="23"/>
       <c r="F961" s="9"/>
       <c r="G961" s="9"/>
       <c r="H961" s="14"/>
-      <c r="I961" s="21"/>
+      <c r="I961" s="22"/>
     </row>
     <row r="962">
-      <c r="C962" s="22"/>
+      <c r="C962" s="23"/>
       <c r="F962" s="9"/>
       <c r="G962" s="9"/>
       <c r="H962" s="14"/>
-      <c r="I962" s="21"/>
+      <c r="I962" s="22"/>
     </row>
     <row r="963">
-      <c r="C963" s="22"/>
+      <c r="C963" s="23"/>
       <c r="F963" s="9"/>
       <c r="G963" s="9"/>
       <c r="H963" s="14"/>
-      <c r="I963" s="21"/>
+      <c r="I963" s="22"/>
     </row>
     <row r="964">
-      <c r="C964" s="22"/>
+      <c r="C964" s="23"/>
       <c r="F964" s="9"/>
       <c r="G964" s="9"/>
       <c r="H964" s="14"/>
-      <c r="I964" s="21"/>
+      <c r="I964" s="22"/>
     </row>
     <row r="965">
-      <c r="C965" s="22"/>
+      <c r="C965" s="23"/>
       <c r="F965" s="9"/>
       <c r="G965" s="9"/>
       <c r="H965" s="14"/>
-      <c r="I965" s="21"/>
+      <c r="I965" s="22"/>
     </row>
     <row r="966">
-      <c r="C966" s="22"/>
+      <c r="C966" s="23"/>
       <c r="F966" s="9"/>
       <c r="G966" s="9"/>
       <c r="H966" s="14"/>
-      <c r="I966" s="21"/>
+      <c r="I966" s="22"/>
     </row>
     <row r="967">
-      <c r="C967" s="22"/>
+      <c r="C967" s="23"/>
       <c r="F967" s="9"/>
       <c r="G967" s="9"/>
       <c r="H967" s="14"/>
-      <c r="I967" s="21"/>
+      <c r="I967" s="22"/>
     </row>
     <row r="968">
-      <c r="C968" s="22"/>
+      <c r="C968" s="23"/>
       <c r="F968" s="9"/>
       <c r="G968" s="9"/>
       <c r="H968" s="14"/>
-      <c r="I968" s="21"/>
+      <c r="I968" s="22"/>
     </row>
     <row r="969">
-      <c r="C969" s="22"/>
+      <c r="C969" s="23"/>
       <c r="F969" s="9"/>
       <c r="G969" s="9"/>
       <c r="H969" s="14"/>
-      <c r="I969" s="21"/>
+      <c r="I969" s="22"/>
     </row>
     <row r="970">
-      <c r="C970" s="22"/>
+      <c r="C970" s="23"/>
       <c r="F970" s="9"/>
       <c r="G970" s="9"/>
       <c r="H970" s="14"/>
-      <c r="I970" s="21"/>
+      <c r="I970" s="22"/>
     </row>
     <row r="971">
-      <c r="C971" s="22"/>
+      <c r="C971" s="23"/>
       <c r="F971" s="9"/>
       <c r="G971" s="9"/>
       <c r="H971" s="14"/>
-      <c r="I971" s="21"/>
+      <c r="I971" s="22"/>
     </row>
     <row r="972">
-      <c r="C972" s="22"/>
+      <c r="C972" s="23"/>
       <c r="F972" s="9"/>
       <c r="G972" s="9"/>
       <c r="H972" s="14"/>
-      <c r="I972" s="21"/>
+      <c r="I972" s="22"/>
     </row>
     <row r="973">
-      <c r="C973" s="22"/>
+      <c r="C973" s="23"/>
       <c r="F973" s="9"/>
       <c r="G973" s="9"/>
       <c r="H973" s="14"/>
-      <c r="I973" s="21"/>
+      <c r="I973" s="22"/>
     </row>
     <row r="974">
-      <c r="C974" s="22"/>
+      <c r="C974" s="23"/>
       <c r="F974" s="9"/>
       <c r="G974" s="9"/>
       <c r="H974" s="14"/>
-      <c r="I974" s="21"/>
+      <c r="I974" s="22"/>
     </row>
     <row r="975">
-      <c r="C975" s="22"/>
+      <c r="C975" s="23"/>
       <c r="F975" s="9"/>
       <c r="G975" s="9"/>
       <c r="H975" s="14"/>
-      <c r="I975" s="21"/>
+      <c r="I975" s="22"/>
     </row>
     <row r="976">
-      <c r="C976" s="22"/>
+      <c r="C976" s="23"/>
       <c r="F976" s="9"/>
       <c r="G976" s="9"/>
       <c r="H976" s="14"/>
-      <c r="I976" s="21"/>
+      <c r="I976" s="22"/>
     </row>
     <row r="977">
-      <c r="C977" s="22"/>
+      <c r="C977" s="23"/>
       <c r="F977" s="9"/>
       <c r="G977" s="9"/>
       <c r="H977" s="14"/>
-      <c r="I977" s="21"/>
+      <c r="I977" s="22"/>
     </row>
     <row r="978">
-      <c r="C978" s="22"/>
+      <c r="C978" s="23"/>
       <c r="F978" s="9"/>
       <c r="G978" s="9"/>
       <c r="H978" s="14"/>
-      <c r="I978" s="21"/>
+      <c r="I978" s="22"/>
     </row>
     <row r="979">
-      <c r="C979" s="22"/>
+      <c r="C979" s="23"/>
       <c r="F979" s="9"/>
       <c r="G979" s="9"/>
       <c r="H979" s="14"/>
-      <c r="I979" s="21"/>
+      <c r="I979" s="22"/>
     </row>
     <row r="980">
-      <c r="C980" s="22"/>
+      <c r="C980" s="23"/>
       <c r="F980" s="9"/>
       <c r="G980" s="9"/>
       <c r="H980" s="14"/>
-      <c r="I980" s="21"/>
+      <c r="I980" s="22"/>
     </row>
     <row r="981">
-      <c r="C981" s="22"/>
+      <c r="C981" s="23"/>
       <c r="F981" s="9"/>
       <c r="G981" s="9"/>
       <c r="H981" s="14"/>
-      <c r="I981" s="21"/>
+      <c r="I981" s="22"/>
     </row>
     <row r="982">
-      <c r="C982" s="22"/>
+      <c r="C982" s="23"/>
       <c r="F982" s="9"/>
       <c r="G982" s="9"/>
       <c r="H982" s="14"/>
-      <c r="I982" s="21"/>
+      <c r="I982" s="22"/>
     </row>
     <row r="983">
-      <c r="C983" s="22"/>
+      <c r="C983" s="23"/>
       <c r="F983" s="9"/>
       <c r="G983" s="9"/>
       <c r="H983" s="14"/>
-      <c r="I983" s="21"/>
+      <c r="I983" s="22"/>
     </row>
     <row r="984">
-      <c r="C984" s="22"/>
+      <c r="C984" s="23"/>
       <c r="F984" s="9"/>
       <c r="G984" s="9"/>
       <c r="H984" s="14"/>
-      <c r="I984" s="21"/>
+      <c r="I984" s="22"/>
     </row>
     <row r="985">
-      <c r="C985" s="22"/>
+      <c r="C985" s="23"/>
       <c r="F985" s="9"/>
       <c r="G985" s="9"/>
       <c r="H985" s="14"/>
-      <c r="I985" s="21"/>
+      <c r="I985" s="22"/>
     </row>
     <row r="986">
-      <c r="C986" s="22"/>
+      <c r="C986" s="23"/>
       <c r="F986" s="9"/>
       <c r="G986" s="9"/>
       <c r="H986" s="14"/>
-      <c r="I986" s="21"/>
+      <c r="I986" s="22"/>
     </row>
     <row r="987">
-      <c r="C987" s="22"/>
+      <c r="C987" s="23"/>
       <c r="F987" s="9"/>
       <c r="G987" s="9"/>
       <c r="H987" s="14"/>
-      <c r="I987" s="21"/>
+      <c r="I987" s="22"/>
     </row>
     <row r="988">
-      <c r="C988" s="22"/>
+      <c r="C988" s="23"/>
       <c r="F988" s="9"/>
       <c r="G988" s="9"/>
       <c r="H988" s="14"/>
-      <c r="I988" s="21"/>
+      <c r="I988" s="22"/>
     </row>
     <row r="989">
-      <c r="C989" s="22"/>
+      <c r="C989" s="23"/>
       <c r="F989" s="9"/>
       <c r="G989" s="9"/>
       <c r="H989" s="14"/>
-      <c r="I989" s="21"/>
+      <c r="I989" s="22"/>
     </row>
     <row r="990">
-      <c r="C990" s="22"/>
+      <c r="C990" s="23"/>
       <c r="F990" s="9"/>
       <c r="G990" s="9"/>
       <c r="H990" s="14"/>
-      <c r="I990" s="21"/>
+      <c r="I990" s="22"/>
     </row>
     <row r="991">
-      <c r="C991" s="22"/>
+      <c r="C991" s="23"/>
       <c r="F991" s="9"/>
       <c r="G991" s="9"/>
       <c r="H991" s="14"/>
-      <c r="I991" s="21"/>
+      <c r="I991" s="22"/>
     </row>
     <row r="992">
-      <c r="C992" s="22"/>
+      <c r="C992" s="23"/>
       <c r="F992" s="9"/>
       <c r="G992" s="9"/>
       <c r="H992" s="14"/>
-      <c r="I992" s="21"/>
+      <c r="I992" s="22"/>
     </row>
     <row r="993">
-      <c r="C993" s="22"/>
+      <c r="C993" s="23"/>
       <c r="F993" s="9"/>
       <c r="G993" s="9"/>
       <c r="H993" s="14"/>
-      <c r="I993" s="21"/>
+      <c r="I993" s="22"/>
     </row>
     <row r="994">
-      <c r="C994" s="22"/>
+      <c r="C994" s="23"/>
       <c r="F994" s="9"/>
       <c r="G994" s="9"/>
       <c r="H994" s="14"/>
-      <c r="I994" s="21"/>
+      <c r="I994" s="22"/>
     </row>
     <row r="995">
-      <c r="C995" s="22"/>
+      <c r="C995" s="23"/>
       <c r="F995" s="9"/>
       <c r="G995" s="9"/>
       <c r="H995" s="14"/>
-      <c r="I995" s="21"/>
+      <c r="I995" s="22"/>
     </row>
     <row r="996">
-      <c r="C996" s="22"/>
+      <c r="C996" s="23"/>
       <c r="F996" s="9"/>
       <c r="G996" s="9"/>
       <c r="H996" s="14"/>
-      <c r="I996" s="21"/>
+      <c r="I996" s="22"/>
     </row>
     <row r="997">
-      <c r="C997" s="22"/>
+      <c r="C997" s="23"/>
       <c r="F997" s="9"/>
       <c r="G997" s="9"/>
       <c r="H997" s="14"/>
-      <c r="I997" s="21"/>
+      <c r="I997" s="22"/>
     </row>
     <row r="998">
-      <c r="C998" s="22"/>
+      <c r="C998" s="23"/>
       <c r="F998" s="9"/>
       <c r="G998" s="9"/>
       <c r="H998" s="14"/>
-      <c r="I998" s="21"/>
+      <c r="I998" s="22"/>
     </row>
     <row r="999">
-      <c r="C999" s="22"/>
+      <c r="C999" s="23"/>
       <c r="F999" s="9"/>
       <c r="G999" s="9"/>
       <c r="H999" s="14"/>
-      <c r="I999" s="21"/>
+      <c r="I999" s="22"/>
     </row>
     <row r="1000">
-      <c r="C1000" s="22"/>
+      <c r="C1000" s="23"/>
       <c r="F1000" s="9"/>
       <c r="G1000" s="9"/>
       <c r="H1000" s="14"/>
-      <c r="I1000" s="21"/>
+      <c r="I1000" s="22"/>
     </row>
     <row r="1001">
-      <c r="C1001" s="22"/>
+      <c r="C1001" s="23"/>
       <c r="F1001" s="9"/>
       <c r="G1001" s="9"/>
       <c r="H1001" s="14"/>
-      <c r="I1001" s="21"/>
+      <c r="I1001" s="22"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A73 C2:I73 B73">

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -29,10 +29,10 @@
     <t>Final Price</t>
   </si>
   <si>
-    <t>VALUE</t>
+    <t>Mine?</t>
   </si>
   <si>
-    <t>Mine?</t>
+    <t>VALUE</t>
   </si>
   <si>
     <t>Inflated Fair Price</t>
@@ -44,16 +44,16 @@
     <t>My Max Bid</t>
   </si>
   <si>
+    <t>New Values</t>
+  </si>
+  <si>
     <t>EnforceUpTo</t>
   </si>
   <si>
-    <t>New Values</t>
+    <t>Spine</t>
   </si>
   <si>
     <t>Value vs Fair</t>
-  </si>
-  <si>
-    <t>Spine</t>
   </si>
   <si>
     <t>Settings</t>
@@ -98,9 +98,6 @@
     <t>Total Spent $</t>
   </si>
   <si>
-    <t>Round 1</t>
-  </si>
-  <si>
     <t>Makai Lemon</t>
   </si>
   <si>
@@ -120,6 +117,9 @@
   </si>
   <si>
     <t>KC Concepcion</t>
+  </si>
+  <si>
+    <t>Round 1</t>
   </si>
   <si>
     <t>Other Teams Remaining</t>
@@ -146,9 +146,6 @@
     <t>Undrafted Predraft$</t>
   </si>
   <si>
-    <t>Round 2</t>
-  </si>
-  <si>
     <t>Arvell Reese</t>
   </si>
   <si>
@@ -164,13 +161,16 @@
     <t>Aggression</t>
   </si>
   <si>
+    <t>Round 2</t>
+  </si>
+  <si>
     <t>Caleb Downs</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>David Bailey</t>
   </si>
   <si>
-    <t>David Bailey</t>
+    <t>Round 3</t>
   </si>
   <si>
     <t>League Spent %</t>
@@ -188,9 +188,6 @@
     <t>Dillon Thieneman</t>
   </si>
   <si>
-    <t>Round 4</t>
-  </si>
-  <si>
     <t>Rueben Bain</t>
   </si>
   <si>
@@ -203,6 +200,9 @@
     <t>Nicholas Singleton</t>
   </si>
   <si>
+    <t>Round 4</t>
+  </si>
+  <si>
     <t>Mike Washington</t>
   </si>
   <si>
@@ -210,9 +210,6 @@
   </si>
   <si>
     <t>Antonio Williams</t>
-  </si>
-  <si>
-    <t>Round 5</t>
   </si>
   <si>
     <t>Elijah Sarratt</t>
@@ -224,13 +221,13 @@
     <t>Chris Brazzell</t>
   </si>
   <si>
+    <t>Round 5</t>
+  </si>
+  <si>
     <t>Max Klare</t>
   </si>
   <si>
     <t>Zachariah Branch</t>
-  </si>
-  <si>
-    <t>Round 6</t>
   </si>
   <si>
     <t>De'Zhaun Stribling</t>
@@ -240,6 +237,9 @@
   </si>
   <si>
     <t>Kaytron Allen</t>
+  </si>
+  <si>
+    <t>Round 6</t>
   </si>
   <si>
     <t>Ted Hurst</t>
@@ -917,16 +917,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F1" s="6">
         <v>2025.0</v>
@@ -1071,7 +1071,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="10" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="10" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -9375,7 +9375,7 @@
         <v>5.0</v>
       </c>
       <c r="X143" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y143" s="7" t="s">
         <v>141</v>
@@ -9455,7 +9455,7 @@
         <v>7.0</v>
       </c>
       <c r="X145" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y145" s="7" t="s">
         <v>143</v>
@@ -9495,7 +9495,7 @@
         <v>8.0</v>
       </c>
       <c r="X146" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Y146" s="7" t="s">
         <v>144</v>
@@ -9535,7 +9535,7 @@
         <v>9.0</v>
       </c>
       <c r="X147" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Y147" s="7" t="s">
         <v>141</v>
@@ -9615,7 +9615,7 @@
         <v>11.0</v>
       </c>
       <c r="X149" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Y149" s="7" t="s">
         <v>143</v>
@@ -9655,7 +9655,7 @@
         <v>12.0</v>
       </c>
       <c r="X150" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y150" s="7" t="s">
         <v>146</v>
@@ -9775,7 +9775,7 @@
         <v>15.0</v>
       </c>
       <c r="X153" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Y153" s="7" t="s">
         <v>141</v>
@@ -10095,7 +10095,7 @@
         <v>23.0</v>
       </c>
       <c r="X161" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Y161" s="7" t="s">
         <v>142</v>
@@ -10135,7 +10135,7 @@
         <v>24.0</v>
       </c>
       <c r="X162" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Y162" s="7" t="s">
         <v>141</v>
@@ -10175,7 +10175,7 @@
         <v>25.0</v>
       </c>
       <c r="X163" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y163" s="7" t="s">
         <v>140</v>
@@ -10215,7 +10215,7 @@
         <v>26.0</v>
       </c>
       <c r="X164" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Y164" s="7" t="s">
         <v>140</v>
@@ -10375,7 +10375,7 @@
         <v>30.0</v>
       </c>
       <c r="X168" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Y168" s="7" t="s">
         <v>141</v>
@@ -10495,7 +10495,7 @@
         <v>33.0</v>
       </c>
       <c r="X171" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y171" s="7" t="s">
         <v>141</v>
@@ -10695,7 +10695,7 @@
         <v>38.0</v>
       </c>
       <c r="X176" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Y176" s="7" t="s">
         <v>141</v>
@@ -10855,7 +10855,7 @@
         <v>42.0</v>
       </c>
       <c r="X180" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Y180" s="7" t="s">
         <v>140</v>
@@ -37456,7 +37456,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>7</v>
@@ -37465,10 +37465,10 @@
         <v>9</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>14</v>
@@ -37652,7 +37652,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" s="8">
         <v>76.0</v>
@@ -37677,7 +37677,7 @@
         <v/>
       </c>
       <c r="K6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L6" s="17">
         <f>L2-L5
@@ -37690,7 +37690,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" s="8">
         <v>66.5</v>
@@ -37715,7 +37715,7 @@
         <v/>
       </c>
       <c r="K7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L7" s="17">
         <f>SUMIF($E$2:$E$500,TRUE,$D$2:$D$500)</f>
@@ -37727,7 +37727,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="8">
         <v>57.5</v>
@@ -37752,7 +37752,7 @@
         <v/>
       </c>
       <c r="K8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L8" s="8">
         <f>L4-L7
@@ -37765,7 +37765,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9" s="8">
         <v>53.0</v>
@@ -37944,7 +37944,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" s="8">
         <v>30.5</v>
@@ -37969,7 +37969,7 @@
         <v/>
       </c>
       <c r="K14" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L14" s="19">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -37981,7 +37981,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" s="8">
         <v>27.5</v>
@@ -38011,7 +38011,7 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" s="8">
         <v>25.5</v>
@@ -38036,7 +38036,7 @@
         <v/>
       </c>
       <c r="K16" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L16" s="1">
         <f>IF($L$18&lt;0.3,
@@ -38088,7 +38088,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="8">
         <v>20.0</v>
@@ -38245,7 +38245,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C23" s="8">
         <v>12.0</v>
@@ -38275,7 +38275,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C24" s="8">
         <v>11.0</v>
@@ -38305,7 +38305,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C25" s="8">
         <v>10.0</v>
@@ -38335,7 +38335,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C26" s="8">
         <v>9.5</v>
@@ -38431,7 +38431,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C29" s="8">
         <v>7.0</v>
@@ -38461,7 +38461,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C30" s="8">
         <v>6.5</v>
@@ -38491,7 +38491,7 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C31" s="8">
         <v>6.0</v>
@@ -38581,7 +38581,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C34" s="8">
         <v>4.5</v>
@@ -38611,7 +38611,7 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C35" s="8">
         <v>4.5</v>
@@ -38641,7 +38641,7 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C36" s="8">
         <v>4.0</v>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -26,19 +26,19 @@
     <t>PLAYER NAME</t>
   </si>
   <si>
-    <t>Decay</t>
-  </si>
-  <si>
     <t>PreDraft$</t>
   </si>
   <si>
-    <t>New Values</t>
+    <t>Decay</t>
   </si>
   <si>
     <t>Final Price</t>
   </si>
   <si>
     <t>Mine?</t>
+  </si>
+  <si>
+    <t>New Values</t>
   </si>
   <si>
     <t>Spine</t>
@@ -65,10 +65,10 @@
     <t>Fractions</t>
   </si>
   <si>
-    <t>Jeremiyah Love</t>
+    <t>Monotone Rounded</t>
   </si>
   <si>
-    <t>Monotone Rounded</t>
+    <t>Jeremiyah Love</t>
   </si>
   <si>
     <t>Final Dollar Per Pick</t>
@@ -95,6 +95,9 @@
     <t>Jordyn Tyson</t>
   </si>
   <si>
+    <t>Round 1</t>
+  </si>
+  <si>
     <t>Total Spent $</t>
   </si>
   <si>
@@ -113,10 +116,10 @@
     <t>Sonny Styles</t>
   </si>
   <si>
-    <t>Round 1</t>
+    <t>My Remaining</t>
   </si>
   <si>
-    <t>My Remaining</t>
+    <t>Round 2</t>
   </si>
   <si>
     <t>KC Concepcion</t>
@@ -134,6 +137,9 @@
     <t>Eli Stowers</t>
   </si>
   <si>
+    <t>Round 3</t>
+  </si>
+  <si>
     <t>Budget Advantage Factor</t>
   </si>
   <si>
@@ -149,16 +155,19 @@
     <t>Arvell Reese</t>
   </si>
   <si>
-    <t>Inflation Factor</t>
+    <t>Round 4</t>
   </si>
   <si>
-    <t>Round 2</t>
+    <t>Inflation Factor</t>
   </si>
   <si>
     <t>Ty Simpson</t>
   </si>
   <si>
     <t>Denzel Boston</t>
+  </si>
+  <si>
+    <t>Round 5</t>
   </si>
   <si>
     <t>Aggression</t>
@@ -170,10 +179,10 @@
     <t>David Bailey</t>
   </si>
   <si>
-    <t>League Spent %</t>
+    <t>Round 6</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>League Spent %</t>
   </si>
   <si>
     <t>Jacob Rodriguez</t>
@@ -198,9 +207,6 @@
   </si>
   <si>
     <t>Nicholas Singleton</t>
-  </si>
-  <si>
-    <t>Round 4</t>
   </si>
   <si>
     <t>Mike Washington</t>
@@ -234,9 +240,6 @@
   </si>
   <si>
     <t>Kaytron Allen</t>
-  </si>
-  <si>
-    <t>Round 5</t>
   </si>
   <si>
     <t>Ted Hurst</t>
@@ -348,9 +351,6 @@
   </si>
   <si>
     <t>Noah Whittington</t>
-  </si>
-  <si>
-    <t>Round 6</t>
   </si>
   <si>
     <t>Standings</t>
@@ -920,10 +920,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>9</v>
@@ -944,7 +944,7 @@
         <v>16</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L1" s="10" t="s">
         <v>19</v>
@@ -1071,7 +1071,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="8" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="8" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="8" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="8" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="8" t="s">
-        <v>112</v>
+        <v>55</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -9255,7 +9255,7 @@
         <v>1.0</v>
       </c>
       <c r="X140" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y140" s="9" t="s">
         <v>140</v>
@@ -9375,7 +9375,7 @@
         <v>5.0</v>
       </c>
       <c r="X143" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y143" s="9" t="s">
         <v>141</v>
@@ -9455,7 +9455,7 @@
         <v>7.0</v>
       </c>
       <c r="X145" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y145" s="9" t="s">
         <v>143</v>
@@ -9495,7 +9495,7 @@
         <v>8.0</v>
       </c>
       <c r="X146" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Y146" s="9" t="s">
         <v>144</v>
@@ -9535,7 +9535,7 @@
         <v>9.0</v>
       </c>
       <c r="X147" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Y147" s="9" t="s">
         <v>141</v>
@@ -9575,7 +9575,7 @@
         <v>10.0</v>
       </c>
       <c r="X148" s="9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Y148" s="9" t="s">
         <v>145</v>
@@ -9615,7 +9615,7 @@
         <v>11.0</v>
       </c>
       <c r="X149" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Y149" s="9" t="s">
         <v>143</v>
@@ -9655,7 +9655,7 @@
         <v>12.0</v>
       </c>
       <c r="X150" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Y150" s="9" t="s">
         <v>146</v>
@@ -9775,7 +9775,7 @@
         <v>15.0</v>
       </c>
       <c r="X153" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y153" s="9" t="s">
         <v>141</v>
@@ -9815,7 +9815,7 @@
         <v>16.0</v>
       </c>
       <c r="X154" s="9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="Y154" s="9" t="s">
         <v>143</v>
@@ -9855,7 +9855,7 @@
         <v>17.0</v>
       </c>
       <c r="X155" s="9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="Y155" s="9" t="s">
         <v>140</v>
@@ -9895,7 +9895,7 @@
         <v>18.0</v>
       </c>
       <c r="X156" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Y156" s="9" t="s">
         <v>145</v>
@@ -9935,7 +9935,7 @@
         <v>19.0</v>
       </c>
       <c r="X157" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y157" s="9" t="s">
         <v>145</v>
@@ -9975,7 +9975,7 @@
         <v>20.0</v>
       </c>
       <c r="X158" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Y158" s="9" t="s">
         <v>140</v>
@@ -10055,7 +10055,7 @@
         <v>22.0</v>
       </c>
       <c r="X160" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y160" s="9" t="s">
         <v>144</v>
@@ -10095,7 +10095,7 @@
         <v>23.0</v>
       </c>
       <c r="X161" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Y161" s="9" t="s">
         <v>142</v>
@@ -10135,7 +10135,7 @@
         <v>24.0</v>
       </c>
       <c r="X162" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Y162" s="9" t="s">
         <v>141</v>
@@ -10175,7 +10175,7 @@
         <v>25.0</v>
       </c>
       <c r="X163" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y163" s="9" t="s">
         <v>140</v>
@@ -10215,7 +10215,7 @@
         <v>26.0</v>
       </c>
       <c r="X164" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Y164" s="9" t="s">
         <v>140</v>
@@ -10335,7 +10335,7 @@
         <v>29.0</v>
       </c>
       <c r="X167" s="9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="Y167" s="9" t="s">
         <v>143</v>
@@ -10375,7 +10375,7 @@
         <v>30.0</v>
       </c>
       <c r="X168" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="Y168" s="9" t="s">
         <v>141</v>
@@ -10415,7 +10415,7 @@
         <v>31.0</v>
       </c>
       <c r="X169" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Y169" s="9" t="s">
         <v>141</v>
@@ -10495,7 +10495,7 @@
         <v>33.0</v>
       </c>
       <c r="X171" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y171" s="9" t="s">
         <v>141</v>
@@ -10535,7 +10535,7 @@
         <v>34.0</v>
       </c>
       <c r="X172" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Y172" s="9" t="s">
         <v>146</v>
@@ -10575,7 +10575,7 @@
         <v>35.0</v>
       </c>
       <c r="X173" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Y173" s="9" t="s">
         <v>143</v>
@@ -10615,7 +10615,7 @@
         <v>36.0</v>
       </c>
       <c r="X174" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Y174" s="9" t="s">
         <v>144</v>
@@ -10695,7 +10695,7 @@
         <v>38.0</v>
       </c>
       <c r="X176" s="9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="Y176" s="9" t="s">
         <v>141</v>
@@ -10735,7 +10735,7 @@
         <v>39.0</v>
       </c>
       <c r="X177" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Y177" s="9" t="s">
         <v>144</v>
@@ -10775,7 +10775,7 @@
         <v>40.0</v>
       </c>
       <c r="X178" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y178" s="9" t="s">
         <v>141</v>
@@ -10815,7 +10815,7 @@
         <v>41.0</v>
       </c>
       <c r="X179" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Y179" s="9" t="s">
         <v>141</v>
@@ -10855,7 +10855,7 @@
         <v>42.0</v>
       </c>
       <c r="X180" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Y180" s="9" t="s">
         <v>140</v>
@@ -10895,7 +10895,7 @@
         <v>43.0</v>
       </c>
       <c r="X181" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y181" s="9" t="s">
         <v>144</v>
@@ -10935,7 +10935,7 @@
         <v>44.0</v>
       </c>
       <c r="X182" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y182" s="9" t="s">
         <v>142</v>
@@ -10975,7 +10975,7 @@
         <v>45.0</v>
       </c>
       <c r="X183" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Y183" s="9" t="s">
         <v>140</v>
@@ -11015,7 +11015,7 @@
         <v>46.0</v>
       </c>
       <c r="X184" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y184" s="9" t="s">
         <v>141</v>
@@ -11055,7 +11055,7 @@
         <v>47.0</v>
       </c>
       <c r="X185" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y185" s="9" t="s">
         <v>141</v>
@@ -11175,7 +11175,7 @@
         <v>50.0</v>
       </c>
       <c r="X188" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Y188" s="9" t="s">
         <v>142</v>
@@ -11295,7 +11295,7 @@
         <v>53.0</v>
       </c>
       <c r="X191" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Y191" s="9" t="s">
         <v>144</v>
@@ -11375,7 +11375,7 @@
         <v>55.0</v>
       </c>
       <c r="X193" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Y193" s="9" t="s">
         <v>141</v>
@@ -11575,7 +11575,7 @@
         <v>60.0</v>
       </c>
       <c r="X198" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Y198" s="9" t="s">
         <v>144</v>
@@ -11655,7 +11655,7 @@
         <v>62.0</v>
       </c>
       <c r="X200" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Y200" s="9" t="s">
         <v>144</v>
@@ -11775,7 +11775,7 @@
         <v>65.0</v>
       </c>
       <c r="X203" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Y203" s="9" t="s">
         <v>142</v>
@@ -11815,7 +11815,7 @@
         <v>66.0</v>
       </c>
       <c r="X204" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y204" s="9" t="s">
         <v>144</v>
@@ -12135,7 +12135,7 @@
         <v>74.0</v>
       </c>
       <c r="X212" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Y212" s="9" t="s">
         <v>142</v>
@@ -37450,13 +37450,13 @@
         <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>10</v>
@@ -37479,7 +37479,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="11">
         <v>139.0</v>
@@ -37639,7 +37639,7 @@
         <v/>
       </c>
       <c r="K5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L5" s="17">
         <f>SUM($D$2:$D$500)
@@ -37652,7 +37652,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="11">
         <v>76.0</v>
@@ -37677,7 +37677,7 @@
         <v/>
       </c>
       <c r="K6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L6" s="17">
         <f>L2-L5
@@ -37690,7 +37690,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" s="11">
         <v>66.5</v>
@@ -37715,7 +37715,7 @@
         <v/>
       </c>
       <c r="K7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L7" s="17">
         <f>SUMIF($E$2:$E$500,TRUE,$D$2:$D$500)</f>
@@ -37727,7 +37727,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="11">
         <v>57.5</v>
@@ -37765,7 +37765,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="11">
         <v>53.0</v>
@@ -37790,7 +37790,7 @@
         <v/>
       </c>
       <c r="K9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L9" s="11">
         <f>L6-L8
@@ -37803,7 +37803,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" s="11">
         <v>48.0</v>
@@ -37828,7 +37828,7 @@
         <v/>
       </c>
       <c r="K10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L10" s="11">
         <f>IF(L3&gt;1,L9/(L3-1),0)</f>
@@ -37840,7 +37840,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" s="11">
         <v>43.0</v>
@@ -37865,7 +37865,7 @@
         <v/>
       </c>
       <c r="K11" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L11" s="19">
         <f>IF(L10&gt;0,L8/L10,1)</f>
@@ -37877,7 +37877,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C12" s="11">
         <v>39.0</v>
@@ -37907,7 +37907,7 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11">
         <v>34.0</v>
@@ -37932,7 +37932,7 @@
         <v/>
       </c>
       <c r="K13" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L13" s="17">
         <f>SUMIF($D$2:$D$73,"",$C$2:$C$73)</f>
@@ -37944,7 +37944,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C14" s="11">
         <v>30.5</v>
@@ -37969,7 +37969,7 @@
         <v/>
       </c>
       <c r="K14" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L14" s="19">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -37981,7 +37981,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C15" s="11">
         <v>27.5</v>
@@ -38011,7 +38011,7 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C16" s="11">
         <v>25.5</v>
@@ -38036,7 +38036,7 @@
         <v/>
       </c>
       <c r="K16" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L16" s="2">
         <f>IF($L$18&lt;0.3,
@@ -38058,7 +38058,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C17" s="11">
         <v>22.5</v>
@@ -38088,7 +38088,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C18" s="11">
         <v>20.0</v>
@@ -38113,7 +38113,7 @@
         <v/>
       </c>
       <c r="K18" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L18" s="20">
         <f>L5/L2</f>
@@ -38125,7 +38125,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C19" s="11">
         <v>18.5</v>
@@ -38155,7 +38155,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C20" s="11">
         <v>16.5</v>
@@ -38185,7 +38185,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C21" s="11">
         <v>14.5</v>
@@ -38215,7 +38215,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C22" s="11">
         <v>13.5</v>
@@ -38245,7 +38245,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C23" s="11">
         <v>12.0</v>
@@ -38275,7 +38275,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C24" s="11">
         <v>11.0</v>
@@ -38305,7 +38305,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C25" s="11">
         <v>10.0</v>
@@ -38335,7 +38335,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C26" s="11">
         <v>9.5</v>
@@ -38365,7 +38365,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C27" s="11">
         <v>8.5</v>
@@ -38390,7 +38390,7 @@
         <v/>
       </c>
       <c r="K27" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L27" s="2">
         <v>0.8</v>
@@ -38401,7 +38401,7 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C28" s="11">
         <v>8.0</v>
@@ -38431,7 +38431,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C29" s="11">
         <v>7.0</v>
@@ -38461,7 +38461,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C30" s="11">
         <v>6.5</v>
@@ -38491,7 +38491,7 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C31" s="11">
         <v>6.0</v>
@@ -38521,7 +38521,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C32" s="11">
         <v>5.5</v>
@@ -38551,7 +38551,7 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C33" s="11">
         <v>5.0</v>
@@ -38581,7 +38581,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C34" s="11">
         <v>4.5</v>
@@ -38611,7 +38611,7 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C35" s="11">
         <v>4.5</v>
@@ -38641,7 +38641,7 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C36" s="11">
         <v>4.0</v>
@@ -38671,7 +38671,7 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C37" s="11">
         <v>4.0</v>
@@ -38701,7 +38701,7 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C38" s="11">
         <v>3.5</v>
@@ -38731,7 +38731,7 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C39" s="11">
         <v>3.5</v>
@@ -38761,7 +38761,7 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C40" s="11">
         <v>3.0</v>
@@ -38791,7 +38791,7 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C41" s="11">
         <v>3.0</v>
@@ -38821,7 +38821,7 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C42" s="11">
         <v>2.5</v>
@@ -38851,7 +38851,7 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C43" s="11">
         <v>2.5</v>
@@ -38881,7 +38881,7 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C44" s="11">
         <v>2.5</v>
@@ -38911,7 +38911,7 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C45" s="11">
         <v>2.5</v>
@@ -38941,7 +38941,7 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C46" s="11">
         <v>2.0</v>
@@ -38971,7 +38971,7 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C47" s="11">
         <v>2.0</v>
@@ -39001,7 +39001,7 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C48" s="11">
         <v>2.0</v>
@@ -39031,7 +39031,7 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C49" s="11">
         <v>2.0</v>
@@ -39061,7 +39061,7 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C50" s="11">
         <v>2.0</v>
@@ -39091,7 +39091,7 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C51" s="11">
         <v>2.0</v>
@@ -39121,7 +39121,7 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C52" s="11">
         <v>2.0</v>
@@ -39151,7 +39151,7 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C53" s="11">
         <v>2.0</v>
@@ -39181,7 +39181,7 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C54" s="11">
         <v>2.0</v>
@@ -39211,7 +39211,7 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C55" s="11">
         <v>2.0</v>
@@ -39241,7 +39241,7 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C56" s="11">
         <v>2.0</v>
@@ -39271,7 +39271,7 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C57" s="11">
         <v>2.0</v>
@@ -39301,7 +39301,7 @@
         <v>57.0</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C58" s="11">
         <v>2.0</v>
@@ -39331,7 +39331,7 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C59" s="11">
         <v>2.0</v>
@@ -39361,7 +39361,7 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C60" s="11">
         <v>2.0</v>
@@ -39391,7 +39391,7 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C61" s="11">
         <v>2.0</v>
@@ -39421,7 +39421,7 @@
         <v>61.0</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C62" s="11">
         <v>1.0</v>
@@ -39451,7 +39451,7 @@
         <v>62.0</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C63" s="11">
         <v>1.0</v>
@@ -39481,7 +39481,7 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C64" s="11">
         <v>1.0</v>
@@ -39511,7 +39511,7 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C65" s="11">
         <v>1.0</v>
@@ -39541,7 +39541,7 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C66" s="11">
         <v>1.0</v>
@@ -39571,7 +39571,7 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C67" s="11">
         <v>1.0</v>
@@ -39601,7 +39601,7 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C68" s="11">
         <v>1.0</v>
@@ -39631,7 +39631,7 @@
         <v>68.0</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C69" s="11">
         <v>1.0</v>
@@ -39661,7 +39661,7 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C70" s="11">
         <v>1.0</v>
@@ -39691,7 +39691,7 @@
         <v>70.0</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C71" s="11">
         <v>1.0</v>
@@ -39721,7 +39721,7 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C72" s="11">
         <v>1.0</v>
@@ -39751,7 +39751,7 @@
         <v>72.0</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C73" s="11">
         <v>1.0</v>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -29,16 +29,16 @@
     <t>PLAYER NAME</t>
   </si>
   <si>
+    <t>New Values</t>
+  </si>
+  <si>
     <t>PreDraft$</t>
   </si>
   <si>
-    <t>New Values</t>
+    <t>Spine</t>
   </si>
   <si>
     <t>Final Price</t>
-  </si>
-  <si>
-    <t>Spine</t>
   </si>
   <si>
     <t>Mine?</t>
@@ -56,10 +56,10 @@
     <t>EnforceUpTo</t>
   </si>
   <si>
-    <t>Value vs Fair</t>
+    <t>Fractions</t>
   </si>
   <si>
-    <t>Fractions</t>
+    <t>Value vs Fair</t>
   </si>
   <si>
     <t>Settings</t>
@@ -107,10 +107,10 @@
     <t>Kenyon Sadiq</t>
   </si>
   <si>
-    <t>Round 1</t>
+    <t>My Spent</t>
   </si>
   <si>
-    <t>My Spent</t>
+    <t>Round 1</t>
   </si>
   <si>
     <t>Sonny Styles</t>
@@ -146,13 +146,13 @@
     <t>Undrafted Predraft$</t>
   </si>
   <si>
+    <t>Round 2</t>
+  </si>
+  <si>
     <t>Arvell Reese</t>
   </si>
   <si>
     <t>Inflation Factor</t>
-  </si>
-  <si>
-    <t>Round 2</t>
   </si>
   <si>
     <t>Ty Simpson</t>
@@ -164,16 +164,19 @@
     <t>Aggression</t>
   </si>
   <si>
-    <t>Caleb Downs</t>
+    <t>Round 3</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>Caleb Downs</t>
   </si>
   <si>
     <t>David Bailey</t>
   </si>
   <si>
     <t>League Spent %</t>
+  </si>
+  <si>
+    <t>Round 4</t>
   </si>
   <si>
     <t>Jacob Rodriguez</t>
@@ -188,9 +191,6 @@
     <t>Dillon Thieneman</t>
   </si>
   <si>
-    <t>Round 4</t>
-  </si>
-  <si>
     <t>Rueben Bain</t>
   </si>
   <si>
@@ -198,6 +198,9 @@
   </si>
   <si>
     <t>Germie Bernard</t>
+  </si>
+  <si>
+    <t>Round 5</t>
   </si>
   <si>
     <t>Nicholas Singleton</t>
@@ -209,9 +212,6 @@
     <t>Enforce % of Fair</t>
   </si>
   <si>
-    <t>Round 5</t>
-  </si>
-  <si>
     <t>Antonio Williams</t>
   </si>
   <si>
@@ -221,6 +221,9 @@
     <t>Emmett Johnson</t>
   </si>
   <si>
+    <t>Round 6</t>
+  </si>
+  <si>
     <t>Chris Brazzell</t>
   </si>
   <si>
@@ -228,9 +231,6 @@
   </si>
   <si>
     <t>Zachariah Branch</t>
-  </si>
-  <si>
-    <t>Round 6</t>
   </si>
   <si>
     <t>De'Zhaun Stribling</t>
@@ -923,10 +923,10 @@
         <v>3</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F1" s="5">
         <v>2025.0</v>
@@ -941,7 +941,7 @@
         <v>12</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>17</v>
@@ -1071,7 +1071,7 @@
       <c r="M2" s="11"/>
       <c r="N2" s="11"/>
       <c r="O2" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="11"/>
       <c r="N3" s="11"/>
       <c r="O3" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="11"/>
       <c r="N4" s="11"/>
       <c r="O4" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
       <c r="O5" s="8" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
       <c r="O6" s="8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="11"/>
       <c r="N7" s="11"/>
       <c r="O7" s="8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -9575,7 +9575,7 @@
         <v>10.0</v>
       </c>
       <c r="X148" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Y148" s="10" t="s">
         <v>145</v>
@@ -9615,7 +9615,7 @@
         <v>11.0</v>
       </c>
       <c r="X149" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Y149" s="10" t="s">
         <v>143</v>
@@ -9815,7 +9815,7 @@
         <v>16.0</v>
       </c>
       <c r="X154" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Y154" s="10" t="s">
         <v>143</v>
@@ -9855,7 +9855,7 @@
         <v>17.0</v>
       </c>
       <c r="X155" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Y155" s="10" t="s">
         <v>140</v>
@@ -9895,7 +9895,7 @@
         <v>18.0</v>
       </c>
       <c r="X156" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Y156" s="10" t="s">
         <v>145</v>
@@ -10215,7 +10215,7 @@
         <v>26.0</v>
       </c>
       <c r="X164" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Y164" s="10" t="s">
         <v>140</v>
@@ -10335,7 +10335,7 @@
         <v>29.0</v>
       </c>
       <c r="X167" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Y167" s="10" t="s">
         <v>143</v>
@@ -10415,7 +10415,7 @@
         <v>31.0</v>
       </c>
       <c r="X169" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y169" s="10" t="s">
         <v>141</v>
@@ -10735,7 +10735,7 @@
         <v>39.0</v>
       </c>
       <c r="X177" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Y177" s="10" t="s">
         <v>144</v>
@@ -37450,10 +37450,10 @@
         <v>4</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>9</v>
@@ -37468,7 +37468,7 @@
         <v>13</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>16</v>
@@ -37715,7 +37715,7 @@
         <v/>
       </c>
       <c r="K7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L7" s="17">
         <f>SUMIF($E$2:$E$500,TRUE,$D$2:$D$500)</f>
@@ -37944,7 +37944,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" s="12">
         <v>30.5</v>
@@ -37969,7 +37969,7 @@
         <v/>
       </c>
       <c r="K14" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L14" s="19">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -38058,7 +38058,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C17" s="12">
         <v>22.5</v>
@@ -38125,7 +38125,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" s="12">
         <v>18.5</v>
@@ -38155,7 +38155,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C20" s="12">
         <v>16.5</v>
@@ -38185,7 +38185,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C21" s="12">
         <v>14.5</v>
@@ -38215,7 +38215,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" s="12">
         <v>13.5</v>
@@ -38335,7 +38335,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C26" s="12">
         <v>9.5</v>
@@ -38365,7 +38365,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" s="12">
         <v>8.5</v>
@@ -38390,7 +38390,7 @@
         <v/>
       </c>
       <c r="K27" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L27" s="3">
         <v>0.8</v>
@@ -38491,7 +38491,7 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C31" s="12">
         <v>6.0</v>
@@ -38521,7 +38521,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C32" s="12">
         <v>5.5</v>
@@ -38551,7 +38551,7 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C33" s="12">
         <v>5.0</v>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -38,6 +38,9 @@
     <t>VALUE</t>
   </si>
   <si>
+    <t>Decay</t>
+  </si>
+  <si>
     <t>My Max Bid</t>
   </si>
   <si>
@@ -50,16 +53,13 @@
     <t>Settings</t>
   </si>
   <si>
-    <t>Decay</t>
-  </si>
-  <si>
     <t>New Values</t>
   </si>
   <si>
-    <t>Spine</t>
+    <t>Jeremiyah Love</t>
   </si>
   <si>
-    <t>Jeremiyah Love</t>
+    <t>Spine</t>
   </si>
   <si>
     <t>Floors</t>
@@ -116,9 +116,6 @@
     <t>Sonny Styles</t>
   </si>
   <si>
-    <t>Round 2</t>
-  </si>
-  <si>
     <t>My Remaining</t>
   </si>
   <si>
@@ -134,9 +131,6 @@
     <t>Avg $ per Other Team</t>
   </si>
   <si>
-    <t>Round 3</t>
-  </si>
-  <si>
     <t>Eli Stowers</t>
   </si>
   <si>
@@ -149,7 +143,7 @@
     <t>CJ Allen</t>
   </si>
   <si>
-    <t>Round 4</t>
+    <t>Round 2</t>
   </si>
   <si>
     <t>Undrafted Predraft$</t>
@@ -167,16 +161,16 @@
     <t>Denzel Boston</t>
   </si>
   <si>
-    <t>Round 5</t>
-  </si>
-  <si>
     <t>Aggression</t>
   </si>
   <si>
-    <t>Round 6</t>
+    <t>Round 3</t>
   </si>
   <si>
     <t>Caleb Downs</t>
+  </si>
+  <si>
+    <t>Round 4</t>
   </si>
   <si>
     <t>David Bailey</t>
@@ -194,6 +188,9 @@
     <t>Jake Golday</t>
   </si>
   <si>
+    <t>Round 5</t>
+  </si>
+  <si>
     <t>Dillon Thieneman</t>
   </si>
   <si>
@@ -207,6 +204,9 @@
   </si>
   <si>
     <t>Nicholas Singleton</t>
+  </si>
+  <si>
+    <t>Round 6</t>
   </si>
   <si>
     <t>Mike Washington</t>
@@ -617,11 +617,11 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
@@ -916,17 +916,17 @@
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F1" s="7">
         <v>2025.0</v>
@@ -1003,7 +1003,7 @@
       <c r="A2" s="13">
         <v>1.01</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="4">
         <v>7580.0</v>
       </c>
       <c r="C2" s="16">
@@ -1132,7 +1132,7 @@
       <c r="A3" s="13">
         <v>1.02</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>5598.5</v>
       </c>
       <c r="C3" s="16">
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="10" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1241,7 +1241,7 @@
       <c r="A4" s="13">
         <v>1.03</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>5649.0</v>
       </c>
       <c r="C4" s="16">
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="10" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1345,7 +1345,7 @@
       <c r="A5" s="13">
         <v>1.04</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>5074.5</v>
       </c>
       <c r="C5" s="16">
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="10" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1449,7 +1449,7 @@
       <c r="A6" s="13">
         <v>1.05</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="4">
         <v>5076.0</v>
       </c>
       <c r="C6" s="16">
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="10" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1553,7 +1553,7 @@
       <c r="A7" s="13">
         <v>1.06</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>4965.0</v>
       </c>
       <c r="C7" s="16">
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="10" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1657,7 +1657,7 @@
       <c r="A8" s="13">
         <v>1.07</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="4">
         <v>4014.5</v>
       </c>
       <c r="C8" s="16">
@@ -1759,7 +1759,7 @@
       <c r="A9" s="13">
         <v>1.08</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="4">
         <v>4308.0</v>
       </c>
       <c r="C9" s="16">
@@ -1822,7 +1822,7 @@
       <c r="A10" s="13">
         <v>1.09</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="4">
         <v>3869.0</v>
       </c>
       <c r="C10" s="16">
@@ -1885,7 +1885,7 @@
       <c r="A11" s="13">
         <v>1.1</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="4">
         <v>4169.0</v>
       </c>
       <c r="C11" s="16">
@@ -1948,7 +1948,7 @@
       <c r="A12" s="13">
         <v>1.11</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="4">
         <v>4164.0</v>
       </c>
       <c r="C12" s="16">
@@ -2011,7 +2011,7 @@
       <c r="A13" s="13">
         <v>1.12</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="4">
         <v>3809.5</v>
       </c>
       <c r="C13" s="16">
@@ -2074,7 +2074,7 @@
       <c r="A14" s="13">
         <v>2.01</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="4">
         <v>3397.5</v>
       </c>
       <c r="C14" s="16">
@@ -2137,7 +2137,7 @@
       <c r="A15" s="13">
         <v>2.02</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="4">
         <v>3611.0</v>
       </c>
       <c r="C15" s="16">
@@ -2200,7 +2200,7 @@
       <c r="A16" s="13">
         <v>2.03</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="4">
         <v>3605.0</v>
       </c>
       <c r="C16" s="16">
@@ -2263,7 +2263,7 @@
       <c r="A17" s="13">
         <v>2.04</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="4">
         <v>3603.0</v>
       </c>
       <c r="C17" s="16">
@@ -2326,7 +2326,7 @@
       <c r="A18" s="13">
         <v>2.05</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="4">
         <v>3440.5</v>
       </c>
       <c r="C18" s="16">
@@ -2389,7 +2389,7 @@
       <c r="A19" s="13">
         <v>2.06</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="4">
         <v>3220.0</v>
       </c>
       <c r="C19" s="16">
@@ -2452,7 +2452,7 @@
       <c r="A20" s="13">
         <v>2.07</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="4">
         <v>3200.0</v>
       </c>
       <c r="C20" s="16">
@@ -2515,7 +2515,7 @@
       <c r="A21" s="13">
         <v>2.08</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="4">
         <v>3127.0</v>
       </c>
       <c r="C21" s="16">
@@ -2578,7 +2578,7 @@
       <c r="A22" s="13">
         <v>2.09</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="4">
         <v>2943.0</v>
       </c>
       <c r="C22" s="16">
@@ -2641,7 +2641,7 @@
       <c r="A23" s="13">
         <v>2.1</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="4">
         <v>3020.0</v>
       </c>
       <c r="C23" s="16">
@@ -2704,7 +2704,7 @@
       <c r="A24" s="13">
         <v>2.11</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="4">
         <v>2537.5</v>
       </c>
       <c r="C24" s="16">
@@ -2767,7 +2767,7 @@
       <c r="A25" s="13">
         <v>2.12</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="4">
         <v>2406.0</v>
       </c>
       <c r="C25" s="16">
@@ -2830,7 +2830,7 @@
       <c r="A26" s="13">
         <v>3.01</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="4">
         <v>2671.0</v>
       </c>
       <c r="C26" s="16">
@@ -2893,7 +2893,7 @@
       <c r="A27" s="13">
         <v>3.02</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="4">
         <v>2628.0</v>
       </c>
       <c r="C27" s="16">
@@ -2956,7 +2956,7 @@
       <c r="A28" s="13">
         <v>3.03</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="4">
         <v>1998.5</v>
       </c>
       <c r="C28" s="16">
@@ -3019,7 +3019,7 @@
       <c r="A29" s="13">
         <v>3.04</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="4">
         <v>2202.5</v>
       </c>
       <c r="C29" s="16">
@@ -3100,7 +3100,7 @@
       <c r="A30" s="13">
         <v>3.05</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="4">
         <v>2252.5</v>
       </c>
       <c r="C30" s="16">
@@ -3175,7 +3175,7 @@
       <c r="A31" s="13">
         <v>3.06</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="4">
         <v>2458.0</v>
       </c>
       <c r="C31" s="16">
@@ -3250,7 +3250,7 @@
       <c r="A32" s="13">
         <v>3.07</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="4">
         <v>2332.5</v>
       </c>
       <c r="C32" s="16">
@@ -3325,7 +3325,7 @@
       <c r="A33" s="13">
         <v>3.08</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="4">
         <v>2331.0</v>
       </c>
       <c r="C33" s="16">
@@ -3400,7 +3400,7 @@
       <c r="A34" s="13">
         <v>3.09</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="4">
         <v>1991.0</v>
       </c>
       <c r="C34" s="16">
@@ -3475,7 +3475,7 @@
       <c r="A35" s="13">
         <v>3.1</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="4">
         <v>2180.5</v>
       </c>
       <c r="C35" s="16">
@@ -3550,7 +3550,7 @@
       <c r="A36" s="13">
         <v>3.11</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="4">
         <v>2432.0</v>
       </c>
       <c r="C36" s="16">
@@ -3625,7 +3625,7 @@
       <c r="A37" s="13">
         <v>3.12</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="4">
         <v>2014.0</v>
       </c>
       <c r="C37" s="16">
@@ -3700,7 +3700,7 @@
       <c r="A38" s="13">
         <v>4.01</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="4">
         <v>1907.0</v>
       </c>
       <c r="C38" s="16">
@@ -3775,7 +3775,7 @@
       <c r="A39" s="13">
         <v>4.02</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39" s="4">
         <v>2089.0</v>
       </c>
       <c r="C39" s="16">
@@ -3850,7 +3850,7 @@
       <c r="A40" s="13">
         <v>4.03</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40" s="4">
         <v>2080.0</v>
       </c>
       <c r="C40" s="16">
@@ -3925,7 +3925,7 @@
       <c r="A41" s="13">
         <v>4.04</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B41" s="4">
         <v>2063.0</v>
       </c>
       <c r="C41" s="16">
@@ -4066,7 +4066,7 @@
       <c r="A43" s="13">
         <v>4.06</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43" s="4">
         <v>1539.5</v>
       </c>
       <c r="C43" s="16">
@@ -4132,7 +4132,7 @@
       <c r="A44" s="13">
         <v>4.07</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B44" s="4">
         <v>1956.0</v>
       </c>
       <c r="C44" s="16">
@@ -4206,7 +4206,7 @@
       <c r="A45" s="13">
         <v>4.08</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45" s="4">
         <v>1953.0</v>
       </c>
       <c r="C45" s="16">
@@ -4296,7 +4296,7 @@
       <c r="A46" s="13">
         <v>4.09</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B46" s="4">
         <v>1945.0</v>
       </c>
       <c r="C46" s="16">
@@ -4374,7 +4374,7 @@
       <c r="A47" s="13">
         <v>4.1</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B47" s="4">
         <v>1938.0</v>
       </c>
       <c r="C47" s="16">
@@ -4452,7 +4452,7 @@
       <c r="A48" s="13">
         <v>4.11</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48" s="4">
         <v>1926.0</v>
       </c>
       <c r="C48" s="16">
@@ -4530,7 +4530,7 @@
       <c r="A49" s="13">
         <v>4.12</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B49" s="4">
         <v>1917.0</v>
       </c>
       <c r="C49" s="16">
@@ -4608,7 +4608,7 @@
       <c r="A50" s="13">
         <v>5.01</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50" s="4">
         <v>1917.0</v>
       </c>
       <c r="C50" s="16">
@@ -4686,7 +4686,7 @@
       <c r="A51" s="13">
         <v>5.02</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B51" s="4">
         <v>1916.0</v>
       </c>
       <c r="C51" s="16">
@@ -4764,7 +4764,7 @@
       <c r="A52" s="13">
         <v>5.03</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52" s="4">
         <v>1647.5</v>
       </c>
       <c r="C52" s="16">
@@ -4842,7 +4842,7 @@
       <c r="A53" s="13">
         <v>5.04</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B53" s="4">
         <v>1374.0</v>
       </c>
       <c r="C53" s="16">
@@ -4920,7 +4920,7 @@
       <c r="A54" s="13">
         <v>5.05</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B54" s="4">
         <v>1424.0</v>
       </c>
       <c r="C54" s="16">
@@ -4998,7 +4998,7 @@
       <c r="A55" s="13">
         <v>5.06</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B55" s="4">
         <v>1370.5</v>
       </c>
       <c r="C55" s="16">
@@ -5076,7 +5076,7 @@
       <c r="A56" s="13">
         <v>5.07</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B56" s="4">
         <v>1643.0</v>
       </c>
       <c r="C56" s="16">
@@ -5154,7 +5154,7 @@
       <c r="A57" s="13">
         <v>5.08</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B57" s="4">
         <v>1628.0</v>
       </c>
       <c r="C57" s="16">
@@ -5232,7 +5232,7 @@
       <c r="A58" s="13">
         <v>5.09</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58" s="4">
         <v>1302.0</v>
       </c>
       <c r="C58" s="16">
@@ -5310,7 +5310,7 @@
       <c r="A59" s="13">
         <v>5.1</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B59" s="4">
         <v>1284.0</v>
       </c>
       <c r="C59" s="16">
@@ -5388,7 +5388,7 @@
       <c r="A60" s="13">
         <v>5.11</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B60" s="4">
         <v>1254.0</v>
       </c>
       <c r="C60" s="16">
@@ -5466,7 +5466,7 @@
       <c r="A61" s="13">
         <v>5.12</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B61" s="4">
         <v>1253.0</v>
       </c>
       <c r="C61" s="16">
@@ -5544,7 +5544,7 @@
       <c r="A62" s="13">
         <v>6.01</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B62" s="4">
         <v>1251.0</v>
       </c>
       <c r="C62" s="16">
@@ -5626,7 +5626,7 @@
       <c r="A63" s="13">
         <v>6.02</v>
       </c>
-      <c r="B63" s="3">
+      <c r="B63" s="4">
         <v>1250.0</v>
       </c>
       <c r="C63" s="16">
@@ -5709,7 +5709,7 @@
       <c r="A64" s="13">
         <v>6.03</v>
       </c>
-      <c r="B64" s="3">
+      <c r="B64" s="4">
         <v>1249.0</v>
       </c>
       <c r="C64" s="16">
@@ -5792,7 +5792,7 @@
       <c r="A65" s="13">
         <v>6.04</v>
       </c>
-      <c r="B65" s="3">
+      <c r="B65" s="4">
         <v>1246.0</v>
       </c>
       <c r="C65" s="16">
@@ -5875,7 +5875,7 @@
       <c r="A66" s="13">
         <v>6.05</v>
       </c>
-      <c r="B66" s="3">
+      <c r="B66" s="4">
         <v>1245.0</v>
       </c>
       <c r="C66" s="16">
@@ -5958,7 +5958,7 @@
       <c r="A67" s="13">
         <v>6.06</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B67" s="4">
         <v>1244.0</v>
       </c>
       <c r="C67" s="16">
@@ -6041,7 +6041,7 @@
       <c r="A68" s="13">
         <v>6.07</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B68" s="4">
         <v>1243.0</v>
       </c>
       <c r="C68" s="16">
@@ -6207,7 +6207,7 @@
       <c r="A70" s="13">
         <v>6.09</v>
       </c>
-      <c r="B70" s="3">
+      <c r="B70" s="4">
         <v>1234.0</v>
       </c>
       <c r="C70" s="16">
@@ -6290,7 +6290,7 @@
       <c r="A71" s="13">
         <v>6.1</v>
       </c>
-      <c r="B71" s="3">
+      <c r="B71" s="4">
         <v>1223.0</v>
       </c>
       <c r="C71" s="16">
@@ -6456,7 +6456,7 @@
       <c r="A73" s="13">
         <v>6.12</v>
       </c>
-      <c r="B73" s="3">
+      <c r="B73" s="4">
         <v>1166.0</v>
       </c>
       <c r="C73" s="16">
@@ -9255,7 +9255,7 @@
         <v>1.0</v>
       </c>
       <c r="X140" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y140" s="6" t="s">
         <v>140</v>
@@ -9535,7 +9535,7 @@
         <v>9.0</v>
       </c>
       <c r="X147" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Y147" s="6" t="s">
         <v>141</v>
@@ -9575,7 +9575,7 @@
         <v>10.0</v>
       </c>
       <c r="X148" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="Y148" s="6" t="s">
         <v>145</v>
@@ -9615,7 +9615,7 @@
         <v>11.0</v>
       </c>
       <c r="X149" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Y149" s="6" t="s">
         <v>143</v>
@@ -9655,7 +9655,7 @@
         <v>12.0</v>
       </c>
       <c r="X150" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Y150" s="6" t="s">
         <v>146</v>
@@ -9775,7 +9775,7 @@
         <v>15.0</v>
       </c>
       <c r="X153" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Y153" s="6" t="s">
         <v>141</v>
@@ -9815,7 +9815,7 @@
         <v>16.0</v>
       </c>
       <c r="X154" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Y154" s="6" t="s">
         <v>143</v>
@@ -9855,7 +9855,7 @@
         <v>17.0</v>
       </c>
       <c r="X155" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Y155" s="6" t="s">
         <v>140</v>
@@ -9895,7 +9895,7 @@
         <v>18.0</v>
       </c>
       <c r="X156" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Y156" s="6" t="s">
         <v>145</v>
@@ -9975,7 +9975,7 @@
         <v>20.0</v>
       </c>
       <c r="X158" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Y158" s="6" t="s">
         <v>140</v>
@@ -10055,7 +10055,7 @@
         <v>22.0</v>
       </c>
       <c r="X160" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Y160" s="6" t="s">
         <v>144</v>
@@ -10095,7 +10095,7 @@
         <v>23.0</v>
       </c>
       <c r="X161" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Y161" s="6" t="s">
         <v>142</v>
@@ -10215,7 +10215,7 @@
         <v>26.0</v>
       </c>
       <c r="X164" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Y164" s="6" t="s">
         <v>140</v>
@@ -10335,7 +10335,7 @@
         <v>29.0</v>
       </c>
       <c r="X167" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Y167" s="6" t="s">
         <v>143</v>
@@ -10375,7 +10375,7 @@
         <v>30.0</v>
       </c>
       <c r="X168" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Y168" s="6" t="s">
         <v>141</v>
@@ -10695,7 +10695,7 @@
         <v>38.0</v>
       </c>
       <c r="X176" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y176" s="6" t="s">
         <v>141</v>
@@ -37458,20 +37458,20 @@
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="H1" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2">
@@ -37479,7 +37479,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" s="8">
         <v>139.0</v>
@@ -37604,7 +37604,7 @@
       <c r="K4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="4">
         <f>'Draft Data'!U63</f>
         <v>180</v>
       </c>
@@ -37752,7 +37752,7 @@
         <v/>
       </c>
       <c r="K8" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L8" s="8">
         <f>L4-L7
@@ -37765,7 +37765,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" s="8">
         <v>53.0</v>
@@ -37790,7 +37790,7 @@
         <v/>
       </c>
       <c r="K9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L9" s="8">
         <f>L6-L8
@@ -37803,7 +37803,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="8">
         <v>48.0</v>
@@ -37828,7 +37828,7 @@
         <v/>
       </c>
       <c r="K10" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L10" s="8">
         <f>IF(L3&gt;1,L9/(L3-1),0)</f>
@@ -37840,7 +37840,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C11" s="8">
         <v>43.0</v>
@@ -37865,7 +37865,7 @@
         <v/>
       </c>
       <c r="K11" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L11" s="19">
         <f>IF(L10&gt;0,L8/L10,1)</f>
@@ -37877,7 +37877,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C12" s="8">
         <v>39.0</v>
@@ -37907,7 +37907,7 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C13" s="8">
         <v>34.0</v>
@@ -37932,7 +37932,7 @@
         <v/>
       </c>
       <c r="K13" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L13" s="17">
         <f>SUMIF($D$2:$D$73,"",$C$2:$C$73)</f>
@@ -37944,7 +37944,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C14" s="8">
         <v>30.5</v>
@@ -37969,7 +37969,7 @@
         <v/>
       </c>
       <c r="K14" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L14" s="19">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -37981,7 +37981,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C15" s="8">
         <v>27.5</v>
@@ -38011,7 +38011,7 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C16" s="8">
         <v>25.5</v>
@@ -38036,7 +38036,7 @@
         <v/>
       </c>
       <c r="K16" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="L16" s="1">
         <f>IF($L$18&lt;0.3,
@@ -38058,7 +38058,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C17" s="8">
         <v>22.5</v>
@@ -38088,7 +38088,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C18" s="8">
         <v>20.0</v>
@@ -38113,7 +38113,7 @@
         <v/>
       </c>
       <c r="K18" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L18" s="20">
         <f>L5/L2</f>
@@ -38125,7 +38125,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C19" s="8">
         <v>18.5</v>
@@ -38155,7 +38155,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C20" s="8">
         <v>16.5</v>
@@ -38185,7 +38185,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C21" s="8">
         <v>14.5</v>
@@ -38215,7 +38215,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C22" s="8">
         <v>13.5</v>
@@ -38245,7 +38245,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C23" s="8">
         <v>12.0</v>
@@ -38275,7 +38275,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C24" s="8">
         <v>11.0</v>
@@ -38305,7 +38305,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C25" s="8">
         <v>10.0</v>
@@ -38335,7 +38335,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C26" s="8">
         <v>9.5</v>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -113,9 +113,6 @@
     <t>Sonny Styles</t>
   </si>
   <si>
-    <t>Round 1</t>
-  </si>
-  <si>
     <t>My Remaining</t>
   </si>
   <si>
@@ -129,6 +126,9 @@
   </si>
   <si>
     <t>Avg $ per Other Team</t>
+  </si>
+  <si>
+    <t>Round 1</t>
   </si>
   <si>
     <t>Eli Stowers</t>
@@ -152,19 +152,16 @@
     <t>Inflation Factor</t>
   </si>
   <si>
-    <t>Round 2</t>
-  </si>
-  <si>
     <t>Ty Simpson</t>
   </si>
   <si>
     <t>Denzel Boston</t>
   </si>
   <si>
-    <t>Aggression</t>
+    <t>Round 2</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>Aggression</t>
   </si>
   <si>
     <t>Caleb Downs</t>
@@ -173,13 +170,13 @@
     <t>David Bailey</t>
   </si>
   <si>
+    <t>Round 3</t>
+  </si>
+  <si>
     <t>League Spent %</t>
   </si>
   <si>
     <t>Jacob Rodriguez</t>
-  </si>
-  <si>
-    <t>Round 4</t>
   </si>
   <si>
     <t>Jonah Coleman</t>
@@ -197,7 +194,7 @@
     <t>Chris Bell</t>
   </si>
   <si>
-    <t>Round 5</t>
+    <t>Round 4</t>
   </si>
   <si>
     <t>Germie Bernard</t>
@@ -218,7 +215,7 @@
     <t>Elijah Sarratt</t>
   </si>
   <si>
-    <t>Round 6</t>
+    <t>Round 5</t>
   </si>
   <si>
     <t>Emmett Johnson</t>
@@ -240,6 +237,9 @@
   </si>
   <si>
     <t>Kaytron Allen</t>
+  </si>
+  <si>
+    <t>Round 6</t>
   </si>
   <si>
     <t>Ted Hurst</t>
@@ -645,11 +645,11 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
@@ -1000,7 +1000,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <v>1.01</v>
       </c>
       <c r="B2" s="4">
@@ -1071,7 +1071,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="10" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1129,7 +1129,7 @@
       <c r="AD2" s="10"/>
     </row>
     <row r="3">
-      <c r="A3" s="13">
+      <c r="A3" s="14">
         <v>1.02</v>
       </c>
       <c r="B3" s="4">
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1238,7 +1238,7 @@
       <c r="AD3" s="10"/>
     </row>
     <row r="4">
-      <c r="A4" s="13">
+      <c r="A4" s="14">
         <v>1.03</v>
       </c>
       <c r="B4" s="4">
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1342,7 +1342,7 @@
       <c r="AD4" s="10"/>
     </row>
     <row r="5">
-      <c r="A5" s="13">
+      <c r="A5" s="14">
         <v>1.04</v>
       </c>
       <c r="B5" s="4">
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="10" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1446,7 +1446,7 @@
       <c r="AD5" s="10"/>
     </row>
     <row r="6">
-      <c r="A6" s="13">
+      <c r="A6" s="14">
         <v>1.05</v>
       </c>
       <c r="B6" s="4">
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="10" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1550,7 +1550,7 @@
       <c r="AD6" s="10"/>
     </row>
     <row r="7">
-      <c r="A7" s="13">
+      <c r="A7" s="14">
         <v>1.06</v>
       </c>
       <c r="B7" s="4">
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="10" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1654,7 +1654,7 @@
       <c r="AD7" s="10"/>
     </row>
     <row r="8">
-      <c r="A8" s="13">
+      <c r="A8" s="14">
         <v>1.07</v>
       </c>
       <c r="B8" s="4">
@@ -1756,7 +1756,7 @@
       <c r="AD8" s="10"/>
     </row>
     <row r="9">
-      <c r="A9" s="13">
+      <c r="A9" s="14">
         <v>1.08</v>
       </c>
       <c r="B9" s="4">
@@ -1819,7 +1819,7 @@
       <c r="AD9" s="12"/>
     </row>
     <row r="10">
-      <c r="A10" s="13">
+      <c r="A10" s="14">
         <v>1.09</v>
       </c>
       <c r="B10" s="4">
@@ -1882,7 +1882,7 @@
       <c r="AD10" s="12"/>
     </row>
     <row r="11">
-      <c r="A11" s="13">
+      <c r="A11" s="14">
         <v>1.1</v>
       </c>
       <c r="B11" s="4">
@@ -1945,7 +1945,7 @@
       <c r="AD11" s="12"/>
     </row>
     <row r="12">
-      <c r="A12" s="13">
+      <c r="A12" s="14">
         <v>1.11</v>
       </c>
       <c r="B12" s="4">
@@ -2008,7 +2008,7 @@
       <c r="AD12" s="12"/>
     </row>
     <row r="13">
-      <c r="A13" s="13">
+      <c r="A13" s="14">
         <v>1.12</v>
       </c>
       <c r="B13" s="4">
@@ -2071,7 +2071,7 @@
       <c r="AD13" s="12"/>
     </row>
     <row r="14">
-      <c r="A14" s="13">
+      <c r="A14" s="14">
         <v>2.01</v>
       </c>
       <c r="B14" s="4">
@@ -2134,7 +2134,7 @@
       <c r="AD14" s="12"/>
     </row>
     <row r="15">
-      <c r="A15" s="13">
+      <c r="A15" s="14">
         <v>2.02</v>
       </c>
       <c r="B15" s="4">
@@ -2197,7 +2197,7 @@
       <c r="AD15" s="12"/>
     </row>
     <row r="16">
-      <c r="A16" s="13">
+      <c r="A16" s="14">
         <v>2.03</v>
       </c>
       <c r="B16" s="4">
@@ -2260,7 +2260,7 @@
       <c r="AD16" s="12"/>
     </row>
     <row r="17">
-      <c r="A17" s="13">
+      <c r="A17" s="14">
         <v>2.04</v>
       </c>
       <c r="B17" s="4">
@@ -2323,7 +2323,7 @@
       <c r="AD17" s="12"/>
     </row>
     <row r="18">
-      <c r="A18" s="13">
+      <c r="A18" s="14">
         <v>2.05</v>
       </c>
       <c r="B18" s="4">
@@ -2386,7 +2386,7 @@
       <c r="AD18" s="12"/>
     </row>
     <row r="19">
-      <c r="A19" s="13">
+      <c r="A19" s="14">
         <v>2.06</v>
       </c>
       <c r="B19" s="4">
@@ -2449,7 +2449,7 @@
       <c r="AD19" s="12"/>
     </row>
     <row r="20">
-      <c r="A20" s="13">
+      <c r="A20" s="14">
         <v>2.07</v>
       </c>
       <c r="B20" s="4">
@@ -2512,7 +2512,7 @@
       <c r="AD20" s="12"/>
     </row>
     <row r="21">
-      <c r="A21" s="13">
+      <c r="A21" s="14">
         <v>2.08</v>
       </c>
       <c r="B21" s="4">
@@ -2575,7 +2575,7 @@
       <c r="AD21" s="12"/>
     </row>
     <row r="22">
-      <c r="A22" s="13">
+      <c r="A22" s="14">
         <v>2.09</v>
       </c>
       <c r="B22" s="4">
@@ -2638,7 +2638,7 @@
       <c r="AD22" s="12"/>
     </row>
     <row r="23">
-      <c r="A23" s="13">
+      <c r="A23" s="14">
         <v>2.1</v>
       </c>
       <c r="B23" s="4">
@@ -2701,7 +2701,7 @@
       <c r="AD23" s="12"/>
     </row>
     <row r="24">
-      <c r="A24" s="13">
+      <c r="A24" s="14">
         <v>2.11</v>
       </c>
       <c r="B24" s="4">
@@ -2764,7 +2764,7 @@
       <c r="AD24" s="12"/>
     </row>
     <row r="25">
-      <c r="A25" s="13">
+      <c r="A25" s="14">
         <v>2.12</v>
       </c>
       <c r="B25" s="4">
@@ -2827,7 +2827,7 @@
       <c r="AD25" s="12"/>
     </row>
     <row r="26">
-      <c r="A26" s="13">
+      <c r="A26" s="14">
         <v>3.01</v>
       </c>
       <c r="B26" s="4">
@@ -2890,7 +2890,7 @@
       <c r="AD26" s="12"/>
     </row>
     <row r="27">
-      <c r="A27" s="13">
+      <c r="A27" s="14">
         <v>3.02</v>
       </c>
       <c r="B27" s="4">
@@ -2953,7 +2953,7 @@
       <c r="AD27" s="12"/>
     </row>
     <row r="28">
-      <c r="A28" s="13">
+      <c r="A28" s="14">
         <v>3.03</v>
       </c>
       <c r="B28" s="4">
@@ -3016,7 +3016,7 @@
       <c r="AD28" s="12"/>
     </row>
     <row r="29">
-      <c r="A29" s="13">
+      <c r="A29" s="14">
         <v>3.04</v>
       </c>
       <c r="B29" s="4">
@@ -3097,7 +3097,7 @@
       <c r="AD29" s="12"/>
     </row>
     <row r="30">
-      <c r="A30" s="13">
+      <c r="A30" s="14">
         <v>3.05</v>
       </c>
       <c r="B30" s="4">
@@ -3172,7 +3172,7 @@
       <c r="AD30" s="12"/>
     </row>
     <row r="31">
-      <c r="A31" s="13">
+      <c r="A31" s="14">
         <v>3.06</v>
       </c>
       <c r="B31" s="4">
@@ -3247,7 +3247,7 @@
       <c r="AD31" s="12"/>
     </row>
     <row r="32">
-      <c r="A32" s="13">
+      <c r="A32" s="14">
         <v>3.07</v>
       </c>
       <c r="B32" s="4">
@@ -3322,7 +3322,7 @@
       <c r="AD32" s="12"/>
     </row>
     <row r="33">
-      <c r="A33" s="13">
+      <c r="A33" s="14">
         <v>3.08</v>
       </c>
       <c r="B33" s="4">
@@ -3397,7 +3397,7 @@
       <c r="AD33" s="12"/>
     </row>
     <row r="34">
-      <c r="A34" s="13">
+      <c r="A34" s="14">
         <v>3.09</v>
       </c>
       <c r="B34" s="4">
@@ -3472,7 +3472,7 @@
       <c r="AD34" s="12"/>
     </row>
     <row r="35">
-      <c r="A35" s="13">
+      <c r="A35" s="14">
         <v>3.1</v>
       </c>
       <c r="B35" s="4">
@@ -3547,7 +3547,7 @@
       <c r="AD35" s="12"/>
     </row>
     <row r="36">
-      <c r="A36" s="13">
+      <c r="A36" s="14">
         <v>3.11</v>
       </c>
       <c r="B36" s="4">
@@ -3622,7 +3622,7 @@
       <c r="AD36" s="12"/>
     </row>
     <row r="37">
-      <c r="A37" s="13">
+      <c r="A37" s="14">
         <v>3.12</v>
       </c>
       <c r="B37" s="4">
@@ -3697,7 +3697,7 @@
       <c r="AD37" s="12"/>
     </row>
     <row r="38">
-      <c r="A38" s="13">
+      <c r="A38" s="14">
         <v>4.01</v>
       </c>
       <c r="B38" s="4">
@@ -3772,7 +3772,7 @@
       <c r="AD38" s="12"/>
     </row>
     <row r="39">
-      <c r="A39" s="13">
+      <c r="A39" s="14">
         <v>4.02</v>
       </c>
       <c r="B39" s="4">
@@ -3847,7 +3847,7 @@
       <c r="AD39" s="12"/>
     </row>
     <row r="40">
-      <c r="A40" s="13">
+      <c r="A40" s="14">
         <v>4.03</v>
       </c>
       <c r="B40" s="4">
@@ -3922,7 +3922,7 @@
       <c r="AD40" s="12"/>
     </row>
     <row r="41">
-      <c r="A41" s="13">
+      <c r="A41" s="14">
         <v>4.04</v>
       </c>
       <c r="B41" s="4">
@@ -3997,7 +3997,7 @@
       <c r="AD41" s="12"/>
     </row>
     <row r="42">
-      <c r="A42" s="13">
+      <c r="A42" s="14">
         <v>4.05</v>
       </c>
       <c r="B42" s="23">
@@ -4063,7 +4063,7 @@
       <c r="AD42" s="12"/>
     </row>
     <row r="43">
-      <c r="A43" s="13">
+      <c r="A43" s="14">
         <v>4.06</v>
       </c>
       <c r="B43" s="4">
@@ -4129,7 +4129,7 @@
       <c r="AD43" s="12"/>
     </row>
     <row r="44">
-      <c r="A44" s="13">
+      <c r="A44" s="14">
         <v>4.07</v>
       </c>
       <c r="B44" s="4">
@@ -4203,7 +4203,7 @@
       <c r="AD44" s="12"/>
     </row>
     <row r="45">
-      <c r="A45" s="13">
+      <c r="A45" s="14">
         <v>4.08</v>
       </c>
       <c r="B45" s="4">
@@ -4293,7 +4293,7 @@
       <c r="AD45" s="12"/>
     </row>
     <row r="46">
-      <c r="A46" s="13">
+      <c r="A46" s="14">
         <v>4.09</v>
       </c>
       <c r="B46" s="4">
@@ -4371,7 +4371,7 @@
       <c r="AD46" s="12"/>
     </row>
     <row r="47">
-      <c r="A47" s="13">
+      <c r="A47" s="14">
         <v>4.1</v>
       </c>
       <c r="B47" s="4">
@@ -4449,7 +4449,7 @@
       <c r="AD47" s="12"/>
     </row>
     <row r="48">
-      <c r="A48" s="13">
+      <c r="A48" s="14">
         <v>4.11</v>
       </c>
       <c r="B48" s="4">
@@ -4527,7 +4527,7 @@
       <c r="AD48" s="12"/>
     </row>
     <row r="49">
-      <c r="A49" s="13">
+      <c r="A49" s="14">
         <v>4.12</v>
       </c>
       <c r="B49" s="4">
@@ -4605,7 +4605,7 @@
       <c r="AD49" s="12"/>
     </row>
     <row r="50">
-      <c r="A50" s="13">
+      <c r="A50" s="14">
         <v>5.01</v>
       </c>
       <c r="B50" s="4">
@@ -4683,7 +4683,7 @@
       <c r="AD50" s="12"/>
     </row>
     <row r="51">
-      <c r="A51" s="13">
+      <c r="A51" s="14">
         <v>5.02</v>
       </c>
       <c r="B51" s="4">
@@ -4761,7 +4761,7 @@
       <c r="AD51" s="12"/>
     </row>
     <row r="52">
-      <c r="A52" s="13">
+      <c r="A52" s="14">
         <v>5.03</v>
       </c>
       <c r="B52" s="4">
@@ -4839,7 +4839,7 @@
       <c r="AD52" s="12"/>
     </row>
     <row r="53">
-      <c r="A53" s="13">
+      <c r="A53" s="14">
         <v>5.04</v>
       </c>
       <c r="B53" s="4">
@@ -4917,7 +4917,7 @@
       <c r="AD53" s="12"/>
     </row>
     <row r="54">
-      <c r="A54" s="13">
+      <c r="A54" s="14">
         <v>5.05</v>
       </c>
       <c r="B54" s="4">
@@ -4995,7 +4995,7 @@
       <c r="AD54" s="12"/>
     </row>
     <row r="55">
-      <c r="A55" s="13">
+      <c r="A55" s="14">
         <v>5.06</v>
       </c>
       <c r="B55" s="4">
@@ -5073,7 +5073,7 @@
       <c r="AD55" s="12"/>
     </row>
     <row r="56">
-      <c r="A56" s="13">
+      <c r="A56" s="14">
         <v>5.07</v>
       </c>
       <c r="B56" s="4">
@@ -5151,7 +5151,7 @@
       <c r="AD56" s="12"/>
     </row>
     <row r="57">
-      <c r="A57" s="13">
+      <c r="A57" s="14">
         <v>5.08</v>
       </c>
       <c r="B57" s="4">
@@ -5229,7 +5229,7 @@
       <c r="AD57" s="12"/>
     </row>
     <row r="58">
-      <c r="A58" s="13">
+      <c r="A58" s="14">
         <v>5.09</v>
       </c>
       <c r="B58" s="4">
@@ -5307,7 +5307,7 @@
       <c r="AD58" s="12"/>
     </row>
     <row r="59">
-      <c r="A59" s="13">
+      <c r="A59" s="14">
         <v>5.1</v>
       </c>
       <c r="B59" s="4">
@@ -5385,7 +5385,7 @@
       <c r="AD59" s="12"/>
     </row>
     <row r="60">
-      <c r="A60" s="13">
+      <c r="A60" s="14">
         <v>5.11</v>
       </c>
       <c r="B60" s="4">
@@ -5463,7 +5463,7 @@
       <c r="AD60" s="12"/>
     </row>
     <row r="61">
-      <c r="A61" s="13">
+      <c r="A61" s="14">
         <v>5.12</v>
       </c>
       <c r="B61" s="4">
@@ -5541,7 +5541,7 @@
       <c r="AD61" s="12"/>
     </row>
     <row r="62">
-      <c r="A62" s="13">
+      <c r="A62" s="14">
         <v>6.01</v>
       </c>
       <c r="B62" s="4">
@@ -5623,7 +5623,7 @@
       <c r="AD62" s="12"/>
     </row>
     <row r="63">
-      <c r="A63" s="13">
+      <c r="A63" s="14">
         <v>6.02</v>
       </c>
       <c r="B63" s="4">
@@ -5706,7 +5706,7 @@
       <c r="AD63" s="12"/>
     </row>
     <row r="64">
-      <c r="A64" s="13">
+      <c r="A64" s="14">
         <v>6.03</v>
       </c>
       <c r="B64" s="4">
@@ -5789,7 +5789,7 @@
       <c r="AD64" s="12"/>
     </row>
     <row r="65">
-      <c r="A65" s="13">
+      <c r="A65" s="14">
         <v>6.04</v>
       </c>
       <c r="B65" s="4">
@@ -5872,7 +5872,7 @@
       <c r="AD65" s="12"/>
     </row>
     <row r="66">
-      <c r="A66" s="13">
+      <c r="A66" s="14">
         <v>6.05</v>
       </c>
       <c r="B66" s="4">
@@ -5955,7 +5955,7 @@
       <c r="AD66" s="12"/>
     </row>
     <row r="67">
-      <c r="A67" s="13">
+      <c r="A67" s="14">
         <v>6.06</v>
       </c>
       <c r="B67" s="4">
@@ -6038,7 +6038,7 @@
       <c r="AD67" s="12"/>
     </row>
     <row r="68">
-      <c r="A68" s="13">
+      <c r="A68" s="14">
         <v>6.07</v>
       </c>
       <c r="B68" s="4">
@@ -6121,7 +6121,7 @@
       <c r="AD68" s="12"/>
     </row>
     <row r="69">
-      <c r="A69" s="13">
+      <c r="A69" s="14">
         <v>6.08</v>
       </c>
       <c r="B69" s="23">
@@ -6204,7 +6204,7 @@
       <c r="AD69" s="12"/>
     </row>
     <row r="70">
-      <c r="A70" s="13">
+      <c r="A70" s="14">
         <v>6.09</v>
       </c>
       <c r="B70" s="4">
@@ -6287,7 +6287,7 @@
       <c r="AD70" s="12"/>
     </row>
     <row r="71">
-      <c r="A71" s="13">
+      <c r="A71" s="14">
         <v>6.1</v>
       </c>
       <c r="B71" s="4">
@@ -6370,7 +6370,7 @@
       <c r="AD71" s="12"/>
     </row>
     <row r="72">
-      <c r="A72" s="13">
+      <c r="A72" s="14">
         <v>6.11</v>
       </c>
       <c r="B72" s="23">
@@ -6453,7 +6453,7 @@
       <c r="AD72" s="12"/>
     </row>
     <row r="73">
-      <c r="A73" s="13">
+      <c r="A73" s="14">
         <v>6.12</v>
       </c>
       <c r="B73" s="4">
@@ -9535,7 +9535,7 @@
         <v>9.0</v>
       </c>
       <c r="X147" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Y147" s="7" t="s">
         <v>141</v>
@@ -9575,7 +9575,7 @@
         <v>10.0</v>
       </c>
       <c r="X148" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Y148" s="7" t="s">
         <v>145</v>
@@ -9655,7 +9655,7 @@
         <v>12.0</v>
       </c>
       <c r="X150" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y150" s="7" t="s">
         <v>146</v>
@@ -9775,7 +9775,7 @@
         <v>15.0</v>
       </c>
       <c r="X153" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Y153" s="7" t="s">
         <v>141</v>
@@ -9855,7 +9855,7 @@
         <v>17.0</v>
       </c>
       <c r="X155" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Y155" s="7" t="s">
         <v>140</v>
@@ -9895,7 +9895,7 @@
         <v>18.0</v>
       </c>
       <c r="X156" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y156" s="7" t="s">
         <v>145</v>
@@ -9975,7 +9975,7 @@
         <v>20.0</v>
       </c>
       <c r="X158" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y158" s="7" t="s">
         <v>140</v>
@@ -10095,7 +10095,7 @@
         <v>23.0</v>
       </c>
       <c r="X161" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Y161" s="7" t="s">
         <v>142</v>
@@ -10135,7 +10135,7 @@
         <v>24.0</v>
       </c>
       <c r="X162" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Y162" s="7" t="s">
         <v>141</v>
@@ -10175,7 +10175,7 @@
         <v>25.0</v>
       </c>
       <c r="X163" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Y163" s="7" t="s">
         <v>140</v>
@@ -10215,7 +10215,7 @@
         <v>26.0</v>
       </c>
       <c r="X164" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y164" s="7" t="s">
         <v>140</v>
@@ -10335,7 +10335,7 @@
         <v>29.0</v>
       </c>
       <c r="X167" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Y167" s="7" t="s">
         <v>143</v>
@@ -10375,7 +10375,7 @@
         <v>30.0</v>
       </c>
       <c r="X168" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Y168" s="7" t="s">
         <v>141</v>
@@ -10415,7 +10415,7 @@
         <v>31.0</v>
       </c>
       <c r="X169" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y169" s="7" t="s">
         <v>141</v>
@@ -10495,7 +10495,7 @@
         <v>33.0</v>
       </c>
       <c r="X171" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y171" s="7" t="s">
         <v>141</v>
@@ -10695,7 +10695,7 @@
         <v>38.0</v>
       </c>
       <c r="X176" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Y176" s="7" t="s">
         <v>141</v>
@@ -10735,7 +10735,7 @@
         <v>39.0</v>
       </c>
       <c r="X177" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Y177" s="7" t="s">
         <v>144</v>
@@ -10815,7 +10815,7 @@
         <v>41.0</v>
       </c>
       <c r="X179" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Y179" s="7" t="s">
         <v>141</v>
@@ -10855,7 +10855,7 @@
         <v>42.0</v>
       </c>
       <c r="X180" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Y180" s="7" t="s">
         <v>140</v>
@@ -37497,7 +37497,7 @@
         <f t="shared" ref="G2:G73" si="2">IF($D2&gt;0,"",MIN($L$8, $C2*$L$14*(1+($L$11-1)*$L$16)))</f>
         <v>150.7741176</v>
       </c>
-      <c r="H2" s="14">
+      <c r="H2" s="13">
         <f t="shared" ref="H2:H73" si="3">IF($D2&lt;&gt;"","",
    IFERROR(
      MIN($L$8, $C2*$L$14*$L$27),
@@ -37551,7 +37551,7 @@
         <f t="shared" si="2"/>
         <v>115.5211765</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="13">
         <f t="shared" si="3"/>
         <v>85.2</v>
       </c>
@@ -37593,7 +37593,7 @@
         <f t="shared" si="2"/>
         <v>100.8776471</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <f t="shared" si="3"/>
         <v>74.4</v>
       </c>
@@ -37630,7 +37630,7 @@
         <f t="shared" si="2"/>
         <v>89.48823529</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <f t="shared" si="3"/>
         <v>66</v>
       </c>
@@ -37668,7 +37668,7 @@
         <f t="shared" si="2"/>
         <v>82.43764706</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <f t="shared" si="3"/>
         <v>60.8</v>
       </c>
@@ -37706,7 +37706,7 @@
         <f t="shared" si="2"/>
         <v>72.13294118</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="13">
         <f t="shared" si="3"/>
         <v>53.2</v>
       </c>
@@ -37743,7 +37743,7 @@
         <f t="shared" si="2"/>
         <v>62.37058824</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="13">
         <f t="shared" si="3"/>
         <v>46</v>
       </c>
@@ -37752,7 +37752,7 @@
         <v/>
       </c>
       <c r="K8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L8" s="9">
         <f>L4-L7
@@ -37765,7 +37765,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9" s="9">
         <v>53.0</v>
@@ -37781,7 +37781,7 @@
         <f t="shared" si="2"/>
         <v>57.48941176</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="13">
         <f t="shared" si="3"/>
         <v>42.4</v>
       </c>
@@ -37790,7 +37790,7 @@
         <v/>
       </c>
       <c r="K9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L9" s="9">
         <f>L6-L8
@@ -37803,7 +37803,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" s="9">
         <v>48.0</v>
@@ -37819,7 +37819,7 @@
         <f t="shared" si="2"/>
         <v>52.06588235</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="13">
         <f t="shared" si="3"/>
         <v>38.4</v>
       </c>
@@ -37828,7 +37828,7 @@
         <v/>
       </c>
       <c r="K10" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L10" s="9">
         <f>IF(L3&gt;1,L9/(L3-1),0)</f>
@@ -37856,7 +37856,7 @@
         <f t="shared" si="2"/>
         <v>46.64235294</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="13">
         <f t="shared" si="3"/>
         <v>34.4</v>
       </c>
@@ -37893,7 +37893,7 @@
         <f t="shared" si="2"/>
         <v>42.30352941</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="13">
         <f t="shared" si="3"/>
         <v>31.2</v>
       </c>
@@ -37923,7 +37923,7 @@
         <f t="shared" si="2"/>
         <v>36.88</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="13">
         <f t="shared" si="3"/>
         <v>27.2</v>
       </c>
@@ -37960,7 +37960,7 @@
         <f t="shared" si="2"/>
         <v>33.08352941</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="13">
         <f t="shared" si="3"/>
         <v>24.4</v>
       </c>
@@ -37981,7 +37981,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" s="9">
         <v>27.5</v>
@@ -37997,7 +37997,7 @@
         <f t="shared" si="2"/>
         <v>29.82941176</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="13">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -38011,7 +38011,7 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" s="9">
         <v>25.5</v>
@@ -38027,7 +38027,7 @@
         <f t="shared" si="2"/>
         <v>27.66</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="13">
         <f t="shared" si="3"/>
         <v>20.4</v>
       </c>
@@ -38058,7 +38058,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C17" s="9">
         <v>22.5</v>
@@ -38074,7 +38074,7 @@
         <f t="shared" si="2"/>
         <v>24.40588235</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="13">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
@@ -38088,7 +38088,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="9">
         <v>20.0</v>
@@ -38104,7 +38104,7 @@
         <f t="shared" si="2"/>
         <v>21.69411765</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="13">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
@@ -38141,7 +38141,7 @@
         <f t="shared" si="2"/>
         <v>20.06705882</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="13">
         <f t="shared" si="3"/>
         <v>14.8</v>
       </c>
@@ -38155,7 +38155,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C20" s="9">
         <v>16.5</v>
@@ -38171,7 +38171,7 @@
         <f t="shared" si="2"/>
         <v>17.89764706</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="13">
         <f t="shared" si="3"/>
         <v>13.2</v>
       </c>
@@ -38185,7 +38185,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C21" s="9">
         <v>14.5</v>
@@ -38201,7 +38201,7 @@
         <f t="shared" si="2"/>
         <v>15.72823529</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="13">
         <f t="shared" si="3"/>
         <v>11.6</v>
       </c>
@@ -38215,7 +38215,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C22" s="9">
         <v>13.5</v>
@@ -38231,7 +38231,7 @@
         <f t="shared" si="2"/>
         <v>14.64352941</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="13">
         <f t="shared" si="3"/>
         <v>10.8</v>
       </c>
@@ -38245,7 +38245,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C23" s="9">
         <v>12.0</v>
@@ -38261,7 +38261,7 @@
         <f t="shared" si="2"/>
         <v>13.01647059</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="13">
         <f t="shared" si="3"/>
         <v>9.6</v>
       </c>
@@ -38275,7 +38275,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C24" s="9">
         <v>11.0</v>
@@ -38291,7 +38291,7 @@
         <f t="shared" si="2"/>
         <v>11.93176471</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="13">
         <f t="shared" si="3"/>
         <v>8.8</v>
       </c>
@@ -38305,7 +38305,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C25" s="9">
         <v>10.0</v>
@@ -38321,7 +38321,7 @@
         <f t="shared" si="2"/>
         <v>10.84705882</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="13">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
@@ -38335,7 +38335,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C26" s="9">
         <v>9.5</v>
@@ -38351,7 +38351,7 @@
         <f t="shared" si="2"/>
         <v>10.30470588</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H26" s="13">
         <f t="shared" si="3"/>
         <v>7.6</v>
       </c>
@@ -38365,7 +38365,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C27" s="9">
         <v>8.5</v>
@@ -38381,7 +38381,7 @@
         <f t="shared" si="2"/>
         <v>9.22</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="13">
         <f t="shared" si="3"/>
         <v>6.8</v>
       </c>
@@ -38390,7 +38390,7 @@
         <v/>
       </c>
       <c r="K27" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L27" s="1">
         <v>0.8</v>
@@ -38401,7 +38401,7 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C28" s="9">
         <v>8.0</v>
@@ -38417,7 +38417,7 @@
         <f t="shared" si="2"/>
         <v>8.677647059</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="13">
         <f t="shared" si="3"/>
         <v>6.4</v>
       </c>
@@ -38431,7 +38431,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C29" s="9">
         <v>7.0</v>
@@ -38447,7 +38447,7 @@
         <f t="shared" si="2"/>
         <v>7.592941176</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H29" s="13">
         <f t="shared" si="3"/>
         <v>5.6</v>
       </c>
@@ -38461,7 +38461,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C30" s="9">
         <v>6.5</v>
@@ -38477,7 +38477,7 @@
         <f t="shared" si="2"/>
         <v>7.050588235</v>
       </c>
-      <c r="H30" s="14">
+      <c r="H30" s="13">
         <f t="shared" si="3"/>
         <v>5.2</v>
       </c>
@@ -38491,7 +38491,7 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C31" s="9">
         <v>6.0</v>
@@ -38507,7 +38507,7 @@
         <f t="shared" si="2"/>
         <v>6.508235294</v>
       </c>
-      <c r="H31" s="14">
+      <c r="H31" s="13">
         <f t="shared" si="3"/>
         <v>4.8</v>
       </c>
@@ -38521,7 +38521,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C32" s="9">
         <v>5.5</v>
@@ -38537,7 +38537,7 @@
         <f t="shared" si="2"/>
         <v>5.965882353</v>
       </c>
-      <c r="H32" s="14">
+      <c r="H32" s="13">
         <f t="shared" si="3"/>
         <v>4.4</v>
       </c>
@@ -38551,7 +38551,7 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C33" s="9">
         <v>5.0</v>
@@ -38567,7 +38567,7 @@
         <f t="shared" si="2"/>
         <v>5.423529412</v>
       </c>
-      <c r="H33" s="14">
+      <c r="H33" s="13">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
@@ -38581,7 +38581,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C34" s="9">
         <v>4.5</v>
@@ -38597,7 +38597,7 @@
         <f t="shared" si="2"/>
         <v>4.881176471</v>
       </c>
-      <c r="H34" s="14">
+      <c r="H34" s="13">
         <f t="shared" si="3"/>
         <v>3.6</v>
       </c>
@@ -38611,7 +38611,7 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C35" s="9">
         <v>4.5</v>
@@ -38627,7 +38627,7 @@
         <f t="shared" si="2"/>
         <v>4.881176471</v>
       </c>
-      <c r="H35" s="14">
+      <c r="H35" s="13">
         <f t="shared" si="3"/>
         <v>3.6</v>
       </c>
@@ -38641,7 +38641,7 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C36" s="9">
         <v>4.0</v>
@@ -38657,7 +38657,7 @@
         <f t="shared" si="2"/>
         <v>4.338823529</v>
       </c>
-      <c r="H36" s="14">
+      <c r="H36" s="13">
         <f t="shared" si="3"/>
         <v>3.2</v>
       </c>
@@ -38687,7 +38687,7 @@
         <f t="shared" si="2"/>
         <v>4.338823529</v>
       </c>
-      <c r="H37" s="14">
+      <c r="H37" s="13">
         <f t="shared" si="3"/>
         <v>3.2</v>
       </c>
@@ -38717,7 +38717,7 @@
         <f t="shared" si="2"/>
         <v>3.796470588</v>
       </c>
-      <c r="H38" s="14">
+      <c r="H38" s="13">
         <f t="shared" si="3"/>
         <v>2.8</v>
       </c>
@@ -38747,7 +38747,7 @@
         <f t="shared" si="2"/>
         <v>3.796470588</v>
       </c>
-      <c r="H39" s="14">
+      <c r="H39" s="13">
         <f t="shared" si="3"/>
         <v>2.8</v>
       </c>
@@ -38777,7 +38777,7 @@
         <f t="shared" si="2"/>
         <v>3.254117647</v>
       </c>
-      <c r="H40" s="14">
+      <c r="H40" s="13">
         <f t="shared" si="3"/>
         <v>2.4</v>
       </c>
@@ -38807,7 +38807,7 @@
         <f t="shared" si="2"/>
         <v>3.254117647</v>
       </c>
-      <c r="H41" s="14">
+      <c r="H41" s="13">
         <f t="shared" si="3"/>
         <v>2.4</v>
       </c>
@@ -38837,7 +38837,7 @@
         <f t="shared" si="2"/>
         <v>2.711764706</v>
       </c>
-      <c r="H42" s="14">
+      <c r="H42" s="13">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
@@ -38867,7 +38867,7 @@
         <f t="shared" si="2"/>
         <v>2.711764706</v>
       </c>
-      <c r="H43" s="14">
+      <c r="H43" s="13">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
@@ -38897,7 +38897,7 @@
         <f t="shared" si="2"/>
         <v>2.711764706</v>
       </c>
-      <c r="H44" s="14">
+      <c r="H44" s="13">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
@@ -38927,7 +38927,7 @@
         <f t="shared" si="2"/>
         <v>2.711764706</v>
       </c>
-      <c r="H45" s="14">
+      <c r="H45" s="13">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
@@ -38957,7 +38957,7 @@
         <f t="shared" si="2"/>
         <v>2.169411765</v>
       </c>
-      <c r="H46" s="14">
+      <c r="H46" s="13">
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
@@ -38987,7 +38987,7 @@
         <f t="shared" si="2"/>
         <v>2.169411765</v>
       </c>
-      <c r="H47" s="14">
+      <c r="H47" s="13">
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
@@ -39017,7 +39017,7 @@
         <f t="shared" si="2"/>
         <v>2.169411765</v>
       </c>
-      <c r="H48" s="14">
+      <c r="H48" s="13">
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
@@ -39047,7 +39047,7 @@
         <f t="shared" si="2"/>
         <v>2.169411765</v>
       </c>
-      <c r="H49" s="14">
+      <c r="H49" s="13">
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
@@ -39077,7 +39077,7 @@
         <f t="shared" si="2"/>
         <v>2.169411765</v>
       </c>
-      <c r="H50" s="14">
+      <c r="H50" s="13">
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
@@ -39107,7 +39107,7 @@
         <f t="shared" si="2"/>
         <v>2.169411765</v>
       </c>
-      <c r="H51" s="14">
+      <c r="H51" s="13">
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
@@ -39137,7 +39137,7 @@
         <f t="shared" si="2"/>
         <v>2.169411765</v>
       </c>
-      <c r="H52" s="14">
+      <c r="H52" s="13">
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
@@ -39167,7 +39167,7 @@
         <f t="shared" si="2"/>
         <v>2.169411765</v>
       </c>
-      <c r="H53" s="14">
+      <c r="H53" s="13">
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
@@ -39197,7 +39197,7 @@
         <f t="shared" si="2"/>
         <v>2.169411765</v>
       </c>
-      <c r="H54" s="14">
+      <c r="H54" s="13">
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
@@ -39227,7 +39227,7 @@
         <f t="shared" si="2"/>
         <v>2.169411765</v>
       </c>
-      <c r="H55" s="14">
+      <c r="H55" s="13">
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
@@ -39257,7 +39257,7 @@
         <f t="shared" si="2"/>
         <v>2.169411765</v>
       </c>
-      <c r="H56" s="14">
+      <c r="H56" s="13">
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
@@ -39287,7 +39287,7 @@
         <f t="shared" si="2"/>
         <v>2.169411765</v>
       </c>
-      <c r="H57" s="14">
+      <c r="H57" s="13">
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
@@ -39317,7 +39317,7 @@
         <f t="shared" si="2"/>
         <v>2.169411765</v>
       </c>
-      <c r="H58" s="14">
+      <c r="H58" s="13">
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
@@ -39347,7 +39347,7 @@
         <f t="shared" si="2"/>
         <v>2.169411765</v>
       </c>
-      <c r="H59" s="14">
+      <c r="H59" s="13">
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
@@ -39377,7 +39377,7 @@
         <f t="shared" si="2"/>
         <v>2.169411765</v>
       </c>
-      <c r="H60" s="14">
+      <c r="H60" s="13">
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
@@ -39407,7 +39407,7 @@
         <f t="shared" si="2"/>
         <v>2.169411765</v>
       </c>
-      <c r="H61" s="14">
+      <c r="H61" s="13">
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
@@ -39437,7 +39437,7 @@
         <f t="shared" si="2"/>
         <v>1.084705882</v>
       </c>
-      <c r="H62" s="14">
+      <c r="H62" s="13">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
@@ -39467,7 +39467,7 @@
         <f t="shared" si="2"/>
         <v>1.084705882</v>
       </c>
-      <c r="H63" s="14">
+      <c r="H63" s="13">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
@@ -39497,7 +39497,7 @@
         <f t="shared" si="2"/>
         <v>1.084705882</v>
       </c>
-      <c r="H64" s="14">
+      <c r="H64" s="13">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
@@ -39527,7 +39527,7 @@
         <f t="shared" si="2"/>
         <v>1.084705882</v>
       </c>
-      <c r="H65" s="14">
+      <c r="H65" s="13">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
@@ -39557,7 +39557,7 @@
         <f t="shared" si="2"/>
         <v>1.084705882</v>
       </c>
-      <c r="H66" s="14">
+      <c r="H66" s="13">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
@@ -39587,7 +39587,7 @@
         <f t="shared" si="2"/>
         <v>1.084705882</v>
       </c>
-      <c r="H67" s="14">
+      <c r="H67" s="13">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
@@ -39617,7 +39617,7 @@
         <f t="shared" si="2"/>
         <v>1.084705882</v>
       </c>
-      <c r="H68" s="14">
+      <c r="H68" s="13">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
@@ -39647,7 +39647,7 @@
         <f t="shared" si="2"/>
         <v>1.084705882</v>
       </c>
-      <c r="H69" s="14">
+      <c r="H69" s="13">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
@@ -39677,7 +39677,7 @@
         <f t="shared" si="2"/>
         <v>1.084705882</v>
       </c>
-      <c r="H70" s="14">
+      <c r="H70" s="13">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
@@ -39707,7 +39707,7 @@
         <f t="shared" si="2"/>
         <v>1.084705882</v>
       </c>
-      <c r="H71" s="14">
+      <c r="H71" s="13">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
@@ -39737,7 +39737,7 @@
         <f t="shared" si="2"/>
         <v>1.084705882</v>
       </c>
-      <c r="H72" s="14">
+      <c r="H72" s="13">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
@@ -39767,7 +39767,7 @@
         <f t="shared" si="2"/>
         <v>1.084705882</v>
       </c>
-      <c r="H73" s="14">
+      <c r="H73" s="13">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
@@ -39782,6496 +39782,6496 @@
       </c>
       <c r="F74" s="9"/>
       <c r="G74" s="9"/>
-      <c r="H74" s="14"/>
+      <c r="H74" s="13"/>
       <c r="I74" s="21"/>
     </row>
     <row r="75">
       <c r="C75" s="22"/>
       <c r="F75" s="9"/>
       <c r="G75" s="9"/>
-      <c r="H75" s="14"/>
+      <c r="H75" s="13"/>
       <c r="I75" s="21"/>
     </row>
     <row r="76">
       <c r="C76" s="22"/>
       <c r="F76" s="9"/>
       <c r="G76" s="9"/>
-      <c r="H76" s="14"/>
+      <c r="H76" s="13"/>
       <c r="I76" s="21"/>
     </row>
     <row r="77">
       <c r="C77" s="22"/>
       <c r="F77" s="9"/>
       <c r="G77" s="9"/>
-      <c r="H77" s="14"/>
+      <c r="H77" s="13"/>
       <c r="I77" s="21"/>
     </row>
     <row r="78">
       <c r="C78" s="22"/>
       <c r="F78" s="9"/>
       <c r="G78" s="9"/>
-      <c r="H78" s="14"/>
+      <c r="H78" s="13"/>
       <c r="I78" s="21"/>
     </row>
     <row r="79">
       <c r="C79" s="22"/>
       <c r="F79" s="9"/>
       <c r="G79" s="9"/>
-      <c r="H79" s="14"/>
+      <c r="H79" s="13"/>
       <c r="I79" s="21"/>
     </row>
     <row r="80">
       <c r="C80" s="22"/>
       <c r="F80" s="9"/>
       <c r="G80" s="9"/>
-      <c r="H80" s="14"/>
+      <c r="H80" s="13"/>
       <c r="I80" s="21"/>
     </row>
     <row r="81">
       <c r="C81" s="22"/>
       <c r="F81" s="9"/>
       <c r="G81" s="9"/>
-      <c r="H81" s="14"/>
+      <c r="H81" s="13"/>
       <c r="I81" s="21"/>
     </row>
     <row r="82">
       <c r="C82" s="22"/>
       <c r="F82" s="9"/>
       <c r="G82" s="9"/>
-      <c r="H82" s="14"/>
+      <c r="H82" s="13"/>
       <c r="I82" s="21"/>
     </row>
     <row r="83">
       <c r="C83" s="22"/>
       <c r="F83" s="9"/>
       <c r="G83" s="9"/>
-      <c r="H83" s="14"/>
+      <c r="H83" s="13"/>
       <c r="I83" s="21"/>
     </row>
     <row r="84">
       <c r="C84" s="22"/>
       <c r="F84" s="9"/>
       <c r="G84" s="9"/>
-      <c r="H84" s="14"/>
+      <c r="H84" s="13"/>
       <c r="I84" s="21"/>
     </row>
     <row r="85">
       <c r="C85" s="22"/>
       <c r="F85" s="9"/>
       <c r="G85" s="9"/>
-      <c r="H85" s="14"/>
+      <c r="H85" s="13"/>
       <c r="I85" s="21"/>
     </row>
     <row r="86">
       <c r="C86" s="22"/>
       <c r="F86" s="9"/>
       <c r="G86" s="9"/>
-      <c r="H86" s="14"/>
+      <c r="H86" s="13"/>
       <c r="I86" s="21"/>
     </row>
     <row r="87">
       <c r="C87" s="22"/>
       <c r="F87" s="9"/>
       <c r="G87" s="9"/>
-      <c r="H87" s="14"/>
+      <c r="H87" s="13"/>
       <c r="I87" s="21"/>
     </row>
     <row r="88">
       <c r="C88" s="22"/>
       <c r="F88" s="9"/>
       <c r="G88" s="9"/>
-      <c r="H88" s="14"/>
+      <c r="H88" s="13"/>
       <c r="I88" s="21"/>
     </row>
     <row r="89">
       <c r="C89" s="22"/>
       <c r="F89" s="9"/>
       <c r="G89" s="9"/>
-      <c r="H89" s="14"/>
+      <c r="H89" s="13"/>
       <c r="I89" s="21"/>
     </row>
     <row r="90">
       <c r="C90" s="22"/>
       <c r="F90" s="9"/>
       <c r="G90" s="9"/>
-      <c r="H90" s="14"/>
+      <c r="H90" s="13"/>
       <c r="I90" s="21"/>
     </row>
     <row r="91">
       <c r="C91" s="22"/>
       <c r="F91" s="9"/>
       <c r="G91" s="9"/>
-      <c r="H91" s="14"/>
+      <c r="H91" s="13"/>
       <c r="I91" s="21"/>
     </row>
     <row r="92">
       <c r="C92" s="22"/>
       <c r="F92" s="9"/>
       <c r="G92" s="9"/>
-      <c r="H92" s="14"/>
+      <c r="H92" s="13"/>
       <c r="I92" s="21"/>
     </row>
     <row r="93">
       <c r="C93" s="22"/>
       <c r="F93" s="9"/>
       <c r="G93" s="9"/>
-      <c r="H93" s="14"/>
+      <c r="H93" s="13"/>
       <c r="I93" s="21"/>
     </row>
     <row r="94">
       <c r="C94" s="22"/>
       <c r="F94" s="9"/>
       <c r="G94" s="9"/>
-      <c r="H94" s="14"/>
+      <c r="H94" s="13"/>
       <c r="I94" s="21"/>
     </row>
     <row r="95">
       <c r="C95" s="22"/>
       <c r="F95" s="9"/>
       <c r="G95" s="9"/>
-      <c r="H95" s="14"/>
+      <c r="H95" s="13"/>
       <c r="I95" s="21"/>
     </row>
     <row r="96">
       <c r="C96" s="22"/>
       <c r="F96" s="9"/>
       <c r="G96" s="9"/>
-      <c r="H96" s="14"/>
+      <c r="H96" s="13"/>
       <c r="I96" s="21"/>
     </row>
     <row r="97">
       <c r="C97" s="22"/>
       <c r="F97" s="9"/>
       <c r="G97" s="9"/>
-      <c r="H97" s="14"/>
+      <c r="H97" s="13"/>
       <c r="I97" s="21"/>
     </row>
     <row r="98">
       <c r="C98" s="22"/>
       <c r="F98" s="9"/>
       <c r="G98" s="9"/>
-      <c r="H98" s="14"/>
+      <c r="H98" s="13"/>
       <c r="I98" s="21"/>
     </row>
     <row r="99">
       <c r="C99" s="22"/>
       <c r="F99" s="9"/>
       <c r="G99" s="9"/>
-      <c r="H99" s="14"/>
+      <c r="H99" s="13"/>
       <c r="I99" s="21"/>
     </row>
     <row r="100">
       <c r="C100" s="22"/>
       <c r="F100" s="9"/>
       <c r="G100" s="9"/>
-      <c r="H100" s="14"/>
+      <c r="H100" s="13"/>
       <c r="I100" s="21"/>
     </row>
     <row r="101">
       <c r="C101" s="22"/>
       <c r="F101" s="9"/>
       <c r="G101" s="9"/>
-      <c r="H101" s="14"/>
+      <c r="H101" s="13"/>
       <c r="I101" s="21"/>
     </row>
     <row r="102">
       <c r="C102" s="22"/>
       <c r="F102" s="9"/>
       <c r="G102" s="9"/>
-      <c r="H102" s="14"/>
+      <c r="H102" s="13"/>
       <c r="I102" s="21"/>
     </row>
     <row r="103">
       <c r="C103" s="22"/>
       <c r="F103" s="9"/>
       <c r="G103" s="9"/>
-      <c r="H103" s="14"/>
+      <c r="H103" s="13"/>
       <c r="I103" s="21"/>
     </row>
     <row r="104">
       <c r="C104" s="22"/>
       <c r="F104" s="9"/>
       <c r="G104" s="9"/>
-      <c r="H104" s="14"/>
+      <c r="H104" s="13"/>
       <c r="I104" s="21"/>
     </row>
     <row r="105">
       <c r="C105" s="22"/>
       <c r="F105" s="9"/>
       <c r="G105" s="9"/>
-      <c r="H105" s="14"/>
+      <c r="H105" s="13"/>
       <c r="I105" s="21"/>
     </row>
     <row r="106">
       <c r="C106" s="22"/>
       <c r="F106" s="9"/>
       <c r="G106" s="9"/>
-      <c r="H106" s="14"/>
+      <c r="H106" s="13"/>
       <c r="I106" s="21"/>
     </row>
     <row r="107">
       <c r="C107" s="22"/>
       <c r="F107" s="9"/>
       <c r="G107" s="9"/>
-      <c r="H107" s="14"/>
+      <c r="H107" s="13"/>
       <c r="I107" s="21"/>
     </row>
     <row r="108">
       <c r="C108" s="22"/>
       <c r="F108" s="9"/>
       <c r="G108" s="9"/>
-      <c r="H108" s="14"/>
+      <c r="H108" s="13"/>
       <c r="I108" s="21"/>
     </row>
     <row r="109">
       <c r="C109" s="22"/>
       <c r="F109" s="9"/>
       <c r="G109" s="9"/>
-      <c r="H109" s="14"/>
+      <c r="H109" s="13"/>
       <c r="I109" s="21"/>
     </row>
     <row r="110">
       <c r="C110" s="22"/>
       <c r="F110" s="9"/>
       <c r="G110" s="9"/>
-      <c r="H110" s="14"/>
+      <c r="H110" s="13"/>
       <c r="I110" s="21"/>
     </row>
     <row r="111">
       <c r="C111" s="22"/>
       <c r="F111" s="9"/>
       <c r="G111" s="9"/>
-      <c r="H111" s="14"/>
+      <c r="H111" s="13"/>
       <c r="I111" s="21"/>
     </row>
     <row r="112">
       <c r="C112" s="22"/>
       <c r="F112" s="9"/>
       <c r="G112" s="9"/>
-      <c r="H112" s="14"/>
+      <c r="H112" s="13"/>
       <c r="I112" s="21"/>
     </row>
     <row r="113">
       <c r="C113" s="22"/>
       <c r="F113" s="9"/>
       <c r="G113" s="9"/>
-      <c r="H113" s="14"/>
+      <c r="H113" s="13"/>
       <c r="I113" s="21"/>
     </row>
     <row r="114">
       <c r="C114" s="22"/>
       <c r="F114" s="9"/>
       <c r="G114" s="9"/>
-      <c r="H114" s="14"/>
+      <c r="H114" s="13"/>
       <c r="I114" s="21"/>
     </row>
     <row r="115">
       <c r="C115" s="22"/>
       <c r="F115" s="9"/>
       <c r="G115" s="9"/>
-      <c r="H115" s="14"/>
+      <c r="H115" s="13"/>
       <c r="I115" s="21"/>
     </row>
     <row r="116">
       <c r="C116" s="22"/>
       <c r="F116" s="9"/>
       <c r="G116" s="9"/>
-      <c r="H116" s="14"/>
+      <c r="H116" s="13"/>
       <c r="I116" s="21"/>
     </row>
     <row r="117">
       <c r="C117" s="22"/>
       <c r="F117" s="9"/>
       <c r="G117" s="9"/>
-      <c r="H117" s="14"/>
+      <c r="H117" s="13"/>
       <c r="I117" s="21"/>
     </row>
     <row r="118">
       <c r="C118" s="22"/>
       <c r="F118" s="9"/>
       <c r="G118" s="9"/>
-      <c r="H118" s="14"/>
+      <c r="H118" s="13"/>
       <c r="I118" s="21"/>
     </row>
     <row r="119">
       <c r="C119" s="22"/>
       <c r="F119" s="9"/>
       <c r="G119" s="9"/>
-      <c r="H119" s="14"/>
+      <c r="H119" s="13"/>
       <c r="I119" s="21"/>
     </row>
     <row r="120">
       <c r="C120" s="22"/>
       <c r="F120" s="9"/>
       <c r="G120" s="9"/>
-      <c r="H120" s="14"/>
+      <c r="H120" s="13"/>
       <c r="I120" s="21"/>
     </row>
     <row r="121">
       <c r="C121" s="22"/>
       <c r="F121" s="9"/>
       <c r="G121" s="9"/>
-      <c r="H121" s="14"/>
+      <c r="H121" s="13"/>
       <c r="I121" s="21"/>
     </row>
     <row r="122">
       <c r="C122" s="22"/>
       <c r="F122" s="9"/>
       <c r="G122" s="9"/>
-      <c r="H122" s="14"/>
+      <c r="H122" s="13"/>
       <c r="I122" s="21"/>
     </row>
     <row r="123">
       <c r="C123" s="22"/>
       <c r="F123" s="9"/>
       <c r="G123" s="9"/>
-      <c r="H123" s="14"/>
+      <c r="H123" s="13"/>
       <c r="I123" s="21"/>
     </row>
     <row r="124">
       <c r="C124" s="22"/>
       <c r="F124" s="9"/>
       <c r="G124" s="9"/>
-      <c r="H124" s="14"/>
+      <c r="H124" s="13"/>
       <c r="I124" s="21"/>
     </row>
     <row r="125">
       <c r="C125" s="22"/>
       <c r="F125" s="9"/>
       <c r="G125" s="9"/>
-      <c r="H125" s="14"/>
+      <c r="H125" s="13"/>
       <c r="I125" s="21"/>
     </row>
     <row r="126">
       <c r="C126" s="22"/>
       <c r="F126" s="9"/>
       <c r="G126" s="9"/>
-      <c r="H126" s="14"/>
+      <c r="H126" s="13"/>
       <c r="I126" s="21"/>
     </row>
     <row r="127">
       <c r="C127" s="22"/>
       <c r="F127" s="9"/>
       <c r="G127" s="9"/>
-      <c r="H127" s="14"/>
+      <c r="H127" s="13"/>
       <c r="I127" s="21"/>
     </row>
     <row r="128">
       <c r="C128" s="22"/>
       <c r="F128" s="9"/>
       <c r="G128" s="9"/>
-      <c r="H128" s="14"/>
+      <c r="H128" s="13"/>
       <c r="I128" s="21"/>
     </row>
     <row r="129">
       <c r="C129" s="22"/>
       <c r="F129" s="9"/>
       <c r="G129" s="9"/>
-      <c r="H129" s="14"/>
+      <c r="H129" s="13"/>
       <c r="I129" s="21"/>
     </row>
     <row r="130">
       <c r="C130" s="22"/>
       <c r="F130" s="9"/>
       <c r="G130" s="9"/>
-      <c r="H130" s="14"/>
+      <c r="H130" s="13"/>
       <c r="I130" s="21"/>
     </row>
     <row r="131">
       <c r="C131" s="22"/>
       <c r="F131" s="9"/>
       <c r="G131" s="9"/>
-      <c r="H131" s="14"/>
+      <c r="H131" s="13"/>
       <c r="I131" s="21"/>
     </row>
     <row r="132">
       <c r="C132" s="22"/>
       <c r="F132" s="9"/>
       <c r="G132" s="9"/>
-      <c r="H132" s="14"/>
+      <c r="H132" s="13"/>
       <c r="I132" s="21"/>
     </row>
     <row r="133">
       <c r="C133" s="22"/>
       <c r="F133" s="9"/>
       <c r="G133" s="9"/>
-      <c r="H133" s="14"/>
+      <c r="H133" s="13"/>
       <c r="I133" s="21"/>
     </row>
     <row r="134">
       <c r="C134" s="22"/>
       <c r="F134" s="9"/>
       <c r="G134" s="9"/>
-      <c r="H134" s="14"/>
+      <c r="H134" s="13"/>
       <c r="I134" s="21"/>
     </row>
     <row r="135">
       <c r="C135" s="22"/>
       <c r="F135" s="9"/>
       <c r="G135" s="9"/>
-      <c r="H135" s="14"/>
+      <c r="H135" s="13"/>
       <c r="I135" s="21"/>
     </row>
     <row r="136">
       <c r="C136" s="22"/>
       <c r="F136" s="9"/>
       <c r="G136" s="9"/>
-      <c r="H136" s="14"/>
+      <c r="H136" s="13"/>
       <c r="I136" s="21"/>
     </row>
     <row r="137">
       <c r="C137" s="22"/>
       <c r="F137" s="9"/>
       <c r="G137" s="9"/>
-      <c r="H137" s="14"/>
+      <c r="H137" s="13"/>
       <c r="I137" s="21"/>
     </row>
     <row r="138">
       <c r="C138" s="22"/>
       <c r="F138" s="9"/>
       <c r="G138" s="9"/>
-      <c r="H138" s="14"/>
+      <c r="H138" s="13"/>
       <c r="I138" s="21"/>
     </row>
     <row r="139">
       <c r="C139" s="22"/>
       <c r="F139" s="9"/>
       <c r="G139" s="9"/>
-      <c r="H139" s="14"/>
+      <c r="H139" s="13"/>
       <c r="I139" s="21"/>
     </row>
     <row r="140">
       <c r="C140" s="22"/>
       <c r="F140" s="9"/>
       <c r="G140" s="9"/>
-      <c r="H140" s="14"/>
+      <c r="H140" s="13"/>
       <c r="I140" s="21"/>
     </row>
     <row r="141">
       <c r="C141" s="22"/>
       <c r="F141" s="9"/>
       <c r="G141" s="9"/>
-      <c r="H141" s="14"/>
+      <c r="H141" s="13"/>
       <c r="I141" s="21"/>
     </row>
     <row r="142">
       <c r="C142" s="22"/>
       <c r="F142" s="9"/>
       <c r="G142" s="9"/>
-      <c r="H142" s="14"/>
+      <c r="H142" s="13"/>
       <c r="I142" s="21"/>
     </row>
     <row r="143">
       <c r="C143" s="22"/>
       <c r="F143" s="9"/>
       <c r="G143" s="9"/>
-      <c r="H143" s="14"/>
+      <c r="H143" s="13"/>
       <c r="I143" s="21"/>
     </row>
     <row r="144">
       <c r="C144" s="22"/>
       <c r="F144" s="9"/>
       <c r="G144" s="9"/>
-      <c r="H144" s="14"/>
+      <c r="H144" s="13"/>
       <c r="I144" s="21"/>
     </row>
     <row r="145">
       <c r="C145" s="22"/>
       <c r="F145" s="9"/>
       <c r="G145" s="9"/>
-      <c r="H145" s="14"/>
+      <c r="H145" s="13"/>
       <c r="I145" s="21"/>
     </row>
     <row r="146">
       <c r="C146" s="22"/>
       <c r="F146" s="9"/>
       <c r="G146" s="9"/>
-      <c r="H146" s="14"/>
+      <c r="H146" s="13"/>
       <c r="I146" s="21"/>
     </row>
     <row r="147">
       <c r="C147" s="22"/>
       <c r="F147" s="9"/>
       <c r="G147" s="9"/>
-      <c r="H147" s="14"/>
+      <c r="H147" s="13"/>
       <c r="I147" s="21"/>
     </row>
     <row r="148">
       <c r="C148" s="22"/>
       <c r="F148" s="9"/>
       <c r="G148" s="9"/>
-      <c r="H148" s="14"/>
+      <c r="H148" s="13"/>
       <c r="I148" s="21"/>
     </row>
     <row r="149">
       <c r="C149" s="22"/>
       <c r="F149" s="9"/>
       <c r="G149" s="9"/>
-      <c r="H149" s="14"/>
+      <c r="H149" s="13"/>
       <c r="I149" s="21"/>
     </row>
     <row r="150">
       <c r="C150" s="22"/>
       <c r="F150" s="9"/>
       <c r="G150" s="9"/>
-      <c r="H150" s="14"/>
+      <c r="H150" s="13"/>
       <c r="I150" s="21"/>
     </row>
     <row r="151">
       <c r="C151" s="22"/>
       <c r="F151" s="9"/>
       <c r="G151" s="9"/>
-      <c r="H151" s="14"/>
+      <c r="H151" s="13"/>
       <c r="I151" s="21"/>
     </row>
     <row r="152">
       <c r="C152" s="22"/>
       <c r="F152" s="9"/>
       <c r="G152" s="9"/>
-      <c r="H152" s="14"/>
+      <c r="H152" s="13"/>
       <c r="I152" s="21"/>
     </row>
     <row r="153">
       <c r="C153" s="22"/>
       <c r="F153" s="9"/>
       <c r="G153" s="9"/>
-      <c r="H153" s="14"/>
+      <c r="H153" s="13"/>
       <c r="I153" s="21"/>
     </row>
     <row r="154">
       <c r="C154" s="22"/>
       <c r="F154" s="9"/>
       <c r="G154" s="9"/>
-      <c r="H154" s="14"/>
+      <c r="H154" s="13"/>
       <c r="I154" s="21"/>
     </row>
     <row r="155">
       <c r="C155" s="22"/>
       <c r="F155" s="9"/>
       <c r="G155" s="9"/>
-      <c r="H155" s="14"/>
+      <c r="H155" s="13"/>
       <c r="I155" s="21"/>
     </row>
     <row r="156">
       <c r="C156" s="22"/>
       <c r="F156" s="9"/>
       <c r="G156" s="9"/>
-      <c r="H156" s="14"/>
+      <c r="H156" s="13"/>
       <c r="I156" s="21"/>
     </row>
     <row r="157">
       <c r="C157" s="22"/>
       <c r="F157" s="9"/>
       <c r="G157" s="9"/>
-      <c r="H157" s="14"/>
+      <c r="H157" s="13"/>
       <c r="I157" s="21"/>
     </row>
     <row r="158">
       <c r="C158" s="22"/>
       <c r="F158" s="9"/>
       <c r="G158" s="9"/>
-      <c r="H158" s="14"/>
+      <c r="H158" s="13"/>
       <c r="I158" s="21"/>
     </row>
     <row r="159">
       <c r="C159" s="22"/>
       <c r="F159" s="9"/>
       <c r="G159" s="9"/>
-      <c r="H159" s="14"/>
+      <c r="H159" s="13"/>
       <c r="I159" s="21"/>
     </row>
     <row r="160">
       <c r="C160" s="22"/>
       <c r="F160" s="9"/>
       <c r="G160" s="9"/>
-      <c r="H160" s="14"/>
+      <c r="H160" s="13"/>
       <c r="I160" s="21"/>
     </row>
     <row r="161">
       <c r="C161" s="22"/>
       <c r="F161" s="9"/>
       <c r="G161" s="9"/>
-      <c r="H161" s="14"/>
+      <c r="H161" s="13"/>
       <c r="I161" s="21"/>
     </row>
     <row r="162">
       <c r="C162" s="22"/>
       <c r="F162" s="9"/>
       <c r="G162" s="9"/>
-      <c r="H162" s="14"/>
+      <c r="H162" s="13"/>
       <c r="I162" s="21"/>
     </row>
     <row r="163">
       <c r="C163" s="22"/>
       <c r="F163" s="9"/>
       <c r="G163" s="9"/>
-      <c r="H163" s="14"/>
+      <c r="H163" s="13"/>
       <c r="I163" s="21"/>
     </row>
     <row r="164">
       <c r="C164" s="22"/>
       <c r="F164" s="9"/>
       <c r="G164" s="9"/>
-      <c r="H164" s="14"/>
+      <c r="H164" s="13"/>
       <c r="I164" s="21"/>
     </row>
     <row r="165">
       <c r="C165" s="22"/>
       <c r="F165" s="9"/>
       <c r="G165" s="9"/>
-      <c r="H165" s="14"/>
+      <c r="H165" s="13"/>
       <c r="I165" s="21"/>
     </row>
     <row r="166">
       <c r="C166" s="22"/>
       <c r="F166" s="9"/>
       <c r="G166" s="9"/>
-      <c r="H166" s="14"/>
+      <c r="H166" s="13"/>
       <c r="I166" s="21"/>
     </row>
     <row r="167">
       <c r="C167" s="22"/>
       <c r="F167" s="9"/>
       <c r="G167" s="9"/>
-      <c r="H167" s="14"/>
+      <c r="H167" s="13"/>
       <c r="I167" s="21"/>
     </row>
     <row r="168">
       <c r="C168" s="22"/>
       <c r="F168" s="9"/>
       <c r="G168" s="9"/>
-      <c r="H168" s="14"/>
+      <c r="H168" s="13"/>
       <c r="I168" s="21"/>
     </row>
     <row r="169">
       <c r="C169" s="22"/>
       <c r="F169" s="9"/>
       <c r="G169" s="9"/>
-      <c r="H169" s="14"/>
+      <c r="H169" s="13"/>
       <c r="I169" s="21"/>
     </row>
     <row r="170">
       <c r="C170" s="22"/>
       <c r="F170" s="9"/>
       <c r="G170" s="9"/>
-      <c r="H170" s="14"/>
+      <c r="H170" s="13"/>
       <c r="I170" s="21"/>
     </row>
     <row r="171">
       <c r="C171" s="22"/>
       <c r="F171" s="9"/>
       <c r="G171" s="9"/>
-      <c r="H171" s="14"/>
+      <c r="H171" s="13"/>
       <c r="I171" s="21"/>
     </row>
     <row r="172">
       <c r="C172" s="22"/>
       <c r="F172" s="9"/>
       <c r="G172" s="9"/>
-      <c r="H172" s="14"/>
+      <c r="H172" s="13"/>
       <c r="I172" s="21"/>
     </row>
     <row r="173">
       <c r="C173" s="22"/>
       <c r="F173" s="9"/>
       <c r="G173" s="9"/>
-      <c r="H173" s="14"/>
+      <c r="H173" s="13"/>
       <c r="I173" s="21"/>
     </row>
     <row r="174">
       <c r="C174" s="22"/>
       <c r="F174" s="9"/>
       <c r="G174" s="9"/>
-      <c r="H174" s="14"/>
+      <c r="H174" s="13"/>
       <c r="I174" s="21"/>
     </row>
     <row r="175">
       <c r="C175" s="22"/>
       <c r="F175" s="9"/>
       <c r="G175" s="9"/>
-      <c r="H175" s="14"/>
+      <c r="H175" s="13"/>
       <c r="I175" s="21"/>
     </row>
     <row r="176">
       <c r="C176" s="22"/>
       <c r="F176" s="9"/>
       <c r="G176" s="9"/>
-      <c r="H176" s="14"/>
+      <c r="H176" s="13"/>
       <c r="I176" s="21"/>
     </row>
     <row r="177">
       <c r="C177" s="22"/>
       <c r="F177" s="9"/>
       <c r="G177" s="9"/>
-      <c r="H177" s="14"/>
+      <c r="H177" s="13"/>
       <c r="I177" s="21"/>
     </row>
     <row r="178">
       <c r="C178" s="22"/>
       <c r="F178" s="9"/>
       <c r="G178" s="9"/>
-      <c r="H178" s="14"/>
+      <c r="H178" s="13"/>
       <c r="I178" s="21"/>
     </row>
     <row r="179">
       <c r="C179" s="22"/>
       <c r="F179" s="9"/>
       <c r="G179" s="9"/>
-      <c r="H179" s="14"/>
+      <c r="H179" s="13"/>
       <c r="I179" s="21"/>
     </row>
     <row r="180">
       <c r="C180" s="22"/>
       <c r="F180" s="9"/>
       <c r="G180" s="9"/>
-      <c r="H180" s="14"/>
+      <c r="H180" s="13"/>
       <c r="I180" s="21"/>
     </row>
     <row r="181">
       <c r="C181" s="22"/>
       <c r="F181" s="9"/>
       <c r="G181" s="9"/>
-      <c r="H181" s="14"/>
+      <c r="H181" s="13"/>
       <c r="I181" s="21"/>
     </row>
     <row r="182">
       <c r="C182" s="22"/>
       <c r="F182" s="9"/>
       <c r="G182" s="9"/>
-      <c r="H182" s="14"/>
+      <c r="H182" s="13"/>
       <c r="I182" s="21"/>
     </row>
     <row r="183">
       <c r="C183" s="22"/>
       <c r="F183" s="9"/>
       <c r="G183" s="9"/>
-      <c r="H183" s="14"/>
+      <c r="H183" s="13"/>
       <c r="I183" s="21"/>
     </row>
     <row r="184">
       <c r="C184" s="22"/>
       <c r="F184" s="9"/>
       <c r="G184" s="9"/>
-      <c r="H184" s="14"/>
+      <c r="H184" s="13"/>
       <c r="I184" s="21"/>
     </row>
     <row r="185">
       <c r="C185" s="22"/>
       <c r="F185" s="9"/>
       <c r="G185" s="9"/>
-      <c r="H185" s="14"/>
+      <c r="H185" s="13"/>
       <c r="I185" s="21"/>
     </row>
     <row r="186">
       <c r="C186" s="22"/>
       <c r="F186" s="9"/>
       <c r="G186" s="9"/>
-      <c r="H186" s="14"/>
+      <c r="H186" s="13"/>
       <c r="I186" s="21"/>
     </row>
     <row r="187">
       <c r="C187" s="22"/>
       <c r="F187" s="9"/>
       <c r="G187" s="9"/>
-      <c r="H187" s="14"/>
+      <c r="H187" s="13"/>
       <c r="I187" s="21"/>
     </row>
     <row r="188">
       <c r="C188" s="22"/>
       <c r="F188" s="9"/>
       <c r="G188" s="9"/>
-      <c r="H188" s="14"/>
+      <c r="H188" s="13"/>
       <c r="I188" s="21"/>
     </row>
     <row r="189">
       <c r="C189" s="22"/>
       <c r="F189" s="9"/>
       <c r="G189" s="9"/>
-      <c r="H189" s="14"/>
+      <c r="H189" s="13"/>
       <c r="I189" s="21"/>
     </row>
     <row r="190">
       <c r="C190" s="22"/>
       <c r="F190" s="9"/>
       <c r="G190" s="9"/>
-      <c r="H190" s="14"/>
+      <c r="H190" s="13"/>
       <c r="I190" s="21"/>
     </row>
     <row r="191">
       <c r="C191" s="22"/>
       <c r="F191" s="9"/>
       <c r="G191" s="9"/>
-      <c r="H191" s="14"/>
+      <c r="H191" s="13"/>
       <c r="I191" s="21"/>
     </row>
     <row r="192">
       <c r="C192" s="22"/>
       <c r="F192" s="9"/>
       <c r="G192" s="9"/>
-      <c r="H192" s="14"/>
+      <c r="H192" s="13"/>
       <c r="I192" s="21"/>
     </row>
     <row r="193">
       <c r="C193" s="22"/>
       <c r="F193" s="9"/>
       <c r="G193" s="9"/>
-      <c r="H193" s="14"/>
+      <c r="H193" s="13"/>
       <c r="I193" s="21"/>
     </row>
     <row r="194">
       <c r="C194" s="22"/>
       <c r="F194" s="9"/>
       <c r="G194" s="9"/>
-      <c r="H194" s="14"/>
+      <c r="H194" s="13"/>
       <c r="I194" s="21"/>
     </row>
     <row r="195">
       <c r="C195" s="22"/>
       <c r="F195" s="9"/>
       <c r="G195" s="9"/>
-      <c r="H195" s="14"/>
+      <c r="H195" s="13"/>
       <c r="I195" s="21"/>
     </row>
     <row r="196">
       <c r="C196" s="22"/>
       <c r="F196" s="9"/>
       <c r="G196" s="9"/>
-      <c r="H196" s="14"/>
+      <c r="H196" s="13"/>
       <c r="I196" s="21"/>
     </row>
     <row r="197">
       <c r="C197" s="22"/>
       <c r="F197" s="9"/>
       <c r="G197" s="9"/>
-      <c r="H197" s="14"/>
+      <c r="H197" s="13"/>
       <c r="I197" s="21"/>
     </row>
     <row r="198">
       <c r="C198" s="22"/>
       <c r="F198" s="9"/>
       <c r="G198" s="9"/>
-      <c r="H198" s="14"/>
+      <c r="H198" s="13"/>
       <c r="I198" s="21"/>
     </row>
     <row r="199">
       <c r="C199" s="22"/>
       <c r="F199" s="9"/>
       <c r="G199" s="9"/>
-      <c r="H199" s="14"/>
+      <c r="H199" s="13"/>
       <c r="I199" s="21"/>
     </row>
     <row r="200">
       <c r="C200" s="22"/>
       <c r="F200" s="9"/>
       <c r="G200" s="9"/>
-      <c r="H200" s="14"/>
+      <c r="H200" s="13"/>
       <c r="I200" s="21"/>
     </row>
     <row r="201">
       <c r="C201" s="22"/>
       <c r="F201" s="9"/>
       <c r="G201" s="9"/>
-      <c r="H201" s="14"/>
+      <c r="H201" s="13"/>
       <c r="I201" s="21"/>
     </row>
     <row r="202">
       <c r="C202" s="22"/>
       <c r="F202" s="9"/>
       <c r="G202" s="9"/>
-      <c r="H202" s="14"/>
+      <c r="H202" s="13"/>
       <c r="I202" s="21"/>
     </row>
     <row r="203">
       <c r="C203" s="22"/>
       <c r="F203" s="9"/>
       <c r="G203" s="9"/>
-      <c r="H203" s="14"/>
+      <c r="H203" s="13"/>
       <c r="I203" s="21"/>
     </row>
     <row r="204">
       <c r="C204" s="22"/>
       <c r="F204" s="9"/>
       <c r="G204" s="9"/>
-      <c r="H204" s="14"/>
+      <c r="H204" s="13"/>
       <c r="I204" s="21"/>
     </row>
     <row r="205">
       <c r="C205" s="22"/>
       <c r="F205" s="9"/>
       <c r="G205" s="9"/>
-      <c r="H205" s="14"/>
+      <c r="H205" s="13"/>
       <c r="I205" s="21"/>
     </row>
     <row r="206">
       <c r="C206" s="22"/>
       <c r="F206" s="9"/>
       <c r="G206" s="9"/>
-      <c r="H206" s="14"/>
+      <c r="H206" s="13"/>
       <c r="I206" s="21"/>
     </row>
     <row r="207">
       <c r="C207" s="22"/>
       <c r="F207" s="9"/>
       <c r="G207" s="9"/>
-      <c r="H207" s="14"/>
+      <c r="H207" s="13"/>
       <c r="I207" s="21"/>
     </row>
     <row r="208">
       <c r="C208" s="22"/>
       <c r="F208" s="9"/>
       <c r="G208" s="9"/>
-      <c r="H208" s="14"/>
+      <c r="H208" s="13"/>
       <c r="I208" s="21"/>
     </row>
     <row r="209">
       <c r="C209" s="22"/>
       <c r="F209" s="9"/>
       <c r="G209" s="9"/>
-      <c r="H209" s="14"/>
+      <c r="H209" s="13"/>
       <c r="I209" s="21"/>
     </row>
     <row r="210">
       <c r="C210" s="22"/>
       <c r="F210" s="9"/>
       <c r="G210" s="9"/>
-      <c r="H210" s="14"/>
+      <c r="H210" s="13"/>
       <c r="I210" s="21"/>
     </row>
     <row r="211">
       <c r="C211" s="22"/>
       <c r="F211" s="9"/>
       <c r="G211" s="9"/>
-      <c r="H211" s="14"/>
+      <c r="H211" s="13"/>
       <c r="I211" s="21"/>
     </row>
     <row r="212">
       <c r="C212" s="22"/>
       <c r="F212" s="9"/>
       <c r="G212" s="9"/>
-      <c r="H212" s="14"/>
+      <c r="H212" s="13"/>
       <c r="I212" s="21"/>
     </row>
     <row r="213">
       <c r="C213" s="22"/>
       <c r="F213" s="9"/>
       <c r="G213" s="9"/>
-      <c r="H213" s="14"/>
+      <c r="H213" s="13"/>
       <c r="I213" s="21"/>
     </row>
     <row r="214">
       <c r="C214" s="22"/>
       <c r="F214" s="9"/>
       <c r="G214" s="9"/>
-      <c r="H214" s="14"/>
+      <c r="H214" s="13"/>
       <c r="I214" s="21"/>
     </row>
     <row r="215">
       <c r="C215" s="22"/>
       <c r="F215" s="9"/>
       <c r="G215" s="9"/>
-      <c r="H215" s="14"/>
+      <c r="H215" s="13"/>
       <c r="I215" s="21"/>
     </row>
     <row r="216">
       <c r="C216" s="22"/>
       <c r="F216" s="9"/>
       <c r="G216" s="9"/>
-      <c r="H216" s="14"/>
+      <c r="H216" s="13"/>
       <c r="I216" s="21"/>
     </row>
     <row r="217">
       <c r="C217" s="22"/>
       <c r="F217" s="9"/>
       <c r="G217" s="9"/>
-      <c r="H217" s="14"/>
+      <c r="H217" s="13"/>
       <c r="I217" s="21"/>
     </row>
     <row r="218">
       <c r="C218" s="22"/>
       <c r="F218" s="9"/>
       <c r="G218" s="9"/>
-      <c r="H218" s="14"/>
+      <c r="H218" s="13"/>
       <c r="I218" s="21"/>
     </row>
     <row r="219">
       <c r="C219" s="22"/>
       <c r="F219" s="9"/>
       <c r="G219" s="9"/>
-      <c r="H219" s="14"/>
+      <c r="H219" s="13"/>
       <c r="I219" s="21"/>
     </row>
     <row r="220">
       <c r="C220" s="22"/>
       <c r="F220" s="9"/>
       <c r="G220" s="9"/>
-      <c r="H220" s="14"/>
+      <c r="H220" s="13"/>
       <c r="I220" s="21"/>
     </row>
     <row r="221">
       <c r="C221" s="22"/>
       <c r="F221" s="9"/>
       <c r="G221" s="9"/>
-      <c r="H221" s="14"/>
+      <c r="H221" s="13"/>
       <c r="I221" s="21"/>
     </row>
     <row r="222">
       <c r="C222" s="22"/>
       <c r="F222" s="9"/>
       <c r="G222" s="9"/>
-      <c r="H222" s="14"/>
+      <c r="H222" s="13"/>
       <c r="I222" s="21"/>
     </row>
     <row r="223">
       <c r="C223" s="22"/>
       <c r="F223" s="9"/>
       <c r="G223" s="9"/>
-      <c r="H223" s="14"/>
+      <c r="H223" s="13"/>
       <c r="I223" s="21"/>
     </row>
     <row r="224">
       <c r="C224" s="22"/>
       <c r="F224" s="9"/>
       <c r="G224" s="9"/>
-      <c r="H224" s="14"/>
+      <c r="H224" s="13"/>
       <c r="I224" s="21"/>
     </row>
     <row r="225">
       <c r="C225" s="22"/>
       <c r="F225" s="9"/>
       <c r="G225" s="9"/>
-      <c r="H225" s="14"/>
+      <c r="H225" s="13"/>
       <c r="I225" s="21"/>
     </row>
     <row r="226">
       <c r="C226" s="22"/>
       <c r="F226" s="9"/>
       <c r="G226" s="9"/>
-      <c r="H226" s="14"/>
+      <c r="H226" s="13"/>
       <c r="I226" s="21"/>
     </row>
     <row r="227">
       <c r="C227" s="22"/>
       <c r="F227" s="9"/>
       <c r="G227" s="9"/>
-      <c r="H227" s="14"/>
+      <c r="H227" s="13"/>
       <c r="I227" s="21"/>
     </row>
     <row r="228">
       <c r="C228" s="22"/>
       <c r="F228" s="9"/>
       <c r="G228" s="9"/>
-      <c r="H228" s="14"/>
+      <c r="H228" s="13"/>
       <c r="I228" s="21"/>
     </row>
     <row r="229">
       <c r="C229" s="22"/>
       <c r="F229" s="9"/>
       <c r="G229" s="9"/>
-      <c r="H229" s="14"/>
+      <c r="H229" s="13"/>
       <c r="I229" s="21"/>
     </row>
     <row r="230">
       <c r="C230" s="22"/>
       <c r="F230" s="9"/>
       <c r="G230" s="9"/>
-      <c r="H230" s="14"/>
+      <c r="H230" s="13"/>
       <c r="I230" s="21"/>
     </row>
     <row r="231">
       <c r="C231" s="22"/>
       <c r="F231" s="9"/>
       <c r="G231" s="9"/>
-      <c r="H231" s="14"/>
+      <c r="H231" s="13"/>
       <c r="I231" s="21"/>
     </row>
     <row r="232">
       <c r="C232" s="22"/>
       <c r="F232" s="9"/>
       <c r="G232" s="9"/>
-      <c r="H232" s="14"/>
+      <c r="H232" s="13"/>
       <c r="I232" s="21"/>
     </row>
     <row r="233">
       <c r="C233" s="22"/>
       <c r="F233" s="9"/>
       <c r="G233" s="9"/>
-      <c r="H233" s="14"/>
+      <c r="H233" s="13"/>
       <c r="I233" s="21"/>
     </row>
     <row r="234">
       <c r="C234" s="22"/>
       <c r="F234" s="9"/>
       <c r="G234" s="9"/>
-      <c r="H234" s="14"/>
+      <c r="H234" s="13"/>
       <c r="I234" s="21"/>
     </row>
     <row r="235">
       <c r="C235" s="22"/>
       <c r="F235" s="9"/>
       <c r="G235" s="9"/>
-      <c r="H235" s="14"/>
+      <c r="H235" s="13"/>
       <c r="I235" s="21"/>
     </row>
     <row r="236">
       <c r="C236" s="22"/>
       <c r="F236" s="9"/>
       <c r="G236" s="9"/>
-      <c r="H236" s="14"/>
+      <c r="H236" s="13"/>
       <c r="I236" s="21"/>
     </row>
     <row r="237">
       <c r="C237" s="22"/>
       <c r="F237" s="9"/>
       <c r="G237" s="9"/>
-      <c r="H237" s="14"/>
+      <c r="H237" s="13"/>
       <c r="I237" s="21"/>
     </row>
     <row r="238">
       <c r="C238" s="22"/>
       <c r="F238" s="9"/>
       <c r="G238" s="9"/>
-      <c r="H238" s="14"/>
+      <c r="H238" s="13"/>
       <c r="I238" s="21"/>
     </row>
     <row r="239">
       <c r="C239" s="22"/>
       <c r="F239" s="9"/>
       <c r="G239" s="9"/>
-      <c r="H239" s="14"/>
+      <c r="H239" s="13"/>
       <c r="I239" s="21"/>
     </row>
     <row r="240">
       <c r="C240" s="22"/>
       <c r="F240" s="9"/>
       <c r="G240" s="9"/>
-      <c r="H240" s="14"/>
+      <c r="H240" s="13"/>
       <c r="I240" s="21"/>
     </row>
     <row r="241">
       <c r="C241" s="22"/>
       <c r="F241" s="9"/>
       <c r="G241" s="9"/>
-      <c r="H241" s="14"/>
+      <c r="H241" s="13"/>
       <c r="I241" s="21"/>
     </row>
     <row r="242">
       <c r="C242" s="22"/>
       <c r="F242" s="9"/>
       <c r="G242" s="9"/>
-      <c r="H242" s="14"/>
+      <c r="H242" s="13"/>
       <c r="I242" s="21"/>
     </row>
     <row r="243">
       <c r="C243" s="22"/>
       <c r="F243" s="9"/>
       <c r="G243" s="9"/>
-      <c r="H243" s="14"/>
+      <c r="H243" s="13"/>
       <c r="I243" s="21"/>
     </row>
     <row r="244">
       <c r="C244" s="22"/>
       <c r="F244" s="9"/>
       <c r="G244" s="9"/>
-      <c r="H244" s="14"/>
+      <c r="H244" s="13"/>
       <c r="I244" s="21"/>
     </row>
     <row r="245">
       <c r="C245" s="22"/>
       <c r="F245" s="9"/>
       <c r="G245" s="9"/>
-      <c r="H245" s="14"/>
+      <c r="H245" s="13"/>
       <c r="I245" s="21"/>
     </row>
     <row r="246">
       <c r="C246" s="22"/>
       <c r="F246" s="9"/>
       <c r="G246" s="9"/>
-      <c r="H246" s="14"/>
+      <c r="H246" s="13"/>
       <c r="I246" s="21"/>
     </row>
     <row r="247">
       <c r="C247" s="22"/>
       <c r="F247" s="9"/>
       <c r="G247" s="9"/>
-      <c r="H247" s="14"/>
+      <c r="H247" s="13"/>
       <c r="I247" s="21"/>
     </row>
     <row r="248">
       <c r="C248" s="22"/>
       <c r="F248" s="9"/>
       <c r="G248" s="9"/>
-      <c r="H248" s="14"/>
+      <c r="H248" s="13"/>
       <c r="I248" s="21"/>
     </row>
     <row r="249">
       <c r="C249" s="22"/>
       <c r="F249" s="9"/>
       <c r="G249" s="9"/>
-      <c r="H249" s="14"/>
+      <c r="H249" s="13"/>
       <c r="I249" s="21"/>
     </row>
     <row r="250">
       <c r="C250" s="22"/>
       <c r="F250" s="9"/>
       <c r="G250" s="9"/>
-      <c r="H250" s="14"/>
+      <c r="H250" s="13"/>
       <c r="I250" s="21"/>
     </row>
     <row r="251">
       <c r="C251" s="22"/>
       <c r="F251" s="9"/>
       <c r="G251" s="9"/>
-      <c r="H251" s="14"/>
+      <c r="H251" s="13"/>
       <c r="I251" s="21"/>
     </row>
     <row r="252">
       <c r="C252" s="22"/>
       <c r="F252" s="9"/>
       <c r="G252" s="9"/>
-      <c r="H252" s="14"/>
+      <c r="H252" s="13"/>
       <c r="I252" s="21"/>
     </row>
     <row r="253">
       <c r="C253" s="22"/>
       <c r="F253" s="9"/>
       <c r="G253" s="9"/>
-      <c r="H253" s="14"/>
+      <c r="H253" s="13"/>
       <c r="I253" s="21"/>
     </row>
     <row r="254">
       <c r="C254" s="22"/>
       <c r="F254" s="9"/>
       <c r="G254" s="9"/>
-      <c r="H254" s="14"/>
+      <c r="H254" s="13"/>
       <c r="I254" s="21"/>
     </row>
     <row r="255">
       <c r="C255" s="22"/>
       <c r="F255" s="9"/>
       <c r="G255" s="9"/>
-      <c r="H255" s="14"/>
+      <c r="H255" s="13"/>
       <c r="I255" s="21"/>
     </row>
     <row r="256">
       <c r="C256" s="22"/>
       <c r="F256" s="9"/>
       <c r="G256" s="9"/>
-      <c r="H256" s="14"/>
+      <c r="H256" s="13"/>
       <c r="I256" s="21"/>
     </row>
     <row r="257">
       <c r="C257" s="22"/>
       <c r="F257" s="9"/>
       <c r="G257" s="9"/>
-      <c r="H257" s="14"/>
+      <c r="H257" s="13"/>
       <c r="I257" s="21"/>
     </row>
     <row r="258">
       <c r="C258" s="22"/>
       <c r="F258" s="9"/>
       <c r="G258" s="9"/>
-      <c r="H258" s="14"/>
+      <c r="H258" s="13"/>
       <c r="I258" s="21"/>
     </row>
     <row r="259">
       <c r="C259" s="22"/>
       <c r="F259" s="9"/>
       <c r="G259" s="9"/>
-      <c r="H259" s="14"/>
+      <c r="H259" s="13"/>
       <c r="I259" s="21"/>
     </row>
     <row r="260">
       <c r="C260" s="22"/>
       <c r="F260" s="9"/>
       <c r="G260" s="9"/>
-      <c r="H260" s="14"/>
+      <c r="H260" s="13"/>
       <c r="I260" s="21"/>
     </row>
     <row r="261">
       <c r="C261" s="22"/>
       <c r="F261" s="9"/>
       <c r="G261" s="9"/>
-      <c r="H261" s="14"/>
+      <c r="H261" s="13"/>
       <c r="I261" s="21"/>
     </row>
     <row r="262">
       <c r="C262" s="22"/>
       <c r="F262" s="9"/>
       <c r="G262" s="9"/>
-      <c r="H262" s="14"/>
+      <c r="H262" s="13"/>
       <c r="I262" s="21"/>
     </row>
     <row r="263">
       <c r="C263" s="22"/>
       <c r="F263" s="9"/>
       <c r="G263" s="9"/>
-      <c r="H263" s="14"/>
+      <c r="H263" s="13"/>
       <c r="I263" s="21"/>
     </row>
     <row r="264">
       <c r="C264" s="22"/>
       <c r="F264" s="9"/>
       <c r="G264" s="9"/>
-      <c r="H264" s="14"/>
+      <c r="H264" s="13"/>
       <c r="I264" s="21"/>
     </row>
     <row r="265">
       <c r="C265" s="22"/>
       <c r="F265" s="9"/>
       <c r="G265" s="9"/>
-      <c r="H265" s="14"/>
+      <c r="H265" s="13"/>
       <c r="I265" s="21"/>
     </row>
     <row r="266">
       <c r="C266" s="22"/>
       <c r="F266" s="9"/>
       <c r="G266" s="9"/>
-      <c r="H266" s="14"/>
+      <c r="H266" s="13"/>
       <c r="I266" s="21"/>
     </row>
     <row r="267">
       <c r="C267" s="22"/>
       <c r="F267" s="9"/>
       <c r="G267" s="9"/>
-      <c r="H267" s="14"/>
+      <c r="H267" s="13"/>
       <c r="I267" s="21"/>
     </row>
     <row r="268">
       <c r="C268" s="22"/>
       <c r="F268" s="9"/>
       <c r="G268" s="9"/>
-      <c r="H268" s="14"/>
+      <c r="H268" s="13"/>
       <c r="I268" s="21"/>
     </row>
     <row r="269">
       <c r="C269" s="22"/>
       <c r="F269" s="9"/>
       <c r="G269" s="9"/>
-      <c r="H269" s="14"/>
+      <c r="H269" s="13"/>
       <c r="I269" s="21"/>
     </row>
     <row r="270">
       <c r="C270" s="22"/>
       <c r="F270" s="9"/>
       <c r="G270" s="9"/>
-      <c r="H270" s="14"/>
+      <c r="H270" s="13"/>
       <c r="I270" s="21"/>
     </row>
     <row r="271">
       <c r="C271" s="22"/>
       <c r="F271" s="9"/>
       <c r="G271" s="9"/>
-      <c r="H271" s="14"/>
+      <c r="H271" s="13"/>
       <c r="I271" s="21"/>
     </row>
     <row r="272">
       <c r="C272" s="22"/>
       <c r="F272" s="9"/>
       <c r="G272" s="9"/>
-      <c r="H272" s="14"/>
+      <c r="H272" s="13"/>
       <c r="I272" s="21"/>
     </row>
     <row r="273">
       <c r="C273" s="22"/>
       <c r="F273" s="9"/>
       <c r="G273" s="9"/>
-      <c r="H273" s="14"/>
+      <c r="H273" s="13"/>
       <c r="I273" s="21"/>
     </row>
     <row r="274">
       <c r="C274" s="22"/>
       <c r="F274" s="9"/>
       <c r="G274" s="9"/>
-      <c r="H274" s="14"/>
+      <c r="H274" s="13"/>
       <c r="I274" s="21"/>
     </row>
     <row r="275">
       <c r="C275" s="22"/>
       <c r="F275" s="9"/>
       <c r="G275" s="9"/>
-      <c r="H275" s="14"/>
+      <c r="H275" s="13"/>
       <c r="I275" s="21"/>
     </row>
     <row r="276">
       <c r="C276" s="22"/>
       <c r="F276" s="9"/>
       <c r="G276" s="9"/>
-      <c r="H276" s="14"/>
+      <c r="H276" s="13"/>
       <c r="I276" s="21"/>
     </row>
     <row r="277">
       <c r="C277" s="22"/>
       <c r="F277" s="9"/>
       <c r="G277" s="9"/>
-      <c r="H277" s="14"/>
+      <c r="H277" s="13"/>
       <c r="I277" s="21"/>
     </row>
     <row r="278">
       <c r="C278" s="22"/>
       <c r="F278" s="9"/>
       <c r="G278" s="9"/>
-      <c r="H278" s="14"/>
+      <c r="H278" s="13"/>
       <c r="I278" s="21"/>
     </row>
     <row r="279">
       <c r="C279" s="22"/>
       <c r="F279" s="9"/>
       <c r="G279" s="9"/>
-      <c r="H279" s="14"/>
+      <c r="H279" s="13"/>
       <c r="I279" s="21"/>
     </row>
     <row r="280">
       <c r="C280" s="22"/>
       <c r="F280" s="9"/>
       <c r="G280" s="9"/>
-      <c r="H280" s="14"/>
+      <c r="H280" s="13"/>
       <c r="I280" s="21"/>
     </row>
     <row r="281">
       <c r="C281" s="22"/>
       <c r="F281" s="9"/>
       <c r="G281" s="9"/>
-      <c r="H281" s="14"/>
+      <c r="H281" s="13"/>
       <c r="I281" s="21"/>
     </row>
     <row r="282">
       <c r="C282" s="22"/>
       <c r="F282" s="9"/>
       <c r="G282" s="9"/>
-      <c r="H282" s="14"/>
+      <c r="H282" s="13"/>
       <c r="I282" s="21"/>
     </row>
     <row r="283">
       <c r="C283" s="22"/>
       <c r="F283" s="9"/>
       <c r="G283" s="9"/>
-      <c r="H283" s="14"/>
+      <c r="H283" s="13"/>
       <c r="I283" s="21"/>
     </row>
     <row r="284">
       <c r="C284" s="22"/>
       <c r="F284" s="9"/>
       <c r="G284" s="9"/>
-      <c r="H284" s="14"/>
+      <c r="H284" s="13"/>
       <c r="I284" s="21"/>
     </row>
     <row r="285">
       <c r="C285" s="22"/>
       <c r="F285" s="9"/>
       <c r="G285" s="9"/>
-      <c r="H285" s="14"/>
+      <c r="H285" s="13"/>
       <c r="I285" s="21"/>
     </row>
     <row r="286">
       <c r="C286" s="22"/>
       <c r="F286" s="9"/>
       <c r="G286" s="9"/>
-      <c r="H286" s="14"/>
+      <c r="H286" s="13"/>
       <c r="I286" s="21"/>
     </row>
     <row r="287">
       <c r="C287" s="22"/>
       <c r="F287" s="9"/>
       <c r="G287" s="9"/>
-      <c r="H287" s="14"/>
+      <c r="H287" s="13"/>
       <c r="I287" s="21"/>
     </row>
     <row r="288">
       <c r="C288" s="22"/>
       <c r="F288" s="9"/>
       <c r="G288" s="9"/>
-      <c r="H288" s="14"/>
+      <c r="H288" s="13"/>
       <c r="I288" s="21"/>
     </row>
     <row r="289">
       <c r="C289" s="22"/>
       <c r="F289" s="9"/>
       <c r="G289" s="9"/>
-      <c r="H289" s="14"/>
+      <c r="H289" s="13"/>
       <c r="I289" s="21"/>
     </row>
     <row r="290">
       <c r="C290" s="22"/>
       <c r="F290" s="9"/>
       <c r="G290" s="9"/>
-      <c r="H290" s="14"/>
+      <c r="H290" s="13"/>
       <c r="I290" s="21"/>
     </row>
     <row r="291">
       <c r="C291" s="22"/>
       <c r="F291" s="9"/>
       <c r="G291" s="9"/>
-      <c r="H291" s="14"/>
+      <c r="H291" s="13"/>
       <c r="I291" s="21"/>
     </row>
     <row r="292">
       <c r="C292" s="22"/>
       <c r="F292" s="9"/>
       <c r="G292" s="9"/>
-      <c r="H292" s="14"/>
+      <c r="H292" s="13"/>
       <c r="I292" s="21"/>
     </row>
     <row r="293">
       <c r="C293" s="22"/>
       <c r="F293" s="9"/>
       <c r="G293" s="9"/>
-      <c r="H293" s="14"/>
+      <c r="H293" s="13"/>
       <c r="I293" s="21"/>
     </row>
     <row r="294">
       <c r="C294" s="22"/>
       <c r="F294" s="9"/>
       <c r="G294" s="9"/>
-      <c r="H294" s="14"/>
+      <c r="H294" s="13"/>
       <c r="I294" s="21"/>
     </row>
     <row r="295">
       <c r="C295" s="22"/>
       <c r="F295" s="9"/>
       <c r="G295" s="9"/>
-      <c r="H295" s="14"/>
+      <c r="H295" s="13"/>
       <c r="I295" s="21"/>
     </row>
     <row r="296">
       <c r="C296" s="22"/>
       <c r="F296" s="9"/>
       <c r="G296" s="9"/>
-      <c r="H296" s="14"/>
+      <c r="H296" s="13"/>
       <c r="I296" s="21"/>
     </row>
     <row r="297">
       <c r="C297" s="22"/>
       <c r="F297" s="9"/>
       <c r="G297" s="9"/>
-      <c r="H297" s="14"/>
+      <c r="H297" s="13"/>
       <c r="I297" s="21"/>
     </row>
     <row r="298">
       <c r="C298" s="22"/>
       <c r="F298" s="9"/>
       <c r="G298" s="9"/>
-      <c r="H298" s="14"/>
+      <c r="H298" s="13"/>
       <c r="I298" s="21"/>
     </row>
     <row r="299">
       <c r="C299" s="22"/>
       <c r="F299" s="9"/>
       <c r="G299" s="9"/>
-      <c r="H299" s="14"/>
+      <c r="H299" s="13"/>
       <c r="I299" s="21"/>
     </row>
     <row r="300">
       <c r="C300" s="22"/>
       <c r="F300" s="9"/>
       <c r="G300" s="9"/>
-      <c r="H300" s="14"/>
+      <c r="H300" s="13"/>
       <c r="I300" s="21"/>
     </row>
     <row r="301">
       <c r="C301" s="22"/>
       <c r="F301" s="9"/>
       <c r="G301" s="9"/>
-      <c r="H301" s="14"/>
+      <c r="H301" s="13"/>
       <c r="I301" s="21"/>
     </row>
     <row r="302">
       <c r="C302" s="22"/>
       <c r="F302" s="9"/>
       <c r="G302" s="9"/>
-      <c r="H302" s="14"/>
+      <c r="H302" s="13"/>
       <c r="I302" s="21"/>
     </row>
     <row r="303">
       <c r="C303" s="22"/>
       <c r="F303" s="9"/>
       <c r="G303" s="9"/>
-      <c r="H303" s="14"/>
+      <c r="H303" s="13"/>
       <c r="I303" s="21"/>
     </row>
     <row r="304">
       <c r="C304" s="22"/>
       <c r="F304" s="9"/>
       <c r="G304" s="9"/>
-      <c r="H304" s="14"/>
+      <c r="H304" s="13"/>
       <c r="I304" s="21"/>
     </row>
     <row r="305">
       <c r="C305" s="22"/>
       <c r="F305" s="9"/>
       <c r="G305" s="9"/>
-      <c r="H305" s="14"/>
+      <c r="H305" s="13"/>
       <c r="I305" s="21"/>
     </row>
     <row r="306">
       <c r="C306" s="22"/>
       <c r="F306" s="9"/>
       <c r="G306" s="9"/>
-      <c r="H306" s="14"/>
+      <c r="H306" s="13"/>
       <c r="I306" s="21"/>
     </row>
     <row r="307">
       <c r="C307" s="22"/>
       <c r="F307" s="9"/>
       <c r="G307" s="9"/>
-      <c r="H307" s="14"/>
+      <c r="H307" s="13"/>
       <c r="I307" s="21"/>
     </row>
     <row r="308">
       <c r="C308" s="22"/>
       <c r="F308" s="9"/>
       <c r="G308" s="9"/>
-      <c r="H308" s="14"/>
+      <c r="H308" s="13"/>
       <c r="I308" s="21"/>
     </row>
     <row r="309">
       <c r="C309" s="22"/>
       <c r="F309" s="9"/>
       <c r="G309" s="9"/>
-      <c r="H309" s="14"/>
+      <c r="H309" s="13"/>
       <c r="I309" s="21"/>
     </row>
     <row r="310">
       <c r="C310" s="22"/>
       <c r="F310" s="9"/>
       <c r="G310" s="9"/>
-      <c r="H310" s="14"/>
+      <c r="H310" s="13"/>
       <c r="I310" s="21"/>
     </row>
     <row r="311">
       <c r="C311" s="22"/>
       <c r="F311" s="9"/>
       <c r="G311" s="9"/>
-      <c r="H311" s="14"/>
+      <c r="H311" s="13"/>
       <c r="I311" s="21"/>
     </row>
     <row r="312">
       <c r="C312" s="22"/>
       <c r="F312" s="9"/>
       <c r="G312" s="9"/>
-      <c r="H312" s="14"/>
+      <c r="H312" s="13"/>
       <c r="I312" s="21"/>
     </row>
     <row r="313">
       <c r="C313" s="22"/>
       <c r="F313" s="9"/>
       <c r="G313" s="9"/>
-      <c r="H313" s="14"/>
+      <c r="H313" s="13"/>
       <c r="I313" s="21"/>
     </row>
     <row r="314">
       <c r="C314" s="22"/>
       <c r="F314" s="9"/>
       <c r="G314" s="9"/>
-      <c r="H314" s="14"/>
+      <c r="H314" s="13"/>
       <c r="I314" s="21"/>
     </row>
     <row r="315">
       <c r="C315" s="22"/>
       <c r="F315" s="9"/>
       <c r="G315" s="9"/>
-      <c r="H315" s="14"/>
+      <c r="H315" s="13"/>
       <c r="I315" s="21"/>
     </row>
     <row r="316">
       <c r="C316" s="22"/>
       <c r="F316" s="9"/>
       <c r="G316" s="9"/>
-      <c r="H316" s="14"/>
+      <c r="H316" s="13"/>
       <c r="I316" s="21"/>
     </row>
     <row r="317">
       <c r="C317" s="22"/>
       <c r="F317" s="9"/>
       <c r="G317" s="9"/>
-      <c r="H317" s="14"/>
+      <c r="H317" s="13"/>
       <c r="I317" s="21"/>
     </row>
     <row r="318">
       <c r="C318" s="22"/>
       <c r="F318" s="9"/>
       <c r="G318" s="9"/>
-      <c r="H318" s="14"/>
+      <c r="H318" s="13"/>
       <c r="I318" s="21"/>
     </row>
     <row r="319">
       <c r="C319" s="22"/>
       <c r="F319" s="9"/>
       <c r="G319" s="9"/>
-      <c r="H319" s="14"/>
+      <c r="H319" s="13"/>
       <c r="I319" s="21"/>
     </row>
     <row r="320">
       <c r="C320" s="22"/>
       <c r="F320" s="9"/>
       <c r="G320" s="9"/>
-      <c r="H320" s="14"/>
+      <c r="H320" s="13"/>
       <c r="I320" s="21"/>
     </row>
     <row r="321">
       <c r="C321" s="22"/>
       <c r="F321" s="9"/>
       <c r="G321" s="9"/>
-      <c r="H321" s="14"/>
+      <c r="H321" s="13"/>
       <c r="I321" s="21"/>
     </row>
     <row r="322">
       <c r="C322" s="22"/>
       <c r="F322" s="9"/>
       <c r="G322" s="9"/>
-      <c r="H322" s="14"/>
+      <c r="H322" s="13"/>
       <c r="I322" s="21"/>
     </row>
     <row r="323">
       <c r="C323" s="22"/>
       <c r="F323" s="9"/>
       <c r="G323" s="9"/>
-      <c r="H323" s="14"/>
+      <c r="H323" s="13"/>
       <c r="I323" s="21"/>
     </row>
     <row r="324">
       <c r="C324" s="22"/>
       <c r="F324" s="9"/>
       <c r="G324" s="9"/>
-      <c r="H324" s="14"/>
+      <c r="H324" s="13"/>
       <c r="I324" s="21"/>
     </row>
     <row r="325">
       <c r="C325" s="22"/>
       <c r="F325" s="9"/>
       <c r="G325" s="9"/>
-      <c r="H325" s="14"/>
+      <c r="H325" s="13"/>
       <c r="I325" s="21"/>
     </row>
     <row r="326">
       <c r="C326" s="22"/>
       <c r="F326" s="9"/>
       <c r="G326" s="9"/>
-      <c r="H326" s="14"/>
+      <c r="H326" s="13"/>
       <c r="I326" s="21"/>
     </row>
     <row r="327">
       <c r="C327" s="22"/>
       <c r="F327" s="9"/>
       <c r="G327" s="9"/>
-      <c r="H327" s="14"/>
+      <c r="H327" s="13"/>
       <c r="I327" s="21"/>
     </row>
     <row r="328">
       <c r="C328" s="22"/>
       <c r="F328" s="9"/>
       <c r="G328" s="9"/>
-      <c r="H328" s="14"/>
+      <c r="H328" s="13"/>
       <c r="I328" s="21"/>
     </row>
     <row r="329">
       <c r="C329" s="22"/>
       <c r="F329" s="9"/>
       <c r="G329" s="9"/>
-      <c r="H329" s="14"/>
+      <c r="H329" s="13"/>
       <c r="I329" s="21"/>
     </row>
     <row r="330">
       <c r="C330" s="22"/>
       <c r="F330" s="9"/>
       <c r="G330" s="9"/>
-      <c r="H330" s="14"/>
+      <c r="H330" s="13"/>
       <c r="I330" s="21"/>
     </row>
     <row r="331">
       <c r="C331" s="22"/>
       <c r="F331" s="9"/>
       <c r="G331" s="9"/>
-      <c r="H331" s="14"/>
+      <c r="H331" s="13"/>
       <c r="I331" s="21"/>
     </row>
     <row r="332">
       <c r="C332" s="22"/>
       <c r="F332" s="9"/>
       <c r="G332" s="9"/>
-      <c r="H332" s="14"/>
+      <c r="H332" s="13"/>
       <c r="I332" s="21"/>
     </row>
     <row r="333">
       <c r="C333" s="22"/>
       <c r="F333" s="9"/>
       <c r="G333" s="9"/>
-      <c r="H333" s="14"/>
+      <c r="H333" s="13"/>
       <c r="I333" s="21"/>
     </row>
     <row r="334">
       <c r="C334" s="22"/>
       <c r="F334" s="9"/>
       <c r="G334" s="9"/>
-      <c r="H334" s="14"/>
+      <c r="H334" s="13"/>
       <c r="I334" s="21"/>
     </row>
     <row r="335">
       <c r="C335" s="22"/>
       <c r="F335" s="9"/>
       <c r="G335" s="9"/>
-      <c r="H335" s="14"/>
+      <c r="H335" s="13"/>
       <c r="I335" s="21"/>
     </row>
     <row r="336">
       <c r="C336" s="22"/>
       <c r="F336" s="9"/>
       <c r="G336" s="9"/>
-      <c r="H336" s="14"/>
+      <c r="H336" s="13"/>
       <c r="I336" s="21"/>
     </row>
     <row r="337">
       <c r="C337" s="22"/>
       <c r="F337" s="9"/>
       <c r="G337" s="9"/>
-      <c r="H337" s="14"/>
+      <c r="H337" s="13"/>
       <c r="I337" s="21"/>
     </row>
     <row r="338">
       <c r="C338" s="22"/>
       <c r="F338" s="9"/>
       <c r="G338" s="9"/>
-      <c r="H338" s="14"/>
+      <c r="H338" s="13"/>
       <c r="I338" s="21"/>
     </row>
     <row r="339">
       <c r="C339" s="22"/>
       <c r="F339" s="9"/>
       <c r="G339" s="9"/>
-      <c r="H339" s="14"/>
+      <c r="H339" s="13"/>
       <c r="I339" s="21"/>
     </row>
     <row r="340">
       <c r="C340" s="22"/>
       <c r="F340" s="9"/>
       <c r="G340" s="9"/>
-      <c r="H340" s="14"/>
+      <c r="H340" s="13"/>
       <c r="I340" s="21"/>
     </row>
     <row r="341">
       <c r="C341" s="22"/>
       <c r="F341" s="9"/>
       <c r="G341" s="9"/>
-      <c r="H341" s="14"/>
+      <c r="H341" s="13"/>
       <c r="I341" s="21"/>
     </row>
     <row r="342">
       <c r="C342" s="22"/>
       <c r="F342" s="9"/>
       <c r="G342" s="9"/>
-      <c r="H342" s="14"/>
+      <c r="H342" s="13"/>
       <c r="I342" s="21"/>
     </row>
     <row r="343">
       <c r="C343" s="22"/>
       <c r="F343" s="9"/>
       <c r="G343" s="9"/>
-      <c r="H343" s="14"/>
+      <c r="H343" s="13"/>
       <c r="I343" s="21"/>
     </row>
     <row r="344">
       <c r="C344" s="22"/>
       <c r="F344" s="9"/>
       <c r="G344" s="9"/>
-      <c r="H344" s="14"/>
+      <c r="H344" s="13"/>
       <c r="I344" s="21"/>
     </row>
     <row r="345">
       <c r="C345" s="22"/>
       <c r="F345" s="9"/>
       <c r="G345" s="9"/>
-      <c r="H345" s="14"/>
+      <c r="H345" s="13"/>
       <c r="I345" s="21"/>
     </row>
     <row r="346">
       <c r="C346" s="22"/>
       <c r="F346" s="9"/>
       <c r="G346" s="9"/>
-      <c r="H346" s="14"/>
+      <c r="H346" s="13"/>
       <c r="I346" s="21"/>
     </row>
     <row r="347">
       <c r="C347" s="22"/>
       <c r="F347" s="9"/>
       <c r="G347" s="9"/>
-      <c r="H347" s="14"/>
+      <c r="H347" s="13"/>
       <c r="I347" s="21"/>
     </row>
     <row r="348">
       <c r="C348" s="22"/>
       <c r="F348" s="9"/>
       <c r="G348" s="9"/>
-      <c r="H348" s="14"/>
+      <c r="H348" s="13"/>
       <c r="I348" s="21"/>
     </row>
     <row r="349">
       <c r="C349" s="22"/>
       <c r="F349" s="9"/>
       <c r="G349" s="9"/>
-      <c r="H349" s="14"/>
+      <c r="H349" s="13"/>
       <c r="I349" s="21"/>
     </row>
     <row r="350">
       <c r="C350" s="22"/>
       <c r="F350" s="9"/>
       <c r="G350" s="9"/>
-      <c r="H350" s="14"/>
+      <c r="H350" s="13"/>
       <c r="I350" s="21"/>
     </row>
     <row r="351">
       <c r="C351" s="22"/>
       <c r="F351" s="9"/>
       <c r="G351" s="9"/>
-      <c r="H351" s="14"/>
+      <c r="H351" s="13"/>
       <c r="I351" s="21"/>
     </row>
     <row r="352">
       <c r="C352" s="22"/>
       <c r="F352" s="9"/>
       <c r="G352" s="9"/>
-      <c r="H352" s="14"/>
+      <c r="H352" s="13"/>
       <c r="I352" s="21"/>
     </row>
     <row r="353">
       <c r="C353" s="22"/>
       <c r="F353" s="9"/>
       <c r="G353" s="9"/>
-      <c r="H353" s="14"/>
+      <c r="H353" s="13"/>
       <c r="I353" s="21"/>
     </row>
     <row r="354">
       <c r="C354" s="22"/>
       <c r="F354" s="9"/>
       <c r="G354" s="9"/>
-      <c r="H354" s="14"/>
+      <c r="H354" s="13"/>
       <c r="I354" s="21"/>
     </row>
     <row r="355">
       <c r="C355" s="22"/>
       <c r="F355" s="9"/>
       <c r="G355" s="9"/>
-      <c r="H355" s="14"/>
+      <c r="H355" s="13"/>
       <c r="I355" s="21"/>
     </row>
     <row r="356">
       <c r="C356" s="22"/>
       <c r="F356" s="9"/>
       <c r="G356" s="9"/>
-      <c r="H356" s="14"/>
+      <c r="H356" s="13"/>
       <c r="I356" s="21"/>
     </row>
     <row r="357">
       <c r="C357" s="22"/>
       <c r="F357" s="9"/>
       <c r="G357" s="9"/>
-      <c r="H357" s="14"/>
+      <c r="H357" s="13"/>
       <c r="I357" s="21"/>
     </row>
     <row r="358">
       <c r="C358" s="22"/>
       <c r="F358" s="9"/>
       <c r="G358" s="9"/>
-      <c r="H358" s="14"/>
+      <c r="H358" s="13"/>
       <c r="I358" s="21"/>
     </row>
     <row r="359">
       <c r="C359" s="22"/>
       <c r="F359" s="9"/>
       <c r="G359" s="9"/>
-      <c r="H359" s="14"/>
+      <c r="H359" s="13"/>
       <c r="I359" s="21"/>
     </row>
     <row r="360">
       <c r="C360" s="22"/>
       <c r="F360" s="9"/>
       <c r="G360" s="9"/>
-      <c r="H360" s="14"/>
+      <c r="H360" s="13"/>
       <c r="I360" s="21"/>
     </row>
     <row r="361">
       <c r="C361" s="22"/>
       <c r="F361" s="9"/>
       <c r="G361" s="9"/>
-      <c r="H361" s="14"/>
+      <c r="H361" s="13"/>
       <c r="I361" s="21"/>
     </row>
     <row r="362">
       <c r="C362" s="22"/>
       <c r="F362" s="9"/>
       <c r="G362" s="9"/>
-      <c r="H362" s="14"/>
+      <c r="H362" s="13"/>
       <c r="I362" s="21"/>
     </row>
     <row r="363">
       <c r="C363" s="22"/>
       <c r="F363" s="9"/>
       <c r="G363" s="9"/>
-      <c r="H363" s="14"/>
+      <c r="H363" s="13"/>
       <c r="I363" s="21"/>
     </row>
     <row r="364">
       <c r="C364" s="22"/>
       <c r="F364" s="9"/>
       <c r="G364" s="9"/>
-      <c r="H364" s="14"/>
+      <c r="H364" s="13"/>
       <c r="I364" s="21"/>
     </row>
     <row r="365">
       <c r="C365" s="22"/>
       <c r="F365" s="9"/>
       <c r="G365" s="9"/>
-      <c r="H365" s="14"/>
+      <c r="H365" s="13"/>
       <c r="I365" s="21"/>
     </row>
     <row r="366">
       <c r="C366" s="22"/>
       <c r="F366" s="9"/>
       <c r="G366" s="9"/>
-      <c r="H366" s="14"/>
+      <c r="H366" s="13"/>
       <c r="I366" s="21"/>
     </row>
     <row r="367">
       <c r="C367" s="22"/>
       <c r="F367" s="9"/>
       <c r="G367" s="9"/>
-      <c r="H367" s="14"/>
+      <c r="H367" s="13"/>
       <c r="I367" s="21"/>
     </row>
     <row r="368">
       <c r="C368" s="22"/>
       <c r="F368" s="9"/>
       <c r="G368" s="9"/>
-      <c r="H368" s="14"/>
+      <c r="H368" s="13"/>
       <c r="I368" s="21"/>
     </row>
     <row r="369">
       <c r="C369" s="22"/>
       <c r="F369" s="9"/>
       <c r="G369" s="9"/>
-      <c r="H369" s="14"/>
+      <c r="H369" s="13"/>
       <c r="I369" s="21"/>
     </row>
     <row r="370">
       <c r="C370" s="22"/>
       <c r="F370" s="9"/>
       <c r="G370" s="9"/>
-      <c r="H370" s="14"/>
+      <c r="H370" s="13"/>
       <c r="I370" s="21"/>
     </row>
     <row r="371">
       <c r="C371" s="22"/>
       <c r="F371" s="9"/>
       <c r="G371" s="9"/>
-      <c r="H371" s="14"/>
+      <c r="H371" s="13"/>
       <c r="I371" s="21"/>
     </row>
     <row r="372">
       <c r="C372" s="22"/>
       <c r="F372" s="9"/>
       <c r="G372" s="9"/>
-      <c r="H372" s="14"/>
+      <c r="H372" s="13"/>
       <c r="I372" s="21"/>
     </row>
     <row r="373">
       <c r="C373" s="22"/>
       <c r="F373" s="9"/>
       <c r="G373" s="9"/>
-      <c r="H373" s="14"/>
+      <c r="H373" s="13"/>
       <c r="I373" s="21"/>
     </row>
     <row r="374">
       <c r="C374" s="22"/>
       <c r="F374" s="9"/>
       <c r="G374" s="9"/>
-      <c r="H374" s="14"/>
+      <c r="H374" s="13"/>
       <c r="I374" s="21"/>
     </row>
     <row r="375">
       <c r="C375" s="22"/>
       <c r="F375" s="9"/>
       <c r="G375" s="9"/>
-      <c r="H375" s="14"/>
+      <c r="H375" s="13"/>
       <c r="I375" s="21"/>
     </row>
     <row r="376">
       <c r="C376" s="22"/>
       <c r="F376" s="9"/>
       <c r="G376" s="9"/>
-      <c r="H376" s="14"/>
+      <c r="H376" s="13"/>
       <c r="I376" s="21"/>
     </row>
     <row r="377">
       <c r="C377" s="22"/>
       <c r="F377" s="9"/>
       <c r="G377" s="9"/>
-      <c r="H377" s="14"/>
+      <c r="H377" s="13"/>
       <c r="I377" s="21"/>
     </row>
     <row r="378">
       <c r="C378" s="22"/>
       <c r="F378" s="9"/>
       <c r="G378" s="9"/>
-      <c r="H378" s="14"/>
+      <c r="H378" s="13"/>
       <c r="I378" s="21"/>
     </row>
     <row r="379">
       <c r="C379" s="22"/>
       <c r="F379" s="9"/>
       <c r="G379" s="9"/>
-      <c r="H379" s="14"/>
+      <c r="H379" s="13"/>
       <c r="I379" s="21"/>
     </row>
     <row r="380">
       <c r="C380" s="22"/>
       <c r="F380" s="9"/>
       <c r="G380" s="9"/>
-      <c r="H380" s="14"/>
+      <c r="H380" s="13"/>
       <c r="I380" s="21"/>
     </row>
     <row r="381">
       <c r="C381" s="22"/>
       <c r="F381" s="9"/>
       <c r="G381" s="9"/>
-      <c r="H381" s="14"/>
+      <c r="H381" s="13"/>
       <c r="I381" s="21"/>
     </row>
     <row r="382">
       <c r="C382" s="22"/>
       <c r="F382" s="9"/>
       <c r="G382" s="9"/>
-      <c r="H382" s="14"/>
+      <c r="H382" s="13"/>
       <c r="I382" s="21"/>
     </row>
     <row r="383">
       <c r="C383" s="22"/>
       <c r="F383" s="9"/>
       <c r="G383" s="9"/>
-      <c r="H383" s="14"/>
+      <c r="H383" s="13"/>
       <c r="I383" s="21"/>
     </row>
     <row r="384">
       <c r="C384" s="22"/>
       <c r="F384" s="9"/>
       <c r="G384" s="9"/>
-      <c r="H384" s="14"/>
+      <c r="H384" s="13"/>
       <c r="I384" s="21"/>
     </row>
     <row r="385">
       <c r="C385" s="22"/>
       <c r="F385" s="9"/>
       <c r="G385" s="9"/>
-      <c r="H385" s="14"/>
+      <c r="H385" s="13"/>
       <c r="I385" s="21"/>
     </row>
     <row r="386">
       <c r="C386" s="22"/>
       <c r="F386" s="9"/>
       <c r="G386" s="9"/>
-      <c r="H386" s="14"/>
+      <c r="H386" s="13"/>
       <c r="I386" s="21"/>
     </row>
     <row r="387">
       <c r="C387" s="22"/>
       <c r="F387" s="9"/>
       <c r="G387" s="9"/>
-      <c r="H387" s="14"/>
+      <c r="H387" s="13"/>
       <c r="I387" s="21"/>
     </row>
     <row r="388">
       <c r="C388" s="22"/>
       <c r="F388" s="9"/>
       <c r="G388" s="9"/>
-      <c r="H388" s="14"/>
+      <c r="H388" s="13"/>
       <c r="I388" s="21"/>
     </row>
     <row r="389">
       <c r="C389" s="22"/>
       <c r="F389" s="9"/>
       <c r="G389" s="9"/>
-      <c r="H389" s="14"/>
+      <c r="H389" s="13"/>
       <c r="I389" s="21"/>
     </row>
     <row r="390">
       <c r="C390" s="22"/>
       <c r="F390" s="9"/>
       <c r="G390" s="9"/>
-      <c r="H390" s="14"/>
+      <c r="H390" s="13"/>
       <c r="I390" s="21"/>
     </row>
     <row r="391">
       <c r="C391" s="22"/>
       <c r="F391" s="9"/>
       <c r="G391" s="9"/>
-      <c r="H391" s="14"/>
+      <c r="H391" s="13"/>
       <c r="I391" s="21"/>
     </row>
     <row r="392">
       <c r="C392" s="22"/>
       <c r="F392" s="9"/>
       <c r="G392" s="9"/>
-      <c r="H392" s="14"/>
+      <c r="H392" s="13"/>
       <c r="I392" s="21"/>
     </row>
     <row r="393">
       <c r="C393" s="22"/>
       <c r="F393" s="9"/>
       <c r="G393" s="9"/>
-      <c r="H393" s="14"/>
+      <c r="H393" s="13"/>
       <c r="I393" s="21"/>
     </row>
     <row r="394">
       <c r="C394" s="22"/>
       <c r="F394" s="9"/>
       <c r="G394" s="9"/>
-      <c r="H394" s="14"/>
+      <c r="H394" s="13"/>
       <c r="I394" s="21"/>
     </row>
     <row r="395">
       <c r="C395" s="22"/>
       <c r="F395" s="9"/>
       <c r="G395" s="9"/>
-      <c r="H395" s="14"/>
+      <c r="H395" s="13"/>
       <c r="I395" s="21"/>
     </row>
     <row r="396">
       <c r="C396" s="22"/>
       <c r="F396" s="9"/>
       <c r="G396" s="9"/>
-      <c r="H396" s="14"/>
+      <c r="H396" s="13"/>
       <c r="I396" s="21"/>
     </row>
     <row r="397">
       <c r="C397" s="22"/>
       <c r="F397" s="9"/>
       <c r="G397" s="9"/>
-      <c r="H397" s="14"/>
+      <c r="H397" s="13"/>
       <c r="I397" s="21"/>
     </row>
     <row r="398">
       <c r="C398" s="22"/>
       <c r="F398" s="9"/>
       <c r="G398" s="9"/>
-      <c r="H398" s="14"/>
+      <c r="H398" s="13"/>
       <c r="I398" s="21"/>
     </row>
     <row r="399">
       <c r="C399" s="22"/>
       <c r="F399" s="9"/>
       <c r="G399" s="9"/>
-      <c r="H399" s="14"/>
+      <c r="H399" s="13"/>
       <c r="I399" s="21"/>
     </row>
     <row r="400">
       <c r="C400" s="22"/>
       <c r="F400" s="9"/>
       <c r="G400" s="9"/>
-      <c r="H400" s="14"/>
+      <c r="H400" s="13"/>
       <c r="I400" s="21"/>
     </row>
     <row r="401">
       <c r="C401" s="22"/>
       <c r="F401" s="9"/>
       <c r="G401" s="9"/>
-      <c r="H401" s="14"/>
+      <c r="H401" s="13"/>
       <c r="I401" s="21"/>
     </row>
     <row r="402">
       <c r="C402" s="22"/>
       <c r="F402" s="9"/>
       <c r="G402" s="9"/>
-      <c r="H402" s="14"/>
+      <c r="H402" s="13"/>
       <c r="I402" s="21"/>
     </row>
     <row r="403">
       <c r="C403" s="22"/>
       <c r="F403" s="9"/>
       <c r="G403" s="9"/>
-      <c r="H403" s="14"/>
+      <c r="H403" s="13"/>
       <c r="I403" s="21"/>
     </row>
     <row r="404">
       <c r="C404" s="22"/>
       <c r="F404" s="9"/>
       <c r="G404" s="9"/>
-      <c r="H404" s="14"/>
+      <c r="H404" s="13"/>
       <c r="I404" s="21"/>
     </row>
     <row r="405">
       <c r="C405" s="22"/>
       <c r="F405" s="9"/>
       <c r="G405" s="9"/>
-      <c r="H405" s="14"/>
+      <c r="H405" s="13"/>
       <c r="I405" s="21"/>
     </row>
     <row r="406">
       <c r="C406" s="22"/>
       <c r="F406" s="9"/>
       <c r="G406" s="9"/>
-      <c r="H406" s="14"/>
+      <c r="H406" s="13"/>
       <c r="I406" s="21"/>
     </row>
     <row r="407">
       <c r="C407" s="22"/>
       <c r="F407" s="9"/>
       <c r="G407" s="9"/>
-      <c r="H407" s="14"/>
+      <c r="H407" s="13"/>
       <c r="I407" s="21"/>
     </row>
     <row r="408">
       <c r="C408" s="22"/>
       <c r="F408" s="9"/>
       <c r="G408" s="9"/>
-      <c r="H408" s="14"/>
+      <c r="H408" s="13"/>
       <c r="I408" s="21"/>
     </row>
     <row r="409">
       <c r="C409" s="22"/>
       <c r="F409" s="9"/>
       <c r="G409" s="9"/>
-      <c r="H409" s="14"/>
+      <c r="H409" s="13"/>
       <c r="I409" s="21"/>
     </row>
     <row r="410">
       <c r="C410" s="22"/>
       <c r="F410" s="9"/>
       <c r="G410" s="9"/>
-      <c r="H410" s="14"/>
+      <c r="H410" s="13"/>
       <c r="I410" s="21"/>
     </row>
     <row r="411">
       <c r="C411" s="22"/>
       <c r="F411" s="9"/>
       <c r="G411" s="9"/>
-      <c r="H411" s="14"/>
+      <c r="H411" s="13"/>
       <c r="I411" s="21"/>
     </row>
     <row r="412">
       <c r="C412" s="22"/>
       <c r="F412" s="9"/>
       <c r="G412" s="9"/>
-      <c r="H412" s="14"/>
+      <c r="H412" s="13"/>
       <c r="I412" s="21"/>
     </row>
     <row r="413">
       <c r="C413" s="22"/>
       <c r="F413" s="9"/>
       <c r="G413" s="9"/>
-      <c r="H413" s="14"/>
+      <c r="H413" s="13"/>
       <c r="I413" s="21"/>
     </row>
     <row r="414">
       <c r="C414" s="22"/>
       <c r="F414" s="9"/>
       <c r="G414" s="9"/>
-      <c r="H414" s="14"/>
+      <c r="H414" s="13"/>
       <c r="I414" s="21"/>
     </row>
     <row r="415">
       <c r="C415" s="22"/>
       <c r="F415" s="9"/>
       <c r="G415" s="9"/>
-      <c r="H415" s="14"/>
+      <c r="H415" s="13"/>
       <c r="I415" s="21"/>
     </row>
     <row r="416">
       <c r="C416" s="22"/>
       <c r="F416" s="9"/>
       <c r="G416" s="9"/>
-      <c r="H416" s="14"/>
+      <c r="H416" s="13"/>
       <c r="I416" s="21"/>
     </row>
     <row r="417">
       <c r="C417" s="22"/>
       <c r="F417" s="9"/>
       <c r="G417" s="9"/>
-      <c r="H417" s="14"/>
+      <c r="H417" s="13"/>
       <c r="I417" s="21"/>
     </row>
     <row r="418">
       <c r="C418" s="22"/>
       <c r="F418" s="9"/>
       <c r="G418" s="9"/>
-      <c r="H418" s="14"/>
+      <c r="H418" s="13"/>
       <c r="I418" s="21"/>
     </row>
     <row r="419">
       <c r="C419" s="22"/>
       <c r="F419" s="9"/>
       <c r="G419" s="9"/>
-      <c r="H419" s="14"/>
+      <c r="H419" s="13"/>
       <c r="I419" s="21"/>
     </row>
     <row r="420">
       <c r="C420" s="22"/>
       <c r="F420" s="9"/>
       <c r="G420" s="9"/>
-      <c r="H420" s="14"/>
+      <c r="H420" s="13"/>
       <c r="I420" s="21"/>
     </row>
     <row r="421">
       <c r="C421" s="22"/>
       <c r="F421" s="9"/>
       <c r="G421" s="9"/>
-      <c r="H421" s="14"/>
+      <c r="H421" s="13"/>
       <c r="I421" s="21"/>
     </row>
     <row r="422">
       <c r="C422" s="22"/>
       <c r="F422" s="9"/>
       <c r="G422" s="9"/>
-      <c r="H422" s="14"/>
+      <c r="H422" s="13"/>
       <c r="I422" s="21"/>
     </row>
     <row r="423">
       <c r="C423" s="22"/>
       <c r="F423" s="9"/>
       <c r="G423" s="9"/>
-      <c r="H423" s="14"/>
+      <c r="H423" s="13"/>
       <c r="I423" s="21"/>
     </row>
     <row r="424">
       <c r="C424" s="22"/>
       <c r="F424" s="9"/>
       <c r="G424" s="9"/>
-      <c r="H424" s="14"/>
+      <c r="H424" s="13"/>
       <c r="I424" s="21"/>
     </row>
     <row r="425">
       <c r="C425" s="22"/>
       <c r="F425" s="9"/>
       <c r="G425" s="9"/>
-      <c r="H425" s="14"/>
+      <c r="H425" s="13"/>
       <c r="I425" s="21"/>
     </row>
     <row r="426">
       <c r="C426" s="22"/>
       <c r="F426" s="9"/>
       <c r="G426" s="9"/>
-      <c r="H426" s="14"/>
+      <c r="H426" s="13"/>
       <c r="I426" s="21"/>
     </row>
     <row r="427">
       <c r="C427" s="22"/>
       <c r="F427" s="9"/>
       <c r="G427" s="9"/>
-      <c r="H427" s="14"/>
+      <c r="H427" s="13"/>
       <c r="I427" s="21"/>
     </row>
     <row r="428">
       <c r="C428" s="22"/>
       <c r="F428" s="9"/>
       <c r="G428" s="9"/>
-      <c r="H428" s="14"/>
+      <c r="H428" s="13"/>
       <c r="I428" s="21"/>
     </row>
     <row r="429">
       <c r="C429" s="22"/>
       <c r="F429" s="9"/>
       <c r="G429" s="9"/>
-      <c r="H429" s="14"/>
+      <c r="H429" s="13"/>
       <c r="I429" s="21"/>
     </row>
     <row r="430">
       <c r="C430" s="22"/>
       <c r="F430" s="9"/>
       <c r="G430" s="9"/>
-      <c r="H430" s="14"/>
+      <c r="H430" s="13"/>
       <c r="I430" s="21"/>
     </row>
     <row r="431">
       <c r="C431" s="22"/>
       <c r="F431" s="9"/>
       <c r="G431" s="9"/>
-      <c r="H431" s="14"/>
+      <c r="H431" s="13"/>
       <c r="I431" s="21"/>
     </row>
     <row r="432">
       <c r="C432" s="22"/>
       <c r="F432" s="9"/>
       <c r="G432" s="9"/>
-      <c r="H432" s="14"/>
+      <c r="H432" s="13"/>
       <c r="I432" s="21"/>
     </row>
     <row r="433">
       <c r="C433" s="22"/>
       <c r="F433" s="9"/>
       <c r="G433" s="9"/>
-      <c r="H433" s="14"/>
+      <c r="H433" s="13"/>
       <c r="I433" s="21"/>
     </row>
     <row r="434">
       <c r="C434" s="22"/>
       <c r="F434" s="9"/>
       <c r="G434" s="9"/>
-      <c r="H434" s="14"/>
+      <c r="H434" s="13"/>
       <c r="I434" s="21"/>
     </row>
     <row r="435">
       <c r="C435" s="22"/>
       <c r="F435" s="9"/>
       <c r="G435" s="9"/>
-      <c r="H435" s="14"/>
+      <c r="H435" s="13"/>
       <c r="I435" s="21"/>
     </row>
     <row r="436">
       <c r="C436" s="22"/>
       <c r="F436" s="9"/>
       <c r="G436" s="9"/>
-      <c r="H436" s="14"/>
+      <c r="H436" s="13"/>
       <c r="I436" s="21"/>
     </row>
     <row r="437">
       <c r="C437" s="22"/>
       <c r="F437" s="9"/>
       <c r="G437" s="9"/>
-      <c r="H437" s="14"/>
+      <c r="H437" s="13"/>
       <c r="I437" s="21"/>
     </row>
     <row r="438">
       <c r="C438" s="22"/>
       <c r="F438" s="9"/>
       <c r="G438" s="9"/>
-      <c r="H438" s="14"/>
+      <c r="H438" s="13"/>
       <c r="I438" s="21"/>
     </row>
     <row r="439">
       <c r="C439" s="22"/>
       <c r="F439" s="9"/>
       <c r="G439" s="9"/>
-      <c r="H439" s="14"/>
+      <c r="H439" s="13"/>
       <c r="I439" s="21"/>
     </row>
     <row r="440">
       <c r="C440" s="22"/>
       <c r="F440" s="9"/>
       <c r="G440" s="9"/>
-      <c r="H440" s="14"/>
+      <c r="H440" s="13"/>
       <c r="I440" s="21"/>
     </row>
     <row r="441">
       <c r="C441" s="22"/>
       <c r="F441" s="9"/>
       <c r="G441" s="9"/>
-      <c r="H441" s="14"/>
+      <c r="H441" s="13"/>
       <c r="I441" s="21"/>
     </row>
     <row r="442">
       <c r="C442" s="22"/>
       <c r="F442" s="9"/>
       <c r="G442" s="9"/>
-      <c r="H442" s="14"/>
+      <c r="H442" s="13"/>
       <c r="I442" s="21"/>
     </row>
     <row r="443">
       <c r="C443" s="22"/>
       <c r="F443" s="9"/>
       <c r="G443" s="9"/>
-      <c r="H443" s="14"/>
+      <c r="H443" s="13"/>
       <c r="I443" s="21"/>
     </row>
     <row r="444">
       <c r="C444" s="22"/>
       <c r="F444" s="9"/>
       <c r="G444" s="9"/>
-      <c r="H444" s="14"/>
+      <c r="H444" s="13"/>
       <c r="I444" s="21"/>
     </row>
     <row r="445">
       <c r="C445" s="22"/>
       <c r="F445" s="9"/>
       <c r="G445" s="9"/>
-      <c r="H445" s="14"/>
+      <c r="H445" s="13"/>
       <c r="I445" s="21"/>
     </row>
     <row r="446">
       <c r="C446" s="22"/>
       <c r="F446" s="9"/>
       <c r="G446" s="9"/>
-      <c r="H446" s="14"/>
+      <c r="H446" s="13"/>
       <c r="I446" s="21"/>
     </row>
     <row r="447">
       <c r="C447" s="22"/>
       <c r="F447" s="9"/>
       <c r="G447" s="9"/>
-      <c r="H447" s="14"/>
+      <c r="H447" s="13"/>
       <c r="I447" s="21"/>
     </row>
     <row r="448">
       <c r="C448" s="22"/>
       <c r="F448" s="9"/>
       <c r="G448" s="9"/>
-      <c r="H448" s="14"/>
+      <c r="H448" s="13"/>
       <c r="I448" s="21"/>
     </row>
     <row r="449">
       <c r="C449" s="22"/>
       <c r="F449" s="9"/>
       <c r="G449" s="9"/>
-      <c r="H449" s="14"/>
+      <c r="H449" s="13"/>
       <c r="I449" s="21"/>
     </row>
     <row r="450">
       <c r="C450" s="22"/>
       <c r="F450" s="9"/>
       <c r="G450" s="9"/>
-      <c r="H450" s="14"/>
+      <c r="H450" s="13"/>
       <c r="I450" s="21"/>
     </row>
     <row r="451">
       <c r="C451" s="22"/>
       <c r="F451" s="9"/>
       <c r="G451" s="9"/>
-      <c r="H451" s="14"/>
+      <c r="H451" s="13"/>
       <c r="I451" s="21"/>
     </row>
     <row r="452">
       <c r="C452" s="22"/>
       <c r="F452" s="9"/>
       <c r="G452" s="9"/>
-      <c r="H452" s="14"/>
+      <c r="H452" s="13"/>
       <c r="I452" s="21"/>
     </row>
     <row r="453">
       <c r="C453" s="22"/>
       <c r="F453" s="9"/>
       <c r="G453" s="9"/>
-      <c r="H453" s="14"/>
+      <c r="H453" s="13"/>
       <c r="I453" s="21"/>
     </row>
     <row r="454">
       <c r="C454" s="22"/>
       <c r="F454" s="9"/>
       <c r="G454" s="9"/>
-      <c r="H454" s="14"/>
+      <c r="H454" s="13"/>
       <c r="I454" s="21"/>
     </row>
     <row r="455">
       <c r="C455" s="22"/>
       <c r="F455" s="9"/>
       <c r="G455" s="9"/>
-      <c r="H455" s="14"/>
+      <c r="H455" s="13"/>
       <c r="I455" s="21"/>
     </row>
     <row r="456">
       <c r="C456" s="22"/>
       <c r="F456" s="9"/>
       <c r="G456" s="9"/>
-      <c r="H456" s="14"/>
+      <c r="H456" s="13"/>
       <c r="I456" s="21"/>
     </row>
     <row r="457">
       <c r="C457" s="22"/>
       <c r="F457" s="9"/>
       <c r="G457" s="9"/>
-      <c r="H457" s="14"/>
+      <c r="H457" s="13"/>
       <c r="I457" s="21"/>
     </row>
     <row r="458">
       <c r="C458" s="22"/>
       <c r="F458" s="9"/>
       <c r="G458" s="9"/>
-      <c r="H458" s="14"/>
+      <c r="H458" s="13"/>
       <c r="I458" s="21"/>
     </row>
     <row r="459">
       <c r="C459" s="22"/>
       <c r="F459" s="9"/>
       <c r="G459" s="9"/>
-      <c r="H459" s="14"/>
+      <c r="H459" s="13"/>
       <c r="I459" s="21"/>
     </row>
     <row r="460">
       <c r="C460" s="22"/>
       <c r="F460" s="9"/>
       <c r="G460" s="9"/>
-      <c r="H460" s="14"/>
+      <c r="H460" s="13"/>
       <c r="I460" s="21"/>
     </row>
     <row r="461">
       <c r="C461" s="22"/>
       <c r="F461" s="9"/>
       <c r="G461" s="9"/>
-      <c r="H461" s="14"/>
+      <c r="H461" s="13"/>
       <c r="I461" s="21"/>
     </row>
     <row r="462">
       <c r="C462" s="22"/>
       <c r="F462" s="9"/>
       <c r="G462" s="9"/>
-      <c r="H462" s="14"/>
+      <c r="H462" s="13"/>
       <c r="I462" s="21"/>
     </row>
     <row r="463">
       <c r="C463" s="22"/>
       <c r="F463" s="9"/>
       <c r="G463" s="9"/>
-      <c r="H463" s="14"/>
+      <c r="H463" s="13"/>
       <c r="I463" s="21"/>
     </row>
     <row r="464">
       <c r="C464" s="22"/>
       <c r="F464" s="9"/>
       <c r="G464" s="9"/>
-      <c r="H464" s="14"/>
+      <c r="H464" s="13"/>
       <c r="I464" s="21"/>
     </row>
     <row r="465">
       <c r="C465" s="22"/>
       <c r="F465" s="9"/>
       <c r="G465" s="9"/>
-      <c r="H465" s="14"/>
+      <c r="H465" s="13"/>
       <c r="I465" s="21"/>
     </row>
     <row r="466">
       <c r="C466" s="22"/>
       <c r="F466" s="9"/>
       <c r="G466" s="9"/>
-      <c r="H466" s="14"/>
+      <c r="H466" s="13"/>
       <c r="I466" s="21"/>
     </row>
     <row r="467">
       <c r="C467" s="22"/>
       <c r="F467" s="9"/>
       <c r="G467" s="9"/>
-      <c r="H467" s="14"/>
+      <c r="H467" s="13"/>
       <c r="I467" s="21"/>
     </row>
     <row r="468">
       <c r="C468" s="22"/>
       <c r="F468" s="9"/>
       <c r="G468" s="9"/>
-      <c r="H468" s="14"/>
+      <c r="H468" s="13"/>
       <c r="I468" s="21"/>
     </row>
     <row r="469">
       <c r="C469" s="22"/>
       <c r="F469" s="9"/>
       <c r="G469" s="9"/>
-      <c r="H469" s="14"/>
+      <c r="H469" s="13"/>
       <c r="I469" s="21"/>
     </row>
     <row r="470">
       <c r="C470" s="22"/>
       <c r="F470" s="9"/>
       <c r="G470" s="9"/>
-      <c r="H470" s="14"/>
+      <c r="H470" s="13"/>
       <c r="I470" s="21"/>
     </row>
     <row r="471">
       <c r="C471" s="22"/>
       <c r="F471" s="9"/>
       <c r="G471" s="9"/>
-      <c r="H471" s="14"/>
+      <c r="H471" s="13"/>
       <c r="I471" s="21"/>
     </row>
     <row r="472">
       <c r="C472" s="22"/>
       <c r="F472" s="9"/>
       <c r="G472" s="9"/>
-      <c r="H472" s="14"/>
+      <c r="H472" s="13"/>
       <c r="I472" s="21"/>
     </row>
     <row r="473">
       <c r="C473" s="22"/>
       <c r="F473" s="9"/>
       <c r="G473" s="9"/>
-      <c r="H473" s="14"/>
+      <c r="H473" s="13"/>
       <c r="I473" s="21"/>
     </row>
     <row r="474">
       <c r="C474" s="22"/>
       <c r="F474" s="9"/>
       <c r="G474" s="9"/>
-      <c r="H474" s="14"/>
+      <c r="H474" s="13"/>
       <c r="I474" s="21"/>
     </row>
     <row r="475">
       <c r="C475" s="22"/>
       <c r="F475" s="9"/>
       <c r="G475" s="9"/>
-      <c r="H475" s="14"/>
+      <c r="H475" s="13"/>
       <c r="I475" s="21"/>
     </row>
     <row r="476">
       <c r="C476" s="22"/>
       <c r="F476" s="9"/>
       <c r="G476" s="9"/>
-      <c r="H476" s="14"/>
+      <c r="H476" s="13"/>
       <c r="I476" s="21"/>
     </row>
     <row r="477">
       <c r="C477" s="22"/>
       <c r="F477" s="9"/>
       <c r="G477" s="9"/>
-      <c r="H477" s="14"/>
+      <c r="H477" s="13"/>
       <c r="I477" s="21"/>
     </row>
     <row r="478">
       <c r="C478" s="22"/>
       <c r="F478" s="9"/>
       <c r="G478" s="9"/>
-      <c r="H478" s="14"/>
+      <c r="H478" s="13"/>
       <c r="I478" s="21"/>
     </row>
     <row r="479">
       <c r="C479" s="22"/>
       <c r="F479" s="9"/>
       <c r="G479" s="9"/>
-      <c r="H479" s="14"/>
+      <c r="H479" s="13"/>
       <c r="I479" s="21"/>
     </row>
     <row r="480">
       <c r="C480" s="22"/>
       <c r="F480" s="9"/>
       <c r="G480" s="9"/>
-      <c r="H480" s="14"/>
+      <c r="H480" s="13"/>
       <c r="I480" s="21"/>
     </row>
     <row r="481">
       <c r="C481" s="22"/>
       <c r="F481" s="9"/>
       <c r="G481" s="9"/>
-      <c r="H481" s="14"/>
+      <c r="H481" s="13"/>
       <c r="I481" s="21"/>
     </row>
     <row r="482">
       <c r="C482" s="22"/>
       <c r="F482" s="9"/>
       <c r="G482" s="9"/>
-      <c r="H482" s="14"/>
+      <c r="H482" s="13"/>
       <c r="I482" s="21"/>
     </row>
     <row r="483">
       <c r="C483" s="22"/>
       <c r="F483" s="9"/>
       <c r="G483" s="9"/>
-      <c r="H483" s="14"/>
+      <c r="H483" s="13"/>
       <c r="I483" s="21"/>
     </row>
     <row r="484">
       <c r="C484" s="22"/>
       <c r="F484" s="9"/>
       <c r="G484" s="9"/>
-      <c r="H484" s="14"/>
+      <c r="H484" s="13"/>
       <c r="I484" s="21"/>
     </row>
     <row r="485">
       <c r="C485" s="22"/>
       <c r="F485" s="9"/>
       <c r="G485" s="9"/>
-      <c r="H485" s="14"/>
+      <c r="H485" s="13"/>
       <c r="I485" s="21"/>
     </row>
     <row r="486">
       <c r="C486" s="22"/>
       <c r="F486" s="9"/>
       <c r="G486" s="9"/>
-      <c r="H486" s="14"/>
+      <c r="H486" s="13"/>
       <c r="I486" s="21"/>
     </row>
     <row r="487">
       <c r="C487" s="22"/>
       <c r="F487" s="9"/>
       <c r="G487" s="9"/>
-      <c r="H487" s="14"/>
+      <c r="H487" s="13"/>
       <c r="I487" s="21"/>
     </row>
     <row r="488">
       <c r="C488" s="22"/>
       <c r="F488" s="9"/>
       <c r="G488" s="9"/>
-      <c r="H488" s="14"/>
+      <c r="H488" s="13"/>
       <c r="I488" s="21"/>
     </row>
     <row r="489">
       <c r="C489" s="22"/>
       <c r="F489" s="9"/>
       <c r="G489" s="9"/>
-      <c r="H489" s="14"/>
+      <c r="H489" s="13"/>
       <c r="I489" s="21"/>
     </row>
     <row r="490">
       <c r="C490" s="22"/>
       <c r="F490" s="9"/>
       <c r="G490" s="9"/>
-      <c r="H490" s="14"/>
+      <c r="H490" s="13"/>
       <c r="I490" s="21"/>
     </row>
     <row r="491">
       <c r="C491" s="22"/>
       <c r="F491" s="9"/>
       <c r="G491" s="9"/>
-      <c r="H491" s="14"/>
+      <c r="H491" s="13"/>
       <c r="I491" s="21"/>
     </row>
     <row r="492">
       <c r="C492" s="22"/>
       <c r="F492" s="9"/>
       <c r="G492" s="9"/>
-      <c r="H492" s="14"/>
+      <c r="H492" s="13"/>
       <c r="I492" s="21"/>
     </row>
     <row r="493">
       <c r="C493" s="22"/>
       <c r="F493" s="9"/>
       <c r="G493" s="9"/>
-      <c r="H493" s="14"/>
+      <c r="H493" s="13"/>
       <c r="I493" s="21"/>
     </row>
     <row r="494">
       <c r="C494" s="22"/>
       <c r="F494" s="9"/>
       <c r="G494" s="9"/>
-      <c r="H494" s="14"/>
+      <c r="H494" s="13"/>
       <c r="I494" s="21"/>
     </row>
     <row r="495">
       <c r="C495" s="22"/>
       <c r="F495" s="9"/>
       <c r="G495" s="9"/>
-      <c r="H495" s="14"/>
+      <c r="H495" s="13"/>
       <c r="I495" s="21"/>
     </row>
     <row r="496">
       <c r="C496" s="22"/>
       <c r="F496" s="9"/>
       <c r="G496" s="9"/>
-      <c r="H496" s="14"/>
+      <c r="H496" s="13"/>
       <c r="I496" s="21"/>
     </row>
     <row r="497">
       <c r="C497" s="22"/>
       <c r="F497" s="9"/>
       <c r="G497" s="9"/>
-      <c r="H497" s="14"/>
+      <c r="H497" s="13"/>
       <c r="I497" s="21"/>
     </row>
     <row r="498">
       <c r="C498" s="22"/>
       <c r="F498" s="9"/>
       <c r="G498" s="9"/>
-      <c r="H498" s="14"/>
+      <c r="H498" s="13"/>
       <c r="I498" s="21"/>
     </row>
     <row r="499">
       <c r="C499" s="22"/>
       <c r="F499" s="9"/>
       <c r="G499" s="9"/>
-      <c r="H499" s="14"/>
+      <c r="H499" s="13"/>
       <c r="I499" s="21"/>
     </row>
     <row r="500">
       <c r="C500" s="22"/>
       <c r="F500" s="9"/>
       <c r="G500" s="9"/>
-      <c r="H500" s="14"/>
+      <c r="H500" s="13"/>
       <c r="I500" s="21"/>
     </row>
     <row r="501">
       <c r="C501" s="22"/>
       <c r="F501" s="9"/>
       <c r="G501" s="9"/>
-      <c r="H501" s="14"/>
+      <c r="H501" s="13"/>
       <c r="I501" s="21"/>
     </row>
     <row r="502">
       <c r="C502" s="22"/>
       <c r="F502" s="9"/>
       <c r="G502" s="9"/>
-      <c r="H502" s="14"/>
+      <c r="H502" s="13"/>
       <c r="I502" s="21"/>
     </row>
     <row r="503">
       <c r="C503" s="22"/>
       <c r="F503" s="9"/>
       <c r="G503" s="9"/>
-      <c r="H503" s="14"/>
+      <c r="H503" s="13"/>
       <c r="I503" s="21"/>
     </row>
     <row r="504">
       <c r="C504" s="22"/>
       <c r="F504" s="9"/>
       <c r="G504" s="9"/>
-      <c r="H504" s="14"/>
+      <c r="H504" s="13"/>
       <c r="I504" s="21"/>
     </row>
     <row r="505">
       <c r="C505" s="22"/>
       <c r="F505" s="9"/>
       <c r="G505" s="9"/>
-      <c r="H505" s="14"/>
+      <c r="H505" s="13"/>
       <c r="I505" s="21"/>
     </row>
     <row r="506">
       <c r="C506" s="22"/>
       <c r="F506" s="9"/>
       <c r="G506" s="9"/>
-      <c r="H506" s="14"/>
+      <c r="H506" s="13"/>
       <c r="I506" s="21"/>
     </row>
     <row r="507">
       <c r="C507" s="22"/>
       <c r="F507" s="9"/>
       <c r="G507" s="9"/>
-      <c r="H507" s="14"/>
+      <c r="H507" s="13"/>
       <c r="I507" s="21"/>
     </row>
     <row r="508">
       <c r="C508" s="22"/>
       <c r="F508" s="9"/>
       <c r="G508" s="9"/>
-      <c r="H508" s="14"/>
+      <c r="H508" s="13"/>
       <c r="I508" s="21"/>
     </row>
     <row r="509">
       <c r="C509" s="22"/>
       <c r="F509" s="9"/>
       <c r="G509" s="9"/>
-      <c r="H509" s="14"/>
+      <c r="H509" s="13"/>
       <c r="I509" s="21"/>
     </row>
     <row r="510">
       <c r="C510" s="22"/>
       <c r="F510" s="9"/>
       <c r="G510" s="9"/>
-      <c r="H510" s="14"/>
+      <c r="H510" s="13"/>
       <c r="I510" s="21"/>
     </row>
     <row r="511">
       <c r="C511" s="22"/>
       <c r="F511" s="9"/>
       <c r="G511" s="9"/>
-      <c r="H511" s="14"/>
+      <c r="H511" s="13"/>
       <c r="I511" s="21"/>
     </row>
     <row r="512">
       <c r="C512" s="22"/>
       <c r="F512" s="9"/>
       <c r="G512" s="9"/>
-      <c r="H512" s="14"/>
+      <c r="H512" s="13"/>
       <c r="I512" s="21"/>
     </row>
     <row r="513">
       <c r="C513" s="22"/>
       <c r="F513" s="9"/>
       <c r="G513" s="9"/>
-      <c r="H513" s="14"/>
+      <c r="H513" s="13"/>
       <c r="I513" s="21"/>
     </row>
     <row r="514">
       <c r="C514" s="22"/>
       <c r="F514" s="9"/>
       <c r="G514" s="9"/>
-      <c r="H514" s="14"/>
+      <c r="H514" s="13"/>
       <c r="I514" s="21"/>
     </row>
     <row r="515">
       <c r="C515" s="22"/>
       <c r="F515" s="9"/>
       <c r="G515" s="9"/>
-      <c r="H515" s="14"/>
+      <c r="H515" s="13"/>
       <c r="I515" s="21"/>
     </row>
     <row r="516">
       <c r="C516" s="22"/>
       <c r="F516" s="9"/>
       <c r="G516" s="9"/>
-      <c r="H516" s="14"/>
+      <c r="H516" s="13"/>
       <c r="I516" s="21"/>
     </row>
     <row r="517">
       <c r="C517" s="22"/>
       <c r="F517" s="9"/>
       <c r="G517" s="9"/>
-      <c r="H517" s="14"/>
+      <c r="H517" s="13"/>
       <c r="I517" s="21"/>
     </row>
     <row r="518">
       <c r="C518" s="22"/>
       <c r="F518" s="9"/>
       <c r="G518" s="9"/>
-      <c r="H518" s="14"/>
+      <c r="H518" s="13"/>
       <c r="I518" s="21"/>
     </row>
     <row r="519">
       <c r="C519" s="22"/>
       <c r="F519" s="9"/>
       <c r="G519" s="9"/>
-      <c r="H519" s="14"/>
+      <c r="H519" s="13"/>
       <c r="I519" s="21"/>
     </row>
     <row r="520">
       <c r="C520" s="22"/>
       <c r="F520" s="9"/>
       <c r="G520" s="9"/>
-      <c r="H520" s="14"/>
+      <c r="H520" s="13"/>
       <c r="I520" s="21"/>
     </row>
     <row r="521">
       <c r="C521" s="22"/>
       <c r="F521" s="9"/>
       <c r="G521" s="9"/>
-      <c r="H521" s="14"/>
+      <c r="H521" s="13"/>
       <c r="I521" s="21"/>
     </row>
     <row r="522">
       <c r="C522" s="22"/>
       <c r="F522" s="9"/>
       <c r="G522" s="9"/>
-      <c r="H522" s="14"/>
+      <c r="H522" s="13"/>
       <c r="I522" s="21"/>
     </row>
     <row r="523">
       <c r="C523" s="22"/>
       <c r="F523" s="9"/>
       <c r="G523" s="9"/>
-      <c r="H523" s="14"/>
+      <c r="H523" s="13"/>
       <c r="I523" s="21"/>
     </row>
     <row r="524">
       <c r="C524" s="22"/>
       <c r="F524" s="9"/>
       <c r="G524" s="9"/>
-      <c r="H524" s="14"/>
+      <c r="H524" s="13"/>
       <c r="I524" s="21"/>
     </row>
     <row r="525">
       <c r="C525" s="22"/>
       <c r="F525" s="9"/>
       <c r="G525" s="9"/>
-      <c r="H525" s="14"/>
+      <c r="H525" s="13"/>
       <c r="I525" s="21"/>
     </row>
     <row r="526">
       <c r="C526" s="22"/>
       <c r="F526" s="9"/>
       <c r="G526" s="9"/>
-      <c r="H526" s="14"/>
+      <c r="H526" s="13"/>
       <c r="I526" s="21"/>
     </row>
     <row r="527">
       <c r="C527" s="22"/>
       <c r="F527" s="9"/>
       <c r="G527" s="9"/>
-      <c r="H527" s="14"/>
+      <c r="H527" s="13"/>
       <c r="I527" s="21"/>
     </row>
     <row r="528">
       <c r="C528" s="22"/>
       <c r="F528" s="9"/>
       <c r="G528" s="9"/>
-      <c r="H528" s="14"/>
+      <c r="H528" s="13"/>
       <c r="I528" s="21"/>
     </row>
     <row r="529">
       <c r="C529" s="22"/>
       <c r="F529" s="9"/>
       <c r="G529" s="9"/>
-      <c r="H529" s="14"/>
+      <c r="H529" s="13"/>
       <c r="I529" s="21"/>
     </row>
     <row r="530">
       <c r="C530" s="22"/>
       <c r="F530" s="9"/>
       <c r="G530" s="9"/>
-      <c r="H530" s="14"/>
+      <c r="H530" s="13"/>
       <c r="I530" s="21"/>
     </row>
     <row r="531">
       <c r="C531" s="22"/>
       <c r="F531" s="9"/>
       <c r="G531" s="9"/>
-      <c r="H531" s="14"/>
+      <c r="H531" s="13"/>
       <c r="I531" s="21"/>
     </row>
     <row r="532">
       <c r="C532" s="22"/>
       <c r="F532" s="9"/>
       <c r="G532" s="9"/>
-      <c r="H532" s="14"/>
+      <c r="H532" s="13"/>
       <c r="I532" s="21"/>
     </row>
     <row r="533">
       <c r="C533" s="22"/>
       <c r="F533" s="9"/>
       <c r="G533" s="9"/>
-      <c r="H533" s="14"/>
+      <c r="H533" s="13"/>
       <c r="I533" s="21"/>
     </row>
     <row r="534">
       <c r="C534" s="22"/>
       <c r="F534" s="9"/>
       <c r="G534" s="9"/>
-      <c r="H534" s="14"/>
+      <c r="H534" s="13"/>
       <c r="I534" s="21"/>
     </row>
     <row r="535">
       <c r="C535" s="22"/>
       <c r="F535" s="9"/>
       <c r="G535" s="9"/>
-      <c r="H535" s="14"/>
+      <c r="H535" s="13"/>
       <c r="I535" s="21"/>
     </row>
     <row r="536">
       <c r="C536" s="22"/>
       <c r="F536" s="9"/>
       <c r="G536" s="9"/>
-      <c r="H536" s="14"/>
+      <c r="H536" s="13"/>
       <c r="I536" s="21"/>
     </row>
     <row r="537">
       <c r="C537" s="22"/>
       <c r="F537" s="9"/>
       <c r="G537" s="9"/>
-      <c r="H537" s="14"/>
+      <c r="H537" s="13"/>
       <c r="I537" s="21"/>
     </row>
     <row r="538">
       <c r="C538" s="22"/>
       <c r="F538" s="9"/>
       <c r="G538" s="9"/>
-      <c r="H538" s="14"/>
+      <c r="H538" s="13"/>
       <c r="I538" s="21"/>
     </row>
     <row r="539">
       <c r="C539" s="22"/>
       <c r="F539" s="9"/>
       <c r="G539" s="9"/>
-      <c r="H539" s="14"/>
+      <c r="H539" s="13"/>
       <c r="I539" s="21"/>
     </row>
     <row r="540">
       <c r="C540" s="22"/>
       <c r="F540" s="9"/>
       <c r="G540" s="9"/>
-      <c r="H540" s="14"/>
+      <c r="H540" s="13"/>
       <c r="I540" s="21"/>
     </row>
     <row r="541">
       <c r="C541" s="22"/>
       <c r="F541" s="9"/>
       <c r="G541" s="9"/>
-      <c r="H541" s="14"/>
+      <c r="H541" s="13"/>
       <c r="I541" s="21"/>
     </row>
     <row r="542">
       <c r="C542" s="22"/>
       <c r="F542" s="9"/>
       <c r="G542" s="9"/>
-      <c r="H542" s="14"/>
+      <c r="H542" s="13"/>
       <c r="I542" s="21"/>
     </row>
     <row r="543">
       <c r="C543" s="22"/>
       <c r="F543" s="9"/>
       <c r="G543" s="9"/>
-      <c r="H543" s="14"/>
+      <c r="H543" s="13"/>
       <c r="I543" s="21"/>
     </row>
     <row r="544">
       <c r="C544" s="22"/>
       <c r="F544" s="9"/>
       <c r="G544" s="9"/>
-      <c r="H544" s="14"/>
+      <c r="H544" s="13"/>
       <c r="I544" s="21"/>
     </row>
     <row r="545">
       <c r="C545" s="22"/>
       <c r="F545" s="9"/>
       <c r="G545" s="9"/>
-      <c r="H545" s="14"/>
+      <c r="H545" s="13"/>
       <c r="I545" s="21"/>
     </row>
     <row r="546">
       <c r="C546" s="22"/>
       <c r="F546" s="9"/>
       <c r="G546" s="9"/>
-      <c r="H546" s="14"/>
+      <c r="H546" s="13"/>
       <c r="I546" s="21"/>
     </row>
     <row r="547">
       <c r="C547" s="22"/>
       <c r="F547" s="9"/>
       <c r="G547" s="9"/>
-      <c r="H547" s="14"/>
+      <c r="H547" s="13"/>
       <c r="I547" s="21"/>
     </row>
     <row r="548">
       <c r="C548" s="22"/>
       <c r="F548" s="9"/>
       <c r="G548" s="9"/>
-      <c r="H548" s="14"/>
+      <c r="H548" s="13"/>
       <c r="I548" s="21"/>
     </row>
     <row r="549">
       <c r="C549" s="22"/>
       <c r="F549" s="9"/>
       <c r="G549" s="9"/>
-      <c r="H549" s="14"/>
+      <c r="H549" s="13"/>
       <c r="I549" s="21"/>
     </row>
     <row r="550">
       <c r="C550" s="22"/>
       <c r="F550" s="9"/>
       <c r="G550" s="9"/>
-      <c r="H550" s="14"/>
+      <c r="H550" s="13"/>
       <c r="I550" s="21"/>
     </row>
     <row r="551">
       <c r="C551" s="22"/>
       <c r="F551" s="9"/>
       <c r="G551" s="9"/>
-      <c r="H551" s="14"/>
+      <c r="H551" s="13"/>
       <c r="I551" s="21"/>
     </row>
     <row r="552">
       <c r="C552" s="22"/>
       <c r="F552" s="9"/>
       <c r="G552" s="9"/>
-      <c r="H552" s="14"/>
+      <c r="H552" s="13"/>
       <c r="I552" s="21"/>
     </row>
     <row r="553">
       <c r="C553" s="22"/>
       <c r="F553" s="9"/>
       <c r="G553" s="9"/>
-      <c r="H553" s="14"/>
+      <c r="H553" s="13"/>
       <c r="I553" s="21"/>
     </row>
     <row r="554">
       <c r="C554" s="22"/>
       <c r="F554" s="9"/>
       <c r="G554" s="9"/>
-      <c r="H554" s="14"/>
+      <c r="H554" s="13"/>
       <c r="I554" s="21"/>
     </row>
     <row r="555">
       <c r="C555" s="22"/>
       <c r="F555" s="9"/>
       <c r="G555" s="9"/>
-      <c r="H555" s="14"/>
+      <c r="H555" s="13"/>
       <c r="I555" s="21"/>
     </row>
     <row r="556">
       <c r="C556" s="22"/>
       <c r="F556" s="9"/>
       <c r="G556" s="9"/>
-      <c r="H556" s="14"/>
+      <c r="H556" s="13"/>
       <c r="I556" s="21"/>
     </row>
     <row r="557">
       <c r="C557" s="22"/>
       <c r="F557" s="9"/>
       <c r="G557" s="9"/>
-      <c r="H557" s="14"/>
+      <c r="H557" s="13"/>
       <c r="I557" s="21"/>
     </row>
     <row r="558">
       <c r="C558" s="22"/>
       <c r="F558" s="9"/>
       <c r="G558" s="9"/>
-      <c r="H558" s="14"/>
+      <c r="H558" s="13"/>
       <c r="I558" s="21"/>
     </row>
     <row r="559">
       <c r="C559" s="22"/>
       <c r="F559" s="9"/>
       <c r="G559" s="9"/>
-      <c r="H559" s="14"/>
+      <c r="H559" s="13"/>
       <c r="I559" s="21"/>
     </row>
     <row r="560">
       <c r="C560" s="22"/>
       <c r="F560" s="9"/>
       <c r="G560" s="9"/>
-      <c r="H560" s="14"/>
+      <c r="H560" s="13"/>
       <c r="I560" s="21"/>
     </row>
     <row r="561">
       <c r="C561" s="22"/>
       <c r="F561" s="9"/>
       <c r="G561" s="9"/>
-      <c r="H561" s="14"/>
+      <c r="H561" s="13"/>
       <c r="I561" s="21"/>
     </row>
     <row r="562">
       <c r="C562" s="22"/>
       <c r="F562" s="9"/>
       <c r="G562" s="9"/>
-      <c r="H562" s="14"/>
+      <c r="H562" s="13"/>
       <c r="I562" s="21"/>
     </row>
     <row r="563">
       <c r="C563" s="22"/>
       <c r="F563" s="9"/>
       <c r="G563" s="9"/>
-      <c r="H563" s="14"/>
+      <c r="H563" s="13"/>
       <c r="I563" s="21"/>
     </row>
     <row r="564">
       <c r="C564" s="22"/>
       <c r="F564" s="9"/>
       <c r="G564" s="9"/>
-      <c r="H564" s="14"/>
+      <c r="H564" s="13"/>
       <c r="I564" s="21"/>
     </row>
     <row r="565">
       <c r="C565" s="22"/>
       <c r="F565" s="9"/>
       <c r="G565" s="9"/>
-      <c r="H565" s="14"/>
+      <c r="H565" s="13"/>
       <c r="I565" s="21"/>
     </row>
     <row r="566">
       <c r="C566" s="22"/>
       <c r="F566" s="9"/>
       <c r="G566" s="9"/>
-      <c r="H566" s="14"/>
+      <c r="H566" s="13"/>
       <c r="I566" s="21"/>
     </row>
     <row r="567">
       <c r="C567" s="22"/>
       <c r="F567" s="9"/>
       <c r="G567" s="9"/>
-      <c r="H567" s="14"/>
+      <c r="H567" s="13"/>
       <c r="I567" s="21"/>
     </row>
     <row r="568">
       <c r="C568" s="22"/>
       <c r="F568" s="9"/>
       <c r="G568" s="9"/>
-      <c r="H568" s="14"/>
+      <c r="H568" s="13"/>
       <c r="I568" s="21"/>
     </row>
     <row r="569">
       <c r="C569" s="22"/>
       <c r="F569" s="9"/>
       <c r="G569" s="9"/>
-      <c r="H569" s="14"/>
+      <c r="H569" s="13"/>
       <c r="I569" s="21"/>
     </row>
     <row r="570">
       <c r="C570" s="22"/>
       <c r="F570" s="9"/>
       <c r="G570" s="9"/>
-      <c r="H570" s="14"/>
+      <c r="H570" s="13"/>
       <c r="I570" s="21"/>
     </row>
     <row r="571">
       <c r="C571" s="22"/>
       <c r="F571" s="9"/>
       <c r="G571" s="9"/>
-      <c r="H571" s="14"/>
+      <c r="H571" s="13"/>
       <c r="I571" s="21"/>
     </row>
     <row r="572">
       <c r="C572" s="22"/>
       <c r="F572" s="9"/>
       <c r="G572" s="9"/>
-      <c r="H572" s="14"/>
+      <c r="H572" s="13"/>
       <c r="I572" s="21"/>
     </row>
     <row r="573">
       <c r="C573" s="22"/>
       <c r="F573" s="9"/>
       <c r="G573" s="9"/>
-      <c r="H573" s="14"/>
+      <c r="H573" s="13"/>
       <c r="I573" s="21"/>
     </row>
     <row r="574">
       <c r="C574" s="22"/>
       <c r="F574" s="9"/>
       <c r="G574" s="9"/>
-      <c r="H574" s="14"/>
+      <c r="H574" s="13"/>
       <c r="I574" s="21"/>
     </row>
     <row r="575">
       <c r="C575" s="22"/>
       <c r="F575" s="9"/>
       <c r="G575" s="9"/>
-      <c r="H575" s="14"/>
+      <c r="H575" s="13"/>
       <c r="I575" s="21"/>
     </row>
     <row r="576">
       <c r="C576" s="22"/>
       <c r="F576" s="9"/>
       <c r="G576" s="9"/>
-      <c r="H576" s="14"/>
+      <c r="H576" s="13"/>
       <c r="I576" s="21"/>
     </row>
     <row r="577">
       <c r="C577" s="22"/>
       <c r="F577" s="9"/>
       <c r="G577" s="9"/>
-      <c r="H577" s="14"/>
+      <c r="H577" s="13"/>
       <c r="I577" s="21"/>
     </row>
     <row r="578">
       <c r="C578" s="22"/>
       <c r="F578" s="9"/>
       <c r="G578" s="9"/>
-      <c r="H578" s="14"/>
+      <c r="H578" s="13"/>
       <c r="I578" s="21"/>
     </row>
     <row r="579">
       <c r="C579" s="22"/>
       <c r="F579" s="9"/>
       <c r="G579" s="9"/>
-      <c r="H579" s="14"/>
+      <c r="H579" s="13"/>
       <c r="I579" s="21"/>
     </row>
     <row r="580">
       <c r="C580" s="22"/>
       <c r="F580" s="9"/>
       <c r="G580" s="9"/>
-      <c r="H580" s="14"/>
+      <c r="H580" s="13"/>
       <c r="I580" s="21"/>
     </row>
     <row r="581">
       <c r="C581" s="22"/>
       <c r="F581" s="9"/>
       <c r="G581" s="9"/>
-      <c r="H581" s="14"/>
+      <c r="H581" s="13"/>
       <c r="I581" s="21"/>
     </row>
     <row r="582">
       <c r="C582" s="22"/>
       <c r="F582" s="9"/>
       <c r="G582" s="9"/>
-      <c r="H582" s="14"/>
+      <c r="H582" s="13"/>
       <c r="I582" s="21"/>
     </row>
     <row r="583">
       <c r="C583" s="22"/>
       <c r="F583" s="9"/>
       <c r="G583" s="9"/>
-      <c r="H583" s="14"/>
+      <c r="H583" s="13"/>
       <c r="I583" s="21"/>
     </row>
     <row r="584">
       <c r="C584" s="22"/>
       <c r="F584" s="9"/>
       <c r="G584" s="9"/>
-      <c r="H584" s="14"/>
+      <c r="H584" s="13"/>
       <c r="I584" s="21"/>
     </row>
     <row r="585">
       <c r="C585" s="22"/>
       <c r="F585" s="9"/>
       <c r="G585" s="9"/>
-      <c r="H585" s="14"/>
+      <c r="H585" s="13"/>
       <c r="I585" s="21"/>
     </row>
     <row r="586">
       <c r="C586" s="22"/>
       <c r="F586" s="9"/>
       <c r="G586" s="9"/>
-      <c r="H586" s="14"/>
+      <c r="H586" s="13"/>
       <c r="I586" s="21"/>
     </row>
     <row r="587">
       <c r="C587" s="22"/>
       <c r="F587" s="9"/>
       <c r="G587" s="9"/>
-      <c r="H587" s="14"/>
+      <c r="H587" s="13"/>
       <c r="I587" s="21"/>
     </row>
     <row r="588">
       <c r="C588" s="22"/>
       <c r="F588" s="9"/>
       <c r="G588" s="9"/>
-      <c r="H588" s="14"/>
+      <c r="H588" s="13"/>
       <c r="I588" s="21"/>
     </row>
     <row r="589">
       <c r="C589" s="22"/>
       <c r="F589" s="9"/>
       <c r="G589" s="9"/>
-      <c r="H589" s="14"/>
+      <c r="H589" s="13"/>
       <c r="I589" s="21"/>
     </row>
     <row r="590">
       <c r="C590" s="22"/>
       <c r="F590" s="9"/>
       <c r="G590" s="9"/>
-      <c r="H590" s="14"/>
+      <c r="H590" s="13"/>
       <c r="I590" s="21"/>
     </row>
     <row r="591">
       <c r="C591" s="22"/>
       <c r="F591" s="9"/>
       <c r="G591" s="9"/>
-      <c r="H591" s="14"/>
+      <c r="H591" s="13"/>
       <c r="I591" s="21"/>
     </row>
     <row r="592">
       <c r="C592" s="22"/>
       <c r="F592" s="9"/>
       <c r="G592" s="9"/>
-      <c r="H592" s="14"/>
+      <c r="H592" s="13"/>
       <c r="I592" s="21"/>
     </row>
     <row r="593">
       <c r="C593" s="22"/>
       <c r="F593" s="9"/>
       <c r="G593" s="9"/>
-      <c r="H593" s="14"/>
+      <c r="H593" s="13"/>
       <c r="I593" s="21"/>
     </row>
     <row r="594">
       <c r="C594" s="22"/>
       <c r="F594" s="9"/>
       <c r="G594" s="9"/>
-      <c r="H594" s="14"/>
+      <c r="H594" s="13"/>
       <c r="I594" s="21"/>
     </row>
     <row r="595">
       <c r="C595" s="22"/>
       <c r="F595" s="9"/>
       <c r="G595" s="9"/>
-      <c r="H595" s="14"/>
+      <c r="H595" s="13"/>
       <c r="I595" s="21"/>
     </row>
     <row r="596">
       <c r="C596" s="22"/>
       <c r="F596" s="9"/>
       <c r="G596" s="9"/>
-      <c r="H596" s="14"/>
+      <c r="H596" s="13"/>
       <c r="I596" s="21"/>
     </row>
     <row r="597">
       <c r="C597" s="22"/>
       <c r="F597" s="9"/>
       <c r="G597" s="9"/>
-      <c r="H597" s="14"/>
+      <c r="H597" s="13"/>
       <c r="I597" s="21"/>
     </row>
     <row r="598">
       <c r="C598" s="22"/>
       <c r="F598" s="9"/>
       <c r="G598" s="9"/>
-      <c r="H598" s="14"/>
+      <c r="H598" s="13"/>
       <c r="I598" s="21"/>
     </row>
     <row r="599">
       <c r="C599" s="22"/>
       <c r="F599" s="9"/>
       <c r="G599" s="9"/>
-      <c r="H599" s="14"/>
+      <c r="H599" s="13"/>
       <c r="I599" s="21"/>
     </row>
     <row r="600">
       <c r="C600" s="22"/>
       <c r="F600" s="9"/>
       <c r="G600" s="9"/>
-      <c r="H600" s="14"/>
+      <c r="H600" s="13"/>
       <c r="I600" s="21"/>
     </row>
     <row r="601">
       <c r="C601" s="22"/>
       <c r="F601" s="9"/>
       <c r="G601" s="9"/>
-      <c r="H601" s="14"/>
+      <c r="H601" s="13"/>
       <c r="I601" s="21"/>
     </row>
     <row r="602">
       <c r="C602" s="22"/>
       <c r="F602" s="9"/>
       <c r="G602" s="9"/>
-      <c r="H602" s="14"/>
+      <c r="H602" s="13"/>
       <c r="I602" s="21"/>
     </row>
     <row r="603">
       <c r="C603" s="22"/>
       <c r="F603" s="9"/>
       <c r="G603" s="9"/>
-      <c r="H603" s="14"/>
+      <c r="H603" s="13"/>
       <c r="I603" s="21"/>
     </row>
     <row r="604">
       <c r="C604" s="22"/>
       <c r="F604" s="9"/>
       <c r="G604" s="9"/>
-      <c r="H604" s="14"/>
+      <c r="H604" s="13"/>
       <c r="I604" s="21"/>
     </row>
     <row r="605">
       <c r="C605" s="22"/>
       <c r="F605" s="9"/>
       <c r="G605" s="9"/>
-      <c r="H605" s="14"/>
+      <c r="H605" s="13"/>
       <c r="I605" s="21"/>
     </row>
     <row r="606">
       <c r="C606" s="22"/>
       <c r="F606" s="9"/>
       <c r="G606" s="9"/>
-      <c r="H606" s="14"/>
+      <c r="H606" s="13"/>
       <c r="I606" s="21"/>
     </row>
     <row r="607">
       <c r="C607" s="22"/>
       <c r="F607" s="9"/>
       <c r="G607" s="9"/>
-      <c r="H607" s="14"/>
+      <c r="H607" s="13"/>
       <c r="I607" s="21"/>
     </row>
     <row r="608">
       <c r="C608" s="22"/>
       <c r="F608" s="9"/>
       <c r="G608" s="9"/>
-      <c r="H608" s="14"/>
+      <c r="H608" s="13"/>
       <c r="I608" s="21"/>
     </row>
     <row r="609">
       <c r="C609" s="22"/>
       <c r="F609" s="9"/>
       <c r="G609" s="9"/>
-      <c r="H609" s="14"/>
+      <c r="H609" s="13"/>
       <c r="I609" s="21"/>
     </row>
     <row r="610">
       <c r="C610" s="22"/>
       <c r="F610" s="9"/>
       <c r="G610" s="9"/>
-      <c r="H610" s="14"/>
+      <c r="H610" s="13"/>
       <c r="I610" s="21"/>
     </row>
     <row r="611">
       <c r="C611" s="22"/>
       <c r="F611" s="9"/>
       <c r="G611" s="9"/>
-      <c r="H611" s="14"/>
+      <c r="H611" s="13"/>
       <c r="I611" s="21"/>
     </row>
     <row r="612">
       <c r="C612" s="22"/>
       <c r="F612" s="9"/>
       <c r="G612" s="9"/>
-      <c r="H612" s="14"/>
+      <c r="H612" s="13"/>
       <c r="I612" s="21"/>
     </row>
     <row r="613">
       <c r="C613" s="22"/>
       <c r="F613" s="9"/>
       <c r="G613" s="9"/>
-      <c r="H613" s="14"/>
+      <c r="H613" s="13"/>
       <c r="I613" s="21"/>
     </row>
     <row r="614">
       <c r="C614" s="22"/>
       <c r="F614" s="9"/>
       <c r="G614" s="9"/>
-      <c r="H614" s="14"/>
+      <c r="H614" s="13"/>
       <c r="I614" s="21"/>
     </row>
     <row r="615">
       <c r="C615" s="22"/>
       <c r="F615" s="9"/>
       <c r="G615" s="9"/>
-      <c r="H615" s="14"/>
+      <c r="H615" s="13"/>
       <c r="I615" s="21"/>
     </row>
     <row r="616">
       <c r="C616" s="22"/>
       <c r="F616" s="9"/>
       <c r="G616" s="9"/>
-      <c r="H616" s="14"/>
+      <c r="H616" s="13"/>
       <c r="I616" s="21"/>
     </row>
     <row r="617">
       <c r="C617" s="22"/>
       <c r="F617" s="9"/>
       <c r="G617" s="9"/>
-      <c r="H617" s="14"/>
+      <c r="H617" s="13"/>
       <c r="I617" s="21"/>
     </row>
     <row r="618">
       <c r="C618" s="22"/>
       <c r="F618" s="9"/>
       <c r="G618" s="9"/>
-      <c r="H618" s="14"/>
+      <c r="H618" s="13"/>
       <c r="I618" s="21"/>
     </row>
     <row r="619">
       <c r="C619" s="22"/>
       <c r="F619" s="9"/>
       <c r="G619" s="9"/>
-      <c r="H619" s="14"/>
+      <c r="H619" s="13"/>
       <c r="I619" s="21"/>
     </row>
     <row r="620">
       <c r="C620" s="22"/>
       <c r="F620" s="9"/>
       <c r="G620" s="9"/>
-      <c r="H620" s="14"/>
+      <c r="H620" s="13"/>
       <c r="I620" s="21"/>
     </row>
     <row r="621">
       <c r="C621" s="22"/>
       <c r="F621" s="9"/>
       <c r="G621" s="9"/>
-      <c r="H621" s="14"/>
+      <c r="H621" s="13"/>
       <c r="I621" s="21"/>
     </row>
     <row r="622">
       <c r="C622" s="22"/>
       <c r="F622" s="9"/>
       <c r="G622" s="9"/>
-      <c r="H622" s="14"/>
+      <c r="H622" s="13"/>
       <c r="I622" s="21"/>
     </row>
     <row r="623">
       <c r="C623" s="22"/>
       <c r="F623" s="9"/>
       <c r="G623" s="9"/>
-      <c r="H623" s="14"/>
+      <c r="H623" s="13"/>
       <c r="I623" s="21"/>
     </row>
     <row r="624">
       <c r="C624" s="22"/>
       <c r="F624" s="9"/>
       <c r="G624" s="9"/>
-      <c r="H624" s="14"/>
+      <c r="H624" s="13"/>
       <c r="I624" s="21"/>
     </row>
     <row r="625">
       <c r="C625" s="22"/>
       <c r="F625" s="9"/>
       <c r="G625" s="9"/>
-      <c r="H625" s="14"/>
+      <c r="H625" s="13"/>
       <c r="I625" s="21"/>
     </row>
     <row r="626">
       <c r="C626" s="22"/>
       <c r="F626" s="9"/>
       <c r="G626" s="9"/>
-      <c r="H626" s="14"/>
+      <c r="H626" s="13"/>
       <c r="I626" s="21"/>
     </row>
     <row r="627">
       <c r="C627" s="22"/>
       <c r="F627" s="9"/>
       <c r="G627" s="9"/>
-      <c r="H627" s="14"/>
+      <c r="H627" s="13"/>
       <c r="I627" s="21"/>
     </row>
     <row r="628">
       <c r="C628" s="22"/>
       <c r="F628" s="9"/>
       <c r="G628" s="9"/>
-      <c r="H628" s="14"/>
+      <c r="H628" s="13"/>
       <c r="I628" s="21"/>
     </row>
     <row r="629">
       <c r="C629" s="22"/>
       <c r="F629" s="9"/>
       <c r="G629" s="9"/>
-      <c r="H629" s="14"/>
+      <c r="H629" s="13"/>
       <c r="I629" s="21"/>
     </row>
     <row r="630">
       <c r="C630" s="22"/>
       <c r="F630" s="9"/>
       <c r="G630" s="9"/>
-      <c r="H630" s="14"/>
+      <c r="H630" s="13"/>
       <c r="I630" s="21"/>
     </row>
     <row r="631">
       <c r="C631" s="22"/>
       <c r="F631" s="9"/>
       <c r="G631" s="9"/>
-      <c r="H631" s="14"/>
+      <c r="H631" s="13"/>
       <c r="I631" s="21"/>
     </row>
     <row r="632">
       <c r="C632" s="22"/>
       <c r="F632" s="9"/>
       <c r="G632" s="9"/>
-      <c r="H632" s="14"/>
+      <c r="H632" s="13"/>
       <c r="I632" s="21"/>
     </row>
     <row r="633">
       <c r="C633" s="22"/>
       <c r="F633" s="9"/>
       <c r="G633" s="9"/>
-      <c r="H633" s="14"/>
+      <c r="H633" s="13"/>
       <c r="I633" s="21"/>
     </row>
     <row r="634">
       <c r="C634" s="22"/>
       <c r="F634" s="9"/>
       <c r="G634" s="9"/>
-      <c r="H634" s="14"/>
+      <c r="H634" s="13"/>
       <c r="I634" s="21"/>
     </row>
     <row r="635">
       <c r="C635" s="22"/>
       <c r="F635" s="9"/>
       <c r="G635" s="9"/>
-      <c r="H635" s="14"/>
+      <c r="H635" s="13"/>
       <c r="I635" s="21"/>
     </row>
     <row r="636">
       <c r="C636" s="22"/>
       <c r="F636" s="9"/>
       <c r="G636" s="9"/>
-      <c r="H636" s="14"/>
+      <c r="H636" s="13"/>
       <c r="I636" s="21"/>
     </row>
     <row r="637">
       <c r="C637" s="22"/>
       <c r="F637" s="9"/>
       <c r="G637" s="9"/>
-      <c r="H637" s="14"/>
+      <c r="H637" s="13"/>
       <c r="I637" s="21"/>
     </row>
     <row r="638">
       <c r="C638" s="22"/>
       <c r="F638" s="9"/>
       <c r="G638" s="9"/>
-      <c r="H638" s="14"/>
+      <c r="H638" s="13"/>
       <c r="I638" s="21"/>
     </row>
     <row r="639">
       <c r="C639" s="22"/>
       <c r="F639" s="9"/>
       <c r="G639" s="9"/>
-      <c r="H639" s="14"/>
+      <c r="H639" s="13"/>
       <c r="I639" s="21"/>
     </row>
     <row r="640">
       <c r="C640" s="22"/>
       <c r="F640" s="9"/>
       <c r="G640" s="9"/>
-      <c r="H640" s="14"/>
+      <c r="H640" s="13"/>
       <c r="I640" s="21"/>
     </row>
     <row r="641">
       <c r="C641" s="22"/>
       <c r="F641" s="9"/>
       <c r="G641" s="9"/>
-      <c r="H641" s="14"/>
+      <c r="H641" s="13"/>
       <c r="I641" s="21"/>
     </row>
     <row r="642">
       <c r="C642" s="22"/>
       <c r="F642" s="9"/>
       <c r="G642" s="9"/>
-      <c r="H642" s="14"/>
+      <c r="H642" s="13"/>
       <c r="I642" s="21"/>
     </row>
     <row r="643">
       <c r="C643" s="22"/>
       <c r="F643" s="9"/>
       <c r="G643" s="9"/>
-      <c r="H643" s="14"/>
+      <c r="H643" s="13"/>
       <c r="I643" s="21"/>
     </row>
     <row r="644">
       <c r="C644" s="22"/>
       <c r="F644" s="9"/>
       <c r="G644" s="9"/>
-      <c r="H644" s="14"/>
+      <c r="H644" s="13"/>
       <c r="I644" s="21"/>
     </row>
     <row r="645">
       <c r="C645" s="22"/>
       <c r="F645" s="9"/>
       <c r="G645" s="9"/>
-      <c r="H645" s="14"/>
+      <c r="H645" s="13"/>
       <c r="I645" s="21"/>
     </row>
     <row r="646">
       <c r="C646" s="22"/>
       <c r="F646" s="9"/>
       <c r="G646" s="9"/>
-      <c r="H646" s="14"/>
+      <c r="H646" s="13"/>
       <c r="I646" s="21"/>
     </row>
     <row r="647">
       <c r="C647" s="22"/>
       <c r="F647" s="9"/>
       <c r="G647" s="9"/>
-      <c r="H647" s="14"/>
+      <c r="H647" s="13"/>
       <c r="I647" s="21"/>
     </row>
     <row r="648">
       <c r="C648" s="22"/>
       <c r="F648" s="9"/>
       <c r="G648" s="9"/>
-      <c r="H648" s="14"/>
+      <c r="H648" s="13"/>
       <c r="I648" s="21"/>
     </row>
     <row r="649">
       <c r="C649" s="22"/>
       <c r="F649" s="9"/>
       <c r="G649" s="9"/>
-      <c r="H649" s="14"/>
+      <c r="H649" s="13"/>
       <c r="I649" s="21"/>
     </row>
     <row r="650">
       <c r="C650" s="22"/>
       <c r="F650" s="9"/>
       <c r="G650" s="9"/>
-      <c r="H650" s="14"/>
+      <c r="H650" s="13"/>
       <c r="I650" s="21"/>
     </row>
     <row r="651">
       <c r="C651" s="22"/>
       <c r="F651" s="9"/>
       <c r="G651" s="9"/>
-      <c r="H651" s="14"/>
+      <c r="H651" s="13"/>
       <c r="I651" s="21"/>
     </row>
     <row r="652">
       <c r="C652" s="22"/>
       <c r="F652" s="9"/>
       <c r="G652" s="9"/>
-      <c r="H652" s="14"/>
+      <c r="H652" s="13"/>
       <c r="I652" s="21"/>
     </row>
     <row r="653">
       <c r="C653" s="22"/>
       <c r="F653" s="9"/>
       <c r="G653" s="9"/>
-      <c r="H653" s="14"/>
+      <c r="H653" s="13"/>
       <c r="I653" s="21"/>
     </row>
     <row r="654">
       <c r="C654" s="22"/>
       <c r="F654" s="9"/>
       <c r="G654" s="9"/>
-      <c r="H654" s="14"/>
+      <c r="H654" s="13"/>
       <c r="I654" s="21"/>
     </row>
     <row r="655">
       <c r="C655" s="22"/>
       <c r="F655" s="9"/>
       <c r="G655" s="9"/>
-      <c r="H655" s="14"/>
+      <c r="H655" s="13"/>
       <c r="I655" s="21"/>
     </row>
     <row r="656">
       <c r="C656" s="22"/>
       <c r="F656" s="9"/>
       <c r="G656" s="9"/>
-      <c r="H656" s="14"/>
+      <c r="H656" s="13"/>
       <c r="I656" s="21"/>
     </row>
     <row r="657">
       <c r="C657" s="22"/>
       <c r="F657" s="9"/>
       <c r="G657" s="9"/>
-      <c r="H657" s="14"/>
+      <c r="H657" s="13"/>
       <c r="I657" s="21"/>
     </row>
     <row r="658">
       <c r="C658" s="22"/>
       <c r="F658" s="9"/>
       <c r="G658" s="9"/>
-      <c r="H658" s="14"/>
+      <c r="H658" s="13"/>
       <c r="I658" s="21"/>
     </row>
     <row r="659">
       <c r="C659" s="22"/>
       <c r="F659" s="9"/>
       <c r="G659" s="9"/>
-      <c r="H659" s="14"/>
+      <c r="H659" s="13"/>
       <c r="I659" s="21"/>
     </row>
     <row r="660">
       <c r="C660" s="22"/>
       <c r="F660" s="9"/>
       <c r="G660" s="9"/>
-      <c r="H660" s="14"/>
+      <c r="H660" s="13"/>
       <c r="I660" s="21"/>
     </row>
     <row r="661">
       <c r="C661" s="22"/>
       <c r="F661" s="9"/>
       <c r="G661" s="9"/>
-      <c r="H661" s="14"/>
+      <c r="H661" s="13"/>
       <c r="I661" s="21"/>
     </row>
     <row r="662">
       <c r="C662" s="22"/>
       <c r="F662" s="9"/>
       <c r="G662" s="9"/>
-      <c r="H662" s="14"/>
+      <c r="H662" s="13"/>
       <c r="I662" s="21"/>
     </row>
     <row r="663">
       <c r="C663" s="22"/>
       <c r="F663" s="9"/>
       <c r="G663" s="9"/>
-      <c r="H663" s="14"/>
+      <c r="H663" s="13"/>
       <c r="I663" s="21"/>
     </row>
     <row r="664">
       <c r="C664" s="22"/>
       <c r="F664" s="9"/>
       <c r="G664" s="9"/>
-      <c r="H664" s="14"/>
+      <c r="H664" s="13"/>
       <c r="I664" s="21"/>
     </row>
     <row r="665">
       <c r="C665" s="22"/>
       <c r="F665" s="9"/>
       <c r="G665" s="9"/>
-      <c r="H665" s="14"/>
+      <c r="H665" s="13"/>
       <c r="I665" s="21"/>
     </row>
     <row r="666">
       <c r="C666" s="22"/>
       <c r="F666" s="9"/>
       <c r="G666" s="9"/>
-      <c r="H666" s="14"/>
+      <c r="H666" s="13"/>
       <c r="I666" s="21"/>
     </row>
     <row r="667">
       <c r="C667" s="22"/>
       <c r="F667" s="9"/>
       <c r="G667" s="9"/>
-      <c r="H667" s="14"/>
+      <c r="H667" s="13"/>
       <c r="I667" s="21"/>
     </row>
     <row r="668">
       <c r="C668" s="22"/>
       <c r="F668" s="9"/>
       <c r="G668" s="9"/>
-      <c r="H668" s="14"/>
+      <c r="H668" s="13"/>
       <c r="I668" s="21"/>
     </row>
     <row r="669">
       <c r="C669" s="22"/>
       <c r="F669" s="9"/>
       <c r="G669" s="9"/>
-      <c r="H669" s="14"/>
+      <c r="H669" s="13"/>
       <c r="I669" s="21"/>
     </row>
     <row r="670">
       <c r="C670" s="22"/>
       <c r="F670" s="9"/>
       <c r="G670" s="9"/>
-      <c r="H670" s="14"/>
+      <c r="H670" s="13"/>
       <c r="I670" s="21"/>
     </row>
     <row r="671">
       <c r="C671" s="22"/>
       <c r="F671" s="9"/>
       <c r="G671" s="9"/>
-      <c r="H671" s="14"/>
+      <c r="H671" s="13"/>
       <c r="I671" s="21"/>
     </row>
     <row r="672">
       <c r="C672" s="22"/>
       <c r="F672" s="9"/>
       <c r="G672" s="9"/>
-      <c r="H672" s="14"/>
+      <c r="H672" s="13"/>
       <c r="I672" s="21"/>
     </row>
     <row r="673">
       <c r="C673" s="22"/>
       <c r="F673" s="9"/>
       <c r="G673" s="9"/>
-      <c r="H673" s="14"/>
+      <c r="H673" s="13"/>
       <c r="I673" s="21"/>
     </row>
     <row r="674">
       <c r="C674" s="22"/>
       <c r="F674" s="9"/>
       <c r="G674" s="9"/>
-      <c r="H674" s="14"/>
+      <c r="H674" s="13"/>
       <c r="I674" s="21"/>
     </row>
     <row r="675">
       <c r="C675" s="22"/>
       <c r="F675" s="9"/>
       <c r="G675" s="9"/>
-      <c r="H675" s="14"/>
+      <c r="H675" s="13"/>
       <c r="I675" s="21"/>
     </row>
     <row r="676">
       <c r="C676" s="22"/>
       <c r="F676" s="9"/>
       <c r="G676" s="9"/>
-      <c r="H676" s="14"/>
+      <c r="H676" s="13"/>
       <c r="I676" s="21"/>
     </row>
     <row r="677">
       <c r="C677" s="22"/>
       <c r="F677" s="9"/>
       <c r="G677" s="9"/>
-      <c r="H677" s="14"/>
+      <c r="H677" s="13"/>
       <c r="I677" s="21"/>
     </row>
     <row r="678">
       <c r="C678" s="22"/>
       <c r="F678" s="9"/>
       <c r="G678" s="9"/>
-      <c r="H678" s="14"/>
+      <c r="H678" s="13"/>
       <c r="I678" s="21"/>
     </row>
     <row r="679">
       <c r="C679" s="22"/>
       <c r="F679" s="9"/>
       <c r="G679" s="9"/>
-      <c r="H679" s="14"/>
+      <c r="H679" s="13"/>
       <c r="I679" s="21"/>
     </row>
     <row r="680">
       <c r="C680" s="22"/>
       <c r="F680" s="9"/>
       <c r="G680" s="9"/>
-      <c r="H680" s="14"/>
+      <c r="H680" s="13"/>
       <c r="I680" s="21"/>
     </row>
     <row r="681">
       <c r="C681" s="22"/>
       <c r="F681" s="9"/>
       <c r="G681" s="9"/>
-      <c r="H681" s="14"/>
+      <c r="H681" s="13"/>
       <c r="I681" s="21"/>
     </row>
     <row r="682">
       <c r="C682" s="22"/>
       <c r="F682" s="9"/>
       <c r="G682" s="9"/>
-      <c r="H682" s="14"/>
+      <c r="H682" s="13"/>
       <c r="I682" s="21"/>
     </row>
     <row r="683">
       <c r="C683" s="22"/>
       <c r="F683" s="9"/>
       <c r="G683" s="9"/>
-      <c r="H683" s="14"/>
+      <c r="H683" s="13"/>
       <c r="I683" s="21"/>
     </row>
     <row r="684">
       <c r="C684" s="22"/>
       <c r="F684" s="9"/>
       <c r="G684" s="9"/>
-      <c r="H684" s="14"/>
+      <c r="H684" s="13"/>
       <c r="I684" s="21"/>
     </row>
     <row r="685">
       <c r="C685" s="22"/>
       <c r="F685" s="9"/>
       <c r="G685" s="9"/>
-      <c r="H685" s="14"/>
+      <c r="H685" s="13"/>
       <c r="I685" s="21"/>
     </row>
     <row r="686">
       <c r="C686" s="22"/>
       <c r="F686" s="9"/>
       <c r="G686" s="9"/>
-      <c r="H686" s="14"/>
+      <c r="H686" s="13"/>
       <c r="I686" s="21"/>
     </row>
     <row r="687">
       <c r="C687" s="22"/>
       <c r="F687" s="9"/>
       <c r="G687" s="9"/>
-      <c r="H687" s="14"/>
+      <c r="H687" s="13"/>
       <c r="I687" s="21"/>
     </row>
     <row r="688">
       <c r="C688" s="22"/>
       <c r="F688" s="9"/>
       <c r="G688" s="9"/>
-      <c r="H688" s="14"/>
+      <c r="H688" s="13"/>
       <c r="I688" s="21"/>
     </row>
     <row r="689">
       <c r="C689" s="22"/>
       <c r="F689" s="9"/>
       <c r="G689" s="9"/>
-      <c r="H689" s="14"/>
+      <c r="H689" s="13"/>
       <c r="I689" s="21"/>
     </row>
     <row r="690">
       <c r="C690" s="22"/>
       <c r="F690" s="9"/>
       <c r="G690" s="9"/>
-      <c r="H690" s="14"/>
+      <c r="H690" s="13"/>
       <c r="I690" s="21"/>
     </row>
     <row r="691">
       <c r="C691" s="22"/>
       <c r="F691" s="9"/>
       <c r="G691" s="9"/>
-      <c r="H691" s="14"/>
+      <c r="H691" s="13"/>
       <c r="I691" s="21"/>
     </row>
     <row r="692">
       <c r="C692" s="22"/>
       <c r="F692" s="9"/>
       <c r="G692" s="9"/>
-      <c r="H692" s="14"/>
+      <c r="H692" s="13"/>
       <c r="I692" s="21"/>
     </row>
     <row r="693">
       <c r="C693" s="22"/>
       <c r="F693" s="9"/>
       <c r="G693" s="9"/>
-      <c r="H693" s="14"/>
+      <c r="H693" s="13"/>
       <c r="I693" s="21"/>
     </row>
     <row r="694">
       <c r="C694" s="22"/>
       <c r="F694" s="9"/>
       <c r="G694" s="9"/>
-      <c r="H694" s="14"/>
+      <c r="H694" s="13"/>
       <c r="I694" s="21"/>
     </row>
     <row r="695">
       <c r="C695" s="22"/>
       <c r="F695" s="9"/>
       <c r="G695" s="9"/>
-      <c r="H695" s="14"/>
+      <c r="H695" s="13"/>
       <c r="I695" s="21"/>
     </row>
     <row r="696">
       <c r="C696" s="22"/>
       <c r="F696" s="9"/>
       <c r="G696" s="9"/>
-      <c r="H696" s="14"/>
+      <c r="H696" s="13"/>
       <c r="I696" s="21"/>
     </row>
     <row r="697">
       <c r="C697" s="22"/>
       <c r="F697" s="9"/>
       <c r="G697" s="9"/>
-      <c r="H697" s="14"/>
+      <c r="H697" s="13"/>
       <c r="I697" s="21"/>
     </row>
     <row r="698">
       <c r="C698" s="22"/>
       <c r="F698" s="9"/>
       <c r="G698" s="9"/>
-      <c r="H698" s="14"/>
+      <c r="H698" s="13"/>
       <c r="I698" s="21"/>
     </row>
     <row r="699">
       <c r="C699" s="22"/>
       <c r="F699" s="9"/>
       <c r="G699" s="9"/>
-      <c r="H699" s="14"/>
+      <c r="H699" s="13"/>
       <c r="I699" s="21"/>
     </row>
     <row r="700">
       <c r="C700" s="22"/>
       <c r="F700" s="9"/>
       <c r="G700" s="9"/>
-      <c r="H700" s="14"/>
+      <c r="H700" s="13"/>
       <c r="I700" s="21"/>
     </row>
     <row r="701">
       <c r="C701" s="22"/>
       <c r="F701" s="9"/>
       <c r="G701" s="9"/>
-      <c r="H701" s="14"/>
+      <c r="H701" s="13"/>
       <c r="I701" s="21"/>
     </row>
     <row r="702">
       <c r="C702" s="22"/>
       <c r="F702" s="9"/>
       <c r="G702" s="9"/>
-      <c r="H702" s="14"/>
+      <c r="H702" s="13"/>
       <c r="I702" s="21"/>
     </row>
     <row r="703">
       <c r="C703" s="22"/>
       <c r="F703" s="9"/>
       <c r="G703" s="9"/>
-      <c r="H703" s="14"/>
+      <c r="H703" s="13"/>
       <c r="I703" s="21"/>
     </row>
     <row r="704">
       <c r="C704" s="22"/>
       <c r="F704" s="9"/>
       <c r="G704" s="9"/>
-      <c r="H704" s="14"/>
+      <c r="H704" s="13"/>
       <c r="I704" s="21"/>
     </row>
     <row r="705">
       <c r="C705" s="22"/>
       <c r="F705" s="9"/>
       <c r="G705" s="9"/>
-      <c r="H705" s="14"/>
+      <c r="H705" s="13"/>
       <c r="I705" s="21"/>
     </row>
     <row r="706">
       <c r="C706" s="22"/>
       <c r="F706" s="9"/>
       <c r="G706" s="9"/>
-      <c r="H706" s="14"/>
+      <c r="H706" s="13"/>
       <c r="I706" s="21"/>
     </row>
     <row r="707">
       <c r="C707" s="22"/>
       <c r="F707" s="9"/>
       <c r="G707" s="9"/>
-      <c r="H707" s="14"/>
+      <c r="H707" s="13"/>
       <c r="I707" s="21"/>
     </row>
     <row r="708">
       <c r="C708" s="22"/>
       <c r="F708" s="9"/>
       <c r="G708" s="9"/>
-      <c r="H708" s="14"/>
+      <c r="H708" s="13"/>
       <c r="I708" s="21"/>
     </row>
     <row r="709">
       <c r="C709" s="22"/>
       <c r="F709" s="9"/>
       <c r="G709" s="9"/>
-      <c r="H709" s="14"/>
+      <c r="H709" s="13"/>
       <c r="I709" s="21"/>
     </row>
     <row r="710">
       <c r="C710" s="22"/>
       <c r="F710" s="9"/>
       <c r="G710" s="9"/>
-      <c r="H710" s="14"/>
+      <c r="H710" s="13"/>
       <c r="I710" s="21"/>
     </row>
     <row r="711">
       <c r="C711" s="22"/>
       <c r="F711" s="9"/>
       <c r="G711" s="9"/>
-      <c r="H711" s="14"/>
+      <c r="H711" s="13"/>
       <c r="I711" s="21"/>
     </row>
     <row r="712">
       <c r="C712" s="22"/>
       <c r="F712" s="9"/>
       <c r="G712" s="9"/>
-      <c r="H712" s="14"/>
+      <c r="H712" s="13"/>
       <c r="I712" s="21"/>
     </row>
     <row r="713">
       <c r="C713" s="22"/>
       <c r="F713" s="9"/>
       <c r="G713" s="9"/>
-      <c r="H713" s="14"/>
+      <c r="H713" s="13"/>
       <c r="I713" s="21"/>
     </row>
     <row r="714">
       <c r="C714" s="22"/>
       <c r="F714" s="9"/>
       <c r="G714" s="9"/>
-      <c r="H714" s="14"/>
+      <c r="H714" s="13"/>
       <c r="I714" s="21"/>
     </row>
     <row r="715">
       <c r="C715" s="22"/>
       <c r="F715" s="9"/>
       <c r="G715" s="9"/>
-      <c r="H715" s="14"/>
+      <c r="H715" s="13"/>
       <c r="I715" s="21"/>
     </row>
     <row r="716">
       <c r="C716" s="22"/>
       <c r="F716" s="9"/>
       <c r="G716" s="9"/>
-      <c r="H716" s="14"/>
+      <c r="H716" s="13"/>
       <c r="I716" s="21"/>
     </row>
     <row r="717">
       <c r="C717" s="22"/>
       <c r="F717" s="9"/>
       <c r="G717" s="9"/>
-      <c r="H717" s="14"/>
+      <c r="H717" s="13"/>
       <c r="I717" s="21"/>
     </row>
     <row r="718">
       <c r="C718" s="22"/>
       <c r="F718" s="9"/>
       <c r="G718" s="9"/>
-      <c r="H718" s="14"/>
+      <c r="H718" s="13"/>
       <c r="I718" s="21"/>
     </row>
     <row r="719">
       <c r="C719" s="22"/>
       <c r="F719" s="9"/>
       <c r="G719" s="9"/>
-      <c r="H719" s="14"/>
+      <c r="H719" s="13"/>
       <c r="I719" s="21"/>
     </row>
     <row r="720">
       <c r="C720" s="22"/>
       <c r="F720" s="9"/>
       <c r="G720" s="9"/>
-      <c r="H720" s="14"/>
+      <c r="H720" s="13"/>
       <c r="I720" s="21"/>
     </row>
     <row r="721">
       <c r="C721" s="22"/>
       <c r="F721" s="9"/>
       <c r="G721" s="9"/>
-      <c r="H721" s="14"/>
+      <c r="H721" s="13"/>
       <c r="I721" s="21"/>
     </row>
     <row r="722">
       <c r="C722" s="22"/>
       <c r="F722" s="9"/>
       <c r="G722" s="9"/>
-      <c r="H722" s="14"/>
+      <c r="H722" s="13"/>
       <c r="I722" s="21"/>
     </row>
     <row r="723">
       <c r="C723" s="22"/>
       <c r="F723" s="9"/>
       <c r="G723" s="9"/>
-      <c r="H723" s="14"/>
+      <c r="H723" s="13"/>
       <c r="I723" s="21"/>
     </row>
     <row r="724">
       <c r="C724" s="22"/>
       <c r="F724" s="9"/>
       <c r="G724" s="9"/>
-      <c r="H724" s="14"/>
+      <c r="H724" s="13"/>
       <c r="I724" s="21"/>
     </row>
     <row r="725">
       <c r="C725" s="22"/>
       <c r="F725" s="9"/>
       <c r="G725" s="9"/>
-      <c r="H725" s="14"/>
+      <c r="H725" s="13"/>
       <c r="I725" s="21"/>
     </row>
     <row r="726">
       <c r="C726" s="22"/>
       <c r="F726" s="9"/>
       <c r="G726" s="9"/>
-      <c r="H726" s="14"/>
+      <c r="H726" s="13"/>
       <c r="I726" s="21"/>
     </row>
     <row r="727">
       <c r="C727" s="22"/>
       <c r="F727" s="9"/>
       <c r="G727" s="9"/>
-      <c r="H727" s="14"/>
+      <c r="H727" s="13"/>
       <c r="I727" s="21"/>
     </row>
     <row r="728">
       <c r="C728" s="22"/>
       <c r="F728" s="9"/>
       <c r="G728" s="9"/>
-      <c r="H728" s="14"/>
+      <c r="H728" s="13"/>
       <c r="I728" s="21"/>
     </row>
     <row r="729">
       <c r="C729" s="22"/>
       <c r="F729" s="9"/>
       <c r="G729" s="9"/>
-      <c r="H729" s="14"/>
+      <c r="H729" s="13"/>
       <c r="I729" s="21"/>
     </row>
     <row r="730">
       <c r="C730" s="22"/>
       <c r="F730" s="9"/>
       <c r="G730" s="9"/>
-      <c r="H730" s="14"/>
+      <c r="H730" s="13"/>
       <c r="I730" s="21"/>
     </row>
     <row r="731">
       <c r="C731" s="22"/>
       <c r="F731" s="9"/>
       <c r="G731" s="9"/>
-      <c r="H731" s="14"/>
+      <c r="H731" s="13"/>
       <c r="I731" s="21"/>
     </row>
     <row r="732">
       <c r="C732" s="22"/>
       <c r="F732" s="9"/>
       <c r="G732" s="9"/>
-      <c r="H732" s="14"/>
+      <c r="H732" s="13"/>
       <c r="I732" s="21"/>
     </row>
     <row r="733">
       <c r="C733" s="22"/>
       <c r="F733" s="9"/>
       <c r="G733" s="9"/>
-      <c r="H733" s="14"/>
+      <c r="H733" s="13"/>
       <c r="I733" s="21"/>
     </row>
     <row r="734">
       <c r="C734" s="22"/>
       <c r="F734" s="9"/>
       <c r="G734" s="9"/>
-      <c r="H734" s="14"/>
+      <c r="H734" s="13"/>
       <c r="I734" s="21"/>
     </row>
     <row r="735">
       <c r="C735" s="22"/>
       <c r="F735" s="9"/>
       <c r="G735" s="9"/>
-      <c r="H735" s="14"/>
+      <c r="H735" s="13"/>
       <c r="I735" s="21"/>
     </row>
     <row r="736">
       <c r="C736" s="22"/>
       <c r="F736" s="9"/>
       <c r="G736" s="9"/>
-      <c r="H736" s="14"/>
+      <c r="H736" s="13"/>
       <c r="I736" s="21"/>
     </row>
     <row r="737">
       <c r="C737" s="22"/>
       <c r="F737" s="9"/>
       <c r="G737" s="9"/>
-      <c r="H737" s="14"/>
+      <c r="H737" s="13"/>
       <c r="I737" s="21"/>
     </row>
     <row r="738">
       <c r="C738" s="22"/>
       <c r="F738" s="9"/>
       <c r="G738" s="9"/>
-      <c r="H738" s="14"/>
+      <c r="H738" s="13"/>
       <c r="I738" s="21"/>
     </row>
     <row r="739">
       <c r="C739" s="22"/>
       <c r="F739" s="9"/>
       <c r="G739" s="9"/>
-      <c r="H739" s="14"/>
+      <c r="H739" s="13"/>
       <c r="I739" s="21"/>
     </row>
     <row r="740">
       <c r="C740" s="22"/>
       <c r="F740" s="9"/>
       <c r="G740" s="9"/>
-      <c r="H740" s="14"/>
+      <c r="H740" s="13"/>
       <c r="I740" s="21"/>
     </row>
     <row r="741">
       <c r="C741" s="22"/>
       <c r="F741" s="9"/>
       <c r="G741" s="9"/>
-      <c r="H741" s="14"/>
+      <c r="H741" s="13"/>
       <c r="I741" s="21"/>
     </row>
     <row r="742">
       <c r="C742" s="22"/>
       <c r="F742" s="9"/>
       <c r="G742" s="9"/>
-      <c r="H742" s="14"/>
+      <c r="H742" s="13"/>
       <c r="I742" s="21"/>
     </row>
     <row r="743">
       <c r="C743" s="22"/>
       <c r="F743" s="9"/>
       <c r="G743" s="9"/>
-      <c r="H743" s="14"/>
+      <c r="H743" s="13"/>
       <c r="I743" s="21"/>
     </row>
     <row r="744">
       <c r="C744" s="22"/>
       <c r="F744" s="9"/>
       <c r="G744" s="9"/>
-      <c r="H744" s="14"/>
+      <c r="H744" s="13"/>
       <c r="I744" s="21"/>
     </row>
     <row r="745">
       <c r="C745" s="22"/>
       <c r="F745" s="9"/>
       <c r="G745" s="9"/>
-      <c r="H745" s="14"/>
+      <c r="H745" s="13"/>
       <c r="I745" s="21"/>
     </row>
     <row r="746">
       <c r="C746" s="22"/>
       <c r="F746" s="9"/>
       <c r="G746" s="9"/>
-      <c r="H746" s="14"/>
+      <c r="H746" s="13"/>
       <c r="I746" s="21"/>
     </row>
     <row r="747">
       <c r="C747" s="22"/>
       <c r="F747" s="9"/>
       <c r="G747" s="9"/>
-      <c r="H747" s="14"/>
+      <c r="H747" s="13"/>
       <c r="I747" s="21"/>
     </row>
     <row r="748">
       <c r="C748" s="22"/>
       <c r="F748" s="9"/>
       <c r="G748" s="9"/>
-      <c r="H748" s="14"/>
+      <c r="H748" s="13"/>
       <c r="I748" s="21"/>
     </row>
     <row r="749">
       <c r="C749" s="22"/>
       <c r="F749" s="9"/>
       <c r="G749" s="9"/>
-      <c r="H749" s="14"/>
+      <c r="H749" s="13"/>
       <c r="I749" s="21"/>
     </row>
     <row r="750">
       <c r="C750" s="22"/>
       <c r="F750" s="9"/>
       <c r="G750" s="9"/>
-      <c r="H750" s="14"/>
+      <c r="H750" s="13"/>
       <c r="I750" s="21"/>
     </row>
     <row r="751">
       <c r="C751" s="22"/>
       <c r="F751" s="9"/>
       <c r="G751" s="9"/>
-      <c r="H751" s="14"/>
+      <c r="H751" s="13"/>
       <c r="I751" s="21"/>
     </row>
     <row r="752">
       <c r="C752" s="22"/>
       <c r="F752" s="9"/>
       <c r="G752" s="9"/>
-      <c r="H752" s="14"/>
+      <c r="H752" s="13"/>
       <c r="I752" s="21"/>
     </row>
     <row r="753">
       <c r="C753" s="22"/>
       <c r="F753" s="9"/>
       <c r="G753" s="9"/>
-      <c r="H753" s="14"/>
+      <c r="H753" s="13"/>
       <c r="I753" s="21"/>
     </row>
     <row r="754">
       <c r="C754" s="22"/>
       <c r="F754" s="9"/>
       <c r="G754" s="9"/>
-      <c r="H754" s="14"/>
+      <c r="H754" s="13"/>
       <c r="I754" s="21"/>
     </row>
     <row r="755">
       <c r="C755" s="22"/>
       <c r="F755" s="9"/>
       <c r="G755" s="9"/>
-      <c r="H755" s="14"/>
+      <c r="H755" s="13"/>
       <c r="I755" s="21"/>
     </row>
     <row r="756">
       <c r="C756" s="22"/>
       <c r="F756" s="9"/>
       <c r="G756" s="9"/>
-      <c r="H756" s="14"/>
+      <c r="H756" s="13"/>
       <c r="I756" s="21"/>
     </row>
     <row r="757">
       <c r="C757" s="22"/>
       <c r="F757" s="9"/>
       <c r="G757" s="9"/>
-      <c r="H757" s="14"/>
+      <c r="H757" s="13"/>
       <c r="I757" s="21"/>
     </row>
     <row r="758">
       <c r="C758" s="22"/>
       <c r="F758" s="9"/>
       <c r="G758" s="9"/>
-      <c r="H758" s="14"/>
+      <c r="H758" s="13"/>
       <c r="I758" s="21"/>
     </row>
     <row r="759">
       <c r="C759" s="22"/>
       <c r="F759" s="9"/>
       <c r="G759" s="9"/>
-      <c r="H759" s="14"/>
+      <c r="H759" s="13"/>
       <c r="I759" s="21"/>
     </row>
     <row r="760">
       <c r="C760" s="22"/>
       <c r="F760" s="9"/>
       <c r="G760" s="9"/>
-      <c r="H760" s="14"/>
+      <c r="H760" s="13"/>
       <c r="I760" s="21"/>
     </row>
     <row r="761">
       <c r="C761" s="22"/>
       <c r="F761" s="9"/>
       <c r="G761" s="9"/>
-      <c r="H761" s="14"/>
+      <c r="H761" s="13"/>
       <c r="I761" s="21"/>
     </row>
     <row r="762">
       <c r="C762" s="22"/>
       <c r="F762" s="9"/>
       <c r="G762" s="9"/>
-      <c r="H762" s="14"/>
+      <c r="H762" s="13"/>
       <c r="I762" s="21"/>
     </row>
     <row r="763">
       <c r="C763" s="22"/>
       <c r="F763" s="9"/>
       <c r="G763" s="9"/>
-      <c r="H763" s="14"/>
+      <c r="H763" s="13"/>
       <c r="I763" s="21"/>
     </row>
     <row r="764">
       <c r="C764" s="22"/>
       <c r="F764" s="9"/>
       <c r="G764" s="9"/>
-      <c r="H764" s="14"/>
+      <c r="H764" s="13"/>
       <c r="I764" s="21"/>
     </row>
     <row r="765">
       <c r="C765" s="22"/>
       <c r="F765" s="9"/>
       <c r="G765" s="9"/>
-      <c r="H765" s="14"/>
+      <c r="H765" s="13"/>
       <c r="I765" s="21"/>
     </row>
     <row r="766">
       <c r="C766" s="22"/>
       <c r="F766" s="9"/>
       <c r="G766" s="9"/>
-      <c r="H766" s="14"/>
+      <c r="H766" s="13"/>
       <c r="I766" s="21"/>
     </row>
     <row r="767">
       <c r="C767" s="22"/>
       <c r="F767" s="9"/>
       <c r="G767" s="9"/>
-      <c r="H767" s="14"/>
+      <c r="H767" s="13"/>
       <c r="I767" s="21"/>
     </row>
     <row r="768">
       <c r="C768" s="22"/>
       <c r="F768" s="9"/>
       <c r="G768" s="9"/>
-      <c r="H768" s="14"/>
+      <c r="H768" s="13"/>
       <c r="I768" s="21"/>
     </row>
     <row r="769">
       <c r="C769" s="22"/>
       <c r="F769" s="9"/>
       <c r="G769" s="9"/>
-      <c r="H769" s="14"/>
+      <c r="H769" s="13"/>
       <c r="I769" s="21"/>
     </row>
     <row r="770">
       <c r="C770" s="22"/>
       <c r="F770" s="9"/>
       <c r="G770" s="9"/>
-      <c r="H770" s="14"/>
+      <c r="H770" s="13"/>
       <c r="I770" s="21"/>
     </row>
     <row r="771">
       <c r="C771" s="22"/>
       <c r="F771" s="9"/>
       <c r="G771" s="9"/>
-      <c r="H771" s="14"/>
+      <c r="H771" s="13"/>
       <c r="I771" s="21"/>
     </row>
     <row r="772">
       <c r="C772" s="22"/>
       <c r="F772" s="9"/>
       <c r="G772" s="9"/>
-      <c r="H772" s="14"/>
+      <c r="H772" s="13"/>
       <c r="I772" s="21"/>
     </row>
     <row r="773">
       <c r="C773" s="22"/>
       <c r="F773" s="9"/>
       <c r="G773" s="9"/>
-      <c r="H773" s="14"/>
+      <c r="H773" s="13"/>
       <c r="I773" s="21"/>
     </row>
     <row r="774">
       <c r="C774" s="22"/>
       <c r="F774" s="9"/>
       <c r="G774" s="9"/>
-      <c r="H774" s="14"/>
+      <c r="H774" s="13"/>
       <c r="I774" s="21"/>
     </row>
     <row r="775">
       <c r="C775" s="22"/>
       <c r="F775" s="9"/>
       <c r="G775" s="9"/>
-      <c r="H775" s="14"/>
+      <c r="H775" s="13"/>
       <c r="I775" s="21"/>
     </row>
     <row r="776">
       <c r="C776" s="22"/>
       <c r="F776" s="9"/>
       <c r="G776" s="9"/>
-      <c r="H776" s="14"/>
+      <c r="H776" s="13"/>
       <c r="I776" s="21"/>
     </row>
     <row r="777">
       <c r="C777" s="22"/>
       <c r="F777" s="9"/>
       <c r="G777" s="9"/>
-      <c r="H777" s="14"/>
+      <c r="H777" s="13"/>
       <c r="I777" s="21"/>
     </row>
     <row r="778">
       <c r="C778" s="22"/>
       <c r="F778" s="9"/>
       <c r="G778" s="9"/>
-      <c r="H778" s="14"/>
+      <c r="H778" s="13"/>
       <c r="I778" s="21"/>
     </row>
     <row r="779">
       <c r="C779" s="22"/>
       <c r="F779" s="9"/>
       <c r="G779" s="9"/>
-      <c r="H779" s="14"/>
+      <c r="H779" s="13"/>
       <c r="I779" s="21"/>
     </row>
     <row r="780">
       <c r="C780" s="22"/>
       <c r="F780" s="9"/>
       <c r="G780" s="9"/>
-      <c r="H780" s="14"/>
+      <c r="H780" s="13"/>
       <c r="I780" s="21"/>
     </row>
     <row r="781">
       <c r="C781" s="22"/>
       <c r="F781" s="9"/>
       <c r="G781" s="9"/>
-      <c r="H781" s="14"/>
+      <c r="H781" s="13"/>
       <c r="I781" s="21"/>
     </row>
     <row r="782">
       <c r="C782" s="22"/>
       <c r="F782" s="9"/>
       <c r="G782" s="9"/>
-      <c r="H782" s="14"/>
+      <c r="H782" s="13"/>
       <c r="I782" s="21"/>
     </row>
     <row r="783">
       <c r="C783" s="22"/>
       <c r="F783" s="9"/>
       <c r="G783" s="9"/>
-      <c r="H783" s="14"/>
+      <c r="H783" s="13"/>
       <c r="I783" s="21"/>
     </row>
     <row r="784">
       <c r="C784" s="22"/>
       <c r="F784" s="9"/>
       <c r="G784" s="9"/>
-      <c r="H784" s="14"/>
+      <c r="H784" s="13"/>
       <c r="I784" s="21"/>
     </row>
     <row r="785">
       <c r="C785" s="22"/>
       <c r="F785" s="9"/>
       <c r="G785" s="9"/>
-      <c r="H785" s="14"/>
+      <c r="H785" s="13"/>
       <c r="I785" s="21"/>
     </row>
     <row r="786">
       <c r="C786" s="22"/>
       <c r="F786" s="9"/>
       <c r="G786" s="9"/>
-      <c r="H786" s="14"/>
+      <c r="H786" s="13"/>
       <c r="I786" s="21"/>
     </row>
     <row r="787">
       <c r="C787" s="22"/>
       <c r="F787" s="9"/>
       <c r="G787" s="9"/>
-      <c r="H787" s="14"/>
+      <c r="H787" s="13"/>
       <c r="I787" s="21"/>
     </row>
     <row r="788">
       <c r="C788" s="22"/>
       <c r="F788" s="9"/>
       <c r="G788" s="9"/>
-      <c r="H788" s="14"/>
+      <c r="H788" s="13"/>
       <c r="I788" s="21"/>
     </row>
     <row r="789">
       <c r="C789" s="22"/>
       <c r="F789" s="9"/>
       <c r="G789" s="9"/>
-      <c r="H789" s="14"/>
+      <c r="H789" s="13"/>
       <c r="I789" s="21"/>
     </row>
     <row r="790">
       <c r="C790" s="22"/>
       <c r="F790" s="9"/>
       <c r="G790" s="9"/>
-      <c r="H790" s="14"/>
+      <c r="H790" s="13"/>
       <c r="I790" s="21"/>
     </row>
     <row r="791">
       <c r="C791" s="22"/>
       <c r="F791" s="9"/>
       <c r="G791" s="9"/>
-      <c r="H791" s="14"/>
+      <c r="H791" s="13"/>
       <c r="I791" s="21"/>
     </row>
     <row r="792">
       <c r="C792" s="22"/>
       <c r="F792" s="9"/>
       <c r="G792" s="9"/>
-      <c r="H792" s="14"/>
+      <c r="H792" s="13"/>
       <c r="I792" s="21"/>
     </row>
     <row r="793">
       <c r="C793" s="22"/>
       <c r="F793" s="9"/>
       <c r="G793" s="9"/>
-      <c r="H793" s="14"/>
+      <c r="H793" s="13"/>
       <c r="I793" s="21"/>
     </row>
     <row r="794">
       <c r="C794" s="22"/>
       <c r="F794" s="9"/>
       <c r="G794" s="9"/>
-      <c r="H794" s="14"/>
+      <c r="H794" s="13"/>
       <c r="I794" s="21"/>
     </row>
     <row r="795">
       <c r="C795" s="22"/>
       <c r="F795" s="9"/>
       <c r="G795" s="9"/>
-      <c r="H795" s="14"/>
+      <c r="H795" s="13"/>
       <c r="I795" s="21"/>
     </row>
     <row r="796">
       <c r="C796" s="22"/>
       <c r="F796" s="9"/>
       <c r="G796" s="9"/>
-      <c r="H796" s="14"/>
+      <c r="H796" s="13"/>
       <c r="I796" s="21"/>
     </row>
     <row r="797">
       <c r="C797" s="22"/>
       <c r="F797" s="9"/>
       <c r="G797" s="9"/>
-      <c r="H797" s="14"/>
+      <c r="H797" s="13"/>
       <c r="I797" s="21"/>
     </row>
     <row r="798">
       <c r="C798" s="22"/>
       <c r="F798" s="9"/>
       <c r="G798" s="9"/>
-      <c r="H798" s="14"/>
+      <c r="H798" s="13"/>
       <c r="I798" s="21"/>
     </row>
     <row r="799">
       <c r="C799" s="22"/>
       <c r="F799" s="9"/>
       <c r="G799" s="9"/>
-      <c r="H799" s="14"/>
+      <c r="H799" s="13"/>
       <c r="I799" s="21"/>
     </row>
     <row r="800">
       <c r="C800" s="22"/>
       <c r="F800" s="9"/>
       <c r="G800" s="9"/>
-      <c r="H800" s="14"/>
+      <c r="H800" s="13"/>
       <c r="I800" s="21"/>
     </row>
     <row r="801">
       <c r="C801" s="22"/>
       <c r="F801" s="9"/>
       <c r="G801" s="9"/>
-      <c r="H801" s="14"/>
+      <c r="H801" s="13"/>
       <c r="I801" s="21"/>
     </row>
     <row r="802">
       <c r="C802" s="22"/>
       <c r="F802" s="9"/>
       <c r="G802" s="9"/>
-      <c r="H802" s="14"/>
+      <c r="H802" s="13"/>
       <c r="I802" s="21"/>
     </row>
     <row r="803">
       <c r="C803" s="22"/>
       <c r="F803" s="9"/>
       <c r="G803" s="9"/>
-      <c r="H803" s="14"/>
+      <c r="H803" s="13"/>
       <c r="I803" s="21"/>
     </row>
     <row r="804">
       <c r="C804" s="22"/>
       <c r="F804" s="9"/>
       <c r="G804" s="9"/>
-      <c r="H804" s="14"/>
+      <c r="H804" s="13"/>
       <c r="I804" s="21"/>
     </row>
     <row r="805">
       <c r="C805" s="22"/>
       <c r="F805" s="9"/>
       <c r="G805" s="9"/>
-      <c r="H805" s="14"/>
+      <c r="H805" s="13"/>
       <c r="I805" s="21"/>
     </row>
     <row r="806">
       <c r="C806" s="22"/>
       <c r="F806" s="9"/>
       <c r="G806" s="9"/>
-      <c r="H806" s="14"/>
+      <c r="H806" s="13"/>
       <c r="I806" s="21"/>
     </row>
     <row r="807">
       <c r="C807" s="22"/>
       <c r="F807" s="9"/>
       <c r="G807" s="9"/>
-      <c r="H807" s="14"/>
+      <c r="H807" s="13"/>
       <c r="I807" s="21"/>
     </row>
     <row r="808">
       <c r="C808" s="22"/>
       <c r="F808" s="9"/>
       <c r="G808" s="9"/>
-      <c r="H808" s="14"/>
+      <c r="H808" s="13"/>
       <c r="I808" s="21"/>
     </row>
     <row r="809">
       <c r="C809" s="22"/>
       <c r="F809" s="9"/>
       <c r="G809" s="9"/>
-      <c r="H809" s="14"/>
+      <c r="H809" s="13"/>
       <c r="I809" s="21"/>
     </row>
     <row r="810">
       <c r="C810" s="22"/>
       <c r="F810" s="9"/>
       <c r="G810" s="9"/>
-      <c r="H810" s="14"/>
+      <c r="H810" s="13"/>
       <c r="I810" s="21"/>
     </row>
     <row r="811">
       <c r="C811" s="22"/>
       <c r="F811" s="9"/>
       <c r="G811" s="9"/>
-      <c r="H811" s="14"/>
+      <c r="H811" s="13"/>
       <c r="I811" s="21"/>
     </row>
     <row r="812">
       <c r="C812" s="22"/>
       <c r="F812" s="9"/>
       <c r="G812" s="9"/>
-      <c r="H812" s="14"/>
+      <c r="H812" s="13"/>
       <c r="I812" s="21"/>
     </row>
     <row r="813">
       <c r="C813" s="22"/>
       <c r="F813" s="9"/>
       <c r="G813" s="9"/>
-      <c r="H813" s="14"/>
+      <c r="H813" s="13"/>
       <c r="I813" s="21"/>
     </row>
     <row r="814">
       <c r="C814" s="22"/>
       <c r="F814" s="9"/>
       <c r="G814" s="9"/>
-      <c r="H814" s="14"/>
+      <c r="H814" s="13"/>
       <c r="I814" s="21"/>
     </row>
     <row r="815">
       <c r="C815" s="22"/>
       <c r="F815" s="9"/>
       <c r="G815" s="9"/>
-      <c r="H815" s="14"/>
+      <c r="H815" s="13"/>
       <c r="I815" s="21"/>
     </row>
     <row r="816">
       <c r="C816" s="22"/>
       <c r="F816" s="9"/>
       <c r="G816" s="9"/>
-      <c r="H816" s="14"/>
+      <c r="H816" s="13"/>
       <c r="I816" s="21"/>
     </row>
     <row r="817">
       <c r="C817" s="22"/>
       <c r="F817" s="9"/>
       <c r="G817" s="9"/>
-      <c r="H817" s="14"/>
+      <c r="H817" s="13"/>
       <c r="I817" s="21"/>
     </row>
     <row r="818">
       <c r="C818" s="22"/>
       <c r="F818" s="9"/>
       <c r="G818" s="9"/>
-      <c r="H818" s="14"/>
+      <c r="H818" s="13"/>
       <c r="I818" s="21"/>
     </row>
     <row r="819">
       <c r="C819" s="22"/>
       <c r="F819" s="9"/>
       <c r="G819" s="9"/>
-      <c r="H819" s="14"/>
+      <c r="H819" s="13"/>
       <c r="I819" s="21"/>
     </row>
     <row r="820">
       <c r="C820" s="22"/>
       <c r="F820" s="9"/>
       <c r="G820" s="9"/>
-      <c r="H820" s="14"/>
+      <c r="H820" s="13"/>
       <c r="I820" s="21"/>
     </row>
     <row r="821">
       <c r="C821" s="22"/>
       <c r="F821" s="9"/>
       <c r="G821" s="9"/>
-      <c r="H821" s="14"/>
+      <c r="H821" s="13"/>
       <c r="I821" s="21"/>
     </row>
     <row r="822">
       <c r="C822" s="22"/>
       <c r="F822" s="9"/>
       <c r="G822" s="9"/>
-      <c r="H822" s="14"/>
+      <c r="H822" s="13"/>
       <c r="I822" s="21"/>
     </row>
     <row r="823">
       <c r="C823" s="22"/>
       <c r="F823" s="9"/>
       <c r="G823" s="9"/>
-      <c r="H823" s="14"/>
+      <c r="H823" s="13"/>
       <c r="I823" s="21"/>
     </row>
     <row r="824">
       <c r="C824" s="22"/>
       <c r="F824" s="9"/>
       <c r="G824" s="9"/>
-      <c r="H824" s="14"/>
+      <c r="H824" s="13"/>
       <c r="I824" s="21"/>
     </row>
     <row r="825">
       <c r="C825" s="22"/>
       <c r="F825" s="9"/>
       <c r="G825" s="9"/>
-      <c r="H825" s="14"/>
+      <c r="H825" s="13"/>
       <c r="I825" s="21"/>
     </row>
     <row r="826">
       <c r="C826" s="22"/>
       <c r="F826" s="9"/>
       <c r="G826" s="9"/>
-      <c r="H826" s="14"/>
+      <c r="H826" s="13"/>
       <c r="I826" s="21"/>
     </row>
     <row r="827">
       <c r="C827" s="22"/>
       <c r="F827" s="9"/>
       <c r="G827" s="9"/>
-      <c r="H827" s="14"/>
+      <c r="H827" s="13"/>
       <c r="I827" s="21"/>
     </row>
     <row r="828">
       <c r="C828" s="22"/>
       <c r="F828" s="9"/>
       <c r="G828" s="9"/>
-      <c r="H828" s="14"/>
+      <c r="H828" s="13"/>
       <c r="I828" s="21"/>
     </row>
     <row r="829">
       <c r="C829" s="22"/>
       <c r="F829" s="9"/>
       <c r="G829" s="9"/>
-      <c r="H829" s="14"/>
+      <c r="H829" s="13"/>
       <c r="I829" s="21"/>
     </row>
     <row r="830">
       <c r="C830" s="22"/>
       <c r="F830" s="9"/>
       <c r="G830" s="9"/>
-      <c r="H830" s="14"/>
+      <c r="H830" s="13"/>
       <c r="I830" s="21"/>
     </row>
     <row r="831">
       <c r="C831" s="22"/>
       <c r="F831" s="9"/>
       <c r="G831" s="9"/>
-      <c r="H831" s="14"/>
+      <c r="H831" s="13"/>
       <c r="I831" s="21"/>
     </row>
     <row r="832">
       <c r="C832" s="22"/>
       <c r="F832" s="9"/>
       <c r="G832" s="9"/>
-      <c r="H832" s="14"/>
+      <c r="H832" s="13"/>
       <c r="I832" s="21"/>
     </row>
     <row r="833">
       <c r="C833" s="22"/>
       <c r="F833" s="9"/>
       <c r="G833" s="9"/>
-      <c r="H833" s="14"/>
+      <c r="H833" s="13"/>
       <c r="I833" s="21"/>
     </row>
     <row r="834">
       <c r="C834" s="22"/>
       <c r="F834" s="9"/>
       <c r="G834" s="9"/>
-      <c r="H834" s="14"/>
+      <c r="H834" s="13"/>
       <c r="I834" s="21"/>
     </row>
     <row r="835">
       <c r="C835" s="22"/>
       <c r="F835" s="9"/>
       <c r="G835" s="9"/>
-      <c r="H835" s="14"/>
+      <c r="H835" s="13"/>
       <c r="I835" s="21"/>
     </row>
     <row r="836">
       <c r="C836" s="22"/>
       <c r="F836" s="9"/>
       <c r="G836" s="9"/>
-      <c r="H836" s="14"/>
+      <c r="H836" s="13"/>
       <c r="I836" s="21"/>
     </row>
     <row r="837">
       <c r="C837" s="22"/>
       <c r="F837" s="9"/>
       <c r="G837" s="9"/>
-      <c r="H837" s="14"/>
+      <c r="H837" s="13"/>
       <c r="I837" s="21"/>
     </row>
     <row r="838">
       <c r="C838" s="22"/>
       <c r="F838" s="9"/>
       <c r="G838" s="9"/>
-      <c r="H838" s="14"/>
+      <c r="H838" s="13"/>
       <c r="I838" s="21"/>
     </row>
     <row r="839">
       <c r="C839" s="22"/>
       <c r="F839" s="9"/>
       <c r="G839" s="9"/>
-      <c r="H839" s="14"/>
+      <c r="H839" s="13"/>
       <c r="I839" s="21"/>
     </row>
     <row r="840">
       <c r="C840" s="22"/>
       <c r="F840" s="9"/>
       <c r="G840" s="9"/>
-      <c r="H840" s="14"/>
+      <c r="H840" s="13"/>
       <c r="I840" s="21"/>
     </row>
     <row r="841">
       <c r="C841" s="22"/>
       <c r="F841" s="9"/>
       <c r="G841" s="9"/>
-      <c r="H841" s="14"/>
+      <c r="H841" s="13"/>
       <c r="I841" s="21"/>
     </row>
     <row r="842">
       <c r="C842" s="22"/>
       <c r="F842" s="9"/>
       <c r="G842" s="9"/>
-      <c r="H842" s="14"/>
+      <c r="H842" s="13"/>
       <c r="I842" s="21"/>
     </row>
     <row r="843">
       <c r="C843" s="22"/>
       <c r="F843" s="9"/>
       <c r="G843" s="9"/>
-      <c r="H843" s="14"/>
+      <c r="H843" s="13"/>
       <c r="I843" s="21"/>
     </row>
     <row r="844">
       <c r="C844" s="22"/>
       <c r="F844" s="9"/>
       <c r="G844" s="9"/>
-      <c r="H844" s="14"/>
+      <c r="H844" s="13"/>
       <c r="I844" s="21"/>
     </row>
     <row r="845">
       <c r="C845" s="22"/>
       <c r="F845" s="9"/>
       <c r="G845" s="9"/>
-      <c r="H845" s="14"/>
+      <c r="H845" s="13"/>
       <c r="I845" s="21"/>
     </row>
     <row r="846">
       <c r="C846" s="22"/>
       <c r="F846" s="9"/>
       <c r="G846" s="9"/>
-      <c r="H846" s="14"/>
+      <c r="H846" s="13"/>
       <c r="I846" s="21"/>
     </row>
     <row r="847">
       <c r="C847" s="22"/>
       <c r="F847" s="9"/>
       <c r="G847" s="9"/>
-      <c r="H847" s="14"/>
+      <c r="H847" s="13"/>
       <c r="I847" s="21"/>
     </row>
     <row r="848">
       <c r="C848" s="22"/>
       <c r="F848" s="9"/>
       <c r="G848" s="9"/>
-      <c r="H848" s="14"/>
+      <c r="H848" s="13"/>
       <c r="I848" s="21"/>
     </row>
     <row r="849">
       <c r="C849" s="22"/>
       <c r="F849" s="9"/>
       <c r="G849" s="9"/>
-      <c r="H849" s="14"/>
+      <c r="H849" s="13"/>
       <c r="I849" s="21"/>
     </row>
     <row r="850">
       <c r="C850" s="22"/>
       <c r="F850" s="9"/>
       <c r="G850" s="9"/>
-      <c r="H850" s="14"/>
+      <c r="H850" s="13"/>
       <c r="I850" s="21"/>
     </row>
     <row r="851">
       <c r="C851" s="22"/>
       <c r="F851" s="9"/>
       <c r="G851" s="9"/>
-      <c r="H851" s="14"/>
+      <c r="H851" s="13"/>
       <c r="I851" s="21"/>
     </row>
     <row r="852">
       <c r="C852" s="22"/>
       <c r="F852" s="9"/>
       <c r="G852" s="9"/>
-      <c r="H852" s="14"/>
+      <c r="H852" s="13"/>
       <c r="I852" s="21"/>
     </row>
     <row r="853">
       <c r="C853" s="22"/>
       <c r="F853" s="9"/>
       <c r="G853" s="9"/>
-      <c r="H853" s="14"/>
+      <c r="H853" s="13"/>
       <c r="I853" s="21"/>
     </row>
     <row r="854">
       <c r="C854" s="22"/>
       <c r="F854" s="9"/>
       <c r="G854" s="9"/>
-      <c r="H854" s="14"/>
+      <c r="H854" s="13"/>
       <c r="I854" s="21"/>
     </row>
     <row r="855">
       <c r="C855" s="22"/>
       <c r="F855" s="9"/>
       <c r="G855" s="9"/>
-      <c r="H855" s="14"/>
+      <c r="H855" s="13"/>
       <c r="I855" s="21"/>
     </row>
     <row r="856">
       <c r="C856" s="22"/>
       <c r="F856" s="9"/>
       <c r="G856" s="9"/>
-      <c r="H856" s="14"/>
+      <c r="H856" s="13"/>
       <c r="I856" s="21"/>
     </row>
     <row r="857">
       <c r="C857" s="22"/>
       <c r="F857" s="9"/>
       <c r="G857" s="9"/>
-      <c r="H857" s="14"/>
+      <c r="H857" s="13"/>
       <c r="I857" s="21"/>
     </row>
     <row r="858">
       <c r="C858" s="22"/>
       <c r="F858" s="9"/>
       <c r="G858" s="9"/>
-      <c r="H858" s="14"/>
+      <c r="H858" s="13"/>
       <c r="I858" s="21"/>
     </row>
     <row r="859">
       <c r="C859" s="22"/>
       <c r="F859" s="9"/>
       <c r="G859" s="9"/>
-      <c r="H859" s="14"/>
+      <c r="H859" s="13"/>
       <c r="I859" s="21"/>
     </row>
     <row r="860">
       <c r="C860" s="22"/>
       <c r="F860" s="9"/>
       <c r="G860" s="9"/>
-      <c r="H860" s="14"/>
+      <c r="H860" s="13"/>
       <c r="I860" s="21"/>
     </row>
     <row r="861">
       <c r="C861" s="22"/>
       <c r="F861" s="9"/>
       <c r="G861" s="9"/>
-      <c r="H861" s="14"/>
+      <c r="H861" s="13"/>
       <c r="I861" s="21"/>
     </row>
     <row r="862">
       <c r="C862" s="22"/>
       <c r="F862" s="9"/>
       <c r="G862" s="9"/>
-      <c r="H862" s="14"/>
+      <c r="H862" s="13"/>
       <c r="I862" s="21"/>
     </row>
     <row r="863">
       <c r="C863" s="22"/>
       <c r="F863" s="9"/>
       <c r="G863" s="9"/>
-      <c r="H863" s="14"/>
+      <c r="H863" s="13"/>
       <c r="I863" s="21"/>
     </row>
     <row r="864">
       <c r="C864" s="22"/>
       <c r="F864" s="9"/>
       <c r="G864" s="9"/>
-      <c r="H864" s="14"/>
+      <c r="H864" s="13"/>
       <c r="I864" s="21"/>
     </row>
     <row r="865">
       <c r="C865" s="22"/>
       <c r="F865" s="9"/>
       <c r="G865" s="9"/>
-      <c r="H865" s="14"/>
+      <c r="H865" s="13"/>
       <c r="I865" s="21"/>
     </row>
     <row r="866">
       <c r="C866" s="22"/>
       <c r="F866" s="9"/>
       <c r="G866" s="9"/>
-      <c r="H866" s="14"/>
+      <c r="H866" s="13"/>
       <c r="I866" s="21"/>
     </row>
     <row r="867">
       <c r="C867" s="22"/>
       <c r="F867" s="9"/>
       <c r="G867" s="9"/>
-      <c r="H867" s="14"/>
+      <c r="H867" s="13"/>
       <c r="I867" s="21"/>
     </row>
     <row r="868">
       <c r="C868" s="22"/>
       <c r="F868" s="9"/>
       <c r="G868" s="9"/>
-      <c r="H868" s="14"/>
+      <c r="H868" s="13"/>
       <c r="I868" s="21"/>
     </row>
     <row r="869">
       <c r="C869" s="22"/>
       <c r="F869" s="9"/>
       <c r="G869" s="9"/>
-      <c r="H869" s="14"/>
+      <c r="H869" s="13"/>
       <c r="I869" s="21"/>
     </row>
     <row r="870">
       <c r="C870" s="22"/>
       <c r="F870" s="9"/>
       <c r="G870" s="9"/>
-      <c r="H870" s="14"/>
+      <c r="H870" s="13"/>
       <c r="I870" s="21"/>
     </row>
     <row r="871">
       <c r="C871" s="22"/>
       <c r="F871" s="9"/>
       <c r="G871" s="9"/>
-      <c r="H871" s="14"/>
+      <c r="H871" s="13"/>
       <c r="I871" s="21"/>
     </row>
     <row r="872">
       <c r="C872" s="22"/>
       <c r="F872" s="9"/>
       <c r="G872" s="9"/>
-      <c r="H872" s="14"/>
+      <c r="H872" s="13"/>
       <c r="I872" s="21"/>
     </row>
     <row r="873">
       <c r="C873" s="22"/>
       <c r="F873" s="9"/>
       <c r="G873" s="9"/>
-      <c r="H873" s="14"/>
+      <c r="H873" s="13"/>
       <c r="I873" s="21"/>
     </row>
     <row r="874">
       <c r="C874" s="22"/>
       <c r="F874" s="9"/>
       <c r="G874" s="9"/>
-      <c r="H874" s="14"/>
+      <c r="H874" s="13"/>
       <c r="I874" s="21"/>
     </row>
     <row r="875">
       <c r="C875" s="22"/>
       <c r="F875" s="9"/>
       <c r="G875" s="9"/>
-      <c r="H875" s="14"/>
+      <c r="H875" s="13"/>
       <c r="I875" s="21"/>
     </row>
     <row r="876">
       <c r="C876" s="22"/>
       <c r="F876" s="9"/>
       <c r="G876" s="9"/>
-      <c r="H876" s="14"/>
+      <c r="H876" s="13"/>
       <c r="I876" s="21"/>
     </row>
     <row r="877">
       <c r="C877" s="22"/>
       <c r="F877" s="9"/>
       <c r="G877" s="9"/>
-      <c r="H877" s="14"/>
+      <c r="H877" s="13"/>
       <c r="I877" s="21"/>
     </row>
     <row r="878">
       <c r="C878" s="22"/>
       <c r="F878" s="9"/>
       <c r="G878" s="9"/>
-      <c r="H878" s="14"/>
+      <c r="H878" s="13"/>
       <c r="I878" s="21"/>
     </row>
     <row r="879">
       <c r="C879" s="22"/>
       <c r="F879" s="9"/>
       <c r="G879" s="9"/>
-      <c r="H879" s="14"/>
+      <c r="H879" s="13"/>
       <c r="I879" s="21"/>
     </row>
     <row r="880">
       <c r="C880" s="22"/>
       <c r="F880" s="9"/>
       <c r="G880" s="9"/>
-      <c r="H880" s="14"/>
+      <c r="H880" s="13"/>
       <c r="I880" s="21"/>
     </row>
     <row r="881">
       <c r="C881" s="22"/>
       <c r="F881" s="9"/>
       <c r="G881" s="9"/>
-      <c r="H881" s="14"/>
+      <c r="H881" s="13"/>
       <c r="I881" s="21"/>
     </row>
     <row r="882">
       <c r="C882" s="22"/>
       <c r="F882" s="9"/>
       <c r="G882" s="9"/>
-      <c r="H882" s="14"/>
+      <c r="H882" s="13"/>
       <c r="I882" s="21"/>
     </row>
     <row r="883">
       <c r="C883" s="22"/>
       <c r="F883" s="9"/>
       <c r="G883" s="9"/>
-      <c r="H883" s="14"/>
+      <c r="H883" s="13"/>
       <c r="I883" s="21"/>
     </row>
     <row r="884">
       <c r="C884" s="22"/>
       <c r="F884" s="9"/>
       <c r="G884" s="9"/>
-      <c r="H884" s="14"/>
+      <c r="H884" s="13"/>
       <c r="I884" s="21"/>
     </row>
     <row r="885">
       <c r="C885" s="22"/>
       <c r="F885" s="9"/>
       <c r="G885" s="9"/>
-      <c r="H885" s="14"/>
+      <c r="H885" s="13"/>
       <c r="I885" s="21"/>
     </row>
     <row r="886">
       <c r="C886" s="22"/>
       <c r="F886" s="9"/>
       <c r="G886" s="9"/>
-      <c r="H886" s="14"/>
+      <c r="H886" s="13"/>
       <c r="I886" s="21"/>
     </row>
     <row r="887">
       <c r="C887" s="22"/>
       <c r="F887" s="9"/>
       <c r="G887" s="9"/>
-      <c r="H887" s="14"/>
+      <c r="H887" s="13"/>
       <c r="I887" s="21"/>
     </row>
     <row r="888">
       <c r="C888" s="22"/>
       <c r="F888" s="9"/>
       <c r="G888" s="9"/>
-      <c r="H888" s="14"/>
+      <c r="H888" s="13"/>
       <c r="I888" s="21"/>
     </row>
     <row r="889">
       <c r="C889" s="22"/>
       <c r="F889" s="9"/>
       <c r="G889" s="9"/>
-      <c r="H889" s="14"/>
+      <c r="H889" s="13"/>
       <c r="I889" s="21"/>
     </row>
     <row r="890">
       <c r="C890" s="22"/>
       <c r="F890" s="9"/>
       <c r="G890" s="9"/>
-      <c r="H890" s="14"/>
+      <c r="H890" s="13"/>
       <c r="I890" s="21"/>
     </row>
     <row r="891">
       <c r="C891" s="22"/>
       <c r="F891" s="9"/>
       <c r="G891" s="9"/>
-      <c r="H891" s="14"/>
+      <c r="H891" s="13"/>
       <c r="I891" s="21"/>
     </row>
     <row r="892">
       <c r="C892" s="22"/>
       <c r="F892" s="9"/>
       <c r="G892" s="9"/>
-      <c r="H892" s="14"/>
+      <c r="H892" s="13"/>
       <c r="I892" s="21"/>
     </row>
     <row r="893">
       <c r="C893" s="22"/>
       <c r="F893" s="9"/>
       <c r="G893" s="9"/>
-      <c r="H893" s="14"/>
+      <c r="H893" s="13"/>
       <c r="I893" s="21"/>
     </row>
     <row r="894">
       <c r="C894" s="22"/>
       <c r="F894" s="9"/>
       <c r="G894" s="9"/>
-      <c r="H894" s="14"/>
+      <c r="H894" s="13"/>
       <c r="I894" s="21"/>
     </row>
     <row r="895">
       <c r="C895" s="22"/>
       <c r="F895" s="9"/>
       <c r="G895" s="9"/>
-      <c r="H895" s="14"/>
+      <c r="H895" s="13"/>
       <c r="I895" s="21"/>
     </row>
     <row r="896">
       <c r="C896" s="22"/>
       <c r="F896" s="9"/>
       <c r="G896" s="9"/>
-      <c r="H896" s="14"/>
+      <c r="H896" s="13"/>
       <c r="I896" s="21"/>
     </row>
     <row r="897">
       <c r="C897" s="22"/>
       <c r="F897" s="9"/>
       <c r="G897" s="9"/>
-      <c r="H897" s="14"/>
+      <c r="H897" s="13"/>
       <c r="I897" s="21"/>
     </row>
     <row r="898">
       <c r="C898" s="22"/>
       <c r="F898" s="9"/>
       <c r="G898" s="9"/>
-      <c r="H898" s="14"/>
+      <c r="H898" s="13"/>
       <c r="I898" s="21"/>
     </row>
     <row r="899">
       <c r="C899" s="22"/>
       <c r="F899" s="9"/>
       <c r="G899" s="9"/>
-      <c r="H899" s="14"/>
+      <c r="H899" s="13"/>
       <c r="I899" s="21"/>
     </row>
     <row r="900">
       <c r="C900" s="22"/>
       <c r="F900" s="9"/>
       <c r="G900" s="9"/>
-      <c r="H900" s="14"/>
+      <c r="H900" s="13"/>
       <c r="I900" s="21"/>
     </row>
     <row r="901">
       <c r="C901" s="22"/>
       <c r="F901" s="9"/>
       <c r="G901" s="9"/>
-      <c r="H901" s="14"/>
+      <c r="H901" s="13"/>
       <c r="I901" s="21"/>
     </row>
     <row r="902">
       <c r="C902" s="22"/>
       <c r="F902" s="9"/>
       <c r="G902" s="9"/>
-      <c r="H902" s="14"/>
+      <c r="H902" s="13"/>
       <c r="I902" s="21"/>
     </row>
     <row r="903">
       <c r="C903" s="22"/>
       <c r="F903" s="9"/>
       <c r="G903" s="9"/>
-      <c r="H903" s="14"/>
+      <c r="H903" s="13"/>
       <c r="I903" s="21"/>
     </row>
     <row r="904">
       <c r="C904" s="22"/>
       <c r="F904" s="9"/>
       <c r="G904" s="9"/>
-      <c r="H904" s="14"/>
+      <c r="H904" s="13"/>
       <c r="I904" s="21"/>
     </row>
     <row r="905">
       <c r="C905" s="22"/>
       <c r="F905" s="9"/>
       <c r="G905" s="9"/>
-      <c r="H905" s="14"/>
+      <c r="H905" s="13"/>
       <c r="I905" s="21"/>
     </row>
     <row r="906">
       <c r="C906" s="22"/>
       <c r="F906" s="9"/>
       <c r="G906" s="9"/>
-      <c r="H906" s="14"/>
+      <c r="H906" s="13"/>
       <c r="I906" s="21"/>
     </row>
     <row r="907">
       <c r="C907" s="22"/>
       <c r="F907" s="9"/>
       <c r="G907" s="9"/>
-      <c r="H907" s="14"/>
+      <c r="H907" s="13"/>
       <c r="I907" s="21"/>
     </row>
     <row r="908">
       <c r="C908" s="22"/>
       <c r="F908" s="9"/>
       <c r="G908" s="9"/>
-      <c r="H908" s="14"/>
+      <c r="H908" s="13"/>
       <c r="I908" s="21"/>
     </row>
     <row r="909">
       <c r="C909" s="22"/>
       <c r="F909" s="9"/>
       <c r="G909" s="9"/>
-      <c r="H909" s="14"/>
+      <c r="H909" s="13"/>
       <c r="I909" s="21"/>
     </row>
     <row r="910">
       <c r="C910" s="22"/>
       <c r="F910" s="9"/>
       <c r="G910" s="9"/>
-      <c r="H910" s="14"/>
+      <c r="H910" s="13"/>
       <c r="I910" s="21"/>
     </row>
     <row r="911">
       <c r="C911" s="22"/>
       <c r="F911" s="9"/>
       <c r="G911" s="9"/>
-      <c r="H911" s="14"/>
+      <c r="H911" s="13"/>
       <c r="I911" s="21"/>
     </row>
     <row r="912">
       <c r="C912" s="22"/>
       <c r="F912" s="9"/>
       <c r="G912" s="9"/>
-      <c r="H912" s="14"/>
+      <c r="H912" s="13"/>
       <c r="I912" s="21"/>
     </row>
     <row r="913">
       <c r="C913" s="22"/>
       <c r="F913" s="9"/>
       <c r="G913" s="9"/>
-      <c r="H913" s="14"/>
+      <c r="H913" s="13"/>
       <c r="I913" s="21"/>
     </row>
     <row r="914">
       <c r="C914" s="22"/>
       <c r="F914" s="9"/>
       <c r="G914" s="9"/>
-      <c r="H914" s="14"/>
+      <c r="H914" s="13"/>
       <c r="I914" s="21"/>
     </row>
     <row r="915">
       <c r="C915" s="22"/>
       <c r="F915" s="9"/>
       <c r="G915" s="9"/>
-      <c r="H915" s="14"/>
+      <c r="H915" s="13"/>
       <c r="I915" s="21"/>
     </row>
     <row r="916">
       <c r="C916" s="22"/>
       <c r="F916" s="9"/>
       <c r="G916" s="9"/>
-      <c r="H916" s="14"/>
+      <c r="H916" s="13"/>
       <c r="I916" s="21"/>
     </row>
     <row r="917">
       <c r="C917" s="22"/>
       <c r="F917" s="9"/>
       <c r="G917" s="9"/>
-      <c r="H917" s="14"/>
+      <c r="H917" s="13"/>
       <c r="I917" s="21"/>
     </row>
     <row r="918">
       <c r="C918" s="22"/>
       <c r="F918" s="9"/>
       <c r="G918" s="9"/>
-      <c r="H918" s="14"/>
+      <c r="H918" s="13"/>
       <c r="I918" s="21"/>
     </row>
     <row r="919">
       <c r="C919" s="22"/>
       <c r="F919" s="9"/>
       <c r="G919" s="9"/>
-      <c r="H919" s="14"/>
+      <c r="H919" s="13"/>
       <c r="I919" s="21"/>
     </row>
     <row r="920">
       <c r="C920" s="22"/>
       <c r="F920" s="9"/>
       <c r="G920" s="9"/>
-      <c r="H920" s="14"/>
+      <c r="H920" s="13"/>
       <c r="I920" s="21"/>
     </row>
     <row r="921">
       <c r="C921" s="22"/>
       <c r="F921" s="9"/>
       <c r="G921" s="9"/>
-      <c r="H921" s="14"/>
+      <c r="H921" s="13"/>
       <c r="I921" s="21"/>
     </row>
     <row r="922">
       <c r="C922" s="22"/>
       <c r="F922" s="9"/>
       <c r="G922" s="9"/>
-      <c r="H922" s="14"/>
+      <c r="H922" s="13"/>
       <c r="I922" s="21"/>
     </row>
     <row r="923">
       <c r="C923" s="22"/>
       <c r="F923" s="9"/>
       <c r="G923" s="9"/>
-      <c r="H923" s="14"/>
+      <c r="H923" s="13"/>
       <c r="I923" s="21"/>
     </row>
     <row r="924">
       <c r="C924" s="22"/>
       <c r="F924" s="9"/>
       <c r="G924" s="9"/>
-      <c r="H924" s="14"/>
+      <c r="H924" s="13"/>
       <c r="I924" s="21"/>
     </row>
     <row r="925">
       <c r="C925" s="22"/>
       <c r="F925" s="9"/>
       <c r="G925" s="9"/>
-      <c r="H925" s="14"/>
+      <c r="H925" s="13"/>
       <c r="I925" s="21"/>
     </row>
     <row r="926">
       <c r="C926" s="22"/>
       <c r="F926" s="9"/>
       <c r="G926" s="9"/>
-      <c r="H926" s="14"/>
+      <c r="H926" s="13"/>
       <c r="I926" s="21"/>
     </row>
     <row r="927">
       <c r="C927" s="22"/>
       <c r="F927" s="9"/>
       <c r="G927" s="9"/>
-      <c r="H927" s="14"/>
+      <c r="H927" s="13"/>
       <c r="I927" s="21"/>
     </row>
     <row r="928">
       <c r="C928" s="22"/>
       <c r="F928" s="9"/>
       <c r="G928" s="9"/>
-      <c r="H928" s="14"/>
+      <c r="H928" s="13"/>
       <c r="I928" s="21"/>
     </row>
     <row r="929">
       <c r="C929" s="22"/>
       <c r="F929" s="9"/>
       <c r="G929" s="9"/>
-      <c r="H929" s="14"/>
+      <c r="H929" s="13"/>
       <c r="I929" s="21"/>
     </row>
     <row r="930">
       <c r="C930" s="22"/>
       <c r="F930" s="9"/>
       <c r="G930" s="9"/>
-      <c r="H930" s="14"/>
+      <c r="H930" s="13"/>
       <c r="I930" s="21"/>
     </row>
     <row r="931">
       <c r="C931" s="22"/>
       <c r="F931" s="9"/>
       <c r="G931" s="9"/>
-      <c r="H931" s="14"/>
+      <c r="H931" s="13"/>
       <c r="I931" s="21"/>
     </row>
     <row r="932">
       <c r="C932" s="22"/>
       <c r="F932" s="9"/>
       <c r="G932" s="9"/>
-      <c r="H932" s="14"/>
+      <c r="H932" s="13"/>
       <c r="I932" s="21"/>
     </row>
     <row r="933">
       <c r="C933" s="22"/>
       <c r="F933" s="9"/>
       <c r="G933" s="9"/>
-      <c r="H933" s="14"/>
+      <c r="H933" s="13"/>
       <c r="I933" s="21"/>
     </row>
     <row r="934">
       <c r="C934" s="22"/>
       <c r="F934" s="9"/>
       <c r="G934" s="9"/>
-      <c r="H934" s="14"/>
+      <c r="H934" s="13"/>
       <c r="I934" s="21"/>
     </row>
     <row r="935">
       <c r="C935" s="22"/>
       <c r="F935" s="9"/>
       <c r="G935" s="9"/>
-      <c r="H935" s="14"/>
+      <c r="H935" s="13"/>
       <c r="I935" s="21"/>
     </row>
     <row r="936">
       <c r="C936" s="22"/>
       <c r="F936" s="9"/>
       <c r="G936" s="9"/>
-      <c r="H936" s="14"/>
+      <c r="H936" s="13"/>
       <c r="I936" s="21"/>
     </row>
     <row r="937">
       <c r="C937" s="22"/>
       <c r="F937" s="9"/>
       <c r="G937" s="9"/>
-      <c r="H937" s="14"/>
+      <c r="H937" s="13"/>
       <c r="I937" s="21"/>
     </row>
     <row r="938">
       <c r="C938" s="22"/>
       <c r="F938" s="9"/>
       <c r="G938" s="9"/>
-      <c r="H938" s="14"/>
+      <c r="H938" s="13"/>
       <c r="I938" s="21"/>
     </row>
     <row r="939">
       <c r="C939" s="22"/>
       <c r="F939" s="9"/>
       <c r="G939" s="9"/>
-      <c r="H939" s="14"/>
+      <c r="H939" s="13"/>
       <c r="I939" s="21"/>
     </row>
     <row r="940">
       <c r="C940" s="22"/>
       <c r="F940" s="9"/>
       <c r="G940" s="9"/>
-      <c r="H940" s="14"/>
+      <c r="H940" s="13"/>
       <c r="I940" s="21"/>
     </row>
     <row r="941">
       <c r="C941" s="22"/>
       <c r="F941" s="9"/>
       <c r="G941" s="9"/>
-      <c r="H941" s="14"/>
+      <c r="H941" s="13"/>
       <c r="I941" s="21"/>
     </row>
     <row r="942">
       <c r="C942" s="22"/>
       <c r="F942" s="9"/>
       <c r="G942" s="9"/>
-      <c r="H942" s="14"/>
+      <c r="H942" s="13"/>
       <c r="I942" s="21"/>
     </row>
     <row r="943">
       <c r="C943" s="22"/>
       <c r="F943" s="9"/>
       <c r="G943" s="9"/>
-      <c r="H943" s="14"/>
+      <c r="H943" s="13"/>
       <c r="I943" s="21"/>
     </row>
     <row r="944">
       <c r="C944" s="22"/>
       <c r="F944" s="9"/>
       <c r="G944" s="9"/>
-      <c r="H944" s="14"/>
+      <c r="H944" s="13"/>
       <c r="I944" s="21"/>
     </row>
     <row r="945">
       <c r="C945" s="22"/>
       <c r="F945" s="9"/>
       <c r="G945" s="9"/>
-      <c r="H945" s="14"/>
+      <c r="H945" s="13"/>
       <c r="I945" s="21"/>
     </row>
     <row r="946">
       <c r="C946" s="22"/>
       <c r="F946" s="9"/>
       <c r="G946" s="9"/>
-      <c r="H946" s="14"/>
+      <c r="H946" s="13"/>
       <c r="I946" s="21"/>
     </row>
     <row r="947">
       <c r="C947" s="22"/>
       <c r="F947" s="9"/>
       <c r="G947" s="9"/>
-      <c r="H947" s="14"/>
+      <c r="H947" s="13"/>
       <c r="I947" s="21"/>
     </row>
     <row r="948">
       <c r="C948" s="22"/>
       <c r="F948" s="9"/>
       <c r="G948" s="9"/>
-      <c r="H948" s="14"/>
+      <c r="H948" s="13"/>
       <c r="I948" s="21"/>
     </row>
     <row r="949">
       <c r="C949" s="22"/>
       <c r="F949" s="9"/>
       <c r="G949" s="9"/>
-      <c r="H949" s="14"/>
+      <c r="H949" s="13"/>
       <c r="I949" s="21"/>
     </row>
     <row r="950">
       <c r="C950" s="22"/>
       <c r="F950" s="9"/>
       <c r="G950" s="9"/>
-      <c r="H950" s="14"/>
+      <c r="H950" s="13"/>
       <c r="I950" s="21"/>
     </row>
     <row r="951">
       <c r="C951" s="22"/>
       <c r="F951" s="9"/>
       <c r="G951" s="9"/>
-      <c r="H951" s="14"/>
+      <c r="H951" s="13"/>
       <c r="I951" s="21"/>
     </row>
     <row r="952">
       <c r="C952" s="22"/>
       <c r="F952" s="9"/>
       <c r="G952" s="9"/>
-      <c r="H952" s="14"/>
+      <c r="H952" s="13"/>
       <c r="I952" s="21"/>
     </row>
     <row r="953">
       <c r="C953" s="22"/>
       <c r="F953" s="9"/>
       <c r="G953" s="9"/>
-      <c r="H953" s="14"/>
+      <c r="H953" s="13"/>
       <c r="I953" s="21"/>
     </row>
     <row r="954">
       <c r="C954" s="22"/>
       <c r="F954" s="9"/>
       <c r="G954" s="9"/>
-      <c r="H954" s="14"/>
+      <c r="H954" s="13"/>
       <c r="I954" s="21"/>
     </row>
     <row r="955">
       <c r="C955" s="22"/>
       <c r="F955" s="9"/>
       <c r="G955" s="9"/>
-      <c r="H955" s="14"/>
+      <c r="H955" s="13"/>
       <c r="I955" s="21"/>
     </row>
     <row r="956">
       <c r="C956" s="22"/>
       <c r="F956" s="9"/>
       <c r="G956" s="9"/>
-      <c r="H956" s="14"/>
+      <c r="H956" s="13"/>
       <c r="I956" s="21"/>
     </row>
     <row r="957">
       <c r="C957" s="22"/>
       <c r="F957" s="9"/>
       <c r="G957" s="9"/>
-      <c r="H957" s="14"/>
+      <c r="H957" s="13"/>
       <c r="I957" s="21"/>
     </row>
     <row r="958">
       <c r="C958" s="22"/>
       <c r="F958" s="9"/>
       <c r="G958" s="9"/>
-      <c r="H958" s="14"/>
+      <c r="H958" s="13"/>
       <c r="I958" s="21"/>
     </row>
     <row r="959">
       <c r="C959" s="22"/>
       <c r="F959" s="9"/>
       <c r="G959" s="9"/>
-      <c r="H959" s="14"/>
+      <c r="H959" s="13"/>
       <c r="I959" s="21"/>
     </row>
     <row r="960">
       <c r="C960" s="22"/>
       <c r="F960" s="9"/>
       <c r="G960" s="9"/>
-      <c r="H960" s="14"/>
+      <c r="H960" s="13"/>
       <c r="I960" s="21"/>
     </row>
     <row r="961">
       <c r="C961" s="22"/>
       <c r="F961" s="9"/>
       <c r="G961" s="9"/>
-      <c r="H961" s="14"/>
+      <c r="H961" s="13"/>
       <c r="I961" s="21"/>
     </row>
     <row r="962">
       <c r="C962" s="22"/>
       <c r="F962" s="9"/>
       <c r="G962" s="9"/>
-      <c r="H962" s="14"/>
+      <c r="H962" s="13"/>
       <c r="I962" s="21"/>
     </row>
     <row r="963">
       <c r="C963" s="22"/>
       <c r="F963" s="9"/>
       <c r="G963" s="9"/>
-      <c r="H963" s="14"/>
+      <c r="H963" s="13"/>
       <c r="I963" s="21"/>
     </row>
     <row r="964">
       <c r="C964" s="22"/>
       <c r="F964" s="9"/>
       <c r="G964" s="9"/>
-      <c r="H964" s="14"/>
+      <c r="H964" s="13"/>
       <c r="I964" s="21"/>
     </row>
     <row r="965">
       <c r="C965" s="22"/>
       <c r="F965" s="9"/>
       <c r="G965" s="9"/>
-      <c r="H965" s="14"/>
+      <c r="H965" s="13"/>
       <c r="I965" s="21"/>
     </row>
     <row r="966">
       <c r="C966" s="22"/>
       <c r="F966" s="9"/>
       <c r="G966" s="9"/>
-      <c r="H966" s="14"/>
+      <c r="H966" s="13"/>
       <c r="I966" s="21"/>
     </row>
     <row r="967">
       <c r="C967" s="22"/>
       <c r="F967" s="9"/>
       <c r="G967" s="9"/>
-      <c r="H967" s="14"/>
+      <c r="H967" s="13"/>
       <c r="I967" s="21"/>
     </row>
     <row r="968">
       <c r="C968" s="22"/>
       <c r="F968" s="9"/>
       <c r="G968" s="9"/>
-      <c r="H968" s="14"/>
+      <c r="H968" s="13"/>
       <c r="I968" s="21"/>
     </row>
     <row r="969">
       <c r="C969" s="22"/>
       <c r="F969" s="9"/>
       <c r="G969" s="9"/>
-      <c r="H969" s="14"/>
+      <c r="H969" s="13"/>
       <c r="I969" s="21"/>
     </row>
     <row r="970">
       <c r="C970" s="22"/>
       <c r="F970" s="9"/>
       <c r="G970" s="9"/>
-      <c r="H970" s="14"/>
+      <c r="H970" s="13"/>
       <c r="I970" s="21"/>
     </row>
     <row r="971">
       <c r="C971" s="22"/>
       <c r="F971" s="9"/>
       <c r="G971" s="9"/>
-      <c r="H971" s="14"/>
+      <c r="H971" s="13"/>
       <c r="I971" s="21"/>
     </row>
     <row r="972">
       <c r="C972" s="22"/>
       <c r="F972" s="9"/>
       <c r="G972" s="9"/>
-      <c r="H972" s="14"/>
+      <c r="H972" s="13"/>
       <c r="I972" s="21"/>
     </row>
     <row r="973">
       <c r="C973" s="22"/>
       <c r="F973" s="9"/>
       <c r="G973" s="9"/>
-      <c r="H973" s="14"/>
+      <c r="H973" s="13"/>
       <c r="I973" s="21"/>
     </row>
     <row r="974">
       <c r="C974" s="22"/>
       <c r="F974" s="9"/>
       <c r="G974" s="9"/>
-      <c r="H974" s="14"/>
+      <c r="H974" s="13"/>
       <c r="I974" s="21"/>
     </row>
     <row r="975">
       <c r="C975" s="22"/>
       <c r="F975" s="9"/>
       <c r="G975" s="9"/>
-      <c r="H975" s="14"/>
+      <c r="H975" s="13"/>
       <c r="I975" s="21"/>
     </row>
     <row r="976">
       <c r="C976" s="22"/>
       <c r="F976" s="9"/>
       <c r="G976" s="9"/>
-      <c r="H976" s="14"/>
+      <c r="H976" s="13"/>
       <c r="I976" s="21"/>
     </row>
     <row r="977">
       <c r="C977" s="22"/>
       <c r="F977" s="9"/>
       <c r="G977" s="9"/>
-      <c r="H977" s="14"/>
+      <c r="H977" s="13"/>
       <c r="I977" s="21"/>
     </row>
     <row r="978">
       <c r="C978" s="22"/>
       <c r="F978" s="9"/>
       <c r="G978" s="9"/>
-      <c r="H978" s="14"/>
+      <c r="H978" s="13"/>
       <c r="I978" s="21"/>
     </row>
     <row r="979">
       <c r="C979" s="22"/>
       <c r="F979" s="9"/>
       <c r="G979" s="9"/>
-      <c r="H979" s="14"/>
+      <c r="H979" s="13"/>
       <c r="I979" s="21"/>
     </row>
     <row r="980">
       <c r="C980" s="22"/>
       <c r="F980" s="9"/>
       <c r="G980" s="9"/>
-      <c r="H980" s="14"/>
+      <c r="H980" s="13"/>
       <c r="I980" s="21"/>
     </row>
     <row r="981">
       <c r="C981" s="22"/>
       <c r="F981" s="9"/>
       <c r="G981" s="9"/>
-      <c r="H981" s="14"/>
+      <c r="H981" s="13"/>
       <c r="I981" s="21"/>
     </row>
     <row r="982">
       <c r="C982" s="22"/>
       <c r="F982" s="9"/>
       <c r="G982" s="9"/>
-      <c r="H982" s="14"/>
+      <c r="H982" s="13"/>
       <c r="I982" s="21"/>
     </row>
     <row r="983">
       <c r="C983" s="22"/>
       <c r="F983" s="9"/>
       <c r="G983" s="9"/>
-      <c r="H983" s="14"/>
+      <c r="H983" s="13"/>
       <c r="I983" s="21"/>
     </row>
     <row r="984">
       <c r="C984" s="22"/>
       <c r="F984" s="9"/>
       <c r="G984" s="9"/>
-      <c r="H984" s="14"/>
+      <c r="H984" s="13"/>
       <c r="I984" s="21"/>
     </row>
     <row r="985">
       <c r="C985" s="22"/>
       <c r="F985" s="9"/>
       <c r="G985" s="9"/>
-      <c r="H985" s="14"/>
+      <c r="H985" s="13"/>
       <c r="I985" s="21"/>
     </row>
     <row r="986">
       <c r="C986" s="22"/>
       <c r="F986" s="9"/>
       <c r="G986" s="9"/>
-      <c r="H986" s="14"/>
+      <c r="H986" s="13"/>
       <c r="I986" s="21"/>
     </row>
     <row r="987">
       <c r="C987" s="22"/>
       <c r="F987" s="9"/>
       <c r="G987" s="9"/>
-      <c r="H987" s="14"/>
+      <c r="H987" s="13"/>
       <c r="I987" s="21"/>
     </row>
     <row r="988">
       <c r="C988" s="22"/>
       <c r="F988" s="9"/>
       <c r="G988" s="9"/>
-      <c r="H988" s="14"/>
+      <c r="H988" s="13"/>
       <c r="I988" s="21"/>
     </row>
     <row r="989">
       <c r="C989" s="22"/>
       <c r="F989" s="9"/>
       <c r="G989" s="9"/>
-      <c r="H989" s="14"/>
+      <c r="H989" s="13"/>
       <c r="I989" s="21"/>
     </row>
     <row r="990">
       <c r="C990" s="22"/>
       <c r="F990" s="9"/>
       <c r="G990" s="9"/>
-      <c r="H990" s="14"/>
+      <c r="H990" s="13"/>
       <c r="I990" s="21"/>
     </row>
     <row r="991">
       <c r="C991" s="22"/>
       <c r="F991" s="9"/>
       <c r="G991" s="9"/>
-      <c r="H991" s="14"/>
+      <c r="H991" s="13"/>
       <c r="I991" s="21"/>
     </row>
     <row r="992">
       <c r="C992" s="22"/>
       <c r="F992" s="9"/>
       <c r="G992" s="9"/>
-      <c r="H992" s="14"/>
+      <c r="H992" s="13"/>
       <c r="I992" s="21"/>
     </row>
     <row r="993">
       <c r="C993" s="22"/>
       <c r="F993" s="9"/>
       <c r="G993" s="9"/>
-      <c r="H993" s="14"/>
+      <c r="H993" s="13"/>
       <c r="I993" s="21"/>
     </row>
     <row r="994">
       <c r="C994" s="22"/>
       <c r="F994" s="9"/>
       <c r="G994" s="9"/>
-      <c r="H994" s="14"/>
+      <c r="H994" s="13"/>
       <c r="I994" s="21"/>
     </row>
     <row r="995">
       <c r="C995" s="22"/>
       <c r="F995" s="9"/>
       <c r="G995" s="9"/>
-      <c r="H995" s="14"/>
+      <c r="H995" s="13"/>
       <c r="I995" s="21"/>
     </row>
     <row r="996">
       <c r="C996" s="22"/>
       <c r="F996" s="9"/>
       <c r="G996" s="9"/>
-      <c r="H996" s="14"/>
+      <c r="H996" s="13"/>
       <c r="I996" s="21"/>
     </row>
     <row r="997">
       <c r="C997" s="22"/>
       <c r="F997" s="9"/>
       <c r="G997" s="9"/>
-      <c r="H997" s="14"/>
+      <c r="H997" s="13"/>
       <c r="I997" s="21"/>
     </row>
     <row r="998">
       <c r="C998" s="22"/>
       <c r="F998" s="9"/>
       <c r="G998" s="9"/>
-      <c r="H998" s="14"/>
+      <c r="H998" s="13"/>
       <c r="I998" s="21"/>
     </row>
     <row r="999">
       <c r="C999" s="22"/>
       <c r="F999" s="9"/>
       <c r="G999" s="9"/>
-      <c r="H999" s="14"/>
+      <c r="H999" s="13"/>
       <c r="I999" s="21"/>
     </row>
     <row r="1000">
       <c r="C1000" s="22"/>
       <c r="F1000" s="9"/>
       <c r="G1000" s="9"/>
-      <c r="H1000" s="14"/>
+      <c r="H1000" s="13"/>
       <c r="I1000" s="21"/>
     </row>
     <row r="1001">
       <c r="C1001" s="22"/>
       <c r="F1001" s="9"/>
       <c r="G1001" s="9"/>
-      <c r="H1001" s="14"/>
+      <c r="H1001" s="13"/>
       <c r="I1001" s="21"/>
     </row>
   </sheetData>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -14,13 +14,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="178">
   <si>
-    <t>PICK</t>
-  </si>
-  <si>
     <t>Rank</t>
   </si>
   <si>
-    <t>VALUE</t>
+    <t>PICK</t>
   </si>
   <si>
     <t>PLAYER NAME</t>
@@ -30,6 +27,9 @@
   </si>
   <si>
     <t>Final Price</t>
+  </si>
+  <si>
+    <t>VALUE</t>
   </si>
   <si>
     <t>Mine?</t>
@@ -47,16 +47,16 @@
     <t>EnforceUpTo</t>
   </si>
   <si>
+    <t>New Values</t>
+  </si>
+  <si>
     <t>Value vs Fair</t>
   </si>
   <si>
-    <t>Settings</t>
+    <t>Spine</t>
   </si>
   <si>
-    <t>New Values</t>
-  </si>
-  <si>
-    <t>Spine</t>
+    <t>Settings</t>
   </si>
   <si>
     <t>Jeremiyah Love</t>
@@ -152,22 +152,22 @@
     <t>Inflation Factor</t>
   </si>
   <si>
+    <t>Round 2</t>
+  </si>
+  <si>
     <t>Ty Simpson</t>
   </si>
   <si>
     <t>Denzel Boston</t>
   </si>
   <si>
-    <t>Round 2</t>
-  </si>
-  <si>
     <t>Aggression</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>Caleb Downs</t>
   </si>
   <si>
-    <t>Caleb Downs</t>
+    <t>Round 3</t>
   </si>
   <si>
     <t>David Bailey</t>
@@ -179,13 +179,13 @@
     <t>Jacob Rodriguez</t>
   </si>
   <si>
-    <t>Round 4</t>
-  </si>
-  <si>
     <t>Jonah Coleman</t>
   </si>
   <si>
     <t>Jake Golday</t>
+  </si>
+  <si>
+    <t>Round 4</t>
   </si>
   <si>
     <t>Dillon Thieneman</t>
@@ -198,9 +198,6 @@
   </si>
   <si>
     <t>Germie Bernard</t>
-  </si>
-  <si>
-    <t>Round 5</t>
   </si>
   <si>
     <t>Nicholas Singleton</t>
@@ -224,10 +221,10 @@
     <t>Chris Brazzell</t>
   </si>
   <si>
-    <t>Max Klare</t>
+    <t>Round 5</t>
   </si>
   <si>
-    <t>Round 6</t>
+    <t>Max Klare</t>
   </si>
   <si>
     <t>Zachariah Branch</t>
@@ -243,6 +240,9 @@
   </si>
   <si>
     <t>Ted Hurst</t>
+  </si>
+  <si>
+    <t>Round 6</t>
   </si>
   <si>
     <t>Ja'Kobi Lane</t>
@@ -566,11 +566,11 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF1B1C1D"/>
@@ -611,66 +611,66 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -913,25 +913,25 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="7">
+      <c r="F1" s="6">
         <v>2025.0</v>
       </c>
-      <c r="G1" s="7">
+      <c r="G1" s="6">
         <v>2024.0</v>
       </c>
       <c r="H1" s="9">
@@ -949,52 +949,52 @@
       <c r="L1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="7">
+      <c r="M1" s="6">
         <v>12.0</v>
       </c>
       <c r="N1" s="12"/>
       <c r="O1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="7">
+      <c r="P1" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q1" s="7">
+      <c r="Q1" s="6">
         <v>2.0</v>
       </c>
-      <c r="R1" s="7">
+      <c r="R1" s="6">
         <v>3.0</v>
       </c>
-      <c r="S1" s="7">
+      <c r="S1" s="6">
         <v>4.0</v>
       </c>
-      <c r="T1" s="7">
+      <c r="T1" s="6">
         <v>5.0</v>
       </c>
-      <c r="U1" s="7">
+      <c r="U1" s="6">
         <v>6.0</v>
       </c>
-      <c r="V1" s="7">
+      <c r="V1" s="6">
         <v>7.0</v>
       </c>
-      <c r="W1" s="7">
+      <c r="W1" s="6">
         <v>8.0</v>
       </c>
-      <c r="X1" s="7">
+      <c r="X1" s="6">
         <v>9.0</v>
       </c>
-      <c r="Y1" s="7">
+      <c r="Y1" s="6">
         <v>10.0</v>
       </c>
-      <c r="Z1" s="7">
+      <c r="Z1" s="6">
         <v>11.0</v>
       </c>
-      <c r="AA1" s="7">
+      <c r="AA1" s="6">
         <v>12.0</v>
       </c>
       <c r="AB1" s="10"/>
       <c r="AC1" s="10"/>
-      <c r="AD1" s="7">
+      <c r="AD1" s="6">
         <f>1200 / SUM($P$2:$AA$7)</f>
         <v>1</v>
       </c>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="10" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="10" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -3142,14 +3142,14 @@
       </c>
       <c r="M30" s="12"/>
       <c r="N30" s="12"/>
-      <c r="O30" s="7">
+      <c r="O30" s="6">
         <v>1.0</v>
       </c>
       <c r="P30" s="10" t="s">
         <v>122</v>
       </c>
       <c r="Q30" s="12"/>
-      <c r="R30" s="7">
+      <c r="R30" s="6">
         <v>12.0</v>
       </c>
       <c r="S30" s="12"/>
@@ -3160,7 +3160,7 @@
       <c r="U30" s="12"/>
       <c r="V30" s="23"/>
       <c r="W30" s="23"/>
-      <c r="X30" s="6"/>
+      <c r="X30" s="7"/>
       <c r="Y30" s="12" t="str">
         <f t="shared" ref="Y30:Y81" si="17">TEXT(V30,"0")&amp;"|"&amp;TRIM(W30)</f>
         <v>0|</v>
@@ -3217,14 +3217,14 @@
       </c>
       <c r="M31" s="12"/>
       <c r="N31" s="12"/>
-      <c r="O31" s="7">
+      <c r="O31" s="6">
         <v>2.0</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>123</v>
       </c>
       <c r="Q31" s="12"/>
-      <c r="R31" s="7">
+      <c r="R31" s="6">
         <v>11.0</v>
       </c>
       <c r="S31" s="12"/>
@@ -3234,8 +3234,8 @@
       </c>
       <c r="U31" s="12"/>
       <c r="V31" s="9"/>
-      <c r="W31" s="6"/>
-      <c r="X31" s="6"/>
+      <c r="W31" s="7"/>
+      <c r="X31" s="7"/>
       <c r="Y31" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3292,14 +3292,14 @@
       </c>
       <c r="M32" s="12"/>
       <c r="N32" s="12"/>
-      <c r="O32" s="7">
+      <c r="O32" s="6">
         <v>3.0</v>
       </c>
       <c r="P32" s="10" t="s">
         <v>124</v>
       </c>
       <c r="Q32" s="12"/>
-      <c r="R32" s="7">
+      <c r="R32" s="6">
         <v>10.0</v>
       </c>
       <c r="S32" s="12"/>
@@ -3309,8 +3309,8 @@
       </c>
       <c r="U32" s="12"/>
       <c r="V32" s="9"/>
-      <c r="W32" s="6"/>
-      <c r="X32" s="6"/>
+      <c r="W32" s="7"/>
+      <c r="X32" s="7"/>
       <c r="Y32" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3367,14 +3367,14 @@
       </c>
       <c r="M33" s="12"/>
       <c r="N33" s="12"/>
-      <c r="O33" s="7">
+      <c r="O33" s="6">
         <v>4.0</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>125</v>
       </c>
       <c r="Q33" s="12"/>
-      <c r="R33" s="7">
+      <c r="R33" s="6">
         <v>9.0</v>
       </c>
       <c r="S33" s="12"/>
@@ -3384,8 +3384,8 @@
       </c>
       <c r="U33" s="12"/>
       <c r="V33" s="9"/>
-      <c r="W33" s="6"/>
-      <c r="X33" s="6"/>
+      <c r="W33" s="7"/>
+      <c r="X33" s="7"/>
       <c r="Y33" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="M34" s="12"/>
       <c r="N34" s="12"/>
-      <c r="O34" s="7">
+      <c r="O34" s="6">
         <v>5.0</v>
       </c>
       <c r="P34" s="10" t="s">
         <v>126</v>
       </c>
       <c r="Q34" s="12"/>
-      <c r="R34" s="7">
+      <c r="R34" s="6">
         <v>8.0</v>
       </c>
       <c r="S34" s="12"/>
@@ -3459,8 +3459,8 @@
       </c>
       <c r="U34" s="12"/>
       <c r="V34" s="9"/>
-      <c r="W34" s="6"/>
-      <c r="X34" s="6"/>
+      <c r="W34" s="7"/>
+      <c r="X34" s="7"/>
       <c r="Y34" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3517,14 +3517,14 @@
       </c>
       <c r="M35" s="12"/>
       <c r="N35" s="12"/>
-      <c r="O35" s="7">
+      <c r="O35" s="6">
         <v>6.0</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>127</v>
       </c>
       <c r="Q35" s="12"/>
-      <c r="R35" s="7">
+      <c r="R35" s="6">
         <v>7.0</v>
       </c>
       <c r="S35" s="12"/>
@@ -3534,8 +3534,8 @@
       </c>
       <c r="U35" s="12"/>
       <c r="V35" s="9"/>
-      <c r="W35" s="6"/>
-      <c r="X35" s="6"/>
+      <c r="W35" s="7"/>
+      <c r="X35" s="7"/>
       <c r="Y35" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3592,14 +3592,14 @@
       </c>
       <c r="M36" s="12"/>
       <c r="N36" s="12"/>
-      <c r="O36" s="7">
+      <c r="O36" s="6">
         <v>7.0</v>
       </c>
       <c r="P36" s="10" t="s">
         <v>128</v>
       </c>
       <c r="Q36" s="12"/>
-      <c r="R36" s="7">
+      <c r="R36" s="6">
         <v>6.0</v>
       </c>
       <c r="S36" s="12"/>
@@ -3609,8 +3609,8 @@
       </c>
       <c r="U36" s="12"/>
       <c r="V36" s="9"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="6"/>
+      <c r="W36" s="7"/>
+      <c r="X36" s="7"/>
       <c r="Y36" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3667,14 +3667,14 @@
       </c>
       <c r="M37" s="12"/>
       <c r="N37" s="12"/>
-      <c r="O37" s="7">
+      <c r="O37" s="6">
         <v>8.0</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>129</v>
       </c>
       <c r="Q37" s="12"/>
-      <c r="R37" s="7">
+      <c r="R37" s="6">
         <v>5.0</v>
       </c>
       <c r="S37" s="12"/>
@@ -3684,8 +3684,8 @@
       </c>
       <c r="U37" s="12"/>
       <c r="V37" s="9"/>
-      <c r="W37" s="6"/>
-      <c r="X37" s="6"/>
+      <c r="W37" s="7"/>
+      <c r="X37" s="7"/>
       <c r="Y37" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3742,14 +3742,14 @@
       </c>
       <c r="M38" s="12"/>
       <c r="N38" s="12"/>
-      <c r="O38" s="7">
+      <c r="O38" s="6">
         <v>9.0</v>
       </c>
       <c r="P38" s="10" t="s">
         <v>130</v>
       </c>
       <c r="Q38" s="12"/>
-      <c r="R38" s="7">
+      <c r="R38" s="6">
         <v>4.0</v>
       </c>
       <c r="S38" s="12"/>
@@ -3759,8 +3759,8 @@
       </c>
       <c r="U38" s="12"/>
       <c r="V38" s="9"/>
-      <c r="W38" s="6"/>
-      <c r="X38" s="6"/>
+      <c r="W38" s="7"/>
+      <c r="X38" s="7"/>
       <c r="Y38" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3817,14 +3817,14 @@
       </c>
       <c r="M39" s="12"/>
       <c r="N39" s="12"/>
-      <c r="O39" s="7">
+      <c r="O39" s="6">
         <v>10.0</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>131</v>
       </c>
       <c r="Q39" s="12"/>
-      <c r="R39" s="7">
+      <c r="R39" s="6">
         <v>3.0</v>
       </c>
       <c r="S39" s="12"/>
@@ -3834,8 +3834,8 @@
       </c>
       <c r="U39" s="12"/>
       <c r="V39" s="9"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="6"/>
+      <c r="W39" s="7"/>
+      <c r="X39" s="7"/>
       <c r="Y39" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3892,14 +3892,14 @@
       </c>
       <c r="M40" s="12"/>
       <c r="N40" s="12"/>
-      <c r="O40" s="7">
+      <c r="O40" s="6">
         <v>11.0</v>
       </c>
       <c r="P40" s="10" t="s">
         <v>132</v>
       </c>
       <c r="Q40" s="12"/>
-      <c r="R40" s="7">
+      <c r="R40" s="6">
         <v>2.0</v>
       </c>
       <c r="S40" s="12"/>
@@ -3909,8 +3909,8 @@
       </c>
       <c r="U40" s="12"/>
       <c r="V40" s="9"/>
-      <c r="W40" s="6"/>
-      <c r="X40" s="6"/>
+      <c r="W40" s="7"/>
+      <c r="X40" s="7"/>
       <c r="Y40" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3967,14 +3967,14 @@
       </c>
       <c r="M41" s="12"/>
       <c r="N41" s="12"/>
-      <c r="O41" s="7">
+      <c r="O41" s="6">
         <v>12.0</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>133</v>
       </c>
       <c r="Q41" s="12"/>
-      <c r="R41" s="7">
+      <c r="R41" s="6">
         <v>1.0</v>
       </c>
       <c r="S41" s="12"/>
@@ -3984,8 +3984,8 @@
       </c>
       <c r="U41" s="12"/>
       <c r="V41" s="9"/>
-      <c r="W41" s="6"/>
-      <c r="X41" s="6"/>
+      <c r="W41" s="7"/>
+      <c r="X41" s="7"/>
       <c r="Y41" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4050,8 +4050,8 @@
       <c r="T42" s="12"/>
       <c r="U42" s="12"/>
       <c r="V42" s="9"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="6"/>
+      <c r="W42" s="7"/>
+      <c r="X42" s="7"/>
       <c r="Y42" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4116,8 +4116,8 @@
       <c r="T43" s="12"/>
       <c r="U43" s="12"/>
       <c r="V43" s="9"/>
-      <c r="W43" s="6"/>
-      <c r="X43" s="6"/>
+      <c r="W43" s="7"/>
+      <c r="X43" s="7"/>
       <c r="Y43" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4190,8 +4190,8 @@
       <c r="T44" s="12"/>
       <c r="U44" s="12"/>
       <c r="V44" s="9"/>
-      <c r="W44" s="6"/>
-      <c r="X44" s="6"/>
+      <c r="W44" s="7"/>
+      <c r="X44" s="7"/>
       <c r="Y44" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4280,8 +4280,8 @@
       <c r="T45" s="12"/>
       <c r="U45" s="12"/>
       <c r="V45" s="9"/>
-      <c r="W45" s="6"/>
-      <c r="X45" s="6"/>
+      <c r="W45" s="7"/>
+      <c r="X45" s="7"/>
       <c r="Y45" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4358,8 +4358,8 @@
       <c r="T46" s="12"/>
       <c r="U46" s="12"/>
       <c r="V46" s="9"/>
-      <c r="W46" s="6"/>
-      <c r="X46" s="6"/>
+      <c r="W46" s="7"/>
+      <c r="X46" s="7"/>
       <c r="Y46" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4436,8 +4436,8 @@
       <c r="T47" s="12"/>
       <c r="U47" s="12"/>
       <c r="V47" s="9"/>
-      <c r="W47" s="6"/>
-      <c r="X47" s="6"/>
+      <c r="W47" s="7"/>
+      <c r="X47" s="7"/>
       <c r="Y47" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4514,8 +4514,8 @@
       <c r="T48" s="12"/>
       <c r="U48" s="12"/>
       <c r="V48" s="9"/>
-      <c r="W48" s="6"/>
-      <c r="X48" s="6"/>
+      <c r="W48" s="7"/>
+      <c r="X48" s="7"/>
       <c r="Y48" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4592,8 +4592,8 @@
       <c r="T49" s="12"/>
       <c r="U49" s="12"/>
       <c r="V49" s="9"/>
-      <c r="W49" s="6"/>
-      <c r="X49" s="6"/>
+      <c r="W49" s="7"/>
+      <c r="X49" s="7"/>
       <c r="Y49" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4670,8 +4670,8 @@
       <c r="T50" s="12"/>
       <c r="U50" s="12"/>
       <c r="V50" s="9"/>
-      <c r="W50" s="6"/>
-      <c r="X50" s="6"/>
+      <c r="W50" s="7"/>
+      <c r="X50" s="7"/>
       <c r="Y50" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4748,8 +4748,8 @@
       <c r="T51" s="12"/>
       <c r="U51" s="12"/>
       <c r="V51" s="9"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="6"/>
+      <c r="W51" s="7"/>
+      <c r="X51" s="7"/>
       <c r="Y51" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4826,8 +4826,8 @@
       <c r="T52" s="12"/>
       <c r="U52" s="12"/>
       <c r="V52" s="9"/>
-      <c r="W52" s="6"/>
-      <c r="X52" s="6"/>
+      <c r="W52" s="7"/>
+      <c r="X52" s="7"/>
       <c r="Y52" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4904,8 +4904,8 @@
       <c r="T53" s="12"/>
       <c r="U53" s="12"/>
       <c r="V53" s="9"/>
-      <c r="W53" s="6"/>
-      <c r="X53" s="6"/>
+      <c r="W53" s="7"/>
+      <c r="X53" s="7"/>
       <c r="Y53" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4982,8 +4982,8 @@
       <c r="T54" s="12"/>
       <c r="U54" s="12"/>
       <c r="V54" s="9"/>
-      <c r="W54" s="6"/>
-      <c r="X54" s="6"/>
+      <c r="W54" s="7"/>
+      <c r="X54" s="7"/>
       <c r="Y54" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5060,8 +5060,8 @@
       <c r="T55" s="12"/>
       <c r="U55" s="12"/>
       <c r="V55" s="9"/>
-      <c r="W55" s="6"/>
-      <c r="X55" s="6"/>
+      <c r="W55" s="7"/>
+      <c r="X55" s="7"/>
       <c r="Y55" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5138,8 +5138,8 @@
       <c r="T56" s="12"/>
       <c r="U56" s="12"/>
       <c r="V56" s="9"/>
-      <c r="W56" s="6"/>
-      <c r="X56" s="6"/>
+      <c r="W56" s="7"/>
+      <c r="X56" s="7"/>
       <c r="Y56" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5216,8 +5216,8 @@
       <c r="T57" s="12"/>
       <c r="U57" s="12"/>
       <c r="V57" s="9"/>
-      <c r="W57" s="6"/>
-      <c r="X57" s="6"/>
+      <c r="W57" s="7"/>
+      <c r="X57" s="7"/>
       <c r="Y57" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5295,7 +5295,7 @@
       <c r="U58" s="12"/>
       <c r="V58" s="23"/>
       <c r="W58" s="23"/>
-      <c r="X58" s="6"/>
+      <c r="X58" s="7"/>
       <c r="Y58" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5373,7 +5373,7 @@
       <c r="U59" s="12"/>
       <c r="V59" s="23"/>
       <c r="W59" s="23"/>
-      <c r="X59" s="6"/>
+      <c r="X59" s="7"/>
       <c r="Y59" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5451,7 +5451,7 @@
       <c r="U60" s="12"/>
       <c r="V60" s="23"/>
       <c r="W60" s="23"/>
-      <c r="X60" s="6"/>
+      <c r="X60" s="7"/>
       <c r="Y60" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5528,8 +5528,8 @@
       <c r="T61" s="12"/>
       <c r="U61" s="12"/>
       <c r="V61" s="9"/>
-      <c r="W61" s="6"/>
-      <c r="X61" s="6"/>
+      <c r="W61" s="7"/>
+      <c r="X61" s="7"/>
       <c r="Y61" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5609,9 +5609,9 @@
       <c r="U62" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="V62" s="6"/>
-      <c r="W62" s="6"/>
-      <c r="X62" s="6"/>
+      <c r="V62" s="7"/>
+      <c r="W62" s="7"/>
+      <c r="X62" s="7"/>
       <c r="Y62" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5692,9 +5692,9 @@
         <f t="shared" ref="U63:U74" si="22">SUMIF($R$45:$R$116, T63, $Q$45:$Q$116)</f>
         <v>180</v>
       </c>
-      <c r="V63" s="6"/>
-      <c r="W63" s="6"/>
-      <c r="X63" s="6"/>
+      <c r="V63" s="7"/>
+      <c r="W63" s="7"/>
+      <c r="X63" s="7"/>
       <c r="Y63" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="V64" s="23"/>
       <c r="W64" s="23"/>
-      <c r="X64" s="6"/>
+      <c r="X64" s="7"/>
       <c r="Y64" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5858,9 +5858,9 @@
         <f t="shared" si="22"/>
         <v>132.5</v>
       </c>
-      <c r="V65" s="6"/>
-      <c r="W65" s="6"/>
-      <c r="X65" s="6"/>
+      <c r="V65" s="7"/>
+      <c r="W65" s="7"/>
+      <c r="X65" s="7"/>
       <c r="Y65" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5942,8 +5942,8 @@
         <v>117.5</v>
       </c>
       <c r="V66" s="9"/>
-      <c r="W66" s="6"/>
-      <c r="X66" s="6"/>
+      <c r="W66" s="7"/>
+      <c r="X66" s="7"/>
       <c r="Y66" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -6025,8 +6025,8 @@
         <v>109.5</v>
       </c>
       <c r="V67" s="9"/>
-      <c r="W67" s="6"/>
-      <c r="X67" s="6"/>
+      <c r="W67" s="7"/>
+      <c r="X67" s="7"/>
       <c r="Y67" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -6108,8 +6108,8 @@
         <v>99.5</v>
       </c>
       <c r="V68" s="9"/>
-      <c r="W68" s="6"/>
-      <c r="X68" s="6"/>
+      <c r="W68" s="7"/>
+      <c r="X68" s="7"/>
       <c r="Y68" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="V69" s="23"/>
       <c r="W69" s="23"/>
-      <c r="X69" s="6"/>
+      <c r="X69" s="7"/>
       <c r="Y69" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -6600,7 +6600,7 @@
     </row>
     <row r="75">
       <c r="A75" s="5"/>
-      <c r="B75" s="6"/>
+      <c r="B75" s="7"/>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
@@ -6696,7 +6696,7 @@
     </row>
     <row r="77">
       <c r="A77" s="5"/>
-      <c r="B77" s="6"/>
+      <c r="B77" s="7"/>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
@@ -6743,7 +6743,7 @@
     </row>
     <row r="78">
       <c r="A78" s="5"/>
-      <c r="B78" s="6"/>
+      <c r="B78" s="7"/>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
       <c r="E78" s="5"/>
@@ -6790,7 +6790,7 @@
     </row>
     <row r="79">
       <c r="A79" s="5"/>
-      <c r="B79" s="6"/>
+      <c r="B79" s="7"/>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
@@ -6837,7 +6837,7 @@
     </row>
     <row r="80">
       <c r="A80" s="5"/>
-      <c r="B80" s="6"/>
+      <c r="B80" s="7"/>
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
       <c r="E80" s="5"/>
@@ -6884,7 +6884,7 @@
     </row>
     <row r="81">
       <c r="A81" s="5"/>
-      <c r="B81" s="6"/>
+      <c r="B81" s="7"/>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
@@ -6931,7 +6931,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5"/>
-      <c r="B82" s="6"/>
+      <c r="B82" s="7"/>
       <c r="C82" s="5"/>
       <c r="D82" s="5"/>
       <c r="E82" s="5"/>
@@ -6975,7 +6975,7 @@
     </row>
     <row r="83">
       <c r="A83" s="12"/>
-      <c r="B83" s="6"/>
+      <c r="B83" s="7"/>
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
@@ -7019,7 +7019,7 @@
     </row>
     <row r="84">
       <c r="A84" s="12"/>
-      <c r="B84" s="6"/>
+      <c r="B84" s="7"/>
       <c r="C84" s="5"/>
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
@@ -7106,7 +7106,7 @@
     </row>
     <row r="86">
       <c r="A86" s="12"/>
-      <c r="B86" s="6"/>
+      <c r="B86" s="7"/>
       <c r="C86" s="5"/>
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
@@ -7150,7 +7150,7 @@
     </row>
     <row r="87">
       <c r="A87" s="12"/>
-      <c r="B87" s="6"/>
+      <c r="B87" s="7"/>
       <c r="C87" s="5"/>
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
@@ -7194,7 +7194,7 @@
     </row>
     <row r="88">
       <c r="A88" s="12"/>
-      <c r="B88" s="6"/>
+      <c r="B88" s="7"/>
       <c r="C88" s="5"/>
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
@@ -7238,7 +7238,7 @@
     </row>
     <row r="89">
       <c r="A89" s="12"/>
-      <c r="B89" s="6"/>
+      <c r="B89" s="7"/>
       <c r="C89" s="5"/>
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
@@ -7282,7 +7282,7 @@
     </row>
     <row r="90">
       <c r="A90" s="5"/>
-      <c r="B90" s="6"/>
+      <c r="B90" s="7"/>
       <c r="C90" s="5"/>
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
@@ -7326,7 +7326,7 @@
     </row>
     <row r="91">
       <c r="A91" s="5"/>
-      <c r="B91" s="6"/>
+      <c r="B91" s="7"/>
       <c r="C91" s="5"/>
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
@@ -7370,7 +7370,7 @@
     </row>
     <row r="92">
       <c r="A92" s="5"/>
-      <c r="B92" s="6"/>
+      <c r="B92" s="7"/>
       <c r="C92" s="5"/>
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
@@ -7414,7 +7414,7 @@
     </row>
     <row r="93">
       <c r="A93" s="5"/>
-      <c r="B93" s="6"/>
+      <c r="B93" s="7"/>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
@@ -7458,7 +7458,7 @@
     </row>
     <row r="94">
       <c r="A94" s="12"/>
-      <c r="B94" s="6"/>
+      <c r="B94" s="7"/>
       <c r="C94" s="5"/>
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
@@ -7502,7 +7502,7 @@
     </row>
     <row r="95">
       <c r="A95" s="12"/>
-      <c r="B95" s="6"/>
+      <c r="B95" s="7"/>
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
@@ -7546,7 +7546,7 @@
     </row>
     <row r="96">
       <c r="A96" s="12"/>
-      <c r="B96" s="6"/>
+      <c r="B96" s="7"/>
       <c r="C96" s="5"/>
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
@@ -7590,7 +7590,7 @@
     </row>
     <row r="97">
       <c r="A97" s="12"/>
-      <c r="B97" s="6"/>
+      <c r="B97" s="7"/>
       <c r="C97" s="5"/>
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
@@ -7634,7 +7634,7 @@
     </row>
     <row r="98">
       <c r="A98" s="12"/>
-      <c r="B98" s="6"/>
+      <c r="B98" s="7"/>
       <c r="C98" s="5"/>
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
@@ -7678,7 +7678,7 @@
     </row>
     <row r="99">
       <c r="A99" s="12"/>
-      <c r="B99" s="6"/>
+      <c r="B99" s="7"/>
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
       <c r="E99" s="5"/>
@@ -7722,7 +7722,7 @@
     </row>
     <row r="100">
       <c r="A100" s="12"/>
-      <c r="B100" s="6"/>
+      <c r="B100" s="7"/>
       <c r="C100" s="5"/>
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
@@ -7766,7 +7766,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5"/>
-      <c r="B101" s="6"/>
+      <c r="B101" s="7"/>
       <c r="C101" s="5"/>
       <c r="D101" s="5"/>
       <c r="E101" s="5"/>
@@ -7810,7 +7810,7 @@
     </row>
     <row r="102">
       <c r="A102" s="5"/>
-      <c r="B102" s="6"/>
+      <c r="B102" s="7"/>
       <c r="C102" s="5"/>
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
@@ -9146,7 +9146,7 @@
       <c r="W137" s="12"/>
       <c r="X137" s="12"/>
       <c r="Y137" s="12"/>
-      <c r="Z137" s="6" t="s">
+      <c r="Z137" s="7" t="s">
         <v>137</v>
       </c>
       <c r="AA137" s="12"/>
@@ -9180,7 +9180,7 @@
       <c r="W138" s="12"/>
       <c r="X138" s="12"/>
       <c r="Y138" s="12"/>
-      <c r="Z138" s="6">
+      <c r="Z138" s="7">
         <v>6817.0</v>
       </c>
       <c r="AA138" s="12"/>
@@ -9211,16 +9211,16 @@
       <c r="T139" s="12"/>
       <c r="U139" s="12"/>
       <c r="V139" s="12"/>
-      <c r="W139" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="X139" s="6" t="s">
+      <c r="W139" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="X139" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="Y139" s="6" t="s">
+      <c r="Y139" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="Z139" s="6">
+      <c r="Z139" s="7">
         <v>5203.0</v>
       </c>
       <c r="AA139" s="12"/>
@@ -9251,16 +9251,16 @@
       <c r="T140" s="12"/>
       <c r="U140" s="12"/>
       <c r="V140" s="12"/>
-      <c r="W140" s="6">
+      <c r="W140" s="7">
         <v>1.0</v>
       </c>
-      <c r="X140" s="6" t="s">
+      <c r="X140" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="Y140" s="6" t="s">
+      <c r="Y140" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z140" s="6">
+      <c r="Z140" s="7">
         <v>5103.0</v>
       </c>
       <c r="AA140" s="12"/>
@@ -9291,16 +9291,16 @@
       <c r="T141" s="12"/>
       <c r="U141" s="12"/>
       <c r="V141" s="12"/>
-      <c r="W141" s="6">
+      <c r="W141" s="7">
         <v>3.0</v>
       </c>
-      <c r="X141" s="6" t="s">
+      <c r="X141" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="Y141" s="6" t="s">
+      <c r="Y141" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z141" s="6">
+      <c r="Z141" s="7">
         <v>5020.0</v>
       </c>
       <c r="AA141" s="12"/>
@@ -9331,16 +9331,16 @@
       <c r="T142" s="12"/>
       <c r="U142" s="12"/>
       <c r="V142" s="12"/>
-      <c r="W142" s="6">
+      <c r="W142" s="7">
         <v>4.0</v>
       </c>
-      <c r="X142" s="6" t="s">
+      <c r="X142" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="Y142" s="6" t="s">
+      <c r="Y142" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z142" s="6">
+      <c r="Z142" s="7">
         <v>4517.0</v>
       </c>
       <c r="AA142" s="12"/>
@@ -9371,16 +9371,16 @@
       <c r="T143" s="12"/>
       <c r="U143" s="12"/>
       <c r="V143" s="12"/>
-      <c r="W143" s="6">
+      <c r="W143" s="7">
         <v>5.0</v>
       </c>
-      <c r="X143" s="6" t="s">
+      <c r="X143" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="Y143" s="6" t="s">
+      <c r="Y143" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z143" s="6">
+      <c r="Z143" s="7">
         <v>4164.0</v>
       </c>
       <c r="AA143" s="12"/>
@@ -9411,16 +9411,16 @@
       <c r="T144" s="12"/>
       <c r="U144" s="12"/>
       <c r="V144" s="12"/>
-      <c r="W144" s="6">
+      <c r="W144" s="7">
         <v>6.0</v>
       </c>
-      <c r="X144" s="6" t="s">
+      <c r="X144" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="Y144" s="6" t="s">
+      <c r="Y144" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z144" s="6">
+      <c r="Z144" s="7">
         <v>4025.0</v>
       </c>
       <c r="AA144" s="12"/>
@@ -9451,16 +9451,16 @@
       <c r="T145" s="12"/>
       <c r="U145" s="12"/>
       <c r="V145" s="12"/>
-      <c r="W145" s="6">
+      <c r="W145" s="7">
         <v>7.0</v>
       </c>
-      <c r="X145" s="6" t="s">
+      <c r="X145" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="Y145" s="6" t="s">
+      <c r="Y145" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Z145" s="6">
+      <c r="Z145" s="7">
         <v>3650.0</v>
       </c>
       <c r="AA145" s="12"/>
@@ -9491,16 +9491,16 @@
       <c r="T146" s="12"/>
       <c r="U146" s="12"/>
       <c r="V146" s="12"/>
-      <c r="W146" s="6">
+      <c r="W146" s="7">
         <v>8.0</v>
       </c>
-      <c r="X146" s="6" t="s">
+      <c r="X146" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="Y146" s="6" t="s">
+      <c r="Y146" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z146" s="6">
+      <c r="Z146" s="7">
         <v>3611.0</v>
       </c>
       <c r="AA146" s="12"/>
@@ -9531,16 +9531,16 @@
       <c r="T147" s="12"/>
       <c r="U147" s="12"/>
       <c r="V147" s="12"/>
-      <c r="W147" s="6">
+      <c r="W147" s="7">
         <v>9.0</v>
       </c>
-      <c r="X147" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y147" s="6" t="s">
+      <c r="X147" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y147" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z147" s="6">
+      <c r="Z147" s="7">
         <v>3608.0</v>
       </c>
       <c r="AA147" s="12"/>
@@ -9571,16 +9571,16 @@
       <c r="T148" s="12"/>
       <c r="U148" s="12"/>
       <c r="V148" s="12"/>
-      <c r="W148" s="6">
+      <c r="W148" s="7">
         <v>10.0</v>
       </c>
-      <c r="X148" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y148" s="6" t="s">
+      <c r="X148" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y148" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="Z148" s="6">
+      <c r="Z148" s="7">
         <v>3596.0</v>
       </c>
       <c r="AA148" s="12"/>
@@ -9611,16 +9611,16 @@
       <c r="T149" s="12"/>
       <c r="U149" s="12"/>
       <c r="V149" s="12"/>
-      <c r="W149" s="6">
+      <c r="W149" s="7">
         <v>11.0</v>
       </c>
-      <c r="X149" s="6" t="s">
+      <c r="X149" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="Y149" s="6" t="s">
+      <c r="Y149" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Z149" s="6">
+      <c r="Z149" s="7">
         <v>3426.0</v>
       </c>
       <c r="AA149" s="12"/>
@@ -9651,16 +9651,16 @@
       <c r="T150" s="12"/>
       <c r="U150" s="12"/>
       <c r="V150" s="12"/>
-      <c r="W150" s="6">
+      <c r="W150" s="7">
         <v>12.0</v>
       </c>
-      <c r="X150" s="6" t="s">
+      <c r="X150" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="Y150" s="6" t="s">
+      <c r="Y150" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="Z150" s="6">
+      <c r="Z150" s="7">
         <v>3264.0</v>
       </c>
       <c r="AA150" s="12"/>
@@ -9691,16 +9691,16 @@
       <c r="T151" s="12"/>
       <c r="U151" s="12"/>
       <c r="V151" s="12"/>
-      <c r="W151" s="6">
+      <c r="W151" s="7">
         <v>13.0</v>
       </c>
-      <c r="X151" s="6" t="s">
+      <c r="X151" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="Y151" s="6" t="s">
+      <c r="Y151" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="Z151" s="6">
+      <c r="Z151" s="7">
         <v>3179.0</v>
       </c>
       <c r="AA151" s="12"/>
@@ -9731,16 +9731,16 @@
       <c r="T152" s="12"/>
       <c r="U152" s="12"/>
       <c r="V152" s="12"/>
-      <c r="W152" s="6">
+      <c r="W152" s="7">
         <v>14.0</v>
       </c>
-      <c r="X152" s="6" t="s">
+      <c r="X152" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="Y152" s="6" t="s">
+      <c r="Y152" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Z152" s="6">
+      <c r="Z152" s="7">
         <v>3162.0</v>
       </c>
       <c r="AA152" s="12"/>
@@ -9771,16 +9771,16 @@
       <c r="T153" s="12"/>
       <c r="U153" s="12"/>
       <c r="V153" s="12"/>
-      <c r="W153" s="6">
+      <c r="W153" s="7">
         <v>15.0</v>
       </c>
-      <c r="X153" s="6" t="s">
+      <c r="X153" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="Y153" s="6" t="s">
+      <c r="Y153" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z153" s="6">
+      <c r="Z153" s="7">
         <v>3125.0</v>
       </c>
       <c r="AA153" s="12"/>
@@ -9811,16 +9811,16 @@
       <c r="T154" s="12"/>
       <c r="U154" s="12"/>
       <c r="V154" s="12"/>
-      <c r="W154" s="6">
+      <c r="W154" s="7">
         <v>16.0</v>
       </c>
-      <c r="X154" s="6" t="s">
+      <c r="X154" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="Y154" s="6" t="s">
+      <c r="Y154" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Z154" s="6">
+      <c r="Z154" s="7">
         <v>2971.0</v>
       </c>
       <c r="AA154" s="12"/>
@@ -9851,16 +9851,16 @@
       <c r="T155" s="12"/>
       <c r="U155" s="12"/>
       <c r="V155" s="12"/>
-      <c r="W155" s="6">
+      <c r="W155" s="7">
         <v>17.0</v>
       </c>
-      <c r="X155" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y155" s="6" t="s">
+      <c r="X155" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y155" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z155" s="6">
+      <c r="Z155" s="7">
         <v>2963.0</v>
       </c>
       <c r="AA155" s="12"/>
@@ -9891,16 +9891,16 @@
       <c r="T156" s="12"/>
       <c r="U156" s="12"/>
       <c r="V156" s="12"/>
-      <c r="W156" s="6">
+      <c r="W156" s="7">
         <v>18.0</v>
       </c>
-      <c r="X156" s="6" t="s">
+      <c r="X156" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="Y156" s="6" t="s">
+      <c r="Y156" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="Z156" s="6">
+      <c r="Z156" s="7">
         <v>2953.0</v>
       </c>
       <c r="AA156" s="12"/>
@@ -9931,16 +9931,16 @@
       <c r="T157" s="12"/>
       <c r="U157" s="12"/>
       <c r="V157" s="12"/>
-      <c r="W157" s="6">
+      <c r="W157" s="7">
         <v>19.0</v>
       </c>
-      <c r="X157" s="6" t="s">
+      <c r="X157" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="Y157" s="6" t="s">
+      <c r="Y157" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="Z157" s="6">
+      <c r="Z157" s="7">
         <v>2807.0</v>
       </c>
       <c r="AA157" s="12"/>
@@ -9971,16 +9971,16 @@
       <c r="T158" s="12"/>
       <c r="U158" s="12"/>
       <c r="V158" s="12"/>
-      <c r="W158" s="6">
+      <c r="W158" s="7">
         <v>20.0</v>
       </c>
-      <c r="X158" s="6" t="s">
+      <c r="X158" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="Y158" s="6" t="s">
+      <c r="Y158" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z158" s="6">
+      <c r="Z158" s="7">
         <v>2696.0</v>
       </c>
       <c r="AA158" s="12"/>
@@ -10011,16 +10011,16 @@
       <c r="T159" s="12"/>
       <c r="U159" s="12"/>
       <c r="V159" s="12"/>
-      <c r="W159" s="6">
+      <c r="W159" s="7">
         <v>21.0</v>
       </c>
-      <c r="X159" s="6" t="s">
+      <c r="X159" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="Y159" s="6" t="s">
+      <c r="Y159" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z159" s="6">
+      <c r="Z159" s="7">
         <v>2672.0</v>
       </c>
       <c r="AA159" s="12"/>
@@ -10051,16 +10051,16 @@
       <c r="T160" s="12"/>
       <c r="U160" s="12"/>
       <c r="V160" s="12"/>
-      <c r="W160" s="6">
+      <c r="W160" s="7">
         <v>22.0</v>
       </c>
-      <c r="X160" s="6" t="s">
+      <c r="X160" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="Y160" s="6" t="s">
+      <c r="Y160" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z160" s="6">
+      <c r="Z160" s="7">
         <v>2480.0</v>
       </c>
       <c r="AA160" s="12"/>
@@ -10091,16 +10091,16 @@
       <c r="T161" s="12"/>
       <c r="U161" s="12"/>
       <c r="V161" s="12"/>
-      <c r="W161" s="6">
+      <c r="W161" s="7">
         <v>23.0</v>
       </c>
-      <c r="X161" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y161" s="6" t="s">
+      <c r="X161" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y161" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z161" s="6">
+      <c r="Z161" s="7">
         <v>2416.0</v>
       </c>
       <c r="AA161" s="12"/>
@@ -10131,16 +10131,16 @@
       <c r="T162" s="12"/>
       <c r="U162" s="12"/>
       <c r="V162" s="12"/>
-      <c r="W162" s="6">
+      <c r="W162" s="7">
         <v>24.0</v>
       </c>
-      <c r="X162" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y162" s="6" t="s">
+      <c r="X162" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y162" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z162" s="6">
+      <c r="Z162" s="7">
         <v>2416.0</v>
       </c>
       <c r="AA162" s="12"/>
@@ -10171,16 +10171,16 @@
       <c r="T163" s="12"/>
       <c r="U163" s="12"/>
       <c r="V163" s="12"/>
-      <c r="W163" s="6">
+      <c r="W163" s="7">
         <v>25.0</v>
       </c>
-      <c r="X163" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y163" s="6" t="s">
+      <c r="X163" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y163" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z163" s="6">
+      <c r="Z163" s="7">
         <v>2109.0</v>
       </c>
       <c r="AA163" s="12"/>
@@ -10211,16 +10211,16 @@
       <c r="T164" s="12"/>
       <c r="U164" s="12"/>
       <c r="V164" s="12"/>
-      <c r="W164" s="6">
+      <c r="W164" s="7">
         <v>26.0</v>
       </c>
-      <c r="X164" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y164" s="6" t="s">
+      <c r="X164" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y164" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z164" s="6">
+      <c r="Z164" s="7">
         <v>2106.0</v>
       </c>
       <c r="AA164" s="12"/>
@@ -10251,16 +10251,16 @@
       <c r="T165" s="12"/>
       <c r="U165" s="12"/>
       <c r="V165" s="12"/>
-      <c r="W165" s="6">
+      <c r="W165" s="7">
         <v>27.0</v>
       </c>
-      <c r="X165" s="6" t="s">
+      <c r="X165" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="Y165" s="6" t="s">
+      <c r="Y165" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z165" s="6">
+      <c r="Z165" s="7">
         <v>2098.0</v>
       </c>
       <c r="AA165" s="12"/>
@@ -10291,16 +10291,16 @@
       <c r="T166" s="12"/>
       <c r="U166" s="12"/>
       <c r="V166" s="12"/>
-      <c r="W166" s="6">
+      <c r="W166" s="7">
         <v>28.0</v>
       </c>
-      <c r="X166" s="6" t="s">
+      <c r="X166" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="Y166" s="6" t="s">
+      <c r="Y166" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z166" s="6">
+      <c r="Z166" s="7">
         <v>2078.0</v>
       </c>
       <c r="AA166" s="12"/>
@@ -10331,16 +10331,16 @@
       <c r="T167" s="12"/>
       <c r="U167" s="12"/>
       <c r="V167" s="12"/>
-      <c r="W167" s="6">
+      <c r="W167" s="7">
         <v>29.0</v>
       </c>
-      <c r="X167" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y167" s="6" t="s">
+      <c r="X167" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y167" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Z167" s="6">
+      <c r="Z167" s="7">
         <v>2074.0</v>
       </c>
       <c r="AA167" s="12"/>
@@ -10371,16 +10371,16 @@
       <c r="T168" s="12"/>
       <c r="U168" s="12"/>
       <c r="V168" s="12"/>
-      <c r="W168" s="6">
+      <c r="W168" s="7">
         <v>30.0</v>
       </c>
-      <c r="X168" s="6" t="s">
+      <c r="X168" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="Y168" s="6" t="s">
+      <c r="Y168" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z168" s="6">
+      <c r="Z168" s="7">
         <v>2066.0</v>
       </c>
       <c r="AA168" s="12"/>
@@ -10411,16 +10411,16 @@
       <c r="T169" s="12"/>
       <c r="U169" s="12"/>
       <c r="V169" s="12"/>
-      <c r="W169" s="6">
+      <c r="W169" s="7">
         <v>31.0</v>
       </c>
-      <c r="X169" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y169" s="6" t="s">
+      <c r="X169" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y169" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z169" s="6">
+      <c r="Z169" s="7">
         <v>2045.0</v>
       </c>
       <c r="AA169" s="12"/>
@@ -10451,16 +10451,16 @@
       <c r="T170" s="12"/>
       <c r="U170" s="12"/>
       <c r="V170" s="12"/>
-      <c r="W170" s="6">
+      <c r="W170" s="7">
         <v>32.0</v>
       </c>
-      <c r="X170" s="6" t="s">
+      <c r="X170" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="Y170" s="6" t="s">
+      <c r="Y170" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z170" s="6">
+      <c r="Z170" s="7">
         <v>1977.0</v>
       </c>
       <c r="AA170" s="12"/>
@@ -10491,16 +10491,16 @@
       <c r="T171" s="12"/>
       <c r="U171" s="12"/>
       <c r="V171" s="12"/>
-      <c r="W171" s="6">
+      <c r="W171" s="7">
         <v>33.0</v>
       </c>
-      <c r="X171" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y171" s="6" t="s">
+      <c r="X171" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y171" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z171" s="6">
+      <c r="Z171" s="7">
         <v>1967.0</v>
       </c>
       <c r="AA171" s="12"/>
@@ -10531,16 +10531,16 @@
       <c r="T172" s="12"/>
       <c r="U172" s="12"/>
       <c r="V172" s="12"/>
-      <c r="W172" s="6">
+      <c r="W172" s="7">
         <v>34.0</v>
       </c>
-      <c r="X172" s="6" t="s">
+      <c r="X172" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="Y172" s="6" t="s">
+      <c r="Y172" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="Z172" s="6">
+      <c r="Z172" s="7">
         <v>1962.0</v>
       </c>
       <c r="AA172" s="12"/>
@@ -10571,16 +10571,16 @@
       <c r="T173" s="12"/>
       <c r="U173" s="12"/>
       <c r="V173" s="12"/>
-      <c r="W173" s="6">
+      <c r="W173" s="7">
         <v>35.0</v>
       </c>
-      <c r="X173" s="6" t="s">
+      <c r="X173" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="Y173" s="6" t="s">
+      <c r="Y173" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Z173" s="6">
+      <c r="Z173" s="7">
         <v>1961.0</v>
       </c>
       <c r="AA173" s="12"/>
@@ -10611,16 +10611,16 @@
       <c r="T174" s="12"/>
       <c r="U174" s="12"/>
       <c r="V174" s="12"/>
-      <c r="W174" s="6">
+      <c r="W174" s="7">
         <v>36.0</v>
       </c>
-      <c r="X174" s="6" t="s">
+      <c r="X174" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="Y174" s="6" t="s">
+      <c r="Y174" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z174" s="6">
+      <c r="Z174" s="7">
         <v>1910.0</v>
       </c>
       <c r="AA174" s="12"/>
@@ -10651,16 +10651,16 @@
       <c r="T175" s="12"/>
       <c r="U175" s="12"/>
       <c r="V175" s="12"/>
-      <c r="W175" s="6">
+      <c r="W175" s="7">
         <v>37.0</v>
       </c>
-      <c r="X175" s="6" t="s">
+      <c r="X175" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="Y175" s="6" t="s">
+      <c r="Y175" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Z175" s="6">
+      <c r="Z175" s="7">
         <v>1873.0</v>
       </c>
       <c r="AA175" s="12"/>
@@ -10691,16 +10691,16 @@
       <c r="T176" s="12"/>
       <c r="U176" s="12"/>
       <c r="V176" s="12"/>
-      <c r="W176" s="6">
+      <c r="W176" s="7">
         <v>38.0</v>
       </c>
-      <c r="X176" s="6" t="s">
+      <c r="X176" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="Y176" s="6" t="s">
+      <c r="Y176" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z176" s="6">
+      <c r="Z176" s="7">
         <v>1822.0</v>
       </c>
       <c r="AA176" s="12"/>
@@ -10731,16 +10731,16 @@
       <c r="T177" s="12"/>
       <c r="U177" s="12"/>
       <c r="V177" s="12"/>
-      <c r="W177" s="6">
+      <c r="W177" s="7">
         <v>39.0</v>
       </c>
-      <c r="X177" s="6" t="s">
+      <c r="X177" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="Y177" s="6" t="s">
+      <c r="Y177" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z177" s="6">
+      <c r="Z177" s="7">
         <v>1741.0</v>
       </c>
       <c r="AA177" s="12"/>
@@ -10771,16 +10771,16 @@
       <c r="T178" s="12"/>
       <c r="U178" s="12"/>
       <c r="V178" s="12"/>
-      <c r="W178" s="6">
+      <c r="W178" s="7">
         <v>40.0</v>
       </c>
-      <c r="X178" s="6" t="s">
+      <c r="X178" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="Y178" s="6" t="s">
+      <c r="Y178" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z178" s="6">
+      <c r="Z178" s="7">
         <v>1724.0</v>
       </c>
       <c r="AA178" s="12"/>
@@ -10811,16 +10811,16 @@
       <c r="T179" s="12"/>
       <c r="U179" s="12"/>
       <c r="V179" s="12"/>
-      <c r="W179" s="6">
+      <c r="W179" s="7">
         <v>41.0</v>
       </c>
-      <c r="X179" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y179" s="6" t="s">
+      <c r="X179" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y179" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z179" s="6">
+      <c r="Z179" s="7">
         <v>1660.0</v>
       </c>
       <c r="AA179" s="12"/>
@@ -10851,16 +10851,16 @@
       <c r="T180" s="12"/>
       <c r="U180" s="12"/>
       <c r="V180" s="12"/>
-      <c r="W180" s="6">
+      <c r="W180" s="7">
         <v>42.0</v>
       </c>
-      <c r="X180" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y180" s="6" t="s">
+      <c r="X180" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y180" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z180" s="6">
+      <c r="Z180" s="7">
         <v>1640.0</v>
       </c>
       <c r="AA180" s="12"/>
@@ -10891,16 +10891,16 @@
       <c r="T181" s="12"/>
       <c r="U181" s="12"/>
       <c r="V181" s="12"/>
-      <c r="W181" s="6">
+      <c r="W181" s="7">
         <v>43.0</v>
       </c>
-      <c r="X181" s="6" t="s">
+      <c r="X181" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="Y181" s="6" t="s">
+      <c r="Y181" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z181" s="6">
+      <c r="Z181" s="7">
         <v>1577.0</v>
       </c>
       <c r="AA181" s="12"/>
@@ -10931,16 +10931,16 @@
       <c r="T182" s="12"/>
       <c r="U182" s="12"/>
       <c r="V182" s="12"/>
-      <c r="W182" s="6">
+      <c r="W182" s="7">
         <v>44.0</v>
       </c>
-      <c r="X182" s="6" t="s">
+      <c r="X182" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="Y182" s="6" t="s">
+      <c r="Y182" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z182" s="6">
+      <c r="Z182" s="7">
         <v>1565.0</v>
       </c>
       <c r="AA182" s="12"/>
@@ -10971,16 +10971,16 @@
       <c r="T183" s="12"/>
       <c r="U183" s="12"/>
       <c r="V183" s="12"/>
-      <c r="W183" s="6">
+      <c r="W183" s="7">
         <v>45.0</v>
       </c>
-      <c r="X183" s="6" t="s">
+      <c r="X183" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="Y183" s="6" t="s">
+      <c r="Y183" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z183" s="6">
+      <c r="Z183" s="7">
         <v>1552.0</v>
       </c>
       <c r="AA183" s="12"/>
@@ -11011,16 +11011,16 @@
       <c r="T184" s="12"/>
       <c r="U184" s="12"/>
       <c r="V184" s="12"/>
-      <c r="W184" s="6">
+      <c r="W184" s="7">
         <v>46.0</v>
       </c>
-      <c r="X184" s="6" t="s">
+      <c r="X184" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="Y184" s="6" t="s">
+      <c r="Y184" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z184" s="6">
+      <c r="Z184" s="7">
         <v>1404.0</v>
       </c>
       <c r="AA184" s="12"/>
@@ -11051,16 +11051,16 @@
       <c r="T185" s="12"/>
       <c r="U185" s="12"/>
       <c r="V185" s="12"/>
-      <c r="W185" s="6">
+      <c r="W185" s="7">
         <v>47.0</v>
       </c>
-      <c r="X185" s="6" t="s">
+      <c r="X185" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="Y185" s="6" t="s">
+      <c r="Y185" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z185" s="6">
+      <c r="Z185" s="7">
         <v>1351.0</v>
       </c>
       <c r="AA185" s="12"/>
@@ -11091,16 +11091,16 @@
       <c r="T186" s="12"/>
       <c r="U186" s="12"/>
       <c r="V186" s="12"/>
-      <c r="W186" s="6">
+      <c r="W186" s="7">
         <v>48.0</v>
       </c>
-      <c r="X186" s="6" t="s">
+      <c r="X186" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="Y186" s="6" t="s">
+      <c r="Y186" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z186" s="6">
+      <c r="Z186" s="7">
         <v>1344.0</v>
       </c>
       <c r="AA186" s="12"/>
@@ -11131,16 +11131,16 @@
       <c r="T187" s="12"/>
       <c r="U187" s="12"/>
       <c r="V187" s="12"/>
-      <c r="W187" s="6">
+      <c r="W187" s="7">
         <v>49.0</v>
       </c>
-      <c r="X187" s="6" t="s">
+      <c r="X187" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="Y187" s="6" t="s">
+      <c r="Y187" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z187" s="6">
+      <c r="Z187" s="7">
         <v>1299.0</v>
       </c>
       <c r="AA187" s="12"/>
@@ -11171,16 +11171,16 @@
       <c r="T188" s="12"/>
       <c r="U188" s="12"/>
       <c r="V188" s="12"/>
-      <c r="W188" s="6">
+      <c r="W188" s="7">
         <v>50.0</v>
       </c>
-      <c r="X188" s="6" t="s">
+      <c r="X188" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="Y188" s="6" t="s">
+      <c r="Y188" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z188" s="6">
+      <c r="Z188" s="7">
         <v>1261.0</v>
       </c>
       <c r="AA188" s="12"/>
@@ -11211,16 +11211,16 @@
       <c r="T189" s="12"/>
       <c r="U189" s="12"/>
       <c r="V189" s="12"/>
-      <c r="W189" s="6">
+      <c r="W189" s="7">
         <v>51.0</v>
       </c>
-      <c r="X189" s="6" t="s">
+      <c r="X189" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="Y189" s="6" t="s">
+      <c r="Y189" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z189" s="6">
+      <c r="Z189" s="7">
         <v>1247.0</v>
       </c>
       <c r="AA189" s="12"/>
@@ -11251,16 +11251,16 @@
       <c r="T190" s="12"/>
       <c r="U190" s="12"/>
       <c r="V190" s="12"/>
-      <c r="W190" s="6">
+      <c r="W190" s="7">
         <v>52.0</v>
       </c>
-      <c r="X190" s="6" t="s">
+      <c r="X190" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="Y190" s="6" t="s">
+      <c r="Y190" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z190" s="6">
+      <c r="Z190" s="7">
         <v>1226.0</v>
       </c>
       <c r="AA190" s="12"/>
@@ -11291,16 +11291,16 @@
       <c r="T191" s="12"/>
       <c r="U191" s="12"/>
       <c r="V191" s="12"/>
-      <c r="W191" s="6">
+      <c r="W191" s="7">
         <v>53.0</v>
       </c>
-      <c r="X191" s="6" t="s">
+      <c r="X191" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="Y191" s="6" t="s">
+      <c r="Y191" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z191" s="6">
+      <c r="Z191" s="7">
         <v>1211.0</v>
       </c>
       <c r="AA191" s="12"/>
@@ -11331,16 +11331,16 @@
       <c r="T192" s="12"/>
       <c r="U192" s="12"/>
       <c r="V192" s="12"/>
-      <c r="W192" s="6">
+      <c r="W192" s="7">
         <v>54.0</v>
       </c>
-      <c r="X192" s="6" t="s">
+      <c r="X192" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="Y192" s="6" t="s">
+      <c r="Y192" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z192" s="6">
+      <c r="Z192" s="7">
         <v>1197.0</v>
       </c>
       <c r="AA192" s="12"/>
@@ -11371,16 +11371,16 @@
       <c r="T193" s="12"/>
       <c r="U193" s="12"/>
       <c r="V193" s="12"/>
-      <c r="W193" s="6">
+      <c r="W193" s="7">
         <v>55.0</v>
       </c>
-      <c r="X193" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y193" s="6" t="s">
+      <c r="X193" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y193" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z193" s="6">
+      <c r="Z193" s="7">
         <v>1184.0</v>
       </c>
       <c r="AA193" s="12"/>
@@ -11411,16 +11411,16 @@
       <c r="T194" s="12"/>
       <c r="U194" s="12"/>
       <c r="V194" s="12"/>
-      <c r="W194" s="6">
+      <c r="W194" s="7">
         <v>56.0</v>
       </c>
-      <c r="X194" s="6" t="s">
+      <c r="X194" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="Y194" s="6" t="s">
+      <c r="Y194" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z194" s="6">
+      <c r="Z194" s="7">
         <v>1157.0</v>
       </c>
       <c r="AA194" s="12"/>
@@ -11451,16 +11451,16 @@
       <c r="T195" s="12"/>
       <c r="U195" s="12"/>
       <c r="V195" s="12"/>
-      <c r="W195" s="6">
+      <c r="W195" s="7">
         <v>57.0</v>
       </c>
-      <c r="X195" s="6" t="s">
+      <c r="X195" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="Y195" s="6" t="s">
+      <c r="Y195" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z195" s="6">
+      <c r="Z195" s="7">
         <v>1143.0</v>
       </c>
       <c r="AA195" s="12"/>
@@ -11491,16 +11491,16 @@
       <c r="T196" s="12"/>
       <c r="U196" s="12"/>
       <c r="V196" s="12"/>
-      <c r="W196" s="6">
+      <c r="W196" s="7">
         <v>58.0</v>
       </c>
-      <c r="X196" s="6" t="s">
+      <c r="X196" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="Y196" s="6" t="s">
+      <c r="Y196" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z196" s="6">
+      <c r="Z196" s="7">
         <v>1078.0</v>
       </c>
       <c r="AA196" s="12"/>
@@ -11531,16 +11531,16 @@
       <c r="T197" s="12"/>
       <c r="U197" s="12"/>
       <c r="V197" s="12"/>
-      <c r="W197" s="6">
+      <c r="W197" s="7">
         <v>59.0</v>
       </c>
-      <c r="X197" s="6" t="s">
+      <c r="X197" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="Y197" s="6" t="s">
+      <c r="Y197" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z197" s="6">
+      <c r="Z197" s="7">
         <v>1069.0</v>
       </c>
       <c r="AA197" s="12"/>
@@ -11571,16 +11571,16 @@
       <c r="T198" s="12"/>
       <c r="U198" s="12"/>
       <c r="V198" s="12"/>
-      <c r="W198" s="6">
+      <c r="W198" s="7">
         <v>60.0</v>
       </c>
-      <c r="X198" s="6" t="s">
+      <c r="X198" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="Y198" s="6" t="s">
+      <c r="Y198" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z198" s="6">
+      <c r="Z198" s="7">
         <v>1000.0</v>
       </c>
       <c r="AA198" s="12"/>
@@ -11611,16 +11611,16 @@
       <c r="T199" s="12"/>
       <c r="U199" s="12"/>
       <c r="V199" s="12"/>
-      <c r="W199" s="6">
+      <c r="W199" s="7">
         <v>61.0</v>
       </c>
-      <c r="X199" s="6" t="s">
+      <c r="X199" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="Y199" s="6" t="s">
+      <c r="Y199" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z199" s="6">
+      <c r="Z199" s="7">
         <v>987.0</v>
       </c>
       <c r="AA199" s="12"/>
@@ -11651,16 +11651,16 @@
       <c r="T200" s="12"/>
       <c r="U200" s="12"/>
       <c r="V200" s="12"/>
-      <c r="W200" s="6">
+      <c r="W200" s="7">
         <v>62.0</v>
       </c>
-      <c r="X200" s="6" t="s">
+      <c r="X200" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="Y200" s="6" t="s">
+      <c r="Y200" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z200" s="6">
+      <c r="Z200" s="7">
         <v>952.0</v>
       </c>
       <c r="AA200" s="12"/>
@@ -11691,16 +11691,16 @@
       <c r="T201" s="12"/>
       <c r="U201" s="12"/>
       <c r="V201" s="12"/>
-      <c r="W201" s="6">
+      <c r="W201" s="7">
         <v>63.0</v>
       </c>
-      <c r="X201" s="6" t="s">
+      <c r="X201" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="Y201" s="6" t="s">
+      <c r="Y201" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z201" s="6">
+      <c r="Z201" s="7">
         <v>913.0</v>
       </c>
       <c r="AA201" s="12"/>
@@ -11731,16 +11731,16 @@
       <c r="T202" s="12"/>
       <c r="U202" s="12"/>
       <c r="V202" s="12"/>
-      <c r="W202" s="6">
+      <c r="W202" s="7">
         <v>64.0</v>
       </c>
-      <c r="X202" s="6" t="s">
+      <c r="X202" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="Y202" s="6" t="s">
+      <c r="Y202" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z202" s="6">
+      <c r="Z202" s="7">
         <v>905.0</v>
       </c>
       <c r="AA202" s="12"/>
@@ -11771,16 +11771,16 @@
       <c r="T203" s="12"/>
       <c r="U203" s="12"/>
       <c r="V203" s="12"/>
-      <c r="W203" s="6">
+      <c r="W203" s="7">
         <v>65.0</v>
       </c>
-      <c r="X203" s="6" t="s">
+      <c r="X203" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="Y203" s="6" t="s">
+      <c r="Y203" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z203" s="6">
+      <c r="Z203" s="7">
         <v>842.0</v>
       </c>
       <c r="AA203" s="12"/>
@@ -11811,16 +11811,16 @@
       <c r="T204" s="12"/>
       <c r="U204" s="12"/>
       <c r="V204" s="12"/>
-      <c r="W204" s="6">
+      <c r="W204" s="7">
         <v>66.0</v>
       </c>
-      <c r="X204" s="6" t="s">
+      <c r="X204" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="Y204" s="6" t="s">
+      <c r="Y204" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z204" s="6">
+      <c r="Z204" s="7">
         <v>823.0</v>
       </c>
       <c r="AA204" s="12"/>
@@ -11851,16 +11851,16 @@
       <c r="T205" s="12"/>
       <c r="U205" s="12"/>
       <c r="V205" s="12"/>
-      <c r="W205" s="6">
+      <c r="W205" s="7">
         <v>67.0</v>
       </c>
-      <c r="X205" s="6" t="s">
+      <c r="X205" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="Y205" s="6" t="s">
+      <c r="Y205" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z205" s="6">
+      <c r="Z205" s="7">
         <v>820.0</v>
       </c>
       <c r="AA205" s="12"/>
@@ -11891,16 +11891,16 @@
       <c r="T206" s="12"/>
       <c r="U206" s="12"/>
       <c r="V206" s="12"/>
-      <c r="W206" s="6">
+      <c r="W206" s="7">
         <v>68.0</v>
       </c>
-      <c r="X206" s="6" t="s">
+      <c r="X206" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="Y206" s="6" t="s">
+      <c r="Y206" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z206" s="6">
+      <c r="Z206" s="7">
         <v>805.0</v>
       </c>
       <c r="AA206" s="12"/>
@@ -11931,16 +11931,16 @@
       <c r="T207" s="12"/>
       <c r="U207" s="12"/>
       <c r="V207" s="12"/>
-      <c r="W207" s="6">
+      <c r="W207" s="7">
         <v>69.0</v>
       </c>
-      <c r="X207" s="6" t="s">
+      <c r="X207" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="Y207" s="6" t="s">
+      <c r="Y207" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z207" s="6">
+      <c r="Z207" s="7">
         <v>782.0</v>
       </c>
       <c r="AA207" s="12"/>
@@ -11971,16 +11971,16 @@
       <c r="T208" s="12"/>
       <c r="U208" s="12"/>
       <c r="V208" s="12"/>
-      <c r="W208" s="6">
+      <c r="W208" s="7">
         <v>70.0</v>
       </c>
-      <c r="X208" s="6" t="s">
+      <c r="X208" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="Y208" s="6" t="s">
+      <c r="Y208" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z208" s="6">
+      <c r="Z208" s="7">
         <v>736.0</v>
       </c>
       <c r="AA208" s="12"/>
@@ -12011,16 +12011,16 @@
       <c r="T209" s="12"/>
       <c r="U209" s="12"/>
       <c r="V209" s="12"/>
-      <c r="W209" s="6">
+      <c r="W209" s="7">
         <v>71.0</v>
       </c>
-      <c r="X209" s="6" t="s">
+      <c r="X209" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="Y209" s="6" t="s">
+      <c r="Y209" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z209" s="6">
+      <c r="Z209" s="7">
         <v>733.0</v>
       </c>
       <c r="AA209" s="12"/>
@@ -12051,16 +12051,16 @@
       <c r="T210" s="12"/>
       <c r="U210" s="12"/>
       <c r="V210" s="12"/>
-      <c r="W210" s="6">
+      <c r="W210" s="7">
         <v>72.0</v>
       </c>
-      <c r="X210" s="6" t="s">
+      <c r="X210" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="Y210" s="6" t="s">
+      <c r="Y210" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z210" s="6">
+      <c r="Z210" s="7">
         <v>700.0</v>
       </c>
       <c r="AA210" s="12"/>
@@ -12091,16 +12091,16 @@
       <c r="T211" s="12"/>
       <c r="U211" s="12"/>
       <c r="V211" s="12"/>
-      <c r="W211" s="6">
+      <c r="W211" s="7">
         <v>73.0</v>
       </c>
-      <c r="X211" s="6" t="s">
+      <c r="X211" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="Y211" s="6" t="s">
+      <c r="Y211" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z211" s="6">
+      <c r="Z211" s="7">
         <v>649.0</v>
       </c>
       <c r="AA211" s="12"/>
@@ -12131,16 +12131,16 @@
       <c r="T212" s="12"/>
       <c r="U212" s="12"/>
       <c r="V212" s="12"/>
-      <c r="W212" s="6">
+      <c r="W212" s="7">
         <v>74.0</v>
       </c>
-      <c r="X212" s="6" t="s">
+      <c r="X212" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="Y212" s="6" t="s">
+      <c r="Y212" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z212" s="6">
+      <c r="Z212" s="7">
         <v>636.0</v>
       </c>
       <c r="AA212" s="12"/>
@@ -12171,16 +12171,16 @@
       <c r="T213" s="12"/>
       <c r="U213" s="12"/>
       <c r="V213" s="12"/>
-      <c r="W213" s="6">
+      <c r="W213" s="7">
         <v>75.0</v>
       </c>
-      <c r="X213" s="6" t="s">
+      <c r="X213" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="Y213" s="6" t="s">
+      <c r="Y213" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z213" s="6">
+      <c r="Z213" s="7">
         <v>528.0</v>
       </c>
       <c r="AA213" s="12"/>
@@ -12211,16 +12211,16 @@
       <c r="T214" s="12"/>
       <c r="U214" s="12"/>
       <c r="V214" s="12"/>
-      <c r="W214" s="6">
+      <c r="W214" s="7">
         <v>76.0</v>
       </c>
-      <c r="X214" s="6" t="s">
+      <c r="X214" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="Y214" s="6" t="s">
+      <c r="Y214" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z214" s="6">
+      <c r="Z214" s="7">
         <v>473.0</v>
       </c>
       <c r="AA214" s="12"/>
@@ -12251,16 +12251,16 @@
       <c r="T215" s="12"/>
       <c r="U215" s="12"/>
       <c r="V215" s="12"/>
-      <c r="W215" s="6">
+      <c r="W215" s="7">
         <v>78.0</v>
       </c>
-      <c r="X215" s="6" t="s">
+      <c r="X215" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="Y215" s="6" t="s">
+      <c r="Y215" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z215" s="6">
+      <c r="Z215" s="7">
         <v>435.0</v>
       </c>
       <c r="AA215" s="12"/>
@@ -12291,13 +12291,13 @@
       <c r="T216" s="12"/>
       <c r="U216" s="12"/>
       <c r="V216" s="12"/>
-      <c r="W216" s="6">
+      <c r="W216" s="7">
         <v>79.0</v>
       </c>
-      <c r="X216" s="6" t="s">
+      <c r="X216" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="Y216" s="6" t="s">
+      <c r="Y216" s="7" t="s">
         <v>140</v>
       </c>
       <c r="Z216" s="12"/>
@@ -12329,13 +12329,13 @@
       <c r="T217" s="12"/>
       <c r="U217" s="12"/>
       <c r="V217" s="12"/>
-      <c r="W217" s="6">
+      <c r="W217" s="7">
         <v>80.0</v>
       </c>
-      <c r="X217" s="6" t="s">
+      <c r="X217" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="Y217" s="6" t="s">
+      <c r="Y217" s="7" t="s">
         <v>140</v>
       </c>
       <c r="Z217" s="12"/>
@@ -37443,19 +37443,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F1" s="4" t="s">
@@ -37467,25 +37467,25 @@
       <c r="H1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>1.0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C2" s="8">
         <v>139.0</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="b">
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F2" s="8">
@@ -37522,25 +37522,25 @@
 </f>
         <v/>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="1">
         <v>1200.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>2.0</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="8">
         <v>106.5</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="b">
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F3" s="8">
@@ -37564,25 +37564,25 @@
 </f>
         <v/>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="1">
         <v>12.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>3.0</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="8">
         <v>93.0</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="b">
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F4" s="8">
@@ -37601,7 +37601,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>25</v>
       </c>
       <c r="L4" s="4">
@@ -37610,10 +37610,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>4.0</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C5" s="8">
@@ -37638,7 +37638,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L5" s="17">
@@ -37648,10 +37648,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>5.0</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="8">
@@ -37676,7 +37676,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="1" t="s">
         <v>29</v>
       </c>
       <c r="L6" s="17">
@@ -37686,10 +37686,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>6.0</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>30</v>
       </c>
       <c r="C7" s="8">
@@ -37714,7 +37714,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" s="1" t="s">
         <v>31</v>
       </c>
       <c r="L7" s="17">
@@ -37723,10 +37723,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>7.0</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C8" s="8">
@@ -37751,7 +37751,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="1" t="s">
         <v>34</v>
       </c>
       <c r="L8" s="8">
@@ -37761,10 +37761,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>8.0</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>35</v>
       </c>
       <c r="C9" s="8">
@@ -37789,7 +37789,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L9" s="8">
@@ -37799,10 +37799,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>9.0</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C10" s="8">
@@ -37827,7 +37827,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" s="1" t="s">
         <v>38</v>
       </c>
       <c r="L10" s="8">
@@ -37836,10 +37836,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>10.0</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="8">
@@ -37864,7 +37864,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" s="1" t="s">
         <v>40</v>
       </c>
       <c r="L11" s="19">
@@ -37873,10 +37873,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>11.0</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="8">
@@ -37903,10 +37903,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>12.0</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>42</v>
       </c>
       <c r="C13" s="8">
@@ -37931,7 +37931,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="K13" s="1" t="s">
         <v>43</v>
       </c>
       <c r="L13" s="17">
@@ -37940,10 +37940,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>13.0</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>44</v>
       </c>
       <c r="C14" s="8">
@@ -37968,7 +37968,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="K14" s="1" t="s">
         <v>45</v>
       </c>
       <c r="L14" s="19">
@@ -37977,11 +37977,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>14.0</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>46</v>
+      <c r="B15" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="C15" s="8">
         <v>27.5</v>
@@ -38007,11 +38007,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2">
+      <c r="A16" s="1">
         <v>15.0</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>47</v>
+      <c r="B16" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="C16" s="8">
         <v>25.5</v>
@@ -38035,10 +38035,10 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="K16" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16" s="1">
         <f>IF($L$18&lt;0.3,
      IF($L$11&gt;=1.3,0.09,
         IF($L$11&gt;=1.1,0.07,0.05)),
@@ -38054,11 +38054,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>16.0</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>51</v>
+      <c r="B17" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="C17" s="8">
         <v>22.5</v>
@@ -38084,10 +38084,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2">
+      <c r="A18" s="1">
         <v>17.0</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="8">
@@ -38112,7 +38112,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="K18" s="1" t="s">
         <v>53</v>
       </c>
       <c r="L18" s="20">
@@ -38121,10 +38121,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2">
+      <c r="A19" s="1">
         <v>18.0</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>54</v>
       </c>
       <c r="C19" s="8">
@@ -38151,11 +38151,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2">
+      <c r="A20" s="1">
         <v>19.0</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>56</v>
+      <c r="B20" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="C20" s="8">
         <v>16.5</v>
@@ -38181,11 +38181,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2">
+      <c r="A21" s="1">
         <v>20.0</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>57</v>
+      <c r="B21" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C21" s="8">
         <v>14.5</v>
@@ -38211,10 +38211,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2">
+      <c r="A22" s="1">
         <v>21.0</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C22" s="8">
@@ -38241,10 +38241,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2">
+      <c r="A23" s="1">
         <v>22.0</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="7" t="s">
         <v>59</v>
       </c>
       <c r="C23" s="8">
@@ -38271,10 +38271,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2">
+      <c r="A24" s="1">
         <v>23.0</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="7" t="s">
         <v>60</v>
       </c>
       <c r="C24" s="8">
@@ -38301,10 +38301,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2">
+      <c r="A25" s="1">
         <v>24.0</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="7" t="s">
         <v>61</v>
       </c>
       <c r="C25" s="8">
@@ -38331,11 +38331,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2">
+      <c r="A26" s="1">
         <v>25.0</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>63</v>
+      <c r="B26" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="C26" s="8">
         <v>9.5</v>
@@ -38361,11 +38361,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2">
+      <c r="A27" s="1">
         <v>26.0</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>64</v>
+      <c r="B27" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="C27" s="8">
         <v>8.5</v>
@@ -38389,19 +38389,19 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K27" s="2" t="s">
+      <c r="K27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1">
+        <v>27.0</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>65</v>
-      </c>
-      <c r="L27" s="2">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2">
-        <v>27.0</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>66</v>
       </c>
       <c r="C28" s="8">
         <v>8.0</v>
@@ -38427,11 +38427,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2">
+      <c r="A29" s="1">
         <v>28.0</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>67</v>
+      <c r="B29" s="7" t="s">
+        <v>66</v>
       </c>
       <c r="C29" s="8">
         <v>7.0</v>
@@ -38457,11 +38457,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2">
+      <c r="A30" s="1">
         <v>29.0</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>68</v>
+      <c r="B30" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="C30" s="8">
         <v>6.5</v>
@@ -38487,11 +38487,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2">
+      <c r="A31" s="1">
         <v>30.0</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>69</v>
+      <c r="B31" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="C31" s="8">
         <v>6.0</v>
@@ -38517,10 +38517,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2">
+      <c r="A32" s="1">
         <v>31.0</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C32" s="8">
@@ -38547,11 +38547,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2">
+      <c r="A33" s="1">
         <v>32.0</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>72</v>
+      <c r="B33" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="C33" s="8">
         <v>5.0</v>
@@ -38577,11 +38577,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2">
+      <c r="A34" s="1">
         <v>33.0</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>73</v>
+      <c r="B34" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="C34" s="8">
         <v>4.5</v>
@@ -38607,11 +38607,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2">
+      <c r="A35" s="1">
         <v>34.0</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>74</v>
+      <c r="B35" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="C35" s="8">
         <v>4.5</v>
@@ -38637,11 +38637,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2">
+      <c r="A36" s="1">
         <v>35.0</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>75</v>
+      <c r="B36" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="C36" s="8">
         <v>4.0</v>
@@ -38667,11 +38667,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2">
+      <c r="A37" s="1">
         <v>36.0</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>76</v>
+      <c r="B37" s="7" t="s">
+        <v>75</v>
       </c>
       <c r="C37" s="8">
         <v>4.0</v>
@@ -38697,10 +38697,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2">
+      <c r="A38" s="1">
         <v>37.0</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="7" t="s">
         <v>77</v>
       </c>
       <c r="C38" s="8">
@@ -38727,10 +38727,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2">
+      <c r="A39" s="1">
         <v>38.0</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="7" t="s">
         <v>78</v>
       </c>
       <c r="C39" s="8">
@@ -38757,10 +38757,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2">
+      <c r="A40" s="1">
         <v>39.0</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="7" t="s">
         <v>79</v>
       </c>
       <c r="C40" s="8">
@@ -38787,10 +38787,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2">
+      <c r="A41" s="1">
         <v>40.0</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="7" t="s">
         <v>80</v>
       </c>
       <c r="C41" s="8">
@@ -38817,10 +38817,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2">
+      <c r="A42" s="1">
         <v>41.0</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="7" t="s">
         <v>81</v>
       </c>
       <c r="C42" s="8">
@@ -38847,10 +38847,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2">
+      <c r="A43" s="1">
         <v>42.0</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="7" t="s">
         <v>82</v>
       </c>
       <c r="C43" s="8">
@@ -38877,10 +38877,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2">
+      <c r="A44" s="1">
         <v>43.0</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C44" s="8">
@@ -38907,10 +38907,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2">
+      <c r="A45" s="1">
         <v>44.0</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="7" t="s">
         <v>84</v>
       </c>
       <c r="C45" s="8">
@@ -38937,10 +38937,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2">
+      <c r="A46" s="1">
         <v>45.0</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="7" t="s">
         <v>85</v>
       </c>
       <c r="C46" s="8">
@@ -38967,10 +38967,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2">
+      <c r="A47" s="1">
         <v>46.0</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="7" t="s">
         <v>86</v>
       </c>
       <c r="C47" s="8">
@@ -38997,10 +38997,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2">
+      <c r="A48" s="1">
         <v>47.0</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="7" t="s">
         <v>87</v>
       </c>
       <c r="C48" s="8">
@@ -39027,10 +39027,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2">
+      <c r="A49" s="1">
         <v>48.0</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C49" s="8">
@@ -39057,10 +39057,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2">
+      <c r="A50" s="1">
         <v>49.0</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="7" t="s">
         <v>89</v>
       </c>
       <c r="C50" s="8">
@@ -39087,10 +39087,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2">
+      <c r="A51" s="1">
         <v>50.0</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="7" t="s">
         <v>90</v>
       </c>
       <c r="C51" s="8">
@@ -39117,10 +39117,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2">
+      <c r="A52" s="1">
         <v>51.0</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="7" t="s">
         <v>91</v>
       </c>
       <c r="C52" s="8">
@@ -39147,10 +39147,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2">
+      <c r="A53" s="1">
         <v>52.0</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="7" t="s">
         <v>92</v>
       </c>
       <c r="C53" s="8">
@@ -39177,10 +39177,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2">
+      <c r="A54" s="1">
         <v>53.0</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="7" t="s">
         <v>93</v>
       </c>
       <c r="C54" s="8">
@@ -39207,10 +39207,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2">
+      <c r="A55" s="1">
         <v>54.0</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="7" t="s">
         <v>94</v>
       </c>
       <c r="C55" s="8">
@@ -39237,10 +39237,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2">
+      <c r="A56" s="1">
         <v>55.0</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="7" t="s">
         <v>95</v>
       </c>
       <c r="C56" s="8">
@@ -39267,10 +39267,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2">
+      <c r="A57" s="1">
         <v>56.0</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="7" t="s">
         <v>96</v>
       </c>
       <c r="C57" s="8">
@@ -39297,10 +39297,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2">
+      <c r="A58" s="1">
         <v>57.0</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C58" s="8">
@@ -39327,10 +39327,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2">
+      <c r="A59" s="1">
         <v>58.0</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="7" t="s">
         <v>98</v>
       </c>
       <c r="C59" s="8">
@@ -39357,10 +39357,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2">
+      <c r="A60" s="1">
         <v>59.0</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="7" t="s">
         <v>99</v>
       </c>
       <c r="C60" s="8">
@@ -39387,10 +39387,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2">
+      <c r="A61" s="1">
         <v>60.0</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C61" s="8">
@@ -39417,10 +39417,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2">
+      <c r="A62" s="1">
         <v>61.0</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="7" t="s">
         <v>101</v>
       </c>
       <c r="C62" s="8">
@@ -39447,10 +39447,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2">
+      <c r="A63" s="1">
         <v>62.0</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="7" t="s">
         <v>102</v>
       </c>
       <c r="C63" s="8">
@@ -39477,10 +39477,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2">
+      <c r="A64" s="1">
         <v>63.0</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="7" t="s">
         <v>103</v>
       </c>
       <c r="C64" s="8">
@@ -39507,10 +39507,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2">
+      <c r="A65" s="1">
         <v>64.0</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="7" t="s">
         <v>104</v>
       </c>
       <c r="C65" s="8">
@@ -39537,10 +39537,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2">
+      <c r="A66" s="1">
         <v>65.0</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="7" t="s">
         <v>105</v>
       </c>
       <c r="C66" s="8">
@@ -39567,10 +39567,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2">
+      <c r="A67" s="1">
         <v>66.0</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="7" t="s">
         <v>106</v>
       </c>
       <c r="C67" s="8">
@@ -39597,10 +39597,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2">
+      <c r="A68" s="1">
         <v>67.0</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="7" t="s">
         <v>107</v>
       </c>
       <c r="C68" s="8">
@@ -39627,10 +39627,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2">
+      <c r="A69" s="1">
         <v>68.0</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="7" t="s">
         <v>108</v>
       </c>
       <c r="C69" s="8">
@@ -39657,10 +39657,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2">
+      <c r="A70" s="1">
         <v>69.0</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="7" t="s">
         <v>109</v>
       </c>
       <c r="C70" s="8">
@@ -39687,10 +39687,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2">
+      <c r="A71" s="1">
         <v>70.0</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="7" t="s">
         <v>110</v>
       </c>
       <c r="C71" s="8">
@@ -39717,10 +39717,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2">
+      <c r="A72" s="1">
         <v>71.0</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="7" t="s">
         <v>111</v>
       </c>
       <c r="C72" s="8">
@@ -39747,10 +39747,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2">
+      <c r="A73" s="1">
         <v>72.0</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="1" t="s">
         <v>112</v>
       </c>
       <c r="C73" s="8">

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -107,6 +107,9 @@
     <t>Kenyon Sadiq</t>
   </si>
   <si>
+    <t>Round 1</t>
+  </si>
+  <si>
     <t>My Spent</t>
   </si>
   <si>
@@ -126,9 +129,6 @@
   </si>
   <si>
     <t>Avg $ per Other Team</t>
-  </si>
-  <si>
-    <t>Round 1</t>
   </si>
   <si>
     <t>Eli Stowers</t>
@@ -152,6 +152,9 @@
     <t>Inflation Factor</t>
   </si>
   <si>
+    <t>Round 2</t>
+  </si>
+  <si>
     <t>Ty Simpson</t>
   </si>
   <si>
@@ -161,7 +164,7 @@
     <t>Aggression</t>
   </si>
   <si>
-    <t>Round 2</t>
+    <t>Round 3</t>
   </si>
   <si>
     <t>Caleb Downs</t>
@@ -173,7 +176,7 @@
     <t>League Spent %</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>Round 4</t>
   </si>
   <si>
     <t>Jacob Rodriguez</t>
@@ -188,7 +191,7 @@
     <t>Dillon Thieneman</t>
   </si>
   <si>
-    <t>Round 4</t>
+    <t>Round 5</t>
   </si>
   <si>
     <t>Rueben Bain</t>
@@ -206,13 +209,13 @@
     <t>Mike Washington</t>
   </si>
   <si>
+    <t>Round 6</t>
+  </si>
+  <si>
     <t>Enforce % of Fair</t>
   </si>
   <si>
     <t>Antonio Williams</t>
-  </si>
-  <si>
-    <t>Round 5</t>
   </si>
   <si>
     <t>Elijah Sarratt</t>
@@ -231,9 +234,6 @@
   </si>
   <si>
     <t>De'Zhaun Stribling</t>
-  </si>
-  <si>
-    <t>Round 6</t>
   </si>
   <si>
     <t>Malachi Fields</t>
@@ -1071,7 +1071,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="10" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="10" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="10" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -9455,7 +9455,7 @@
         <v>7.0</v>
       </c>
       <c r="X145" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y145" s="5" t="s">
         <v>143</v>
@@ -9535,7 +9535,7 @@
         <v>9.0</v>
       </c>
       <c r="X147" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Y147" s="5" t="s">
         <v>141</v>
@@ -9575,7 +9575,7 @@
         <v>10.0</v>
       </c>
       <c r="X148" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Y148" s="5" t="s">
         <v>145</v>
@@ -9655,7 +9655,7 @@
         <v>12.0</v>
       </c>
       <c r="X150" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y150" s="5" t="s">
         <v>146</v>
@@ -9775,7 +9775,7 @@
         <v>15.0</v>
       </c>
       <c r="X153" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y153" s="5" t="s">
         <v>141</v>
@@ -9815,7 +9815,7 @@
         <v>16.0</v>
       </c>
       <c r="X154" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Y154" s="5" t="s">
         <v>143</v>
@@ -9855,7 +9855,7 @@
         <v>17.0</v>
       </c>
       <c r="X155" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Y155" s="5" t="s">
         <v>140</v>
@@ -9895,7 +9895,7 @@
         <v>18.0</v>
       </c>
       <c r="X156" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Y156" s="5" t="s">
         <v>145</v>
@@ -9975,7 +9975,7 @@
         <v>20.0</v>
       </c>
       <c r="X158" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y158" s="5" t="s">
         <v>140</v>
@@ -10095,7 +10095,7 @@
         <v>23.0</v>
       </c>
       <c r="X161" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y161" s="5" t="s">
         <v>142</v>
@@ -10135,7 +10135,7 @@
         <v>24.0</v>
       </c>
       <c r="X162" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y162" s="5" t="s">
         <v>141</v>
@@ -10175,7 +10175,7 @@
         <v>25.0</v>
       </c>
       <c r="X163" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Y163" s="5" t="s">
         <v>140</v>
@@ -10215,7 +10215,7 @@
         <v>26.0</v>
       </c>
       <c r="X164" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Y164" s="5" t="s">
         <v>140</v>
@@ -10335,7 +10335,7 @@
         <v>29.0</v>
       </c>
       <c r="X167" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Y167" s="5" t="s">
         <v>143</v>
@@ -10375,7 +10375,7 @@
         <v>30.0</v>
       </c>
       <c r="X168" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y168" s="5" t="s">
         <v>141</v>
@@ -10415,7 +10415,7 @@
         <v>31.0</v>
       </c>
       <c r="X169" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y169" s="5" t="s">
         <v>141</v>
@@ -10695,7 +10695,7 @@
         <v>38.0</v>
       </c>
       <c r="X176" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Y176" s="5" t="s">
         <v>141</v>
@@ -10735,7 +10735,7 @@
         <v>39.0</v>
       </c>
       <c r="X177" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Y177" s="5" t="s">
         <v>144</v>
@@ -10815,7 +10815,7 @@
         <v>41.0</v>
       </c>
       <c r="X179" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Y179" s="5" t="s">
         <v>141</v>
@@ -37715,7 +37715,7 @@
         <v/>
       </c>
       <c r="K7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L7" s="17">
         <f>SUMIF($E$2:$E$500,TRUE,$D$2:$D$500)</f>
@@ -37727,7 +37727,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="7">
         <v>57.5</v>
@@ -37752,7 +37752,7 @@
         <v/>
       </c>
       <c r="K8" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L8" s="7">
         <f>L4-L7
@@ -37765,7 +37765,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" s="7">
         <v>53.0</v>
@@ -37790,7 +37790,7 @@
         <v/>
       </c>
       <c r="K9" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L9" s="7">
         <f>L6-L8
@@ -37803,7 +37803,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" s="7">
         <v>48.0</v>
@@ -37828,7 +37828,7 @@
         <v/>
       </c>
       <c r="K10" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L10" s="7">
         <f>IF(L3&gt;1,L9/(L3-1),0)</f>
@@ -37981,7 +37981,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C15" s="7">
         <v>27.5</v>
@@ -38011,7 +38011,7 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C16" s="7">
         <v>25.5</v>
@@ -38036,7 +38036,7 @@
         <v/>
       </c>
       <c r="K16" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L16" s="1">
         <f>IF($L$18&lt;0.3,
@@ -38058,7 +38058,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C17" s="7">
         <v>22.5</v>
@@ -38088,7 +38088,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" s="7">
         <v>20.0</v>
@@ -38113,7 +38113,7 @@
         <v/>
       </c>
       <c r="K18" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L18" s="20">
         <f>L5/L2</f>
@@ -38125,7 +38125,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" s="7">
         <v>18.5</v>
@@ -38155,7 +38155,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C20" s="7">
         <v>16.5</v>
@@ -38185,7 +38185,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C21" s="7">
         <v>14.5</v>
@@ -38215,7 +38215,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" s="7">
         <v>13.5</v>
@@ -38245,7 +38245,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C23" s="7">
         <v>12.0</v>
@@ -38275,7 +38275,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" s="7">
         <v>11.0</v>
@@ -38305,7 +38305,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C25" s="7">
         <v>10.0</v>
@@ -38335,7 +38335,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C26" s="7">
         <v>9.5</v>
@@ -38365,7 +38365,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" s="7">
         <v>8.5</v>
@@ -38390,7 +38390,7 @@
         <v/>
       </c>
       <c r="K27" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L27" s="1">
         <v>0.8</v>
@@ -38401,7 +38401,7 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C28" s="7">
         <v>8.0</v>
@@ -38431,7 +38431,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29" s="7">
         <v>7.0</v>
@@ -38461,7 +38461,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C30" s="7">
         <v>6.5</v>
@@ -38491,7 +38491,7 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C31" s="7">
         <v>6.0</v>
@@ -38521,7 +38521,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C32" s="7">
         <v>5.5</v>
@@ -38551,7 +38551,7 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C33" s="7">
         <v>5.0</v>
@@ -38581,7 +38581,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C34" s="7">
         <v>4.5</v>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -29,13 +29,13 @@
     <t>PreDraft$</t>
   </si>
   <si>
+    <t>Decay</t>
+  </si>
+  <si>
     <t>Final Price</t>
   </si>
   <si>
     <t>Mine?</t>
-  </si>
-  <si>
-    <t>Decay</t>
   </si>
   <si>
     <t>Inflated Fair Price</t>
@@ -44,10 +44,10 @@
     <t>New Values</t>
   </si>
   <si>
-    <t>My Max Bid</t>
+    <t>Spine</t>
   </si>
   <si>
-    <t>Spine</t>
+    <t>My Max Bid</t>
   </si>
   <si>
     <t>EnforceUpTo</t>
@@ -113,10 +113,10 @@
     <t>Sonny Styles</t>
   </si>
   <si>
-    <t>My Remaining</t>
+    <t>Round 1</t>
   </si>
   <si>
-    <t>Round 1</t>
+    <t>My Remaining</t>
   </si>
   <si>
     <t>KC Concepcion</t>
@@ -152,6 +152,9 @@
     <t>Inflation Factor</t>
   </si>
   <si>
+    <t>Round 2</t>
+  </si>
+  <si>
     <t>Ty Simpson</t>
   </si>
   <si>
@@ -161,10 +164,10 @@
     <t>Aggression</t>
   </si>
   <si>
-    <t>Caleb Downs</t>
+    <t>Round 3</t>
   </si>
   <si>
-    <t>Round 2</t>
+    <t>Caleb Downs</t>
   </si>
   <si>
     <t>David Bailey</t>
@@ -182,6 +185,9 @@
     <t>Jake Golday</t>
   </si>
   <si>
+    <t>Round 4</t>
+  </si>
+  <si>
     <t>Dillon Thieneman</t>
   </si>
   <si>
@@ -197,10 +203,10 @@
     <t>Nicholas Singleton</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>Mike Washington</t>
   </si>
   <si>
-    <t>Mike Washington</t>
+    <t>Round 5</t>
   </si>
   <si>
     <t>Enforce % of Fair</t>
@@ -221,6 +227,9 @@
     <t>Max Klare</t>
   </si>
   <si>
+    <t>Round 6</t>
+  </si>
+  <si>
     <t>Zachariah Branch</t>
   </si>
   <si>
@@ -228,9 +237,6 @@
   </si>
   <si>
     <t>Malachi Fields</t>
-  </si>
-  <si>
-    <t>Round 4</t>
   </si>
   <si>
     <t>Kaytron Allen</t>
@@ -257,9 +263,6 @@
     <t>Dani Dennis-Sutton</t>
   </si>
   <si>
-    <t>Round 5</t>
-  </si>
-  <si>
     <t>Emmanuel McNeil-Warren</t>
   </si>
   <si>
@@ -279,9 +282,6 @@
   </si>
   <si>
     <t>CJ Donaldson</t>
-  </si>
-  <si>
-    <t>Round 6</t>
   </si>
   <si>
     <t>T.J. Parker</t>
@@ -920,13 +920,13 @@
         <v>2</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="6">
         <v>2025.0</v>
@@ -1071,7 +1071,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="9" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="9" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="9" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="9" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -9535,7 +9535,7 @@
         <v>9.0</v>
       </c>
       <c r="X147" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Y147" s="8" t="s">
         <v>141</v>
@@ -9575,7 +9575,7 @@
         <v>10.0</v>
       </c>
       <c r="X148" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Y148" s="8" t="s">
         <v>145</v>
@@ -9655,7 +9655,7 @@
         <v>12.0</v>
       </c>
       <c r="X150" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y150" s="8" t="s">
         <v>146</v>
@@ -9815,7 +9815,7 @@
         <v>16.0</v>
       </c>
       <c r="X154" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Y154" s="8" t="s">
         <v>143</v>
@@ -9855,7 +9855,7 @@
         <v>17.0</v>
       </c>
       <c r="X155" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Y155" s="8" t="s">
         <v>140</v>
@@ -9895,7 +9895,7 @@
         <v>18.0</v>
       </c>
       <c r="X156" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Y156" s="8" t="s">
         <v>145</v>
@@ -9935,7 +9935,7 @@
         <v>19.0</v>
       </c>
       <c r="X157" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y157" s="8" t="s">
         <v>145</v>
@@ -10095,7 +10095,7 @@
         <v>23.0</v>
       </c>
       <c r="X161" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y161" s="8" t="s">
         <v>142</v>
@@ -10135,7 +10135,7 @@
         <v>24.0</v>
       </c>
       <c r="X162" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Y162" s="8" t="s">
         <v>141</v>
@@ -10175,7 +10175,7 @@
         <v>25.0</v>
       </c>
       <c r="X163" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Y163" s="8" t="s">
         <v>140</v>
@@ -10215,7 +10215,7 @@
         <v>26.0</v>
       </c>
       <c r="X164" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Y164" s="8" t="s">
         <v>140</v>
@@ -10335,7 +10335,7 @@
         <v>29.0</v>
       </c>
       <c r="X167" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Y167" s="8" t="s">
         <v>143</v>
@@ -10375,7 +10375,7 @@
         <v>30.0</v>
       </c>
       <c r="X168" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Y168" s="8" t="s">
         <v>141</v>
@@ -10415,7 +10415,7 @@
         <v>31.0</v>
       </c>
       <c r="X169" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Y169" s="8" t="s">
         <v>141</v>
@@ -10495,7 +10495,7 @@
         <v>33.0</v>
       </c>
       <c r="X171" s="8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Y171" s="8" t="s">
         <v>141</v>
@@ -10575,7 +10575,7 @@
         <v>35.0</v>
       </c>
       <c r="X173" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Y173" s="8" t="s">
         <v>143</v>
@@ -10695,7 +10695,7 @@
         <v>38.0</v>
       </c>
       <c r="X176" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Y176" s="8" t="s">
         <v>141</v>
@@ -10735,7 +10735,7 @@
         <v>39.0</v>
       </c>
       <c r="X177" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Y177" s="8" t="s">
         <v>144</v>
@@ -10775,7 +10775,7 @@
         <v>40.0</v>
       </c>
       <c r="X178" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Y178" s="8" t="s">
         <v>141</v>
@@ -10815,7 +10815,7 @@
         <v>41.0</v>
       </c>
       <c r="X179" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Y179" s="8" t="s">
         <v>141</v>
@@ -10855,7 +10855,7 @@
         <v>42.0</v>
       </c>
       <c r="X180" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Y180" s="8" t="s">
         <v>140</v>
@@ -10975,7 +10975,7 @@
         <v>45.0</v>
       </c>
       <c r="X183" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Y183" s="8" t="s">
         <v>140</v>
@@ -11055,7 +11055,7 @@
         <v>47.0</v>
       </c>
       <c r="X185" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Y185" s="8" t="s">
         <v>141</v>
@@ -11295,7 +11295,7 @@
         <v>53.0</v>
       </c>
       <c r="X191" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Y191" s="8" t="s">
         <v>144</v>
@@ -11375,7 +11375,7 @@
         <v>55.0</v>
       </c>
       <c r="X193" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y193" s="8" t="s">
         <v>141</v>
@@ -11815,7 +11815,7 @@
         <v>66.0</v>
       </c>
       <c r="X204" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y204" s="8" t="s">
         <v>144</v>
@@ -37453,16 +37453,16 @@
         <v>4</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>12</v>
@@ -37752,7 +37752,7 @@
         <v/>
       </c>
       <c r="K8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L8" s="10">
         <f>L4-L7
@@ -37981,7 +37981,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C15" s="10">
         <v>27.5</v>
@@ -38011,7 +38011,7 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C16" s="10">
         <v>25.5</v>
@@ -38036,7 +38036,7 @@
         <v/>
       </c>
       <c r="K16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L16" s="2">
         <f>IF($L$18&lt;0.3,
@@ -38058,7 +38058,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C17" s="10">
         <v>22.5</v>
@@ -38088,7 +38088,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" s="10">
         <v>20.0</v>
@@ -38113,7 +38113,7 @@
         <v/>
       </c>
       <c r="K18" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L18" s="20">
         <f>L5/L2</f>
@@ -38125,7 +38125,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" s="10">
         <v>18.5</v>
@@ -38155,7 +38155,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C20" s="10">
         <v>16.5</v>
@@ -38185,7 +38185,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C21" s="10">
         <v>14.5</v>
@@ -38215,7 +38215,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C22" s="10">
         <v>13.5</v>
@@ -38245,7 +38245,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C23" s="10">
         <v>12.0</v>
@@ -38275,7 +38275,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C24" s="10">
         <v>11.0</v>
@@ -38305,7 +38305,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C25" s="10">
         <v>10.0</v>
@@ -38335,7 +38335,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C26" s="10">
         <v>9.5</v>
@@ -38365,7 +38365,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C27" s="10">
         <v>8.5</v>
@@ -38390,7 +38390,7 @@
         <v/>
       </c>
       <c r="K27" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L27" s="2">
         <v>0.8</v>
@@ -38401,7 +38401,7 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C28" s="10">
         <v>8.0</v>
@@ -38431,7 +38431,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C29" s="10">
         <v>7.0</v>
@@ -38461,7 +38461,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C30" s="10">
         <v>6.5</v>
@@ -38491,7 +38491,7 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C31" s="10">
         <v>6.0</v>
@@ -38521,7 +38521,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C32" s="10">
         <v>5.5</v>
@@ -38551,7 +38551,7 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C33" s="10">
         <v>5.0</v>
@@ -38581,7 +38581,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C34" s="10">
         <v>4.5</v>
@@ -38611,7 +38611,7 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C35" s="10">
         <v>4.5</v>
@@ -38641,7 +38641,7 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C36" s="10">
         <v>4.0</v>
@@ -38671,7 +38671,7 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C37" s="10">
         <v>4.0</v>
@@ -38701,7 +38701,7 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C38" s="10">
         <v>3.5</v>
@@ -38731,7 +38731,7 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C39" s="10">
         <v>3.5</v>
@@ -38761,7 +38761,7 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C40" s="10">
         <v>3.0</v>
@@ -38791,7 +38791,7 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C41" s="10">
         <v>3.0</v>
@@ -38821,7 +38821,7 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C42" s="10">
         <v>2.5</v>
@@ -38851,7 +38851,7 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C43" s="10">
         <v>2.5</v>
@@ -38881,7 +38881,7 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C44" s="10">
         <v>2.5</v>
@@ -38911,7 +38911,7 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C45" s="10">
         <v>2.5</v>
@@ -38941,7 +38941,7 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C46" s="10">
         <v>2.0</v>
@@ -38971,7 +38971,7 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C47" s="10">
         <v>2.0</v>
@@ -39001,7 +39001,7 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C48" s="10">
         <v>2.0</v>
@@ -39031,7 +39031,7 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C49" s="10">
         <v>2.0</v>
@@ -39061,7 +39061,7 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C50" s="10">
         <v>2.0</v>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -14,10 +14,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="178">
   <si>
-    <t>PICK</t>
+    <t>Rank</t>
   </si>
   <si>
-    <t>Rank</t>
+    <t>PICK</t>
   </si>
   <si>
     <t>PLAYER NAME</t>
@@ -29,10 +29,10 @@
     <t>Final Price</t>
   </si>
   <si>
-    <t>VALUE</t>
+    <t>Mine?</t>
   </si>
   <si>
-    <t>Mine?</t>
+    <t>VALUE</t>
   </si>
   <si>
     <t>Inflated Fair Price</t>
@@ -95,6 +95,9 @@
     <t>Jordyn Tyson</t>
   </si>
   <si>
+    <t>Round 1</t>
+  </si>
+  <si>
     <t>Total Spent $</t>
   </si>
   <si>
@@ -111,9 +114,6 @@
   </si>
   <si>
     <t>Sonny Styles</t>
-  </si>
-  <si>
-    <t>Round 1</t>
   </si>
   <si>
     <t>My Remaining</t>
@@ -137,6 +137,9 @@
     <t>Budget Advantage Factor</t>
   </si>
   <si>
+    <t>Round 2</t>
+  </si>
+  <si>
     <t>Omar Cooper</t>
   </si>
   <si>
@@ -149,6 +152,9 @@
     <t>Arvell Reese</t>
   </si>
   <si>
+    <t>Round 3</t>
+  </si>
+  <si>
     <t>Inflation Factor</t>
   </si>
   <si>
@@ -158,10 +164,13 @@
     <t>Denzel Boston</t>
   </si>
   <si>
-    <t>Round 2</t>
+    <t>Aggression</t>
   </si>
   <si>
-    <t>Aggression</t>
+    <t>Round 4</t>
+  </si>
+  <si>
+    <t>Round 5</t>
   </si>
   <si>
     <t>Caleb Downs</t>
@@ -170,13 +179,13 @@
     <t>David Bailey</t>
   </si>
   <si>
-    <t>Round 3</t>
-  </si>
-  <si>
     <t>League Spent %</t>
   </si>
   <si>
     <t>Jacob Rodriguez</t>
+  </si>
+  <si>
+    <t>Round 6</t>
   </si>
   <si>
     <t>Jonah Coleman</t>
@@ -186,9 +195,6 @@
   </si>
   <si>
     <t>Dillon Thieneman</t>
-  </si>
-  <si>
-    <t>Round 4</t>
   </si>
   <si>
     <t>Rueben Bain</t>
@@ -201,9 +207,6 @@
   </si>
   <si>
     <t>Nicholas Singleton</t>
-  </si>
-  <si>
-    <t>Round 5</t>
   </si>
   <si>
     <t>Mike Washington</t>
@@ -228,9 +231,6 @@
   </si>
   <si>
     <t>Zachariah Branch</t>
-  </si>
-  <si>
-    <t>Round 6</t>
   </si>
   <si>
     <t>De'Zhaun Stribling</t>
@@ -657,10 +657,10 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -914,10 +914,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>8</v>
@@ -1064,14 +1064,14 @@
         <f>I2 + --(RANK(J2,$J$2:$J$73,0) &lt;= 1200*2 - SUM($I$2:$I$73))</f>
         <v>267</v>
       </c>
-      <c r="L2" s="18">
+      <c r="L2" s="17">
         <f t="shared" ref="L2:L74" si="7">D2</f>
         <v>134.5</v>
       </c>
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="10" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1173,14 +1173,14 @@
 </f>
         <v>199</v>
       </c>
-      <c r="L3" s="18">
+      <c r="L3" s="17">
         <f t="shared" si="7"/>
         <v>100.5</v>
       </c>
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1277,14 +1277,14 @@
         <f t="shared" si="10"/>
         <v>184</v>
       </c>
-      <c r="L4" s="18">
+      <c r="L4" s="17">
         <f t="shared" si="7"/>
         <v>93</v>
       </c>
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1381,14 +1381,14 @@
         <f t="shared" si="10"/>
         <v>159</v>
       </c>
-      <c r="L5" s="18">
+      <c r="L5" s="17">
         <f t="shared" si="7"/>
         <v>80.5</v>
       </c>
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="10" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1485,14 +1485,14 @@
         <f t="shared" si="10"/>
         <v>149</v>
       </c>
-      <c r="L6" s="18">
+      <c r="L6" s="17">
         <f t="shared" si="7"/>
         <v>75.5</v>
       </c>
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="10" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1589,14 +1589,14 @@
         <f t="shared" si="10"/>
         <v>136</v>
       </c>
-      <c r="L7" s="18">
+      <c r="L7" s="17">
         <f t="shared" si="7"/>
         <v>68.5</v>
       </c>
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="10" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1693,7 +1693,7 @@
         <f t="shared" si="10"/>
         <v>108</v>
       </c>
-      <c r="L8" s="18">
+      <c r="L8" s="17">
         <f t="shared" si="7"/>
         <v>54.5</v>
       </c>
@@ -1795,7 +1795,7 @@
         <f t="shared" si="10"/>
         <v>106</v>
       </c>
-      <c r="L9" s="18">
+      <c r="L9" s="17">
         <f t="shared" si="7"/>
         <v>53.5</v>
       </c>
@@ -1858,7 +1858,7 @@
         <f t="shared" si="10"/>
         <v>91</v>
       </c>
-      <c r="L10" s="18">
+      <c r="L10" s="17">
         <f t="shared" si="7"/>
         <v>46</v>
       </c>
@@ -1921,7 +1921,7 @@
         <f t="shared" si="10"/>
         <v>88</v>
       </c>
-      <c r="L11" s="18">
+      <c r="L11" s="17">
         <f t="shared" si="7"/>
         <v>44.5</v>
       </c>
@@ -1984,7 +1984,7 @@
         <f t="shared" si="10"/>
         <v>81</v>
       </c>
-      <c r="L12" s="18">
+      <c r="L12" s="17">
         <f t="shared" si="7"/>
         <v>41</v>
       </c>
@@ -2047,7 +2047,7 @@
         <f t="shared" si="10"/>
         <v>70</v>
       </c>
-      <c r="L13" s="18">
+      <c r="L13" s="17">
         <f t="shared" si="7"/>
         <v>35.5</v>
       </c>
@@ -2110,7 +2110,7 @@
         <f t="shared" si="10"/>
         <v>59</v>
       </c>
-      <c r="L14" s="18">
+      <c r="L14" s="17">
         <f t="shared" si="7"/>
         <v>29.5</v>
       </c>
@@ -2173,7 +2173,7 @@
         <f t="shared" si="10"/>
         <v>57</v>
       </c>
-      <c r="L15" s="18">
+      <c r="L15" s="17">
         <f t="shared" si="7"/>
         <v>28.5</v>
       </c>
@@ -2236,7 +2236,7 @@
         <f t="shared" si="10"/>
         <v>53</v>
       </c>
-      <c r="L16" s="18">
+      <c r="L16" s="17">
         <f t="shared" si="7"/>
         <v>26.5</v>
       </c>
@@ -2299,7 +2299,7 @@
         <f t="shared" si="10"/>
         <v>48</v>
       </c>
-      <c r="L17" s="18">
+      <c r="L17" s="17">
         <f t="shared" si="7"/>
         <v>24</v>
       </c>
@@ -2362,7 +2362,7 @@
         <f t="shared" si="10"/>
         <v>43</v>
       </c>
-      <c r="L18" s="18">
+      <c r="L18" s="17">
         <f t="shared" si="7"/>
         <v>21.5</v>
       </c>
@@ -2425,7 +2425,7 @@
         <f t="shared" si="10"/>
         <v>38</v>
       </c>
-      <c r="L19" s="18">
+      <c r="L19" s="17">
         <f t="shared" si="7"/>
         <v>19</v>
       </c>
@@ -2488,7 +2488,7 @@
         <f t="shared" si="10"/>
         <v>35</v>
       </c>
-      <c r="L20" s="18">
+      <c r="L20" s="17">
         <f t="shared" si="7"/>
         <v>17.5</v>
       </c>
@@ -2551,7 +2551,7 @@
         <f t="shared" si="10"/>
         <v>32</v>
       </c>
-      <c r="L21" s="18">
+      <c r="L21" s="17">
         <f t="shared" si="7"/>
         <v>16</v>
       </c>
@@ -2614,7 +2614,7 @@
         <f t="shared" si="10"/>
         <v>28</v>
       </c>
-      <c r="L22" s="18">
+      <c r="L22" s="17">
         <f t="shared" si="7"/>
         <v>14</v>
       </c>
@@ -2677,7 +2677,7 @@
         <f t="shared" si="10"/>
         <v>27</v>
       </c>
-      <c r="L23" s="18">
+      <c r="L23" s="17">
         <f t="shared" si="7"/>
         <v>13.5</v>
       </c>
@@ -2740,7 +2740,7 @@
         <f t="shared" si="10"/>
         <v>22</v>
       </c>
-      <c r="L24" s="18">
+      <c r="L24" s="17">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
@@ -2803,7 +2803,7 @@
         <f t="shared" si="10"/>
         <v>20</v>
       </c>
-      <c r="L25" s="18">
+      <c r="L25" s="17">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
@@ -2866,7 +2866,7 @@
         <f t="shared" si="10"/>
         <v>19</v>
       </c>
-      <c r="L26" s="18">
+      <c r="L26" s="17">
         <f t="shared" si="7"/>
         <v>9.5</v>
       </c>
@@ -2929,7 +2929,7 @@
         <f t="shared" si="10"/>
         <v>18</v>
       </c>
-      <c r="L27" s="18">
+      <c r="L27" s="17">
         <f t="shared" si="7"/>
         <v>9</v>
       </c>
@@ -2992,7 +2992,7 @@
         <f t="shared" si="10"/>
         <v>14</v>
       </c>
-      <c r="L28" s="18">
+      <c r="L28" s="17">
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
@@ -3055,7 +3055,7 @@
         <f t="shared" si="10"/>
         <v>14</v>
       </c>
-      <c r="L29" s="18">
+      <c r="L29" s="17">
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
@@ -3136,7 +3136,7 @@
         <f t="shared" si="10"/>
         <v>13</v>
       </c>
-      <c r="L30" s="18">
+      <c r="L30" s="17">
         <f t="shared" si="7"/>
         <v>6.5</v>
       </c>
@@ -3211,7 +3211,7 @@
         <f t="shared" si="10"/>
         <v>13</v>
       </c>
-      <c r="L31" s="18">
+      <c r="L31" s="17">
         <f t="shared" si="7"/>
         <v>6.5</v>
       </c>
@@ -3286,7 +3286,7 @@
         <f t="shared" si="10"/>
         <v>11</v>
       </c>
-      <c r="L32" s="18">
+      <c r="L32" s="17">
         <f t="shared" si="7"/>
         <v>5.5</v>
       </c>
@@ -3361,7 +3361,7 @@
         <f t="shared" si="10"/>
         <v>11</v>
       </c>
-      <c r="L33" s="18">
+      <c r="L33" s="17">
         <f t="shared" si="7"/>
         <v>5.5</v>
       </c>
@@ -3436,7 +3436,7 @@
         <f t="shared" si="10"/>
         <v>9</v>
       </c>
-      <c r="L34" s="18">
+      <c r="L34" s="17">
         <f t="shared" si="7"/>
         <v>4.5</v>
       </c>
@@ -3511,7 +3511,7 @@
         <f t="shared" si="10"/>
         <v>9</v>
       </c>
-      <c r="L35" s="18">
+      <c r="L35" s="17">
         <f t="shared" si="7"/>
         <v>4.5</v>
       </c>
@@ -3586,7 +3586,7 @@
         <f t="shared" si="10"/>
         <v>9</v>
       </c>
-      <c r="L36" s="18">
+      <c r="L36" s="17">
         <f t="shared" si="7"/>
         <v>4.5</v>
       </c>
@@ -3661,7 +3661,7 @@
         <f t="shared" si="10"/>
         <v>8</v>
       </c>
-      <c r="L37" s="18">
+      <c r="L37" s="17">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
@@ -3736,7 +3736,7 @@
         <f t="shared" si="10"/>
         <v>7</v>
       </c>
-      <c r="L38" s="18">
+      <c r="L38" s="17">
         <f t="shared" si="7"/>
         <v>3.5</v>
       </c>
@@ -3811,7 +3811,7 @@
         <f t="shared" si="10"/>
         <v>7</v>
       </c>
-      <c r="L39" s="18">
+      <c r="L39" s="17">
         <f t="shared" si="7"/>
         <v>3.5</v>
       </c>
@@ -3886,7 +3886,7 @@
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="L40" s="18">
+      <c r="L40" s="17">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
@@ -3961,7 +3961,7 @@
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="L41" s="18">
+      <c r="L41" s="17">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
@@ -4036,7 +4036,7 @@
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="L42" s="18">
+      <c r="L42" s="17">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
@@ -4102,7 +4102,7 @@
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
-      <c r="L43" s="18">
+      <c r="L43" s="17">
         <f t="shared" si="7"/>
         <v>2.5</v>
       </c>
@@ -4168,7 +4168,7 @@
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
-      <c r="L44" s="18">
+      <c r="L44" s="17">
         <f t="shared" si="7"/>
         <v>2.5</v>
       </c>
@@ -4242,7 +4242,7 @@
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
-      <c r="L45" s="18">
+      <c r="L45" s="17">
         <f t="shared" si="7"/>
         <v>2.5</v>
       </c>
@@ -4332,7 +4332,7 @@
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="L46" s="18">
+      <c r="L46" s="17">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
@@ -4410,7 +4410,7 @@
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="L47" s="18">
+      <c r="L47" s="17">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
@@ -4488,7 +4488,7 @@
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="L48" s="18">
+      <c r="L48" s="17">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
@@ -4566,7 +4566,7 @@
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="L49" s="18">
+      <c r="L49" s="17">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
@@ -4644,7 +4644,7 @@
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="L50" s="18">
+      <c r="L50" s="17">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
@@ -4722,7 +4722,7 @@
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="L51" s="18">
+      <c r="L51" s="17">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
@@ -4800,7 +4800,7 @@
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="L52" s="18">
+      <c r="L52" s="17">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
@@ -4878,7 +4878,7 @@
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="L53" s="18">
+      <c r="L53" s="17">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
@@ -4956,7 +4956,7 @@
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="L54" s="18">
+      <c r="L54" s="17">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
@@ -5034,7 +5034,7 @@
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="L55" s="18">
+      <c r="L55" s="17">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
@@ -5112,7 +5112,7 @@
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="L56" s="18">
+      <c r="L56" s="17">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
@@ -5190,7 +5190,7 @@
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="L57" s="18">
+      <c r="L57" s="17">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
@@ -5268,7 +5268,7 @@
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="L58" s="18">
+      <c r="L58" s="17">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
@@ -5346,7 +5346,7 @@
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="L59" s="18">
+      <c r="L59" s="17">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
@@ -5424,7 +5424,7 @@
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="L60" s="18">
+      <c r="L60" s="17">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
@@ -5502,7 +5502,7 @@
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="L61" s="18">
+      <c r="L61" s="17">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
@@ -5580,7 +5580,7 @@
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="L62" s="18">
+      <c r="L62" s="17">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
@@ -5662,7 +5662,7 @@
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="L63" s="18">
+      <c r="L63" s="17">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
@@ -5745,7 +5745,7 @@
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="L64" s="18">
+      <c r="L64" s="17">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
@@ -5828,7 +5828,7 @@
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="L65" s="18">
+      <c r="L65" s="17">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
@@ -5911,7 +5911,7 @@
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="L66" s="18">
+      <c r="L66" s="17">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
@@ -5994,7 +5994,7 @@
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="L67" s="18">
+      <c r="L67" s="17">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
@@ -6077,7 +6077,7 @@
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="L68" s="18">
+      <c r="L68" s="17">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
@@ -6160,7 +6160,7 @@
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="L69" s="18">
+      <c r="L69" s="17">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
@@ -6243,7 +6243,7 @@
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="L70" s="18">
+      <c r="L70" s="17">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
@@ -6326,7 +6326,7 @@
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="L71" s="18">
+      <c r="L71" s="17">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
@@ -6409,7 +6409,7 @@
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="L72" s="18">
+      <c r="L72" s="17">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
@@ -6492,7 +6492,7 @@
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="L73" s="18">
+      <c r="L73" s="17">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
@@ -6555,7 +6555,7 @@
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
       <c r="K74" s="5"/>
-      <c r="L74" s="18">
+      <c r="L74" s="17">
         <f t="shared" si="7"/>
         <v>1200</v>
       </c>
@@ -9212,7 +9212,7 @@
       <c r="U139" s="12"/>
       <c r="V139" s="12"/>
       <c r="W139" s="7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X139" s="7" t="s">
         <v>138</v>
@@ -9375,7 +9375,7 @@
         <v>5.0</v>
       </c>
       <c r="X143" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y143" s="7" t="s">
         <v>141</v>
@@ -9455,7 +9455,7 @@
         <v>7.0</v>
       </c>
       <c r="X145" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y145" s="7" t="s">
         <v>143</v>
@@ -9495,7 +9495,7 @@
         <v>8.0</v>
       </c>
       <c r="X146" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Y146" s="7" t="s">
         <v>144</v>
@@ -9535,7 +9535,7 @@
         <v>9.0</v>
       </c>
       <c r="X147" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Y147" s="7" t="s">
         <v>141</v>
@@ -9575,7 +9575,7 @@
         <v>10.0</v>
       </c>
       <c r="X148" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Y148" s="7" t="s">
         <v>145</v>
@@ -9615,7 +9615,7 @@
         <v>11.0</v>
       </c>
       <c r="X149" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Y149" s="7" t="s">
         <v>143</v>
@@ -9655,7 +9655,7 @@
         <v>12.0</v>
       </c>
       <c r="X150" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Y150" s="7" t="s">
         <v>146</v>
@@ -9815,7 +9815,7 @@
         <v>16.0</v>
       </c>
       <c r="X154" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Y154" s="7" t="s">
         <v>143</v>
@@ -9855,7 +9855,7 @@
         <v>17.0</v>
       </c>
       <c r="X155" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="Y155" s="7" t="s">
         <v>140</v>
@@ -9895,7 +9895,7 @@
         <v>18.0</v>
       </c>
       <c r="X156" s="7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Y156" s="7" t="s">
         <v>145</v>
@@ -10095,7 +10095,7 @@
         <v>23.0</v>
       </c>
       <c r="X161" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Y161" s="7" t="s">
         <v>142</v>
@@ -10135,7 +10135,7 @@
         <v>24.0</v>
       </c>
       <c r="X162" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y162" s="7" t="s">
         <v>141</v>
@@ -10175,7 +10175,7 @@
         <v>25.0</v>
       </c>
       <c r="X163" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Y163" s="7" t="s">
         <v>140</v>
@@ -10215,7 +10215,7 @@
         <v>26.0</v>
       </c>
       <c r="X164" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Y164" s="7" t="s">
         <v>140</v>
@@ -10335,7 +10335,7 @@
         <v>29.0</v>
       </c>
       <c r="X167" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="Y167" s="7" t="s">
         <v>143</v>
@@ -10375,7 +10375,7 @@
         <v>30.0</v>
       </c>
       <c r="X168" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Y168" s="7" t="s">
         <v>141</v>
@@ -10415,7 +10415,7 @@
         <v>31.0</v>
       </c>
       <c r="X169" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y169" s="7" t="s">
         <v>141</v>
@@ -10695,7 +10695,7 @@
         <v>38.0</v>
       </c>
       <c r="X176" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="Y176" s="7" t="s">
         <v>141</v>
@@ -10735,7 +10735,7 @@
         <v>39.0</v>
       </c>
       <c r="X177" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Y177" s="7" t="s">
         <v>144</v>
@@ -10815,7 +10815,7 @@
         <v>41.0</v>
       </c>
       <c r="X179" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Y179" s="7" t="s">
         <v>141</v>
@@ -37444,7 +37444,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -37456,7 +37456,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>7</v>
@@ -37619,7 +37619,7 @@
       <c r="C5" s="9">
         <v>82.5</v>
       </c>
-      <c r="E5" s="17" t="b">
+      <c r="E5" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F5" s="9">
@@ -37639,9 +37639,9 @@
         <v/>
       </c>
       <c r="K5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5" s="17">
+        <v>28</v>
+      </c>
+      <c r="L5" s="18">
         <f>SUM($D$2:$D$500)
 </f>
         <v>0</v>
@@ -37652,12 +37652,12 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="9">
         <v>76.0</v>
       </c>
-      <c r="E6" s="17" t="b">
+      <c r="E6" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F6" s="9">
@@ -37677,9 +37677,9 @@
         <v/>
       </c>
       <c r="K6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" s="17">
+        <v>30</v>
+      </c>
+      <c r="L6" s="18">
         <f>L2-L5
 </f>
         <v>1200</v>
@@ -37690,12 +37690,12 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" s="9">
         <v>66.5</v>
       </c>
-      <c r="E7" s="17" t="b">
+      <c r="E7" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F7" s="9">
@@ -37715,9 +37715,9 @@
         <v/>
       </c>
       <c r="K7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L7" s="17">
+        <v>32</v>
+      </c>
+      <c r="L7" s="18">
         <f>SUMIF($E$2:$E$500,TRUE,$D$2:$D$500)</f>
         <v>0</v>
       </c>
@@ -37727,12 +37727,12 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="9">
         <v>57.5</v>
       </c>
-      <c r="E8" s="17" t="b">
+      <c r="E8" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F8" s="9">
@@ -37770,7 +37770,7 @@
       <c r="C9" s="9">
         <v>53.0</v>
       </c>
-      <c r="E9" s="17" t="b">
+      <c r="E9" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F9" s="9">
@@ -37808,7 +37808,7 @@
       <c r="C10" s="9">
         <v>48.0</v>
       </c>
-      <c r="E10" s="17" t="b">
+      <c r="E10" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F10" s="9">
@@ -37845,7 +37845,7 @@
       <c r="C11" s="9">
         <v>43.0</v>
       </c>
-      <c r="E11" s="17" t="b">
+      <c r="E11" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F11" s="9">
@@ -37877,12 +37877,12 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12" s="9">
         <v>39.0</v>
       </c>
-      <c r="E12" s="17" t="b">
+      <c r="E12" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F12" s="9">
@@ -37907,12 +37907,12 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13" s="9">
         <v>34.0</v>
       </c>
-      <c r="E13" s="17" t="b">
+      <c r="E13" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F13" s="9">
@@ -37932,9 +37932,9 @@
         <v/>
       </c>
       <c r="K13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L13" s="17">
+        <v>44</v>
+      </c>
+      <c r="L13" s="18">
         <f>SUMIF($D$2:$D$73,"",$C$2:$C$73)</f>
         <v>1200</v>
       </c>
@@ -37944,12 +37944,12 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" s="9">
         <v>30.5</v>
       </c>
-      <c r="E14" s="17" t="b">
+      <c r="E14" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F14" s="9">
@@ -37969,7 +37969,7 @@
         <v/>
       </c>
       <c r="K14" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L14" s="19">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -37981,12 +37981,12 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C15" s="9">
         <v>27.5</v>
       </c>
-      <c r="E15" s="17" t="b">
+      <c r="E15" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F15" s="9">
@@ -38011,12 +38011,12 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C16" s="9">
         <v>25.5</v>
       </c>
-      <c r="E16" s="17" t="b">
+      <c r="E16" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F16" s="9">
@@ -38036,7 +38036,7 @@
         <v/>
       </c>
       <c r="K16" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L16" s="1">
         <f>IF($L$18&lt;0.3,
@@ -38058,12 +38058,12 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C17" s="9">
         <v>22.5</v>
       </c>
-      <c r="E17" s="17" t="b">
+      <c r="E17" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F17" s="9">
@@ -38088,12 +38088,12 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C18" s="9">
         <v>20.0</v>
       </c>
-      <c r="E18" s="17" t="b">
+      <c r="E18" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F18" s="9">
@@ -38113,7 +38113,7 @@
         <v/>
       </c>
       <c r="K18" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L18" s="20">
         <f>L5/L2</f>
@@ -38125,12 +38125,12 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C19" s="9">
         <v>18.5</v>
       </c>
-      <c r="E19" s="17" t="b">
+      <c r="E19" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F19" s="9">
@@ -38155,12 +38155,12 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C20" s="9">
         <v>16.5</v>
       </c>
-      <c r="E20" s="17" t="b">
+      <c r="E20" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F20" s="9">
@@ -38185,12 +38185,12 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C21" s="9">
         <v>14.5</v>
       </c>
-      <c r="E21" s="17" t="b">
+      <c r="E21" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F21" s="9">
@@ -38215,12 +38215,12 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C22" s="9">
         <v>13.5</v>
       </c>
-      <c r="E22" s="17" t="b">
+      <c r="E22" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F22" s="9">
@@ -38245,12 +38245,12 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C23" s="9">
         <v>12.0</v>
       </c>
-      <c r="E23" s="17" t="b">
+      <c r="E23" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F23" s="9">
@@ -38275,12 +38275,12 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C24" s="9">
         <v>11.0</v>
       </c>
-      <c r="E24" s="17" t="b">
+      <c r="E24" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F24" s="9">
@@ -38305,12 +38305,12 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C25" s="9">
         <v>10.0</v>
       </c>
-      <c r="E25" s="17" t="b">
+      <c r="E25" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F25" s="9">
@@ -38335,12 +38335,12 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C26" s="9">
         <v>9.5</v>
       </c>
-      <c r="E26" s="17" t="b">
+      <c r="E26" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F26" s="9">
@@ -38365,12 +38365,12 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C27" s="9">
         <v>8.5</v>
       </c>
-      <c r="E27" s="17" t="b">
+      <c r="E27" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F27" s="9">
@@ -38390,7 +38390,7 @@
         <v/>
       </c>
       <c r="K27" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L27" s="1">
         <v>0.8</v>
@@ -38401,12 +38401,12 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C28" s="9">
         <v>8.0</v>
       </c>
-      <c r="E28" s="17" t="b">
+      <c r="E28" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F28" s="9">
@@ -38431,12 +38431,12 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29" s="9">
         <v>7.0</v>
       </c>
-      <c r="E29" s="17" t="b">
+      <c r="E29" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F29" s="9">
@@ -38461,12 +38461,12 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C30" s="9">
         <v>6.5</v>
       </c>
-      <c r="E30" s="17" t="b">
+      <c r="E30" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F30" s="9">
@@ -38491,12 +38491,12 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C31" s="9">
         <v>6.0</v>
       </c>
-      <c r="E31" s="17" t="b">
+      <c r="E31" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F31" s="9">
@@ -38521,12 +38521,12 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C32" s="9">
         <v>5.5</v>
       </c>
-      <c r="E32" s="17" t="b">
+      <c r="E32" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F32" s="9">
@@ -38551,12 +38551,12 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C33" s="9">
         <v>5.0</v>
       </c>
-      <c r="E33" s="17" t="b">
+      <c r="E33" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F33" s="9">
@@ -38586,7 +38586,7 @@
       <c r="C34" s="9">
         <v>4.5</v>
       </c>
-      <c r="E34" s="17" t="b">
+      <c r="E34" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F34" s="9">
@@ -38616,7 +38616,7 @@
       <c r="C35" s="9">
         <v>4.5</v>
       </c>
-      <c r="E35" s="17" t="b">
+      <c r="E35" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F35" s="9">
@@ -38646,7 +38646,7 @@
       <c r="C36" s="9">
         <v>4.0</v>
       </c>
-      <c r="E36" s="17" t="b">
+      <c r="E36" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F36" s="9">
@@ -38676,7 +38676,7 @@
       <c r="C37" s="9">
         <v>4.0</v>
       </c>
-      <c r="E37" s="17" t="b">
+      <c r="E37" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F37" s="9">
@@ -38706,7 +38706,7 @@
       <c r="C38" s="9">
         <v>3.5</v>
       </c>
-      <c r="E38" s="17" t="b">
+      <c r="E38" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F38" s="9">
@@ -38736,7 +38736,7 @@
       <c r="C39" s="9">
         <v>3.5</v>
       </c>
-      <c r="E39" s="17" t="b">
+      <c r="E39" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F39" s="9">
@@ -38766,7 +38766,7 @@
       <c r="C40" s="9">
         <v>3.0</v>
       </c>
-      <c r="E40" s="17" t="b">
+      <c r="E40" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F40" s="9">
@@ -38796,7 +38796,7 @@
       <c r="C41" s="9">
         <v>3.0</v>
       </c>
-      <c r="E41" s="17" t="b">
+      <c r="E41" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F41" s="9">
@@ -38826,7 +38826,7 @@
       <c r="C42" s="9">
         <v>2.5</v>
       </c>
-      <c r="E42" s="17" t="b">
+      <c r="E42" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F42" s="9">
@@ -38856,7 +38856,7 @@
       <c r="C43" s="9">
         <v>2.5</v>
       </c>
-      <c r="E43" s="17" t="b">
+      <c r="E43" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F43" s="9">
@@ -38886,7 +38886,7 @@
       <c r="C44" s="9">
         <v>2.5</v>
       </c>
-      <c r="E44" s="17" t="b">
+      <c r="E44" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F44" s="9">
@@ -38916,7 +38916,7 @@
       <c r="C45" s="9">
         <v>2.5</v>
       </c>
-      <c r="E45" s="17" t="b">
+      <c r="E45" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F45" s="9">
@@ -38946,7 +38946,7 @@
       <c r="C46" s="9">
         <v>2.0</v>
       </c>
-      <c r="E46" s="17" t="b">
+      <c r="E46" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F46" s="9">
@@ -38976,7 +38976,7 @@
       <c r="C47" s="9">
         <v>2.0</v>
       </c>
-      <c r="E47" s="17" t="b">
+      <c r="E47" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F47" s="9">
@@ -39006,7 +39006,7 @@
       <c r="C48" s="9">
         <v>2.0</v>
       </c>
-      <c r="E48" s="17" t="b">
+      <c r="E48" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F48" s="9">
@@ -39036,7 +39036,7 @@
       <c r="C49" s="9">
         <v>2.0</v>
       </c>
-      <c r="E49" s="17" t="b">
+      <c r="E49" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F49" s="9">
@@ -39066,7 +39066,7 @@
       <c r="C50" s="9">
         <v>2.0</v>
       </c>
-      <c r="E50" s="17" t="b">
+      <c r="E50" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F50" s="9">
@@ -39096,7 +39096,7 @@
       <c r="C51" s="9">
         <v>2.0</v>
       </c>
-      <c r="E51" s="17" t="b">
+      <c r="E51" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F51" s="9">
@@ -39126,7 +39126,7 @@
       <c r="C52" s="9">
         <v>2.0</v>
       </c>
-      <c r="E52" s="17" t="b">
+      <c r="E52" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F52" s="9">
@@ -39156,7 +39156,7 @@
       <c r="C53" s="9">
         <v>2.0</v>
       </c>
-      <c r="E53" s="17" t="b">
+      <c r="E53" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F53" s="9">
@@ -39186,7 +39186,7 @@
       <c r="C54" s="9">
         <v>2.0</v>
       </c>
-      <c r="E54" s="17" t="b">
+      <c r="E54" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F54" s="9">
@@ -39216,7 +39216,7 @@
       <c r="C55" s="9">
         <v>2.0</v>
       </c>
-      <c r="E55" s="17" t="b">
+      <c r="E55" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F55" s="9">
@@ -39246,7 +39246,7 @@
       <c r="C56" s="9">
         <v>2.0</v>
       </c>
-      <c r="E56" s="17" t="b">
+      <c r="E56" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F56" s="9">
@@ -39276,7 +39276,7 @@
       <c r="C57" s="9">
         <v>2.0</v>
       </c>
-      <c r="E57" s="17" t="b">
+      <c r="E57" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F57" s="9">
@@ -39306,7 +39306,7 @@
       <c r="C58" s="9">
         <v>2.0</v>
       </c>
-      <c r="E58" s="17" t="b">
+      <c r="E58" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F58" s="9">
@@ -39336,7 +39336,7 @@
       <c r="C59" s="9">
         <v>2.0</v>
       </c>
-      <c r="E59" s="17" t="b">
+      <c r="E59" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F59" s="9">
@@ -39366,7 +39366,7 @@
       <c r="C60" s="9">
         <v>2.0</v>
       </c>
-      <c r="E60" s="17" t="b">
+      <c r="E60" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F60" s="9">
@@ -39396,7 +39396,7 @@
       <c r="C61" s="9">
         <v>2.0</v>
       </c>
-      <c r="E61" s="17" t="b">
+      <c r="E61" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F61" s="9">
@@ -39426,7 +39426,7 @@
       <c r="C62" s="9">
         <v>1.0</v>
       </c>
-      <c r="E62" s="17" t="b">
+      <c r="E62" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F62" s="9">
@@ -39456,7 +39456,7 @@
       <c r="C63" s="9">
         <v>1.0</v>
       </c>
-      <c r="E63" s="17" t="b">
+      <c r="E63" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F63" s="9">
@@ -39486,7 +39486,7 @@
       <c r="C64" s="9">
         <v>1.0</v>
       </c>
-      <c r="E64" s="17" t="b">
+      <c r="E64" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F64" s="9">
@@ -39516,7 +39516,7 @@
       <c r="C65" s="9">
         <v>1.0</v>
       </c>
-      <c r="E65" s="17" t="b">
+      <c r="E65" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F65" s="9">
@@ -39546,7 +39546,7 @@
       <c r="C66" s="9">
         <v>1.0</v>
       </c>
-      <c r="E66" s="17" t="b">
+      <c r="E66" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F66" s="9">
@@ -39576,7 +39576,7 @@
       <c r="C67" s="9">
         <v>1.0</v>
       </c>
-      <c r="E67" s="17" t="b">
+      <c r="E67" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F67" s="9">
@@ -39606,7 +39606,7 @@
       <c r="C68" s="9">
         <v>1.0</v>
       </c>
-      <c r="E68" s="17" t="b">
+      <c r="E68" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F68" s="9">
@@ -39636,7 +39636,7 @@
       <c r="C69" s="9">
         <v>1.0</v>
       </c>
-      <c r="E69" s="17" t="b">
+      <c r="E69" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F69" s="9">
@@ -39666,7 +39666,7 @@
       <c r="C70" s="9">
         <v>1.0</v>
       </c>
-      <c r="E70" s="17" t="b">
+      <c r="E70" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F70" s="9">
@@ -39696,7 +39696,7 @@
       <c r="C71" s="9">
         <v>1.0</v>
       </c>
-      <c r="E71" s="17" t="b">
+      <c r="E71" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F71" s="9">
@@ -39726,7 +39726,7 @@
       <c r="C72" s="9">
         <v>1.0</v>
       </c>
-      <c r="E72" s="17" t="b">
+      <c r="E72" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F72" s="9">
@@ -39756,7 +39756,7 @@
       <c r="C73" s="9">
         <v>1.0</v>
       </c>
-      <c r="E73" s="17" t="b">
+      <c r="E73" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F73" s="9">

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -29,10 +29,10 @@
     <t>PreDraft$</t>
   </si>
   <si>
-    <t>Final Price</t>
+    <t>Decay</t>
   </si>
   <si>
-    <t>Decay</t>
+    <t>Final Price</t>
   </si>
   <si>
     <t>Mine?</t>
@@ -101,9 +101,6 @@
     <t>Makai Lemon</t>
   </si>
   <si>
-    <t>Round 1</t>
-  </si>
-  <si>
     <t>Remaining Leage $</t>
   </si>
   <si>
@@ -119,6 +116,9 @@
     <t>My Remaining</t>
   </si>
   <si>
+    <t>Round 1</t>
+  </si>
+  <si>
     <t>KC Concepcion</t>
   </si>
   <si>
@@ -132,9 +132,6 @@
   </si>
   <si>
     <t>Eli Stowers</t>
-  </si>
-  <si>
-    <t>Round 2</t>
   </si>
   <si>
     <t>Budget Advantage Factor</t>
@@ -155,7 +152,7 @@
     <t>Inflation Factor</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>Round 2</t>
   </si>
   <si>
     <t>Ty Simpson</t>
@@ -167,10 +164,10 @@
     <t>Aggression</t>
   </si>
   <si>
-    <t>Caleb Downs</t>
+    <t>Round 3</t>
   </si>
   <si>
-    <t>Round 4</t>
+    <t>Caleb Downs</t>
   </si>
   <si>
     <t>David Bailey</t>
@@ -183,6 +180,9 @@
   </si>
   <si>
     <t>Jonah Coleman</t>
+  </si>
+  <si>
+    <t>Round 4</t>
   </si>
   <si>
     <t>Jake Golday</t>
@@ -200,13 +200,13 @@
     <t>Germie Bernard</t>
   </si>
   <si>
+    <t>Round 5</t>
+  </si>
+  <si>
     <t>Nicholas Singleton</t>
   </si>
   <si>
     <t>Mike Washington</t>
-  </si>
-  <si>
-    <t>Round 5</t>
   </si>
   <si>
     <t>Enforce % of Fair</t>
@@ -224,13 +224,13 @@
     <t>Chris Brazzell</t>
   </si>
   <si>
+    <t>Round 6</t>
+  </si>
+  <si>
     <t>Max Klare</t>
   </si>
   <si>
     <t>Zachariah Branch</t>
-  </si>
-  <si>
-    <t>Round 6</t>
   </si>
   <si>
     <t>De'Zhaun Stribling</t>
@@ -920,7 +920,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>9</v>
@@ -1071,7 +1071,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="8" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="8" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="8" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -9455,7 +9455,7 @@
         <v>7.0</v>
       </c>
       <c r="X145" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y145" s="9" t="s">
         <v>143</v>
@@ -9495,7 +9495,7 @@
         <v>8.0</v>
       </c>
       <c r="X146" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Y146" s="9" t="s">
         <v>144</v>
@@ -9535,7 +9535,7 @@
         <v>9.0</v>
       </c>
       <c r="X147" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Y147" s="9" t="s">
         <v>141</v>
@@ -9615,7 +9615,7 @@
         <v>11.0</v>
       </c>
       <c r="X149" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Y149" s="9" t="s">
         <v>143</v>
@@ -9655,7 +9655,7 @@
         <v>12.0</v>
       </c>
       <c r="X150" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Y150" s="9" t="s">
         <v>146</v>
@@ -9815,7 +9815,7 @@
         <v>16.0</v>
       </c>
       <c r="X154" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Y154" s="9" t="s">
         <v>143</v>
@@ -9855,7 +9855,7 @@
         <v>17.0</v>
       </c>
       <c r="X155" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Y155" s="9" t="s">
         <v>140</v>
@@ -10095,7 +10095,7 @@
         <v>23.0</v>
       </c>
       <c r="X161" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Y161" s="9" t="s">
         <v>142</v>
@@ -10215,7 +10215,7 @@
         <v>26.0</v>
       </c>
       <c r="X164" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Y164" s="9" t="s">
         <v>140</v>
@@ -10415,7 +10415,7 @@
         <v>31.0</v>
       </c>
       <c r="X169" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y169" s="9" t="s">
         <v>141</v>
@@ -10735,7 +10735,7 @@
         <v>39.0</v>
       </c>
       <c r="X177" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Y177" s="9" t="s">
         <v>144</v>
@@ -37453,7 +37453,7 @@
         <v>4</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>7</v>
@@ -37677,7 +37677,7 @@
         <v/>
       </c>
       <c r="K6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L6" s="17">
         <f>L2-L5
@@ -37690,7 +37690,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" s="10">
         <v>66.5</v>
@@ -37715,7 +37715,7 @@
         <v/>
       </c>
       <c r="K7" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L7" s="17">
         <f>SUMIF($E$2:$E$500,TRUE,$D$2:$D$500)</f>
@@ -37727,7 +37727,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="10">
         <v>57.5</v>
@@ -37752,7 +37752,7 @@
         <v/>
       </c>
       <c r="K8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L8" s="10">
         <f>L4-L7
@@ -37865,7 +37865,7 @@
         <v/>
       </c>
       <c r="K11" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L11" s="19">
         <f>IF(L10&gt;0,L8/L10,1)</f>
@@ -37877,7 +37877,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="10">
         <v>39.0</v>
@@ -37907,7 +37907,7 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="10">
         <v>34.0</v>
@@ -37932,7 +37932,7 @@
         <v/>
       </c>
       <c r="K13" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L13" s="17">
         <f>SUMIF($D$2:$D$73,"",$C$2:$C$73)</f>
@@ -37944,7 +37944,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" s="10">
         <v>30.5</v>
@@ -37969,7 +37969,7 @@
         <v/>
       </c>
       <c r="K14" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L14" s="19">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -37981,7 +37981,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" s="10">
         <v>27.5</v>
@@ -38011,7 +38011,7 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C16" s="10">
         <v>25.5</v>
@@ -38036,7 +38036,7 @@
         <v/>
       </c>
       <c r="K16" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L16" s="2">
         <f>IF($L$18&lt;0.3,
@@ -38088,7 +38088,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="10">
         <v>20.0</v>
@@ -38113,7 +38113,7 @@
         <v/>
       </c>
       <c r="K18" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L18" s="20">
         <f>L5/L2</f>
@@ -38125,7 +38125,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C19" s="10">
         <v>18.5</v>
@@ -38155,7 +38155,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C20" s="10">
         <v>16.5</v>
@@ -38335,7 +38335,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C26" s="10">
         <v>9.5</v>
@@ -38365,7 +38365,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" s="10">
         <v>8.5</v>
@@ -38521,7 +38521,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C32" s="10">
         <v>5.5</v>
@@ -38551,7 +38551,7 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C33" s="10">
         <v>5.0</v>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -14,13 +14,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="178">
   <si>
-    <t>PICK</t>
-  </si>
-  <si>
     <t>Rank</t>
   </si>
   <si>
-    <t>VALUE</t>
+    <t>PICK</t>
   </si>
   <si>
     <t>PLAYER NAME</t>
@@ -35,6 +32,9 @@
     <t>Mine?</t>
   </si>
   <si>
+    <t>VALUE</t>
+  </si>
+  <si>
     <t>Inflated Fair Price</t>
   </si>
   <si>
@@ -47,16 +47,16 @@
     <t>EnforceUpTo</t>
   </si>
   <si>
+    <t>New Values</t>
+  </si>
+  <si>
     <t>Value vs Fair</t>
   </si>
   <si>
-    <t>New Values</t>
+    <t>Spine</t>
   </si>
   <si>
     <t>Settings</t>
-  </si>
-  <si>
-    <t>Spine</t>
   </si>
   <si>
     <t>Jeremiyah Love</t>
@@ -98,13 +98,13 @@
     <t>Total Spent $</t>
   </si>
   <si>
-    <t>Round 1</t>
-  </si>
-  <si>
     <t>Makai Lemon</t>
   </si>
   <si>
     <t>Remaining Leage $</t>
+  </si>
+  <si>
+    <t>Round 1</t>
   </si>
   <si>
     <t>Kenyon Sadiq</t>
@@ -134,22 +134,19 @@
     <t>Eli Stowers</t>
   </si>
   <si>
-    <t>Round 2</t>
-  </si>
-  <si>
     <t>Budget Advantage Factor</t>
   </si>
   <si>
     <t>Omar Cooper</t>
   </si>
   <si>
+    <t>Round 2</t>
+  </si>
+  <si>
     <t>CJ Allen</t>
   </si>
   <si>
     <t>Undrafted Predraft$</t>
-  </si>
-  <si>
-    <t>Round 3</t>
   </si>
   <si>
     <t>Arvell Reese</t>
@@ -161,6 +158,9 @@
     <t>Ty Simpson</t>
   </si>
   <si>
+    <t>Round 3</t>
+  </si>
+  <si>
     <t>Denzel Boston</t>
   </si>
   <si>
@@ -168,9 +168,6 @@
   </si>
   <si>
     <t>Round 4</t>
-  </si>
-  <si>
-    <t>Round 5</t>
   </si>
   <si>
     <t>Caleb Downs</t>
@@ -185,10 +182,10 @@
     <t>Jacob Rodriguez</t>
   </si>
   <si>
-    <t>Round 6</t>
+    <t>Jonah Coleman</t>
   </si>
   <si>
-    <t>Jonah Coleman</t>
+    <t>Round 5</t>
   </si>
   <si>
     <t>Jake Golday</t>
@@ -204,6 +201,9 @@
   </si>
   <si>
     <t>Germie Bernard</t>
+  </si>
+  <si>
+    <t>Round 6</t>
   </si>
   <si>
     <t>Nicholas Singleton</t>
@@ -338,6 +338,21 @@
     <t>Bryce Lance</t>
   </si>
   <si>
+    <t>Kevin Coleman</t>
+  </si>
+  <si>
+    <t>Garrett Nussmeier</t>
+  </si>
+  <si>
+    <t>Nate Boerkircher</t>
+  </si>
+  <si>
+    <t>Will Kacmarek</t>
+  </si>
+  <si>
+    <t>Noah Whittington</t>
+  </si>
+  <si>
     <t>Standings</t>
   </si>
   <si>
@@ -365,22 +380,7 @@
     <t>Key</t>
   </si>
   <si>
-    <t>Kevin Coleman</t>
-  </si>
-  <si>
-    <t>Garrett Nussmeier</t>
-  </si>
-  <si>
-    <t>Nate Boerkircher</t>
-  </si>
-  <si>
     <t>Ed</t>
-  </si>
-  <si>
-    <t>Will Kacmarek</t>
-  </si>
-  <si>
-    <t>Noah Whittington</t>
   </si>
   <si>
     <t>Brent</t>
@@ -566,11 +566,11 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF1B1C1D"/>
@@ -611,66 +611,66 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -913,20 +913,20 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F1" s="6">
         <v>2025.0</v>
@@ -1071,7 +1071,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="10" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="10" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -3062,33 +3062,33 @@
       <c r="M29" s="12"/>
       <c r="N29" s="12"/>
       <c r="O29" s="10" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="Q29" s="12"/>
       <c r="R29" s="10" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="S29" s="10" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="T29" s="10" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="U29" s="12"/>
       <c r="V29" s="10" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="W29" s="10" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="X29" s="10" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Y29" s="10" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="Z29" s="12"/>
       <c r="AA29" s="12"/>
@@ -3146,7 +3146,7 @@
         <v>1.0</v>
       </c>
       <c r="P30" s="10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q30" s="12"/>
       <c r="R30" s="6">
@@ -3158,8 +3158,8 @@
         <v>Ed</v>
       </c>
       <c r="U30" s="12"/>
-      <c r="V30" s="21"/>
-      <c r="W30" s="21"/>
+      <c r="V30" s="23"/>
+      <c r="W30" s="23"/>
       <c r="X30" s="7"/>
       <c r="Y30" s="12" t="str">
         <f t="shared" ref="Y30:Y81" si="17">TEXT(V30,"0")&amp;"|"&amp;TRIM(W30)</f>
@@ -4000,7 +4000,7 @@
       <c r="A42" s="13">
         <v>4.05</v>
       </c>
-      <c r="B42" s="21">
+      <c r="B42" s="23">
         <v>2048.0</v>
       </c>
       <c r="C42" s="16">
@@ -4175,7 +4175,7 @@
       <c r="M44" s="12"/>
       <c r="N44" s="12"/>
       <c r="O44" s="10" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="P44" s="10" t="s">
         <v>20</v>
@@ -4184,7 +4184,7 @@
         <v>134</v>
       </c>
       <c r="R44" s="10" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="S44" s="12"/>
       <c r="T44" s="12"/>
@@ -5293,8 +5293,8 @@
       <c r="S58" s="12"/>
       <c r="T58" s="12"/>
       <c r="U58" s="12"/>
-      <c r="V58" s="21"/>
-      <c r="W58" s="21"/>
+      <c r="V58" s="23"/>
+      <c r="W58" s="23"/>
       <c r="X58" s="7"/>
       <c r="Y58" s="12" t="str">
         <f t="shared" si="17"/>
@@ -5371,8 +5371,8 @@
       <c r="S59" s="12"/>
       <c r="T59" s="12"/>
       <c r="U59" s="12"/>
-      <c r="V59" s="21"/>
-      <c r="W59" s="21"/>
+      <c r="V59" s="23"/>
+      <c r="W59" s="23"/>
       <c r="X59" s="7"/>
       <c r="Y59" s="12" t="str">
         <f t="shared" si="17"/>
@@ -5449,8 +5449,8 @@
       <c r="S60" s="12"/>
       <c r="T60" s="12"/>
       <c r="U60" s="12"/>
-      <c r="V60" s="21"/>
-      <c r="W60" s="21"/>
+      <c r="V60" s="23"/>
+      <c r="W60" s="23"/>
       <c r="X60" s="7"/>
       <c r="Y60" s="12" t="str">
         <f t="shared" si="17"/>
@@ -5775,8 +5775,8 @@
         <f t="shared" si="22"/>
         <v>144.5</v>
       </c>
-      <c r="V64" s="21"/>
-      <c r="W64" s="21"/>
+      <c r="V64" s="23"/>
+      <c r="W64" s="23"/>
       <c r="X64" s="7"/>
       <c r="Y64" s="12" t="str">
         <f t="shared" si="17"/>
@@ -6124,7 +6124,7 @@
       <c r="A69" s="13">
         <v>6.08</v>
       </c>
-      <c r="B69" s="21">
+      <c r="B69" s="23">
         <v>1242.0</v>
       </c>
       <c r="C69" s="16">
@@ -6190,8 +6190,8 @@
         <f t="shared" si="22"/>
         <v>83</v>
       </c>
-      <c r="V69" s="21"/>
-      <c r="W69" s="21"/>
+      <c r="V69" s="23"/>
+      <c r="W69" s="23"/>
       <c r="X69" s="7"/>
       <c r="Y69" s="12" t="str">
         <f t="shared" si="17"/>
@@ -6373,7 +6373,7 @@
       <c r="A72" s="13">
         <v>6.11</v>
       </c>
-      <c r="B72" s="21">
+      <c r="B72" s="23">
         <v>1190.0</v>
       </c>
       <c r="C72" s="16">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="S74" s="12"/>
       <c r="T74" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="U74" s="16">
         <f t="shared" si="22"/>
@@ -9212,7 +9212,7 @@
       <c r="U139" s="12"/>
       <c r="V139" s="12"/>
       <c r="W139" s="7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X139" s="7" t="s">
         <v>138</v>
@@ -9375,7 +9375,7 @@
         <v>5.0</v>
       </c>
       <c r="X143" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y143" s="7" t="s">
         <v>141</v>
@@ -9575,7 +9575,7 @@
         <v>10.0</v>
       </c>
       <c r="X148" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Y148" s="7" t="s">
         <v>145</v>
@@ -9615,7 +9615,7 @@
         <v>11.0</v>
       </c>
       <c r="X149" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Y149" s="7" t="s">
         <v>143</v>
@@ -9655,7 +9655,7 @@
         <v>12.0</v>
       </c>
       <c r="X150" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Y150" s="7" t="s">
         <v>146</v>
@@ -9815,7 +9815,7 @@
         <v>16.0</v>
       </c>
       <c r="X154" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Y154" s="7" t="s">
         <v>143</v>
@@ -9855,7 +9855,7 @@
         <v>17.0</v>
       </c>
       <c r="X155" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Y155" s="7" t="s">
         <v>140</v>
@@ -9895,7 +9895,7 @@
         <v>18.0</v>
       </c>
       <c r="X156" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Y156" s="7" t="s">
         <v>145</v>
@@ -10095,7 +10095,7 @@
         <v>23.0</v>
       </c>
       <c r="X161" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Y161" s="7" t="s">
         <v>142</v>
@@ -10335,7 +10335,7 @@
         <v>29.0</v>
       </c>
       <c r="X167" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Y167" s="7" t="s">
         <v>143</v>
@@ -10375,7 +10375,7 @@
         <v>30.0</v>
       </c>
       <c r="X168" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Y168" s="7" t="s">
         <v>141</v>
@@ -10695,7 +10695,7 @@
         <v>38.0</v>
       </c>
       <c r="X176" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y176" s="7" t="s">
         <v>141</v>
@@ -10935,7 +10935,7 @@
         <v>44.0</v>
       </c>
       <c r="X182" s="7" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="Y182" s="7" t="s">
         <v>142</v>
@@ -37443,20 +37443,20 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>7</v>
@@ -37467,15 +37467,15 @@
       <c r="H1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>13</v>
+      <c r="I1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>1.0</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -37484,8 +37484,8 @@
       <c r="C2" s="9">
         <v>139.0</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="b">
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F2" s="9">
@@ -37522,15 +37522,15 @@
 </f>
         <v/>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="1">
         <v>1200.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>2.0</v>
       </c>
       <c r="B3" s="7" t="s">
@@ -37539,8 +37539,8 @@
       <c r="C3" s="9">
         <v>106.5</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="b">
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F3" s="9">
@@ -37564,15 +37564,15 @@
 </f>
         <v/>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="1">
         <v>12.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>3.0</v>
       </c>
       <c r="B4" s="7" t="s">
@@ -37581,8 +37581,8 @@
       <c r="C4" s="9">
         <v>93.0</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="b">
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F4" s="9">
@@ -37601,7 +37601,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>25</v>
       </c>
       <c r="L4" s="4">
@@ -37610,7 +37610,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>4.0</v>
       </c>
       <c r="B5" s="7" t="s">
@@ -37638,7 +37638,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L5" s="17">
@@ -37648,11 +37648,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>5.0</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" s="9">
         <v>76.0</v>
@@ -37676,8 +37676,8 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>30</v>
+      <c r="K6" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="L6" s="17">
         <f>L2-L5
@@ -37686,7 +37686,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>6.0</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -37714,7 +37714,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" s="1" t="s">
         <v>32</v>
       </c>
       <c r="L7" s="17">
@@ -37723,7 +37723,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>7.0</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -37751,7 +37751,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="1" t="s">
         <v>34</v>
       </c>
       <c r="L8" s="9">
@@ -37761,7 +37761,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>8.0</v>
       </c>
       <c r="B9" s="7" t="s">
@@ -37789,7 +37789,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L9" s="9">
@@ -37799,7 +37799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>9.0</v>
       </c>
       <c r="B10" s="7" t="s">
@@ -37827,7 +37827,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" s="1" t="s">
         <v>38</v>
       </c>
       <c r="L10" s="9">
@@ -37836,7 +37836,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>10.0</v>
       </c>
       <c r="B11" s="7" t="s">
@@ -37864,8 +37864,8 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>41</v>
+      <c r="K11" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="L11" s="19">
         <f>IF(L10&gt;0,L8/L10,1)</f>
@@ -37873,11 +37873,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>11.0</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="9">
         <v>39.0</v>
@@ -37903,7 +37903,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>12.0</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -37931,7 +37931,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="K13" s="1" t="s">
         <v>44</v>
       </c>
       <c r="L13" s="17">
@@ -37940,11 +37940,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>13.0</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" s="9">
         <v>30.5</v>
@@ -37968,8 +37968,8 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>47</v>
+      <c r="K14" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="L14" s="19">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -37977,11 +37977,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>14.0</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" s="9">
         <v>27.5</v>
@@ -38007,7 +38007,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2">
+      <c r="A16" s="1">
         <v>15.0</v>
       </c>
       <c r="B16" s="7" t="s">
@@ -38035,10 +38035,10 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="K16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16" s="1">
         <f>IF($L$18&lt;0.3,
      IF($L$11&gt;=1.3,0.09,
         IF($L$11&gt;=1.1,0.07,0.05)),
@@ -38054,11 +38054,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>16.0</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C17" s="9">
         <v>22.5</v>
@@ -38084,11 +38084,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2">
+      <c r="A18" s="1">
         <v>17.0</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C18" s="9">
         <v>20.0</v>
@@ -38112,8 +38112,8 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K18" s="2" t="s">
-        <v>55</v>
+      <c r="K18" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="L18" s="20">
         <f>L5/L2</f>
@@ -38121,11 +38121,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2">
+      <c r="A19" s="1">
         <v>18.0</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C19" s="9">
         <v>18.5</v>
@@ -38151,11 +38151,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2">
+      <c r="A20" s="1">
         <v>19.0</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C20" s="9">
         <v>16.5</v>
@@ -38181,11 +38181,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2">
+      <c r="A21" s="1">
         <v>20.0</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C21" s="9">
         <v>14.5</v>
@@ -38211,11 +38211,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2">
+      <c r="A22" s="1">
         <v>21.0</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C22" s="9">
         <v>13.5</v>
@@ -38241,11 +38241,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2">
+      <c r="A23" s="1">
         <v>22.0</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C23" s="9">
         <v>12.0</v>
@@ -38271,11 +38271,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2">
+      <c r="A24" s="1">
         <v>23.0</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C24" s="9">
         <v>11.0</v>
@@ -38301,11 +38301,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2">
+      <c r="A25" s="1">
         <v>24.0</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C25" s="9">
         <v>10.0</v>
@@ -38331,7 +38331,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2">
+      <c r="A26" s="1">
         <v>25.0</v>
       </c>
       <c r="B26" s="7" t="s">
@@ -38361,7 +38361,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2">
+      <c r="A27" s="1">
         <v>26.0</v>
       </c>
       <c r="B27" s="7" t="s">
@@ -38389,15 +38389,15 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K27" s="2" t="s">
+      <c r="K27" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="L27" s="2">
+      <c r="L27" s="1">
         <v>0.8</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2">
+      <c r="A28" s="1">
         <v>27.0</v>
       </c>
       <c r="B28" s="7" t="s">
@@ -38427,7 +38427,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2">
+      <c r="A29" s="1">
         <v>28.0</v>
       </c>
       <c r="B29" s="7" t="s">
@@ -38457,7 +38457,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2">
+      <c r="A30" s="1">
         <v>29.0</v>
       </c>
       <c r="B30" s="7" t="s">
@@ -38487,7 +38487,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2">
+      <c r="A31" s="1">
         <v>30.0</v>
       </c>
       <c r="B31" s="7" t="s">
@@ -38517,7 +38517,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2">
+      <c r="A32" s="1">
         <v>31.0</v>
       </c>
       <c r="B32" s="7" t="s">
@@ -38547,7 +38547,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2">
+      <c r="A33" s="1">
         <v>32.0</v>
       </c>
       <c r="B33" s="7" t="s">
@@ -38577,7 +38577,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2">
+      <c r="A34" s="1">
         <v>33.0</v>
       </c>
       <c r="B34" s="7" t="s">
@@ -38607,7 +38607,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2">
+      <c r="A35" s="1">
         <v>34.0</v>
       </c>
       <c r="B35" s="7" t="s">
@@ -38637,7 +38637,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2">
+      <c r="A36" s="1">
         <v>35.0</v>
       </c>
       <c r="B36" s="7" t="s">
@@ -38667,7 +38667,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2">
+      <c r="A37" s="1">
         <v>36.0</v>
       </c>
       <c r="B37" s="7" t="s">
@@ -38697,7 +38697,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2">
+      <c r="A38" s="1">
         <v>37.0</v>
       </c>
       <c r="B38" s="7" t="s">
@@ -38727,7 +38727,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2">
+      <c r="A39" s="1">
         <v>38.0</v>
       </c>
       <c r="B39" s="7" t="s">
@@ -38757,7 +38757,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2">
+      <c r="A40" s="1">
         <v>39.0</v>
       </c>
       <c r="B40" s="7" t="s">
@@ -38787,7 +38787,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2">
+      <c r="A41" s="1">
         <v>40.0</v>
       </c>
       <c r="B41" s="7" t="s">
@@ -38817,7 +38817,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2">
+      <c r="A42" s="1">
         <v>41.0</v>
       </c>
       <c r="B42" s="7" t="s">
@@ -38847,7 +38847,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2">
+      <c r="A43" s="1">
         <v>42.0</v>
       </c>
       <c r="B43" s="7" t="s">
@@ -38877,7 +38877,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2">
+      <c r="A44" s="1">
         <v>43.0</v>
       </c>
       <c r="B44" s="7" t="s">
@@ -38907,7 +38907,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2">
+      <c r="A45" s="1">
         <v>44.0</v>
       </c>
       <c r="B45" s="7" t="s">
@@ -38937,7 +38937,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2">
+      <c r="A46" s="1">
         <v>45.0</v>
       </c>
       <c r="B46" s="7" t="s">
@@ -38967,7 +38967,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2">
+      <c r="A47" s="1">
         <v>46.0</v>
       </c>
       <c r="B47" s="7" t="s">
@@ -38997,7 +38997,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2">
+      <c r="A48" s="1">
         <v>47.0</v>
       </c>
       <c r="B48" s="7" t="s">
@@ -39027,7 +39027,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2">
+      <c r="A49" s="1">
         <v>48.0</v>
       </c>
       <c r="B49" s="7" t="s">
@@ -39057,7 +39057,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2">
+      <c r="A50" s="1">
         <v>49.0</v>
       </c>
       <c r="B50" s="7" t="s">
@@ -39087,7 +39087,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2">
+      <c r="A51" s="1">
         <v>50.0</v>
       </c>
       <c r="B51" s="7" t="s">
@@ -39117,7 +39117,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2">
+      <c r="A52" s="1">
         <v>51.0</v>
       </c>
       <c r="B52" s="7" t="s">
@@ -39147,7 +39147,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2">
+      <c r="A53" s="1">
         <v>52.0</v>
       </c>
       <c r="B53" s="7" t="s">
@@ -39177,7 +39177,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2">
+      <c r="A54" s="1">
         <v>53.0</v>
       </c>
       <c r="B54" s="7" t="s">
@@ -39207,7 +39207,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2">
+      <c r="A55" s="1">
         <v>54.0</v>
       </c>
       <c r="B55" s="7" t="s">
@@ -39237,7 +39237,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2">
+      <c r="A56" s="1">
         <v>55.0</v>
       </c>
       <c r="B56" s="7" t="s">
@@ -39267,7 +39267,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2">
+      <c r="A57" s="1">
         <v>56.0</v>
       </c>
       <c r="B57" s="7" t="s">
@@ -39297,7 +39297,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2">
+      <c r="A58" s="1">
         <v>57.0</v>
       </c>
       <c r="B58" s="7" t="s">
@@ -39327,7 +39327,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2">
+      <c r="A59" s="1">
         <v>58.0</v>
       </c>
       <c r="B59" s="7" t="s">
@@ -39357,7 +39357,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2">
+      <c r="A60" s="1">
         <v>59.0</v>
       </c>
       <c r="B60" s="7" t="s">
@@ -39387,7 +39387,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2">
+      <c r="A61" s="1">
         <v>60.0</v>
       </c>
       <c r="B61" s="7" t="s">
@@ -39417,7 +39417,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2">
+      <c r="A62" s="1">
         <v>61.0</v>
       </c>
       <c r="B62" s="7" t="s">
@@ -39447,7 +39447,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2">
+      <c r="A63" s="1">
         <v>62.0</v>
       </c>
       <c r="B63" s="7" t="s">
@@ -39477,7 +39477,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2">
+      <c r="A64" s="1">
         <v>63.0</v>
       </c>
       <c r="B64" s="7" t="s">
@@ -39507,7 +39507,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2">
+      <c r="A65" s="1">
         <v>64.0</v>
       </c>
       <c r="B65" s="7" t="s">
@@ -39537,7 +39537,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2">
+      <c r="A66" s="1">
         <v>65.0</v>
       </c>
       <c r="B66" s="7" t="s">
@@ -39567,7 +39567,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2">
+      <c r="A67" s="1">
         <v>66.0</v>
       </c>
       <c r="B67" s="7" t="s">
@@ -39597,7 +39597,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2">
+      <c r="A68" s="1">
         <v>67.0</v>
       </c>
       <c r="B68" s="7" t="s">
@@ -39627,11 +39627,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2">
+      <c r="A69" s="1">
         <v>68.0</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C69" s="9">
         <v>1.0</v>
@@ -39657,11 +39657,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2">
+      <c r="A70" s="1">
         <v>69.0</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C70" s="9">
         <v>1.0</v>
@@ -39687,11 +39687,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2">
+      <c r="A71" s="1">
         <v>70.0</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C71" s="9">
         <v>1.0</v>
@@ -39717,11 +39717,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2">
+      <c r="A72" s="1">
         <v>71.0</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C72" s="9">
         <v>1.0</v>
@@ -39747,11 +39747,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2">
+      <c r="A73" s="1">
         <v>72.0</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>122</v>
+      <c r="B73" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="C73" s="9">
         <v>1.0</v>
@@ -39783,6496 +39783,6496 @@
       <c r="F74" s="9"/>
       <c r="G74" s="9"/>
       <c r="H74" s="14"/>
-      <c r="I74" s="22"/>
+      <c r="I74" s="21"/>
     </row>
     <row r="75">
-      <c r="C75" s="23"/>
+      <c r="C75" s="22"/>
       <c r="F75" s="9"/>
       <c r="G75" s="9"/>
       <c r="H75" s="14"/>
-      <c r="I75" s="22"/>
+      <c r="I75" s="21"/>
     </row>
     <row r="76">
-      <c r="C76" s="23"/>
+      <c r="C76" s="22"/>
       <c r="F76" s="9"/>
       <c r="G76" s="9"/>
       <c r="H76" s="14"/>
-      <c r="I76" s="22"/>
+      <c r="I76" s="21"/>
     </row>
     <row r="77">
-      <c r="C77" s="23"/>
+      <c r="C77" s="22"/>
       <c r="F77" s="9"/>
       <c r="G77" s="9"/>
       <c r="H77" s="14"/>
-      <c r="I77" s="22"/>
+      <c r="I77" s="21"/>
     </row>
     <row r="78">
-      <c r="C78" s="23"/>
+      <c r="C78" s="22"/>
       <c r="F78" s="9"/>
       <c r="G78" s="9"/>
       <c r="H78" s="14"/>
-      <c r="I78" s="22"/>
+      <c r="I78" s="21"/>
     </row>
     <row r="79">
-      <c r="C79" s="23"/>
+      <c r="C79" s="22"/>
       <c r="F79" s="9"/>
       <c r="G79" s="9"/>
       <c r="H79" s="14"/>
-      <c r="I79" s="22"/>
+      <c r="I79" s="21"/>
     </row>
     <row r="80">
-      <c r="C80" s="23"/>
+      <c r="C80" s="22"/>
       <c r="F80" s="9"/>
       <c r="G80" s="9"/>
       <c r="H80" s="14"/>
-      <c r="I80" s="22"/>
+      <c r="I80" s="21"/>
     </row>
     <row r="81">
-      <c r="C81" s="23"/>
+      <c r="C81" s="22"/>
       <c r="F81" s="9"/>
       <c r="G81" s="9"/>
       <c r="H81" s="14"/>
-      <c r="I81" s="22"/>
+      <c r="I81" s="21"/>
     </row>
     <row r="82">
-      <c r="C82" s="23"/>
+      <c r="C82" s="22"/>
       <c r="F82" s="9"/>
       <c r="G82" s="9"/>
       <c r="H82" s="14"/>
-      <c r="I82" s="22"/>
+      <c r="I82" s="21"/>
     </row>
     <row r="83">
-      <c r="C83" s="23"/>
+      <c r="C83" s="22"/>
       <c r="F83" s="9"/>
       <c r="G83" s="9"/>
       <c r="H83" s="14"/>
-      <c r="I83" s="22"/>
+      <c r="I83" s="21"/>
     </row>
     <row r="84">
-      <c r="C84" s="23"/>
+      <c r="C84" s="22"/>
       <c r="F84" s="9"/>
       <c r="G84" s="9"/>
       <c r="H84" s="14"/>
-      <c r="I84" s="22"/>
+      <c r="I84" s="21"/>
     </row>
     <row r="85">
-      <c r="C85" s="23"/>
+      <c r="C85" s="22"/>
       <c r="F85" s="9"/>
       <c r="G85" s="9"/>
       <c r="H85" s="14"/>
-      <c r="I85" s="22"/>
+      <c r="I85" s="21"/>
     </row>
     <row r="86">
-      <c r="C86" s="23"/>
+      <c r="C86" s="22"/>
       <c r="F86" s="9"/>
       <c r="G86" s="9"/>
       <c r="H86" s="14"/>
-      <c r="I86" s="22"/>
+      <c r="I86" s="21"/>
     </row>
     <row r="87">
-      <c r="C87" s="23"/>
+      <c r="C87" s="22"/>
       <c r="F87" s="9"/>
       <c r="G87" s="9"/>
       <c r="H87" s="14"/>
-      <c r="I87" s="22"/>
+      <c r="I87" s="21"/>
     </row>
     <row r="88">
-      <c r="C88" s="23"/>
+      <c r="C88" s="22"/>
       <c r="F88" s="9"/>
       <c r="G88" s="9"/>
       <c r="H88" s="14"/>
-      <c r="I88" s="22"/>
+      <c r="I88" s="21"/>
     </row>
     <row r="89">
-      <c r="C89" s="23"/>
+      <c r="C89" s="22"/>
       <c r="F89" s="9"/>
       <c r="G89" s="9"/>
       <c r="H89" s="14"/>
-      <c r="I89" s="22"/>
+      <c r="I89" s="21"/>
     </row>
     <row r="90">
-      <c r="C90" s="23"/>
+      <c r="C90" s="22"/>
       <c r="F90" s="9"/>
       <c r="G90" s="9"/>
       <c r="H90" s="14"/>
-      <c r="I90" s="22"/>
+      <c r="I90" s="21"/>
     </row>
     <row r="91">
-      <c r="C91" s="23"/>
+      <c r="C91" s="22"/>
       <c r="F91" s="9"/>
       <c r="G91" s="9"/>
       <c r="H91" s="14"/>
-      <c r="I91" s="22"/>
+      <c r="I91" s="21"/>
     </row>
     <row r="92">
-      <c r="C92" s="23"/>
+      <c r="C92" s="22"/>
       <c r="F92" s="9"/>
       <c r="G92" s="9"/>
       <c r="H92" s="14"/>
-      <c r="I92" s="22"/>
+      <c r="I92" s="21"/>
     </row>
     <row r="93">
-      <c r="C93" s="23"/>
+      <c r="C93" s="22"/>
       <c r="F93" s="9"/>
       <c r="G93" s="9"/>
       <c r="H93" s="14"/>
-      <c r="I93" s="22"/>
+      <c r="I93" s="21"/>
     </row>
     <row r="94">
-      <c r="C94" s="23"/>
+      <c r="C94" s="22"/>
       <c r="F94" s="9"/>
       <c r="G94" s="9"/>
       <c r="H94" s="14"/>
-      <c r="I94" s="22"/>
+      <c r="I94" s="21"/>
     </row>
     <row r="95">
-      <c r="C95" s="23"/>
+      <c r="C95" s="22"/>
       <c r="F95" s="9"/>
       <c r="G95" s="9"/>
       <c r="H95" s="14"/>
-      <c r="I95" s="22"/>
+      <c r="I95" s="21"/>
     </row>
     <row r="96">
-      <c r="C96" s="23"/>
+      <c r="C96" s="22"/>
       <c r="F96" s="9"/>
       <c r="G96" s="9"/>
       <c r="H96" s="14"/>
-      <c r="I96" s="22"/>
+      <c r="I96" s="21"/>
     </row>
     <row r="97">
-      <c r="C97" s="23"/>
+      <c r="C97" s="22"/>
       <c r="F97" s="9"/>
       <c r="G97" s="9"/>
       <c r="H97" s="14"/>
-      <c r="I97" s="22"/>
+      <c r="I97" s="21"/>
     </row>
     <row r="98">
-      <c r="C98" s="23"/>
+      <c r="C98" s="22"/>
       <c r="F98" s="9"/>
       <c r="G98" s="9"/>
       <c r="H98" s="14"/>
-      <c r="I98" s="22"/>
+      <c r="I98" s="21"/>
     </row>
     <row r="99">
-      <c r="C99" s="23"/>
+      <c r="C99" s="22"/>
       <c r="F99" s="9"/>
       <c r="G99" s="9"/>
       <c r="H99" s="14"/>
-      <c r="I99" s="22"/>
+      <c r="I99" s="21"/>
     </row>
     <row r="100">
-      <c r="C100" s="23"/>
+      <c r="C100" s="22"/>
       <c r="F100" s="9"/>
       <c r="G100" s="9"/>
       <c r="H100" s="14"/>
-      <c r="I100" s="22"/>
+      <c r="I100" s="21"/>
     </row>
     <row r="101">
-      <c r="C101" s="23"/>
+      <c r="C101" s="22"/>
       <c r="F101" s="9"/>
       <c r="G101" s="9"/>
       <c r="H101" s="14"/>
-      <c r="I101" s="22"/>
+      <c r="I101" s="21"/>
     </row>
     <row r="102">
-      <c r="C102" s="23"/>
+      <c r="C102" s="22"/>
       <c r="F102" s="9"/>
       <c r="G102" s="9"/>
       <c r="H102" s="14"/>
-      <c r="I102" s="22"/>
+      <c r="I102" s="21"/>
     </row>
     <row r="103">
-      <c r="C103" s="23"/>
+      <c r="C103" s="22"/>
       <c r="F103" s="9"/>
       <c r="G103" s="9"/>
       <c r="H103" s="14"/>
-      <c r="I103" s="22"/>
+      <c r="I103" s="21"/>
     </row>
     <row r="104">
-      <c r="C104" s="23"/>
+      <c r="C104" s="22"/>
       <c r="F104" s="9"/>
       <c r="G104" s="9"/>
       <c r="H104" s="14"/>
-      <c r="I104" s="22"/>
+      <c r="I104" s="21"/>
     </row>
     <row r="105">
-      <c r="C105" s="23"/>
+      <c r="C105" s="22"/>
       <c r="F105" s="9"/>
       <c r="G105" s="9"/>
       <c r="H105" s="14"/>
-      <c r="I105" s="22"/>
+      <c r="I105" s="21"/>
     </row>
     <row r="106">
-      <c r="C106" s="23"/>
+      <c r="C106" s="22"/>
       <c r="F106" s="9"/>
       <c r="G106" s="9"/>
       <c r="H106" s="14"/>
-      <c r="I106" s="22"/>
+      <c r="I106" s="21"/>
     </row>
     <row r="107">
-      <c r="C107" s="23"/>
+      <c r="C107" s="22"/>
       <c r="F107" s="9"/>
       <c r="G107" s="9"/>
       <c r="H107" s="14"/>
-      <c r="I107" s="22"/>
+      <c r="I107" s="21"/>
     </row>
     <row r="108">
-      <c r="C108" s="23"/>
+      <c r="C108" s="22"/>
       <c r="F108" s="9"/>
       <c r="G108" s="9"/>
       <c r="H108" s="14"/>
-      <c r="I108" s="22"/>
+      <c r="I108" s="21"/>
     </row>
     <row r="109">
-      <c r="C109" s="23"/>
+      <c r="C109" s="22"/>
       <c r="F109" s="9"/>
       <c r="G109" s="9"/>
       <c r="H109" s="14"/>
-      <c r="I109" s="22"/>
+      <c r="I109" s="21"/>
     </row>
     <row r="110">
-      <c r="C110" s="23"/>
+      <c r="C110" s="22"/>
       <c r="F110" s="9"/>
       <c r="G110" s="9"/>
       <c r="H110" s="14"/>
-      <c r="I110" s="22"/>
+      <c r="I110" s="21"/>
     </row>
     <row r="111">
-      <c r="C111" s="23"/>
+      <c r="C111" s="22"/>
       <c r="F111" s="9"/>
       <c r="G111" s="9"/>
       <c r="H111" s="14"/>
-      <c r="I111" s="22"/>
+      <c r="I111" s="21"/>
     </row>
     <row r="112">
-      <c r="C112" s="23"/>
+      <c r="C112" s="22"/>
       <c r="F112" s="9"/>
       <c r="G112" s="9"/>
       <c r="H112" s="14"/>
-      <c r="I112" s="22"/>
+      <c r="I112" s="21"/>
     </row>
     <row r="113">
-      <c r="C113" s="23"/>
+      <c r="C113" s="22"/>
       <c r="F113" s="9"/>
       <c r="G113" s="9"/>
       <c r="H113" s="14"/>
-      <c r="I113" s="22"/>
+      <c r="I113" s="21"/>
     </row>
     <row r="114">
-      <c r="C114" s="23"/>
+      <c r="C114" s="22"/>
       <c r="F114" s="9"/>
       <c r="G114" s="9"/>
       <c r="H114" s="14"/>
-      <c r="I114" s="22"/>
+      <c r="I114" s="21"/>
     </row>
     <row r="115">
-      <c r="C115" s="23"/>
+      <c r="C115" s="22"/>
       <c r="F115" s="9"/>
       <c r="G115" s="9"/>
       <c r="H115" s="14"/>
-      <c r="I115" s="22"/>
+      <c r="I115" s="21"/>
     </row>
     <row r="116">
-      <c r="C116" s="23"/>
+      <c r="C116" s="22"/>
       <c r="F116" s="9"/>
       <c r="G116" s="9"/>
       <c r="H116" s="14"/>
-      <c r="I116" s="22"/>
+      <c r="I116" s="21"/>
     </row>
     <row r="117">
-      <c r="C117" s="23"/>
+      <c r="C117" s="22"/>
       <c r="F117" s="9"/>
       <c r="G117" s="9"/>
       <c r="H117" s="14"/>
-      <c r="I117" s="22"/>
+      <c r="I117" s="21"/>
     </row>
     <row r="118">
-      <c r="C118" s="23"/>
+      <c r="C118" s="22"/>
       <c r="F118" s="9"/>
       <c r="G118" s="9"/>
       <c r="H118" s="14"/>
-      <c r="I118" s="22"/>
+      <c r="I118" s="21"/>
     </row>
     <row r="119">
-      <c r="C119" s="23"/>
+      <c r="C119" s="22"/>
       <c r="F119" s="9"/>
       <c r="G119" s="9"/>
       <c r="H119" s="14"/>
-      <c r="I119" s="22"/>
+      <c r="I119" s="21"/>
     </row>
     <row r="120">
-      <c r="C120" s="23"/>
+      <c r="C120" s="22"/>
       <c r="F120" s="9"/>
       <c r="G120" s="9"/>
       <c r="H120" s="14"/>
-      <c r="I120" s="22"/>
+      <c r="I120" s="21"/>
     </row>
     <row r="121">
-      <c r="C121" s="23"/>
+      <c r="C121" s="22"/>
       <c r="F121" s="9"/>
       <c r="G121" s="9"/>
       <c r="H121" s="14"/>
-      <c r="I121" s="22"/>
+      <c r="I121" s="21"/>
     </row>
     <row r="122">
-      <c r="C122" s="23"/>
+      <c r="C122" s="22"/>
       <c r="F122" s="9"/>
       <c r="G122" s="9"/>
       <c r="H122" s="14"/>
-      <c r="I122" s="22"/>
+      <c r="I122" s="21"/>
     </row>
     <row r="123">
-      <c r="C123" s="23"/>
+      <c r="C123" s="22"/>
       <c r="F123" s="9"/>
       <c r="G123" s="9"/>
       <c r="H123" s="14"/>
-      <c r="I123" s="22"/>
+      <c r="I123" s="21"/>
     </row>
     <row r="124">
-      <c r="C124" s="23"/>
+      <c r="C124" s="22"/>
       <c r="F124" s="9"/>
       <c r="G124" s="9"/>
       <c r="H124" s="14"/>
-      <c r="I124" s="22"/>
+      <c r="I124" s="21"/>
     </row>
     <row r="125">
-      <c r="C125" s="23"/>
+      <c r="C125" s="22"/>
       <c r="F125" s="9"/>
       <c r="G125" s="9"/>
       <c r="H125" s="14"/>
-      <c r="I125" s="22"/>
+      <c r="I125" s="21"/>
     </row>
     <row r="126">
-      <c r="C126" s="23"/>
+      <c r="C126" s="22"/>
       <c r="F126" s="9"/>
       <c r="G126" s="9"/>
       <c r="H126" s="14"/>
-      <c r="I126" s="22"/>
+      <c r="I126" s="21"/>
     </row>
     <row r="127">
-      <c r="C127" s="23"/>
+      <c r="C127" s="22"/>
       <c r="F127" s="9"/>
       <c r="G127" s="9"/>
       <c r="H127" s="14"/>
-      <c r="I127" s="22"/>
+      <c r="I127" s="21"/>
     </row>
     <row r="128">
-      <c r="C128" s="23"/>
+      <c r="C128" s="22"/>
       <c r="F128" s="9"/>
       <c r="G128" s="9"/>
       <c r="H128" s="14"/>
-      <c r="I128" s="22"/>
+      <c r="I128" s="21"/>
     </row>
     <row r="129">
-      <c r="C129" s="23"/>
+      <c r="C129" s="22"/>
       <c r="F129" s="9"/>
       <c r="G129" s="9"/>
       <c r="H129" s="14"/>
-      <c r="I129" s="22"/>
+      <c r="I129" s="21"/>
     </row>
     <row r="130">
-      <c r="C130" s="23"/>
+      <c r="C130" s="22"/>
       <c r="F130" s="9"/>
       <c r="G130" s="9"/>
       <c r="H130" s="14"/>
-      <c r="I130" s="22"/>
+      <c r="I130" s="21"/>
     </row>
     <row r="131">
-      <c r="C131" s="23"/>
+      <c r="C131" s="22"/>
       <c r="F131" s="9"/>
       <c r="G131" s="9"/>
       <c r="H131" s="14"/>
-      <c r="I131" s="22"/>
+      <c r="I131" s="21"/>
     </row>
     <row r="132">
-      <c r="C132" s="23"/>
+      <c r="C132" s="22"/>
       <c r="F132" s="9"/>
       <c r="G132" s="9"/>
       <c r="H132" s="14"/>
-      <c r="I132" s="22"/>
+      <c r="I132" s="21"/>
     </row>
     <row r="133">
-      <c r="C133" s="23"/>
+      <c r="C133" s="22"/>
       <c r="F133" s="9"/>
       <c r="G133" s="9"/>
       <c r="H133" s="14"/>
-      <c r="I133" s="22"/>
+      <c r="I133" s="21"/>
     </row>
     <row r="134">
-      <c r="C134" s="23"/>
+      <c r="C134" s="22"/>
       <c r="F134" s="9"/>
       <c r="G134" s="9"/>
       <c r="H134" s="14"/>
-      <c r="I134" s="22"/>
+      <c r="I134" s="21"/>
     </row>
     <row r="135">
-      <c r="C135" s="23"/>
+      <c r="C135" s="22"/>
       <c r="F135" s="9"/>
       <c r="G135" s="9"/>
       <c r="H135" s="14"/>
-      <c r="I135" s="22"/>
+      <c r="I135" s="21"/>
     </row>
     <row r="136">
-      <c r="C136" s="23"/>
+      <c r="C136" s="22"/>
       <c r="F136" s="9"/>
       <c r="G136" s="9"/>
       <c r="H136" s="14"/>
-      <c r="I136" s="22"/>
+      <c r="I136" s="21"/>
     </row>
     <row r="137">
-      <c r="C137" s="23"/>
+      <c r="C137" s="22"/>
       <c r="F137" s="9"/>
       <c r="G137" s="9"/>
       <c r="H137" s="14"/>
-      <c r="I137" s="22"/>
+      <c r="I137" s="21"/>
     </row>
     <row r="138">
-      <c r="C138" s="23"/>
+      <c r="C138" s="22"/>
       <c r="F138" s="9"/>
       <c r="G138" s="9"/>
       <c r="H138" s="14"/>
-      <c r="I138" s="22"/>
+      <c r="I138" s="21"/>
     </row>
     <row r="139">
-      <c r="C139" s="23"/>
+      <c r="C139" s="22"/>
       <c r="F139" s="9"/>
       <c r="G139" s="9"/>
       <c r="H139" s="14"/>
-      <c r="I139" s="22"/>
+      <c r="I139" s="21"/>
     </row>
     <row r="140">
-      <c r="C140" s="23"/>
+      <c r="C140" s="22"/>
       <c r="F140" s="9"/>
       <c r="G140" s="9"/>
       <c r="H140" s="14"/>
-      <c r="I140" s="22"/>
+      <c r="I140" s="21"/>
     </row>
     <row r="141">
-      <c r="C141" s="23"/>
+      <c r="C141" s="22"/>
       <c r="F141" s="9"/>
       <c r="G141" s="9"/>
       <c r="H141" s="14"/>
-      <c r="I141" s="22"/>
+      <c r="I141" s="21"/>
     </row>
     <row r="142">
-      <c r="C142" s="23"/>
+      <c r="C142" s="22"/>
       <c r="F142" s="9"/>
       <c r="G142" s="9"/>
       <c r="H142" s="14"/>
-      <c r="I142" s="22"/>
+      <c r="I142" s="21"/>
     </row>
     <row r="143">
-      <c r="C143" s="23"/>
+      <c r="C143" s="22"/>
       <c r="F143" s="9"/>
       <c r="G143" s="9"/>
       <c r="H143" s="14"/>
-      <c r="I143" s="22"/>
+      <c r="I143" s="21"/>
     </row>
     <row r="144">
-      <c r="C144" s="23"/>
+      <c r="C144" s="22"/>
       <c r="F144" s="9"/>
       <c r="G144" s="9"/>
       <c r="H144" s="14"/>
-      <c r="I144" s="22"/>
+      <c r="I144" s="21"/>
     </row>
     <row r="145">
-      <c r="C145" s="23"/>
+      <c r="C145" s="22"/>
       <c r="F145" s="9"/>
       <c r="G145" s="9"/>
       <c r="H145" s="14"/>
-      <c r="I145" s="22"/>
+      <c r="I145" s="21"/>
     </row>
     <row r="146">
-      <c r="C146" s="23"/>
+      <c r="C146" s="22"/>
       <c r="F146" s="9"/>
       <c r="G146" s="9"/>
       <c r="H146" s="14"/>
-      <c r="I146" s="22"/>
+      <c r="I146" s="21"/>
     </row>
     <row r="147">
-      <c r="C147" s="23"/>
+      <c r="C147" s="22"/>
       <c r="F147" s="9"/>
       <c r="G147" s="9"/>
       <c r="H147" s="14"/>
-      <c r="I147" s="22"/>
+      <c r="I147" s="21"/>
     </row>
     <row r="148">
-      <c r="C148" s="23"/>
+      <c r="C148" s="22"/>
       <c r="F148" s="9"/>
       <c r="G148" s="9"/>
       <c r="H148" s="14"/>
-      <c r="I148" s="22"/>
+      <c r="I148" s="21"/>
     </row>
     <row r="149">
-      <c r="C149" s="23"/>
+      <c r="C149" s="22"/>
       <c r="F149" s="9"/>
       <c r="G149" s="9"/>
       <c r="H149" s="14"/>
-      <c r="I149" s="22"/>
+      <c r="I149" s="21"/>
     </row>
     <row r="150">
-      <c r="C150" s="23"/>
+      <c r="C150" s="22"/>
       <c r="F150" s="9"/>
       <c r="G150" s="9"/>
       <c r="H150" s="14"/>
-      <c r="I150" s="22"/>
+      <c r="I150" s="21"/>
     </row>
     <row r="151">
-      <c r="C151" s="23"/>
+      <c r="C151" s="22"/>
       <c r="F151" s="9"/>
       <c r="G151" s="9"/>
       <c r="H151" s="14"/>
-      <c r="I151" s="22"/>
+      <c r="I151" s="21"/>
     </row>
     <row r="152">
-      <c r="C152" s="23"/>
+      <c r="C152" s="22"/>
       <c r="F152" s="9"/>
       <c r="G152" s="9"/>
       <c r="H152" s="14"/>
-      <c r="I152" s="22"/>
+      <c r="I152" s="21"/>
     </row>
     <row r="153">
-      <c r="C153" s="23"/>
+      <c r="C153" s="22"/>
       <c r="F153" s="9"/>
       <c r="G153" s="9"/>
       <c r="H153" s="14"/>
-      <c r="I153" s="22"/>
+      <c r="I153" s="21"/>
     </row>
     <row r="154">
-      <c r="C154" s="23"/>
+      <c r="C154" s="22"/>
       <c r="F154" s="9"/>
       <c r="G154" s="9"/>
       <c r="H154" s="14"/>
-      <c r="I154" s="22"/>
+      <c r="I154" s="21"/>
     </row>
     <row r="155">
-      <c r="C155" s="23"/>
+      <c r="C155" s="22"/>
       <c r="F155" s="9"/>
       <c r="G155" s="9"/>
       <c r="H155" s="14"/>
-      <c r="I155" s="22"/>
+      <c r="I155" s="21"/>
     </row>
     <row r="156">
-      <c r="C156" s="23"/>
+      <c r="C156" s="22"/>
       <c r="F156" s="9"/>
       <c r="G156" s="9"/>
       <c r="H156" s="14"/>
-      <c r="I156" s="22"/>
+      <c r="I156" s="21"/>
     </row>
     <row r="157">
-      <c r="C157" s="23"/>
+      <c r="C157" s="22"/>
       <c r="F157" s="9"/>
       <c r="G157" s="9"/>
       <c r="H157" s="14"/>
-      <c r="I157" s="22"/>
+      <c r="I157" s="21"/>
     </row>
     <row r="158">
-      <c r="C158" s="23"/>
+      <c r="C158" s="22"/>
       <c r="F158" s="9"/>
       <c r="G158" s="9"/>
       <c r="H158" s="14"/>
-      <c r="I158" s="22"/>
+      <c r="I158" s="21"/>
     </row>
     <row r="159">
-      <c r="C159" s="23"/>
+      <c r="C159" s="22"/>
       <c r="F159" s="9"/>
       <c r="G159" s="9"/>
       <c r="H159" s="14"/>
-      <c r="I159" s="22"/>
+      <c r="I159" s="21"/>
     </row>
     <row r="160">
-      <c r="C160" s="23"/>
+      <c r="C160" s="22"/>
       <c r="F160" s="9"/>
       <c r="G160" s="9"/>
       <c r="H160" s="14"/>
-      <c r="I160" s="22"/>
+      <c r="I160" s="21"/>
     </row>
     <row r="161">
-      <c r="C161" s="23"/>
+      <c r="C161" s="22"/>
       <c r="F161" s="9"/>
       <c r="G161" s="9"/>
       <c r="H161" s="14"/>
-      <c r="I161" s="22"/>
+      <c r="I161" s="21"/>
     </row>
     <row r="162">
-      <c r="C162" s="23"/>
+      <c r="C162" s="22"/>
       <c r="F162" s="9"/>
       <c r="G162" s="9"/>
       <c r="H162" s="14"/>
-      <c r="I162" s="22"/>
+      <c r="I162" s="21"/>
     </row>
     <row r="163">
-      <c r="C163" s="23"/>
+      <c r="C163" s="22"/>
       <c r="F163" s="9"/>
       <c r="G163" s="9"/>
       <c r="H163" s="14"/>
-      <c r="I163" s="22"/>
+      <c r="I163" s="21"/>
     </row>
     <row r="164">
-      <c r="C164" s="23"/>
+      <c r="C164" s="22"/>
       <c r="F164" s="9"/>
       <c r="G164" s="9"/>
       <c r="H164" s="14"/>
-      <c r="I164" s="22"/>
+      <c r="I164" s="21"/>
     </row>
     <row r="165">
-      <c r="C165" s="23"/>
+      <c r="C165" s="22"/>
       <c r="F165" s="9"/>
       <c r="G165" s="9"/>
       <c r="H165" s="14"/>
-      <c r="I165" s="22"/>
+      <c r="I165" s="21"/>
     </row>
     <row r="166">
-      <c r="C166" s="23"/>
+      <c r="C166" s="22"/>
       <c r="F166" s="9"/>
       <c r="G166" s="9"/>
       <c r="H166" s="14"/>
-      <c r="I166" s="22"/>
+      <c r="I166" s="21"/>
     </row>
     <row r="167">
-      <c r="C167" s="23"/>
+      <c r="C167" s="22"/>
       <c r="F167" s="9"/>
       <c r="G167" s="9"/>
       <c r="H167" s="14"/>
-      <c r="I167" s="22"/>
+      <c r="I167" s="21"/>
     </row>
     <row r="168">
-      <c r="C168" s="23"/>
+      <c r="C168" s="22"/>
       <c r="F168" s="9"/>
       <c r="G168" s="9"/>
       <c r="H168" s="14"/>
-      <c r="I168" s="22"/>
+      <c r="I168" s="21"/>
     </row>
     <row r="169">
-      <c r="C169" s="23"/>
+      <c r="C169" s="22"/>
       <c r="F169" s="9"/>
       <c r="G169" s="9"/>
       <c r="H169" s="14"/>
-      <c r="I169" s="22"/>
+      <c r="I169" s="21"/>
     </row>
     <row r="170">
-      <c r="C170" s="23"/>
+      <c r="C170" s="22"/>
       <c r="F170" s="9"/>
       <c r="G170" s="9"/>
       <c r="H170" s="14"/>
-      <c r="I170" s="22"/>
+      <c r="I170" s="21"/>
     </row>
     <row r="171">
-      <c r="C171" s="23"/>
+      <c r="C171" s="22"/>
       <c r="F171" s="9"/>
       <c r="G171" s="9"/>
       <c r="H171" s="14"/>
-      <c r="I171" s="22"/>
+      <c r="I171" s="21"/>
     </row>
     <row r="172">
-      <c r="C172" s="23"/>
+      <c r="C172" s="22"/>
       <c r="F172" s="9"/>
       <c r="G172" s="9"/>
       <c r="H172" s="14"/>
-      <c r="I172" s="22"/>
+      <c r="I172" s="21"/>
     </row>
     <row r="173">
-      <c r="C173" s="23"/>
+      <c r="C173" s="22"/>
       <c r="F173" s="9"/>
       <c r="G173" s="9"/>
       <c r="H173" s="14"/>
-      <c r="I173" s="22"/>
+      <c r="I173" s="21"/>
     </row>
     <row r="174">
-      <c r="C174" s="23"/>
+      <c r="C174" s="22"/>
       <c r="F174" s="9"/>
       <c r="G174" s="9"/>
       <c r="H174" s="14"/>
-      <c r="I174" s="22"/>
+      <c r="I174" s="21"/>
     </row>
     <row r="175">
-      <c r="C175" s="23"/>
+      <c r="C175" s="22"/>
       <c r="F175" s="9"/>
       <c r="G175" s="9"/>
       <c r="H175" s="14"/>
-      <c r="I175" s="22"/>
+      <c r="I175" s="21"/>
     </row>
     <row r="176">
-      <c r="C176" s="23"/>
+      <c r="C176" s="22"/>
       <c r="F176" s="9"/>
       <c r="G176" s="9"/>
       <c r="H176" s="14"/>
-      <c r="I176" s="22"/>
+      <c r="I176" s="21"/>
     </row>
     <row r="177">
-      <c r="C177" s="23"/>
+      <c r="C177" s="22"/>
       <c r="F177" s="9"/>
       <c r="G177" s="9"/>
       <c r="H177" s="14"/>
-      <c r="I177" s="22"/>
+      <c r="I177" s="21"/>
     </row>
     <row r="178">
-      <c r="C178" s="23"/>
+      <c r="C178" s="22"/>
       <c r="F178" s="9"/>
       <c r="G178" s="9"/>
       <c r="H178" s="14"/>
-      <c r="I178" s="22"/>
+      <c r="I178" s="21"/>
     </row>
     <row r="179">
-      <c r="C179" s="23"/>
+      <c r="C179" s="22"/>
       <c r="F179" s="9"/>
       <c r="G179" s="9"/>
       <c r="H179" s="14"/>
-      <c r="I179" s="22"/>
+      <c r="I179" s="21"/>
     </row>
     <row r="180">
-      <c r="C180" s="23"/>
+      <c r="C180" s="22"/>
       <c r="F180" s="9"/>
       <c r="G180" s="9"/>
       <c r="H180" s="14"/>
-      <c r="I180" s="22"/>
+      <c r="I180" s="21"/>
     </row>
     <row r="181">
-      <c r="C181" s="23"/>
+      <c r="C181" s="22"/>
       <c r="F181" s="9"/>
       <c r="G181" s="9"/>
       <c r="H181" s="14"/>
-      <c r="I181" s="22"/>
+      <c r="I181" s="21"/>
     </row>
     <row r="182">
-      <c r="C182" s="23"/>
+      <c r="C182" s="22"/>
       <c r="F182" s="9"/>
       <c r="G182" s="9"/>
       <c r="H182" s="14"/>
-      <c r="I182" s="22"/>
+      <c r="I182" s="21"/>
     </row>
     <row r="183">
-      <c r="C183" s="23"/>
+      <c r="C183" s="22"/>
       <c r="F183" s="9"/>
       <c r="G183" s="9"/>
       <c r="H183" s="14"/>
-      <c r="I183" s="22"/>
+      <c r="I183" s="21"/>
     </row>
     <row r="184">
-      <c r="C184" s="23"/>
+      <c r="C184" s="22"/>
       <c r="F184" s="9"/>
       <c r="G184" s="9"/>
       <c r="H184" s="14"/>
-      <c r="I184" s="22"/>
+      <c r="I184" s="21"/>
     </row>
     <row r="185">
-      <c r="C185" s="23"/>
+      <c r="C185" s="22"/>
       <c r="F185" s="9"/>
       <c r="G185" s="9"/>
       <c r="H185" s="14"/>
-      <c r="I185" s="22"/>
+      <c r="I185" s="21"/>
     </row>
     <row r="186">
-      <c r="C186" s="23"/>
+      <c r="C186" s="22"/>
       <c r="F186" s="9"/>
       <c r="G186" s="9"/>
       <c r="H186" s="14"/>
-      <c r="I186" s="22"/>
+      <c r="I186" s="21"/>
     </row>
     <row r="187">
-      <c r="C187" s="23"/>
+      <c r="C187" s="22"/>
       <c r="F187" s="9"/>
       <c r="G187" s="9"/>
       <c r="H187" s="14"/>
-      <c r="I187" s="22"/>
+      <c r="I187" s="21"/>
     </row>
     <row r="188">
-      <c r="C188" s="23"/>
+      <c r="C188" s="22"/>
       <c r="F188" s="9"/>
       <c r="G188" s="9"/>
       <c r="H188" s="14"/>
-      <c r="I188" s="22"/>
+      <c r="I188" s="21"/>
     </row>
     <row r="189">
-      <c r="C189" s="23"/>
+      <c r="C189" s="22"/>
       <c r="F189" s="9"/>
       <c r="G189" s="9"/>
       <c r="H189" s="14"/>
-      <c r="I189" s="22"/>
+      <c r="I189" s="21"/>
     </row>
     <row r="190">
-      <c r="C190" s="23"/>
+      <c r="C190" s="22"/>
       <c r="F190" s="9"/>
       <c r="G190" s="9"/>
       <c r="H190" s="14"/>
-      <c r="I190" s="22"/>
+      <c r="I190" s="21"/>
     </row>
     <row r="191">
-      <c r="C191" s="23"/>
+      <c r="C191" s="22"/>
       <c r="F191" s="9"/>
       <c r="G191" s="9"/>
       <c r="H191" s="14"/>
-      <c r="I191" s="22"/>
+      <c r="I191" s="21"/>
     </row>
     <row r="192">
-      <c r="C192" s="23"/>
+      <c r="C192" s="22"/>
       <c r="F192" s="9"/>
       <c r="G192" s="9"/>
       <c r="H192" s="14"/>
-      <c r="I192" s="22"/>
+      <c r="I192" s="21"/>
     </row>
     <row r="193">
-      <c r="C193" s="23"/>
+      <c r="C193" s="22"/>
       <c r="F193" s="9"/>
       <c r="G193" s="9"/>
       <c r="H193" s="14"/>
-      <c r="I193" s="22"/>
+      <c r="I193" s="21"/>
     </row>
     <row r="194">
-      <c r="C194" s="23"/>
+      <c r="C194" s="22"/>
       <c r="F194" s="9"/>
       <c r="G194" s="9"/>
       <c r="H194" s="14"/>
-      <c r="I194" s="22"/>
+      <c r="I194" s="21"/>
     </row>
     <row r="195">
-      <c r="C195" s="23"/>
+      <c r="C195" s="22"/>
       <c r="F195" s="9"/>
       <c r="G195" s="9"/>
       <c r="H195" s="14"/>
-      <c r="I195" s="22"/>
+      <c r="I195" s="21"/>
     </row>
     <row r="196">
-      <c r="C196" s="23"/>
+      <c r="C196" s="22"/>
       <c r="F196" s="9"/>
       <c r="G196" s="9"/>
       <c r="H196" s="14"/>
-      <c r="I196" s="22"/>
+      <c r="I196" s="21"/>
     </row>
     <row r="197">
-      <c r="C197" s="23"/>
+      <c r="C197" s="22"/>
       <c r="F197" s="9"/>
       <c r="G197" s="9"/>
       <c r="H197" s="14"/>
-      <c r="I197" s="22"/>
+      <c r="I197" s="21"/>
     </row>
     <row r="198">
-      <c r="C198" s="23"/>
+      <c r="C198" s="22"/>
       <c r="F198" s="9"/>
       <c r="G198" s="9"/>
       <c r="H198" s="14"/>
-      <c r="I198" s="22"/>
+      <c r="I198" s="21"/>
     </row>
     <row r="199">
-      <c r="C199" s="23"/>
+      <c r="C199" s="22"/>
       <c r="F199" s="9"/>
       <c r="G199" s="9"/>
       <c r="H199" s="14"/>
-      <c r="I199" s="22"/>
+      <c r="I199" s="21"/>
     </row>
     <row r="200">
-      <c r="C200" s="23"/>
+      <c r="C200" s="22"/>
       <c r="F200" s="9"/>
       <c r="G200" s="9"/>
       <c r="H200" s="14"/>
-      <c r="I200" s="22"/>
+      <c r="I200" s="21"/>
     </row>
     <row r="201">
-      <c r="C201" s="23"/>
+      <c r="C201" s="22"/>
       <c r="F201" s="9"/>
       <c r="G201" s="9"/>
       <c r="H201" s="14"/>
-      <c r="I201" s="22"/>
+      <c r="I201" s="21"/>
     </row>
     <row r="202">
-      <c r="C202" s="23"/>
+      <c r="C202" s="22"/>
       <c r="F202" s="9"/>
       <c r="G202" s="9"/>
       <c r="H202" s="14"/>
-      <c r="I202" s="22"/>
+      <c r="I202" s="21"/>
     </row>
     <row r="203">
-      <c r="C203" s="23"/>
+      <c r="C203" s="22"/>
       <c r="F203" s="9"/>
       <c r="G203" s="9"/>
       <c r="H203" s="14"/>
-      <c r="I203" s="22"/>
+      <c r="I203" s="21"/>
     </row>
     <row r="204">
-      <c r="C204" s="23"/>
+      <c r="C204" s="22"/>
       <c r="F204" s="9"/>
       <c r="G204" s="9"/>
       <c r="H204" s="14"/>
-      <c r="I204" s="22"/>
+      <c r="I204" s="21"/>
     </row>
     <row r="205">
-      <c r="C205" s="23"/>
+      <c r="C205" s="22"/>
       <c r="F205" s="9"/>
       <c r="G205" s="9"/>
       <c r="H205" s="14"/>
-      <c r="I205" s="22"/>
+      <c r="I205" s="21"/>
     </row>
     <row r="206">
-      <c r="C206" s="23"/>
+      <c r="C206" s="22"/>
       <c r="F206" s="9"/>
       <c r="G206" s="9"/>
       <c r="H206" s="14"/>
-      <c r="I206" s="22"/>
+      <c r="I206" s="21"/>
     </row>
     <row r="207">
-      <c r="C207" s="23"/>
+      <c r="C207" s="22"/>
       <c r="F207" s="9"/>
       <c r="G207" s="9"/>
       <c r="H207" s="14"/>
-      <c r="I207" s="22"/>
+      <c r="I207" s="21"/>
     </row>
     <row r="208">
-      <c r="C208" s="23"/>
+      <c r="C208" s="22"/>
       <c r="F208" s="9"/>
       <c r="G208" s="9"/>
       <c r="H208" s="14"/>
-      <c r="I208" s="22"/>
+      <c r="I208" s="21"/>
     </row>
     <row r="209">
-      <c r="C209" s="23"/>
+      <c r="C209" s="22"/>
       <c r="F209" s="9"/>
       <c r="G209" s="9"/>
       <c r="H209" s="14"/>
-      <c r="I209" s="22"/>
+      <c r="I209" s="21"/>
     </row>
     <row r="210">
-      <c r="C210" s="23"/>
+      <c r="C210" s="22"/>
       <c r="F210" s="9"/>
       <c r="G210" s="9"/>
       <c r="H210" s="14"/>
-      <c r="I210" s="22"/>
+      <c r="I210" s="21"/>
     </row>
     <row r="211">
-      <c r="C211" s="23"/>
+      <c r="C211" s="22"/>
       <c r="F211" s="9"/>
       <c r="G211" s="9"/>
       <c r="H211" s="14"/>
-      <c r="I211" s="22"/>
+      <c r="I211" s="21"/>
     </row>
     <row r="212">
-      <c r="C212" s="23"/>
+      <c r="C212" s="22"/>
       <c r="F212" s="9"/>
       <c r="G212" s="9"/>
       <c r="H212" s="14"/>
-      <c r="I212" s="22"/>
+      <c r="I212" s="21"/>
     </row>
     <row r="213">
-      <c r="C213" s="23"/>
+      <c r="C213" s="22"/>
       <c r="F213" s="9"/>
       <c r="G213" s="9"/>
       <c r="H213" s="14"/>
-      <c r="I213" s="22"/>
+      <c r="I213" s="21"/>
     </row>
     <row r="214">
-      <c r="C214" s="23"/>
+      <c r="C214" s="22"/>
       <c r="F214" s="9"/>
       <c r="G214" s="9"/>
       <c r="H214" s="14"/>
-      <c r="I214" s="22"/>
+      <c r="I214" s="21"/>
     </row>
     <row r="215">
-      <c r="C215" s="23"/>
+      <c r="C215" s="22"/>
       <c r="F215" s="9"/>
       <c r="G215" s="9"/>
       <c r="H215" s="14"/>
-      <c r="I215" s="22"/>
+      <c r="I215" s="21"/>
     </row>
     <row r="216">
-      <c r="C216" s="23"/>
+      <c r="C216" s="22"/>
       <c r="F216" s="9"/>
       <c r="G216" s="9"/>
       <c r="H216" s="14"/>
-      <c r="I216" s="22"/>
+      <c r="I216" s="21"/>
     </row>
     <row r="217">
-      <c r="C217" s="23"/>
+      <c r="C217" s="22"/>
       <c r="F217" s="9"/>
       <c r="G217" s="9"/>
       <c r="H217" s="14"/>
-      <c r="I217" s="22"/>
+      <c r="I217" s="21"/>
     </row>
     <row r="218">
-      <c r="C218" s="23"/>
+      <c r="C218" s="22"/>
       <c r="F218" s="9"/>
       <c r="G218" s="9"/>
       <c r="H218" s="14"/>
-      <c r="I218" s="22"/>
+      <c r="I218" s="21"/>
     </row>
     <row r="219">
-      <c r="C219" s="23"/>
+      <c r="C219" s="22"/>
       <c r="F219" s="9"/>
       <c r="G219" s="9"/>
       <c r="H219" s="14"/>
-      <c r="I219" s="22"/>
+      <c r="I219" s="21"/>
     </row>
     <row r="220">
-      <c r="C220" s="23"/>
+      <c r="C220" s="22"/>
       <c r="F220" s="9"/>
       <c r="G220" s="9"/>
       <c r="H220" s="14"/>
-      <c r="I220" s="22"/>
+      <c r="I220" s="21"/>
     </row>
     <row r="221">
-      <c r="C221" s="23"/>
+      <c r="C221" s="22"/>
       <c r="F221" s="9"/>
       <c r="G221" s="9"/>
       <c r="H221" s="14"/>
-      <c r="I221" s="22"/>
+      <c r="I221" s="21"/>
     </row>
     <row r="222">
-      <c r="C222" s="23"/>
+      <c r="C222" s="22"/>
       <c r="F222" s="9"/>
       <c r="G222" s="9"/>
       <c r="H222" s="14"/>
-      <c r="I222" s="22"/>
+      <c r="I222" s="21"/>
     </row>
     <row r="223">
-      <c r="C223" s="23"/>
+      <c r="C223" s="22"/>
       <c r="F223" s="9"/>
       <c r="G223" s="9"/>
       <c r="H223" s="14"/>
-      <c r="I223" s="22"/>
+      <c r="I223" s="21"/>
     </row>
     <row r="224">
-      <c r="C224" s="23"/>
+      <c r="C224" s="22"/>
       <c r="F224" s="9"/>
       <c r="G224" s="9"/>
       <c r="H224" s="14"/>
-      <c r="I224" s="22"/>
+      <c r="I224" s="21"/>
     </row>
     <row r="225">
-      <c r="C225" s="23"/>
+      <c r="C225" s="22"/>
       <c r="F225" s="9"/>
       <c r="G225" s="9"/>
       <c r="H225" s="14"/>
-      <c r="I225" s="22"/>
+      <c r="I225" s="21"/>
     </row>
     <row r="226">
-      <c r="C226" s="23"/>
+      <c r="C226" s="22"/>
       <c r="F226" s="9"/>
       <c r="G226" s="9"/>
       <c r="H226" s="14"/>
-      <c r="I226" s="22"/>
+      <c r="I226" s="21"/>
     </row>
     <row r="227">
-      <c r="C227" s="23"/>
+      <c r="C227" s="22"/>
       <c r="F227" s="9"/>
       <c r="G227" s="9"/>
       <c r="H227" s="14"/>
-      <c r="I227" s="22"/>
+      <c r="I227" s="21"/>
     </row>
     <row r="228">
-      <c r="C228" s="23"/>
+      <c r="C228" s="22"/>
       <c r="F228" s="9"/>
       <c r="G228" s="9"/>
       <c r="H228" s="14"/>
-      <c r="I228" s="22"/>
+      <c r="I228" s="21"/>
     </row>
     <row r="229">
-      <c r="C229" s="23"/>
+      <c r="C229" s="22"/>
       <c r="F229" s="9"/>
       <c r="G229" s="9"/>
       <c r="H229" s="14"/>
-      <c r="I229" s="22"/>
+      <c r="I229" s="21"/>
     </row>
     <row r="230">
-      <c r="C230" s="23"/>
+      <c r="C230" s="22"/>
       <c r="F230" s="9"/>
       <c r="G230" s="9"/>
       <c r="H230" s="14"/>
-      <c r="I230" s="22"/>
+      <c r="I230" s="21"/>
     </row>
     <row r="231">
-      <c r="C231" s="23"/>
+      <c r="C231" s="22"/>
       <c r="F231" s="9"/>
       <c r="G231" s="9"/>
       <c r="H231" s="14"/>
-      <c r="I231" s="22"/>
+      <c r="I231" s="21"/>
     </row>
     <row r="232">
-      <c r="C232" s="23"/>
+      <c r="C232" s="22"/>
       <c r="F232" s="9"/>
       <c r="G232" s="9"/>
       <c r="H232" s="14"/>
-      <c r="I232" s="22"/>
+      <c r="I232" s="21"/>
     </row>
     <row r="233">
-      <c r="C233" s="23"/>
+      <c r="C233" s="22"/>
       <c r="F233" s="9"/>
       <c r="G233" s="9"/>
       <c r="H233" s="14"/>
-      <c r="I233" s="22"/>
+      <c r="I233" s="21"/>
     </row>
     <row r="234">
-      <c r="C234" s="23"/>
+      <c r="C234" s="22"/>
       <c r="F234" s="9"/>
       <c r="G234" s="9"/>
       <c r="H234" s="14"/>
-      <c r="I234" s="22"/>
+      <c r="I234" s="21"/>
     </row>
     <row r="235">
-      <c r="C235" s="23"/>
+      <c r="C235" s="22"/>
       <c r="F235" s="9"/>
       <c r="G235" s="9"/>
       <c r="H235" s="14"/>
-      <c r="I235" s="22"/>
+      <c r="I235" s="21"/>
     </row>
     <row r="236">
-      <c r="C236" s="23"/>
+      <c r="C236" s="22"/>
       <c r="F236" s="9"/>
       <c r="G236" s="9"/>
       <c r="H236" s="14"/>
-      <c r="I236" s="22"/>
+      <c r="I236" s="21"/>
     </row>
     <row r="237">
-      <c r="C237" s="23"/>
+      <c r="C237" s="22"/>
       <c r="F237" s="9"/>
       <c r="G237" s="9"/>
       <c r="H237" s="14"/>
-      <c r="I237" s="22"/>
+      <c r="I237" s="21"/>
     </row>
     <row r="238">
-      <c r="C238" s="23"/>
+      <c r="C238" s="22"/>
       <c r="F238" s="9"/>
       <c r="G238" s="9"/>
       <c r="H238" s="14"/>
-      <c r="I238" s="22"/>
+      <c r="I238" s="21"/>
     </row>
     <row r="239">
-      <c r="C239" s="23"/>
+      <c r="C239" s="22"/>
       <c r="F239" s="9"/>
       <c r="G239" s="9"/>
       <c r="H239" s="14"/>
-      <c r="I239" s="22"/>
+      <c r="I239" s="21"/>
     </row>
     <row r="240">
-      <c r="C240" s="23"/>
+      <c r="C240" s="22"/>
       <c r="F240" s="9"/>
       <c r="G240" s="9"/>
       <c r="H240" s="14"/>
-      <c r="I240" s="22"/>
+      <c r="I240" s="21"/>
     </row>
     <row r="241">
-      <c r="C241" s="23"/>
+      <c r="C241" s="22"/>
       <c r="F241" s="9"/>
       <c r="G241" s="9"/>
       <c r="H241" s="14"/>
-      <c r="I241" s="22"/>
+      <c r="I241" s="21"/>
     </row>
     <row r="242">
-      <c r="C242" s="23"/>
+      <c r="C242" s="22"/>
       <c r="F242" s="9"/>
       <c r="G242" s="9"/>
       <c r="H242" s="14"/>
-      <c r="I242" s="22"/>
+      <c r="I242" s="21"/>
     </row>
     <row r="243">
-      <c r="C243" s="23"/>
+      <c r="C243" s="22"/>
       <c r="F243" s="9"/>
       <c r="G243" s="9"/>
       <c r="H243" s="14"/>
-      <c r="I243" s="22"/>
+      <c r="I243" s="21"/>
     </row>
     <row r="244">
-      <c r="C244" s="23"/>
+      <c r="C244" s="22"/>
       <c r="F244" s="9"/>
       <c r="G244" s="9"/>
       <c r="H244" s="14"/>
-      <c r="I244" s="22"/>
+      <c r="I244" s="21"/>
     </row>
     <row r="245">
-      <c r="C245" s="23"/>
+      <c r="C245" s="22"/>
       <c r="F245" s="9"/>
       <c r="G245" s="9"/>
       <c r="H245" s="14"/>
-      <c r="I245" s="22"/>
+      <c r="I245" s="21"/>
     </row>
     <row r="246">
-      <c r="C246" s="23"/>
+      <c r="C246" s="22"/>
       <c r="F246" s="9"/>
       <c r="G246" s="9"/>
       <c r="H246" s="14"/>
-      <c r="I246" s="22"/>
+      <c r="I246" s="21"/>
     </row>
     <row r="247">
-      <c r="C247" s="23"/>
+      <c r="C247" s="22"/>
       <c r="F247" s="9"/>
       <c r="G247" s="9"/>
       <c r="H247" s="14"/>
-      <c r="I247" s="22"/>
+      <c r="I247" s="21"/>
     </row>
     <row r="248">
-      <c r="C248" s="23"/>
+      <c r="C248" s="22"/>
       <c r="F248" s="9"/>
       <c r="G248" s="9"/>
       <c r="H248" s="14"/>
-      <c r="I248" s="22"/>
+      <c r="I248" s="21"/>
     </row>
     <row r="249">
-      <c r="C249" s="23"/>
+      <c r="C249" s="22"/>
       <c r="F249" s="9"/>
       <c r="G249" s="9"/>
       <c r="H249" s="14"/>
-      <c r="I249" s="22"/>
+      <c r="I249" s="21"/>
     </row>
     <row r="250">
-      <c r="C250" s="23"/>
+      <c r="C250" s="22"/>
       <c r="F250" s="9"/>
       <c r="G250" s="9"/>
       <c r="H250" s="14"/>
-      <c r="I250" s="22"/>
+      <c r="I250" s="21"/>
     </row>
     <row r="251">
-      <c r="C251" s="23"/>
+      <c r="C251" s="22"/>
       <c r="F251" s="9"/>
       <c r="G251" s="9"/>
       <c r="H251" s="14"/>
-      <c r="I251" s="22"/>
+      <c r="I251" s="21"/>
     </row>
     <row r="252">
-      <c r="C252" s="23"/>
+      <c r="C252" s="22"/>
       <c r="F252" s="9"/>
       <c r="G252" s="9"/>
       <c r="H252" s="14"/>
-      <c r="I252" s="22"/>
+      <c r="I252" s="21"/>
     </row>
     <row r="253">
-      <c r="C253" s="23"/>
+      <c r="C253" s="22"/>
       <c r="F253" s="9"/>
       <c r="G253" s="9"/>
       <c r="H253" s="14"/>
-      <c r="I253" s="22"/>
+      <c r="I253" s="21"/>
     </row>
     <row r="254">
-      <c r="C254" s="23"/>
+      <c r="C254" s="22"/>
       <c r="F254" s="9"/>
       <c r="G254" s="9"/>
       <c r="H254" s="14"/>
-      <c r="I254" s="22"/>
+      <c r="I254" s="21"/>
     </row>
     <row r="255">
-      <c r="C255" s="23"/>
+      <c r="C255" s="22"/>
       <c r="F255" s="9"/>
       <c r="G255" s="9"/>
       <c r="H255" s="14"/>
-      <c r="I255" s="22"/>
+      <c r="I255" s="21"/>
     </row>
     <row r="256">
-      <c r="C256" s="23"/>
+      <c r="C256" s="22"/>
       <c r="F256" s="9"/>
       <c r="G256" s="9"/>
       <c r="H256" s="14"/>
-      <c r="I256" s="22"/>
+      <c r="I256" s="21"/>
     </row>
     <row r="257">
-      <c r="C257" s="23"/>
+      <c r="C257" s="22"/>
       <c r="F257" s="9"/>
       <c r="G257" s="9"/>
       <c r="H257" s="14"/>
-      <c r="I257" s="22"/>
+      <c r="I257" s="21"/>
     </row>
     <row r="258">
-      <c r="C258" s="23"/>
+      <c r="C258" s="22"/>
       <c r="F258" s="9"/>
       <c r="G258" s="9"/>
       <c r="H258" s="14"/>
-      <c r="I258" s="22"/>
+      <c r="I258" s="21"/>
     </row>
     <row r="259">
-      <c r="C259" s="23"/>
+      <c r="C259" s="22"/>
       <c r="F259" s="9"/>
       <c r="G259" s="9"/>
       <c r="H259" s="14"/>
-      <c r="I259" s="22"/>
+      <c r="I259" s="21"/>
     </row>
     <row r="260">
-      <c r="C260" s="23"/>
+      <c r="C260" s="22"/>
       <c r="F260" s="9"/>
       <c r="G260" s="9"/>
       <c r="H260" s="14"/>
-      <c r="I260" s="22"/>
+      <c r="I260" s="21"/>
     </row>
     <row r="261">
-      <c r="C261" s="23"/>
+      <c r="C261" s="22"/>
       <c r="F261" s="9"/>
       <c r="G261" s="9"/>
       <c r="H261" s="14"/>
-      <c r="I261" s="22"/>
+      <c r="I261" s="21"/>
     </row>
     <row r="262">
-      <c r="C262" s="23"/>
+      <c r="C262" s="22"/>
       <c r="F262" s="9"/>
       <c r="G262" s="9"/>
       <c r="H262" s="14"/>
-      <c r="I262" s="22"/>
+      <c r="I262" s="21"/>
     </row>
     <row r="263">
-      <c r="C263" s="23"/>
+      <c r="C263" s="22"/>
       <c r="F263" s="9"/>
       <c r="G263" s="9"/>
       <c r="H263" s="14"/>
-      <c r="I263" s="22"/>
+      <c r="I263" s="21"/>
     </row>
     <row r="264">
-      <c r="C264" s="23"/>
+      <c r="C264" s="22"/>
       <c r="F264" s="9"/>
       <c r="G264" s="9"/>
       <c r="H264" s="14"/>
-      <c r="I264" s="22"/>
+      <c r="I264" s="21"/>
     </row>
     <row r="265">
-      <c r="C265" s="23"/>
+      <c r="C265" s="22"/>
       <c r="F265" s="9"/>
       <c r="G265" s="9"/>
       <c r="H265" s="14"/>
-      <c r="I265" s="22"/>
+      <c r="I265" s="21"/>
     </row>
     <row r="266">
-      <c r="C266" s="23"/>
+      <c r="C266" s="22"/>
       <c r="F266" s="9"/>
       <c r="G266" s="9"/>
       <c r="H266" s="14"/>
-      <c r="I266" s="22"/>
+      <c r="I266" s="21"/>
     </row>
     <row r="267">
-      <c r="C267" s="23"/>
+      <c r="C267" s="22"/>
       <c r="F267" s="9"/>
       <c r="G267" s="9"/>
       <c r="H267" s="14"/>
-      <c r="I267" s="22"/>
+      <c r="I267" s="21"/>
     </row>
     <row r="268">
-      <c r="C268" s="23"/>
+      <c r="C268" s="22"/>
       <c r="F268" s="9"/>
       <c r="G268" s="9"/>
       <c r="H268" s="14"/>
-      <c r="I268" s="22"/>
+      <c r="I268" s="21"/>
     </row>
     <row r="269">
-      <c r="C269" s="23"/>
+      <c r="C269" s="22"/>
       <c r="F269" s="9"/>
       <c r="G269" s="9"/>
       <c r="H269" s="14"/>
-      <c r="I269" s="22"/>
+      <c r="I269" s="21"/>
     </row>
     <row r="270">
-      <c r="C270" s="23"/>
+      <c r="C270" s="22"/>
       <c r="F270" s="9"/>
       <c r="G270" s="9"/>
       <c r="H270" s="14"/>
-      <c r="I270" s="22"/>
+      <c r="I270" s="21"/>
     </row>
     <row r="271">
-      <c r="C271" s="23"/>
+      <c r="C271" s="22"/>
       <c r="F271" s="9"/>
       <c r="G271" s="9"/>
       <c r="H271" s="14"/>
-      <c r="I271" s="22"/>
+      <c r="I271" s="21"/>
     </row>
     <row r="272">
-      <c r="C272" s="23"/>
+      <c r="C272" s="22"/>
       <c r="F272" s="9"/>
       <c r="G272" s="9"/>
       <c r="H272" s="14"/>
-      <c r="I272" s="22"/>
+      <c r="I272" s="21"/>
     </row>
     <row r="273">
-      <c r="C273" s="23"/>
+      <c r="C273" s="22"/>
       <c r="F273" s="9"/>
       <c r="G273" s="9"/>
       <c r="H273" s="14"/>
-      <c r="I273" s="22"/>
+      <c r="I273" s="21"/>
     </row>
     <row r="274">
-      <c r="C274" s="23"/>
+      <c r="C274" s="22"/>
       <c r="F274" s="9"/>
       <c r="G274" s="9"/>
       <c r="H274" s="14"/>
-      <c r="I274" s="22"/>
+      <c r="I274" s="21"/>
     </row>
     <row r="275">
-      <c r="C275" s="23"/>
+      <c r="C275" s="22"/>
       <c r="F275" s="9"/>
       <c r="G275" s="9"/>
       <c r="H275" s="14"/>
-      <c r="I275" s="22"/>
+      <c r="I275" s="21"/>
     </row>
     <row r="276">
-      <c r="C276" s="23"/>
+      <c r="C276" s="22"/>
       <c r="F276" s="9"/>
       <c r="G276" s="9"/>
       <c r="H276" s="14"/>
-      <c r="I276" s="22"/>
+      <c r="I276" s="21"/>
     </row>
     <row r="277">
-      <c r="C277" s="23"/>
+      <c r="C277" s="22"/>
       <c r="F277" s="9"/>
       <c r="G277" s="9"/>
       <c r="H277" s="14"/>
-      <c r="I277" s="22"/>
+      <c r="I277" s="21"/>
     </row>
     <row r="278">
-      <c r="C278" s="23"/>
+      <c r="C278" s="22"/>
       <c r="F278" s="9"/>
       <c r="G278" s="9"/>
       <c r="H278" s="14"/>
-      <c r="I278" s="22"/>
+      <c r="I278" s="21"/>
     </row>
     <row r="279">
-      <c r="C279" s="23"/>
+      <c r="C279" s="22"/>
       <c r="F279" s="9"/>
       <c r="G279" s="9"/>
       <c r="H279" s="14"/>
-      <c r="I279" s="22"/>
+      <c r="I279" s="21"/>
     </row>
     <row r="280">
-      <c r="C280" s="23"/>
+      <c r="C280" s="22"/>
       <c r="F280" s="9"/>
       <c r="G280" s="9"/>
       <c r="H280" s="14"/>
-      <c r="I280" s="22"/>
+      <c r="I280" s="21"/>
     </row>
     <row r="281">
-      <c r="C281" s="23"/>
+      <c r="C281" s="22"/>
       <c r="F281" s="9"/>
       <c r="G281" s="9"/>
       <c r="H281" s="14"/>
-      <c r="I281" s="22"/>
+      <c r="I281" s="21"/>
     </row>
     <row r="282">
-      <c r="C282" s="23"/>
+      <c r="C282" s="22"/>
       <c r="F282" s="9"/>
       <c r="G282" s="9"/>
       <c r="H282" s="14"/>
-      <c r="I282" s="22"/>
+      <c r="I282" s="21"/>
     </row>
     <row r="283">
-      <c r="C283" s="23"/>
+      <c r="C283" s="22"/>
       <c r="F283" s="9"/>
       <c r="G283" s="9"/>
       <c r="H283" s="14"/>
-      <c r="I283" s="22"/>
+      <c r="I283" s="21"/>
     </row>
     <row r="284">
-      <c r="C284" s="23"/>
+      <c r="C284" s="22"/>
       <c r="F284" s="9"/>
       <c r="G284" s="9"/>
       <c r="H284" s="14"/>
-      <c r="I284" s="22"/>
+      <c r="I284" s="21"/>
     </row>
     <row r="285">
-      <c r="C285" s="23"/>
+      <c r="C285" s="22"/>
       <c r="F285" s="9"/>
       <c r="G285" s="9"/>
       <c r="H285" s="14"/>
-      <c r="I285" s="22"/>
+      <c r="I285" s="21"/>
     </row>
     <row r="286">
-      <c r="C286" s="23"/>
+      <c r="C286" s="22"/>
       <c r="F286" s="9"/>
       <c r="G286" s="9"/>
       <c r="H286" s="14"/>
-      <c r="I286" s="22"/>
+      <c r="I286" s="21"/>
     </row>
     <row r="287">
-      <c r="C287" s="23"/>
+      <c r="C287" s="22"/>
       <c r="F287" s="9"/>
       <c r="G287" s="9"/>
       <c r="H287" s="14"/>
-      <c r="I287" s="22"/>
+      <c r="I287" s="21"/>
     </row>
     <row r="288">
-      <c r="C288" s="23"/>
+      <c r="C288" s="22"/>
       <c r="F288" s="9"/>
       <c r="G288" s="9"/>
       <c r="H288" s="14"/>
-      <c r="I288" s="22"/>
+      <c r="I288" s="21"/>
     </row>
     <row r="289">
-      <c r="C289" s="23"/>
+      <c r="C289" s="22"/>
       <c r="F289" s="9"/>
       <c r="G289" s="9"/>
       <c r="H289" s="14"/>
-      <c r="I289" s="22"/>
+      <c r="I289" s="21"/>
     </row>
     <row r="290">
-      <c r="C290" s="23"/>
+      <c r="C290" s="22"/>
       <c r="F290" s="9"/>
       <c r="G290" s="9"/>
       <c r="H290" s="14"/>
-      <c r="I290" s="22"/>
+      <c r="I290" s="21"/>
     </row>
     <row r="291">
-      <c r="C291" s="23"/>
+      <c r="C291" s="22"/>
       <c r="F291" s="9"/>
       <c r="G291" s="9"/>
       <c r="H291" s="14"/>
-      <c r="I291" s="22"/>
+      <c r="I291" s="21"/>
     </row>
     <row r="292">
-      <c r="C292" s="23"/>
+      <c r="C292" s="22"/>
       <c r="F292" s="9"/>
       <c r="G292" s="9"/>
       <c r="H292" s="14"/>
-      <c r="I292" s="22"/>
+      <c r="I292" s="21"/>
     </row>
     <row r="293">
-      <c r="C293" s="23"/>
+      <c r="C293" s="22"/>
       <c r="F293" s="9"/>
       <c r="G293" s="9"/>
       <c r="H293" s="14"/>
-      <c r="I293" s="22"/>
+      <c r="I293" s="21"/>
     </row>
     <row r="294">
-      <c r="C294" s="23"/>
+      <c r="C294" s="22"/>
       <c r="F294" s="9"/>
       <c r="G294" s="9"/>
       <c r="H294" s="14"/>
-      <c r="I294" s="22"/>
+      <c r="I294" s="21"/>
     </row>
     <row r="295">
-      <c r="C295" s="23"/>
+      <c r="C295" s="22"/>
       <c r="F295" s="9"/>
       <c r="G295" s="9"/>
       <c r="H295" s="14"/>
-      <c r="I295" s="22"/>
+      <c r="I295" s="21"/>
     </row>
     <row r="296">
-      <c r="C296" s="23"/>
+      <c r="C296" s="22"/>
       <c r="F296" s="9"/>
       <c r="G296" s="9"/>
       <c r="H296" s="14"/>
-      <c r="I296" s="22"/>
+      <c r="I296" s="21"/>
     </row>
     <row r="297">
-      <c r="C297" s="23"/>
+      <c r="C297" s="22"/>
       <c r="F297" s="9"/>
       <c r="G297" s="9"/>
       <c r="H297" s="14"/>
-      <c r="I297" s="22"/>
+      <c r="I297" s="21"/>
     </row>
     <row r="298">
-      <c r="C298" s="23"/>
+      <c r="C298" s="22"/>
       <c r="F298" s="9"/>
       <c r="G298" s="9"/>
       <c r="H298" s="14"/>
-      <c r="I298" s="22"/>
+      <c r="I298" s="21"/>
     </row>
     <row r="299">
-      <c r="C299" s="23"/>
+      <c r="C299" s="22"/>
       <c r="F299" s="9"/>
       <c r="G299" s="9"/>
       <c r="H299" s="14"/>
-      <c r="I299" s="22"/>
+      <c r="I299" s="21"/>
     </row>
     <row r="300">
-      <c r="C300" s="23"/>
+      <c r="C300" s="22"/>
       <c r="F300" s="9"/>
       <c r="G300" s="9"/>
       <c r="H300" s="14"/>
-      <c r="I300" s="22"/>
+      <c r="I300" s="21"/>
     </row>
     <row r="301">
-      <c r="C301" s="23"/>
+      <c r="C301" s="22"/>
       <c r="F301" s="9"/>
       <c r="G301" s="9"/>
       <c r="H301" s="14"/>
-      <c r="I301" s="22"/>
+      <c r="I301" s="21"/>
     </row>
     <row r="302">
-      <c r="C302" s="23"/>
+      <c r="C302" s="22"/>
       <c r="F302" s="9"/>
       <c r="G302" s="9"/>
       <c r="H302" s="14"/>
-      <c r="I302" s="22"/>
+      <c r="I302" s="21"/>
     </row>
     <row r="303">
-      <c r="C303" s="23"/>
+      <c r="C303" s="22"/>
       <c r="F303" s="9"/>
       <c r="G303" s="9"/>
       <c r="H303" s="14"/>
-      <c r="I303" s="22"/>
+      <c r="I303" s="21"/>
     </row>
     <row r="304">
-      <c r="C304" s="23"/>
+      <c r="C304" s="22"/>
       <c r="F304" s="9"/>
       <c r="G304" s="9"/>
       <c r="H304" s="14"/>
-      <c r="I304" s="22"/>
+      <c r="I304" s="21"/>
     </row>
     <row r="305">
-      <c r="C305" s="23"/>
+      <c r="C305" s="22"/>
       <c r="F305" s="9"/>
       <c r="G305" s="9"/>
       <c r="H305" s="14"/>
-      <c r="I305" s="22"/>
+      <c r="I305" s="21"/>
     </row>
     <row r="306">
-      <c r="C306" s="23"/>
+      <c r="C306" s="22"/>
       <c r="F306" s="9"/>
       <c r="G306" s="9"/>
       <c r="H306" s="14"/>
-      <c r="I306" s="22"/>
+      <c r="I306" s="21"/>
     </row>
     <row r="307">
-      <c r="C307" s="23"/>
+      <c r="C307" s="22"/>
       <c r="F307" s="9"/>
       <c r="G307" s="9"/>
       <c r="H307" s="14"/>
-      <c r="I307" s="22"/>
+      <c r="I307" s="21"/>
     </row>
     <row r="308">
-      <c r="C308" s="23"/>
+      <c r="C308" s="22"/>
       <c r="F308" s="9"/>
       <c r="G308" s="9"/>
       <c r="H308" s="14"/>
-      <c r="I308" s="22"/>
+      <c r="I308" s="21"/>
     </row>
     <row r="309">
-      <c r="C309" s="23"/>
+      <c r="C309" s="22"/>
       <c r="F309" s="9"/>
       <c r="G309" s="9"/>
       <c r="H309" s="14"/>
-      <c r="I309" s="22"/>
+      <c r="I309" s="21"/>
     </row>
     <row r="310">
-      <c r="C310" s="23"/>
+      <c r="C310" s="22"/>
       <c r="F310" s="9"/>
       <c r="G310" s="9"/>
       <c r="H310" s="14"/>
-      <c r="I310" s="22"/>
+      <c r="I310" s="21"/>
     </row>
     <row r="311">
-      <c r="C311" s="23"/>
+      <c r="C311" s="22"/>
       <c r="F311" s="9"/>
       <c r="G311" s="9"/>
       <c r="H311" s="14"/>
-      <c r="I311" s="22"/>
+      <c r="I311" s="21"/>
     </row>
     <row r="312">
-      <c r="C312" s="23"/>
+      <c r="C312" s="22"/>
       <c r="F312" s="9"/>
       <c r="G312" s="9"/>
       <c r="H312" s="14"/>
-      <c r="I312" s="22"/>
+      <c r="I312" s="21"/>
     </row>
     <row r="313">
-      <c r="C313" s="23"/>
+      <c r="C313" s="22"/>
       <c r="F313" s="9"/>
       <c r="G313" s="9"/>
       <c r="H313" s="14"/>
-      <c r="I313" s="22"/>
+      <c r="I313" s="21"/>
     </row>
     <row r="314">
-      <c r="C314" s="23"/>
+      <c r="C314" s="22"/>
       <c r="F314" s="9"/>
       <c r="G314" s="9"/>
       <c r="H314" s="14"/>
-      <c r="I314" s="22"/>
+      <c r="I314" s="21"/>
     </row>
     <row r="315">
-      <c r="C315" s="23"/>
+      <c r="C315" s="22"/>
       <c r="F315" s="9"/>
       <c r="G315" s="9"/>
       <c r="H315" s="14"/>
-      <c r="I315" s="22"/>
+      <c r="I315" s="21"/>
     </row>
     <row r="316">
-      <c r="C316" s="23"/>
+      <c r="C316" s="22"/>
       <c r="F316" s="9"/>
       <c r="G316" s="9"/>
       <c r="H316" s="14"/>
-      <c r="I316" s="22"/>
+      <c r="I316" s="21"/>
     </row>
     <row r="317">
-      <c r="C317" s="23"/>
+      <c r="C317" s="22"/>
       <c r="F317" s="9"/>
       <c r="G317" s="9"/>
       <c r="H317" s="14"/>
-      <c r="I317" s="22"/>
+      <c r="I317" s="21"/>
     </row>
     <row r="318">
-      <c r="C318" s="23"/>
+      <c r="C318" s="22"/>
       <c r="F318" s="9"/>
       <c r="G318" s="9"/>
       <c r="H318" s="14"/>
-      <c r="I318" s="22"/>
+      <c r="I318" s="21"/>
     </row>
     <row r="319">
-      <c r="C319" s="23"/>
+      <c r="C319" s="22"/>
       <c r="F319" s="9"/>
       <c r="G319" s="9"/>
       <c r="H319" s="14"/>
-      <c r="I319" s="22"/>
+      <c r="I319" s="21"/>
     </row>
     <row r="320">
-      <c r="C320" s="23"/>
+      <c r="C320" s="22"/>
       <c r="F320" s="9"/>
       <c r="G320" s="9"/>
       <c r="H320" s="14"/>
-      <c r="I320" s="22"/>
+      <c r="I320" s="21"/>
     </row>
     <row r="321">
-      <c r="C321" s="23"/>
+      <c r="C321" s="22"/>
       <c r="F321" s="9"/>
       <c r="G321" s="9"/>
       <c r="H321" s="14"/>
-      <c r="I321" s="22"/>
+      <c r="I321" s="21"/>
     </row>
     <row r="322">
-      <c r="C322" s="23"/>
+      <c r="C322" s="22"/>
       <c r="F322" s="9"/>
       <c r="G322" s="9"/>
       <c r="H322" s="14"/>
-      <c r="I322" s="22"/>
+      <c r="I322" s="21"/>
     </row>
     <row r="323">
-      <c r="C323" s="23"/>
+      <c r="C323" s="22"/>
       <c r="F323" s="9"/>
       <c r="G323" s="9"/>
       <c r="H323" s="14"/>
-      <c r="I323" s="22"/>
+      <c r="I323" s="21"/>
     </row>
     <row r="324">
-      <c r="C324" s="23"/>
+      <c r="C324" s="22"/>
       <c r="F324" s="9"/>
       <c r="G324" s="9"/>
       <c r="H324" s="14"/>
-      <c r="I324" s="22"/>
+      <c r="I324" s="21"/>
     </row>
     <row r="325">
-      <c r="C325" s="23"/>
+      <c r="C325" s="22"/>
       <c r="F325" s="9"/>
       <c r="G325" s="9"/>
       <c r="H325" s="14"/>
-      <c r="I325" s="22"/>
+      <c r="I325" s="21"/>
     </row>
     <row r="326">
-      <c r="C326" s="23"/>
+      <c r="C326" s="22"/>
       <c r="F326" s="9"/>
       <c r="G326" s="9"/>
       <c r="H326" s="14"/>
-      <c r="I326" s="22"/>
+      <c r="I326" s="21"/>
     </row>
     <row r="327">
-      <c r="C327" s="23"/>
+      <c r="C327" s="22"/>
       <c r="F327" s="9"/>
       <c r="G327" s="9"/>
       <c r="H327" s="14"/>
-      <c r="I327" s="22"/>
+      <c r="I327" s="21"/>
     </row>
     <row r="328">
-      <c r="C328" s="23"/>
+      <c r="C328" s="22"/>
       <c r="F328" s="9"/>
       <c r="G328" s="9"/>
       <c r="H328" s="14"/>
-      <c r="I328" s="22"/>
+      <c r="I328" s="21"/>
     </row>
     <row r="329">
-      <c r="C329" s="23"/>
+      <c r="C329" s="22"/>
       <c r="F329" s="9"/>
       <c r="G329" s="9"/>
       <c r="H329" s="14"/>
-      <c r="I329" s="22"/>
+      <c r="I329" s="21"/>
     </row>
     <row r="330">
-      <c r="C330" s="23"/>
+      <c r="C330" s="22"/>
       <c r="F330" s="9"/>
       <c r="G330" s="9"/>
       <c r="H330" s="14"/>
-      <c r="I330" s="22"/>
+      <c r="I330" s="21"/>
     </row>
     <row r="331">
-      <c r="C331" s="23"/>
+      <c r="C331" s="22"/>
       <c r="F331" s="9"/>
       <c r="G331" s="9"/>
       <c r="H331" s="14"/>
-      <c r="I331" s="22"/>
+      <c r="I331" s="21"/>
     </row>
     <row r="332">
-      <c r="C332" s="23"/>
+      <c r="C332" s="22"/>
       <c r="F332" s="9"/>
       <c r="G332" s="9"/>
       <c r="H332" s="14"/>
-      <c r="I332" s="22"/>
+      <c r="I332" s="21"/>
     </row>
     <row r="333">
-      <c r="C333" s="23"/>
+      <c r="C333" s="22"/>
       <c r="F333" s="9"/>
       <c r="G333" s="9"/>
       <c r="H333" s="14"/>
-      <c r="I333" s="22"/>
+      <c r="I333" s="21"/>
     </row>
     <row r="334">
-      <c r="C334" s="23"/>
+      <c r="C334" s="22"/>
       <c r="F334" s="9"/>
       <c r="G334" s="9"/>
       <c r="H334" s="14"/>
-      <c r="I334" s="22"/>
+      <c r="I334" s="21"/>
     </row>
     <row r="335">
-      <c r="C335" s="23"/>
+      <c r="C335" s="22"/>
       <c r="F335" s="9"/>
       <c r="G335" s="9"/>
       <c r="H335" s="14"/>
-      <c r="I335" s="22"/>
+      <c r="I335" s="21"/>
     </row>
     <row r="336">
-      <c r="C336" s="23"/>
+      <c r="C336" s="22"/>
       <c r="F336" s="9"/>
       <c r="G336" s="9"/>
       <c r="H336" s="14"/>
-      <c r="I336" s="22"/>
+      <c r="I336" s="21"/>
     </row>
     <row r="337">
-      <c r="C337" s="23"/>
+      <c r="C337" s="22"/>
       <c r="F337" s="9"/>
       <c r="G337" s="9"/>
       <c r="H337" s="14"/>
-      <c r="I337" s="22"/>
+      <c r="I337" s="21"/>
     </row>
     <row r="338">
-      <c r="C338" s="23"/>
+      <c r="C338" s="22"/>
       <c r="F338" s="9"/>
       <c r="G338" s="9"/>
       <c r="H338" s="14"/>
-      <c r="I338" s="22"/>
+      <c r="I338" s="21"/>
     </row>
     <row r="339">
-      <c r="C339" s="23"/>
+      <c r="C339" s="22"/>
       <c r="F339" s="9"/>
       <c r="G339" s="9"/>
       <c r="H339" s="14"/>
-      <c r="I339" s="22"/>
+      <c r="I339" s="21"/>
     </row>
     <row r="340">
-      <c r="C340" s="23"/>
+      <c r="C340" s="22"/>
       <c r="F340" s="9"/>
       <c r="G340" s="9"/>
       <c r="H340" s="14"/>
-      <c r="I340" s="22"/>
+      <c r="I340" s="21"/>
     </row>
     <row r="341">
-      <c r="C341" s="23"/>
+      <c r="C341" s="22"/>
       <c r="F341" s="9"/>
       <c r="G341" s="9"/>
       <c r="H341" s="14"/>
-      <c r="I341" s="22"/>
+      <c r="I341" s="21"/>
     </row>
     <row r="342">
-      <c r="C342" s="23"/>
+      <c r="C342" s="22"/>
       <c r="F342" s="9"/>
       <c r="G342" s="9"/>
       <c r="H342" s="14"/>
-      <c r="I342" s="22"/>
+      <c r="I342" s="21"/>
     </row>
     <row r="343">
-      <c r="C343" s="23"/>
+      <c r="C343" s="22"/>
       <c r="F343" s="9"/>
       <c r="G343" s="9"/>
       <c r="H343" s="14"/>
-      <c r="I343" s="22"/>
+      <c r="I343" s="21"/>
     </row>
     <row r="344">
-      <c r="C344" s="23"/>
+      <c r="C344" s="22"/>
       <c r="F344" s="9"/>
       <c r="G344" s="9"/>
       <c r="H344" s="14"/>
-      <c r="I344" s="22"/>
+      <c r="I344" s="21"/>
     </row>
     <row r="345">
-      <c r="C345" s="23"/>
+      <c r="C345" s="22"/>
       <c r="F345" s="9"/>
       <c r="G345" s="9"/>
       <c r="H345" s="14"/>
-      <c r="I345" s="22"/>
+      <c r="I345" s="21"/>
     </row>
     <row r="346">
-      <c r="C346" s="23"/>
+      <c r="C346" s="22"/>
       <c r="F346" s="9"/>
       <c r="G346" s="9"/>
       <c r="H346" s="14"/>
-      <c r="I346" s="22"/>
+      <c r="I346" s="21"/>
     </row>
     <row r="347">
-      <c r="C347" s="23"/>
+      <c r="C347" s="22"/>
       <c r="F347" s="9"/>
       <c r="G347" s="9"/>
       <c r="H347" s="14"/>
-      <c r="I347" s="22"/>
+      <c r="I347" s="21"/>
     </row>
     <row r="348">
-      <c r="C348" s="23"/>
+      <c r="C348" s="22"/>
       <c r="F348" s="9"/>
       <c r="G348" s="9"/>
       <c r="H348" s="14"/>
-      <c r="I348" s="22"/>
+      <c r="I348" s="21"/>
     </row>
     <row r="349">
-      <c r="C349" s="23"/>
+      <c r="C349" s="22"/>
       <c r="F349" s="9"/>
       <c r="G349" s="9"/>
       <c r="H349" s="14"/>
-      <c r="I349" s="22"/>
+      <c r="I349" s="21"/>
     </row>
     <row r="350">
-      <c r="C350" s="23"/>
+      <c r="C350" s="22"/>
       <c r="F350" s="9"/>
       <c r="G350" s="9"/>
       <c r="H350" s="14"/>
-      <c r="I350" s="22"/>
+      <c r="I350" s="21"/>
     </row>
     <row r="351">
-      <c r="C351" s="23"/>
+      <c r="C351" s="22"/>
       <c r="F351" s="9"/>
       <c r="G351" s="9"/>
       <c r="H351" s="14"/>
-      <c r="I351" s="22"/>
+      <c r="I351" s="21"/>
     </row>
     <row r="352">
-      <c r="C352" s="23"/>
+      <c r="C352" s="22"/>
       <c r="F352" s="9"/>
       <c r="G352" s="9"/>
       <c r="H352" s="14"/>
-      <c r="I352" s="22"/>
+      <c r="I352" s="21"/>
     </row>
     <row r="353">
-      <c r="C353" s="23"/>
+      <c r="C353" s="22"/>
       <c r="F353" s="9"/>
       <c r="G353" s="9"/>
       <c r="H353" s="14"/>
-      <c r="I353" s="22"/>
+      <c r="I353" s="21"/>
     </row>
     <row r="354">
-      <c r="C354" s="23"/>
+      <c r="C354" s="22"/>
       <c r="F354" s="9"/>
       <c r="G354" s="9"/>
       <c r="H354" s="14"/>
-      <c r="I354" s="22"/>
+      <c r="I354" s="21"/>
     </row>
     <row r="355">
-      <c r="C355" s="23"/>
+      <c r="C355" s="22"/>
       <c r="F355" s="9"/>
       <c r="G355" s="9"/>
       <c r="H355" s="14"/>
-      <c r="I355" s="22"/>
+      <c r="I355" s="21"/>
     </row>
     <row r="356">
-      <c r="C356" s="23"/>
+      <c r="C356" s="22"/>
       <c r="F356" s="9"/>
       <c r="G356" s="9"/>
       <c r="H356" s="14"/>
-      <c r="I356" s="22"/>
+      <c r="I356" s="21"/>
     </row>
     <row r="357">
-      <c r="C357" s="23"/>
+      <c r="C357" s="22"/>
       <c r="F357" s="9"/>
       <c r="G357" s="9"/>
       <c r="H357" s="14"/>
-      <c r="I357" s="22"/>
+      <c r="I357" s="21"/>
     </row>
     <row r="358">
-      <c r="C358" s="23"/>
+      <c r="C358" s="22"/>
       <c r="F358" s="9"/>
       <c r="G358" s="9"/>
       <c r="H358" s="14"/>
-      <c r="I358" s="22"/>
+      <c r="I358" s="21"/>
     </row>
     <row r="359">
-      <c r="C359" s="23"/>
+      <c r="C359" s="22"/>
       <c r="F359" s="9"/>
       <c r="G359" s="9"/>
       <c r="H359" s="14"/>
-      <c r="I359" s="22"/>
+      <c r="I359" s="21"/>
     </row>
     <row r="360">
-      <c r="C360" s="23"/>
+      <c r="C360" s="22"/>
       <c r="F360" s="9"/>
       <c r="G360" s="9"/>
       <c r="H360" s="14"/>
-      <c r="I360" s="22"/>
+      <c r="I360" s="21"/>
     </row>
     <row r="361">
-      <c r="C361" s="23"/>
+      <c r="C361" s="22"/>
       <c r="F361" s="9"/>
       <c r="G361" s="9"/>
       <c r="H361" s="14"/>
-      <c r="I361" s="22"/>
+      <c r="I361" s="21"/>
     </row>
     <row r="362">
-      <c r="C362" s="23"/>
+      <c r="C362" s="22"/>
       <c r="F362" s="9"/>
       <c r="G362" s="9"/>
       <c r="H362" s="14"/>
-      <c r="I362" s="22"/>
+      <c r="I362" s="21"/>
     </row>
     <row r="363">
-      <c r="C363" s="23"/>
+      <c r="C363" s="22"/>
       <c r="F363" s="9"/>
       <c r="G363" s="9"/>
       <c r="H363" s="14"/>
-      <c r="I363" s="22"/>
+      <c r="I363" s="21"/>
     </row>
     <row r="364">
-      <c r="C364" s="23"/>
+      <c r="C364" s="22"/>
       <c r="F364" s="9"/>
       <c r="G364" s="9"/>
       <c r="H364" s="14"/>
-      <c r="I364" s="22"/>
+      <c r="I364" s="21"/>
     </row>
     <row r="365">
-      <c r="C365" s="23"/>
+      <c r="C365" s="22"/>
       <c r="F365" s="9"/>
       <c r="G365" s="9"/>
       <c r="H365" s="14"/>
-      <c r="I365" s="22"/>
+      <c r="I365" s="21"/>
     </row>
     <row r="366">
-      <c r="C366" s="23"/>
+      <c r="C366" s="22"/>
       <c r="F366" s="9"/>
       <c r="G366" s="9"/>
       <c r="H366" s="14"/>
-      <c r="I366" s="22"/>
+      <c r="I366" s="21"/>
     </row>
     <row r="367">
-      <c r="C367" s="23"/>
+      <c r="C367" s="22"/>
       <c r="F367" s="9"/>
       <c r="G367" s="9"/>
       <c r="H367" s="14"/>
-      <c r="I367" s="22"/>
+      <c r="I367" s="21"/>
     </row>
     <row r="368">
-      <c r="C368" s="23"/>
+      <c r="C368" s="22"/>
       <c r="F368" s="9"/>
       <c r="G368" s="9"/>
       <c r="H368" s="14"/>
-      <c r="I368" s="22"/>
+      <c r="I368" s="21"/>
     </row>
     <row r="369">
-      <c r="C369" s="23"/>
+      <c r="C369" s="22"/>
       <c r="F369" s="9"/>
       <c r="G369" s="9"/>
       <c r="H369" s="14"/>
-      <c r="I369" s="22"/>
+      <c r="I369" s="21"/>
     </row>
     <row r="370">
-      <c r="C370" s="23"/>
+      <c r="C370" s="22"/>
       <c r="F370" s="9"/>
       <c r="G370" s="9"/>
       <c r="H370" s="14"/>
-      <c r="I370" s="22"/>
+      <c r="I370" s="21"/>
     </row>
     <row r="371">
-      <c r="C371" s="23"/>
+      <c r="C371" s="22"/>
       <c r="F371" s="9"/>
       <c r="G371" s="9"/>
       <c r="H371" s="14"/>
-      <c r="I371" s="22"/>
+      <c r="I371" s="21"/>
     </row>
     <row r="372">
-      <c r="C372" s="23"/>
+      <c r="C372" s="22"/>
       <c r="F372" s="9"/>
       <c r="G372" s="9"/>
       <c r="H372" s="14"/>
-      <c r="I372" s="22"/>
+      <c r="I372" s="21"/>
     </row>
     <row r="373">
-      <c r="C373" s="23"/>
+      <c r="C373" s="22"/>
       <c r="F373" s="9"/>
       <c r="G373" s="9"/>
       <c r="H373" s="14"/>
-      <c r="I373" s="22"/>
+      <c r="I373" s="21"/>
     </row>
     <row r="374">
-      <c r="C374" s="23"/>
+      <c r="C374" s="22"/>
       <c r="F374" s="9"/>
       <c r="G374" s="9"/>
       <c r="H374" s="14"/>
-      <c r="I374" s="22"/>
+      <c r="I374" s="21"/>
     </row>
     <row r="375">
-      <c r="C375" s="23"/>
+      <c r="C375" s="22"/>
       <c r="F375" s="9"/>
       <c r="G375" s="9"/>
       <c r="H375" s="14"/>
-      <c r="I375" s="22"/>
+      <c r="I375" s="21"/>
     </row>
     <row r="376">
-      <c r="C376" s="23"/>
+      <c r="C376" s="22"/>
       <c r="F376" s="9"/>
       <c r="G376" s="9"/>
       <c r="H376" s="14"/>
-      <c r="I376" s="22"/>
+      <c r="I376" s="21"/>
     </row>
     <row r="377">
-      <c r="C377" s="23"/>
+      <c r="C377" s="22"/>
       <c r="F377" s="9"/>
       <c r="G377" s="9"/>
       <c r="H377" s="14"/>
-      <c r="I377" s="22"/>
+      <c r="I377" s="21"/>
     </row>
     <row r="378">
-      <c r="C378" s="23"/>
+      <c r="C378" s="22"/>
       <c r="F378" s="9"/>
       <c r="G378" s="9"/>
       <c r="H378" s="14"/>
-      <c r="I378" s="22"/>
+      <c r="I378" s="21"/>
     </row>
     <row r="379">
-      <c r="C379" s="23"/>
+      <c r="C379" s="22"/>
       <c r="F379" s="9"/>
       <c r="G379" s="9"/>
       <c r="H379" s="14"/>
-      <c r="I379" s="22"/>
+      <c r="I379" s="21"/>
     </row>
     <row r="380">
-      <c r="C380" s="23"/>
+      <c r="C380" s="22"/>
       <c r="F380" s="9"/>
       <c r="G380" s="9"/>
       <c r="H380" s="14"/>
-      <c r="I380" s="22"/>
+      <c r="I380" s="21"/>
     </row>
     <row r="381">
-      <c r="C381" s="23"/>
+      <c r="C381" s="22"/>
       <c r="F381" s="9"/>
       <c r="G381" s="9"/>
       <c r="H381" s="14"/>
-      <c r="I381" s="22"/>
+      <c r="I381" s="21"/>
     </row>
     <row r="382">
-      <c r="C382" s="23"/>
+      <c r="C382" s="22"/>
       <c r="F382" s="9"/>
       <c r="G382" s="9"/>
       <c r="H382" s="14"/>
-      <c r="I382" s="22"/>
+      <c r="I382" s="21"/>
     </row>
     <row r="383">
-      <c r="C383" s="23"/>
+      <c r="C383" s="22"/>
       <c r="F383" s="9"/>
       <c r="G383" s="9"/>
       <c r="H383" s="14"/>
-      <c r="I383" s="22"/>
+      <c r="I383" s="21"/>
     </row>
     <row r="384">
-      <c r="C384" s="23"/>
+      <c r="C384" s="22"/>
       <c r="F384" s="9"/>
       <c r="G384" s="9"/>
       <c r="H384" s="14"/>
-      <c r="I384" s="22"/>
+      <c r="I384" s="21"/>
     </row>
     <row r="385">
-      <c r="C385" s="23"/>
+      <c r="C385" s="22"/>
       <c r="F385" s="9"/>
       <c r="G385" s="9"/>
       <c r="H385" s="14"/>
-      <c r="I385" s="22"/>
+      <c r="I385" s="21"/>
     </row>
     <row r="386">
-      <c r="C386" s="23"/>
+      <c r="C386" s="22"/>
       <c r="F386" s="9"/>
       <c r="G386" s="9"/>
       <c r="H386" s="14"/>
-      <c r="I386" s="22"/>
+      <c r="I386" s="21"/>
     </row>
     <row r="387">
-      <c r="C387" s="23"/>
+      <c r="C387" s="22"/>
       <c r="F387" s="9"/>
       <c r="G387" s="9"/>
       <c r="H387" s="14"/>
-      <c r="I387" s="22"/>
+      <c r="I387" s="21"/>
     </row>
     <row r="388">
-      <c r="C388" s="23"/>
+      <c r="C388" s="22"/>
       <c r="F388" s="9"/>
       <c r="G388" s="9"/>
       <c r="H388" s="14"/>
-      <c r="I388" s="22"/>
+      <c r="I388" s="21"/>
     </row>
     <row r="389">
-      <c r="C389" s="23"/>
+      <c r="C389" s="22"/>
       <c r="F389" s="9"/>
       <c r="G389" s="9"/>
       <c r="H389" s="14"/>
-      <c r="I389" s="22"/>
+      <c r="I389" s="21"/>
     </row>
     <row r="390">
-      <c r="C390" s="23"/>
+      <c r="C390" s="22"/>
       <c r="F390" s="9"/>
       <c r="G390" s="9"/>
       <c r="H390" s="14"/>
-      <c r="I390" s="22"/>
+      <c r="I390" s="21"/>
     </row>
     <row r="391">
-      <c r="C391" s="23"/>
+      <c r="C391" s="22"/>
       <c r="F391" s="9"/>
       <c r="G391" s="9"/>
       <c r="H391" s="14"/>
-      <c r="I391" s="22"/>
+      <c r="I391" s="21"/>
     </row>
     <row r="392">
-      <c r="C392" s="23"/>
+      <c r="C392" s="22"/>
       <c r="F392" s="9"/>
       <c r="G392" s="9"/>
       <c r="H392" s="14"/>
-      <c r="I392" s="22"/>
+      <c r="I392" s="21"/>
     </row>
     <row r="393">
-      <c r="C393" s="23"/>
+      <c r="C393" s="22"/>
       <c r="F393" s="9"/>
       <c r="G393" s="9"/>
       <c r="H393" s="14"/>
-      <c r="I393" s="22"/>
+      <c r="I393" s="21"/>
     </row>
     <row r="394">
-      <c r="C394" s="23"/>
+      <c r="C394" s="22"/>
       <c r="F394" s="9"/>
       <c r="G394" s="9"/>
       <c r="H394" s="14"/>
-      <c r="I394" s="22"/>
+      <c r="I394" s="21"/>
     </row>
     <row r="395">
-      <c r="C395" s="23"/>
+      <c r="C395" s="22"/>
       <c r="F395" s="9"/>
       <c r="G395" s="9"/>
       <c r="H395" s="14"/>
-      <c r="I395" s="22"/>
+      <c r="I395" s="21"/>
     </row>
     <row r="396">
-      <c r="C396" s="23"/>
+      <c r="C396" s="22"/>
       <c r="F396" s="9"/>
       <c r="G396" s="9"/>
       <c r="H396" s="14"/>
-      <c r="I396" s="22"/>
+      <c r="I396" s="21"/>
     </row>
     <row r="397">
-      <c r="C397" s="23"/>
+      <c r="C397" s="22"/>
       <c r="F397" s="9"/>
       <c r="G397" s="9"/>
       <c r="H397" s="14"/>
-      <c r="I397" s="22"/>
+      <c r="I397" s="21"/>
     </row>
     <row r="398">
-      <c r="C398" s="23"/>
+      <c r="C398" s="22"/>
       <c r="F398" s="9"/>
       <c r="G398" s="9"/>
       <c r="H398" s="14"/>
-      <c r="I398" s="22"/>
+      <c r="I398" s="21"/>
     </row>
     <row r="399">
-      <c r="C399" s="23"/>
+      <c r="C399" s="22"/>
       <c r="F399" s="9"/>
       <c r="G399" s="9"/>
       <c r="H399" s="14"/>
-      <c r="I399" s="22"/>
+      <c r="I399" s="21"/>
     </row>
     <row r="400">
-      <c r="C400" s="23"/>
+      <c r="C400" s="22"/>
       <c r="F400" s="9"/>
       <c r="G400" s="9"/>
       <c r="H400" s="14"/>
-      <c r="I400" s="22"/>
+      <c r="I400" s="21"/>
     </row>
     <row r="401">
-      <c r="C401" s="23"/>
+      <c r="C401" s="22"/>
       <c r="F401" s="9"/>
       <c r="G401" s="9"/>
       <c r="H401" s="14"/>
-      <c r="I401" s="22"/>
+      <c r="I401" s="21"/>
     </row>
     <row r="402">
-      <c r="C402" s="23"/>
+      <c r="C402" s="22"/>
       <c r="F402" s="9"/>
       <c r="G402" s="9"/>
       <c r="H402" s="14"/>
-      <c r="I402" s="22"/>
+      <c r="I402" s="21"/>
     </row>
     <row r="403">
-      <c r="C403" s="23"/>
+      <c r="C403" s="22"/>
       <c r="F403" s="9"/>
       <c r="G403" s="9"/>
       <c r="H403" s="14"/>
-      <c r="I403" s="22"/>
+      <c r="I403" s="21"/>
     </row>
     <row r="404">
-      <c r="C404" s="23"/>
+      <c r="C404" s="22"/>
       <c r="F404" s="9"/>
       <c r="G404" s="9"/>
       <c r="H404" s="14"/>
-      <c r="I404" s="22"/>
+      <c r="I404" s="21"/>
     </row>
     <row r="405">
-      <c r="C405" s="23"/>
+      <c r="C405" s="22"/>
       <c r="F405" s="9"/>
       <c r="G405" s="9"/>
       <c r="H405" s="14"/>
-      <c r="I405" s="22"/>
+      <c r="I405" s="21"/>
     </row>
     <row r="406">
-      <c r="C406" s="23"/>
+      <c r="C406" s="22"/>
       <c r="F406" s="9"/>
       <c r="G406" s="9"/>
       <c r="H406" s="14"/>
-      <c r="I406" s="22"/>
+      <c r="I406" s="21"/>
     </row>
     <row r="407">
-      <c r="C407" s="23"/>
+      <c r="C407" s="22"/>
       <c r="F407" s="9"/>
       <c r="G407" s="9"/>
       <c r="H407" s="14"/>
-      <c r="I407" s="22"/>
+      <c r="I407" s="21"/>
     </row>
     <row r="408">
-      <c r="C408" s="23"/>
+      <c r="C408" s="22"/>
       <c r="F408" s="9"/>
       <c r="G408" s="9"/>
       <c r="H408" s="14"/>
-      <c r="I408" s="22"/>
+      <c r="I408" s="21"/>
     </row>
     <row r="409">
-      <c r="C409" s="23"/>
+      <c r="C409" s="22"/>
       <c r="F409" s="9"/>
       <c r="G409" s="9"/>
       <c r="H409" s="14"/>
-      <c r="I409" s="22"/>
+      <c r="I409" s="21"/>
     </row>
     <row r="410">
-      <c r="C410" s="23"/>
+      <c r="C410" s="22"/>
       <c r="F410" s="9"/>
       <c r="G410" s="9"/>
       <c r="H410" s="14"/>
-      <c r="I410" s="22"/>
+      <c r="I410" s="21"/>
     </row>
     <row r="411">
-      <c r="C411" s="23"/>
+      <c r="C411" s="22"/>
       <c r="F411" s="9"/>
       <c r="G411" s="9"/>
       <c r="H411" s="14"/>
-      <c r="I411" s="22"/>
+      <c r="I411" s="21"/>
     </row>
     <row r="412">
-      <c r="C412" s="23"/>
+      <c r="C412" s="22"/>
       <c r="F412" s="9"/>
       <c r="G412" s="9"/>
       <c r="H412" s="14"/>
-      <c r="I412" s="22"/>
+      <c r="I412" s="21"/>
     </row>
     <row r="413">
-      <c r="C413" s="23"/>
+      <c r="C413" s="22"/>
       <c r="F413" s="9"/>
       <c r="G413" s="9"/>
       <c r="H413" s="14"/>
-      <c r="I413" s="22"/>
+      <c r="I413" s="21"/>
     </row>
     <row r="414">
-      <c r="C414" s="23"/>
+      <c r="C414" s="22"/>
       <c r="F414" s="9"/>
       <c r="G414" s="9"/>
       <c r="H414" s="14"/>
-      <c r="I414" s="22"/>
+      <c r="I414" s="21"/>
     </row>
     <row r="415">
-      <c r="C415" s="23"/>
+      <c r="C415" s="22"/>
       <c r="F415" s="9"/>
       <c r="G415" s="9"/>
       <c r="H415" s="14"/>
-      <c r="I415" s="22"/>
+      <c r="I415" s="21"/>
     </row>
     <row r="416">
-      <c r="C416" s="23"/>
+      <c r="C416" s="22"/>
       <c r="F416" s="9"/>
       <c r="G416" s="9"/>
       <c r="H416" s="14"/>
-      <c r="I416" s="22"/>
+      <c r="I416" s="21"/>
     </row>
     <row r="417">
-      <c r="C417" s="23"/>
+      <c r="C417" s="22"/>
       <c r="F417" s="9"/>
       <c r="G417" s="9"/>
       <c r="H417" s="14"/>
-      <c r="I417" s="22"/>
+      <c r="I417" s="21"/>
     </row>
     <row r="418">
-      <c r="C418" s="23"/>
+      <c r="C418" s="22"/>
       <c r="F418" s="9"/>
       <c r="G418" s="9"/>
       <c r="H418" s="14"/>
-      <c r="I418" s="22"/>
+      <c r="I418" s="21"/>
     </row>
     <row r="419">
-      <c r="C419" s="23"/>
+      <c r="C419" s="22"/>
       <c r="F419" s="9"/>
       <c r="G419" s="9"/>
       <c r="H419" s="14"/>
-      <c r="I419" s="22"/>
+      <c r="I419" s="21"/>
     </row>
     <row r="420">
-      <c r="C420" s="23"/>
+      <c r="C420" s="22"/>
       <c r="F420" s="9"/>
       <c r="G420" s="9"/>
       <c r="H420" s="14"/>
-      <c r="I420" s="22"/>
+      <c r="I420" s="21"/>
     </row>
     <row r="421">
-      <c r="C421" s="23"/>
+      <c r="C421" s="22"/>
       <c r="F421" s="9"/>
       <c r="G421" s="9"/>
       <c r="H421" s="14"/>
-      <c r="I421" s="22"/>
+      <c r="I421" s="21"/>
     </row>
     <row r="422">
-      <c r="C422" s="23"/>
+      <c r="C422" s="22"/>
       <c r="F422" s="9"/>
       <c r="G422" s="9"/>
       <c r="H422" s="14"/>
-      <c r="I422" s="22"/>
+      <c r="I422" s="21"/>
     </row>
     <row r="423">
-      <c r="C423" s="23"/>
+      <c r="C423" s="22"/>
       <c r="F423" s="9"/>
       <c r="G423" s="9"/>
       <c r="H423" s="14"/>
-      <c r="I423" s="22"/>
+      <c r="I423" s="21"/>
     </row>
     <row r="424">
-      <c r="C424" s="23"/>
+      <c r="C424" s="22"/>
       <c r="F424" s="9"/>
       <c r="G424" s="9"/>
       <c r="H424" s="14"/>
-      <c r="I424" s="22"/>
+      <c r="I424" s="21"/>
     </row>
     <row r="425">
-      <c r="C425" s="23"/>
+      <c r="C425" s="22"/>
       <c r="F425" s="9"/>
       <c r="G425" s="9"/>
       <c r="H425" s="14"/>
-      <c r="I425" s="22"/>
+      <c r="I425" s="21"/>
     </row>
     <row r="426">
-      <c r="C426" s="23"/>
+      <c r="C426" s="22"/>
       <c r="F426" s="9"/>
       <c r="G426" s="9"/>
       <c r="H426" s="14"/>
-      <c r="I426" s="22"/>
+      <c r="I426" s="21"/>
     </row>
     <row r="427">
-      <c r="C427" s="23"/>
+      <c r="C427" s="22"/>
       <c r="F427" s="9"/>
       <c r="G427" s="9"/>
       <c r="H427" s="14"/>
-      <c r="I427" s="22"/>
+      <c r="I427" s="21"/>
     </row>
     <row r="428">
-      <c r="C428" s="23"/>
+      <c r="C428" s="22"/>
       <c r="F428" s="9"/>
       <c r="G428" s="9"/>
       <c r="H428" s="14"/>
-      <c r="I428" s="22"/>
+      <c r="I428" s="21"/>
     </row>
     <row r="429">
-      <c r="C429" s="23"/>
+      <c r="C429" s="22"/>
       <c r="F429" s="9"/>
       <c r="G429" s="9"/>
       <c r="H429" s="14"/>
-      <c r="I429" s="22"/>
+      <c r="I429" s="21"/>
     </row>
     <row r="430">
-      <c r="C430" s="23"/>
+      <c r="C430" s="22"/>
       <c r="F430" s="9"/>
       <c r="G430" s="9"/>
       <c r="H430" s="14"/>
-      <c r="I430" s="22"/>
+      <c r="I430" s="21"/>
     </row>
     <row r="431">
-      <c r="C431" s="23"/>
+      <c r="C431" s="22"/>
       <c r="F431" s="9"/>
       <c r="G431" s="9"/>
       <c r="H431" s="14"/>
-      <c r="I431" s="22"/>
+      <c r="I431" s="21"/>
     </row>
     <row r="432">
-      <c r="C432" s="23"/>
+      <c r="C432" s="22"/>
       <c r="F432" s="9"/>
       <c r="G432" s="9"/>
       <c r="H432" s="14"/>
-      <c r="I432" s="22"/>
+      <c r="I432" s="21"/>
     </row>
     <row r="433">
-      <c r="C433" s="23"/>
+      <c r="C433" s="22"/>
       <c r="F433" s="9"/>
       <c r="G433" s="9"/>
       <c r="H433" s="14"/>
-      <c r="I433" s="22"/>
+      <c r="I433" s="21"/>
     </row>
     <row r="434">
-      <c r="C434" s="23"/>
+      <c r="C434" s="22"/>
       <c r="F434" s="9"/>
       <c r="G434" s="9"/>
       <c r="H434" s="14"/>
-      <c r="I434" s="22"/>
+      <c r="I434" s="21"/>
     </row>
     <row r="435">
-      <c r="C435" s="23"/>
+      <c r="C435" s="22"/>
       <c r="F435" s="9"/>
       <c r="G435" s="9"/>
       <c r="H435" s="14"/>
-      <c r="I435" s="22"/>
+      <c r="I435" s="21"/>
     </row>
     <row r="436">
-      <c r="C436" s="23"/>
+      <c r="C436" s="22"/>
       <c r="F436" s="9"/>
       <c r="G436" s="9"/>
       <c r="H436" s="14"/>
-      <c r="I436" s="22"/>
+      <c r="I436" s="21"/>
     </row>
     <row r="437">
-      <c r="C437" s="23"/>
+      <c r="C437" s="22"/>
       <c r="F437" s="9"/>
       <c r="G437" s="9"/>
       <c r="H437" s="14"/>
-      <c r="I437" s="22"/>
+      <c r="I437" s="21"/>
     </row>
     <row r="438">
-      <c r="C438" s="23"/>
+      <c r="C438" s="22"/>
       <c r="F438" s="9"/>
       <c r="G438" s="9"/>
       <c r="H438" s="14"/>
-      <c r="I438" s="22"/>
+      <c r="I438" s="21"/>
     </row>
     <row r="439">
-      <c r="C439" s="23"/>
+      <c r="C439" s="22"/>
       <c r="F439" s="9"/>
       <c r="G439" s="9"/>
       <c r="H439" s="14"/>
-      <c r="I439" s="22"/>
+      <c r="I439" s="21"/>
     </row>
     <row r="440">
-      <c r="C440" s="23"/>
+      <c r="C440" s="22"/>
       <c r="F440" s="9"/>
       <c r="G440" s="9"/>
       <c r="H440" s="14"/>
-      <c r="I440" s="22"/>
+      <c r="I440" s="21"/>
     </row>
     <row r="441">
-      <c r="C441" s="23"/>
+      <c r="C441" s="22"/>
       <c r="F441" s="9"/>
       <c r="G441" s="9"/>
       <c r="H441" s="14"/>
-      <c r="I441" s="22"/>
+      <c r="I441" s="21"/>
     </row>
     <row r="442">
-      <c r="C442" s="23"/>
+      <c r="C442" s="22"/>
       <c r="F442" s="9"/>
       <c r="G442" s="9"/>
       <c r="H442" s="14"/>
-      <c r="I442" s="22"/>
+      <c r="I442" s="21"/>
     </row>
     <row r="443">
-      <c r="C443" s="23"/>
+      <c r="C443" s="22"/>
       <c r="F443" s="9"/>
       <c r="G443" s="9"/>
       <c r="H443" s="14"/>
-      <c r="I443" s="22"/>
+      <c r="I443" s="21"/>
     </row>
     <row r="444">
-      <c r="C444" s="23"/>
+      <c r="C444" s="22"/>
       <c r="F444" s="9"/>
       <c r="G444" s="9"/>
       <c r="H444" s="14"/>
-      <c r="I444" s="22"/>
+      <c r="I444" s="21"/>
     </row>
     <row r="445">
-      <c r="C445" s="23"/>
+      <c r="C445" s="22"/>
       <c r="F445" s="9"/>
       <c r="G445" s="9"/>
       <c r="H445" s="14"/>
-      <c r="I445" s="22"/>
+      <c r="I445" s="21"/>
     </row>
     <row r="446">
-      <c r="C446" s="23"/>
+      <c r="C446" s="22"/>
       <c r="F446" s="9"/>
       <c r="G446" s="9"/>
       <c r="H446" s="14"/>
-      <c r="I446" s="22"/>
+      <c r="I446" s="21"/>
     </row>
     <row r="447">
-      <c r="C447" s="23"/>
+      <c r="C447" s="22"/>
       <c r="F447" s="9"/>
       <c r="G447" s="9"/>
       <c r="H447" s="14"/>
-      <c r="I447" s="22"/>
+      <c r="I447" s="21"/>
     </row>
     <row r="448">
-      <c r="C448" s="23"/>
+      <c r="C448" s="22"/>
       <c r="F448" s="9"/>
       <c r="G448" s="9"/>
       <c r="H448" s="14"/>
-      <c r="I448" s="22"/>
+      <c r="I448" s="21"/>
     </row>
     <row r="449">
-      <c r="C449" s="23"/>
+      <c r="C449" s="22"/>
       <c r="F449" s="9"/>
       <c r="G449" s="9"/>
       <c r="H449" s="14"/>
-      <c r="I449" s="22"/>
+      <c r="I449" s="21"/>
     </row>
     <row r="450">
-      <c r="C450" s="23"/>
+      <c r="C450" s="22"/>
       <c r="F450" s="9"/>
       <c r="G450" s="9"/>
       <c r="H450" s="14"/>
-      <c r="I450" s="22"/>
+      <c r="I450" s="21"/>
     </row>
     <row r="451">
-      <c r="C451" s="23"/>
+      <c r="C451" s="22"/>
       <c r="F451" s="9"/>
       <c r="G451" s="9"/>
       <c r="H451" s="14"/>
-      <c r="I451" s="22"/>
+      <c r="I451" s="21"/>
     </row>
     <row r="452">
-      <c r="C452" s="23"/>
+      <c r="C452" s="22"/>
       <c r="F452" s="9"/>
       <c r="G452" s="9"/>
       <c r="H452" s="14"/>
-      <c r="I452" s="22"/>
+      <c r="I452" s="21"/>
     </row>
     <row r="453">
-      <c r="C453" s="23"/>
+      <c r="C453" s="22"/>
       <c r="F453" s="9"/>
       <c r="G453" s="9"/>
       <c r="H453" s="14"/>
-      <c r="I453" s="22"/>
+      <c r="I453" s="21"/>
     </row>
     <row r="454">
-      <c r="C454" s="23"/>
+      <c r="C454" s="22"/>
       <c r="F454" s="9"/>
       <c r="G454" s="9"/>
       <c r="H454" s="14"/>
-      <c r="I454" s="22"/>
+      <c r="I454" s="21"/>
     </row>
     <row r="455">
-      <c r="C455" s="23"/>
+      <c r="C455" s="22"/>
       <c r="F455" s="9"/>
       <c r="G455" s="9"/>
       <c r="H455" s="14"/>
-      <c r="I455" s="22"/>
+      <c r="I455" s="21"/>
     </row>
     <row r="456">
-      <c r="C456" s="23"/>
+      <c r="C456" s="22"/>
       <c r="F456" s="9"/>
       <c r="G456" s="9"/>
       <c r="H456" s="14"/>
-      <c r="I456" s="22"/>
+      <c r="I456" s="21"/>
     </row>
     <row r="457">
-      <c r="C457" s="23"/>
+      <c r="C457" s="22"/>
       <c r="F457" s="9"/>
       <c r="G457" s="9"/>
       <c r="H457" s="14"/>
-      <c r="I457" s="22"/>
+      <c r="I457" s="21"/>
     </row>
     <row r="458">
-      <c r="C458" s="23"/>
+      <c r="C458" s="22"/>
       <c r="F458" s="9"/>
       <c r="G458" s="9"/>
       <c r="H458" s="14"/>
-      <c r="I458" s="22"/>
+      <c r="I458" s="21"/>
     </row>
     <row r="459">
-      <c r="C459" s="23"/>
+      <c r="C459" s="22"/>
       <c r="F459" s="9"/>
       <c r="G459" s="9"/>
       <c r="H459" s="14"/>
-      <c r="I459" s="22"/>
+      <c r="I459" s="21"/>
     </row>
     <row r="460">
-      <c r="C460" s="23"/>
+      <c r="C460" s="22"/>
       <c r="F460" s="9"/>
       <c r="G460" s="9"/>
       <c r="H460" s="14"/>
-      <c r="I460" s="22"/>
+      <c r="I460" s="21"/>
     </row>
     <row r="461">
-      <c r="C461" s="23"/>
+      <c r="C461" s="22"/>
       <c r="F461" s="9"/>
       <c r="G461" s="9"/>
       <c r="H461" s="14"/>
-      <c r="I461" s="22"/>
+      <c r="I461" s="21"/>
     </row>
     <row r="462">
-      <c r="C462" s="23"/>
+      <c r="C462" s="22"/>
       <c r="F462" s="9"/>
       <c r="G462" s="9"/>
       <c r="H462" s="14"/>
-      <c r="I462" s="22"/>
+      <c r="I462" s="21"/>
     </row>
     <row r="463">
-      <c r="C463" s="23"/>
+      <c r="C463" s="22"/>
       <c r="F463" s="9"/>
       <c r="G463" s="9"/>
       <c r="H463" s="14"/>
-      <c r="I463" s="22"/>
+      <c r="I463" s="21"/>
     </row>
     <row r="464">
-      <c r="C464" s="23"/>
+      <c r="C464" s="22"/>
       <c r="F464" s="9"/>
       <c r="G464" s="9"/>
       <c r="H464" s="14"/>
-      <c r="I464" s="22"/>
+      <c r="I464" s="21"/>
     </row>
     <row r="465">
-      <c r="C465" s="23"/>
+      <c r="C465" s="22"/>
       <c r="F465" s="9"/>
       <c r="G465" s="9"/>
       <c r="H465" s="14"/>
-      <c r="I465" s="22"/>
+      <c r="I465" s="21"/>
     </row>
     <row r="466">
-      <c r="C466" s="23"/>
+      <c r="C466" s="22"/>
       <c r="F466" s="9"/>
       <c r="G466" s="9"/>
       <c r="H466" s="14"/>
-      <c r="I466" s="22"/>
+      <c r="I466" s="21"/>
     </row>
     <row r="467">
-      <c r="C467" s="23"/>
+      <c r="C467" s="22"/>
       <c r="F467" s="9"/>
       <c r="G467" s="9"/>
       <c r="H467" s="14"/>
-      <c r="I467" s="22"/>
+      <c r="I467" s="21"/>
     </row>
     <row r="468">
-      <c r="C468" s="23"/>
+      <c r="C468" s="22"/>
       <c r="F468" s="9"/>
       <c r="G468" s="9"/>
       <c r="H468" s="14"/>
-      <c r="I468" s="22"/>
+      <c r="I468" s="21"/>
     </row>
     <row r="469">
-      <c r="C469" s="23"/>
+      <c r="C469" s="22"/>
       <c r="F469" s="9"/>
       <c r="G469" s="9"/>
       <c r="H469" s="14"/>
-      <c r="I469" s="22"/>
+      <c r="I469" s="21"/>
     </row>
     <row r="470">
-      <c r="C470" s="23"/>
+      <c r="C470" s="22"/>
       <c r="F470" s="9"/>
       <c r="G470" s="9"/>
       <c r="H470" s="14"/>
-      <c r="I470" s="22"/>
+      <c r="I470" s="21"/>
     </row>
     <row r="471">
-      <c r="C471" s="23"/>
+      <c r="C471" s="22"/>
       <c r="F471" s="9"/>
       <c r="G471" s="9"/>
       <c r="H471" s="14"/>
-      <c r="I471" s="22"/>
+      <c r="I471" s="21"/>
     </row>
     <row r="472">
-      <c r="C472" s="23"/>
+      <c r="C472" s="22"/>
       <c r="F472" s="9"/>
       <c r="G472" s="9"/>
       <c r="H472" s="14"/>
-      <c r="I472" s="22"/>
+      <c r="I472" s="21"/>
     </row>
     <row r="473">
-      <c r="C473" s="23"/>
+      <c r="C473" s="22"/>
       <c r="F473" s="9"/>
       <c r="G473" s="9"/>
       <c r="H473" s="14"/>
-      <c r="I473" s="22"/>
+      <c r="I473" s="21"/>
     </row>
     <row r="474">
-      <c r="C474" s="23"/>
+      <c r="C474" s="22"/>
       <c r="F474" s="9"/>
       <c r="G474" s="9"/>
       <c r="H474" s="14"/>
-      <c r="I474" s="22"/>
+      <c r="I474" s="21"/>
     </row>
     <row r="475">
-      <c r="C475" s="23"/>
+      <c r="C475" s="22"/>
       <c r="F475" s="9"/>
       <c r="G475" s="9"/>
       <c r="H475" s="14"/>
-      <c r="I475" s="22"/>
+      <c r="I475" s="21"/>
     </row>
     <row r="476">
-      <c r="C476" s="23"/>
+      <c r="C476" s="22"/>
       <c r="F476" s="9"/>
       <c r="G476" s="9"/>
       <c r="H476" s="14"/>
-      <c r="I476" s="22"/>
+      <c r="I476" s="21"/>
     </row>
     <row r="477">
-      <c r="C477" s="23"/>
+      <c r="C477" s="22"/>
       <c r="F477" s="9"/>
       <c r="G477" s="9"/>
       <c r="H477" s="14"/>
-      <c r="I477" s="22"/>
+      <c r="I477" s="21"/>
     </row>
     <row r="478">
-      <c r="C478" s="23"/>
+      <c r="C478" s="22"/>
       <c r="F478" s="9"/>
       <c r="G478" s="9"/>
       <c r="H478" s="14"/>
-      <c r="I478" s="22"/>
+      <c r="I478" s="21"/>
     </row>
     <row r="479">
-      <c r="C479" s="23"/>
+      <c r="C479" s="22"/>
       <c r="F479" s="9"/>
       <c r="G479" s="9"/>
       <c r="H479" s="14"/>
-      <c r="I479" s="22"/>
+      <c r="I479" s="21"/>
     </row>
     <row r="480">
-      <c r="C480" s="23"/>
+      <c r="C480" s="22"/>
       <c r="F480" s="9"/>
       <c r="G480" s="9"/>
       <c r="H480" s="14"/>
-      <c r="I480" s="22"/>
+      <c r="I480" s="21"/>
     </row>
     <row r="481">
-      <c r="C481" s="23"/>
+      <c r="C481" s="22"/>
       <c r="F481" s="9"/>
       <c r="G481" s="9"/>
       <c r="H481" s="14"/>
-      <c r="I481" s="22"/>
+      <c r="I481" s="21"/>
     </row>
     <row r="482">
-      <c r="C482" s="23"/>
+      <c r="C482" s="22"/>
       <c r="F482" s="9"/>
       <c r="G482" s="9"/>
       <c r="H482" s="14"/>
-      <c r="I482" s="22"/>
+      <c r="I482" s="21"/>
     </row>
     <row r="483">
-      <c r="C483" s="23"/>
+      <c r="C483" s="22"/>
       <c r="F483" s="9"/>
       <c r="G483" s="9"/>
       <c r="H483" s="14"/>
-      <c r="I483" s="22"/>
+      <c r="I483" s="21"/>
     </row>
     <row r="484">
-      <c r="C484" s="23"/>
+      <c r="C484" s="22"/>
       <c r="F484" s="9"/>
       <c r="G484" s="9"/>
       <c r="H484" s="14"/>
-      <c r="I484" s="22"/>
+      <c r="I484" s="21"/>
     </row>
     <row r="485">
-      <c r="C485" s="23"/>
+      <c r="C485" s="22"/>
       <c r="F485" s="9"/>
       <c r="G485" s="9"/>
       <c r="H485" s="14"/>
-      <c r="I485" s="22"/>
+      <c r="I485" s="21"/>
     </row>
     <row r="486">
-      <c r="C486" s="23"/>
+      <c r="C486" s="22"/>
       <c r="F486" s="9"/>
       <c r="G486" s="9"/>
       <c r="H486" s="14"/>
-      <c r="I486" s="22"/>
+      <c r="I486" s="21"/>
     </row>
     <row r="487">
-      <c r="C487" s="23"/>
+      <c r="C487" s="22"/>
       <c r="F487" s="9"/>
       <c r="G487" s="9"/>
       <c r="H487" s="14"/>
-      <c r="I487" s="22"/>
+      <c r="I487" s="21"/>
     </row>
     <row r="488">
-      <c r="C488" s="23"/>
+      <c r="C488" s="22"/>
       <c r="F488" s="9"/>
       <c r="G488" s="9"/>
       <c r="H488" s="14"/>
-      <c r="I488" s="22"/>
+      <c r="I488" s="21"/>
     </row>
     <row r="489">
-      <c r="C489" s="23"/>
+      <c r="C489" s="22"/>
       <c r="F489" s="9"/>
       <c r="G489" s="9"/>
       <c r="H489" s="14"/>
-      <c r="I489" s="22"/>
+      <c r="I489" s="21"/>
     </row>
     <row r="490">
-      <c r="C490" s="23"/>
+      <c r="C490" s="22"/>
       <c r="F490" s="9"/>
       <c r="G490" s="9"/>
       <c r="H490" s="14"/>
-      <c r="I490" s="22"/>
+      <c r="I490" s="21"/>
     </row>
     <row r="491">
-      <c r="C491" s="23"/>
+      <c r="C491" s="22"/>
       <c r="F491" s="9"/>
       <c r="G491" s="9"/>
       <c r="H491" s="14"/>
-      <c r="I491" s="22"/>
+      <c r="I491" s="21"/>
     </row>
     <row r="492">
-      <c r="C492" s="23"/>
+      <c r="C492" s="22"/>
       <c r="F492" s="9"/>
       <c r="G492" s="9"/>
       <c r="H492" s="14"/>
-      <c r="I492" s="22"/>
+      <c r="I492" s="21"/>
     </row>
     <row r="493">
-      <c r="C493" s="23"/>
+      <c r="C493" s="22"/>
       <c r="F493" s="9"/>
       <c r="G493" s="9"/>
       <c r="H493" s="14"/>
-      <c r="I493" s="22"/>
+      <c r="I493" s="21"/>
     </row>
     <row r="494">
-      <c r="C494" s="23"/>
+      <c r="C494" s="22"/>
       <c r="F494" s="9"/>
       <c r="G494" s="9"/>
       <c r="H494" s="14"/>
-      <c r="I494" s="22"/>
+      <c r="I494" s="21"/>
     </row>
     <row r="495">
-      <c r="C495" s="23"/>
+      <c r="C495" s="22"/>
       <c r="F495" s="9"/>
       <c r="G495" s="9"/>
       <c r="H495" s="14"/>
-      <c r="I495" s="22"/>
+      <c r="I495" s="21"/>
     </row>
     <row r="496">
-      <c r="C496" s="23"/>
+      <c r="C496" s="22"/>
       <c r="F496" s="9"/>
       <c r="G496" s="9"/>
       <c r="H496" s="14"/>
-      <c r="I496" s="22"/>
+      <c r="I496" s="21"/>
     </row>
     <row r="497">
-      <c r="C497" s="23"/>
+      <c r="C497" s="22"/>
       <c r="F497" s="9"/>
       <c r="G497" s="9"/>
       <c r="H497" s="14"/>
-      <c r="I497" s="22"/>
+      <c r="I497" s="21"/>
     </row>
     <row r="498">
-      <c r="C498" s="23"/>
+      <c r="C498" s="22"/>
       <c r="F498" s="9"/>
       <c r="G498" s="9"/>
       <c r="H498" s="14"/>
-      <c r="I498" s="22"/>
+      <c r="I498" s="21"/>
     </row>
     <row r="499">
-      <c r="C499" s="23"/>
+      <c r="C499" s="22"/>
       <c r="F499" s="9"/>
       <c r="G499" s="9"/>
       <c r="H499" s="14"/>
-      <c r="I499" s="22"/>
+      <c r="I499" s="21"/>
     </row>
     <row r="500">
-      <c r="C500" s="23"/>
+      <c r="C500" s="22"/>
       <c r="F500" s="9"/>
       <c r="G500" s="9"/>
       <c r="H500" s="14"/>
-      <c r="I500" s="22"/>
+      <c r="I500" s="21"/>
     </row>
     <row r="501">
-      <c r="C501" s="23"/>
+      <c r="C501" s="22"/>
       <c r="F501" s="9"/>
       <c r="G501" s="9"/>
       <c r="H501" s="14"/>
-      <c r="I501" s="22"/>
+      <c r="I501" s="21"/>
     </row>
     <row r="502">
-      <c r="C502" s="23"/>
+      <c r="C502" s="22"/>
       <c r="F502" s="9"/>
       <c r="G502" s="9"/>
       <c r="H502" s="14"/>
-      <c r="I502" s="22"/>
+      <c r="I502" s="21"/>
     </row>
     <row r="503">
-      <c r="C503" s="23"/>
+      <c r="C503" s="22"/>
       <c r="F503" s="9"/>
       <c r="G503" s="9"/>
       <c r="H503" s="14"/>
-      <c r="I503" s="22"/>
+      <c r="I503" s="21"/>
     </row>
     <row r="504">
-      <c r="C504" s="23"/>
+      <c r="C504" s="22"/>
       <c r="F504" s="9"/>
       <c r="G504" s="9"/>
       <c r="H504" s="14"/>
-      <c r="I504" s="22"/>
+      <c r="I504" s="21"/>
     </row>
     <row r="505">
-      <c r="C505" s="23"/>
+      <c r="C505" s="22"/>
       <c r="F505" s="9"/>
       <c r="G505" s="9"/>
       <c r="H505" s="14"/>
-      <c r="I505" s="22"/>
+      <c r="I505" s="21"/>
     </row>
     <row r="506">
-      <c r="C506" s="23"/>
+      <c r="C506" s="22"/>
       <c r="F506" s="9"/>
       <c r="G506" s="9"/>
       <c r="H506" s="14"/>
-      <c r="I506" s="22"/>
+      <c r="I506" s="21"/>
     </row>
     <row r="507">
-      <c r="C507" s="23"/>
+      <c r="C507" s="22"/>
       <c r="F507" s="9"/>
       <c r="G507" s="9"/>
       <c r="H507" s="14"/>
-      <c r="I507" s="22"/>
+      <c r="I507" s="21"/>
     </row>
     <row r="508">
-      <c r="C508" s="23"/>
+      <c r="C508" s="22"/>
       <c r="F508" s="9"/>
       <c r="G508" s="9"/>
       <c r="H508" s="14"/>
-      <c r="I508" s="22"/>
+      <c r="I508" s="21"/>
     </row>
     <row r="509">
-      <c r="C509" s="23"/>
+      <c r="C509" s="22"/>
       <c r="F509" s="9"/>
       <c r="G509" s="9"/>
       <c r="H509" s="14"/>
-      <c r="I509" s="22"/>
+      <c r="I509" s="21"/>
     </row>
     <row r="510">
-      <c r="C510" s="23"/>
+      <c r="C510" s="22"/>
       <c r="F510" s="9"/>
       <c r="G510" s="9"/>
       <c r="H510" s="14"/>
-      <c r="I510" s="22"/>
+      <c r="I510" s="21"/>
     </row>
     <row r="511">
-      <c r="C511" s="23"/>
+      <c r="C511" s="22"/>
       <c r="F511" s="9"/>
       <c r="G511" s="9"/>
       <c r="H511" s="14"/>
-      <c r="I511" s="22"/>
+      <c r="I511" s="21"/>
     </row>
     <row r="512">
-      <c r="C512" s="23"/>
+      <c r="C512" s="22"/>
       <c r="F512" s="9"/>
       <c r="G512" s="9"/>
       <c r="H512" s="14"/>
-      <c r="I512" s="22"/>
+      <c r="I512" s="21"/>
     </row>
     <row r="513">
-      <c r="C513" s="23"/>
+      <c r="C513" s="22"/>
       <c r="F513" s="9"/>
       <c r="G513" s="9"/>
       <c r="H513" s="14"/>
-      <c r="I513" s="22"/>
+      <c r="I513" s="21"/>
     </row>
     <row r="514">
-      <c r="C514" s="23"/>
+      <c r="C514" s="22"/>
       <c r="F514" s="9"/>
       <c r="G514" s="9"/>
       <c r="H514" s="14"/>
-      <c r="I514" s="22"/>
+      <c r="I514" s="21"/>
     </row>
     <row r="515">
-      <c r="C515" s="23"/>
+      <c r="C515" s="22"/>
       <c r="F515" s="9"/>
       <c r="G515" s="9"/>
       <c r="H515" s="14"/>
-      <c r="I515" s="22"/>
+      <c r="I515" s="21"/>
     </row>
     <row r="516">
-      <c r="C516" s="23"/>
+      <c r="C516" s="22"/>
       <c r="F516" s="9"/>
       <c r="G516" s="9"/>
       <c r="H516" s="14"/>
-      <c r="I516" s="22"/>
+      <c r="I516" s="21"/>
     </row>
     <row r="517">
-      <c r="C517" s="23"/>
+      <c r="C517" s="22"/>
       <c r="F517" s="9"/>
       <c r="G517" s="9"/>
       <c r="H517" s="14"/>
-      <c r="I517" s="22"/>
+      <c r="I517" s="21"/>
     </row>
     <row r="518">
-      <c r="C518" s="23"/>
+      <c r="C518" s="22"/>
       <c r="F518" s="9"/>
       <c r="G518" s="9"/>
       <c r="H518" s="14"/>
-      <c r="I518" s="22"/>
+      <c r="I518" s="21"/>
     </row>
     <row r="519">
-      <c r="C519" s="23"/>
+      <c r="C519" s="22"/>
       <c r="F519" s="9"/>
       <c r="G519" s="9"/>
       <c r="H519" s="14"/>
-      <c r="I519" s="22"/>
+      <c r="I519" s="21"/>
     </row>
     <row r="520">
-      <c r="C520" s="23"/>
+      <c r="C520" s="22"/>
       <c r="F520" s="9"/>
       <c r="G520" s="9"/>
       <c r="H520" s="14"/>
-      <c r="I520" s="22"/>
+      <c r="I520" s="21"/>
     </row>
     <row r="521">
-      <c r="C521" s="23"/>
+      <c r="C521" s="22"/>
       <c r="F521" s="9"/>
       <c r="G521" s="9"/>
       <c r="H521" s="14"/>
-      <c r="I521" s="22"/>
+      <c r="I521" s="21"/>
     </row>
     <row r="522">
-      <c r="C522" s="23"/>
+      <c r="C522" s="22"/>
       <c r="F522" s="9"/>
       <c r="G522" s="9"/>
       <c r="H522" s="14"/>
-      <c r="I522" s="22"/>
+      <c r="I522" s="21"/>
     </row>
     <row r="523">
-      <c r="C523" s="23"/>
+      <c r="C523" s="22"/>
       <c r="F523" s="9"/>
       <c r="G523" s="9"/>
       <c r="H523" s="14"/>
-      <c r="I523" s="22"/>
+      <c r="I523" s="21"/>
     </row>
     <row r="524">
-      <c r="C524" s="23"/>
+      <c r="C524" s="22"/>
       <c r="F524" s="9"/>
       <c r="G524" s="9"/>
       <c r="H524" s="14"/>
-      <c r="I524" s="22"/>
+      <c r="I524" s="21"/>
     </row>
     <row r="525">
-      <c r="C525" s="23"/>
+      <c r="C525" s="22"/>
       <c r="F525" s="9"/>
       <c r="G525" s="9"/>
       <c r="H525" s="14"/>
-      <c r="I525" s="22"/>
+      <c r="I525" s="21"/>
     </row>
     <row r="526">
-      <c r="C526" s="23"/>
+      <c r="C526" s="22"/>
       <c r="F526" s="9"/>
       <c r="G526" s="9"/>
       <c r="H526" s="14"/>
-      <c r="I526" s="22"/>
+      <c r="I526" s="21"/>
     </row>
     <row r="527">
-      <c r="C527" s="23"/>
+      <c r="C527" s="22"/>
       <c r="F527" s="9"/>
       <c r="G527" s="9"/>
       <c r="H527" s="14"/>
-      <c r="I527" s="22"/>
+      <c r="I527" s="21"/>
     </row>
     <row r="528">
-      <c r="C528" s="23"/>
+      <c r="C528" s="22"/>
       <c r="F528" s="9"/>
       <c r="G528" s="9"/>
       <c r="H528" s="14"/>
-      <c r="I528" s="22"/>
+      <c r="I528" s="21"/>
     </row>
     <row r="529">
-      <c r="C529" s="23"/>
+      <c r="C529" s="22"/>
       <c r="F529" s="9"/>
       <c r="G529" s="9"/>
       <c r="H529" s="14"/>
-      <c r="I529" s="22"/>
+      <c r="I529" s="21"/>
     </row>
     <row r="530">
-      <c r="C530" s="23"/>
+      <c r="C530" s="22"/>
       <c r="F530" s="9"/>
       <c r="G530" s="9"/>
       <c r="H530" s="14"/>
-      <c r="I530" s="22"/>
+      <c r="I530" s="21"/>
     </row>
     <row r="531">
-      <c r="C531" s="23"/>
+      <c r="C531" s="22"/>
       <c r="F531" s="9"/>
       <c r="G531" s="9"/>
       <c r="H531" s="14"/>
-      <c r="I531" s="22"/>
+      <c r="I531" s="21"/>
     </row>
     <row r="532">
-      <c r="C532" s="23"/>
+      <c r="C532" s="22"/>
       <c r="F532" s="9"/>
       <c r="G532" s="9"/>
       <c r="H532" s="14"/>
-      <c r="I532" s="22"/>
+      <c r="I532" s="21"/>
     </row>
     <row r="533">
-      <c r="C533" s="23"/>
+      <c r="C533" s="22"/>
       <c r="F533" s="9"/>
       <c r="G533" s="9"/>
       <c r="H533" s="14"/>
-      <c r="I533" s="22"/>
+      <c r="I533" s="21"/>
     </row>
     <row r="534">
-      <c r="C534" s="23"/>
+      <c r="C534" s="22"/>
       <c r="F534" s="9"/>
       <c r="G534" s="9"/>
       <c r="H534" s="14"/>
-      <c r="I534" s="22"/>
+      <c r="I534" s="21"/>
     </row>
     <row r="535">
-      <c r="C535" s="23"/>
+      <c r="C535" s="22"/>
       <c r="F535" s="9"/>
       <c r="G535" s="9"/>
       <c r="H535" s="14"/>
-      <c r="I535" s="22"/>
+      <c r="I535" s="21"/>
     </row>
     <row r="536">
-      <c r="C536" s="23"/>
+      <c r="C536" s="22"/>
       <c r="F536" s="9"/>
       <c r="G536" s="9"/>
       <c r="H536" s="14"/>
-      <c r="I536" s="22"/>
+      <c r="I536" s="21"/>
     </row>
     <row r="537">
-      <c r="C537" s="23"/>
+      <c r="C537" s="22"/>
       <c r="F537" s="9"/>
       <c r="G537" s="9"/>
       <c r="H537" s="14"/>
-      <c r="I537" s="22"/>
+      <c r="I537" s="21"/>
     </row>
     <row r="538">
-      <c r="C538" s="23"/>
+      <c r="C538" s="22"/>
       <c r="F538" s="9"/>
       <c r="G538" s="9"/>
       <c r="H538" s="14"/>
-      <c r="I538" s="22"/>
+      <c r="I538" s="21"/>
     </row>
     <row r="539">
-      <c r="C539" s="23"/>
+      <c r="C539" s="22"/>
       <c r="F539" s="9"/>
       <c r="G539" s="9"/>
       <c r="H539" s="14"/>
-      <c r="I539" s="22"/>
+      <c r="I539" s="21"/>
     </row>
     <row r="540">
-      <c r="C540" s="23"/>
+      <c r="C540" s="22"/>
       <c r="F540" s="9"/>
       <c r="G540" s="9"/>
       <c r="H540" s="14"/>
-      <c r="I540" s="22"/>
+      <c r="I540" s="21"/>
     </row>
     <row r="541">
-      <c r="C541" s="23"/>
+      <c r="C541" s="22"/>
       <c r="F541" s="9"/>
       <c r="G541" s="9"/>
       <c r="H541" s="14"/>
-      <c r="I541" s="22"/>
+      <c r="I541" s="21"/>
     </row>
     <row r="542">
-      <c r="C542" s="23"/>
+      <c r="C542" s="22"/>
       <c r="F542" s="9"/>
       <c r="G542" s="9"/>
       <c r="H542" s="14"/>
-      <c r="I542" s="22"/>
+      <c r="I542" s="21"/>
     </row>
     <row r="543">
-      <c r="C543" s="23"/>
+      <c r="C543" s="22"/>
       <c r="F543" s="9"/>
       <c r="G543" s="9"/>
       <c r="H543" s="14"/>
-      <c r="I543" s="22"/>
+      <c r="I543" s="21"/>
     </row>
     <row r="544">
-      <c r="C544" s="23"/>
+      <c r="C544" s="22"/>
       <c r="F544" s="9"/>
       <c r="G544" s="9"/>
       <c r="H544" s="14"/>
-      <c r="I544" s="22"/>
+      <c r="I544" s="21"/>
     </row>
     <row r="545">
-      <c r="C545" s="23"/>
+      <c r="C545" s="22"/>
       <c r="F545" s="9"/>
       <c r="G545" s="9"/>
       <c r="H545" s="14"/>
-      <c r="I545" s="22"/>
+      <c r="I545" s="21"/>
     </row>
     <row r="546">
-      <c r="C546" s="23"/>
+      <c r="C546" s="22"/>
       <c r="F546" s="9"/>
       <c r="G546" s="9"/>
       <c r="H546" s="14"/>
-      <c r="I546" s="22"/>
+      <c r="I546" s="21"/>
     </row>
     <row r="547">
-      <c r="C547" s="23"/>
+      <c r="C547" s="22"/>
       <c r="F547" s="9"/>
       <c r="G547" s="9"/>
       <c r="H547" s="14"/>
-      <c r="I547" s="22"/>
+      <c r="I547" s="21"/>
     </row>
     <row r="548">
-      <c r="C548" s="23"/>
+      <c r="C548" s="22"/>
       <c r="F548" s="9"/>
       <c r="G548" s="9"/>
       <c r="H548" s="14"/>
-      <c r="I548" s="22"/>
+      <c r="I548" s="21"/>
     </row>
     <row r="549">
-      <c r="C549" s="23"/>
+      <c r="C549" s="22"/>
       <c r="F549" s="9"/>
       <c r="G549" s="9"/>
       <c r="H549" s="14"/>
-      <c r="I549" s="22"/>
+      <c r="I549" s="21"/>
     </row>
     <row r="550">
-      <c r="C550" s="23"/>
+      <c r="C550" s="22"/>
       <c r="F550" s="9"/>
       <c r="G550" s="9"/>
       <c r="H550" s="14"/>
-      <c r="I550" s="22"/>
+      <c r="I550" s="21"/>
     </row>
     <row r="551">
-      <c r="C551" s="23"/>
+      <c r="C551" s="22"/>
       <c r="F551" s="9"/>
       <c r="G551" s="9"/>
       <c r="H551" s="14"/>
-      <c r="I551" s="22"/>
+      <c r="I551" s="21"/>
     </row>
     <row r="552">
-      <c r="C552" s="23"/>
+      <c r="C552" s="22"/>
       <c r="F552" s="9"/>
       <c r="G552" s="9"/>
       <c r="H552" s="14"/>
-      <c r="I552" s="22"/>
+      <c r="I552" s="21"/>
     </row>
     <row r="553">
-      <c r="C553" s="23"/>
+      <c r="C553" s="22"/>
       <c r="F553" s="9"/>
       <c r="G553" s="9"/>
       <c r="H553" s="14"/>
-      <c r="I553" s="22"/>
+      <c r="I553" s="21"/>
     </row>
     <row r="554">
-      <c r="C554" s="23"/>
+      <c r="C554" s="22"/>
       <c r="F554" s="9"/>
       <c r="G554" s="9"/>
       <c r="H554" s="14"/>
-      <c r="I554" s="22"/>
+      <c r="I554" s="21"/>
     </row>
     <row r="555">
-      <c r="C555" s="23"/>
+      <c r="C555" s="22"/>
       <c r="F555" s="9"/>
       <c r="G555" s="9"/>
       <c r="H555" s="14"/>
-      <c r="I555" s="22"/>
+      <c r="I555" s="21"/>
     </row>
     <row r="556">
-      <c r="C556" s="23"/>
+      <c r="C556" s="22"/>
       <c r="F556" s="9"/>
       <c r="G556" s="9"/>
       <c r="H556" s="14"/>
-      <c r="I556" s="22"/>
+      <c r="I556" s="21"/>
     </row>
     <row r="557">
-      <c r="C557" s="23"/>
+      <c r="C557" s="22"/>
       <c r="F557" s="9"/>
       <c r="G557" s="9"/>
       <c r="H557" s="14"/>
-      <c r="I557" s="22"/>
+      <c r="I557" s="21"/>
     </row>
     <row r="558">
-      <c r="C558" s="23"/>
+      <c r="C558" s="22"/>
       <c r="F558" s="9"/>
       <c r="G558" s="9"/>
       <c r="H558" s="14"/>
-      <c r="I558" s="22"/>
+      <c r="I558" s="21"/>
     </row>
     <row r="559">
-      <c r="C559" s="23"/>
+      <c r="C559" s="22"/>
       <c r="F559" s="9"/>
       <c r="G559" s="9"/>
       <c r="H559" s="14"/>
-      <c r="I559" s="22"/>
+      <c r="I559" s="21"/>
     </row>
     <row r="560">
-      <c r="C560" s="23"/>
+      <c r="C560" s="22"/>
       <c r="F560" s="9"/>
       <c r="G560" s="9"/>
       <c r="H560" s="14"/>
-      <c r="I560" s="22"/>
+      <c r="I560" s="21"/>
     </row>
     <row r="561">
-      <c r="C561" s="23"/>
+      <c r="C561" s="22"/>
       <c r="F561" s="9"/>
       <c r="G561" s="9"/>
       <c r="H561" s="14"/>
-      <c r="I561" s="22"/>
+      <c r="I561" s="21"/>
     </row>
     <row r="562">
-      <c r="C562" s="23"/>
+      <c r="C562" s="22"/>
       <c r="F562" s="9"/>
       <c r="G562" s="9"/>
       <c r="H562" s="14"/>
-      <c r="I562" s="22"/>
+      <c r="I562" s="21"/>
     </row>
     <row r="563">
-      <c r="C563" s="23"/>
+      <c r="C563" s="22"/>
       <c r="F563" s="9"/>
       <c r="G563" s="9"/>
       <c r="H563" s="14"/>
-      <c r="I563" s="22"/>
+      <c r="I563" s="21"/>
     </row>
     <row r="564">
-      <c r="C564" s="23"/>
+      <c r="C564" s="22"/>
       <c r="F564" s="9"/>
       <c r="G564" s="9"/>
       <c r="H564" s="14"/>
-      <c r="I564" s="22"/>
+      <c r="I564" s="21"/>
     </row>
     <row r="565">
-      <c r="C565" s="23"/>
+      <c r="C565" s="22"/>
       <c r="F565" s="9"/>
       <c r="G565" s="9"/>
       <c r="H565" s="14"/>
-      <c r="I565" s="22"/>
+      <c r="I565" s="21"/>
     </row>
     <row r="566">
-      <c r="C566" s="23"/>
+      <c r="C566" s="22"/>
       <c r="F566" s="9"/>
       <c r="G566" s="9"/>
       <c r="H566" s="14"/>
-      <c r="I566" s="22"/>
+      <c r="I566" s="21"/>
     </row>
     <row r="567">
-      <c r="C567" s="23"/>
+      <c r="C567" s="22"/>
       <c r="F567" s="9"/>
       <c r="G567" s="9"/>
       <c r="H567" s="14"/>
-      <c r="I567" s="22"/>
+      <c r="I567" s="21"/>
     </row>
     <row r="568">
-      <c r="C568" s="23"/>
+      <c r="C568" s="22"/>
       <c r="F568" s="9"/>
       <c r="G568" s="9"/>
       <c r="H568" s="14"/>
-      <c r="I568" s="22"/>
+      <c r="I568" s="21"/>
     </row>
     <row r="569">
-      <c r="C569" s="23"/>
+      <c r="C569" s="22"/>
       <c r="F569" s="9"/>
       <c r="G569" s="9"/>
       <c r="H569" s="14"/>
-      <c r="I569" s="22"/>
+      <c r="I569" s="21"/>
     </row>
     <row r="570">
-      <c r="C570" s="23"/>
+      <c r="C570" s="22"/>
       <c r="F570" s="9"/>
       <c r="G570" s="9"/>
       <c r="H570" s="14"/>
-      <c r="I570" s="22"/>
+      <c r="I570" s="21"/>
     </row>
     <row r="571">
-      <c r="C571" s="23"/>
+      <c r="C571" s="22"/>
       <c r="F571" s="9"/>
       <c r="G571" s="9"/>
       <c r="H571" s="14"/>
-      <c r="I571" s="22"/>
+      <c r="I571" s="21"/>
     </row>
     <row r="572">
-      <c r="C572" s="23"/>
+      <c r="C572" s="22"/>
       <c r="F572" s="9"/>
       <c r="G572" s="9"/>
       <c r="H572" s="14"/>
-      <c r="I572" s="22"/>
+      <c r="I572" s="21"/>
     </row>
     <row r="573">
-      <c r="C573" s="23"/>
+      <c r="C573" s="22"/>
       <c r="F573" s="9"/>
       <c r="G573" s="9"/>
       <c r="H573" s="14"/>
-      <c r="I573" s="22"/>
+      <c r="I573" s="21"/>
     </row>
     <row r="574">
-      <c r="C574" s="23"/>
+      <c r="C574" s="22"/>
       <c r="F574" s="9"/>
       <c r="G574" s="9"/>
       <c r="H574" s="14"/>
-      <c r="I574" s="22"/>
+      <c r="I574" s="21"/>
     </row>
     <row r="575">
-      <c r="C575" s="23"/>
+      <c r="C575" s="22"/>
       <c r="F575" s="9"/>
       <c r="G575" s="9"/>
       <c r="H575" s="14"/>
-      <c r="I575" s="22"/>
+      <c r="I575" s="21"/>
     </row>
     <row r="576">
-      <c r="C576" s="23"/>
+      <c r="C576" s="22"/>
       <c r="F576" s="9"/>
       <c r="G576" s="9"/>
       <c r="H576" s="14"/>
-      <c r="I576" s="22"/>
+      <c r="I576" s="21"/>
     </row>
     <row r="577">
-      <c r="C577" s="23"/>
+      <c r="C577" s="22"/>
       <c r="F577" s="9"/>
       <c r="G577" s="9"/>
       <c r="H577" s="14"/>
-      <c r="I577" s="22"/>
+      <c r="I577" s="21"/>
     </row>
     <row r="578">
-      <c r="C578" s="23"/>
+      <c r="C578" s="22"/>
       <c r="F578" s="9"/>
       <c r="G578" s="9"/>
       <c r="H578" s="14"/>
-      <c r="I578" s="22"/>
+      <c r="I578" s="21"/>
     </row>
     <row r="579">
-      <c r="C579" s="23"/>
+      <c r="C579" s="22"/>
       <c r="F579" s="9"/>
       <c r="G579" s="9"/>
       <c r="H579" s="14"/>
-      <c r="I579" s="22"/>
+      <c r="I579" s="21"/>
     </row>
     <row r="580">
-      <c r="C580" s="23"/>
+      <c r="C580" s="22"/>
       <c r="F580" s="9"/>
       <c r="G580" s="9"/>
       <c r="H580" s="14"/>
-      <c r="I580" s="22"/>
+      <c r="I580" s="21"/>
     </row>
     <row r="581">
-      <c r="C581" s="23"/>
+      <c r="C581" s="22"/>
       <c r="F581" s="9"/>
       <c r="G581" s="9"/>
       <c r="H581" s="14"/>
-      <c r="I581" s="22"/>
+      <c r="I581" s="21"/>
     </row>
     <row r="582">
-      <c r="C582" s="23"/>
+      <c r="C582" s="22"/>
       <c r="F582" s="9"/>
       <c r="G582" s="9"/>
       <c r="H582" s="14"/>
-      <c r="I582" s="22"/>
+      <c r="I582" s="21"/>
     </row>
     <row r="583">
-      <c r="C583" s="23"/>
+      <c r="C583" s="22"/>
       <c r="F583" s="9"/>
       <c r="G583" s="9"/>
       <c r="H583" s="14"/>
-      <c r="I583" s="22"/>
+      <c r="I583" s="21"/>
     </row>
     <row r="584">
-      <c r="C584" s="23"/>
+      <c r="C584" s="22"/>
       <c r="F584" s="9"/>
       <c r="G584" s="9"/>
       <c r="H584" s="14"/>
-      <c r="I584" s="22"/>
+      <c r="I584" s="21"/>
     </row>
     <row r="585">
-      <c r="C585" s="23"/>
+      <c r="C585" s="22"/>
       <c r="F585" s="9"/>
       <c r="G585" s="9"/>
       <c r="H585" s="14"/>
-      <c r="I585" s="22"/>
+      <c r="I585" s="21"/>
     </row>
     <row r="586">
-      <c r="C586" s="23"/>
+      <c r="C586" s="22"/>
       <c r="F586" s="9"/>
       <c r="G586" s="9"/>
       <c r="H586" s="14"/>
-      <c r="I586" s="22"/>
+      <c r="I586" s="21"/>
     </row>
     <row r="587">
-      <c r="C587" s="23"/>
+      <c r="C587" s="22"/>
       <c r="F587" s="9"/>
       <c r="G587" s="9"/>
       <c r="H587" s="14"/>
-      <c r="I587" s="22"/>
+      <c r="I587" s="21"/>
     </row>
     <row r="588">
-      <c r="C588" s="23"/>
+      <c r="C588" s="22"/>
       <c r="F588" s="9"/>
       <c r="G588" s="9"/>
       <c r="H588" s="14"/>
-      <c r="I588" s="22"/>
+      <c r="I588" s="21"/>
     </row>
     <row r="589">
-      <c r="C589" s="23"/>
+      <c r="C589" s="22"/>
       <c r="F589" s="9"/>
       <c r="G589" s="9"/>
       <c r="H589" s="14"/>
-      <c r="I589" s="22"/>
+      <c r="I589" s="21"/>
     </row>
     <row r="590">
-      <c r="C590" s="23"/>
+      <c r="C590" s="22"/>
       <c r="F590" s="9"/>
       <c r="G590" s="9"/>
       <c r="H590" s="14"/>
-      <c r="I590" s="22"/>
+      <c r="I590" s="21"/>
     </row>
     <row r="591">
-      <c r="C591" s="23"/>
+      <c r="C591" s="22"/>
       <c r="F591" s="9"/>
       <c r="G591" s="9"/>
       <c r="H591" s="14"/>
-      <c r="I591" s="22"/>
+      <c r="I591" s="21"/>
     </row>
     <row r="592">
-      <c r="C592" s="23"/>
+      <c r="C592" s="22"/>
       <c r="F592" s="9"/>
       <c r="G592" s="9"/>
       <c r="H592" s="14"/>
-      <c r="I592" s="22"/>
+      <c r="I592" s="21"/>
     </row>
     <row r="593">
-      <c r="C593" s="23"/>
+      <c r="C593" s="22"/>
       <c r="F593" s="9"/>
       <c r="G593" s="9"/>
       <c r="H593" s="14"/>
-      <c r="I593" s="22"/>
+      <c r="I593" s="21"/>
     </row>
     <row r="594">
-      <c r="C594" s="23"/>
+      <c r="C594" s="22"/>
       <c r="F594" s="9"/>
       <c r="G594" s="9"/>
       <c r="H594" s="14"/>
-      <c r="I594" s="22"/>
+      <c r="I594" s="21"/>
     </row>
     <row r="595">
-      <c r="C595" s="23"/>
+      <c r="C595" s="22"/>
       <c r="F595" s="9"/>
       <c r="G595" s="9"/>
       <c r="H595" s="14"/>
-      <c r="I595" s="22"/>
+      <c r="I595" s="21"/>
     </row>
     <row r="596">
-      <c r="C596" s="23"/>
+      <c r="C596" s="22"/>
       <c r="F596" s="9"/>
       <c r="G596" s="9"/>
       <c r="H596" s="14"/>
-      <c r="I596" s="22"/>
+      <c r="I596" s="21"/>
     </row>
     <row r="597">
-      <c r="C597" s="23"/>
+      <c r="C597" s="22"/>
       <c r="F597" s="9"/>
       <c r="G597" s="9"/>
       <c r="H597" s="14"/>
-      <c r="I597" s="22"/>
+      <c r="I597" s="21"/>
     </row>
     <row r="598">
-      <c r="C598" s="23"/>
+      <c r="C598" s="22"/>
       <c r="F598" s="9"/>
       <c r="G598" s="9"/>
       <c r="H598" s="14"/>
-      <c r="I598" s="22"/>
+      <c r="I598" s="21"/>
     </row>
     <row r="599">
-      <c r="C599" s="23"/>
+      <c r="C599" s="22"/>
       <c r="F599" s="9"/>
       <c r="G599" s="9"/>
       <c r="H599" s="14"/>
-      <c r="I599" s="22"/>
+      <c r="I599" s="21"/>
     </row>
     <row r="600">
-      <c r="C600" s="23"/>
+      <c r="C600" s="22"/>
       <c r="F600" s="9"/>
       <c r="G600" s="9"/>
       <c r="H600" s="14"/>
-      <c r="I600" s="22"/>
+      <c r="I600" s="21"/>
     </row>
     <row r="601">
-      <c r="C601" s="23"/>
+      <c r="C601" s="22"/>
       <c r="F601" s="9"/>
       <c r="G601" s="9"/>
       <c r="H601" s="14"/>
-      <c r="I601" s="22"/>
+      <c r="I601" s="21"/>
     </row>
     <row r="602">
-      <c r="C602" s="23"/>
+      <c r="C602" s="22"/>
       <c r="F602" s="9"/>
       <c r="G602" s="9"/>
       <c r="H602" s="14"/>
-      <c r="I602" s="22"/>
+      <c r="I602" s="21"/>
     </row>
     <row r="603">
-      <c r="C603" s="23"/>
+      <c r="C603" s="22"/>
       <c r="F603" s="9"/>
       <c r="G603" s="9"/>
       <c r="H603" s="14"/>
-      <c r="I603" s="22"/>
+      <c r="I603" s="21"/>
     </row>
     <row r="604">
-      <c r="C604" s="23"/>
+      <c r="C604" s="22"/>
       <c r="F604" s="9"/>
       <c r="G604" s="9"/>
       <c r="H604" s="14"/>
-      <c r="I604" s="22"/>
+      <c r="I604" s="21"/>
     </row>
     <row r="605">
-      <c r="C605" s="23"/>
+      <c r="C605" s="22"/>
       <c r="F605" s="9"/>
       <c r="G605" s="9"/>
       <c r="H605" s="14"/>
-      <c r="I605" s="22"/>
+      <c r="I605" s="21"/>
     </row>
     <row r="606">
-      <c r="C606" s="23"/>
+      <c r="C606" s="22"/>
       <c r="F606" s="9"/>
       <c r="G606" s="9"/>
       <c r="H606" s="14"/>
-      <c r="I606" s="22"/>
+      <c r="I606" s="21"/>
     </row>
     <row r="607">
-      <c r="C607" s="23"/>
+      <c r="C607" s="22"/>
       <c r="F607" s="9"/>
       <c r="G607" s="9"/>
       <c r="H607" s="14"/>
-      <c r="I607" s="22"/>
+      <c r="I607" s="21"/>
     </row>
     <row r="608">
-      <c r="C608" s="23"/>
+      <c r="C608" s="22"/>
       <c r="F608" s="9"/>
       <c r="G608" s="9"/>
       <c r="H608" s="14"/>
-      <c r="I608" s="22"/>
+      <c r="I608" s="21"/>
     </row>
     <row r="609">
-      <c r="C609" s="23"/>
+      <c r="C609" s="22"/>
       <c r="F609" s="9"/>
       <c r="G609" s="9"/>
       <c r="H609" s="14"/>
-      <c r="I609" s="22"/>
+      <c r="I609" s="21"/>
     </row>
     <row r="610">
-      <c r="C610" s="23"/>
+      <c r="C610" s="22"/>
       <c r="F610" s="9"/>
       <c r="G610" s="9"/>
       <c r="H610" s="14"/>
-      <c r="I610" s="22"/>
+      <c r="I610" s="21"/>
     </row>
     <row r="611">
-      <c r="C611" s="23"/>
+      <c r="C611" s="22"/>
       <c r="F611" s="9"/>
       <c r="G611" s="9"/>
       <c r="H611" s="14"/>
-      <c r="I611" s="22"/>
+      <c r="I611" s="21"/>
     </row>
     <row r="612">
-      <c r="C612" s="23"/>
+      <c r="C612" s="22"/>
       <c r="F612" s="9"/>
       <c r="G612" s="9"/>
       <c r="H612" s="14"/>
-      <c r="I612" s="22"/>
+      <c r="I612" s="21"/>
     </row>
     <row r="613">
-      <c r="C613" s="23"/>
+      <c r="C613" s="22"/>
       <c r="F613" s="9"/>
       <c r="G613" s="9"/>
       <c r="H613" s="14"/>
-      <c r="I613" s="22"/>
+      <c r="I613" s="21"/>
     </row>
     <row r="614">
-      <c r="C614" s="23"/>
+      <c r="C614" s="22"/>
       <c r="F614" s="9"/>
       <c r="G614" s="9"/>
       <c r="H614" s="14"/>
-      <c r="I614" s="22"/>
+      <c r="I614" s="21"/>
     </row>
     <row r="615">
-      <c r="C615" s="23"/>
+      <c r="C615" s="22"/>
       <c r="F615" s="9"/>
       <c r="G615" s="9"/>
       <c r="H615" s="14"/>
-      <c r="I615" s="22"/>
+      <c r="I615" s="21"/>
     </row>
     <row r="616">
-      <c r="C616" s="23"/>
+      <c r="C616" s="22"/>
       <c r="F616" s="9"/>
       <c r="G616" s="9"/>
       <c r="H616" s="14"/>
-      <c r="I616" s="22"/>
+      <c r="I616" s="21"/>
     </row>
     <row r="617">
-      <c r="C617" s="23"/>
+      <c r="C617" s="22"/>
       <c r="F617" s="9"/>
       <c r="G617" s="9"/>
       <c r="H617" s="14"/>
-      <c r="I617" s="22"/>
+      <c r="I617" s="21"/>
     </row>
     <row r="618">
-      <c r="C618" s="23"/>
+      <c r="C618" s="22"/>
       <c r="F618" s="9"/>
       <c r="G618" s="9"/>
       <c r="H618" s="14"/>
-      <c r="I618" s="22"/>
+      <c r="I618" s="21"/>
     </row>
     <row r="619">
-      <c r="C619" s="23"/>
+      <c r="C619" s="22"/>
       <c r="F619" s="9"/>
       <c r="G619" s="9"/>
       <c r="H619" s="14"/>
-      <c r="I619" s="22"/>
+      <c r="I619" s="21"/>
     </row>
     <row r="620">
-      <c r="C620" s="23"/>
+      <c r="C620" s="22"/>
       <c r="F620" s="9"/>
       <c r="G620" s="9"/>
       <c r="H620" s="14"/>
-      <c r="I620" s="22"/>
+      <c r="I620" s="21"/>
     </row>
     <row r="621">
-      <c r="C621" s="23"/>
+      <c r="C621" s="22"/>
       <c r="F621" s="9"/>
       <c r="G621" s="9"/>
       <c r="H621" s="14"/>
-      <c r="I621" s="22"/>
+      <c r="I621" s="21"/>
     </row>
     <row r="622">
-      <c r="C622" s="23"/>
+      <c r="C622" s="22"/>
       <c r="F622" s="9"/>
       <c r="G622" s="9"/>
       <c r="H622" s="14"/>
-      <c r="I622" s="22"/>
+      <c r="I622" s="21"/>
     </row>
     <row r="623">
-      <c r="C623" s="23"/>
+      <c r="C623" s="22"/>
       <c r="F623" s="9"/>
       <c r="G623" s="9"/>
       <c r="H623" s="14"/>
-      <c r="I623" s="22"/>
+      <c r="I623" s="21"/>
     </row>
     <row r="624">
-      <c r="C624" s="23"/>
+      <c r="C624" s="22"/>
       <c r="F624" s="9"/>
       <c r="G624" s="9"/>
       <c r="H624" s="14"/>
-      <c r="I624" s="22"/>
+      <c r="I624" s="21"/>
     </row>
     <row r="625">
-      <c r="C625" s="23"/>
+      <c r="C625" s="22"/>
       <c r="F625" s="9"/>
       <c r="G625" s="9"/>
       <c r="H625" s="14"/>
-      <c r="I625" s="22"/>
+      <c r="I625" s="21"/>
     </row>
     <row r="626">
-      <c r="C626" s="23"/>
+      <c r="C626" s="22"/>
       <c r="F626" s="9"/>
       <c r="G626" s="9"/>
       <c r="H626" s="14"/>
-      <c r="I626" s="22"/>
+      <c r="I626" s="21"/>
     </row>
     <row r="627">
-      <c r="C627" s="23"/>
+      <c r="C627" s="22"/>
       <c r="F627" s="9"/>
       <c r="G627" s="9"/>
       <c r="H627" s="14"/>
-      <c r="I627" s="22"/>
+      <c r="I627" s="21"/>
     </row>
     <row r="628">
-      <c r="C628" s="23"/>
+      <c r="C628" s="22"/>
       <c r="F628" s="9"/>
       <c r="G628" s="9"/>
       <c r="H628" s="14"/>
-      <c r="I628" s="22"/>
+      <c r="I628" s="21"/>
     </row>
     <row r="629">
-      <c r="C629" s="23"/>
+      <c r="C629" s="22"/>
       <c r="F629" s="9"/>
       <c r="G629" s="9"/>
       <c r="H629" s="14"/>
-      <c r="I629" s="22"/>
+      <c r="I629" s="21"/>
     </row>
     <row r="630">
-      <c r="C630" s="23"/>
+      <c r="C630" s="22"/>
       <c r="F630" s="9"/>
       <c r="G630" s="9"/>
       <c r="H630" s="14"/>
-      <c r="I630" s="22"/>
+      <c r="I630" s="21"/>
     </row>
     <row r="631">
-      <c r="C631" s="23"/>
+      <c r="C631" s="22"/>
       <c r="F631" s="9"/>
       <c r="G631" s="9"/>
       <c r="H631" s="14"/>
-      <c r="I631" s="22"/>
+      <c r="I631" s="21"/>
     </row>
     <row r="632">
-      <c r="C632" s="23"/>
+      <c r="C632" s="22"/>
       <c r="F632" s="9"/>
       <c r="G632" s="9"/>
       <c r="H632" s="14"/>
-      <c r="I632" s="22"/>
+      <c r="I632" s="21"/>
     </row>
     <row r="633">
-      <c r="C633" s="23"/>
+      <c r="C633" s="22"/>
       <c r="F633" s="9"/>
       <c r="G633" s="9"/>
       <c r="H633" s="14"/>
-      <c r="I633" s="22"/>
+      <c r="I633" s="21"/>
     </row>
     <row r="634">
-      <c r="C634" s="23"/>
+      <c r="C634" s="22"/>
       <c r="F634" s="9"/>
       <c r="G634" s="9"/>
       <c r="H634" s="14"/>
-      <c r="I634" s="22"/>
+      <c r="I634" s="21"/>
     </row>
     <row r="635">
-      <c r="C635" s="23"/>
+      <c r="C635" s="22"/>
       <c r="F635" s="9"/>
       <c r="G635" s="9"/>
       <c r="H635" s="14"/>
-      <c r="I635" s="22"/>
+      <c r="I635" s="21"/>
     </row>
     <row r="636">
-      <c r="C636" s="23"/>
+      <c r="C636" s="22"/>
       <c r="F636" s="9"/>
       <c r="G636" s="9"/>
       <c r="H636" s="14"/>
-      <c r="I636" s="22"/>
+      <c r="I636" s="21"/>
     </row>
     <row r="637">
-      <c r="C637" s="23"/>
+      <c r="C637" s="22"/>
       <c r="F637" s="9"/>
       <c r="G637" s="9"/>
       <c r="H637" s="14"/>
-      <c r="I637" s="22"/>
+      <c r="I637" s="21"/>
     </row>
     <row r="638">
-      <c r="C638" s="23"/>
+      <c r="C638" s="22"/>
       <c r="F638" s="9"/>
       <c r="G638" s="9"/>
       <c r="H638" s="14"/>
-      <c r="I638" s="22"/>
+      <c r="I638" s="21"/>
     </row>
     <row r="639">
-      <c r="C639" s="23"/>
+      <c r="C639" s="22"/>
       <c r="F639" s="9"/>
       <c r="G639" s="9"/>
       <c r="H639" s="14"/>
-      <c r="I639" s="22"/>
+      <c r="I639" s="21"/>
     </row>
     <row r="640">
-      <c r="C640" s="23"/>
+      <c r="C640" s="22"/>
       <c r="F640" s="9"/>
       <c r="G640" s="9"/>
       <c r="H640" s="14"/>
-      <c r="I640" s="22"/>
+      <c r="I640" s="21"/>
     </row>
     <row r="641">
-      <c r="C641" s="23"/>
+      <c r="C641" s="22"/>
       <c r="F641" s="9"/>
       <c r="G641" s="9"/>
       <c r="H641" s="14"/>
-      <c r="I641" s="22"/>
+      <c r="I641" s="21"/>
     </row>
     <row r="642">
-      <c r="C642" s="23"/>
+      <c r="C642" s="22"/>
       <c r="F642" s="9"/>
       <c r="G642" s="9"/>
       <c r="H642" s="14"/>
-      <c r="I642" s="22"/>
+      <c r="I642" s="21"/>
     </row>
     <row r="643">
-      <c r="C643" s="23"/>
+      <c r="C643" s="22"/>
       <c r="F643" s="9"/>
       <c r="G643" s="9"/>
       <c r="H643" s="14"/>
-      <c r="I643" s="22"/>
+      <c r="I643" s="21"/>
     </row>
     <row r="644">
-      <c r="C644" s="23"/>
+      <c r="C644" s="22"/>
       <c r="F644" s="9"/>
       <c r="G644" s="9"/>
       <c r="H644" s="14"/>
-      <c r="I644" s="22"/>
+      <c r="I644" s="21"/>
     </row>
     <row r="645">
-      <c r="C645" s="23"/>
+      <c r="C645" s="22"/>
       <c r="F645" s="9"/>
       <c r="G645" s="9"/>
       <c r="H645" s="14"/>
-      <c r="I645" s="22"/>
+      <c r="I645" s="21"/>
     </row>
     <row r="646">
-      <c r="C646" s="23"/>
+      <c r="C646" s="22"/>
       <c r="F646" s="9"/>
       <c r="G646" s="9"/>
       <c r="H646" s="14"/>
-      <c r="I646" s="22"/>
+      <c r="I646" s="21"/>
     </row>
     <row r="647">
-      <c r="C647" s="23"/>
+      <c r="C647" s="22"/>
       <c r="F647" s="9"/>
       <c r="G647" s="9"/>
       <c r="H647" s="14"/>
-      <c r="I647" s="22"/>
+      <c r="I647" s="21"/>
     </row>
     <row r="648">
-      <c r="C648" s="23"/>
+      <c r="C648" s="22"/>
       <c r="F648" s="9"/>
       <c r="G648" s="9"/>
       <c r="H648" s="14"/>
-      <c r="I648" s="22"/>
+      <c r="I648" s="21"/>
     </row>
     <row r="649">
-      <c r="C649" s="23"/>
+      <c r="C649" s="22"/>
       <c r="F649" s="9"/>
       <c r="G649" s="9"/>
       <c r="H649" s="14"/>
-      <c r="I649" s="22"/>
+      <c r="I649" s="21"/>
     </row>
     <row r="650">
-      <c r="C650" s="23"/>
+      <c r="C650" s="22"/>
       <c r="F650" s="9"/>
       <c r="G650" s="9"/>
       <c r="H650" s="14"/>
-      <c r="I650" s="22"/>
+      <c r="I650" s="21"/>
     </row>
     <row r="651">
-      <c r="C651" s="23"/>
+      <c r="C651" s="22"/>
       <c r="F651" s="9"/>
       <c r="G651" s="9"/>
       <c r="H651" s="14"/>
-      <c r="I651" s="22"/>
+      <c r="I651" s="21"/>
     </row>
     <row r="652">
-      <c r="C652" s="23"/>
+      <c r="C652" s="22"/>
       <c r="F652" s="9"/>
       <c r="G652" s="9"/>
       <c r="H652" s="14"/>
-      <c r="I652" s="22"/>
+      <c r="I652" s="21"/>
     </row>
     <row r="653">
-      <c r="C653" s="23"/>
+      <c r="C653" s="22"/>
       <c r="F653" s="9"/>
       <c r="G653" s="9"/>
       <c r="H653" s="14"/>
-      <c r="I653" s="22"/>
+      <c r="I653" s="21"/>
     </row>
     <row r="654">
-      <c r="C654" s="23"/>
+      <c r="C654" s="22"/>
       <c r="F654" s="9"/>
       <c r="G654" s="9"/>
       <c r="H654" s="14"/>
-      <c r="I654" s="22"/>
+      <c r="I654" s="21"/>
     </row>
     <row r="655">
-      <c r="C655" s="23"/>
+      <c r="C655" s="22"/>
       <c r="F655" s="9"/>
       <c r="G655" s="9"/>
       <c r="H655" s="14"/>
-      <c r="I655" s="22"/>
+      <c r="I655" s="21"/>
     </row>
     <row r="656">
-      <c r="C656" s="23"/>
+      <c r="C656" s="22"/>
       <c r="F656" s="9"/>
       <c r="G656" s="9"/>
       <c r="H656" s="14"/>
-      <c r="I656" s="22"/>
+      <c r="I656" s="21"/>
     </row>
     <row r="657">
-      <c r="C657" s="23"/>
+      <c r="C657" s="22"/>
       <c r="F657" s="9"/>
       <c r="G657" s="9"/>
       <c r="H657" s="14"/>
-      <c r="I657" s="22"/>
+      <c r="I657" s="21"/>
     </row>
     <row r="658">
-      <c r="C658" s="23"/>
+      <c r="C658" s="22"/>
       <c r="F658" s="9"/>
       <c r="G658" s="9"/>
       <c r="H658" s="14"/>
-      <c r="I658" s="22"/>
+      <c r="I658" s="21"/>
     </row>
     <row r="659">
-      <c r="C659" s="23"/>
+      <c r="C659" s="22"/>
       <c r="F659" s="9"/>
       <c r="G659" s="9"/>
       <c r="H659" s="14"/>
-      <c r="I659" s="22"/>
+      <c r="I659" s="21"/>
     </row>
     <row r="660">
-      <c r="C660" s="23"/>
+      <c r="C660" s="22"/>
       <c r="F660" s="9"/>
       <c r="G660" s="9"/>
       <c r="H660" s="14"/>
-      <c r="I660" s="22"/>
+      <c r="I660" s="21"/>
     </row>
     <row r="661">
-      <c r="C661" s="23"/>
+      <c r="C661" s="22"/>
       <c r="F661" s="9"/>
       <c r="G661" s="9"/>
       <c r="H661" s="14"/>
-      <c r="I661" s="22"/>
+      <c r="I661" s="21"/>
     </row>
     <row r="662">
-      <c r="C662" s="23"/>
+      <c r="C662" s="22"/>
       <c r="F662" s="9"/>
       <c r="G662" s="9"/>
       <c r="H662" s="14"/>
-      <c r="I662" s="22"/>
+      <c r="I662" s="21"/>
     </row>
     <row r="663">
-      <c r="C663" s="23"/>
+      <c r="C663" s="22"/>
       <c r="F663" s="9"/>
       <c r="G663" s="9"/>
       <c r="H663" s="14"/>
-      <c r="I663" s="22"/>
+      <c r="I663" s="21"/>
     </row>
     <row r="664">
-      <c r="C664" s="23"/>
+      <c r="C664" s="22"/>
       <c r="F664" s="9"/>
       <c r="G664" s="9"/>
       <c r="H664" s="14"/>
-      <c r="I664" s="22"/>
+      <c r="I664" s="21"/>
     </row>
     <row r="665">
-      <c r="C665" s="23"/>
+      <c r="C665" s="22"/>
       <c r="F665" s="9"/>
       <c r="G665" s="9"/>
       <c r="H665" s="14"/>
-      <c r="I665" s="22"/>
+      <c r="I665" s="21"/>
     </row>
     <row r="666">
-      <c r="C666" s="23"/>
+      <c r="C666" s="22"/>
       <c r="F666" s="9"/>
       <c r="G666" s="9"/>
       <c r="H666" s="14"/>
-      <c r="I666" s="22"/>
+      <c r="I666" s="21"/>
     </row>
     <row r="667">
-      <c r="C667" s="23"/>
+      <c r="C667" s="22"/>
       <c r="F667" s="9"/>
       <c r="G667" s="9"/>
       <c r="H667" s="14"/>
-      <c r="I667" s="22"/>
+      <c r="I667" s="21"/>
     </row>
     <row r="668">
-      <c r="C668" s="23"/>
+      <c r="C668" s="22"/>
       <c r="F668" s="9"/>
       <c r="G668" s="9"/>
       <c r="H668" s="14"/>
-      <c r="I668" s="22"/>
+      <c r="I668" s="21"/>
     </row>
     <row r="669">
-      <c r="C669" s="23"/>
+      <c r="C669" s="22"/>
       <c r="F669" s="9"/>
       <c r="G669" s="9"/>
       <c r="H669" s="14"/>
-      <c r="I669" s="22"/>
+      <c r="I669" s="21"/>
     </row>
     <row r="670">
-      <c r="C670" s="23"/>
+      <c r="C670" s="22"/>
       <c r="F670" s="9"/>
       <c r="G670" s="9"/>
       <c r="H670" s="14"/>
-      <c r="I670" s="22"/>
+      <c r="I670" s="21"/>
     </row>
     <row r="671">
-      <c r="C671" s="23"/>
+      <c r="C671" s="22"/>
       <c r="F671" s="9"/>
       <c r="G671" s="9"/>
       <c r="H671" s="14"/>
-      <c r="I671" s="22"/>
+      <c r="I671" s="21"/>
     </row>
     <row r="672">
-      <c r="C672" s="23"/>
+      <c r="C672" s="22"/>
       <c r="F672" s="9"/>
       <c r="G672" s="9"/>
       <c r="H672" s="14"/>
-      <c r="I672" s="22"/>
+      <c r="I672" s="21"/>
     </row>
     <row r="673">
-      <c r="C673" s="23"/>
+      <c r="C673" s="22"/>
       <c r="F673" s="9"/>
       <c r="G673" s="9"/>
       <c r="H673" s="14"/>
-      <c r="I673" s="22"/>
+      <c r="I673" s="21"/>
     </row>
     <row r="674">
-      <c r="C674" s="23"/>
+      <c r="C674" s="22"/>
       <c r="F674" s="9"/>
       <c r="G674" s="9"/>
       <c r="H674" s="14"/>
-      <c r="I674" s="22"/>
+      <c r="I674" s="21"/>
     </row>
     <row r="675">
-      <c r="C675" s="23"/>
+      <c r="C675" s="22"/>
       <c r="F675" s="9"/>
       <c r="G675" s="9"/>
       <c r="H675" s="14"/>
-      <c r="I675" s="22"/>
+      <c r="I675" s="21"/>
     </row>
     <row r="676">
-      <c r="C676" s="23"/>
+      <c r="C676" s="22"/>
       <c r="F676" s="9"/>
       <c r="G676" s="9"/>
       <c r="H676" s="14"/>
-      <c r="I676" s="22"/>
+      <c r="I676" s="21"/>
     </row>
     <row r="677">
-      <c r="C677" s="23"/>
+      <c r="C677" s="22"/>
       <c r="F677" s="9"/>
       <c r="G677" s="9"/>
       <c r="H677" s="14"/>
-      <c r="I677" s="22"/>
+      <c r="I677" s="21"/>
     </row>
     <row r="678">
-      <c r="C678" s="23"/>
+      <c r="C678" s="22"/>
       <c r="F678" s="9"/>
       <c r="G678" s="9"/>
       <c r="H678" s="14"/>
-      <c r="I678" s="22"/>
+      <c r="I678" s="21"/>
     </row>
     <row r="679">
-      <c r="C679" s="23"/>
+      <c r="C679" s="22"/>
       <c r="F679" s="9"/>
       <c r="G679" s="9"/>
       <c r="H679" s="14"/>
-      <c r="I679" s="22"/>
+      <c r="I679" s="21"/>
     </row>
     <row r="680">
-      <c r="C680" s="23"/>
+      <c r="C680" s="22"/>
       <c r="F680" s="9"/>
       <c r="G680" s="9"/>
       <c r="H680" s="14"/>
-      <c r="I680" s="22"/>
+      <c r="I680" s="21"/>
     </row>
     <row r="681">
-      <c r="C681" s="23"/>
+      <c r="C681" s="22"/>
       <c r="F681" s="9"/>
       <c r="G681" s="9"/>
       <c r="H681" s="14"/>
-      <c r="I681" s="22"/>
+      <c r="I681" s="21"/>
     </row>
     <row r="682">
-      <c r="C682" s="23"/>
+      <c r="C682" s="22"/>
       <c r="F682" s="9"/>
       <c r="G682" s="9"/>
       <c r="H682" s="14"/>
-      <c r="I682" s="22"/>
+      <c r="I682" s="21"/>
     </row>
     <row r="683">
-      <c r="C683" s="23"/>
+      <c r="C683" s="22"/>
       <c r="F683" s="9"/>
       <c r="G683" s="9"/>
       <c r="H683" s="14"/>
-      <c r="I683" s="22"/>
+      <c r="I683" s="21"/>
     </row>
     <row r="684">
-      <c r="C684" s="23"/>
+      <c r="C684" s="22"/>
       <c r="F684" s="9"/>
       <c r="G684" s="9"/>
       <c r="H684" s="14"/>
-      <c r="I684" s="22"/>
+      <c r="I684" s="21"/>
     </row>
     <row r="685">
-      <c r="C685" s="23"/>
+      <c r="C685" s="22"/>
       <c r="F685" s="9"/>
       <c r="G685" s="9"/>
       <c r="H685" s="14"/>
-      <c r="I685" s="22"/>
+      <c r="I685" s="21"/>
     </row>
     <row r="686">
-      <c r="C686" s="23"/>
+      <c r="C686" s="22"/>
       <c r="F686" s="9"/>
       <c r="G686" s="9"/>
       <c r="H686" s="14"/>
-      <c r="I686" s="22"/>
+      <c r="I686" s="21"/>
     </row>
     <row r="687">
-      <c r="C687" s="23"/>
+      <c r="C687" s="22"/>
       <c r="F687" s="9"/>
       <c r="G687" s="9"/>
       <c r="H687" s="14"/>
-      <c r="I687" s="22"/>
+      <c r="I687" s="21"/>
     </row>
     <row r="688">
-      <c r="C688" s="23"/>
+      <c r="C688" s="22"/>
       <c r="F688" s="9"/>
       <c r="G688" s="9"/>
       <c r="H688" s="14"/>
-      <c r="I688" s="22"/>
+      <c r="I688" s="21"/>
     </row>
     <row r="689">
-      <c r="C689" s="23"/>
+      <c r="C689" s="22"/>
       <c r="F689" s="9"/>
       <c r="G689" s="9"/>
       <c r="H689" s="14"/>
-      <c r="I689" s="22"/>
+      <c r="I689" s="21"/>
     </row>
     <row r="690">
-      <c r="C690" s="23"/>
+      <c r="C690" s="22"/>
       <c r="F690" s="9"/>
       <c r="G690" s="9"/>
       <c r="H690" s="14"/>
-      <c r="I690" s="22"/>
+      <c r="I690" s="21"/>
     </row>
     <row r="691">
-      <c r="C691" s="23"/>
+      <c r="C691" s="22"/>
       <c r="F691" s="9"/>
       <c r="G691" s="9"/>
       <c r="H691" s="14"/>
-      <c r="I691" s="22"/>
+      <c r="I691" s="21"/>
     </row>
     <row r="692">
-      <c r="C692" s="23"/>
+      <c r="C692" s="22"/>
       <c r="F692" s="9"/>
       <c r="G692" s="9"/>
       <c r="H692" s="14"/>
-      <c r="I692" s="22"/>
+      <c r="I692" s="21"/>
     </row>
     <row r="693">
-      <c r="C693" s="23"/>
+      <c r="C693" s="22"/>
       <c r="F693" s="9"/>
       <c r="G693" s="9"/>
       <c r="H693" s="14"/>
-      <c r="I693" s="22"/>
+      <c r="I693" s="21"/>
     </row>
     <row r="694">
-      <c r="C694" s="23"/>
+      <c r="C694" s="22"/>
       <c r="F694" s="9"/>
       <c r="G694" s="9"/>
       <c r="H694" s="14"/>
-      <c r="I694" s="22"/>
+      <c r="I694" s="21"/>
     </row>
     <row r="695">
-      <c r="C695" s="23"/>
+      <c r="C695" s="22"/>
       <c r="F695" s="9"/>
       <c r="G695" s="9"/>
       <c r="H695" s="14"/>
-      <c r="I695" s="22"/>
+      <c r="I695" s="21"/>
     </row>
     <row r="696">
-      <c r="C696" s="23"/>
+      <c r="C696" s="22"/>
       <c r="F696" s="9"/>
       <c r="G696" s="9"/>
       <c r="H696" s="14"/>
-      <c r="I696" s="22"/>
+      <c r="I696" s="21"/>
     </row>
     <row r="697">
-      <c r="C697" s="23"/>
+      <c r="C697" s="22"/>
       <c r="F697" s="9"/>
       <c r="G697" s="9"/>
       <c r="H697" s="14"/>
-      <c r="I697" s="22"/>
+      <c r="I697" s="21"/>
     </row>
     <row r="698">
-      <c r="C698" s="23"/>
+      <c r="C698" s="22"/>
       <c r="F698" s="9"/>
       <c r="G698" s="9"/>
       <c r="H698" s="14"/>
-      <c r="I698" s="22"/>
+      <c r="I698" s="21"/>
     </row>
     <row r="699">
-      <c r="C699" s="23"/>
+      <c r="C699" s="22"/>
       <c r="F699" s="9"/>
       <c r="G699" s="9"/>
       <c r="H699" s="14"/>
-      <c r="I699" s="22"/>
+      <c r="I699" s="21"/>
     </row>
     <row r="700">
-      <c r="C700" s="23"/>
+      <c r="C700" s="22"/>
       <c r="F700" s="9"/>
       <c r="G700" s="9"/>
       <c r="H700" s="14"/>
-      <c r="I700" s="22"/>
+      <c r="I700" s="21"/>
     </row>
     <row r="701">
-      <c r="C701" s="23"/>
+      <c r="C701" s="22"/>
       <c r="F701" s="9"/>
       <c r="G701" s="9"/>
       <c r="H701" s="14"/>
-      <c r="I701" s="22"/>
+      <c r="I701" s="21"/>
     </row>
     <row r="702">
-      <c r="C702" s="23"/>
+      <c r="C702" s="22"/>
       <c r="F702" s="9"/>
       <c r="G702" s="9"/>
       <c r="H702" s="14"/>
-      <c r="I702" s="22"/>
+      <c r="I702" s="21"/>
     </row>
     <row r="703">
-      <c r="C703" s="23"/>
+      <c r="C703" s="22"/>
       <c r="F703" s="9"/>
       <c r="G703" s="9"/>
       <c r="H703" s="14"/>
-      <c r="I703" s="22"/>
+      <c r="I703" s="21"/>
     </row>
     <row r="704">
-      <c r="C704" s="23"/>
+      <c r="C704" s="22"/>
       <c r="F704" s="9"/>
       <c r="G704" s="9"/>
       <c r="H704" s="14"/>
-      <c r="I704" s="22"/>
+      <c r="I704" s="21"/>
     </row>
     <row r="705">
-      <c r="C705" s="23"/>
+      <c r="C705" s="22"/>
       <c r="F705" s="9"/>
       <c r="G705" s="9"/>
       <c r="H705" s="14"/>
-      <c r="I705" s="22"/>
+      <c r="I705" s="21"/>
     </row>
     <row r="706">
-      <c r="C706" s="23"/>
+      <c r="C706" s="22"/>
       <c r="F706" s="9"/>
       <c r="G706" s="9"/>
       <c r="H706" s="14"/>
-      <c r="I706" s="22"/>
+      <c r="I706" s="21"/>
     </row>
     <row r="707">
-      <c r="C707" s="23"/>
+      <c r="C707" s="22"/>
       <c r="F707" s="9"/>
       <c r="G707" s="9"/>
       <c r="H707" s="14"/>
-      <c r="I707" s="22"/>
+      <c r="I707" s="21"/>
     </row>
     <row r="708">
-      <c r="C708" s="23"/>
+      <c r="C708" s="22"/>
       <c r="F708" s="9"/>
       <c r="G708" s="9"/>
       <c r="H708" s="14"/>
-      <c r="I708" s="22"/>
+      <c r="I708" s="21"/>
     </row>
     <row r="709">
-      <c r="C709" s="23"/>
+      <c r="C709" s="22"/>
       <c r="F709" s="9"/>
       <c r="G709" s="9"/>
       <c r="H709" s="14"/>
-      <c r="I709" s="22"/>
+      <c r="I709" s="21"/>
     </row>
     <row r="710">
-      <c r="C710" s="23"/>
+      <c r="C710" s="22"/>
       <c r="F710" s="9"/>
       <c r="G710" s="9"/>
       <c r="H710" s="14"/>
-      <c r="I710" s="22"/>
+      <c r="I710" s="21"/>
     </row>
     <row r="711">
-      <c r="C711" s="23"/>
+      <c r="C711" s="22"/>
       <c r="F711" s="9"/>
       <c r="G711" s="9"/>
       <c r="H711" s="14"/>
-      <c r="I711" s="22"/>
+      <c r="I711" s="21"/>
     </row>
     <row r="712">
-      <c r="C712" s="23"/>
+      <c r="C712" s="22"/>
       <c r="F712" s="9"/>
       <c r="G712" s="9"/>
       <c r="H712" s="14"/>
-      <c r="I712" s="22"/>
+      <c r="I712" s="21"/>
     </row>
     <row r="713">
-      <c r="C713" s="23"/>
+      <c r="C713" s="22"/>
       <c r="F713" s="9"/>
       <c r="G713" s="9"/>
       <c r="H713" s="14"/>
-      <c r="I713" s="22"/>
+      <c r="I713" s="21"/>
     </row>
     <row r="714">
-      <c r="C714" s="23"/>
+      <c r="C714" s="22"/>
       <c r="F714" s="9"/>
       <c r="G714" s="9"/>
       <c r="H714" s="14"/>
-      <c r="I714" s="22"/>
+      <c r="I714" s="21"/>
     </row>
     <row r="715">
-      <c r="C715" s="23"/>
+      <c r="C715" s="22"/>
       <c r="F715" s="9"/>
       <c r="G715" s="9"/>
       <c r="H715" s="14"/>
-      <c r="I715" s="22"/>
+      <c r="I715" s="21"/>
     </row>
     <row r="716">
-      <c r="C716" s="23"/>
+      <c r="C716" s="22"/>
       <c r="F716" s="9"/>
       <c r="G716" s="9"/>
       <c r="H716" s="14"/>
-      <c r="I716" s="22"/>
+      <c r="I716" s="21"/>
     </row>
     <row r="717">
-      <c r="C717" s="23"/>
+      <c r="C717" s="22"/>
       <c r="F717" s="9"/>
       <c r="G717" s="9"/>
       <c r="H717" s="14"/>
-      <c r="I717" s="22"/>
+      <c r="I717" s="21"/>
     </row>
     <row r="718">
-      <c r="C718" s="23"/>
+      <c r="C718" s="22"/>
       <c r="F718" s="9"/>
       <c r="G718" s="9"/>
       <c r="H718" s="14"/>
-      <c r="I718" s="22"/>
+      <c r="I718" s="21"/>
     </row>
     <row r="719">
-      <c r="C719" s="23"/>
+      <c r="C719" s="22"/>
       <c r="F719" s="9"/>
       <c r="G719" s="9"/>
       <c r="H719" s="14"/>
-      <c r="I719" s="22"/>
+      <c r="I719" s="21"/>
     </row>
     <row r="720">
-      <c r="C720" s="23"/>
+      <c r="C720" s="22"/>
       <c r="F720" s="9"/>
       <c r="G720" s="9"/>
       <c r="H720" s="14"/>
-      <c r="I720" s="22"/>
+      <c r="I720" s="21"/>
     </row>
     <row r="721">
-      <c r="C721" s="23"/>
+      <c r="C721" s="22"/>
       <c r="F721" s="9"/>
       <c r="G721" s="9"/>
       <c r="H721" s="14"/>
-      <c r="I721" s="22"/>
+      <c r="I721" s="21"/>
     </row>
     <row r="722">
-      <c r="C722" s="23"/>
+      <c r="C722" s="22"/>
       <c r="F722" s="9"/>
       <c r="G722" s="9"/>
       <c r="H722" s="14"/>
-      <c r="I722" s="22"/>
+      <c r="I722" s="21"/>
     </row>
     <row r="723">
-      <c r="C723" s="23"/>
+      <c r="C723" s="22"/>
       <c r="F723" s="9"/>
       <c r="G723" s="9"/>
       <c r="H723" s="14"/>
-      <c r="I723" s="22"/>
+      <c r="I723" s="21"/>
     </row>
     <row r="724">
-      <c r="C724" s="23"/>
+      <c r="C724" s="22"/>
       <c r="F724" s="9"/>
       <c r="G724" s="9"/>
       <c r="H724" s="14"/>
-      <c r="I724" s="22"/>
+      <c r="I724" s="21"/>
     </row>
     <row r="725">
-      <c r="C725" s="23"/>
+      <c r="C725" s="22"/>
       <c r="F725" s="9"/>
       <c r="G725" s="9"/>
       <c r="H725" s="14"/>
-      <c r="I725" s="22"/>
+      <c r="I725" s="21"/>
     </row>
     <row r="726">
-      <c r="C726" s="23"/>
+      <c r="C726" s="22"/>
       <c r="F726" s="9"/>
       <c r="G726" s="9"/>
       <c r="H726" s="14"/>
-      <c r="I726" s="22"/>
+      <c r="I726" s="21"/>
     </row>
     <row r="727">
-      <c r="C727" s="23"/>
+      <c r="C727" s="22"/>
       <c r="F727" s="9"/>
       <c r="G727" s="9"/>
       <c r="H727" s="14"/>
-      <c r="I727" s="22"/>
+      <c r="I727" s="21"/>
     </row>
     <row r="728">
-      <c r="C728" s="23"/>
+      <c r="C728" s="22"/>
       <c r="F728" s="9"/>
       <c r="G728" s="9"/>
       <c r="H728" s="14"/>
-      <c r="I728" s="22"/>
+      <c r="I728" s="21"/>
     </row>
     <row r="729">
-      <c r="C729" s="23"/>
+      <c r="C729" s="22"/>
       <c r="F729" s="9"/>
       <c r="G729" s="9"/>
       <c r="H729" s="14"/>
-      <c r="I729" s="22"/>
+      <c r="I729" s="21"/>
     </row>
     <row r="730">
-      <c r="C730" s="23"/>
+      <c r="C730" s="22"/>
       <c r="F730" s="9"/>
       <c r="G730" s="9"/>
       <c r="H730" s="14"/>
-      <c r="I730" s="22"/>
+      <c r="I730" s="21"/>
     </row>
     <row r="731">
-      <c r="C731" s="23"/>
+      <c r="C731" s="22"/>
       <c r="F731" s="9"/>
       <c r="G731" s="9"/>
       <c r="H731" s="14"/>
-      <c r="I731" s="22"/>
+      <c r="I731" s="21"/>
     </row>
     <row r="732">
-      <c r="C732" s="23"/>
+      <c r="C732" s="22"/>
       <c r="F732" s="9"/>
       <c r="G732" s="9"/>
       <c r="H732" s="14"/>
-      <c r="I732" s="22"/>
+      <c r="I732" s="21"/>
     </row>
     <row r="733">
-      <c r="C733" s="23"/>
+      <c r="C733" s="22"/>
       <c r="F733" s="9"/>
       <c r="G733" s="9"/>
       <c r="H733" s="14"/>
-      <c r="I733" s="22"/>
+      <c r="I733" s="21"/>
     </row>
     <row r="734">
-      <c r="C734" s="23"/>
+      <c r="C734" s="22"/>
       <c r="F734" s="9"/>
       <c r="G734" s="9"/>
       <c r="H734" s="14"/>
-      <c r="I734" s="22"/>
+      <c r="I734" s="21"/>
     </row>
     <row r="735">
-      <c r="C735" s="23"/>
+      <c r="C735" s="22"/>
       <c r="F735" s="9"/>
       <c r="G735" s="9"/>
       <c r="H735" s="14"/>
-      <c r="I735" s="22"/>
+      <c r="I735" s="21"/>
     </row>
     <row r="736">
-      <c r="C736" s="23"/>
+      <c r="C736" s="22"/>
       <c r="F736" s="9"/>
       <c r="G736" s="9"/>
       <c r="H736" s="14"/>
-      <c r="I736" s="22"/>
+      <c r="I736" s="21"/>
     </row>
     <row r="737">
-      <c r="C737" s="23"/>
+      <c r="C737" s="22"/>
       <c r="F737" s="9"/>
       <c r="G737" s="9"/>
       <c r="H737" s="14"/>
-      <c r="I737" s="22"/>
+      <c r="I737" s="21"/>
     </row>
     <row r="738">
-      <c r="C738" s="23"/>
+      <c r="C738" s="22"/>
       <c r="F738" s="9"/>
       <c r="G738" s="9"/>
       <c r="H738" s="14"/>
-      <c r="I738" s="22"/>
+      <c r="I738" s="21"/>
     </row>
     <row r="739">
-      <c r="C739" s="23"/>
+      <c r="C739" s="22"/>
       <c r="F739" s="9"/>
       <c r="G739" s="9"/>
       <c r="H739" s="14"/>
-      <c r="I739" s="22"/>
+      <c r="I739" s="21"/>
     </row>
     <row r="740">
-      <c r="C740" s="23"/>
+      <c r="C740" s="22"/>
       <c r="F740" s="9"/>
       <c r="G740" s="9"/>
       <c r="H740" s="14"/>
-      <c r="I740" s="22"/>
+      <c r="I740" s="21"/>
     </row>
     <row r="741">
-      <c r="C741" s="23"/>
+      <c r="C741" s="22"/>
       <c r="F741" s="9"/>
       <c r="G741" s="9"/>
       <c r="H741" s="14"/>
-      <c r="I741" s="22"/>
+      <c r="I741" s="21"/>
     </row>
     <row r="742">
-      <c r="C742" s="23"/>
+      <c r="C742" s="22"/>
       <c r="F742" s="9"/>
       <c r="G742" s="9"/>
       <c r="H742" s="14"/>
-      <c r="I742" s="22"/>
+      <c r="I742" s="21"/>
     </row>
     <row r="743">
-      <c r="C743" s="23"/>
+      <c r="C743" s="22"/>
       <c r="F743" s="9"/>
       <c r="G743" s="9"/>
       <c r="H743" s="14"/>
-      <c r="I743" s="22"/>
+      <c r="I743" s="21"/>
     </row>
     <row r="744">
-      <c r="C744" s="23"/>
+      <c r="C744" s="22"/>
       <c r="F744" s="9"/>
       <c r="G744" s="9"/>
       <c r="H744" s="14"/>
-      <c r="I744" s="22"/>
+      <c r="I744" s="21"/>
     </row>
     <row r="745">
-      <c r="C745" s="23"/>
+      <c r="C745" s="22"/>
       <c r="F745" s="9"/>
       <c r="G745" s="9"/>
       <c r="H745" s="14"/>
-      <c r="I745" s="22"/>
+      <c r="I745" s="21"/>
     </row>
     <row r="746">
-      <c r="C746" s="23"/>
+      <c r="C746" s="22"/>
       <c r="F746" s="9"/>
       <c r="G746" s="9"/>
       <c r="H746" s="14"/>
-      <c r="I746" s="22"/>
+      <c r="I746" s="21"/>
     </row>
     <row r="747">
-      <c r="C747" s="23"/>
+      <c r="C747" s="22"/>
       <c r="F747" s="9"/>
       <c r="G747" s="9"/>
       <c r="H747" s="14"/>
-      <c r="I747" s="22"/>
+      <c r="I747" s="21"/>
     </row>
     <row r="748">
-      <c r="C748" s="23"/>
+      <c r="C748" s="22"/>
       <c r="F748" s="9"/>
       <c r="G748" s="9"/>
       <c r="H748" s="14"/>
-      <c r="I748" s="22"/>
+      <c r="I748" s="21"/>
     </row>
     <row r="749">
-      <c r="C749" s="23"/>
+      <c r="C749" s="22"/>
       <c r="F749" s="9"/>
       <c r="G749" s="9"/>
       <c r="H749" s="14"/>
-      <c r="I749" s="22"/>
+      <c r="I749" s="21"/>
     </row>
     <row r="750">
-      <c r="C750" s="23"/>
+      <c r="C750" s="22"/>
       <c r="F750" s="9"/>
       <c r="G750" s="9"/>
       <c r="H750" s="14"/>
-      <c r="I750" s="22"/>
+      <c r="I750" s="21"/>
     </row>
     <row r="751">
-      <c r="C751" s="23"/>
+      <c r="C751" s="22"/>
       <c r="F751" s="9"/>
       <c r="G751" s="9"/>
       <c r="H751" s="14"/>
-      <c r="I751" s="22"/>
+      <c r="I751" s="21"/>
     </row>
     <row r="752">
-      <c r="C752" s="23"/>
+      <c r="C752" s="22"/>
       <c r="F752" s="9"/>
       <c r="G752" s="9"/>
       <c r="H752" s="14"/>
-      <c r="I752" s="22"/>
+      <c r="I752" s="21"/>
     </row>
     <row r="753">
-      <c r="C753" s="23"/>
+      <c r="C753" s="22"/>
       <c r="F753" s="9"/>
       <c r="G753" s="9"/>
       <c r="H753" s="14"/>
-      <c r="I753" s="22"/>
+      <c r="I753" s="21"/>
     </row>
     <row r="754">
-      <c r="C754" s="23"/>
+      <c r="C754" s="22"/>
       <c r="F754" s="9"/>
       <c r="G754" s="9"/>
       <c r="H754" s="14"/>
-      <c r="I754" s="22"/>
+      <c r="I754" s="21"/>
     </row>
     <row r="755">
-      <c r="C755" s="23"/>
+      <c r="C755" s="22"/>
       <c r="F755" s="9"/>
       <c r="G755" s="9"/>
       <c r="H755" s="14"/>
-      <c r="I755" s="22"/>
+      <c r="I755" s="21"/>
     </row>
     <row r="756">
-      <c r="C756" s="23"/>
+      <c r="C756" s="22"/>
       <c r="F756" s="9"/>
       <c r="G756" s="9"/>
       <c r="H756" s="14"/>
-      <c r="I756" s="22"/>
+      <c r="I756" s="21"/>
     </row>
     <row r="757">
-      <c r="C757" s="23"/>
+      <c r="C757" s="22"/>
       <c r="F757" s="9"/>
       <c r="G757" s="9"/>
       <c r="H757" s="14"/>
-      <c r="I757" s="22"/>
+      <c r="I757" s="21"/>
     </row>
     <row r="758">
-      <c r="C758" s="23"/>
+      <c r="C758" s="22"/>
       <c r="F758" s="9"/>
       <c r="G758" s="9"/>
       <c r="H758" s="14"/>
-      <c r="I758" s="22"/>
+      <c r="I758" s="21"/>
     </row>
     <row r="759">
-      <c r="C759" s="23"/>
+      <c r="C759" s="22"/>
       <c r="F759" s="9"/>
       <c r="G759" s="9"/>
       <c r="H759" s="14"/>
-      <c r="I759" s="22"/>
+      <c r="I759" s="21"/>
     </row>
     <row r="760">
-      <c r="C760" s="23"/>
+      <c r="C760" s="22"/>
       <c r="F760" s="9"/>
       <c r="G760" s="9"/>
       <c r="H760" s="14"/>
-      <c r="I760" s="22"/>
+      <c r="I760" s="21"/>
     </row>
     <row r="761">
-      <c r="C761" s="23"/>
+      <c r="C761" s="22"/>
       <c r="F761" s="9"/>
       <c r="G761" s="9"/>
       <c r="H761" s="14"/>
-      <c r="I761" s="22"/>
+      <c r="I761" s="21"/>
     </row>
     <row r="762">
-      <c r="C762" s="23"/>
+      <c r="C762" s="22"/>
       <c r="F762" s="9"/>
       <c r="G762" s="9"/>
       <c r="H762" s="14"/>
-      <c r="I762" s="22"/>
+      <c r="I762" s="21"/>
     </row>
     <row r="763">
-      <c r="C763" s="23"/>
+      <c r="C763" s="22"/>
       <c r="F763" s="9"/>
       <c r="G763" s="9"/>
       <c r="H763" s="14"/>
-      <c r="I763" s="22"/>
+      <c r="I763" s="21"/>
     </row>
     <row r="764">
-      <c r="C764" s="23"/>
+      <c r="C764" s="22"/>
       <c r="F764" s="9"/>
       <c r="G764" s="9"/>
       <c r="H764" s="14"/>
-      <c r="I764" s="22"/>
+      <c r="I764" s="21"/>
     </row>
     <row r="765">
-      <c r="C765" s="23"/>
+      <c r="C765" s="22"/>
       <c r="F765" s="9"/>
       <c r="G765" s="9"/>
       <c r="H765" s="14"/>
-      <c r="I765" s="22"/>
+      <c r="I765" s="21"/>
     </row>
     <row r="766">
-      <c r="C766" s="23"/>
+      <c r="C766" s="22"/>
       <c r="F766" s="9"/>
       <c r="G766" s="9"/>
       <c r="H766" s="14"/>
-      <c r="I766" s="22"/>
+      <c r="I766" s="21"/>
     </row>
     <row r="767">
-      <c r="C767" s="23"/>
+      <c r="C767" s="22"/>
       <c r="F767" s="9"/>
       <c r="G767" s="9"/>
       <c r="H767" s="14"/>
-      <c r="I767" s="22"/>
+      <c r="I767" s="21"/>
     </row>
     <row r="768">
-      <c r="C768" s="23"/>
+      <c r="C768" s="22"/>
       <c r="F768" s="9"/>
       <c r="G768" s="9"/>
       <c r="H768" s="14"/>
-      <c r="I768" s="22"/>
+      <c r="I768" s="21"/>
     </row>
     <row r="769">
-      <c r="C769" s="23"/>
+      <c r="C769" s="22"/>
       <c r="F769" s="9"/>
       <c r="G769" s="9"/>
       <c r="H769" s="14"/>
-      <c r="I769" s="22"/>
+      <c r="I769" s="21"/>
     </row>
     <row r="770">
-      <c r="C770" s="23"/>
+      <c r="C770" s="22"/>
       <c r="F770" s="9"/>
       <c r="G770" s="9"/>
       <c r="H770" s="14"/>
-      <c r="I770" s="22"/>
+      <c r="I770" s="21"/>
     </row>
     <row r="771">
-      <c r="C771" s="23"/>
+      <c r="C771" s="22"/>
       <c r="F771" s="9"/>
       <c r="G771" s="9"/>
       <c r="H771" s="14"/>
-      <c r="I771" s="22"/>
+      <c r="I771" s="21"/>
     </row>
     <row r="772">
-      <c r="C772" s="23"/>
+      <c r="C772" s="22"/>
       <c r="F772" s="9"/>
       <c r="G772" s="9"/>
       <c r="H772" s="14"/>
-      <c r="I772" s="22"/>
+      <c r="I772" s="21"/>
     </row>
     <row r="773">
-      <c r="C773" s="23"/>
+      <c r="C773" s="22"/>
       <c r="F773" s="9"/>
       <c r="G773" s="9"/>
       <c r="H773" s="14"/>
-      <c r="I773" s="22"/>
+      <c r="I773" s="21"/>
     </row>
     <row r="774">
-      <c r="C774" s="23"/>
+      <c r="C774" s="22"/>
       <c r="F774" s="9"/>
       <c r="G774" s="9"/>
       <c r="H774" s="14"/>
-      <c r="I774" s="22"/>
+      <c r="I774" s="21"/>
     </row>
     <row r="775">
-      <c r="C775" s="23"/>
+      <c r="C775" s="22"/>
       <c r="F775" s="9"/>
       <c r="G775" s="9"/>
       <c r="H775" s="14"/>
-      <c r="I775" s="22"/>
+      <c r="I775" s="21"/>
     </row>
     <row r="776">
-      <c r="C776" s="23"/>
+      <c r="C776" s="22"/>
       <c r="F776" s="9"/>
       <c r="G776" s="9"/>
       <c r="H776" s="14"/>
-      <c r="I776" s="22"/>
+      <c r="I776" s="21"/>
     </row>
     <row r="777">
-      <c r="C777" s="23"/>
+      <c r="C777" s="22"/>
       <c r="F777" s="9"/>
       <c r="G777" s="9"/>
       <c r="H777" s="14"/>
-      <c r="I777" s="22"/>
+      <c r="I777" s="21"/>
     </row>
     <row r="778">
-      <c r="C778" s="23"/>
+      <c r="C778" s="22"/>
       <c r="F778" s="9"/>
       <c r="G778" s="9"/>
       <c r="H778" s="14"/>
-      <c r="I778" s="22"/>
+      <c r="I778" s="21"/>
     </row>
     <row r="779">
-      <c r="C779" s="23"/>
+      <c r="C779" s="22"/>
       <c r="F779" s="9"/>
       <c r="G779" s="9"/>
       <c r="H779" s="14"/>
-      <c r="I779" s="22"/>
+      <c r="I779" s="21"/>
     </row>
     <row r="780">
-      <c r="C780" s="23"/>
+      <c r="C780" s="22"/>
       <c r="F780" s="9"/>
       <c r="G780" s="9"/>
       <c r="H780" s="14"/>
-      <c r="I780" s="22"/>
+      <c r="I780" s="21"/>
     </row>
     <row r="781">
-      <c r="C781" s="23"/>
+      <c r="C781" s="22"/>
       <c r="F781" s="9"/>
       <c r="G781" s="9"/>
       <c r="H781" s="14"/>
-      <c r="I781" s="22"/>
+      <c r="I781" s="21"/>
     </row>
     <row r="782">
-      <c r="C782" s="23"/>
+      <c r="C782" s="22"/>
       <c r="F782" s="9"/>
       <c r="G782" s="9"/>
       <c r="H782" s="14"/>
-      <c r="I782" s="22"/>
+      <c r="I782" s="21"/>
     </row>
     <row r="783">
-      <c r="C783" s="23"/>
+      <c r="C783" s="22"/>
       <c r="F783" s="9"/>
       <c r="G783" s="9"/>
       <c r="H783" s="14"/>
-      <c r="I783" s="22"/>
+      <c r="I783" s="21"/>
     </row>
     <row r="784">
-      <c r="C784" s="23"/>
+      <c r="C784" s="22"/>
       <c r="F784" s="9"/>
       <c r="G784" s="9"/>
       <c r="H784" s="14"/>
-      <c r="I784" s="22"/>
+      <c r="I784" s="21"/>
     </row>
     <row r="785">
-      <c r="C785" s="23"/>
+      <c r="C785" s="22"/>
       <c r="F785" s="9"/>
       <c r="G785" s="9"/>
       <c r="H785" s="14"/>
-      <c r="I785" s="22"/>
+      <c r="I785" s="21"/>
     </row>
     <row r="786">
-      <c r="C786" s="23"/>
+      <c r="C786" s="22"/>
       <c r="F786" s="9"/>
       <c r="G786" s="9"/>
       <c r="H786" s="14"/>
-      <c r="I786" s="22"/>
+      <c r="I786" s="21"/>
     </row>
     <row r="787">
-      <c r="C787" s="23"/>
+      <c r="C787" s="22"/>
       <c r="F787" s="9"/>
       <c r="G787" s="9"/>
       <c r="H787" s="14"/>
-      <c r="I787" s="22"/>
+      <c r="I787" s="21"/>
     </row>
     <row r="788">
-      <c r="C788" s="23"/>
+      <c r="C788" s="22"/>
       <c r="F788" s="9"/>
       <c r="G788" s="9"/>
       <c r="H788" s="14"/>
-      <c r="I788" s="22"/>
+      <c r="I788" s="21"/>
     </row>
     <row r="789">
-      <c r="C789" s="23"/>
+      <c r="C789" s="22"/>
       <c r="F789" s="9"/>
       <c r="G789" s="9"/>
       <c r="H789" s="14"/>
-      <c r="I789" s="22"/>
+      <c r="I789" s="21"/>
     </row>
     <row r="790">
-      <c r="C790" s="23"/>
+      <c r="C790" s="22"/>
       <c r="F790" s="9"/>
       <c r="G790" s="9"/>
       <c r="H790" s="14"/>
-      <c r="I790" s="22"/>
+      <c r="I790" s="21"/>
     </row>
     <row r="791">
-      <c r="C791" s="23"/>
+      <c r="C791" s="22"/>
       <c r="F791" s="9"/>
       <c r="G791" s="9"/>
       <c r="H791" s="14"/>
-      <c r="I791" s="22"/>
+      <c r="I791" s="21"/>
     </row>
     <row r="792">
-      <c r="C792" s="23"/>
+      <c r="C792" s="22"/>
       <c r="F792" s="9"/>
       <c r="G792" s="9"/>
       <c r="H792" s="14"/>
-      <c r="I792" s="22"/>
+      <c r="I792" s="21"/>
     </row>
     <row r="793">
-      <c r="C793" s="23"/>
+      <c r="C793" s="22"/>
       <c r="F793" s="9"/>
       <c r="G793" s="9"/>
       <c r="H793" s="14"/>
-      <c r="I793" s="22"/>
+      <c r="I793" s="21"/>
     </row>
     <row r="794">
-      <c r="C794" s="23"/>
+      <c r="C794" s="22"/>
       <c r="F794" s="9"/>
       <c r="G794" s="9"/>
       <c r="H794" s="14"/>
-      <c r="I794" s="22"/>
+      <c r="I794" s="21"/>
     </row>
     <row r="795">
-      <c r="C795" s="23"/>
+      <c r="C795" s="22"/>
       <c r="F795" s="9"/>
       <c r="G795" s="9"/>
       <c r="H795" s="14"/>
-      <c r="I795" s="22"/>
+      <c r="I795" s="21"/>
     </row>
     <row r="796">
-      <c r="C796" s="23"/>
+      <c r="C796" s="22"/>
       <c r="F796" s="9"/>
       <c r="G796" s="9"/>
       <c r="H796" s="14"/>
-      <c r="I796" s="22"/>
+      <c r="I796" s="21"/>
     </row>
     <row r="797">
-      <c r="C797" s="23"/>
+      <c r="C797" s="22"/>
       <c r="F797" s="9"/>
       <c r="G797" s="9"/>
       <c r="H797" s="14"/>
-      <c r="I797" s="22"/>
+      <c r="I797" s="21"/>
     </row>
     <row r="798">
-      <c r="C798" s="23"/>
+      <c r="C798" s="22"/>
       <c r="F798" s="9"/>
       <c r="G798" s="9"/>
       <c r="H798" s="14"/>
-      <c r="I798" s="22"/>
+      <c r="I798" s="21"/>
     </row>
     <row r="799">
-      <c r="C799" s="23"/>
+      <c r="C799" s="22"/>
       <c r="F799" s="9"/>
       <c r="G799" s="9"/>
       <c r="H799" s="14"/>
-      <c r="I799" s="22"/>
+      <c r="I799" s="21"/>
     </row>
     <row r="800">
-      <c r="C800" s="23"/>
+      <c r="C800" s="22"/>
       <c r="F800" s="9"/>
       <c r="G800" s="9"/>
       <c r="H800" s="14"/>
-      <c r="I800" s="22"/>
+      <c r="I800" s="21"/>
     </row>
     <row r="801">
-      <c r="C801" s="23"/>
+      <c r="C801" s="22"/>
       <c r="F801" s="9"/>
       <c r="G801" s="9"/>
       <c r="H801" s="14"/>
-      <c r="I801" s="22"/>
+      <c r="I801" s="21"/>
     </row>
     <row r="802">
-      <c r="C802" s="23"/>
+      <c r="C802" s="22"/>
       <c r="F802" s="9"/>
       <c r="G802" s="9"/>
       <c r="H802" s="14"/>
-      <c r="I802" s="22"/>
+      <c r="I802" s="21"/>
     </row>
     <row r="803">
-      <c r="C803" s="23"/>
+      <c r="C803" s="22"/>
       <c r="F803" s="9"/>
       <c r="G803" s="9"/>
       <c r="H803" s="14"/>
-      <c r="I803" s="22"/>
+      <c r="I803" s="21"/>
     </row>
     <row r="804">
-      <c r="C804" s="23"/>
+      <c r="C804" s="22"/>
       <c r="F804" s="9"/>
       <c r="G804" s="9"/>
       <c r="H804" s="14"/>
-      <c r="I804" s="22"/>
+      <c r="I804" s="21"/>
     </row>
     <row r="805">
-      <c r="C805" s="23"/>
+      <c r="C805" s="22"/>
       <c r="F805" s="9"/>
       <c r="G805" s="9"/>
       <c r="H805" s="14"/>
-      <c r="I805" s="22"/>
+      <c r="I805" s="21"/>
     </row>
     <row r="806">
-      <c r="C806" s="23"/>
+      <c r="C806" s="22"/>
       <c r="F806" s="9"/>
       <c r="G806" s="9"/>
       <c r="H806" s="14"/>
-      <c r="I806" s="22"/>
+      <c r="I806" s="21"/>
     </row>
     <row r="807">
-      <c r="C807" s="23"/>
+      <c r="C807" s="22"/>
       <c r="F807" s="9"/>
       <c r="G807" s="9"/>
       <c r="H807" s="14"/>
-      <c r="I807" s="22"/>
+      <c r="I807" s="21"/>
     </row>
     <row r="808">
-      <c r="C808" s="23"/>
+      <c r="C808" s="22"/>
       <c r="F808" s="9"/>
       <c r="G808" s="9"/>
       <c r="H808" s="14"/>
-      <c r="I808" s="22"/>
+      <c r="I808" s="21"/>
     </row>
     <row r="809">
-      <c r="C809" s="23"/>
+      <c r="C809" s="22"/>
       <c r="F809" s="9"/>
       <c r="G809" s="9"/>
       <c r="H809" s="14"/>
-      <c r="I809" s="22"/>
+      <c r="I809" s="21"/>
     </row>
     <row r="810">
-      <c r="C810" s="23"/>
+      <c r="C810" s="22"/>
       <c r="F810" s="9"/>
       <c r="G810" s="9"/>
       <c r="H810" s="14"/>
-      <c r="I810" s="22"/>
+      <c r="I810" s="21"/>
     </row>
     <row r="811">
-      <c r="C811" s="23"/>
+      <c r="C811" s="22"/>
       <c r="F811" s="9"/>
       <c r="G811" s="9"/>
       <c r="H811" s="14"/>
-      <c r="I811" s="22"/>
+      <c r="I811" s="21"/>
     </row>
     <row r="812">
-      <c r="C812" s="23"/>
+      <c r="C812" s="22"/>
       <c r="F812" s="9"/>
       <c r="G812" s="9"/>
       <c r="H812" s="14"/>
-      <c r="I812" s="22"/>
+      <c r="I812" s="21"/>
     </row>
     <row r="813">
-      <c r="C813" s="23"/>
+      <c r="C813" s="22"/>
       <c r="F813" s="9"/>
       <c r="G813" s="9"/>
       <c r="H813" s="14"/>
-      <c r="I813" s="22"/>
+      <c r="I813" s="21"/>
     </row>
     <row r="814">
-      <c r="C814" s="23"/>
+      <c r="C814" s="22"/>
       <c r="F814" s="9"/>
       <c r="G814" s="9"/>
       <c r="H814" s="14"/>
-      <c r="I814" s="22"/>
+      <c r="I814" s="21"/>
     </row>
     <row r="815">
-      <c r="C815" s="23"/>
+      <c r="C815" s="22"/>
       <c r="F815" s="9"/>
       <c r="G815" s="9"/>
       <c r="H815" s="14"/>
-      <c r="I815" s="22"/>
+      <c r="I815" s="21"/>
     </row>
     <row r="816">
-      <c r="C816" s="23"/>
+      <c r="C816" s="22"/>
       <c r="F816" s="9"/>
       <c r="G816" s="9"/>
       <c r="H816" s="14"/>
-      <c r="I816" s="22"/>
+      <c r="I816" s="21"/>
     </row>
     <row r="817">
-      <c r="C817" s="23"/>
+      <c r="C817" s="22"/>
       <c r="F817" s="9"/>
       <c r="G817" s="9"/>
       <c r="H817" s="14"/>
-      <c r="I817" s="22"/>
+      <c r="I817" s="21"/>
     </row>
     <row r="818">
-      <c r="C818" s="23"/>
+      <c r="C818" s="22"/>
       <c r="F818" s="9"/>
       <c r="G818" s="9"/>
       <c r="H818" s="14"/>
-      <c r="I818" s="22"/>
+      <c r="I818" s="21"/>
     </row>
     <row r="819">
-      <c r="C819" s="23"/>
+      <c r="C819" s="22"/>
       <c r="F819" s="9"/>
       <c r="G819" s="9"/>
       <c r="H819" s="14"/>
-      <c r="I819" s="22"/>
+      <c r="I819" s="21"/>
     </row>
     <row r="820">
-      <c r="C820" s="23"/>
+      <c r="C820" s="22"/>
       <c r="F820" s="9"/>
       <c r="G820" s="9"/>
       <c r="H820" s="14"/>
-      <c r="I820" s="22"/>
+      <c r="I820" s="21"/>
     </row>
     <row r="821">
-      <c r="C821" s="23"/>
+      <c r="C821" s="22"/>
       <c r="F821" s="9"/>
       <c r="G821" s="9"/>
       <c r="H821" s="14"/>
-      <c r="I821" s="22"/>
+      <c r="I821" s="21"/>
     </row>
     <row r="822">
-      <c r="C822" s="23"/>
+      <c r="C822" s="22"/>
       <c r="F822" s="9"/>
       <c r="G822" s="9"/>
       <c r="H822" s="14"/>
-      <c r="I822" s="22"/>
+      <c r="I822" s="21"/>
     </row>
     <row r="823">
-      <c r="C823" s="23"/>
+      <c r="C823" s="22"/>
       <c r="F823" s="9"/>
       <c r="G823" s="9"/>
       <c r="H823" s="14"/>
-      <c r="I823" s="22"/>
+      <c r="I823" s="21"/>
     </row>
     <row r="824">
-      <c r="C824" s="23"/>
+      <c r="C824" s="22"/>
       <c r="F824" s="9"/>
       <c r="G824" s="9"/>
       <c r="H824" s="14"/>
-      <c r="I824" s="22"/>
+      <c r="I824" s="21"/>
     </row>
     <row r="825">
-      <c r="C825" s="23"/>
+      <c r="C825" s="22"/>
       <c r="F825" s="9"/>
       <c r="G825" s="9"/>
       <c r="H825" s="14"/>
-      <c r="I825" s="22"/>
+      <c r="I825" s="21"/>
     </row>
     <row r="826">
-      <c r="C826" s="23"/>
+      <c r="C826" s="22"/>
       <c r="F826" s="9"/>
       <c r="G826" s="9"/>
       <c r="H826" s="14"/>
-      <c r="I826" s="22"/>
+      <c r="I826" s="21"/>
     </row>
     <row r="827">
-      <c r="C827" s="23"/>
+      <c r="C827" s="22"/>
       <c r="F827" s="9"/>
       <c r="G827" s="9"/>
       <c r="H827" s="14"/>
-      <c r="I827" s="22"/>
+      <c r="I827" s="21"/>
     </row>
     <row r="828">
-      <c r="C828" s="23"/>
+      <c r="C828" s="22"/>
       <c r="F828" s="9"/>
       <c r="G828" s="9"/>
       <c r="H828" s="14"/>
-      <c r="I828" s="22"/>
+      <c r="I828" s="21"/>
     </row>
     <row r="829">
-      <c r="C829" s="23"/>
+      <c r="C829" s="22"/>
       <c r="F829" s="9"/>
       <c r="G829" s="9"/>
       <c r="H829" s="14"/>
-      <c r="I829" s="22"/>
+      <c r="I829" s="21"/>
     </row>
     <row r="830">
-      <c r="C830" s="23"/>
+      <c r="C830" s="22"/>
       <c r="F830" s="9"/>
       <c r="G830" s="9"/>
       <c r="H830" s="14"/>
-      <c r="I830" s="22"/>
+      <c r="I830" s="21"/>
     </row>
     <row r="831">
-      <c r="C831" s="23"/>
+      <c r="C831" s="22"/>
       <c r="F831" s="9"/>
       <c r="G831" s="9"/>
       <c r="H831" s="14"/>
-      <c r="I831" s="22"/>
+      <c r="I831" s="21"/>
     </row>
     <row r="832">
-      <c r="C832" s="23"/>
+      <c r="C832" s="22"/>
       <c r="F832" s="9"/>
       <c r="G832" s="9"/>
       <c r="H832" s="14"/>
-      <c r="I832" s="22"/>
+      <c r="I832" s="21"/>
     </row>
     <row r="833">
-      <c r="C833" s="23"/>
+      <c r="C833" s="22"/>
       <c r="F833" s="9"/>
       <c r="G833" s="9"/>
       <c r="H833" s="14"/>
-      <c r="I833" s="22"/>
+      <c r="I833" s="21"/>
     </row>
     <row r="834">
-      <c r="C834" s="23"/>
+      <c r="C834" s="22"/>
       <c r="F834" s="9"/>
       <c r="G834" s="9"/>
       <c r="H834" s="14"/>
-      <c r="I834" s="22"/>
+      <c r="I834" s="21"/>
     </row>
     <row r="835">
-      <c r="C835" s="23"/>
+      <c r="C835" s="22"/>
       <c r="F835" s="9"/>
       <c r="G835" s="9"/>
       <c r="H835" s="14"/>
-      <c r="I835" s="22"/>
+      <c r="I835" s="21"/>
     </row>
     <row r="836">
-      <c r="C836" s="23"/>
+      <c r="C836" s="22"/>
       <c r="F836" s="9"/>
       <c r="G836" s="9"/>
       <c r="H836" s="14"/>
-      <c r="I836" s="22"/>
+      <c r="I836" s="21"/>
     </row>
     <row r="837">
-      <c r="C837" s="23"/>
+      <c r="C837" s="22"/>
       <c r="F837" s="9"/>
       <c r="G837" s="9"/>
       <c r="H837" s="14"/>
-      <c r="I837" s="22"/>
+      <c r="I837" s="21"/>
     </row>
     <row r="838">
-      <c r="C838" s="23"/>
+      <c r="C838" s="22"/>
       <c r="F838" s="9"/>
       <c r="G838" s="9"/>
       <c r="H838" s="14"/>
-      <c r="I838" s="22"/>
+      <c r="I838" s="21"/>
     </row>
     <row r="839">
-      <c r="C839" s="23"/>
+      <c r="C839" s="22"/>
       <c r="F839" s="9"/>
       <c r="G839" s="9"/>
       <c r="H839" s="14"/>
-      <c r="I839" s="22"/>
+      <c r="I839" s="21"/>
     </row>
     <row r="840">
-      <c r="C840" s="23"/>
+      <c r="C840" s="22"/>
       <c r="F840" s="9"/>
       <c r="G840" s="9"/>
       <c r="H840" s="14"/>
-      <c r="I840" s="22"/>
+      <c r="I840" s="21"/>
     </row>
     <row r="841">
-      <c r="C841" s="23"/>
+      <c r="C841" s="22"/>
       <c r="F841" s="9"/>
       <c r="G841" s="9"/>
       <c r="H841" s="14"/>
-      <c r="I841" s="22"/>
+      <c r="I841" s="21"/>
     </row>
     <row r="842">
-      <c r="C842" s="23"/>
+      <c r="C842" s="22"/>
       <c r="F842" s="9"/>
       <c r="G842" s="9"/>
       <c r="H842" s="14"/>
-      <c r="I842" s="22"/>
+      <c r="I842" s="21"/>
     </row>
     <row r="843">
-      <c r="C843" s="23"/>
+      <c r="C843" s="22"/>
       <c r="F843" s="9"/>
       <c r="G843" s="9"/>
       <c r="H843" s="14"/>
-      <c r="I843" s="22"/>
+      <c r="I843" s="21"/>
     </row>
     <row r="844">
-      <c r="C844" s="23"/>
+      <c r="C844" s="22"/>
       <c r="F844" s="9"/>
       <c r="G844" s="9"/>
       <c r="H844" s="14"/>
-      <c r="I844" s="22"/>
+      <c r="I844" s="21"/>
     </row>
     <row r="845">
-      <c r="C845" s="23"/>
+      <c r="C845" s="22"/>
       <c r="F845" s="9"/>
       <c r="G845" s="9"/>
       <c r="H845" s="14"/>
-      <c r="I845" s="22"/>
+      <c r="I845" s="21"/>
     </row>
     <row r="846">
-      <c r="C846" s="23"/>
+      <c r="C846" s="22"/>
       <c r="F846" s="9"/>
       <c r="G846" s="9"/>
       <c r="H846" s="14"/>
-      <c r="I846" s="22"/>
+      <c r="I846" s="21"/>
     </row>
     <row r="847">
-      <c r="C847" s="23"/>
+      <c r="C847" s="22"/>
       <c r="F847" s="9"/>
       <c r="G847" s="9"/>
       <c r="H847" s="14"/>
-      <c r="I847" s="22"/>
+      <c r="I847" s="21"/>
     </row>
     <row r="848">
-      <c r="C848" s="23"/>
+      <c r="C848" s="22"/>
       <c r="F848" s="9"/>
       <c r="G848" s="9"/>
       <c r="H848" s="14"/>
-      <c r="I848" s="22"/>
+      <c r="I848" s="21"/>
     </row>
     <row r="849">
-      <c r="C849" s="23"/>
+      <c r="C849" s="22"/>
       <c r="F849" s="9"/>
       <c r="G849" s="9"/>
       <c r="H849" s="14"/>
-      <c r="I849" s="22"/>
+      <c r="I849" s="21"/>
     </row>
     <row r="850">
-      <c r="C850" s="23"/>
+      <c r="C850" s="22"/>
       <c r="F850" s="9"/>
       <c r="G850" s="9"/>
       <c r="H850" s="14"/>
-      <c r="I850" s="22"/>
+      <c r="I850" s="21"/>
     </row>
     <row r="851">
-      <c r="C851" s="23"/>
+      <c r="C851" s="22"/>
       <c r="F851" s="9"/>
       <c r="G851" s="9"/>
       <c r="H851" s="14"/>
-      <c r="I851" s="22"/>
+      <c r="I851" s="21"/>
     </row>
     <row r="852">
-      <c r="C852" s="23"/>
+      <c r="C852" s="22"/>
       <c r="F852" s="9"/>
       <c r="G852" s="9"/>
       <c r="H852" s="14"/>
-      <c r="I852" s="22"/>
+      <c r="I852" s="21"/>
     </row>
     <row r="853">
-      <c r="C853" s="23"/>
+      <c r="C853" s="22"/>
       <c r="F853" s="9"/>
       <c r="G853" s="9"/>
       <c r="H853" s="14"/>
-      <c r="I853" s="22"/>
+      <c r="I853" s="21"/>
     </row>
     <row r="854">
-      <c r="C854" s="23"/>
+      <c r="C854" s="22"/>
       <c r="F854" s="9"/>
       <c r="G854" s="9"/>
       <c r="H854" s="14"/>
-      <c r="I854" s="22"/>
+      <c r="I854" s="21"/>
     </row>
     <row r="855">
-      <c r="C855" s="23"/>
+      <c r="C855" s="22"/>
       <c r="F855" s="9"/>
       <c r="G855" s="9"/>
       <c r="H855" s="14"/>
-      <c r="I855" s="22"/>
+      <c r="I855" s="21"/>
     </row>
     <row r="856">
-      <c r="C856" s="23"/>
+      <c r="C856" s="22"/>
       <c r="F856" s="9"/>
       <c r="G856" s="9"/>
       <c r="H856" s="14"/>
-      <c r="I856" s="22"/>
+      <c r="I856" s="21"/>
     </row>
     <row r="857">
-      <c r="C857" s="23"/>
+      <c r="C857" s="22"/>
       <c r="F857" s="9"/>
       <c r="G857" s="9"/>
       <c r="H857" s="14"/>
-      <c r="I857" s="22"/>
+      <c r="I857" s="21"/>
     </row>
     <row r="858">
-      <c r="C858" s="23"/>
+      <c r="C858" s="22"/>
       <c r="F858" s="9"/>
       <c r="G858" s="9"/>
       <c r="H858" s="14"/>
-      <c r="I858" s="22"/>
+      <c r="I858" s="21"/>
     </row>
     <row r="859">
-      <c r="C859" s="23"/>
+      <c r="C859" s="22"/>
       <c r="F859" s="9"/>
       <c r="G859" s="9"/>
       <c r="H859" s="14"/>
-      <c r="I859" s="22"/>
+      <c r="I859" s="21"/>
     </row>
     <row r="860">
-      <c r="C860" s="23"/>
+      <c r="C860" s="22"/>
       <c r="F860" s="9"/>
       <c r="G860" s="9"/>
       <c r="H860" s="14"/>
-      <c r="I860" s="22"/>
+      <c r="I860" s="21"/>
     </row>
     <row r="861">
-      <c r="C861" s="23"/>
+      <c r="C861" s="22"/>
       <c r="F861" s="9"/>
       <c r="G861" s="9"/>
       <c r="H861" s="14"/>
-      <c r="I861" s="22"/>
+      <c r="I861" s="21"/>
     </row>
     <row r="862">
-      <c r="C862" s="23"/>
+      <c r="C862" s="22"/>
       <c r="F862" s="9"/>
       <c r="G862" s="9"/>
       <c r="H862" s="14"/>
-      <c r="I862" s="22"/>
+      <c r="I862" s="21"/>
     </row>
     <row r="863">
-      <c r="C863" s="23"/>
+      <c r="C863" s="22"/>
       <c r="F863" s="9"/>
       <c r="G863" s="9"/>
       <c r="H863" s="14"/>
-      <c r="I863" s="22"/>
+      <c r="I863" s="21"/>
     </row>
     <row r="864">
-      <c r="C864" s="23"/>
+      <c r="C864" s="22"/>
       <c r="F864" s="9"/>
       <c r="G864" s="9"/>
       <c r="H864" s="14"/>
-      <c r="I864" s="22"/>
+      <c r="I864" s="21"/>
     </row>
     <row r="865">
-      <c r="C865" s="23"/>
+      <c r="C865" s="22"/>
       <c r="F865" s="9"/>
       <c r="G865" s="9"/>
       <c r="H865" s="14"/>
-      <c r="I865" s="22"/>
+      <c r="I865" s="21"/>
     </row>
     <row r="866">
-      <c r="C866" s="23"/>
+      <c r="C866" s="22"/>
       <c r="F866" s="9"/>
       <c r="G866" s="9"/>
       <c r="H866" s="14"/>
-      <c r="I866" s="22"/>
+      <c r="I866" s="21"/>
     </row>
     <row r="867">
-      <c r="C867" s="23"/>
+      <c r="C867" s="22"/>
       <c r="F867" s="9"/>
       <c r="G867" s="9"/>
       <c r="H867" s="14"/>
-      <c r="I867" s="22"/>
+      <c r="I867" s="21"/>
     </row>
     <row r="868">
-      <c r="C868" s="23"/>
+      <c r="C868" s="22"/>
       <c r="F868" s="9"/>
       <c r="G868" s="9"/>
       <c r="H868" s="14"/>
-      <c r="I868" s="22"/>
+      <c r="I868" s="21"/>
     </row>
     <row r="869">
-      <c r="C869" s="23"/>
+      <c r="C869" s="22"/>
       <c r="F869" s="9"/>
       <c r="G869" s="9"/>
       <c r="H869" s="14"/>
-      <c r="I869" s="22"/>
+      <c r="I869" s="21"/>
     </row>
     <row r="870">
-      <c r="C870" s="23"/>
+      <c r="C870" s="22"/>
       <c r="F870" s="9"/>
       <c r="G870" s="9"/>
       <c r="H870" s="14"/>
-      <c r="I870" s="22"/>
+      <c r="I870" s="21"/>
     </row>
     <row r="871">
-      <c r="C871" s="23"/>
+      <c r="C871" s="22"/>
       <c r="F871" s="9"/>
       <c r="G871" s="9"/>
       <c r="H871" s="14"/>
-      <c r="I871" s="22"/>
+      <c r="I871" s="21"/>
     </row>
     <row r="872">
-      <c r="C872" s="23"/>
+      <c r="C872" s="22"/>
       <c r="F872" s="9"/>
       <c r="G872" s="9"/>
       <c r="H872" s="14"/>
-      <c r="I872" s="22"/>
+      <c r="I872" s="21"/>
     </row>
     <row r="873">
-      <c r="C873" s="23"/>
+      <c r="C873" s="22"/>
       <c r="F873" s="9"/>
       <c r="G873" s="9"/>
       <c r="H873" s="14"/>
-      <c r="I873" s="22"/>
+      <c r="I873" s="21"/>
     </row>
     <row r="874">
-      <c r="C874" s="23"/>
+      <c r="C874" s="22"/>
       <c r="F874" s="9"/>
       <c r="G874" s="9"/>
       <c r="H874" s="14"/>
-      <c r="I874" s="22"/>
+      <c r="I874" s="21"/>
     </row>
     <row r="875">
-      <c r="C875" s="23"/>
+      <c r="C875" s="22"/>
       <c r="F875" s="9"/>
       <c r="G875" s="9"/>
       <c r="H875" s="14"/>
-      <c r="I875" s="22"/>
+      <c r="I875" s="21"/>
     </row>
     <row r="876">
-      <c r="C876" s="23"/>
+      <c r="C876" s="22"/>
       <c r="F876" s="9"/>
       <c r="G876" s="9"/>
       <c r="H876" s="14"/>
-      <c r="I876" s="22"/>
+      <c r="I876" s="21"/>
     </row>
     <row r="877">
-      <c r="C877" s="23"/>
+      <c r="C877" s="22"/>
       <c r="F877" s="9"/>
       <c r="G877" s="9"/>
       <c r="H877" s="14"/>
-      <c r="I877" s="22"/>
+      <c r="I877" s="21"/>
     </row>
     <row r="878">
-      <c r="C878" s="23"/>
+      <c r="C878" s="22"/>
       <c r="F878" s="9"/>
       <c r="G878" s="9"/>
       <c r="H878" s="14"/>
-      <c r="I878" s="22"/>
+      <c r="I878" s="21"/>
     </row>
     <row r="879">
-      <c r="C879" s="23"/>
+      <c r="C879" s="22"/>
       <c r="F879" s="9"/>
       <c r="G879" s="9"/>
       <c r="H879" s="14"/>
-      <c r="I879" s="22"/>
+      <c r="I879" s="21"/>
     </row>
     <row r="880">
-      <c r="C880" s="23"/>
+      <c r="C880" s="22"/>
       <c r="F880" s="9"/>
       <c r="G880" s="9"/>
       <c r="H880" s="14"/>
-      <c r="I880" s="22"/>
+      <c r="I880" s="21"/>
     </row>
     <row r="881">
-      <c r="C881" s="23"/>
+      <c r="C881" s="22"/>
       <c r="F881" s="9"/>
       <c r="G881" s="9"/>
       <c r="H881" s="14"/>
-      <c r="I881" s="22"/>
+      <c r="I881" s="21"/>
     </row>
     <row r="882">
-      <c r="C882" s="23"/>
+      <c r="C882" s="22"/>
       <c r="F882" s="9"/>
       <c r="G882" s="9"/>
       <c r="H882" s="14"/>
-      <c r="I882" s="22"/>
+      <c r="I882" s="21"/>
     </row>
     <row r="883">
-      <c r="C883" s="23"/>
+      <c r="C883" s="22"/>
       <c r="F883" s="9"/>
       <c r="G883" s="9"/>
       <c r="H883" s="14"/>
-      <c r="I883" s="22"/>
+      <c r="I883" s="21"/>
     </row>
     <row r="884">
-      <c r="C884" s="23"/>
+      <c r="C884" s="22"/>
       <c r="F884" s="9"/>
       <c r="G884" s="9"/>
       <c r="H884" s="14"/>
-      <c r="I884" s="22"/>
+      <c r="I884" s="21"/>
     </row>
     <row r="885">
-      <c r="C885" s="23"/>
+      <c r="C885" s="22"/>
       <c r="F885" s="9"/>
       <c r="G885" s="9"/>
       <c r="H885" s="14"/>
-      <c r="I885" s="22"/>
+      <c r="I885" s="21"/>
     </row>
     <row r="886">
-      <c r="C886" s="23"/>
+      <c r="C886" s="22"/>
       <c r="F886" s="9"/>
       <c r="G886" s="9"/>
       <c r="H886" s="14"/>
-      <c r="I886" s="22"/>
+      <c r="I886" s="21"/>
     </row>
     <row r="887">
-      <c r="C887" s="23"/>
+      <c r="C887" s="22"/>
       <c r="F887" s="9"/>
       <c r="G887" s="9"/>
       <c r="H887" s="14"/>
-      <c r="I887" s="22"/>
+      <c r="I887" s="21"/>
     </row>
     <row r="888">
-      <c r="C888" s="23"/>
+      <c r="C888" s="22"/>
       <c r="F888" s="9"/>
       <c r="G888" s="9"/>
       <c r="H888" s="14"/>
-      <c r="I888" s="22"/>
+      <c r="I888" s="21"/>
     </row>
     <row r="889">
-      <c r="C889" s="23"/>
+      <c r="C889" s="22"/>
       <c r="F889" s="9"/>
       <c r="G889" s="9"/>
       <c r="H889" s="14"/>
-      <c r="I889" s="22"/>
+      <c r="I889" s="21"/>
     </row>
     <row r="890">
-      <c r="C890" s="23"/>
+      <c r="C890" s="22"/>
       <c r="F890" s="9"/>
       <c r="G890" s="9"/>
       <c r="H890" s="14"/>
-      <c r="I890" s="22"/>
+      <c r="I890" s="21"/>
     </row>
     <row r="891">
-      <c r="C891" s="23"/>
+      <c r="C891" s="22"/>
       <c r="F891" s="9"/>
       <c r="G891" s="9"/>
       <c r="H891" s="14"/>
-      <c r="I891" s="22"/>
+      <c r="I891" s="21"/>
     </row>
     <row r="892">
-      <c r="C892" s="23"/>
+      <c r="C892" s="22"/>
       <c r="F892" s="9"/>
       <c r="G892" s="9"/>
       <c r="H892" s="14"/>
-      <c r="I892" s="22"/>
+      <c r="I892" s="21"/>
     </row>
     <row r="893">
-      <c r="C893" s="23"/>
+      <c r="C893" s="22"/>
       <c r="F893" s="9"/>
       <c r="G893" s="9"/>
       <c r="H893" s="14"/>
-      <c r="I893" s="22"/>
+      <c r="I893" s="21"/>
     </row>
     <row r="894">
-      <c r="C894" s="23"/>
+      <c r="C894" s="22"/>
       <c r="F894" s="9"/>
       <c r="G894" s="9"/>
       <c r="H894" s="14"/>
-      <c r="I894" s="22"/>
+      <c r="I894" s="21"/>
     </row>
     <row r="895">
-      <c r="C895" s="23"/>
+      <c r="C895" s="22"/>
       <c r="F895" s="9"/>
       <c r="G895" s="9"/>
       <c r="H895" s="14"/>
-      <c r="I895" s="22"/>
+      <c r="I895" s="21"/>
     </row>
     <row r="896">
-      <c r="C896" s="23"/>
+      <c r="C896" s="22"/>
       <c r="F896" s="9"/>
       <c r="G896" s="9"/>
       <c r="H896" s="14"/>
-      <c r="I896" s="22"/>
+      <c r="I896" s="21"/>
     </row>
     <row r="897">
-      <c r="C897" s="23"/>
+      <c r="C897" s="22"/>
       <c r="F897" s="9"/>
       <c r="G897" s="9"/>
       <c r="H897" s="14"/>
-      <c r="I897" s="22"/>
+      <c r="I897" s="21"/>
     </row>
     <row r="898">
-      <c r="C898" s="23"/>
+      <c r="C898" s="22"/>
       <c r="F898" s="9"/>
       <c r="G898" s="9"/>
       <c r="H898" s="14"/>
-      <c r="I898" s="22"/>
+      <c r="I898" s="21"/>
     </row>
     <row r="899">
-      <c r="C899" s="23"/>
+      <c r="C899" s="22"/>
       <c r="F899" s="9"/>
       <c r="G899" s="9"/>
       <c r="H899" s="14"/>
-      <c r="I899" s="22"/>
+      <c r="I899" s="21"/>
     </row>
     <row r="900">
-      <c r="C900" s="23"/>
+      <c r="C900" s="22"/>
       <c r="F900" s="9"/>
       <c r="G900" s="9"/>
       <c r="H900" s="14"/>
-      <c r="I900" s="22"/>
+      <c r="I900" s="21"/>
     </row>
     <row r="901">
-      <c r="C901" s="23"/>
+      <c r="C901" s="22"/>
       <c r="F901" s="9"/>
       <c r="G901" s="9"/>
       <c r="H901" s="14"/>
-      <c r="I901" s="22"/>
+      <c r="I901" s="21"/>
     </row>
     <row r="902">
-      <c r="C902" s="23"/>
+      <c r="C902" s="22"/>
       <c r="F902" s="9"/>
       <c r="G902" s="9"/>
       <c r="H902" s="14"/>
-      <c r="I902" s="22"/>
+      <c r="I902" s="21"/>
     </row>
     <row r="903">
-      <c r="C903" s="23"/>
+      <c r="C903" s="22"/>
       <c r="F903" s="9"/>
       <c r="G903" s="9"/>
       <c r="H903" s="14"/>
-      <c r="I903" s="22"/>
+      <c r="I903" s="21"/>
     </row>
     <row r="904">
-      <c r="C904" s="23"/>
+      <c r="C904" s="22"/>
       <c r="F904" s="9"/>
       <c r="G904" s="9"/>
       <c r="H904" s="14"/>
-      <c r="I904" s="22"/>
+      <c r="I904" s="21"/>
     </row>
     <row r="905">
-      <c r="C905" s="23"/>
+      <c r="C905" s="22"/>
       <c r="F905" s="9"/>
       <c r="G905" s="9"/>
       <c r="H905" s="14"/>
-      <c r="I905" s="22"/>
+      <c r="I905" s="21"/>
     </row>
     <row r="906">
-      <c r="C906" s="23"/>
+      <c r="C906" s="22"/>
       <c r="F906" s="9"/>
       <c r="G906" s="9"/>
       <c r="H906" s="14"/>
-      <c r="I906" s="22"/>
+      <c r="I906" s="21"/>
     </row>
     <row r="907">
-      <c r="C907" s="23"/>
+      <c r="C907" s="22"/>
       <c r="F907" s="9"/>
       <c r="G907" s="9"/>
       <c r="H907" s="14"/>
-      <c r="I907" s="22"/>
+      <c r="I907" s="21"/>
     </row>
     <row r="908">
-      <c r="C908" s="23"/>
+      <c r="C908" s="22"/>
       <c r="F908" s="9"/>
       <c r="G908" s="9"/>
       <c r="H908" s="14"/>
-      <c r="I908" s="22"/>
+      <c r="I908" s="21"/>
     </row>
     <row r="909">
-      <c r="C909" s="23"/>
+      <c r="C909" s="22"/>
       <c r="F909" s="9"/>
       <c r="G909" s="9"/>
       <c r="H909" s="14"/>
-      <c r="I909" s="22"/>
+      <c r="I909" s="21"/>
     </row>
     <row r="910">
-      <c r="C910" s="23"/>
+      <c r="C910" s="22"/>
       <c r="F910" s="9"/>
       <c r="G910" s="9"/>
       <c r="H910" s="14"/>
-      <c r="I910" s="22"/>
+      <c r="I910" s="21"/>
     </row>
     <row r="911">
-      <c r="C911" s="23"/>
+      <c r="C911" s="22"/>
       <c r="F911" s="9"/>
       <c r="G911" s="9"/>
       <c r="H911" s="14"/>
-      <c r="I911" s="22"/>
+      <c r="I911" s="21"/>
     </row>
     <row r="912">
-      <c r="C912" s="23"/>
+      <c r="C912" s="22"/>
       <c r="F912" s="9"/>
       <c r="G912" s="9"/>
       <c r="H912" s="14"/>
-      <c r="I912" s="22"/>
+      <c r="I912" s="21"/>
     </row>
     <row r="913">
-      <c r="C913" s="23"/>
+      <c r="C913" s="22"/>
       <c r="F913" s="9"/>
       <c r="G913" s="9"/>
       <c r="H913" s="14"/>
-      <c r="I913" s="22"/>
+      <c r="I913" s="21"/>
     </row>
     <row r="914">
-      <c r="C914" s="23"/>
+      <c r="C914" s="22"/>
       <c r="F914" s="9"/>
       <c r="G914" s="9"/>
       <c r="H914" s="14"/>
-      <c r="I914" s="22"/>
+      <c r="I914" s="21"/>
     </row>
     <row r="915">
-      <c r="C915" s="23"/>
+      <c r="C915" s="22"/>
       <c r="F915" s="9"/>
       <c r="G915" s="9"/>
       <c r="H915" s="14"/>
-      <c r="I915" s="22"/>
+      <c r="I915" s="21"/>
     </row>
     <row r="916">
-      <c r="C916" s="23"/>
+      <c r="C916" s="22"/>
       <c r="F916" s="9"/>
       <c r="G916" s="9"/>
       <c r="H916" s="14"/>
-      <c r="I916" s="22"/>
+      <c r="I916" s="21"/>
     </row>
     <row r="917">
-      <c r="C917" s="23"/>
+      <c r="C917" s="22"/>
       <c r="F917" s="9"/>
       <c r="G917" s="9"/>
       <c r="H917" s="14"/>
-      <c r="I917" s="22"/>
+      <c r="I917" s="21"/>
     </row>
     <row r="918">
-      <c r="C918" s="23"/>
+      <c r="C918" s="22"/>
       <c r="F918" s="9"/>
       <c r="G918" s="9"/>
       <c r="H918" s="14"/>
-      <c r="I918" s="22"/>
+      <c r="I918" s="21"/>
     </row>
     <row r="919">
-      <c r="C919" s="23"/>
+      <c r="C919" s="22"/>
       <c r="F919" s="9"/>
       <c r="G919" s="9"/>
       <c r="H919" s="14"/>
-      <c r="I919" s="22"/>
+      <c r="I919" s="21"/>
     </row>
     <row r="920">
-      <c r="C920" s="23"/>
+      <c r="C920" s="22"/>
       <c r="F920" s="9"/>
       <c r="G920" s="9"/>
       <c r="H920" s="14"/>
-      <c r="I920" s="22"/>
+      <c r="I920" s="21"/>
     </row>
     <row r="921">
-      <c r="C921" s="23"/>
+      <c r="C921" s="22"/>
       <c r="F921" s="9"/>
       <c r="G921" s="9"/>
       <c r="H921" s="14"/>
-      <c r="I921" s="22"/>
+      <c r="I921" s="21"/>
     </row>
     <row r="922">
-      <c r="C922" s="23"/>
+      <c r="C922" s="22"/>
       <c r="F922" s="9"/>
       <c r="G922" s="9"/>
       <c r="H922" s="14"/>
-      <c r="I922" s="22"/>
+      <c r="I922" s="21"/>
     </row>
     <row r="923">
-      <c r="C923" s="23"/>
+      <c r="C923" s="22"/>
       <c r="F923" s="9"/>
       <c r="G923" s="9"/>
       <c r="H923" s="14"/>
-      <c r="I923" s="22"/>
+      <c r="I923" s="21"/>
     </row>
     <row r="924">
-      <c r="C924" s="23"/>
+      <c r="C924" s="22"/>
       <c r="F924" s="9"/>
       <c r="G924" s="9"/>
       <c r="H924" s="14"/>
-      <c r="I924" s="22"/>
+      <c r="I924" s="21"/>
     </row>
     <row r="925">
-      <c r="C925" s="23"/>
+      <c r="C925" s="22"/>
       <c r="F925" s="9"/>
       <c r="G925" s="9"/>
       <c r="H925" s="14"/>
-      <c r="I925" s="22"/>
+      <c r="I925" s="21"/>
     </row>
     <row r="926">
-      <c r="C926" s="23"/>
+      <c r="C926" s="22"/>
       <c r="F926" s="9"/>
       <c r="G926" s="9"/>
       <c r="H926" s="14"/>
-      <c r="I926" s="22"/>
+      <c r="I926" s="21"/>
     </row>
     <row r="927">
-      <c r="C927" s="23"/>
+      <c r="C927" s="22"/>
       <c r="F927" s="9"/>
       <c r="G927" s="9"/>
       <c r="H927" s="14"/>
-      <c r="I927" s="22"/>
+      <c r="I927" s="21"/>
     </row>
     <row r="928">
-      <c r="C928" s="23"/>
+      <c r="C928" s="22"/>
       <c r="F928" s="9"/>
       <c r="G928" s="9"/>
       <c r="H928" s="14"/>
-      <c r="I928" s="22"/>
+      <c r="I928" s="21"/>
     </row>
     <row r="929">
-      <c r="C929" s="23"/>
+      <c r="C929" s="22"/>
       <c r="F929" s="9"/>
       <c r="G929" s="9"/>
       <c r="H929" s="14"/>
-      <c r="I929" s="22"/>
+      <c r="I929" s="21"/>
     </row>
     <row r="930">
-      <c r="C930" s="23"/>
+      <c r="C930" s="22"/>
       <c r="F930" s="9"/>
       <c r="G930" s="9"/>
       <c r="H930" s="14"/>
-      <c r="I930" s="22"/>
+      <c r="I930" s="21"/>
     </row>
     <row r="931">
-      <c r="C931" s="23"/>
+      <c r="C931" s="22"/>
       <c r="F931" s="9"/>
       <c r="G931" s="9"/>
       <c r="H931" s="14"/>
-      <c r="I931" s="22"/>
+      <c r="I931" s="21"/>
     </row>
     <row r="932">
-      <c r="C932" s="23"/>
+      <c r="C932" s="22"/>
       <c r="F932" s="9"/>
       <c r="G932" s="9"/>
       <c r="H932" s="14"/>
-      <c r="I932" s="22"/>
+      <c r="I932" s="21"/>
     </row>
     <row r="933">
-      <c r="C933" s="23"/>
+      <c r="C933" s="22"/>
       <c r="F933" s="9"/>
       <c r="G933" s="9"/>
       <c r="H933" s="14"/>
-      <c r="I933" s="22"/>
+      <c r="I933" s="21"/>
     </row>
     <row r="934">
-      <c r="C934" s="23"/>
+      <c r="C934" s="22"/>
       <c r="F934" s="9"/>
       <c r="G934" s="9"/>
       <c r="H934" s="14"/>
-      <c r="I934" s="22"/>
+      <c r="I934" s="21"/>
     </row>
     <row r="935">
-      <c r="C935" s="23"/>
+      <c r="C935" s="22"/>
       <c r="F935" s="9"/>
       <c r="G935" s="9"/>
       <c r="H935" s="14"/>
-      <c r="I935" s="22"/>
+      <c r="I935" s="21"/>
     </row>
     <row r="936">
-      <c r="C936" s="23"/>
+      <c r="C936" s="22"/>
       <c r="F936" s="9"/>
       <c r="G936" s="9"/>
       <c r="H936" s="14"/>
-      <c r="I936" s="22"/>
+      <c r="I936" s="21"/>
     </row>
     <row r="937">
-      <c r="C937" s="23"/>
+      <c r="C937" s="22"/>
       <c r="F937" s="9"/>
       <c r="G937" s="9"/>
       <c r="H937" s="14"/>
-      <c r="I937" s="22"/>
+      <c r="I937" s="21"/>
     </row>
     <row r="938">
-      <c r="C938" s="23"/>
+      <c r="C938" s="22"/>
       <c r="F938" s="9"/>
       <c r="G938" s="9"/>
       <c r="H938" s="14"/>
-      <c r="I938" s="22"/>
+      <c r="I938" s="21"/>
     </row>
     <row r="939">
-      <c r="C939" s="23"/>
+      <c r="C939" s="22"/>
       <c r="F939" s="9"/>
       <c r="G939" s="9"/>
       <c r="H939" s="14"/>
-      <c r="I939" s="22"/>
+      <c r="I939" s="21"/>
     </row>
     <row r="940">
-      <c r="C940" s="23"/>
+      <c r="C940" s="22"/>
       <c r="F940" s="9"/>
       <c r="G940" s="9"/>
       <c r="H940" s="14"/>
-      <c r="I940" s="22"/>
+      <c r="I940" s="21"/>
     </row>
     <row r="941">
-      <c r="C941" s="23"/>
+      <c r="C941" s="22"/>
       <c r="F941" s="9"/>
       <c r="G941" s="9"/>
       <c r="H941" s="14"/>
-      <c r="I941" s="22"/>
+      <c r="I941" s="21"/>
     </row>
     <row r="942">
-      <c r="C942" s="23"/>
+      <c r="C942" s="22"/>
       <c r="F942" s="9"/>
       <c r="G942" s="9"/>
       <c r="H942" s="14"/>
-      <c r="I942" s="22"/>
+      <c r="I942" s="21"/>
     </row>
     <row r="943">
-      <c r="C943" s="23"/>
+      <c r="C943" s="22"/>
       <c r="F943" s="9"/>
       <c r="G943" s="9"/>
       <c r="H943" s="14"/>
-      <c r="I943" s="22"/>
+      <c r="I943" s="21"/>
     </row>
     <row r="944">
-      <c r="C944" s="23"/>
+      <c r="C944" s="22"/>
       <c r="F944" s="9"/>
       <c r="G944" s="9"/>
       <c r="H944" s="14"/>
-      <c r="I944" s="22"/>
+      <c r="I944" s="21"/>
     </row>
     <row r="945">
-      <c r="C945" s="23"/>
+      <c r="C945" s="22"/>
       <c r="F945" s="9"/>
       <c r="G945" s="9"/>
       <c r="H945" s="14"/>
-      <c r="I945" s="22"/>
+      <c r="I945" s="21"/>
     </row>
     <row r="946">
-      <c r="C946" s="23"/>
+      <c r="C946" s="22"/>
       <c r="F946" s="9"/>
       <c r="G946" s="9"/>
       <c r="H946" s="14"/>
-      <c r="I946" s="22"/>
+      <c r="I946" s="21"/>
     </row>
     <row r="947">
-      <c r="C947" s="23"/>
+      <c r="C947" s="22"/>
       <c r="F947" s="9"/>
       <c r="G947" s="9"/>
       <c r="H947" s="14"/>
-      <c r="I947" s="22"/>
+      <c r="I947" s="21"/>
     </row>
     <row r="948">
-      <c r="C948" s="23"/>
+      <c r="C948" s="22"/>
       <c r="F948" s="9"/>
       <c r="G948" s="9"/>
       <c r="H948" s="14"/>
-      <c r="I948" s="22"/>
+      <c r="I948" s="21"/>
     </row>
     <row r="949">
-      <c r="C949" s="23"/>
+      <c r="C949" s="22"/>
       <c r="F949" s="9"/>
       <c r="G949" s="9"/>
       <c r="H949" s="14"/>
-      <c r="I949" s="22"/>
+      <c r="I949" s="21"/>
     </row>
     <row r="950">
-      <c r="C950" s="23"/>
+      <c r="C950" s="22"/>
       <c r="F950" s="9"/>
       <c r="G950" s="9"/>
       <c r="H950" s="14"/>
-      <c r="I950" s="22"/>
+      <c r="I950" s="21"/>
     </row>
     <row r="951">
-      <c r="C951" s="23"/>
+      <c r="C951" s="22"/>
       <c r="F951" s="9"/>
       <c r="G951" s="9"/>
       <c r="H951" s="14"/>
-      <c r="I951" s="22"/>
+      <c r="I951" s="21"/>
     </row>
     <row r="952">
-      <c r="C952" s="23"/>
+      <c r="C952" s="22"/>
       <c r="F952" s="9"/>
       <c r="G952" s="9"/>
       <c r="H952" s="14"/>
-      <c r="I952" s="22"/>
+      <c r="I952" s="21"/>
     </row>
     <row r="953">
-      <c r="C953" s="23"/>
+      <c r="C953" s="22"/>
       <c r="F953" s="9"/>
       <c r="G953" s="9"/>
       <c r="H953" s="14"/>
-      <c r="I953" s="22"/>
+      <c r="I953" s="21"/>
     </row>
     <row r="954">
-      <c r="C954" s="23"/>
+      <c r="C954" s="22"/>
       <c r="F954" s="9"/>
       <c r="G954" s="9"/>
       <c r="H954" s="14"/>
-      <c r="I954" s="22"/>
+      <c r="I954" s="21"/>
     </row>
     <row r="955">
-      <c r="C955" s="23"/>
+      <c r="C955" s="22"/>
       <c r="F955" s="9"/>
       <c r="G955" s="9"/>
       <c r="H955" s="14"/>
-      <c r="I955" s="22"/>
+      <c r="I955" s="21"/>
     </row>
     <row r="956">
-      <c r="C956" s="23"/>
+      <c r="C956" s="22"/>
       <c r="F956" s="9"/>
       <c r="G956" s="9"/>
       <c r="H956" s="14"/>
-      <c r="I956" s="22"/>
+      <c r="I956" s="21"/>
     </row>
     <row r="957">
-      <c r="C957" s="23"/>
+      <c r="C957" s="22"/>
       <c r="F957" s="9"/>
       <c r="G957" s="9"/>
       <c r="H957" s="14"/>
-      <c r="I957" s="22"/>
+      <c r="I957" s="21"/>
     </row>
     <row r="958">
-      <c r="C958" s="23"/>
+      <c r="C958" s="22"/>
       <c r="F958" s="9"/>
       <c r="G958" s="9"/>
       <c r="H958" s="14"/>
-      <c r="I958" s="22"/>
+      <c r="I958" s="21"/>
     </row>
     <row r="959">
-      <c r="C959" s="23"/>
+      <c r="C959" s="22"/>
       <c r="F959" s="9"/>
       <c r="G959" s="9"/>
       <c r="H959" s="14"/>
-      <c r="I959" s="22"/>
+      <c r="I959" s="21"/>
     </row>
     <row r="960">
-      <c r="C960" s="23"/>
+      <c r="C960" s="22"/>
       <c r="F960" s="9"/>
       <c r="G960" s="9"/>
       <c r="H960" s="14"/>
-      <c r="I960" s="22"/>
+      <c r="I960" s="21"/>
     </row>
     <row r="961">
-      <c r="C961" s="23"/>
+      <c r="C961" s="22"/>
       <c r="F961" s="9"/>
       <c r="G961" s="9"/>
       <c r="H961" s="14"/>
-      <c r="I961" s="22"/>
+      <c r="I961" s="21"/>
     </row>
     <row r="962">
-      <c r="C962" s="23"/>
+      <c r="C962" s="22"/>
       <c r="F962" s="9"/>
       <c r="G962" s="9"/>
       <c r="H962" s="14"/>
-      <c r="I962" s="22"/>
+      <c r="I962" s="21"/>
     </row>
     <row r="963">
-      <c r="C963" s="23"/>
+      <c r="C963" s="22"/>
       <c r="F963" s="9"/>
       <c r="G963" s="9"/>
       <c r="H963" s="14"/>
-      <c r="I963" s="22"/>
+      <c r="I963" s="21"/>
     </row>
     <row r="964">
-      <c r="C964" s="23"/>
+      <c r="C964" s="22"/>
       <c r="F964" s="9"/>
       <c r="G964" s="9"/>
       <c r="H964" s="14"/>
-      <c r="I964" s="22"/>
+      <c r="I964" s="21"/>
     </row>
     <row r="965">
-      <c r="C965" s="23"/>
+      <c r="C965" s="22"/>
       <c r="F965" s="9"/>
       <c r="G965" s="9"/>
       <c r="H965" s="14"/>
-      <c r="I965" s="22"/>
+      <c r="I965" s="21"/>
     </row>
     <row r="966">
-      <c r="C966" s="23"/>
+      <c r="C966" s="22"/>
       <c r="F966" s="9"/>
       <c r="G966" s="9"/>
       <c r="H966" s="14"/>
-      <c r="I966" s="22"/>
+      <c r="I966" s="21"/>
     </row>
     <row r="967">
-      <c r="C967" s="23"/>
+      <c r="C967" s="22"/>
       <c r="F967" s="9"/>
       <c r="G967" s="9"/>
       <c r="H967" s="14"/>
-      <c r="I967" s="22"/>
+      <c r="I967" s="21"/>
     </row>
     <row r="968">
-      <c r="C968" s="23"/>
+      <c r="C968" s="22"/>
       <c r="F968" s="9"/>
       <c r="G968" s="9"/>
       <c r="H968" s="14"/>
-      <c r="I968" s="22"/>
+      <c r="I968" s="21"/>
     </row>
     <row r="969">
-      <c r="C969" s="23"/>
+      <c r="C969" s="22"/>
       <c r="F969" s="9"/>
       <c r="G969" s="9"/>
       <c r="H969" s="14"/>
-      <c r="I969" s="22"/>
+      <c r="I969" s="21"/>
     </row>
     <row r="970">
-      <c r="C970" s="23"/>
+      <c r="C970" s="22"/>
       <c r="F970" s="9"/>
       <c r="G970" s="9"/>
       <c r="H970" s="14"/>
-      <c r="I970" s="22"/>
+      <c r="I970" s="21"/>
     </row>
     <row r="971">
-      <c r="C971" s="23"/>
+      <c r="C971" s="22"/>
       <c r="F971" s="9"/>
       <c r="G971" s="9"/>
       <c r="H971" s="14"/>
-      <c r="I971" s="22"/>
+      <c r="I971" s="21"/>
     </row>
     <row r="972">
-      <c r="C972" s="23"/>
+      <c r="C972" s="22"/>
       <c r="F972" s="9"/>
       <c r="G972" s="9"/>
       <c r="H972" s="14"/>
-      <c r="I972" s="22"/>
+      <c r="I972" s="21"/>
     </row>
     <row r="973">
-      <c r="C973" s="23"/>
+      <c r="C973" s="22"/>
       <c r="F973" s="9"/>
       <c r="G973" s="9"/>
       <c r="H973" s="14"/>
-      <c r="I973" s="22"/>
+      <c r="I973" s="21"/>
     </row>
     <row r="974">
-      <c r="C974" s="23"/>
+      <c r="C974" s="22"/>
       <c r="F974" s="9"/>
       <c r="G974" s="9"/>
       <c r="H974" s="14"/>
-      <c r="I974" s="22"/>
+      <c r="I974" s="21"/>
     </row>
     <row r="975">
-      <c r="C975" s="23"/>
+      <c r="C975" s="22"/>
       <c r="F975" s="9"/>
       <c r="G975" s="9"/>
       <c r="H975" s="14"/>
-      <c r="I975" s="22"/>
+      <c r="I975" s="21"/>
     </row>
     <row r="976">
-      <c r="C976" s="23"/>
+      <c r="C976" s="22"/>
       <c r="F976" s="9"/>
       <c r="G976" s="9"/>
       <c r="H976" s="14"/>
-      <c r="I976" s="22"/>
+      <c r="I976" s="21"/>
     </row>
     <row r="977">
-      <c r="C977" s="23"/>
+      <c r="C977" s="22"/>
       <c r="F977" s="9"/>
       <c r="G977" s="9"/>
       <c r="H977" s="14"/>
-      <c r="I977" s="22"/>
+      <c r="I977" s="21"/>
     </row>
     <row r="978">
-      <c r="C978" s="23"/>
+      <c r="C978" s="22"/>
       <c r="F978" s="9"/>
       <c r="G978" s="9"/>
       <c r="H978" s="14"/>
-      <c r="I978" s="22"/>
+      <c r="I978" s="21"/>
     </row>
     <row r="979">
-      <c r="C979" s="23"/>
+      <c r="C979" s="22"/>
       <c r="F979" s="9"/>
       <c r="G979" s="9"/>
       <c r="H979" s="14"/>
-      <c r="I979" s="22"/>
+      <c r="I979" s="21"/>
     </row>
     <row r="980">
-      <c r="C980" s="23"/>
+      <c r="C980" s="22"/>
       <c r="F980" s="9"/>
       <c r="G980" s="9"/>
       <c r="H980" s="14"/>
-      <c r="I980" s="22"/>
+      <c r="I980" s="21"/>
     </row>
     <row r="981">
-      <c r="C981" s="23"/>
+      <c r="C981" s="22"/>
       <c r="F981" s="9"/>
       <c r="G981" s="9"/>
       <c r="H981" s="14"/>
-      <c r="I981" s="22"/>
+      <c r="I981" s="21"/>
     </row>
     <row r="982">
-      <c r="C982" s="23"/>
+      <c r="C982" s="22"/>
       <c r="F982" s="9"/>
       <c r="G982" s="9"/>
       <c r="H982" s="14"/>
-      <c r="I982" s="22"/>
+      <c r="I982" s="21"/>
     </row>
     <row r="983">
-      <c r="C983" s="23"/>
+      <c r="C983" s="22"/>
       <c r="F983" s="9"/>
       <c r="G983" s="9"/>
       <c r="H983" s="14"/>
-      <c r="I983" s="22"/>
+      <c r="I983" s="21"/>
     </row>
     <row r="984">
-      <c r="C984" s="23"/>
+      <c r="C984" s="22"/>
       <c r="F984" s="9"/>
       <c r="G984" s="9"/>
       <c r="H984" s="14"/>
-      <c r="I984" s="22"/>
+      <c r="I984" s="21"/>
     </row>
     <row r="985">
-      <c r="C985" s="23"/>
+      <c r="C985" s="22"/>
       <c r="F985" s="9"/>
       <c r="G985" s="9"/>
       <c r="H985" s="14"/>
-      <c r="I985" s="22"/>
+      <c r="I985" s="21"/>
     </row>
     <row r="986">
-      <c r="C986" s="23"/>
+      <c r="C986" s="22"/>
       <c r="F986" s="9"/>
       <c r="G986" s="9"/>
       <c r="H986" s="14"/>
-      <c r="I986" s="22"/>
+      <c r="I986" s="21"/>
     </row>
     <row r="987">
-      <c r="C987" s="23"/>
+      <c r="C987" s="22"/>
       <c r="F987" s="9"/>
       <c r="G987" s="9"/>
       <c r="H987" s="14"/>
-      <c r="I987" s="22"/>
+      <c r="I987" s="21"/>
     </row>
     <row r="988">
-      <c r="C988" s="23"/>
+      <c r="C988" s="22"/>
       <c r="F988" s="9"/>
       <c r="G988" s="9"/>
       <c r="H988" s="14"/>
-      <c r="I988" s="22"/>
+      <c r="I988" s="21"/>
     </row>
     <row r="989">
-      <c r="C989" s="23"/>
+      <c r="C989" s="22"/>
       <c r="F989" s="9"/>
       <c r="G989" s="9"/>
       <c r="H989" s="14"/>
-      <c r="I989" s="22"/>
+      <c r="I989" s="21"/>
     </row>
     <row r="990">
-      <c r="C990" s="23"/>
+      <c r="C990" s="22"/>
       <c r="F990" s="9"/>
       <c r="G990" s="9"/>
       <c r="H990" s="14"/>
-      <c r="I990" s="22"/>
+      <c r="I990" s="21"/>
     </row>
     <row r="991">
-      <c r="C991" s="23"/>
+      <c r="C991" s="22"/>
       <c r="F991" s="9"/>
       <c r="G991" s="9"/>
       <c r="H991" s="14"/>
-      <c r="I991" s="22"/>
+      <c r="I991" s="21"/>
     </row>
     <row r="992">
-      <c r="C992" s="23"/>
+      <c r="C992" s="22"/>
       <c r="F992" s="9"/>
       <c r="G992" s="9"/>
       <c r="H992" s="14"/>
-      <c r="I992" s="22"/>
+      <c r="I992" s="21"/>
     </row>
     <row r="993">
-      <c r="C993" s="23"/>
+      <c r="C993" s="22"/>
       <c r="F993" s="9"/>
       <c r="G993" s="9"/>
       <c r="H993" s="14"/>
-      <c r="I993" s="22"/>
+      <c r="I993" s="21"/>
     </row>
     <row r="994">
-      <c r="C994" s="23"/>
+      <c r="C994" s="22"/>
       <c r="F994" s="9"/>
       <c r="G994" s="9"/>
       <c r="H994" s="14"/>
-      <c r="I994" s="22"/>
+      <c r="I994" s="21"/>
     </row>
     <row r="995">
-      <c r="C995" s="23"/>
+      <c r="C995" s="22"/>
       <c r="F995" s="9"/>
       <c r="G995" s="9"/>
       <c r="H995" s="14"/>
-      <c r="I995" s="22"/>
+      <c r="I995" s="21"/>
     </row>
     <row r="996">
-      <c r="C996" s="23"/>
+      <c r="C996" s="22"/>
       <c r="F996" s="9"/>
       <c r="G996" s="9"/>
       <c r="H996" s="14"/>
-      <c r="I996" s="22"/>
+      <c r="I996" s="21"/>
     </row>
     <row r="997">
-      <c r="C997" s="23"/>
+      <c r="C997" s="22"/>
       <c r="F997" s="9"/>
       <c r="G997" s="9"/>
       <c r="H997" s="14"/>
-      <c r="I997" s="22"/>
+      <c r="I997" s="21"/>
     </row>
     <row r="998">
-      <c r="C998" s="23"/>
+      <c r="C998" s="22"/>
       <c r="F998" s="9"/>
       <c r="G998" s="9"/>
       <c r="H998" s="14"/>
-      <c r="I998" s="22"/>
+      <c r="I998" s="21"/>
     </row>
     <row r="999">
-      <c r="C999" s="23"/>
+      <c r="C999" s="22"/>
       <c r="F999" s="9"/>
       <c r="G999" s="9"/>
       <c r="H999" s="14"/>
-      <c r="I999" s="22"/>
+      <c r="I999" s="21"/>
     </row>
     <row r="1000">
-      <c r="C1000" s="23"/>
+      <c r="C1000" s="22"/>
       <c r="F1000" s="9"/>
       <c r="G1000" s="9"/>
       <c r="H1000" s="14"/>
-      <c r="I1000" s="22"/>
+      <c r="I1000" s="21"/>
     </row>
     <row r="1001">
-      <c r="C1001" s="23"/>
+      <c r="C1001" s="22"/>
       <c r="F1001" s="9"/>
       <c r="G1001" s="9"/>
       <c r="H1001" s="14"/>
-      <c r="I1001" s="22"/>
+      <c r="I1001" s="21"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A73 C2:I73 B73">

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -14,10 +14,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="178">
   <si>
-    <t>Rank</t>
+    <t>PICK</t>
   </si>
   <si>
-    <t>PICK</t>
+    <t>Rank</t>
   </si>
   <si>
     <t>PLAYER NAME</t>
@@ -29,10 +29,10 @@
     <t>Final Price</t>
   </si>
   <si>
-    <t>Mine?</t>
+    <t>VALUE</t>
   </si>
   <si>
-    <t>VALUE</t>
+    <t>Mine?</t>
   </si>
   <si>
     <t>Inflated Fair Price</t>
@@ -50,10 +50,10 @@
     <t>New Values</t>
   </si>
   <si>
-    <t>Value vs Fair</t>
+    <t>Spine</t>
   </si>
   <si>
-    <t>Spine</t>
+    <t>Value vs Fair</t>
   </si>
   <si>
     <t>Settings</t>
@@ -101,10 +101,10 @@
     <t>Makai Lemon</t>
   </si>
   <si>
-    <t>Remaining Leage $</t>
+    <t>Round 1</t>
   </si>
   <si>
-    <t>Round 1</t>
+    <t>Remaining Leage $</t>
   </si>
   <si>
     <t>Kenyon Sadiq</t>
@@ -131,6 +131,9 @@
     <t>Avg $ per Other Team</t>
   </si>
   <si>
+    <t>Round 2</t>
+  </si>
+  <si>
     <t>Eli Stowers</t>
   </si>
   <si>
@@ -140,13 +143,13 @@
     <t>Omar Cooper</t>
   </si>
   <si>
-    <t>Round 2</t>
-  </si>
-  <si>
     <t>CJ Allen</t>
   </si>
   <si>
     <t>Undrafted Predraft$</t>
+  </si>
+  <si>
+    <t>Round 3</t>
   </si>
   <si>
     <t>Arvell Reese</t>
@@ -158,16 +161,16 @@
     <t>Ty Simpson</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>Denzel Boston</t>
   </si>
   <si>
-    <t>Denzel Boston</t>
+    <t>Round 4</t>
   </si>
   <si>
     <t>Aggression</t>
   </si>
   <si>
-    <t>Round 4</t>
+    <t>Round 5</t>
   </si>
   <si>
     <t>Caleb Downs</t>
@@ -182,10 +185,10 @@
     <t>Jacob Rodriguez</t>
   </si>
   <si>
-    <t>Jonah Coleman</t>
+    <t>Round 6</t>
   </si>
   <si>
-    <t>Round 5</t>
+    <t>Jonah Coleman</t>
   </si>
   <si>
     <t>Jake Golday</t>
@@ -201,9 +204,6 @@
   </si>
   <si>
     <t>Germie Bernard</t>
-  </si>
-  <si>
-    <t>Round 6</t>
   </si>
   <si>
     <t>Nicholas Singleton</t>
@@ -914,10 +914,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>8</v>
@@ -926,7 +926,7 @@
         <v>11</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F1" s="6">
         <v>2025.0</v>
@@ -1071,7 +1071,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="10" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="10" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -9212,7 +9212,7 @@
       <c r="U139" s="12"/>
       <c r="V139" s="12"/>
       <c r="W139" s="7" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X139" s="7" t="s">
         <v>138</v>
@@ -9575,7 +9575,7 @@
         <v>10.0</v>
       </c>
       <c r="X148" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y148" s="7" t="s">
         <v>145</v>
@@ -9615,7 +9615,7 @@
         <v>11.0</v>
       </c>
       <c r="X149" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Y149" s="7" t="s">
         <v>143</v>
@@ -9655,7 +9655,7 @@
         <v>12.0</v>
       </c>
       <c r="X150" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Y150" s="7" t="s">
         <v>146</v>
@@ -9815,7 +9815,7 @@
         <v>16.0</v>
       </c>
       <c r="X154" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Y154" s="7" t="s">
         <v>143</v>
@@ -9855,7 +9855,7 @@
         <v>17.0</v>
       </c>
       <c r="X155" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Y155" s="7" t="s">
         <v>140</v>
@@ -9895,7 +9895,7 @@
         <v>18.0</v>
       </c>
       <c r="X156" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Y156" s="7" t="s">
         <v>145</v>
@@ -10055,7 +10055,7 @@
         <v>22.0</v>
       </c>
       <c r="X160" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y160" s="7" t="s">
         <v>144</v>
@@ -10095,7 +10095,7 @@
         <v>23.0</v>
       </c>
       <c r="X161" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Y161" s="7" t="s">
         <v>142</v>
@@ -10335,7 +10335,7 @@
         <v>29.0</v>
       </c>
       <c r="X167" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Y167" s="7" t="s">
         <v>143</v>
@@ -10375,7 +10375,7 @@
         <v>30.0</v>
       </c>
       <c r="X168" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Y168" s="7" t="s">
         <v>141</v>
@@ -10695,7 +10695,7 @@
         <v>38.0</v>
       </c>
       <c r="X176" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Y176" s="7" t="s">
         <v>141</v>
@@ -37444,7 +37444,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -37456,7 +37456,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>7</v>
@@ -37468,7 +37468,7 @@
         <v>10</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>14</v>
@@ -37677,7 +37677,7 @@
         <v/>
       </c>
       <c r="K6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L6" s="17">
         <f>L2-L5
@@ -37840,7 +37840,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" s="9">
         <v>43.0</v>
@@ -37865,7 +37865,7 @@
         <v/>
       </c>
       <c r="K11" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L11" s="19">
         <f>IF(L10&gt;0,L8/L10,1)</f>
@@ -37877,7 +37877,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12" s="9">
         <v>39.0</v>
@@ -37944,7 +37944,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C14" s="9">
         <v>30.5</v>
@@ -37969,7 +37969,7 @@
         <v/>
       </c>
       <c r="K14" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L14" s="19">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -37981,7 +37981,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C15" s="9">
         <v>27.5</v>
@@ -38036,7 +38036,7 @@
         <v/>
       </c>
       <c r="K16" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L16" s="1">
         <f>IF($L$18&lt;0.3,
@@ -38058,7 +38058,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C17" s="9">
         <v>22.5</v>
@@ -38088,7 +38088,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C18" s="9">
         <v>20.0</v>
@@ -38113,7 +38113,7 @@
         <v/>
       </c>
       <c r="K18" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L18" s="20">
         <f>L5/L2</f>
@@ -38125,7 +38125,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C19" s="9">
         <v>18.5</v>
@@ -38155,7 +38155,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C20" s="9">
         <v>16.5</v>
@@ -38185,7 +38185,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21" s="9">
         <v>14.5</v>
@@ -38215,7 +38215,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C22" s="9">
         <v>13.5</v>
@@ -38245,7 +38245,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23" s="9">
         <v>12.0</v>
@@ -38275,7 +38275,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C24" s="9">
         <v>11.0</v>
@@ -38305,7 +38305,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C25" s="9">
         <v>10.0</v>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -29,10 +29,10 @@
     <t>Spine</t>
   </si>
   <si>
-    <t>Rank</t>
+    <t>Floors</t>
   </si>
   <si>
-    <t>Floors</t>
+    <t>Rank</t>
   </si>
   <si>
     <t>Fractions</t>
@@ -95,13 +95,13 @@
     <t>Jordyn Tyson</t>
   </si>
   <si>
-    <t>Round 1</t>
-  </si>
-  <si>
     <t>Total Spent $</t>
   </si>
   <si>
     <t>Makai Lemon</t>
+  </si>
+  <si>
+    <t>Round 1</t>
   </si>
   <si>
     <t>Remaining Leage $</t>
@@ -194,13 +194,13 @@
     <t>Dillon Thieneman</t>
   </si>
   <si>
-    <t>Round 6</t>
-  </si>
-  <si>
     <t>Rueben Bain</t>
   </si>
   <si>
     <t>Chris Bell</t>
+  </si>
+  <si>
+    <t>Round 6</t>
   </si>
   <si>
     <t>Germie Bernard</t>
@@ -347,6 +347,12 @@
     <t>Nate Boerkircher</t>
   </si>
   <si>
+    <t>Will Kacmarek</t>
+  </si>
+  <si>
+    <t>Noah Whittington</t>
+  </si>
+  <si>
     <t>Standings</t>
   </si>
   <si>
@@ -372,12 +378,6 @@
   </si>
   <si>
     <t>Key</t>
-  </si>
-  <si>
-    <t>Will Kacmarek</t>
-  </si>
-  <si>
-    <t>Noah Whittington</t>
   </si>
   <si>
     <t>Ed</t>
@@ -651,16 +651,16 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -938,7 +938,7 @@
         <v>2026.0</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>7</v>
@@ -1006,7 +1006,7 @@
       <c r="B2" s="10">
         <v>7580.0</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="16">
         <f t="shared" ref="C2:C73" si="2">1 + --(INT((ROW()-ROW($B$2))/12)=4)
   + (1200-84) * (
       0.6 *
@@ -1026,7 +1026,7 @@
 </f>
         <v>133.317836</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="16">
         <f t="shared" ref="D2:D73" si="3">( K2
    + IF(
        ROW()-ROW($K$2) &lt; $M$1,
@@ -1038,90 +1038,90 @@
 </f>
         <v>134.5</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="16">
         <f t="shared" ref="E2:E73" si="4">(MEDIAN(F2:H2)+AVERAGE(F2:H2))/2
 </f>
         <v>126.4166667</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="16">
         <v>125.5</v>
       </c>
-      <c r="G2" s="15">
+      <c r="G2" s="16">
         <v>122.5</v>
       </c>
-      <c r="H2" s="15">
+      <c r="H2" s="16">
         <v>134.0</v>
       </c>
-      <c r="I2" s="15">
+      <c r="I2" s="16">
         <f t="shared" ref="I2:I73" si="5">ROUNDDOWN(C2*2,0)</f>
         <v>266</v>
       </c>
-      <c r="J2" s="15">
+      <c r="J2" s="16">
         <f t="shared" ref="J2:J73" si="6">C2*2 - I2</f>
         <v>0.6356720614</v>
       </c>
-      <c r="K2" s="15">
+      <c r="K2" s="16">
         <f>I2 + --(RANK(J2,$J$2:$J$73,0) &lt;= 1200*2 - SUM($I$2:$I$73))</f>
         <v>267</v>
       </c>
-      <c r="L2" s="17">
+      <c r="L2" s="18">
         <f t="shared" ref="L2:L74" si="7">D2</f>
         <v>134.5</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
       <c r="O2" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" s="15">
+        <v>29</v>
+      </c>
+      <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
         <v>134.5</v>
       </c>
-      <c r="Q2" s="15">
+      <c r="Q2" s="16">
         <f t="shared" si="1"/>
         <v>100.5</v>
       </c>
-      <c r="R2" s="15">
+      <c r="R2" s="16">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
-      <c r="S2" s="15">
+      <c r="S2" s="16">
         <f t="shared" si="1"/>
         <v>80.5</v>
       </c>
-      <c r="T2" s="15">
+      <c r="T2" s="16">
         <f t="shared" si="1"/>
         <v>75.5</v>
       </c>
-      <c r="U2" s="15">
+      <c r="U2" s="16">
         <f t="shared" si="1"/>
         <v>68.5</v>
       </c>
-      <c r="V2" s="15">
+      <c r="V2" s="16">
         <f t="shared" si="1"/>
         <v>54.5</v>
       </c>
-      <c r="W2" s="15">
+      <c r="W2" s="16">
         <f t="shared" si="1"/>
         <v>53.5</v>
       </c>
-      <c r="X2" s="15">
+      <c r="X2" s="16">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="Y2" s="15">
+      <c r="Y2" s="16">
         <f t="shared" si="1"/>
         <v>44.5</v>
       </c>
-      <c r="Z2" s="15">
+      <c r="Z2" s="16">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
-      <c r="AA2" s="15">
+      <c r="AA2" s="16">
         <f t="shared" si="1"/>
         <v>35.5</v>
       </c>
-      <c r="AB2" s="15">
+      <c r="AB2" s="16">
         <f t="shared" ref="AB2:AB7" si="9">SUM(P2:AA2)</f>
         <v>827.5</v>
       </c>
@@ -1135,36 +1135,36 @@
       <c r="B3" s="10">
         <v>5598.5</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="16">
         <f t="shared" si="2"/>
         <v>99.38361855</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="16">
         <f t="shared" si="3"/>
         <v>100.5</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="16">
         <f t="shared" si="4"/>
         <v>103.0833333</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="16">
         <v>95.0</v>
       </c>
-      <c r="G3" s="15">
+      <c r="G3" s="16">
         <v>113.5</v>
       </c>
-      <c r="H3" s="15">
+      <c r="H3" s="16">
         <v>102.5</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="16">
         <f t="shared" si="5"/>
         <v>198</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="16">
         <f t="shared" si="6"/>
         <v>0.7672370964</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="16">
         <f t="shared" ref="K3:K73" si="10">MIN(
   I3 + --(RANK(J3,$J$2:$J$73,0) &lt;= 1200*2 - SUM($I$2:$I$73)),
   IF(INT((ROW()-ROW($C$2))/12)=4, 4, IF(INT((ROW()-ROW($C$2))/12)=5, 2, 10^9)),
@@ -1173,7 +1173,7 @@
 </f>
         <v>199</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="18">
         <f t="shared" si="7"/>
         <v>100.5</v>
       </c>
@@ -1182,55 +1182,55 @@
       <c r="O3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
         <v>29.5</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="16">
         <f t="shared" si="8"/>
         <v>28.5</v>
       </c>
-      <c r="R3" s="15">
+      <c r="R3" s="16">
         <f t="shared" si="8"/>
         <v>26.5</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="16">
         <f t="shared" si="8"/>
         <v>24</v>
       </c>
-      <c r="T3" s="15">
+      <c r="T3" s="16">
         <f t="shared" si="8"/>
         <v>21.5</v>
       </c>
-      <c r="U3" s="15">
+      <c r="U3" s="16">
         <f t="shared" si="8"/>
         <v>19</v>
       </c>
-      <c r="V3" s="15">
+      <c r="V3" s="16">
         <f t="shared" si="8"/>
         <v>17.5</v>
       </c>
-      <c r="W3" s="15">
+      <c r="W3" s="16">
         <f t="shared" si="8"/>
         <v>16</v>
       </c>
-      <c r="X3" s="15">
+      <c r="X3" s="16">
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="Y3" s="15">
+      <c r="Y3" s="16">
         <f t="shared" si="8"/>
         <v>13.5</v>
       </c>
-      <c r="Z3" s="15">
+      <c r="Z3" s="16">
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
-      <c r="AA3" s="15">
+      <c r="AA3" s="16">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="AB3" s="15">
+      <c r="AB3" s="16">
         <f t="shared" si="9"/>
         <v>231</v>
       </c>
@@ -1244,40 +1244,40 @@
       <c r="B4" s="10">
         <v>5649.0</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="16">
         <f t="shared" si="2"/>
         <v>91.80264821</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="16">
         <f t="shared" si="3"/>
         <v>93</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="16">
         <f t="shared" si="4"/>
         <v>90.66666667</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="16">
         <v>85.5</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="16">
         <v>91.5</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="16">
         <v>92.5</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="16">
         <f t="shared" si="5"/>
         <v>183</v>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="16">
         <f t="shared" si="6"/>
         <v>0.6052964259</v>
       </c>
-      <c r="K4" s="15">
+      <c r="K4" s="16">
         <f t="shared" si="10"/>
         <v>184</v>
       </c>
-      <c r="L4" s="17">
+      <c r="L4" s="18">
         <f t="shared" si="7"/>
         <v>93</v>
       </c>
@@ -1286,55 +1286,55 @@
       <c r="O4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="P4" s="15">
+      <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
         <v>9.5</v>
       </c>
-      <c r="Q4" s="15">
+      <c r="Q4" s="16">
         <f t="shared" si="11"/>
         <v>9</v>
       </c>
-      <c r="R4" s="15">
+      <c r="R4" s="16">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="S4" s="15">
+      <c r="S4" s="16">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="T4" s="15">
+      <c r="T4" s="16">
         <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
-      <c r="U4" s="15">
+      <c r="U4" s="16">
         <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
-      <c r="V4" s="15">
+      <c r="V4" s="16">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="W4" s="15">
+      <c r="W4" s="16">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="X4" s="15">
+      <c r="X4" s="16">
         <f t="shared" si="11"/>
         <v>4.5</v>
       </c>
-      <c r="Y4" s="15">
+      <c r="Y4" s="16">
         <f t="shared" si="11"/>
         <v>4.5</v>
       </c>
-      <c r="Z4" s="15">
+      <c r="Z4" s="16">
         <f t="shared" si="11"/>
         <v>4.5</v>
       </c>
-      <c r="AA4" s="15">
+      <c r="AA4" s="16">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="AB4" s="15">
+      <c r="AB4" s="16">
         <f t="shared" si="9"/>
         <v>74</v>
       </c>
@@ -1348,40 +1348,40 @@
       <c r="B5" s="10">
         <v>5074.5</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="16">
         <f t="shared" si="2"/>
         <v>79.37165519</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="16">
         <f t="shared" si="3"/>
         <v>80.5</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="16">
         <f t="shared" si="4"/>
         <v>80.66666667</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="16">
         <v>77.5</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="16">
         <v>84.5</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="16">
         <v>80.5</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="16">
         <f t="shared" si="5"/>
         <v>158</v>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="16">
         <f t="shared" si="6"/>
         <v>0.7433103774</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="16">
         <f t="shared" si="10"/>
         <v>159</v>
       </c>
-      <c r="L5" s="17">
+      <c r="L5" s="18">
         <f t="shared" si="7"/>
         <v>80.5</v>
       </c>
@@ -1390,55 +1390,55 @@
       <c r="O5" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="P5" s="15">
+      <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
         <v>3.5</v>
       </c>
-      <c r="Q5" s="15">
+      <c r="Q5" s="16">
         <f t="shared" si="12"/>
         <v>3.5</v>
       </c>
-      <c r="R5" s="15">
+      <c r="R5" s="16">
         <f t="shared" si="12"/>
         <v>3</v>
       </c>
-      <c r="S5" s="15">
+      <c r="S5" s="16">
         <f t="shared" si="12"/>
         <v>3</v>
       </c>
-      <c r="T5" s="15">
+      <c r="T5" s="16">
         <f t="shared" si="12"/>
         <v>3</v>
       </c>
-      <c r="U5" s="15">
+      <c r="U5" s="16">
         <f t="shared" si="12"/>
         <v>2.5</v>
       </c>
-      <c r="V5" s="15">
+      <c r="V5" s="16">
         <f t="shared" si="12"/>
         <v>2.5</v>
       </c>
-      <c r="W5" s="15">
+      <c r="W5" s="16">
         <f t="shared" si="12"/>
         <v>2.5</v>
       </c>
-      <c r="X5" s="15">
+      <c r="X5" s="16">
         <f t="shared" si="12"/>
         <v>2</v>
       </c>
-      <c r="Y5" s="15">
+      <c r="Y5" s="16">
         <f t="shared" si="12"/>
         <v>2</v>
       </c>
-      <c r="Z5" s="15">
+      <c r="Z5" s="16">
         <f t="shared" si="12"/>
         <v>2</v>
       </c>
-      <c r="AA5" s="15">
+      <c r="AA5" s="16">
         <f t="shared" si="12"/>
         <v>2</v>
       </c>
-      <c r="AB5" s="15">
+      <c r="AB5" s="16">
         <f t="shared" si="9"/>
         <v>31.5</v>
       </c>
@@ -1452,40 +1452,40 @@
       <c r="B6" s="10">
         <v>5076.0</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="16">
         <f t="shared" si="2"/>
         <v>74.3655612</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="16">
         <f t="shared" si="3"/>
         <v>75.5</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="16">
         <f t="shared" si="4"/>
         <v>75.08333333</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="16">
         <v>73.0</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="16">
         <v>79.5</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="16">
         <v>74.5</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="16">
         <f t="shared" si="5"/>
         <v>148</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="16">
         <f t="shared" si="6"/>
         <v>0.7311223994</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="16">
         <f t="shared" si="10"/>
         <v>149</v>
       </c>
-      <c r="L6" s="17">
+      <c r="L6" s="18">
         <f t="shared" si="7"/>
         <v>75.5</v>
       </c>
@@ -1494,55 +1494,55 @@
       <c r="O6" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="P6" s="15">
+      <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
         <v>2</v>
       </c>
-      <c r="Q6" s="15">
+      <c r="Q6" s="16">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="R6" s="15">
+      <c r="R6" s="16">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="S6" s="15">
+      <c r="S6" s="16">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="T6" s="15">
+      <c r="T6" s="16">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="U6" s="15">
+      <c r="U6" s="16">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="V6" s="15">
+      <c r="V6" s="16">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="W6" s="15">
+      <c r="W6" s="16">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="X6" s="15">
+      <c r="X6" s="16">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="Y6" s="15">
+      <c r="Y6" s="16">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="Z6" s="15">
+      <c r="Z6" s="16">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="AA6" s="15">
+      <c r="AA6" s="16">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="AB6" s="15">
+      <c r="AB6" s="16">
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
@@ -1556,97 +1556,97 @@
       <c r="B7" s="10">
         <v>4965.0</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="16">
         <f t="shared" si="2"/>
         <v>67.755402</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="16">
         <f t="shared" si="3"/>
         <v>68.5</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="16">
         <f t="shared" si="4"/>
         <v>67.58333333</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="16">
         <v>67.5</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="16">
         <v>67.5</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="16">
         <v>68.0</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="16">
         <f t="shared" si="5"/>
         <v>135</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="16">
         <f t="shared" si="6"/>
         <v>0.5108040066</v>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="16">
         <f t="shared" si="10"/>
         <v>136</v>
       </c>
-      <c r="L7" s="17">
+      <c r="L7" s="18">
         <f t="shared" si="7"/>
         <v>68.5</v>
       </c>
       <c r="M7" s="9"/>
       <c r="N7" s="9"/>
       <c r="O7" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="P7" s="15">
+        <v>62</v>
+      </c>
+      <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
         <v>1</v>
       </c>
-      <c r="Q7" s="15">
+      <c r="Q7" s="16">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="R7" s="15">
+      <c r="R7" s="16">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="S7" s="15">
+      <c r="S7" s="16">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="T7" s="15">
+      <c r="T7" s="16">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="U7" s="15">
+      <c r="U7" s="16">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="V7" s="15">
+      <c r="V7" s="16">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="W7" s="15">
+      <c r="W7" s="16">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="X7" s="15">
+      <c r="X7" s="16">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="Y7" s="15">
+      <c r="Y7" s="16">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="Z7" s="15">
+      <c r="Z7" s="16">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="AA7" s="15">
+      <c r="AA7" s="16">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="AB7" s="15">
+      <c r="AB7" s="16">
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
@@ -1660,95 +1660,95 @@
       <c r="B8" s="10">
         <v>4014.5</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="16">
         <f t="shared" si="2"/>
         <v>54.14386456</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="16">
         <f t="shared" si="3"/>
         <v>54.5</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="16">
         <f t="shared" si="4"/>
         <v>58</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="16">
         <v>62.0</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="16">
         <v>57.5</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="16">
         <v>56.0</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="16">
         <f t="shared" si="5"/>
         <v>108</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="16">
         <f t="shared" si="6"/>
         <v>0.2877291223</v>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="16">
         <f t="shared" si="10"/>
         <v>108</v>
       </c>
-      <c r="L8" s="17">
+      <c r="L8" s="18">
         <f t="shared" si="7"/>
         <v>54.5</v>
       </c>
       <c r="M8" s="9"/>
       <c r="N8" s="9"/>
       <c r="O8" s="9"/>
-      <c r="P8" s="15">
+      <c r="P8" s="16">
         <f t="shared" ref="P8:AB8" si="15">SUM(P2:P7)</f>
         <v>180</v>
       </c>
-      <c r="Q8" s="15">
+      <c r="Q8" s="16">
         <f t="shared" si="15"/>
         <v>144.5</v>
       </c>
-      <c r="R8" s="15">
+      <c r="R8" s="16">
         <f t="shared" si="15"/>
         <v>132.5</v>
       </c>
-      <c r="S8" s="15">
+      <c r="S8" s="16">
         <f t="shared" si="15"/>
         <v>117.5</v>
       </c>
-      <c r="T8" s="15">
+      <c r="T8" s="16">
         <f t="shared" si="15"/>
         <v>109.5</v>
       </c>
-      <c r="U8" s="15">
+      <c r="U8" s="16">
         <f t="shared" si="15"/>
         <v>99.5</v>
       </c>
-      <c r="V8" s="15">
+      <c r="V8" s="16">
         <f t="shared" si="15"/>
         <v>83</v>
       </c>
-      <c r="W8" s="15">
+      <c r="W8" s="16">
         <f t="shared" si="15"/>
         <v>80.5</v>
       </c>
-      <c r="X8" s="15">
+      <c r="X8" s="16">
         <f t="shared" si="15"/>
         <v>69.5</v>
       </c>
-      <c r="Y8" s="15">
+      <c r="Y8" s="16">
         <f t="shared" si="15"/>
         <v>67.5</v>
       </c>
-      <c r="Z8" s="15">
+      <c r="Z8" s="16">
         <f t="shared" si="15"/>
         <v>61.5</v>
       </c>
-      <c r="AA8" s="15">
+      <c r="AA8" s="16">
         <f t="shared" si="15"/>
         <v>54.5</v>
       </c>
-      <c r="AB8" s="15">
+      <c r="AB8" s="16">
         <f t="shared" si="15"/>
         <v>1200</v>
       </c>
@@ -1762,40 +1762,40 @@
       <c r="B9" s="10">
         <v>4308.0</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="16">
         <f t="shared" si="2"/>
         <v>52.77059949</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="16">
         <f t="shared" si="3"/>
         <v>53.5</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="16">
         <f t="shared" si="4"/>
         <v>54.33333333</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="16">
         <v>57.0</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="16">
         <v>53.0</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="16">
         <v>54.0</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="16">
         <f t="shared" si="5"/>
         <v>105</v>
       </c>
-      <c r="J9" s="15">
+      <c r="J9" s="16">
         <f t="shared" si="6"/>
         <v>0.5411989831</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="16">
         <f t="shared" si="10"/>
         <v>106</v>
       </c>
-      <c r="L9" s="17">
+      <c r="L9" s="18">
         <f t="shared" si="7"/>
         <v>53.5</v>
       </c>
@@ -1825,48 +1825,48 @@
       <c r="B10" s="10">
         <v>3869.0</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="16">
         <f t="shared" si="2"/>
         <v>45.5279227</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="16">
         <f t="shared" si="3"/>
         <v>46</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="16">
         <f t="shared" si="4"/>
         <v>48.58333333</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="16">
         <v>52.5</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="16">
         <v>48.0</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="16">
         <v>47.0</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I10" s="16">
         <f t="shared" si="5"/>
         <v>91</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="16">
         <f t="shared" si="6"/>
         <v>0.05584540002</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="16">
         <f t="shared" si="10"/>
         <v>91</v>
       </c>
-      <c r="L10" s="17">
+      <c r="L10" s="18">
         <f t="shared" si="7"/>
         <v>46</v>
       </c>
       <c r="M10" s="9"/>
       <c r="N10" s="9"/>
       <c r="O10" s="9"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
       <c r="R10" s="9"/>
       <c r="S10" s="9"/>
       <c r="T10" s="9"/>
@@ -1888,48 +1888,48 @@
       <c r="B11" s="10">
         <v>4169.0</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="16">
         <f t="shared" si="2"/>
         <v>43.91121089</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="16">
         <f t="shared" si="3"/>
         <v>44.5</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="16">
         <f t="shared" si="4"/>
         <v>44.25</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="16">
         <v>45.0</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="16">
         <v>42.5</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="16">
         <v>44.5</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="16">
         <f t="shared" si="5"/>
         <v>87</v>
       </c>
-      <c r="J11" s="15">
+      <c r="J11" s="16">
         <f t="shared" si="6"/>
         <v>0.8224217757</v>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="16">
         <f t="shared" si="10"/>
         <v>88</v>
       </c>
-      <c r="L11" s="17">
+      <c r="L11" s="18">
         <f t="shared" si="7"/>
         <v>44.5</v>
       </c>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
       <c r="O11" s="9"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
       <c r="R11" s="9"/>
       <c r="S11" s="9"/>
       <c r="T11" s="3"/>
@@ -1951,48 +1951,48 @@
       <c r="B12" s="10">
         <v>4164.0</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="16">
         <f t="shared" si="2"/>
         <v>40.67669146</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="16">
         <f t="shared" si="3"/>
         <v>41</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="16">
         <f t="shared" si="4"/>
         <v>40.66666667</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="16">
         <v>41.0</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="16">
         <v>39.0</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="16">
         <v>41.0</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I12" s="16">
         <f t="shared" si="5"/>
         <v>81</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J12" s="16">
         <f t="shared" si="6"/>
         <v>0.3533829233</v>
       </c>
-      <c r="K12" s="15">
+      <c r="K12" s="16">
         <f t="shared" si="10"/>
         <v>81</v>
       </c>
-      <c r="L12" s="17">
+      <c r="L12" s="18">
         <f t="shared" si="7"/>
         <v>41</v>
       </c>
       <c r="M12" s="9"/>
       <c r="N12" s="9"/>
       <c r="O12" s="9"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
       <c r="R12" s="9"/>
       <c r="S12" s="9"/>
       <c r="T12" s="3"/>
@@ -2014,48 +2014,48 @@
       <c r="B13" s="10">
         <v>3809.5</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="16">
         <f t="shared" si="2"/>
         <v>35.11775951</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="16">
         <f t="shared" si="3"/>
         <v>35.5</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="16">
         <f t="shared" si="4"/>
         <v>35.66666667</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="16">
         <v>37.5</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="16">
         <v>34.5</v>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="16">
         <v>35.5</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I13" s="16">
         <f t="shared" si="5"/>
         <v>70</v>
       </c>
-      <c r="J13" s="15">
+      <c r="J13" s="16">
         <f t="shared" si="6"/>
         <v>0.2355190156</v>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="16">
         <f t="shared" si="10"/>
         <v>70</v>
       </c>
-      <c r="L13" s="17">
+      <c r="L13" s="18">
         <f t="shared" si="7"/>
         <v>35.5</v>
       </c>
       <c r="M13" s="9"/>
       <c r="N13" s="9"/>
       <c r="O13" s="9"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
       <c r="R13" s="9"/>
       <c r="S13" s="9"/>
       <c r="T13" s="3"/>
@@ -2077,48 +2077,48 @@
       <c r="B14" s="10">
         <v>3397.5</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="16">
         <f t="shared" si="2"/>
         <v>29.5432517</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="16">
         <f t="shared" si="3"/>
         <v>29.5</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="16">
         <f t="shared" si="4"/>
         <v>30.41666667</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="16">
         <v>33.0</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="16">
         <v>30.0</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="16">
         <v>29.5</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I14" s="16">
         <f t="shared" si="5"/>
         <v>59</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="16">
         <f t="shared" si="6"/>
         <v>0.08650340414</v>
       </c>
-      <c r="K14" s="15">
+      <c r="K14" s="16">
         <f t="shared" si="10"/>
         <v>59</v>
       </c>
-      <c r="L14" s="17">
+      <c r="L14" s="18">
         <f t="shared" si="7"/>
         <v>29.5</v>
       </c>
       <c r="M14" s="9"/>
       <c r="N14" s="9"/>
       <c r="O14" s="9"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
       <c r="R14" s="9"/>
       <c r="S14" s="9"/>
       <c r="T14" s="3"/>
@@ -2140,48 +2140,48 @@
       <c r="B15" s="10">
         <v>3611.0</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="16">
         <f t="shared" si="2"/>
         <v>28.42496232</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="16">
         <f t="shared" si="3"/>
         <v>28.5</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="16">
         <f t="shared" si="4"/>
         <v>28.16666667</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="16">
         <v>30.0</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="16">
         <v>27.0</v>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="16">
         <v>28.0</v>
       </c>
-      <c r="I15" s="15"